--- a/气象/For_Python_站点信息和记录.xlsx
+++ b/气象/For_Python_站点信息和记录.xlsx
@@ -787,8 +787,8 @@
     <col width="18.59765625" customWidth="1" style="8" min="25" max="25"/>
     <col width="12.59765625" customWidth="1" style="5" min="26" max="30"/>
     <col width="12.59765625" customWidth="1" style="8" min="31" max="32"/>
-    <col width="12.59765625" customWidth="1" style="5" min="33" max="268"/>
-    <col width="12.59765625" customWidth="1" style="5" min="269" max="16384"/>
+    <col width="12.59765625" customWidth="1" style="5" min="33" max="270"/>
+    <col width="12.59765625" customWidth="1" style="5" min="271" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="27.75" customFormat="1" customHeight="1" s="11">
@@ -1011,13 +1011,13 @@
         </is>
       </c>
       <c r="O2" s="32" t="n">
-        <v>-37.7</v>
+        <v>-39</v>
       </c>
       <c r="P2" s="32" t="n">
-        <v>-18.9</v>
+        <v>-22.9</v>
       </c>
       <c r="Q2" s="32" t="n">
-        <v>-27.96</v>
+        <v>-31.98</v>
       </c>
       <c r="R2" s="23" t="inlineStr">
         <is>
@@ -1117,10 +1117,10 @@
         </is>
       </c>
       <c r="O3" s="32" t="n">
-        <v>-33.8</v>
+        <v>-39.9</v>
       </c>
       <c r="P3" s="32" t="n">
-        <v>-19.9</v>
+        <v>-20.2</v>
       </c>
       <c r="Q3" s="32" t="n"/>
       <c r="R3" s="23" t="n"/>
@@ -1221,10 +1221,10 @@
         </is>
       </c>
       <c r="O4" s="32" t="n">
-        <v>-30.9</v>
+        <v>-39.2</v>
       </c>
       <c r="P4" s="32" t="n">
-        <v>-17.2</v>
+        <v>-22.1</v>
       </c>
       <c r="Q4" s="32" t="n"/>
       <c r="R4" s="23" t="n"/>
@@ -1317,10 +1317,10 @@
       </c>
       <c r="N5" s="2" t="n"/>
       <c r="O5" s="32" t="n">
-        <v>-24.4</v>
+        <v>-34.7</v>
       </c>
       <c r="P5" s="32" t="n">
-        <v>-13.5</v>
+        <v>-20</v>
       </c>
       <c r="Q5" s="32" t="n"/>
       <c r="R5" s="23" t="n"/>
@@ -1417,10 +1417,10 @@
         </is>
       </c>
       <c r="O6" s="32" t="n">
-        <v>-28.9</v>
+        <v>-35.5</v>
       </c>
       <c r="P6" s="32" t="n">
-        <v>-11.9</v>
+        <v>-19.3</v>
       </c>
       <c r="Q6" s="32" t="n"/>
       <c r="R6" s="23" t="n"/>
@@ -1517,10 +1517,10 @@
         </is>
       </c>
       <c r="O7" s="32" t="n">
-        <v>-22.6</v>
+        <v>-30.7</v>
       </c>
       <c r="P7" s="32" t="n">
-        <v>-16.9</v>
+        <v>-20.5</v>
       </c>
       <c r="Q7" s="32" t="n"/>
       <c r="R7" s="23" t="n"/>
@@ -1625,13 +1625,13 @@
       </c>
       <c r="N8" s="2" t="n"/>
       <c r="O8" s="32" t="n">
-        <v>-17.6</v>
+        <v>-27</v>
       </c>
       <c r="P8" s="32" t="n">
-        <v>-7.1</v>
+        <v>-11.2</v>
       </c>
       <c r="Q8" s="32" t="n">
-        <v>-12.79</v>
+        <v>-20.6</v>
       </c>
       <c r="R8" s="23" t="inlineStr">
         <is>
@@ -1737,13 +1737,13 @@
       </c>
       <c r="N9" s="2" t="n"/>
       <c r="O9" s="32" t="n">
-        <v>-29.5</v>
+        <v>-32.4</v>
       </c>
       <c r="P9" s="32" t="n">
-        <v>-13.9</v>
+        <v>-14.4</v>
       </c>
       <c r="Q9" s="32" t="n">
-        <v>-22.21</v>
+        <v>-24.81</v>
       </c>
       <c r="R9" s="23" t="inlineStr">
         <is>
@@ -1853,13 +1853,13 @@
       </c>
       <c r="N10" s="3" t="n"/>
       <c r="O10" s="32" t="n">
-        <v>-24.9</v>
+        <v>-41.3</v>
       </c>
       <c r="P10" s="32" t="n">
-        <v>-14</v>
+        <v>-20.7</v>
       </c>
       <c r="Q10" s="32" t="n">
-        <v>-21.19</v>
+        <v>-31.07</v>
       </c>
       <c r="R10" s="23" t="inlineStr">
         <is>
@@ -1969,13 +1969,13 @@
         </is>
       </c>
       <c r="O11" s="32" t="n">
-        <v>-29.3</v>
+        <v>-40.7</v>
       </c>
       <c r="P11" s="32" t="n">
-        <v>-18.4</v>
+        <v>-17.5</v>
       </c>
       <c r="Q11" s="32" t="n">
-        <v>-23.46</v>
+        <v>-28.37</v>
       </c>
       <c r="R11" s="23" t="inlineStr">
         <is>
@@ -2081,13 +2081,13 @@
       </c>
       <c r="N12" s="2" t="n"/>
       <c r="O12" s="32" t="n">
-        <v>-25.3</v>
+        <v>-37.3</v>
       </c>
       <c r="P12" s="32" t="n">
-        <v>-13.6</v>
+        <v>-18.6</v>
       </c>
       <c r="Q12" s="32" t="n">
-        <v>-20.5</v>
+        <v>-30.52</v>
       </c>
       <c r="R12" s="23" t="inlineStr">
         <is>
@@ -2197,13 +2197,13 @@
         </is>
       </c>
       <c r="O13" s="32" t="n">
-        <v>-25.9</v>
+        <v>-27.7</v>
       </c>
       <c r="P13" s="32" t="n">
-        <v>-15.1</v>
+        <v>-20.4</v>
       </c>
       <c r="Q13" s="32" t="n">
-        <v>-22.09</v>
+        <v>-24.36</v>
       </c>
       <c r="R13" s="23" t="inlineStr">
         <is>
@@ -2309,13 +2309,13 @@
       </c>
       <c r="N14" s="2" t="n"/>
       <c r="O14" s="32" t="n">
-        <v>-17</v>
+        <v>-21.6</v>
       </c>
       <c r="P14" s="32" t="n">
-        <v>-4.3</v>
+        <v>-16.2</v>
       </c>
       <c r="Q14" s="32" t="n">
-        <v>-12.46</v>
+        <v>-19.35</v>
       </c>
       <c r="R14" s="23" t="inlineStr">
         <is>
@@ -7813,13 +7813,13 @@
       </c>
       <c r="N75" s="2" t="n"/>
       <c r="O75" s="32" t="n">
-        <v>-19.1</v>
+        <v>-1.5</v>
       </c>
       <c r="P75" s="32" t="n">
-        <v>1.6</v>
+        <v>0.7</v>
       </c>
       <c r="Q75" s="32" t="n">
-        <v>-8.119999999999999</v>
+        <v>-0.35</v>
       </c>
       <c r="R75" s="23" t="inlineStr">
         <is>
@@ -7925,13 +7925,13 @@
       </c>
       <c r="N76" s="2" t="n"/>
       <c r="O76" s="32" t="n">
-        <v>-18.7</v>
+        <v>-12.4</v>
       </c>
       <c r="P76" s="32" t="n">
-        <v>-3.6</v>
+        <v>1.6</v>
       </c>
       <c r="Q76" s="32" t="n">
-        <v>-11.56</v>
+        <v>-4.25</v>
       </c>
       <c r="R76" s="23" t="inlineStr">
         <is>
@@ -8041,13 +8041,13 @@
         </is>
       </c>
       <c r="O77" s="32" t="n">
-        <v>-16.8</v>
+        <v>-13.6</v>
       </c>
       <c r="P77" s="32" t="n">
-        <v>-3</v>
+        <v>-6.1</v>
       </c>
       <c r="Q77" s="32" t="n">
-        <v>-10.04</v>
+        <v>-8.140000000000001</v>
       </c>
       <c r="R77" s="23" t="inlineStr">
         <is>
@@ -8153,13 +8153,13 @@
       </c>
       <c r="N78" s="2" t="n"/>
       <c r="O78" s="32" t="n">
-        <v>-9.9</v>
+        <v>-15.7</v>
       </c>
       <c r="P78" s="32" t="n">
-        <v>-2.2</v>
+        <v>-2.3</v>
       </c>
       <c r="Q78" s="32" t="n">
-        <v>-7.71</v>
+        <v>-8.6</v>
       </c>
       <c r="R78" s="23" t="inlineStr">
         <is>
@@ -8269,13 +8269,13 @@
         </is>
       </c>
       <c r="O79" s="32" t="n">
-        <v>-21.7</v>
+        <v>-21.4</v>
       </c>
       <c r="P79" s="32" t="n">
-        <v>-5.9</v>
+        <v>-10.3</v>
       </c>
       <c r="Q79" s="32" t="n">
-        <v>-13.61</v>
+        <v>-14.55</v>
       </c>
       <c r="R79" s="23" t="inlineStr">
         <is>
@@ -8381,13 +8381,13 @@
       </c>
       <c r="N80" s="2" t="n"/>
       <c r="O80" s="32" t="n">
+        <v>-19.1</v>
+      </c>
+      <c r="P80" s="32" t="n">
         <v>-14.8</v>
       </c>
-      <c r="P80" s="32" t="n">
-        <v>-5.2</v>
-      </c>
       <c r="Q80" s="32" t="n">
-        <v>-11.59</v>
+        <v>-18.15</v>
       </c>
       <c r="R80" s="23" t="inlineStr">
         <is>
@@ -8497,13 +8497,13 @@
         </is>
       </c>
       <c r="O81" s="32" t="n">
-        <v>-18.7</v>
+        <v>-23.7</v>
       </c>
       <c r="P81" s="32" t="n">
-        <v>-9.800000000000001</v>
+        <v>-16.7</v>
       </c>
       <c r="Q81" s="32" t="n">
-        <v>-14.19</v>
+        <v>-19.71</v>
       </c>
       <c r="R81" s="23" t="inlineStr">
         <is>
@@ -8618,13 +8618,13 @@
         </is>
       </c>
       <c r="O82" s="32" t="n">
-        <v>-30</v>
+        <v>-34.7</v>
       </c>
       <c r="P82" s="32" t="n">
-        <v>-7.9</v>
+        <v>-18</v>
       </c>
       <c r="Q82" s="32" t="n">
-        <v>-20.49</v>
+        <v>-25.65</v>
       </c>
       <c r="R82" s="23" t="inlineStr">
         <is>
@@ -8730,13 +8730,13 @@
       </c>
       <c r="N83" s="2" t="n"/>
       <c r="O83" s="32" t="n">
-        <v>-16.9</v>
+        <v>-27.8</v>
       </c>
       <c r="P83" s="32" t="n">
-        <v>-11.5</v>
+        <v>-14.8</v>
       </c>
       <c r="Q83" s="32" t="n">
-        <v>-13.8</v>
+        <v>-20.38</v>
       </c>
       <c r="R83" s="23" t="inlineStr">
         <is>
@@ -8846,13 +8846,13 @@
         </is>
       </c>
       <c r="O84" s="32" t="n">
-        <v>-27</v>
+        <v>-29.1</v>
       </c>
       <c r="P84" s="32" t="n">
-        <v>-13.9</v>
+        <v>-16.6</v>
       </c>
       <c r="Q84" s="32" t="n">
-        <v>-19.39</v>
+        <v>-23.65</v>
       </c>
       <c r="R84" s="23" t="inlineStr">
         <is>
@@ -8962,13 +8962,13 @@
         </is>
       </c>
       <c r="O85" s="32" t="n">
-        <v>-24</v>
+        <v>-35.1</v>
       </c>
       <c r="P85" s="32" t="n">
-        <v>-8.1</v>
+        <v>-18.5</v>
       </c>
       <c r="Q85" s="32" t="n">
-        <v>-16.04</v>
+        <v>-26.75</v>
       </c>
       <c r="R85" s="23" t="inlineStr">
         <is>
@@ -9074,13 +9074,13 @@
       </c>
       <c r="N86" s="2" t="n"/>
       <c r="O86" s="32" t="n">
-        <v>-23.7</v>
+        <v>-31.2</v>
       </c>
       <c r="P86" s="32" t="n">
-        <v>-8.6</v>
+        <v>-16.8</v>
       </c>
       <c r="Q86" s="32" t="n">
-        <v>-15.88</v>
+        <v>-23.41</v>
       </c>
       <c r="R86" s="23" t="inlineStr">
         <is>
@@ -9198,13 +9198,13 @@
         </is>
       </c>
       <c r="O87" s="32" t="n">
-        <v>-28.1</v>
+        <v>-32.8</v>
       </c>
       <c r="P87" s="32" t="n">
-        <v>-16.9</v>
+        <v>-19.7</v>
       </c>
       <c r="Q87" s="32" t="n">
-        <v>-22.21</v>
+        <v>-25.48</v>
       </c>
       <c r="R87" s="23" t="inlineStr">
         <is>
@@ -9310,13 +9310,13 @@
       </c>
       <c r="N88" s="2" t="n"/>
       <c r="O88" s="32" t="n">
-        <v>-28.2</v>
+        <v>-24.5</v>
       </c>
       <c r="P88" s="32" t="n">
-        <v>-11.8</v>
+        <v>-13.8</v>
       </c>
       <c r="Q88" s="32" t="n">
-        <v>-20.71</v>
+        <v>-19.89</v>
       </c>
       <c r="R88" s="23" t="inlineStr">
         <is>
@@ -9528,13 +9528,13 @@
         </is>
       </c>
       <c r="O90" s="32" t="n">
-        <v>-28.4</v>
+        <v>-17.6</v>
       </c>
       <c r="P90" s="32" t="n">
-        <v>-14.4</v>
+        <v>-8.4</v>
       </c>
       <c r="Q90" s="32" t="n">
-        <v>-20.95</v>
+        <v>-12.6</v>
       </c>
       <c r="R90" s="23" t="inlineStr">
         <is>
@@ -9636,13 +9636,13 @@
       </c>
       <c r="N91" s="2" t="n"/>
       <c r="O91" s="32" t="n">
-        <v>-27.1</v>
+        <v>-19.4</v>
       </c>
       <c r="P91" s="32" t="n">
-        <v>-9.4</v>
+        <v>-11.3</v>
       </c>
       <c r="Q91" s="32" t="n">
-        <v>-20.85</v>
+        <v>-15.04</v>
       </c>
       <c r="R91" s="23" t="inlineStr">
         <is>
@@ -9744,13 +9744,13 @@
       </c>
       <c r="N92" s="2" t="n"/>
       <c r="O92" s="32" t="n">
-        <v>-5.4</v>
+        <v>-14.2</v>
       </c>
       <c r="P92" s="32" t="n">
-        <v>6.9</v>
+        <v>2.6</v>
       </c>
       <c r="Q92" s="32" t="n">
-        <v>0.51</v>
+        <v>-3.41</v>
       </c>
       <c r="R92" s="23" t="inlineStr">
         <is>
@@ -9856,13 +9856,13 @@
       </c>
       <c r="N93" s="2" t="n"/>
       <c r="O93" s="32" t="n">
-        <v>-1</v>
+        <v>-2.5</v>
       </c>
       <c r="P93" s="32" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="Q93" s="32" t="n">
-        <v>7.26</v>
+        <v>0.65</v>
       </c>
       <c r="R93" s="23" t="inlineStr">
         <is>
@@ -9976,10 +9976,10 @@
         </is>
       </c>
       <c r="O94" s="32" t="n">
-        <v>-1.3</v>
+        <v>-5.6</v>
       </c>
       <c r="P94" s="32" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="Q94" s="32" t="n"/>
       <c r="R94" s="23" t="inlineStr">
@@ -10094,13 +10094,13 @@
       </c>
       <c r="N95" s="2" t="n"/>
       <c r="O95" s="32" t="n">
-        <v>3.6</v>
+        <v>-8.5</v>
       </c>
       <c r="P95" s="32" t="n">
-        <v>15.3</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="Q95" s="32" t="n">
-        <v>8.41</v>
+        <v>-3.46</v>
       </c>
       <c r="R95" s="23" t="inlineStr">
         <is>
@@ -10222,10 +10222,10 @@
         </is>
       </c>
       <c r="O96" s="32" t="n">
-        <v>-4.9</v>
+        <v>-5.7</v>
       </c>
       <c r="P96" s="32" t="n">
-        <v>13.2</v>
+        <v>7.3</v>
       </c>
       <c r="Q96" s="32" t="n"/>
       <c r="R96" s="23" t="inlineStr">
@@ -10340,13 +10340,13 @@
       </c>
       <c r="N97" s="2" t="n"/>
       <c r="O97" s="32" t="n">
-        <v>-1.6</v>
+        <v>-8.5</v>
       </c>
       <c r="P97" s="32" t="n">
         <v>10.9</v>
       </c>
       <c r="Q97" s="32" t="n">
-        <v>5.98</v>
+        <v>-1.12</v>
       </c>
       <c r="R97" s="23" t="inlineStr">
         <is>
@@ -10460,10 +10460,10 @@
       </c>
       <c r="N98" s="2" t="n"/>
       <c r="O98" s="32" t="n">
-        <v>-11.6</v>
+        <v>-6.9</v>
       </c>
       <c r="P98" s="32" t="n">
-        <v>-0.1</v>
+        <v>3.2</v>
       </c>
       <c r="Q98" s="32" t="n"/>
       <c r="R98" s="23" t="inlineStr">
@@ -10578,13 +10578,13 @@
       </c>
       <c r="N99" s="2" t="n"/>
       <c r="O99" s="32" t="n">
-        <v>-16.4</v>
+        <v>-10.4</v>
       </c>
       <c r="P99" s="32" t="n">
-        <v>-4.8</v>
+        <v>-7.2</v>
       </c>
       <c r="Q99" s="32" t="n">
-        <v>-9.69</v>
+        <v>-8.77</v>
       </c>
       <c r="R99" s="23" t="inlineStr">
         <is>
@@ -10910,13 +10910,13 @@
       </c>
       <c r="N102" s="2" t="n"/>
       <c r="O102" s="32" t="n">
-        <v>-18.7</v>
+        <v>-16.7</v>
       </c>
       <c r="P102" s="32" t="n">
-        <v>-7.4</v>
+        <v>-11.2</v>
       </c>
       <c r="Q102" s="32" t="n">
-        <v>-11.46</v>
+        <v>-15.34</v>
       </c>
       <c r="R102" s="23" t="inlineStr">
         <is>
@@ -11026,10 +11026,10 @@
       </c>
       <c r="N103" s="2" t="n"/>
       <c r="O103" s="32" t="n">
-        <v>-20.2</v>
+        <v>-16.3</v>
       </c>
       <c r="P103" s="32" t="n">
-        <v>-7</v>
+        <v>-11.4</v>
       </c>
       <c r="Q103" s="32" t="n"/>
       <c r="R103" s="23" t="inlineStr">
@@ -11136,10 +11136,10 @@
       </c>
       <c r="N104" s="2" t="n"/>
       <c r="O104" s="32" t="n">
-        <v>-21.1</v>
+        <v>-17.8</v>
       </c>
       <c r="P104" s="32" t="n">
-        <v>-4.1</v>
+        <v>-9.699999999999999</v>
       </c>
       <c r="Q104" s="32" t="n"/>
       <c r="R104" s="23" t="inlineStr">
@@ -11262,13 +11262,13 @@
         </is>
       </c>
       <c r="O105" s="32" t="n">
-        <v>-24.3</v>
+        <v>-17.7</v>
       </c>
       <c r="P105" s="32" t="n">
-        <v>-3.2</v>
+        <v>-8.5</v>
       </c>
       <c r="Q105" s="32" t="n">
-        <v>-13.26</v>
+        <v>-15.11</v>
       </c>
       <c r="R105" s="23" t="inlineStr">
         <is>
@@ -11378,10 +11378,10 @@
         </is>
       </c>
       <c r="O106" s="32" t="n">
-        <v>-19.4</v>
+        <v>-16.1</v>
       </c>
       <c r="P106" s="32" t="n">
-        <v>-5.6</v>
+        <v>-8.6</v>
       </c>
       <c r="Q106" s="32" t="n"/>
       <c r="R106" s="23" t="inlineStr">
@@ -11598,13 +11598,13 @@
       </c>
       <c r="N108" s="2" t="n"/>
       <c r="O108" s="32" t="n">
-        <v>-11.4</v>
+        <v>-16.4</v>
       </c>
       <c r="P108" s="32" t="n">
-        <v>-5.7</v>
+        <v>-8</v>
       </c>
       <c r="Q108" s="32" t="n">
-        <v>-8.529999999999999</v>
+        <v>-14.12</v>
       </c>
       <c r="R108" s="23" t="inlineStr">
         <is>
@@ -11926,13 +11926,13 @@
       </c>
       <c r="N111" s="2" t="n"/>
       <c r="O111" s="32" t="n">
-        <v>-10.5</v>
+        <v>-20.5</v>
       </c>
       <c r="P111" s="32" t="n">
-        <v>1.1</v>
+        <v>-4.8</v>
       </c>
       <c r="Q111" s="32" t="n">
-        <v>-5.11</v>
+        <v>-16</v>
       </c>
       <c r="R111" s="23" t="inlineStr">
         <is>
@@ -12038,10 +12038,10 @@
       </c>
       <c r="N112" s="2" t="n"/>
       <c r="O112" s="32" t="n">
-        <v>-11.9</v>
+        <v>-16.8</v>
       </c>
       <c r="P112" s="32" t="n">
-        <v>5</v>
+        <v>-12</v>
       </c>
       <c r="Q112" s="32" t="n"/>
       <c r="R112" s="23" t="inlineStr">
@@ -12144,10 +12144,10 @@
       </c>
       <c r="N113" s="2" t="n"/>
       <c r="O113" s="32" t="n">
-        <v>-17.9</v>
+        <v>-17.3</v>
       </c>
       <c r="P113" s="32" t="n">
-        <v>1.9</v>
+        <v>-0.1</v>
       </c>
       <c r="Q113" s="32" t="n"/>
       <c r="R113" s="23" t="inlineStr">
@@ -12258,10 +12258,10 @@
         </is>
       </c>
       <c r="O114" s="32" t="n">
-        <v>-25.1</v>
+        <v>-22.3</v>
       </c>
       <c r="P114" s="32" t="n">
-        <v>2.4</v>
+        <v>1.5</v>
       </c>
       <c r="Q114" s="32" t="n"/>
       <c r="R114" s="23" t="inlineStr">
@@ -12380,10 +12380,10 @@
         </is>
       </c>
       <c r="O115" s="32" t="n">
-        <v>-18.1</v>
+        <v>-20.5</v>
       </c>
       <c r="P115" s="32" t="n">
-        <v>0.2</v>
+        <v>-2.8</v>
       </c>
       <c r="Q115" s="32" t="n"/>
       <c r="R115" s="23" t="inlineStr">
@@ -12498,13 +12498,13 @@
       </c>
       <c r="N116" s="2" t="n"/>
       <c r="O116" s="32" t="n">
-        <v>-9.300000000000001</v>
+        <v>-12.7</v>
       </c>
       <c r="P116" s="32" t="n">
-        <v>5.3</v>
+        <v>4.1</v>
       </c>
       <c r="Q116" s="32" t="n">
-        <v>-5.58</v>
+        <v>-5.79</v>
       </c>
       <c r="R116" s="23" t="inlineStr">
         <is>
@@ -12610,10 +12610,10 @@
       </c>
       <c r="N117" s="2" t="n"/>
       <c r="O117" s="32" t="n">
-        <v>-6.8</v>
+        <v>-9.1</v>
       </c>
       <c r="P117" s="32" t="n">
-        <v>-0.1</v>
+        <v>1.3</v>
       </c>
       <c r="Q117" s="32" t="n"/>
       <c r="R117" s="23" t="inlineStr">
@@ -12724,10 +12724,10 @@
         </is>
       </c>
       <c r="O118" s="32" t="n">
-        <v>-28.7</v>
+        <v>-20.7</v>
       </c>
       <c r="P118" s="32" t="n">
-        <v>-9.300000000000001</v>
+        <v>-6.2</v>
       </c>
       <c r="Q118" s="32" t="n"/>
       <c r="R118" s="23" t="inlineStr">
@@ -12842,13 +12842,13 @@
       </c>
       <c r="N119" s="2" t="n"/>
       <c r="O119" s="32" t="n">
-        <v>-20.7</v>
+        <v>-14.1</v>
       </c>
       <c r="P119" s="32" t="n">
-        <v>-9.800000000000001</v>
+        <v>-3.4</v>
       </c>
       <c r="Q119" s="32" t="n">
-        <v>-15.04</v>
+        <v>-8.24</v>
       </c>
       <c r="R119" s="23" t="inlineStr">
         <is>
@@ -13076,13 +13076,13 @@
       </c>
       <c r="N121" s="2" t="n"/>
       <c r="O121" s="32" t="n">
-        <v>-7.8</v>
+        <v>-10.4</v>
       </c>
       <c r="P121" s="32" t="n">
-        <v>3.8</v>
+        <v>1.4</v>
       </c>
       <c r="Q121" s="32" t="n">
-        <v>-3.61</v>
+        <v>-2.16</v>
       </c>
       <c r="R121" s="23" t="inlineStr">
         <is>
@@ -13200,10 +13200,10 @@
       </c>
       <c r="N122" s="2" t="n"/>
       <c r="O122" s="32" t="n">
-        <v>-25.3</v>
+        <v>-12.1</v>
       </c>
       <c r="P122" s="32" t="n">
-        <v>-1.9</v>
+        <v>-2.4</v>
       </c>
       <c r="Q122" s="32" t="n"/>
       <c r="R122" s="23" t="inlineStr">
@@ -13424,13 +13424,13 @@
       </c>
       <c r="N124" s="2" t="n"/>
       <c r="O124" s="32" t="n">
-        <v>-5.8</v>
+        <v>-11.4</v>
       </c>
       <c r="P124" s="32" t="n">
-        <v>6.8</v>
+        <v>-2.3</v>
       </c>
       <c r="Q124" s="32" t="n">
-        <v>0.8</v>
+        <v>-7.34</v>
       </c>
       <c r="R124" s="23" t="inlineStr">
         <is>
@@ -13548,13 +13548,13 @@
       </c>
       <c r="N125" s="2" t="n"/>
       <c r="O125" s="32" t="n">
-        <v>1.4</v>
+        <v>0.6</v>
       </c>
       <c r="P125" s="32" t="n">
-        <v>19.8</v>
+        <v>12.6</v>
       </c>
       <c r="Q125" s="32" t="n">
-        <v>9.619999999999999</v>
+        <v>4.01</v>
       </c>
       <c r="R125" s="23" t="inlineStr">
         <is>
@@ -13652,10 +13652,10 @@
       </c>
       <c r="N126" s="2" t="n"/>
       <c r="O126" s="32" t="n">
-        <v>5.9</v>
+        <v>0.9</v>
       </c>
       <c r="P126" s="32" t="n">
-        <v>23</v>
+        <v>17.3</v>
       </c>
       <c r="Q126" s="32" t="n"/>
       <c r="R126" s="23" t="inlineStr">
@@ -13762,13 +13762,13 @@
       </c>
       <c r="N127" s="2" t="n"/>
       <c r="O127" s="32" t="n">
-        <v>5.3</v>
+        <v>-3.2</v>
       </c>
       <c r="P127" s="32" t="n">
-        <v>15.5</v>
+        <v>7.4</v>
       </c>
       <c r="Q127" s="32" t="n">
-        <v>10.53</v>
+        <v>2</v>
       </c>
       <c r="R127" s="23" t="inlineStr">
         <is>
@@ -13882,10 +13882,10 @@
       </c>
       <c r="N128" s="2" t="n"/>
       <c r="O128" s="32" t="n">
-        <v>9.9</v>
+        <v>7.7</v>
       </c>
       <c r="P128" s="32" t="n">
-        <v>26</v>
+        <v>20.1</v>
       </c>
       <c r="Q128" s="32" t="n"/>
       <c r="R128" s="23" t="inlineStr">
@@ -13992,13 +13992,13 @@
       </c>
       <c r="N129" s="2" t="n"/>
       <c r="O129" s="32" t="n">
-        <v>-1.7</v>
+        <v>1.7</v>
       </c>
       <c r="P129" s="32" t="n">
-        <v>18.4</v>
+        <v>12.3</v>
       </c>
       <c r="Q129" s="32" t="n">
-        <v>8.949999999999999</v>
+        <v>5.51</v>
       </c>
       <c r="R129" s="23" t="inlineStr">
         <is>
@@ -14112,13 +14112,13 @@
       </c>
       <c r="N130" s="2" t="n"/>
       <c r="O130" s="32" t="n">
-        <v>-3.8</v>
+        <v>-6.1</v>
       </c>
       <c r="P130" s="32" t="n">
-        <v>13.9</v>
+        <v>11.9</v>
       </c>
       <c r="Q130" s="32" t="n">
-        <v>5.66</v>
+        <v>2.64</v>
       </c>
       <c r="R130" s="23" t="inlineStr">
         <is>
@@ -14232,13 +14232,13 @@
       </c>
       <c r="N131" s="2" t="n"/>
       <c r="O131" s="32" t="n">
-        <v>13.7</v>
+        <v>6.3</v>
       </c>
       <c r="P131" s="32" t="n">
-        <v>23.4</v>
+        <v>20.5</v>
       </c>
       <c r="Q131" s="32" t="n">
-        <v>18.45</v>
+        <v>10.53</v>
       </c>
       <c r="R131" s="23" t="inlineStr">
         <is>
@@ -14348,13 +14348,13 @@
       </c>
       <c r="N132" s="2" t="n"/>
       <c r="O132" s="32" t="n">
-        <v>5.4</v>
+        <v>13.2</v>
       </c>
       <c r="P132" s="32" t="n">
-        <v>27.7</v>
+        <v>21.6</v>
       </c>
       <c r="Q132" s="32" t="n">
-        <v>17.06</v>
+        <v>16.25</v>
       </c>
       <c r="R132" s="23" t="inlineStr">
         <is>
@@ -14464,13 +14464,13 @@
       </c>
       <c r="N133" s="2" t="n"/>
       <c r="O133" s="32" t="n">
-        <v>9.9</v>
+        <v>10</v>
       </c>
       <c r="P133" s="32" t="n">
-        <v>23.8</v>
+        <v>19.5</v>
       </c>
       <c r="Q133" s="32" t="n">
-        <v>16.41</v>
+        <v>13.99</v>
       </c>
       <c r="R133" s="23" t="inlineStr">
         <is>
@@ -14686,13 +14686,13 @@
       </c>
       <c r="N135" s="2" t="n"/>
       <c r="O135" s="32" t="n">
-        <v>6.9</v>
+        <v>12.1</v>
       </c>
       <c r="P135" s="32" t="n">
-        <v>19.8</v>
+        <v>25.9</v>
       </c>
       <c r="Q135" s="32" t="n">
-        <v>12.56</v>
+        <v>17.94</v>
       </c>
       <c r="R135" s="23" t="inlineStr">
         <is>
@@ -14802,13 +14802,13 @@
       </c>
       <c r="N136" s="2" t="n"/>
       <c r="O136" s="32" t="n">
-        <v>4.5</v>
+        <v>11.8</v>
       </c>
       <c r="P136" s="32" t="n">
-        <v>19.8</v>
+        <v>25.3</v>
       </c>
       <c r="Q136" s="32" t="n">
-        <v>10.05</v>
+        <v>18.14</v>
       </c>
       <c r="R136" s="23" t="inlineStr">
         <is>
@@ -14918,13 +14918,13 @@
       </c>
       <c r="N137" s="2" t="n"/>
       <c r="O137" s="32" t="n">
-        <v>4.8</v>
+        <v>7.6</v>
       </c>
       <c r="P137" s="32" t="n">
-        <v>23.5</v>
+        <v>25</v>
       </c>
       <c r="Q137" s="32" t="n">
-        <v>13.95</v>
+        <v>15.95</v>
       </c>
       <c r="R137" s="23" t="inlineStr">
         <is>
@@ -15034,10 +15034,10 @@
       </c>
       <c r="N138" s="2" t="n"/>
       <c r="O138" s="32" t="n">
-        <v>4.8</v>
+        <v>7</v>
       </c>
       <c r="P138" s="32" t="n">
-        <v>23.9</v>
+        <v>21.4</v>
       </c>
       <c r="Q138" s="32" t="n"/>
       <c r="R138" s="23" t="inlineStr">
@@ -15148,13 +15148,13 @@
       </c>
       <c r="N139" s="2" t="n"/>
       <c r="O139" s="32" t="n">
-        <v>6.1</v>
+        <v>11</v>
       </c>
       <c r="P139" s="32" t="n">
-        <v>23.3</v>
+        <v>21.9</v>
       </c>
       <c r="Q139" s="32" t="n">
-        <v>15.06</v>
+        <v>16.36</v>
       </c>
       <c r="R139" s="23" t="inlineStr">
         <is>
@@ -15264,13 +15264,13 @@
       </c>
       <c r="N140" s="2" t="n"/>
       <c r="O140" s="32" t="n">
-        <v>6.9</v>
+        <v>10.8</v>
       </c>
       <c r="P140" s="32" t="n">
-        <v>24.2</v>
+        <v>25.8</v>
       </c>
       <c r="Q140" s="32" t="n">
-        <v>14.94</v>
+        <v>17.16</v>
       </c>
       <c r="R140" s="23" t="inlineStr">
         <is>
@@ -15482,13 +15482,13 @@
       </c>
       <c r="N142" s="2" t="n"/>
       <c r="O142" s="32" t="n">
-        <v>10.1</v>
+        <v>13.7</v>
       </c>
       <c r="P142" s="32" t="n">
-        <v>25.2</v>
+        <v>29</v>
       </c>
       <c r="Q142" s="32" t="n">
-        <v>16.25</v>
+        <v>20.07</v>
       </c>
       <c r="R142" s="23" t="inlineStr">
         <is>
@@ -15598,13 +15598,13 @@
       </c>
       <c r="N143" s="2" t="n"/>
       <c r="O143" s="32" t="n">
-        <v>13.4</v>
+        <v>17.7</v>
       </c>
       <c r="P143" s="32" t="n">
-        <v>24.7</v>
+        <v>28.5</v>
       </c>
       <c r="Q143" s="32" t="n">
-        <v>18.5</v>
+        <v>21.82</v>
       </c>
       <c r="R143" s="23" t="inlineStr">
         <is>
@@ -15914,13 +15914,13 @@
       </c>
       <c r="N146" s="2" t="n"/>
       <c r="O146" s="32" t="n">
-        <v>19.8</v>
+        <v>20.4</v>
       </c>
       <c r="P146" s="32" t="n">
-        <v>27.3</v>
+        <v>27.5</v>
       </c>
       <c r="Q146" s="32" t="n">
-        <v>23.47</v>
+        <v>23.7</v>
       </c>
       <c r="R146" s="23" t="inlineStr">
         <is>
@@ -16022,13 +16022,13 @@
       </c>
       <c r="N147" s="2" t="n"/>
       <c r="O147" s="32" t="n">
-        <v>14.2</v>
+        <v>18.6</v>
       </c>
       <c r="P147" s="32" t="n">
-        <v>23.2</v>
+        <v>26.8</v>
       </c>
       <c r="Q147" s="32" t="n">
-        <v>18.73</v>
+        <v>22.1</v>
       </c>
       <c r="R147" s="23" t="inlineStr">
         <is>
@@ -16240,13 +16240,13 @@
       </c>
       <c r="N149" s="2" t="n"/>
       <c r="O149" s="32" t="n">
-        <v>9.5</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="P149" s="32" t="n">
-        <v>22.8</v>
+        <v>22.2</v>
       </c>
       <c r="Q149" s="32" t="n">
-        <v>16.74</v>
+        <v>16.01</v>
       </c>
       <c r="R149" s="23" t="inlineStr">
         <is>
@@ -16356,13 +16356,13 @@
       </c>
       <c r="N150" s="2" t="n"/>
       <c r="O150" s="32" t="n">
-        <v>12</v>
+        <v>12.1</v>
       </c>
       <c r="P150" s="32" t="n">
-        <v>22.4</v>
+        <v>17.3</v>
       </c>
       <c r="Q150" s="32" t="n">
-        <v>15.49</v>
+        <v>13.99</v>
       </c>
       <c r="R150" s="23" t="inlineStr">
         <is>
@@ -16472,13 +16472,13 @@
       </c>
       <c r="N151" s="2" t="n"/>
       <c r="O151" s="32" t="n">
-        <v>11.3</v>
+        <v>13</v>
       </c>
       <c r="P151" s="32" t="n">
-        <v>25</v>
+        <v>24.7</v>
       </c>
       <c r="Q151" s="32" t="n">
-        <v>17.02</v>
+        <v>17.89</v>
       </c>
       <c r="R151" s="23" t="inlineStr">
         <is>
@@ -16678,13 +16678,13 @@
       </c>
       <c r="N153" s="2" t="n"/>
       <c r="O153" s="32" t="n">
-        <v>5.3</v>
+        <v>7.7</v>
       </c>
       <c r="P153" s="32" t="n">
-        <v>22.2</v>
+        <v>21.9</v>
       </c>
       <c r="Q153" s="32" t="n">
-        <v>12.65</v>
+        <v>13.97</v>
       </c>
       <c r="R153" s="23" t="inlineStr">
         <is>
@@ -16798,13 +16798,13 @@
       </c>
       <c r="N154" s="2" t="n"/>
       <c r="O154" s="32" t="n">
-        <v>-2.2</v>
+        <v>-1.3</v>
       </c>
       <c r="P154" s="32" t="n">
-        <v>11.6</v>
+        <v>9.1</v>
       </c>
       <c r="Q154" s="32" t="n">
-        <v>4.34</v>
+        <v>3.17</v>
       </c>
       <c r="R154" s="23" t="inlineStr">
         <is>
@@ -17000,10 +17000,10 @@
       </c>
       <c r="N156" s="2" t="n"/>
       <c r="O156" s="32" t="n">
-        <v>-4</v>
+        <v>-10.5</v>
       </c>
       <c r="P156" s="32" t="n">
-        <v>8.5</v>
+        <v>-3.1</v>
       </c>
       <c r="Q156" s="32" t="n"/>
       <c r="R156" s="23" t="inlineStr">
@@ -17106,10 +17106,10 @@
       </c>
       <c r="N157" s="2" t="n"/>
       <c r="O157" s="32" t="n">
-        <v>8.199999999999999</v>
+        <v>10.6</v>
       </c>
       <c r="P157" s="32" t="n">
-        <v>22.7</v>
+        <v>22.3</v>
       </c>
       <c r="Q157" s="32" t="n"/>
       <c r="R157" s="23" t="inlineStr">
@@ -17494,10 +17494,10 @@
       </c>
       <c r="N161" s="2" t="n"/>
       <c r="O161" s="32" t="n">
-        <v>-1.3</v>
+        <v>-0.5</v>
       </c>
       <c r="P161" s="32" t="n">
-        <v>16.4</v>
+        <v>13.1</v>
       </c>
       <c r="Q161" s="32" t="n"/>
       <c r="R161" s="23" t="inlineStr">
@@ -17607,12 +17607,8 @@
           <t>⚡</t>
         </is>
       </c>
-      <c r="O162" s="32" t="n">
-        <v>-26.1</v>
-      </c>
-      <c r="P162" s="32" t="n">
-        <v>-6.4</v>
-      </c>
+      <c r="O162" s="32" t="n"/>
+      <c r="P162" s="32" t="n"/>
       <c r="Q162" s="32" t="n"/>
       <c r="R162" s="23" t="inlineStr">
         <is>
@@ -17721,8 +17717,12 @@
           <t>▼</t>
         </is>
       </c>
-      <c r="O163" s="32" t="n"/>
-      <c r="P163" s="32" t="n"/>
+      <c r="O163" s="32" t="n">
+        <v>-17.2</v>
+      </c>
+      <c r="P163" s="32" t="n">
+        <v>-11.8</v>
+      </c>
       <c r="Q163" s="32" t="n"/>
       <c r="R163" s="23" t="inlineStr">
         <is>
@@ -17938,10 +17938,10 @@
         </is>
       </c>
       <c r="O165" s="32" t="n">
-        <v>-17.2</v>
+        <v>-16.6</v>
       </c>
       <c r="P165" s="32" t="n">
-        <v>-3.6</v>
+        <v>-6.9</v>
       </c>
       <c r="Q165" s="32" t="n"/>
       <c r="R165" s="23" t="inlineStr">
@@ -18264,10 +18264,10 @@
         </is>
       </c>
       <c r="O168" s="32" t="n">
-        <v>-30.4</v>
+        <v>-15.8</v>
       </c>
       <c r="P168" s="32" t="n">
-        <v>-7.9</v>
+        <v>-2.1</v>
       </c>
       <c r="Q168" s="32" t="n"/>
       <c r="R168" s="23" t="inlineStr">
@@ -18378,10 +18378,10 @@
         </is>
       </c>
       <c r="O169" s="32" t="n">
-        <v>-38.4</v>
+        <v>-27.5</v>
       </c>
       <c r="P169" s="32" t="n">
-        <v>-11.3</v>
+        <v>-7.1</v>
       </c>
       <c r="Q169" s="32" t="n"/>
       <c r="R169" s="23" t="inlineStr">
@@ -18704,10 +18704,10 @@
       </c>
       <c r="N172" s="3" t="n"/>
       <c r="O172" s="32" t="n">
-        <v>-17.1</v>
+        <v>-15.4</v>
       </c>
       <c r="P172" s="32" t="n">
-        <v>2.5</v>
+        <v>-1</v>
       </c>
       <c r="Q172" s="32" t="n"/>
       <c r="R172" s="23" t="inlineStr">
@@ -18814,10 +18814,10 @@
       </c>
       <c r="N173" s="2" t="n"/>
       <c r="O173" s="32" t="n">
+        <v>-20.4</v>
+      </c>
+      <c r="P173" s="32" t="n">
         <v>-13</v>
-      </c>
-      <c r="P173" s="32" t="n">
-        <v>5.5</v>
       </c>
       <c r="Q173" s="32" t="n"/>
       <c r="R173" s="23" t="inlineStr">
@@ -19136,10 +19136,10 @@
       </c>
       <c r="N176" s="2" t="n"/>
       <c r="O176" s="32" t="n">
-        <v>3</v>
+        <v>5.8</v>
       </c>
       <c r="P176" s="32" t="n">
-        <v>11.9</v>
+        <v>11.2</v>
       </c>
       <c r="Q176" s="32" t="n"/>
       <c r="R176" s="23" t="inlineStr">
@@ -19238,10 +19238,10 @@
       </c>
       <c r="N177" s="2" t="n"/>
       <c r="O177" s="32" t="n">
-        <v>-11.4</v>
+        <v>-26.2</v>
       </c>
       <c r="P177" s="32" t="n">
-        <v>-4.2</v>
+        <v>-5.3</v>
       </c>
       <c r="Q177" s="32" t="n"/>
       <c r="R177" s="23" t="inlineStr">
@@ -20129,13 +20129,13 @@
       </c>
       <c r="N186" s="2" t="n"/>
       <c r="O186" s="32" t="n">
-        <v>-47.5</v>
+        <v>-48.2</v>
       </c>
       <c r="P186" s="32" t="n">
-        <v>-35.3</v>
+        <v>-32.8</v>
       </c>
       <c r="Q186" s="32" t="n">
-        <v>-42.8</v>
+        <v>-42.91</v>
       </c>
       <c r="R186" s="23" t="inlineStr">
         <is>
@@ -20238,13 +20238,13 @@
       </c>
       <c r="N187" s="2" t="n"/>
       <c r="O187" s="32" t="n">
-        <v>-46</v>
+        <v>-48.4</v>
       </c>
       <c r="P187" s="32" t="n">
-        <v>-33</v>
+        <v>-34.9</v>
       </c>
       <c r="Q187" s="32" t="n">
-        <v>-41.31</v>
+        <v>-42.62</v>
       </c>
       <c r="R187" s="23" t="inlineStr">
         <is>
@@ -20342,13 +20342,13 @@
       </c>
       <c r="N188" s="2" t="n"/>
       <c r="O188" s="32" t="n">
-        <v>-48</v>
+        <v>-46.8</v>
       </c>
       <c r="P188" s="32" t="n">
-        <v>-36.4</v>
+        <v>-34.7</v>
       </c>
       <c r="Q188" s="32" t="n">
-        <v>-42.31</v>
+        <v>-41.44</v>
       </c>
       <c r="R188" s="23" t="inlineStr">
         <is>
@@ -20446,13 +20446,13 @@
       </c>
       <c r="N189" s="2" t="n"/>
       <c r="O189" s="32" t="n">
-        <v>-51.9</v>
+        <v>-50.8</v>
       </c>
       <c r="P189" s="32" t="n">
-        <v>-31.2</v>
+        <v>-34.7</v>
       </c>
       <c r="Q189" s="32" t="n">
-        <v>-43.65</v>
+        <v>-43.89</v>
       </c>
       <c r="R189" s="23" t="inlineStr">
         <is>
@@ -20550,13 +20550,13 @@
       </c>
       <c r="N190" s="2" t="n"/>
       <c r="O190" s="32" t="n">
-        <v>-51.9</v>
+        <v>-51.6</v>
       </c>
       <c r="P190" s="32" t="n">
-        <v>-41.7</v>
+        <v>-40.2</v>
       </c>
       <c r="Q190" s="32" t="n">
-        <v>-48.48</v>
+        <v>-47.44</v>
       </c>
       <c r="R190" s="23" t="inlineStr">
         <is>
@@ -20654,13 +20654,13 @@
       </c>
       <c r="N191" s="2" t="n"/>
       <c r="O191" s="32" t="n">
-        <v>-47.6</v>
+        <v>-47.4</v>
       </c>
       <c r="P191" s="32" t="n">
-        <v>-30.6</v>
+        <v>-31.5</v>
       </c>
       <c r="Q191" s="32" t="n">
-        <v>-42.32</v>
+        <v>-42.01</v>
       </c>
       <c r="R191" s="23" t="inlineStr">
         <is>
@@ -20754,13 +20754,13 @@
       </c>
       <c r="N192" s="2" t="n"/>
       <c r="O192" s="32" t="n">
-        <v>-47.1</v>
+        <v>-46.3</v>
       </c>
       <c r="P192" s="32" t="n">
-        <v>-34.6</v>
+        <v>-31.5</v>
       </c>
       <c r="Q192" s="32" t="n">
-        <v>-42.1</v>
+        <v>-40.91</v>
       </c>
       <c r="R192" s="23" t="inlineStr">
         <is>
@@ -20859,13 +20859,13 @@
       </c>
       <c r="N193" s="2" t="n"/>
       <c r="O193" s="32" t="n">
-        <v>-23.8</v>
+        <v>-27.5</v>
       </c>
       <c r="P193" s="32" t="n">
-        <v>-17.1</v>
+        <v>-23.1</v>
       </c>
       <c r="Q193" s="32" t="n">
-        <v>-20.69</v>
+        <v>-25.93</v>
       </c>
       <c r="R193" s="23" t="inlineStr">
         <is>
@@ -20967,10 +20967,10 @@
       </c>
       <c r="N194" s="2" t="n"/>
       <c r="O194" s="32" t="n">
-        <v>-42.8</v>
+        <v>-49</v>
       </c>
       <c r="P194" s="32" t="n">
-        <v>-36.6</v>
+        <v>-37.6</v>
       </c>
       <c r="Q194" s="32" t="n"/>
       <c r="R194" s="23" t="inlineStr">
@@ -21065,13 +21065,13 @@
       </c>
       <c r="N195" s="2" t="n"/>
       <c r="O195" s="32" t="n">
-        <v>-19.5</v>
+        <v>-24.5</v>
       </c>
       <c r="P195" s="32" t="n">
-        <v>-16.2</v>
+        <v>-16.3</v>
       </c>
       <c r="Q195" s="32" t="n">
-        <v>-17.48</v>
+        <v>-21.4</v>
       </c>
       <c r="R195" s="23" t="inlineStr">
         <is>
@@ -21169,14 +21169,12 @@
       </c>
       <c r="N196" s="2" t="n"/>
       <c r="O196" s="32" t="n">
-        <v>-47.7</v>
+        <v>-40</v>
       </c>
       <c r="P196" s="32" t="n">
-        <v>-30.4</v>
-      </c>
-      <c r="Q196" s="32" t="n">
-        <v>-40.35</v>
-      </c>
+        <v>-22.2</v>
+      </c>
+      <c r="Q196" s="32" t="n"/>
       <c r="R196" s="23" t="inlineStr">
         <is>
           <t>Y</t>
@@ -21273,13 +21271,13 @@
       </c>
       <c r="N197" s="24" t="n"/>
       <c r="O197" s="32" t="n">
-        <v>-43.3</v>
+        <v>-43.4</v>
       </c>
       <c r="P197" s="32" t="n">
-        <v>-32.4</v>
+        <v>-27.9</v>
       </c>
       <c r="Q197" s="32" t="n">
-        <v>-38.84</v>
+        <v>-37.59</v>
       </c>
       <c r="R197" s="23" t="inlineStr">
         <is>
@@ -21670,8 +21668,12 @@
         </is>
       </c>
       <c r="N201" s="2" t="n"/>
-      <c r="O201" s="32" t="n"/>
-      <c r="P201" s="32" t="n"/>
+      <c r="O201" s="32" t="n">
+        <v>-18</v>
+      </c>
+      <c r="P201" s="32" t="n">
+        <v>-11.9</v>
+      </c>
       <c r="Q201" s="32" t="n"/>
       <c r="R201" s="23" t="inlineStr">
         <is>
@@ -24184,8 +24186,12 @@
         </is>
       </c>
       <c r="N226" s="2" t="n"/>
-      <c r="O226" s="32" t="n"/>
-      <c r="P226" s="32" t="n"/>
+      <c r="O226" s="32" t="n">
+        <v>-22.7</v>
+      </c>
+      <c r="P226" s="32" t="n">
+        <v>-14.8</v>
+      </c>
       <c r="Q226" s="32" t="n"/>
       <c r="R226" s="23" t="n"/>
       <c r="S226" s="37" t="n"/>
@@ -26207,13 +26213,13 @@
       </c>
       <c r="N247" s="2" t="n"/>
       <c r="O247" s="32" t="n">
-        <v>-12.6</v>
+        <v>-11.8</v>
       </c>
       <c r="P247" s="32" t="n">
-        <v>-5</v>
+        <v>-3</v>
       </c>
       <c r="Q247" s="32" t="n">
-        <v>-9.69</v>
+        <v>-7.49</v>
       </c>
       <c r="R247" s="23" t="inlineStr">
         <is>
@@ -26319,13 +26325,13 @@
       </c>
       <c r="N248" s="2" t="n"/>
       <c r="O248" s="32" t="n">
-        <v>-33.6</v>
+        <v>-17.9</v>
       </c>
       <c r="P248" s="32" t="n">
-        <v>-14.8</v>
+        <v>-8.6</v>
       </c>
       <c r="Q248" s="32" t="n">
-        <v>-24.84</v>
+        <v>-13.11</v>
       </c>
       <c r="R248" s="23" t="inlineStr">
         <is>
@@ -26427,13 +26433,13 @@
       </c>
       <c r="N249" s="2" t="n"/>
       <c r="O249" s="32" t="n">
-        <v>-2.1</v>
+        <v>0.6</v>
       </c>
       <c r="P249" s="32" t="n">
-        <v>2.1</v>
+        <v>5</v>
       </c>
       <c r="Q249" s="32" t="n">
-        <v>-0.09</v>
+        <v>3.09</v>
       </c>
       <c r="R249" s="23" t="inlineStr">
         <is>
@@ -26539,13 +26545,13 @@
       </c>
       <c r="N250" s="2" t="n"/>
       <c r="O250" s="32" t="n">
-        <v>-19.7</v>
+        <v>-27.6</v>
       </c>
       <c r="P250" s="32" t="n">
-        <v>-9.800000000000001</v>
+        <v>-14</v>
       </c>
       <c r="Q250" s="32" t="n">
-        <v>-14.39</v>
+        <v>-20.61</v>
       </c>
       <c r="R250" s="23" t="inlineStr">
         <is>
@@ -26659,10 +26665,10 @@
         </is>
       </c>
       <c r="O251" s="32" t="n">
-        <v>-49.6</v>
+        <v>-49.3</v>
       </c>
       <c r="P251" s="32" t="n">
-        <v>-29.6</v>
+        <v>-28.5</v>
       </c>
       <c r="Q251" s="32" t="n"/>
       <c r="R251" s="23" t="inlineStr">
@@ -26757,13 +26763,13 @@
       </c>
       <c r="N252" s="2" t="n"/>
       <c r="O252" s="32" t="n">
-        <v>-24.3</v>
+        <v>-31.8</v>
       </c>
       <c r="P252" s="32" t="n">
-        <v>-15.3</v>
+        <v>-20.1</v>
       </c>
       <c r="Q252" s="32" t="n">
-        <v>-20.23</v>
+        <v>-25.94</v>
       </c>
       <c r="R252" s="23" t="inlineStr">
         <is>
@@ -26955,13 +26961,13 @@
       </c>
       <c r="N254" s="2" t="n"/>
       <c r="O254" s="32" t="n">
-        <v>-52</v>
+        <v>-49.7</v>
       </c>
       <c r="P254" s="32" t="n">
-        <v>-38.7</v>
+        <v>-31.9</v>
       </c>
       <c r="Q254" s="32" t="n">
-        <v>-45.69</v>
+        <v>-42.81</v>
       </c>
       <c r="R254" s="23" t="inlineStr">
         <is>
@@ -27529,13 +27535,13 @@
       </c>
       <c r="N260" s="2" t="n"/>
       <c r="O260" s="32" t="n">
-        <v>-26</v>
+        <v>-36.8</v>
       </c>
       <c r="P260" s="32" t="n">
-        <v>-12.3</v>
+        <v>-14.4</v>
       </c>
       <c r="Q260" s="32" t="n">
-        <v>-18.75</v>
+        <v>-23.96</v>
       </c>
       <c r="R260" s="23" t="inlineStr">
         <is>
@@ -27637,13 +27643,13 @@
       </c>
       <c r="N261" s="2" t="n"/>
       <c r="O261" s="32" t="n">
-        <v>-21.5</v>
+        <v>-20.3</v>
       </c>
       <c r="P261" s="32" t="n">
-        <v>-7.7</v>
+        <v>-13.6</v>
       </c>
       <c r="Q261" s="32" t="n">
-        <v>-14.07</v>
+        <v>-17.49</v>
       </c>
       <c r="R261" s="23" t="inlineStr">
         <is>
@@ -27749,13 +27755,13 @@
       </c>
       <c r="N262" s="2" t="n"/>
       <c r="O262" s="32" t="n">
-        <v>-30.1</v>
+        <v>-23.4</v>
       </c>
       <c r="P262" s="32" t="n">
-        <v>-15.5</v>
+        <v>-14.9</v>
       </c>
       <c r="Q262" s="32" t="n">
-        <v>-21.16</v>
+        <v>-20.11</v>
       </c>
       <c r="R262" s="23" t="inlineStr">
         <is>
@@ -27955,13 +27961,13 @@
       </c>
       <c r="N264" s="2" t="n"/>
       <c r="O264" s="32" t="n">
+        <v>-18.9</v>
+      </c>
+      <c r="P264" s="32" t="n">
         <v>-14.7</v>
       </c>
-      <c r="P264" s="32" t="n">
-        <v>-9.6</v>
-      </c>
       <c r="Q264" s="32" t="n">
-        <v>-12.6</v>
+        <v>-17.21</v>
       </c>
       <c r="R264" s="23" t="inlineStr">
         <is>
@@ -28075,10 +28081,10 @@
       </c>
       <c r="N265" s="2" t="n"/>
       <c r="O265" s="32" t="n">
-        <v>-32.5</v>
+        <v>-42.6</v>
       </c>
       <c r="P265" s="32" t="n">
-        <v>-24.8</v>
+        <v>-25.8</v>
       </c>
       <c r="Q265" s="32" t="n"/>
       <c r="R265" s="23" t="inlineStr">
@@ -29119,13 +29125,13 @@
       </c>
       <c r="N276" s="2" t="n"/>
       <c r="O276" s="32" t="n">
-        <v>-25.5</v>
+        <v>-20.9</v>
       </c>
       <c r="P276" s="32" t="n">
-        <v>-8.1</v>
+        <v>-8.4</v>
       </c>
       <c r="Q276" s="32" t="n">
-        <v>-12.47</v>
+        <v>-14.85</v>
       </c>
       <c r="R276" s="23" t="inlineStr">
         <is>
@@ -30028,12 +30034,8 @@
         </is>
       </c>
       <c r="N286" s="2" t="n"/>
-      <c r="O286" s="32" t="n">
-        <v>-26.9</v>
-      </c>
-      <c r="P286" s="32" t="n">
-        <v>-6.2</v>
-      </c>
+      <c r="O286" s="32" t="n"/>
+      <c r="P286" s="32" t="n"/>
       <c r="Q286" s="32" t="n"/>
       <c r="R286" s="23" t="inlineStr">
         <is>
@@ -30302,37 +30304,103 @@
       <c r="AH288" s="2" t="n"/>
     </row>
     <row r="289" ht="24" customHeight="1" s="45">
-      <c r="A289" s="2" t="n"/>
+      <c r="A289" s="2" t="n">
+        <v>288</v>
+      </c>
       <c r="B289" s="2" t="n"/>
       <c r="C289" s="27" t="n"/>
       <c r="D289" s="2" t="n"/>
       <c r="E289" s="4" t="n"/>
-      <c r="F289" s="39" t="n"/>
-      <c r="G289" s="29" t="n"/>
-      <c r="H289" s="29" t="n"/>
-      <c r="I289" s="2" t="n"/>
-      <c r="J289" s="27" t="n"/>
-      <c r="K289" s="4" t="n"/>
+      <c r="F289" s="39" t="inlineStr">
+        <is>
+          <t>C0107</t>
+        </is>
+      </c>
+      <c r="G289" s="29" t="n">
+        <v>49.6797</v>
+      </c>
+      <c r="H289" s="29" t="n">
+        <v>116.8136</v>
+      </c>
+      <c r="I289" s="2" t="n">
+        <v>710</v>
+      </c>
+      <c r="J289" s="27" t="n">
+        <v>12</v>
+      </c>
+      <c r="K289" s="31" t="inlineStr">
+        <is>
+          <t>🇨🇳</t>
+        </is>
+      </c>
       <c r="L289" s="2" t="n"/>
-      <c r="M289" s="14" t="n"/>
+      <c r="M289" s="14" t="inlineStr">
+        <is>
+          <t>新佰路克</t>
+        </is>
+      </c>
       <c r="N289" s="2" t="n"/>
-      <c r="O289" s="32" t="n"/>
-      <c r="P289" s="32" t="n"/>
+      <c r="O289" s="32" t="n">
+        <v>-23</v>
+      </c>
+      <c r="P289" s="32" t="n">
+        <v>-13</v>
+      </c>
       <c r="Q289" s="32" t="n"/>
-      <c r="R289" s="23" t="n"/>
+      <c r="R289" s="23" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="S289" s="37" t="n"/>
-      <c r="T289" s="41" t="n"/>
-      <c r="U289" s="2" t="n"/>
-      <c r="V289" s="4" t="n"/>
-      <c r="W289" s="4" t="n"/>
-      <c r="X289" s="4" t="n"/>
+      <c r="T289" s="41" t="inlineStr">
+        <is>
+          <t>呼伦贝尔</t>
+        </is>
+      </c>
+      <c r="U289" s="2" t="inlineStr">
+        <is>
+          <t>内蒙古</t>
+        </is>
+      </c>
+      <c r="V289" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="W289" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="X289" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="Y289" s="4" t="n"/>
-      <c r="Z289" s="2" t="n"/>
-      <c r="AA289" s="2" t="n"/>
+      <c r="Z289" s="2" t="inlineStr">
+        <is>
+          <t>呼伦贝尔市</t>
+        </is>
+      </c>
+      <c r="AA289" s="2" t="inlineStr">
+        <is>
+          <t>新巴尔虎右旗</t>
+        </is>
+      </c>
       <c r="AB289" s="2" t="n"/>
       <c r="AC289" s="2" t="n"/>
-      <c r="AD289" s="2" t="n"/>
-      <c r="AE289" s="4" t="n"/>
+      <c r="AD289" s="2" t="inlineStr">
+        <is>
+          <t>中国</t>
+        </is>
+      </c>
+      <c r="AE289" s="4" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
       <c r="AF289" s="4" t="n"/>
       <c r="AG289" s="2" t="n"/>
       <c r="AH289" s="2" t="n"/>

--- a/气象/For_Python_站点信息和记录.xlsx
+++ b/气象/For_Python_站点信息和记录.xlsx
@@ -228,7 +228,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -364,6 +364,15 @@
     </xf>
     <xf numFmtId="0" fontId="13" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -767,7 +776,7 @@
   <cols>
     <col width="4.59765625" customWidth="1" style="5" min="1" max="1"/>
     <col width="12.59765625" customWidth="1" style="5" min="2" max="2"/>
-    <col width="8.59765625" customWidth="1" style="28" min="3" max="3"/>
+    <col width="8.59765625" customWidth="1" style="47" min="3" max="3"/>
     <col width="8.59765625" customWidth="1" style="5" min="4" max="4"/>
     <col width="8.59765625" customWidth="1" style="8" min="5" max="5"/>
     <col width="8.59765625" customWidth="1" style="40" min="6" max="6"/>
@@ -787,8 +796,8 @@
     <col width="18.59765625" customWidth="1" style="8" min="25" max="25"/>
     <col width="12.59765625" customWidth="1" style="5" min="26" max="30"/>
     <col width="12.59765625" customWidth="1" style="8" min="31" max="32"/>
-    <col width="12.59765625" customWidth="1" style="5" min="33" max="270"/>
-    <col width="12.59765625" customWidth="1" style="5" min="271" max="16384"/>
+    <col width="12.59765625" customWidth="1" style="5" min="33" max="285"/>
+    <col width="12.59765625" customWidth="1" style="5" min="286" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="27.75" customFormat="1" customHeight="1" s="11">
@@ -802,7 +811,7 @@
           <t>source</t>
         </is>
       </c>
-      <c r="C1" s="26" t="inlineStr">
+      <c r="C1" s="45" t="inlineStr">
         <is>
           <t>USAF</t>
         </is>
@@ -963,7 +972,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="24" customHeight="1" s="45">
+    <row r="2" ht="24" customHeight="1" s="48">
       <c r="A2" s="2" t="n">
         <v>1</v>
       </c>
@@ -972,7 +981,7 @@
           <t>ogimet</t>
         </is>
       </c>
-      <c r="C2" s="27" t="n">
+      <c r="C2" s="46" t="n">
         <v>44211</v>
       </c>
       <c r="D2" s="2" t="n"/>
@@ -1011,13 +1020,13 @@
         </is>
       </c>
       <c r="O2" s="32" t="n">
-        <v>-39</v>
+        <v>-40.1</v>
       </c>
       <c r="P2" s="32" t="n">
-        <v>-22.9</v>
+        <v>-26.9</v>
       </c>
       <c r="Q2" s="32" t="n">
-        <v>-31.98</v>
+        <v>-31.19</v>
       </c>
       <c r="R2" s="23" t="inlineStr">
         <is>
@@ -1077,12 +1086,12 @@
       </c>
       <c r="AH2" s="2" t="n"/>
     </row>
-    <row r="3" ht="24" customHeight="1" s="45">
+    <row r="3" ht="24" customHeight="1" s="48">
       <c r="A3" s="2" t="n">
         <v>2</v>
       </c>
       <c r="B3" s="2" t="n"/>
-      <c r="C3" s="27" t="n"/>
+      <c r="C3" s="46" t="n"/>
       <c r="D3" s="2" t="n"/>
       <c r="E3" s="4" t="n"/>
       <c r="F3" s="39" t="n">
@@ -1117,10 +1126,10 @@
         </is>
       </c>
       <c r="O3" s="32" t="n">
-        <v>-39.9</v>
+        <v>-37.4</v>
       </c>
       <c r="P3" s="32" t="n">
-        <v>-20.2</v>
+        <v>-24.4</v>
       </c>
       <c r="Q3" s="32" t="n"/>
       <c r="R3" s="23" t="n"/>
@@ -1181,12 +1190,12 @@
       </c>
       <c r="AH3" s="2" t="n"/>
     </row>
-    <row r="4" ht="24" customHeight="1" s="45">
+    <row r="4" ht="24" customHeight="1" s="48">
       <c r="A4" s="2" t="n">
         <v>3</v>
       </c>
       <c r="B4" s="2" t="n"/>
-      <c r="C4" s="27" t="n"/>
+      <c r="C4" s="46" t="n"/>
       <c r="D4" s="2" t="n"/>
       <c r="E4" s="4" t="n"/>
       <c r="F4" s="39" t="n">
@@ -1221,10 +1230,10 @@
         </is>
       </c>
       <c r="O4" s="32" t="n">
-        <v>-39.2</v>
+        <v>-38.3</v>
       </c>
       <c r="P4" s="32" t="n">
-        <v>-22.1</v>
+        <v>-23.1</v>
       </c>
       <c r="Q4" s="32" t="n"/>
       <c r="R4" s="23" t="n"/>
@@ -1281,12 +1290,12 @@
       </c>
       <c r="AH4" s="2" t="n"/>
     </row>
-    <row r="5" ht="24" customHeight="1" s="45">
+    <row r="5" ht="24" customHeight="1" s="48">
       <c r="A5" s="2" t="n">
         <v>4</v>
       </c>
       <c r="B5" s="2" t="n"/>
-      <c r="C5" s="27" t="n"/>
+      <c r="C5" s="46" t="n"/>
       <c r="D5" s="2" t="n"/>
       <c r="E5" s="4" t="n"/>
       <c r="F5" s="39" t="n">
@@ -1317,10 +1326,10 @@
       </c>
       <c r="N5" s="2" t="n"/>
       <c r="O5" s="32" t="n">
-        <v>-34.7</v>
+        <v>-35.9</v>
       </c>
       <c r="P5" s="32" t="n">
-        <v>-20</v>
+        <v>-15.4</v>
       </c>
       <c r="Q5" s="32" t="n"/>
       <c r="R5" s="23" t="n"/>
@@ -1377,12 +1386,12 @@
       </c>
       <c r="AH5" s="2" t="n"/>
     </row>
-    <row r="6" ht="24" customHeight="1" s="45">
+    <row r="6" ht="24" customHeight="1" s="48">
       <c r="A6" s="2" t="n">
         <v>5</v>
       </c>
       <c r="B6" s="2" t="n"/>
-      <c r="C6" s="27" t="n"/>
+      <c r="C6" s="46" t="n"/>
       <c r="D6" s="2" t="n"/>
       <c r="E6" s="4" t="n"/>
       <c r="F6" s="39" t="n">
@@ -1417,10 +1426,10 @@
         </is>
       </c>
       <c r="O6" s="32" t="n">
-        <v>-35.5</v>
+        <v>-33</v>
       </c>
       <c r="P6" s="32" t="n">
-        <v>-19.3</v>
+        <v>-10.4</v>
       </c>
       <c r="Q6" s="32" t="n"/>
       <c r="R6" s="23" t="n"/>
@@ -1477,12 +1486,12 @@
       </c>
       <c r="AH6" s="2" t="n"/>
     </row>
-    <row r="7" ht="24" customHeight="1" s="45">
+    <row r="7" ht="24" customHeight="1" s="48">
       <c r="A7" s="2" t="n">
         <v>6</v>
       </c>
       <c r="B7" s="2" t="n"/>
-      <c r="C7" s="27" t="n"/>
+      <c r="C7" s="46" t="n"/>
       <c r="D7" s="2" t="n"/>
       <c r="E7" s="4" t="n"/>
       <c r="F7" s="39" t="n">
@@ -1517,10 +1526,10 @@
         </is>
       </c>
       <c r="O7" s="32" t="n">
-        <v>-30.7</v>
+        <v>-32.4</v>
       </c>
       <c r="P7" s="32" t="n">
-        <v>-20.5</v>
+        <v>-18.7</v>
       </c>
       <c r="Q7" s="32" t="n"/>
       <c r="R7" s="23" t="n"/>
@@ -1577,7 +1586,7 @@
       </c>
       <c r="AH7" s="2" t="n"/>
     </row>
-    <row r="8" ht="24" customHeight="1" s="45">
+    <row r="8" ht="24" customHeight="1" s="48">
       <c r="A8" s="2" t="n">
         <v>7</v>
       </c>
@@ -1586,7 +1595,7 @@
           <t>rp5</t>
         </is>
       </c>
-      <c r="C8" s="27" t="n">
+      <c r="C8" s="46" t="n">
         <v>44243</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -1625,13 +1634,13 @@
       </c>
       <c r="N8" s="2" t="n"/>
       <c r="O8" s="32" t="n">
-        <v>-27</v>
+        <v>-30.7</v>
       </c>
       <c r="P8" s="32" t="n">
-        <v>-11.2</v>
+        <v>-15.2</v>
       </c>
       <c r="Q8" s="32" t="n">
-        <v>-20.6</v>
+        <v>-23.9</v>
       </c>
       <c r="R8" s="23" t="inlineStr">
         <is>
@@ -1691,7 +1700,7 @@
       </c>
       <c r="AH8" s="2" t="n"/>
     </row>
-    <row r="9" ht="24" customHeight="1" s="45">
+    <row r="9" ht="24" customHeight="1" s="48">
       <c r="A9" s="2" t="n">
         <v>8</v>
       </c>
@@ -1700,7 +1709,7 @@
           <t>rp5</t>
         </is>
       </c>
-      <c r="C9" s="27" t="n">
+      <c r="C9" s="46" t="n">
         <v>44212</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -1737,13 +1746,13 @@
       </c>
       <c r="N9" s="2" t="n"/>
       <c r="O9" s="32" t="n">
-        <v>-32.4</v>
+        <v>-35.9</v>
       </c>
       <c r="P9" s="32" t="n">
-        <v>-14.4</v>
+        <v>-20.5</v>
       </c>
       <c r="Q9" s="32" t="n">
-        <v>-24.81</v>
+        <v>-28.34</v>
       </c>
       <c r="R9" s="23" t="inlineStr">
         <is>
@@ -1807,7 +1816,7 @@
       </c>
       <c r="AH9" s="2" t="n"/>
     </row>
-    <row r="10" ht="24" customHeight="1" s="45">
+    <row r="10" ht="24" customHeight="1" s="48">
       <c r="A10" s="2" t="n">
         <v>9</v>
       </c>
@@ -1816,7 +1825,7 @@
           <t>rp5</t>
         </is>
       </c>
-      <c r="C10" s="27" t="n">
+      <c r="C10" s="46" t="n">
         <v>44221</v>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -1853,13 +1862,13 @@
       </c>
       <c r="N10" s="3" t="n"/>
       <c r="O10" s="32" t="n">
-        <v>-41.3</v>
+        <v>-30.9</v>
       </c>
       <c r="P10" s="32" t="n">
-        <v>-20.7</v>
+        <v>-21.7</v>
       </c>
       <c r="Q10" s="32" t="n">
-        <v>-31.07</v>
+        <v>-27</v>
       </c>
       <c r="R10" s="23" t="inlineStr">
         <is>
@@ -1919,7 +1928,7 @@
       </c>
       <c r="AH10" s="2" t="n"/>
     </row>
-    <row r="11" ht="24" customHeight="1" s="45">
+    <row r="11" ht="24" customHeight="1" s="48">
       <c r="A11" s="2" t="n">
         <v>10</v>
       </c>
@@ -1928,7 +1937,7 @@
           <t>rp5</t>
         </is>
       </c>
-      <c r="C11" s="27" t="n">
+      <c r="C11" s="46" t="n">
         <v>44224</v>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -1969,13 +1978,13 @@
         </is>
       </c>
       <c r="O11" s="32" t="n">
-        <v>-40.7</v>
+        <v>-33.1</v>
       </c>
       <c r="P11" s="32" t="n">
-        <v>-17.5</v>
+        <v>-16</v>
       </c>
       <c r="Q11" s="32" t="n">
-        <v>-28.37</v>
+        <v>-24.35</v>
       </c>
       <c r="R11" s="23" t="inlineStr">
         <is>
@@ -2035,7 +2044,7 @@
       </c>
       <c r="AH11" s="2" t="n"/>
     </row>
-    <row r="12" ht="24" customHeight="1" s="45">
+    <row r="12" ht="24" customHeight="1" s="48">
       <c r="A12" s="2" t="n">
         <v>11</v>
       </c>
@@ -2044,7 +2053,7 @@
           <t>rp5</t>
         </is>
       </c>
-      <c r="C12" s="27" t="n">
+      <c r="C12" s="46" t="n">
         <v>44225</v>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -2081,13 +2090,13 @@
       </c>
       <c r="N12" s="2" t="n"/>
       <c r="O12" s="32" t="n">
-        <v>-37.3</v>
+        <v>-32.2</v>
       </c>
       <c r="P12" s="32" t="n">
-        <v>-18.6</v>
+        <v>-15</v>
       </c>
       <c r="Q12" s="32" t="n">
-        <v>-30.52</v>
+        <v>-24.91</v>
       </c>
       <c r="R12" s="23" t="inlineStr">
         <is>
@@ -2147,7 +2156,7 @@
       </c>
       <c r="AH12" s="2" t="n"/>
     </row>
-    <row r="13" ht="24" customHeight="1" s="45">
+    <row r="13" ht="24" customHeight="1" s="48">
       <c r="A13" s="2" t="n">
         <v>12</v>
       </c>
@@ -2156,7 +2165,7 @@
           <t>rp5</t>
         </is>
       </c>
-      <c r="C13" s="27" t="n">
+      <c r="C13" s="46" t="n">
         <v>44203</v>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -2197,13 +2206,13 @@
         </is>
       </c>
       <c r="O13" s="32" t="n">
-        <v>-27.7</v>
+        <v>-33.1</v>
       </c>
       <c r="P13" s="32" t="n">
-        <v>-20.4</v>
+        <v>-21.3</v>
       </c>
       <c r="Q13" s="32" t="n">
-        <v>-24.36</v>
+        <v>-28.31</v>
       </c>
       <c r="R13" s="23" t="inlineStr">
         <is>
@@ -2263,7 +2272,7 @@
       </c>
       <c r="AH13" s="2" t="n"/>
     </row>
-    <row r="14" ht="24" customHeight="1" s="45">
+    <row r="14" ht="24" customHeight="1" s="48">
       <c r="A14" s="2" t="n">
         <v>13</v>
       </c>
@@ -2272,7 +2281,7 @@
           <t>rp5</t>
         </is>
       </c>
-      <c r="C14" s="27" t="n">
+      <c r="C14" s="46" t="n">
         <v>44292</v>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -2309,13 +2318,13 @@
       </c>
       <c r="N14" s="2" t="n"/>
       <c r="O14" s="32" t="n">
-        <v>-21.6</v>
+        <v>-20.5</v>
       </c>
       <c r="P14" s="32" t="n">
-        <v>-16.2</v>
+        <v>-7.9</v>
       </c>
       <c r="Q14" s="32" t="n">
-        <v>-19.35</v>
+        <v>-15.07</v>
       </c>
       <c r="R14" s="23" t="inlineStr">
         <is>
@@ -2379,12 +2388,12 @@
       </c>
       <c r="AH14" s="2" t="n"/>
     </row>
-    <row r="15" ht="24" customHeight="1" s="45">
+    <row r="15" ht="24" customHeight="1" s="48">
       <c r="A15" s="2" t="n">
         <v>14</v>
       </c>
       <c r="B15" s="2" t="n"/>
-      <c r="C15" s="27" t="n"/>
+      <c r="C15" s="46" t="n"/>
       <c r="D15" s="2" t="n"/>
       <c r="E15" s="4" t="n"/>
       <c r="F15" s="39" t="n">
@@ -2414,8 +2423,12 @@
         </is>
       </c>
       <c r="N15" s="2" t="n"/>
-      <c r="O15" s="32" t="n"/>
-      <c r="P15" s="32" t="n"/>
+      <c r="O15" s="32" t="n">
+        <v>-34.5</v>
+      </c>
+      <c r="P15" s="32" t="n">
+        <v>-12</v>
+      </c>
       <c r="Q15" s="32" t="n"/>
       <c r="R15" s="23" t="n"/>
       <c r="S15" s="37" t="n"/>
@@ -2467,7 +2480,7 @@
       </c>
       <c r="AH15" s="2" t="n"/>
     </row>
-    <row r="16" ht="24" customHeight="1" s="45">
+    <row r="16" ht="24" customHeight="1" s="48">
       <c r="A16" s="2" t="n">
         <v>15</v>
       </c>
@@ -2476,7 +2489,7 @@
           <t>ogimet</t>
         </is>
       </c>
-      <c r="C16" s="27" t="n">
+      <c r="C16" s="46" t="n">
         <v>44291</v>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -2567,12 +2580,12 @@
       </c>
       <c r="AH16" s="2" t="n"/>
     </row>
-    <row r="17" ht="24" customHeight="1" s="45">
+    <row r="17" ht="24" customHeight="1" s="48">
       <c r="A17" s="2" t="n">
         <v>16</v>
       </c>
       <c r="B17" s="2" t="n"/>
-      <c r="C17" s="27" t="n"/>
+      <c r="C17" s="46" t="n"/>
       <c r="D17" s="2" t="n"/>
       <c r="E17" s="4" t="n"/>
       <c r="F17" s="39" t="n">
@@ -2659,12 +2672,12 @@
       </c>
       <c r="AH17" s="2" t="n"/>
     </row>
-    <row r="18" ht="24" customHeight="1" s="45">
+    <row r="18" ht="24" customHeight="1" s="48">
       <c r="A18" s="2" t="n">
         <v>17</v>
       </c>
       <c r="B18" s="2" t="n"/>
-      <c r="C18" s="27" t="n"/>
+      <c r="C18" s="46" t="n"/>
       <c r="D18" s="2" t="n"/>
       <c r="E18" s="4" t="n"/>
       <c r="F18" s="39" t="n">
@@ -2747,7 +2760,7 @@
       </c>
       <c r="AH18" s="2" t="n"/>
     </row>
-    <row r="19" ht="24" customHeight="1" s="45">
+    <row r="19" ht="24" customHeight="1" s="48">
       <c r="A19" s="2" t="n">
         <v>18</v>
       </c>
@@ -2756,7 +2769,7 @@
           <t>ogimet</t>
         </is>
       </c>
-      <c r="C19" s="27" t="n">
+      <c r="C19" s="46" t="n">
         <v>44275</v>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -2847,7 +2860,7 @@
       </c>
       <c r="AH19" s="2" t="n"/>
     </row>
-    <row r="20" ht="24" customHeight="1" s="45">
+    <row r="20" ht="24" customHeight="1" s="48">
       <c r="A20" s="2" t="n">
         <v>19</v>
       </c>
@@ -2856,7 +2869,7 @@
           <t>ogimet</t>
         </is>
       </c>
-      <c r="C20" s="27" t="n">
+      <c r="C20" s="46" t="n">
         <v>44284</v>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -2947,12 +2960,12 @@
       </c>
       <c r="AH20" s="2" t="n"/>
     </row>
-    <row r="21" ht="24" customHeight="1" s="45">
+    <row r="21" ht="24" customHeight="1" s="48">
       <c r="A21" s="2" t="n">
         <v>20</v>
       </c>
       <c r="B21" s="2" t="n"/>
-      <c r="C21" s="27" t="n"/>
+      <c r="C21" s="46" t="n"/>
       <c r="D21" s="2" t="n"/>
       <c r="E21" s="4" t="n"/>
       <c r="F21" s="39" t="n">
@@ -3035,12 +3048,12 @@
       </c>
       <c r="AH21" s="2" t="n"/>
     </row>
-    <row r="22" ht="24" customHeight="1" s="45">
+    <row r="22" ht="24" customHeight="1" s="48">
       <c r="A22" s="2" t="n">
         <v>21</v>
       </c>
       <c r="B22" s="2" t="n"/>
-      <c r="C22" s="27" t="n"/>
+      <c r="C22" s="46" t="n"/>
       <c r="D22" s="2" t="n"/>
       <c r="E22" s="4" t="n"/>
       <c r="F22" s="39" t="n">
@@ -3123,12 +3136,12 @@
       </c>
       <c r="AH22" s="2" t="n"/>
     </row>
-    <row r="23" ht="24" customHeight="1" s="45">
+    <row r="23" ht="24" customHeight="1" s="48">
       <c r="A23" s="2" t="n">
         <v>22</v>
       </c>
       <c r="B23" s="2" t="n"/>
-      <c r="C23" s="27" t="n"/>
+      <c r="C23" s="46" t="n"/>
       <c r="D23" s="2" t="n"/>
       <c r="E23" s="4" t="n"/>
       <c r="F23" s="39" t="n">
@@ -3211,7 +3224,7 @@
       </c>
       <c r="AH23" s="2" t="n"/>
     </row>
-    <row r="24" ht="24" customHeight="1" s="45">
+    <row r="24" ht="24" customHeight="1" s="48">
       <c r="A24" s="2" t="n">
         <v>23</v>
       </c>
@@ -3220,7 +3233,7 @@
           <t>ogimet</t>
         </is>
       </c>
-      <c r="C24" s="27" t="n">
+      <c r="C24" s="46" t="n">
         <v>44265</v>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -3311,12 +3324,12 @@
       </c>
       <c r="AH24" s="2" t="n"/>
     </row>
-    <row r="25" ht="24" customHeight="1" s="45">
+    <row r="25" ht="24" customHeight="1" s="48">
       <c r="A25" s="2" t="n">
         <v>24</v>
       </c>
       <c r="B25" s="2" t="n"/>
-      <c r="C25" s="27" t="n"/>
+      <c r="C25" s="46" t="n"/>
       <c r="D25" s="2" t="n"/>
       <c r="E25" s="4" t="n"/>
       <c r="F25" s="39" t="n">
@@ -3399,12 +3412,12 @@
       </c>
       <c r="AH25" s="2" t="n"/>
     </row>
-    <row r="26" ht="24" customHeight="1" s="45">
+    <row r="26" ht="24" customHeight="1" s="48">
       <c r="A26" s="2" t="n">
         <v>25</v>
       </c>
       <c r="B26" s="2" t="n"/>
-      <c r="C26" s="27" t="n"/>
+      <c r="C26" s="46" t="n"/>
       <c r="D26" s="2" t="n"/>
       <c r="E26" s="4" t="n"/>
       <c r="F26" s="39" t="n">
@@ -3487,7 +3500,7 @@
       </c>
       <c r="AH26" s="2" t="n"/>
     </row>
-    <row r="27" ht="24" customHeight="1" s="45">
+    <row r="27" ht="24" customHeight="1" s="48">
       <c r="A27" s="2" t="n">
         <v>26</v>
       </c>
@@ -3496,7 +3509,7 @@
           <t>ogimet</t>
         </is>
       </c>
-      <c r="C27" s="27" t="n">
+      <c r="C27" s="46" t="n">
         <v>44277</v>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -3591,12 +3604,12 @@
       </c>
       <c r="AH27" s="2" t="n"/>
     </row>
-    <row r="28" ht="24" customHeight="1" s="45">
+    <row r="28" ht="24" customHeight="1" s="48">
       <c r="A28" s="2" t="n">
         <v>27</v>
       </c>
       <c r="B28" s="2" t="n"/>
-      <c r="C28" s="27" t="n"/>
+      <c r="C28" s="46" t="n"/>
       <c r="D28" s="2" t="n"/>
       <c r="E28" s="4" t="n"/>
       <c r="F28" s="39" t="n">
@@ -3675,12 +3688,12 @@
       <c r="AG28" s="2" t="n"/>
       <c r="AH28" s="2" t="n"/>
     </row>
-    <row r="29" ht="24" customHeight="1" s="45">
+    <row r="29" ht="24" customHeight="1" s="48">
       <c r="A29" s="2" t="n">
         <v>28</v>
       </c>
       <c r="B29" s="2" t="n"/>
-      <c r="C29" s="27" t="n"/>
+      <c r="C29" s="46" t="n"/>
       <c r="D29" s="2" t="n"/>
       <c r="E29" s="4" t="n"/>
       <c r="F29" s="39" t="n">
@@ -3763,12 +3776,12 @@
       </c>
       <c r="AH29" s="2" t="n"/>
     </row>
-    <row r="30" ht="24" customHeight="1" s="45">
+    <row r="30" ht="24" customHeight="1" s="48">
       <c r="A30" s="2" t="n">
         <v>29</v>
       </c>
       <c r="B30" s="2" t="n"/>
-      <c r="C30" s="27" t="n"/>
+      <c r="C30" s="46" t="n"/>
       <c r="D30" s="2" t="n"/>
       <c r="E30" s="4" t="n"/>
       <c r="F30" s="39" t="n">
@@ -3851,12 +3864,12 @@
       </c>
       <c r="AH30" s="2" t="n"/>
     </row>
-    <row r="31" ht="24" customHeight="1" s="45">
+    <row r="31" ht="24" customHeight="1" s="48">
       <c r="A31" s="2" t="n">
         <v>30</v>
       </c>
       <c r="B31" s="2" t="n"/>
-      <c r="C31" s="27" t="n"/>
+      <c r="C31" s="46" t="n"/>
       <c r="D31" s="2" t="n"/>
       <c r="E31" s="4" t="n"/>
       <c r="F31" s="39" t="n">
@@ -3939,7 +3952,7 @@
       </c>
       <c r="AH31" s="2" t="n"/>
     </row>
-    <row r="32" ht="24" customHeight="1" s="45">
+    <row r="32" ht="24" customHeight="1" s="48">
       <c r="A32" s="2" t="n">
         <v>31</v>
       </c>
@@ -3948,7 +3961,7 @@
           <t>ogimet</t>
         </is>
       </c>
-      <c r="C32" s="27" t="n">
+      <c r="C32" s="46" t="n">
         <v>44207</v>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -4039,7 +4052,7 @@
       </c>
       <c r="AH32" s="2" t="n"/>
     </row>
-    <row r="33" ht="24" customHeight="1" s="45">
+    <row r="33" ht="24" customHeight="1" s="48">
       <c r="A33" s="2" t="n">
         <v>32</v>
       </c>
@@ -4048,7 +4061,7 @@
           <t>ogimet</t>
         </is>
       </c>
-      <c r="C33" s="27" t="n">
+      <c r="C33" s="46" t="n">
         <v>44231</v>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -4139,12 +4152,12 @@
       <c r="AG33" s="2" t="n"/>
       <c r="AH33" s="2" t="n"/>
     </row>
-    <row r="34" ht="24" customHeight="1" s="45">
+    <row r="34" ht="24" customHeight="1" s="48">
       <c r="A34" s="2" t="n">
         <v>33</v>
       </c>
       <c r="B34" s="2" t="n"/>
-      <c r="C34" s="27" t="n"/>
+      <c r="C34" s="46" t="n"/>
       <c r="D34" s="2" t="n"/>
       <c r="E34" s="4" t="n"/>
       <c r="F34" s="39" t="n">
@@ -4223,12 +4236,12 @@
       <c r="AG34" s="2" t="n"/>
       <c r="AH34" s="2" t="n"/>
     </row>
-    <row r="35" ht="24" customHeight="1" s="45">
+    <row r="35" ht="24" customHeight="1" s="48">
       <c r="A35" s="2" t="n">
         <v>34</v>
       </c>
       <c r="B35" s="2" t="n"/>
-      <c r="C35" s="27" t="n"/>
+      <c r="C35" s="46" t="n"/>
       <c r="D35" s="2" t="n"/>
       <c r="E35" s="4" t="n"/>
       <c r="F35" s="39" t="n">
@@ -4311,12 +4324,12 @@
       </c>
       <c r="AH35" s="2" t="n"/>
     </row>
-    <row r="36" ht="24" customHeight="1" s="45">
+    <row r="36" ht="24" customHeight="1" s="48">
       <c r="A36" s="2" t="n">
         <v>35</v>
       </c>
       <c r="B36" s="2" t="n"/>
-      <c r="C36" s="27" t="n"/>
+      <c r="C36" s="46" t="n"/>
       <c r="D36" s="2" t="n"/>
       <c r="E36" s="4" t="n"/>
       <c r="F36" s="39" t="n">
@@ -4399,12 +4412,12 @@
       </c>
       <c r="AH36" s="2" t="n"/>
     </row>
-    <row r="37" ht="24" customHeight="1" s="45">
+    <row r="37" ht="24" customHeight="1" s="48">
       <c r="A37" s="2" t="n">
         <v>36</v>
       </c>
       <c r="B37" s="2" t="n"/>
-      <c r="C37" s="27" t="n"/>
+      <c r="C37" s="46" t="n"/>
       <c r="D37" s="2" t="n"/>
       <c r="E37" s="4" t="n"/>
       <c r="F37" s="39" t="n">
@@ -4487,12 +4500,12 @@
       </c>
       <c r="AH37" s="2" t="n"/>
     </row>
-    <row r="38" ht="24" customHeight="1" s="45">
+    <row r="38" ht="24" customHeight="1" s="48">
       <c r="A38" s="2" t="n">
         <v>37</v>
       </c>
       <c r="B38" s="2" t="n"/>
-      <c r="C38" s="27" t="n"/>
+      <c r="C38" s="46" t="n"/>
       <c r="D38" s="2" t="n"/>
       <c r="E38" s="4" t="n"/>
       <c r="F38" s="39" t="n">
@@ -4575,12 +4588,12 @@
       </c>
       <c r="AH38" s="2" t="n"/>
     </row>
-    <row r="39" ht="24" customHeight="1" s="45">
+    <row r="39" ht="24" customHeight="1" s="48">
       <c r="A39" s="2" t="n">
         <v>38</v>
       </c>
       <c r="B39" s="2" t="n"/>
-      <c r="C39" s="27" t="n"/>
+      <c r="C39" s="46" t="n"/>
       <c r="D39" s="2" t="n"/>
       <c r="E39" s="4" t="n"/>
       <c r="F39" s="39" t="n">
@@ -4659,12 +4672,12 @@
       <c r="AG39" s="2" t="n"/>
       <c r="AH39" s="2" t="n"/>
     </row>
-    <row r="40" ht="24" customHeight="1" s="45">
+    <row r="40" ht="24" customHeight="1" s="48">
       <c r="A40" s="2" t="n">
         <v>39</v>
       </c>
       <c r="B40" s="2" t="n"/>
-      <c r="C40" s="27" t="n"/>
+      <c r="C40" s="46" t="n"/>
       <c r="D40" s="2" t="n"/>
       <c r="E40" s="4" t="n"/>
       <c r="F40" s="39" t="n">
@@ -4747,12 +4760,12 @@
       </c>
       <c r="AH40" s="2" t="n"/>
     </row>
-    <row r="41" ht="24" customHeight="1" s="45">
+    <row r="41" ht="24" customHeight="1" s="48">
       <c r="A41" s="2" t="n">
         <v>40</v>
       </c>
       <c r="B41" s="2" t="n"/>
-      <c r="C41" s="27" t="n"/>
+      <c r="C41" s="46" t="n"/>
       <c r="D41" s="2" t="n"/>
       <c r="E41" s="4" t="n"/>
       <c r="F41" s="39" t="n">
@@ -4831,12 +4844,12 @@
       <c r="AG41" s="2" t="n"/>
       <c r="AH41" s="2" t="n"/>
     </row>
-    <row r="42" ht="24" customHeight="1" s="45">
+    <row r="42" ht="24" customHeight="1" s="48">
       <c r="A42" s="2" t="n">
         <v>41</v>
       </c>
       <c r="B42" s="2" t="n"/>
-      <c r="C42" s="27" t="n"/>
+      <c r="C42" s="46" t="n"/>
       <c r="D42" s="2" t="n"/>
       <c r="E42" s="4" t="n"/>
       <c r="F42" s="39" t="n">
@@ -4919,12 +4932,12 @@
       </c>
       <c r="AH42" s="2" t="n"/>
     </row>
-    <row r="43" ht="24" customHeight="1" s="45">
+    <row r="43" ht="24" customHeight="1" s="48">
       <c r="A43" s="2" t="n">
         <v>42</v>
       </c>
       <c r="B43" s="2" t="n"/>
-      <c r="C43" s="27" t="n"/>
+      <c r="C43" s="46" t="n"/>
       <c r="D43" s="2" t="n"/>
       <c r="E43" s="4" t="n"/>
       <c r="F43" s="39" t="n">
@@ -5007,12 +5020,12 @@
       </c>
       <c r="AH43" s="2" t="n"/>
     </row>
-    <row r="44" ht="24" customHeight="1" s="45">
+    <row r="44" ht="24" customHeight="1" s="48">
       <c r="A44" s="2" t="n">
         <v>43</v>
       </c>
       <c r="B44" s="2" t="n"/>
-      <c r="C44" s="27" t="n"/>
+      <c r="C44" s="46" t="n"/>
       <c r="D44" s="2" t="n"/>
       <c r="E44" s="4" t="n"/>
       <c r="F44" s="39" t="n">
@@ -5095,7 +5108,7 @@
       </c>
       <c r="AH44" s="2" t="n"/>
     </row>
-    <row r="45" ht="24" customHeight="1" s="45">
+    <row r="45" ht="24" customHeight="1" s="48">
       <c r="A45" s="2" t="n">
         <v>44</v>
       </c>
@@ -5104,7 +5117,7 @@
           <t>ogimet</t>
         </is>
       </c>
-      <c r="C45" s="27" t="n">
+      <c r="C45" s="46" t="n">
         <v>44215</v>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -5195,12 +5208,12 @@
       </c>
       <c r="AH45" s="2" t="n"/>
     </row>
-    <row r="46" ht="24" customHeight="1" s="45">
+    <row r="46" ht="24" customHeight="1" s="48">
       <c r="A46" s="2" t="n">
         <v>45</v>
       </c>
       <c r="B46" s="2" t="n"/>
-      <c r="C46" s="27" t="n"/>
+      <c r="C46" s="46" t="n"/>
       <c r="D46" s="2" t="n"/>
       <c r="E46" s="4" t="n"/>
       <c r="F46" s="39" t="n">
@@ -5283,12 +5296,12 @@
       </c>
       <c r="AH46" s="2" t="n"/>
     </row>
-    <row r="47" ht="24" customHeight="1" s="45">
+    <row r="47" ht="24" customHeight="1" s="48">
       <c r="A47" s="2" t="n">
         <v>46</v>
       </c>
       <c r="B47" s="2" t="n"/>
-      <c r="C47" s="27" t="n"/>
+      <c r="C47" s="46" t="n"/>
       <c r="D47" s="2" t="n"/>
       <c r="E47" s="4" t="n"/>
       <c r="F47" s="39" t="n">
@@ -5371,7 +5384,7 @@
       </c>
       <c r="AH47" s="2" t="n"/>
     </row>
-    <row r="48" ht="24" customHeight="1" s="45">
+    <row r="48" ht="24" customHeight="1" s="48">
       <c r="A48" s="2" t="n">
         <v>47</v>
       </c>
@@ -5380,7 +5393,7 @@
           <t>ogimet</t>
         </is>
       </c>
-      <c r="C48" s="27" t="n">
+      <c r="C48" s="46" t="n">
         <v>44213</v>
       </c>
       <c r="D48" s="2" t="inlineStr">
@@ -5471,12 +5484,12 @@
       </c>
       <c r="AH48" s="2" t="n"/>
     </row>
-    <row r="49" ht="24" customHeight="1" s="45">
+    <row r="49" ht="24" customHeight="1" s="48">
       <c r="A49" s="2" t="n">
         <v>48</v>
       </c>
       <c r="B49" s="2" t="n"/>
-      <c r="C49" s="27" t="n"/>
+      <c r="C49" s="46" t="n"/>
       <c r="D49" s="2" t="n"/>
       <c r="E49" s="4" t="n"/>
       <c r="F49" s="39" t="n">
@@ -5559,12 +5572,12 @@
       </c>
       <c r="AH49" s="2" t="n"/>
     </row>
-    <row r="50" ht="24" customHeight="1" s="45">
+    <row r="50" ht="24" customHeight="1" s="48">
       <c r="A50" s="2" t="n">
         <v>49</v>
       </c>
       <c r="B50" s="2" t="n"/>
-      <c r="C50" s="27" t="n"/>
+      <c r="C50" s="46" t="n"/>
       <c r="D50" s="2" t="n"/>
       <c r="E50" s="4" t="n"/>
       <c r="F50" s="39" t="n">
@@ -5643,12 +5656,12 @@
       <c r="AG50" s="2" t="n"/>
       <c r="AH50" s="2" t="n"/>
     </row>
-    <row r="51" ht="24" customHeight="1" s="45">
+    <row r="51" ht="24" customHeight="1" s="48">
       <c r="A51" s="2" t="n">
         <v>50</v>
       </c>
       <c r="B51" s="2" t="n"/>
-      <c r="C51" s="27" t="n"/>
+      <c r="C51" s="46" t="n"/>
       <c r="D51" s="2" t="n"/>
       <c r="E51" s="4" t="n"/>
       <c r="F51" s="39" t="n">
@@ -5727,12 +5740,12 @@
       <c r="AG51" s="2" t="n"/>
       <c r="AH51" s="2" t="n"/>
     </row>
-    <row r="52" ht="24" customHeight="1" s="45">
+    <row r="52" ht="24" customHeight="1" s="48">
       <c r="A52" s="2" t="n">
         <v>51</v>
       </c>
       <c r="B52" s="2" t="n"/>
-      <c r="C52" s="27" t="n"/>
+      <c r="C52" s="46" t="n"/>
       <c r="D52" s="2" t="n"/>
       <c r="E52" s="4" t="n"/>
       <c r="F52" s="39" t="n">
@@ -5815,12 +5828,12 @@
       </c>
       <c r="AH52" s="2" t="n"/>
     </row>
-    <row r="53" ht="24" customHeight="1" s="45">
+    <row r="53" ht="24" customHeight="1" s="48">
       <c r="A53" s="2" t="n">
         <v>52</v>
       </c>
       <c r="B53" s="2" t="n"/>
-      <c r="C53" s="27" t="n"/>
+      <c r="C53" s="46" t="n"/>
       <c r="D53" s="2" t="n"/>
       <c r="E53" s="4" t="n"/>
       <c r="F53" s="39" t="n">
@@ -5903,12 +5916,12 @@
       </c>
       <c r="AH53" s="2" t="n"/>
     </row>
-    <row r="54" ht="24" customHeight="1" s="45">
+    <row r="54" ht="24" customHeight="1" s="48">
       <c r="A54" s="2" t="n">
         <v>53</v>
       </c>
       <c r="B54" s="2" t="n"/>
-      <c r="C54" s="27" t="n"/>
+      <c r="C54" s="46" t="n"/>
       <c r="D54" s="2" t="n"/>
       <c r="E54" s="4" t="n"/>
       <c r="F54" s="39" t="n">
@@ -5991,12 +6004,12 @@
       </c>
       <c r="AH54" s="2" t="n"/>
     </row>
-    <row r="55" ht="24" customHeight="1" s="45">
+    <row r="55" ht="24" customHeight="1" s="48">
       <c r="A55" s="2" t="n">
         <v>54</v>
       </c>
       <c r="B55" s="2" t="n"/>
-      <c r="C55" s="27" t="n"/>
+      <c r="C55" s="46" t="n"/>
       <c r="D55" s="2" t="n"/>
       <c r="E55" s="4" t="n"/>
       <c r="F55" s="39" t="n">
@@ -6079,12 +6092,12 @@
       </c>
       <c r="AH55" s="2" t="n"/>
     </row>
-    <row r="56" ht="24" customHeight="1" s="45">
+    <row r="56" ht="24" customHeight="1" s="48">
       <c r="A56" s="2" t="n">
         <v>55</v>
       </c>
       <c r="B56" s="2" t="n"/>
-      <c r="C56" s="27" t="n"/>
+      <c r="C56" s="46" t="n"/>
       <c r="D56" s="2" t="n"/>
       <c r="E56" s="4" t="n"/>
       <c r="F56" s="39" t="n">
@@ -6167,12 +6180,12 @@
       </c>
       <c r="AH56" s="2" t="n"/>
     </row>
-    <row r="57" ht="24" customHeight="1" s="45">
+    <row r="57" ht="24" customHeight="1" s="48">
       <c r="A57" s="2" t="n">
         <v>56</v>
       </c>
       <c r="B57" s="2" t="n"/>
-      <c r="C57" s="27" t="n"/>
+      <c r="C57" s="46" t="n"/>
       <c r="D57" s="2" t="n"/>
       <c r="E57" s="4" t="n"/>
       <c r="F57" s="39" t="n">
@@ -6251,12 +6264,12 @@
       <c r="AG57" s="2" t="n"/>
       <c r="AH57" s="2" t="n"/>
     </row>
-    <row r="58" ht="24" customHeight="1" s="45">
+    <row r="58" ht="24" customHeight="1" s="48">
       <c r="A58" s="2" t="n">
         <v>57</v>
       </c>
       <c r="B58" s="2" t="n"/>
-      <c r="C58" s="27" t="n"/>
+      <c r="C58" s="46" t="n"/>
       <c r="D58" s="2" t="n"/>
       <c r="E58" s="4" t="n"/>
       <c r="F58" s="39" t="n">
@@ -6339,12 +6352,12 @@
       </c>
       <c r="AH58" s="2" t="n"/>
     </row>
-    <row r="59" ht="24" customHeight="1" s="45">
+    <row r="59" ht="24" customHeight="1" s="48">
       <c r="A59" s="2" t="n">
         <v>58</v>
       </c>
       <c r="B59" s="2" t="n"/>
-      <c r="C59" s="27" t="n"/>
+      <c r="C59" s="46" t="n"/>
       <c r="D59" s="2" t="n"/>
       <c r="E59" s="4" t="n"/>
       <c r="F59" s="39" t="n">
@@ -6427,12 +6440,12 @@
       </c>
       <c r="AH59" s="2" t="n"/>
     </row>
-    <row r="60" ht="24" customHeight="1" s="45">
+    <row r="60" ht="24" customHeight="1" s="48">
       <c r="A60" s="2" t="n">
         <v>59</v>
       </c>
       <c r="B60" s="2" t="n"/>
-      <c r="C60" s="27" t="n"/>
+      <c r="C60" s="46" t="n"/>
       <c r="D60" s="2" t="n"/>
       <c r="E60" s="4" t="n"/>
       <c r="F60" s="39" t="n">
@@ -6515,12 +6528,12 @@
       </c>
       <c r="AH60" s="2" t="n"/>
     </row>
-    <row r="61" ht="24" customHeight="1" s="45">
+    <row r="61" ht="24" customHeight="1" s="48">
       <c r="A61" s="2" t="n">
         <v>60</v>
       </c>
       <c r="B61" s="2" t="n"/>
-      <c r="C61" s="27" t="n"/>
+      <c r="C61" s="46" t="n"/>
       <c r="D61" s="2" t="n"/>
       <c r="E61" s="4" t="n"/>
       <c r="F61" s="39" t="n">
@@ -6603,12 +6616,12 @@
       </c>
       <c r="AH61" s="2" t="n"/>
     </row>
-    <row r="62" ht="24" customHeight="1" s="45">
+    <row r="62" ht="24" customHeight="1" s="48">
       <c r="A62" s="2" t="n">
         <v>61</v>
       </c>
       <c r="B62" s="2" t="n"/>
-      <c r="C62" s="27" t="n"/>
+      <c r="C62" s="46" t="n"/>
       <c r="D62" s="2" t="n"/>
       <c r="E62" s="4" t="n"/>
       <c r="F62" s="39" t="n">
@@ -6691,7 +6704,7 @@
       </c>
       <c r="AH62" s="2" t="n"/>
     </row>
-    <row r="63" ht="24" customHeight="1" s="45">
+    <row r="63" ht="24" customHeight="1" s="48">
       <c r="A63" s="2" t="n">
         <v>62</v>
       </c>
@@ -6700,7 +6713,7 @@
           <t>ogimet</t>
         </is>
       </c>
-      <c r="C63" s="27" t="n">
+      <c r="C63" s="46" t="n">
         <v>44263</v>
       </c>
       <c r="D63" s="2" t="inlineStr">
@@ -6791,12 +6804,12 @@
       </c>
       <c r="AH63" s="2" t="n"/>
     </row>
-    <row r="64" ht="24" customHeight="1" s="45">
+    <row r="64" ht="24" customHeight="1" s="48">
       <c r="A64" s="2" t="n">
         <v>63</v>
       </c>
       <c r="B64" s="2" t="n"/>
-      <c r="C64" s="27" t="n"/>
+      <c r="C64" s="46" t="n"/>
       <c r="D64" s="2" t="n"/>
       <c r="E64" s="4" t="n"/>
       <c r="F64" s="39" t="n">
@@ -6879,12 +6892,12 @@
       </c>
       <c r="AH64" s="2" t="n"/>
     </row>
-    <row r="65" ht="24" customHeight="1" s="45">
+    <row r="65" ht="24" customHeight="1" s="48">
       <c r="A65" s="2" t="n">
         <v>64</v>
       </c>
       <c r="B65" s="2" t="n"/>
-      <c r="C65" s="27" t="n"/>
+      <c r="C65" s="46" t="n"/>
       <c r="D65" s="2" t="n"/>
       <c r="E65" s="4" t="n"/>
       <c r="F65" s="39" t="n">
@@ -6967,12 +6980,12 @@
       </c>
       <c r="AH65" s="2" t="n"/>
     </row>
-    <row r="66" ht="24" customHeight="1" s="45">
+    <row r="66" ht="24" customHeight="1" s="48">
       <c r="A66" s="2" t="n">
         <v>65</v>
       </c>
       <c r="B66" s="2" t="n"/>
-      <c r="C66" s="27" t="n"/>
+      <c r="C66" s="46" t="n"/>
       <c r="D66" s="2" t="n"/>
       <c r="E66" s="4" t="n"/>
       <c r="F66" s="39" t="n">
@@ -7055,12 +7068,12 @@
       </c>
       <c r="AH66" s="2" t="n"/>
     </row>
-    <row r="67" ht="24" customHeight="1" s="45">
+    <row r="67" ht="24" customHeight="1" s="48">
       <c r="A67" s="2" t="n">
         <v>66</v>
       </c>
       <c r="B67" s="2" t="n"/>
-      <c r="C67" s="27" t="n"/>
+      <c r="C67" s="46" t="n"/>
       <c r="D67" s="2" t="n"/>
       <c r="E67" s="4" t="n"/>
       <c r="F67" s="39" t="n">
@@ -7143,7 +7156,7 @@
       </c>
       <c r="AH67" s="2" t="n"/>
     </row>
-    <row r="68" ht="24" customHeight="1" s="45">
+    <row r="68" ht="24" customHeight="1" s="48">
       <c r="A68" s="2" t="n">
         <v>67</v>
       </c>
@@ -7152,7 +7165,7 @@
           <t>ogimet</t>
         </is>
       </c>
-      <c r="C68" s="27" t="n">
+      <c r="C68" s="46" t="n">
         <v>44229</v>
       </c>
       <c r="D68" s="2" t="inlineStr">
@@ -7243,12 +7256,12 @@
       </c>
       <c r="AH68" s="2" t="n"/>
     </row>
-    <row r="69" ht="24" customHeight="1" s="45">
+    <row r="69" ht="24" customHeight="1" s="48">
       <c r="A69" s="2" t="n">
         <v>68</v>
       </c>
       <c r="B69" s="2" t="n"/>
-      <c r="C69" s="27" t="n"/>
+      <c r="C69" s="46" t="n"/>
       <c r="D69" s="2" t="n"/>
       <c r="E69" s="4" t="n"/>
       <c r="F69" s="39" t="n">
@@ -7331,12 +7344,12 @@
       </c>
       <c r="AH69" s="2" t="n"/>
     </row>
-    <row r="70" ht="24" customHeight="1" s="45">
+    <row r="70" ht="24" customHeight="1" s="48">
       <c r="A70" s="2" t="n">
         <v>69</v>
       </c>
       <c r="B70" s="2" t="n"/>
-      <c r="C70" s="27" t="n"/>
+      <c r="C70" s="46" t="n"/>
       <c r="D70" s="2" t="n"/>
       <c r="E70" s="4" t="n"/>
       <c r="F70" s="39" t="n">
@@ -7419,12 +7432,12 @@
       </c>
       <c r="AH70" s="2" t="n"/>
     </row>
-    <row r="71" ht="24" customHeight="1" s="45">
+    <row r="71" ht="24" customHeight="1" s="48">
       <c r="A71" s="2" t="n">
         <v>70</v>
       </c>
       <c r="B71" s="2" t="n"/>
-      <c r="C71" s="27" t="n"/>
+      <c r="C71" s="46" t="n"/>
       <c r="D71" s="2" t="n"/>
       <c r="E71" s="4" t="n"/>
       <c r="F71" s="39" t="n">
@@ -7507,12 +7520,12 @@
       </c>
       <c r="AH71" s="2" t="n"/>
     </row>
-    <row r="72" ht="24" customHeight="1" s="45">
+    <row r="72" ht="24" customHeight="1" s="48">
       <c r="A72" s="2" t="n">
         <v>71</v>
       </c>
       <c r="B72" s="2" t="n"/>
-      <c r="C72" s="27" t="n"/>
+      <c r="C72" s="46" t="n"/>
       <c r="D72" s="2" t="n"/>
       <c r="E72" s="4" t="n"/>
       <c r="F72" s="39" t="n">
@@ -7595,12 +7608,12 @@
       </c>
       <c r="AH72" s="2" t="n"/>
     </row>
-    <row r="73" ht="24" customHeight="1" s="45">
+    <row r="73" ht="24" customHeight="1" s="48">
       <c r="A73" s="2" t="n">
         <v>72</v>
       </c>
       <c r="B73" s="2" t="n"/>
-      <c r="C73" s="27" t="n"/>
+      <c r="C73" s="46" t="n"/>
       <c r="D73" s="2" t="n"/>
       <c r="E73" s="4" t="n"/>
       <c r="F73" s="39" t="n">
@@ -7630,8 +7643,12 @@
         </is>
       </c>
       <c r="N73" s="2" t="n"/>
-      <c r="O73" s="32" t="n"/>
-      <c r="P73" s="32" t="n"/>
+      <c r="O73" s="32" t="n">
+        <v>-36.6</v>
+      </c>
+      <c r="P73" s="32" t="n">
+        <v>-13.1</v>
+      </c>
       <c r="Q73" s="32" t="n"/>
       <c r="R73" s="23" t="n"/>
       <c r="S73" s="37" t="n"/>
@@ -7683,12 +7700,12 @@
       </c>
       <c r="AH73" s="2" t="n"/>
     </row>
-    <row r="74" ht="24" customHeight="1" s="45">
+    <row r="74" ht="24" customHeight="1" s="48">
       <c r="A74" s="2" t="n">
         <v>73</v>
       </c>
       <c r="B74" s="2" t="n"/>
-      <c r="C74" s="27" t="n"/>
+      <c r="C74" s="46" t="n"/>
       <c r="D74" s="2" t="n"/>
       <c r="E74" s="4" t="n"/>
       <c r="F74" s="39" t="n">
@@ -7767,7 +7784,7 @@
       <c r="AG74" s="2" t="n"/>
       <c r="AH74" s="2" t="n"/>
     </row>
-    <row r="75" ht="24" customHeight="1" s="45">
+    <row r="75" ht="24" customHeight="1" s="48">
       <c r="A75" s="2" t="n">
         <v>74</v>
       </c>
@@ -7776,7 +7793,7 @@
           <t>ogimet</t>
         </is>
       </c>
-      <c r="C75" s="27" t="n">
+      <c r="C75" s="46" t="n">
         <v>31702</v>
       </c>
       <c r="D75" s="2" t="inlineStr">
@@ -7813,13 +7830,13 @@
       </c>
       <c r="N75" s="2" t="n"/>
       <c r="O75" s="32" t="n">
-        <v>-1.5</v>
+        <v>-17.6</v>
       </c>
       <c r="P75" s="32" t="n">
-        <v>0.7</v>
+        <v>-9.800000000000001</v>
       </c>
       <c r="Q75" s="32" t="n">
-        <v>-0.35</v>
+        <v>-14.19</v>
       </c>
       <c r="R75" s="23" t="inlineStr">
         <is>
@@ -7879,7 +7896,7 @@
       </c>
       <c r="AH75" s="2" t="n"/>
     </row>
-    <row r="76" ht="24" customHeight="1" s="45">
+    <row r="76" ht="24" customHeight="1" s="48">
       <c r="A76" s="2" t="n">
         <v>75</v>
       </c>
@@ -7888,7 +7905,7 @@
           <t>ogimet</t>
         </is>
       </c>
-      <c r="C76" s="27" t="n">
+      <c r="C76" s="46" t="n">
         <v>31532</v>
       </c>
       <c r="D76" s="2" t="inlineStr">
@@ -7925,13 +7942,13 @@
       </c>
       <c r="N76" s="2" t="n"/>
       <c r="O76" s="32" t="n">
-        <v>-12.4</v>
+        <v>-26.5</v>
       </c>
       <c r="P76" s="32" t="n">
-        <v>1.6</v>
+        <v>-11.6</v>
       </c>
       <c r="Q76" s="32" t="n">
-        <v>-4.25</v>
+        <v>-20.7</v>
       </c>
       <c r="R76" s="23" t="inlineStr">
         <is>
@@ -7991,7 +8008,7 @@
       </c>
       <c r="AH76" s="2" t="n"/>
     </row>
-    <row r="77" ht="24" customHeight="1" s="45">
+    <row r="77" ht="24" customHeight="1" s="48">
       <c r="A77" s="2" t="n">
         <v>76</v>
       </c>
@@ -8000,7 +8017,7 @@
           <t>ogimet</t>
         </is>
       </c>
-      <c r="C77" s="27" t="n">
+      <c r="C77" s="46" t="n">
         <v>31478</v>
       </c>
       <c r="D77" s="2" t="inlineStr">
@@ -8041,13 +8058,13 @@
         </is>
       </c>
       <c r="O77" s="32" t="n">
-        <v>-13.6</v>
+        <v>-32.8</v>
       </c>
       <c r="P77" s="32" t="n">
-        <v>-6.1</v>
+        <v>-14.4</v>
       </c>
       <c r="Q77" s="32" t="n">
-        <v>-8.140000000000001</v>
+        <v>-24.18</v>
       </c>
       <c r="R77" s="23" t="inlineStr">
         <is>
@@ -8107,7 +8124,7 @@
       </c>
       <c r="AH77" s="2" t="n"/>
     </row>
-    <row r="78" ht="24" customHeight="1" s="45">
+    <row r="78" ht="24" customHeight="1" s="48">
       <c r="A78" s="2" t="n">
         <v>77</v>
       </c>
@@ -8116,7 +8133,7 @@
           <t>ogimet</t>
         </is>
       </c>
-      <c r="C78" s="27" t="n">
+      <c r="C78" s="46" t="n">
         <v>31329</v>
       </c>
       <c r="D78" s="2" t="inlineStr">
@@ -8153,13 +8170,13 @@
       </c>
       <c r="N78" s="2" t="n"/>
       <c r="O78" s="32" t="n">
-        <v>-15.7</v>
+        <v>-30.6</v>
       </c>
       <c r="P78" s="32" t="n">
-        <v>-2.3</v>
+        <v>-13.5</v>
       </c>
       <c r="Q78" s="32" t="n">
-        <v>-8.6</v>
+        <v>-22.94</v>
       </c>
       <c r="R78" s="23" t="inlineStr">
         <is>
@@ -8219,7 +8236,7 @@
       </c>
       <c r="AH78" s="2" t="n"/>
     </row>
-    <row r="79" ht="24" customHeight="1" s="45">
+    <row r="79" ht="24" customHeight="1" s="48">
       <c r="A79" s="2" t="n">
         <v>78</v>
       </c>
@@ -8228,7 +8245,7 @@
           <t>ogimet</t>
         </is>
       </c>
-      <c r="C79" s="27" t="n">
+      <c r="C79" s="46" t="n">
         <v>31348</v>
       </c>
       <c r="D79" s="2" t="inlineStr">
@@ -8269,13 +8286,13 @@
         </is>
       </c>
       <c r="O79" s="32" t="n">
-        <v>-21.4</v>
+        <v>-32.5</v>
       </c>
       <c r="P79" s="32" t="n">
-        <v>-10.3</v>
+        <v>-10.8</v>
       </c>
       <c r="Q79" s="32" t="n">
-        <v>-14.55</v>
+        <v>-21.74</v>
       </c>
       <c r="R79" s="23" t="inlineStr">
         <is>
@@ -8335,7 +8352,7 @@
       </c>
       <c r="AH79" s="2" t="n"/>
     </row>
-    <row r="80" ht="24" customHeight="1" s="45">
+    <row r="80" ht="24" customHeight="1" s="48">
       <c r="A80" s="2" t="n">
         <v>79</v>
       </c>
@@ -8344,7 +8361,7 @@
           <t>ogimet</t>
         </is>
       </c>
-      <c r="C80" s="27" t="n">
+      <c r="C80" s="46" t="n">
         <v>30673</v>
       </c>
       <c r="D80" s="2" t="inlineStr">
@@ -8381,13 +8398,13 @@
       </c>
       <c r="N80" s="2" t="n"/>
       <c r="O80" s="32" t="n">
-        <v>-19.1</v>
+        <v>-36.1</v>
       </c>
       <c r="P80" s="32" t="n">
-        <v>-14.8</v>
+        <v>-16.8</v>
       </c>
       <c r="Q80" s="32" t="n">
-        <v>-18.15</v>
+        <v>-26.62</v>
       </c>
       <c r="R80" s="23" t="inlineStr">
         <is>
@@ -8447,7 +8464,7 @@
       </c>
       <c r="AH80" s="2" t="n"/>
     </row>
-    <row r="81" ht="24" customHeight="1" s="45">
+    <row r="81" ht="24" customHeight="1" s="48">
       <c r="A81" s="2" t="n">
         <v>80</v>
       </c>
@@ -8456,7 +8473,7 @@
           <t>rp5</t>
         </is>
       </c>
-      <c r="C81" s="27" t="n">
+      <c r="C81" s="46" t="n">
         <v>30565</v>
       </c>
       <c r="D81" s="2" t="inlineStr">
@@ -8497,13 +8514,13 @@
         </is>
       </c>
       <c r="O81" s="32" t="n">
-        <v>-23.7</v>
+        <v>-43.6</v>
       </c>
       <c r="P81" s="32" t="n">
-        <v>-16.7</v>
+        <v>-17.5</v>
       </c>
       <c r="Q81" s="32" t="n">
-        <v>-19.71</v>
+        <v>-31.95</v>
       </c>
       <c r="R81" s="23" t="inlineStr">
         <is>
@@ -8568,7 +8585,7 @@
         </is>
       </c>
     </row>
-    <row r="82" ht="24" customHeight="1" s="45">
+    <row r="82" ht="24" customHeight="1" s="48">
       <c r="A82" s="2" t="n">
         <v>81</v>
       </c>
@@ -8577,7 +8594,7 @@
           <t>ogimet</t>
         </is>
       </c>
-      <c r="C82" s="27" t="n">
+      <c r="C82" s="46" t="n">
         <v>30664</v>
       </c>
       <c r="D82" s="2" t="inlineStr">
@@ -8618,13 +8635,13 @@
         </is>
       </c>
       <c r="O82" s="32" t="n">
-        <v>-34.7</v>
+        <v>-43.7</v>
       </c>
       <c r="P82" s="32" t="n">
-        <v>-18</v>
+        <v>-15.5</v>
       </c>
       <c r="Q82" s="32" t="n">
-        <v>-25.65</v>
+        <v>-32.56</v>
       </c>
       <c r="R82" s="23" t="inlineStr">
         <is>
@@ -8684,7 +8701,7 @@
       </c>
       <c r="AH82" s="2" t="n"/>
     </row>
-    <row r="83" ht="24" customHeight="1" s="45">
+    <row r="83" ht="24" customHeight="1" s="48">
       <c r="A83" s="2" t="n">
         <v>82</v>
       </c>
@@ -8693,7 +8710,7 @@
           <t>ogimet</t>
         </is>
       </c>
-      <c r="C83" s="27" t="n">
+      <c r="C83" s="46" t="n">
         <v>30636</v>
       </c>
       <c r="D83" s="2" t="inlineStr">
@@ -8730,13 +8747,13 @@
       </c>
       <c r="N83" s="2" t="n"/>
       <c r="O83" s="32" t="n">
-        <v>-27.8</v>
+        <v>-36.3</v>
       </c>
       <c r="P83" s="32" t="n">
-        <v>-14.8</v>
+        <v>-21.1</v>
       </c>
       <c r="Q83" s="32" t="n">
-        <v>-20.38</v>
+        <v>-29.14</v>
       </c>
       <c r="R83" s="23" t="inlineStr">
         <is>
@@ -8796,7 +8813,7 @@
       </c>
       <c r="AH83" s="2" t="n"/>
     </row>
-    <row r="84" ht="24" customHeight="1" s="45">
+    <row r="84" ht="24" customHeight="1" s="48">
       <c r="A84" s="2" t="n">
         <v>83</v>
       </c>
@@ -8805,7 +8822,7 @@
           <t>ogimet</t>
         </is>
       </c>
-      <c r="C84" s="27" t="n">
+      <c r="C84" s="46" t="n">
         <v>30622</v>
       </c>
       <c r="D84" s="2" t="inlineStr">
@@ -8846,13 +8863,13 @@
         </is>
       </c>
       <c r="O84" s="32" t="n">
-        <v>-29.1</v>
+        <v>-41.4</v>
       </c>
       <c r="P84" s="32" t="n">
-        <v>-16.6</v>
+        <v>-21.5</v>
       </c>
       <c r="Q84" s="32" t="n">
-        <v>-23.65</v>
+        <v>-32.38</v>
       </c>
       <c r="R84" s="23" t="inlineStr">
         <is>
@@ -8912,7 +8929,7 @@
       </c>
       <c r="AH84" s="2" t="n"/>
     </row>
-    <row r="85" ht="24" customHeight="1" s="45">
+    <row r="85" ht="24" customHeight="1" s="48">
       <c r="A85" s="2" t="n">
         <v>84</v>
       </c>
@@ -8921,7 +8938,7 @@
           <t>ogimet</t>
         </is>
       </c>
-      <c r="C85" s="27" t="n">
+      <c r="C85" s="46" t="n">
         <v>36104</v>
       </c>
       <c r="D85" s="2" t="inlineStr">
@@ -8962,13 +8979,13 @@
         </is>
       </c>
       <c r="O85" s="32" t="n">
-        <v>-35.1</v>
+        <v>-40.7</v>
       </c>
       <c r="P85" s="32" t="n">
-        <v>-18.5</v>
+        <v>-20.5</v>
       </c>
       <c r="Q85" s="32" t="n">
-        <v>-26.75</v>
+        <v>-29.51</v>
       </c>
       <c r="R85" s="23" t="inlineStr">
         <is>
@@ -9028,7 +9045,7 @@
       </c>
       <c r="AH85" s="2" t="n"/>
     </row>
-    <row r="86" ht="24" customHeight="1" s="45">
+    <row r="86" ht="24" customHeight="1" s="48">
       <c r="A86" s="2" t="n">
         <v>85</v>
       </c>
@@ -9037,7 +9054,7 @@
           <t>ogimet</t>
         </is>
       </c>
-      <c r="C86" s="27" t="n">
+      <c r="C86" s="46" t="n">
         <v>36096</v>
       </c>
       <c r="D86" s="2" t="inlineStr">
@@ -9074,13 +9091,13 @@
       </c>
       <c r="N86" s="2" t="n"/>
       <c r="O86" s="32" t="n">
-        <v>-31.2</v>
+        <v>-35.1</v>
       </c>
       <c r="P86" s="32" t="n">
-        <v>-16.8</v>
+        <v>-20.8</v>
       </c>
       <c r="Q86" s="32" t="n">
-        <v>-23.41</v>
+        <v>-28.34</v>
       </c>
       <c r="R86" s="23" t="inlineStr">
         <is>
@@ -9148,7 +9165,7 @@
       </c>
       <c r="AH86" s="2" t="n"/>
     </row>
-    <row r="87" ht="24" customHeight="1" s="45">
+    <row r="87" ht="24" customHeight="1" s="48">
       <c r="A87" s="2" t="n">
         <v>86</v>
       </c>
@@ -9157,7 +9174,7 @@
           <t>ogimet</t>
         </is>
       </c>
-      <c r="C87" s="27" t="n">
+      <c r="C87" s="46" t="n">
         <v>36307</v>
       </c>
       <c r="D87" s="2" t="inlineStr">
@@ -9198,13 +9215,13 @@
         </is>
       </c>
       <c r="O87" s="32" t="n">
-        <v>-32.8</v>
+        <v>-32.5</v>
       </c>
       <c r="P87" s="32" t="n">
-        <v>-19.7</v>
+        <v>-18.2</v>
       </c>
       <c r="Q87" s="32" t="n">
-        <v>-25.48</v>
+        <v>-26.24</v>
       </c>
       <c r="R87" s="23" t="inlineStr">
         <is>
@@ -9264,7 +9281,7 @@
       </c>
       <c r="AH87" s="2" t="n"/>
     </row>
-    <row r="88" ht="24" customHeight="1" s="45">
+    <row r="88" ht="24" customHeight="1" s="48">
       <c r="A88" s="2" t="n">
         <v>87</v>
       </c>
@@ -9273,7 +9290,7 @@
           <t>ogimet</t>
         </is>
       </c>
-      <c r="C88" s="27" t="n">
+      <c r="C88" s="46" t="n">
         <v>36259</v>
       </c>
       <c r="D88" s="2" t="inlineStr">
@@ -9310,13 +9327,13 @@
       </c>
       <c r="N88" s="2" t="n"/>
       <c r="O88" s="32" t="n">
-        <v>-24.5</v>
+        <v>-32.2</v>
       </c>
       <c r="P88" s="32" t="n">
-        <v>-13.8</v>
+        <v>-16.9</v>
       </c>
       <c r="Q88" s="32" t="n">
-        <v>-19.89</v>
+        <v>-24.56</v>
       </c>
       <c r="R88" s="23" t="inlineStr">
         <is>
@@ -9376,7 +9393,7 @@
       </c>
       <c r="AH88" s="2" t="n"/>
     </row>
-    <row r="89" ht="24" customHeight="1" s="45">
+    <row r="89" ht="24" customHeight="1" s="48">
       <c r="A89" s="2" t="n">
         <v>88</v>
       </c>
@@ -9385,7 +9402,7 @@
           <t>ogimet</t>
         </is>
       </c>
-      <c r="C89" s="27" t="n">
+      <c r="C89" s="46" t="n">
         <v>30781</v>
       </c>
       <c r="D89" s="2" t="inlineStr">
@@ -9421,9 +9438,15 @@
         </is>
       </c>
       <c r="N89" s="2" t="n"/>
-      <c r="O89" s="32" t="n"/>
-      <c r="P89" s="32" t="n"/>
-      <c r="Q89" s="32" t="n"/>
+      <c r="O89" s="32" t="n">
+        <v>-38.6</v>
+      </c>
+      <c r="P89" s="32" t="n">
+        <v>-12.8</v>
+      </c>
+      <c r="Q89" s="32" t="n">
+        <v>-27.24</v>
+      </c>
       <c r="R89" s="23" t="inlineStr">
         <is>
           <t>Y</t>
@@ -9478,7 +9501,7 @@
       </c>
       <c r="AH89" s="2" t="n"/>
     </row>
-    <row r="90" ht="24" customHeight="1" s="45">
+    <row r="90" ht="24" customHeight="1" s="48">
       <c r="A90" s="2" t="n">
         <v>89</v>
       </c>
@@ -9487,7 +9510,7 @@
           <t>ogimet</t>
         </is>
       </c>
-      <c r="C90" s="27" t="n">
+      <c r="C90" s="46" t="n">
         <v>36535</v>
       </c>
       <c r="D90" s="2" t="inlineStr">
@@ -9528,13 +9551,13 @@
         </is>
       </c>
       <c r="O90" s="32" t="n">
-        <v>-17.6</v>
+        <v>-36.1</v>
       </c>
       <c r="P90" s="32" t="n">
-        <v>-8.4</v>
+        <v>-22.3</v>
       </c>
       <c r="Q90" s="32" t="n">
-        <v>-12.6</v>
+        <v>-28.17</v>
       </c>
       <c r="R90" s="23" t="inlineStr">
         <is>
@@ -9590,7 +9613,7 @@
       <c r="AG90" s="2" t="n"/>
       <c r="AH90" s="2" t="n"/>
     </row>
-    <row r="91" ht="24" customHeight="1" s="45">
+    <row r="91" ht="24" customHeight="1" s="48">
       <c r="A91" s="2" t="n">
         <v>90</v>
       </c>
@@ -9599,7 +9622,7 @@
           <t>ogimet</t>
         </is>
       </c>
-      <c r="C91" s="27" t="n">
+      <c r="C91" s="46" t="n">
         <v>36566</v>
       </c>
       <c r="D91" s="2" t="inlineStr">
@@ -9636,13 +9659,13 @@
       </c>
       <c r="N91" s="2" t="n"/>
       <c r="O91" s="32" t="n">
-        <v>-19.4</v>
+        <v>-34.1</v>
       </c>
       <c r="P91" s="32" t="n">
-        <v>-11.3</v>
+        <v>-23.5</v>
       </c>
       <c r="Q91" s="32" t="n">
-        <v>-15.04</v>
+        <v>-27.89</v>
       </c>
       <c r="R91" s="23" t="inlineStr">
         <is>
@@ -9698,7 +9721,7 @@
       </c>
       <c r="AH91" s="2" t="n"/>
     </row>
-    <row r="92" ht="24" customHeight="1" s="45">
+    <row r="92" ht="24" customHeight="1" s="48">
       <c r="A92" s="2" t="n">
         <v>91</v>
       </c>
@@ -9707,7 +9730,7 @@
           <t>ogimet</t>
         </is>
       </c>
-      <c r="C92" s="27" t="n">
+      <c r="C92" s="46" t="n">
         <v>47005</v>
       </c>
       <c r="D92" s="2" t="inlineStr">
@@ -9744,13 +9767,13 @@
       </c>
       <c r="N92" s="2" t="n"/>
       <c r="O92" s="32" t="n">
-        <v>-14.2</v>
+        <v>-9.4</v>
       </c>
       <c r="P92" s="32" t="n">
         <v>2.6</v>
       </c>
       <c r="Q92" s="32" t="n">
-        <v>-3.41</v>
+        <v>-3.7</v>
       </c>
       <c r="R92" s="23" t="inlineStr">
         <is>
@@ -9810,7 +9833,7 @@
       </c>
       <c r="AH92" s="2" t="n"/>
     </row>
-    <row r="93" ht="24" customHeight="1" s="45">
+    <row r="93" ht="24" customHeight="1" s="48">
       <c r="A93" s="2" t="n">
         <v>92</v>
       </c>
@@ -9819,7 +9842,7 @@
           <t>ogimet</t>
         </is>
       </c>
-      <c r="C93" s="27" t="n">
+      <c r="C93" s="46" t="n">
         <v>54342</v>
       </c>
       <c r="D93" s="2" t="inlineStr">
@@ -9856,13 +9879,13 @@
       </c>
       <c r="N93" s="2" t="n"/>
       <c r="O93" s="32" t="n">
-        <v>-2.5</v>
+        <v>-8.1</v>
       </c>
       <c r="P93" s="32" t="n">
-        <v>9</v>
+        <v>1.9</v>
       </c>
       <c r="Q93" s="32" t="n">
-        <v>0.65</v>
+        <v>-2.85</v>
       </c>
       <c r="R93" s="23" t="inlineStr">
         <is>
@@ -9934,12 +9957,12 @@
       </c>
       <c r="AH93" s="2" t="n"/>
     </row>
-    <row r="94" ht="24" customHeight="1" s="45">
+    <row r="94" ht="24" customHeight="1" s="48">
       <c r="A94" s="2" t="n">
         <v>93</v>
       </c>
       <c r="B94" s="2" t="n"/>
-      <c r="C94" s="27" t="n">
+      <c r="C94" s="46" t="n">
         <v>54252</v>
       </c>
       <c r="D94" s="2" t="n"/>
@@ -9976,10 +9999,10 @@
         </is>
       </c>
       <c r="O94" s="32" t="n">
-        <v>-5.6</v>
+        <v>-11.6</v>
       </c>
       <c r="P94" s="32" t="n">
-        <v>9</v>
+        <v>-1.4</v>
       </c>
       <c r="Q94" s="32" t="n"/>
       <c r="R94" s="23" t="inlineStr">
@@ -10048,7 +10071,7 @@
       </c>
       <c r="AH94" s="2" t="n"/>
     </row>
-    <row r="95" ht="24" customHeight="1" s="45">
+    <row r="95" ht="24" customHeight="1" s="48">
       <c r="A95" s="2" t="n">
         <v>94</v>
       </c>
@@ -10057,7 +10080,7 @@
           <t>ogimet</t>
         </is>
       </c>
-      <c r="C95" s="27" t="n">
+      <c r="C95" s="46" t="n">
         <v>54161</v>
       </c>
       <c r="D95" s="2" t="inlineStr">
@@ -10094,13 +10117,13 @@
       </c>
       <c r="N95" s="2" t="n"/>
       <c r="O95" s="32" t="n">
-        <v>-8.5</v>
+        <v>-13.6</v>
       </c>
       <c r="P95" s="32" t="n">
-        <v>8.699999999999999</v>
+        <v>-3.4</v>
       </c>
       <c r="Q95" s="32" t="n">
-        <v>-3.46</v>
+        <v>-8.720000000000001</v>
       </c>
       <c r="R95" s="23" t="inlineStr">
         <is>
@@ -10172,7 +10195,7 @@
       </c>
       <c r="AH95" s="2" t="n"/>
     </row>
-    <row r="96" ht="24" customHeight="1" s="45">
+    <row r="96" ht="24" customHeight="1" s="48">
       <c r="A96" s="2" t="n">
         <v>95</v>
       </c>
@@ -10181,7 +10204,7 @@
           <t>ogimet</t>
         </is>
       </c>
-      <c r="C96" s="27" t="n">
+      <c r="C96" s="46" t="n">
         <v>54273</v>
       </c>
       <c r="D96" s="2" t="inlineStr">
@@ -10222,10 +10245,10 @@
         </is>
       </c>
       <c r="O96" s="32" t="n">
-        <v>-5.7</v>
+        <v>-11.7</v>
       </c>
       <c r="P96" s="32" t="n">
-        <v>7.3</v>
+        <v>-2.4</v>
       </c>
       <c r="Q96" s="32" t="n"/>
       <c r="R96" s="23" t="inlineStr">
@@ -10294,7 +10317,7 @@
       </c>
       <c r="AH96" s="2" t="n"/>
     </row>
-    <row r="97" ht="24" customHeight="1" s="45">
+    <row r="97" ht="24" customHeight="1" s="48">
       <c r="A97" s="2" t="n">
         <v>96</v>
       </c>
@@ -10303,7 +10326,7 @@
           <t>ogimet</t>
         </is>
       </c>
-      <c r="C97" s="27" t="n">
+      <c r="C97" s="46" t="n">
         <v>50953</v>
       </c>
       <c r="D97" s="2" t="inlineStr">
@@ -10340,13 +10363,13 @@
       </c>
       <c r="N97" s="2" t="n"/>
       <c r="O97" s="32" t="n">
-        <v>-8.5</v>
+        <v>-18.8</v>
       </c>
       <c r="P97" s="32" t="n">
-        <v>10.9</v>
+        <v>-5.4</v>
       </c>
       <c r="Q97" s="32" t="n">
-        <v>-1.12</v>
+        <v>-11.85</v>
       </c>
       <c r="R97" s="23" t="inlineStr">
         <is>
@@ -10422,12 +10445,12 @@
       </c>
       <c r="AH97" s="2" t="n"/>
     </row>
-    <row r="98" ht="24" customHeight="1" s="45">
+    <row r="98" ht="24" customHeight="1" s="48">
       <c r="A98" s="2" t="n">
         <v>97</v>
       </c>
       <c r="B98" s="2" t="n"/>
-      <c r="C98" s="27" t="n">
+      <c r="C98" s="46" t="n">
         <v>50673</v>
       </c>
       <c r="D98" s="2" t="n"/>
@@ -10460,10 +10483,10 @@
       </c>
       <c r="N98" s="2" t="n"/>
       <c r="O98" s="32" t="n">
-        <v>-6.9</v>
+        <v>-17.9</v>
       </c>
       <c r="P98" s="32" t="n">
-        <v>3.2</v>
+        <v>-10.8</v>
       </c>
       <c r="Q98" s="32" t="n"/>
       <c r="R98" s="23" t="inlineStr">
@@ -10532,7 +10555,7 @@
       </c>
       <c r="AH98" s="2" t="n"/>
     </row>
-    <row r="99" ht="24" customHeight="1" s="45">
+    <row r="99" ht="24" customHeight="1" s="48">
       <c r="A99" s="2" t="n">
         <v>98</v>
       </c>
@@ -10541,7 +10564,7 @@
           <t>ogimet</t>
         </is>
       </c>
-      <c r="C99" s="27" t="n">
+      <c r="C99" s="46" t="n">
         <v>50353</v>
       </c>
       <c r="D99" s="2" t="inlineStr">
@@ -10578,13 +10601,13 @@
       </c>
       <c r="N99" s="2" t="n"/>
       <c r="O99" s="32" t="n">
-        <v>-10.4</v>
+        <v>-38.8</v>
       </c>
       <c r="P99" s="32" t="n">
-        <v>-7.2</v>
+        <v>-16.8</v>
       </c>
       <c r="Q99" s="32" t="n">
-        <v>-8.77</v>
+        <v>-29.57</v>
       </c>
       <c r="R99" s="23" t="inlineStr">
         <is>
@@ -10652,12 +10675,12 @@
       </c>
       <c r="AH99" s="2" t="n"/>
     </row>
-    <row r="100" ht="24" customHeight="1" s="45">
+    <row r="100" ht="24" customHeight="1" s="48">
       <c r="A100" s="2" t="n">
         <v>99</v>
       </c>
       <c r="B100" s="2" t="n"/>
-      <c r="C100" s="27" t="n">
+      <c r="C100" s="46" t="n">
         <v>50246</v>
       </c>
       <c r="D100" s="2" t="n"/>
@@ -10758,12 +10781,12 @@
       </c>
       <c r="AH100" s="2" t="n"/>
     </row>
-    <row r="101" ht="24" customHeight="1" s="45">
+    <row r="101" ht="24" customHeight="1" s="48">
       <c r="A101" s="2" t="n">
         <v>100</v>
       </c>
       <c r="B101" s="2" t="n"/>
-      <c r="C101" s="27" t="n">
+      <c r="C101" s="46" t="n">
         <v>50247</v>
       </c>
       <c r="D101" s="2" t="n"/>
@@ -10795,8 +10818,12 @@
         </is>
       </c>
       <c r="N101" s="2" t="n"/>
-      <c r="O101" s="32" t="n"/>
-      <c r="P101" s="32" t="n"/>
+      <c r="O101" s="32" t="n">
+        <v>-40.7</v>
+      </c>
+      <c r="P101" s="32" t="n">
+        <v>-12.2</v>
+      </c>
       <c r="Q101" s="32" t="n"/>
       <c r="R101" s="23" t="inlineStr">
         <is>
@@ -10864,7 +10891,7 @@
       </c>
       <c r="AH101" s="2" t="n"/>
     </row>
-    <row r="102" ht="24" customHeight="1" s="45">
+    <row r="102" ht="24" customHeight="1" s="48">
       <c r="A102" s="2" t="n">
         <v>101</v>
       </c>
@@ -10873,7 +10900,7 @@
           <t>ogimet</t>
         </is>
       </c>
-      <c r="C102" s="27" t="n">
+      <c r="C102" s="46" t="n">
         <v>50136</v>
       </c>
       <c r="D102" s="2" t="inlineStr">
@@ -10910,13 +10937,13 @@
       </c>
       <c r="N102" s="2" t="n"/>
       <c r="O102" s="32" t="n">
-        <v>-16.7</v>
+        <v>-40</v>
       </c>
       <c r="P102" s="32" t="n">
-        <v>-11.2</v>
+        <v>-14.8</v>
       </c>
       <c r="Q102" s="32" t="n">
-        <v>-15.34</v>
+        <v>-29.12</v>
       </c>
       <c r="R102" s="23" t="inlineStr">
         <is>
@@ -10988,12 +11015,12 @@
       </c>
       <c r="AH102" s="2" t="n"/>
     </row>
-    <row r="103" ht="24" customHeight="1" s="45">
+    <row r="103" ht="24" customHeight="1" s="48">
       <c r="A103" s="2" t="n">
         <v>102</v>
       </c>
       <c r="B103" s="2" t="n"/>
-      <c r="C103" s="27" t="n">
+      <c r="C103" s="46" t="n">
         <v>50137</v>
       </c>
       <c r="D103" s="2" t="n"/>
@@ -11026,10 +11053,10 @@
       </c>
       <c r="N103" s="2" t="n"/>
       <c r="O103" s="32" t="n">
-        <v>-16.3</v>
+        <v>-38.4</v>
       </c>
       <c r="P103" s="32" t="n">
-        <v>-11.4</v>
+        <v>-15.1</v>
       </c>
       <c r="Q103" s="32" t="n"/>
       <c r="R103" s="23" t="inlineStr">
@@ -11098,12 +11125,12 @@
       </c>
       <c r="AH103" s="2" t="n"/>
     </row>
-    <row r="104" ht="24" customHeight="1" s="45">
+    <row r="104" ht="24" customHeight="1" s="48">
       <c r="A104" s="2" t="n">
         <v>103</v>
       </c>
       <c r="B104" s="2" t="n"/>
-      <c r="C104" s="27" t="n">
+      <c r="C104" s="46" t="n">
         <v>50431</v>
       </c>
       <c r="D104" s="2" t="n"/>
@@ -11136,10 +11163,10 @@
       </c>
       <c r="N104" s="2" t="n"/>
       <c r="O104" s="32" t="n">
-        <v>-17.8</v>
+        <v>-36.9</v>
       </c>
       <c r="P104" s="32" t="n">
-        <v>-9.699999999999999</v>
+        <v>-13.2</v>
       </c>
       <c r="Q104" s="32" t="n"/>
       <c r="R104" s="23" t="inlineStr">
@@ -11212,7 +11239,7 @@
       </c>
       <c r="AH104" s="2" t="n"/>
     </row>
-    <row r="105" ht="24" customHeight="1" s="45">
+    <row r="105" ht="24" customHeight="1" s="48">
       <c r="A105" s="2" t="n">
         <v>104</v>
       </c>
@@ -11221,7 +11248,7 @@
           <t>ogimet</t>
         </is>
       </c>
-      <c r="C105" s="27" t="n">
+      <c r="C105" s="46" t="n">
         <v>50434</v>
       </c>
       <c r="D105" s="2" t="inlineStr">
@@ -11262,13 +11289,13 @@
         </is>
       </c>
       <c r="O105" s="32" t="n">
-        <v>-17.7</v>
+        <v>-41.2</v>
       </c>
       <c r="P105" s="32" t="n">
-        <v>-8.5</v>
+        <v>-13.4</v>
       </c>
       <c r="Q105" s="32" t="n">
-        <v>-15.11</v>
+        <v>-28.4</v>
       </c>
       <c r="R105" s="23" t="inlineStr">
         <is>
@@ -11336,12 +11363,12 @@
       </c>
       <c r="AH105" s="2" t="n"/>
     </row>
-    <row r="106" ht="24" customHeight="1" s="45">
+    <row r="106" ht="24" customHeight="1" s="48">
       <c r="A106" s="2" t="n">
         <v>105</v>
       </c>
       <c r="B106" s="2" t="n"/>
-      <c r="C106" s="27" t="n">
+      <c r="C106" s="46" t="n">
         <v>50425</v>
       </c>
       <c r="D106" s="2" t="n"/>
@@ -11378,10 +11405,10 @@
         </is>
       </c>
       <c r="O106" s="32" t="n">
-        <v>-16.1</v>
+        <v>-36.9</v>
       </c>
       <c r="P106" s="32" t="n">
-        <v>-8.6</v>
+        <v>-21.6</v>
       </c>
       <c r="Q106" s="32" t="n"/>
       <c r="R106" s="23" t="inlineStr">
@@ -11450,12 +11477,12 @@
       </c>
       <c r="AH106" s="2" t="n"/>
     </row>
-    <row r="107" ht="24" customHeight="1" s="45">
+    <row r="107" ht="24" customHeight="1" s="48">
       <c r="A107" s="2" t="n">
         <v>106</v>
       </c>
       <c r="B107" s="2" t="n"/>
-      <c r="C107" s="27" t="n">
+      <c r="C107" s="46" t="n">
         <v>50524</v>
       </c>
       <c r="D107" s="2" t="n"/>
@@ -11552,7 +11579,7 @@
       </c>
       <c r="AH107" s="2" t="n"/>
     </row>
-    <row r="108" ht="24" customHeight="1" s="45">
+    <row r="108" ht="24" customHeight="1" s="48">
       <c r="A108" s="2" t="n">
         <v>107</v>
       </c>
@@ -11561,7 +11588,7 @@
           <t>ogimet</t>
         </is>
       </c>
-      <c r="C108" s="27" t="n">
+      <c r="C108" s="46" t="n">
         <v>50527</v>
       </c>
       <c r="D108" s="2" t="inlineStr">
@@ -11598,13 +11625,13 @@
       </c>
       <c r="N108" s="2" t="n"/>
       <c r="O108" s="32" t="n">
-        <v>-16.4</v>
+        <v>-33.1</v>
       </c>
       <c r="P108" s="32" t="n">
-        <v>-8</v>
+        <v>-18.7</v>
       </c>
       <c r="Q108" s="32" t="n">
-        <v>-14.12</v>
+        <v>-26.45</v>
       </c>
       <c r="R108" s="23" t="inlineStr">
         <is>
@@ -11672,12 +11699,12 @@
       </c>
       <c r="AH108" s="2" t="n"/>
     </row>
-    <row r="109" ht="24" customHeight="1" s="45">
+    <row r="109" ht="24" customHeight="1" s="48">
       <c r="A109" s="2" t="n">
         <v>108</v>
       </c>
       <c r="B109" s="2" t="n"/>
-      <c r="C109" s="27" t="n">
+      <c r="C109" s="46" t="n">
         <v>50525</v>
       </c>
       <c r="D109" s="2" t="n"/>
@@ -11774,12 +11801,12 @@
       </c>
       <c r="AH109" s="2" t="n"/>
     </row>
-    <row r="110" ht="24" customHeight="1" s="45">
+    <row r="110" ht="24" customHeight="1" s="48">
       <c r="A110" s="2" t="n">
         <v>109</v>
       </c>
       <c r="B110" s="2" t="n"/>
-      <c r="C110" s="27" t="n">
+      <c r="C110" s="46" t="n">
         <v>50526</v>
       </c>
       <c r="D110" s="2" t="n"/>
@@ -11811,8 +11838,12 @@
         </is>
       </c>
       <c r="N110" s="2" t="n"/>
-      <c r="O110" s="32" t="n"/>
-      <c r="P110" s="32" t="n"/>
+      <c r="O110" s="32" t="n">
+        <v>-39.4</v>
+      </c>
+      <c r="P110" s="32" t="n">
+        <v>-15.9</v>
+      </c>
       <c r="Q110" s="32" t="n"/>
       <c r="R110" s="23" t="inlineStr">
         <is>
@@ -11880,7 +11911,7 @@
       </c>
       <c r="AH110" s="2" t="n"/>
     </row>
-    <row r="111" ht="24" customHeight="1" s="45">
+    <row r="111" ht="24" customHeight="1" s="48">
       <c r="A111" s="2" t="n">
         <v>110</v>
       </c>
@@ -11889,7 +11920,7 @@
           <t>ogimet</t>
         </is>
       </c>
-      <c r="C111" s="27" t="n">
+      <c r="C111" s="46" t="n">
         <v>50727</v>
       </c>
       <c r="D111" s="2" t="inlineStr">
@@ -11926,13 +11957,13 @@
       </c>
       <c r="N111" s="2" t="n"/>
       <c r="O111" s="32" t="n">
-        <v>-20.5</v>
+        <v>-30.8</v>
       </c>
       <c r="P111" s="32" t="n">
-        <v>-4.8</v>
+        <v>-7.7</v>
       </c>
       <c r="Q111" s="32" t="n">
-        <v>-16</v>
+        <v>-19.81</v>
       </c>
       <c r="R111" s="23" t="inlineStr">
         <is>
@@ -12000,12 +12031,12 @@
       </c>
       <c r="AH111" s="2" t="n"/>
     </row>
-    <row r="112" ht="24" customHeight="1" s="45">
+    <row r="112" ht="24" customHeight="1" s="48">
       <c r="A112" s="2" t="n">
         <v>111</v>
       </c>
       <c r="B112" s="2" t="n"/>
-      <c r="C112" s="27" t="n">
+      <c r="C112" s="46" t="n">
         <v>53392</v>
       </c>
       <c r="D112" s="2" t="n"/>
@@ -12038,10 +12069,10 @@
       </c>
       <c r="N112" s="2" t="n"/>
       <c r="O112" s="32" t="n">
-        <v>-16.8</v>
+        <v>-8.6</v>
       </c>
       <c r="P112" s="32" t="n">
-        <v>-12</v>
+        <v>-1.8</v>
       </c>
       <c r="Q112" s="32" t="n"/>
       <c r="R112" s="23" t="inlineStr">
@@ -12106,12 +12137,12 @@
       <c r="AG112" s="2" t="n"/>
       <c r="AH112" s="2" t="n"/>
     </row>
-    <row r="113" ht="24" customHeight="1" s="45">
+    <row r="113" ht="24" customHeight="1" s="48">
       <c r="A113" s="2" t="n">
         <v>112</v>
       </c>
       <c r="B113" s="2" t="n"/>
-      <c r="C113" s="27" t="n">
+      <c r="C113" s="46" t="n">
         <v>55294</v>
       </c>
       <c r="D113" s="2" t="n"/>
@@ -12144,10 +12175,10 @@
       </c>
       <c r="N113" s="2" t="n"/>
       <c r="O113" s="32" t="n">
-        <v>-17.3</v>
+        <v>-18</v>
       </c>
       <c r="P113" s="32" t="n">
-        <v>-0.1</v>
+        <v>0.5</v>
       </c>
       <c r="Q113" s="32" t="n"/>
       <c r="R113" s="23" t="inlineStr">
@@ -12216,12 +12247,12 @@
       </c>
       <c r="AH113" s="2" t="n"/>
     </row>
-    <row r="114" ht="24" customHeight="1" s="45">
+    <row r="114" ht="24" customHeight="1" s="48">
       <c r="A114" s="2" t="n">
         <v>113</v>
       </c>
       <c r="B114" s="2" t="n"/>
-      <c r="C114" s="27" t="n">
+      <c r="C114" s="46" t="n">
         <v>56034</v>
       </c>
       <c r="D114" s="2" t="n"/>
@@ -12258,10 +12289,10 @@
         </is>
       </c>
       <c r="O114" s="32" t="n">
-        <v>-22.3</v>
+        <v>-25.1</v>
       </c>
       <c r="P114" s="32" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="Q114" s="32" t="n"/>
       <c r="R114" s="23" t="inlineStr">
@@ -12330,7 +12361,7 @@
       </c>
       <c r="AH114" s="2" t="n"/>
     </row>
-    <row r="115" ht="24" customHeight="1" s="45">
+    <row r="115" ht="24" customHeight="1" s="48">
       <c r="A115" s="2" t="n">
         <v>114</v>
       </c>
@@ -12339,7 +12370,7 @@
           <t>ogimet</t>
         </is>
       </c>
-      <c r="C115" s="27" t="n">
+      <c r="C115" s="46" t="n">
         <v>52908</v>
       </c>
       <c r="D115" s="2" t="inlineStr">
@@ -12380,10 +12411,10 @@
         </is>
       </c>
       <c r="O115" s="32" t="n">
-        <v>-20.5</v>
+        <v>-23.3</v>
       </c>
       <c r="P115" s="32" t="n">
-        <v>-2.8</v>
+        <v>-3.7</v>
       </c>
       <c r="Q115" s="32" t="n"/>
       <c r="R115" s="23" t="inlineStr">
@@ -12452,7 +12483,7 @@
       </c>
       <c r="AH115" s="2" t="n"/>
     </row>
-    <row r="116" ht="24" customHeight="1" s="45">
+    <row r="116" ht="24" customHeight="1" s="48">
       <c r="A116" s="2" t="n">
         <v>115</v>
       </c>
@@ -12461,7 +12492,7 @@
           <t>ogimet</t>
         </is>
       </c>
-      <c r="C116" s="27" t="n">
+      <c r="C116" s="46" t="n">
         <v>52323</v>
       </c>
       <c r="D116" s="2" t="inlineStr">
@@ -12498,13 +12529,13 @@
       </c>
       <c r="N116" s="2" t="n"/>
       <c r="O116" s="32" t="n">
-        <v>-12.7</v>
+        <v>-6.5</v>
       </c>
       <c r="P116" s="32" t="n">
-        <v>4.1</v>
+        <v>6.8</v>
       </c>
       <c r="Q116" s="32" t="n">
-        <v>-5.79</v>
+        <v>-0.71</v>
       </c>
       <c r="R116" s="23" t="inlineStr">
         <is>
@@ -12572,12 +12603,12 @@
       </c>
       <c r="AH116" s="2" t="n"/>
     </row>
-    <row r="117" ht="24" customHeight="1" s="45">
+    <row r="117" ht="24" customHeight="1" s="48">
       <c r="A117" s="2" t="n">
         <v>116</v>
       </c>
       <c r="B117" s="2" t="n"/>
-      <c r="C117" s="27" t="n">
+      <c r="C117" s="46" t="n">
         <v>52101</v>
       </c>
       <c r="D117" s="2" t="n"/>
@@ -12610,10 +12641,10 @@
       </c>
       <c r="N117" s="2" t="n"/>
       <c r="O117" s="32" t="n">
-        <v>-9.1</v>
+        <v>-11.9</v>
       </c>
       <c r="P117" s="32" t="n">
-        <v>1.3</v>
+        <v>-2.4</v>
       </c>
       <c r="Q117" s="32" t="n"/>
       <c r="R117" s="23" t="inlineStr">
@@ -12682,12 +12713,12 @@
       </c>
       <c r="AH117" s="2" t="n"/>
     </row>
-    <row r="118" ht="24" customHeight="1" s="45">
+    <row r="118" ht="24" customHeight="1" s="48">
       <c r="A118" s="2" t="n">
         <v>117</v>
       </c>
       <c r="B118" s="2" t="n"/>
-      <c r="C118" s="27" t="n">
+      <c r="C118" s="46" t="n">
         <v>51186</v>
       </c>
       <c r="D118" s="2" t="n"/>
@@ -12724,10 +12755,10 @@
         </is>
       </c>
       <c r="O118" s="32" t="n">
-        <v>-20.7</v>
+        <v>-15.1</v>
       </c>
       <c r="P118" s="32" t="n">
-        <v>-6.2</v>
+        <v>-7.8</v>
       </c>
       <c r="Q118" s="32" t="n"/>
       <c r="R118" s="23" t="inlineStr">
@@ -12796,7 +12827,7 @@
       </c>
       <c r="AH118" s="2" t="n"/>
     </row>
-    <row r="119" ht="24" customHeight="1" s="45">
+    <row r="119" ht="24" customHeight="1" s="48">
       <c r="A119" s="2" t="n">
         <v>118</v>
       </c>
@@ -12805,7 +12836,7 @@
           <t>ogimet</t>
         </is>
       </c>
-      <c r="C119" s="27" t="n">
+      <c r="C119" s="46" t="n">
         <v>51076</v>
       </c>
       <c r="D119" s="2" t="inlineStr">
@@ -12842,13 +12873,13 @@
       </c>
       <c r="N119" s="2" t="n"/>
       <c r="O119" s="32" t="n">
-        <v>-14.1</v>
+        <v>-27.4</v>
       </c>
       <c r="P119" s="32" t="n">
-        <v>-3.4</v>
+        <v>-17.4</v>
       </c>
       <c r="Q119" s="32" t="n">
-        <v>-8.24</v>
+        <v>-22.2</v>
       </c>
       <c r="R119" s="23" t="inlineStr">
         <is>
@@ -12924,7 +12955,7 @@
       </c>
       <c r="AH119" s="2" t="n"/>
     </row>
-    <row r="120" ht="24" customHeight="1" s="45">
+    <row r="120" ht="24" customHeight="1" s="48">
       <c r="A120" s="2" t="n">
         <v>119</v>
       </c>
@@ -12933,7 +12964,7 @@
           <t>ogimet</t>
         </is>
       </c>
-      <c r="C120" s="27" t="n">
+      <c r="C120" s="46" t="n">
         <v>51573</v>
       </c>
       <c r="D120" s="2" t="inlineStr">
@@ -13030,7 +13061,7 @@
       </c>
       <c r="AH120" s="2" t="n"/>
     </row>
-    <row r="121" ht="24" customHeight="1" s="45">
+    <row r="121" ht="24" customHeight="1" s="48">
       <c r="A121" s="2" t="n">
         <v>120</v>
       </c>
@@ -13039,7 +13070,7 @@
           <t>ogimet</t>
         </is>
       </c>
-      <c r="C121" s="27" t="n">
+      <c r="C121" s="46" t="n">
         <v>51463</v>
       </c>
       <c r="D121" s="2" t="inlineStr">
@@ -13076,13 +13107,13 @@
       </c>
       <c r="N121" s="2" t="n"/>
       <c r="O121" s="32" t="n">
-        <v>-10.4</v>
+        <v>-12</v>
       </c>
       <c r="P121" s="32" t="n">
-        <v>1.4</v>
+        <v>-8.6</v>
       </c>
       <c r="Q121" s="32" t="n">
-        <v>-2.16</v>
+        <v>-10.47</v>
       </c>
       <c r="R121" s="23" t="inlineStr">
         <is>
@@ -13154,7 +13185,7 @@
       </c>
       <c r="AH121" s="2" t="n"/>
     </row>
-    <row r="122" ht="24" customHeight="1" s="45">
+    <row r="122" ht="24" customHeight="1" s="48">
       <c r="A122" s="2" t="n">
         <v>121</v>
       </c>
@@ -13163,7 +13194,7 @@
           <t>ogimet</t>
         </is>
       </c>
-      <c r="C122" s="27" t="n">
+      <c r="C122" s="46" t="n">
         <v>51542</v>
       </c>
       <c r="D122" s="2" t="inlineStr">
@@ -13200,10 +13231,10 @@
       </c>
       <c r="N122" s="2" t="n"/>
       <c r="O122" s="32" t="n">
-        <v>-12.1</v>
+        <v>-12.9</v>
       </c>
       <c r="P122" s="32" t="n">
-        <v>-2.4</v>
+        <v>-5.4</v>
       </c>
       <c r="Q122" s="32" t="n"/>
       <c r="R122" s="23" t="inlineStr">
@@ -13272,12 +13303,12 @@
       </c>
       <c r="AH122" s="2" t="n"/>
     </row>
-    <row r="123" ht="24" customHeight="1" s="45">
+    <row r="123" ht="24" customHeight="1" s="48">
       <c r="A123" s="2" t="n">
         <v>122</v>
       </c>
       <c r="B123" s="2" t="n"/>
-      <c r="C123" s="27" t="n">
+      <c r="C123" s="46" t="n">
         <v>51437</v>
       </c>
       <c r="D123" s="2" t="n"/>
@@ -13378,7 +13409,7 @@
       </c>
       <c r="AH123" s="2" t="n"/>
     </row>
-    <row r="124" ht="24" customHeight="1" s="45">
+    <row r="124" ht="24" customHeight="1" s="48">
       <c r="A124" s="2" t="n">
         <v>123</v>
       </c>
@@ -13387,7 +13418,7 @@
           <t>ogimet</t>
         </is>
       </c>
-      <c r="C124" s="27" t="n">
+      <c r="C124" s="46" t="n">
         <v>53463</v>
       </c>
       <c r="D124" s="2" t="inlineStr">
@@ -13424,13 +13455,13 @@
       </c>
       <c r="N124" s="2" t="n"/>
       <c r="O124" s="32" t="n">
-        <v>-11.4</v>
+        <v>-1.1</v>
       </c>
       <c r="P124" s="32" t="n">
-        <v>-2.3</v>
+        <v>5.8</v>
       </c>
       <c r="Q124" s="32" t="n">
-        <v>-7.34</v>
+        <v>2.23</v>
       </c>
       <c r="R124" s="23" t="inlineStr">
         <is>
@@ -13502,7 +13533,7 @@
       </c>
       <c r="AH124" s="2" t="n"/>
     </row>
-    <row r="125" ht="24" customHeight="1" s="45">
+    <row r="125" ht="24" customHeight="1" s="48">
       <c r="A125" s="2" t="n">
         <v>124</v>
       </c>
@@ -13511,7 +13542,7 @@
           <t>ogimet</t>
         </is>
       </c>
-      <c r="C125" s="27" t="n">
+      <c r="C125" s="46" t="n">
         <v>54511</v>
       </c>
       <c r="D125" s="2" t="inlineStr">
@@ -13548,13 +13579,13 @@
       </c>
       <c r="N125" s="2" t="n"/>
       <c r="O125" s="32" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="P125" s="32" t="n">
-        <v>12.6</v>
+        <v>3.6</v>
       </c>
       <c r="Q125" s="32" t="n">
-        <v>4.01</v>
+        <v>1.8</v>
       </c>
       <c r="R125" s="23" t="inlineStr">
         <is>
@@ -13614,12 +13645,12 @@
       <c r="AG125" s="2" t="n"/>
       <c r="AH125" s="2" t="n"/>
     </row>
-    <row r="126" ht="24" customHeight="1" s="45">
+    <row r="126" ht="24" customHeight="1" s="48">
       <c r="A126" s="2" t="n">
         <v>125</v>
       </c>
       <c r="B126" s="2" t="n"/>
-      <c r="C126" s="27" t="n">
+      <c r="C126" s="46" t="n">
         <v>54517</v>
       </c>
       <c r="D126" s="2" t="n"/>
@@ -13652,10 +13683,10 @@
       </c>
       <c r="N126" s="2" t="n"/>
       <c r="O126" s="32" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="P126" s="32" t="n">
-        <v>17.3</v>
+        <v>2.1</v>
       </c>
       <c r="Q126" s="32" t="n"/>
       <c r="R126" s="23" t="inlineStr">
@@ -13716,7 +13747,7 @@
         </is>
       </c>
     </row>
-    <row r="127" ht="24" customHeight="1" s="45">
+    <row r="127" ht="24" customHeight="1" s="48">
       <c r="A127" s="2" t="n">
         <v>126</v>
       </c>
@@ -13725,7 +13756,7 @@
           <t>ogimet</t>
         </is>
       </c>
-      <c r="C127" s="27" t="n">
+      <c r="C127" s="46" t="n">
         <v>53614</v>
       </c>
       <c r="D127" s="2" t="inlineStr">
@@ -13762,13 +13793,13 @@
       </c>
       <c r="N127" s="2" t="n"/>
       <c r="O127" s="32" t="n">
-        <v>-3.2</v>
+        <v>0.4</v>
       </c>
       <c r="P127" s="32" t="n">
-        <v>7.4</v>
+        <v>12.2</v>
       </c>
       <c r="Q127" s="32" t="n">
-        <v>2</v>
+        <v>6.54</v>
       </c>
       <c r="R127" s="23" t="inlineStr">
         <is>
@@ -13836,7 +13867,7 @@
       </c>
       <c r="AH127" s="2" t="n"/>
     </row>
-    <row r="128" ht="24" customHeight="1" s="45">
+    <row r="128" ht="24" customHeight="1" s="48">
       <c r="A128" s="2" t="n">
         <v>127</v>
       </c>
@@ -13845,7 +13876,7 @@
           <t>ogimet</t>
         </is>
       </c>
-      <c r="C128" s="27" t="n">
+      <c r="C128" s="46" t="n">
         <v>53698</v>
       </c>
       <c r="D128" s="2" t="inlineStr">
@@ -13882,10 +13913,10 @@
       </c>
       <c r="N128" s="2" t="n"/>
       <c r="O128" s="32" t="n">
-        <v>7.7</v>
+        <v>1.7</v>
       </c>
       <c r="P128" s="32" t="n">
-        <v>20.1</v>
+        <v>4.7</v>
       </c>
       <c r="Q128" s="32" t="n"/>
       <c r="R128" s="23" t="inlineStr">
@@ -13946,7 +13977,7 @@
       <c r="AG128" s="2" t="n"/>
       <c r="AH128" s="2" t="n"/>
     </row>
-    <row r="129" ht="24" customHeight="1" s="45">
+    <row r="129" ht="24" customHeight="1" s="48">
       <c r="A129" s="2" t="n">
         <v>128</v>
       </c>
@@ -13955,7 +13986,7 @@
           <t>ogimet</t>
         </is>
       </c>
-      <c r="C129" s="27" t="n">
+      <c r="C129" s="46" t="n">
         <v>53772</v>
       </c>
       <c r="D129" s="2" t="inlineStr">
@@ -13992,13 +14023,13 @@
       </c>
       <c r="N129" s="2" t="n"/>
       <c r="O129" s="32" t="n">
-        <v>1.7</v>
+        <v>2.3</v>
       </c>
       <c r="P129" s="32" t="n">
-        <v>12.3</v>
+        <v>5.9</v>
       </c>
       <c r="Q129" s="32" t="n">
-        <v>5.51</v>
+        <v>2.66</v>
       </c>
       <c r="R129" s="23" t="inlineStr">
         <is>
@@ -14066,7 +14097,7 @@
       </c>
       <c r="AH129" s="2" t="n"/>
     </row>
-    <row r="130" ht="24" customHeight="1" s="45">
+    <row r="130" ht="24" customHeight="1" s="48">
       <c r="A130" s="2" t="n">
         <v>129</v>
       </c>
@@ -14075,7 +14106,7 @@
           <t>ogimet</t>
         </is>
       </c>
-      <c r="C130" s="27" t="n">
+      <c r="C130" s="46" t="n">
         <v>52866</v>
       </c>
       <c r="D130" s="2" t="inlineStr">
@@ -14112,13 +14143,13 @@
       </c>
       <c r="N130" s="2" t="n"/>
       <c r="O130" s="32" t="n">
-        <v>-6.1</v>
+        <v>-3.6</v>
       </c>
       <c r="P130" s="32" t="n">
-        <v>11.9</v>
+        <v>10.9</v>
       </c>
       <c r="Q130" s="32" t="n">
-        <v>2.64</v>
+        <v>3.52</v>
       </c>
       <c r="R130" s="23" t="inlineStr">
         <is>
@@ -14186,7 +14217,7 @@
       </c>
       <c r="AH130" s="2" t="n"/>
     </row>
-    <row r="131" ht="24" customHeight="1" s="45">
+    <row r="131" ht="24" customHeight="1" s="48">
       <c r="A131" s="2" t="n">
         <v>130</v>
       </c>
@@ -14195,7 +14226,7 @@
           <t>ogimet</t>
         </is>
       </c>
-      <c r="C131" s="27" t="n">
+      <c r="C131" s="46" t="n">
         <v>54823</v>
       </c>
       <c r="D131" s="2" t="inlineStr">
@@ -14232,13 +14263,13 @@
       </c>
       <c r="N131" s="2" t="n"/>
       <c r="O131" s="32" t="n">
-        <v>6.3</v>
+        <v>3.9</v>
       </c>
       <c r="P131" s="32" t="n">
-        <v>20.5</v>
+        <v>11.5</v>
       </c>
       <c r="Q131" s="32" t="n">
-        <v>10.53</v>
+        <v>6.14</v>
       </c>
       <c r="R131" s="23" t="inlineStr">
         <is>
@@ -14302,7 +14333,7 @@
       </c>
       <c r="AH131" s="2" t="n"/>
     </row>
-    <row r="132" ht="24" customHeight="1" s="45">
+    <row r="132" ht="24" customHeight="1" s="48">
       <c r="A132" s="2" t="n">
         <v>131</v>
       </c>
@@ -14311,7 +14342,7 @@
           <t>ogimet</t>
         </is>
       </c>
-      <c r="C132" s="27" t="n">
+      <c r="C132" s="46" t="n">
         <v>57083</v>
       </c>
       <c r="D132" s="2" t="inlineStr">
@@ -14348,13 +14379,13 @@
       </c>
       <c r="N132" s="2" t="n"/>
       <c r="O132" s="32" t="n">
-        <v>13.2</v>
+        <v>3.3</v>
       </c>
       <c r="P132" s="32" t="n">
-        <v>21.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Q132" s="32" t="n">
-        <v>16.25</v>
+        <v>5.3</v>
       </c>
       <c r="R132" s="23" t="inlineStr">
         <is>
@@ -14418,7 +14449,7 @@
       </c>
       <c r="AH132" s="2" t="n"/>
     </row>
-    <row r="133" ht="24" customHeight="1" s="45">
+    <row r="133" ht="24" customHeight="1" s="48">
       <c r="A133" s="2" t="n">
         <v>132</v>
       </c>
@@ -14427,7 +14458,7 @@
           <t>ogimet</t>
         </is>
       </c>
-      <c r="C133" s="27" t="n">
+      <c r="C133" s="46" t="n">
         <v>57131</v>
       </c>
       <c r="D133" s="2" t="inlineStr">
@@ -14464,13 +14495,13 @@
       </c>
       <c r="N133" s="2" t="n"/>
       <c r="O133" s="32" t="n">
-        <v>10</v>
+        <v>6.5</v>
       </c>
       <c r="P133" s="32" t="n">
-        <v>19.5</v>
+        <v>9.5</v>
       </c>
       <c r="Q133" s="32" t="n">
-        <v>13.99</v>
+        <v>7.74</v>
       </c>
       <c r="R133" s="23" t="inlineStr">
         <is>
@@ -14538,7 +14569,7 @@
         </is>
       </c>
     </row>
-    <row r="134" ht="24" customHeight="1" s="45">
+    <row r="134" ht="24" customHeight="1" s="48">
       <c r="A134" s="2" t="n">
         <v>133</v>
       </c>
@@ -14547,7 +14578,7 @@
           <t>ogimet</t>
         </is>
       </c>
-      <c r="C134" s="27" t="n">
+      <c r="C134" s="46" t="n">
         <v>57245</v>
       </c>
       <c r="D134" s="2" t="inlineStr">
@@ -14640,7 +14671,7 @@
       </c>
       <c r="AH134" s="2" t="n"/>
     </row>
-    <row r="135" ht="24" customHeight="1" s="45">
+    <row r="135" ht="24" customHeight="1" s="48">
       <c r="A135" s="2" t="n">
         <v>134</v>
       </c>
@@ -14649,7 +14680,7 @@
           <t>ogimet</t>
         </is>
       </c>
-      <c r="C135" s="27" t="n">
+      <c r="C135" s="46" t="n">
         <v>57687</v>
       </c>
       <c r="D135" s="2" t="inlineStr">
@@ -14686,13 +14717,13 @@
       </c>
       <c r="N135" s="2" t="n"/>
       <c r="O135" s="32" t="n">
-        <v>12.1</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="P135" s="32" t="n">
-        <v>25.9</v>
+        <v>10.9</v>
       </c>
       <c r="Q135" s="32" t="n">
-        <v>17.94</v>
+        <v>9.49</v>
       </c>
       <c r="R135" s="23" t="inlineStr">
         <is>
@@ -14756,7 +14787,7 @@
       </c>
       <c r="AH135" s="2" t="n"/>
     </row>
-    <row r="136" ht="24" customHeight="1" s="45">
+    <row r="136" ht="24" customHeight="1" s="48">
       <c r="A136" s="2" t="n">
         <v>135</v>
       </c>
@@ -14765,7 +14796,7 @@
           <t>ogimet</t>
         </is>
       </c>
-      <c r="C136" s="27" t="n">
+      <c r="C136" s="46" t="n">
         <v>58606</v>
       </c>
       <c r="D136" s="2" t="inlineStr">
@@ -14802,13 +14833,13 @@
       </c>
       <c r="N136" s="2" t="n"/>
       <c r="O136" s="32" t="n">
-        <v>11.8</v>
+        <v>10</v>
       </c>
       <c r="P136" s="32" t="n">
-        <v>25.3</v>
+        <v>13.5</v>
       </c>
       <c r="Q136" s="32" t="n">
-        <v>18.14</v>
+        <v>11.55</v>
       </c>
       <c r="R136" s="23" t="inlineStr">
         <is>
@@ -14872,7 +14903,7 @@
       </c>
       <c r="AH136" s="2" t="n"/>
     </row>
-    <row r="137" ht="24" customHeight="1" s="45">
+    <row r="137" ht="24" customHeight="1" s="48">
       <c r="A137" s="2" t="n">
         <v>136</v>
       </c>
@@ -14881,7 +14912,7 @@
           <t>ogimet</t>
         </is>
       </c>
-      <c r="C137" s="27" t="n">
+      <c r="C137" s="46" t="n">
         <v>57494</v>
       </c>
       <c r="D137" s="2" t="inlineStr">
@@ -14918,13 +14949,13 @@
       </c>
       <c r="N137" s="2" t="n"/>
       <c r="O137" s="32" t="n">
-        <v>7.6</v>
+        <v>9.9</v>
       </c>
       <c r="P137" s="32" t="n">
-        <v>25</v>
+        <v>13.8</v>
       </c>
       <c r="Q137" s="32" t="n">
-        <v>15.95</v>
+        <v>11.42</v>
       </c>
       <c r="R137" s="23" t="inlineStr">
         <is>
@@ -14988,7 +15019,7 @@
       </c>
       <c r="AH137" s="2" t="n"/>
     </row>
-    <row r="138" ht="24" customHeight="1" s="45">
+    <row r="138" ht="24" customHeight="1" s="48">
       <c r="A138" s="2" t="n">
         <v>137</v>
       </c>
@@ -14997,7 +15028,7 @@
           <t>ogimet</t>
         </is>
       </c>
-      <c r="C138" s="27" t="n">
+      <c r="C138" s="46" t="n">
         <v>58321</v>
       </c>
       <c r="D138" s="2" t="inlineStr">
@@ -15034,10 +15065,10 @@
       </c>
       <c r="N138" s="2" t="n"/>
       <c r="O138" s="32" t="n">
-        <v>7</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="P138" s="32" t="n">
-        <v>21.4</v>
+        <v>13.8</v>
       </c>
       <c r="Q138" s="32" t="n"/>
       <c r="R138" s="23" t="inlineStr">
@@ -15102,7 +15133,7 @@
       </c>
       <c r="AH138" s="2" t="n"/>
     </row>
-    <row r="139" ht="24" customHeight="1" s="45">
+    <row r="139" ht="24" customHeight="1" s="48">
       <c r="A139" s="2" t="n">
         <v>138</v>
       </c>
@@ -15111,7 +15142,7 @@
           <t>ogimet</t>
         </is>
       </c>
-      <c r="C139" s="27" t="n">
+      <c r="C139" s="46" t="n">
         <v>58238</v>
       </c>
       <c r="D139" s="2" t="inlineStr">
@@ -15148,13 +15179,13 @@
       </c>
       <c r="N139" s="2" t="n"/>
       <c r="O139" s="32" t="n">
-        <v>11</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="P139" s="32" t="n">
-        <v>21.9</v>
+        <v>13.4</v>
       </c>
       <c r="Q139" s="32" t="n">
-        <v>16.36</v>
+        <v>10.49</v>
       </c>
       <c r="R139" s="23" t="inlineStr">
         <is>
@@ -15218,7 +15249,7 @@
       </c>
       <c r="AH139" s="2" t="n"/>
     </row>
-    <row r="140" ht="24" customHeight="1" s="45">
+    <row r="140" ht="24" customHeight="1" s="48">
       <c r="A140" s="2" t="n">
         <v>139</v>
       </c>
@@ -15227,7 +15258,7 @@
           <t>ogimet</t>
         </is>
       </c>
-      <c r="C140" s="27" t="n">
+      <c r="C140" s="46" t="n">
         <v>58457</v>
       </c>
       <c r="D140" s="2" t="inlineStr">
@@ -15264,13 +15295,13 @@
       </c>
       <c r="N140" s="2" t="n"/>
       <c r="O140" s="32" t="n">
-        <v>10.8</v>
+        <v>9.5</v>
       </c>
       <c r="P140" s="32" t="n">
-        <v>25.8</v>
+        <v>12.8</v>
       </c>
       <c r="Q140" s="32" t="n">
-        <v>17.16</v>
+        <v>10.96</v>
       </c>
       <c r="R140" s="23" t="inlineStr">
         <is>
@@ -15334,7 +15365,7 @@
       </c>
       <c r="AH140" s="2" t="n"/>
     </row>
-    <row r="141" ht="24" customHeight="1" s="45">
+    <row r="141" ht="24" customHeight="1" s="48">
       <c r="A141" s="2" t="n">
         <v>140</v>
       </c>
@@ -15343,7 +15374,7 @@
           <t>ogimet</t>
         </is>
       </c>
-      <c r="C141" s="27" t="n">
+      <c r="C141" s="46" t="n">
         <v>58646</v>
       </c>
       <c r="D141" s="2" t="inlineStr">
@@ -15436,7 +15467,7 @@
       </c>
       <c r="AH141" s="2" t="n"/>
     </row>
-    <row r="142" ht="24" customHeight="1" s="45">
+    <row r="142" ht="24" customHeight="1" s="48">
       <c r="A142" s="2" t="n">
         <v>141</v>
       </c>
@@ -15445,7 +15476,7 @@
           <t>ogimet</t>
         </is>
       </c>
-      <c r="C142" s="27" t="n">
+      <c r="C142" s="46" t="n">
         <v>58847</v>
       </c>
       <c r="D142" s="2" t="inlineStr">
@@ -15482,13 +15513,13 @@
       </c>
       <c r="N142" s="2" t="n"/>
       <c r="O142" s="32" t="n">
-        <v>13.7</v>
+        <v>12.8</v>
       </c>
       <c r="P142" s="32" t="n">
-        <v>29</v>
+        <v>15.7</v>
       </c>
       <c r="Q142" s="32" t="n">
-        <v>20.07</v>
+        <v>14.18</v>
       </c>
       <c r="R142" s="23" t="inlineStr">
         <is>
@@ -15552,7 +15583,7 @@
       </c>
       <c r="AH142" s="2" t="n"/>
     </row>
-    <row r="143" ht="24" customHeight="1" s="45">
+    <row r="143" ht="24" customHeight="1" s="48">
       <c r="A143" s="2" t="n">
         <v>142</v>
       </c>
@@ -15561,7 +15592,7 @@
           <t>ogimet</t>
         </is>
       </c>
-      <c r="C143" s="27" t="n">
+      <c r="C143" s="46" t="n">
         <v>59287</v>
       </c>
       <c r="D143" s="2" t="inlineStr">
@@ -15598,13 +15629,13 @@
       </c>
       <c r="N143" s="2" t="n"/>
       <c r="O143" s="32" t="n">
-        <v>17.7</v>
+        <v>19.8</v>
       </c>
       <c r="P143" s="32" t="n">
-        <v>28.5</v>
+        <v>23.2</v>
       </c>
       <c r="Q143" s="32" t="n">
-        <v>21.82</v>
+        <v>21.25</v>
       </c>
       <c r="R143" s="23" t="inlineStr">
         <is>
@@ -15668,7 +15699,7 @@
       </c>
       <c r="AH143" s="2" t="n"/>
     </row>
-    <row r="144" ht="24" customHeight="1" s="45">
+    <row r="144" ht="24" customHeight="1" s="48">
       <c r="A144" s="2" t="n">
         <v>143</v>
       </c>
@@ -15677,7 +15708,7 @@
           <t>ogimet</t>
         </is>
       </c>
-      <c r="C144" s="27" t="n">
+      <c r="C144" s="46" t="n">
         <v>59758</v>
       </c>
       <c r="D144" s="2" t="inlineStr">
@@ -15770,7 +15801,7 @@
       <c r="AG144" s="2" t="n"/>
       <c r="AH144" s="2" t="n"/>
     </row>
-    <row r="145" ht="24" customHeight="1" s="45">
+    <row r="145" ht="24" customHeight="1" s="48">
       <c r="A145" s="2" t="n">
         <v>144</v>
       </c>
@@ -15779,7 +15810,7 @@
           <t>ogimet</t>
         </is>
       </c>
-      <c r="C145" s="27" t="n">
+      <c r="C145" s="46" t="n">
         <v>59948</v>
       </c>
       <c r="D145" s="2" t="inlineStr">
@@ -15868,7 +15899,7 @@
       <c r="AG145" s="2" t="n"/>
       <c r="AH145" s="2" t="n"/>
     </row>
-    <row r="146" ht="24" customHeight="1" s="45">
+    <row r="146" ht="24" customHeight="1" s="48">
       <c r="A146" s="2" t="n">
         <v>145</v>
       </c>
@@ -15877,7 +15908,7 @@
           <t>ogimet</t>
         </is>
       </c>
-      <c r="C146" s="27" t="n">
+      <c r="C146" s="46" t="n">
         <v>59838</v>
       </c>
       <c r="D146" s="2" t="inlineStr">
@@ -15914,13 +15945,13 @@
       </c>
       <c r="N146" s="2" t="n"/>
       <c r="O146" s="32" t="n">
-        <v>20.4</v>
+        <v>23.6</v>
       </c>
       <c r="P146" s="32" t="n">
-        <v>27.5</v>
+        <v>30</v>
       </c>
       <c r="Q146" s="32" t="n">
-        <v>23.7</v>
+        <v>26.95</v>
       </c>
       <c r="R146" s="23" t="inlineStr">
         <is>
@@ -15976,7 +16007,7 @@
       <c r="AG146" s="2" t="n"/>
       <c r="AH146" s="2" t="n"/>
     </row>
-    <row r="147" ht="24" customHeight="1" s="45">
+    <row r="147" ht="24" customHeight="1" s="48">
       <c r="A147" s="2" t="n">
         <v>146</v>
       </c>
@@ -15985,7 +16016,7 @@
           <t>ogimet</t>
         </is>
       </c>
-      <c r="C147" s="27" t="n">
+      <c r="C147" s="46" t="n">
         <v>59431</v>
       </c>
       <c r="D147" s="2" t="inlineStr">
@@ -16022,13 +16053,13 @@
       </c>
       <c r="N147" s="2" t="n"/>
       <c r="O147" s="32" t="n">
-        <v>18.6</v>
+        <v>21.3</v>
       </c>
       <c r="P147" s="32" t="n">
-        <v>26.8</v>
+        <v>25.6</v>
       </c>
       <c r="Q147" s="32" t="n">
-        <v>22.1</v>
+        <v>22.8</v>
       </c>
       <c r="R147" s="23" t="inlineStr">
         <is>
@@ -16092,7 +16123,7 @@
       </c>
       <c r="AH147" s="2" t="n"/>
     </row>
-    <row r="148" ht="24" customHeight="1" s="45">
+    <row r="148" ht="24" customHeight="1" s="48">
       <c r="A148" s="2" t="n">
         <v>147</v>
       </c>
@@ -16101,7 +16132,7 @@
           <t>ogimet</t>
         </is>
       </c>
-      <c r="C148" s="27" t="n">
+      <c r="C148" s="46" t="n">
         <v>56966</v>
       </c>
       <c r="D148" s="2" t="inlineStr">
@@ -16194,7 +16225,7 @@
       </c>
       <c r="AH148" s="2" t="n"/>
     </row>
-    <row r="149" ht="24" customHeight="1" s="45">
+    <row r="149" ht="24" customHeight="1" s="48">
       <c r="A149" s="2" t="n">
         <v>148</v>
       </c>
@@ -16203,7 +16234,7 @@
           <t>ogimet</t>
         </is>
       </c>
-      <c r="C149" s="27" t="n">
+      <c r="C149" s="46" t="n">
         <v>56778</v>
       </c>
       <c r="D149" s="2" t="inlineStr">
@@ -16240,13 +16271,13 @@
       </c>
       <c r="N149" s="2" t="n"/>
       <c r="O149" s="32" t="n">
-        <v>9.699999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="P149" s="32" t="n">
-        <v>22.2</v>
+        <v>18.5</v>
       </c>
       <c r="Q149" s="32" t="n">
-        <v>16.01</v>
+        <v>13.96</v>
       </c>
       <c r="R149" s="23" t="inlineStr">
         <is>
@@ -16310,7 +16341,7 @@
       </c>
       <c r="AH149" s="2" t="n"/>
     </row>
-    <row r="150" ht="24" customHeight="1" s="45">
+    <row r="150" ht="24" customHeight="1" s="48">
       <c r="A150" s="2" t="n">
         <v>149</v>
       </c>
@@ -16319,7 +16350,7 @@
           <t>ogimet</t>
         </is>
       </c>
-      <c r="C150" s="27" t="n">
+      <c r="C150" s="46" t="n">
         <v>57816</v>
       </c>
       <c r="D150" s="2" t="inlineStr">
@@ -16356,13 +16387,13 @@
       </c>
       <c r="N150" s="2" t="n"/>
       <c r="O150" s="32" t="n">
-        <v>12.1</v>
+        <v>8</v>
       </c>
       <c r="P150" s="32" t="n">
-        <v>17.3</v>
+        <v>22.4</v>
       </c>
       <c r="Q150" s="32" t="n">
-        <v>13.99</v>
+        <v>12.06</v>
       </c>
       <c r="R150" s="23" t="inlineStr">
         <is>
@@ -16426,7 +16457,7 @@
       </c>
       <c r="AH150" s="2" t="n"/>
     </row>
-    <row r="151" ht="24" customHeight="1" s="45">
+    <row r="151" ht="24" customHeight="1" s="48">
       <c r="A151" s="2" t="n">
         <v>150</v>
       </c>
@@ -16435,7 +16466,7 @@
           <t>ogimet</t>
         </is>
       </c>
-      <c r="C151" s="27" t="n">
+      <c r="C151" s="46" t="n">
         <v>57516</v>
       </c>
       <c r="D151" s="2" t="inlineStr">
@@ -16472,13 +16503,13 @@
       </c>
       <c r="N151" s="2" t="n"/>
       <c r="O151" s="32" t="n">
-        <v>13</v>
+        <v>15.6</v>
       </c>
       <c r="P151" s="32" t="n">
-        <v>24.7</v>
+        <v>18.5</v>
       </c>
       <c r="Q151" s="32" t="n">
-        <v>17.89</v>
+        <v>16.64</v>
       </c>
       <c r="R151" s="23" t="inlineStr">
         <is>
@@ -16538,12 +16569,12 @@
       </c>
       <c r="AH151" s="2" t="n"/>
     </row>
-    <row r="152" ht="24" customHeight="1" s="45">
+    <row r="152" ht="24" customHeight="1" s="48">
       <c r="A152" s="2" t="n">
         <v>151</v>
       </c>
       <c r="B152" s="2" t="n"/>
-      <c r="C152" s="27" t="n">
+      <c r="C152" s="46" t="n">
         <v>57413</v>
       </c>
       <c r="D152" s="2" t="n"/>
@@ -16632,7 +16663,7 @@
       </c>
       <c r="AH152" s="2" t="n"/>
     </row>
-    <row r="153" ht="24" customHeight="1" s="45">
+    <row r="153" ht="24" customHeight="1" s="48">
       <c r="A153" s="2" t="n">
         <v>152</v>
       </c>
@@ -16641,7 +16672,7 @@
           <t>ogimet</t>
         </is>
       </c>
-      <c r="C153" s="27" t="n">
+      <c r="C153" s="46" t="n">
         <v>56187</v>
       </c>
       <c r="D153" s="2" t="inlineStr">
@@ -16678,13 +16709,13 @@
       </c>
       <c r="N153" s="2" t="n"/>
       <c r="O153" s="32" t="n">
-        <v>7.7</v>
+        <v>12.9</v>
       </c>
       <c r="P153" s="32" t="n">
-        <v>21.9</v>
+        <v>15.4</v>
       </c>
       <c r="Q153" s="32" t="n">
-        <v>13.97</v>
+        <v>13.57</v>
       </c>
       <c r="R153" s="23" t="inlineStr">
         <is>
@@ -16752,7 +16783,7 @@
         </is>
       </c>
     </row>
-    <row r="154" ht="24" customHeight="1" s="45">
+    <row r="154" ht="24" customHeight="1" s="48">
       <c r="A154" s="2" t="n">
         <v>153</v>
       </c>
@@ -16761,7 +16792,7 @@
           <t>ogimet</t>
         </is>
       </c>
-      <c r="C154" s="27" t="n">
+      <c r="C154" s="46" t="n">
         <v>55591</v>
       </c>
       <c r="D154" s="2" t="inlineStr">
@@ -16798,13 +16829,13 @@
       </c>
       <c r="N154" s="2" t="n"/>
       <c r="O154" s="32" t="n">
-        <v>-1.3</v>
+        <v>-0.7</v>
       </c>
       <c r="P154" s="32" t="n">
-        <v>9.1</v>
+        <v>16.8</v>
       </c>
       <c r="Q154" s="32" t="n">
-        <v>3.17</v>
+        <v>7.68</v>
       </c>
       <c r="R154" s="23" t="inlineStr">
         <is>
@@ -16868,12 +16899,12 @@
       </c>
       <c r="AH154" s="2" t="n"/>
     </row>
-    <row r="155" ht="24" customHeight="1" s="45">
+    <row r="155" ht="24" customHeight="1" s="48">
       <c r="A155" s="2" t="n">
         <v>154</v>
       </c>
       <c r="B155" s="2" t="n"/>
-      <c r="C155" s="27" t="n">
+      <c r="C155" s="46" t="n">
         <v>52267</v>
       </c>
       <c r="D155" s="2" t="n"/>
@@ -16962,12 +16993,12 @@
       </c>
       <c r="AH155" s="2" t="n"/>
     </row>
-    <row r="156" ht="24" customHeight="1" s="45">
+    <row r="156" ht="24" customHeight="1" s="48">
       <c r="A156" s="2" t="n">
         <v>155</v>
       </c>
       <c r="B156" s="2" t="n"/>
-      <c r="C156" s="27" t="n">
+      <c r="C156" s="46" t="n">
         <v>53478</v>
       </c>
       <c r="D156" s="2" t="n"/>
@@ -17000,10 +17031,10 @@
       </c>
       <c r="N156" s="2" t="n"/>
       <c r="O156" s="32" t="n">
-        <v>-10.5</v>
+        <v>-2.9</v>
       </c>
       <c r="P156" s="32" t="n">
-        <v>-3.1</v>
+        <v>4</v>
       </c>
       <c r="Q156" s="32" t="n"/>
       <c r="R156" s="23" t="inlineStr">
@@ -17068,12 +17099,12 @@
       <c r="AG156" s="2" t="n"/>
       <c r="AH156" s="2" t="n"/>
     </row>
-    <row r="157" ht="24" customHeight="1" s="45">
+    <row r="157" ht="24" customHeight="1" s="48">
       <c r="A157" s="2" t="n">
         <v>156</v>
       </c>
       <c r="B157" s="2" t="n"/>
-      <c r="C157" s="27" t="n">
+      <c r="C157" s="46" t="n">
         <v>58367</v>
       </c>
       <c r="D157" s="2" t="n"/>
@@ -17106,10 +17137,10 @@
       </c>
       <c r="N157" s="2" t="n"/>
       <c r="O157" s="32" t="n">
-        <v>10.6</v>
+        <v>8.6</v>
       </c>
       <c r="P157" s="32" t="n">
-        <v>22.3</v>
+        <v>14</v>
       </c>
       <c r="Q157" s="32" t="n"/>
       <c r="R157" s="23" t="inlineStr">
@@ -17174,12 +17205,12 @@
       </c>
       <c r="AH157" s="2" t="n"/>
     </row>
-    <row r="158" ht="24" customHeight="1" s="45">
+    <row r="158" ht="24" customHeight="1" s="48">
       <c r="A158" s="2" t="n">
         <v>157</v>
       </c>
       <c r="B158" s="2" t="n"/>
-      <c r="C158" s="27" t="n">
+      <c r="C158" s="46" t="n">
         <v>58826</v>
       </c>
       <c r="D158" s="2" t="n"/>
@@ -17268,12 +17299,12 @@
       </c>
       <c r="AH158" s="2" t="n"/>
     </row>
-    <row r="159" ht="24" customHeight="1" s="45">
+    <row r="159" ht="24" customHeight="1" s="48">
       <c r="A159" s="2" t="n">
         <v>158</v>
       </c>
       <c r="B159" s="2" t="n"/>
-      <c r="C159" s="27" t="n">
+      <c r="C159" s="46" t="n">
         <v>58623</v>
       </c>
       <c r="D159" s="2" t="n"/>
@@ -17362,12 +17393,12 @@
       </c>
       <c r="AH159" s="2" t="n"/>
     </row>
-    <row r="160" ht="24" customHeight="1" s="45">
+    <row r="160" ht="24" customHeight="1" s="48">
       <c r="A160" s="2" t="n">
         <v>159</v>
       </c>
       <c r="B160" s="2" t="n"/>
-      <c r="C160" s="27" t="n">
+      <c r="C160" s="46" t="n">
         <v>57778</v>
       </c>
       <c r="D160" s="2" t="n"/>
@@ -17456,12 +17487,12 @@
       </c>
       <c r="AH160" s="2" t="n"/>
     </row>
-    <row r="161" ht="24" customHeight="1" s="45">
+    <row r="161" ht="24" customHeight="1" s="48">
       <c r="A161" s="2" t="n">
         <v>160</v>
       </c>
       <c r="B161" s="2" t="n"/>
-      <c r="C161" s="27" t="n">
+      <c r="C161" s="46" t="n">
         <v>52889</v>
       </c>
       <c r="D161" s="2" t="n"/>
@@ -17494,10 +17525,10 @@
       </c>
       <c r="N161" s="2" t="n"/>
       <c r="O161" s="32" t="n">
-        <v>-0.5</v>
+        <v>1.7</v>
       </c>
       <c r="P161" s="32" t="n">
-        <v>13.1</v>
+        <v>13.7</v>
       </c>
       <c r="Q161" s="32" t="n"/>
       <c r="R161" s="23" t="inlineStr">
@@ -17566,12 +17597,12 @@
         </is>
       </c>
     </row>
-    <row r="162" ht="24" customHeight="1" s="45">
+    <row r="162" ht="24" customHeight="1" s="48">
       <c r="A162" s="2" t="n">
         <v>161</v>
       </c>
       <c r="B162" s="2" t="n"/>
-      <c r="C162" s="27" t="n">
+      <c r="C162" s="46" t="n">
         <v>50341</v>
       </c>
       <c r="D162" s="2" t="n"/>
@@ -17607,8 +17638,12 @@
           <t>⚡</t>
         </is>
       </c>
-      <c r="O162" s="32" t="n"/>
-      <c r="P162" s="32" t="n"/>
+      <c r="O162" s="32" t="n">
+        <v>-43.5</v>
+      </c>
+      <c r="P162" s="32" t="n">
+        <v>-12.2</v>
+      </c>
       <c r="Q162" s="32" t="n"/>
       <c r="R162" s="23" t="inlineStr">
         <is>
@@ -17676,12 +17711,12 @@
         </is>
       </c>
     </row>
-    <row r="163" ht="24" customHeight="1" s="45">
+    <row r="163" ht="24" customHeight="1" s="48">
       <c r="A163" s="2" t="n">
         <v>162</v>
       </c>
       <c r="B163" s="2" t="n"/>
-      <c r="C163" s="27" t="n"/>
+      <c r="C163" s="46" t="n"/>
       <c r="D163" s="2" t="n"/>
       <c r="E163" s="4" t="n"/>
       <c r="F163" s="39" t="inlineStr">
@@ -17717,12 +17752,8 @@
           <t>▼</t>
         </is>
       </c>
-      <c r="O163" s="32" t="n">
-        <v>-17.2</v>
-      </c>
-      <c r="P163" s="32" t="n">
-        <v>-11.8</v>
-      </c>
+      <c r="O163" s="32" t="n"/>
+      <c r="P163" s="32" t="n"/>
       <c r="Q163" s="32" t="n"/>
       <c r="R163" s="23" t="inlineStr">
         <is>
@@ -17786,12 +17817,12 @@
       </c>
       <c r="AH163" s="2" t="n"/>
     </row>
-    <row r="164" ht="24" customHeight="1" s="45">
+    <row r="164" ht="24" customHeight="1" s="48">
       <c r="A164" s="2" t="n">
         <v>163</v>
       </c>
       <c r="B164" s="2" t="n"/>
-      <c r="C164" s="27" t="n"/>
+      <c r="C164" s="46" t="n"/>
       <c r="D164" s="2" t="n"/>
       <c r="E164" s="4" t="n"/>
       <c r="F164" s="39" t="inlineStr">
@@ -17896,12 +17927,12 @@
       </c>
       <c r="AH164" s="2" t="n"/>
     </row>
-    <row r="165" ht="24" customHeight="1" s="45">
+    <row r="165" ht="24" customHeight="1" s="48">
       <c r="A165" s="2" t="n">
         <v>164</v>
       </c>
       <c r="B165" s="2" t="n"/>
-      <c r="C165" s="27" t="n"/>
+      <c r="C165" s="46" t="n"/>
       <c r="D165" s="2" t="n"/>
       <c r="E165" s="4" t="n"/>
       <c r="F165" s="39" t="inlineStr">
@@ -17938,10 +17969,10 @@
         </is>
       </c>
       <c r="O165" s="32" t="n">
-        <v>-16.6</v>
+        <v>-44.2</v>
       </c>
       <c r="P165" s="32" t="n">
-        <v>-6.9</v>
+        <v>-17.7</v>
       </c>
       <c r="Q165" s="32" t="n"/>
       <c r="R165" s="23" t="inlineStr">
@@ -18010,12 +18041,12 @@
       </c>
       <c r="AH165" s="2" t="n"/>
     </row>
-    <row r="166" ht="24" customHeight="1" s="45">
+    <row r="166" ht="24" customHeight="1" s="48">
       <c r="A166" s="2" t="n">
         <v>165</v>
       </c>
       <c r="B166" s="2" t="n"/>
-      <c r="C166" s="27" t="n"/>
+      <c r="C166" s="46" t="n"/>
       <c r="D166" s="2" t="n"/>
       <c r="E166" s="4" t="n"/>
       <c r="F166" s="39" t="inlineStr">
@@ -18120,12 +18151,12 @@
         </is>
       </c>
     </row>
-    <row r="167" ht="24" customHeight="1" s="45">
+    <row r="167" ht="24" customHeight="1" s="48">
       <c r="A167" s="2" t="n">
         <v>166</v>
       </c>
       <c r="B167" s="2" t="n"/>
-      <c r="C167" s="27" t="n"/>
+      <c r="C167" s="46" t="n"/>
       <c r="D167" s="2" t="n"/>
       <c r="E167" s="4" t="n"/>
       <c r="F167" s="39" t="inlineStr">
@@ -18222,12 +18253,12 @@
       </c>
       <c r="AH167" s="2" t="n"/>
     </row>
-    <row r="168" ht="24" customHeight="1" s="45">
+    <row r="168" ht="24" customHeight="1" s="48">
       <c r="A168" s="2" t="n">
         <v>167</v>
       </c>
       <c r="B168" s="2" t="n"/>
-      <c r="C168" s="27" t="n"/>
+      <c r="C168" s="46" t="n"/>
       <c r="D168" s="2" t="n"/>
       <c r="E168" s="4" t="n"/>
       <c r="F168" s="39" t="inlineStr">
@@ -18264,10 +18295,10 @@
         </is>
       </c>
       <c r="O168" s="32" t="n">
-        <v>-15.8</v>
+        <v>-32.7</v>
       </c>
       <c r="P168" s="32" t="n">
-        <v>-2.1</v>
+        <v>-9.4</v>
       </c>
       <c r="Q168" s="32" t="n"/>
       <c r="R168" s="23" t="inlineStr">
@@ -18336,12 +18367,12 @@
       </c>
       <c r="AH168" s="2" t="n"/>
     </row>
-    <row r="169" ht="24" customHeight="1" s="45">
+    <row r="169" ht="24" customHeight="1" s="48">
       <c r="A169" s="2" t="n">
         <v>168</v>
       </c>
       <c r="B169" s="2" t="n"/>
-      <c r="C169" s="27" t="n"/>
+      <c r="C169" s="46" t="n"/>
       <c r="D169" s="2" t="n"/>
       <c r="E169" s="4" t="n"/>
       <c r="F169" s="39" t="inlineStr">
@@ -18378,10 +18409,10 @@
         </is>
       </c>
       <c r="O169" s="32" t="n">
-        <v>-27.5</v>
+        <v>-26.9</v>
       </c>
       <c r="P169" s="32" t="n">
-        <v>-7.1</v>
+        <v>-11.1</v>
       </c>
       <c r="Q169" s="32" t="n"/>
       <c r="R169" s="23" t="inlineStr">
@@ -18450,12 +18481,12 @@
       </c>
       <c r="AH169" s="2" t="n"/>
     </row>
-    <row r="170" ht="24" customHeight="1" s="45">
+    <row r="170" ht="24" customHeight="1" s="48">
       <c r="A170" s="2" t="n">
         <v>169</v>
       </c>
       <c r="B170" s="2" t="n"/>
-      <c r="C170" s="27" t="n"/>
+      <c r="C170" s="46" t="n"/>
       <c r="D170" s="2" t="n"/>
       <c r="E170" s="4" t="n"/>
       <c r="F170" s="39" t="inlineStr">
@@ -18560,12 +18591,12 @@
         </is>
       </c>
     </row>
-    <row r="171" ht="24" customHeight="1" s="45">
+    <row r="171" ht="24" customHeight="1" s="48">
       <c r="A171" s="2" t="n">
         <v>170</v>
       </c>
       <c r="B171" s="2" t="n"/>
-      <c r="C171" s="27" t="n"/>
+      <c r="C171" s="46" t="n"/>
       <c r="D171" s="2" t="n"/>
       <c r="E171" s="4" t="n"/>
       <c r="F171" s="39" t="inlineStr">
@@ -18666,12 +18697,12 @@
         </is>
       </c>
     </row>
-    <row r="172" ht="24" customHeight="1" s="45">
+    <row r="172" ht="24" customHeight="1" s="48">
       <c r="A172" s="2" t="n">
         <v>171</v>
       </c>
       <c r="B172" s="2" t="n"/>
-      <c r="C172" s="27" t="n"/>
+      <c r="C172" s="46" t="n"/>
       <c r="D172" s="2" t="n"/>
       <c r="E172" s="4" t="n"/>
       <c r="F172" s="39" t="inlineStr">
@@ -18704,10 +18735,10 @@
       </c>
       <c r="N172" s="3" t="n"/>
       <c r="O172" s="32" t="n">
-        <v>-15.4</v>
+        <v>-20.5</v>
       </c>
       <c r="P172" s="32" t="n">
-        <v>-1</v>
+        <v>-6.1</v>
       </c>
       <c r="Q172" s="32" t="n"/>
       <c r="R172" s="23" t="inlineStr">
@@ -18776,12 +18807,12 @@
       </c>
       <c r="AH172" s="2" t="n"/>
     </row>
-    <row r="173" ht="24" customHeight="1" s="45">
+    <row r="173" ht="24" customHeight="1" s="48">
       <c r="A173" s="2" t="n">
         <v>172</v>
       </c>
       <c r="B173" s="2" t="n"/>
-      <c r="C173" s="27" t="n"/>
+      <c r="C173" s="46" t="n"/>
       <c r="D173" s="2" t="n"/>
       <c r="E173" s="4" t="n"/>
       <c r="F173" s="39" t="inlineStr">
@@ -18814,10 +18845,10 @@
       </c>
       <c r="N173" s="2" t="n"/>
       <c r="O173" s="32" t="n">
-        <v>-20.4</v>
+        <v>-11.5</v>
       </c>
       <c r="P173" s="32" t="n">
-        <v>-13</v>
+        <v>-5.5</v>
       </c>
       <c r="Q173" s="32" t="n"/>
       <c r="R173" s="23" t="inlineStr">
@@ -18882,12 +18913,12 @@
       <c r="AG173" s="2" t="n"/>
       <c r="AH173" s="2" t="n"/>
     </row>
-    <row r="174" ht="24" customHeight="1" s="45">
+    <row r="174" ht="24" customHeight="1" s="48">
       <c r="A174" s="2" t="n">
         <v>173</v>
       </c>
       <c r="B174" s="2" t="n"/>
-      <c r="C174" s="27" t="n">
+      <c r="C174" s="46" t="n">
         <v>53589</v>
       </c>
       <c r="D174" s="2" t="n"/>
@@ -18988,12 +19019,12 @@
         </is>
       </c>
     </row>
-    <row r="175" ht="24" customHeight="1" s="45">
+    <row r="175" ht="24" customHeight="1" s="48">
       <c r="A175" s="2" t="n">
         <v>174</v>
       </c>
       <c r="B175" s="2" t="n"/>
-      <c r="C175" s="27" t="n"/>
+      <c r="C175" s="46" t="n"/>
       <c r="D175" s="2" t="n"/>
       <c r="E175" s="4" t="n"/>
       <c r="F175" s="39" t="inlineStr">
@@ -19090,7 +19121,7 @@
       </c>
       <c r="AH175" s="2" t="n"/>
     </row>
-    <row r="176" ht="24" customHeight="1" s="45">
+    <row r="176" ht="24" customHeight="1" s="48">
       <c r="A176" s="2" t="n">
         <v>175</v>
       </c>
@@ -19099,7 +19130,7 @@
           <t>ogimet</t>
         </is>
       </c>
-      <c r="C176" s="27" t="n">
+      <c r="C176" s="46" t="n">
         <v>58437</v>
       </c>
       <c r="D176" s="2" t="inlineStr">
@@ -19136,10 +19167,10 @@
       </c>
       <c r="N176" s="2" t="n"/>
       <c r="O176" s="32" t="n">
-        <v>5.8</v>
+        <v>4.4</v>
       </c>
       <c r="P176" s="32" t="n">
-        <v>11.2</v>
+        <v>10.9</v>
       </c>
       <c r="Q176" s="32" t="n"/>
       <c r="R176" s="23" t="inlineStr">
@@ -19200,12 +19231,12 @@
         </is>
       </c>
     </row>
-    <row r="177" ht="24" customHeight="1" s="45">
+    <row r="177" ht="24" customHeight="1" s="48">
       <c r="A177" s="2" t="n">
         <v>176</v>
       </c>
       <c r="B177" s="2" t="n"/>
-      <c r="C177" s="27" t="n">
+      <c r="C177" s="46" t="n">
         <v>54287</v>
       </c>
       <c r="D177" s="2" t="n"/>
@@ -19238,10 +19269,10 @@
       </c>
       <c r="N177" s="2" t="n"/>
       <c r="O177" s="32" t="n">
-        <v>-26.2</v>
+        <v>-15.4</v>
       </c>
       <c r="P177" s="32" t="n">
-        <v>-5.3</v>
+        <v>-8.5</v>
       </c>
       <c r="Q177" s="32" t="n"/>
       <c r="R177" s="23" t="inlineStr">
@@ -19314,12 +19345,12 @@
         </is>
       </c>
     </row>
-    <row r="178" ht="24" customHeight="1" s="45">
+    <row r="178" ht="24" customHeight="1" s="48">
       <c r="A178" s="2" t="n">
         <v>177</v>
       </c>
       <c r="B178" s="2" t="n"/>
-      <c r="C178" s="27" t="n"/>
+      <c r="C178" s="46" t="n"/>
       <c r="D178" s="2" t="n"/>
       <c r="E178" s="4" t="n"/>
       <c r="F178" s="39" t="inlineStr">
@@ -19351,8 +19382,12 @@
         </is>
       </c>
       <c r="N178" s="2" t="n"/>
-      <c r="O178" s="32" t="n"/>
-      <c r="P178" s="32" t="n"/>
+      <c r="O178" s="32" t="n">
+        <v>-32.2</v>
+      </c>
+      <c r="P178" s="32" t="n">
+        <v>-11.5</v>
+      </c>
       <c r="Q178" s="32" t="n"/>
       <c r="R178" s="23" t="inlineStr">
         <is>
@@ -19424,12 +19459,12 @@
         </is>
       </c>
     </row>
-    <row r="179" ht="24" customHeight="1" s="45">
+    <row r="179" ht="24" customHeight="1" s="48">
       <c r="A179" s="2" t="n">
         <v>178</v>
       </c>
       <c r="B179" s="2" t="n"/>
-      <c r="C179" s="27" t="n">
+      <c r="C179" s="46" t="n">
         <v>51337</v>
       </c>
       <c r="D179" s="2" t="n"/>
@@ -19530,12 +19565,12 @@
         </is>
       </c>
     </row>
-    <row r="180" ht="24" customHeight="1" s="45">
+    <row r="180" ht="24" customHeight="1" s="48">
       <c r="A180" s="2" t="n">
         <v>179</v>
       </c>
       <c r="B180" s="2" t="n"/>
-      <c r="C180" s="27" t="n"/>
+      <c r="C180" s="46" t="n"/>
       <c r="D180" s="2" t="n"/>
       <c r="E180" s="4" t="n"/>
       <c r="F180" s="39" t="inlineStr">
@@ -19632,12 +19667,12 @@
         </is>
       </c>
     </row>
-    <row r="181" ht="24" customHeight="1" s="45">
+    <row r="181" ht="24" customHeight="1" s="48">
       <c r="A181" s="2" t="n">
         <v>180</v>
       </c>
       <c r="B181" s="2" t="n"/>
-      <c r="C181" s="27" t="n"/>
+      <c r="C181" s="46" t="n"/>
       <c r="D181" s="2" t="n"/>
       <c r="E181" s="4" t="n"/>
       <c r="F181" s="39" t="inlineStr">
@@ -19730,12 +19765,12 @@
         </is>
       </c>
     </row>
-    <row r="182" ht="24" customHeight="1" s="45">
+    <row r="182" ht="24" customHeight="1" s="48">
       <c r="A182" s="2" t="n">
         <v>181</v>
       </c>
       <c r="B182" s="2" t="n"/>
-      <c r="C182" s="27" t="n">
+      <c r="C182" s="46" t="n">
         <v>58968</v>
       </c>
       <c r="D182" s="2" t="inlineStr">
@@ -19816,12 +19851,12 @@
       <c r="AG182" s="2" t="n"/>
       <c r="AH182" s="2" t="n"/>
     </row>
-    <row r="183" ht="24" customHeight="1" s="45">
+    <row r="183" ht="24" customHeight="1" s="48">
       <c r="A183" s="2" t="n">
         <v>182</v>
       </c>
       <c r="B183" s="2" t="n"/>
-      <c r="C183" s="27" t="n">
+      <c r="C183" s="46" t="n">
         <v>45007</v>
       </c>
       <c r="D183" s="2" t="inlineStr">
@@ -19898,12 +19933,12 @@
       <c r="AG183" s="2" t="n"/>
       <c r="AH183" s="2" t="n"/>
     </row>
-    <row r="184" ht="24" customHeight="1" s="45">
+    <row r="184" ht="24" customHeight="1" s="48">
       <c r="A184" s="2" t="n">
         <v>183</v>
       </c>
       <c r="B184" s="2" t="n"/>
-      <c r="C184" s="27" t="n">
+      <c r="C184" s="46" t="n">
         <v>45011</v>
       </c>
       <c r="D184" s="2" t="inlineStr">
@@ -19980,7 +20015,7 @@
       <c r="AG184" s="2" t="n"/>
       <c r="AH184" s="2" t="n"/>
     </row>
-    <row r="185" ht="24" customHeight="1" s="45">
+    <row r="185" ht="24" customHeight="1" s="48">
       <c r="A185" s="2" t="n">
         <v>184</v>
       </c>
@@ -19989,7 +20024,7 @@
           <t>ogimet</t>
         </is>
       </c>
-      <c r="C185" s="27" t="n">
+      <c r="C185" s="46" t="n">
         <v>31137</v>
       </c>
       <c r="D185" s="2" t="inlineStr">
@@ -20083,7 +20118,7 @@
         </is>
       </c>
     </row>
-    <row r="186" ht="24" customHeight="1" s="45">
+    <row r="186" ht="24" customHeight="1" s="48">
       <c r="A186" s="2" t="n">
         <v>185</v>
       </c>
@@ -20092,7 +20127,7 @@
           <t>ogimet</t>
         </is>
       </c>
-      <c r="C186" s="27" t="n">
+      <c r="C186" s="46" t="n">
         <v>24688</v>
       </c>
       <c r="D186" s="2" t="inlineStr">
@@ -20129,13 +20164,13 @@
       </c>
       <c r="N186" s="2" t="n"/>
       <c r="O186" s="32" t="n">
-        <v>-48.2</v>
+        <v>-36.8</v>
       </c>
       <c r="P186" s="32" t="n">
-        <v>-32.8</v>
+        <v>-21.6</v>
       </c>
       <c r="Q186" s="32" t="n">
-        <v>-42.91</v>
+        <v>-30.18</v>
       </c>
       <c r="R186" s="23" t="inlineStr">
         <is>
@@ -20192,7 +20227,7 @@
         </is>
       </c>
     </row>
-    <row r="187" ht="24" customHeight="1" s="45">
+    <row r="187" ht="24" customHeight="1" s="48">
       <c r="A187" s="2" t="n">
         <v>186</v>
       </c>
@@ -20201,7 +20236,7 @@
           <t>ogimet</t>
         </is>
       </c>
-      <c r="C187" s="27" t="n">
+      <c r="C187" s="46" t="n">
         <v>24585</v>
       </c>
       <c r="D187" s="2" t="inlineStr">
@@ -20238,13 +20273,13 @@
       </c>
       <c r="N187" s="2" t="n"/>
       <c r="O187" s="32" t="n">
-        <v>-48.4</v>
+        <v>-36.5</v>
       </c>
       <c r="P187" s="32" t="n">
-        <v>-34.9</v>
+        <v>-21.2</v>
       </c>
       <c r="Q187" s="32" t="n">
-        <v>-42.62</v>
+        <v>-30.03</v>
       </c>
       <c r="R187" s="23" t="inlineStr">
         <is>
@@ -20296,7 +20331,7 @@
       </c>
       <c r="AH187" s="2" t="n"/>
     </row>
-    <row r="188" ht="24" customHeight="1" s="45">
+    <row r="188" ht="24" customHeight="1" s="48">
       <c r="A188" s="2" t="n">
         <v>187</v>
       </c>
@@ -20305,7 +20340,7 @@
           <t>ogimet</t>
         </is>
       </c>
-      <c r="C188" s="27" t="n">
+      <c r="C188" s="46" t="n">
         <v>24588</v>
       </c>
       <c r="D188" s="2" t="inlineStr">
@@ -20342,13 +20377,13 @@
       </c>
       <c r="N188" s="2" t="n"/>
       <c r="O188" s="32" t="n">
-        <v>-46.8</v>
+        <v>-38</v>
       </c>
       <c r="P188" s="32" t="n">
-        <v>-34.7</v>
+        <v>-26.2</v>
       </c>
       <c r="Q188" s="32" t="n">
-        <v>-41.44</v>
+        <v>-35.39</v>
       </c>
       <c r="R188" s="23" t="inlineStr">
         <is>
@@ -20400,7 +20435,7 @@
       </c>
       <c r="AH188" s="2" t="n"/>
     </row>
-    <row r="189" ht="24" customHeight="1" s="45">
+    <row r="189" ht="24" customHeight="1" s="48">
       <c r="A189" s="2" t="n">
         <v>188</v>
       </c>
@@ -20409,7 +20444,7 @@
           <t>ogimet</t>
         </is>
       </c>
-      <c r="C189" s="27" t="n">
+      <c r="C189" s="46" t="n">
         <v>24691</v>
       </c>
       <c r="D189" s="2" t="inlineStr">
@@ -20446,13 +20481,13 @@
       </c>
       <c r="N189" s="2" t="n"/>
       <c r="O189" s="32" t="n">
-        <v>-50.8</v>
+        <v>-38.8</v>
       </c>
       <c r="P189" s="32" t="n">
-        <v>-34.7</v>
+        <v>-18</v>
       </c>
       <c r="Q189" s="32" t="n">
-        <v>-43.89</v>
+        <v>-29.42</v>
       </c>
       <c r="R189" s="23" t="inlineStr">
         <is>
@@ -20504,7 +20539,7 @@
       </c>
       <c r="AH189" s="2" t="n"/>
     </row>
-    <row r="190" ht="24" customHeight="1" s="45">
+    <row r="190" ht="24" customHeight="1" s="48">
       <c r="A190" s="2" t="n">
         <v>189</v>
       </c>
@@ -20513,7 +20548,7 @@
           <t>ogimet</t>
         </is>
       </c>
-      <c r="C190" s="27" t="n">
+      <c r="C190" s="46" t="n">
         <v>24266</v>
       </c>
       <c r="D190" s="2" t="inlineStr">
@@ -20550,13 +20585,13 @@
       </c>
       <c r="N190" s="2" t="n"/>
       <c r="O190" s="32" t="n">
-        <v>-51.6</v>
+        <v>-33.1</v>
       </c>
       <c r="P190" s="32" t="n">
-        <v>-40.2</v>
+        <v>-24.9</v>
       </c>
       <c r="Q190" s="32" t="n">
-        <v>-47.44</v>
+        <v>-29.8</v>
       </c>
       <c r="R190" s="23" t="inlineStr">
         <is>
@@ -20608,7 +20643,7 @@
       </c>
       <c r="AH190" s="2" t="n"/>
     </row>
-    <row r="191" ht="24" customHeight="1" s="45">
+    <row r="191" ht="24" customHeight="1" s="48">
       <c r="A191" s="2" t="n">
         <v>190</v>
       </c>
@@ -20617,7 +20652,7 @@
           <t>ogimet</t>
         </is>
       </c>
-      <c r="C191" s="27" t="n">
+      <c r="C191" s="46" t="n">
         <v>24684</v>
       </c>
       <c r="D191" s="2" t="inlineStr">
@@ -20654,13 +20689,13 @@
       </c>
       <c r="N191" s="2" t="n"/>
       <c r="O191" s="32" t="n">
-        <v>-47.4</v>
+        <v>-37.7</v>
       </c>
       <c r="P191" s="32" t="n">
-        <v>-31.5</v>
+        <v>-21</v>
       </c>
       <c r="Q191" s="32" t="n">
-        <v>-42.01</v>
+        <v>-31.31</v>
       </c>
       <c r="R191" s="23" t="inlineStr">
         <is>
@@ -20708,7 +20743,7 @@
       <c r="AG191" s="2" t="n"/>
       <c r="AH191" s="2" t="n"/>
     </row>
-    <row r="192" ht="24" customHeight="1" s="45">
+    <row r="192" ht="24" customHeight="1" s="48">
       <c r="A192" s="2" t="n">
         <v>191</v>
       </c>
@@ -20717,7 +20752,7 @@
           <t>ogimet</t>
         </is>
       </c>
-      <c r="C192" s="27" t="n">
+      <c r="C192" s="46" t="n">
         <v>24382</v>
       </c>
       <c r="D192" s="2" t="inlineStr">
@@ -20754,13 +20789,13 @@
       </c>
       <c r="N192" s="2" t="n"/>
       <c r="O192" s="32" t="n">
-        <v>-46.3</v>
+        <v>-39.1</v>
       </c>
       <c r="P192" s="32" t="n">
-        <v>-31.5</v>
+        <v>-27.2</v>
       </c>
       <c r="Q192" s="32" t="n">
-        <v>-40.91</v>
+        <v>-33.09</v>
       </c>
       <c r="R192" s="23" t="inlineStr">
         <is>
@@ -20813,7 +20848,7 @@
       </c>
       <c r="AH192" s="2" t="n"/>
     </row>
-    <row r="193" ht="24" customHeight="1" s="45">
+    <row r="193" ht="24" customHeight="1" s="48">
       <c r="A193" s="2" t="n">
         <v>192</v>
       </c>
@@ -20822,7 +20857,7 @@
           <t>ogimet</t>
         </is>
       </c>
-      <c r="C193" s="27" t="n">
+      <c r="C193" s="46" t="n">
         <v>24959</v>
       </c>
       <c r="D193" s="2" t="inlineStr">
@@ -20859,13 +20894,13 @@
       </c>
       <c r="N193" s="2" t="n"/>
       <c r="O193" s="32" t="n">
-        <v>-27.5</v>
+        <v>-28.1</v>
       </c>
       <c r="P193" s="32" t="n">
-        <v>-23.1</v>
+        <v>-17.5</v>
       </c>
       <c r="Q193" s="32" t="n">
-        <v>-25.93</v>
+        <v>-20.65</v>
       </c>
       <c r="R193" s="23" t="inlineStr">
         <is>
@@ -20921,7 +20956,7 @@
       </c>
       <c r="AH193" s="2" t="n"/>
     </row>
-    <row r="194" ht="24" customHeight="1" s="45">
+    <row r="194" ht="24" customHeight="1" s="48">
       <c r="A194" s="2" t="n">
         <v>193</v>
       </c>
@@ -20930,7 +20965,7 @@
           <t>ogimet</t>
         </is>
       </c>
-      <c r="C194" s="27" t="n">
+      <c r="C194" s="46" t="n">
         <v>24477</v>
       </c>
       <c r="D194" s="2" t="inlineStr">
@@ -20967,10 +21002,10 @@
       </c>
       <c r="N194" s="2" t="n"/>
       <c r="O194" s="32" t="n">
-        <v>-49</v>
+        <v>-37.5</v>
       </c>
       <c r="P194" s="32" t="n">
-        <v>-37.6</v>
+        <v>-27.6</v>
       </c>
       <c r="Q194" s="32" t="n"/>
       <c r="R194" s="23" t="inlineStr">
@@ -21019,7 +21054,7 @@
       <c r="AG194" s="2" t="n"/>
       <c r="AH194" s="2" t="n"/>
     </row>
-    <row r="195" ht="24" customHeight="1" s="45">
+    <row r="195" ht="24" customHeight="1" s="48">
       <c r="A195" s="2" t="n">
         <v>194</v>
       </c>
@@ -21028,7 +21063,7 @@
           <t>ogimet</t>
         </is>
       </c>
-      <c r="C195" s="27" t="n">
+      <c r="C195" s="46" t="n">
         <v>25428</v>
       </c>
       <c r="D195" s="2" t="inlineStr">
@@ -21065,13 +21100,13 @@
       </c>
       <c r="N195" s="2" t="n"/>
       <c r="O195" s="32" t="n">
-        <v>-24.5</v>
+        <v>-32.2</v>
       </c>
       <c r="P195" s="32" t="n">
-        <v>-16.3</v>
+        <v>-17.8</v>
       </c>
       <c r="Q195" s="32" t="n">
-        <v>-21.4</v>
+        <v>-26.04</v>
       </c>
       <c r="R195" s="23" t="inlineStr">
         <is>
@@ -21123,7 +21158,7 @@
       </c>
       <c r="AH195" s="2" t="n"/>
     </row>
-    <row r="196" ht="24" customHeight="1" s="45">
+    <row r="196" ht="24" customHeight="1" s="48">
       <c r="A196" s="2" t="n">
         <v>195</v>
       </c>
@@ -21132,7 +21167,7 @@
           <t>ogimet</t>
         </is>
       </c>
-      <c r="C196" s="27" t="n">
+      <c r="C196" s="46" t="n">
         <v>25700</v>
       </c>
       <c r="D196" s="2" t="inlineStr">
@@ -21169,12 +21204,14 @@
       </c>
       <c r="N196" s="2" t="n"/>
       <c r="O196" s="32" t="n">
-        <v>-40</v>
+        <v>-34.4</v>
       </c>
       <c r="P196" s="32" t="n">
-        <v>-22.2</v>
-      </c>
-      <c r="Q196" s="32" t="n"/>
+        <v>-17.9</v>
+      </c>
+      <c r="Q196" s="32" t="n">
+        <v>-28.14</v>
+      </c>
       <c r="R196" s="23" t="inlineStr">
         <is>
           <t>Y</t>
@@ -21225,7 +21262,7 @@
       </c>
       <c r="AH196" s="2" t="n"/>
     </row>
-    <row r="197" ht="24" customHeight="1" s="45">
+    <row r="197" ht="24" customHeight="1" s="48">
       <c r="A197" s="2" t="n">
         <v>196</v>
       </c>
@@ -21234,7 +21271,7 @@
           <t>ogimet</t>
         </is>
       </c>
-      <c r="C197" s="27" t="n">
+      <c r="C197" s="46" t="n">
         <v>24507</v>
       </c>
       <c r="D197" s="2" t="inlineStr">
@@ -21271,13 +21308,13 @@
       </c>
       <c r="N197" s="24" t="n"/>
       <c r="O197" s="32" t="n">
-        <v>-43.4</v>
+        <v>-27.7</v>
       </c>
       <c r="P197" s="32" t="n">
-        <v>-27.9</v>
+        <v>-15.8</v>
       </c>
       <c r="Q197" s="32" t="n">
-        <v>-37.59</v>
+        <v>-21.68</v>
       </c>
       <c r="R197" s="23" t="inlineStr">
         <is>
@@ -21329,12 +21366,12 @@
       </c>
       <c r="AH197" s="2" t="n"/>
     </row>
-    <row r="198" ht="24" customHeight="1" s="45">
+    <row r="198" ht="24" customHeight="1" s="48">
       <c r="A198" s="2" t="n">
         <v>197</v>
       </c>
       <c r="B198" s="2" t="n"/>
-      <c r="C198" s="27" t="n"/>
+      <c r="C198" s="46" t="n"/>
       <c r="D198" s="2" t="n"/>
       <c r="E198" s="4" t="n"/>
       <c r="F198" s="39" t="inlineStr">
@@ -21431,12 +21468,12 @@
       </c>
       <c r="AH198" s="2" t="n"/>
     </row>
-    <row r="199" ht="24" customHeight="1" s="45">
+    <row r="199" ht="24" customHeight="1" s="48">
       <c r="A199" s="2" t="n">
         <v>198</v>
       </c>
       <c r="B199" s="2" t="n"/>
-      <c r="C199" s="27" t="n">
+      <c r="C199" s="46" t="n">
         <v>50349</v>
       </c>
       <c r="D199" s="2" t="n"/>
@@ -21468,8 +21505,12 @@
         </is>
       </c>
       <c r="N199" s="2" t="n"/>
-      <c r="O199" s="32" t="n"/>
-      <c r="P199" s="32" t="n"/>
+      <c r="O199" s="32" t="n">
+        <v>-39.8</v>
+      </c>
+      <c r="P199" s="32" t="n">
+        <v>-11.4</v>
+      </c>
       <c r="Q199" s="32" t="n"/>
       <c r="R199" s="23" t="inlineStr">
         <is>
@@ -21529,12 +21570,12 @@
       </c>
       <c r="AH199" s="2" t="n"/>
     </row>
-    <row r="200" ht="24" customHeight="1" s="45">
+    <row r="200" ht="24" customHeight="1" s="48">
       <c r="A200" s="2" t="n">
         <v>199</v>
       </c>
       <c r="B200" s="2" t="n"/>
-      <c r="C200" s="27" t="n">
+      <c r="C200" s="46" t="n">
         <v>50134</v>
       </c>
       <c r="D200" s="2" t="n"/>
@@ -21631,12 +21672,12 @@
       </c>
       <c r="AH200" s="2" t="n"/>
     </row>
-    <row r="201" ht="24" customHeight="1" s="45">
+    <row r="201" ht="24" customHeight="1" s="48">
       <c r="A201" s="2" t="n">
         <v>200</v>
       </c>
       <c r="B201" s="2" t="n"/>
-      <c r="C201" s="27" t="n"/>
+      <c r="C201" s="46" t="n"/>
       <c r="D201" s="2" t="n"/>
       <c r="E201" s="4" t="n"/>
       <c r="F201" s="39" t="inlineStr">
@@ -21668,12 +21709,8 @@
         </is>
       </c>
       <c r="N201" s="2" t="n"/>
-      <c r="O201" s="32" t="n">
-        <v>-18</v>
-      </c>
-      <c r="P201" s="32" t="n">
-        <v>-11.9</v>
-      </c>
+      <c r="O201" s="32" t="n"/>
+      <c r="P201" s="32" t="n"/>
       <c r="Q201" s="32" t="n"/>
       <c r="R201" s="23" t="inlineStr">
         <is>
@@ -21737,12 +21774,12 @@
       </c>
       <c r="AH201" s="2" t="n"/>
     </row>
-    <row r="202" ht="24" customHeight="1" s="45">
+    <row r="202" ht="24" customHeight="1" s="48">
       <c r="A202" s="2" t="n">
         <v>201</v>
       </c>
       <c r="B202" s="2" t="n"/>
-      <c r="C202" s="27" t="n">
+      <c r="C202" s="46" t="n">
         <v>50674</v>
       </c>
       <c r="D202" s="2" t="n"/>
@@ -21839,12 +21876,12 @@
       </c>
       <c r="AH202" s="2" t="n"/>
     </row>
-    <row r="203" ht="24" customHeight="1" s="45">
+    <row r="203" ht="24" customHeight="1" s="48">
       <c r="A203" s="2" t="n">
         <v>202</v>
       </c>
       <c r="B203" s="2" t="n"/>
-      <c r="C203" s="27" t="n">
+      <c r="C203" s="46" t="n">
         <v>50655</v>
       </c>
       <c r="D203" s="2" t="n"/>
@@ -21941,12 +21978,12 @@
       </c>
       <c r="AH203" s="2" t="n"/>
     </row>
-    <row r="204" ht="24" customHeight="1" s="45">
+    <row r="204" ht="24" customHeight="1" s="48">
       <c r="A204" s="2" t="n">
         <v>203</v>
       </c>
       <c r="B204" s="2" t="n"/>
-      <c r="C204" s="27" t="n"/>
+      <c r="C204" s="46" t="n"/>
       <c r="D204" s="2" t="n"/>
       <c r="E204" s="4" t="n"/>
       <c r="F204" s="39" t="inlineStr">
@@ -22043,12 +22080,12 @@
       </c>
       <c r="AH204" s="2" t="n"/>
     </row>
-    <row r="205" ht="24" customHeight="1" s="45">
+    <row r="205" ht="24" customHeight="1" s="48">
       <c r="A205" s="2" t="n">
         <v>204</v>
       </c>
       <c r="B205" s="2" t="n"/>
-      <c r="C205" s="27" t="n"/>
+      <c r="C205" s="46" t="n"/>
       <c r="D205" s="2" t="n"/>
       <c r="E205" s="4" t="n"/>
       <c r="F205" s="39" t="inlineStr">
@@ -22145,12 +22182,12 @@
       </c>
       <c r="AH205" s="2" t="n"/>
     </row>
-    <row r="206" ht="24" customHeight="1" s="45">
+    <row r="206" ht="24" customHeight="1" s="48">
       <c r="A206" s="2" t="n">
         <v>205</v>
       </c>
       <c r="B206" s="2" t="n"/>
-      <c r="C206" s="27" t="n"/>
+      <c r="C206" s="46" t="n"/>
       <c r="D206" s="2" t="n"/>
       <c r="E206" s="4" t="n"/>
       <c r="F206" s="39" t="inlineStr">
@@ -22247,12 +22284,12 @@
       </c>
       <c r="AH206" s="2" t="n"/>
     </row>
-    <row r="207" ht="24" customHeight="1" s="45">
+    <row r="207" ht="24" customHeight="1" s="48">
       <c r="A207" s="2" t="n">
         <v>206</v>
       </c>
       <c r="B207" s="2" t="n"/>
-      <c r="C207" s="27" t="n"/>
+      <c r="C207" s="46" t="n"/>
       <c r="D207" s="2" t="n"/>
       <c r="E207" s="4" t="n"/>
       <c r="F207" s="39" t="inlineStr">
@@ -22284,8 +22321,12 @@
         </is>
       </c>
       <c r="N207" s="2" t="n"/>
-      <c r="O207" s="32" t="n"/>
-      <c r="P207" s="32" t="n"/>
+      <c r="O207" s="32" t="n">
+        <v>-44</v>
+      </c>
+      <c r="P207" s="32" t="n">
+        <v>-10</v>
+      </c>
       <c r="Q207" s="32" t="n"/>
       <c r="R207" s="23" t="inlineStr">
         <is>
@@ -22345,12 +22386,12 @@
       <c r="AG207" s="2" t="n"/>
       <c r="AH207" s="2" t="n"/>
     </row>
-    <row r="208" ht="24" customHeight="1" s="45">
+    <row r="208" ht="24" customHeight="1" s="48">
       <c r="A208" s="2" t="n">
         <v>207</v>
       </c>
       <c r="B208" s="2" t="n"/>
-      <c r="C208" s="27" t="n"/>
+      <c r="C208" s="46" t="n"/>
       <c r="D208" s="2" t="n"/>
       <c r="E208" s="4" t="n"/>
       <c r="F208" s="39" t="n"/>
@@ -22437,12 +22478,12 @@
       </c>
       <c r="AH208" s="2" t="n"/>
     </row>
-    <row r="209" ht="24" customHeight="1" s="45">
+    <row r="209" ht="24" customHeight="1" s="48">
       <c r="A209" s="2" t="n">
         <v>208</v>
       </c>
       <c r="B209" s="2" t="n"/>
-      <c r="C209" s="27" t="n">
+      <c r="C209" s="46" t="n">
         <v>50962</v>
       </c>
       <c r="D209" s="2" t="n"/>
@@ -22539,12 +22580,12 @@
       <c r="AG209" s="2" t="n"/>
       <c r="AH209" s="2" t="n"/>
     </row>
-    <row r="210" ht="24" customHeight="1" s="45">
+    <row r="210" ht="24" customHeight="1" s="48">
       <c r="A210" s="2" t="n">
         <v>209</v>
       </c>
       <c r="B210" s="2" t="n"/>
-      <c r="C210" s="27" t="n">
+      <c r="C210" s="46" t="n">
         <v>50442</v>
       </c>
       <c r="D210" s="2" t="n"/>
@@ -22637,12 +22678,12 @@
       </c>
       <c r="AH210" s="2" t="n"/>
     </row>
-    <row r="211" ht="24" customHeight="1" s="45">
+    <row r="211" ht="24" customHeight="1" s="48">
       <c r="A211" s="2" t="n">
         <v>210</v>
       </c>
       <c r="B211" s="2" t="n"/>
-      <c r="C211" s="27" t="n"/>
+      <c r="C211" s="46" t="n"/>
       <c r="D211" s="2" t="n"/>
       <c r="E211" s="4" t="n"/>
       <c r="F211" s="39" t="inlineStr">
@@ -22739,12 +22780,12 @@
       </c>
       <c r="AH211" s="2" t="n"/>
     </row>
-    <row r="212" ht="24" customHeight="1" s="45">
+    <row r="212" ht="24" customHeight="1" s="48">
       <c r="A212" s="2" t="n">
         <v>211</v>
       </c>
       <c r="B212" s="2" t="n"/>
-      <c r="C212" s="27" t="n"/>
+      <c r="C212" s="46" t="n"/>
       <c r="D212" s="2" t="n"/>
       <c r="E212" s="4" t="n"/>
       <c r="F212" s="39" t="inlineStr">
@@ -22841,12 +22882,12 @@
       </c>
       <c r="AH212" s="2" t="n"/>
     </row>
-    <row r="213" ht="24" customHeight="1" s="45">
+    <row r="213" ht="24" customHeight="1" s="48">
       <c r="A213" s="2" t="n">
         <v>212</v>
       </c>
       <c r="B213" s="2" t="n"/>
-      <c r="C213" s="27" t="n"/>
+      <c r="C213" s="46" t="n"/>
       <c r="D213" s="2" t="n"/>
       <c r="E213" s="4" t="n"/>
       <c r="F213" s="39" t="inlineStr">
@@ -22943,12 +22984,12 @@
       </c>
       <c r="AH213" s="2" t="n"/>
     </row>
-    <row r="214" ht="24" customHeight="1" s="45">
+    <row r="214" ht="24" customHeight="1" s="48">
       <c r="A214" s="2" t="n">
         <v>213</v>
       </c>
       <c r="B214" s="2" t="n"/>
-      <c r="C214" s="27" t="n"/>
+      <c r="C214" s="46" t="n"/>
       <c r="D214" s="2" t="n"/>
       <c r="E214" s="4" t="n"/>
       <c r="F214" s="39" t="inlineStr">
@@ -23045,12 +23086,12 @@
       </c>
       <c r="AH214" s="2" t="n"/>
     </row>
-    <row r="215" ht="24" customHeight="1" s="45">
+    <row r="215" ht="24" customHeight="1" s="48">
       <c r="A215" s="2" t="n">
         <v>214</v>
       </c>
       <c r="B215" s="2" t="n"/>
-      <c r="C215" s="27" t="n"/>
+      <c r="C215" s="46" t="n"/>
       <c r="D215" s="2" t="n"/>
       <c r="E215" s="4" t="n"/>
       <c r="F215" s="39" t="inlineStr">
@@ -23147,12 +23188,12 @@
       </c>
       <c r="AH215" s="2" t="n"/>
     </row>
-    <row r="216" ht="24" customHeight="1" s="45">
+    <row r="216" ht="24" customHeight="1" s="48">
       <c r="A216" s="2" t="n">
         <v>215</v>
       </c>
       <c r="B216" s="2" t="n"/>
-      <c r="C216" s="27" t="n"/>
+      <c r="C216" s="46" t="n"/>
       <c r="D216" s="2" t="n"/>
       <c r="E216" s="4" t="n"/>
       <c r="F216" s="39" t="inlineStr">
@@ -23249,12 +23290,12 @@
       </c>
       <c r="AH216" s="2" t="n"/>
     </row>
-    <row r="217" ht="24" customHeight="1" s="45">
+    <row r="217" ht="24" customHeight="1" s="48">
       <c r="A217" s="2" t="n">
         <v>216</v>
       </c>
       <c r="B217" s="2" t="n"/>
-      <c r="C217" s="27" t="n"/>
+      <c r="C217" s="46" t="n"/>
       <c r="D217" s="2" t="n"/>
       <c r="E217" s="4" t="n"/>
       <c r="F217" s="39" t="n"/>
@@ -23337,12 +23378,12 @@
       </c>
       <c r="AH217" s="2" t="n"/>
     </row>
-    <row r="218" ht="24" customHeight="1" s="45">
+    <row r="218" ht="24" customHeight="1" s="48">
       <c r="A218" s="2" t="n">
         <v>217</v>
       </c>
       <c r="B218" s="2" t="n"/>
-      <c r="C218" s="27" t="n"/>
+      <c r="C218" s="46" t="n"/>
       <c r="D218" s="2" t="n"/>
       <c r="E218" s="4" t="n"/>
       <c r="F218" s="39" t="inlineStr">
@@ -23439,12 +23480,12 @@
       </c>
       <c r="AH218" s="2" t="n"/>
     </row>
-    <row r="219" ht="24" customHeight="1" s="45">
+    <row r="219" ht="24" customHeight="1" s="48">
       <c r="A219" s="2" t="n">
         <v>218</v>
       </c>
       <c r="B219" s="2" t="n"/>
-      <c r="C219" s="27" t="n">
+      <c r="C219" s="46" t="n">
         <v>50445</v>
       </c>
       <c r="D219" s="2" t="n"/>
@@ -23541,12 +23582,12 @@
       </c>
       <c r="AH219" s="2" t="n"/>
     </row>
-    <row r="220" ht="24" customHeight="1" s="45">
+    <row r="220" ht="24" customHeight="1" s="48">
       <c r="A220" s="2" t="n">
         <v>219</v>
       </c>
       <c r="B220" s="2" t="n"/>
-      <c r="C220" s="27" t="n"/>
+      <c r="C220" s="46" t="n"/>
       <c r="D220" s="2" t="n"/>
       <c r="E220" s="4" t="n"/>
       <c r="F220" s="39" t="inlineStr">
@@ -23643,12 +23684,12 @@
       </c>
       <c r="AH220" s="2" t="n"/>
     </row>
-    <row r="221" ht="24" customHeight="1" s="45">
+    <row r="221" ht="24" customHeight="1" s="48">
       <c r="A221" s="2" t="n">
         <v>220</v>
       </c>
       <c r="B221" s="2" t="n"/>
-      <c r="C221" s="27" t="n"/>
+      <c r="C221" s="46" t="n"/>
       <c r="D221" s="2" t="n"/>
       <c r="E221" s="4" t="n"/>
       <c r="F221" s="39" t="n"/>
@@ -23735,12 +23776,12 @@
       </c>
       <c r="AH221" s="2" t="n"/>
     </row>
-    <row r="222" ht="24" customHeight="1" s="45">
+    <row r="222" ht="24" customHeight="1" s="48">
       <c r="A222" s="2" t="n">
         <v>221</v>
       </c>
       <c r="B222" s="2" t="n"/>
-      <c r="C222" s="27" t="n"/>
+      <c r="C222" s="46" t="n"/>
       <c r="D222" s="2" t="n"/>
       <c r="E222" s="4" t="n"/>
       <c r="F222" s="39" t="inlineStr">
@@ -23835,12 +23876,12 @@
       </c>
       <c r="AH222" s="2" t="n"/>
     </row>
-    <row r="223" ht="24" customHeight="1" s="45">
+    <row r="223" ht="24" customHeight="1" s="48">
       <c r="A223" s="2" t="n">
         <v>222</v>
       </c>
       <c r="B223" s="2" t="n"/>
-      <c r="C223" s="27" t="n"/>
+      <c r="C223" s="46" t="n"/>
       <c r="D223" s="2" t="n"/>
       <c r="E223" s="4" t="n"/>
       <c r="F223" s="39" t="inlineStr">
@@ -23937,12 +23978,12 @@
       </c>
       <c r="AH223" s="2" t="n"/>
     </row>
-    <row r="224" ht="24" customHeight="1" s="45">
+    <row r="224" ht="24" customHeight="1" s="48">
       <c r="A224" s="2" t="n">
         <v>223</v>
       </c>
       <c r="B224" s="2" t="n"/>
-      <c r="C224" s="27" t="n"/>
+      <c r="C224" s="46" t="n"/>
       <c r="D224" s="2" t="n"/>
       <c r="E224" s="4" t="n"/>
       <c r="F224" s="39" t="inlineStr">
@@ -24039,12 +24080,12 @@
       </c>
       <c r="AH224" s="2" t="n"/>
     </row>
-    <row r="225" ht="24" customHeight="1" s="45">
+    <row r="225" ht="24" customHeight="1" s="48">
       <c r="A225" s="2" t="n">
         <v>224</v>
       </c>
       <c r="B225" s="2" t="n"/>
-      <c r="C225" s="27" t="n">
+      <c r="C225" s="46" t="n">
         <v>50618</v>
       </c>
       <c r="D225" s="2" t="n"/>
@@ -24141,7 +24182,7 @@
       </c>
       <c r="AH225" s="2" t="n"/>
     </row>
-    <row r="226" ht="24" customHeight="1" s="45">
+    <row r="226" ht="24" customHeight="1" s="48">
       <c r="A226" s="2" t="n">
         <v>225</v>
       </c>
@@ -24150,7 +24191,7 @@
           <t>ogimet</t>
         </is>
       </c>
-      <c r="C226" s="27" t="n">
+      <c r="C226" s="46" t="n">
         <v>53083</v>
       </c>
       <c r="D226" s="2" t="inlineStr">
@@ -24186,12 +24227,8 @@
         </is>
       </c>
       <c r="N226" s="2" t="n"/>
-      <c r="O226" s="32" t="n">
-        <v>-22.7</v>
-      </c>
-      <c r="P226" s="32" t="n">
-        <v>-14.8</v>
-      </c>
+      <c r="O226" s="32" t="n"/>
+      <c r="P226" s="32" t="n"/>
       <c r="Q226" s="32" t="n"/>
       <c r="R226" s="23" t="n"/>
       <c r="S226" s="37" t="n"/>
@@ -24247,12 +24284,12 @@
       <c r="AG226" s="2" t="n"/>
       <c r="AH226" s="2" t="n"/>
     </row>
-    <row r="227" ht="24" customHeight="1" s="45">
+    <row r="227" ht="24" customHeight="1" s="48">
       <c r="A227" s="2" t="n">
         <v>226</v>
       </c>
       <c r="B227" s="2" t="n"/>
-      <c r="C227" s="27" t="n"/>
+      <c r="C227" s="46" t="n"/>
       <c r="D227" s="2" t="n"/>
       <c r="E227" s="4" t="n"/>
       <c r="F227" s="39" t="inlineStr">
@@ -24349,7 +24386,7 @@
       </c>
       <c r="AH227" s="2" t="n"/>
     </row>
-    <row r="228" ht="24" customHeight="1" s="45">
+    <row r="228" ht="24" customHeight="1" s="48">
       <c r="A228" s="2" t="n">
         <v>227</v>
       </c>
@@ -24358,7 +24395,7 @@
           <t>ogimet</t>
         </is>
       </c>
-      <c r="C228" s="27" t="n">
+      <c r="C228" s="46" t="n">
         <v>50548</v>
       </c>
       <c r="D228" s="2" t="inlineStr">
@@ -24455,12 +24492,12 @@
       </c>
       <c r="AH228" s="2" t="n"/>
     </row>
-    <row r="229" ht="24" customHeight="1" s="45">
+    <row r="229" ht="24" customHeight="1" s="48">
       <c r="A229" s="2" t="n">
         <v>228</v>
       </c>
       <c r="B229" s="2" t="n"/>
-      <c r="C229" s="27" t="n"/>
+      <c r="C229" s="46" t="n"/>
       <c r="D229" s="2" t="n"/>
       <c r="E229" s="4" t="n"/>
       <c r="F229" s="39" t="inlineStr">
@@ -24551,12 +24588,12 @@
       </c>
       <c r="AH229" s="2" t="n"/>
     </row>
-    <row r="230" ht="24" customHeight="1" s="45">
+    <row r="230" ht="24" customHeight="1" s="48">
       <c r="A230" s="2" t="n">
         <v>229</v>
       </c>
       <c r="B230" s="2" t="n"/>
-      <c r="C230" s="27" t="n"/>
+      <c r="C230" s="46" t="n"/>
       <c r="D230" s="2" t="n"/>
       <c r="E230" s="4" t="n"/>
       <c r="F230" s="39" t="inlineStr">
@@ -24647,12 +24684,12 @@
       </c>
       <c r="AH230" s="2" t="n"/>
     </row>
-    <row r="231" ht="24" customHeight="1" s="45">
+    <row r="231" ht="24" customHeight="1" s="48">
       <c r="A231" s="2" t="n">
         <v>230</v>
       </c>
       <c r="B231" s="2" t="n"/>
-      <c r="C231" s="27" t="n"/>
+      <c r="C231" s="46" t="n"/>
       <c r="D231" s="2" t="n"/>
       <c r="E231" s="4" t="n"/>
       <c r="F231" s="39" t="n"/>
@@ -24735,12 +24772,12 @@
       </c>
       <c r="AH231" s="2" t="n"/>
     </row>
-    <row r="232" ht="24" customHeight="1" s="45">
+    <row r="232" ht="24" customHeight="1" s="48">
       <c r="A232" s="2" t="n">
         <v>231</v>
       </c>
       <c r="B232" s="2" t="n"/>
-      <c r="C232" s="27" t="n"/>
+      <c r="C232" s="46" t="n"/>
       <c r="D232" s="2" t="n"/>
       <c r="E232" s="4" t="n"/>
       <c r="F232" s="39" t="n"/>
@@ -24827,12 +24864,12 @@
       </c>
       <c r="AH232" s="2" t="n"/>
     </row>
-    <row r="233" ht="24" customHeight="1" s="45">
+    <row r="233" ht="24" customHeight="1" s="48">
       <c r="A233" s="2" t="n">
         <v>232</v>
       </c>
       <c r="B233" s="2" t="n"/>
-      <c r="C233" s="27" t="n"/>
+      <c r="C233" s="46" t="n"/>
       <c r="D233" s="2" t="n"/>
       <c r="E233" s="4" t="n"/>
       <c r="F233" s="39" t="n"/>
@@ -24919,12 +24956,12 @@
       </c>
       <c r="AH233" s="2" t="n"/>
     </row>
-    <row r="234" ht="24" customHeight="1" s="45">
+    <row r="234" ht="24" customHeight="1" s="48">
       <c r="A234" s="2" t="n">
         <v>233</v>
       </c>
       <c r="B234" s="2" t="n"/>
-      <c r="C234" s="27" t="n"/>
+      <c r="C234" s="46" t="n"/>
       <c r="D234" s="2" t="n"/>
       <c r="E234" s="4" t="n"/>
       <c r="F234" s="39" t="inlineStr">
@@ -25015,12 +25052,12 @@
       </c>
       <c r="AH234" s="2" t="n"/>
     </row>
-    <row r="235" ht="24" customHeight="1" s="45">
+    <row r="235" ht="24" customHeight="1" s="48">
       <c r="A235" s="2" t="n">
         <v>234</v>
       </c>
       <c r="B235" s="2" t="n"/>
-      <c r="C235" s="27" t="n"/>
+      <c r="C235" s="46" t="n"/>
       <c r="D235" s="2" t="n"/>
       <c r="E235" s="4" t="n"/>
       <c r="F235" s="39" t="inlineStr">
@@ -25111,12 +25148,12 @@
       </c>
       <c r="AH235" s="2" t="n"/>
     </row>
-    <row r="236" ht="24" customHeight="1" s="45">
+    <row r="236" ht="24" customHeight="1" s="48">
       <c r="A236" s="2" t="n">
         <v>235</v>
       </c>
       <c r="B236" s="2" t="n"/>
-      <c r="C236" s="27" t="n"/>
+      <c r="C236" s="46" t="n"/>
       <c r="D236" s="2" t="n"/>
       <c r="E236" s="4" t="n"/>
       <c r="F236" s="39" t="n"/>
@@ -25203,12 +25240,12 @@
       </c>
       <c r="AH236" s="2" t="n"/>
     </row>
-    <row r="237" ht="24" customHeight="1" s="45">
+    <row r="237" ht="24" customHeight="1" s="48">
       <c r="A237" s="2" t="n">
         <v>236</v>
       </c>
       <c r="B237" s="2" t="n"/>
-      <c r="C237" s="27" t="n">
+      <c r="C237" s="46" t="n">
         <v>52645</v>
       </c>
       <c r="D237" s="2" t="n"/>
@@ -25305,12 +25342,12 @@
       </c>
       <c r="AH237" s="2" t="n"/>
     </row>
-    <row r="238" ht="24" customHeight="1" s="45">
+    <row r="238" ht="24" customHeight="1" s="48">
       <c r="A238" s="2" t="n">
         <v>237</v>
       </c>
       <c r="B238" s="2" t="n"/>
-      <c r="C238" s="27" t="n"/>
+      <c r="C238" s="46" t="n"/>
       <c r="D238" s="2" t="n"/>
       <c r="E238" s="4" t="n"/>
       <c r="F238" s="39" t="inlineStr">
@@ -25407,12 +25444,12 @@
       </c>
       <c r="AH238" s="2" t="n"/>
     </row>
-    <row r="239" ht="24" customHeight="1" s="45">
+    <row r="239" ht="24" customHeight="1" s="48">
       <c r="A239" s="2" t="n">
         <v>238</v>
       </c>
       <c r="B239" s="2" t="n"/>
-      <c r="C239" s="27" t="n"/>
+      <c r="C239" s="46" t="n"/>
       <c r="D239" s="2" t="n"/>
       <c r="E239" s="4" t="n"/>
       <c r="F239" s="39" t="inlineStr">
@@ -25505,12 +25542,12 @@
       <c r="AG239" s="2" t="n"/>
       <c r="AH239" s="2" t="n"/>
     </row>
-    <row r="240" ht="24" customHeight="1" s="45">
+    <row r="240" ht="24" customHeight="1" s="48">
       <c r="A240" s="2" t="n">
         <v>239</v>
       </c>
       <c r="B240" s="2" t="n"/>
-      <c r="C240" s="27" t="n"/>
+      <c r="C240" s="46" t="n"/>
       <c r="D240" s="2" t="n"/>
       <c r="E240" s="4" t="n"/>
       <c r="F240" s="39" t="inlineStr">
@@ -25601,12 +25638,12 @@
       </c>
       <c r="AH240" s="2" t="n"/>
     </row>
-    <row r="241" ht="24" customHeight="1" s="45">
+    <row r="241" ht="24" customHeight="1" s="48">
       <c r="A241" s="2" t="n">
         <v>240</v>
       </c>
       <c r="B241" s="2" t="n"/>
-      <c r="C241" s="27" t="n"/>
+      <c r="C241" s="46" t="n"/>
       <c r="D241" s="2" t="n"/>
       <c r="E241" s="4" t="n"/>
       <c r="F241" s="39" t="inlineStr">
@@ -25638,8 +25675,12 @@
         </is>
       </c>
       <c r="N241" s="2" t="n"/>
-      <c r="O241" s="32" t="n"/>
-      <c r="P241" s="32" t="n"/>
+      <c r="O241" s="32" t="n">
+        <v>-40.7</v>
+      </c>
+      <c r="P241" s="32" t="n">
+        <v>-15.5</v>
+      </c>
       <c r="Q241" s="32" t="n"/>
       <c r="R241" s="23" t="inlineStr">
         <is>
@@ -25703,12 +25744,12 @@
       </c>
       <c r="AH241" s="2" t="n"/>
     </row>
-    <row r="242" ht="24" customHeight="1" s="45">
+    <row r="242" ht="24" customHeight="1" s="48">
       <c r="A242" s="2" t="n">
         <v>241</v>
       </c>
       <c r="B242" s="2" t="n"/>
-      <c r="C242" s="27" t="n"/>
+      <c r="C242" s="46" t="n"/>
       <c r="D242" s="2" t="n"/>
       <c r="E242" s="4" t="n"/>
       <c r="F242" s="39" t="n"/>
@@ -25793,7 +25834,7 @@
       <c r="AG242" s="2" t="n"/>
       <c r="AH242" s="2" t="n"/>
     </row>
-    <row r="243" ht="24" customHeight="1" s="45">
+    <row r="243" ht="24" customHeight="1" s="48">
       <c r="A243" s="2" t="n">
         <v>242</v>
       </c>
@@ -25802,7 +25843,7 @@
           <t>ogimet</t>
         </is>
       </c>
-      <c r="C243" s="27" t="n">
+      <c r="C243" s="46" t="n">
         <v>44313</v>
       </c>
       <c r="D243" s="2" t="inlineStr">
@@ -25891,12 +25932,12 @@
       <c r="AG243" s="2" t="n"/>
       <c r="AH243" s="2" t="n"/>
     </row>
-    <row r="244" ht="24" customHeight="1" s="45">
+    <row r="244" ht="24" customHeight="1" s="48">
       <c r="A244" s="2" t="n">
         <v>243</v>
       </c>
       <c r="B244" s="2" t="n"/>
-      <c r="C244" s="27" t="n"/>
+      <c r="C244" s="46" t="n"/>
       <c r="D244" s="2" t="n"/>
       <c r="E244" s="4" t="n"/>
       <c r="F244" s="39" t="n">
@@ -25987,12 +26028,12 @@
       </c>
       <c r="AH244" s="2" t="n"/>
     </row>
-    <row r="245" ht="24" customHeight="1" s="45">
+    <row r="245" ht="24" customHeight="1" s="48">
       <c r="A245" s="2" t="n">
         <v>244</v>
       </c>
       <c r="B245" s="2" t="n"/>
-      <c r="C245" s="27" t="n"/>
+      <c r="C245" s="46" t="n"/>
       <c r="D245" s="2" t="n"/>
       <c r="E245" s="4" t="n"/>
       <c r="F245" s="39" t="n">
@@ -26079,12 +26120,12 @@
       <c r="AG245" s="2" t="n"/>
       <c r="AH245" s="2" t="n"/>
     </row>
-    <row r="246" ht="24" customHeight="1" s="45">
+    <row r="246" ht="24" customHeight="1" s="48">
       <c r="A246" s="2" t="n">
         <v>245</v>
       </c>
       <c r="B246" s="2" t="n"/>
-      <c r="C246" s="27" t="n"/>
+      <c r="C246" s="46" t="n"/>
       <c r="D246" s="2" t="n"/>
       <c r="E246" s="4" t="n"/>
       <c r="F246" s="39" t="n">
@@ -26167,7 +26208,7 @@
       <c r="AG246" s="2" t="n"/>
       <c r="AH246" s="2" t="n"/>
     </row>
-    <row r="247" ht="24" customHeight="1" s="45">
+    <row r="247" ht="24" customHeight="1" s="48">
       <c r="A247" s="2" t="n">
         <v>246</v>
       </c>
@@ -26176,7 +26217,7 @@
           <t>ogimet</t>
         </is>
       </c>
-      <c r="C247" s="27" t="n">
+      <c r="C247" s="46" t="n">
         <v>35188</v>
       </c>
       <c r="D247" s="2" t="inlineStr">
@@ -26213,13 +26254,13 @@
       </c>
       <c r="N247" s="2" t="n"/>
       <c r="O247" s="32" t="n">
-        <v>-11.8</v>
+        <v>-27.3</v>
       </c>
       <c r="P247" s="32" t="n">
-        <v>-3</v>
+        <v>-18.1</v>
       </c>
       <c r="Q247" s="32" t="n">
-        <v>-7.49</v>
+        <v>-23.49</v>
       </c>
       <c r="R247" s="23" t="inlineStr">
         <is>
@@ -26279,7 +26320,7 @@
       <c r="AG247" s="2" t="n"/>
       <c r="AH247" s="2" t="n"/>
     </row>
-    <row r="248" ht="24" customHeight="1" s="45">
+    <row r="248" ht="24" customHeight="1" s="48">
       <c r="A248" s="2" t="n">
         <v>247</v>
       </c>
@@ -26288,7 +26329,7 @@
           <t>ogimet</t>
         </is>
       </c>
-      <c r="C248" s="27" t="n">
+      <c r="C248" s="46" t="n">
         <v>36421</v>
       </c>
       <c r="D248" s="2" t="inlineStr">
@@ -26325,13 +26366,13 @@
       </c>
       <c r="N248" s="2" t="n"/>
       <c r="O248" s="32" t="n">
-        <v>-17.9</v>
+        <v>-41.8</v>
       </c>
       <c r="P248" s="32" t="n">
-        <v>-8.6</v>
+        <v>-23.7</v>
       </c>
       <c r="Q248" s="32" t="n">
-        <v>-13.11</v>
+        <v>-33.75</v>
       </c>
       <c r="R248" s="23" t="inlineStr">
         <is>
@@ -26387,7 +26428,7 @@
       </c>
       <c r="AH248" s="2" t="n"/>
     </row>
-    <row r="249" ht="24" customHeight="1" s="45">
+    <row r="249" ht="24" customHeight="1" s="48">
       <c r="A249" s="2" t="n">
         <v>248</v>
       </c>
@@ -26396,7 +26437,7 @@
           <t>ogimet</t>
         </is>
       </c>
-      <c r="C249" s="27" t="n">
+      <c r="C249" s="46" t="n">
         <v>31960</v>
       </c>
       <c r="D249" s="2" t="inlineStr">
@@ -26433,13 +26474,13 @@
       </c>
       <c r="N249" s="2" t="n"/>
       <c r="O249" s="32" t="n">
-        <v>0.6</v>
+        <v>-8.699999999999999</v>
       </c>
       <c r="P249" s="32" t="n">
-        <v>5</v>
+        <v>-4.4</v>
       </c>
       <c r="Q249" s="32" t="n">
-        <v>3.09</v>
+        <v>-7.17</v>
       </c>
       <c r="R249" s="23" t="inlineStr">
         <is>
@@ -26499,7 +26540,7 @@
       <c r="AG249" s="2" t="n"/>
       <c r="AH249" s="2" t="n"/>
     </row>
-    <row r="250" ht="24" customHeight="1" s="45">
+    <row r="250" ht="24" customHeight="1" s="48">
       <c r="A250" s="2" t="n">
         <v>249</v>
       </c>
@@ -26508,7 +26549,7 @@
           <t>ogimet</t>
         </is>
       </c>
-      <c r="C250" s="27" t="n">
+      <c r="C250" s="46" t="n">
         <v>30823</v>
       </c>
       <c r="D250" s="2" t="inlineStr">
@@ -26545,13 +26586,13 @@
       </c>
       <c r="N250" s="2" t="n"/>
       <c r="O250" s="32" t="n">
-        <v>-27.6</v>
+        <v>-31.7</v>
       </c>
       <c r="P250" s="32" t="n">
-        <v>-14</v>
+        <v>-15.5</v>
       </c>
       <c r="Q250" s="32" t="n">
-        <v>-20.61</v>
+        <v>-23.89</v>
       </c>
       <c r="R250" s="23" t="inlineStr">
         <is>
@@ -26615,7 +26656,7 @@
       </c>
       <c r="AH250" s="2" t="n"/>
     </row>
-    <row r="251" ht="24" customHeight="1" s="45">
+    <row r="251" ht="24" customHeight="1" s="48">
       <c r="A251" s="2" t="n">
         <v>250</v>
       </c>
@@ -26624,7 +26665,7 @@
           <t>ogimet</t>
         </is>
       </c>
-      <c r="C251" s="27" t="n">
+      <c r="C251" s="46" t="n">
         <v>23699</v>
       </c>
       <c r="D251" s="2" t="inlineStr">
@@ -26665,10 +26706,10 @@
         </is>
       </c>
       <c r="O251" s="32" t="n">
-        <v>-49.3</v>
+        <v>-34.2</v>
       </c>
       <c r="P251" s="32" t="n">
-        <v>-28.5</v>
+        <v>-19.4</v>
       </c>
       <c r="Q251" s="32" t="n"/>
       <c r="R251" s="23" t="inlineStr">
@@ -26717,7 +26758,7 @@
       <c r="AG251" s="2" t="n"/>
       <c r="AH251" s="2" t="n"/>
     </row>
-    <row r="252" ht="24" customHeight="1" s="45">
+    <row r="252" ht="24" customHeight="1" s="48">
       <c r="A252" s="2" t="n">
         <v>251</v>
       </c>
@@ -26726,7 +26767,7 @@
           <t>rp5</t>
         </is>
       </c>
-      <c r="C252" s="27" t="n">
+      <c r="C252" s="46" t="n">
         <v>29570</v>
       </c>
       <c r="D252" s="2" t="inlineStr">
@@ -26763,13 +26804,13 @@
       </c>
       <c r="N252" s="2" t="n"/>
       <c r="O252" s="32" t="n">
-        <v>-31.8</v>
+        <v>-31</v>
       </c>
       <c r="P252" s="32" t="n">
-        <v>-20.1</v>
+        <v>-16.5</v>
       </c>
       <c r="Q252" s="32" t="n">
-        <v>-25.94</v>
+        <v>-24.32</v>
       </c>
       <c r="R252" s="23" t="inlineStr">
         <is>
@@ -26829,12 +26870,12 @@
       <c r="AG252" s="2" t="n"/>
       <c r="AH252" s="2" t="n"/>
     </row>
-    <row r="253" ht="24" customHeight="1" s="45">
+    <row r="253" ht="24" customHeight="1" s="48">
       <c r="A253" s="2" t="n">
         <v>252</v>
       </c>
       <c r="B253" s="2" t="n"/>
-      <c r="C253" s="27" t="n">
+      <c r="C253" s="46" t="n">
         <v>23499</v>
       </c>
       <c r="D253" s="2" t="n"/>
@@ -26915,7 +26956,7 @@
       <c r="AG253" s="2" t="n"/>
       <c r="AH253" s="2" t="n"/>
     </row>
-    <row r="254" ht="24" customHeight="1" s="45">
+    <row r="254" ht="24" customHeight="1" s="48">
       <c r="A254" s="2" t="n">
         <v>253</v>
       </c>
@@ -26924,7 +26965,7 @@
           <t>ogimet</t>
         </is>
       </c>
-      <c r="C254" s="27" t="n">
+      <c r="C254" s="46" t="n">
         <v>24136</v>
       </c>
       <c r="D254" s="2" t="inlineStr">
@@ -26961,13 +27002,13 @@
       </c>
       <c r="N254" s="2" t="n"/>
       <c r="O254" s="32" t="n">
-        <v>-49.7</v>
+        <v>-34</v>
       </c>
       <c r="P254" s="32" t="n">
-        <v>-31.9</v>
+        <v>-20.8</v>
       </c>
       <c r="Q254" s="32" t="n">
-        <v>-42.81</v>
+        <v>-26.44</v>
       </c>
       <c r="R254" s="23" t="inlineStr">
         <is>
@@ -27019,7 +27060,7 @@
       <c r="AG254" s="2" t="n"/>
       <c r="AH254" s="2" t="n"/>
     </row>
-    <row r="255" ht="24" customHeight="1" s="45">
+    <row r="255" ht="24" customHeight="1" s="48">
       <c r="A255" s="2" t="n">
         <v>254</v>
       </c>
@@ -27028,7 +27069,7 @@
           <t>ogimet</t>
         </is>
       </c>
-      <c r="C255" s="27" t="n">
+      <c r="C255" s="46" t="n">
         <v>24525</v>
       </c>
       <c r="D255" s="2" t="inlineStr">
@@ -27113,7 +27154,7 @@
       <c r="AG255" s="2" t="n"/>
       <c r="AH255" s="2" t="n"/>
     </row>
-    <row r="256" ht="24" customHeight="1" s="45">
+    <row r="256" ht="24" customHeight="1" s="48">
       <c r="A256" s="2" t="n">
         <v>255</v>
       </c>
@@ -27122,7 +27163,7 @@
           <t>ogimet</t>
         </is>
       </c>
-      <c r="C256" s="27" t="n">
+      <c r="C256" s="46" t="n">
         <v>24856</v>
       </c>
       <c r="D256" s="2" t="inlineStr">
@@ -27211,7 +27252,7 @@
       </c>
       <c r="AH256" s="2" t="n"/>
     </row>
-    <row r="257" ht="24" customHeight="1" s="45">
+    <row r="257" ht="24" customHeight="1" s="48">
       <c r="A257" s="2" t="n">
         <v>256</v>
       </c>
@@ -27220,7 +27261,7 @@
           <t>ogimet</t>
         </is>
       </c>
-      <c r="C257" s="27" t="n">
+      <c r="C257" s="46" t="n">
         <v>24668</v>
       </c>
       <c r="D257" s="2" t="inlineStr">
@@ -27309,7 +27350,7 @@
       </c>
       <c r="AH257" s="2" t="n"/>
     </row>
-    <row r="258" ht="24" customHeight="1" s="45">
+    <row r="258" ht="24" customHeight="1" s="48">
       <c r="A258" s="2" t="n">
         <v>257</v>
       </c>
@@ -27318,7 +27359,7 @@
           <t>ogimet</t>
         </is>
       </c>
-      <c r="C258" s="27" t="n">
+      <c r="C258" s="46" t="n">
         <v>31005</v>
       </c>
       <c r="D258" s="2" t="inlineStr">
@@ -27399,7 +27440,7 @@
       <c r="AG258" s="2" t="n"/>
       <c r="AH258" s="2" t="n"/>
     </row>
-    <row r="259" ht="24" customHeight="1" s="45">
+    <row r="259" ht="24" customHeight="1" s="48">
       <c r="A259" s="2" t="n">
         <v>258</v>
       </c>
@@ -27408,7 +27449,7 @@
           <t>ogimet</t>
         </is>
       </c>
-      <c r="C259" s="27" t="n">
+      <c r="C259" s="46" t="n">
         <v>24538</v>
       </c>
       <c r="D259" s="2" t="inlineStr">
@@ -27489,7 +27530,7 @@
       <c r="AG259" s="2" t="n"/>
       <c r="AH259" s="2" t="n"/>
     </row>
-    <row r="260" ht="24" customHeight="1" s="45">
+    <row r="260" ht="24" customHeight="1" s="48">
       <c r="A260" s="2" t="n">
         <v>259</v>
       </c>
@@ -27498,7 +27539,7 @@
           <t>ogimet</t>
         </is>
       </c>
-      <c r="C260" s="27" t="n">
+      <c r="C260" s="46" t="n">
         <v>36103</v>
       </c>
       <c r="D260" s="2" t="inlineStr">
@@ -27535,13 +27576,13 @@
       </c>
       <c r="N260" s="2" t="n"/>
       <c r="O260" s="32" t="n">
-        <v>-36.8</v>
+        <v>-32.9</v>
       </c>
       <c r="P260" s="32" t="n">
-        <v>-14.4</v>
+        <v>-13.2</v>
       </c>
       <c r="Q260" s="32" t="n">
-        <v>-23.96</v>
+        <v>-23.09</v>
       </c>
       <c r="R260" s="23" t="inlineStr">
         <is>
@@ -27597,7 +27638,7 @@
       </c>
       <c r="AH260" s="2" t="n"/>
     </row>
-    <row r="261" ht="24" customHeight="1" s="45">
+    <row r="261" ht="24" customHeight="1" s="48">
       <c r="A261" s="2" t="n">
         <v>260</v>
       </c>
@@ -27606,7 +27647,7 @@
           <t>ogimet</t>
         </is>
       </c>
-      <c r="C261" s="27" t="n">
+      <c r="C261" s="46" t="n">
         <v>30758</v>
       </c>
       <c r="D261" s="2" t="inlineStr">
@@ -27643,13 +27684,13 @@
       </c>
       <c r="N261" s="2" t="n"/>
       <c r="O261" s="32" t="n">
-        <v>-20.3</v>
+        <v>-34.8</v>
       </c>
       <c r="P261" s="32" t="n">
-        <v>-13.6</v>
+        <v>-13.7</v>
       </c>
       <c r="Q261" s="32" t="n">
-        <v>-17.49</v>
+        <v>-24.82</v>
       </c>
       <c r="R261" s="23" t="inlineStr">
         <is>
@@ -27709,7 +27750,7 @@
       <c r="AG261" s="2" t="n"/>
       <c r="AH261" s="2" t="n"/>
     </row>
-    <row r="262" ht="24" customHeight="1" s="45">
+    <row r="262" ht="24" customHeight="1" s="48">
       <c r="A262" s="2" t="n">
         <v>261</v>
       </c>
@@ -27718,7 +27759,7 @@
           <t>ogimet</t>
         </is>
       </c>
-      <c r="C262" s="27" t="n">
+      <c r="C262" s="46" t="n">
         <v>29638</v>
       </c>
       <c r="D262" s="2" t="inlineStr">
@@ -27755,13 +27796,13 @@
       </c>
       <c r="N262" s="2" t="n"/>
       <c r="O262" s="32" t="n">
-        <v>-23.4</v>
+        <v>-25.9</v>
       </c>
       <c r="P262" s="32" t="n">
-        <v>-14.9</v>
+        <v>-21</v>
       </c>
       <c r="Q262" s="32" t="n">
-        <v>-20.11</v>
+        <v>-23.68</v>
       </c>
       <c r="R262" s="23" t="inlineStr">
         <is>
@@ -27821,7 +27862,7 @@
       <c r="AG262" s="2" t="n"/>
       <c r="AH262" s="2" t="n"/>
     </row>
-    <row r="263" ht="24" customHeight="1" s="45">
+    <row r="263" ht="24" customHeight="1" s="48">
       <c r="A263" s="2" t="n">
         <v>262</v>
       </c>
@@ -27830,7 +27871,7 @@
           <t>ogimet</t>
         </is>
       </c>
-      <c r="C263" s="27" t="n">
+      <c r="C263" s="46" t="n">
         <v>30337</v>
       </c>
       <c r="D263" s="2" t="inlineStr">
@@ -27915,7 +27956,7 @@
       </c>
       <c r="AH263" s="2" t="n"/>
     </row>
-    <row r="264" ht="24" customHeight="1" s="45">
+    <row r="264" ht="24" customHeight="1" s="48">
       <c r="A264" s="2" t="n">
         <v>263</v>
       </c>
@@ -27924,7 +27965,7 @@
           <t>ogimet</t>
         </is>
       </c>
-      <c r="C264" s="27" t="n">
+      <c r="C264" s="46" t="n">
         <v>30710</v>
       </c>
       <c r="D264" s="2" t="inlineStr">
@@ -27961,13 +28002,13 @@
       </c>
       <c r="N264" s="2" t="n"/>
       <c r="O264" s="32" t="n">
-        <v>-18.9</v>
+        <v>-27.8</v>
       </c>
       <c r="P264" s="32" t="n">
-        <v>-14.7</v>
+        <v>-16.9</v>
       </c>
       <c r="Q264" s="32" t="n">
-        <v>-17.21</v>
+        <v>-22.02</v>
       </c>
       <c r="R264" s="23" t="inlineStr">
         <is>
@@ -28031,7 +28072,7 @@
       </c>
       <c r="AH264" s="2" t="n"/>
     </row>
-    <row r="265" ht="24" customHeight="1" s="45">
+    <row r="265" ht="24" customHeight="1" s="48">
       <c r="A265" s="2" t="n">
         <v>264</v>
       </c>
@@ -28040,7 +28081,7 @@
           <t>ogimet</t>
         </is>
       </c>
-      <c r="C265" s="27" t="n">
+      <c r="C265" s="46" t="n">
         <v>89606</v>
       </c>
       <c r="D265" s="2" t="inlineStr">
@@ -28081,10 +28122,10 @@
       </c>
       <c r="N265" s="2" t="n"/>
       <c r="O265" s="32" t="n">
-        <v>-42.6</v>
+        <v>-51.1</v>
       </c>
       <c r="P265" s="32" t="n">
-        <v>-25.8</v>
+        <v>-43.6</v>
       </c>
       <c r="Q265" s="32" t="n"/>
       <c r="R265" s="23" t="inlineStr">
@@ -28133,12 +28174,12 @@
       </c>
       <c r="AH265" s="2" t="n"/>
     </row>
-    <row r="266" ht="24" customHeight="1" s="45">
+    <row r="266" ht="24" customHeight="1" s="48">
       <c r="A266" s="2" t="n">
         <v>265</v>
       </c>
       <c r="B266" s="2" t="n"/>
-      <c r="C266" s="27" t="n"/>
+      <c r="C266" s="46" t="n"/>
       <c r="D266" s="2" t="n"/>
       <c r="E266" s="4" t="n"/>
       <c r="F266" s="39" t="inlineStr">
@@ -28225,12 +28266,12 @@
       <c r="AG266" s="2" t="n"/>
       <c r="AH266" s="2" t="n"/>
     </row>
-    <row r="267" ht="24" customHeight="1" s="45">
+    <row r="267" ht="24" customHeight="1" s="48">
       <c r="A267" s="2" t="n">
         <v>266</v>
       </c>
       <c r="B267" s="2" t="n"/>
-      <c r="C267" s="27" t="n"/>
+      <c r="C267" s="46" t="n"/>
       <c r="D267" s="2" t="n"/>
       <c r="E267" s="4" t="n"/>
       <c r="F267" s="39" t="n"/>
@@ -28311,12 +28352,12 @@
       <c r="AG267" s="2" t="n"/>
       <c r="AH267" s="2" t="n"/>
     </row>
-    <row r="268" ht="24" customHeight="1" s="45">
+    <row r="268" ht="24" customHeight="1" s="48">
       <c r="A268" s="2" t="n">
         <v>267</v>
       </c>
       <c r="B268" s="2" t="n"/>
-      <c r="C268" s="27" t="n"/>
+      <c r="C268" s="46" t="n"/>
       <c r="D268" s="2" t="n"/>
       <c r="E268" s="4" t="n"/>
       <c r="F268" s="39" t="inlineStr">
@@ -28403,7 +28444,7 @@
       <c r="AG268" s="2" t="n"/>
       <c r="AH268" s="2" t="n"/>
     </row>
-    <row r="269" ht="24" customHeight="1" s="45">
+    <row r="269" ht="24" customHeight="1" s="48">
       <c r="A269" s="2" t="n">
         <v>268</v>
       </c>
@@ -28412,7 +28453,7 @@
           <t>ogimet</t>
         </is>
       </c>
-      <c r="C269" s="27" t="n">
+      <c r="C269" s="46" t="n">
         <v>50915</v>
       </c>
       <c r="D269" s="2" t="inlineStr">
@@ -28501,12 +28542,12 @@
       <c r="AG269" s="2" t="n"/>
       <c r="AH269" s="2" t="n"/>
     </row>
-    <row r="270" ht="24" customHeight="1" s="45">
+    <row r="270" ht="24" customHeight="1" s="48">
       <c r="A270" s="2" t="n">
         <v>269</v>
       </c>
       <c r="B270" s="2" t="n"/>
-      <c r="C270" s="27" t="n">
+      <c r="C270" s="46" t="n">
         <v>50913</v>
       </c>
       <c r="D270" s="2" t="n"/>
@@ -28595,7 +28636,7 @@
       <c r="AG270" s="2" t="n"/>
       <c r="AH270" s="2" t="n"/>
     </row>
-    <row r="271" ht="24" customHeight="1" s="45">
+    <row r="271" ht="24" customHeight="1" s="48">
       <c r="A271" s="2" t="n">
         <v>270</v>
       </c>
@@ -28604,7 +28645,7 @@
           <t>ogimet</t>
         </is>
       </c>
-      <c r="C271" s="27" t="n">
+      <c r="C271" s="46" t="n">
         <v>54012</v>
       </c>
       <c r="D271" s="2" t="inlineStr">
@@ -28693,7 +28734,7 @@
       <c r="AG271" s="2" t="n"/>
       <c r="AH271" s="2" t="n"/>
     </row>
-    <row r="272" ht="24" customHeight="1" s="45">
+    <row r="272" ht="24" customHeight="1" s="48">
       <c r="A272" s="2" t="n">
         <v>271</v>
       </c>
@@ -28702,7 +28743,7 @@
           <t>ogimet</t>
         </is>
       </c>
-      <c r="C272" s="27" t="n">
+      <c r="C272" s="46" t="n">
         <v>51087</v>
       </c>
       <c r="D272" s="2" t="inlineStr">
@@ -28795,12 +28836,12 @@
       </c>
       <c r="AH272" s="2" t="n"/>
     </row>
-    <row r="273" ht="24" customHeight="1" s="45">
+    <row r="273" ht="24" customHeight="1" s="48">
       <c r="A273" s="2" t="n">
         <v>272</v>
       </c>
       <c r="B273" s="2" t="n"/>
-      <c r="C273" s="27" t="n">
+      <c r="C273" s="46" t="n">
         <v>51060</v>
       </c>
       <c r="D273" s="2" t="n"/>
@@ -28889,12 +28930,12 @@
       </c>
       <c r="AH273" s="2" t="n"/>
     </row>
-    <row r="274" ht="24" customHeight="1" s="45">
+    <row r="274" ht="24" customHeight="1" s="48">
       <c r="A274" s="2" t="n">
         <v>273</v>
       </c>
       <c r="B274" s="2" t="n"/>
-      <c r="C274" s="27" t="n">
+      <c r="C274" s="46" t="n">
         <v>50861</v>
       </c>
       <c r="D274" s="2" t="n"/>
@@ -28991,12 +29032,12 @@
       </c>
       <c r="AH274" s="2" t="n"/>
     </row>
-    <row r="275" ht="24" customHeight="1" s="45">
+    <row r="275" ht="24" customHeight="1" s="48">
       <c r="A275" s="2" t="n">
         <v>274</v>
       </c>
       <c r="B275" s="2" t="n"/>
-      <c r="C275" s="27" t="n"/>
+      <c r="C275" s="46" t="n"/>
       <c r="D275" s="2" t="n"/>
       <c r="E275" s="4" t="n"/>
       <c r="F275" s="39" t="n"/>
@@ -29079,7 +29120,7 @@
       <c r="AG275" s="2" t="n"/>
       <c r="AH275" s="2" t="n"/>
     </row>
-    <row r="276" ht="24" customHeight="1" s="45">
+    <row r="276" ht="24" customHeight="1" s="48">
       <c r="A276" s="2" t="n">
         <v>275</v>
       </c>
@@ -29088,7 +29129,7 @@
           <t>ogimet</t>
         </is>
       </c>
-      <c r="C276" s="27" t="n">
+      <c r="C276" s="46" t="n">
         <v>25248</v>
       </c>
       <c r="D276" s="2" t="inlineStr">
@@ -29125,13 +29166,13 @@
       </c>
       <c r="N276" s="2" t="n"/>
       <c r="O276" s="32" t="n">
-        <v>-20.9</v>
+        <v>-43.6</v>
       </c>
       <c r="P276" s="32" t="n">
-        <v>-8.4</v>
+        <v>-31.1</v>
       </c>
       <c r="Q276" s="32" t="n">
-        <v>-14.85</v>
+        <v>-37.93</v>
       </c>
       <c r="R276" s="23" t="inlineStr">
         <is>
@@ -29183,12 +29224,12 @@
       <c r="AG276" s="2" t="n"/>
       <c r="AH276" s="2" t="n"/>
     </row>
-    <row r="277" ht="24" customHeight="1" s="45">
+    <row r="277" ht="24" customHeight="1" s="48">
       <c r="A277" s="2" t="n">
         <v>276</v>
       </c>
       <c r="B277" s="2" t="n"/>
-      <c r="C277" s="27" t="n"/>
+      <c r="C277" s="46" t="n"/>
       <c r="D277" s="2" t="n"/>
       <c r="E277" s="4" t="n"/>
       <c r="F277" s="39" t="inlineStr">
@@ -29271,12 +29312,12 @@
       <c r="AG277" s="2" t="n"/>
       <c r="AH277" s="2" t="n"/>
     </row>
-    <row r="278" ht="24" customHeight="1" s="45">
+    <row r="278" ht="24" customHeight="1" s="48">
       <c r="A278" s="2" t="n">
         <v>277</v>
       </c>
       <c r="B278" s="2" t="n"/>
-      <c r="C278" s="27" t="n">
+      <c r="C278" s="46" t="n">
         <v>54276</v>
       </c>
       <c r="D278" s="2" t="n"/>
@@ -29369,12 +29410,12 @@
       <c r="AG278" s="2" t="n"/>
       <c r="AH278" s="2" t="n"/>
     </row>
-    <row r="279" ht="24" customHeight="1" s="45">
+    <row r="279" ht="24" customHeight="1" s="48">
       <c r="A279" s="2" t="n">
         <v>278</v>
       </c>
       <c r="B279" s="2" t="n"/>
-      <c r="C279" s="27" t="n"/>
+      <c r="C279" s="46" t="n"/>
       <c r="D279" s="2" t="n"/>
       <c r="E279" s="4" t="n"/>
       <c r="F279" s="39" t="inlineStr">
@@ -29461,12 +29502,12 @@
       <c r="AG279" s="2" t="n"/>
       <c r="AH279" s="2" t="n"/>
     </row>
-    <row r="280" ht="24" customHeight="1" s="45">
+    <row r="280" ht="24" customHeight="1" s="48">
       <c r="A280" s="2" t="n">
         <v>279</v>
       </c>
       <c r="B280" s="2" t="n"/>
-      <c r="C280" s="27" t="n"/>
+      <c r="C280" s="46" t="n"/>
       <c r="D280" s="2" t="n"/>
       <c r="E280" s="4" t="n"/>
       <c r="F280" s="39" t="n"/>
@@ -29545,12 +29586,12 @@
       <c r="AG280" s="2" t="n"/>
       <c r="AH280" s="2" t="n"/>
     </row>
-    <row r="281" ht="24" customHeight="1" s="45">
+    <row r="281" ht="24" customHeight="1" s="48">
       <c r="A281" s="2" t="n">
         <v>280</v>
       </c>
       <c r="B281" s="2" t="n"/>
-      <c r="C281" s="27" t="n"/>
+      <c r="C281" s="46" t="n"/>
       <c r="D281" s="2" t="n"/>
       <c r="E281" s="4" t="n"/>
       <c r="F281" s="39" t="inlineStr">
@@ -29637,12 +29678,12 @@
       <c r="AG281" s="2" t="n"/>
       <c r="AH281" s="2" t="n"/>
     </row>
-    <row r="282" ht="24" customHeight="1" s="45">
+    <row r="282" ht="24" customHeight="1" s="48">
       <c r="A282" s="2" t="n">
         <v>281</v>
       </c>
       <c r="B282" s="2" t="n"/>
-      <c r="C282" s="27" t="n"/>
+      <c r="C282" s="46" t="n"/>
       <c r="D282" s="2" t="n"/>
       <c r="E282" s="4" t="n"/>
       <c r="F282" s="39" t="n"/>
@@ -29717,12 +29758,12 @@
       <c r="AG282" s="2" t="n"/>
       <c r="AH282" s="2" t="n"/>
     </row>
-    <row r="283" ht="24" customHeight="1" s="45">
+    <row r="283" ht="24" customHeight="1" s="48">
       <c r="A283" s="2" t="n">
         <v>282</v>
       </c>
       <c r="B283" s="2" t="n"/>
-      <c r="C283" s="27" t="n">
+      <c r="C283" s="46" t="n">
         <v>50779</v>
       </c>
       <c r="D283" s="2" t="n"/>
@@ -29809,12 +29850,12 @@
       <c r="AG283" s="2" t="n"/>
       <c r="AH283" s="2" t="n"/>
     </row>
-    <row r="284" ht="24" customHeight="1" s="45">
+    <row r="284" ht="24" customHeight="1" s="48">
       <c r="A284" s="2" t="n">
         <v>283</v>
       </c>
       <c r="B284" s="2" t="n"/>
-      <c r="C284" s="27" t="n">
+      <c r="C284" s="46" t="n">
         <v>51058</v>
       </c>
       <c r="D284" s="2" t="n"/>
@@ -29895,12 +29936,12 @@
       <c r="AG284" s="2" t="n"/>
       <c r="AH284" s="2" t="n"/>
     </row>
-    <row r="285" ht="24" customHeight="1" s="45">
+    <row r="285" ht="24" customHeight="1" s="48">
       <c r="A285" s="2" t="n">
         <v>284</v>
       </c>
       <c r="B285" s="2" t="n"/>
-      <c r="C285" s="27" t="n">
+      <c r="C285" s="46" t="n">
         <v>51068</v>
       </c>
       <c r="D285" s="2" t="n"/>
@@ -29997,12 +30038,12 @@
       </c>
       <c r="AH285" s="2" t="n"/>
     </row>
-    <row r="286" ht="24" customHeight="1" s="45">
+    <row r="286" ht="24" customHeight="1" s="48">
       <c r="A286" s="2" t="n">
         <v>285</v>
       </c>
       <c r="B286" s="2" t="n"/>
-      <c r="C286" s="27" t="n">
+      <c r="C286" s="46" t="n">
         <v>50429</v>
       </c>
       <c r="D286" s="2" t="n"/>
@@ -30099,12 +30140,12 @@
       </c>
       <c r="AH286" s="2" t="n"/>
     </row>
-    <row r="287" ht="24" customHeight="1" s="45">
+    <row r="287" ht="24" customHeight="1" s="48">
       <c r="A287" s="2" t="n">
         <v>286</v>
       </c>
       <c r="B287" s="2" t="n"/>
-      <c r="C287" s="27" t="n"/>
+      <c r="C287" s="46" t="n"/>
       <c r="D287" s="2" t="n"/>
       <c r="E287" s="4" t="n"/>
       <c r="F287" s="39" t="inlineStr">
@@ -30201,12 +30242,12 @@
       </c>
       <c r="AH287" s="2" t="n"/>
     </row>
-    <row r="288" ht="24" customHeight="1" s="45">
+    <row r="288" ht="24" customHeight="1" s="48">
       <c r="A288" s="2" t="n">
         <v>287</v>
       </c>
       <c r="B288" s="2" t="n"/>
-      <c r="C288" s="27" t="n"/>
+      <c r="C288" s="46" t="n"/>
       <c r="D288" s="2" t="n"/>
       <c r="E288" s="4" t="n"/>
       <c r="F288" s="39" t="inlineStr">
@@ -30303,12 +30344,12 @@
       </c>
       <c r="AH288" s="2" t="n"/>
     </row>
-    <row r="289" ht="24" customHeight="1" s="45">
+    <row r="289" ht="24" customHeight="1" s="48">
       <c r="A289" s="2" t="n">
         <v>288</v>
       </c>
       <c r="B289" s="2" t="n"/>
-      <c r="C289" s="27" t="n"/>
+      <c r="C289" s="46" t="n"/>
       <c r="D289" s="2" t="n"/>
       <c r="E289" s="4" t="n"/>
       <c r="F289" s="39" t="inlineStr">
@@ -30340,12 +30381,8 @@
         </is>
       </c>
       <c r="N289" s="2" t="n"/>
-      <c r="O289" s="32" t="n">
-        <v>-23</v>
-      </c>
-      <c r="P289" s="32" t="n">
-        <v>-13</v>
-      </c>
+      <c r="O289" s="32" t="n"/>
+      <c r="P289" s="32" t="n"/>
       <c r="Q289" s="32" t="n"/>
       <c r="R289" s="23" t="inlineStr">
         <is>
@@ -30405,82 +30442,200 @@
       <c r="AG289" s="2" t="n"/>
       <c r="AH289" s="2" t="n"/>
     </row>
-    <row r="290" ht="24" customHeight="1" s="45">
-      <c r="A290" s="2" t="n"/>
+    <row r="290" ht="24" customHeight="1" s="48">
+      <c r="A290" s="2" t="n">
+        <v>289</v>
+      </c>
       <c r="B290" s="2" t="n"/>
-      <c r="C290" s="27" t="n"/>
+      <c r="C290" s="46" t="n">
+        <v>50514</v>
+      </c>
       <c r="D290" s="2" t="n"/>
-      <c r="E290" s="4" t="n"/>
+      <c r="E290" s="4" t="n">
+        <v>99999</v>
+      </c>
       <c r="F290" s="39" t="n"/>
-      <c r="G290" s="29" t="n"/>
-      <c r="H290" s="29" t="n"/>
-      <c r="I290" s="2" t="n"/>
-      <c r="J290" s="27" t="n"/>
-      <c r="K290" s="4" t="n"/>
+      <c r="G290" s="29" t="n">
+        <v>49.5817</v>
+      </c>
+      <c r="H290" s="29" t="n">
+        <v>117.3269</v>
+      </c>
+      <c r="I290" s="2" t="n">
+        <v>660.4</v>
+      </c>
+      <c r="J290" s="27" t="n">
+        <v>12</v>
+      </c>
+      <c r="K290" s="31" t="inlineStr">
+        <is>
+          <t>🇨🇳</t>
+        </is>
+      </c>
       <c r="L290" s="2" t="n"/>
-      <c r="M290" s="14" t="n"/>
+      <c r="M290" s="14" t="inlineStr">
+        <is>
+          <t>满洲里</t>
+        </is>
+      </c>
       <c r="N290" s="2" t="n"/>
       <c r="O290" s="32" t="n"/>
       <c r="P290" s="32" t="n"/>
       <c r="Q290" s="32" t="n"/>
-      <c r="R290" s="23" t="n"/>
+      <c r="R290" s="23" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="S290" s="37" t="n"/>
-      <c r="T290" s="41" t="n"/>
-      <c r="U290" s="2" t="n"/>
-      <c r="V290" s="4" t="n"/>
-      <c r="W290" s="4" t="n"/>
-      <c r="X290" s="4" t="n"/>
+      <c r="T290" s="41" t="inlineStr">
+        <is>
+          <t>呼伦贝尔</t>
+        </is>
+      </c>
+      <c r="U290" s="2" t="inlineStr">
+        <is>
+          <t>内蒙古</t>
+        </is>
+      </c>
+      <c r="V290" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="W290" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="X290" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="Y290" s="4" t="n"/>
-      <c r="Z290" s="2" t="n"/>
-      <c r="AA290" s="2" t="n"/>
+      <c r="Z290" s="2" t="inlineStr">
+        <is>
+          <t>呼伦贝尔市</t>
+        </is>
+      </c>
+      <c r="AA290" s="2" t="inlineStr">
+        <is>
+          <t>满洲里市</t>
+        </is>
+      </c>
       <c r="AB290" s="2" t="n"/>
       <c r="AC290" s="2" t="n"/>
-      <c r="AD290" s="2" t="n"/>
-      <c r="AE290" s="4" t="n"/>
+      <c r="AD290" s="2" t="inlineStr">
+        <is>
+          <t>中国</t>
+        </is>
+      </c>
+      <c r="AE290" s="4" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
       <c r="AF290" s="4" t="n"/>
       <c r="AG290" s="2" t="n"/>
       <c r="AH290" s="2" t="n"/>
     </row>
-    <row r="291" ht="24" customHeight="1" s="45">
-      <c r="A291" s="2" t="n"/>
+    <row r="291" ht="24" customHeight="1" s="48">
+      <c r="A291" s="2" t="n">
+        <v>290</v>
+      </c>
       <c r="B291" s="2" t="n"/>
-      <c r="C291" s="27" t="n"/>
+      <c r="C291" s="46" t="inlineStr">
+        <is>
+          <t>04419</t>
+        </is>
+      </c>
       <c r="D291" s="2" t="n"/>
-      <c r="E291" s="4" t="n"/>
+      <c r="E291" s="4" t="n">
+        <v>99999</v>
+      </c>
       <c r="F291" s="39" t="n"/>
-      <c r="G291" s="29" t="n"/>
-      <c r="H291" s="29" t="n"/>
-      <c r="I291" s="2" t="n"/>
-      <c r="J291" s="27" t="n"/>
-      <c r="K291" s="4" t="n"/>
+      <c r="G291" s="29" t="n">
+        <v>72.572778</v>
+      </c>
+      <c r="H291" s="29" t="n">
+        <v>-38.470278</v>
+      </c>
+      <c r="I291" s="2" t="n">
+        <v>3204</v>
+      </c>
+      <c r="J291" s="27" t="n">
+        <v>12</v>
+      </c>
+      <c r="K291" s="31" t="inlineStr">
+        <is>
+          <t>🇩🇰</t>
+        </is>
+      </c>
       <c r="L291" s="2" t="n"/>
-      <c r="M291" s="14" t="n"/>
+      <c r="M291" s="14" t="inlineStr">
+        <is>
+          <t>顶峰营</t>
+        </is>
+      </c>
       <c r="N291" s="2" t="n"/>
       <c r="O291" s="32" t="n"/>
       <c r="P291" s="32" t="n"/>
       <c r="Q291" s="32" t="n"/>
-      <c r="R291" s="23" t="n"/>
+      <c r="R291" s="23" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="S291" s="37" t="n"/>
-      <c r="T291" s="41" t="n"/>
-      <c r="U291" s="2" t="n"/>
-      <c r="V291" s="4" t="n"/>
+      <c r="T291" s="41" t="inlineStr">
+        <is>
+          <t>格陵兰岛&lt;br&gt;美国顶峰营</t>
+        </is>
+      </c>
+      <c r="U291" s="2" t="inlineStr">
+        <is>
+          <t>格陵兰自治区</t>
+        </is>
+      </c>
+      <c r="V291" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="W291" s="4" t="n"/>
-      <c r="X291" s="4" t="n"/>
+      <c r="X291" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="Y291" s="4" t="n"/>
       <c r="Z291" s="2" t="n"/>
       <c r="AA291" s="2" t="n"/>
       <c r="AB291" s="2" t="n"/>
       <c r="AC291" s="2" t="n"/>
-      <c r="AD291" s="2" t="n"/>
-      <c r="AE291" s="4" t="n"/>
+      <c r="AD291" s="2" t="inlineStr">
+        <is>
+          <t>丹麦</t>
+        </is>
+      </c>
+      <c r="AE291" s="4" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
       <c r="AF291" s="4" t="n"/>
-      <c r="AG291" s="2" t="n"/>
+      <c r="AG291" s="2" t="inlineStr">
+        <is>
+          <t>格陵兰岛</t>
+        </is>
+      </c>
       <c r="AH291" s="2" t="n"/>
     </row>
-    <row r="292" ht="24" customHeight="1" s="45">
+    <row r="292" ht="24" customHeight="1" s="48">
       <c r="A292" s="2" t="n"/>
       <c r="B292" s="2" t="n"/>
-      <c r="C292" s="27" t="n"/>
+      <c r="C292" s="46" t="n"/>
       <c r="D292" s="2" t="n"/>
       <c r="E292" s="4" t="n"/>
       <c r="F292" s="39" t="n"/>
@@ -30513,10 +30668,10 @@
       <c r="AG292" s="2" t="n"/>
       <c r="AH292" s="2" t="n"/>
     </row>
-    <row r="293" ht="24" customHeight="1" s="45">
+    <row r="293" ht="24" customHeight="1" s="48">
       <c r="A293" s="2" t="n"/>
       <c r="B293" s="2" t="n"/>
-      <c r="C293" s="27" t="n"/>
+      <c r="C293" s="46" t="n"/>
       <c r="D293" s="2" t="n"/>
       <c r="E293" s="4" t="n"/>
       <c r="F293" s="39" t="n"/>
@@ -30549,10 +30704,10 @@
       <c r="AG293" s="2" t="n"/>
       <c r="AH293" s="2" t="n"/>
     </row>
-    <row r="294" ht="24" customHeight="1" s="45">
+    <row r="294" ht="24" customHeight="1" s="48">
       <c r="A294" s="2" t="n"/>
       <c r="B294" s="2" t="n"/>
-      <c r="C294" s="27" t="n"/>
+      <c r="C294" s="46" t="n"/>
       <c r="D294" s="2" t="n"/>
       <c r="E294" s="4" t="n"/>
       <c r="F294" s="39" t="n"/>
@@ -30585,10 +30740,10 @@
       <c r="AG294" s="2" t="n"/>
       <c r="AH294" s="2" t="n"/>
     </row>
-    <row r="295" ht="24" customHeight="1" s="45">
+    <row r="295" ht="24" customHeight="1" s="48">
       <c r="A295" s="2" t="n"/>
       <c r="B295" s="2" t="n"/>
-      <c r="C295" s="27" t="n"/>
+      <c r="C295" s="46" t="n"/>
       <c r="D295" s="2" t="n"/>
       <c r="E295" s="4" t="n"/>
       <c r="F295" s="39" t="n"/>
@@ -30621,10 +30776,10 @@
       <c r="AG295" s="2" t="n"/>
       <c r="AH295" s="2" t="n"/>
     </row>
-    <row r="296" ht="24" customHeight="1" s="45">
+    <row r="296" ht="24" customHeight="1" s="48">
       <c r="A296" s="2" t="n"/>
       <c r="B296" s="2" t="n"/>
-      <c r="C296" s="27" t="n"/>
+      <c r="C296" s="46" t="n"/>
       <c r="D296" s="2" t="n"/>
       <c r="E296" s="4" t="n"/>
       <c r="F296" s="39" t="n"/>
@@ -30657,10 +30812,10 @@
       <c r="AG296" s="2" t="n"/>
       <c r="AH296" s="2" t="n"/>
     </row>
-    <row r="297" ht="24" customHeight="1" s="45">
+    <row r="297" ht="24" customHeight="1" s="48">
       <c r="A297" s="2" t="n"/>
       <c r="B297" s="2" t="n"/>
-      <c r="C297" s="27" t="n"/>
+      <c r="C297" s="46" t="n"/>
       <c r="D297" s="2" t="n"/>
       <c r="E297" s="4" t="n"/>
       <c r="F297" s="39" t="n"/>
@@ -30693,10 +30848,10 @@
       <c r="AG297" s="2" t="n"/>
       <c r="AH297" s="2" t="n"/>
     </row>
-    <row r="298" ht="24" customHeight="1" s="45">
+    <row r="298" ht="24" customHeight="1" s="48">
       <c r="A298" s="2" t="n"/>
       <c r="B298" s="2" t="n"/>
-      <c r="C298" s="27" t="n"/>
+      <c r="C298" s="46" t="n"/>
       <c r="D298" s="2" t="n"/>
       <c r="E298" s="4" t="n"/>
       <c r="F298" s="39" t="n"/>
@@ -30729,10 +30884,10 @@
       <c r="AG298" s="2" t="n"/>
       <c r="AH298" s="2" t="n"/>
     </row>
-    <row r="299" ht="24" customHeight="1" s="45">
+    <row r="299" ht="24" customHeight="1" s="48">
       <c r="A299" s="2" t="n"/>
       <c r="B299" s="2" t="n"/>
-      <c r="C299" s="27" t="n"/>
+      <c r="C299" s="46" t="n"/>
       <c r="D299" s="2" t="n"/>
       <c r="E299" s="4" t="n"/>
       <c r="F299" s="39" t="n"/>
@@ -30765,10 +30920,10 @@
       <c r="AG299" s="2" t="n"/>
       <c r="AH299" s="2" t="n"/>
     </row>
-    <row r="300" ht="24" customHeight="1" s="45">
+    <row r="300" ht="24" customHeight="1" s="48">
       <c r="A300" s="2" t="n"/>
       <c r="B300" s="2" t="n"/>
-      <c r="C300" s="27" t="n"/>
+      <c r="C300" s="46" t="n"/>
       <c r="D300" s="2" t="n"/>
       <c r="E300" s="4" t="n"/>
       <c r="F300" s="39" t="n"/>
@@ -30801,10 +30956,10 @@
       <c r="AG300" s="2" t="n"/>
       <c r="AH300" s="2" t="n"/>
     </row>
-    <row r="301" ht="24" customHeight="1" s="45">
+    <row r="301" ht="24" customHeight="1" s="48">
       <c r="A301" s="2" t="n"/>
       <c r="B301" s="2" t="n"/>
-      <c r="C301" s="27" t="n"/>
+      <c r="C301" s="46" t="n"/>
       <c r="D301" s="2" t="n"/>
       <c r="E301" s="4" t="n"/>
       <c r="F301" s="39" t="n"/>
@@ -30837,10 +30992,10 @@
       <c r="AG301" s="2" t="n"/>
       <c r="AH301" s="2" t="n"/>
     </row>
-    <row r="302" ht="24" customHeight="1" s="45">
+    <row r="302" ht="24" customHeight="1" s="48">
       <c r="A302" s="2" t="n"/>
       <c r="B302" s="2" t="n"/>
-      <c r="C302" s="27" t="n"/>
+      <c r="C302" s="46" t="n"/>
       <c r="D302" s="2" t="n"/>
       <c r="E302" s="4" t="n"/>
       <c r="F302" s="39" t="n"/>
@@ -30873,10 +31028,10 @@
       <c r="AG302" s="2" t="n"/>
       <c r="AH302" s="2" t="n"/>
     </row>
-    <row r="303" ht="24" customHeight="1" s="45">
+    <row r="303" ht="24" customHeight="1" s="48">
       <c r="A303" s="2" t="n"/>
       <c r="B303" s="2" t="n"/>
-      <c r="C303" s="27" t="n"/>
+      <c r="C303" s="46" t="n"/>
       <c r="D303" s="2" t="n"/>
       <c r="E303" s="4" t="n"/>
       <c r="F303" s="39" t="n"/>
@@ -30909,10 +31064,10 @@
       <c r="AG303" s="2" t="n"/>
       <c r="AH303" s="2" t="n"/>
     </row>
-    <row r="304" ht="24" customHeight="1" s="45">
+    <row r="304" ht="24" customHeight="1" s="48">
       <c r="A304" s="2" t="n"/>
       <c r="B304" s="2" t="n"/>
-      <c r="C304" s="27" t="n"/>
+      <c r="C304" s="46" t="n"/>
       <c r="D304" s="2" t="n"/>
       <c r="E304" s="4" t="n"/>
       <c r="F304" s="39" t="n"/>
@@ -30945,10 +31100,10 @@
       <c r="AG304" s="2" t="n"/>
       <c r="AH304" s="2" t="n"/>
     </row>
-    <row r="305" ht="24" customHeight="1" s="45">
+    <row r="305" ht="24" customHeight="1" s="48">
       <c r="A305" s="2" t="n"/>
       <c r="B305" s="2" t="n"/>
-      <c r="C305" s="27" t="n"/>
+      <c r="C305" s="46" t="n"/>
       <c r="D305" s="2" t="n"/>
       <c r="E305" s="4" t="n"/>
       <c r="F305" s="39" t="n"/>
@@ -30981,10 +31136,10 @@
       <c r="AG305" s="2" t="n"/>
       <c r="AH305" s="2" t="n"/>
     </row>
-    <row r="306" ht="24" customHeight="1" s="45">
+    <row r="306" ht="24" customHeight="1" s="48">
       <c r="A306" s="2" t="n"/>
       <c r="B306" s="2" t="n"/>
-      <c r="C306" s="27" t="n"/>
+      <c r="C306" s="46" t="n"/>
       <c r="D306" s="2" t="n"/>
       <c r="E306" s="4" t="n"/>
       <c r="F306" s="39" t="n"/>
@@ -31017,10 +31172,10 @@
       <c r="AG306" s="2" t="n"/>
       <c r="AH306" s="2" t="n"/>
     </row>
-    <row r="307" ht="24" customHeight="1" s="45">
+    <row r="307" ht="24" customHeight="1" s="48">
       <c r="A307" s="2" t="n"/>
       <c r="B307" s="2" t="n"/>
-      <c r="C307" s="27" t="n"/>
+      <c r="C307" s="46" t="n"/>
       <c r="D307" s="2" t="n"/>
       <c r="E307" s="4" t="n"/>
       <c r="F307" s="39" t="n"/>
@@ -31053,10 +31208,10 @@
       <c r="AG307" s="2" t="n"/>
       <c r="AH307" s="2" t="n"/>
     </row>
-    <row r="308" ht="24" customHeight="1" s="45">
+    <row r="308" ht="24" customHeight="1" s="48">
       <c r="A308" s="2" t="n"/>
       <c r="B308" s="2" t="n"/>
-      <c r="C308" s="27" t="n"/>
+      <c r="C308" s="46" t="n"/>
       <c r="D308" s="2" t="n"/>
       <c r="E308" s="4" t="n"/>
       <c r="F308" s="39" t="n"/>
@@ -31089,10 +31244,10 @@
       <c r="AG308" s="2" t="n"/>
       <c r="AH308" s="2" t="n"/>
     </row>
-    <row r="309" ht="24" customHeight="1" s="45">
+    <row r="309" ht="24" customHeight="1" s="48">
       <c r="A309" s="2" t="n"/>
       <c r="B309" s="2" t="n"/>
-      <c r="C309" s="27" t="n"/>
+      <c r="C309" s="46" t="n"/>
       <c r="D309" s="2" t="n"/>
       <c r="E309" s="4" t="n"/>
       <c r="F309" s="39" t="n"/>
@@ -31125,10 +31280,10 @@
       <c r="AG309" s="2" t="n"/>
       <c r="AH309" s="2" t="n"/>
     </row>
-    <row r="310" ht="24" customHeight="1" s="45">
+    <row r="310" ht="24" customHeight="1" s="48">
       <c r="A310" s="2" t="n"/>
       <c r="B310" s="2" t="n"/>
-      <c r="C310" s="27" t="n"/>
+      <c r="C310" s="46" t="n"/>
       <c r="D310" s="2" t="n"/>
       <c r="E310" s="4" t="n"/>
       <c r="F310" s="39" t="n"/>
@@ -31161,10 +31316,10 @@
       <c r="AG310" s="2" t="n"/>
       <c r="AH310" s="2" t="n"/>
     </row>
-    <row r="311" ht="24" customHeight="1" s="45">
+    <row r="311" ht="24" customHeight="1" s="48">
       <c r="A311" s="2" t="n"/>
       <c r="B311" s="2" t="n"/>
-      <c r="C311" s="27" t="n"/>
+      <c r="C311" s="46" t="n"/>
       <c r="D311" s="2" t="n"/>
       <c r="E311" s="4" t="n"/>
       <c r="F311" s="39" t="n"/>
@@ -31197,10 +31352,10 @@
       <c r="AG311" s="2" t="n"/>
       <c r="AH311" s="2" t="n"/>
     </row>
-    <row r="312" ht="24" customHeight="1" s="45">
+    <row r="312" ht="24" customHeight="1" s="48">
       <c r="A312" s="2" t="n"/>
       <c r="B312" s="2" t="n"/>
-      <c r="C312" s="27" t="n"/>
+      <c r="C312" s="46" t="n"/>
       <c r="D312" s="2" t="n"/>
       <c r="E312" s="4" t="n"/>
       <c r="F312" s="39" t="n"/>
@@ -31233,10 +31388,10 @@
       <c r="AG312" s="2" t="n"/>
       <c r="AH312" s="2" t="n"/>
     </row>
-    <row r="313" ht="24" customHeight="1" s="45">
+    <row r="313" ht="24" customHeight="1" s="48">
       <c r="A313" s="2" t="n"/>
       <c r="B313" s="2" t="n"/>
-      <c r="C313" s="27" t="n"/>
+      <c r="C313" s="46" t="n"/>
       <c r="D313" s="2" t="n"/>
       <c r="E313" s="4" t="n"/>
       <c r="F313" s="39" t="n"/>
@@ -31269,10 +31424,10 @@
       <c r="AG313" s="2" t="n"/>
       <c r="AH313" s="2" t="n"/>
     </row>
-    <row r="314" ht="24" customHeight="1" s="45">
+    <row r="314" ht="24" customHeight="1" s="48">
       <c r="A314" s="2" t="n"/>
       <c r="B314" s="2" t="n"/>
-      <c r="C314" s="27" t="n"/>
+      <c r="C314" s="46" t="n"/>
       <c r="D314" s="2" t="n"/>
       <c r="E314" s="4" t="n"/>
       <c r="F314" s="39" t="n"/>
@@ -31305,10 +31460,10 @@
       <c r="AG314" s="2" t="n"/>
       <c r="AH314" s="2" t="n"/>
     </row>
-    <row r="315" ht="24" customHeight="1" s="45">
+    <row r="315" ht="24" customHeight="1" s="48">
       <c r="A315" s="2" t="n"/>
       <c r="B315" s="2" t="n"/>
-      <c r="C315" s="27" t="n"/>
+      <c r="C315" s="46" t="n"/>
       <c r="D315" s="2" t="n"/>
       <c r="E315" s="4" t="n"/>
       <c r="F315" s="39" t="n"/>
@@ -31341,10 +31496,10 @@
       <c r="AG315" s="2" t="n"/>
       <c r="AH315" s="2" t="n"/>
     </row>
-    <row r="316" ht="24" customHeight="1" s="45">
+    <row r="316" ht="24" customHeight="1" s="48">
       <c r="A316" s="2" t="n"/>
       <c r="B316" s="2" t="n"/>
-      <c r="C316" s="27" t="n"/>
+      <c r="C316" s="46" t="n"/>
       <c r="D316" s="2" t="n"/>
       <c r="E316" s="4" t="n"/>
       <c r="F316" s="39" t="n"/>
@@ -31377,10 +31532,10 @@
       <c r="AG316" s="2" t="n"/>
       <c r="AH316" s="2" t="n"/>
     </row>
-    <row r="317" ht="24" customHeight="1" s="45">
+    <row r="317" ht="24" customHeight="1" s="48">
       <c r="A317" s="2" t="n"/>
       <c r="B317" s="2" t="n"/>
-      <c r="C317" s="27" t="n"/>
+      <c r="C317" s="46" t="n"/>
       <c r="D317" s="2" t="n"/>
       <c r="E317" s="4" t="n"/>
       <c r="F317" s="39" t="n"/>
@@ -31413,10 +31568,10 @@
       <c r="AG317" s="2" t="n"/>
       <c r="AH317" s="2" t="n"/>
     </row>
-    <row r="318" ht="24" customHeight="1" s="45">
+    <row r="318" ht="24" customHeight="1" s="48">
       <c r="A318" s="2" t="n"/>
       <c r="B318" s="2" t="n"/>
-      <c r="C318" s="27" t="n"/>
+      <c r="C318" s="46" t="n"/>
       <c r="D318" s="2" t="n"/>
       <c r="E318" s="4" t="n"/>
       <c r="F318" s="39" t="n"/>
@@ -31449,10 +31604,10 @@
       <c r="AG318" s="2" t="n"/>
       <c r="AH318" s="2" t="n"/>
     </row>
-    <row r="319" ht="24" customHeight="1" s="45">
+    <row r="319" ht="24" customHeight="1" s="48">
       <c r="A319" s="2" t="n"/>
       <c r="B319" s="2" t="n"/>
-      <c r="C319" s="27" t="n"/>
+      <c r="C319" s="46" t="n"/>
       <c r="D319" s="2" t="n"/>
       <c r="E319" s="4" t="n"/>
       <c r="F319" s="39" t="n"/>
@@ -31485,10 +31640,10 @@
       <c r="AG319" s="2" t="n"/>
       <c r="AH319" s="2" t="n"/>
     </row>
-    <row r="320" ht="24" customHeight="1" s="45">
+    <row r="320" ht="24" customHeight="1" s="48">
       <c r="A320" s="2" t="n"/>
       <c r="B320" s="2" t="n"/>
-      <c r="C320" s="27" t="n"/>
+      <c r="C320" s="46" t="n"/>
       <c r="D320" s="2" t="n"/>
       <c r="E320" s="4" t="n"/>
       <c r="F320" s="39" t="n"/>
@@ -31521,10 +31676,10 @@
       <c r="AG320" s="2" t="n"/>
       <c r="AH320" s="2" t="n"/>
     </row>
-    <row r="321" ht="24" customHeight="1" s="45">
+    <row r="321" ht="24" customHeight="1" s="48">
       <c r="A321" s="2" t="n"/>
       <c r="B321" s="2" t="n"/>
-      <c r="C321" s="27" t="n"/>
+      <c r="C321" s="46" t="n"/>
       <c r="D321" s="2" t="n"/>
       <c r="E321" s="4" t="n"/>
       <c r="F321" s="39" t="n"/>
@@ -31557,10 +31712,10 @@
       <c r="AG321" s="2" t="n"/>
       <c r="AH321" s="2" t="n"/>
     </row>
-    <row r="322" ht="24" customHeight="1" s="45">
+    <row r="322" ht="24" customHeight="1" s="48">
       <c r="A322" s="2" t="n"/>
       <c r="B322" s="2" t="n"/>
-      <c r="C322" s="27" t="n"/>
+      <c r="C322" s="46" t="n"/>
       <c r="D322" s="2" t="n"/>
       <c r="E322" s="4" t="n"/>
       <c r="F322" s="39" t="n"/>
@@ -31593,10 +31748,10 @@
       <c r="AG322" s="2" t="n"/>
       <c r="AH322" s="2" t="n"/>
     </row>
-    <row r="323" ht="24" customHeight="1" s="45">
+    <row r="323" ht="24" customHeight="1" s="48">
       <c r="A323" s="2" t="n"/>
       <c r="B323" s="2" t="n"/>
-      <c r="C323" s="27" t="n"/>
+      <c r="C323" s="46" t="n"/>
       <c r="D323" s="2" t="n"/>
       <c r="E323" s="4" t="n"/>
       <c r="F323" s="39" t="n"/>
@@ -31629,10 +31784,10 @@
       <c r="AG323" s="2" t="n"/>
       <c r="AH323" s="2" t="n"/>
     </row>
-    <row r="324" ht="24" customHeight="1" s="45">
+    <row r="324" ht="24" customHeight="1" s="48">
       <c r="A324" s="2" t="n"/>
       <c r="B324" s="2" t="n"/>
-      <c r="C324" s="27" t="n"/>
+      <c r="C324" s="46" t="n"/>
       <c r="D324" s="2" t="n"/>
       <c r="E324" s="4" t="n"/>
       <c r="F324" s="39" t="n"/>
@@ -31665,10 +31820,10 @@
       <c r="AG324" s="2" t="n"/>
       <c r="AH324" s="2" t="n"/>
     </row>
-    <row r="325" ht="24" customHeight="1" s="45">
+    <row r="325" ht="24" customHeight="1" s="48">
       <c r="A325" s="2" t="n"/>
       <c r="B325" s="2" t="n"/>
-      <c r="C325" s="27" t="n"/>
+      <c r="C325" s="46" t="n"/>
       <c r="D325" s="2" t="n"/>
       <c r="E325" s="4" t="n"/>
       <c r="F325" s="39" t="n"/>
@@ -31701,10 +31856,10 @@
       <c r="AG325" s="2" t="n"/>
       <c r="AH325" s="2" t="n"/>
     </row>
-    <row r="326" ht="24" customHeight="1" s="45">
+    <row r="326" ht="24" customHeight="1" s="48">
       <c r="A326" s="2" t="n"/>
       <c r="B326" s="2" t="n"/>
-      <c r="C326" s="27" t="n"/>
+      <c r="C326" s="46" t="n"/>
       <c r="D326" s="2" t="n"/>
       <c r="E326" s="4" t="n"/>
       <c r="F326" s="39" t="n"/>
@@ -31737,10 +31892,10 @@
       <c r="AG326" s="2" t="n"/>
       <c r="AH326" s="2" t="n"/>
     </row>
-    <row r="327" ht="24" customHeight="1" s="45">
+    <row r="327" ht="24" customHeight="1" s="48">
       <c r="A327" s="2" t="n"/>
       <c r="B327" s="2" t="n"/>
-      <c r="C327" s="27" t="n"/>
+      <c r="C327" s="46" t="n"/>
       <c r="D327" s="2" t="n"/>
       <c r="E327" s="4" t="n"/>
       <c r="F327" s="39" t="n"/>
@@ -31773,10 +31928,10 @@
       <c r="AG327" s="2" t="n"/>
       <c r="AH327" s="2" t="n"/>
     </row>
-    <row r="328" ht="24" customHeight="1" s="45">
+    <row r="328" ht="24" customHeight="1" s="48">
       <c r="A328" s="2" t="n"/>
       <c r="B328" s="2" t="n"/>
-      <c r="C328" s="27" t="n"/>
+      <c r="C328" s="46" t="n"/>
       <c r="D328" s="2" t="n"/>
       <c r="E328" s="4" t="n"/>
       <c r="F328" s="39" t="n"/>
@@ -31809,10 +31964,10 @@
       <c r="AG328" s="2" t="n"/>
       <c r="AH328" s="2" t="n"/>
     </row>
-    <row r="329" ht="24" customHeight="1" s="45">
+    <row r="329" ht="24" customHeight="1" s="48">
       <c r="A329" s="2" t="n"/>
       <c r="B329" s="2" t="n"/>
-      <c r="C329" s="27" t="n"/>
+      <c r="C329" s="46" t="n"/>
       <c r="D329" s="2" t="n"/>
       <c r="E329" s="4" t="n"/>
       <c r="F329" s="39" t="n"/>
@@ -31845,10 +32000,10 @@
       <c r="AG329" s="2" t="n"/>
       <c r="AH329" s="2" t="n"/>
     </row>
-    <row r="330" ht="24" customHeight="1" s="45">
+    <row r="330" ht="24" customHeight="1" s="48">
       <c r="A330" s="2" t="n"/>
       <c r="B330" s="2" t="n"/>
-      <c r="C330" s="27" t="n"/>
+      <c r="C330" s="46" t="n"/>
       <c r="D330" s="2" t="n"/>
       <c r="E330" s="4" t="n"/>
       <c r="F330" s="39" t="n"/>
@@ -31881,10 +32036,10 @@
       <c r="AG330" s="2" t="n"/>
       <c r="AH330" s="2" t="n"/>
     </row>
-    <row r="331" ht="24" customHeight="1" s="45">
+    <row r="331" ht="24" customHeight="1" s="48">
       <c r="A331" s="2" t="n"/>
       <c r="B331" s="2" t="n"/>
-      <c r="C331" s="27" t="n"/>
+      <c r="C331" s="46" t="n"/>
       <c r="D331" s="2" t="n"/>
       <c r="E331" s="4" t="n"/>
       <c r="F331" s="39" t="n"/>
@@ -31917,10 +32072,10 @@
       <c r="AG331" s="2" t="n"/>
       <c r="AH331" s="2" t="n"/>
     </row>
-    <row r="332" ht="24" customHeight="1" s="45">
+    <row r="332" ht="24" customHeight="1" s="48">
       <c r="A332" s="2" t="n"/>
       <c r="B332" s="2" t="n"/>
-      <c r="C332" s="27" t="n"/>
+      <c r="C332" s="46" t="n"/>
       <c r="D332" s="2" t="n"/>
       <c r="E332" s="4" t="n"/>
       <c r="F332" s="39" t="n"/>
@@ -31953,10 +32108,10 @@
       <c r="AG332" s="2" t="n"/>
       <c r="AH332" s="2" t="n"/>
     </row>
-    <row r="333" ht="24" customHeight="1" s="45">
+    <row r="333" ht="24" customHeight="1" s="48">
       <c r="A333" s="2" t="n"/>
       <c r="B333" s="2" t="n"/>
-      <c r="C333" s="27" t="n"/>
+      <c r="C333" s="46" t="n"/>
       <c r="D333" s="2" t="n"/>
       <c r="E333" s="4" t="n"/>
       <c r="F333" s="39" t="n"/>
@@ -31989,10 +32144,10 @@
       <c r="AG333" s="2" t="n"/>
       <c r="AH333" s="2" t="n"/>
     </row>
-    <row r="334" ht="24" customHeight="1" s="45">
+    <row r="334" ht="24" customHeight="1" s="48">
       <c r="A334" s="2" t="n"/>
       <c r="B334" s="2" t="n"/>
-      <c r="C334" s="27" t="n"/>
+      <c r="C334" s="46" t="n"/>
       <c r="D334" s="2" t="n"/>
       <c r="E334" s="4" t="n"/>
       <c r="F334" s="39" t="n"/>
@@ -32025,10 +32180,10 @@
       <c r="AG334" s="2" t="n"/>
       <c r="AH334" s="2" t="n"/>
     </row>
-    <row r="335" ht="24" customHeight="1" s="45">
+    <row r="335" ht="24" customHeight="1" s="48">
       <c r="A335" s="2" t="n"/>
       <c r="B335" s="2" t="n"/>
-      <c r="C335" s="27" t="n"/>
+      <c r="C335" s="46" t="n"/>
       <c r="D335" s="2" t="n"/>
       <c r="E335" s="4" t="n"/>
       <c r="F335" s="39" t="n"/>
@@ -32061,10 +32216,10 @@
       <c r="AG335" s="2" t="n"/>
       <c r="AH335" s="2" t="n"/>
     </row>
-    <row r="336" ht="24" customHeight="1" s="45">
+    <row r="336" ht="24" customHeight="1" s="48">
       <c r="A336" s="2" t="n"/>
       <c r="B336" s="2" t="n"/>
-      <c r="C336" s="27" t="n"/>
+      <c r="C336" s="46" t="n"/>
       <c r="D336" s="2" t="n"/>
       <c r="E336" s="4" t="n"/>
       <c r="F336" s="39" t="n"/>
@@ -32097,10 +32252,10 @@
       <c r="AG336" s="2" t="n"/>
       <c r="AH336" s="2" t="n"/>
     </row>
-    <row r="337" ht="24" customHeight="1" s="45">
+    <row r="337" ht="24" customHeight="1" s="48">
       <c r="A337" s="2" t="n"/>
       <c r="B337" s="2" t="n"/>
-      <c r="C337" s="27" t="n"/>
+      <c r="C337" s="46" t="n"/>
       <c r="D337" s="2" t="n"/>
       <c r="E337" s="4" t="n"/>
       <c r="F337" s="39" t="n"/>
@@ -32133,10 +32288,10 @@
       <c r="AG337" s="2" t="n"/>
       <c r="AH337" s="2" t="n"/>
     </row>
-    <row r="338" ht="24" customHeight="1" s="45">
+    <row r="338" ht="24" customHeight="1" s="48">
       <c r="A338" s="2" t="n"/>
       <c r="B338" s="2" t="n"/>
-      <c r="C338" s="27" t="n"/>
+      <c r="C338" s="46" t="n"/>
       <c r="D338" s="2" t="n"/>
       <c r="E338" s="4" t="n"/>
       <c r="F338" s="39" t="n"/>
@@ -32169,10 +32324,10 @@
       <c r="AG338" s="2" t="n"/>
       <c r="AH338" s="2" t="n"/>
     </row>
-    <row r="339" ht="24" customHeight="1" s="45">
+    <row r="339" ht="24" customHeight="1" s="48">
       <c r="A339" s="2" t="n"/>
       <c r="B339" s="2" t="n"/>
-      <c r="C339" s="27" t="n"/>
+      <c r="C339" s="46" t="n"/>
       <c r="D339" s="2" t="n"/>
       <c r="E339" s="4" t="n"/>
       <c r="F339" s="39" t="n"/>
@@ -32205,10 +32360,10 @@
       <c r="AG339" s="2" t="n"/>
       <c r="AH339" s="2" t="n"/>
     </row>
-    <row r="340" ht="24" customHeight="1" s="45">
+    <row r="340" ht="24" customHeight="1" s="48">
       <c r="A340" s="2" t="n"/>
       <c r="B340" s="2" t="n"/>
-      <c r="C340" s="27" t="n"/>
+      <c r="C340" s="46" t="n"/>
       <c r="D340" s="2" t="n"/>
       <c r="E340" s="4" t="n"/>
       <c r="F340" s="39" t="n"/>
@@ -32241,10 +32396,10 @@
       <c r="AG340" s="2" t="n"/>
       <c r="AH340" s="2" t="n"/>
     </row>
-    <row r="341" ht="24" customHeight="1" s="45">
+    <row r="341" ht="24" customHeight="1" s="48">
       <c r="A341" s="2" t="n"/>
       <c r="B341" s="2" t="n"/>
-      <c r="C341" s="27" t="n"/>
+      <c r="C341" s="46" t="n"/>
       <c r="D341" s="2" t="n"/>
       <c r="E341" s="4" t="n"/>
       <c r="F341" s="39" t="n"/>
@@ -32277,10 +32432,10 @@
       <c r="AG341" s="2" t="n"/>
       <c r="AH341" s="2" t="n"/>
     </row>
-    <row r="342" ht="24" customHeight="1" s="45">
+    <row r="342" ht="24" customHeight="1" s="48">
       <c r="A342" s="2" t="n"/>
       <c r="B342" s="2" t="n"/>
-      <c r="C342" s="27" t="n"/>
+      <c r="C342" s="46" t="n"/>
       <c r="D342" s="2" t="n"/>
       <c r="E342" s="4" t="n"/>
       <c r="F342" s="39" t="n"/>
@@ -32313,10 +32468,10 @@
       <c r="AG342" s="2" t="n"/>
       <c r="AH342" s="2" t="n"/>
     </row>
-    <row r="343" ht="24" customHeight="1" s="45">
+    <row r="343" ht="24" customHeight="1" s="48">
       <c r="A343" s="2" t="n"/>
       <c r="B343" s="2" t="n"/>
-      <c r="C343" s="27" t="n"/>
+      <c r="C343" s="46" t="n"/>
       <c r="D343" s="2" t="n"/>
       <c r="E343" s="4" t="n"/>
       <c r="F343" s="39" t="n"/>
@@ -32349,10 +32504,10 @@
       <c r="AG343" s="2" t="n"/>
       <c r="AH343" s="2" t="n"/>
     </row>
-    <row r="344" ht="24" customHeight="1" s="45">
+    <row r="344" ht="24" customHeight="1" s="48">
       <c r="A344" s="2" t="n"/>
       <c r="B344" s="2" t="n"/>
-      <c r="C344" s="27" t="n"/>
+      <c r="C344" s="46" t="n"/>
       <c r="D344" s="2" t="n"/>
       <c r="E344" s="4" t="n"/>
       <c r="F344" s="39" t="n"/>
@@ -32385,10 +32540,10 @@
       <c r="AG344" s="2" t="n"/>
       <c r="AH344" s="2" t="n"/>
     </row>
-    <row r="345" ht="24" customHeight="1" s="45">
+    <row r="345" ht="24" customHeight="1" s="48">
       <c r="A345" s="2" t="n"/>
       <c r="B345" s="2" t="n"/>
-      <c r="C345" s="27" t="n"/>
+      <c r="C345" s="46" t="n"/>
       <c r="D345" s="2" t="n"/>
       <c r="E345" s="4" t="n"/>
       <c r="F345" s="39" t="n"/>
@@ -32421,10 +32576,10 @@
       <c r="AG345" s="2" t="n"/>
       <c r="AH345" s="2" t="n"/>
     </row>
-    <row r="346" ht="24" customHeight="1" s="45">
+    <row r="346" ht="24" customHeight="1" s="48">
       <c r="A346" s="2" t="n"/>
       <c r="B346" s="2" t="n"/>
-      <c r="C346" s="27" t="n"/>
+      <c r="C346" s="46" t="n"/>
       <c r="D346" s="2" t="n"/>
       <c r="E346" s="4" t="n"/>
       <c r="F346" s="39" t="n"/>
@@ -32457,10 +32612,10 @@
       <c r="AG346" s="2" t="n"/>
       <c r="AH346" s="2" t="n"/>
     </row>
-    <row r="347" ht="24" customHeight="1" s="45">
+    <row r="347" ht="24" customHeight="1" s="48">
       <c r="A347" s="2" t="n"/>
       <c r="B347" s="2" t="n"/>
-      <c r="C347" s="27" t="n"/>
+      <c r="C347" s="46" t="n"/>
       <c r="D347" s="2" t="n"/>
       <c r="E347" s="4" t="n"/>
       <c r="F347" s="39" t="n"/>
@@ -32493,10 +32648,10 @@
       <c r="AG347" s="2" t="n"/>
       <c r="AH347" s="2" t="n"/>
     </row>
-    <row r="348" ht="24" customHeight="1" s="45">
+    <row r="348" ht="24" customHeight="1" s="48">
       <c r="A348" s="2" t="n"/>
       <c r="B348" s="2" t="n"/>
-      <c r="C348" s="27" t="n"/>
+      <c r="C348" s="46" t="n"/>
       <c r="D348" s="2" t="n"/>
       <c r="E348" s="4" t="n"/>
       <c r="F348" s="39" t="n"/>
@@ -32529,10 +32684,10 @@
       <c r="AG348" s="2" t="n"/>
       <c r="AH348" s="2" t="n"/>
     </row>
-    <row r="349" ht="24" customHeight="1" s="45">
+    <row r="349" ht="24" customHeight="1" s="48">
       <c r="A349" s="2" t="n"/>
       <c r="B349" s="2" t="n"/>
-      <c r="C349" s="27" t="n"/>
+      <c r="C349" s="46" t="n"/>
       <c r="D349" s="2" t="n"/>
       <c r="E349" s="4" t="n"/>
       <c r="F349" s="39" t="n"/>
@@ -32565,10 +32720,10 @@
       <c r="AG349" s="2" t="n"/>
       <c r="AH349" s="2" t="n"/>
     </row>
-    <row r="350" ht="24" customHeight="1" s="45">
+    <row r="350" ht="24" customHeight="1" s="48">
       <c r="A350" s="2" t="n"/>
       <c r="B350" s="2" t="n"/>
-      <c r="C350" s="27" t="n"/>
+      <c r="C350" s="46" t="n"/>
       <c r="D350" s="2" t="n"/>
       <c r="E350" s="4" t="n"/>
       <c r="F350" s="39" t="n"/>
@@ -32601,10 +32756,10 @@
       <c r="AG350" s="2" t="n"/>
       <c r="AH350" s="2" t="n"/>
     </row>
-    <row r="351" ht="24" customHeight="1" s="45">
+    <row r="351" ht="24" customHeight="1" s="48">
       <c r="A351" s="14" t="n"/>
       <c r="B351" s="2" t="n"/>
-      <c r="C351" s="27" t="n"/>
+      <c r="C351" s="46" t="n"/>
       <c r="D351" s="2" t="n"/>
       <c r="E351" s="4" t="n"/>
       <c r="F351" s="39" t="n"/>
@@ -32637,10 +32792,10 @@
       <c r="AG351" s="2" t="n"/>
       <c r="AH351" s="2" t="n"/>
     </row>
-    <row r="352" ht="24" customHeight="1" s="45">
+    <row r="352" ht="24" customHeight="1" s="48">
       <c r="A352" s="13" t="n"/>
       <c r="B352" s="2" t="n"/>
-      <c r="C352" s="27" t="n"/>
+      <c r="C352" s="46" t="n"/>
       <c r="D352" s="2" t="n"/>
       <c r="E352" s="4" t="n"/>
       <c r="F352" s="39" t="n"/>
@@ -32673,10 +32828,10 @@
       <c r="AG352" s="2" t="n"/>
       <c r="AH352" s="2" t="n"/>
     </row>
-    <row r="353" ht="24" customHeight="1" s="45">
+    <row r="353" ht="24" customHeight="1" s="48">
       <c r="A353" s="13" t="n"/>
       <c r="B353" s="2" t="n"/>
-      <c r="C353" s="27" t="n"/>
+      <c r="C353" s="46" t="n"/>
       <c r="D353" s="2" t="n"/>
       <c r="E353" s="4" t="n"/>
       <c r="F353" s="39" t="n"/>
@@ -32709,10 +32864,10 @@
       <c r="AG353" s="2" t="n"/>
       <c r="AH353" s="2" t="n"/>
     </row>
-    <row r="354" ht="24" customHeight="1" s="45">
+    <row r="354" ht="24" customHeight="1" s="48">
       <c r="A354" s="13" t="n"/>
       <c r="B354" s="2" t="n"/>
-      <c r="C354" s="27" t="n"/>
+      <c r="C354" s="46" t="n"/>
       <c r="D354" s="2" t="n"/>
       <c r="E354" s="4" t="n"/>
       <c r="F354" s="39" t="n"/>
@@ -32745,10 +32900,10 @@
       <c r="AG354" s="2" t="n"/>
       <c r="AH354" s="2" t="n"/>
     </row>
-    <row r="355" ht="24" customHeight="1" s="45">
+    <row r="355" ht="24" customHeight="1" s="48">
       <c r="A355" s="13" t="n"/>
       <c r="B355" s="2" t="n"/>
-      <c r="C355" s="27" t="n"/>
+      <c r="C355" s="46" t="n"/>
       <c r="D355" s="2" t="n"/>
       <c r="E355" s="4" t="n"/>
       <c r="F355" s="39" t="n"/>
@@ -32781,10 +32936,10 @@
       <c r="AG355" s="2" t="n"/>
       <c r="AH355" s="2" t="n"/>
     </row>
-    <row r="356" ht="24" customHeight="1" s="45">
+    <row r="356" ht="24" customHeight="1" s="48">
       <c r="A356" s="13" t="n"/>
       <c r="B356" s="2" t="n"/>
-      <c r="C356" s="27" t="n"/>
+      <c r="C356" s="46" t="n"/>
       <c r="D356" s="2" t="n"/>
       <c r="E356" s="4" t="n"/>
       <c r="F356" s="39" t="n"/>
@@ -32817,10 +32972,10 @@
       <c r="AG356" s="2" t="n"/>
       <c r="AH356" s="2" t="n"/>
     </row>
-    <row r="357" ht="24" customHeight="1" s="45">
+    <row r="357" ht="24" customHeight="1" s="48">
       <c r="A357" s="13" t="n"/>
       <c r="B357" s="2" t="n"/>
-      <c r="C357" s="27" t="n"/>
+      <c r="C357" s="46" t="n"/>
       <c r="D357" s="2" t="n"/>
       <c r="E357" s="4" t="n"/>
       <c r="F357" s="39" t="n"/>
@@ -32853,10 +33008,10 @@
       <c r="AG357" s="2" t="n"/>
       <c r="AH357" s="2" t="n"/>
     </row>
-    <row r="358" ht="24" customHeight="1" s="45">
+    <row r="358" ht="24" customHeight="1" s="48">
       <c r="A358" s="13" t="n"/>
       <c r="B358" s="2" t="n"/>
-      <c r="C358" s="27" t="n"/>
+      <c r="C358" s="46" t="n"/>
       <c r="D358" s="2" t="n"/>
       <c r="E358" s="4" t="n"/>
       <c r="F358" s="39" t="n"/>
@@ -32889,10 +33044,10 @@
       <c r="AG358" s="2" t="n"/>
       <c r="AH358" s="2" t="n"/>
     </row>
-    <row r="359" ht="24" customHeight="1" s="45">
+    <row r="359" ht="24" customHeight="1" s="48">
       <c r="A359" s="13" t="n"/>
       <c r="B359" s="2" t="n"/>
-      <c r="C359" s="27" t="n"/>
+      <c r="C359" s="46" t="n"/>
       <c r="D359" s="2" t="n"/>
       <c r="E359" s="4" t="n"/>
       <c r="F359" s="39" t="n"/>
@@ -32925,10 +33080,10 @@
       <c r="AG359" s="2" t="n"/>
       <c r="AH359" s="2" t="n"/>
     </row>
-    <row r="360" ht="24" customHeight="1" s="45">
+    <row r="360" ht="24" customHeight="1" s="48">
       <c r="A360" s="13" t="n"/>
       <c r="B360" s="2" t="n"/>
-      <c r="C360" s="27" t="n"/>
+      <c r="C360" s="46" t="n"/>
       <c r="D360" s="2" t="n"/>
       <c r="E360" s="4" t="n"/>
       <c r="F360" s="39" t="n"/>
@@ -32961,10 +33116,10 @@
       <c r="AG360" s="2" t="n"/>
       <c r="AH360" s="2" t="n"/>
     </row>
-    <row r="361" ht="24" customHeight="1" s="45">
+    <row r="361" ht="24" customHeight="1" s="48">
       <c r="A361" s="13" t="n"/>
       <c r="B361" s="2" t="n"/>
-      <c r="C361" s="27" t="n"/>
+      <c r="C361" s="46" t="n"/>
       <c r="D361" s="2" t="n"/>
       <c r="E361" s="4" t="n"/>
       <c r="F361" s="39" t="n"/>
@@ -32997,10 +33152,10 @@
       <c r="AG361" s="2" t="n"/>
       <c r="AH361" s="2" t="n"/>
     </row>
-    <row r="362" ht="24" customHeight="1" s="45">
+    <row r="362" ht="24" customHeight="1" s="48">
       <c r="A362" s="13" t="n"/>
       <c r="B362" s="2" t="n"/>
-      <c r="C362" s="27" t="n"/>
+      <c r="C362" s="46" t="n"/>
       <c r="D362" s="2" t="n"/>
       <c r="E362" s="4" t="n"/>
       <c r="F362" s="39" t="n"/>
@@ -33033,10 +33188,10 @@
       <c r="AG362" s="2" t="n"/>
       <c r="AH362" s="2" t="n"/>
     </row>
-    <row r="363" ht="24" customHeight="1" s="45">
+    <row r="363" ht="24" customHeight="1" s="48">
       <c r="A363" s="13" t="n"/>
       <c r="B363" s="2" t="n"/>
-      <c r="C363" s="27" t="n"/>
+      <c r="C363" s="46" t="n"/>
       <c r="D363" s="2" t="n"/>
       <c r="E363" s="4" t="n"/>
       <c r="F363" s="39" t="n"/>
@@ -33069,10 +33224,10 @@
       <c r="AG363" s="2" t="n"/>
       <c r="AH363" s="2" t="n"/>
     </row>
-    <row r="364" ht="24" customHeight="1" s="45">
+    <row r="364" ht="24" customHeight="1" s="48">
       <c r="A364" s="13" t="n"/>
       <c r="B364" s="2" t="n"/>
-      <c r="C364" s="27" t="n"/>
+      <c r="C364" s="46" t="n"/>
       <c r="D364" s="2" t="n"/>
       <c r="E364" s="4" t="n"/>
       <c r="F364" s="39" t="n"/>
@@ -33105,10 +33260,10 @@
       <c r="AG364" s="2" t="n"/>
       <c r="AH364" s="2" t="n"/>
     </row>
-    <row r="365" ht="24" customHeight="1" s="45">
+    <row r="365" ht="24" customHeight="1" s="48">
       <c r="A365" s="13" t="n"/>
       <c r="B365" s="2" t="n"/>
-      <c r="C365" s="27" t="n"/>
+      <c r="C365" s="46" t="n"/>
       <c r="D365" s="2" t="n"/>
       <c r="E365" s="4" t="n"/>
       <c r="F365" s="39" t="n"/>
@@ -33141,10 +33296,10 @@
       <c r="AG365" s="2" t="n"/>
       <c r="AH365" s="2" t="n"/>
     </row>
-    <row r="366" ht="24" customHeight="1" s="45">
+    <row r="366" ht="24" customHeight="1" s="48">
       <c r="A366" s="13" t="n"/>
       <c r="B366" s="2" t="n"/>
-      <c r="C366" s="27" t="n"/>
+      <c r="C366" s="46" t="n"/>
       <c r="D366" s="2" t="n"/>
       <c r="E366" s="4" t="n"/>
       <c r="F366" s="39" t="n"/>
@@ -33177,10 +33332,10 @@
       <c r="AG366" s="2" t="n"/>
       <c r="AH366" s="2" t="n"/>
     </row>
-    <row r="367" ht="24" customHeight="1" s="45">
+    <row r="367" ht="24" customHeight="1" s="48">
       <c r="A367" s="13" t="n"/>
       <c r="B367" s="2" t="n"/>
-      <c r="C367" s="27" t="n"/>
+      <c r="C367" s="46" t="n"/>
       <c r="D367" s="2" t="n"/>
       <c r="E367" s="4" t="n"/>
       <c r="F367" s="39" t="n"/>
@@ -33213,10 +33368,10 @@
       <c r="AG367" s="2" t="n"/>
       <c r="AH367" s="2" t="n"/>
     </row>
-    <row r="368" ht="24" customHeight="1" s="45">
+    <row r="368" ht="24" customHeight="1" s="48">
       <c r="A368" s="13" t="n"/>
       <c r="B368" s="2" t="n"/>
-      <c r="C368" s="27" t="n"/>
+      <c r="C368" s="46" t="n"/>
       <c r="D368" s="2" t="n"/>
       <c r="E368" s="4" t="n"/>
       <c r="F368" s="39" t="n"/>
@@ -33249,10 +33404,10 @@
       <c r="AG368" s="2" t="n"/>
       <c r="AH368" s="2" t="n"/>
     </row>
-    <row r="369" ht="24" customHeight="1" s="45">
+    <row r="369" ht="24" customHeight="1" s="48">
       <c r="A369" s="13" t="n"/>
       <c r="B369" s="2" t="n"/>
-      <c r="C369" s="27" t="n"/>
+      <c r="C369" s="46" t="n"/>
       <c r="D369" s="2" t="n"/>
       <c r="E369" s="4" t="n"/>
       <c r="F369" s="39" t="n"/>
@@ -33285,10 +33440,10 @@
       <c r="AG369" s="2" t="n"/>
       <c r="AH369" s="2" t="n"/>
     </row>
-    <row r="370" ht="24" customHeight="1" s="45">
+    <row r="370" ht="24" customHeight="1" s="48">
       <c r="A370" s="13" t="n"/>
       <c r="B370" s="2" t="n"/>
-      <c r="C370" s="27" t="n"/>
+      <c r="C370" s="46" t="n"/>
       <c r="D370" s="2" t="n"/>
       <c r="E370" s="4" t="n"/>
       <c r="F370" s="39" t="n"/>
@@ -33321,10 +33476,10 @@
       <c r="AG370" s="2" t="n"/>
       <c r="AH370" s="2" t="n"/>
     </row>
-    <row r="371" ht="24" customHeight="1" s="45">
+    <row r="371" ht="24" customHeight="1" s="48">
       <c r="A371" s="13" t="n"/>
       <c r="B371" s="2" t="n"/>
-      <c r="C371" s="27" t="n"/>
+      <c r="C371" s="46" t="n"/>
       <c r="D371" s="2" t="n"/>
       <c r="E371" s="4" t="n"/>
       <c r="F371" s="39" t="n"/>
@@ -33357,10 +33512,10 @@
       <c r="AG371" s="2" t="n"/>
       <c r="AH371" s="2" t="n"/>
     </row>
-    <row r="372" ht="24" customHeight="1" s="45">
+    <row r="372" ht="24" customHeight="1" s="48">
       <c r="A372" s="13" t="n"/>
       <c r="B372" s="2" t="n"/>
-      <c r="C372" s="27" t="n"/>
+      <c r="C372" s="46" t="n"/>
       <c r="D372" s="2" t="n"/>
       <c r="E372" s="4" t="n"/>
       <c r="F372" s="39" t="n"/>
@@ -33393,10 +33548,10 @@
       <c r="AG372" s="2" t="n"/>
       <c r="AH372" s="2" t="n"/>
     </row>
-    <row r="373" ht="24" customHeight="1" s="45">
+    <row r="373" ht="24" customHeight="1" s="48">
       <c r="A373" s="13" t="n"/>
       <c r="B373" s="2" t="n"/>
-      <c r="C373" s="27" t="n"/>
+      <c r="C373" s="46" t="n"/>
       <c r="D373" s="2" t="n"/>
       <c r="E373" s="4" t="n"/>
       <c r="F373" s="39" t="n"/>
@@ -33429,10 +33584,10 @@
       <c r="AG373" s="2" t="n"/>
       <c r="AH373" s="2" t="n"/>
     </row>
-    <row r="374" ht="24" customHeight="1" s="45">
+    <row r="374" ht="24" customHeight="1" s="48">
       <c r="A374" s="13" t="n"/>
       <c r="B374" s="2" t="n"/>
-      <c r="C374" s="27" t="n"/>
+      <c r="C374" s="46" t="n"/>
       <c r="D374" s="2" t="n"/>
       <c r="E374" s="4" t="n"/>
       <c r="F374" s="39" t="n"/>
@@ -33465,10 +33620,10 @@
       <c r="AG374" s="2" t="n"/>
       <c r="AH374" s="2" t="n"/>
     </row>
-    <row r="375" ht="24" customHeight="1" s="45">
+    <row r="375" ht="24" customHeight="1" s="48">
       <c r="A375" s="13" t="n"/>
       <c r="B375" s="2" t="n"/>
-      <c r="C375" s="27" t="n"/>
+      <c r="C375" s="46" t="n"/>
       <c r="D375" s="2" t="n"/>
       <c r="E375" s="4" t="n"/>
       <c r="F375" s="39" t="n"/>
@@ -33501,10 +33656,10 @@
       <c r="AG375" s="2" t="n"/>
       <c r="AH375" s="2" t="n"/>
     </row>
-    <row r="376" ht="24" customHeight="1" s="45">
+    <row r="376" ht="24" customHeight="1" s="48">
       <c r="A376" s="13" t="n"/>
       <c r="B376" s="2" t="n"/>
-      <c r="C376" s="27" t="n"/>
+      <c r="C376" s="46" t="n"/>
       <c r="D376" s="2" t="n"/>
       <c r="E376" s="4" t="n"/>
       <c r="F376" s="39" t="n"/>
@@ -33537,10 +33692,10 @@
       <c r="AG376" s="2" t="n"/>
       <c r="AH376" s="2" t="n"/>
     </row>
-    <row r="377" ht="24" customHeight="1" s="45">
+    <row r="377" ht="24" customHeight="1" s="48">
       <c r="A377" s="13" t="n"/>
       <c r="B377" s="2" t="n"/>
-      <c r="C377" s="27" t="n"/>
+      <c r="C377" s="46" t="n"/>
       <c r="D377" s="2" t="n"/>
       <c r="E377" s="4" t="n"/>
       <c r="F377" s="39" t="n"/>
@@ -33573,10 +33728,10 @@
       <c r="AG377" s="2" t="n"/>
       <c r="AH377" s="2" t="n"/>
     </row>
-    <row r="378" ht="24" customHeight="1" s="45">
+    <row r="378" ht="24" customHeight="1" s="48">
       <c r="A378" s="13" t="n"/>
       <c r="B378" s="2" t="n"/>
-      <c r="C378" s="27" t="n"/>
+      <c r="C378" s="46" t="n"/>
       <c r="D378" s="2" t="n"/>
       <c r="E378" s="4" t="n"/>
       <c r="F378" s="39" t="n"/>
@@ -33609,10 +33764,10 @@
       <c r="AG378" s="2" t="n"/>
       <c r="AH378" s="2" t="n"/>
     </row>
-    <row r="379" ht="24" customHeight="1" s="45">
+    <row r="379" ht="24" customHeight="1" s="48">
       <c r="A379" s="13" t="n"/>
       <c r="B379" s="2" t="n"/>
-      <c r="C379" s="27" t="n"/>
+      <c r="C379" s="46" t="n"/>
       <c r="D379" s="2" t="n"/>
       <c r="E379" s="4" t="n"/>
       <c r="F379" s="39" t="n"/>
@@ -33645,10 +33800,10 @@
       <c r="AG379" s="2" t="n"/>
       <c r="AH379" s="2" t="n"/>
     </row>
-    <row r="380" ht="24" customHeight="1" s="45">
+    <row r="380" ht="24" customHeight="1" s="48">
       <c r="A380" s="13" t="n"/>
       <c r="B380" s="2" t="n"/>
-      <c r="C380" s="27" t="n"/>
+      <c r="C380" s="46" t="n"/>
       <c r="D380" s="2" t="n"/>
       <c r="E380" s="4" t="n"/>
       <c r="F380" s="39" t="n"/>
@@ -33681,10 +33836,10 @@
       <c r="AG380" s="2" t="n"/>
       <c r="AH380" s="2" t="n"/>
     </row>
-    <row r="381" ht="24" customHeight="1" s="45">
+    <row r="381" ht="24" customHeight="1" s="48">
       <c r="A381" s="13" t="n"/>
       <c r="B381" s="2" t="n"/>
-      <c r="C381" s="27" t="n"/>
+      <c r="C381" s="46" t="n"/>
       <c r="D381" s="2" t="n"/>
       <c r="E381" s="4" t="n"/>
       <c r="F381" s="39" t="n"/>
@@ -33717,10 +33872,10 @@
       <c r="AG381" s="2" t="n"/>
       <c r="AH381" s="2" t="n"/>
     </row>
-    <row r="382" ht="24" customHeight="1" s="45">
+    <row r="382" ht="24" customHeight="1" s="48">
       <c r="A382" s="13" t="n"/>
       <c r="B382" s="2" t="n"/>
-      <c r="C382" s="27" t="n"/>
+      <c r="C382" s="46" t="n"/>
       <c r="D382" s="2" t="n"/>
       <c r="E382" s="4" t="n"/>
       <c r="F382" s="39" t="n"/>
@@ -33753,10 +33908,10 @@
       <c r="AG382" s="2" t="n"/>
       <c r="AH382" s="2" t="n"/>
     </row>
-    <row r="383" ht="24" customHeight="1" s="45">
+    <row r="383" ht="24" customHeight="1" s="48">
       <c r="A383" s="13" t="n"/>
       <c r="B383" s="2" t="n"/>
-      <c r="C383" s="27" t="n"/>
+      <c r="C383" s="46" t="n"/>
       <c r="D383" s="2" t="n"/>
       <c r="E383" s="4" t="n"/>
       <c r="F383" s="39" t="n"/>
@@ -33789,10 +33944,10 @@
       <c r="AG383" s="2" t="n"/>
       <c r="AH383" s="2" t="n"/>
     </row>
-    <row r="384" ht="24" customHeight="1" s="45">
+    <row r="384" ht="24" customHeight="1" s="48">
       <c r="A384" s="13" t="n"/>
       <c r="B384" s="2" t="n"/>
-      <c r="C384" s="27" t="n"/>
+      <c r="C384" s="46" t="n"/>
       <c r="D384" s="2" t="n"/>
       <c r="E384" s="4" t="n"/>
       <c r="F384" s="39" t="n"/>
@@ -33825,10 +33980,10 @@
       <c r="AG384" s="2" t="n"/>
       <c r="AH384" s="2" t="n"/>
     </row>
-    <row r="385" ht="24" customHeight="1" s="45">
+    <row r="385" ht="24" customHeight="1" s="48">
       <c r="A385" s="13" t="n"/>
       <c r="B385" s="2" t="n"/>
-      <c r="C385" s="27" t="n"/>
+      <c r="C385" s="46" t="n"/>
       <c r="D385" s="2" t="n"/>
       <c r="E385" s="4" t="n"/>
       <c r="F385" s="39" t="n"/>
@@ -33861,10 +34016,10 @@
       <c r="AG385" s="2" t="n"/>
       <c r="AH385" s="2" t="n"/>
     </row>
-    <row r="386" ht="24" customHeight="1" s="45">
+    <row r="386" ht="24" customHeight="1" s="48">
       <c r="A386" s="13" t="n"/>
       <c r="B386" s="2" t="n"/>
-      <c r="C386" s="27" t="n"/>
+      <c r="C386" s="46" t="n"/>
       <c r="D386" s="2" t="n"/>
       <c r="E386" s="4" t="n"/>
       <c r="F386" s="39" t="n"/>
@@ -33897,10 +34052,10 @@
       <c r="AG386" s="2" t="n"/>
       <c r="AH386" s="2" t="n"/>
     </row>
-    <row r="387" ht="24" customHeight="1" s="45">
+    <row r="387" ht="24" customHeight="1" s="48">
       <c r="A387" s="13" t="n"/>
       <c r="B387" s="2" t="n"/>
-      <c r="C387" s="27" t="n"/>
+      <c r="C387" s="46" t="n"/>
       <c r="D387" s="2" t="n"/>
       <c r="E387" s="4" t="n"/>
       <c r="F387" s="39" t="n"/>
@@ -33933,10 +34088,10 @@
       <c r="AG387" s="2" t="n"/>
       <c r="AH387" s="2" t="n"/>
     </row>
-    <row r="388" ht="24" customHeight="1" s="45">
+    <row r="388" ht="24" customHeight="1" s="48">
       <c r="A388" s="13" t="n"/>
       <c r="B388" s="2" t="n"/>
-      <c r="C388" s="27" t="n"/>
+      <c r="C388" s="46" t="n"/>
       <c r="D388" s="2" t="n"/>
       <c r="E388" s="4" t="n"/>
       <c r="F388" s="39" t="n"/>
@@ -33969,10 +34124,10 @@
       <c r="AG388" s="2" t="n"/>
       <c r="AH388" s="2" t="n"/>
     </row>
-    <row r="389" ht="24" customHeight="1" s="45">
+    <row r="389" ht="24" customHeight="1" s="48">
       <c r="A389" s="13" t="n"/>
       <c r="B389" s="2" t="n"/>
-      <c r="C389" s="27" t="n"/>
+      <c r="C389" s="46" t="n"/>
       <c r="D389" s="2" t="n"/>
       <c r="E389" s="4" t="n"/>
       <c r="F389" s="39" t="n"/>
@@ -34005,10 +34160,10 @@
       <c r="AG389" s="2" t="n"/>
       <c r="AH389" s="2" t="n"/>
     </row>
-    <row r="390" ht="24" customHeight="1" s="45">
+    <row r="390" ht="24" customHeight="1" s="48">
       <c r="A390" s="13" t="n"/>
       <c r="B390" s="2" t="n"/>
-      <c r="C390" s="27" t="n"/>
+      <c r="C390" s="46" t="n"/>
       <c r="D390" s="2" t="n"/>
       <c r="E390" s="4" t="n"/>
       <c r="F390" s="39" t="n"/>
@@ -34041,10 +34196,10 @@
       <c r="AG390" s="2" t="n"/>
       <c r="AH390" s="2" t="n"/>
     </row>
-    <row r="391" ht="24" customHeight="1" s="45">
+    <row r="391" ht="24" customHeight="1" s="48">
       <c r="A391" s="13" t="n"/>
       <c r="B391" s="2" t="n"/>
-      <c r="C391" s="27" t="n"/>
+      <c r="C391" s="46" t="n"/>
       <c r="D391" s="2" t="n"/>
       <c r="E391" s="4" t="n"/>
       <c r="F391" s="39" t="n"/>
@@ -34077,10 +34232,10 @@
       <c r="AG391" s="2" t="n"/>
       <c r="AH391" s="2" t="n"/>
     </row>
-    <row r="392" ht="24" customHeight="1" s="45">
+    <row r="392" ht="24" customHeight="1" s="48">
       <c r="A392" s="13" t="n"/>
       <c r="B392" s="2" t="n"/>
-      <c r="C392" s="27" t="n"/>
+      <c r="C392" s="46" t="n"/>
       <c r="D392" s="2" t="n"/>
       <c r="E392" s="4" t="n"/>
       <c r="F392" s="39" t="n"/>
@@ -34113,10 +34268,10 @@
       <c r="AG392" s="2" t="n"/>
       <c r="AH392" s="2" t="n"/>
     </row>
-    <row r="393" ht="24" customHeight="1" s="45">
+    <row r="393" ht="24" customHeight="1" s="48">
       <c r="A393" s="13" t="n"/>
       <c r="B393" s="2" t="n"/>
-      <c r="C393" s="27" t="n"/>
+      <c r="C393" s="46" t="n"/>
       <c r="D393" s="2" t="n"/>
       <c r="E393" s="4" t="n"/>
       <c r="F393" s="39" t="n"/>
@@ -34149,10 +34304,10 @@
       <c r="AG393" s="2" t="n"/>
       <c r="AH393" s="2" t="n"/>
     </row>
-    <row r="394" ht="24" customHeight="1" s="45">
+    <row r="394" ht="24" customHeight="1" s="48">
       <c r="A394" s="13" t="n"/>
       <c r="B394" s="2" t="n"/>
-      <c r="C394" s="27" t="n"/>
+      <c r="C394" s="46" t="n"/>
       <c r="D394" s="2" t="n"/>
       <c r="E394" s="4" t="n"/>
       <c r="F394" s="39" t="n"/>
@@ -34185,10 +34340,10 @@
       <c r="AG394" s="2" t="n"/>
       <c r="AH394" s="2" t="n"/>
     </row>
-    <row r="395" ht="24" customHeight="1" s="45">
+    <row r="395" ht="24" customHeight="1" s="48">
       <c r="A395" s="13" t="n"/>
       <c r="B395" s="2" t="n"/>
-      <c r="C395" s="27" t="n"/>
+      <c r="C395" s="46" t="n"/>
       <c r="D395" s="2" t="n"/>
       <c r="E395" s="4" t="n"/>
       <c r="F395" s="39" t="n"/>
@@ -34221,10 +34376,10 @@
       <c r="AG395" s="2" t="n"/>
       <c r="AH395" s="2" t="n"/>
     </row>
-    <row r="396" ht="24" customHeight="1" s="45">
+    <row r="396" ht="24" customHeight="1" s="48">
       <c r="A396" s="13" t="n"/>
       <c r="B396" s="2" t="n"/>
-      <c r="C396" s="27" t="n"/>
+      <c r="C396" s="46" t="n"/>
       <c r="D396" s="2" t="n"/>
       <c r="E396" s="4" t="n"/>
       <c r="F396" s="39" t="n"/>
@@ -34257,10 +34412,10 @@
       <c r="AG396" s="2" t="n"/>
       <c r="AH396" s="2" t="n"/>
     </row>
-    <row r="397" ht="24" customHeight="1" s="45">
+    <row r="397" ht="24" customHeight="1" s="48">
       <c r="A397" s="13" t="n"/>
       <c r="B397" s="2" t="n"/>
-      <c r="C397" s="27" t="n"/>
+      <c r="C397" s="46" t="n"/>
       <c r="D397" s="2" t="n"/>
       <c r="E397" s="4" t="n"/>
       <c r="F397" s="39" t="n"/>
@@ -34293,10 +34448,10 @@
       <c r="AG397" s="2" t="n"/>
       <c r="AH397" s="2" t="n"/>
     </row>
-    <row r="398" ht="24" customHeight="1" s="45">
+    <row r="398" ht="24" customHeight="1" s="48">
       <c r="A398" s="13" t="n"/>
       <c r="B398" s="2" t="n"/>
-      <c r="C398" s="27" t="n"/>
+      <c r="C398" s="46" t="n"/>
       <c r="D398" s="2" t="n"/>
       <c r="E398" s="4" t="n"/>
       <c r="F398" s="39" t="n"/>
@@ -34329,10 +34484,10 @@
       <c r="AG398" s="2" t="n"/>
       <c r="AH398" s="2" t="n"/>
     </row>
-    <row r="399" ht="24" customHeight="1" s="45">
+    <row r="399" ht="24" customHeight="1" s="48">
       <c r="A399" s="13" t="n"/>
       <c r="B399" s="2" t="n"/>
-      <c r="C399" s="27" t="n"/>
+      <c r="C399" s="46" t="n"/>
       <c r="D399" s="2" t="n"/>
       <c r="E399" s="4" t="n"/>
       <c r="F399" s="39" t="n"/>
@@ -34365,10 +34520,10 @@
       <c r="AG399" s="2" t="n"/>
       <c r="AH399" s="2" t="n"/>
     </row>
-    <row r="400" ht="24" customHeight="1" s="45">
+    <row r="400" ht="24" customHeight="1" s="48">
       <c r="A400" s="13" t="n"/>
       <c r="B400" s="2" t="n"/>
-      <c r="C400" s="27" t="n"/>
+      <c r="C400" s="46" t="n"/>
       <c r="D400" s="2" t="n"/>
       <c r="E400" s="4" t="n"/>
       <c r="F400" s="39" t="n"/>
@@ -34401,12 +34556,12 @@
       <c r="AG400" s="2" t="n"/>
       <c r="AH400" s="2" t="n"/>
     </row>
-    <row r="401" ht="24" customHeight="1" s="45">
+    <row r="401" ht="24" customHeight="1" s="48">
       <c r="A401" s="12" t="n">
         <v>400</v>
       </c>
       <c r="B401" s="2" t="n"/>
-      <c r="C401" s="27" t="n"/>
+      <c r="C401" s="46" t="n"/>
       <c r="D401" s="2" t="n"/>
       <c r="E401" s="4" t="n"/>
       <c r="F401" s="39" t="n"/>
@@ -34632,7 +34787,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="27.75" customHeight="1" s="45">
+    <row r="2" ht="27.75" customHeight="1" s="48">
       <c r="A2" s="0" t="n">
         <v>1</v>
       </c>
@@ -34711,7 +34866,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="27.75" customHeight="1" s="45">
+    <row r="3" ht="27.75" customHeight="1" s="48">
       <c r="A3" s="0" t="n">
         <v>2</v>
       </c>
@@ -35152,7 +35307,7 @@
   <dimension ref="A1:K4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.9"/>
   <cols>
-    <col width="18.59765625" customWidth="1" style="46" min="11" max="11"/>
+    <col width="18.59765625" customWidth="1" style="49" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -35206,7 +35361,7 @@
           <t>level2</t>
         </is>
       </c>
-      <c r="K1" s="46" t="inlineStr">
+      <c r="K1" s="49" t="inlineStr">
         <is>
           <t>date</t>
         </is>
@@ -35251,7 +35406,7 @@
           <t>大兴安岭地区</t>
         </is>
       </c>
-      <c r="K2" s="46" t="n">
+      <c r="K2" s="49" t="n">
         <v>25199</v>
       </c>
     </row>
@@ -35291,7 +35446,7 @@
           <t>呼伦贝尔市</t>
         </is>
       </c>
-      <c r="K3" s="46" t="n">
+      <c r="K3" s="49" t="n">
         <v>45993</v>
       </c>
     </row>
@@ -35331,7 +35486,7 @@
           <t>阿勒泰地区</t>
         </is>
       </c>
-      <c r="K4" s="46" t="n">
+      <c r="K4" s="49" t="n">
         <v>45995</v>
       </c>
     </row>

--- a/气象/For_Python_站点信息和记录.xlsx
+++ b/气象/For_Python_站点信息和记录.xlsx
@@ -796,8 +796,8 @@
     <col width="18.59765625" customWidth="1" style="8" min="25" max="25"/>
     <col width="12.59765625" customWidth="1" style="5" min="26" max="30"/>
     <col width="12.59765625" customWidth="1" style="8" min="31" max="32"/>
-    <col width="12.59765625" customWidth="1" style="5" min="33" max="285"/>
-    <col width="12.59765625" customWidth="1" style="5" min="286" max="16384"/>
+    <col width="12.59765625" customWidth="1" style="5" min="33" max="287"/>
+    <col width="12.59765625" customWidth="1" style="5" min="288" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="27.75" customFormat="1" customHeight="1" s="11">
@@ -1020,13 +1020,13 @@
         </is>
       </c>
       <c r="O2" s="32" t="n">
-        <v>-40.1</v>
+        <v>-38.4</v>
       </c>
       <c r="P2" s="32" t="n">
-        <v>-26.9</v>
+        <v>-24.1</v>
       </c>
       <c r="Q2" s="32" t="n">
-        <v>-31.19</v>
+        <v>-30.86</v>
       </c>
       <c r="R2" s="23" t="inlineStr">
         <is>
@@ -1036,7 +1036,7 @@
       <c r="S2" s="37" t="n"/>
       <c r="T2" s="41" t="inlineStr">
         <is>
-          <t>东亚昼温王&lt;br&gt;特斯河 乌布苏省</t>
+          <t>东亚昼温王&lt;br&gt;乌布苏特斯河</t>
         </is>
       </c>
       <c r="U2" s="2" t="inlineStr">
@@ -1126,10 +1126,10 @@
         </is>
       </c>
       <c r="O3" s="32" t="n">
-        <v>-37.4</v>
+        <v>-40</v>
       </c>
       <c r="P3" s="32" t="n">
-        <v>-24.4</v>
+        <v>-21.9</v>
       </c>
       <c r="Q3" s="32" t="n"/>
       <c r="R3" s="23" t="n"/>
@@ -1229,18 +1229,14 @@
           <t>⚡</t>
         </is>
       </c>
-      <c r="O4" s="32" t="n">
-        <v>-38.3</v>
-      </c>
-      <c r="P4" s="32" t="n">
-        <v>-23.1</v>
-      </c>
+      <c r="O4" s="32" t="n"/>
+      <c r="P4" s="32" t="n"/>
       <c r="Q4" s="32" t="n"/>
       <c r="R4" s="23" t="n"/>
       <c r="S4" s="37" t="n"/>
       <c r="T4" s="41" t="inlineStr">
         <is>
-          <t>蒙古爆发王&lt;br&gt;特斯河 扎布汗省</t>
+          <t>蒙古明星站爆发王&lt;br&gt;扎布汗特斯河</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -1326,10 +1322,10 @@
       </c>
       <c r="N5" s="2" t="n"/>
       <c r="O5" s="32" t="n">
-        <v>-35.9</v>
+        <v>-34.2</v>
       </c>
       <c r="P5" s="32" t="n">
-        <v>-15.4</v>
+        <v>-18.1</v>
       </c>
       <c r="Q5" s="32" t="n"/>
       <c r="R5" s="23" t="n"/>
@@ -1426,10 +1422,10 @@
         </is>
       </c>
       <c r="O6" s="32" t="n">
-        <v>-33</v>
+        <v>-34.4</v>
       </c>
       <c r="P6" s="32" t="n">
-        <v>-10.4</v>
+        <v>-12.3</v>
       </c>
       <c r="Q6" s="32" t="n"/>
       <c r="R6" s="23" t="n"/>
@@ -1526,10 +1522,10 @@
         </is>
       </c>
       <c r="O7" s="32" t="n">
-        <v>-32.4</v>
+        <v>-34.7</v>
       </c>
       <c r="P7" s="32" t="n">
-        <v>-18.7</v>
+        <v>-20.7</v>
       </c>
       <c r="Q7" s="32" t="n"/>
       <c r="R7" s="23" t="n"/>
@@ -1634,13 +1630,13 @@
       </c>
       <c r="N8" s="2" t="n"/>
       <c r="O8" s="32" t="n">
-        <v>-30.7</v>
+        <v>-32.5</v>
       </c>
       <c r="P8" s="32" t="n">
-        <v>-15.2</v>
+        <v>-18.6</v>
       </c>
       <c r="Q8" s="32" t="n">
-        <v>-23.9</v>
+        <v>-25.93</v>
       </c>
       <c r="R8" s="23" t="inlineStr">
         <is>
@@ -1746,13 +1742,13 @@
       </c>
       <c r="N9" s="2" t="n"/>
       <c r="O9" s="32" t="n">
-        <v>-35.9</v>
+        <v>-34.3</v>
       </c>
       <c r="P9" s="32" t="n">
-        <v>-20.5</v>
+        <v>-21.1</v>
       </c>
       <c r="Q9" s="32" t="n">
-        <v>-28.34</v>
+        <v>-28.8</v>
       </c>
       <c r="R9" s="23" t="inlineStr">
         <is>
@@ -1862,13 +1858,13 @@
       </c>
       <c r="N10" s="3" t="n"/>
       <c r="O10" s="32" t="n">
-        <v>-30.9</v>
+        <v>-36.6</v>
       </c>
       <c r="P10" s="32" t="n">
-        <v>-21.7</v>
+        <v>-16.2</v>
       </c>
       <c r="Q10" s="32" t="n">
-        <v>-27</v>
+        <v>-26.55</v>
       </c>
       <c r="R10" s="23" t="inlineStr">
         <is>
@@ -1978,13 +1974,13 @@
         </is>
       </c>
       <c r="O11" s="32" t="n">
-        <v>-33.1</v>
+        <v>-37.2</v>
       </c>
       <c r="P11" s="32" t="n">
-        <v>-16</v>
+        <v>-12.7</v>
       </c>
       <c r="Q11" s="32" t="n">
-        <v>-24.35</v>
+        <v>-24.31</v>
       </c>
       <c r="R11" s="23" t="inlineStr">
         <is>
@@ -2090,13 +2086,13 @@
       </c>
       <c r="N12" s="2" t="n"/>
       <c r="O12" s="32" t="n">
-        <v>-32.2</v>
+        <v>-34.5</v>
       </c>
       <c r="P12" s="32" t="n">
-        <v>-15</v>
+        <v>-16</v>
       </c>
       <c r="Q12" s="32" t="n">
-        <v>-24.91</v>
+        <v>-26.59</v>
       </c>
       <c r="R12" s="23" t="inlineStr">
         <is>
@@ -2206,13 +2202,13 @@
         </is>
       </c>
       <c r="O13" s="32" t="n">
-        <v>-33.1</v>
+        <v>-38</v>
       </c>
       <c r="P13" s="32" t="n">
-        <v>-21.3</v>
+        <v>-24.9</v>
       </c>
       <c r="Q13" s="32" t="n">
-        <v>-28.31</v>
+        <v>-31</v>
       </c>
       <c r="R13" s="23" t="inlineStr">
         <is>
@@ -2318,10 +2314,10 @@
       </c>
       <c r="N14" s="2" t="n"/>
       <c r="O14" s="32" t="n">
-        <v>-20.5</v>
+        <v>-21.1</v>
       </c>
       <c r="P14" s="32" t="n">
-        <v>-7.9</v>
+        <v>-8.800000000000001</v>
       </c>
       <c r="Q14" s="32" t="n">
         <v>-15.07</v>
@@ -2423,12 +2419,8 @@
         </is>
       </c>
       <c r="N15" s="2" t="n"/>
-      <c r="O15" s="32" t="n">
-        <v>-34.5</v>
-      </c>
-      <c r="P15" s="32" t="n">
-        <v>-12</v>
-      </c>
+      <c r="O15" s="32" t="n"/>
+      <c r="P15" s="32" t="n"/>
       <c r="Q15" s="32" t="n"/>
       <c r="R15" s="23" t="n"/>
       <c r="S15" s="37" t="n"/>
@@ -2486,7 +2478,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>ogimet</t>
+          <t>rp5</t>
         </is>
       </c>
       <c r="C16" s="46" t="n">
@@ -3723,8 +3715,12 @@
         </is>
       </c>
       <c r="N29" s="2" t="n"/>
-      <c r="O29" s="32" t="n"/>
-      <c r="P29" s="32" t="n"/>
+      <c r="O29" s="32" t="n">
+        <v>-38.2</v>
+      </c>
+      <c r="P29" s="32" t="n">
+        <v>-19.8</v>
+      </c>
       <c r="Q29" s="32" t="n"/>
       <c r="R29" s="23" t="n"/>
       <c r="S29" s="37" t="n"/>
@@ -7643,12 +7639,8 @@
         </is>
       </c>
       <c r="N73" s="2" t="n"/>
-      <c r="O73" s="32" t="n">
-        <v>-36.6</v>
-      </c>
-      <c r="P73" s="32" t="n">
-        <v>-13.1</v>
-      </c>
+      <c r="O73" s="32" t="n"/>
+      <c r="P73" s="32" t="n"/>
       <c r="Q73" s="32" t="n"/>
       <c r="R73" s="23" t="n"/>
       <c r="S73" s="37" t="n"/>
@@ -7830,13 +7822,13 @@
       </c>
       <c r="N75" s="2" t="n"/>
       <c r="O75" s="32" t="n">
-        <v>-17.6</v>
+        <v>-31.9</v>
       </c>
       <c r="P75" s="32" t="n">
-        <v>-9.800000000000001</v>
+        <v>-9</v>
       </c>
       <c r="Q75" s="32" t="n">
-        <v>-14.19</v>
+        <v>-19.8</v>
       </c>
       <c r="R75" s="23" t="inlineStr">
         <is>
@@ -7942,13 +7934,13 @@
       </c>
       <c r="N76" s="2" t="n"/>
       <c r="O76" s="32" t="n">
-        <v>-26.5</v>
+        <v>-35.3</v>
       </c>
       <c r="P76" s="32" t="n">
-        <v>-11.6</v>
+        <v>-14.4</v>
       </c>
       <c r="Q76" s="32" t="n">
-        <v>-20.7</v>
+        <v>-24.71</v>
       </c>
       <c r="R76" s="23" t="inlineStr">
         <is>
@@ -8058,13 +8050,13 @@
         </is>
       </c>
       <c r="O77" s="32" t="n">
-        <v>-32.8</v>
+        <v>-37</v>
       </c>
       <c r="P77" s="32" t="n">
-        <v>-14.4</v>
+        <v>-15.6</v>
       </c>
       <c r="Q77" s="32" t="n">
-        <v>-24.18</v>
+        <v>-26.4</v>
       </c>
       <c r="R77" s="23" t="inlineStr">
         <is>
@@ -8170,13 +8162,13 @@
       </c>
       <c r="N78" s="2" t="n"/>
       <c r="O78" s="32" t="n">
-        <v>-30.6</v>
+        <v>-32.9</v>
       </c>
       <c r="P78" s="32" t="n">
-        <v>-13.5</v>
+        <v>-15.8</v>
       </c>
       <c r="Q78" s="32" t="n">
-        <v>-22.94</v>
+        <v>-24.03</v>
       </c>
       <c r="R78" s="23" t="inlineStr">
         <is>
@@ -8286,13 +8278,13 @@
         </is>
       </c>
       <c r="O79" s="32" t="n">
-        <v>-32.5</v>
+        <v>-22.3</v>
       </c>
       <c r="P79" s="32" t="n">
-        <v>-10.8</v>
+        <v>-5.8</v>
       </c>
       <c r="Q79" s="32" t="n">
-        <v>-21.74</v>
+        <v>-13.54</v>
       </c>
       <c r="R79" s="23" t="inlineStr">
         <is>
@@ -8398,13 +8390,13 @@
       </c>
       <c r="N80" s="2" t="n"/>
       <c r="O80" s="32" t="n">
-        <v>-36.1</v>
+        <v>-32.6</v>
       </c>
       <c r="P80" s="32" t="n">
-        <v>-16.8</v>
+        <v>-15.6</v>
       </c>
       <c r="Q80" s="32" t="n">
-        <v>-26.62</v>
+        <v>-25.16</v>
       </c>
       <c r="R80" s="23" t="inlineStr">
         <is>
@@ -8514,13 +8506,13 @@
         </is>
       </c>
       <c r="O81" s="32" t="n">
-        <v>-43.6</v>
+        <v>-42.1</v>
       </c>
       <c r="P81" s="32" t="n">
-        <v>-17.5</v>
+        <v>-14.7</v>
       </c>
       <c r="Q81" s="32" t="n">
-        <v>-31.95</v>
+        <v>-30.77</v>
       </c>
       <c r="R81" s="23" t="inlineStr">
         <is>
@@ -8635,13 +8627,13 @@
         </is>
       </c>
       <c r="O82" s="32" t="n">
-        <v>-43.7</v>
+        <v>-38.1</v>
       </c>
       <c r="P82" s="32" t="n">
-        <v>-15.5</v>
+        <v>-12</v>
       </c>
       <c r="Q82" s="32" t="n">
-        <v>-32.56</v>
+        <v>-28.55</v>
       </c>
       <c r="R82" s="23" t="inlineStr">
         <is>
@@ -8747,13 +8739,13 @@
       </c>
       <c r="N83" s="2" t="n"/>
       <c r="O83" s="32" t="n">
-        <v>-36.3</v>
+        <v>-35.2</v>
       </c>
       <c r="P83" s="32" t="n">
-        <v>-21.1</v>
+        <v>-19.4</v>
       </c>
       <c r="Q83" s="32" t="n">
-        <v>-29.14</v>
+        <v>-28.21</v>
       </c>
       <c r="R83" s="23" t="inlineStr">
         <is>
@@ -8863,13 +8855,13 @@
         </is>
       </c>
       <c r="O84" s="32" t="n">
-        <v>-41.4</v>
+        <v>-35.3</v>
       </c>
       <c r="P84" s="32" t="n">
-        <v>-21.5</v>
+        <v>-17.9</v>
       </c>
       <c r="Q84" s="32" t="n">
-        <v>-32.38</v>
+        <v>-28.46</v>
       </c>
       <c r="R84" s="23" t="inlineStr">
         <is>
@@ -8979,13 +8971,13 @@
         </is>
       </c>
       <c r="O85" s="32" t="n">
-        <v>-40.7</v>
+        <v>-33</v>
       </c>
       <c r="P85" s="32" t="n">
-        <v>-20.5</v>
+        <v>-18.2</v>
       </c>
       <c r="Q85" s="32" t="n">
-        <v>-29.51</v>
+        <v>-25.51</v>
       </c>
       <c r="R85" s="23" t="inlineStr">
         <is>
@@ -9091,13 +9083,13 @@
       </c>
       <c r="N86" s="2" t="n"/>
       <c r="O86" s="32" t="n">
-        <v>-35.1</v>
+        <v>-29.5</v>
       </c>
       <c r="P86" s="32" t="n">
-        <v>-20.8</v>
+        <v>-17.8</v>
       </c>
       <c r="Q86" s="32" t="n">
-        <v>-28.34</v>
+        <v>-24.44</v>
       </c>
       <c r="R86" s="23" t="inlineStr">
         <is>
@@ -9215,13 +9207,13 @@
         </is>
       </c>
       <c r="O87" s="32" t="n">
-        <v>-32.5</v>
+        <v>-34.4</v>
       </c>
       <c r="P87" s="32" t="n">
-        <v>-18.2</v>
+        <v>-22</v>
       </c>
       <c r="Q87" s="32" t="n">
-        <v>-26.24</v>
+        <v>-28.46</v>
       </c>
       <c r="R87" s="23" t="inlineStr">
         <is>
@@ -9327,13 +9319,13 @@
       </c>
       <c r="N88" s="2" t="n"/>
       <c r="O88" s="32" t="n">
-        <v>-32.2</v>
+        <v>-23.1</v>
       </c>
       <c r="P88" s="32" t="n">
-        <v>-16.9</v>
+        <v>-15.4</v>
       </c>
       <c r="Q88" s="32" t="n">
-        <v>-24.56</v>
+        <v>-19.53</v>
       </c>
       <c r="R88" s="23" t="inlineStr">
         <is>
@@ -9444,9 +9436,7 @@
       <c r="P89" s="32" t="n">
         <v>-12.8</v>
       </c>
-      <c r="Q89" s="32" t="n">
-        <v>-27.24</v>
-      </c>
+      <c r="Q89" s="32" t="n"/>
       <c r="R89" s="23" t="inlineStr">
         <is>
           <t>Y</t>
@@ -9551,13 +9541,13 @@
         </is>
       </c>
       <c r="O90" s="32" t="n">
-        <v>-36.1</v>
+        <v>-29.8</v>
       </c>
       <c r="P90" s="32" t="n">
-        <v>-22.3</v>
+        <v>-19.5</v>
       </c>
       <c r="Q90" s="32" t="n">
-        <v>-28.17</v>
+        <v>-24.9</v>
       </c>
       <c r="R90" s="23" t="inlineStr">
         <is>
@@ -9659,13 +9649,13 @@
       </c>
       <c r="N91" s="2" t="n"/>
       <c r="O91" s="32" t="n">
-        <v>-34.1</v>
+        <v>-27.9</v>
       </c>
       <c r="P91" s="32" t="n">
-        <v>-23.5</v>
+        <v>-17.4</v>
       </c>
       <c r="Q91" s="32" t="n">
-        <v>-27.89</v>
+        <v>-22.86</v>
       </c>
       <c r="R91" s="23" t="inlineStr">
         <is>
@@ -9767,13 +9757,13 @@
       </c>
       <c r="N92" s="2" t="n"/>
       <c r="O92" s="32" t="n">
-        <v>-9.4</v>
+        <v>-8.800000000000001</v>
       </c>
       <c r="P92" s="32" t="n">
-        <v>2.6</v>
+        <v>0.1</v>
       </c>
       <c r="Q92" s="32" t="n">
-        <v>-3.7</v>
+        <v>-4.02</v>
       </c>
       <c r="R92" s="23" t="inlineStr">
         <is>
@@ -9879,13 +9869,13 @@
       </c>
       <c r="N93" s="2" t="n"/>
       <c r="O93" s="32" t="n">
-        <v>-8.1</v>
+        <v>-2.2</v>
       </c>
       <c r="P93" s="32" t="n">
-        <v>1.9</v>
+        <v>0.2</v>
       </c>
       <c r="Q93" s="32" t="n">
-        <v>-2.85</v>
+        <v>-0.88</v>
       </c>
       <c r="R93" s="23" t="inlineStr">
         <is>
@@ -9999,10 +9989,10 @@
         </is>
       </c>
       <c r="O94" s="32" t="n">
-        <v>-11.6</v>
+        <v>-5.5</v>
       </c>
       <c r="P94" s="32" t="n">
-        <v>-1.4</v>
+        <v>0.5</v>
       </c>
       <c r="Q94" s="32" t="n"/>
       <c r="R94" s="23" t="inlineStr">
@@ -10117,13 +10107,13 @@
       </c>
       <c r="N95" s="2" t="n"/>
       <c r="O95" s="32" t="n">
-        <v>-13.6</v>
+        <v>-7.6</v>
       </c>
       <c r="P95" s="32" t="n">
-        <v>-3.4</v>
+        <v>2.7</v>
       </c>
       <c r="Q95" s="32" t="n">
-        <v>-8.720000000000001</v>
+        <v>-3.29</v>
       </c>
       <c r="R95" s="23" t="inlineStr">
         <is>
@@ -10245,10 +10235,10 @@
         </is>
       </c>
       <c r="O96" s="32" t="n">
-        <v>-11.7</v>
+        <v>-4.4</v>
       </c>
       <c r="P96" s="32" t="n">
-        <v>-2.4</v>
+        <v>-0.5</v>
       </c>
       <c r="Q96" s="32" t="n"/>
       <c r="R96" s="23" t="inlineStr">
@@ -10363,13 +10353,13 @@
       </c>
       <c r="N97" s="2" t="n"/>
       <c r="O97" s="32" t="n">
-        <v>-18.8</v>
+        <v>-14.8</v>
       </c>
       <c r="P97" s="32" t="n">
-        <v>-5.4</v>
+        <v>-2.9</v>
       </c>
       <c r="Q97" s="32" t="n">
-        <v>-11.85</v>
+        <v>-9.140000000000001</v>
       </c>
       <c r="R97" s="23" t="inlineStr">
         <is>
@@ -10483,10 +10473,10 @@
       </c>
       <c r="N98" s="2" t="n"/>
       <c r="O98" s="32" t="n">
-        <v>-17.9</v>
+        <v>-31.4</v>
       </c>
       <c r="P98" s="32" t="n">
-        <v>-10.8</v>
+        <v>-11.2</v>
       </c>
       <c r="Q98" s="32" t="n"/>
       <c r="R98" s="23" t="inlineStr">
@@ -10604,10 +10594,10 @@
         <v>-38.8</v>
       </c>
       <c r="P99" s="32" t="n">
-        <v>-16.8</v>
+        <v>-17.5</v>
       </c>
       <c r="Q99" s="32" t="n">
-        <v>-29.57</v>
+        <v>-28.52</v>
       </c>
       <c r="R99" s="23" t="inlineStr">
         <is>
@@ -10617,7 +10607,7 @@
       <c r="S99" s="37" t="n"/>
       <c r="T99" s="41" t="inlineStr">
         <is>
-          <t>大兴安岭</t>
+          <t>黑龙江大兴安岭</t>
         </is>
       </c>
       <c r="U99" s="2" t="inlineStr">
@@ -10723,7 +10713,7 @@
       <c r="S100" s="37" t="n"/>
       <c r="T100" s="41" t="inlineStr">
         <is>
-          <t>大兴安岭</t>
+          <t>黑龙江大兴安岭</t>
         </is>
       </c>
       <c r="U100" s="2" t="inlineStr">
@@ -10818,12 +10808,8 @@
         </is>
       </c>
       <c r="N101" s="2" t="n"/>
-      <c r="O101" s="32" t="n">
-        <v>-40.7</v>
-      </c>
-      <c r="P101" s="32" t="n">
-        <v>-12.2</v>
-      </c>
+      <c r="O101" s="32" t="n"/>
+      <c r="P101" s="32" t="n"/>
       <c r="Q101" s="32" t="n"/>
       <c r="R101" s="23" t="inlineStr">
         <is>
@@ -10833,7 +10819,7 @@
       <c r="S101" s="37" t="n"/>
       <c r="T101" s="41" t="inlineStr">
         <is>
-          <t>大兴安岭</t>
+          <t>黑龙江大兴安岭</t>
         </is>
       </c>
       <c r="U101" s="2" t="inlineStr">
@@ -10937,13 +10923,13 @@
       </c>
       <c r="N102" s="2" t="n"/>
       <c r="O102" s="32" t="n">
-        <v>-40</v>
+        <v>-37.1</v>
       </c>
       <c r="P102" s="32" t="n">
-        <v>-14.8</v>
+        <v>-11.6</v>
       </c>
       <c r="Q102" s="32" t="n">
-        <v>-29.12</v>
+        <v>-26.06</v>
       </c>
       <c r="R102" s="23" t="inlineStr">
         <is>
@@ -10957,7 +10943,7 @@
       </c>
       <c r="T102" s="41" t="inlineStr">
         <is>
-          <t>大兴安岭</t>
+          <t>黑龙江大兴安岭</t>
         </is>
       </c>
       <c r="U102" s="2" t="inlineStr">
@@ -11053,10 +11039,10 @@
       </c>
       <c r="N103" s="2" t="n"/>
       <c r="O103" s="32" t="n">
-        <v>-38.4</v>
+        <v>-37.1</v>
       </c>
       <c r="P103" s="32" t="n">
-        <v>-15.1</v>
+        <v>-14.3</v>
       </c>
       <c r="Q103" s="32" t="n"/>
       <c r="R103" s="23" t="inlineStr">
@@ -11067,7 +11053,7 @@
       <c r="S103" s="37" t="n"/>
       <c r="T103" s="41" t="inlineStr">
         <is>
-          <t>前任国内最低记录&lt;br&gt;黑龙江</t>
+          <t>前任国内最低记录&lt;br&gt;黑龙江大兴安岭</t>
         </is>
       </c>
       <c r="U103" s="2" t="inlineStr">
@@ -11163,10 +11149,10 @@
       </c>
       <c r="N104" s="2" t="n"/>
       <c r="O104" s="32" t="n">
-        <v>-36.9</v>
+        <v>-28.3</v>
       </c>
       <c r="P104" s="32" t="n">
-        <v>-13.2</v>
+        <v>-10.1</v>
       </c>
       <c r="Q104" s="32" t="n"/>
       <c r="R104" s="23" t="inlineStr">
@@ -11181,7 +11167,7 @@
       </c>
       <c r="T104" s="41" t="inlineStr">
         <is>
-          <t>国家站最冷单月</t>
+          <t>国家站最冷单月 呼伦贝尔</t>
         </is>
       </c>
       <c r="U104" s="2" t="inlineStr">
@@ -11289,13 +11275,13 @@
         </is>
       </c>
       <c r="O105" s="32" t="n">
-        <v>-41.2</v>
+        <v>-32.3</v>
       </c>
       <c r="P105" s="32" t="n">
-        <v>-13.4</v>
+        <v>-10.7</v>
       </c>
       <c r="Q105" s="32" t="n">
-        <v>-28.4</v>
+        <v>-20.86</v>
       </c>
       <c r="R105" s="23" t="inlineStr">
         <is>
@@ -11405,10 +11391,10 @@
         </is>
       </c>
       <c r="O106" s="32" t="n">
-        <v>-36.9</v>
+        <v>-28.3</v>
       </c>
       <c r="P106" s="32" t="n">
-        <v>-21.6</v>
+        <v>-12</v>
       </c>
       <c r="Q106" s="32" t="n"/>
       <c r="R106" s="23" t="inlineStr">
@@ -11625,13 +11611,13 @@
       </c>
       <c r="N108" s="2" t="n"/>
       <c r="O108" s="32" t="n">
-        <v>-33.1</v>
+        <v>-20.9</v>
       </c>
       <c r="P108" s="32" t="n">
-        <v>-18.7</v>
+        <v>-9.4</v>
       </c>
       <c r="Q108" s="32" t="n">
-        <v>-26.45</v>
+        <v>-16.3</v>
       </c>
       <c r="R108" s="23" t="inlineStr">
         <is>
@@ -11838,12 +11824,8 @@
         </is>
       </c>
       <c r="N110" s="2" t="n"/>
-      <c r="O110" s="32" t="n">
-        <v>-39.4</v>
-      </c>
-      <c r="P110" s="32" t="n">
-        <v>-15.9</v>
-      </c>
+      <c r="O110" s="32" t="n"/>
+      <c r="P110" s="32" t="n"/>
       <c r="Q110" s="32" t="n"/>
       <c r="R110" s="23" t="inlineStr">
         <is>
@@ -11957,13 +11939,13 @@
       </c>
       <c r="N111" s="2" t="n"/>
       <c r="O111" s="32" t="n">
-        <v>-30.8</v>
+        <v>-15.7</v>
       </c>
       <c r="P111" s="32" t="n">
-        <v>-7.7</v>
+        <v>-9</v>
       </c>
       <c r="Q111" s="32" t="n">
-        <v>-19.81</v>
+        <v>-13.26</v>
       </c>
       <c r="R111" s="23" t="inlineStr">
         <is>
@@ -12069,10 +12051,10 @@
       </c>
       <c r="N112" s="2" t="n"/>
       <c r="O112" s="32" t="n">
-        <v>-8.6</v>
+        <v>-6.4</v>
       </c>
       <c r="P112" s="32" t="n">
-        <v>-1.8</v>
+        <v>5</v>
       </c>
       <c r="Q112" s="32" t="n"/>
       <c r="R112" s="23" t="inlineStr">
@@ -12178,7 +12160,7 @@
         <v>-18</v>
       </c>
       <c r="P113" s="32" t="n">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
       <c r="Q113" s="32" t="n"/>
       <c r="R113" s="23" t="inlineStr">
@@ -12289,10 +12271,10 @@
         </is>
       </c>
       <c r="O114" s="32" t="n">
-        <v>-25.1</v>
+        <v>-24.2</v>
       </c>
       <c r="P114" s="32" t="n">
-        <v>2</v>
+        <v>0.4</v>
       </c>
       <c r="Q114" s="32" t="n"/>
       <c r="R114" s="23" t="inlineStr">
@@ -12411,10 +12393,10 @@
         </is>
       </c>
       <c r="O115" s="32" t="n">
-        <v>-23.3</v>
+        <v>-21.7</v>
       </c>
       <c r="P115" s="32" t="n">
-        <v>-3.7</v>
+        <v>-3.6</v>
       </c>
       <c r="Q115" s="32" t="n"/>
       <c r="R115" s="23" t="inlineStr">
@@ -12529,13 +12511,13 @@
       </c>
       <c r="N116" s="2" t="n"/>
       <c r="O116" s="32" t="n">
-        <v>-6.5</v>
+        <v>-8.800000000000001</v>
       </c>
       <c r="P116" s="32" t="n">
-        <v>6.8</v>
+        <v>1.9</v>
       </c>
       <c r="Q116" s="32" t="n">
-        <v>-0.71</v>
+        <v>-4.55</v>
       </c>
       <c r="R116" s="23" t="inlineStr">
         <is>
@@ -12641,7 +12623,7 @@
       </c>
       <c r="N117" s="2" t="n"/>
       <c r="O117" s="32" t="n">
-        <v>-11.9</v>
+        <v>-13.2</v>
       </c>
       <c r="P117" s="32" t="n">
         <v>-2.4</v>
@@ -12755,10 +12737,10 @@
         </is>
       </c>
       <c r="O118" s="32" t="n">
-        <v>-15.1</v>
+        <v>-27.9</v>
       </c>
       <c r="P118" s="32" t="n">
-        <v>-7.8</v>
+        <v>-11.4</v>
       </c>
       <c r="Q118" s="32" t="n"/>
       <c r="R118" s="23" t="inlineStr">
@@ -12873,13 +12855,13 @@
       </c>
       <c r="N119" s="2" t="n"/>
       <c r="O119" s="32" t="n">
-        <v>-27.4</v>
+        <v>-25</v>
       </c>
       <c r="P119" s="32" t="n">
-        <v>-17.4</v>
+        <v>-15.8</v>
       </c>
       <c r="Q119" s="32" t="n">
-        <v>-22.2</v>
+        <v>-20.55</v>
       </c>
       <c r="R119" s="23" t="inlineStr">
         <is>
@@ -13107,13 +13089,13 @@
       </c>
       <c r="N121" s="2" t="n"/>
       <c r="O121" s="32" t="n">
-        <v>-12</v>
+        <v>-14.1</v>
       </c>
       <c r="P121" s="32" t="n">
-        <v>-8.6</v>
+        <v>-8.800000000000001</v>
       </c>
       <c r="Q121" s="32" t="n">
-        <v>-10.47</v>
+        <v>-11.88</v>
       </c>
       <c r="R121" s="23" t="inlineStr">
         <is>
@@ -13231,10 +13213,10 @@
       </c>
       <c r="N122" s="2" t="n"/>
       <c r="O122" s="32" t="n">
-        <v>-12.9</v>
+        <v>-19.2</v>
       </c>
       <c r="P122" s="32" t="n">
-        <v>-5.4</v>
+        <v>-8.699999999999999</v>
       </c>
       <c r="Q122" s="32" t="n"/>
       <c r="R122" s="23" t="inlineStr">
@@ -13455,13 +13437,13 @@
       </c>
       <c r="N124" s="2" t="n"/>
       <c r="O124" s="32" t="n">
-        <v>-1.1</v>
+        <v>0.4</v>
       </c>
       <c r="P124" s="32" t="n">
-        <v>5.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Q124" s="32" t="n">
-        <v>2.23</v>
+        <v>3.63</v>
       </c>
       <c r="R124" s="23" t="inlineStr">
         <is>
@@ -13579,13 +13561,13 @@
       </c>
       <c r="N125" s="2" t="n"/>
       <c r="O125" s="32" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="P125" s="32" t="n">
-        <v>3.6</v>
+        <v>5.8</v>
       </c>
       <c r="Q125" s="32" t="n">
-        <v>1.8</v>
+        <v>2.92</v>
       </c>
       <c r="R125" s="23" t="inlineStr">
         <is>
@@ -13683,10 +13665,10 @@
       </c>
       <c r="N126" s="2" t="n"/>
       <c r="O126" s="32" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="P126" s="32" t="n">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="Q126" s="32" t="n"/>
       <c r="R126" s="23" t="inlineStr">
@@ -13793,13 +13775,13 @@
       </c>
       <c r="N127" s="2" t="n"/>
       <c r="O127" s="32" t="n">
-        <v>0.4</v>
+        <v>1.3</v>
       </c>
       <c r="P127" s="32" t="n">
-        <v>12.2</v>
+        <v>8.9</v>
       </c>
       <c r="Q127" s="32" t="n">
-        <v>6.54</v>
+        <v>5.25</v>
       </c>
       <c r="R127" s="23" t="inlineStr">
         <is>
@@ -13913,10 +13895,10 @@
       </c>
       <c r="N128" s="2" t="n"/>
       <c r="O128" s="32" t="n">
-        <v>1.7</v>
+        <v>0.2</v>
       </c>
       <c r="P128" s="32" t="n">
-        <v>4.7</v>
+        <v>2.2</v>
       </c>
       <c r="Q128" s="32" t="n"/>
       <c r="R128" s="23" t="inlineStr">
@@ -14023,13 +14005,13 @@
       </c>
       <c r="N129" s="2" t="n"/>
       <c r="O129" s="32" t="n">
-        <v>2.3</v>
+        <v>0.3</v>
       </c>
       <c r="P129" s="32" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="Q129" s="32" t="n">
-        <v>2.66</v>
+        <v>2.59</v>
       </c>
       <c r="R129" s="23" t="inlineStr">
         <is>
@@ -14143,13 +14125,13 @@
       </c>
       <c r="N130" s="2" t="n"/>
       <c r="O130" s="32" t="n">
-        <v>-3.6</v>
+        <v>-3.7</v>
       </c>
       <c r="P130" s="32" t="n">
-        <v>10.9</v>
+        <v>13.6</v>
       </c>
       <c r="Q130" s="32" t="n">
-        <v>3.52</v>
+        <v>3.15</v>
       </c>
       <c r="R130" s="23" t="inlineStr">
         <is>
@@ -14263,13 +14245,13 @@
       </c>
       <c r="N131" s="2" t="n"/>
       <c r="O131" s="32" t="n">
-        <v>3.9</v>
+        <v>1.7</v>
       </c>
       <c r="P131" s="32" t="n">
-        <v>11.5</v>
+        <v>5.1</v>
       </c>
       <c r="Q131" s="32" t="n">
-        <v>6.14</v>
+        <v>2.79</v>
       </c>
       <c r="R131" s="23" t="inlineStr">
         <is>
@@ -14379,13 +14361,13 @@
       </c>
       <c r="N132" s="2" t="n"/>
       <c r="O132" s="32" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="P132" s="32" t="n">
         <v>3.3</v>
       </c>
-      <c r="P132" s="32" t="n">
-        <v>9.199999999999999</v>
-      </c>
       <c r="Q132" s="32" t="n">
-        <v>5.3</v>
+        <v>1.96</v>
       </c>
       <c r="R132" s="23" t="inlineStr">
         <is>
@@ -14495,13 +14477,13 @@
       </c>
       <c r="N133" s="2" t="n"/>
       <c r="O133" s="32" t="n">
-        <v>6.5</v>
+        <v>3.4</v>
       </c>
       <c r="P133" s="32" t="n">
-        <v>9.5</v>
+        <v>7.5</v>
       </c>
       <c r="Q133" s="32" t="n">
-        <v>7.74</v>
+        <v>4.4</v>
       </c>
       <c r="R133" s="23" t="inlineStr">
         <is>
@@ -14717,13 +14699,13 @@
       </c>
       <c r="N135" s="2" t="n"/>
       <c r="O135" s="32" t="n">
-        <v>8.699999999999999</v>
+        <v>8</v>
       </c>
       <c r="P135" s="32" t="n">
-        <v>10.9</v>
+        <v>10.7</v>
       </c>
       <c r="Q135" s="32" t="n">
-        <v>9.49</v>
+        <v>9.84</v>
       </c>
       <c r="R135" s="23" t="inlineStr">
         <is>
@@ -14833,13 +14815,13 @@
       </c>
       <c r="N136" s="2" t="n"/>
       <c r="O136" s="32" t="n">
-        <v>10</v>
+        <v>12.1</v>
       </c>
       <c r="P136" s="32" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="Q136" s="32" t="n">
-        <v>11.55</v>
+        <v>12.81</v>
       </c>
       <c r="R136" s="23" t="inlineStr">
         <is>
@@ -14949,13 +14931,13 @@
       </c>
       <c r="N137" s="2" t="n"/>
       <c r="O137" s="32" t="n">
-        <v>9.9</v>
+        <v>6.5</v>
       </c>
       <c r="P137" s="32" t="n">
-        <v>13.8</v>
+        <v>11.9</v>
       </c>
       <c r="Q137" s="32" t="n">
-        <v>11.42</v>
+        <v>9.15</v>
       </c>
       <c r="R137" s="23" t="inlineStr">
         <is>
@@ -15068,7 +15050,7 @@
         <v>8.699999999999999</v>
       </c>
       <c r="P138" s="32" t="n">
-        <v>13.8</v>
+        <v>11</v>
       </c>
       <c r="Q138" s="32" t="n"/>
       <c r="R138" s="23" t="inlineStr">
@@ -15179,13 +15161,13 @@
       </c>
       <c r="N139" s="2" t="n"/>
       <c r="O139" s="32" t="n">
-        <v>8.199999999999999</v>
+        <v>9.9</v>
       </c>
       <c r="P139" s="32" t="n">
-        <v>13.4</v>
+        <v>12</v>
       </c>
       <c r="Q139" s="32" t="n">
-        <v>10.49</v>
+        <v>11.09</v>
       </c>
       <c r="R139" s="23" t="inlineStr">
         <is>
@@ -15295,13 +15277,13 @@
       </c>
       <c r="N140" s="2" t="n"/>
       <c r="O140" s="32" t="n">
-        <v>9.5</v>
+        <v>10.7</v>
       </c>
       <c r="P140" s="32" t="n">
-        <v>12.8</v>
+        <v>14</v>
       </c>
       <c r="Q140" s="32" t="n">
-        <v>10.96</v>
+        <v>12.1</v>
       </c>
       <c r="R140" s="23" t="inlineStr">
         <is>
@@ -15513,13 +15495,13 @@
       </c>
       <c r="N142" s="2" t="n"/>
       <c r="O142" s="32" t="n">
-        <v>12.8</v>
+        <v>14</v>
       </c>
       <c r="P142" s="32" t="n">
-        <v>15.7</v>
+        <v>17.7</v>
       </c>
       <c r="Q142" s="32" t="n">
-        <v>14.18</v>
+        <v>15.39</v>
       </c>
       <c r="R142" s="23" t="inlineStr">
         <is>
@@ -15629,13 +15611,13 @@
       </c>
       <c r="N143" s="2" t="n"/>
       <c r="O143" s="32" t="n">
-        <v>19.8</v>
+        <v>19</v>
       </c>
       <c r="P143" s="32" t="n">
-        <v>23.2</v>
+        <v>23.1</v>
       </c>
       <c r="Q143" s="32" t="n">
-        <v>21.25</v>
+        <v>20.9</v>
       </c>
       <c r="R143" s="23" t="inlineStr">
         <is>
@@ -15945,13 +15927,13 @@
       </c>
       <c r="N146" s="2" t="n"/>
       <c r="O146" s="32" t="n">
-        <v>23.6</v>
+        <v>26</v>
       </c>
       <c r="P146" s="32" t="n">
-        <v>30</v>
+        <v>30.9</v>
       </c>
       <c r="Q146" s="32" t="n">
-        <v>26.95</v>
+        <v>28.49</v>
       </c>
       <c r="R146" s="23" t="inlineStr">
         <is>
@@ -16053,13 +16035,13 @@
       </c>
       <c r="N147" s="2" t="n"/>
       <c r="O147" s="32" t="n">
-        <v>21.3</v>
+        <v>22.9</v>
       </c>
       <c r="P147" s="32" t="n">
-        <v>25.6</v>
+        <v>30.5</v>
       </c>
       <c r="Q147" s="32" t="n">
-        <v>22.8</v>
+        <v>25.49</v>
       </c>
       <c r="R147" s="23" t="inlineStr">
         <is>
@@ -16271,13 +16253,13 @@
       </c>
       <c r="N149" s="2" t="n"/>
       <c r="O149" s="32" t="n">
-        <v>8.800000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="P149" s="32" t="n">
-        <v>18.5</v>
+        <v>21.7</v>
       </c>
       <c r="Q149" s="32" t="n">
-        <v>13.96</v>
+        <v>14.55</v>
       </c>
       <c r="R149" s="23" t="inlineStr">
         <is>
@@ -16387,13 +16369,13 @@
       </c>
       <c r="N150" s="2" t="n"/>
       <c r="O150" s="32" t="n">
-        <v>8</v>
+        <v>7.2</v>
       </c>
       <c r="P150" s="32" t="n">
-        <v>22.4</v>
+        <v>13.3</v>
       </c>
       <c r="Q150" s="32" t="n">
-        <v>12.06</v>
+        <v>9.029999999999999</v>
       </c>
       <c r="R150" s="23" t="inlineStr">
         <is>
@@ -16503,13 +16485,13 @@
       </c>
       <c r="N151" s="2" t="n"/>
       <c r="O151" s="32" t="n">
-        <v>15.6</v>
+        <v>14.8</v>
       </c>
       <c r="P151" s="32" t="n">
-        <v>18.5</v>
+        <v>16.5</v>
       </c>
       <c r="Q151" s="32" t="n">
-        <v>16.64</v>
+        <v>15.45</v>
       </c>
       <c r="R151" s="23" t="inlineStr">
         <is>
@@ -16709,13 +16691,13 @@
       </c>
       <c r="N153" s="2" t="n"/>
       <c r="O153" s="32" t="n">
-        <v>12.9</v>
+        <v>11.2</v>
       </c>
       <c r="P153" s="32" t="n">
-        <v>15.4</v>
+        <v>17.8</v>
       </c>
       <c r="Q153" s="32" t="n">
-        <v>13.57</v>
+        <v>13.61</v>
       </c>
       <c r="R153" s="23" t="inlineStr">
         <is>
@@ -16829,13 +16811,13 @@
       </c>
       <c r="N154" s="2" t="n"/>
       <c r="O154" s="32" t="n">
-        <v>-0.7</v>
+        <v>1.5</v>
       </c>
       <c r="P154" s="32" t="n">
-        <v>16.8</v>
+        <v>13.9</v>
       </c>
       <c r="Q154" s="32" t="n">
-        <v>7.68</v>
+        <v>8.06</v>
       </c>
       <c r="R154" s="23" t="inlineStr">
         <is>
@@ -17031,10 +17013,10 @@
       </c>
       <c r="N156" s="2" t="n"/>
       <c r="O156" s="32" t="n">
-        <v>-2.9</v>
+        <v>-5.5</v>
       </c>
       <c r="P156" s="32" t="n">
-        <v>4</v>
+        <v>7.6</v>
       </c>
       <c r="Q156" s="32" t="n"/>
       <c r="R156" s="23" t="inlineStr">
@@ -17137,10 +17119,10 @@
       </c>
       <c r="N157" s="2" t="n"/>
       <c r="O157" s="32" t="n">
-        <v>8.6</v>
+        <v>11.6</v>
       </c>
       <c r="P157" s="32" t="n">
-        <v>14</v>
+        <v>13.3</v>
       </c>
       <c r="Q157" s="32" t="n"/>
       <c r="R157" s="23" t="inlineStr">
@@ -17525,10 +17507,10 @@
       </c>
       <c r="N161" s="2" t="n"/>
       <c r="O161" s="32" t="n">
-        <v>1.7</v>
+        <v>4.1</v>
       </c>
       <c r="P161" s="32" t="n">
-        <v>13.7</v>
+        <v>16.4</v>
       </c>
       <c r="Q161" s="32" t="n"/>
       <c r="R161" s="23" t="inlineStr">
@@ -17638,12 +17620,8 @@
           <t>⚡</t>
         </is>
       </c>
-      <c r="O162" s="32" t="n">
-        <v>-43.5</v>
-      </c>
-      <c r="P162" s="32" t="n">
-        <v>-12.2</v>
-      </c>
+      <c r="O162" s="32" t="n"/>
+      <c r="P162" s="32" t="n"/>
       <c r="Q162" s="32" t="n"/>
       <c r="R162" s="23" t="inlineStr">
         <is>
@@ -17969,10 +17947,10 @@
         </is>
       </c>
       <c r="O165" s="32" t="n">
-        <v>-44.2</v>
+        <v>-31.3</v>
       </c>
       <c r="P165" s="32" t="n">
-        <v>-17.7</v>
+        <v>-10.3</v>
       </c>
       <c r="Q165" s="32" t="n"/>
       <c r="R165" s="23" t="inlineStr">
@@ -18295,7 +18273,7 @@
         </is>
       </c>
       <c r="O168" s="32" t="n">
-        <v>-32.7</v>
+        <v>-21.6</v>
       </c>
       <c r="P168" s="32" t="n">
         <v>-9.4</v>
@@ -18409,10 +18387,10 @@
         </is>
       </c>
       <c r="O169" s="32" t="n">
-        <v>-26.9</v>
+        <v>-33.6</v>
       </c>
       <c r="P169" s="32" t="n">
-        <v>-11.1</v>
+        <v>-12.9</v>
       </c>
       <c r="Q169" s="32" t="n"/>
       <c r="R169" s="23" t="inlineStr">
@@ -18522,8 +18500,12 @@
           <t>⚡</t>
         </is>
       </c>
-      <c r="O170" s="32" t="n"/>
-      <c r="P170" s="32" t="n"/>
+      <c r="O170" s="32" t="n">
+        <v>-33.3</v>
+      </c>
+      <c r="P170" s="32" t="n">
+        <v>-19.4</v>
+      </c>
       <c r="Q170" s="32" t="n"/>
       <c r="R170" s="23" t="inlineStr">
         <is>
@@ -18735,10 +18717,10 @@
       </c>
       <c r="N172" s="3" t="n"/>
       <c r="O172" s="32" t="n">
-        <v>-20.5</v>
+        <v>-22.5</v>
       </c>
       <c r="P172" s="32" t="n">
-        <v>-6.1</v>
+        <v>-6.6</v>
       </c>
       <c r="Q172" s="32" t="n"/>
       <c r="R172" s="23" t="inlineStr">
@@ -18845,10 +18827,10 @@
       </c>
       <c r="N173" s="2" t="n"/>
       <c r="O173" s="32" t="n">
-        <v>-11.5</v>
+        <v>-8.699999999999999</v>
       </c>
       <c r="P173" s="32" t="n">
-        <v>-5.5</v>
+        <v>4.1</v>
       </c>
       <c r="Q173" s="32" t="n"/>
       <c r="R173" s="23" t="inlineStr">
@@ -19167,10 +19149,10 @@
       </c>
       <c r="N176" s="2" t="n"/>
       <c r="O176" s="32" t="n">
-        <v>4.4</v>
+        <v>6.8</v>
       </c>
       <c r="P176" s="32" t="n">
-        <v>10.9</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="Q176" s="32" t="n"/>
       <c r="R176" s="23" t="inlineStr">
@@ -19269,10 +19251,10 @@
       </c>
       <c r="N177" s="2" t="n"/>
       <c r="O177" s="32" t="n">
-        <v>-15.4</v>
+        <v>-13.5</v>
       </c>
       <c r="P177" s="32" t="n">
-        <v>-8.5</v>
+        <v>-9.1</v>
       </c>
       <c r="Q177" s="32" t="n"/>
       <c r="R177" s="23" t="inlineStr">
@@ -19382,12 +19364,8 @@
         </is>
       </c>
       <c r="N178" s="2" t="n"/>
-      <c r="O178" s="32" t="n">
-        <v>-32.2</v>
-      </c>
-      <c r="P178" s="32" t="n">
-        <v>-11.5</v>
-      </c>
+      <c r="O178" s="32" t="n"/>
+      <c r="P178" s="32" t="n"/>
       <c r="Q178" s="32" t="n"/>
       <c r="R178" s="23" t="inlineStr">
         <is>
@@ -20164,13 +20142,13 @@
       </c>
       <c r="N186" s="2" t="n"/>
       <c r="O186" s="32" t="n">
-        <v>-36.8</v>
+        <v>-34.5</v>
       </c>
       <c r="P186" s="32" t="n">
-        <v>-21.6</v>
+        <v>-19.6</v>
       </c>
       <c r="Q186" s="32" t="n">
-        <v>-30.18</v>
+        <v>-25.5</v>
       </c>
       <c r="R186" s="23" t="inlineStr">
         <is>
@@ -20273,13 +20251,13 @@
       </c>
       <c r="N187" s="2" t="n"/>
       <c r="O187" s="32" t="n">
-        <v>-36.5</v>
+        <v>-37.4</v>
       </c>
       <c r="P187" s="32" t="n">
-        <v>-21.2</v>
+        <v>-19</v>
       </c>
       <c r="Q187" s="32" t="n">
-        <v>-30.03</v>
+        <v>-28.74</v>
       </c>
       <c r="R187" s="23" t="inlineStr">
         <is>
@@ -20380,10 +20358,10 @@
         <v>-38</v>
       </c>
       <c r="P188" s="32" t="n">
-        <v>-26.2</v>
+        <v>-25</v>
       </c>
       <c r="Q188" s="32" t="n">
-        <v>-35.39</v>
+        <v>-31.74</v>
       </c>
       <c r="R188" s="23" t="inlineStr">
         <is>
@@ -20481,13 +20459,13 @@
       </c>
       <c r="N189" s="2" t="n"/>
       <c r="O189" s="32" t="n">
-        <v>-38.8</v>
+        <v>-38.1</v>
       </c>
       <c r="P189" s="32" t="n">
-        <v>-18</v>
+        <v>-19.4</v>
       </c>
       <c r="Q189" s="32" t="n">
-        <v>-29.42</v>
+        <v>-30.2</v>
       </c>
       <c r="R189" s="23" t="inlineStr">
         <is>
@@ -20585,13 +20563,13 @@
       </c>
       <c r="N190" s="2" t="n"/>
       <c r="O190" s="32" t="n">
-        <v>-33.1</v>
+        <v>-40.6</v>
       </c>
       <c r="P190" s="32" t="n">
-        <v>-24.9</v>
+        <v>-25.4</v>
       </c>
       <c r="Q190" s="32" t="n">
-        <v>-29.8</v>
+        <v>-33.62</v>
       </c>
       <c r="R190" s="23" t="inlineStr">
         <is>
@@ -20689,13 +20667,13 @@
       </c>
       <c r="N191" s="2" t="n"/>
       <c r="O191" s="32" t="n">
-        <v>-37.7</v>
+        <v>-36.3</v>
       </c>
       <c r="P191" s="32" t="n">
-        <v>-21</v>
+        <v>-19.8</v>
       </c>
       <c r="Q191" s="32" t="n">
-        <v>-31.31</v>
+        <v>-27.85</v>
       </c>
       <c r="R191" s="23" t="inlineStr">
         <is>
@@ -20789,13 +20767,13 @@
       </c>
       <c r="N192" s="2" t="n"/>
       <c r="O192" s="32" t="n">
-        <v>-39.1</v>
+        <v>-40.1</v>
       </c>
       <c r="P192" s="32" t="n">
-        <v>-27.2</v>
+        <v>-25.1</v>
       </c>
       <c r="Q192" s="32" t="n">
-        <v>-33.09</v>
+        <v>-34.35</v>
       </c>
       <c r="R192" s="23" t="inlineStr">
         <is>
@@ -20894,13 +20872,13 @@
       </c>
       <c r="N193" s="2" t="n"/>
       <c r="O193" s="32" t="n">
-        <v>-28.1</v>
+        <v>-35.6</v>
       </c>
       <c r="P193" s="32" t="n">
-        <v>-17.5</v>
+        <v>-21.8</v>
       </c>
       <c r="Q193" s="32" t="n">
-        <v>-20.65</v>
+        <v>-29.26</v>
       </c>
       <c r="R193" s="23" t="inlineStr">
         <is>
@@ -21002,10 +20980,10 @@
       </c>
       <c r="N194" s="2" t="n"/>
       <c r="O194" s="32" t="n">
-        <v>-37.5</v>
+        <v>-41</v>
       </c>
       <c r="P194" s="32" t="n">
-        <v>-27.6</v>
+        <v>-29.5</v>
       </c>
       <c r="Q194" s="32" t="n"/>
       <c r="R194" s="23" t="inlineStr">
@@ -21100,13 +21078,13 @@
       </c>
       <c r="N195" s="2" t="n"/>
       <c r="O195" s="32" t="n">
-        <v>-32.2</v>
+        <v>-33.9</v>
       </c>
       <c r="P195" s="32" t="n">
-        <v>-17.8</v>
+        <v>-15.9</v>
       </c>
       <c r="Q195" s="32" t="n">
-        <v>-26.04</v>
+        <v>-26.7</v>
       </c>
       <c r="R195" s="23" t="inlineStr">
         <is>
@@ -21204,13 +21182,13 @@
       </c>
       <c r="N196" s="2" t="n"/>
       <c r="O196" s="32" t="n">
-        <v>-34.4</v>
+        <v>-35.2</v>
       </c>
       <c r="P196" s="32" t="n">
-        <v>-17.9</v>
+        <v>-18.5</v>
       </c>
       <c r="Q196" s="32" t="n">
-        <v>-28.14</v>
+        <v>-28.1</v>
       </c>
       <c r="R196" s="23" t="inlineStr">
         <is>
@@ -21308,13 +21286,13 @@
       </c>
       <c r="N197" s="24" t="n"/>
       <c r="O197" s="32" t="n">
-        <v>-27.7</v>
+        <v>-35.2</v>
       </c>
       <c r="P197" s="32" t="n">
-        <v>-15.8</v>
+        <v>-20.4</v>
       </c>
       <c r="Q197" s="32" t="n">
-        <v>-21.68</v>
+        <v>-28.54</v>
       </c>
       <c r="R197" s="23" t="inlineStr">
         <is>
@@ -21403,8 +21381,12 @@
         </is>
       </c>
       <c r="N198" s="2" t="n"/>
-      <c r="O198" s="32" t="n"/>
-      <c r="P198" s="32" t="n"/>
+      <c r="O198" s="32" t="n">
+        <v>-40.3</v>
+      </c>
+      <c r="P198" s="32" t="n">
+        <v>-14.3</v>
+      </c>
       <c r="Q198" s="32" t="n"/>
       <c r="R198" s="23" t="inlineStr">
         <is>
@@ -21505,12 +21487,8 @@
         </is>
       </c>
       <c r="N199" s="2" t="n"/>
-      <c r="O199" s="32" t="n">
-        <v>-39.8</v>
-      </c>
-      <c r="P199" s="32" t="n">
-        <v>-11.4</v>
-      </c>
+      <c r="O199" s="32" t="n"/>
+      <c r="P199" s="32" t="n"/>
       <c r="Q199" s="32" t="n"/>
       <c r="R199" s="23" t="inlineStr">
         <is>
@@ -22322,10 +22300,10 @@
       </c>
       <c r="N207" s="2" t="n"/>
       <c r="O207" s="32" t="n">
-        <v>-44</v>
+        <v>-41.2</v>
       </c>
       <c r="P207" s="32" t="n">
-        <v>-10</v>
+        <v>-6.8</v>
       </c>
       <c r="Q207" s="32" t="n"/>
       <c r="R207" s="23" t="inlineStr">
@@ -25675,12 +25653,8 @@
         </is>
       </c>
       <c r="N241" s="2" t="n"/>
-      <c r="O241" s="32" t="n">
-        <v>-40.7</v>
-      </c>
-      <c r="P241" s="32" t="n">
-        <v>-15.5</v>
-      </c>
+      <c r="O241" s="32" t="n"/>
+      <c r="P241" s="32" t="n"/>
       <c r="Q241" s="32" t="n"/>
       <c r="R241" s="23" t="inlineStr">
         <is>
@@ -26254,13 +26228,13 @@
       </c>
       <c r="N247" s="2" t="n"/>
       <c r="O247" s="32" t="n">
-        <v>-27.3</v>
+        <v>-24.5</v>
       </c>
       <c r="P247" s="32" t="n">
-        <v>-18.1</v>
+        <v>-13.1</v>
       </c>
       <c r="Q247" s="32" t="n">
-        <v>-23.49</v>
+        <v>-19.73</v>
       </c>
       <c r="R247" s="23" t="inlineStr">
         <is>
@@ -26366,13 +26340,13 @@
       </c>
       <c r="N248" s="2" t="n"/>
       <c r="O248" s="32" t="n">
-        <v>-41.8</v>
+        <v>-33.6</v>
       </c>
       <c r="P248" s="32" t="n">
-        <v>-23.7</v>
+        <v>-20.1</v>
       </c>
       <c r="Q248" s="32" t="n">
-        <v>-33.75</v>
+        <v>-25.31</v>
       </c>
       <c r="R248" s="23" t="inlineStr">
         <is>
@@ -26474,13 +26448,13 @@
       </c>
       <c r="N249" s="2" t="n"/>
       <c r="O249" s="32" t="n">
-        <v>-8.699999999999999</v>
+        <v>-10.8</v>
       </c>
       <c r="P249" s="32" t="n">
-        <v>-4.4</v>
+        <v>-5.4</v>
       </c>
       <c r="Q249" s="32" t="n">
-        <v>-7.17</v>
+        <v>-8.56</v>
       </c>
       <c r="R249" s="23" t="inlineStr">
         <is>
@@ -26586,13 +26560,13 @@
       </c>
       <c r="N250" s="2" t="n"/>
       <c r="O250" s="32" t="n">
-        <v>-31.7</v>
+        <v>-29</v>
       </c>
       <c r="P250" s="32" t="n">
-        <v>-15.5</v>
+        <v>-12.6</v>
       </c>
       <c r="Q250" s="32" t="n">
-        <v>-23.89</v>
+        <v>-20.46</v>
       </c>
       <c r="R250" s="23" t="inlineStr">
         <is>
@@ -26706,10 +26680,10 @@
         </is>
       </c>
       <c r="O251" s="32" t="n">
-        <v>-34.2</v>
+        <v>-40.4</v>
       </c>
       <c r="P251" s="32" t="n">
-        <v>-19.4</v>
+        <v>-23.7</v>
       </c>
       <c r="Q251" s="32" t="n"/>
       <c r="R251" s="23" t="inlineStr">
@@ -26804,13 +26778,13 @@
       </c>
       <c r="N252" s="2" t="n"/>
       <c r="O252" s="32" t="n">
-        <v>-31</v>
+        <v>-27.8</v>
       </c>
       <c r="P252" s="32" t="n">
-        <v>-16.5</v>
+        <v>-16.8</v>
       </c>
       <c r="Q252" s="32" t="n">
-        <v>-24.32</v>
+        <v>-22.83</v>
       </c>
       <c r="R252" s="23" t="inlineStr">
         <is>
@@ -27002,13 +26976,13 @@
       </c>
       <c r="N254" s="2" t="n"/>
       <c r="O254" s="32" t="n">
-        <v>-34</v>
+        <v>-31.5</v>
       </c>
       <c r="P254" s="32" t="n">
-        <v>-20.8</v>
+        <v>-22</v>
       </c>
       <c r="Q254" s="32" t="n">
-        <v>-26.44</v>
+        <v>-26.21</v>
       </c>
       <c r="R254" s="23" t="inlineStr">
         <is>
@@ -27576,13 +27550,13 @@
       </c>
       <c r="N260" s="2" t="n"/>
       <c r="O260" s="32" t="n">
-        <v>-32.9</v>
+        <v>-33.6</v>
       </c>
       <c r="P260" s="32" t="n">
-        <v>-13.2</v>
+        <v>-13.8</v>
       </c>
       <c r="Q260" s="32" t="n">
-        <v>-23.09</v>
+        <v>-24.99</v>
       </c>
       <c r="R260" s="23" t="inlineStr">
         <is>
@@ -27684,13 +27658,13 @@
       </c>
       <c r="N261" s="2" t="n"/>
       <c r="O261" s="32" t="n">
-        <v>-34.8</v>
+        <v>-27.1</v>
       </c>
       <c r="P261" s="32" t="n">
-        <v>-13.7</v>
+        <v>-12.2</v>
       </c>
       <c r="Q261" s="32" t="n">
-        <v>-24.82</v>
+        <v>-19.44</v>
       </c>
       <c r="R261" s="23" t="inlineStr">
         <is>
@@ -27796,13 +27770,13 @@
       </c>
       <c r="N262" s="2" t="n"/>
       <c r="O262" s="32" t="n">
-        <v>-25.9</v>
+        <v>-34</v>
       </c>
       <c r="P262" s="32" t="n">
-        <v>-21</v>
+        <v>-21.9</v>
       </c>
       <c r="Q262" s="32" t="n">
-        <v>-23.68</v>
+        <v>-28.25</v>
       </c>
       <c r="R262" s="23" t="inlineStr">
         <is>
@@ -28002,13 +27976,13 @@
       </c>
       <c r="N264" s="2" t="n"/>
       <c r="O264" s="32" t="n">
-        <v>-27.8</v>
+        <v>-26.8</v>
       </c>
       <c r="P264" s="32" t="n">
-        <v>-16.9</v>
+        <v>-12.1</v>
       </c>
       <c r="Q264" s="32" t="n">
-        <v>-22.02</v>
+        <v>-19.74</v>
       </c>
       <c r="R264" s="23" t="inlineStr">
         <is>
@@ -28122,10 +28096,10 @@
       </c>
       <c r="N265" s="2" t="n"/>
       <c r="O265" s="32" t="n">
-        <v>-51.1</v>
+        <v>-56.3</v>
       </c>
       <c r="P265" s="32" t="n">
-        <v>-43.6</v>
+        <v>-47.4</v>
       </c>
       <c r="Q265" s="32" t="n"/>
       <c r="R265" s="23" t="inlineStr">
@@ -29166,13 +29140,13 @@
       </c>
       <c r="N276" s="2" t="n"/>
       <c r="O276" s="32" t="n">
-        <v>-43.6</v>
+        <v>-41.8</v>
       </c>
       <c r="P276" s="32" t="n">
-        <v>-31.1</v>
+        <v>-28.8</v>
       </c>
       <c r="Q276" s="32" t="n">
-        <v>-37.93</v>
+        <v>-37.06</v>
       </c>
       <c r="R276" s="23" t="inlineStr">
         <is>
@@ -30633,37 +30607,103 @@
       <c r="AH291" s="2" t="n"/>
     </row>
     <row r="292" ht="24" customHeight="1" s="48">
-      <c r="A292" s="2" t="n"/>
+      <c r="A292" s="2" t="n">
+        <v>291</v>
+      </c>
       <c r="B292" s="2" t="n"/>
       <c r="C292" s="46" t="n"/>
       <c r="D292" s="2" t="n"/>
       <c r="E292" s="4" t="n"/>
-      <c r="F292" s="39" t="n"/>
-      <c r="G292" s="29" t="n"/>
-      <c r="H292" s="29" t="n"/>
-      <c r="I292" s="2" t="n"/>
-      <c r="J292" s="27" t="n"/>
-      <c r="K292" s="4" t="n"/>
+      <c r="F292" s="39" t="inlineStr">
+        <is>
+          <t>C0059</t>
+        </is>
+      </c>
+      <c r="G292" s="29" t="n">
+        <v>50.0086</v>
+      </c>
+      <c r="H292" s="29" t="n">
+        <v>125.0403</v>
+      </c>
+      <c r="I292" s="2" t="n">
+        <v>365</v>
+      </c>
+      <c r="J292" s="27" t="n">
+        <v>12</v>
+      </c>
+      <c r="K292" s="31" t="inlineStr">
+        <is>
+          <t>🇨🇳</t>
+        </is>
+      </c>
       <c r="L292" s="2" t="n"/>
-      <c r="M292" s="14" t="n"/>
+      <c r="M292" s="14" t="inlineStr">
+        <is>
+          <t>古里农场</t>
+        </is>
+      </c>
       <c r="N292" s="2" t="n"/>
-      <c r="O292" s="32" t="n"/>
-      <c r="P292" s="32" t="n"/>
+      <c r="O292" s="32" t="n">
+        <v>-39.8</v>
+      </c>
+      <c r="P292" s="32" t="n">
+        <v>-11.4</v>
+      </c>
       <c r="Q292" s="32" t="n"/>
-      <c r="R292" s="23" t="n"/>
+      <c r="R292" s="23" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="S292" s="37" t="n"/>
-      <c r="T292" s="41" t="n"/>
-      <c r="U292" s="2" t="n"/>
-      <c r="V292" s="4" t="n"/>
-      <c r="W292" s="4" t="n"/>
-      <c r="X292" s="4" t="n"/>
+      <c r="T292" s="41" t="inlineStr">
+        <is>
+          <t>呼伦贝尔</t>
+        </is>
+      </c>
+      <c r="U292" s="2" t="inlineStr">
+        <is>
+          <t>内蒙古</t>
+        </is>
+      </c>
+      <c r="V292" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="W292" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="X292" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="Y292" s="4" t="n"/>
-      <c r="Z292" s="2" t="n"/>
-      <c r="AA292" s="2" t="n"/>
+      <c r="Z292" s="2" t="inlineStr">
+        <is>
+          <t>呼伦贝尔市</t>
+        </is>
+      </c>
+      <c r="AA292" s="2" t="inlineStr">
+        <is>
+          <t>鄂伦春自治旗</t>
+        </is>
+      </c>
       <c r="AB292" s="2" t="n"/>
       <c r="AC292" s="2" t="n"/>
-      <c r="AD292" s="2" t="n"/>
-      <c r="AE292" s="4" t="n"/>
+      <c r="AD292" s="2" t="inlineStr">
+        <is>
+          <t>中国</t>
+        </is>
+      </c>
+      <c r="AE292" s="4" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
       <c r="AF292" s="4" t="n"/>
       <c r="AG292" s="2" t="n"/>
       <c r="AH292" s="2" t="n"/>

--- a/气象/For_Python_站点信息和记录.xlsx
+++ b/气象/For_Python_站点信息和记录.xlsx
@@ -796,8 +796,8 @@
     <col width="18.59765625" customWidth="1" style="8" min="25" max="25"/>
     <col width="12.59765625" customWidth="1" style="5" min="26" max="30"/>
     <col width="12.59765625" customWidth="1" style="8" min="31" max="32"/>
-    <col width="12.59765625" customWidth="1" style="5" min="33" max="293"/>
-    <col width="12.59765625" customWidth="1" style="5" min="294" max="16384"/>
+    <col width="12.59765625" customWidth="1" style="5" min="33" max="297"/>
+    <col width="12.59765625" customWidth="1" style="5" min="298" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="27.75" customFormat="1" customHeight="1" s="11">
@@ -1020,13 +1020,13 @@
         </is>
       </c>
       <c r="O2" s="32" t="n">
-        <v>-33.8</v>
+        <v>-31</v>
       </c>
       <c r="P2" s="32" t="n">
-        <v>-21.4</v>
+        <v>-18.3</v>
       </c>
       <c r="Q2" s="32" t="n">
-        <v>-26.2</v>
+        <v>-24.39</v>
       </c>
       <c r="R2" s="23" t="inlineStr">
         <is>
@@ -1126,10 +1126,10 @@
         </is>
       </c>
       <c r="O3" s="32" t="n">
-        <v>-35.8</v>
+        <v>-33.4</v>
       </c>
       <c r="P3" s="32" t="n">
-        <v>-19.8</v>
+        <v>-16.8</v>
       </c>
       <c r="Q3" s="32" t="n"/>
       <c r="R3" s="23" t="n"/>
@@ -1322,10 +1322,10 @@
       </c>
       <c r="N5" s="2" t="n"/>
       <c r="O5" s="32" t="n">
-        <v>-26.2</v>
+        <v>-24.8</v>
       </c>
       <c r="P5" s="32" t="n">
-        <v>-12</v>
+        <v>-8.300000000000001</v>
       </c>
       <c r="Q5" s="32" t="n"/>
       <c r="R5" s="23" t="n"/>
@@ -1422,10 +1422,10 @@
         </is>
       </c>
       <c r="O6" s="32" t="n">
-        <v>-26.7</v>
+        <v>-28.5</v>
       </c>
       <c r="P6" s="32" t="n">
-        <v>-11.2</v>
+        <v>-9.800000000000001</v>
       </c>
       <c r="Q6" s="32" t="n"/>
       <c r="R6" s="23" t="n"/>
@@ -1522,10 +1522,10 @@
         </is>
       </c>
       <c r="O7" s="32" t="n">
-        <v>-30.4</v>
+        <v>-24.2</v>
       </c>
       <c r="P7" s="32" t="n">
-        <v>-16.4</v>
+        <v>-11.6</v>
       </c>
       <c r="Q7" s="32" t="n"/>
       <c r="R7" s="23" t="n"/>
@@ -1630,13 +1630,13 @@
       </c>
       <c r="N8" s="2" t="n"/>
       <c r="O8" s="32" t="n">
-        <v>-34.3</v>
+        <v>-23.9</v>
       </c>
       <c r="P8" s="32" t="n">
-        <v>-16.2</v>
+        <v>-8.1</v>
       </c>
       <c r="Q8" s="32" t="n">
-        <v>-26.34</v>
+        <v>-17.66</v>
       </c>
       <c r="R8" s="23" t="inlineStr">
         <is>
@@ -1742,13 +1742,13 @@
       </c>
       <c r="N9" s="2" t="n"/>
       <c r="O9" s="32" t="n">
-        <v>-33.7</v>
+        <v>-30</v>
       </c>
       <c r="P9" s="32" t="n">
-        <v>-18.2</v>
+        <v>-13</v>
       </c>
       <c r="Q9" s="32" t="n">
-        <v>-25.38</v>
+        <v>-21.81</v>
       </c>
       <c r="R9" s="23" t="inlineStr">
         <is>
@@ -1862,13 +1862,13 @@
         </is>
       </c>
       <c r="O10" s="32" t="n">
-        <v>-27</v>
+        <v>-26.9</v>
       </c>
       <c r="P10" s="32" t="n">
-        <v>-15.3</v>
+        <v>-11.3</v>
       </c>
       <c r="Q10" s="32" t="n">
-        <v>-22</v>
+        <v>-18.02</v>
       </c>
       <c r="R10" s="23" t="inlineStr">
         <is>
@@ -1978,13 +1978,13 @@
         </is>
       </c>
       <c r="O11" s="32" t="n">
-        <v>-28.6</v>
+        <v>-27</v>
       </c>
       <c r="P11" s="32" t="n">
-        <v>-13</v>
+        <v>-6.4</v>
       </c>
       <c r="Q11" s="32" t="n">
-        <v>-21.35</v>
+        <v>-17.17</v>
       </c>
       <c r="R11" s="23" t="inlineStr">
         <is>
@@ -2090,13 +2090,13 @@
       </c>
       <c r="N12" s="2" t="n"/>
       <c r="O12" s="32" t="n">
-        <v>-28.8</v>
+        <v>-26.1</v>
       </c>
       <c r="P12" s="32" t="n">
-        <v>-12.2</v>
+        <v>-6.5</v>
       </c>
       <c r="Q12" s="32" t="n">
-        <v>-21.64</v>
+        <v>-18.39</v>
       </c>
       <c r="R12" s="23" t="inlineStr">
         <is>
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="O13" s="32" t="n">
-        <v>-34.2</v>
+        <v>-24.9</v>
       </c>
       <c r="P13" s="32" t="n">
-        <v>-18.6</v>
+        <v>-7.9</v>
       </c>
       <c r="Q13" s="32" t="n">
-        <v>-27.46</v>
+        <v>-18.3</v>
       </c>
       <c r="R13" s="23" t="inlineStr">
         <is>
@@ -2318,13 +2318,13 @@
       </c>
       <c r="N14" s="2" t="n"/>
       <c r="O14" s="32" t="n">
-        <v>-21.3</v>
+        <v>-12.7</v>
       </c>
       <c r="P14" s="32" t="n">
-        <v>-9.300000000000001</v>
+        <v>0.9</v>
       </c>
       <c r="Q14" s="32" t="n">
-        <v>-16.03</v>
+        <v>-7.48</v>
       </c>
       <c r="R14" s="23" t="inlineStr">
         <is>
@@ -2423,12 +2423,8 @@
         </is>
       </c>
       <c r="N15" s="2" t="n"/>
-      <c r="O15" s="32" t="n">
-        <v>-32.9</v>
-      </c>
-      <c r="P15" s="32" t="n">
-        <v>-11.2</v>
-      </c>
+      <c r="O15" s="32" t="n"/>
+      <c r="P15" s="32" t="n"/>
       <c r="Q15" s="32" t="n"/>
       <c r="R15" s="23" t="n"/>
       <c r="S15" s="37" t="n"/>
@@ -4972,10 +4968,10 @@
         </is>
       </c>
       <c r="O43" s="32" t="n">
-        <v>-29.6</v>
+        <v>-29.7</v>
       </c>
       <c r="P43" s="32" t="n">
-        <v>-22.3</v>
+        <v>-19.1</v>
       </c>
       <c r="Q43" s="32" t="n"/>
       <c r="R43" s="23" t="n"/>
@@ -5251,12 +5247,8 @@
         </is>
       </c>
       <c r="N46" s="2" t="n"/>
-      <c r="O46" s="32" t="n">
-        <v>-31.4</v>
-      </c>
-      <c r="P46" s="32" t="n">
-        <v>-22.2</v>
-      </c>
+      <c r="O46" s="32" t="n"/>
+      <c r="P46" s="32" t="n"/>
       <c r="Q46" s="32" t="n"/>
       <c r="R46" s="23" t="n"/>
       <c r="S46" s="37" t="n"/>
@@ -7659,12 +7651,8 @@
         </is>
       </c>
       <c r="N73" s="2" t="n"/>
-      <c r="O73" s="32" t="n">
-        <v>-35.7</v>
-      </c>
-      <c r="P73" s="32" t="n">
-        <v>-14.6</v>
-      </c>
+      <c r="O73" s="32" t="n"/>
+      <c r="P73" s="32" t="n"/>
       <c r="Q73" s="32" t="n"/>
       <c r="R73" s="23" t="n"/>
       <c r="S73" s="37" t="n"/>
@@ -7846,13 +7834,13 @@
       </c>
       <c r="N75" s="2" t="n"/>
       <c r="O75" s="32" t="n">
-        <v>-10.1</v>
+        <v>-26.3</v>
       </c>
       <c r="P75" s="32" t="n">
-        <v>-0.9</v>
+        <v>-6.4</v>
       </c>
       <c r="Q75" s="32" t="n">
-        <v>-4.76</v>
+        <v>-16.85</v>
       </c>
       <c r="R75" s="23" t="inlineStr">
         <is>
@@ -7962,13 +7950,13 @@
         </is>
       </c>
       <c r="O76" s="32" t="n">
-        <v>-23</v>
+        <v>-26.6</v>
       </c>
       <c r="P76" s="32" t="n">
-        <v>-2.3</v>
+        <v>-7.9</v>
       </c>
       <c r="Q76" s="32" t="n">
-        <v>-12.99</v>
+        <v>-17.09</v>
       </c>
       <c r="R76" s="23" t="inlineStr">
         <is>
@@ -8078,13 +8066,13 @@
         </is>
       </c>
       <c r="O77" s="32" t="n">
-        <v>-12</v>
+        <v>-29.2</v>
       </c>
       <c r="P77" s="32" t="n">
-        <v>-4.2</v>
+        <v>-7.9</v>
       </c>
       <c r="Q77" s="32" t="n">
-        <v>-9.199999999999999</v>
+        <v>-19.35</v>
       </c>
       <c r="R77" s="23" t="inlineStr">
         <is>
@@ -8190,13 +8178,13 @@
       </c>
       <c r="N78" s="2" t="n"/>
       <c r="O78" s="32" t="n">
-        <v>-21.7</v>
+        <v>-26.1</v>
       </c>
       <c r="P78" s="32" t="n">
-        <v>-0.7</v>
+        <v>-7.2</v>
       </c>
       <c r="Q78" s="32" t="n">
-        <v>-12.03</v>
+        <v>-16.68</v>
       </c>
       <c r="R78" s="23" t="inlineStr">
         <is>
@@ -8306,13 +8294,13 @@
         </is>
       </c>
       <c r="O79" s="32" t="n">
-        <v>-26.6</v>
+        <v>-13.5</v>
       </c>
       <c r="P79" s="32" t="n">
-        <v>-8.699999999999999</v>
+        <v>-4.8</v>
       </c>
       <c r="Q79" s="32" t="n">
-        <v>-15.15</v>
+        <v>-9.34</v>
       </c>
       <c r="R79" s="23" t="inlineStr">
         <is>
@@ -8418,13 +8406,13 @@
       </c>
       <c r="N80" s="2" t="n"/>
       <c r="O80" s="32" t="n">
-        <v>-23.1</v>
+        <v>-25.2</v>
       </c>
       <c r="P80" s="32" t="n">
-        <v>-12</v>
+        <v>-4.2</v>
       </c>
       <c r="Q80" s="32" t="n">
-        <v>-18.2</v>
+        <v>-15.45</v>
       </c>
       <c r="R80" s="23" t="inlineStr">
         <is>
@@ -8534,13 +8522,13 @@
         </is>
       </c>
       <c r="O81" s="32" t="n">
-        <v>-35.5</v>
+        <v>-23</v>
       </c>
       <c r="P81" s="32" t="n">
-        <v>-12</v>
+        <v>-2.6</v>
       </c>
       <c r="Q81" s="32" t="n">
-        <v>-23.86</v>
+        <v>-14.1</v>
       </c>
       <c r="R81" s="23" t="inlineStr">
         <is>
@@ -8655,13 +8643,13 @@
         </is>
       </c>
       <c r="O82" s="32" t="n">
-        <v>-37.6</v>
+        <v>-25.5</v>
       </c>
       <c r="P82" s="32" t="n">
-        <v>-10.3</v>
+        <v>-2.5</v>
       </c>
       <c r="Q82" s="32" t="n">
-        <v>-26.01</v>
+        <v>-16.68</v>
       </c>
       <c r="R82" s="23" t="inlineStr">
         <is>
@@ -8767,13 +8755,13 @@
       </c>
       <c r="N83" s="2" t="n"/>
       <c r="O83" s="32" t="n">
-        <v>-31.7</v>
+        <v>-23.2</v>
       </c>
       <c r="P83" s="32" t="n">
-        <v>-15.1</v>
+        <v>-1.9</v>
       </c>
       <c r="Q83" s="32" t="n">
-        <v>-24.41</v>
+        <v>-15.07</v>
       </c>
       <c r="R83" s="23" t="inlineStr">
         <is>
@@ -8883,13 +8871,13 @@
         </is>
       </c>
       <c r="O84" s="32" t="n">
-        <v>-36.5</v>
+        <v>-19.5</v>
       </c>
       <c r="P84" s="32" t="n">
-        <v>-15.6</v>
+        <v>1</v>
       </c>
       <c r="Q84" s="32" t="n">
-        <v>-27.32</v>
+        <v>-11.66</v>
       </c>
       <c r="R84" s="23" t="inlineStr">
         <is>
@@ -8999,13 +8987,13 @@
         </is>
       </c>
       <c r="O85" s="32" t="n">
-        <v>-35.3</v>
+        <v>-17.9</v>
       </c>
       <c r="P85" s="32" t="n">
-        <v>-15.2</v>
+        <v>-4.8</v>
       </c>
       <c r="Q85" s="32" t="n">
-        <v>-26.14</v>
+        <v>-11.9</v>
       </c>
       <c r="R85" s="23" t="inlineStr">
         <is>
@@ -9111,13 +9099,13 @@
       </c>
       <c r="N86" s="2" t="n"/>
       <c r="O86" s="32" t="n">
-        <v>-29</v>
+        <v>-16.9</v>
       </c>
       <c r="P86" s="32" t="n">
-        <v>-14.3</v>
+        <v>-4.2</v>
       </c>
       <c r="Q86" s="32" t="n">
-        <v>-22.21</v>
+        <v>-11.3</v>
       </c>
       <c r="R86" s="23" t="inlineStr">
         <is>
@@ -9235,13 +9223,13 @@
         </is>
       </c>
       <c r="O87" s="32" t="n">
-        <v>-29.5</v>
+        <v>-26.8</v>
       </c>
       <c r="P87" s="32" t="n">
-        <v>-16.2</v>
+        <v>-12.7</v>
       </c>
       <c r="Q87" s="32" t="n">
-        <v>-24.02</v>
+        <v>-19.44</v>
       </c>
       <c r="R87" s="23" t="inlineStr">
         <is>
@@ -9347,13 +9335,13 @@
       </c>
       <c r="N88" s="2" t="n"/>
       <c r="O88" s="32" t="n">
-        <v>-23.1</v>
+        <v>-18.2</v>
       </c>
       <c r="P88" s="32" t="n">
-        <v>-7</v>
+        <v>-1.4</v>
       </c>
       <c r="Q88" s="32" t="n">
-        <v>-15.61</v>
+        <v>-10.45</v>
       </c>
       <c r="R88" s="23" t="inlineStr">
         <is>
@@ -9565,13 +9553,13 @@
         </is>
       </c>
       <c r="O90" s="32" t="n">
-        <v>-14.5</v>
+        <v>-16.1</v>
       </c>
       <c r="P90" s="32" t="n">
-        <v>-8</v>
+        <v>-0.9</v>
       </c>
       <c r="Q90" s="32" t="n">
-        <v>-11.94</v>
+        <v>-8.48</v>
       </c>
       <c r="R90" s="23" t="inlineStr">
         <is>
@@ -9673,13 +9661,13 @@
       </c>
       <c r="N91" s="2" t="n"/>
       <c r="O91" s="32" t="n">
-        <v>-20</v>
+        <v>-14</v>
       </c>
       <c r="P91" s="32" t="n">
-        <v>-12.3</v>
+        <v>-5.2</v>
       </c>
       <c r="Q91" s="32" t="n">
-        <v>-15.92</v>
+        <v>-8.67</v>
       </c>
       <c r="R91" s="23" t="inlineStr">
         <is>
@@ -9781,13 +9769,13 @@
       </c>
       <c r="N92" s="2" t="n"/>
       <c r="O92" s="32" t="n">
-        <v>-10.4</v>
+        <v>-27</v>
       </c>
       <c r="P92" s="32" t="n">
-        <v>-1.5</v>
+        <v>-6.5</v>
       </c>
       <c r="Q92" s="32" t="n">
-        <v>-6.11</v>
+        <v>-14.52</v>
       </c>
       <c r="R92" s="23" t="inlineStr">
         <is>
@@ -9893,13 +9881,13 @@
       </c>
       <c r="N93" s="2" t="n"/>
       <c r="O93" s="32" t="n">
-        <v>-13.3</v>
+        <v>-14.2</v>
       </c>
       <c r="P93" s="32" t="n">
-        <v>-1.1</v>
+        <v>2.8</v>
       </c>
       <c r="Q93" s="32" t="n">
-        <v>-5.71</v>
+        <v>-4.51</v>
       </c>
       <c r="R93" s="23" t="inlineStr">
         <is>
@@ -10013,10 +10001,10 @@
         </is>
       </c>
       <c r="O94" s="32" t="n">
-        <v>-15.3</v>
+        <v>-18.1</v>
       </c>
       <c r="P94" s="32" t="n">
-        <v>-1.3</v>
+        <v>0.9</v>
       </c>
       <c r="Q94" s="32" t="n"/>
       <c r="R94" s="23" t="inlineStr">
@@ -10131,13 +10119,13 @@
       </c>
       <c r="N95" s="2" t="n"/>
       <c r="O95" s="32" t="n">
-        <v>-12.1</v>
+        <v>-16.9</v>
       </c>
       <c r="P95" s="32" t="n">
-        <v>-3.5</v>
+        <v>-0.1</v>
       </c>
       <c r="Q95" s="32" t="n">
-        <v>-8.26</v>
+        <v>-7.65</v>
       </c>
       <c r="R95" s="23" t="inlineStr">
         <is>
@@ -10259,10 +10247,10 @@
         </is>
       </c>
       <c r="O96" s="32" t="n">
-        <v>-9.6</v>
+        <v>-15.5</v>
       </c>
       <c r="P96" s="32" t="n">
-        <v>-1.3</v>
+        <v>-0.6</v>
       </c>
       <c r="Q96" s="32" t="n"/>
       <c r="R96" s="23" t="inlineStr">
@@ -10377,13 +10365,13 @@
       </c>
       <c r="N97" s="2" t="n"/>
       <c r="O97" s="32" t="n">
-        <v>-14.4</v>
+        <v>-18.5</v>
       </c>
       <c r="P97" s="32" t="n">
-        <v>-5.2</v>
+        <v>-3.3</v>
       </c>
       <c r="Q97" s="32" t="n">
-        <v>-9.85</v>
+        <v>-11.44</v>
       </c>
       <c r="R97" s="23" t="inlineStr">
         <is>
@@ -10497,10 +10485,10 @@
       </c>
       <c r="N98" s="2" t="n"/>
       <c r="O98" s="32" t="n">
-        <v>-10.3</v>
+        <v>-28.1</v>
       </c>
       <c r="P98" s="32" t="n">
-        <v>-2.2</v>
+        <v>-6.6</v>
       </c>
       <c r="Q98" s="32" t="n"/>
       <c r="R98" s="23" t="inlineStr">
@@ -10615,13 +10603,13 @@
       </c>
       <c r="N99" s="2" t="n"/>
       <c r="O99" s="32" t="n">
-        <v>-20.6</v>
+        <v>-34.8</v>
       </c>
       <c r="P99" s="32" t="n">
-        <v>-6.6</v>
+        <v>-7.7</v>
       </c>
       <c r="Q99" s="32" t="n">
-        <v>-10.49</v>
+        <v>-23.24</v>
       </c>
       <c r="R99" s="23" t="inlineStr">
         <is>
@@ -10947,13 +10935,13 @@
       </c>
       <c r="N102" s="2" t="n"/>
       <c r="O102" s="32" t="n">
-        <v>-27.2</v>
+        <v>-33.4</v>
       </c>
       <c r="P102" s="32" t="n">
-        <v>-10.5</v>
+        <v>-2.6</v>
       </c>
       <c r="Q102" s="32" t="n">
-        <v>-20.2</v>
+        <v>-18.85</v>
       </c>
       <c r="R102" s="23" t="inlineStr">
         <is>
@@ -11063,10 +11051,10 @@
       </c>
       <c r="N103" s="2" t="n"/>
       <c r="O103" s="32" t="n">
-        <v>-25.1</v>
+        <v>-30.2</v>
       </c>
       <c r="P103" s="32" t="n">
-        <v>-9.699999999999999</v>
+        <v>-3.2</v>
       </c>
       <c r="Q103" s="32" t="n"/>
       <c r="R103" s="23" t="inlineStr">
@@ -11173,10 +11161,10 @@
       </c>
       <c r="N104" s="2" t="n"/>
       <c r="O104" s="32" t="n">
-        <v>-28.5</v>
+        <v>-32.6</v>
       </c>
       <c r="P104" s="32" t="n">
-        <v>-12.4</v>
+        <v>-6.7</v>
       </c>
       <c r="Q104" s="32" t="n"/>
       <c r="R104" s="23" t="inlineStr">
@@ -11299,13 +11287,13 @@
         </is>
       </c>
       <c r="O105" s="32" t="n">
-        <v>-29.3</v>
+        <v>-36</v>
       </c>
       <c r="P105" s="32" t="n">
-        <v>-13.8</v>
+        <v>-5.6</v>
       </c>
       <c r="Q105" s="32" t="n">
-        <v>-21.41</v>
+        <v>-21.76</v>
       </c>
       <c r="R105" s="23" t="inlineStr">
         <is>
@@ -11415,10 +11403,10 @@
         </is>
       </c>
       <c r="O106" s="32" t="n">
-        <v>-25.4</v>
+        <v>-32.4</v>
       </c>
       <c r="P106" s="32" t="n">
-        <v>-15.4</v>
+        <v>-13.9</v>
       </c>
       <c r="Q106" s="32" t="n"/>
       <c r="R106" s="23" t="inlineStr">
@@ -11635,13 +11623,13 @@
       </c>
       <c r="N108" s="2" t="n"/>
       <c r="O108" s="32" t="n">
-        <v>-25.9</v>
+        <v>-27.8</v>
       </c>
       <c r="P108" s="32" t="n">
-        <v>-17.7</v>
+        <v>-8.300000000000001</v>
       </c>
       <c r="Q108" s="32" t="n">
-        <v>-21.62</v>
+        <v>-19.24</v>
       </c>
       <c r="R108" s="23" t="inlineStr">
         <is>
@@ -11848,8 +11836,12 @@
         </is>
       </c>
       <c r="N110" s="2" t="n"/>
-      <c r="O110" s="32" t="n"/>
-      <c r="P110" s="32" t="n"/>
+      <c r="O110" s="32" t="n">
+        <v>-35.7</v>
+      </c>
+      <c r="P110" s="32" t="n">
+        <v>-8.6</v>
+      </c>
       <c r="Q110" s="32" t="n"/>
       <c r="R110" s="23" t="inlineStr">
         <is>
@@ -11963,13 +11955,13 @@
       </c>
       <c r="N111" s="2" t="n"/>
       <c r="O111" s="32" t="n">
-        <v>-28.3</v>
+        <v>-30</v>
       </c>
       <c r="P111" s="32" t="n">
-        <v>-14.6</v>
+        <v>-3.6</v>
       </c>
       <c r="Q111" s="32" t="n">
-        <v>-20.24</v>
+        <v>-17.61</v>
       </c>
       <c r="R111" s="23" t="inlineStr">
         <is>
@@ -12075,10 +12067,10 @@
       </c>
       <c r="N112" s="2" t="n"/>
       <c r="O112" s="32" t="n">
-        <v>-15.4</v>
+        <v>-16.8</v>
       </c>
       <c r="P112" s="32" t="n">
-        <v>-1.7</v>
+        <v>5</v>
       </c>
       <c r="Q112" s="32" t="n"/>
       <c r="R112" s="23" t="inlineStr">
@@ -12181,10 +12173,10 @@
       </c>
       <c r="N113" s="2" t="n"/>
       <c r="O113" s="32" t="n">
-        <v>-18.6</v>
+        <v>-9.4</v>
       </c>
       <c r="P113" s="32" t="n">
-        <v>4.1</v>
+        <v>9.4</v>
       </c>
       <c r="Q113" s="32" t="n"/>
       <c r="R113" s="23" t="inlineStr">
@@ -12295,10 +12287,10 @@
         </is>
       </c>
       <c r="O114" s="32" t="n">
-        <v>-25.3</v>
+        <v>-11</v>
       </c>
       <c r="P114" s="32" t="n">
-        <v>3.5</v>
+        <v>6.5</v>
       </c>
       <c r="Q114" s="32" t="n"/>
       <c r="R114" s="23" t="inlineStr">
@@ -12417,10 +12409,10 @@
         </is>
       </c>
       <c r="O115" s="32" t="n">
-        <v>-15.3</v>
+        <v>-11.7</v>
       </c>
       <c r="P115" s="32" t="n">
-        <v>0.4</v>
+        <v>3.5</v>
       </c>
       <c r="Q115" s="32" t="n"/>
       <c r="R115" s="23" t="inlineStr">
@@ -12535,13 +12527,13 @@
       </c>
       <c r="N116" s="2" t="n"/>
       <c r="O116" s="32" t="n">
-        <v>-7.8</v>
+        <v>-8.300000000000001</v>
       </c>
       <c r="P116" s="32" t="n">
-        <v>6.5</v>
+        <v>7.6</v>
       </c>
       <c r="Q116" s="32" t="n">
-        <v>-0.89</v>
+        <v>0.09</v>
       </c>
       <c r="R116" s="23" t="inlineStr">
         <is>
@@ -12647,10 +12639,10 @@
       </c>
       <c r="N117" s="2" t="n"/>
       <c r="O117" s="32" t="n">
-        <v>-10.1</v>
+        <v>-8.199999999999999</v>
       </c>
       <c r="P117" s="32" t="n">
-        <v>0.9</v>
+        <v>4.8</v>
       </c>
       <c r="Q117" s="32" t="n"/>
       <c r="R117" s="23" t="inlineStr">
@@ -12761,10 +12753,10 @@
         </is>
       </c>
       <c r="O118" s="32" t="n">
-        <v>-23.3</v>
+        <v>-15.1</v>
       </c>
       <c r="P118" s="32" t="n">
-        <v>-6.2</v>
+        <v>0.3</v>
       </c>
       <c r="Q118" s="32" t="n"/>
       <c r="R118" s="23" t="inlineStr">
@@ -12879,13 +12871,13 @@
       </c>
       <c r="N119" s="2" t="n"/>
       <c r="O119" s="32" t="n">
-        <v>-15.5</v>
+        <v>-10.7</v>
       </c>
       <c r="P119" s="32" t="n">
-        <v>-4.1</v>
+        <v>1.9</v>
       </c>
       <c r="Q119" s="32" t="n">
-        <v>-9.93</v>
+        <v>-4.68</v>
       </c>
       <c r="R119" s="23" t="inlineStr">
         <is>
@@ -13113,13 +13105,13 @@
       </c>
       <c r="N121" s="2" t="n"/>
       <c r="O121" s="32" t="n">
-        <v>-10.6</v>
+        <v>-3.6</v>
       </c>
       <c r="P121" s="32" t="n">
-        <v>-0.9</v>
+        <v>1.2</v>
       </c>
       <c r="Q121" s="32" t="n">
-        <v>-5.97</v>
+        <v>-1.3</v>
       </c>
       <c r="R121" s="23" t="inlineStr">
         <is>
@@ -13237,10 +13229,10 @@
       </c>
       <c r="N122" s="2" t="n"/>
       <c r="O122" s="32" t="n">
-        <v>-21.9</v>
+        <v>-13.9</v>
       </c>
       <c r="P122" s="32" t="n">
-        <v>-4.5</v>
+        <v>-1.4</v>
       </c>
       <c r="Q122" s="32" t="n"/>
       <c r="R122" s="23" t="inlineStr">
@@ -13461,13 +13453,13 @@
       </c>
       <c r="N124" s="2" t="n"/>
       <c r="O124" s="32" t="n">
-        <v>-5.6</v>
+        <v>-10.8</v>
       </c>
       <c r="P124" s="32" t="n">
-        <v>5.5</v>
+        <v>7</v>
       </c>
       <c r="Q124" s="32" t="n">
-        <v>0.24</v>
+        <v>-2.45</v>
       </c>
       <c r="R124" s="23" t="inlineStr">
         <is>
@@ -13585,13 +13577,13 @@
       </c>
       <c r="N125" s="2" t="n"/>
       <c r="O125" s="32" t="n">
-        <v>-1</v>
+        <v>-3.7</v>
       </c>
       <c r="P125" s="32" t="n">
-        <v>6.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="Q125" s="32" t="n">
-        <v>1.65</v>
+        <v>2.44</v>
       </c>
       <c r="R125" s="23" t="inlineStr">
         <is>
@@ -13689,10 +13681,10 @@
       </c>
       <c r="N126" s="2" t="n"/>
       <c r="O126" s="32" t="n">
-        <v>0.6</v>
+        <v>-3.2</v>
       </c>
       <c r="P126" s="32" t="n">
-        <v>6.1</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Q126" s="32" t="n"/>
       <c r="R126" s="23" t="inlineStr">
@@ -13799,13 +13791,13 @@
       </c>
       <c r="N127" s="2" t="n"/>
       <c r="O127" s="32" t="n">
-        <v>1.2</v>
+        <v>-2.5</v>
       </c>
       <c r="P127" s="32" t="n">
-        <v>11.3</v>
+        <v>9.6</v>
       </c>
       <c r="Q127" s="32" t="n">
-        <v>5.31</v>
+        <v>2.76</v>
       </c>
       <c r="R127" s="23" t="inlineStr">
         <is>
@@ -13919,10 +13911,10 @@
       </c>
       <c r="N128" s="2" t="n"/>
       <c r="O128" s="32" t="n">
-        <v>-1.2</v>
+        <v>-1.6</v>
       </c>
       <c r="P128" s="32" t="n">
-        <v>3.3</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="Q128" s="32" t="n"/>
       <c r="R128" s="23" t="inlineStr">
@@ -14029,13 +14021,13 @@
       </c>
       <c r="N129" s="2" t="n"/>
       <c r="O129" s="32" t="n">
-        <v>0.4</v>
+        <v>-1.7</v>
       </c>
       <c r="P129" s="32" t="n">
-        <v>6.2</v>
+        <v>5.6</v>
       </c>
       <c r="Q129" s="32" t="n">
-        <v>2.74</v>
+        <v>1.78</v>
       </c>
       <c r="R129" s="23" t="inlineStr">
         <is>
@@ -14149,13 +14141,13 @@
       </c>
       <c r="N130" s="2" t="n"/>
       <c r="O130" s="32" t="n">
-        <v>-4.1</v>
+        <v>-1.1</v>
       </c>
       <c r="P130" s="32" t="n">
-        <v>15.5</v>
+        <v>13</v>
       </c>
       <c r="Q130" s="32" t="n">
-        <v>4.19</v>
+        <v>5.61</v>
       </c>
       <c r="R130" s="23" t="inlineStr">
         <is>
@@ -14269,13 +14261,13 @@
       </c>
       <c r="N131" s="2" t="n"/>
       <c r="O131" s="32" t="n">
-        <v>2.9</v>
+        <v>-1.4</v>
       </c>
       <c r="P131" s="32" t="n">
-        <v>6.9</v>
+        <v>11</v>
       </c>
       <c r="Q131" s="32" t="n">
-        <v>4.66</v>
+        <v>4.61</v>
       </c>
       <c r="R131" s="23" t="inlineStr">
         <is>
@@ -14385,13 +14377,13 @@
       </c>
       <c r="N132" s="2" t="n"/>
       <c r="O132" s="32" t="n">
-        <v>4.1</v>
+        <v>1.5</v>
       </c>
       <c r="P132" s="32" t="n">
-        <v>7</v>
+        <v>5.7</v>
       </c>
       <c r="Q132" s="32" t="n">
-        <v>5.16</v>
+        <v>3.62</v>
       </c>
       <c r="R132" s="23" t="inlineStr">
         <is>
@@ -14501,13 +14493,13 @@
       </c>
       <c r="N133" s="2" t="n"/>
       <c r="O133" s="32" t="n">
-        <v>4.9</v>
+        <v>2.5</v>
       </c>
       <c r="P133" s="32" t="n">
-        <v>15.1</v>
+        <v>5.4</v>
       </c>
       <c r="Q133" s="32" t="n">
-        <v>9.210000000000001</v>
+        <v>3.54</v>
       </c>
       <c r="R133" s="23" t="inlineStr">
         <is>
@@ -14723,13 +14715,13 @@
       </c>
       <c r="N135" s="2" t="n"/>
       <c r="O135" s="32" t="n">
-        <v>5.7</v>
+        <v>8.4</v>
       </c>
       <c r="P135" s="32" t="n">
-        <v>14.5</v>
+        <v>14.4</v>
       </c>
       <c r="Q135" s="32" t="n">
-        <v>9.69</v>
+        <v>10.91</v>
       </c>
       <c r="R135" s="23" t="inlineStr">
         <is>
@@ -14842,10 +14834,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="P136" s="32" t="n">
-        <v>11.9</v>
+        <v>17.6</v>
       </c>
       <c r="Q136" s="32" t="n">
-        <v>9.91</v>
+        <v>12.41</v>
       </c>
       <c r="R136" s="23" t="inlineStr">
         <is>
@@ -14955,13 +14947,13 @@
       </c>
       <c r="N137" s="2" t="n"/>
       <c r="O137" s="32" t="n">
-        <v>6.4</v>
+        <v>5.2</v>
       </c>
       <c r="P137" s="32" t="n">
-        <v>13.9</v>
+        <v>14.4</v>
       </c>
       <c r="Q137" s="32" t="n">
-        <v>10.64</v>
+        <v>10.06</v>
       </c>
       <c r="R137" s="23" t="inlineStr">
         <is>
@@ -15071,10 +15063,10 @@
       </c>
       <c r="N138" s="2" t="n"/>
       <c r="O138" s="32" t="n">
-        <v>5.2</v>
+        <v>3.2</v>
       </c>
       <c r="P138" s="32" t="n">
-        <v>11</v>
+        <v>11.7</v>
       </c>
       <c r="Q138" s="32" t="n"/>
       <c r="R138" s="23" t="inlineStr">
@@ -15185,13 +15177,13 @@
       </c>
       <c r="N139" s="2" t="n"/>
       <c r="O139" s="32" t="n">
-        <v>6</v>
+        <v>2.6</v>
       </c>
       <c r="P139" s="32" t="n">
-        <v>9.9</v>
+        <v>11.1</v>
       </c>
       <c r="Q139" s="32" t="n">
-        <v>7.45</v>
+        <v>6.61</v>
       </c>
       <c r="R139" s="23" t="inlineStr">
         <is>
@@ -15301,13 +15293,13 @@
       </c>
       <c r="N140" s="2" t="n"/>
       <c r="O140" s="32" t="n">
-        <v>7.4</v>
+        <v>6</v>
       </c>
       <c r="P140" s="32" t="n">
-        <v>11.7</v>
+        <v>12.4</v>
       </c>
       <c r="Q140" s="32" t="n">
-        <v>9.07</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="R140" s="23" t="inlineStr">
         <is>
@@ -15519,13 +15511,13 @@
       </c>
       <c r="N142" s="2" t="n"/>
       <c r="O142" s="32" t="n">
-        <v>10.5</v>
+        <v>10.4</v>
       </c>
       <c r="P142" s="32" t="n">
-        <v>16.5</v>
+        <v>16.7</v>
       </c>
       <c r="Q142" s="32" t="n">
-        <v>12.96</v>
+        <v>12.72</v>
       </c>
       <c r="R142" s="23" t="inlineStr">
         <is>
@@ -15635,13 +15627,13 @@
       </c>
       <c r="N143" s="2" t="n"/>
       <c r="O143" s="32" t="n">
-        <v>12.5</v>
+        <v>12.6</v>
       </c>
       <c r="P143" s="32" t="n">
-        <v>16.7</v>
+        <v>25.1</v>
       </c>
       <c r="Q143" s="32" t="n">
-        <v>14.36</v>
+        <v>18.01</v>
       </c>
       <c r="R143" s="23" t="inlineStr">
         <is>
@@ -15951,13 +15943,13 @@
       </c>
       <c r="N146" s="2" t="n"/>
       <c r="O146" s="32" t="n">
-        <v>18.8</v>
+        <v>20.3</v>
       </c>
       <c r="P146" s="32" t="n">
-        <v>24.7</v>
+        <v>27.3</v>
       </c>
       <c r="Q146" s="32" t="n">
-        <v>21.51</v>
+        <v>23.99</v>
       </c>
       <c r="R146" s="23" t="inlineStr">
         <is>
@@ -16059,13 +16051,13 @@
       </c>
       <c r="N147" s="2" t="n"/>
       <c r="O147" s="32" t="n">
-        <v>12.8</v>
+        <v>17.6</v>
       </c>
       <c r="P147" s="32" t="n">
-        <v>19.9</v>
+        <v>23.6</v>
       </c>
       <c r="Q147" s="32" t="n">
-        <v>15.26</v>
+        <v>20.36</v>
       </c>
       <c r="R147" s="23" t="inlineStr">
         <is>
@@ -16277,13 +16269,13 @@
       </c>
       <c r="N149" s="2" t="n"/>
       <c r="O149" s="32" t="n">
-        <v>10.2</v>
+        <v>13.1</v>
       </c>
       <c r="P149" s="32" t="n">
-        <v>21.2</v>
+        <v>21.5</v>
       </c>
       <c r="Q149" s="32" t="n">
-        <v>13.89</v>
+        <v>16.88</v>
       </c>
       <c r="R149" s="23" t="inlineStr">
         <is>
@@ -16393,13 +16385,13 @@
       </c>
       <c r="N150" s="2" t="n"/>
       <c r="O150" s="32" t="n">
-        <v>6.1</v>
+        <v>7.7</v>
       </c>
       <c r="P150" s="32" t="n">
-        <v>18.2</v>
+        <v>11.4</v>
       </c>
       <c r="Q150" s="32" t="n">
-        <v>11.06</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="R150" s="23" t="inlineStr">
         <is>
@@ -16509,13 +16501,13 @@
       </c>
       <c r="N151" s="2" t="n"/>
       <c r="O151" s="32" t="n">
-        <v>12.9</v>
+        <v>13.5</v>
       </c>
       <c r="P151" s="32" t="n">
-        <v>23.8</v>
+        <v>18.9</v>
       </c>
       <c r="Q151" s="32" t="n">
-        <v>17.01</v>
+        <v>15.29</v>
       </c>
       <c r="R151" s="23" t="inlineStr">
         <is>
@@ -16715,13 +16707,13 @@
       </c>
       <c r="N153" s="2" t="n"/>
       <c r="O153" s="32" t="n">
-        <v>5.8</v>
+        <v>12</v>
       </c>
       <c r="P153" s="32" t="n">
-        <v>20.5</v>
+        <v>16.5</v>
       </c>
       <c r="Q153" s="32" t="n">
-        <v>13.41</v>
+        <v>13.11</v>
       </c>
       <c r="R153" s="23" t="inlineStr">
         <is>
@@ -16835,13 +16827,13 @@
       </c>
       <c r="N154" s="2" t="n"/>
       <c r="O154" s="32" t="n">
-        <v>-2.1</v>
+        <v>2.2</v>
       </c>
       <c r="P154" s="32" t="n">
-        <v>16</v>
+        <v>19.6</v>
       </c>
       <c r="Q154" s="32" t="n">
-        <v>6.11</v>
+        <v>10.64</v>
       </c>
       <c r="R154" s="23" t="inlineStr">
         <is>
@@ -17037,10 +17029,10 @@
       </c>
       <c r="N156" s="2" t="n"/>
       <c r="O156" s="32" t="n">
-        <v>-8.5</v>
+        <v>-17.1</v>
       </c>
       <c r="P156" s="32" t="n">
-        <v>5.8</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="Q156" s="32" t="n"/>
       <c r="R156" s="23" t="inlineStr">
@@ -17143,10 +17135,10 @@
       </c>
       <c r="N157" s="2" t="n"/>
       <c r="O157" s="32" t="n">
-        <v>7.4</v>
+        <v>5</v>
       </c>
       <c r="P157" s="32" t="n">
-        <v>10.7</v>
+        <v>11.4</v>
       </c>
       <c r="Q157" s="32" t="n"/>
       <c r="R157" s="23" t="inlineStr">
@@ -17531,10 +17523,10 @@
       </c>
       <c r="N161" s="2" t="n"/>
       <c r="O161" s="32" t="n">
-        <v>1.1</v>
+        <v>3.3</v>
       </c>
       <c r="P161" s="32" t="n">
-        <v>13.6</v>
+        <v>17.2</v>
       </c>
       <c r="Q161" s="32" t="n"/>
       <c r="R161" s="23" t="inlineStr">
@@ -17645,10 +17637,10 @@
         </is>
       </c>
       <c r="O162" s="32" t="n">
-        <v>-34</v>
+        <v>-36.5</v>
       </c>
       <c r="P162" s="32" t="n">
-        <v>-10.1</v>
+        <v>-2.4</v>
       </c>
       <c r="Q162" s="32" t="n"/>
       <c r="R162" s="23" t="inlineStr">
@@ -17971,10 +17963,10 @@
         </is>
       </c>
       <c r="O165" s="32" t="n">
-        <v>-33</v>
+        <v>-39.9</v>
       </c>
       <c r="P165" s="32" t="n">
-        <v>-16.5</v>
+        <v>-9.9</v>
       </c>
       <c r="Q165" s="32" t="n"/>
       <c r="R165" s="23" t="inlineStr">
@@ -18297,10 +18289,10 @@
         </is>
       </c>
       <c r="O168" s="32" t="n">
-        <v>-20.9</v>
+        <v>-14.3</v>
       </c>
       <c r="P168" s="32" t="n">
-        <v>-2.6</v>
+        <v>3.6</v>
       </c>
       <c r="Q168" s="32" t="n"/>
       <c r="R168" s="23" t="inlineStr">
@@ -18411,10 +18403,10 @@
         </is>
       </c>
       <c r="O169" s="32" t="n">
-        <v>-29.5</v>
+        <v>-16.9</v>
       </c>
       <c r="P169" s="32" t="n">
-        <v>-8.199999999999999</v>
+        <v>-0.5</v>
       </c>
       <c r="Q169" s="32" t="n"/>
       <c r="R169" s="23" t="inlineStr">
@@ -18737,10 +18729,10 @@
       </c>
       <c r="N172" s="3" t="n"/>
       <c r="O172" s="32" t="n">
-        <v>-17.7</v>
+        <v>-11.7</v>
       </c>
       <c r="P172" s="32" t="n">
-        <v>-3.4</v>
+        <v>1.6</v>
       </c>
       <c r="Q172" s="32" t="n"/>
       <c r="R172" s="23" t="inlineStr">
@@ -18847,10 +18839,10 @@
       </c>
       <c r="N173" s="2" t="n"/>
       <c r="O173" s="32" t="n">
-        <v>-24.6</v>
+        <v>-25.6</v>
       </c>
       <c r="P173" s="32" t="n">
-        <v>-6.2</v>
+        <v>1</v>
       </c>
       <c r="Q173" s="32" t="n"/>
       <c r="R173" s="23" t="inlineStr">
@@ -19169,10 +19161,10 @@
       </c>
       <c r="N176" s="2" t="n"/>
       <c r="O176" s="32" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="P176" s="32" t="n">
-        <v>5.2</v>
+        <v>8.5</v>
       </c>
       <c r="Q176" s="32" t="n"/>
       <c r="R176" s="23" t="inlineStr">
@@ -19271,10 +19263,10 @@
       </c>
       <c r="N177" s="2" t="n"/>
       <c r="O177" s="32" t="n">
-        <v>-18.3</v>
+        <v>-26.6</v>
       </c>
       <c r="P177" s="32" t="n">
-        <v>-11.8</v>
+        <v>-18.8</v>
       </c>
       <c r="Q177" s="32" t="n"/>
       <c r="R177" s="23" t="inlineStr">
@@ -20162,13 +20154,13 @@
       </c>
       <c r="N186" s="2" t="n"/>
       <c r="O186" s="32" t="n">
-        <v>-38</v>
+        <v>-36.9</v>
       </c>
       <c r="P186" s="32" t="n">
-        <v>-14.1</v>
+        <v>-21.3</v>
       </c>
       <c r="Q186" s="32" t="n">
-        <v>-27.76</v>
+        <v>-29.8</v>
       </c>
       <c r="R186" s="23" t="inlineStr">
         <is>
@@ -20271,13 +20263,13 @@
       </c>
       <c r="N187" s="2" t="n"/>
       <c r="O187" s="32" t="n">
-        <v>-29.2</v>
+        <v>-37.4</v>
       </c>
       <c r="P187" s="32" t="n">
-        <v>-13.4</v>
+        <v>-21.6</v>
       </c>
       <c r="Q187" s="32" t="n">
-        <v>-23.07</v>
+        <v>-30.66</v>
       </c>
       <c r="R187" s="23" t="inlineStr">
         <is>
@@ -20378,10 +20370,10 @@
         <v>-37</v>
       </c>
       <c r="P188" s="32" t="n">
-        <v>-14.8</v>
+        <v>-24.4</v>
       </c>
       <c r="Q188" s="32" t="n">
-        <v>-25.47</v>
+        <v>-31.61</v>
       </c>
       <c r="R188" s="23" t="inlineStr">
         <is>
@@ -20479,13 +20471,13 @@
       </c>
       <c r="N189" s="2" t="n"/>
       <c r="O189" s="32" t="n">
-        <v>-35.4</v>
+        <v>-43</v>
       </c>
       <c r="P189" s="32" t="n">
-        <v>-13.2</v>
+        <v>-23.6</v>
       </c>
       <c r="Q189" s="32" t="n">
-        <v>-25.85</v>
+        <v>-34.38</v>
       </c>
       <c r="R189" s="23" t="inlineStr">
         <is>
@@ -20583,13 +20575,13 @@
       </c>
       <c r="N190" s="2" t="n"/>
       <c r="O190" s="32" t="n">
-        <v>-41.5</v>
+        <v>-45.9</v>
       </c>
       <c r="P190" s="32" t="n">
-        <v>-21.5</v>
+        <v>-27</v>
       </c>
       <c r="Q190" s="32" t="n">
-        <v>-32.1</v>
+        <v>-38.66</v>
       </c>
       <c r="R190" s="23" t="inlineStr">
         <is>
@@ -20687,13 +20679,13 @@
       </c>
       <c r="N191" s="2" t="n"/>
       <c r="O191" s="32" t="n">
-        <v>-37.1</v>
+        <v>-36.4</v>
       </c>
       <c r="P191" s="32" t="n">
-        <v>-16.8</v>
+        <v>-19.4</v>
       </c>
       <c r="Q191" s="32" t="n">
-        <v>-28.95</v>
+        <v>-29.45</v>
       </c>
       <c r="R191" s="23" t="inlineStr">
         <is>
@@ -20787,13 +20779,13 @@
       </c>
       <c r="N192" s="2" t="n"/>
       <c r="O192" s="32" t="n">
-        <v>-25.2</v>
+        <v>-37.5</v>
       </c>
       <c r="P192" s="32" t="n">
-        <v>-14.6</v>
+        <v>-21</v>
       </c>
       <c r="Q192" s="32" t="n">
-        <v>-18.88</v>
+        <v>-30.21</v>
       </c>
       <c r="R192" s="23" t="inlineStr">
         <is>
@@ -20892,13 +20884,13 @@
       </c>
       <c r="N193" s="2" t="n"/>
       <c r="O193" s="32" t="n">
-        <v>-32</v>
+        <v>-33.3</v>
       </c>
       <c r="P193" s="32" t="n">
-        <v>-18.7</v>
+        <v>-13.5</v>
       </c>
       <c r="Q193" s="32" t="n">
-        <v>-24.04</v>
+        <v>-24.56</v>
       </c>
       <c r="R193" s="23" t="inlineStr">
         <is>
@@ -21000,10 +20992,10 @@
       </c>
       <c r="N194" s="2" t="n"/>
       <c r="O194" s="32" t="n">
-        <v>-39.9</v>
+        <v>-34</v>
       </c>
       <c r="P194" s="32" t="n">
-        <v>-24</v>
+        <v>-17.4</v>
       </c>
       <c r="Q194" s="32" t="n"/>
       <c r="R194" s="23" t="inlineStr">
@@ -21098,13 +21090,13 @@
       </c>
       <c r="N195" s="2" t="n"/>
       <c r="O195" s="32" t="n">
-        <v>-21</v>
+        <v>-39.1</v>
       </c>
       <c r="P195" s="32" t="n">
-        <v>-11.5</v>
+        <v>-20.8</v>
       </c>
       <c r="Q195" s="32" t="n">
-        <v>-17.38</v>
+        <v>-31.09</v>
       </c>
       <c r="R195" s="23" t="inlineStr">
         <is>
@@ -21202,13 +21194,13 @@
       </c>
       <c r="N196" s="2" t="n"/>
       <c r="O196" s="32" t="n">
-        <v>-29.6</v>
+        <v>-35.5</v>
       </c>
       <c r="P196" s="32" t="n">
-        <v>-9.300000000000001</v>
+        <v>-16.5</v>
       </c>
       <c r="Q196" s="32" t="n">
-        <v>-19.64</v>
+        <v>-27.41</v>
       </c>
       <c r="R196" s="23" t="inlineStr">
         <is>
@@ -21306,13 +21298,13 @@
       </c>
       <c r="N197" s="24" t="n"/>
       <c r="O197" s="32" t="n">
-        <v>-30.3</v>
+        <v>-33.4</v>
       </c>
       <c r="P197" s="32" t="n">
-        <v>-19</v>
+        <v>-16.4</v>
       </c>
       <c r="Q197" s="32" t="n">
-        <v>-25.78</v>
+        <v>-25.12</v>
       </c>
       <c r="R197" s="23" t="inlineStr">
         <is>
@@ -22315,8 +22307,12 @@
         </is>
       </c>
       <c r="N207" s="2" t="n"/>
-      <c r="O207" s="32" t="n"/>
-      <c r="P207" s="32" t="n"/>
+      <c r="O207" s="32" t="n">
+        <v>-37.7</v>
+      </c>
+      <c r="P207" s="32" t="n">
+        <v>-1.8</v>
+      </c>
       <c r="Q207" s="32" t="n"/>
       <c r="R207" s="23" t="inlineStr">
         <is>
@@ -22909,12 +22905,8 @@
         </is>
       </c>
       <c r="N213" s="2" t="n"/>
-      <c r="O213" s="32" t="n">
-        <v>-36.3</v>
-      </c>
-      <c r="P213" s="32" t="n">
-        <v>-13.5</v>
-      </c>
+      <c r="O213" s="32" t="n"/>
+      <c r="P213" s="32" t="n"/>
       <c r="Q213" s="32" t="n"/>
       <c r="R213" s="23" t="inlineStr">
         <is>
@@ -24425,12 +24417,8 @@
         </is>
       </c>
       <c r="N228" s="2" t="n"/>
-      <c r="O228" s="32" t="n">
-        <v>-30.6</v>
-      </c>
-      <c r="P228" s="32" t="n">
-        <v>-6.2</v>
-      </c>
+      <c r="O228" s="32" t="n"/>
+      <c r="P228" s="32" t="n"/>
       <c r="Q228" s="32" t="n"/>
       <c r="R228" s="23" t="n"/>
       <c r="S228" s="37" t="n"/>
@@ -25674,10 +25662,10 @@
       </c>
       <c r="N241" s="2" t="n"/>
       <c r="O241" s="32" t="n">
-        <v>-33.3</v>
+        <v>-23</v>
       </c>
       <c r="P241" s="32" t="n">
-        <v>-11.1</v>
+        <v>-5.5</v>
       </c>
       <c r="Q241" s="32" t="n"/>
       <c r="R241" s="23" t="inlineStr">
@@ -26252,13 +26240,13 @@
       </c>
       <c r="N247" s="2" t="n"/>
       <c r="O247" s="32" t="n">
-        <v>-8.4</v>
+        <v>-5.1</v>
       </c>
       <c r="P247" s="32" t="n">
-        <v>-1.6</v>
+        <v>-0.2</v>
       </c>
       <c r="Q247" s="32" t="n">
-        <v>-4.79</v>
+        <v>-2.38</v>
       </c>
       <c r="R247" s="23" t="inlineStr">
         <is>
@@ -26368,13 +26356,13 @@
         </is>
       </c>
       <c r="O248" s="32" t="n">
-        <v>-13.7</v>
+        <v>-9</v>
       </c>
       <c r="P248" s="32" t="n">
-        <v>-8.4</v>
+        <v>-2</v>
       </c>
       <c r="Q248" s="32" t="n">
-        <v>-11.95</v>
+        <v>-5.1</v>
       </c>
       <c r="R248" s="23" t="inlineStr">
         <is>
@@ -26476,13 +26464,13 @@
       </c>
       <c r="N249" s="2" t="n"/>
       <c r="O249" s="32" t="n">
-        <v>-9.300000000000001</v>
+        <v>-8.800000000000001</v>
       </c>
       <c r="P249" s="32" t="n">
-        <v>0.2</v>
+        <v>-1.8</v>
       </c>
       <c r="Q249" s="32" t="n">
-        <v>-4.94</v>
+        <v>-5.39</v>
       </c>
       <c r="R249" s="23" t="inlineStr">
         <is>
@@ -26588,13 +26576,13 @@
       </c>
       <c r="N250" s="2" t="n"/>
       <c r="O250" s="32" t="n">
-        <v>-28.2</v>
+        <v>-20</v>
       </c>
       <c r="P250" s="32" t="n">
-        <v>-10.6</v>
+        <v>-0.3</v>
       </c>
       <c r="Q250" s="32" t="n">
-        <v>-19.7</v>
+        <v>-11.62</v>
       </c>
       <c r="R250" s="23" t="inlineStr">
         <is>
@@ -26708,10 +26696,10 @@
         </is>
       </c>
       <c r="O251" s="32" t="n">
-        <v>-22.1</v>
+        <v>-35.7</v>
       </c>
       <c r="P251" s="32" t="n">
-        <v>-17.9</v>
+        <v>-13.3</v>
       </c>
       <c r="Q251" s="32" t="n"/>
       <c r="R251" s="23" t="inlineStr">
@@ -26806,13 +26794,13 @@
       </c>
       <c r="N252" s="2" t="n"/>
       <c r="O252" s="32" t="n">
-        <v>-13.3</v>
+        <v>-19.5</v>
       </c>
       <c r="P252" s="32" t="n">
-        <v>-4.9</v>
+        <v>-2.4</v>
       </c>
       <c r="Q252" s="32" t="n">
-        <v>-9.210000000000001</v>
+        <v>-11.5</v>
       </c>
       <c r="R252" s="23" t="inlineStr">
         <is>
@@ -27004,13 +26992,13 @@
       </c>
       <c r="N254" s="2" t="n"/>
       <c r="O254" s="32" t="n">
-        <v>-45</v>
+        <v>-29.9</v>
       </c>
       <c r="P254" s="32" t="n">
-        <v>-28</v>
+        <v>-18.2</v>
       </c>
       <c r="Q254" s="32" t="n">
-        <v>-37.91</v>
+        <v>-24.95</v>
       </c>
       <c r="R254" s="23" t="inlineStr">
         <is>
@@ -27578,13 +27566,13 @@
       </c>
       <c r="N260" s="2" t="n"/>
       <c r="O260" s="32" t="n">
-        <v>-23.3</v>
+        <v>-14.6</v>
       </c>
       <c r="P260" s="32" t="n">
-        <v>-4</v>
+        <v>1.1</v>
       </c>
       <c r="Q260" s="32" t="n">
-        <v>-16.02</v>
+        <v>-6.25</v>
       </c>
       <c r="R260" s="23" t="inlineStr">
         <is>
@@ -27686,13 +27674,13 @@
       </c>
       <c r="N261" s="2" t="n"/>
       <c r="O261" s="32" t="n">
-        <v>-30.4</v>
+        <v>-17.1</v>
       </c>
       <c r="P261" s="32" t="n">
-        <v>-10.2</v>
+        <v>2.3</v>
       </c>
       <c r="Q261" s="32" t="n">
-        <v>-21.06</v>
+        <v>-9.68</v>
       </c>
       <c r="R261" s="23" t="inlineStr">
         <is>
@@ -27798,13 +27786,13 @@
       </c>
       <c r="N262" s="2" t="n"/>
       <c r="O262" s="32" t="n">
-        <v>-24.2</v>
+        <v>-22</v>
       </c>
       <c r="P262" s="32" t="n">
-        <v>-7.8</v>
+        <v>-1.9</v>
       </c>
       <c r="Q262" s="32" t="n">
-        <v>-13.36</v>
+        <v>-12.46</v>
       </c>
       <c r="R262" s="23" t="inlineStr">
         <is>
@@ -28004,13 +27992,13 @@
       </c>
       <c r="N264" s="2" t="n"/>
       <c r="O264" s="32" t="n">
-        <v>-23.5</v>
+        <v>-13.2</v>
       </c>
       <c r="P264" s="32" t="n">
-        <v>-8.300000000000001</v>
+        <v>0.9</v>
       </c>
       <c r="Q264" s="32" t="n">
-        <v>-16.7</v>
+        <v>-7.62</v>
       </c>
       <c r="R264" s="23" t="inlineStr">
         <is>
@@ -28124,10 +28112,10 @@
       </c>
       <c r="N265" s="2" t="n"/>
       <c r="O265" s="32" t="n">
-        <v>-44.7</v>
+        <v>-52.1</v>
       </c>
       <c r="P265" s="32" t="n">
-        <v>-38.5</v>
+        <v>-41.6</v>
       </c>
       <c r="Q265" s="32" t="n"/>
       <c r="R265" s="23" t="inlineStr">
@@ -29168,13 +29156,13 @@
       </c>
       <c r="N276" s="2" t="n"/>
       <c r="O276" s="32" t="n">
-        <v>-33.2</v>
+        <v>-45</v>
       </c>
       <c r="P276" s="32" t="n">
-        <v>-19.7</v>
+        <v>-30</v>
       </c>
       <c r="Q276" s="32" t="n">
-        <v>-26.54</v>
+        <v>-38.8</v>
       </c>
       <c r="R276" s="23" t="inlineStr">
         <is>

--- a/气象/For_Python_站点信息和记录.xlsx
+++ b/气象/For_Python_站点信息和记录.xlsx
@@ -796,8 +796,8 @@
     <col width="18.59765625" customWidth="1" style="8" min="25" max="25"/>
     <col width="12.59765625" customWidth="1" style="5" min="26" max="30"/>
     <col width="12.59765625" customWidth="1" style="8" min="31" max="32"/>
-    <col width="12.59765625" customWidth="1" style="5" min="33" max="297"/>
-    <col width="12.59765625" customWidth="1" style="5" min="298" max="16384"/>
+    <col width="12.59765625" customWidth="1" style="5" min="33" max="299"/>
+    <col width="12.59765625" customWidth="1" style="5" min="300" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="27.75" customFormat="1" customHeight="1" s="11">
@@ -1020,13 +1020,13 @@
         </is>
       </c>
       <c r="O2" s="32" t="n">
-        <v>-31</v>
+        <v>-31.7</v>
       </c>
       <c r="P2" s="32" t="n">
-        <v>-18.3</v>
+        <v>-17.9</v>
       </c>
       <c r="Q2" s="32" t="n">
-        <v>-24.39</v>
+        <v>-24.75</v>
       </c>
       <c r="R2" s="23" t="inlineStr">
         <is>
@@ -1126,10 +1126,10 @@
         </is>
       </c>
       <c r="O3" s="32" t="n">
-        <v>-33.4</v>
+        <v>-33.1</v>
       </c>
       <c r="P3" s="32" t="n">
-        <v>-16.8</v>
+        <v>-16.1</v>
       </c>
       <c r="Q3" s="32" t="n"/>
       <c r="R3" s="23" t="n"/>
@@ -1322,10 +1322,10 @@
       </c>
       <c r="N5" s="2" t="n"/>
       <c r="O5" s="32" t="n">
-        <v>-24.8</v>
+        <v>-26.4</v>
       </c>
       <c r="P5" s="32" t="n">
-        <v>-8.300000000000001</v>
+        <v>-10.7</v>
       </c>
       <c r="Q5" s="32" t="n"/>
       <c r="R5" s="23" t="n"/>
@@ -1422,10 +1422,10 @@
         </is>
       </c>
       <c r="O6" s="32" t="n">
-        <v>-28.5</v>
+        <v>-30.4</v>
       </c>
       <c r="P6" s="32" t="n">
-        <v>-9.800000000000001</v>
+        <v>-9.199999999999999</v>
       </c>
       <c r="Q6" s="32" t="n"/>
       <c r="R6" s="23" t="n"/>
@@ -1522,10 +1522,10 @@
         </is>
       </c>
       <c r="O7" s="32" t="n">
-        <v>-24.2</v>
+        <v>-24</v>
       </c>
       <c r="P7" s="32" t="n">
-        <v>-11.6</v>
+        <v>-9.1</v>
       </c>
       <c r="Q7" s="32" t="n"/>
       <c r="R7" s="23" t="n"/>
@@ -1630,13 +1630,13 @@
       </c>
       <c r="N8" s="2" t="n"/>
       <c r="O8" s="32" t="n">
-        <v>-23.9</v>
+        <v>-26.7</v>
       </c>
       <c r="P8" s="32" t="n">
-        <v>-8.1</v>
+        <v>-6.7</v>
       </c>
       <c r="Q8" s="32" t="n">
-        <v>-17.66</v>
+        <v>-17.05</v>
       </c>
       <c r="R8" s="23" t="inlineStr">
         <is>
@@ -1742,13 +1742,13 @@
       </c>
       <c r="N9" s="2" t="n"/>
       <c r="O9" s="32" t="n">
-        <v>-30</v>
+        <v>-27.8</v>
       </c>
       <c r="P9" s="32" t="n">
-        <v>-13</v>
+        <v>-12.8</v>
       </c>
       <c r="Q9" s="32" t="n">
-        <v>-21.81</v>
+        <v>-21.29</v>
       </c>
       <c r="R9" s="23" t="inlineStr">
         <is>
@@ -1862,13 +1862,13 @@
         </is>
       </c>
       <c r="O10" s="32" t="n">
-        <v>-26.9</v>
+        <v>-27.9</v>
       </c>
       <c r="P10" s="32" t="n">
-        <v>-11.3</v>
+        <v>-6.2</v>
       </c>
       <c r="Q10" s="32" t="n">
-        <v>-18.02</v>
+        <v>-18.56</v>
       </c>
       <c r="R10" s="23" t="inlineStr">
         <is>
@@ -1978,13 +1978,13 @@
         </is>
       </c>
       <c r="O11" s="32" t="n">
-        <v>-27</v>
+        <v>-28.2</v>
       </c>
       <c r="P11" s="32" t="n">
-        <v>-6.4</v>
+        <v>-1.9</v>
       </c>
       <c r="Q11" s="32" t="n">
-        <v>-17.17</v>
+        <v>-15.72</v>
       </c>
       <c r="R11" s="23" t="inlineStr">
         <is>
@@ -2090,13 +2090,13 @@
       </c>
       <c r="N12" s="2" t="n"/>
       <c r="O12" s="32" t="n">
-        <v>-26.1</v>
+        <v>-27.6</v>
       </c>
       <c r="P12" s="32" t="n">
-        <v>-6.5</v>
+        <v>-9.699999999999999</v>
       </c>
       <c r="Q12" s="32" t="n">
-        <v>-18.39</v>
+        <v>-19.19</v>
       </c>
       <c r="R12" s="23" t="inlineStr">
         <is>
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="O13" s="32" t="n">
-        <v>-24.9</v>
+        <v>-28.4</v>
       </c>
       <c r="P13" s="32" t="n">
-        <v>-7.9</v>
+        <v>-11.4</v>
       </c>
       <c r="Q13" s="32" t="n">
-        <v>-18.3</v>
+        <v>-20.21</v>
       </c>
       <c r="R13" s="23" t="inlineStr">
         <is>
@@ -2318,13 +2318,13 @@
       </c>
       <c r="N14" s="2" t="n"/>
       <c r="O14" s="32" t="n">
-        <v>-12.7</v>
+        <v>-13.8</v>
       </c>
       <c r="P14" s="32" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="Q14" s="32" t="n">
-        <v>-7.48</v>
+        <v>-6.71</v>
       </c>
       <c r="R14" s="23" t="inlineStr">
         <is>
@@ -2423,8 +2423,12 @@
         </is>
       </c>
       <c r="N15" s="2" t="n"/>
-      <c r="O15" s="32" t="n"/>
-      <c r="P15" s="32" t="n"/>
+      <c r="O15" s="32" t="n">
+        <v>-25.7</v>
+      </c>
+      <c r="P15" s="32" t="n">
+        <v>-2.4</v>
+      </c>
       <c r="Q15" s="32" t="n"/>
       <c r="R15" s="23" t="n"/>
       <c r="S15" s="37" t="n"/>
@@ -4968,10 +4972,10 @@
         </is>
       </c>
       <c r="O43" s="32" t="n">
-        <v>-29.7</v>
+        <v>-29.8</v>
       </c>
       <c r="P43" s="32" t="n">
-        <v>-19.1</v>
+        <v>-18.6</v>
       </c>
       <c r="Q43" s="32" t="n"/>
       <c r="R43" s="23" t="n"/>
@@ -7834,13 +7838,13 @@
       </c>
       <c r="N75" s="2" t="n"/>
       <c r="O75" s="32" t="n">
-        <v>-26.3</v>
+        <v>-24.3</v>
       </c>
       <c r="P75" s="32" t="n">
-        <v>-6.4</v>
+        <v>-5.1</v>
       </c>
       <c r="Q75" s="32" t="n">
-        <v>-16.85</v>
+        <v>-14.72</v>
       </c>
       <c r="R75" s="23" t="inlineStr">
         <is>
@@ -7950,13 +7954,13 @@
         </is>
       </c>
       <c r="O76" s="32" t="n">
-        <v>-26.6</v>
+        <v>-29.8</v>
       </c>
       <c r="P76" s="32" t="n">
-        <v>-7.9</v>
+        <v>-7.4</v>
       </c>
       <c r="Q76" s="32" t="n">
-        <v>-17.09</v>
+        <v>-19.6</v>
       </c>
       <c r="R76" s="23" t="inlineStr">
         <is>
@@ -8066,13 +8070,13 @@
         </is>
       </c>
       <c r="O77" s="32" t="n">
-        <v>-29.2</v>
+        <v>-32.5</v>
       </c>
       <c r="P77" s="32" t="n">
-        <v>-7.9</v>
+        <v>-7.6</v>
       </c>
       <c r="Q77" s="32" t="n">
-        <v>-19.35</v>
+        <v>-20.61</v>
       </c>
       <c r="R77" s="23" t="inlineStr">
         <is>
@@ -8178,13 +8182,13 @@
       </c>
       <c r="N78" s="2" t="n"/>
       <c r="O78" s="32" t="n">
-        <v>-26.1</v>
+        <v>-26.9</v>
       </c>
       <c r="P78" s="32" t="n">
-        <v>-7.2</v>
+        <v>-6</v>
       </c>
       <c r="Q78" s="32" t="n">
-        <v>-16.68</v>
+        <v>-17.26</v>
       </c>
       <c r="R78" s="23" t="inlineStr">
         <is>
@@ -8294,13 +8298,13 @@
         </is>
       </c>
       <c r="O79" s="32" t="n">
-        <v>-13.5</v>
+        <v>-29.5</v>
       </c>
       <c r="P79" s="32" t="n">
-        <v>-4.8</v>
+        <v>-4.6</v>
       </c>
       <c r="Q79" s="32" t="n">
-        <v>-9.34</v>
+        <v>-17.36</v>
       </c>
       <c r="R79" s="23" t="inlineStr">
         <is>
@@ -8406,13 +8410,13 @@
       </c>
       <c r="N80" s="2" t="n"/>
       <c r="O80" s="32" t="n">
-        <v>-25.2</v>
+        <v>-22.9</v>
       </c>
       <c r="P80" s="32" t="n">
-        <v>-4.2</v>
+        <v>-4.4</v>
       </c>
       <c r="Q80" s="32" t="n">
-        <v>-15.45</v>
+        <v>-13.3</v>
       </c>
       <c r="R80" s="23" t="inlineStr">
         <is>
@@ -8522,14 +8526,12 @@
         </is>
       </c>
       <c r="O81" s="32" t="n">
-        <v>-23</v>
+        <v>-28.7</v>
       </c>
       <c r="P81" s="32" t="n">
-        <v>-2.6</v>
-      </c>
-      <c r="Q81" s="32" t="n">
-        <v>-14.1</v>
-      </c>
+        <v>-3.4</v>
+      </c>
+      <c r="Q81" s="32" t="n"/>
       <c r="R81" s="23" t="inlineStr">
         <is>
           <t>Y</t>
@@ -8643,10 +8645,10 @@
         </is>
       </c>
       <c r="O82" s="32" t="n">
-        <v>-25.5</v>
+        <v>-29.1</v>
       </c>
       <c r="P82" s="32" t="n">
-        <v>-2.5</v>
+        <v>-1.9</v>
       </c>
       <c r="Q82" s="32" t="n">
         <v>-16.68</v>
@@ -8755,13 +8757,13 @@
       </c>
       <c r="N83" s="2" t="n"/>
       <c r="O83" s="32" t="n">
-        <v>-23.2</v>
+        <v>-17</v>
       </c>
       <c r="P83" s="32" t="n">
-        <v>-1.9</v>
+        <v>-4.7</v>
       </c>
       <c r="Q83" s="32" t="n">
-        <v>-15.07</v>
+        <v>-10.05</v>
       </c>
       <c r="R83" s="23" t="inlineStr">
         <is>
@@ -8871,13 +8873,13 @@
         </is>
       </c>
       <c r="O84" s="32" t="n">
-        <v>-19.5</v>
+        <v>-24.9</v>
       </c>
       <c r="P84" s="32" t="n">
-        <v>1</v>
+        <v>-5.1</v>
       </c>
       <c r="Q84" s="32" t="n">
-        <v>-11.66</v>
+        <v>-16.01</v>
       </c>
       <c r="R84" s="23" t="inlineStr">
         <is>
@@ -8987,13 +8989,13 @@
         </is>
       </c>
       <c r="O85" s="32" t="n">
-        <v>-17.9</v>
+        <v>-23.6</v>
       </c>
       <c r="P85" s="32" t="n">
-        <v>-4.8</v>
+        <v>-5.6</v>
       </c>
       <c r="Q85" s="32" t="n">
-        <v>-11.9</v>
+        <v>-15.34</v>
       </c>
       <c r="R85" s="23" t="inlineStr">
         <is>
@@ -9099,13 +9101,13 @@
       </c>
       <c r="N86" s="2" t="n"/>
       <c r="O86" s="32" t="n">
-        <v>-16.9</v>
+        <v>-20.7</v>
       </c>
       <c r="P86" s="32" t="n">
-        <v>-4.2</v>
+        <v>-6</v>
       </c>
       <c r="Q86" s="32" t="n">
-        <v>-11.3</v>
+        <v>-13.64</v>
       </c>
       <c r="R86" s="23" t="inlineStr">
         <is>
@@ -9223,13 +9225,13 @@
         </is>
       </c>
       <c r="O87" s="32" t="n">
-        <v>-26.8</v>
+        <v>-28.6</v>
       </c>
       <c r="P87" s="32" t="n">
-        <v>-12.7</v>
+        <v>-13.8</v>
       </c>
       <c r="Q87" s="32" t="n">
-        <v>-19.44</v>
+        <v>-21.9</v>
       </c>
       <c r="R87" s="23" t="inlineStr">
         <is>
@@ -9335,13 +9337,13 @@
       </c>
       <c r="N88" s="2" t="n"/>
       <c r="O88" s="32" t="n">
-        <v>-18.2</v>
+        <v>-18.7</v>
       </c>
       <c r="P88" s="32" t="n">
-        <v>-1.4</v>
+        <v>-3.4</v>
       </c>
       <c r="Q88" s="32" t="n">
-        <v>-10.45</v>
+        <v>-11.74</v>
       </c>
       <c r="R88" s="23" t="inlineStr">
         <is>
@@ -9553,13 +9555,13 @@
         </is>
       </c>
       <c r="O90" s="32" t="n">
-        <v>-16.1</v>
+        <v>-15.6</v>
       </c>
       <c r="P90" s="32" t="n">
-        <v>-0.9</v>
+        <v>0.8</v>
       </c>
       <c r="Q90" s="32" t="n">
-        <v>-8.48</v>
+        <v>-8.34</v>
       </c>
       <c r="R90" s="23" t="inlineStr">
         <is>
@@ -9661,13 +9663,13 @@
       </c>
       <c r="N91" s="2" t="n"/>
       <c r="O91" s="32" t="n">
-        <v>-14</v>
+        <v>-19</v>
       </c>
       <c r="P91" s="32" t="n">
-        <v>-5.2</v>
+        <v>-5.8</v>
       </c>
       <c r="Q91" s="32" t="n">
-        <v>-8.67</v>
+        <v>-11.21</v>
       </c>
       <c r="R91" s="23" t="inlineStr">
         <is>
@@ -9769,13 +9771,13 @@
       </c>
       <c r="N92" s="2" t="n"/>
       <c r="O92" s="32" t="n">
-        <v>-27</v>
+        <v>-24.9</v>
       </c>
       <c r="P92" s="32" t="n">
-        <v>-6.5</v>
+        <v>-2.5</v>
       </c>
       <c r="Q92" s="32" t="n">
-        <v>-14.52</v>
+        <v>-12.18</v>
       </c>
       <c r="R92" s="23" t="inlineStr">
         <is>
@@ -9881,13 +9883,13 @@
       </c>
       <c r="N93" s="2" t="n"/>
       <c r="O93" s="32" t="n">
-        <v>-14.2</v>
+        <v>-8.9</v>
       </c>
       <c r="P93" s="32" t="n">
-        <v>2.8</v>
+        <v>6.8</v>
       </c>
       <c r="Q93" s="32" t="n">
-        <v>-4.51</v>
+        <v>-1.67</v>
       </c>
       <c r="R93" s="23" t="inlineStr">
         <is>
@@ -10001,10 +10003,10 @@
         </is>
       </c>
       <c r="O94" s="32" t="n">
-        <v>-18.1</v>
+        <v>-12.7</v>
       </c>
       <c r="P94" s="32" t="n">
-        <v>0.9</v>
+        <v>5.2</v>
       </c>
       <c r="Q94" s="32" t="n"/>
       <c r="R94" s="23" t="inlineStr">
@@ -10119,13 +10121,13 @@
       </c>
       <c r="N95" s="2" t="n"/>
       <c r="O95" s="32" t="n">
-        <v>-16.9</v>
+        <v>-10</v>
       </c>
       <c r="P95" s="32" t="n">
-        <v>-0.1</v>
+        <v>3.5</v>
       </c>
       <c r="Q95" s="32" t="n">
-        <v>-7.65</v>
+        <v>-2.55</v>
       </c>
       <c r="R95" s="23" t="inlineStr">
         <is>
@@ -10247,10 +10249,10 @@
         </is>
       </c>
       <c r="O96" s="32" t="n">
-        <v>-15.5</v>
+        <v>-12.7</v>
       </c>
       <c r="P96" s="32" t="n">
-        <v>-0.6</v>
+        <v>2.8</v>
       </c>
       <c r="Q96" s="32" t="n"/>
       <c r="R96" s="23" t="inlineStr">
@@ -10365,13 +10367,13 @@
       </c>
       <c r="N97" s="2" t="n"/>
       <c r="O97" s="32" t="n">
-        <v>-18.5</v>
+        <v>-15.5</v>
       </c>
       <c r="P97" s="32" t="n">
-        <v>-3.3</v>
+        <v>1.3</v>
       </c>
       <c r="Q97" s="32" t="n">
-        <v>-11.44</v>
+        <v>-7.19</v>
       </c>
       <c r="R97" s="23" t="inlineStr">
         <is>
@@ -10485,10 +10487,10 @@
       </c>
       <c r="N98" s="2" t="n"/>
       <c r="O98" s="32" t="n">
-        <v>-28.1</v>
+        <v>-27</v>
       </c>
       <c r="P98" s="32" t="n">
-        <v>-6.6</v>
+        <v>-5.4</v>
       </c>
       <c r="Q98" s="32" t="n"/>
       <c r="R98" s="23" t="inlineStr">
@@ -10603,13 +10605,13 @@
       </c>
       <c r="N99" s="2" t="n"/>
       <c r="O99" s="32" t="n">
-        <v>-34.8</v>
+        <v>-26.4</v>
       </c>
       <c r="P99" s="32" t="n">
-        <v>-7.7</v>
+        <v>-4.9</v>
       </c>
       <c r="Q99" s="32" t="n">
-        <v>-23.24</v>
+        <v>-17.34</v>
       </c>
       <c r="R99" s="23" t="inlineStr">
         <is>
@@ -10935,13 +10937,13 @@
       </c>
       <c r="N102" s="2" t="n"/>
       <c r="O102" s="32" t="n">
-        <v>-33.4</v>
+        <v>-26.2</v>
       </c>
       <c r="P102" s="32" t="n">
-        <v>-2.6</v>
+        <v>-2.2</v>
       </c>
       <c r="Q102" s="32" t="n">
-        <v>-18.85</v>
+        <v>-14.2</v>
       </c>
       <c r="R102" s="23" t="inlineStr">
         <is>
@@ -11051,10 +11053,10 @@
       </c>
       <c r="N103" s="2" t="n"/>
       <c r="O103" s="32" t="n">
-        <v>-30.2</v>
+        <v>-27.4</v>
       </c>
       <c r="P103" s="32" t="n">
-        <v>-3.2</v>
+        <v>-1.6</v>
       </c>
       <c r="Q103" s="32" t="n"/>
       <c r="R103" s="23" t="inlineStr">
@@ -11161,10 +11163,10 @@
       </c>
       <c r="N104" s="2" t="n"/>
       <c r="O104" s="32" t="n">
-        <v>-32.6</v>
+        <v>-26.2</v>
       </c>
       <c r="P104" s="32" t="n">
-        <v>-6.7</v>
+        <v>-1.2</v>
       </c>
       <c r="Q104" s="32" t="n"/>
       <c r="R104" s="23" t="inlineStr">
@@ -11287,13 +11289,13 @@
         </is>
       </c>
       <c r="O105" s="32" t="n">
-        <v>-36</v>
+        <v>-26.5</v>
       </c>
       <c r="P105" s="32" t="n">
-        <v>-5.6</v>
+        <v>-2.8</v>
       </c>
       <c r="Q105" s="32" t="n">
-        <v>-21.76</v>
+        <v>-14.89</v>
       </c>
       <c r="R105" s="23" t="inlineStr">
         <is>
@@ -11403,10 +11405,10 @@
         </is>
       </c>
       <c r="O106" s="32" t="n">
-        <v>-32.4</v>
+        <v>-25.9</v>
       </c>
       <c r="P106" s="32" t="n">
-        <v>-13.9</v>
+        <v>-11.5</v>
       </c>
       <c r="Q106" s="32" t="n"/>
       <c r="R106" s="23" t="inlineStr">
@@ -11623,13 +11625,13 @@
       </c>
       <c r="N108" s="2" t="n"/>
       <c r="O108" s="32" t="n">
-        <v>-27.8</v>
+        <v>-24.2</v>
       </c>
       <c r="P108" s="32" t="n">
-        <v>-8.300000000000001</v>
+        <v>-11.9</v>
       </c>
       <c r="Q108" s="32" t="n">
-        <v>-19.24</v>
+        <v>-18.01</v>
       </c>
       <c r="R108" s="23" t="inlineStr">
         <is>
@@ -11836,12 +11838,8 @@
         </is>
       </c>
       <c r="N110" s="2" t="n"/>
-      <c r="O110" s="32" t="n">
-        <v>-35.7</v>
-      </c>
-      <c r="P110" s="32" t="n">
-        <v>-8.6</v>
-      </c>
+      <c r="O110" s="32" t="n"/>
+      <c r="P110" s="32" t="n"/>
       <c r="Q110" s="32" t="n"/>
       <c r="R110" s="23" t="inlineStr">
         <is>
@@ -11955,13 +11953,13 @@
       </c>
       <c r="N111" s="2" t="n"/>
       <c r="O111" s="32" t="n">
-        <v>-30</v>
+        <v>-20.6</v>
       </c>
       <c r="P111" s="32" t="n">
-        <v>-3.6</v>
+        <v>-7.6</v>
       </c>
       <c r="Q111" s="32" t="n">
-        <v>-17.61</v>
+        <v>-13.43</v>
       </c>
       <c r="R111" s="23" t="inlineStr">
         <is>
@@ -12067,10 +12065,10 @@
       </c>
       <c r="N112" s="2" t="n"/>
       <c r="O112" s="32" t="n">
-        <v>-16.8</v>
+        <v>-10.8</v>
       </c>
       <c r="P112" s="32" t="n">
-        <v>5</v>
+        <v>-0.5</v>
       </c>
       <c r="Q112" s="32" t="n"/>
       <c r="R112" s="23" t="inlineStr">
@@ -12173,10 +12171,10 @@
       </c>
       <c r="N113" s="2" t="n"/>
       <c r="O113" s="32" t="n">
-        <v>-9.4</v>
+        <v>-9.699999999999999</v>
       </c>
       <c r="P113" s="32" t="n">
-        <v>9.4</v>
+        <v>6.4</v>
       </c>
       <c r="Q113" s="32" t="n"/>
       <c r="R113" s="23" t="inlineStr">
@@ -12287,10 +12285,10 @@
         </is>
       </c>
       <c r="O114" s="32" t="n">
-        <v>-11</v>
+        <v>-16</v>
       </c>
       <c r="P114" s="32" t="n">
-        <v>6.5</v>
+        <v>3.5</v>
       </c>
       <c r="Q114" s="32" t="n"/>
       <c r="R114" s="23" t="inlineStr">
@@ -12409,10 +12407,10 @@
         </is>
       </c>
       <c r="O115" s="32" t="n">
-        <v>-11.7</v>
+        <v>-12.9</v>
       </c>
       <c r="P115" s="32" t="n">
-        <v>3.5</v>
+        <v>0.9</v>
       </c>
       <c r="Q115" s="32" t="n"/>
       <c r="R115" s="23" t="inlineStr">
@@ -12527,13 +12525,13 @@
       </c>
       <c r="N116" s="2" t="n"/>
       <c r="O116" s="32" t="n">
-        <v>-8.300000000000001</v>
+        <v>-6.5</v>
       </c>
       <c r="P116" s="32" t="n">
-        <v>7.6</v>
+        <v>12.1</v>
       </c>
       <c r="Q116" s="32" t="n">
-        <v>0.09</v>
+        <v>2.83</v>
       </c>
       <c r="R116" s="23" t="inlineStr">
         <is>
@@ -12639,10 +12637,10 @@
       </c>
       <c r="N117" s="2" t="n"/>
       <c r="O117" s="32" t="n">
-        <v>-8.199999999999999</v>
+        <v>-8.1</v>
       </c>
       <c r="P117" s="32" t="n">
-        <v>4.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Q117" s="32" t="n"/>
       <c r="R117" s="23" t="inlineStr">
@@ -12753,10 +12751,10 @@
         </is>
       </c>
       <c r="O118" s="32" t="n">
-        <v>-15.1</v>
+        <v>-19</v>
       </c>
       <c r="P118" s="32" t="n">
-        <v>0.3</v>
+        <v>-0.7</v>
       </c>
       <c r="Q118" s="32" t="n"/>
       <c r="R118" s="23" t="inlineStr">
@@ -12871,13 +12869,13 @@
       </c>
       <c r="N119" s="2" t="n"/>
       <c r="O119" s="32" t="n">
-        <v>-10.7</v>
+        <v>-9.800000000000001</v>
       </c>
       <c r="P119" s="32" t="n">
-        <v>1.9</v>
+        <v>6.1</v>
       </c>
       <c r="Q119" s="32" t="n">
-        <v>-4.68</v>
+        <v>-2.26</v>
       </c>
       <c r="R119" s="23" t="inlineStr">
         <is>
@@ -13108,10 +13106,10 @@
         <v>-3.6</v>
       </c>
       <c r="P121" s="32" t="n">
-        <v>1.2</v>
+        <v>4.2</v>
       </c>
       <c r="Q121" s="32" t="n">
-        <v>-1.3</v>
+        <v>-0.6</v>
       </c>
       <c r="R121" s="23" t="inlineStr">
         <is>
@@ -13229,10 +13227,10 @@
       </c>
       <c r="N122" s="2" t="n"/>
       <c r="O122" s="32" t="n">
-        <v>-13.9</v>
+        <v>-16.2</v>
       </c>
       <c r="P122" s="32" t="n">
-        <v>-1.4</v>
+        <v>-3.5</v>
       </c>
       <c r="Q122" s="32" t="n"/>
       <c r="R122" s="23" t="inlineStr">
@@ -13453,13 +13451,13 @@
       </c>
       <c r="N124" s="2" t="n"/>
       <c r="O124" s="32" t="n">
-        <v>-10.8</v>
+        <v>-6.1</v>
       </c>
       <c r="P124" s="32" t="n">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="Q124" s="32" t="n">
-        <v>-2.45</v>
+        <v>0.41</v>
       </c>
       <c r="R124" s="23" t="inlineStr">
         <is>
@@ -13577,13 +13575,13 @@
       </c>
       <c r="N125" s="2" t="n"/>
       <c r="O125" s="32" t="n">
-        <v>-3.7</v>
+        <v>0.7</v>
       </c>
       <c r="P125" s="32" t="n">
-        <v>8.300000000000001</v>
+        <v>13.1</v>
       </c>
       <c r="Q125" s="32" t="n">
-        <v>2.44</v>
+        <v>7.51</v>
       </c>
       <c r="R125" s="23" t="inlineStr">
         <is>
@@ -13681,10 +13679,10 @@
       </c>
       <c r="N126" s="2" t="n"/>
       <c r="O126" s="32" t="n">
-        <v>-3.2</v>
+        <v>2.3</v>
       </c>
       <c r="P126" s="32" t="n">
-        <v>9.800000000000001</v>
+        <v>12</v>
       </c>
       <c r="Q126" s="32" t="n"/>
       <c r="R126" s="23" t="inlineStr">
@@ -13791,13 +13789,13 @@
       </c>
       <c r="N127" s="2" t="n"/>
       <c r="O127" s="32" t="n">
-        <v>-2.5</v>
+        <v>-0.2</v>
       </c>
       <c r="P127" s="32" t="n">
-        <v>9.6</v>
+        <v>11.3</v>
       </c>
       <c r="Q127" s="32" t="n">
-        <v>2.76</v>
+        <v>5.11</v>
       </c>
       <c r="R127" s="23" t="inlineStr">
         <is>
@@ -13911,10 +13909,10 @@
       </c>
       <c r="N128" s="2" t="n"/>
       <c r="O128" s="32" t="n">
-        <v>-1.6</v>
+        <v>0.7</v>
       </c>
       <c r="P128" s="32" t="n">
-        <v>9.699999999999999</v>
+        <v>13.9</v>
       </c>
       <c r="Q128" s="32" t="n"/>
       <c r="R128" s="23" t="inlineStr">
@@ -14021,13 +14019,13 @@
       </c>
       <c r="N129" s="2" t="n"/>
       <c r="O129" s="32" t="n">
-        <v>-1.7</v>
+        <v>-2.2</v>
       </c>
       <c r="P129" s="32" t="n">
-        <v>5.6</v>
+        <v>10.3</v>
       </c>
       <c r="Q129" s="32" t="n">
-        <v>1.78</v>
+        <v>4.12</v>
       </c>
       <c r="R129" s="23" t="inlineStr">
         <is>
@@ -14141,13 +14139,13 @@
       </c>
       <c r="N130" s="2" t="n"/>
       <c r="O130" s="32" t="n">
-        <v>-1.1</v>
+        <v>-0.3</v>
       </c>
       <c r="P130" s="32" t="n">
-        <v>13</v>
+        <v>8.1</v>
       </c>
       <c r="Q130" s="32" t="n">
-        <v>5.61</v>
+        <v>1.25</v>
       </c>
       <c r="R130" s="23" t="inlineStr">
         <is>
@@ -14261,13 +14259,13 @@
       </c>
       <c r="N131" s="2" t="n"/>
       <c r="O131" s="32" t="n">
-        <v>-1.4</v>
+        <v>4.8</v>
       </c>
       <c r="P131" s="32" t="n">
-        <v>11</v>
+        <v>11.7</v>
       </c>
       <c r="Q131" s="32" t="n">
-        <v>4.61</v>
+        <v>7.26</v>
       </c>
       <c r="R131" s="23" t="inlineStr">
         <is>
@@ -14377,13 +14375,13 @@
       </c>
       <c r="N132" s="2" t="n"/>
       <c r="O132" s="32" t="n">
-        <v>1.5</v>
+        <v>3.3</v>
       </c>
       <c r="P132" s="32" t="n">
-        <v>5.7</v>
+        <v>14.4</v>
       </c>
       <c r="Q132" s="32" t="n">
-        <v>3.62</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="R132" s="23" t="inlineStr">
         <is>
@@ -14493,13 +14491,13 @@
       </c>
       <c r="N133" s="2" t="n"/>
       <c r="O133" s="32" t="n">
-        <v>2.5</v>
+        <v>4.5</v>
       </c>
       <c r="P133" s="32" t="n">
-        <v>5.4</v>
+        <v>8.1</v>
       </c>
       <c r="Q133" s="32" t="n">
-        <v>3.54</v>
+        <v>5.91</v>
       </c>
       <c r="R133" s="23" t="inlineStr">
         <is>
@@ -14715,13 +14713,13 @@
       </c>
       <c r="N135" s="2" t="n"/>
       <c r="O135" s="32" t="n">
-        <v>8.4</v>
+        <v>7.5</v>
       </c>
       <c r="P135" s="32" t="n">
-        <v>14.4</v>
+        <v>10.6</v>
       </c>
       <c r="Q135" s="32" t="n">
-        <v>10.91</v>
+        <v>8.34</v>
       </c>
       <c r="R135" s="23" t="inlineStr">
         <is>
@@ -14831,13 +14829,13 @@
       </c>
       <c r="N136" s="2" t="n"/>
       <c r="O136" s="32" t="n">
-        <v>8.800000000000001</v>
+        <v>7.9</v>
       </c>
       <c r="P136" s="32" t="n">
-        <v>17.6</v>
+        <v>14.9</v>
       </c>
       <c r="Q136" s="32" t="n">
-        <v>12.41</v>
+        <v>11.39</v>
       </c>
       <c r="R136" s="23" t="inlineStr">
         <is>
@@ -14947,13 +14945,13 @@
       </c>
       <c r="N137" s="2" t="n"/>
       <c r="O137" s="32" t="n">
-        <v>5.2</v>
+        <v>6.9</v>
       </c>
       <c r="P137" s="32" t="n">
-        <v>14.4</v>
+        <v>13.5</v>
       </c>
       <c r="Q137" s="32" t="n">
-        <v>10.06</v>
+        <v>9.24</v>
       </c>
       <c r="R137" s="23" t="inlineStr">
         <is>
@@ -15063,10 +15061,10 @@
       </c>
       <c r="N138" s="2" t="n"/>
       <c r="O138" s="32" t="n">
-        <v>3.2</v>
+        <v>5.2</v>
       </c>
       <c r="P138" s="32" t="n">
-        <v>11.7</v>
+        <v>14.8</v>
       </c>
       <c r="Q138" s="32" t="n"/>
       <c r="R138" s="23" t="inlineStr">
@@ -15177,13 +15175,13 @@
       </c>
       <c r="N139" s="2" t="n"/>
       <c r="O139" s="32" t="n">
-        <v>2.6</v>
+        <v>4.5</v>
       </c>
       <c r="P139" s="32" t="n">
-        <v>11.1</v>
+        <v>13.1</v>
       </c>
       <c r="Q139" s="32" t="n">
-        <v>6.61</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="R139" s="23" t="inlineStr">
         <is>
@@ -15293,13 +15291,13 @@
       </c>
       <c r="N140" s="2" t="n"/>
       <c r="O140" s="32" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="P140" s="32" t="n">
-        <v>12.4</v>
+        <v>14</v>
       </c>
       <c r="Q140" s="32" t="n">
-        <v>9.050000000000001</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="R140" s="23" t="inlineStr">
         <is>
@@ -15511,13 +15509,13 @@
       </c>
       <c r="N142" s="2" t="n"/>
       <c r="O142" s="32" t="n">
-        <v>10.4</v>
+        <v>9.5</v>
       </c>
       <c r="P142" s="32" t="n">
-        <v>16.7</v>
+        <v>17.3</v>
       </c>
       <c r="Q142" s="32" t="n">
-        <v>12.72</v>
+        <v>12.11</v>
       </c>
       <c r="R142" s="23" t="inlineStr">
         <is>
@@ -15627,13 +15625,13 @@
       </c>
       <c r="N143" s="2" t="n"/>
       <c r="O143" s="32" t="n">
-        <v>12.6</v>
+        <v>15.1</v>
       </c>
       <c r="P143" s="32" t="n">
-        <v>25.1</v>
+        <v>26.1</v>
       </c>
       <c r="Q143" s="32" t="n">
-        <v>18.01</v>
+        <v>19.95</v>
       </c>
       <c r="R143" s="23" t="inlineStr">
         <is>
@@ -15943,13 +15941,13 @@
       </c>
       <c r="N146" s="2" t="n"/>
       <c r="O146" s="32" t="n">
-        <v>20.3</v>
+        <v>20.8</v>
       </c>
       <c r="P146" s="32" t="n">
-        <v>27.3</v>
+        <v>26.5</v>
       </c>
       <c r="Q146" s="32" t="n">
-        <v>23.99</v>
+        <v>23.68</v>
       </c>
       <c r="R146" s="23" t="inlineStr">
         <is>
@@ -16051,13 +16049,13 @@
       </c>
       <c r="N147" s="2" t="n"/>
       <c r="O147" s="32" t="n">
-        <v>17.6</v>
+        <v>18</v>
       </c>
       <c r="P147" s="32" t="n">
-        <v>23.6</v>
+        <v>22.2</v>
       </c>
       <c r="Q147" s="32" t="n">
-        <v>20.36</v>
+        <v>20.05</v>
       </c>
       <c r="R147" s="23" t="inlineStr">
         <is>
@@ -16269,13 +16267,13 @@
       </c>
       <c r="N149" s="2" t="n"/>
       <c r="O149" s="32" t="n">
-        <v>13.1</v>
+        <v>10.2</v>
       </c>
       <c r="P149" s="32" t="n">
-        <v>21.5</v>
+        <v>22</v>
       </c>
       <c r="Q149" s="32" t="n">
-        <v>16.88</v>
+        <v>16.61</v>
       </c>
       <c r="R149" s="23" t="inlineStr">
         <is>
@@ -16385,13 +16383,13 @@
       </c>
       <c r="N150" s="2" t="n"/>
       <c r="O150" s="32" t="n">
-        <v>7.7</v>
+        <v>6.1</v>
       </c>
       <c r="P150" s="32" t="n">
-        <v>11.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Q150" s="32" t="n">
-        <v>9.119999999999999</v>
+        <v>6.91</v>
       </c>
       <c r="R150" s="23" t="inlineStr">
         <is>
@@ -16501,13 +16499,13 @@
       </c>
       <c r="N151" s="2" t="n"/>
       <c r="O151" s="32" t="n">
-        <v>13.5</v>
+        <v>13.2</v>
       </c>
       <c r="P151" s="32" t="n">
-        <v>18.9</v>
+        <v>16</v>
       </c>
       <c r="Q151" s="32" t="n">
-        <v>15.29</v>
+        <v>14.39</v>
       </c>
       <c r="R151" s="23" t="inlineStr">
         <is>
@@ -16707,13 +16705,13 @@
       </c>
       <c r="N153" s="2" t="n"/>
       <c r="O153" s="32" t="n">
-        <v>12</v>
+        <v>10.2</v>
       </c>
       <c r="P153" s="32" t="n">
-        <v>16.5</v>
+        <v>13.2</v>
       </c>
       <c r="Q153" s="32" t="n">
-        <v>13.11</v>
+        <v>11.68</v>
       </c>
       <c r="R153" s="23" t="inlineStr">
         <is>
@@ -16827,13 +16825,13 @@
       </c>
       <c r="N154" s="2" t="n"/>
       <c r="O154" s="32" t="n">
-        <v>2.2</v>
+        <v>2.8</v>
       </c>
       <c r="P154" s="32" t="n">
-        <v>19.6</v>
+        <v>20</v>
       </c>
       <c r="Q154" s="32" t="n">
-        <v>10.64</v>
+        <v>11.26</v>
       </c>
       <c r="R154" s="23" t="inlineStr">
         <is>
@@ -17029,10 +17027,10 @@
       </c>
       <c r="N156" s="2" t="n"/>
       <c r="O156" s="32" t="n">
-        <v>-17.1</v>
+        <v>-9.699999999999999</v>
       </c>
       <c r="P156" s="32" t="n">
-        <v>8.699999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="Q156" s="32" t="n"/>
       <c r="R156" s="23" t="inlineStr">
@@ -17135,10 +17133,10 @@
       </c>
       <c r="N157" s="2" t="n"/>
       <c r="O157" s="32" t="n">
-        <v>5</v>
+        <v>5.9</v>
       </c>
       <c r="P157" s="32" t="n">
-        <v>11.4</v>
+        <v>13.4</v>
       </c>
       <c r="Q157" s="32" t="n"/>
       <c r="R157" s="23" t="inlineStr">
@@ -17526,7 +17524,7 @@
         <v>3.3</v>
       </c>
       <c r="P161" s="32" t="n">
-        <v>17.2</v>
+        <v>13.2</v>
       </c>
       <c r="Q161" s="32" t="n"/>
       <c r="R161" s="23" t="inlineStr">
@@ -17636,12 +17634,8 @@
           <t>⚡</t>
         </is>
       </c>
-      <c r="O162" s="32" t="n">
-        <v>-36.5</v>
-      </c>
-      <c r="P162" s="32" t="n">
-        <v>-2.4</v>
-      </c>
+      <c r="O162" s="32" t="n"/>
+      <c r="P162" s="32" t="n"/>
       <c r="Q162" s="32" t="n"/>
       <c r="R162" s="23" t="inlineStr">
         <is>
@@ -17963,10 +17957,10 @@
         </is>
       </c>
       <c r="O165" s="32" t="n">
-        <v>-39.9</v>
+        <v>-29.3</v>
       </c>
       <c r="P165" s="32" t="n">
-        <v>-9.9</v>
+        <v>-13.8</v>
       </c>
       <c r="Q165" s="32" t="n"/>
       <c r="R165" s="23" t="inlineStr">
@@ -18289,10 +18283,10 @@
         </is>
       </c>
       <c r="O168" s="32" t="n">
-        <v>-14.3</v>
+        <v>-18.9</v>
       </c>
       <c r="P168" s="32" t="n">
-        <v>3.6</v>
+        <v>-0.1</v>
       </c>
       <c r="Q168" s="32" t="n"/>
       <c r="R168" s="23" t="inlineStr">
@@ -18403,10 +18397,10 @@
         </is>
       </c>
       <c r="O169" s="32" t="n">
-        <v>-16.9</v>
+        <v>-23.6</v>
       </c>
       <c r="P169" s="32" t="n">
-        <v>-0.5</v>
+        <v>0</v>
       </c>
       <c r="Q169" s="32" t="n"/>
       <c r="R169" s="23" t="inlineStr">
@@ -18516,8 +18510,12 @@
           <t>⚡</t>
         </is>
       </c>
-      <c r="O170" s="32" t="n"/>
-      <c r="P170" s="32" t="n"/>
+      <c r="O170" s="32" t="n">
+        <v>-32.5</v>
+      </c>
+      <c r="P170" s="32" t="n">
+        <v>-2.9</v>
+      </c>
       <c r="Q170" s="32" t="n"/>
       <c r="R170" s="23" t="inlineStr">
         <is>
@@ -18729,10 +18727,10 @@
       </c>
       <c r="N172" s="3" t="n"/>
       <c r="O172" s="32" t="n">
-        <v>-11.7</v>
+        <v>-13.3</v>
       </c>
       <c r="P172" s="32" t="n">
-        <v>1.6</v>
+        <v>2.5</v>
       </c>
       <c r="Q172" s="32" t="n"/>
       <c r="R172" s="23" t="inlineStr">
@@ -18839,10 +18837,10 @@
       </c>
       <c r="N173" s="2" t="n"/>
       <c r="O173" s="32" t="n">
-        <v>-25.6</v>
+        <v>-18</v>
       </c>
       <c r="P173" s="32" t="n">
-        <v>1</v>
+        <v>-3.9</v>
       </c>
       <c r="Q173" s="32" t="n"/>
       <c r="R173" s="23" t="inlineStr">
@@ -19161,10 +19159,10 @@
       </c>
       <c r="N176" s="2" t="n"/>
       <c r="O176" s="32" t="n">
-        <v>1.3</v>
+        <v>0.1</v>
       </c>
       <c r="P176" s="32" t="n">
-        <v>8.5</v>
+        <v>8.1</v>
       </c>
       <c r="Q176" s="32" t="n"/>
       <c r="R176" s="23" t="inlineStr">
@@ -19263,10 +19261,10 @@
       </c>
       <c r="N177" s="2" t="n"/>
       <c r="O177" s="32" t="n">
-        <v>-26.6</v>
+        <v>-19.4</v>
       </c>
       <c r="P177" s="32" t="n">
-        <v>-18.8</v>
+        <v>-15.5</v>
       </c>
       <c r="Q177" s="32" t="n"/>
       <c r="R177" s="23" t="inlineStr">
@@ -20050,7 +20048,9 @@
         </is>
       </c>
       <c r="N185" s="2" t="n"/>
-      <c r="O185" s="32" t="n"/>
+      <c r="O185" s="32" t="n">
+        <v>-35.6</v>
+      </c>
       <c r="P185" s="32" t="n"/>
       <c r="Q185" s="32" t="n"/>
       <c r="R185" s="23" t="inlineStr">
@@ -20149,18 +20149,18 @@
       <c r="L186" s="3" t="n"/>
       <c r="M186" s="16" t="inlineStr">
         <is>
-          <t>奥伊米亚康</t>
+          <t>Tomtor</t>
         </is>
       </c>
       <c r="N186" s="2" t="n"/>
       <c r="O186" s="32" t="n">
-        <v>-36.9</v>
+        <v>-42.2</v>
       </c>
       <c r="P186" s="32" t="n">
-        <v>-21.3</v>
+        <v>-21.5</v>
       </c>
       <c r="Q186" s="32" t="n">
-        <v>-29.8</v>
+        <v>-33</v>
       </c>
       <c r="R186" s="23" t="inlineStr">
         <is>
@@ -20170,7 +20170,7 @@
       <c r="S186" s="37" t="n"/>
       <c r="T186" s="41" t="inlineStr">
         <is>
-          <t>明星站&lt;br&gt;北半球一均王</t>
+          <t>明星站 奥伊米亚康&lt;br&gt;北半球一均王</t>
         </is>
       </c>
       <c r="U186" s="2" t="inlineStr">
@@ -20263,13 +20263,13 @@
       </c>
       <c r="N187" s="2" t="n"/>
       <c r="O187" s="32" t="n">
-        <v>-37.4</v>
+        <v>-40.2</v>
       </c>
       <c r="P187" s="32" t="n">
-        <v>-21.6</v>
+        <v>-21</v>
       </c>
       <c r="Q187" s="32" t="n">
-        <v>-30.66</v>
+        <v>-32.55</v>
       </c>
       <c r="R187" s="23" t="inlineStr">
         <is>
@@ -20367,13 +20367,13 @@
       </c>
       <c r="N188" s="2" t="n"/>
       <c r="O188" s="32" t="n">
-        <v>-37</v>
+        <v>-38.9</v>
       </c>
       <c r="P188" s="32" t="n">
-        <v>-24.4</v>
+        <v>-25.5</v>
       </c>
       <c r="Q188" s="32" t="n">
-        <v>-31.61</v>
+        <v>-32.46</v>
       </c>
       <c r="R188" s="23" t="inlineStr">
         <is>
@@ -20471,13 +20471,13 @@
       </c>
       <c r="N189" s="2" t="n"/>
       <c r="O189" s="32" t="n">
-        <v>-43</v>
+        <v>-45</v>
       </c>
       <c r="P189" s="32" t="n">
-        <v>-23.6</v>
+        <v>-22.4</v>
       </c>
       <c r="Q189" s="32" t="n">
-        <v>-34.38</v>
+        <v>-35.99</v>
       </c>
       <c r="R189" s="23" t="inlineStr">
         <is>
@@ -20575,13 +20575,13 @@
       </c>
       <c r="N190" s="2" t="n"/>
       <c r="O190" s="32" t="n">
-        <v>-45.9</v>
+        <v>-44.6</v>
       </c>
       <c r="P190" s="32" t="n">
-        <v>-27</v>
+        <v>-25.9</v>
       </c>
       <c r="Q190" s="32" t="n">
-        <v>-38.66</v>
+        <v>-37.2</v>
       </c>
       <c r="R190" s="23" t="inlineStr">
         <is>
@@ -20679,13 +20679,13 @@
       </c>
       <c r="N191" s="2" t="n"/>
       <c r="O191" s="32" t="n">
-        <v>-36.4</v>
+        <v>-40.8</v>
       </c>
       <c r="P191" s="32" t="n">
-        <v>-19.4</v>
+        <v>-20.5</v>
       </c>
       <c r="Q191" s="32" t="n">
-        <v>-29.45</v>
+        <v>-32.43</v>
       </c>
       <c r="R191" s="23" t="inlineStr">
         <is>
@@ -20779,13 +20779,13 @@
       </c>
       <c r="N192" s="2" t="n"/>
       <c r="O192" s="32" t="n">
-        <v>-37.5</v>
+        <v>-39.8</v>
       </c>
       <c r="P192" s="32" t="n">
-        <v>-21</v>
+        <v>-19.7</v>
       </c>
       <c r="Q192" s="32" t="n">
-        <v>-30.21</v>
+        <v>-31.42</v>
       </c>
       <c r="R192" s="23" t="inlineStr">
         <is>
@@ -20884,13 +20884,13 @@
       </c>
       <c r="N193" s="2" t="n"/>
       <c r="O193" s="32" t="n">
-        <v>-33.3</v>
+        <v>-25.1</v>
       </c>
       <c r="P193" s="32" t="n">
-        <v>-13.5</v>
+        <v>-13</v>
       </c>
       <c r="Q193" s="32" t="n">
-        <v>-24.56</v>
+        <v>-19.8</v>
       </c>
       <c r="R193" s="23" t="inlineStr">
         <is>
@@ -20992,10 +20992,10 @@
       </c>
       <c r="N194" s="2" t="n"/>
       <c r="O194" s="32" t="n">
-        <v>-34</v>
+        <v>-39.6</v>
       </c>
       <c r="P194" s="32" t="n">
-        <v>-17.4</v>
+        <v>-28.9</v>
       </c>
       <c r="Q194" s="32" t="n"/>
       <c r="R194" s="23" t="inlineStr">
@@ -21090,13 +21090,13 @@
       </c>
       <c r="N195" s="2" t="n"/>
       <c r="O195" s="32" t="n">
-        <v>-39.1</v>
+        <v>-34.1</v>
       </c>
       <c r="P195" s="32" t="n">
-        <v>-20.8</v>
+        <v>-19.2</v>
       </c>
       <c r="Q195" s="32" t="n">
-        <v>-31.09</v>
+        <v>-28.09</v>
       </c>
       <c r="R195" s="23" t="inlineStr">
         <is>
@@ -21194,13 +21194,13 @@
       </c>
       <c r="N196" s="2" t="n"/>
       <c r="O196" s="32" t="n">
-        <v>-35.5</v>
+        <v>-36.3</v>
       </c>
       <c r="P196" s="32" t="n">
-        <v>-16.5</v>
+        <v>-14.4</v>
       </c>
       <c r="Q196" s="32" t="n">
-        <v>-27.41</v>
+        <v>-26.96</v>
       </c>
       <c r="R196" s="23" t="inlineStr">
         <is>
@@ -21298,13 +21298,13 @@
       </c>
       <c r="N197" s="24" t="n"/>
       <c r="O197" s="32" t="n">
-        <v>-33.4</v>
+        <v>-38.8</v>
       </c>
       <c r="P197" s="32" t="n">
-        <v>-16.4</v>
+        <v>-18.1</v>
       </c>
       <c r="Q197" s="32" t="n">
-        <v>-25.12</v>
+        <v>-28.75</v>
       </c>
       <c r="R197" s="23" t="inlineStr">
         <is>
@@ -21695,8 +21695,12 @@
         </is>
       </c>
       <c r="N201" s="2" t="n"/>
-      <c r="O201" s="32" t="n"/>
-      <c r="P201" s="32" t="n"/>
+      <c r="O201" s="32" t="n">
+        <v>-29.2</v>
+      </c>
+      <c r="P201" s="32" t="n">
+        <v>-1.8</v>
+      </c>
       <c r="Q201" s="32" t="n"/>
       <c r="R201" s="23" t="inlineStr">
         <is>
@@ -21797,8 +21801,12 @@
         </is>
       </c>
       <c r="N202" s="2" t="n"/>
-      <c r="O202" s="32" t="n"/>
-      <c r="P202" s="32" t="n"/>
+      <c r="O202" s="32" t="n">
+        <v>-26.8</v>
+      </c>
+      <c r="P202" s="32" t="n">
+        <v>-3.1</v>
+      </c>
       <c r="Q202" s="32" t="n"/>
       <c r="R202" s="23" t="inlineStr">
         <is>
@@ -21899,8 +21907,12 @@
         </is>
       </c>
       <c r="N203" s="2" t="n"/>
-      <c r="O203" s="32" t="n"/>
-      <c r="P203" s="32" t="n"/>
+      <c r="O203" s="32" t="n">
+        <v>-27</v>
+      </c>
+      <c r="P203" s="32" t="n">
+        <v>-5.9</v>
+      </c>
       <c r="Q203" s="32" t="n"/>
       <c r="R203" s="23" t="inlineStr">
         <is>
@@ -22307,12 +22319,8 @@
         </is>
       </c>
       <c r="N207" s="2" t="n"/>
-      <c r="O207" s="32" t="n">
-        <v>-37.7</v>
-      </c>
-      <c r="P207" s="32" t="n">
-        <v>-1.8</v>
-      </c>
+      <c r="O207" s="32" t="n"/>
+      <c r="P207" s="32" t="n"/>
       <c r="Q207" s="32" t="n"/>
       <c r="R207" s="23" t="inlineStr">
         <is>
@@ -22803,8 +22811,12 @@
         </is>
       </c>
       <c r="N212" s="2" t="n"/>
-      <c r="O212" s="32" t="n"/>
-      <c r="P212" s="32" t="n"/>
+      <c r="O212" s="32" t="n">
+        <v>-31.3</v>
+      </c>
+      <c r="P212" s="32" t="n">
+        <v>-3.4</v>
+      </c>
       <c r="Q212" s="32" t="n"/>
       <c r="R212" s="23" t="inlineStr">
         <is>
@@ -24509,8 +24521,12 @@
         </is>
       </c>
       <c r="N229" s="2" t="n"/>
-      <c r="O229" s="32" t="n"/>
-      <c r="P229" s="32" t="n"/>
+      <c r="O229" s="32" t="n">
+        <v>-28.4</v>
+      </c>
+      <c r="P229" s="32" t="n">
+        <v>-16</v>
+      </c>
       <c r="Q229" s="32" t="n"/>
       <c r="R229" s="23" t="inlineStr">
         <is>
@@ -25661,12 +25677,8 @@
         </is>
       </c>
       <c r="N241" s="2" t="n"/>
-      <c r="O241" s="32" t="n">
-        <v>-23</v>
-      </c>
-      <c r="P241" s="32" t="n">
-        <v>-5.5</v>
-      </c>
+      <c r="O241" s="32" t="n"/>
+      <c r="P241" s="32" t="n"/>
       <c r="Q241" s="32" t="n"/>
       <c r="R241" s="23" t="inlineStr">
         <is>
@@ -26240,13 +26252,13 @@
       </c>
       <c r="N247" s="2" t="n"/>
       <c r="O247" s="32" t="n">
-        <v>-5.1</v>
+        <v>-1.4</v>
       </c>
       <c r="P247" s="32" t="n">
-        <v>-0.2</v>
+        <v>1.5</v>
       </c>
       <c r="Q247" s="32" t="n">
-        <v>-2.38</v>
+        <v>-0.36</v>
       </c>
       <c r="R247" s="23" t="inlineStr">
         <is>
@@ -26356,13 +26368,13 @@
         </is>
       </c>
       <c r="O248" s="32" t="n">
-        <v>-9</v>
+        <v>-16.7</v>
       </c>
       <c r="P248" s="32" t="n">
-        <v>-2</v>
+        <v>-3.8</v>
       </c>
       <c r="Q248" s="32" t="n">
-        <v>-5.1</v>
+        <v>-10.73</v>
       </c>
       <c r="R248" s="23" t="inlineStr">
         <is>
@@ -26464,13 +26476,13 @@
       </c>
       <c r="N249" s="2" t="n"/>
       <c r="O249" s="32" t="n">
-        <v>-8.800000000000001</v>
+        <v>-9.1</v>
       </c>
       <c r="P249" s="32" t="n">
-        <v>-1.8</v>
+        <v>0.6</v>
       </c>
       <c r="Q249" s="32" t="n">
-        <v>-5.39</v>
+        <v>-5.3</v>
       </c>
       <c r="R249" s="23" t="inlineStr">
         <is>
@@ -26576,13 +26588,13 @@
       </c>
       <c r="N250" s="2" t="n"/>
       <c r="O250" s="32" t="n">
-        <v>-20</v>
+        <v>-14.9</v>
       </c>
       <c r="P250" s="32" t="n">
-        <v>-0.3</v>
+        <v>0.3</v>
       </c>
       <c r="Q250" s="32" t="n">
-        <v>-11.62</v>
+        <v>-7.4</v>
       </c>
       <c r="R250" s="23" t="inlineStr">
         <is>
@@ -26696,10 +26708,10 @@
         </is>
       </c>
       <c r="O251" s="32" t="n">
-        <v>-35.7</v>
+        <v>-39.8</v>
       </c>
       <c r="P251" s="32" t="n">
-        <v>-13.3</v>
+        <v>-15</v>
       </c>
       <c r="Q251" s="32" t="n"/>
       <c r="R251" s="23" t="inlineStr">
@@ -26794,13 +26806,13 @@
       </c>
       <c r="N252" s="2" t="n"/>
       <c r="O252" s="32" t="n">
-        <v>-19.5</v>
+        <v>-10.8</v>
       </c>
       <c r="P252" s="32" t="n">
-        <v>-2.4</v>
+        <v>1.5</v>
       </c>
       <c r="Q252" s="32" t="n">
-        <v>-11.5</v>
+        <v>-1.91</v>
       </c>
       <c r="R252" s="23" t="inlineStr">
         <is>
@@ -26992,13 +27004,13 @@
       </c>
       <c r="N254" s="2" t="n"/>
       <c r="O254" s="32" t="n">
-        <v>-29.9</v>
+        <v>-31.6</v>
       </c>
       <c r="P254" s="32" t="n">
-        <v>-18.2</v>
+        <v>-22.8</v>
       </c>
       <c r="Q254" s="32" t="n">
-        <v>-24.95</v>
+        <v>-25.84</v>
       </c>
       <c r="R254" s="23" t="inlineStr">
         <is>
@@ -27566,13 +27578,13 @@
       </c>
       <c r="N260" s="2" t="n"/>
       <c r="O260" s="32" t="n">
-        <v>-14.6</v>
+        <v>-22.6</v>
       </c>
       <c r="P260" s="32" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="Q260" s="32" t="n">
-        <v>-6.25</v>
+        <v>-10.84</v>
       </c>
       <c r="R260" s="23" t="inlineStr">
         <is>
@@ -27674,13 +27686,13 @@
       </c>
       <c r="N261" s="2" t="n"/>
       <c r="O261" s="32" t="n">
-        <v>-17.1</v>
+        <v>-15.6</v>
       </c>
       <c r="P261" s="32" t="n">
-        <v>2.3</v>
+        <v>1.3</v>
       </c>
       <c r="Q261" s="32" t="n">
-        <v>-9.68</v>
+        <v>-6.34</v>
       </c>
       <c r="R261" s="23" t="inlineStr">
         <is>
@@ -27786,13 +27798,13 @@
       </c>
       <c r="N262" s="2" t="n"/>
       <c r="O262" s="32" t="n">
-        <v>-22</v>
+        <v>-1.9</v>
       </c>
       <c r="P262" s="32" t="n">
-        <v>-1.9</v>
+        <v>1.9</v>
       </c>
       <c r="Q262" s="32" t="n">
-        <v>-12.46</v>
+        <v>0.29</v>
       </c>
       <c r="R262" s="23" t="inlineStr">
         <is>
@@ -27992,13 +28004,13 @@
       </c>
       <c r="N264" s="2" t="n"/>
       <c r="O264" s="32" t="n">
-        <v>-13.2</v>
+        <v>-11.7</v>
       </c>
       <c r="P264" s="32" t="n">
-        <v>0.9</v>
+        <v>5.3</v>
       </c>
       <c r="Q264" s="32" t="n">
-        <v>-7.62</v>
+        <v>-3.96</v>
       </c>
       <c r="R264" s="23" t="inlineStr">
         <is>
@@ -28112,10 +28124,10 @@
       </c>
       <c r="N265" s="2" t="n"/>
       <c r="O265" s="32" t="n">
-        <v>-52.1</v>
+        <v>-54.1</v>
       </c>
       <c r="P265" s="32" t="n">
-        <v>-41.6</v>
+        <v>-41.9</v>
       </c>
       <c r="Q265" s="32" t="n"/>
       <c r="R265" s="23" t="inlineStr">
@@ -29156,13 +29168,13 @@
       </c>
       <c r="N276" s="2" t="n"/>
       <c r="O276" s="32" t="n">
-        <v>-45</v>
+        <v>-44.2</v>
       </c>
       <c r="P276" s="32" t="n">
-        <v>-30</v>
+        <v>-28.9</v>
       </c>
       <c r="Q276" s="32" t="n">
-        <v>-38.8</v>
+        <v>-37.14</v>
       </c>
       <c r="R276" s="23" t="inlineStr">
         <is>

--- a/气象/For_Python_站点信息和记录.xlsx
+++ b/气象/For_Python_站点信息和记录.xlsx
@@ -796,8 +796,8 @@
     <col width="18.59765625" customWidth="1" style="8" min="25" max="25"/>
     <col width="12.59765625" customWidth="1" style="5" min="26" max="30"/>
     <col width="12.59765625" customWidth="1" style="8" min="31" max="32"/>
-    <col width="12.59765625" customWidth="1" style="5" min="33" max="299"/>
-    <col width="12.59765625" customWidth="1" style="5" min="300" max="16384"/>
+    <col width="12.59765625" customWidth="1" style="5" min="33" max="304"/>
+    <col width="12.59765625" customWidth="1" style="5" min="305" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="27.75" customFormat="1" customHeight="1" s="11">
@@ -1020,13 +1020,13 @@
         </is>
       </c>
       <c r="O2" s="32" t="n">
-        <v>-31.7</v>
+        <v>-26.1</v>
       </c>
       <c r="P2" s="32" t="n">
-        <v>-17.9</v>
+        <v>-14.4</v>
       </c>
       <c r="Q2" s="32" t="n">
-        <v>-24.75</v>
+        <v>-20.4</v>
       </c>
       <c r="R2" s="23" t="inlineStr">
         <is>
@@ -1126,10 +1126,10 @@
         </is>
       </c>
       <c r="O3" s="32" t="n">
-        <v>-33.1</v>
+        <v>-26.4</v>
       </c>
       <c r="P3" s="32" t="n">
-        <v>-16.1</v>
+        <v>-13</v>
       </c>
       <c r="Q3" s="32" t="n"/>
       <c r="R3" s="23" t="n"/>
@@ -1322,10 +1322,10 @@
       </c>
       <c r="N5" s="2" t="n"/>
       <c r="O5" s="32" t="n">
-        <v>-26.4</v>
+        <v>-21</v>
       </c>
       <c r="P5" s="32" t="n">
-        <v>-10.7</v>
+        <v>-2.3</v>
       </c>
       <c r="Q5" s="32" t="n"/>
       <c r="R5" s="23" t="n"/>
@@ -1422,10 +1422,10 @@
         </is>
       </c>
       <c r="O6" s="32" t="n">
-        <v>-30.4</v>
+        <v>-25.6</v>
       </c>
       <c r="P6" s="32" t="n">
-        <v>-9.199999999999999</v>
+        <v>-4.4</v>
       </c>
       <c r="Q6" s="32" t="n"/>
       <c r="R6" s="23" t="n"/>
@@ -1522,10 +1522,10 @@
         </is>
       </c>
       <c r="O7" s="32" t="n">
-        <v>-24</v>
+        <v>-22.3</v>
       </c>
       <c r="P7" s="32" t="n">
-        <v>-9.1</v>
+        <v>-6.5</v>
       </c>
       <c r="Q7" s="32" t="n"/>
       <c r="R7" s="23" t="n"/>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>rp5</t>
+          <t>ogimet</t>
         </is>
       </c>
       <c r="C8" s="46" t="n">
@@ -1630,13 +1630,13 @@
       </c>
       <c r="N8" s="2" t="n"/>
       <c r="O8" s="32" t="n">
-        <v>-26.7</v>
+        <v>-22.4</v>
       </c>
       <c r="P8" s="32" t="n">
-        <v>-6.7</v>
+        <v>-3.3</v>
       </c>
       <c r="Q8" s="32" t="n">
-        <v>-17.05</v>
+        <v>-13.46</v>
       </c>
       <c r="R8" s="23" t="inlineStr">
         <is>
@@ -1702,7 +1702,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>rp5</t>
+          <t>ogimet</t>
         </is>
       </c>
       <c r="C9" s="46" t="n">
@@ -1742,13 +1742,13 @@
       </c>
       <c r="N9" s="2" t="n"/>
       <c r="O9" s="32" t="n">
-        <v>-27.8</v>
+        <v>-24.5</v>
       </c>
       <c r="P9" s="32" t="n">
-        <v>-12.8</v>
+        <v>-10.8</v>
       </c>
       <c r="Q9" s="32" t="n">
-        <v>-21.29</v>
+        <v>-18.25</v>
       </c>
       <c r="R9" s="23" t="inlineStr">
         <is>
@@ -1818,7 +1818,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>rp5</t>
+          <t>ogimet</t>
         </is>
       </c>
       <c r="C10" s="46" t="n">
@@ -1862,13 +1862,13 @@
         </is>
       </c>
       <c r="O10" s="32" t="n">
-        <v>-27.9</v>
+        <v>-20.2</v>
       </c>
       <c r="P10" s="32" t="n">
-        <v>-6.2</v>
+        <v>1.5</v>
       </c>
       <c r="Q10" s="32" t="n">
-        <v>-18.56</v>
+        <v>-9.91</v>
       </c>
       <c r="R10" s="23" t="inlineStr">
         <is>
@@ -1934,7 +1934,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>rp5</t>
+          <t>ogimet</t>
         </is>
       </c>
       <c r="C11" s="46" t="n">
@@ -1978,13 +1978,13 @@
         </is>
       </c>
       <c r="O11" s="32" t="n">
-        <v>-28.2</v>
+        <v>-19.8</v>
       </c>
       <c r="P11" s="32" t="n">
-        <v>-1.9</v>
+        <v>6.4</v>
       </c>
       <c r="Q11" s="32" t="n">
-        <v>-15.72</v>
+        <v>-5.24</v>
       </c>
       <c r="R11" s="23" t="inlineStr">
         <is>
@@ -2050,7 +2050,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>rp5</t>
+          <t>ogimet</t>
         </is>
       </c>
       <c r="C12" s="46" t="n">
@@ -2090,13 +2090,13 @@
       </c>
       <c r="N12" s="2" t="n"/>
       <c r="O12" s="32" t="n">
-        <v>-27.6</v>
+        <v>-21.2</v>
       </c>
       <c r="P12" s="32" t="n">
-        <v>-9.699999999999999</v>
+        <v>0.2</v>
       </c>
       <c r="Q12" s="32" t="n">
-        <v>-19.19</v>
+        <v>-11.54</v>
       </c>
       <c r="R12" s="23" t="inlineStr">
         <is>
@@ -2162,7 +2162,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>rp5</t>
+          <t>ogimet</t>
         </is>
       </c>
       <c r="C13" s="46" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="O13" s="32" t="n">
-        <v>-28.4</v>
+        <v>-23.3</v>
       </c>
       <c r="P13" s="32" t="n">
-        <v>-11.4</v>
+        <v>-6.6</v>
       </c>
       <c r="Q13" s="32" t="n">
-        <v>-20.21</v>
+        <v>-16.72</v>
       </c>
       <c r="R13" s="23" t="inlineStr">
         <is>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>rp5</t>
+          <t>ogimet</t>
         </is>
       </c>
       <c r="C14" s="46" t="n">
@@ -2318,13 +2318,13 @@
       </c>
       <c r="N14" s="2" t="n"/>
       <c r="O14" s="32" t="n">
-        <v>-13.8</v>
+        <v>-10.1</v>
       </c>
       <c r="P14" s="32" t="n">
-        <v>0.6</v>
+        <v>4.9</v>
       </c>
       <c r="Q14" s="32" t="n">
-        <v>-6.71</v>
+        <v>-3.47</v>
       </c>
       <c r="R14" s="23" t="inlineStr">
         <is>
@@ -2424,10 +2424,10 @@
       </c>
       <c r="N15" s="2" t="n"/>
       <c r="O15" s="32" t="n">
-        <v>-25.7</v>
+        <v>-21.9</v>
       </c>
       <c r="P15" s="32" t="n">
-        <v>-2.4</v>
+        <v>1.8</v>
       </c>
       <c r="Q15" s="32" t="n"/>
       <c r="R15" s="23" t="n"/>
@@ -2486,7 +2486,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>rp5</t>
+          <t>ogimet</t>
         </is>
       </c>
       <c r="C16" s="46" t="n">
@@ -4971,12 +4971,8 @@
           <t>▲</t>
         </is>
       </c>
-      <c r="O43" s="32" t="n">
-        <v>-29.8</v>
-      </c>
-      <c r="P43" s="32" t="n">
-        <v>-18.6</v>
-      </c>
+      <c r="O43" s="32" t="n"/>
+      <c r="P43" s="32" t="n"/>
       <c r="Q43" s="32" t="n"/>
       <c r="R43" s="23" t="n"/>
       <c r="S43" s="37" t="n"/>
@@ -7838,13 +7834,13 @@
       </c>
       <c r="N75" s="2" t="n"/>
       <c r="O75" s="32" t="n">
-        <v>-24.3</v>
+        <v>-19.8</v>
       </c>
       <c r="P75" s="32" t="n">
-        <v>-5.1</v>
+        <v>1.9</v>
       </c>
       <c r="Q75" s="32" t="n">
-        <v>-14.72</v>
+        <v>-10.31</v>
       </c>
       <c r="R75" s="23" t="inlineStr">
         <is>
@@ -7954,13 +7950,13 @@
         </is>
       </c>
       <c r="O76" s="32" t="n">
-        <v>-29.8</v>
+        <v>-28.5</v>
       </c>
       <c r="P76" s="32" t="n">
-        <v>-7.4</v>
+        <v>-7.9</v>
       </c>
       <c r="Q76" s="32" t="n">
-        <v>-19.6</v>
+        <v>-17.82</v>
       </c>
       <c r="R76" s="23" t="inlineStr">
         <is>
@@ -8070,13 +8066,13 @@
         </is>
       </c>
       <c r="O77" s="32" t="n">
-        <v>-32.5</v>
+        <v>-34.4</v>
       </c>
       <c r="P77" s="32" t="n">
-        <v>-7.6</v>
+        <v>-7.4</v>
       </c>
       <c r="Q77" s="32" t="n">
-        <v>-20.61</v>
+        <v>-21.52</v>
       </c>
       <c r="R77" s="23" t="inlineStr">
         <is>
@@ -8182,13 +8178,13 @@
       </c>
       <c r="N78" s="2" t="n"/>
       <c r="O78" s="32" t="n">
-        <v>-26.9</v>
+        <v>-28.6</v>
       </c>
       <c r="P78" s="32" t="n">
-        <v>-6</v>
+        <v>-5.7</v>
       </c>
       <c r="Q78" s="32" t="n">
-        <v>-17.26</v>
+        <v>-17.49</v>
       </c>
       <c r="R78" s="23" t="inlineStr">
         <is>
@@ -8298,13 +8294,13 @@
         </is>
       </c>
       <c r="O79" s="32" t="n">
-        <v>-29.5</v>
+        <v>-32.9</v>
       </c>
       <c r="P79" s="32" t="n">
-        <v>-4.6</v>
+        <v>-3.8</v>
       </c>
       <c r="Q79" s="32" t="n">
-        <v>-17.36</v>
+        <v>-18.54</v>
       </c>
       <c r="R79" s="23" t="inlineStr">
         <is>
@@ -8410,13 +8406,13 @@
       </c>
       <c r="N80" s="2" t="n"/>
       <c r="O80" s="32" t="n">
-        <v>-22.9</v>
+        <v>-20.9</v>
       </c>
       <c r="P80" s="32" t="n">
-        <v>-4.4</v>
+        <v>-1.2</v>
       </c>
       <c r="Q80" s="32" t="n">
-        <v>-13.3</v>
+        <v>-10.94</v>
       </c>
       <c r="R80" s="23" t="inlineStr">
         <is>
@@ -8482,7 +8478,7 @@
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>rp5</t>
+          <t>ogimet</t>
         </is>
       </c>
       <c r="C81" s="46" t="n">
@@ -8526,10 +8522,10 @@
         </is>
       </c>
       <c r="O81" s="32" t="n">
-        <v>-28.7</v>
+        <v>-26.8</v>
       </c>
       <c r="P81" s="32" t="n">
-        <v>-3.4</v>
+        <v>2.6</v>
       </c>
       <c r="Q81" s="32" t="n"/>
       <c r="R81" s="23" t="inlineStr">
@@ -8645,13 +8641,13 @@
         </is>
       </c>
       <c r="O82" s="32" t="n">
-        <v>-29.1</v>
+        <v>-27</v>
       </c>
       <c r="P82" s="32" t="n">
-        <v>-1.9</v>
+        <v>1</v>
       </c>
       <c r="Q82" s="32" t="n">
-        <v>-16.68</v>
+        <v>-14.54</v>
       </c>
       <c r="R82" s="23" t="inlineStr">
         <is>
@@ -8757,13 +8753,13 @@
       </c>
       <c r="N83" s="2" t="n"/>
       <c r="O83" s="32" t="n">
-        <v>-17</v>
+        <v>-19.7</v>
       </c>
       <c r="P83" s="32" t="n">
-        <v>-4.7</v>
+        <v>-0.9</v>
       </c>
       <c r="Q83" s="32" t="n">
-        <v>-10.05</v>
+        <v>-10.9</v>
       </c>
       <c r="R83" s="23" t="inlineStr">
         <is>
@@ -8873,13 +8869,13 @@
         </is>
       </c>
       <c r="O84" s="32" t="n">
-        <v>-24.9</v>
+        <v>-21.2</v>
       </c>
       <c r="P84" s="32" t="n">
-        <v>-5.1</v>
+        <v>0.9</v>
       </c>
       <c r="Q84" s="32" t="n">
-        <v>-16.01</v>
+        <v>-11.77</v>
       </c>
       <c r="R84" s="23" t="inlineStr">
         <is>
@@ -8989,13 +8985,13 @@
         </is>
       </c>
       <c r="O85" s="32" t="n">
-        <v>-23.6</v>
+        <v>-21.2</v>
       </c>
       <c r="P85" s="32" t="n">
-        <v>-5.6</v>
+        <v>1.4</v>
       </c>
       <c r="Q85" s="32" t="n">
-        <v>-15.34</v>
+        <v>-10.16</v>
       </c>
       <c r="R85" s="23" t="inlineStr">
         <is>
@@ -9101,13 +9097,13 @@
       </c>
       <c r="N86" s="2" t="n"/>
       <c r="O86" s="32" t="n">
-        <v>-20.7</v>
+        <v>-16.2</v>
       </c>
       <c r="P86" s="32" t="n">
-        <v>-6</v>
+        <v>-3.2</v>
       </c>
       <c r="Q86" s="32" t="n">
-        <v>-13.64</v>
+        <v>-9.85</v>
       </c>
       <c r="R86" s="23" t="inlineStr">
         <is>
@@ -9225,13 +9221,13 @@
         </is>
       </c>
       <c r="O87" s="32" t="n">
-        <v>-28.6</v>
+        <v>-23.5</v>
       </c>
       <c r="P87" s="32" t="n">
-        <v>-13.8</v>
+        <v>-11.1</v>
       </c>
       <c r="Q87" s="32" t="n">
-        <v>-21.9</v>
+        <v>-17.62</v>
       </c>
       <c r="R87" s="23" t="inlineStr">
         <is>
@@ -9337,13 +9333,13 @@
       </c>
       <c r="N88" s="2" t="n"/>
       <c r="O88" s="32" t="n">
-        <v>-18.7</v>
+        <v>-8.5</v>
       </c>
       <c r="P88" s="32" t="n">
-        <v>-3.4</v>
+        <v>6.8</v>
       </c>
       <c r="Q88" s="32" t="n">
-        <v>-11.74</v>
+        <v>-0.95</v>
       </c>
       <c r="R88" s="23" t="inlineStr">
         <is>
@@ -9555,13 +9551,13 @@
         </is>
       </c>
       <c r="O90" s="32" t="n">
-        <v>-15.6</v>
+        <v>-1.1</v>
       </c>
       <c r="P90" s="32" t="n">
-        <v>0.8</v>
+        <v>4.6</v>
       </c>
       <c r="Q90" s="32" t="n">
-        <v>-8.34</v>
+        <v>1.1</v>
       </c>
       <c r="R90" s="23" t="inlineStr">
         <is>
@@ -9663,13 +9659,13 @@
       </c>
       <c r="N91" s="2" t="n"/>
       <c r="O91" s="32" t="n">
-        <v>-19</v>
+        <v>-3.7</v>
       </c>
       <c r="P91" s="32" t="n">
-        <v>-5.8</v>
+        <v>1.1</v>
       </c>
       <c r="Q91" s="32" t="n">
-        <v>-11.21</v>
+        <v>-0.71</v>
       </c>
       <c r="R91" s="23" t="inlineStr">
         <is>
@@ -9771,13 +9767,13 @@
       </c>
       <c r="N92" s="2" t="n"/>
       <c r="O92" s="32" t="n">
-        <v>-24.9</v>
+        <v>-24.6</v>
       </c>
       <c r="P92" s="32" t="n">
-        <v>-2.5</v>
+        <v>-3.5</v>
       </c>
       <c r="Q92" s="32" t="n">
-        <v>-12.18</v>
+        <v>-12.1</v>
       </c>
       <c r="R92" s="23" t="inlineStr">
         <is>
@@ -9883,13 +9879,13 @@
       </c>
       <c r="N93" s="2" t="n"/>
       <c r="O93" s="32" t="n">
-        <v>-8.9</v>
+        <v>-8.6</v>
       </c>
       <c r="P93" s="32" t="n">
-        <v>6.8</v>
+        <v>10.3</v>
       </c>
       <c r="Q93" s="32" t="n">
-        <v>-1.67</v>
+        <v>0.96</v>
       </c>
       <c r="R93" s="23" t="inlineStr">
         <is>
@@ -10003,10 +9999,10 @@
         </is>
       </c>
       <c r="O94" s="32" t="n">
-        <v>-12.7</v>
+        <v>-12.5</v>
       </c>
       <c r="P94" s="32" t="n">
-        <v>5.2</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="Q94" s="32" t="n"/>
       <c r="R94" s="23" t="inlineStr">
@@ -10121,13 +10117,13 @@
       </c>
       <c r="N95" s="2" t="n"/>
       <c r="O95" s="32" t="n">
-        <v>-10</v>
+        <v>-8.9</v>
       </c>
       <c r="P95" s="32" t="n">
-        <v>3.5</v>
+        <v>7.4</v>
       </c>
       <c r="Q95" s="32" t="n">
-        <v>-2.55</v>
+        <v>0.48</v>
       </c>
       <c r="R95" s="23" t="inlineStr">
         <is>
@@ -10249,10 +10245,10 @@
         </is>
       </c>
       <c r="O96" s="32" t="n">
-        <v>-12.7</v>
+        <v>-12.2</v>
       </c>
       <c r="P96" s="32" t="n">
-        <v>2.8</v>
+        <v>6.9</v>
       </c>
       <c r="Q96" s="32" t="n"/>
       <c r="R96" s="23" t="inlineStr">
@@ -10367,14 +10363,12 @@
       </c>
       <c r="N97" s="2" t="n"/>
       <c r="O97" s="32" t="n">
-        <v>-15.5</v>
+        <v>-6.4</v>
       </c>
       <c r="P97" s="32" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Q97" s="32" t="n">
-        <v>-7.19</v>
-      </c>
+        <v>7.3</v>
+      </c>
+      <c r="Q97" s="32" t="n"/>
       <c r="R97" s="23" t="inlineStr">
         <is>
           <t>Y</t>
@@ -10487,10 +10481,10 @@
       </c>
       <c r="N98" s="2" t="n"/>
       <c r="O98" s="32" t="n">
-        <v>-27</v>
+        <v>-22.7</v>
       </c>
       <c r="P98" s="32" t="n">
-        <v>-5.4</v>
+        <v>-1.6</v>
       </c>
       <c r="Q98" s="32" t="n"/>
       <c r="R98" s="23" t="inlineStr">
@@ -10605,13 +10599,13 @@
       </c>
       <c r="N99" s="2" t="n"/>
       <c r="O99" s="32" t="n">
-        <v>-26.4</v>
+        <v>-16.6</v>
       </c>
       <c r="P99" s="32" t="n">
-        <v>-4.9</v>
+        <v>-3.4</v>
       </c>
       <c r="Q99" s="32" t="n">
-        <v>-17.34</v>
+        <v>-8.6</v>
       </c>
       <c r="R99" s="23" t="inlineStr">
         <is>
@@ -10937,13 +10931,13 @@
       </c>
       <c r="N102" s="2" t="n"/>
       <c r="O102" s="32" t="n">
-        <v>-26.2</v>
+        <v>-15.4</v>
       </c>
       <c r="P102" s="32" t="n">
-        <v>-2.2</v>
+        <v>-0.7</v>
       </c>
       <c r="Q102" s="32" t="n">
-        <v>-14.2</v>
+        <v>-8.15</v>
       </c>
       <c r="R102" s="23" t="inlineStr">
         <is>
@@ -11053,10 +11047,10 @@
       </c>
       <c r="N103" s="2" t="n"/>
       <c r="O103" s="32" t="n">
-        <v>-27.4</v>
+        <v>-15.1</v>
       </c>
       <c r="P103" s="32" t="n">
-        <v>-1.6</v>
+        <v>-0.6</v>
       </c>
       <c r="Q103" s="32" t="n"/>
       <c r="R103" s="23" t="inlineStr">
@@ -11163,10 +11157,10 @@
       </c>
       <c r="N104" s="2" t="n"/>
       <c r="O104" s="32" t="n">
-        <v>-26.2</v>
+        <v>-24.5</v>
       </c>
       <c r="P104" s="32" t="n">
-        <v>-1.2</v>
+        <v>1.2</v>
       </c>
       <c r="Q104" s="32" t="n"/>
       <c r="R104" s="23" t="inlineStr">
@@ -11289,13 +11283,13 @@
         </is>
       </c>
       <c r="O105" s="32" t="n">
-        <v>-26.5</v>
+        <v>-27.5</v>
       </c>
       <c r="P105" s="32" t="n">
-        <v>-2.8</v>
+        <v>-1.1</v>
       </c>
       <c r="Q105" s="32" t="n">
-        <v>-14.89</v>
+        <v>-13.74</v>
       </c>
       <c r="R105" s="23" t="inlineStr">
         <is>
@@ -11405,10 +11399,10 @@
         </is>
       </c>
       <c r="O106" s="32" t="n">
-        <v>-25.9</v>
+        <v>-26</v>
       </c>
       <c r="P106" s="32" t="n">
-        <v>-11.5</v>
+        <v>-9.9</v>
       </c>
       <c r="Q106" s="32" t="n"/>
       <c r="R106" s="23" t="inlineStr">
@@ -11625,13 +11619,13 @@
       </c>
       <c r="N108" s="2" t="n"/>
       <c r="O108" s="32" t="n">
-        <v>-24.2</v>
+        <v>-21.3</v>
       </c>
       <c r="P108" s="32" t="n">
-        <v>-11.9</v>
+        <v>-9.300000000000001</v>
       </c>
       <c r="Q108" s="32" t="n">
-        <v>-18.01</v>
+        <v>-15.33</v>
       </c>
       <c r="R108" s="23" t="inlineStr">
         <is>
@@ -11838,8 +11832,12 @@
         </is>
       </c>
       <c r="N110" s="2" t="n"/>
-      <c r="O110" s="32" t="n"/>
-      <c r="P110" s="32" t="n"/>
+      <c r="O110" s="32" t="n">
+        <v>-27.1</v>
+      </c>
+      <c r="P110" s="32" t="n">
+        <v>-8.300000000000001</v>
+      </c>
       <c r="Q110" s="32" t="n"/>
       <c r="R110" s="23" t="inlineStr">
         <is>
@@ -11953,13 +11951,13 @@
       </c>
       <c r="N111" s="2" t="n"/>
       <c r="O111" s="32" t="n">
-        <v>-20.6</v>
+        <v>-16.9</v>
       </c>
       <c r="P111" s="32" t="n">
-        <v>-7.6</v>
+        <v>-1.2</v>
       </c>
       <c r="Q111" s="32" t="n">
-        <v>-13.43</v>
+        <v>-8.029999999999999</v>
       </c>
       <c r="R111" s="23" t="inlineStr">
         <is>
@@ -12065,10 +12063,10 @@
       </c>
       <c r="N112" s="2" t="n"/>
       <c r="O112" s="32" t="n">
-        <v>-10.8</v>
+        <v>-7.8</v>
       </c>
       <c r="P112" s="32" t="n">
-        <v>-0.5</v>
+        <v>5.5</v>
       </c>
       <c r="Q112" s="32" t="n"/>
       <c r="R112" s="23" t="inlineStr">
@@ -12171,10 +12169,10 @@
       </c>
       <c r="N113" s="2" t="n"/>
       <c r="O113" s="32" t="n">
-        <v>-9.699999999999999</v>
+        <v>-14.1</v>
       </c>
       <c r="P113" s="32" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="Q113" s="32" t="n"/>
       <c r="R113" s="23" t="inlineStr">
@@ -12285,10 +12283,10 @@
         </is>
       </c>
       <c r="O114" s="32" t="n">
-        <v>-16</v>
+        <v>-21.6</v>
       </c>
       <c r="P114" s="32" t="n">
-        <v>3.5</v>
+        <v>6.7</v>
       </c>
       <c r="Q114" s="32" t="n"/>
       <c r="R114" s="23" t="inlineStr">
@@ -12407,10 +12405,10 @@
         </is>
       </c>
       <c r="O115" s="32" t="n">
-        <v>-12.9</v>
+        <v>-17.7</v>
       </c>
       <c r="P115" s="32" t="n">
-        <v>0.9</v>
+        <v>7.2</v>
       </c>
       <c r="Q115" s="32" t="n"/>
       <c r="R115" s="23" t="inlineStr">
@@ -12525,13 +12523,13 @@
       </c>
       <c r="N116" s="2" t="n"/>
       <c r="O116" s="32" t="n">
-        <v>-6.5</v>
+        <v>-6.2</v>
       </c>
       <c r="P116" s="32" t="n">
-        <v>12.1</v>
+        <v>20.1</v>
       </c>
       <c r="Q116" s="32" t="n">
-        <v>2.83</v>
+        <v>5.97</v>
       </c>
       <c r="R116" s="23" t="inlineStr">
         <is>
@@ -12637,10 +12635,10 @@
       </c>
       <c r="N117" s="2" t="n"/>
       <c r="O117" s="32" t="n">
-        <v>-8.1</v>
+        <v>-2.1</v>
       </c>
       <c r="P117" s="32" t="n">
-        <v>9.199999999999999</v>
+        <v>16.9</v>
       </c>
       <c r="Q117" s="32" t="n"/>
       <c r="R117" s="23" t="inlineStr">
@@ -12751,10 +12749,10 @@
         </is>
       </c>
       <c r="O118" s="32" t="n">
-        <v>-19</v>
+        <v>-10.4</v>
       </c>
       <c r="P118" s="32" t="n">
-        <v>-0.7</v>
+        <v>6.2</v>
       </c>
       <c r="Q118" s="32" t="n"/>
       <c r="R118" s="23" t="inlineStr">
@@ -12869,13 +12867,13 @@
       </c>
       <c r="N119" s="2" t="n"/>
       <c r="O119" s="32" t="n">
-        <v>-9.800000000000001</v>
+        <v>4</v>
       </c>
       <c r="P119" s="32" t="n">
-        <v>6.1</v>
+        <v>7.9</v>
       </c>
       <c r="Q119" s="32" t="n">
-        <v>-2.26</v>
+        <v>5.12</v>
       </c>
       <c r="R119" s="23" t="inlineStr">
         <is>
@@ -13103,13 +13101,13 @@
       </c>
       <c r="N121" s="2" t="n"/>
       <c r="O121" s="32" t="n">
-        <v>-3.6</v>
+        <v>-1.9</v>
       </c>
       <c r="P121" s="32" t="n">
-        <v>4.2</v>
+        <v>11.6</v>
       </c>
       <c r="Q121" s="32" t="n">
-        <v>-0.6</v>
+        <v>2.71</v>
       </c>
       <c r="R121" s="23" t="inlineStr">
         <is>
@@ -13227,10 +13225,10 @@
       </c>
       <c r="N122" s="2" t="n"/>
       <c r="O122" s="32" t="n">
-        <v>-16.2</v>
+        <v>-19.6</v>
       </c>
       <c r="P122" s="32" t="n">
-        <v>-3.5</v>
+        <v>4.3</v>
       </c>
       <c r="Q122" s="32" t="n"/>
       <c r="R122" s="23" t="inlineStr">
@@ -13451,13 +13449,13 @@
       </c>
       <c r="N124" s="2" t="n"/>
       <c r="O124" s="32" t="n">
-        <v>-6.1</v>
+        <v>-1.4</v>
       </c>
       <c r="P124" s="32" t="n">
-        <v>7.5</v>
+        <v>12.8</v>
       </c>
       <c r="Q124" s="32" t="n">
-        <v>0.41</v>
+        <v>4.68</v>
       </c>
       <c r="R124" s="23" t="inlineStr">
         <is>
@@ -13575,13 +13573,13 @@
       </c>
       <c r="N125" s="2" t="n"/>
       <c r="O125" s="32" t="n">
-        <v>0.7</v>
+        <v>2.8</v>
       </c>
       <c r="P125" s="32" t="n">
-        <v>13.1</v>
+        <v>12.2</v>
       </c>
       <c r="Q125" s="32" t="n">
-        <v>7.51</v>
+        <v>6.74</v>
       </c>
       <c r="R125" s="23" t="inlineStr">
         <is>
@@ -13679,10 +13677,10 @@
       </c>
       <c r="N126" s="2" t="n"/>
       <c r="O126" s="32" t="n">
-        <v>2.3</v>
+        <v>4</v>
       </c>
       <c r="P126" s="32" t="n">
-        <v>12</v>
+        <v>12.9</v>
       </c>
       <c r="Q126" s="32" t="n"/>
       <c r="R126" s="23" t="inlineStr">
@@ -13789,13 +13787,13 @@
       </c>
       <c r="N127" s="2" t="n"/>
       <c r="O127" s="32" t="n">
-        <v>-0.2</v>
+        <v>-0.9</v>
       </c>
       <c r="P127" s="32" t="n">
-        <v>11.3</v>
+        <v>18.6</v>
       </c>
       <c r="Q127" s="32" t="n">
-        <v>5.11</v>
+        <v>7.8</v>
       </c>
       <c r="R127" s="23" t="inlineStr">
         <is>
@@ -13909,10 +13907,10 @@
       </c>
       <c r="N128" s="2" t="n"/>
       <c r="O128" s="32" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="P128" s="32" t="n">
-        <v>13.9</v>
+        <v>15</v>
       </c>
       <c r="Q128" s="32" t="n"/>
       <c r="R128" s="23" t="inlineStr">
@@ -14019,13 +14017,13 @@
       </c>
       <c r="N129" s="2" t="n"/>
       <c r="O129" s="32" t="n">
-        <v>-2.2</v>
+        <v>0</v>
       </c>
       <c r="P129" s="32" t="n">
-        <v>10.3</v>
+        <v>17.4</v>
       </c>
       <c r="Q129" s="32" t="n">
-        <v>4.12</v>
+        <v>7.61</v>
       </c>
       <c r="R129" s="23" t="inlineStr">
         <is>
@@ -14139,13 +14137,13 @@
       </c>
       <c r="N130" s="2" t="n"/>
       <c r="O130" s="32" t="n">
-        <v>-0.3</v>
+        <v>-2.3</v>
       </c>
       <c r="P130" s="32" t="n">
-        <v>8.1</v>
+        <v>17.8</v>
       </c>
       <c r="Q130" s="32" t="n">
-        <v>1.25</v>
+        <v>6.35</v>
       </c>
       <c r="R130" s="23" t="inlineStr">
         <is>
@@ -14259,13 +14257,13 @@
       </c>
       <c r="N131" s="2" t="n"/>
       <c r="O131" s="32" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="P131" s="32" t="n">
-        <v>11.7</v>
+        <v>15.4</v>
       </c>
       <c r="Q131" s="32" t="n">
-        <v>7.26</v>
+        <v>10.55</v>
       </c>
       <c r="R131" s="23" t="inlineStr">
         <is>
@@ -14375,13 +14373,13 @@
       </c>
       <c r="N132" s="2" t="n"/>
       <c r="O132" s="32" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="P132" s="32" t="n">
-        <v>14.4</v>
+        <v>17.6</v>
       </c>
       <c r="Q132" s="32" t="n">
-        <v>8.109999999999999</v>
+        <v>10.14</v>
       </c>
       <c r="R132" s="23" t="inlineStr">
         <is>
@@ -14491,13 +14489,13 @@
       </c>
       <c r="N133" s="2" t="n"/>
       <c r="O133" s="32" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="P133" s="32" t="n">
-        <v>8.1</v>
+        <v>19.4</v>
       </c>
       <c r="Q133" s="32" t="n">
-        <v>5.91</v>
+        <v>10.51</v>
       </c>
       <c r="R133" s="23" t="inlineStr">
         <is>
@@ -14713,13 +14711,13 @@
       </c>
       <c r="N135" s="2" t="n"/>
       <c r="O135" s="32" t="n">
-        <v>7.5</v>
+        <v>6.4</v>
       </c>
       <c r="P135" s="32" t="n">
-        <v>10.6</v>
+        <v>17.9</v>
       </c>
       <c r="Q135" s="32" t="n">
-        <v>8.34</v>
+        <v>11.73</v>
       </c>
       <c r="R135" s="23" t="inlineStr">
         <is>
@@ -14829,13 +14827,13 @@
       </c>
       <c r="N136" s="2" t="n"/>
       <c r="O136" s="32" t="n">
-        <v>7.9</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="P136" s="32" t="n">
-        <v>14.9</v>
+        <v>18.3</v>
       </c>
       <c r="Q136" s="32" t="n">
-        <v>11.39</v>
+        <v>13.16</v>
       </c>
       <c r="R136" s="23" t="inlineStr">
         <is>
@@ -14945,13 +14943,13 @@
       </c>
       <c r="N137" s="2" t="n"/>
       <c r="O137" s="32" t="n">
-        <v>6.9</v>
+        <v>3.3</v>
       </c>
       <c r="P137" s="32" t="n">
-        <v>13.5</v>
+        <v>18</v>
       </c>
       <c r="Q137" s="32" t="n">
-        <v>9.24</v>
+        <v>10.63</v>
       </c>
       <c r="R137" s="23" t="inlineStr">
         <is>
@@ -15061,10 +15059,10 @@
       </c>
       <c r="N138" s="2" t="n"/>
       <c r="O138" s="32" t="n">
-        <v>5.2</v>
+        <v>0.3</v>
       </c>
       <c r="P138" s="32" t="n">
-        <v>14.8</v>
+        <v>17</v>
       </c>
       <c r="Q138" s="32" t="n"/>
       <c r="R138" s="23" t="inlineStr">
@@ -15175,13 +15173,13 @@
       </c>
       <c r="N139" s="2" t="n"/>
       <c r="O139" s="32" t="n">
-        <v>4.5</v>
+        <v>2.5</v>
       </c>
       <c r="P139" s="32" t="n">
-        <v>13.1</v>
+        <v>15</v>
       </c>
       <c r="Q139" s="32" t="n">
-        <v>8.119999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="R139" s="23" t="inlineStr">
         <is>
@@ -15291,13 +15289,13 @@
       </c>
       <c r="N140" s="2" t="n"/>
       <c r="O140" s="32" t="n">
-        <v>6.6</v>
+        <v>4.2</v>
       </c>
       <c r="P140" s="32" t="n">
-        <v>14</v>
+        <v>15.4</v>
       </c>
       <c r="Q140" s="32" t="n">
-        <v>9.210000000000001</v>
+        <v>10.04</v>
       </c>
       <c r="R140" s="23" t="inlineStr">
         <is>
@@ -15512,10 +15510,10 @@
         <v>9.5</v>
       </c>
       <c r="P142" s="32" t="n">
-        <v>17.3</v>
+        <v>17.7</v>
       </c>
       <c r="Q142" s="32" t="n">
-        <v>12.11</v>
+        <v>12.21</v>
       </c>
       <c r="R142" s="23" t="inlineStr">
         <is>
@@ -15625,13 +15623,13 @@
       </c>
       <c r="N143" s="2" t="n"/>
       <c r="O143" s="32" t="n">
-        <v>15.1</v>
+        <v>12.4</v>
       </c>
       <c r="P143" s="32" t="n">
-        <v>26.1</v>
+        <v>17.6</v>
       </c>
       <c r="Q143" s="32" t="n">
-        <v>19.95</v>
+        <v>14.98</v>
       </c>
       <c r="R143" s="23" t="inlineStr">
         <is>
@@ -15941,13 +15939,13 @@
       </c>
       <c r="N146" s="2" t="n"/>
       <c r="O146" s="32" t="n">
-        <v>20.8</v>
+        <v>18.9</v>
       </c>
       <c r="P146" s="32" t="n">
-        <v>26.5</v>
+        <v>23.6</v>
       </c>
       <c r="Q146" s="32" t="n">
-        <v>23.68</v>
+        <v>20.29</v>
       </c>
       <c r="R146" s="23" t="inlineStr">
         <is>
@@ -16049,13 +16047,13 @@
       </c>
       <c r="N147" s="2" t="n"/>
       <c r="O147" s="32" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="P147" s="32" t="n">
-        <v>22.2</v>
+        <v>18.3</v>
       </c>
       <c r="Q147" s="32" t="n">
-        <v>20.05</v>
+        <v>15.1</v>
       </c>
       <c r="R147" s="23" t="inlineStr">
         <is>
@@ -16267,13 +16265,13 @@
       </c>
       <c r="N149" s="2" t="n"/>
       <c r="O149" s="32" t="n">
-        <v>10.2</v>
+        <v>7.8</v>
       </c>
       <c r="P149" s="32" t="n">
-        <v>22</v>
+        <v>18.3</v>
       </c>
       <c r="Q149" s="32" t="n">
-        <v>16.61</v>
+        <v>11.66</v>
       </c>
       <c r="R149" s="23" t="inlineStr">
         <is>
@@ -16383,13 +16381,13 @@
       </c>
       <c r="N150" s="2" t="n"/>
       <c r="O150" s="32" t="n">
-        <v>6.1</v>
+        <v>4.8</v>
       </c>
       <c r="P150" s="32" t="n">
-        <v>9.199999999999999</v>
+        <v>16.8</v>
       </c>
       <c r="Q150" s="32" t="n">
-        <v>6.91</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="R150" s="23" t="inlineStr">
         <is>
@@ -16499,13 +16497,13 @@
       </c>
       <c r="N151" s="2" t="n"/>
       <c r="O151" s="32" t="n">
-        <v>13.2</v>
+        <v>10.9</v>
       </c>
       <c r="P151" s="32" t="n">
-        <v>16</v>
+        <v>23.2</v>
       </c>
       <c r="Q151" s="32" t="n">
-        <v>14.39</v>
+        <v>16.26</v>
       </c>
       <c r="R151" s="23" t="inlineStr">
         <is>
@@ -16705,13 +16703,13 @@
       </c>
       <c r="N153" s="2" t="n"/>
       <c r="O153" s="32" t="n">
-        <v>10.2</v>
+        <v>12</v>
       </c>
       <c r="P153" s="32" t="n">
-        <v>13.2</v>
+        <v>19.7</v>
       </c>
       <c r="Q153" s="32" t="n">
-        <v>11.68</v>
+        <v>15.4</v>
       </c>
       <c r="R153" s="23" t="inlineStr">
         <is>
@@ -16825,13 +16823,13 @@
       </c>
       <c r="N154" s="2" t="n"/>
       <c r="O154" s="32" t="n">
-        <v>2.8</v>
+        <v>1.7</v>
       </c>
       <c r="P154" s="32" t="n">
-        <v>20</v>
+        <v>15.8</v>
       </c>
       <c r="Q154" s="32" t="n">
-        <v>11.26</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="R154" s="23" t="inlineStr">
         <is>
@@ -17027,10 +17025,10 @@
       </c>
       <c r="N156" s="2" t="n"/>
       <c r="O156" s="32" t="n">
-        <v>-9.699999999999999</v>
+        <v>-8.6</v>
       </c>
       <c r="P156" s="32" t="n">
-        <v>7.8</v>
+        <v>11.9</v>
       </c>
       <c r="Q156" s="32" t="n"/>
       <c r="R156" s="23" t="inlineStr">
@@ -17133,10 +17131,10 @@
       </c>
       <c r="N157" s="2" t="n"/>
       <c r="O157" s="32" t="n">
-        <v>5.9</v>
+        <v>4.2</v>
       </c>
       <c r="P157" s="32" t="n">
-        <v>13.4</v>
+        <v>14.4</v>
       </c>
       <c r="Q157" s="32" t="n"/>
       <c r="R157" s="23" t="inlineStr">
@@ -17521,10 +17519,10 @@
       </c>
       <c r="N161" s="2" t="n"/>
       <c r="O161" s="32" t="n">
-        <v>3.3</v>
+        <v>1.1</v>
       </c>
       <c r="P161" s="32" t="n">
-        <v>13.2</v>
+        <v>22.7</v>
       </c>
       <c r="Q161" s="32" t="n"/>
       <c r="R161" s="23" t="inlineStr">
@@ -17957,10 +17955,10 @@
         </is>
       </c>
       <c r="O165" s="32" t="n">
-        <v>-29.3</v>
+        <v>-30.2</v>
       </c>
       <c r="P165" s="32" t="n">
-        <v>-13.8</v>
+        <v>-9.300000000000001</v>
       </c>
       <c r="Q165" s="32" t="n"/>
       <c r="R165" s="23" t="inlineStr">
@@ -18283,10 +18281,10 @@
         </is>
       </c>
       <c r="O168" s="32" t="n">
-        <v>-18.9</v>
+        <v>-7</v>
       </c>
       <c r="P168" s="32" t="n">
-        <v>-0.1</v>
+        <v>6</v>
       </c>
       <c r="Q168" s="32" t="n"/>
       <c r="R168" s="23" t="inlineStr">
@@ -18397,10 +18395,10 @@
         </is>
       </c>
       <c r="O169" s="32" t="n">
-        <v>-23.6</v>
+        <v>-9.9</v>
       </c>
       <c r="P169" s="32" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="Q169" s="32" t="n"/>
       <c r="R169" s="23" t="inlineStr">
@@ -18511,10 +18509,10 @@
         </is>
       </c>
       <c r="O170" s="32" t="n">
-        <v>-32.5</v>
+        <v>-21.4</v>
       </c>
       <c r="P170" s="32" t="n">
-        <v>-2.9</v>
+        <v>1</v>
       </c>
       <c r="Q170" s="32" t="n"/>
       <c r="R170" s="23" t="inlineStr">
@@ -18727,10 +18725,10 @@
       </c>
       <c r="N172" s="3" t="n"/>
       <c r="O172" s="32" t="n">
-        <v>-13.3</v>
+        <v>-12.3</v>
       </c>
       <c r="P172" s="32" t="n">
-        <v>2.5</v>
+        <v>6.2</v>
       </c>
       <c r="Q172" s="32" t="n"/>
       <c r="R172" s="23" t="inlineStr">
@@ -18837,10 +18835,10 @@
       </c>
       <c r="N173" s="2" t="n"/>
       <c r="O173" s="32" t="n">
-        <v>-18</v>
+        <v>-12.9</v>
       </c>
       <c r="P173" s="32" t="n">
-        <v>-3.9</v>
+        <v>3</v>
       </c>
       <c r="Q173" s="32" t="n"/>
       <c r="R173" s="23" t="inlineStr">
@@ -19159,10 +19157,10 @@
       </c>
       <c r="N176" s="2" t="n"/>
       <c r="O176" s="32" t="n">
-        <v>0.1</v>
+        <v>-3.5</v>
       </c>
       <c r="P176" s="32" t="n">
-        <v>8.1</v>
+        <v>6.6</v>
       </c>
       <c r="Q176" s="32" t="n"/>
       <c r="R176" s="23" t="inlineStr">
@@ -19261,10 +19259,10 @@
       </c>
       <c r="N177" s="2" t="n"/>
       <c r="O177" s="32" t="n">
-        <v>-19.4</v>
+        <v>-21.9</v>
       </c>
       <c r="P177" s="32" t="n">
-        <v>-15.5</v>
+        <v>-13.2</v>
       </c>
       <c r="Q177" s="32" t="n"/>
       <c r="R177" s="23" t="inlineStr">
@@ -20049,9 +20047,11 @@
       </c>
       <c r="N185" s="2" t="n"/>
       <c r="O185" s="32" t="n">
-        <v>-35.6</v>
-      </c>
-      <c r="P185" s="32" t="n"/>
+        <v>-37.8</v>
+      </c>
+      <c r="P185" s="32" t="n">
+        <v>-10.8</v>
+      </c>
       <c r="Q185" s="32" t="n"/>
       <c r="R185" s="23" t="inlineStr">
         <is>
@@ -20154,13 +20154,13 @@
       </c>
       <c r="N186" s="2" t="n"/>
       <c r="O186" s="32" t="n">
-        <v>-42.2</v>
+        <v>-28.6</v>
       </c>
       <c r="P186" s="32" t="n">
-        <v>-21.5</v>
+        <v>-18</v>
       </c>
       <c r="Q186" s="32" t="n">
-        <v>-33</v>
+        <v>-22.74</v>
       </c>
       <c r="R186" s="23" t="inlineStr">
         <is>
@@ -20263,13 +20263,13 @@
       </c>
       <c r="N187" s="2" t="n"/>
       <c r="O187" s="32" t="n">
-        <v>-40.2</v>
+        <v>-31.8</v>
       </c>
       <c r="P187" s="32" t="n">
-        <v>-21</v>
+        <v>-15</v>
       </c>
       <c r="Q187" s="32" t="n">
-        <v>-32.55</v>
+        <v>-24.99</v>
       </c>
       <c r="R187" s="23" t="inlineStr">
         <is>
@@ -20367,13 +20367,13 @@
       </c>
       <c r="N188" s="2" t="n"/>
       <c r="O188" s="32" t="n">
-        <v>-38.9</v>
+        <v>-35.8</v>
       </c>
       <c r="P188" s="32" t="n">
-        <v>-25.5</v>
+        <v>-20.8</v>
       </c>
       <c r="Q188" s="32" t="n">
-        <v>-32.46</v>
+        <v>-27.75</v>
       </c>
       <c r="R188" s="23" t="inlineStr">
         <is>
@@ -20471,13 +20471,13 @@
       </c>
       <c r="N189" s="2" t="n"/>
       <c r="O189" s="32" t="n">
-        <v>-45</v>
+        <v>-27.4</v>
       </c>
       <c r="P189" s="32" t="n">
-        <v>-22.4</v>
+        <v>-17.5</v>
       </c>
       <c r="Q189" s="32" t="n">
-        <v>-35.99</v>
+        <v>-22.2</v>
       </c>
       <c r="R189" s="23" t="inlineStr">
         <is>
@@ -20575,13 +20575,13 @@
       </c>
       <c r="N190" s="2" t="n"/>
       <c r="O190" s="32" t="n">
-        <v>-44.6</v>
+        <v>-43.7</v>
       </c>
       <c r="P190" s="32" t="n">
-        <v>-25.9</v>
+        <v>-22.3</v>
       </c>
       <c r="Q190" s="32" t="n">
-        <v>-37.2</v>
+        <v>-34.65</v>
       </c>
       <c r="R190" s="23" t="inlineStr">
         <is>
@@ -20679,13 +20679,13 @@
       </c>
       <c r="N191" s="2" t="n"/>
       <c r="O191" s="32" t="n">
-        <v>-40.8</v>
+        <v>-32.5</v>
       </c>
       <c r="P191" s="32" t="n">
-        <v>-20.5</v>
+        <v>-19.1</v>
       </c>
       <c r="Q191" s="32" t="n">
-        <v>-32.43</v>
+        <v>-25.16</v>
       </c>
       <c r="R191" s="23" t="inlineStr">
         <is>
@@ -20779,13 +20779,13 @@
       </c>
       <c r="N192" s="2" t="n"/>
       <c r="O192" s="32" t="n">
-        <v>-39.8</v>
+        <v>-34.2</v>
       </c>
       <c r="P192" s="32" t="n">
-        <v>-19.7</v>
+        <v>-21</v>
       </c>
       <c r="Q192" s="32" t="n">
-        <v>-31.42</v>
+        <v>-27.25</v>
       </c>
       <c r="R192" s="23" t="inlineStr">
         <is>
@@ -20884,13 +20884,13 @@
       </c>
       <c r="N193" s="2" t="n"/>
       <c r="O193" s="32" t="n">
-        <v>-25.1</v>
+        <v>-35.4</v>
       </c>
       <c r="P193" s="32" t="n">
-        <v>-13</v>
+        <v>-13.2</v>
       </c>
       <c r="Q193" s="32" t="n">
-        <v>-19.8</v>
+        <v>-26.76</v>
       </c>
       <c r="R193" s="23" t="inlineStr">
         <is>
@@ -20992,10 +20992,10 @@
       </c>
       <c r="N194" s="2" t="n"/>
       <c r="O194" s="32" t="n">
-        <v>-39.6</v>
+        <v>-40.3</v>
       </c>
       <c r="P194" s="32" t="n">
-        <v>-28.9</v>
+        <v>-20.4</v>
       </c>
       <c r="Q194" s="32" t="n"/>
       <c r="R194" s="23" t="inlineStr">
@@ -21090,13 +21090,13 @@
       </c>
       <c r="N195" s="2" t="n"/>
       <c r="O195" s="32" t="n">
-        <v>-34.1</v>
+        <v>-30</v>
       </c>
       <c r="P195" s="32" t="n">
-        <v>-19.2</v>
+        <v>-4.3</v>
       </c>
       <c r="Q195" s="32" t="n">
-        <v>-28.09</v>
+        <v>-15.69</v>
       </c>
       <c r="R195" s="23" t="inlineStr">
         <is>
@@ -21194,13 +21194,13 @@
       </c>
       <c r="N196" s="2" t="n"/>
       <c r="O196" s="32" t="n">
-        <v>-36.3</v>
+        <v>-19.2</v>
       </c>
       <c r="P196" s="32" t="n">
-        <v>-14.4</v>
+        <v>-10.8</v>
       </c>
       <c r="Q196" s="32" t="n">
-        <v>-26.96</v>
+        <v>-15.38</v>
       </c>
       <c r="R196" s="23" t="inlineStr">
         <is>
@@ -21298,13 +21298,13 @@
       </c>
       <c r="N197" s="24" t="n"/>
       <c r="O197" s="32" t="n">
-        <v>-38.8</v>
+        <v>-15.4</v>
       </c>
       <c r="P197" s="32" t="n">
-        <v>-18.1</v>
+        <v>-1.9</v>
       </c>
       <c r="Q197" s="32" t="n">
-        <v>-28.75</v>
+        <v>-6.9</v>
       </c>
       <c r="R197" s="23" t="inlineStr">
         <is>
@@ -21393,8 +21393,12 @@
         </is>
       </c>
       <c r="N198" s="2" t="n"/>
-      <c r="O198" s="32" t="n"/>
-      <c r="P198" s="32" t="n"/>
+      <c r="O198" s="32" t="n">
+        <v>-21.2</v>
+      </c>
+      <c r="P198" s="32" t="n">
+        <v>-0.9</v>
+      </c>
       <c r="Q198" s="32" t="n"/>
       <c r="R198" s="23" t="inlineStr">
         <is>
@@ -21695,12 +21699,8 @@
         </is>
       </c>
       <c r="N201" s="2" t="n"/>
-      <c r="O201" s="32" t="n">
-        <v>-29.2</v>
-      </c>
-      <c r="P201" s="32" t="n">
-        <v>-1.8</v>
-      </c>
+      <c r="O201" s="32" t="n"/>
+      <c r="P201" s="32" t="n"/>
       <c r="Q201" s="32" t="n"/>
       <c r="R201" s="23" t="inlineStr">
         <is>
@@ -21801,12 +21801,8 @@
         </is>
       </c>
       <c r="N202" s="2" t="n"/>
-      <c r="O202" s="32" t="n">
-        <v>-26.8</v>
-      </c>
-      <c r="P202" s="32" t="n">
-        <v>-3.1</v>
-      </c>
+      <c r="O202" s="32" t="n"/>
+      <c r="P202" s="32" t="n"/>
       <c r="Q202" s="32" t="n"/>
       <c r="R202" s="23" t="inlineStr">
         <is>
@@ -21907,12 +21903,8 @@
         </is>
       </c>
       <c r="N203" s="2" t="n"/>
-      <c r="O203" s="32" t="n">
-        <v>-27</v>
-      </c>
-      <c r="P203" s="32" t="n">
-        <v>-5.9</v>
-      </c>
+      <c r="O203" s="32" t="n"/>
+      <c r="P203" s="32" t="n"/>
       <c r="Q203" s="32" t="n"/>
       <c r="R203" s="23" t="inlineStr">
         <is>
@@ -22811,12 +22803,8 @@
         </is>
       </c>
       <c r="N212" s="2" t="n"/>
-      <c r="O212" s="32" t="n">
-        <v>-31.3</v>
-      </c>
-      <c r="P212" s="32" t="n">
-        <v>-3.4</v>
-      </c>
+      <c r="O212" s="32" t="n"/>
+      <c r="P212" s="32" t="n"/>
       <c r="Q212" s="32" t="n"/>
       <c r="R212" s="23" t="inlineStr">
         <is>
@@ -22917,8 +22905,12 @@
         </is>
       </c>
       <c r="N213" s="2" t="n"/>
-      <c r="O213" s="32" t="n"/>
-      <c r="P213" s="32" t="n"/>
+      <c r="O213" s="32" t="n">
+        <v>-31.8</v>
+      </c>
+      <c r="P213" s="32" t="n">
+        <v>-1.5</v>
+      </c>
       <c r="Q213" s="32" t="n"/>
       <c r="R213" s="23" t="inlineStr">
         <is>
@@ -24521,12 +24513,8 @@
         </is>
       </c>
       <c r="N229" s="2" t="n"/>
-      <c r="O229" s="32" t="n">
-        <v>-28.4</v>
-      </c>
-      <c r="P229" s="32" t="n">
-        <v>-16</v>
-      </c>
+      <c r="O229" s="32" t="n"/>
+      <c r="P229" s="32" t="n"/>
       <c r="Q229" s="32" t="n"/>
       <c r="R229" s="23" t="inlineStr">
         <is>
@@ -26252,13 +26240,13 @@
       </c>
       <c r="N247" s="2" t="n"/>
       <c r="O247" s="32" t="n">
-        <v>-1.4</v>
+        <v>-19.6</v>
       </c>
       <c r="P247" s="32" t="n">
-        <v>1.5</v>
+        <v>-3.2</v>
       </c>
       <c r="Q247" s="32" t="n">
-        <v>-0.36</v>
+        <v>-10.74</v>
       </c>
       <c r="R247" s="23" t="inlineStr">
         <is>
@@ -26368,13 +26356,13 @@
         </is>
       </c>
       <c r="O248" s="32" t="n">
-        <v>-16.7</v>
+        <v>-0.8</v>
       </c>
       <c r="P248" s="32" t="n">
-        <v>-3.8</v>
+        <v>6.2</v>
       </c>
       <c r="Q248" s="32" t="n">
-        <v>-10.73</v>
+        <v>1.41</v>
       </c>
       <c r="R248" s="23" t="inlineStr">
         <is>
@@ -26476,13 +26464,13 @@
       </c>
       <c r="N249" s="2" t="n"/>
       <c r="O249" s="32" t="n">
-        <v>-9.1</v>
+        <v>-5.7</v>
       </c>
       <c r="P249" s="32" t="n">
-        <v>0.6</v>
+        <v>2.5</v>
       </c>
       <c r="Q249" s="32" t="n">
-        <v>-5.3</v>
+        <v>-2.39</v>
       </c>
       <c r="R249" s="23" t="inlineStr">
         <is>
@@ -26588,13 +26576,13 @@
       </c>
       <c r="N250" s="2" t="n"/>
       <c r="O250" s="32" t="n">
-        <v>-14.9</v>
+        <v>-12.3</v>
       </c>
       <c r="P250" s="32" t="n">
-        <v>0.3</v>
+        <v>3.6</v>
       </c>
       <c r="Q250" s="32" t="n">
-        <v>-7.4</v>
+        <v>-4.42</v>
       </c>
       <c r="R250" s="23" t="inlineStr">
         <is>
@@ -26708,10 +26696,10 @@
         </is>
       </c>
       <c r="O251" s="32" t="n">
-        <v>-39.8</v>
+        <v>-17.6</v>
       </c>
       <c r="P251" s="32" t="n">
-        <v>-15</v>
+        <v>-2.8</v>
       </c>
       <c r="Q251" s="32" t="n"/>
       <c r="R251" s="23" t="inlineStr">
@@ -26766,7 +26754,7 @@
       </c>
       <c r="B252" s="2" t="inlineStr">
         <is>
-          <t>rp5</t>
+          <t>ogimet</t>
         </is>
       </c>
       <c r="C252" s="46" t="n">
@@ -26806,14 +26794,12 @@
       </c>
       <c r="N252" s="2" t="n"/>
       <c r="O252" s="32" t="n">
-        <v>-10.8</v>
+        <v>-6.2</v>
       </c>
       <c r="P252" s="32" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="Q252" s="32" t="n">
-        <v>-1.91</v>
-      </c>
+        <v>3.8</v>
+      </c>
+      <c r="Q252" s="32" t="n"/>
       <c r="R252" s="23" t="inlineStr">
         <is>
           <t>Y</t>
@@ -27004,13 +26990,13 @@
       </c>
       <c r="N254" s="2" t="n"/>
       <c r="O254" s="32" t="n">
-        <v>-31.6</v>
+        <v>-22.5</v>
       </c>
       <c r="P254" s="32" t="n">
-        <v>-22.8</v>
+        <v>-11.4</v>
       </c>
       <c r="Q254" s="32" t="n">
-        <v>-25.84</v>
+        <v>-17.25</v>
       </c>
       <c r="R254" s="23" t="inlineStr">
         <is>
@@ -27578,13 +27564,13 @@
       </c>
       <c r="N260" s="2" t="n"/>
       <c r="O260" s="32" t="n">
-        <v>-22.6</v>
+        <v>-18</v>
       </c>
       <c r="P260" s="32" t="n">
-        <v>1.2</v>
+        <v>9.4</v>
       </c>
       <c r="Q260" s="32" t="n">
-        <v>-10.84</v>
+        <v>-5.16</v>
       </c>
       <c r="R260" s="23" t="inlineStr">
         <is>
@@ -27686,13 +27672,13 @@
       </c>
       <c r="N261" s="2" t="n"/>
       <c r="O261" s="32" t="n">
-        <v>-15.6</v>
+        <v>-16.1</v>
       </c>
       <c r="P261" s="32" t="n">
-        <v>1.3</v>
+        <v>4.7</v>
       </c>
       <c r="Q261" s="32" t="n">
-        <v>-6.34</v>
+        <v>-6.84</v>
       </c>
       <c r="R261" s="23" t="inlineStr">
         <is>
@@ -27798,13 +27784,13 @@
       </c>
       <c r="N262" s="2" t="n"/>
       <c r="O262" s="32" t="n">
-        <v>-1.9</v>
+        <v>-5.8</v>
       </c>
       <c r="P262" s="32" t="n">
-        <v>1.9</v>
+        <v>-2.5</v>
       </c>
       <c r="Q262" s="32" t="n">
-        <v>0.29</v>
+        <v>-3.76</v>
       </c>
       <c r="R262" s="23" t="inlineStr">
         <is>
@@ -28004,13 +27990,13 @@
       </c>
       <c r="N264" s="2" t="n"/>
       <c r="O264" s="32" t="n">
-        <v>-11.7</v>
+        <v>-7.1</v>
       </c>
       <c r="P264" s="32" t="n">
-        <v>5.3</v>
+        <v>4.6</v>
       </c>
       <c r="Q264" s="32" t="n">
-        <v>-3.96</v>
+        <v>-2.01</v>
       </c>
       <c r="R264" s="23" t="inlineStr">
         <is>
@@ -28124,10 +28110,10 @@
       </c>
       <c r="N265" s="2" t="n"/>
       <c r="O265" s="32" t="n">
-        <v>-54.1</v>
+        <v>-56.1</v>
       </c>
       <c r="P265" s="32" t="n">
-        <v>-41.9</v>
+        <v>-44.1</v>
       </c>
       <c r="Q265" s="32" t="n"/>
       <c r="R265" s="23" t="inlineStr">
@@ -29168,13 +29154,13 @@
       </c>
       <c r="N276" s="2" t="n"/>
       <c r="O276" s="32" t="n">
-        <v>-44.2</v>
+        <v>-41.9</v>
       </c>
       <c r="P276" s="32" t="n">
-        <v>-28.9</v>
+        <v>-16.8</v>
       </c>
       <c r="Q276" s="32" t="n">
-        <v>-37.14</v>
+        <v>-30.45</v>
       </c>
       <c r="R276" s="23" t="inlineStr">
         <is>

--- a/气象/For_Python_站点信息和记录.xlsx
+++ b/气象/For_Python_站点信息和记录.xlsx
@@ -796,8 +796,8 @@
     <col width="18.59765625" customWidth="1" style="8" min="25" max="25"/>
     <col width="12.59765625" customWidth="1" style="5" min="26" max="30"/>
     <col width="12.59765625" customWidth="1" style="8" min="31" max="32"/>
-    <col width="12.59765625" customWidth="1" style="5" min="33" max="304"/>
-    <col width="12.59765625" customWidth="1" style="5" min="305" max="16384"/>
+    <col width="12.59765625" customWidth="1" style="5" min="33" max="311"/>
+    <col width="12.59765625" customWidth="1" style="5" min="312" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="27.75" customFormat="1" customHeight="1" s="11">
@@ -1020,13 +1020,13 @@
         </is>
       </c>
       <c r="O2" s="32" t="n">
-        <v>-26.1</v>
+        <v>-28.2</v>
       </c>
       <c r="P2" s="32" t="n">
-        <v>-14.4</v>
+        <v>-10.4</v>
       </c>
       <c r="Q2" s="32" t="n">
-        <v>-20.4</v>
+        <v>-18.19</v>
       </c>
       <c r="R2" s="23" t="inlineStr">
         <is>
@@ -1126,10 +1126,10 @@
         </is>
       </c>
       <c r="O3" s="32" t="n">
-        <v>-26.4</v>
+        <v>-23.6</v>
       </c>
       <c r="P3" s="32" t="n">
-        <v>-13</v>
+        <v>-11.8</v>
       </c>
       <c r="Q3" s="32" t="n"/>
       <c r="R3" s="23" t="n"/>
@@ -1321,12 +1321,8 @@
         </is>
       </c>
       <c r="N5" s="2" t="n"/>
-      <c r="O5" s="32" t="n">
-        <v>-21</v>
-      </c>
-      <c r="P5" s="32" t="n">
-        <v>-2.3</v>
-      </c>
+      <c r="O5" s="32" t="n"/>
+      <c r="P5" s="32" t="n"/>
       <c r="Q5" s="32" t="n"/>
       <c r="R5" s="23" t="n"/>
       <c r="S5" s="37" t="n"/>
@@ -1422,10 +1418,10 @@
         </is>
       </c>
       <c r="O6" s="32" t="n">
-        <v>-25.6</v>
+        <v>-18.2</v>
       </c>
       <c r="P6" s="32" t="n">
-        <v>-4.4</v>
+        <v>-1.4</v>
       </c>
       <c r="Q6" s="32" t="n"/>
       <c r="R6" s="23" t="n"/>
@@ -1522,10 +1518,10 @@
         </is>
       </c>
       <c r="O7" s="32" t="n">
-        <v>-22.3</v>
+        <v>-22</v>
       </c>
       <c r="P7" s="32" t="n">
-        <v>-6.5</v>
+        <v>-1</v>
       </c>
       <c r="Q7" s="32" t="n"/>
       <c r="R7" s="23" t="n"/>
@@ -1630,13 +1626,13 @@
       </c>
       <c r="N8" s="2" t="n"/>
       <c r="O8" s="32" t="n">
-        <v>-22.4</v>
+        <v>-11.6</v>
       </c>
       <c r="P8" s="32" t="n">
-        <v>-3.3</v>
+        <v>0.8</v>
       </c>
       <c r="Q8" s="32" t="n">
-        <v>-13.46</v>
+        <v>-4.37</v>
       </c>
       <c r="R8" s="23" t="inlineStr">
         <is>
@@ -1742,13 +1738,13 @@
       </c>
       <c r="N9" s="2" t="n"/>
       <c r="O9" s="32" t="n">
-        <v>-24.5</v>
+        <v>-24.4</v>
       </c>
       <c r="P9" s="32" t="n">
-        <v>-10.8</v>
+        <v>-8.300000000000001</v>
       </c>
       <c r="Q9" s="32" t="n">
-        <v>-18.25</v>
+        <v>-15.03</v>
       </c>
       <c r="R9" s="23" t="inlineStr">
         <is>
@@ -1862,13 +1858,13 @@
         </is>
       </c>
       <c r="O10" s="32" t="n">
-        <v>-20.2</v>
+        <v>-17.1</v>
       </c>
       <c r="P10" s="32" t="n">
-        <v>1.5</v>
+        <v>-4.3</v>
       </c>
       <c r="Q10" s="32" t="n">
-        <v>-9.91</v>
+        <v>-13.11</v>
       </c>
       <c r="R10" s="23" t="inlineStr">
         <is>
@@ -1978,13 +1974,13 @@
         </is>
       </c>
       <c r="O11" s="32" t="n">
-        <v>-19.8</v>
+        <v>-21.3</v>
       </c>
       <c r="P11" s="32" t="n">
-        <v>6.4</v>
+        <v>-4.5</v>
       </c>
       <c r="Q11" s="32" t="n">
-        <v>-5.24</v>
+        <v>-13.79</v>
       </c>
       <c r="R11" s="23" t="inlineStr">
         <is>
@@ -2090,13 +2086,13 @@
       </c>
       <c r="N12" s="2" t="n"/>
       <c r="O12" s="32" t="n">
-        <v>-21.2</v>
+        <v>-14.6</v>
       </c>
       <c r="P12" s="32" t="n">
-        <v>0.2</v>
+        <v>-1.4</v>
       </c>
       <c r="Q12" s="32" t="n">
-        <v>-11.54</v>
+        <v>-9.91</v>
       </c>
       <c r="R12" s="23" t="inlineStr">
         <is>
@@ -2206,13 +2202,13 @@
         </is>
       </c>
       <c r="O13" s="32" t="n">
-        <v>-23.3</v>
+        <v>-20.7</v>
       </c>
       <c r="P13" s="32" t="n">
-        <v>-6.6</v>
+        <v>-2</v>
       </c>
       <c r="Q13" s="32" t="n">
-        <v>-16.72</v>
+        <v>-17.24</v>
       </c>
       <c r="R13" s="23" t="inlineStr">
         <is>
@@ -2318,13 +2314,13 @@
       </c>
       <c r="N14" s="2" t="n"/>
       <c r="O14" s="32" t="n">
-        <v>-10.1</v>
+        <v>-9.199999999999999</v>
       </c>
       <c r="P14" s="32" t="n">
-        <v>4.9</v>
+        <v>9.9</v>
       </c>
       <c r="Q14" s="32" t="n">
-        <v>-3.47</v>
+        <v>-0.39</v>
       </c>
       <c r="R14" s="23" t="inlineStr">
         <is>
@@ -2423,12 +2419,8 @@
         </is>
       </c>
       <c r="N15" s="2" t="n"/>
-      <c r="O15" s="32" t="n">
-        <v>-21.9</v>
-      </c>
-      <c r="P15" s="32" t="n">
-        <v>1.8</v>
-      </c>
+      <c r="O15" s="32" t="n"/>
+      <c r="P15" s="32" t="n"/>
       <c r="Q15" s="32" t="n"/>
       <c r="R15" s="23" t="n"/>
       <c r="S15" s="37" t="n"/>
@@ -7834,13 +7826,13 @@
       </c>
       <c r="N75" s="2" t="n"/>
       <c r="O75" s="32" t="n">
-        <v>-19.8</v>
+        <v>-17.3</v>
       </c>
       <c r="P75" s="32" t="n">
-        <v>1.9</v>
+        <v>4.9</v>
       </c>
       <c r="Q75" s="32" t="n">
-        <v>-10.31</v>
+        <v>-8.01</v>
       </c>
       <c r="R75" s="23" t="inlineStr">
         <is>
@@ -7950,13 +7942,13 @@
         </is>
       </c>
       <c r="O76" s="32" t="n">
-        <v>-28.5</v>
+        <v>-28.6</v>
       </c>
       <c r="P76" s="32" t="n">
-        <v>-7.9</v>
+        <v>-5.3</v>
       </c>
       <c r="Q76" s="32" t="n">
-        <v>-17.82</v>
+        <v>-18.32</v>
       </c>
       <c r="R76" s="23" t="inlineStr">
         <is>
@@ -8066,13 +8058,13 @@
         </is>
       </c>
       <c r="O77" s="32" t="n">
-        <v>-34.4</v>
+        <v>-29.6</v>
       </c>
       <c r="P77" s="32" t="n">
-        <v>-7.4</v>
+        <v>-1.8</v>
       </c>
       <c r="Q77" s="32" t="n">
-        <v>-21.52</v>
+        <v>-17.55</v>
       </c>
       <c r="R77" s="23" t="inlineStr">
         <is>
@@ -8178,13 +8170,13 @@
       </c>
       <c r="N78" s="2" t="n"/>
       <c r="O78" s="32" t="n">
-        <v>-28.6</v>
+        <v>-25.6</v>
       </c>
       <c r="P78" s="32" t="n">
-        <v>-5.7</v>
+        <v>-0.7</v>
       </c>
       <c r="Q78" s="32" t="n">
-        <v>-17.49</v>
+        <v>-14.16</v>
       </c>
       <c r="R78" s="23" t="inlineStr">
         <is>
@@ -8294,13 +8286,13 @@
         </is>
       </c>
       <c r="O79" s="32" t="n">
-        <v>-32.9</v>
+        <v>-31.8</v>
       </c>
       <c r="P79" s="32" t="n">
-        <v>-3.8</v>
+        <v>-0.2</v>
       </c>
       <c r="Q79" s="32" t="n">
-        <v>-18.54</v>
+        <v>-16.73</v>
       </c>
       <c r="R79" s="23" t="inlineStr">
         <is>
@@ -8406,13 +8398,13 @@
       </c>
       <c r="N80" s="2" t="n"/>
       <c r="O80" s="32" t="n">
-        <v>-20.9</v>
+        <v>-5.5</v>
       </c>
       <c r="P80" s="32" t="n">
-        <v>-1.2</v>
+        <v>2.4</v>
       </c>
       <c r="Q80" s="32" t="n">
-        <v>-10.94</v>
+        <v>-1.56</v>
       </c>
       <c r="R80" s="23" t="inlineStr">
         <is>
@@ -8522,10 +8514,10 @@
         </is>
       </c>
       <c r="O81" s="32" t="n">
-        <v>-26.8</v>
+        <v>-3.8</v>
       </c>
       <c r="P81" s="32" t="n">
-        <v>2.6</v>
+        <v>0.6</v>
       </c>
       <c r="Q81" s="32" t="n"/>
       <c r="R81" s="23" t="inlineStr">
@@ -8641,13 +8633,13 @@
         </is>
       </c>
       <c r="O82" s="32" t="n">
-        <v>-27</v>
+        <v>-10</v>
       </c>
       <c r="P82" s="32" t="n">
-        <v>1</v>
+        <v>3.6</v>
       </c>
       <c r="Q82" s="32" t="n">
-        <v>-14.54</v>
+        <v>-3.15</v>
       </c>
       <c r="R82" s="23" t="inlineStr">
         <is>
@@ -8753,13 +8745,13 @@
       </c>
       <c r="N83" s="2" t="n"/>
       <c r="O83" s="32" t="n">
-        <v>-19.7</v>
+        <v>-11.1</v>
       </c>
       <c r="P83" s="32" t="n">
-        <v>-0.9</v>
+        <v>0.5</v>
       </c>
       <c r="Q83" s="32" t="n">
-        <v>-10.9</v>
+        <v>-4.3</v>
       </c>
       <c r="R83" s="23" t="inlineStr">
         <is>
@@ -8869,13 +8861,13 @@
         </is>
       </c>
       <c r="O84" s="32" t="n">
-        <v>-21.2</v>
+        <v>-16.8</v>
       </c>
       <c r="P84" s="32" t="n">
-        <v>0.9</v>
+        <v>-0.2</v>
       </c>
       <c r="Q84" s="32" t="n">
-        <v>-11.77</v>
+        <v>-9.619999999999999</v>
       </c>
       <c r="R84" s="23" t="inlineStr">
         <is>
@@ -8985,13 +8977,13 @@
         </is>
       </c>
       <c r="O85" s="32" t="n">
-        <v>-21.2</v>
+        <v>-27.4</v>
       </c>
       <c r="P85" s="32" t="n">
-        <v>1.4</v>
+        <v>-7.3</v>
       </c>
       <c r="Q85" s="32" t="n">
-        <v>-10.16</v>
+        <v>-14.9</v>
       </c>
       <c r="R85" s="23" t="inlineStr">
         <is>
@@ -9097,13 +9089,13 @@
       </c>
       <c r="N86" s="2" t="n"/>
       <c r="O86" s="32" t="n">
-        <v>-16.2</v>
+        <v>-20.4</v>
       </c>
       <c r="P86" s="32" t="n">
-        <v>-3.2</v>
+        <v>-5.6</v>
       </c>
       <c r="Q86" s="32" t="n">
-        <v>-9.85</v>
+        <v>-13.05</v>
       </c>
       <c r="R86" s="23" t="inlineStr">
         <is>
@@ -9221,13 +9213,13 @@
         </is>
       </c>
       <c r="O87" s="32" t="n">
-        <v>-23.5</v>
+        <v>-20.7</v>
       </c>
       <c r="P87" s="32" t="n">
-        <v>-11.1</v>
+        <v>-5.1</v>
       </c>
       <c r="Q87" s="32" t="n">
-        <v>-17.62</v>
+        <v>-13.81</v>
       </c>
       <c r="R87" s="23" t="inlineStr">
         <is>
@@ -9333,13 +9325,13 @@
       </c>
       <c r="N88" s="2" t="n"/>
       <c r="O88" s="32" t="n">
-        <v>-8.5</v>
+        <v>-23.2</v>
       </c>
       <c r="P88" s="32" t="n">
-        <v>6.8</v>
+        <v>-10.1</v>
       </c>
       <c r="Q88" s="32" t="n">
-        <v>-0.95</v>
+        <v>-16.51</v>
       </c>
       <c r="R88" s="23" t="inlineStr">
         <is>
@@ -9551,13 +9543,13 @@
         </is>
       </c>
       <c r="O90" s="32" t="n">
-        <v>-1.1</v>
+        <v>-27</v>
       </c>
       <c r="P90" s="32" t="n">
-        <v>4.6</v>
+        <v>-12.3</v>
       </c>
       <c r="Q90" s="32" t="n">
-        <v>1.1</v>
+        <v>-19.39</v>
       </c>
       <c r="R90" s="23" t="inlineStr">
         <is>
@@ -9659,13 +9651,13 @@
       </c>
       <c r="N91" s="2" t="n"/>
       <c r="O91" s="32" t="n">
-        <v>-3.7</v>
+        <v>-27.5</v>
       </c>
       <c r="P91" s="32" t="n">
-        <v>1.1</v>
+        <v>-16.9</v>
       </c>
       <c r="Q91" s="32" t="n">
-        <v>-0.71</v>
+        <v>-22.39</v>
       </c>
       <c r="R91" s="23" t="inlineStr">
         <is>
@@ -9767,13 +9759,13 @@
       </c>
       <c r="N92" s="2" t="n"/>
       <c r="O92" s="32" t="n">
-        <v>-24.6</v>
+        <v>-21.5</v>
       </c>
       <c r="P92" s="32" t="n">
-        <v>-3.5</v>
+        <v>0.4</v>
       </c>
       <c r="Q92" s="32" t="n">
-        <v>-12.1</v>
+        <v>-8.789999999999999</v>
       </c>
       <c r="R92" s="23" t="inlineStr">
         <is>
@@ -9879,13 +9871,13 @@
       </c>
       <c r="N93" s="2" t="n"/>
       <c r="O93" s="32" t="n">
-        <v>-8.6</v>
+        <v>-6.7</v>
       </c>
       <c r="P93" s="32" t="n">
-        <v>10.3</v>
+        <v>10.8</v>
       </c>
       <c r="Q93" s="32" t="n">
-        <v>0.96</v>
+        <v>3.53</v>
       </c>
       <c r="R93" s="23" t="inlineStr">
         <is>
@@ -9999,10 +9991,10 @@
         </is>
       </c>
       <c r="O94" s="32" t="n">
-        <v>-12.5</v>
+        <v>-11.3</v>
       </c>
       <c r="P94" s="32" t="n">
-        <v>9.300000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Q94" s="32" t="n"/>
       <c r="R94" s="23" t="inlineStr">
@@ -10117,14 +10109,12 @@
       </c>
       <c r="N95" s="2" t="n"/>
       <c r="O95" s="32" t="n">
-        <v>-8.9</v>
+        <v>-10.2</v>
       </c>
       <c r="P95" s="32" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="Q95" s="32" t="n">
-        <v>0.48</v>
-      </c>
+        <v>7.3</v>
+      </c>
+      <c r="Q95" s="32" t="n"/>
       <c r="R95" s="23" t="inlineStr">
         <is>
           <t>Y</t>
@@ -10245,10 +10235,10 @@
         </is>
       </c>
       <c r="O96" s="32" t="n">
-        <v>-12.2</v>
+        <v>-9.300000000000001</v>
       </c>
       <c r="P96" s="32" t="n">
-        <v>6.9</v>
+        <v>7</v>
       </c>
       <c r="Q96" s="32" t="n"/>
       <c r="R96" s="23" t="inlineStr">
@@ -10363,12 +10353,14 @@
       </c>
       <c r="N97" s="2" t="n"/>
       <c r="O97" s="32" t="n">
-        <v>-6.4</v>
+        <v>-12.3</v>
       </c>
       <c r="P97" s="32" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="Q97" s="32" t="n"/>
+        <v>5.7</v>
+      </c>
+      <c r="Q97" s="32" t="n">
+        <v>-3.04</v>
+      </c>
       <c r="R97" s="23" t="inlineStr">
         <is>
           <t>Y</t>
@@ -10481,10 +10473,10 @@
       </c>
       <c r="N98" s="2" t="n"/>
       <c r="O98" s="32" t="n">
-        <v>-22.7</v>
+        <v>-23</v>
       </c>
       <c r="P98" s="32" t="n">
-        <v>-1.6</v>
+        <v>1.6</v>
       </c>
       <c r="Q98" s="32" t="n"/>
       <c r="R98" s="23" t="inlineStr">
@@ -10599,13 +10591,13 @@
       </c>
       <c r="N99" s="2" t="n"/>
       <c r="O99" s="32" t="n">
-        <v>-16.6</v>
+        <v>-17.2</v>
       </c>
       <c r="P99" s="32" t="n">
-        <v>-3.4</v>
+        <v>3.2</v>
       </c>
       <c r="Q99" s="32" t="n">
-        <v>-8.6</v>
+        <v>-7.14</v>
       </c>
       <c r="R99" s="23" t="inlineStr">
         <is>
@@ -10931,13 +10923,13 @@
       </c>
       <c r="N102" s="2" t="n"/>
       <c r="O102" s="32" t="n">
-        <v>-15.4</v>
+        <v>-16.2</v>
       </c>
       <c r="P102" s="32" t="n">
-        <v>-0.7</v>
+        <v>5.4</v>
       </c>
       <c r="Q102" s="32" t="n">
-        <v>-8.15</v>
+        <v>-4.39</v>
       </c>
       <c r="R102" s="23" t="inlineStr">
         <is>
@@ -11047,10 +11039,10 @@
       </c>
       <c r="N103" s="2" t="n"/>
       <c r="O103" s="32" t="n">
-        <v>-15.1</v>
+        <v>-16.1</v>
       </c>
       <c r="P103" s="32" t="n">
-        <v>-0.6</v>
+        <v>1.6</v>
       </c>
       <c r="Q103" s="32" t="n"/>
       <c r="R103" s="23" t="inlineStr">
@@ -11157,10 +11149,10 @@
       </c>
       <c r="N104" s="2" t="n"/>
       <c r="O104" s="32" t="n">
-        <v>-24.5</v>
+        <v>-18.5</v>
       </c>
       <c r="P104" s="32" t="n">
-        <v>1.2</v>
+        <v>5.9</v>
       </c>
       <c r="Q104" s="32" t="n"/>
       <c r="R104" s="23" t="inlineStr">
@@ -11283,13 +11275,13 @@
         </is>
       </c>
       <c r="O105" s="32" t="n">
-        <v>-27.5</v>
+        <v>-20.9</v>
       </c>
       <c r="P105" s="32" t="n">
-        <v>-1.1</v>
+        <v>7.1</v>
       </c>
       <c r="Q105" s="32" t="n">
-        <v>-13.74</v>
+        <v>-6.7</v>
       </c>
       <c r="R105" s="23" t="inlineStr">
         <is>
@@ -11399,10 +11391,10 @@
         </is>
       </c>
       <c r="O106" s="32" t="n">
-        <v>-26</v>
+        <v>-19.8</v>
       </c>
       <c r="P106" s="32" t="n">
-        <v>-9.9</v>
+        <v>3.9</v>
       </c>
       <c r="Q106" s="32" t="n"/>
       <c r="R106" s="23" t="inlineStr">
@@ -11619,13 +11611,13 @@
       </c>
       <c r="N108" s="2" t="n"/>
       <c r="O108" s="32" t="n">
-        <v>-21.3</v>
+        <v>-13.4</v>
       </c>
       <c r="P108" s="32" t="n">
-        <v>-9.300000000000001</v>
+        <v>4</v>
       </c>
       <c r="Q108" s="32" t="n">
-        <v>-15.33</v>
+        <v>-2.2</v>
       </c>
       <c r="R108" s="23" t="inlineStr">
         <is>
@@ -11832,12 +11824,8 @@
         </is>
       </c>
       <c r="N110" s="2" t="n"/>
-      <c r="O110" s="32" t="n">
-        <v>-27.1</v>
-      </c>
-      <c r="P110" s="32" t="n">
-        <v>-8.300000000000001</v>
-      </c>
+      <c r="O110" s="32" t="n"/>
+      <c r="P110" s="32" t="n"/>
       <c r="Q110" s="32" t="n"/>
       <c r="R110" s="23" t="inlineStr">
         <is>
@@ -11951,13 +11939,13 @@
       </c>
       <c r="N111" s="2" t="n"/>
       <c r="O111" s="32" t="n">
-        <v>-16.9</v>
+        <v>-13.7</v>
       </c>
       <c r="P111" s="32" t="n">
-        <v>-1.2</v>
+        <v>6.8</v>
       </c>
       <c r="Q111" s="32" t="n">
-        <v>-8.029999999999999</v>
+        <v>-3.58</v>
       </c>
       <c r="R111" s="23" t="inlineStr">
         <is>
@@ -12063,10 +12051,10 @@
       </c>
       <c r="N112" s="2" t="n"/>
       <c r="O112" s="32" t="n">
-        <v>-7.8</v>
+        <v>-10.2</v>
       </c>
       <c r="P112" s="32" t="n">
-        <v>5.5</v>
+        <v>9.4</v>
       </c>
       <c r="Q112" s="32" t="n"/>
       <c r="R112" s="23" t="inlineStr">
@@ -12169,10 +12157,10 @@
       </c>
       <c r="N113" s="2" t="n"/>
       <c r="O113" s="32" t="n">
-        <v>-14.1</v>
+        <v>-8.5</v>
       </c>
       <c r="P113" s="32" t="n">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="Q113" s="32" t="n"/>
       <c r="R113" s="23" t="inlineStr">
@@ -12283,10 +12271,10 @@
         </is>
       </c>
       <c r="O114" s="32" t="n">
-        <v>-21.6</v>
+        <v>-19.6</v>
       </c>
       <c r="P114" s="32" t="n">
-        <v>6.7</v>
+        <v>9.6</v>
       </c>
       <c r="Q114" s="32" t="n"/>
       <c r="R114" s="23" t="inlineStr">
@@ -12405,10 +12393,10 @@
         </is>
       </c>
       <c r="O115" s="32" t="n">
-        <v>-17.7</v>
+        <v>-9.199999999999999</v>
       </c>
       <c r="P115" s="32" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="Q115" s="32" t="n"/>
       <c r="R115" s="23" t="inlineStr">
@@ -12523,13 +12511,13 @@
       </c>
       <c r="N116" s="2" t="n"/>
       <c r="O116" s="32" t="n">
-        <v>-6.2</v>
+        <v>-8.699999999999999</v>
       </c>
       <c r="P116" s="32" t="n">
-        <v>20.1</v>
+        <v>-0.4</v>
       </c>
       <c r="Q116" s="32" t="n">
-        <v>5.97</v>
+        <v>-6.44</v>
       </c>
       <c r="R116" s="23" t="inlineStr">
         <is>
@@ -12635,10 +12623,10 @@
       </c>
       <c r="N117" s="2" t="n"/>
       <c r="O117" s="32" t="n">
-        <v>-2.1</v>
+        <v>-15.5</v>
       </c>
       <c r="P117" s="32" t="n">
-        <v>16.9</v>
+        <v>-4.8</v>
       </c>
       <c r="Q117" s="32" t="n"/>
       <c r="R117" s="23" t="inlineStr">
@@ -12749,10 +12737,10 @@
         </is>
       </c>
       <c r="O118" s="32" t="n">
-        <v>-10.4</v>
+        <v>-22</v>
       </c>
       <c r="P118" s="32" t="n">
-        <v>6.2</v>
+        <v>-6.4</v>
       </c>
       <c r="Q118" s="32" t="n"/>
       <c r="R118" s="23" t="inlineStr">
@@ -12867,13 +12855,13 @@
       </c>
       <c r="N119" s="2" t="n"/>
       <c r="O119" s="32" t="n">
-        <v>4</v>
+        <v>-18.3</v>
       </c>
       <c r="P119" s="32" t="n">
-        <v>7.9</v>
+        <v>-8</v>
       </c>
       <c r="Q119" s="32" t="n">
-        <v>5.12</v>
+        <v>-13.39</v>
       </c>
       <c r="R119" s="23" t="inlineStr">
         <is>
@@ -13101,13 +13089,13 @@
       </c>
       <c r="N121" s="2" t="n"/>
       <c r="O121" s="32" t="n">
-        <v>-1.9</v>
+        <v>-11.2</v>
       </c>
       <c r="P121" s="32" t="n">
-        <v>11.6</v>
+        <v>-6.1</v>
       </c>
       <c r="Q121" s="32" t="n">
-        <v>2.71</v>
+        <v>-9.460000000000001</v>
       </c>
       <c r="R121" s="23" t="inlineStr">
         <is>
@@ -13225,10 +13213,10 @@
       </c>
       <c r="N122" s="2" t="n"/>
       <c r="O122" s="32" t="n">
-        <v>-19.6</v>
+        <v>-21.5</v>
       </c>
       <c r="P122" s="32" t="n">
-        <v>4.3</v>
+        <v>-9.199999999999999</v>
       </c>
       <c r="Q122" s="32" t="n"/>
       <c r="R122" s="23" t="inlineStr">
@@ -13449,13 +13437,13 @@
       </c>
       <c r="N124" s="2" t="n"/>
       <c r="O124" s="32" t="n">
-        <v>-1.4</v>
+        <v>-2.9</v>
       </c>
       <c r="P124" s="32" t="n">
-        <v>12.8</v>
+        <v>15.8</v>
       </c>
       <c r="Q124" s="32" t="n">
-        <v>4.68</v>
+        <v>5.71</v>
       </c>
       <c r="R124" s="23" t="inlineStr">
         <is>
@@ -13573,13 +13561,13 @@
       </c>
       <c r="N125" s="2" t="n"/>
       <c r="O125" s="32" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="P125" s="32" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="Q125" s="32" t="n">
-        <v>6.74</v>
+        <v>7.09</v>
       </c>
       <c r="R125" s="23" t="inlineStr">
         <is>
@@ -13677,10 +13665,10 @@
       </c>
       <c r="N126" s="2" t="n"/>
       <c r="O126" s="32" t="n">
-        <v>4</v>
+        <v>0.6</v>
       </c>
       <c r="P126" s="32" t="n">
-        <v>12.9</v>
+        <v>12.2</v>
       </c>
       <c r="Q126" s="32" t="n"/>
       <c r="R126" s="23" t="inlineStr">
@@ -13787,13 +13775,13 @@
       </c>
       <c r="N127" s="2" t="n"/>
       <c r="O127" s="32" t="n">
-        <v>-0.9</v>
+        <v>3.8</v>
       </c>
       <c r="P127" s="32" t="n">
-        <v>18.6</v>
+        <v>18</v>
       </c>
       <c r="Q127" s="32" t="n">
-        <v>7.8</v>
+        <v>10.94</v>
       </c>
       <c r="R127" s="23" t="inlineStr">
         <is>
@@ -13907,10 +13895,10 @@
       </c>
       <c r="N128" s="2" t="n"/>
       <c r="O128" s="32" t="n">
-        <v>1.1</v>
+        <v>3.1</v>
       </c>
       <c r="P128" s="32" t="n">
-        <v>15</v>
+        <v>13.4</v>
       </c>
       <c r="Q128" s="32" t="n"/>
       <c r="R128" s="23" t="inlineStr">
@@ -14017,13 +14005,13 @@
       </c>
       <c r="N129" s="2" t="n"/>
       <c r="O129" s="32" t="n">
-        <v>0</v>
+        <v>-0.2</v>
       </c>
       <c r="P129" s="32" t="n">
-        <v>17.4</v>
+        <v>16.5</v>
       </c>
       <c r="Q129" s="32" t="n">
-        <v>7.61</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="R129" s="23" t="inlineStr">
         <is>
@@ -14137,13 +14125,13 @@
       </c>
       <c r="N130" s="2" t="n"/>
       <c r="O130" s="32" t="n">
-        <v>-2.3</v>
+        <v>0.2</v>
       </c>
       <c r="P130" s="32" t="n">
-        <v>17.8</v>
+        <v>13.8</v>
       </c>
       <c r="Q130" s="32" t="n">
-        <v>6.35</v>
+        <v>6.26</v>
       </c>
       <c r="R130" s="23" t="inlineStr">
         <is>
@@ -14257,13 +14245,13 @@
       </c>
       <c r="N131" s="2" t="n"/>
       <c r="O131" s="32" t="n">
-        <v>4.5</v>
+        <v>2.9</v>
       </c>
       <c r="P131" s="32" t="n">
-        <v>15.4</v>
+        <v>15.7</v>
       </c>
       <c r="Q131" s="32" t="n">
-        <v>10.55</v>
+        <v>8.9</v>
       </c>
       <c r="R131" s="23" t="inlineStr">
         <is>
@@ -14373,13 +14361,13 @@
       </c>
       <c r="N132" s="2" t="n"/>
       <c r="O132" s="32" t="n">
-        <v>3.2</v>
+        <v>5.6</v>
       </c>
       <c r="P132" s="32" t="n">
-        <v>17.6</v>
+        <v>15.4</v>
       </c>
       <c r="Q132" s="32" t="n">
-        <v>10.14</v>
+        <v>10.56</v>
       </c>
       <c r="R132" s="23" t="inlineStr">
         <is>
@@ -14489,13 +14477,13 @@
       </c>
       <c r="N133" s="2" t="n"/>
       <c r="O133" s="32" t="n">
-        <v>4.3</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="P133" s="32" t="n">
-        <v>19.4</v>
+        <v>18.9</v>
       </c>
       <c r="Q133" s="32" t="n">
-        <v>10.51</v>
+        <v>13.84</v>
       </c>
       <c r="R133" s="23" t="inlineStr">
         <is>
@@ -14711,13 +14699,13 @@
       </c>
       <c r="N135" s="2" t="n"/>
       <c r="O135" s="32" t="n">
-        <v>6.4</v>
+        <v>11.9</v>
       </c>
       <c r="P135" s="32" t="n">
-        <v>17.9</v>
+        <v>20.8</v>
       </c>
       <c r="Q135" s="32" t="n">
-        <v>11.73</v>
+        <v>15.65</v>
       </c>
       <c r="R135" s="23" t="inlineStr">
         <is>
@@ -14827,13 +14815,13 @@
       </c>
       <c r="N136" s="2" t="n"/>
       <c r="O136" s="32" t="n">
-        <v>8.300000000000001</v>
+        <v>12.3</v>
       </c>
       <c r="P136" s="32" t="n">
-        <v>18.3</v>
+        <v>21.6</v>
       </c>
       <c r="Q136" s="32" t="n">
-        <v>13.16</v>
+        <v>16.2</v>
       </c>
       <c r="R136" s="23" t="inlineStr">
         <is>
@@ -14943,13 +14931,13 @@
       </c>
       <c r="N137" s="2" t="n"/>
       <c r="O137" s="32" t="n">
-        <v>3.3</v>
+        <v>8</v>
       </c>
       <c r="P137" s="32" t="n">
-        <v>18</v>
+        <v>21.2</v>
       </c>
       <c r="Q137" s="32" t="n">
-        <v>10.63</v>
+        <v>15.49</v>
       </c>
       <c r="R137" s="23" t="inlineStr">
         <is>
@@ -15059,7 +15047,7 @@
       </c>
       <c r="N138" s="2" t="n"/>
       <c r="O138" s="32" t="n">
-        <v>0.3</v>
+        <v>3.6</v>
       </c>
       <c r="P138" s="32" t="n">
         <v>17</v>
@@ -15173,13 +15161,13 @@
       </c>
       <c r="N139" s="2" t="n"/>
       <c r="O139" s="32" t="n">
-        <v>2.5</v>
+        <v>4.7</v>
       </c>
       <c r="P139" s="32" t="n">
-        <v>15</v>
+        <v>16.9</v>
       </c>
       <c r="Q139" s="32" t="n">
-        <v>8.800000000000001</v>
+        <v>10.85</v>
       </c>
       <c r="R139" s="23" t="inlineStr">
         <is>
@@ -15289,13 +15277,13 @@
       </c>
       <c r="N140" s="2" t="n"/>
       <c r="O140" s="32" t="n">
-        <v>4.2</v>
+        <v>7.2</v>
       </c>
       <c r="P140" s="32" t="n">
-        <v>15.4</v>
+        <v>17.1</v>
       </c>
       <c r="Q140" s="32" t="n">
-        <v>10.04</v>
+        <v>11.49</v>
       </c>
       <c r="R140" s="23" t="inlineStr">
         <is>
@@ -15507,13 +15495,13 @@
       </c>
       <c r="N142" s="2" t="n"/>
       <c r="O142" s="32" t="n">
-        <v>9.5</v>
+        <v>8.1</v>
       </c>
       <c r="P142" s="32" t="n">
-        <v>17.7</v>
+        <v>21.3</v>
       </c>
       <c r="Q142" s="32" t="n">
-        <v>12.21</v>
+        <v>13.72</v>
       </c>
       <c r="R142" s="23" t="inlineStr">
         <is>
@@ -15623,13 +15611,13 @@
       </c>
       <c r="N143" s="2" t="n"/>
       <c r="O143" s="32" t="n">
-        <v>12.4</v>
+        <v>11.6</v>
       </c>
       <c r="P143" s="32" t="n">
-        <v>17.6</v>
+        <v>28.5</v>
       </c>
       <c r="Q143" s="32" t="n">
-        <v>14.98</v>
+        <v>18.7</v>
       </c>
       <c r="R143" s="23" t="inlineStr">
         <is>
@@ -15939,13 +15927,13 @@
       </c>
       <c r="N146" s="2" t="n"/>
       <c r="O146" s="32" t="n">
-        <v>18.9</v>
+        <v>20.1</v>
       </c>
       <c r="P146" s="32" t="n">
-        <v>23.6</v>
+        <v>26.8</v>
       </c>
       <c r="Q146" s="32" t="n">
-        <v>20.29</v>
+        <v>22.5</v>
       </c>
       <c r="R146" s="23" t="inlineStr">
         <is>
@@ -16050,10 +16038,10 @@
         <v>13</v>
       </c>
       <c r="P147" s="32" t="n">
-        <v>18.3</v>
+        <v>26.1</v>
       </c>
       <c r="Q147" s="32" t="n">
-        <v>15.1</v>
+        <v>19.64</v>
       </c>
       <c r="R147" s="23" t="inlineStr">
         <is>
@@ -16265,13 +16253,13 @@
       </c>
       <c r="N149" s="2" t="n"/>
       <c r="O149" s="32" t="n">
-        <v>7.8</v>
+        <v>11.8</v>
       </c>
       <c r="P149" s="32" t="n">
         <v>18.3</v>
       </c>
       <c r="Q149" s="32" t="n">
-        <v>11.66</v>
+        <v>13.8</v>
       </c>
       <c r="R149" s="23" t="inlineStr">
         <is>
@@ -16381,13 +16369,13 @@
       </c>
       <c r="N150" s="2" t="n"/>
       <c r="O150" s="32" t="n">
-        <v>4.8</v>
+        <v>8.1</v>
       </c>
       <c r="P150" s="32" t="n">
-        <v>16.8</v>
+        <v>21.4</v>
       </c>
       <c r="Q150" s="32" t="n">
-        <v>9.550000000000001</v>
+        <v>14.7</v>
       </c>
       <c r="R150" s="23" t="inlineStr">
         <is>
@@ -16497,13 +16485,13 @@
       </c>
       <c r="N151" s="2" t="n"/>
       <c r="O151" s="32" t="n">
-        <v>10.9</v>
+        <v>14.2</v>
       </c>
       <c r="P151" s="32" t="n">
-        <v>23.2</v>
+        <v>26.3</v>
       </c>
       <c r="Q151" s="32" t="n">
-        <v>16.26</v>
+        <v>19.43</v>
       </c>
       <c r="R151" s="23" t="inlineStr">
         <is>
@@ -16703,13 +16691,13 @@
       </c>
       <c r="N153" s="2" t="n"/>
       <c r="O153" s="32" t="n">
-        <v>12</v>
+        <v>13.7</v>
       </c>
       <c r="P153" s="32" t="n">
-        <v>19.7</v>
+        <v>18</v>
       </c>
       <c r="Q153" s="32" t="n">
-        <v>15.4</v>
+        <v>15.53</v>
       </c>
       <c r="R153" s="23" t="inlineStr">
         <is>
@@ -16823,13 +16811,13 @@
       </c>
       <c r="N154" s="2" t="n"/>
       <c r="O154" s="32" t="n">
-        <v>1.7</v>
+        <v>1.3</v>
       </c>
       <c r="P154" s="32" t="n">
-        <v>15.8</v>
+        <v>17.2</v>
       </c>
       <c r="Q154" s="32" t="n">
-        <v>9.140000000000001</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="R154" s="23" t="inlineStr">
         <is>
@@ -17025,10 +17013,10 @@
       </c>
       <c r="N156" s="2" t="n"/>
       <c r="O156" s="32" t="n">
-        <v>-8.6</v>
+        <v>-12</v>
       </c>
       <c r="P156" s="32" t="n">
-        <v>11.9</v>
+        <v>12.8</v>
       </c>
       <c r="Q156" s="32" t="n"/>
       <c r="R156" s="23" t="inlineStr">
@@ -17131,10 +17119,10 @@
       </c>
       <c r="N157" s="2" t="n"/>
       <c r="O157" s="32" t="n">
-        <v>4.2</v>
+        <v>7.2</v>
       </c>
       <c r="P157" s="32" t="n">
-        <v>14.4</v>
+        <v>15</v>
       </c>
       <c r="Q157" s="32" t="n"/>
       <c r="R157" s="23" t="inlineStr">
@@ -17519,10 +17507,10 @@
       </c>
       <c r="N161" s="2" t="n"/>
       <c r="O161" s="32" t="n">
-        <v>1.1</v>
+        <v>4.7</v>
       </c>
       <c r="P161" s="32" t="n">
-        <v>22.7</v>
+        <v>18.9</v>
       </c>
       <c r="Q161" s="32" t="n"/>
       <c r="R161" s="23" t="inlineStr">
@@ -17955,10 +17943,10 @@
         </is>
       </c>
       <c r="O165" s="32" t="n">
-        <v>-30.2</v>
+        <v>-23.2</v>
       </c>
       <c r="P165" s="32" t="n">
-        <v>-9.300000000000001</v>
+        <v>4.7</v>
       </c>
       <c r="Q165" s="32" t="n"/>
       <c r="R165" s="23" t="inlineStr">
@@ -18281,10 +18269,10 @@
         </is>
       </c>
       <c r="O168" s="32" t="n">
-        <v>-7</v>
+        <v>-28.3</v>
       </c>
       <c r="P168" s="32" t="n">
-        <v>6</v>
+        <v>-6.9</v>
       </c>
       <c r="Q168" s="32" t="n"/>
       <c r="R168" s="23" t="inlineStr">
@@ -18395,10 +18383,10 @@
         </is>
       </c>
       <c r="O169" s="32" t="n">
-        <v>-9.9</v>
+        <v>-32.5</v>
       </c>
       <c r="P169" s="32" t="n">
-        <v>3.5</v>
+        <v>-10.4</v>
       </c>
       <c r="Q169" s="32" t="n"/>
       <c r="R169" s="23" t="inlineStr">
@@ -18508,12 +18496,8 @@
           <t>⚡</t>
         </is>
       </c>
-      <c r="O170" s="32" t="n">
-        <v>-21.4</v>
-      </c>
-      <c r="P170" s="32" t="n">
-        <v>1</v>
-      </c>
+      <c r="O170" s="32" t="n"/>
+      <c r="P170" s="32" t="n"/>
       <c r="Q170" s="32" t="n"/>
       <c r="R170" s="23" t="inlineStr">
         <is>
@@ -18614,12 +18598,16 @@
       <c r="L171" s="3" t="n"/>
       <c r="M171" s="14" t="inlineStr">
         <is>
-          <t>可可托海山顶</t>
+          <t>可可托海雪场</t>
         </is>
       </c>
       <c r="N171" s="2" t="n"/>
-      <c r="O171" s="32" t="n"/>
-      <c r="P171" s="32" t="n"/>
+      <c r="O171" s="32" t="n">
+        <v>-28.8</v>
+      </c>
+      <c r="P171" s="32" t="n">
+        <v>-19.4</v>
+      </c>
       <c r="Q171" s="32" t="n"/>
       <c r="R171" s="23" t="inlineStr">
         <is>
@@ -18629,7 +18617,7 @@
       <c r="S171" s="37" t="n"/>
       <c r="T171" s="41" t="inlineStr">
         <is>
-          <t>阿勒泰&lt;br&gt;阿尔泰山</t>
+          <t>阿勒泰 阿尔泰山&lt;br&gt;3100m山顶</t>
         </is>
       </c>
       <c r="U171" s="2" t="inlineStr">
@@ -18725,10 +18713,10 @@
       </c>
       <c r="N172" s="3" t="n"/>
       <c r="O172" s="32" t="n">
-        <v>-12.3</v>
+        <v>-22.3</v>
       </c>
       <c r="P172" s="32" t="n">
-        <v>6.2</v>
+        <v>-8.6</v>
       </c>
       <c r="Q172" s="32" t="n"/>
       <c r="R172" s="23" t="inlineStr">
@@ -18835,10 +18823,10 @@
       </c>
       <c r="N173" s="2" t="n"/>
       <c r="O173" s="32" t="n">
-        <v>-12.9</v>
+        <v>-15.4</v>
       </c>
       <c r="P173" s="32" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="Q173" s="32" t="n"/>
       <c r="R173" s="23" t="inlineStr">
@@ -19157,10 +19145,10 @@
       </c>
       <c r="N176" s="2" t="n"/>
       <c r="O176" s="32" t="n">
-        <v>-3.5</v>
+        <v>-1.6</v>
       </c>
       <c r="P176" s="32" t="n">
-        <v>6.6</v>
+        <v>5.1</v>
       </c>
       <c r="Q176" s="32" t="n"/>
       <c r="R176" s="23" t="inlineStr">
@@ -19259,10 +19247,10 @@
       </c>
       <c r="N177" s="2" t="n"/>
       <c r="O177" s="32" t="n">
-        <v>-21.9</v>
+        <v>-18.4</v>
       </c>
       <c r="P177" s="32" t="n">
-        <v>-13.2</v>
+        <v>-12.6</v>
       </c>
       <c r="Q177" s="32" t="n"/>
       <c r="R177" s="23" t="inlineStr">
@@ -19372,8 +19360,12 @@
         </is>
       </c>
       <c r="N178" s="2" t="n"/>
-      <c r="O178" s="32" t="n"/>
-      <c r="P178" s="32" t="n"/>
+      <c r="O178" s="32" t="n">
+        <v>-30.3</v>
+      </c>
+      <c r="P178" s="32" t="n">
+        <v>-10.5</v>
+      </c>
       <c r="Q178" s="32" t="n"/>
       <c r="R178" s="23" t="inlineStr">
         <is>
@@ -20047,10 +20039,10 @@
       </c>
       <c r="N185" s="2" t="n"/>
       <c r="O185" s="32" t="n">
-        <v>-37.8</v>
+        <v>-36.5</v>
       </c>
       <c r="P185" s="32" t="n">
-        <v>-10.8</v>
+        <v>-8.1</v>
       </c>
       <c r="Q185" s="32" t="n"/>
       <c r="R185" s="23" t="inlineStr">
@@ -20154,13 +20146,13 @@
       </c>
       <c r="N186" s="2" t="n"/>
       <c r="O186" s="32" t="n">
-        <v>-28.6</v>
+        <v>-37.5</v>
       </c>
       <c r="P186" s="32" t="n">
-        <v>-18</v>
+        <v>-8.800000000000001</v>
       </c>
       <c r="Q186" s="32" t="n">
-        <v>-22.74</v>
+        <v>-24.75</v>
       </c>
       <c r="R186" s="23" t="inlineStr">
         <is>
@@ -20263,13 +20255,13 @@
       </c>
       <c r="N187" s="2" t="n"/>
       <c r="O187" s="32" t="n">
-        <v>-31.8</v>
+        <v>-34.7</v>
       </c>
       <c r="P187" s="32" t="n">
-        <v>-15</v>
+        <v>-13.3</v>
       </c>
       <c r="Q187" s="32" t="n">
-        <v>-24.99</v>
+        <v>-24.44</v>
       </c>
       <c r="R187" s="23" t="inlineStr">
         <is>
@@ -20367,13 +20359,13 @@
       </c>
       <c r="N188" s="2" t="n"/>
       <c r="O188" s="32" t="n">
-        <v>-35.8</v>
+        <v>-34</v>
       </c>
       <c r="P188" s="32" t="n">
-        <v>-20.8</v>
+        <v>-18.5</v>
       </c>
       <c r="Q188" s="32" t="n">
-        <v>-27.75</v>
+        <v>-26.43</v>
       </c>
       <c r="R188" s="23" t="inlineStr">
         <is>
@@ -20471,13 +20463,13 @@
       </c>
       <c r="N189" s="2" t="n"/>
       <c r="O189" s="32" t="n">
-        <v>-27.4</v>
+        <v>-36</v>
       </c>
       <c r="P189" s="32" t="n">
-        <v>-17.5</v>
+        <v>-8.9</v>
       </c>
       <c r="Q189" s="32" t="n">
-        <v>-22.2</v>
+        <v>-23.92</v>
       </c>
       <c r="R189" s="23" t="inlineStr">
         <is>
@@ -20575,13 +20567,13 @@
       </c>
       <c r="N190" s="2" t="n"/>
       <c r="O190" s="32" t="n">
-        <v>-43.7</v>
+        <v>-24.5</v>
       </c>
       <c r="P190" s="32" t="n">
-        <v>-22.3</v>
+        <v>-0.5</v>
       </c>
       <c r="Q190" s="32" t="n">
-        <v>-34.65</v>
+        <v>-10.91</v>
       </c>
       <c r="R190" s="23" t="inlineStr">
         <is>
@@ -20679,13 +20671,13 @@
       </c>
       <c r="N191" s="2" t="n"/>
       <c r="O191" s="32" t="n">
-        <v>-32.5</v>
+        <v>-33.8</v>
       </c>
       <c r="P191" s="32" t="n">
-        <v>-19.1</v>
+        <v>-13.9</v>
       </c>
       <c r="Q191" s="32" t="n">
-        <v>-25.16</v>
+        <v>-25.47</v>
       </c>
       <c r="R191" s="23" t="inlineStr">
         <is>
@@ -20779,13 +20771,13 @@
       </c>
       <c r="N192" s="2" t="n"/>
       <c r="O192" s="32" t="n">
-        <v>-34.2</v>
+        <v>-10</v>
       </c>
       <c r="P192" s="32" t="n">
-        <v>-21</v>
+        <v>-5</v>
       </c>
       <c r="Q192" s="32" t="n">
-        <v>-27.25</v>
+        <v>-7.72</v>
       </c>
       <c r="R192" s="23" t="inlineStr">
         <is>
@@ -20884,13 +20876,13 @@
       </c>
       <c r="N193" s="2" t="n"/>
       <c r="O193" s="32" t="n">
-        <v>-35.4</v>
+        <v>-15.2</v>
       </c>
       <c r="P193" s="32" t="n">
-        <v>-13.2</v>
+        <v>-7.2</v>
       </c>
       <c r="Q193" s="32" t="n">
-        <v>-26.76</v>
+        <v>-10.25</v>
       </c>
       <c r="R193" s="23" t="inlineStr">
         <is>
@@ -20992,10 +20984,10 @@
       </c>
       <c r="N194" s="2" t="n"/>
       <c r="O194" s="32" t="n">
-        <v>-40.3</v>
+        <v>-19.2</v>
       </c>
       <c r="P194" s="32" t="n">
-        <v>-20.4</v>
+        <v>-11.1</v>
       </c>
       <c r="Q194" s="32" t="n"/>
       <c r="R194" s="23" t="inlineStr">
@@ -21090,13 +21082,13 @@
       </c>
       <c r="N195" s="2" t="n"/>
       <c r="O195" s="32" t="n">
-        <v>-30</v>
+        <v>-7.5</v>
       </c>
       <c r="P195" s="32" t="n">
-        <v>-4.3</v>
+        <v>-1.2</v>
       </c>
       <c r="Q195" s="32" t="n">
-        <v>-15.69</v>
+        <v>-3.36</v>
       </c>
       <c r="R195" s="23" t="inlineStr">
         <is>
@@ -21194,13 +21186,13 @@
       </c>
       <c r="N196" s="2" t="n"/>
       <c r="O196" s="32" t="n">
-        <v>-19.2</v>
+        <v>-22</v>
       </c>
       <c r="P196" s="32" t="n">
-        <v>-10.8</v>
+        <v>-4.5</v>
       </c>
       <c r="Q196" s="32" t="n">
-        <v>-15.38</v>
+        <v>-9.609999999999999</v>
       </c>
       <c r="R196" s="23" t="inlineStr">
         <is>
@@ -21298,13 +21290,13 @@
       </c>
       <c r="N197" s="24" t="n"/>
       <c r="O197" s="32" t="n">
-        <v>-15.4</v>
+        <v>-29.4</v>
       </c>
       <c r="P197" s="32" t="n">
-        <v>-1.9</v>
+        <v>-16.2</v>
       </c>
       <c r="Q197" s="32" t="n">
-        <v>-6.9</v>
+        <v>-22.68</v>
       </c>
       <c r="R197" s="23" t="inlineStr">
         <is>
@@ -21393,12 +21385,8 @@
         </is>
       </c>
       <c r="N198" s="2" t="n"/>
-      <c r="O198" s="32" t="n">
-        <v>-21.2</v>
-      </c>
-      <c r="P198" s="32" t="n">
-        <v>-0.9</v>
-      </c>
+      <c r="O198" s="32" t="n"/>
+      <c r="P198" s="32" t="n"/>
       <c r="Q198" s="32" t="n"/>
       <c r="R198" s="23" t="inlineStr">
         <is>
@@ -21801,8 +21789,12 @@
         </is>
       </c>
       <c r="N202" s="2" t="n"/>
-      <c r="O202" s="32" t="n"/>
-      <c r="P202" s="32" t="n"/>
+      <c r="O202" s="32" t="n">
+        <v>-24.2</v>
+      </c>
+      <c r="P202" s="32" t="n">
+        <v>2.8</v>
+      </c>
       <c r="Q202" s="32" t="n"/>
       <c r="R202" s="23" t="inlineStr">
         <is>
@@ -22005,8 +21997,12 @@
         </is>
       </c>
       <c r="N204" s="2" t="n"/>
-      <c r="O204" s="32" t="n"/>
-      <c r="P204" s="32" t="n"/>
+      <c r="O204" s="32" t="n">
+        <v>-21.2</v>
+      </c>
+      <c r="P204" s="32" t="n">
+        <v>5.3</v>
+      </c>
       <c r="Q204" s="32" t="n"/>
       <c r="R204" s="23" t="inlineStr">
         <is>
@@ -22311,8 +22307,12 @@
         </is>
       </c>
       <c r="N207" s="2" t="n"/>
-      <c r="O207" s="32" t="n"/>
-      <c r="P207" s="32" t="n"/>
+      <c r="O207" s="32" t="n">
+        <v>-26</v>
+      </c>
+      <c r="P207" s="32" t="n">
+        <v>3.6</v>
+      </c>
       <c r="Q207" s="32" t="n"/>
       <c r="R207" s="23" t="inlineStr">
         <is>
@@ -22905,12 +22905,8 @@
         </is>
       </c>
       <c r="N213" s="2" t="n"/>
-      <c r="O213" s="32" t="n">
-        <v>-31.8</v>
-      </c>
-      <c r="P213" s="32" t="n">
-        <v>-1.5</v>
-      </c>
+      <c r="O213" s="32" t="n"/>
+      <c r="P213" s="32" t="n"/>
       <c r="Q213" s="32" t="n"/>
       <c r="R213" s="23" t="inlineStr">
         <is>
@@ -26240,13 +26236,13 @@
       </c>
       <c r="N247" s="2" t="n"/>
       <c r="O247" s="32" t="n">
-        <v>-19.6</v>
+        <v>-15.8</v>
       </c>
       <c r="P247" s="32" t="n">
-        <v>-3.2</v>
+        <v>-5.2</v>
       </c>
       <c r="Q247" s="32" t="n">
-        <v>-10.74</v>
+        <v>-8.949999999999999</v>
       </c>
       <c r="R247" s="23" t="inlineStr">
         <is>
@@ -26356,13 +26352,13 @@
         </is>
       </c>
       <c r="O248" s="32" t="n">
-        <v>-0.8</v>
+        <v>-30.1</v>
       </c>
       <c r="P248" s="32" t="n">
-        <v>6.2</v>
+        <v>-14.4</v>
       </c>
       <c r="Q248" s="32" t="n">
-        <v>1.41</v>
+        <v>-22.29</v>
       </c>
       <c r="R248" s="23" t="inlineStr">
         <is>
@@ -26464,13 +26460,13 @@
       </c>
       <c r="N249" s="2" t="n"/>
       <c r="O249" s="32" t="n">
-        <v>-5.7</v>
+        <v>-2.9</v>
       </c>
       <c r="P249" s="32" t="n">
-        <v>2.5</v>
+        <v>4.1</v>
       </c>
       <c r="Q249" s="32" t="n">
-        <v>-2.39</v>
+        <v>-0.14</v>
       </c>
       <c r="R249" s="23" t="inlineStr">
         <is>
@@ -26576,13 +26572,13 @@
       </c>
       <c r="N250" s="2" t="n"/>
       <c r="O250" s="32" t="n">
-        <v>-12.3</v>
+        <v>-11</v>
       </c>
       <c r="P250" s="32" t="n">
-        <v>3.6</v>
+        <v>2.4</v>
       </c>
       <c r="Q250" s="32" t="n">
-        <v>-4.42</v>
+        <v>-4.49</v>
       </c>
       <c r="R250" s="23" t="inlineStr">
         <is>
@@ -26696,10 +26692,10 @@
         </is>
       </c>
       <c r="O251" s="32" t="n">
-        <v>-17.6</v>
+        <v>-34.8</v>
       </c>
       <c r="P251" s="32" t="n">
-        <v>-2.8</v>
+        <v>-14.5</v>
       </c>
       <c r="Q251" s="32" t="n"/>
       <c r="R251" s="23" t="inlineStr">
@@ -26794,10 +26790,10 @@
       </c>
       <c r="N252" s="2" t="n"/>
       <c r="O252" s="32" t="n">
-        <v>-6.2</v>
+        <v>-18.1</v>
       </c>
       <c r="P252" s="32" t="n">
-        <v>3.8</v>
+        <v>-10.4</v>
       </c>
       <c r="Q252" s="32" t="n"/>
       <c r="R252" s="23" t="inlineStr">
@@ -26990,13 +26986,13 @@
       </c>
       <c r="N254" s="2" t="n"/>
       <c r="O254" s="32" t="n">
-        <v>-22.5</v>
+        <v>-25.7</v>
       </c>
       <c r="P254" s="32" t="n">
-        <v>-11.4</v>
+        <v>-4.7</v>
       </c>
       <c r="Q254" s="32" t="n">
-        <v>-17.25</v>
+        <v>-17.38</v>
       </c>
       <c r="R254" s="23" t="inlineStr">
         <is>
@@ -27564,13 +27560,13 @@
       </c>
       <c r="N260" s="2" t="n"/>
       <c r="O260" s="32" t="n">
-        <v>-18</v>
+        <v>-28.1</v>
       </c>
       <c r="P260" s="32" t="n">
-        <v>9.4</v>
+        <v>-7.8</v>
       </c>
       <c r="Q260" s="32" t="n">
-        <v>-5.16</v>
+        <v>-15.6</v>
       </c>
       <c r="R260" s="23" t="inlineStr">
         <is>
@@ -27672,13 +27668,13 @@
       </c>
       <c r="N261" s="2" t="n"/>
       <c r="O261" s="32" t="n">
-        <v>-16.1</v>
+        <v>-6.7</v>
       </c>
       <c r="P261" s="32" t="n">
-        <v>4.7</v>
+        <v>3.1</v>
       </c>
       <c r="Q261" s="32" t="n">
-        <v>-6.84</v>
+        <v>-2.56</v>
       </c>
       <c r="R261" s="23" t="inlineStr">
         <is>
@@ -27784,13 +27780,13 @@
       </c>
       <c r="N262" s="2" t="n"/>
       <c r="O262" s="32" t="n">
-        <v>-5.8</v>
+        <v>-18.2</v>
       </c>
       <c r="P262" s="32" t="n">
-        <v>-2.5</v>
+        <v>-7.6</v>
       </c>
       <c r="Q262" s="32" t="n">
-        <v>-3.76</v>
+        <v>-12.76</v>
       </c>
       <c r="R262" s="23" t="inlineStr">
         <is>
@@ -27990,13 +27986,13 @@
       </c>
       <c r="N264" s="2" t="n"/>
       <c r="O264" s="32" t="n">
-        <v>-7.1</v>
+        <v>-10.7</v>
       </c>
       <c r="P264" s="32" t="n">
-        <v>4.6</v>
+        <v>1.1</v>
       </c>
       <c r="Q264" s="32" t="n">
-        <v>-2.01</v>
+        <v>-7.67</v>
       </c>
       <c r="R264" s="23" t="inlineStr">
         <is>
@@ -28110,10 +28106,10 @@
       </c>
       <c r="N265" s="2" t="n"/>
       <c r="O265" s="32" t="n">
-        <v>-56.1</v>
+        <v>-51.6</v>
       </c>
       <c r="P265" s="32" t="n">
-        <v>-44.1</v>
+        <v>-45</v>
       </c>
       <c r="Q265" s="32" t="n"/>
       <c r="R265" s="23" t="inlineStr">
@@ -29154,13 +29150,13 @@
       </c>
       <c r="N276" s="2" t="n"/>
       <c r="O276" s="32" t="n">
-        <v>-41.9</v>
+        <v>-22</v>
       </c>
       <c r="P276" s="32" t="n">
-        <v>-16.8</v>
+        <v>-8.699999999999999</v>
       </c>
       <c r="Q276" s="32" t="n">
-        <v>-30.45</v>
+        <v>-15.22</v>
       </c>
       <c r="R276" s="23" t="inlineStr">
         <is>
@@ -30817,39 +30813,111 @@
       <c r="AH293" s="2" t="n"/>
     </row>
     <row r="294" ht="24" customHeight="1" s="48">
-      <c r="A294" s="2" t="n"/>
+      <c r="A294" s="2" t="n">
+        <v>293</v>
+      </c>
       <c r="B294" s="2" t="n"/>
-      <c r="C294" s="46" t="n"/>
+      <c r="C294" s="46" t="inlineStr">
+        <is>
+          <t>51468</t>
+        </is>
+      </c>
       <c r="D294" s="2" t="n"/>
-      <c r="E294" s="4" t="n"/>
+      <c r="E294" s="4" t="n">
+        <v>99999</v>
+      </c>
       <c r="F294" s="39" t="n"/>
-      <c r="G294" s="29" t="n"/>
-      <c r="H294" s="29" t="n"/>
-      <c r="I294" s="2" t="n"/>
-      <c r="J294" s="27" t="n"/>
-      <c r="K294" s="4" t="n"/>
+      <c r="G294" s="29" t="n">
+        <v>43.1131</v>
+      </c>
+      <c r="H294" s="29" t="n">
+        <v>86.84310000000001</v>
+      </c>
+      <c r="I294" s="2" t="n">
+        <v>3540.5</v>
+      </c>
+      <c r="J294" s="27" t="n">
+        <v>12</v>
+      </c>
+      <c r="K294" s="31" t="inlineStr">
+        <is>
+          <t>🇨🇳</t>
+        </is>
+      </c>
       <c r="L294" s="2" t="n"/>
-      <c r="M294" s="14" t="n"/>
+      <c r="M294" s="14" t="inlineStr">
+        <is>
+          <t>天山大西沟</t>
+        </is>
+      </c>
       <c r="N294" s="2" t="n"/>
-      <c r="O294" s="32" t="n"/>
-      <c r="P294" s="32" t="n"/>
+      <c r="O294" s="32" t="n">
+        <v>-23.2</v>
+      </c>
+      <c r="P294" s="32" t="n">
+        <v>-14.7</v>
+      </c>
       <c r="Q294" s="32" t="n"/>
-      <c r="R294" s="23" t="n"/>
+      <c r="R294" s="23" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="S294" s="37" t="n"/>
-      <c r="T294" s="41" t="n"/>
-      <c r="U294" s="2" t="n"/>
-      <c r="V294" s="4" t="n"/>
-      <c r="W294" s="4" t="n"/>
-      <c r="X294" s="4" t="n"/>
+      <c r="T294" s="41" t="inlineStr">
+        <is>
+          <t>天山 海拔3540.5m</t>
+        </is>
+      </c>
+      <c r="U294" s="2" t="inlineStr">
+        <is>
+          <t>新疆</t>
+        </is>
+      </c>
+      <c r="V294" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="W294" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="X294" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="Y294" s="4" t="n"/>
-      <c r="Z294" s="2" t="n"/>
-      <c r="AA294" s="2" t="n"/>
+      <c r="Z294" s="2" t="inlineStr">
+        <is>
+          <t>乌鲁木齐市</t>
+        </is>
+      </c>
+      <c r="AA294" s="2" t="inlineStr">
+        <is>
+          <t>乌鲁木齐县</t>
+        </is>
+      </c>
       <c r="AB294" s="2" t="n"/>
       <c r="AC294" s="2" t="n"/>
-      <c r="AD294" s="2" t="n"/>
-      <c r="AE294" s="4" t="n"/>
+      <c r="AD294" s="2" t="inlineStr">
+        <is>
+          <t>中国</t>
+        </is>
+      </c>
+      <c r="AE294" s="4" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
       <c r="AF294" s="4" t="n"/>
-      <c r="AG294" s="2" t="n"/>
+      <c r="AG294" s="2" t="inlineStr">
+        <is>
+          <t>天山</t>
+        </is>
+      </c>
       <c r="AH294" s="2" t="n"/>
     </row>
     <row r="295" ht="24" customHeight="1" s="48">

--- a/气象/For_Python_站点信息和记录.xlsx
+++ b/气象/For_Python_站点信息和记录.xlsx
@@ -796,8 +796,8 @@
     <col width="18.59765625" customWidth="1" style="8" min="25" max="25"/>
     <col width="12.59765625" customWidth="1" style="5" min="26" max="30"/>
     <col width="12.59765625" customWidth="1" style="8" min="31" max="32"/>
-    <col width="12.59765625" customWidth="1" style="5" min="33" max="336"/>
-    <col width="12.59765625" customWidth="1" style="5" min="337" max="16384"/>
+    <col width="12.59765625" customWidth="1" style="5" min="33" max="349"/>
+    <col width="12.59765625" customWidth="1" style="5" min="350" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="27.75" customFormat="1" customHeight="1" s="11">
@@ -1020,13 +1020,13 @@
         </is>
       </c>
       <c r="O2" s="32" t="n">
-        <v>-19.1</v>
+        <v>-11.9</v>
       </c>
       <c r="P2" s="32" t="n">
-        <v>-6.4</v>
+        <v>-1.4</v>
       </c>
       <c r="Q2" s="32" t="n">
-        <v>-11.07</v>
+        <v>-7.1</v>
       </c>
       <c r="R2" s="23" t="inlineStr">
         <is>
@@ -1126,10 +1126,10 @@
         </is>
       </c>
       <c r="O3" s="32" t="n">
-        <v>-22.6</v>
+        <v>-18.9</v>
       </c>
       <c r="P3" s="32" t="n">
-        <v>-6</v>
+        <v>-0.4</v>
       </c>
       <c r="Q3" s="32" t="n"/>
       <c r="R3" s="23" t="n"/>
@@ -1418,10 +1418,10 @@
         </is>
       </c>
       <c r="O6" s="32" t="n">
-        <v>-19.1</v>
+        <v>-14.7</v>
       </c>
       <c r="P6" s="32" t="n">
-        <v>4.4</v>
+        <v>2.5</v>
       </c>
       <c r="Q6" s="32" t="n"/>
       <c r="R6" s="23" t="n"/>
@@ -1518,10 +1518,10 @@
         </is>
       </c>
       <c r="O7" s="32" t="n">
-        <v>-17</v>
+        <v>-11.2</v>
       </c>
       <c r="P7" s="32" t="n">
-        <v>-0.1</v>
+        <v>2.7</v>
       </c>
       <c r="Q7" s="32" t="n"/>
       <c r="R7" s="23" t="n"/>
@@ -1626,13 +1626,13 @@
       </c>
       <c r="N8" s="2" t="n"/>
       <c r="O8" s="32" t="n">
-        <v>-9.300000000000001</v>
+        <v>-6</v>
       </c>
       <c r="P8" s="32" t="n">
-        <v>6.1</v>
+        <v>11.3</v>
       </c>
       <c r="Q8" s="32" t="n">
-        <v>-1.82</v>
+        <v>1.26</v>
       </c>
       <c r="R8" s="23" t="inlineStr">
         <is>
@@ -1738,13 +1738,13 @@
       </c>
       <c r="N9" s="2" t="n"/>
       <c r="O9" s="32" t="n">
-        <v>-12.9</v>
+        <v>-5.7</v>
       </c>
       <c r="P9" s="32" t="n">
-        <v>-3.8</v>
+        <v>2.2</v>
       </c>
       <c r="Q9" s="32" t="n">
-        <v>-8.619999999999999</v>
+        <v>-1.89</v>
       </c>
       <c r="R9" s="23" t="inlineStr">
         <is>
@@ -1858,13 +1858,13 @@
         </is>
       </c>
       <c r="O10" s="32" t="n">
-        <v>-18.7</v>
+        <v>-10.2</v>
       </c>
       <c r="P10" s="32" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="Q10" s="32" t="n">
-        <v>-9.029999999999999</v>
+        <v>-5.18</v>
       </c>
       <c r="R10" s="23" t="inlineStr">
         <is>
@@ -1974,13 +1974,13 @@
         </is>
       </c>
       <c r="O11" s="32" t="n">
-        <v>-18.8</v>
+        <v>-15.6</v>
       </c>
       <c r="P11" s="32" t="n">
-        <v>5.3</v>
+        <v>3</v>
       </c>
       <c r="Q11" s="32" t="n">
-        <v>-6.92</v>
+        <v>-5.81</v>
       </c>
       <c r="R11" s="23" t="inlineStr">
         <is>
@@ -2086,13 +2086,13 @@
       </c>
       <c r="N12" s="2" t="n"/>
       <c r="O12" s="32" t="n">
-        <v>-15.9</v>
+        <v>-8.5</v>
       </c>
       <c r="P12" s="32" t="n">
-        <v>3.2</v>
+        <v>4.7</v>
       </c>
       <c r="Q12" s="32" t="n">
-        <v>-6.94</v>
+        <v>-2.83</v>
       </c>
       <c r="R12" s="23" t="inlineStr">
         <is>
@@ -2202,13 +2202,13 @@
         </is>
       </c>
       <c r="O13" s="32" t="n">
-        <v>-19.4</v>
+        <v>-11.9</v>
       </c>
       <c r="P13" s="32" t="n">
-        <v>-0.1</v>
+        <v>2.3</v>
       </c>
       <c r="Q13" s="32" t="n">
-        <v>-9.720000000000001</v>
+        <v>-4.61</v>
       </c>
       <c r="R13" s="23" t="inlineStr">
         <is>
@@ -2314,13 +2314,13 @@
       </c>
       <c r="N14" s="2" t="n"/>
       <c r="O14" s="32" t="n">
-        <v>-8.300000000000001</v>
+        <v>-9</v>
       </c>
       <c r="P14" s="32" t="n">
-        <v>8.300000000000001</v>
+        <v>6.9</v>
       </c>
       <c r="Q14" s="32" t="n">
-        <v>-1.19</v>
+        <v>-1.15</v>
       </c>
       <c r="R14" s="23" t="inlineStr">
         <is>
@@ -2420,10 +2420,10 @@
       </c>
       <c r="N15" s="2" t="n"/>
       <c r="O15" s="32" t="n">
-        <v>-19.7</v>
+        <v>-13.1</v>
       </c>
       <c r="P15" s="32" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="Q15" s="32" t="n"/>
       <c r="R15" s="23" t="n"/>
@@ -7829,20 +7829,10 @@
         </is>
       </c>
       <c r="N75" s="2" t="n"/>
-      <c r="O75" s="32" t="n">
-        <v>-12.3</v>
-      </c>
-      <c r="P75" s="32" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="Q75" s="32" t="n">
-        <v>-2.86</v>
-      </c>
-      <c r="R75" s="23" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="O75" s="32" t="n"/>
+      <c r="P75" s="32" t="n"/>
+      <c r="Q75" s="32" t="n"/>
+      <c r="R75" s="23" t="n"/>
       <c r="S75" s="37" t="n"/>
       <c r="T75" s="41" t="inlineStr">
         <is>
@@ -7945,20 +7935,10 @@
           <t>▲</t>
         </is>
       </c>
-      <c r="O76" s="32" t="n">
-        <v>-18.2</v>
-      </c>
-      <c r="P76" s="32" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="Q76" s="32" t="n">
-        <v>-8</v>
-      </c>
-      <c r="R76" s="23" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="O76" s="32" t="n"/>
+      <c r="P76" s="32" t="n"/>
+      <c r="Q76" s="32" t="n"/>
+      <c r="R76" s="23" t="n"/>
       <c r="S76" s="37" t="n"/>
       <c r="T76" s="41" t="inlineStr">
         <is>
@@ -8062,13 +8042,13 @@
         </is>
       </c>
       <c r="O77" s="32" t="n">
-        <v>-16.3</v>
+        <v>-4.2</v>
       </c>
       <c r="P77" s="32" t="n">
-        <v>0.3</v>
+        <v>2.3</v>
       </c>
       <c r="Q77" s="32" t="n">
-        <v>-7.11</v>
+        <v>-1.59</v>
       </c>
       <c r="R77" s="23" t="inlineStr">
         <is>
@@ -8173,20 +8153,10 @@
         </is>
       </c>
       <c r="N78" s="2" t="n"/>
-      <c r="O78" s="32" t="n">
-        <v>-11.5</v>
-      </c>
-      <c r="P78" s="32" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q78" s="32" t="n">
-        <v>-4.49</v>
-      </c>
-      <c r="R78" s="23" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="O78" s="32" t="n"/>
+      <c r="P78" s="32" t="n"/>
+      <c r="Q78" s="32" t="n"/>
+      <c r="R78" s="23" t="n"/>
       <c r="S78" s="37" t="n"/>
       <c r="T78" s="41" t="inlineStr">
         <is>
@@ -8289,20 +8259,10 @@
           <t>⚡</t>
         </is>
       </c>
-      <c r="O79" s="32" t="n">
-        <v>-10.5</v>
-      </c>
-      <c r="P79" s="32" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="Q79" s="32" t="n">
-        <v>-0.55</v>
-      </c>
-      <c r="R79" s="23" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="O79" s="32" t="n"/>
+      <c r="P79" s="32" t="n"/>
+      <c r="Q79" s="32" t="n"/>
+      <c r="R79" s="23" t="n"/>
       <c r="S79" s="37" t="n"/>
       <c r="T79" s="41" t="inlineStr">
         <is>
@@ -8401,20 +8361,10 @@
         </is>
       </c>
       <c r="N80" s="2" t="n"/>
-      <c r="O80" s="32" t="n">
-        <v>-19.4</v>
-      </c>
-      <c r="P80" s="32" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="Q80" s="32" t="n">
-        <v>-6.95</v>
-      </c>
-      <c r="R80" s="23" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="O80" s="32" t="n"/>
+      <c r="P80" s="32" t="n"/>
+      <c r="Q80" s="32" t="n"/>
+      <c r="R80" s="23" t="n"/>
       <c r="S80" s="37" t="n"/>
       <c r="T80" s="41" t="inlineStr">
         <is>
@@ -8518,12 +8468,14 @@
         </is>
       </c>
       <c r="O81" s="32" t="n">
-        <v>-24.1</v>
+        <v>-18.2</v>
       </c>
       <c r="P81" s="32" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="Q81" s="32" t="n"/>
+        <v>6.1</v>
+      </c>
+      <c r="Q81" s="32" t="n">
+        <v>-4.6</v>
+      </c>
       <c r="R81" s="23" t="inlineStr">
         <is>
           <t>Y</t>
@@ -8637,13 +8589,13 @@
         </is>
       </c>
       <c r="O82" s="32" t="n">
-        <v>-23.5</v>
+        <v>-17.8</v>
       </c>
       <c r="P82" s="32" t="n">
-        <v>4.2</v>
+        <v>5.6</v>
       </c>
       <c r="Q82" s="32" t="n">
-        <v>-10.34</v>
+        <v>-5.34</v>
       </c>
       <c r="R82" s="23" t="inlineStr">
         <is>
@@ -8748,20 +8700,10 @@
         </is>
       </c>
       <c r="N83" s="2" t="n"/>
-      <c r="O83" s="32" t="n">
-        <v>-2.9</v>
-      </c>
-      <c r="P83" s="32" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="Q83" s="32" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="R83" s="23" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="O83" s="32" t="n"/>
+      <c r="P83" s="32" t="n"/>
+      <c r="Q83" s="32" t="n"/>
+      <c r="R83" s="23" t="n"/>
       <c r="S83" s="37" t="n"/>
       <c r="T83" s="41" t="inlineStr">
         <is>
@@ -8865,13 +8807,13 @@
         </is>
       </c>
       <c r="O84" s="32" t="n">
-        <v>-13.6</v>
+        <v>-2.8</v>
       </c>
       <c r="P84" s="32" t="n">
-        <v>6.7</v>
+        <v>7.3</v>
       </c>
       <c r="Q84" s="32" t="n">
-        <v>-3.8</v>
+        <v>2.26</v>
       </c>
       <c r="R84" s="23" t="inlineStr">
         <is>
@@ -8980,20 +8922,10 @@
           <t>⚡</t>
         </is>
       </c>
-      <c r="O85" s="32" t="n">
-        <v>-15.5</v>
-      </c>
-      <c r="P85" s="32" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="Q85" s="32" t="n">
-        <v>-5.61</v>
-      </c>
-      <c r="R85" s="23" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="O85" s="32" t="n"/>
+      <c r="P85" s="32" t="n"/>
+      <c r="Q85" s="32" t="n"/>
+      <c r="R85" s="23" t="n"/>
       <c r="S85" s="37" t="n"/>
       <c r="T85" s="41" t="inlineStr">
         <is>
@@ -9093,13 +9025,13 @@
       </c>
       <c r="N86" s="2" t="n"/>
       <c r="O86" s="32" t="n">
-        <v>-7.5</v>
+        <v>-5.8</v>
       </c>
       <c r="P86" s="32" t="n">
-        <v>4.9</v>
+        <v>10.3</v>
       </c>
       <c r="Q86" s="32" t="n">
-        <v>-1.89</v>
+        <v>1.7</v>
       </c>
       <c r="R86" s="23" t="inlineStr">
         <is>
@@ -9216,20 +9148,10 @@
           <t>▲</t>
         </is>
       </c>
-      <c r="O87" s="32" t="n">
-        <v>-16.7</v>
-      </c>
-      <c r="P87" s="32" t="n">
-        <v>-1.9</v>
-      </c>
-      <c r="Q87" s="32" t="n">
-        <v>-9.119999999999999</v>
-      </c>
-      <c r="R87" s="23" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="O87" s="32" t="n"/>
+      <c r="P87" s="32" t="n"/>
+      <c r="Q87" s="32" t="n"/>
+      <c r="R87" s="23" t="n"/>
       <c r="S87" s="37" t="n"/>
       <c r="T87" s="41" t="inlineStr">
         <is>
@@ -9329,13 +9251,13 @@
       </c>
       <c r="N88" s="2" t="n"/>
       <c r="O88" s="32" t="n">
-        <v>-11.9</v>
+        <v>-8.800000000000001</v>
       </c>
       <c r="P88" s="32" t="n">
-        <v>7.9</v>
+        <v>9.9</v>
       </c>
       <c r="Q88" s="32" t="n">
-        <v>-2.97</v>
+        <v>-0.17</v>
       </c>
       <c r="R88" s="23" t="inlineStr">
         <is>
@@ -9440,20 +9362,10 @@
         </is>
       </c>
       <c r="N89" s="2" t="n"/>
-      <c r="O89" s="32" t="n">
-        <v>-20.3</v>
-      </c>
-      <c r="P89" s="32" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="Q89" s="32" t="n">
-        <v>-6.69</v>
-      </c>
-      <c r="R89" s="23" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="O89" s="32" t="n"/>
+      <c r="P89" s="32" t="n"/>
+      <c r="Q89" s="32" t="n"/>
+      <c r="R89" s="23" t="n"/>
       <c r="S89" s="37" t="n"/>
       <c r="T89" s="41" t="inlineStr">
         <is>
@@ -9552,20 +9464,10 @@
           <t>↓</t>
         </is>
       </c>
-      <c r="O90" s="32" t="n">
-        <v>-14</v>
-      </c>
-      <c r="P90" s="32" t="n">
-        <v>-3.6</v>
-      </c>
-      <c r="Q90" s="32" t="n">
-        <v>-8.109999999999999</v>
-      </c>
-      <c r="R90" s="23" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="O90" s="32" t="n"/>
+      <c r="P90" s="32" t="n"/>
+      <c r="Q90" s="32" t="n"/>
+      <c r="R90" s="23" t="n"/>
       <c r="S90" s="37" t="n"/>
       <c r="T90" s="41" t="inlineStr">
         <is>
@@ -9661,13 +9563,13 @@
       </c>
       <c r="N91" s="2" t="n"/>
       <c r="O91" s="32" t="n">
-        <v>-18.3</v>
+        <v>-10.9</v>
       </c>
       <c r="P91" s="32" t="n">
-        <v>-3</v>
+        <v>1.6</v>
       </c>
       <c r="Q91" s="32" t="n">
-        <v>-10.27</v>
+        <v>-4.81</v>
       </c>
       <c r="R91" s="23" t="inlineStr">
         <is>
@@ -9769,13 +9671,13 @@
       </c>
       <c r="N92" s="2" t="n"/>
       <c r="O92" s="32" t="n">
-        <v>-2</v>
+        <v>-3.7</v>
       </c>
       <c r="P92" s="32" t="n">
-        <v>6</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="Q92" s="32" t="n">
-        <v>0.48</v>
+        <v>2.06</v>
       </c>
       <c r="R92" s="23" t="inlineStr">
         <is>
@@ -9881,13 +9783,13 @@
       </c>
       <c r="N93" s="2" t="n"/>
       <c r="O93" s="32" t="n">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="P93" s="32" t="n">
-        <v>11.1</v>
+        <v>13.6</v>
       </c>
       <c r="Q93" s="32" t="n">
-        <v>6.8</v>
+        <v>7.46</v>
       </c>
       <c r="R93" s="23" t="inlineStr">
         <is>
@@ -10001,10 +9903,10 @@
         </is>
       </c>
       <c r="O94" s="32" t="n">
-        <v>-1.1</v>
+        <v>-3.3</v>
       </c>
       <c r="P94" s="32" t="n">
-        <v>10.5</v>
+        <v>13.8</v>
       </c>
       <c r="Q94" s="32" t="n"/>
       <c r="R94" s="23" t="inlineStr">
@@ -10119,13 +10021,13 @@
       </c>
       <c r="N95" s="2" t="n"/>
       <c r="O95" s="32" t="n">
-        <v>0.5</v>
+        <v>3</v>
       </c>
       <c r="P95" s="32" t="n">
-        <v>10.7</v>
+        <v>13.4</v>
       </c>
       <c r="Q95" s="32" t="n">
-        <v>6.79</v>
+        <v>8.76</v>
       </c>
       <c r="R95" s="23" t="inlineStr">
         <is>
@@ -10247,10 +10149,10 @@
         </is>
       </c>
       <c r="O96" s="32" t="n">
-        <v>1.6</v>
+        <v>-4</v>
       </c>
       <c r="P96" s="32" t="n">
-        <v>9</v>
+        <v>14.1</v>
       </c>
       <c r="Q96" s="32" t="n"/>
       <c r="R96" s="23" t="inlineStr">
@@ -10365,13 +10267,13 @@
       </c>
       <c r="N97" s="2" t="n"/>
       <c r="O97" s="32" t="n">
-        <v>-1.3</v>
+        <v>-0.5</v>
       </c>
       <c r="P97" s="32" t="n">
         <v>12.4</v>
       </c>
       <c r="Q97" s="32" t="n">
-        <v>4.1</v>
+        <v>5.14</v>
       </c>
       <c r="R97" s="23" t="inlineStr">
         <is>
@@ -10485,10 +10387,10 @@
       </c>
       <c r="N98" s="2" t="n"/>
       <c r="O98" s="32" t="n">
-        <v>-15.5</v>
+        <v>-3.8</v>
       </c>
       <c r="P98" s="32" t="n">
-        <v>6.9</v>
+        <v>6.2</v>
       </c>
       <c r="Q98" s="32" t="n"/>
       <c r="R98" s="23" t="inlineStr">
@@ -10603,13 +10505,13 @@
       </c>
       <c r="N99" s="2" t="n"/>
       <c r="O99" s="32" t="n">
-        <v>-18.6</v>
+        <v>-6.9</v>
       </c>
       <c r="P99" s="32" t="n">
-        <v>4.8</v>
+        <v>6.8</v>
       </c>
       <c r="Q99" s="32" t="n">
-        <v>-7.04</v>
+        <v>-0.15</v>
       </c>
       <c r="R99" s="23" t="inlineStr">
         <is>
@@ -10935,13 +10837,13 @@
       </c>
       <c r="N102" s="2" t="n"/>
       <c r="O102" s="32" t="n">
-        <v>-17.9</v>
+        <v>-6.5</v>
       </c>
       <c r="P102" s="32" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="Q102" s="32" t="n">
-        <v>-4.9</v>
+        <v>0.1</v>
       </c>
       <c r="R102" s="23" t="inlineStr">
         <is>
@@ -11051,10 +10953,10 @@
       </c>
       <c r="N103" s="2" t="n"/>
       <c r="O103" s="32" t="n">
-        <v>-19.4</v>
+        <v>-8.6</v>
       </c>
       <c r="P103" s="32" t="n">
-        <v>6.1</v>
+        <v>7.1</v>
       </c>
       <c r="Q103" s="32" t="n"/>
       <c r="R103" s="23" t="inlineStr">
@@ -11161,10 +11063,10 @@
       </c>
       <c r="N104" s="2" t="n"/>
       <c r="O104" s="32" t="n">
-        <v>-20.5</v>
+        <v>-8.699999999999999</v>
       </c>
       <c r="P104" s="32" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="Q104" s="32" t="n"/>
       <c r="R104" s="23" t="inlineStr">
@@ -11287,13 +11189,13 @@
         </is>
       </c>
       <c r="O105" s="32" t="n">
-        <v>-24.4</v>
+        <v>-12.6</v>
       </c>
       <c r="P105" s="32" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="Q105" s="32" t="n">
-        <v>-9.300000000000001</v>
+        <v>-3.4</v>
       </c>
       <c r="R105" s="23" t="inlineStr">
         <is>
@@ -11403,10 +11305,10 @@
         </is>
       </c>
       <c r="O106" s="32" t="n">
-        <v>-20.1</v>
+        <v>-6.3</v>
       </c>
       <c r="P106" s="32" t="n">
-        <v>-0.1</v>
+        <v>3.5</v>
       </c>
       <c r="Q106" s="32" t="n"/>
       <c r="R106" s="23" t="inlineStr">
@@ -11623,13 +11525,13 @@
       </c>
       <c r="N108" s="2" t="n"/>
       <c r="O108" s="32" t="n">
-        <v>-17.8</v>
+        <v>-4.1</v>
       </c>
       <c r="P108" s="32" t="n">
-        <v>0.9</v>
+        <v>1.9</v>
       </c>
       <c r="Q108" s="32" t="n">
-        <v>-8.460000000000001</v>
+        <v>-1.51</v>
       </c>
       <c r="R108" s="23" t="inlineStr">
         <is>
@@ -11951,13 +11853,13 @@
       </c>
       <c r="N111" s="2" t="n"/>
       <c r="O111" s="32" t="n">
-        <v>-15.2</v>
+        <v>-4.7</v>
       </c>
       <c r="P111" s="32" t="n">
-        <v>1.4</v>
+        <v>3.5</v>
       </c>
       <c r="Q111" s="32" t="n">
-        <v>-6.72</v>
+        <v>-1.85</v>
       </c>
       <c r="R111" s="23" t="inlineStr">
         <is>
@@ -12063,10 +11965,10 @@
       </c>
       <c r="N112" s="2" t="n"/>
       <c r="O112" s="32" t="n">
-        <v>-5.7</v>
+        <v>-2.2</v>
       </c>
       <c r="P112" s="32" t="n">
-        <v>7.6</v>
+        <v>5.4</v>
       </c>
       <c r="Q112" s="32" t="n"/>
       <c r="R112" s="23" t="inlineStr">
@@ -12169,10 +12071,10 @@
       </c>
       <c r="N113" s="2" t="n"/>
       <c r="O113" s="32" t="n">
-        <v>-7.1</v>
+        <v>-12</v>
       </c>
       <c r="P113" s="32" t="n">
-        <v>3.3</v>
+        <v>6.7</v>
       </c>
       <c r="Q113" s="32" t="n"/>
       <c r="R113" s="23" t="inlineStr">
@@ -12283,10 +12185,10 @@
         </is>
       </c>
       <c r="O114" s="32" t="n">
-        <v>-7.8</v>
+        <v>-8.800000000000001</v>
       </c>
       <c r="P114" s="32" t="n">
-        <v>5.8</v>
+        <v>1.9</v>
       </c>
       <c r="Q114" s="32" t="n"/>
       <c r="R114" s="23" t="inlineStr">
@@ -12405,10 +12307,10 @@
         </is>
       </c>
       <c r="O115" s="32" t="n">
-        <v>-13</v>
+        <v>-15.3</v>
       </c>
       <c r="P115" s="32" t="n">
-        <v>2.3</v>
+        <v>3.6</v>
       </c>
       <c r="Q115" s="32" t="n"/>
       <c r="R115" s="23" t="inlineStr">
@@ -12523,13 +12425,13 @@
       </c>
       <c r="N116" s="2" t="n"/>
       <c r="O116" s="32" t="n">
-        <v>-4.6</v>
+        <v>-4.3</v>
       </c>
       <c r="P116" s="32" t="n">
-        <v>8.1</v>
+        <v>8.9</v>
       </c>
       <c r="Q116" s="32" t="n">
-        <v>1.46</v>
+        <v>2.71</v>
       </c>
       <c r="R116" s="23" t="inlineStr">
         <is>
@@ -12635,10 +12537,10 @@
       </c>
       <c r="N117" s="2" t="n"/>
       <c r="O117" s="32" t="n">
-        <v>-2.6</v>
+        <v>-4.3</v>
       </c>
       <c r="P117" s="32" t="n">
-        <v>9.699999999999999</v>
+        <v>8.5</v>
       </c>
       <c r="Q117" s="32" t="n"/>
       <c r="R117" s="23" t="inlineStr">
@@ -12749,10 +12651,10 @@
         </is>
       </c>
       <c r="O118" s="32" t="n">
-        <v>-11</v>
+        <v>-3</v>
       </c>
       <c r="P118" s="32" t="n">
-        <v>6.1</v>
+        <v>12.5</v>
       </c>
       <c r="Q118" s="32" t="n"/>
       <c r="R118" s="23" t="inlineStr">
@@ -12867,13 +12769,13 @@
       </c>
       <c r="N119" s="2" t="n"/>
       <c r="O119" s="32" t="n">
-        <v>-3.7</v>
+        <v>1.3</v>
       </c>
       <c r="P119" s="32" t="n">
-        <v>10.9</v>
+        <v>16.5</v>
       </c>
       <c r="Q119" s="32" t="n">
-        <v>3.25</v>
+        <v>10.38</v>
       </c>
       <c r="R119" s="23" t="inlineStr">
         <is>
@@ -13101,13 +13003,13 @@
       </c>
       <c r="N121" s="2" t="n"/>
       <c r="O121" s="32" t="n">
-        <v>0.7</v>
+        <v>3.6</v>
       </c>
       <c r="P121" s="32" t="n">
-        <v>10.3</v>
+        <v>13.9</v>
       </c>
       <c r="Q121" s="32" t="n">
-        <v>4.91</v>
+        <v>8.52</v>
       </c>
       <c r="R121" s="23" t="inlineStr">
         <is>
@@ -13225,10 +13127,10 @@
       </c>
       <c r="N122" s="2" t="n"/>
       <c r="O122" s="32" t="n">
-        <v>-9.800000000000001</v>
+        <v>-5</v>
       </c>
       <c r="P122" s="32" t="n">
-        <v>3.7</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="Q122" s="32" t="n"/>
       <c r="R122" s="23" t="inlineStr">
@@ -13449,13 +13351,13 @@
       </c>
       <c r="N124" s="2" t="n"/>
       <c r="O124" s="32" t="n">
-        <v>-0.2</v>
+        <v>-1</v>
       </c>
       <c r="P124" s="32" t="n">
-        <v>12.3</v>
+        <v>13.1</v>
       </c>
       <c r="Q124" s="32" t="n">
-        <v>6.53</v>
+        <v>6.16</v>
       </c>
       <c r="R124" s="23" t="inlineStr">
         <is>
@@ -13573,13 +13475,13 @@
       </c>
       <c r="N125" s="2" t="n"/>
       <c r="O125" s="32" t="n">
-        <v>5.6</v>
+        <v>11.1</v>
       </c>
       <c r="P125" s="32" t="n">
-        <v>22.6</v>
+        <v>23.5</v>
       </c>
       <c r="Q125" s="32" t="n">
-        <v>14.79</v>
+        <v>16.32</v>
       </c>
       <c r="R125" s="23" t="inlineStr">
         <is>
@@ -13677,10 +13579,10 @@
       </c>
       <c r="N126" s="2" t="n"/>
       <c r="O126" s="32" t="n">
-        <v>9.800000000000001</v>
+        <v>10.2</v>
       </c>
       <c r="P126" s="32" t="n">
-        <v>21.8</v>
+        <v>22.1</v>
       </c>
       <c r="Q126" s="32" t="n"/>
       <c r="R126" s="23" t="inlineStr">
@@ -13787,13 +13689,13 @@
       </c>
       <c r="N127" s="2" t="n"/>
       <c r="O127" s="32" t="n">
-        <v>-1.2</v>
+        <v>2.1</v>
       </c>
       <c r="P127" s="32" t="n">
-        <v>10.6</v>
+        <v>13.8</v>
       </c>
       <c r="Q127" s="32" t="n">
-        <v>5.11</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="R127" s="23" t="inlineStr">
         <is>
@@ -13907,10 +13809,10 @@
       </c>
       <c r="N128" s="2" t="n"/>
       <c r="O128" s="32" t="n">
-        <v>9.4</v>
+        <v>8.4</v>
       </c>
       <c r="P128" s="32" t="n">
-        <v>22.5</v>
+        <v>23.4</v>
       </c>
       <c r="Q128" s="32" t="n"/>
       <c r="R128" s="23" t="inlineStr">
@@ -14017,13 +13919,13 @@
       </c>
       <c r="N129" s="2" t="n"/>
       <c r="O129" s="32" t="n">
-        <v>1</v>
+        <v>1.9</v>
       </c>
       <c r="P129" s="32" t="n">
-        <v>15.9</v>
+        <v>20.6</v>
       </c>
       <c r="Q129" s="32" t="n">
-        <v>9.470000000000001</v>
+        <v>11.19</v>
       </c>
       <c r="R129" s="23" t="inlineStr">
         <is>
@@ -14137,13 +14039,13 @@
       </c>
       <c r="N130" s="2" t="n"/>
       <c r="O130" s="32" t="n">
-        <v>-0.6</v>
+        <v>0.5</v>
       </c>
       <c r="P130" s="32" t="n">
-        <v>6.2</v>
+        <v>9.6</v>
       </c>
       <c r="Q130" s="32" t="n">
-        <v>2.31</v>
+        <v>4.04</v>
       </c>
       <c r="R130" s="23" t="inlineStr">
         <is>
@@ -14257,13 +14159,13 @@
       </c>
       <c r="N131" s="2" t="n"/>
       <c r="O131" s="32" t="n">
-        <v>12.9</v>
+        <v>14.1</v>
       </c>
       <c r="P131" s="32" t="n">
-        <v>20.9</v>
+        <v>22.1</v>
       </c>
       <c r="Q131" s="32" t="n">
-        <v>15.62</v>
+        <v>18.01</v>
       </c>
       <c r="R131" s="23" t="inlineStr">
         <is>
@@ -14373,13 +14275,13 @@
       </c>
       <c r="N132" s="2" t="n"/>
       <c r="O132" s="32" t="n">
-        <v>8.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="P132" s="32" t="n">
-        <v>21.8</v>
+        <v>24.5</v>
       </c>
       <c r="Q132" s="32" t="n">
-        <v>16.48</v>
+        <v>17.99</v>
       </c>
       <c r="R132" s="23" t="inlineStr">
         <is>
@@ -14489,13 +14391,13 @@
       </c>
       <c r="N133" s="2" t="n"/>
       <c r="O133" s="32" t="n">
-        <v>8.1</v>
+        <v>10.3</v>
       </c>
       <c r="P133" s="32" t="n">
         <v>18.5</v>
       </c>
       <c r="Q133" s="32" t="n">
-        <v>13.69</v>
+        <v>14.78</v>
       </c>
       <c r="R133" s="23" t="inlineStr">
         <is>
@@ -14711,13 +14613,13 @@
       </c>
       <c r="N135" s="2" t="n"/>
       <c r="O135" s="32" t="n">
-        <v>12.3</v>
+        <v>13.1</v>
       </c>
       <c r="P135" s="32" t="n">
-        <v>14.4</v>
+        <v>16.8</v>
       </c>
       <c r="Q135" s="32" t="n">
-        <v>13.29</v>
+        <v>15.21</v>
       </c>
       <c r="R135" s="23" t="inlineStr">
         <is>
@@ -14827,13 +14729,13 @@
       </c>
       <c r="N136" s="2" t="n"/>
       <c r="O136" s="32" t="n">
-        <v>13.7</v>
+        <v>16</v>
       </c>
       <c r="P136" s="32" t="n">
-        <v>15.3</v>
+        <v>22.4</v>
       </c>
       <c r="Q136" s="32" t="n">
-        <v>14.38</v>
+        <v>18.91</v>
       </c>
       <c r="R136" s="23" t="inlineStr">
         <is>
@@ -14943,13 +14845,13 @@
       </c>
       <c r="N137" s="2" t="n"/>
       <c r="O137" s="32" t="n">
-        <v>13.7</v>
+        <v>11.3</v>
       </c>
       <c r="P137" s="32" t="n">
-        <v>20.5</v>
+        <v>22.6</v>
       </c>
       <c r="Q137" s="32" t="n">
-        <v>16.59</v>
+        <v>17.35</v>
       </c>
       <c r="R137" s="23" t="inlineStr">
         <is>
@@ -15059,10 +14961,10 @@
       </c>
       <c r="N138" s="2" t="n"/>
       <c r="O138" s="32" t="n">
-        <v>9.5</v>
+        <v>9.1</v>
       </c>
       <c r="P138" s="32" t="n">
-        <v>21.8</v>
+        <v>25.5</v>
       </c>
       <c r="Q138" s="32" t="n"/>
       <c r="R138" s="23" t="inlineStr">
@@ -15173,13 +15075,13 @@
       </c>
       <c r="N139" s="2" t="n"/>
       <c r="O139" s="32" t="n">
-        <v>9.800000000000001</v>
+        <v>12.2</v>
       </c>
       <c r="P139" s="32" t="n">
-        <v>22</v>
+        <v>25.7</v>
       </c>
       <c r="Q139" s="32" t="n">
-        <v>14.9</v>
+        <v>19.24</v>
       </c>
       <c r="R139" s="23" t="inlineStr">
         <is>
@@ -15289,13 +15191,13 @@
       </c>
       <c r="N140" s="2" t="n"/>
       <c r="O140" s="32" t="n">
-        <v>12.4</v>
+        <v>15.5</v>
       </c>
       <c r="P140" s="32" t="n">
-        <v>18.9</v>
+        <v>26</v>
       </c>
       <c r="Q140" s="32" t="n">
-        <v>14.94</v>
+        <v>19.46</v>
       </c>
       <c r="R140" s="23" t="inlineStr">
         <is>
@@ -15507,13 +15409,13 @@
       </c>
       <c r="N142" s="2" t="n"/>
       <c r="O142" s="32" t="n">
-        <v>13.9</v>
+        <v>15.6</v>
       </c>
       <c r="P142" s="32" t="n">
-        <v>26.5</v>
+        <v>27.1</v>
       </c>
       <c r="Q142" s="32" t="n">
-        <v>17.8</v>
+        <v>19.07</v>
       </c>
       <c r="R142" s="23" t="inlineStr">
         <is>
@@ -15626,10 +15528,10 @@
         <v>20</v>
       </c>
       <c r="P143" s="32" t="n">
-        <v>26.6</v>
+        <v>27.6</v>
       </c>
       <c r="Q143" s="32" t="n">
-        <v>22.56</v>
+        <v>23</v>
       </c>
       <c r="R143" s="23" t="inlineStr">
         <is>
@@ -15939,13 +15841,13 @@
       </c>
       <c r="N146" s="2" t="n"/>
       <c r="O146" s="32" t="n">
-        <v>22.7</v>
+        <v>23.5</v>
       </c>
       <c r="P146" s="32" t="n">
-        <v>28.6</v>
+        <v>30.9</v>
       </c>
       <c r="Q146" s="32" t="n">
-        <v>25.69</v>
+        <v>27.35</v>
       </c>
       <c r="R146" s="23" t="inlineStr">
         <is>
@@ -16047,13 +15949,13 @@
       </c>
       <c r="N147" s="2" t="n"/>
       <c r="O147" s="32" t="n">
-        <v>17.1</v>
+        <v>19.5</v>
       </c>
       <c r="P147" s="32" t="n">
-        <v>24</v>
+        <v>24.2</v>
       </c>
       <c r="Q147" s="32" t="n">
-        <v>20.05</v>
+        <v>21.16</v>
       </c>
       <c r="R147" s="23" t="inlineStr">
         <is>
@@ -16265,13 +16167,13 @@
       </c>
       <c r="N149" s="2" t="n"/>
       <c r="O149" s="32" t="n">
-        <v>11.5</v>
+        <v>10.7</v>
       </c>
       <c r="P149" s="32" t="n">
-        <v>19.7</v>
+        <v>21.2</v>
       </c>
       <c r="Q149" s="32" t="n">
-        <v>14.74</v>
+        <v>14.46</v>
       </c>
       <c r="R149" s="23" t="inlineStr">
         <is>
@@ -16381,13 +16283,13 @@
       </c>
       <c r="N150" s="2" t="n"/>
       <c r="O150" s="32" t="n">
-        <v>9.199999999999999</v>
+        <v>11.6</v>
       </c>
       <c r="P150" s="32" t="n">
-        <v>16.1</v>
+        <v>19.5</v>
       </c>
       <c r="Q150" s="32" t="n">
-        <v>12.09</v>
+        <v>14.81</v>
       </c>
       <c r="R150" s="23" t="inlineStr">
         <is>
@@ -16497,13 +16399,13 @@
       </c>
       <c r="N151" s="2" t="n"/>
       <c r="O151" s="32" t="n">
-        <v>15.6</v>
+        <v>15.3</v>
       </c>
       <c r="P151" s="32" t="n">
-        <v>21.7</v>
+        <v>19.8</v>
       </c>
       <c r="Q151" s="32" t="n">
-        <v>18.66</v>
+        <v>17.05</v>
       </c>
       <c r="R151" s="23" t="inlineStr">
         <is>
@@ -16703,13 +16605,13 @@
       </c>
       <c r="N153" s="2" t="n"/>
       <c r="O153" s="32" t="n">
-        <v>11.4</v>
+        <v>14.7</v>
       </c>
       <c r="P153" s="32" t="n">
-        <v>20.1</v>
+        <v>19.2</v>
       </c>
       <c r="Q153" s="32" t="n">
-        <v>15.17</v>
+        <v>16</v>
       </c>
       <c r="R153" s="23" t="inlineStr">
         <is>
@@ -16823,13 +16725,13 @@
       </c>
       <c r="N154" s="2" t="n"/>
       <c r="O154" s="32" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="P154" s="32" t="n">
-        <v>13.9</v>
+        <v>15.2</v>
       </c>
       <c r="Q154" s="32" t="n">
-        <v>8.33</v>
+        <v>6.85</v>
       </c>
       <c r="R154" s="23" t="inlineStr">
         <is>
@@ -17025,10 +16927,10 @@
       </c>
       <c r="N156" s="2" t="n"/>
       <c r="O156" s="32" t="n">
-        <v>-9.300000000000001</v>
+        <v>-4.5</v>
       </c>
       <c r="P156" s="32" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="Q156" s="32" t="n"/>
       <c r="R156" s="23" t="inlineStr">
@@ -17131,10 +17033,10 @@
       </c>
       <c r="N157" s="2" t="n"/>
       <c r="O157" s="32" t="n">
-        <v>9.9</v>
+        <v>14.7</v>
       </c>
       <c r="P157" s="32" t="n">
-        <v>20</v>
+        <v>22.1</v>
       </c>
       <c r="Q157" s="32" t="n"/>
       <c r="R157" s="23" t="inlineStr">
@@ -17519,10 +17421,10 @@
       </c>
       <c r="N161" s="2" t="n"/>
       <c r="O161" s="32" t="n">
-        <v>7.1</v>
+        <v>3.2</v>
       </c>
       <c r="P161" s="32" t="n">
-        <v>13.6</v>
+        <v>12.5</v>
       </c>
       <c r="Q161" s="32" t="n"/>
       <c r="R161" s="23" t="inlineStr">
@@ -17739,10 +17641,10 @@
       </c>
       <c r="N163" s="2" t="n"/>
       <c r="O163" s="32" t="n">
-        <v>-20.9</v>
+        <v>-11.2</v>
       </c>
       <c r="P163" s="32" t="n">
-        <v>4.5</v>
+        <v>6</v>
       </c>
       <c r="Q163" s="32" t="n"/>
       <c r="R163" s="23" t="inlineStr">
@@ -17959,10 +17861,10 @@
         </is>
       </c>
       <c r="O165" s="32" t="n">
-        <v>-27.6</v>
+        <v>-8.1</v>
       </c>
       <c r="P165" s="32" t="n">
-        <v>-3.7</v>
+        <v>1.9</v>
       </c>
       <c r="Q165" s="32" t="n"/>
       <c r="R165" s="23" t="inlineStr">
@@ -18285,10 +18187,10 @@
         </is>
       </c>
       <c r="O168" s="32" t="n">
-        <v>-15</v>
+        <v>-10</v>
       </c>
       <c r="P168" s="32" t="n">
-        <v>10.5</v>
+        <v>12.2</v>
       </c>
       <c r="Q168" s="32" t="n"/>
       <c r="R168" s="23" t="inlineStr">
@@ -18399,10 +18301,10 @@
         </is>
       </c>
       <c r="O169" s="32" t="n">
-        <v>-18</v>
+        <v>-8.4</v>
       </c>
       <c r="P169" s="32" t="n">
-        <v>4.6</v>
+        <v>6.7</v>
       </c>
       <c r="Q169" s="32" t="n"/>
       <c r="R169" s="23" t="inlineStr">
@@ -18512,8 +18414,12 @@
           <t>⚡</t>
         </is>
       </c>
-      <c r="O170" s="32" t="n"/>
-      <c r="P170" s="32" t="n"/>
+      <c r="O170" s="32" t="n">
+        <v>-26.9</v>
+      </c>
+      <c r="P170" s="32" t="n">
+        <v>0.1</v>
+      </c>
       <c r="Q170" s="32" t="n"/>
       <c r="R170" s="23" t="inlineStr">
         <is>
@@ -18618,8 +18524,12 @@
         </is>
       </c>
       <c r="N171" s="2" t="n"/>
-      <c r="O171" s="32" t="n"/>
-      <c r="P171" s="32" t="n"/>
+      <c r="O171" s="32" t="n">
+        <v>-9.1</v>
+      </c>
+      <c r="P171" s="32" t="n">
+        <v>-5.3</v>
+      </c>
       <c r="Q171" s="32" t="n"/>
       <c r="R171" s="23" t="inlineStr">
         <is>
@@ -18724,12 +18634,8 @@
         </is>
       </c>
       <c r="N172" s="3" t="n"/>
-      <c r="O172" s="32" t="n">
-        <v>-11.5</v>
-      </c>
-      <c r="P172" s="32" t="n">
-        <v>4.8</v>
-      </c>
+      <c r="O172" s="32" t="n"/>
+      <c r="P172" s="32" t="n"/>
       <c r="Q172" s="32" t="n"/>
       <c r="R172" s="23" t="inlineStr">
         <is>
@@ -18835,10 +18741,10 @@
       </c>
       <c r="N173" s="2" t="n"/>
       <c r="O173" s="32" t="n">
-        <v>-7.8</v>
+        <v>-2.9</v>
       </c>
       <c r="P173" s="32" t="n">
-        <v>6.6</v>
+        <v>8.5</v>
       </c>
       <c r="Q173" s="32" t="n"/>
       <c r="R173" s="23" t="inlineStr">
@@ -19157,10 +19063,10 @@
       </c>
       <c r="N176" s="2" t="n"/>
       <c r="O176" s="32" t="n">
-        <v>4.2</v>
+        <v>5.7</v>
       </c>
       <c r="P176" s="32" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="Q176" s="32" t="n"/>
       <c r="R176" s="23" t="inlineStr">
@@ -19259,10 +19165,10 @@
       </c>
       <c r="N177" s="2" t="n"/>
       <c r="O177" s="32" t="n">
-        <v>-12.1</v>
+        <v>-7.4</v>
       </c>
       <c r="P177" s="32" t="n">
-        <v>-7.6</v>
+        <v>-3.5</v>
       </c>
       <c r="Q177" s="32" t="n"/>
       <c r="R177" s="23" t="inlineStr">
@@ -20046,18 +19952,10 @@
         </is>
       </c>
       <c r="N185" s="2" t="n"/>
-      <c r="O185" s="32" t="n">
-        <v>-12.3</v>
-      </c>
-      <c r="P185" s="32" t="n">
-        <v>-3</v>
-      </c>
+      <c r="O185" s="32" t="n"/>
+      <c r="P185" s="32" t="n"/>
       <c r="Q185" s="32" t="n"/>
-      <c r="R185" s="23" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="R185" s="23" t="n"/>
       <c r="S185" s="37" t="n"/>
       <c r="T185" s="41" t="inlineStr">
         <is>
@@ -20153,20 +20051,10 @@
         </is>
       </c>
       <c r="N186" s="2" t="n"/>
-      <c r="O186" s="32" t="n">
-        <v>-5.4</v>
-      </c>
-      <c r="P186" s="32" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="Q186" s="32" t="n">
-        <v>-3.2</v>
-      </c>
-      <c r="R186" s="23" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="O186" s="32" t="n"/>
+      <c r="P186" s="32" t="n"/>
+      <c r="Q186" s="32" t="n"/>
+      <c r="R186" s="23" t="n"/>
       <c r="S186" s="37" t="n"/>
       <c r="T186" s="41" t="inlineStr">
         <is>
@@ -20262,20 +20150,10 @@
         </is>
       </c>
       <c r="N187" s="2" t="n"/>
-      <c r="O187" s="32" t="n">
-        <v>-6.3</v>
-      </c>
-      <c r="P187" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q187" s="32" t="n">
-        <v>-3.49</v>
-      </c>
-      <c r="R187" s="23" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="O187" s="32" t="n"/>
+      <c r="P187" s="32" t="n"/>
+      <c r="Q187" s="32" t="n"/>
+      <c r="R187" s="23" t="n"/>
       <c r="S187" s="37" t="n"/>
       <c r="T187" s="41" t="inlineStr">
         <is>
@@ -20366,20 +20244,10 @@
         </is>
       </c>
       <c r="N188" s="2" t="n"/>
-      <c r="O188" s="32" t="n">
-        <v>-9.4</v>
-      </c>
-      <c r="P188" s="32" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Q188" s="32" t="n">
-        <v>-5.44</v>
-      </c>
-      <c r="R188" s="23" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="O188" s="32" t="n"/>
+      <c r="P188" s="32" t="n"/>
+      <c r="Q188" s="32" t="n"/>
+      <c r="R188" s="23" t="n"/>
       <c r="S188" s="37" t="n"/>
       <c r="T188" s="41" t="inlineStr">
         <is>
@@ -20470,20 +20338,10 @@
         </is>
       </c>
       <c r="N189" s="2" t="n"/>
-      <c r="O189" s="32" t="n">
-        <v>-8.5</v>
-      </c>
-      <c r="P189" s="32" t="n">
-        <v>-1</v>
-      </c>
-      <c r="Q189" s="32" t="n">
-        <v>-4.49</v>
-      </c>
-      <c r="R189" s="23" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="O189" s="32" t="n"/>
+      <c r="P189" s="32" t="n"/>
+      <c r="Q189" s="32" t="n"/>
+      <c r="R189" s="23" t="n"/>
       <c r="S189" s="37" t="n"/>
       <c r="T189" s="41" t="inlineStr">
         <is>
@@ -20574,20 +20432,10 @@
         </is>
       </c>
       <c r="N190" s="2" t="n"/>
-      <c r="O190" s="32" t="n">
-        <v>-15.1</v>
-      </c>
-      <c r="P190" s="32" t="n">
-        <v>-4</v>
-      </c>
-      <c r="Q190" s="32" t="n">
-        <v>-9.34</v>
-      </c>
-      <c r="R190" s="23" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="O190" s="32" t="n"/>
+      <c r="P190" s="32" t="n"/>
+      <c r="Q190" s="32" t="n"/>
+      <c r="R190" s="23" t="n"/>
       <c r="S190" s="37" t="n"/>
       <c r="T190" s="41" t="inlineStr">
         <is>
@@ -20678,20 +20526,10 @@
         </is>
       </c>
       <c r="N191" s="2" t="n"/>
-      <c r="O191" s="32" t="n">
-        <v>-9.6</v>
-      </c>
-      <c r="P191" s="32" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="Q191" s="32" t="n">
-        <v>-5.05</v>
-      </c>
-      <c r="R191" s="23" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="O191" s="32" t="n"/>
+      <c r="P191" s="32" t="n"/>
+      <c r="Q191" s="32" t="n"/>
+      <c r="R191" s="23" t="n"/>
       <c r="S191" s="37" t="n"/>
       <c r="T191" s="41" t="inlineStr">
         <is>
@@ -20778,20 +20616,10 @@
         </is>
       </c>
       <c r="N192" s="2" t="n"/>
-      <c r="O192" s="32" t="n">
-        <v>-14.3</v>
-      </c>
-      <c r="P192" s="32" t="n">
-        <v>-3</v>
-      </c>
-      <c r="Q192" s="32" t="n">
-        <v>-8.93</v>
-      </c>
-      <c r="R192" s="23" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="O192" s="32" t="n"/>
+      <c r="P192" s="32" t="n"/>
+      <c r="Q192" s="32" t="n"/>
+      <c r="R192" s="23" t="n"/>
       <c r="S192" s="37" t="n"/>
       <c r="T192" s="41" t="inlineStr">
         <is>
@@ -20883,20 +20711,10 @@
         </is>
       </c>
       <c r="N193" s="2" t="n"/>
-      <c r="O193" s="32" t="n">
-        <v>-21.6</v>
-      </c>
-      <c r="P193" s="32" t="n">
-        <v>-2.2</v>
-      </c>
-      <c r="Q193" s="32" t="n">
-        <v>-11.65</v>
-      </c>
-      <c r="R193" s="23" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="O193" s="32" t="n"/>
+      <c r="P193" s="32" t="n"/>
+      <c r="Q193" s="32" t="n"/>
+      <c r="R193" s="23" t="n"/>
       <c r="S193" s="37" t="n"/>
       <c r="T193" s="41" t="inlineStr">
         <is>
@@ -20991,18 +20809,10 @@
         </is>
       </c>
       <c r="N194" s="2" t="n"/>
-      <c r="O194" s="32" t="n">
-        <v>-15</v>
-      </c>
-      <c r="P194" s="32" t="n">
-        <v>-4.6</v>
-      </c>
+      <c r="O194" s="32" t="n"/>
+      <c r="P194" s="32" t="n"/>
       <c r="Q194" s="32" t="n"/>
-      <c r="R194" s="23" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="R194" s="23" t="n"/>
       <c r="S194" s="37" t="n"/>
       <c r="T194" s="41" t="inlineStr">
         <is>
@@ -21089,20 +20899,10 @@
         </is>
       </c>
       <c r="N195" s="2" t="n"/>
-      <c r="O195" s="32" t="n">
-        <v>-4.9</v>
-      </c>
-      <c r="P195" s="32" t="n">
-        <v>-0.3</v>
-      </c>
-      <c r="Q195" s="32" t="n">
-        <v>-1.99</v>
-      </c>
-      <c r="R195" s="23" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="O195" s="32" t="n"/>
+      <c r="P195" s="32" t="n"/>
+      <c r="Q195" s="32" t="n"/>
+      <c r="R195" s="23" t="n"/>
       <c r="S195" s="37" t="n"/>
       <c r="T195" s="41" t="inlineStr">
         <is>
@@ -21193,20 +20993,10 @@
         </is>
       </c>
       <c r="N196" s="2" t="n"/>
-      <c r="O196" s="32" t="n">
-        <v>-13.2</v>
-      </c>
-      <c r="P196" s="32" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="Q196" s="32" t="n">
-        <v>-5.36</v>
-      </c>
-      <c r="R196" s="23" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="O196" s="32" t="n"/>
+      <c r="P196" s="32" t="n"/>
+      <c r="Q196" s="32" t="n"/>
+      <c r="R196" s="23" t="n"/>
       <c r="S196" s="37" t="n"/>
       <c r="T196" s="41" t="inlineStr">
         <is>
@@ -21297,20 +21087,10 @@
         </is>
       </c>
       <c r="N197" s="24" t="n"/>
-      <c r="O197" s="32" t="n">
-        <v>-37.5</v>
-      </c>
-      <c r="P197" s="32" t="n">
-        <v>-13.4</v>
-      </c>
-      <c r="Q197" s="32" t="n">
-        <v>-25.62</v>
-      </c>
-      <c r="R197" s="23" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="O197" s="32" t="n"/>
+      <c r="P197" s="32" t="n"/>
+      <c r="Q197" s="32" t="n"/>
+      <c r="R197" s="23" t="n"/>
       <c r="S197" s="37" t="n"/>
       <c r="T197" s="41" t="inlineStr">
         <is>
@@ -21695,12 +21475,8 @@
         </is>
       </c>
       <c r="N201" s="2" t="n"/>
-      <c r="O201" s="32" t="n">
-        <v>-22.7</v>
-      </c>
-      <c r="P201" s="32" t="n">
-        <v>5.8</v>
-      </c>
+      <c r="O201" s="32" t="n"/>
+      <c r="P201" s="32" t="n"/>
       <c r="Q201" s="32" t="n"/>
       <c r="R201" s="23" t="inlineStr">
         <is>
@@ -22906,10 +22682,10 @@
       </c>
       <c r="N213" s="2" t="n"/>
       <c r="O213" s="32" t="n">
-        <v>-28.3</v>
+        <v>-15.9</v>
       </c>
       <c r="P213" s="32" t="n">
-        <v>4.1</v>
+        <v>1.3</v>
       </c>
       <c r="Q213" s="32" t="n"/>
       <c r="R213" s="23" t="inlineStr">
@@ -25666,10 +25442,10 @@
       </c>
       <c r="N241" s="2" t="n"/>
       <c r="O241" s="32" t="n">
-        <v>-24.9</v>
+        <v>-21.5</v>
       </c>
       <c r="P241" s="32" t="n">
-        <v>3.1</v>
+        <v>5</v>
       </c>
       <c r="Q241" s="32" t="n"/>
       <c r="R241" s="23" t="inlineStr">
@@ -26243,20 +26019,10 @@
         </is>
       </c>
       <c r="N247" s="2" t="n"/>
-      <c r="O247" s="32" t="n">
-        <v>-5.2</v>
-      </c>
-      <c r="P247" s="32" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="Q247" s="32" t="n">
-        <v>-0.8100000000000001</v>
-      </c>
-      <c r="R247" s="23" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="O247" s="32" t="n"/>
+      <c r="P247" s="32" t="n"/>
+      <c r="Q247" s="32" t="n"/>
+      <c r="R247" s="23" t="n"/>
       <c r="S247" s="37" t="n"/>
       <c r="T247" s="41" t="inlineStr">
         <is>
@@ -26360,13 +26126,13 @@
         </is>
       </c>
       <c r="O248" s="32" t="n">
-        <v>-17.4</v>
+        <v>-8.800000000000001</v>
       </c>
       <c r="P248" s="32" t="n">
-        <v>-0.1</v>
+        <v>5.1</v>
       </c>
       <c r="Q248" s="32" t="n">
-        <v>-8.74</v>
+        <v>-1.58</v>
       </c>
       <c r="R248" s="23" t="inlineStr">
         <is>
@@ -26467,20 +26233,10 @@
         </is>
       </c>
       <c r="N249" s="2" t="n"/>
-      <c r="O249" s="32" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="P249" s="32" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="Q249" s="32" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="R249" s="23" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="O249" s="32" t="n"/>
+      <c r="P249" s="32" t="n"/>
+      <c r="Q249" s="32" t="n"/>
+      <c r="R249" s="23" t="n"/>
       <c r="S249" s="37" t="n"/>
       <c r="T249" s="41" t="inlineStr">
         <is>
@@ -26579,20 +26335,10 @@
         </is>
       </c>
       <c r="N250" s="2" t="n"/>
-      <c r="O250" s="32" t="n">
-        <v>-6.9</v>
-      </c>
-      <c r="P250" s="32" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="Q250" s="32" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="R250" s="23" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="O250" s="32" t="n"/>
+      <c r="P250" s="32" t="n"/>
+      <c r="Q250" s="32" t="n"/>
+      <c r="R250" s="23" t="n"/>
       <c r="S250" s="37" t="n"/>
       <c r="T250" s="41" t="inlineStr">
         <is>
@@ -26699,20 +26445,10 @@
           <t>♦️</t>
         </is>
       </c>
-      <c r="O251" s="32" t="n">
-        <v>-37.9</v>
-      </c>
-      <c r="P251" s="32" t="n">
-        <v>-6.2</v>
-      </c>
-      <c r="Q251" s="32" t="n">
-        <v>-23.82</v>
-      </c>
-      <c r="R251" s="23" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="O251" s="32" t="n"/>
+      <c r="P251" s="32" t="n"/>
+      <c r="Q251" s="32" t="n"/>
+      <c r="R251" s="23" t="n"/>
       <c r="S251" s="37" t="n"/>
       <c r="T251" s="41" t="inlineStr">
         <is>
@@ -26799,18 +26535,10 @@
         </is>
       </c>
       <c r="N252" s="2" t="n"/>
-      <c r="O252" s="32" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="P252" s="32" t="n">
-        <v>6.8</v>
-      </c>
+      <c r="O252" s="32" t="n"/>
+      <c r="P252" s="32" t="n"/>
       <c r="Q252" s="32" t="n"/>
-      <c r="R252" s="23" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="R252" s="23" t="n"/>
       <c r="S252" s="37" t="n"/>
       <c r="T252" s="41" t="inlineStr">
         <is>
@@ -26995,20 +26723,10 @@
         </is>
       </c>
       <c r="N254" s="2" t="n"/>
-      <c r="O254" s="32" t="n">
-        <v>-37.4</v>
-      </c>
-      <c r="P254" s="32" t="n">
-        <v>-8.5</v>
-      </c>
-      <c r="Q254" s="32" t="n">
-        <v>-22.81</v>
-      </c>
-      <c r="R254" s="23" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="O254" s="32" t="n"/>
+      <c r="P254" s="32" t="n"/>
+      <c r="Q254" s="32" t="n"/>
+      <c r="R254" s="23" t="n"/>
       <c r="S254" s="37" t="n"/>
       <c r="T254" s="41" t="inlineStr">
         <is>
@@ -27569,20 +27287,10 @@
         </is>
       </c>
       <c r="N260" s="2" t="n"/>
-      <c r="O260" s="32" t="n">
-        <v>-15.5</v>
-      </c>
-      <c r="P260" s="32" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="Q260" s="32" t="n">
-        <v>-2.49</v>
-      </c>
-      <c r="R260" s="23" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="O260" s="32" t="n"/>
+      <c r="P260" s="32" t="n"/>
+      <c r="Q260" s="32" t="n"/>
+      <c r="R260" s="23" t="n"/>
       <c r="S260" s="37" t="n"/>
       <c r="T260" s="41" t="inlineStr">
         <is>
@@ -27677,20 +27385,10 @@
         </is>
       </c>
       <c r="N261" s="2" t="n"/>
-      <c r="O261" s="32" t="n">
-        <v>-7.4</v>
-      </c>
-      <c r="P261" s="32" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="Q261" s="32" t="n">
-        <v>-0.25</v>
-      </c>
-      <c r="R261" s="23" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="O261" s="32" t="n"/>
+      <c r="P261" s="32" t="n"/>
+      <c r="Q261" s="32" t="n"/>
+      <c r="R261" s="23" t="n"/>
       <c r="S261" s="37" t="n"/>
       <c r="T261" s="41" t="inlineStr">
         <is>
@@ -27789,20 +27487,10 @@
         </is>
       </c>
       <c r="N262" s="2" t="n"/>
-      <c r="O262" s="32" t="n">
-        <v>-2.9</v>
-      </c>
-      <c r="P262" s="32" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="Q262" s="32" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="R262" s="23" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="O262" s="32" t="n"/>
+      <c r="P262" s="32" t="n"/>
+      <c r="Q262" s="32" t="n"/>
+      <c r="R262" s="23" t="n"/>
       <c r="S262" s="37" t="n"/>
       <c r="T262" s="41" t="inlineStr">
         <is>
@@ -27995,20 +27683,10 @@
         </is>
       </c>
       <c r="N264" s="2" t="n"/>
-      <c r="O264" s="32" t="n">
-        <v>-5.3</v>
-      </c>
-      <c r="P264" s="32" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="Q264" s="32" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="R264" s="23" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="O264" s="32" t="n"/>
+      <c r="P264" s="32" t="n"/>
+      <c r="Q264" s="32" t="n"/>
+      <c r="R264" s="23" t="n"/>
       <c r="S264" s="37" t="n"/>
       <c r="T264" s="41" t="inlineStr">
         <is>
@@ -28116,10 +27794,10 @@
       </c>
       <c r="N265" s="2" t="n"/>
       <c r="O265" s="32" t="n">
-        <v>-71.5</v>
+        <v>-59.3</v>
       </c>
       <c r="P265" s="32" t="n">
-        <v>-64.40000000000001</v>
+        <v>-56.3</v>
       </c>
       <c r="Q265" s="32" t="n"/>
       <c r="R265" s="23" t="inlineStr">
@@ -29159,20 +28837,10 @@
         </is>
       </c>
       <c r="N276" s="2" t="n"/>
-      <c r="O276" s="32" t="n">
-        <v>-31</v>
-      </c>
-      <c r="P276" s="32" t="n">
-        <v>-9.800000000000001</v>
-      </c>
-      <c r="Q276" s="32" t="n">
-        <v>-21.3</v>
-      </c>
-      <c r="R276" s="23" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="O276" s="32" t="n"/>
+      <c r="P276" s="32" t="n"/>
+      <c r="Q276" s="32" t="n"/>
+      <c r="R276" s="23" t="n"/>
       <c r="S276" s="37" t="n"/>
       <c r="T276" s="41" t="inlineStr">
         <is>
@@ -30966,10 +30634,10 @@
       </c>
       <c r="N295" s="2" t="n"/>
       <c r="O295" s="32" t="n">
-        <v>-15.7</v>
+        <v>-15.2</v>
       </c>
       <c r="P295" s="32" t="n">
-        <v>-7</v>
+        <v>0</v>
       </c>
       <c r="Q295" s="32" t="n"/>
       <c r="R295" s="23" t="inlineStr">
@@ -31035,111 +30703,303 @@
       <c r="AH295" s="2" t="n"/>
     </row>
     <row r="296" ht="24" customHeight="1" s="48">
-      <c r="A296" s="2" t="n"/>
+      <c r="A296" s="2" t="n">
+        <v>295</v>
+      </c>
       <c r="B296" s="2" t="n"/>
       <c r="C296" s="46" t="n"/>
       <c r="D296" s="2" t="n"/>
       <c r="E296" s="4" t="n"/>
-      <c r="F296" s="39" t="n"/>
-      <c r="G296" s="29" t="n"/>
-      <c r="H296" s="29" t="n"/>
-      <c r="I296" s="2" t="n"/>
-      <c r="J296" s="27" t="n"/>
-      <c r="K296" s="4" t="n"/>
+      <c r="F296" s="39" t="inlineStr">
+        <is>
+          <t>Y5316</t>
+        </is>
+      </c>
+      <c r="G296" s="29" t="n">
+        <v>47.1381</v>
+      </c>
+      <c r="H296" s="29" t="n">
+        <v>85.5975</v>
+      </c>
+      <c r="I296" s="2" t="n">
+        <v>2914</v>
+      </c>
+      <c r="J296" s="27" t="n">
+        <v>12</v>
+      </c>
+      <c r="K296" s="31" t="inlineStr">
+        <is>
+          <t>🇨🇳</t>
+        </is>
+      </c>
       <c r="L296" s="2" t="n"/>
-      <c r="M296" s="14" t="n"/>
+      <c r="M296" s="14" t="inlineStr">
+        <is>
+          <t>吉木乃冰川站</t>
+        </is>
+      </c>
       <c r="N296" s="2" t="n"/>
       <c r="O296" s="32" t="n"/>
       <c r="P296" s="32" t="n"/>
       <c r="Q296" s="32" t="n"/>
-      <c r="R296" s="23" t="n"/>
+      <c r="R296" s="23" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="S296" s="37" t="n"/>
-      <c r="T296" s="41" t="n"/>
-      <c r="U296" s="2" t="n"/>
-      <c r="V296" s="4" t="n"/>
-      <c r="W296" s="4" t="n"/>
-      <c r="X296" s="4" t="n"/>
+      <c r="T296" s="41" t="inlineStr">
+        <is>
+          <t>阿勒泰</t>
+        </is>
+      </c>
+      <c r="U296" s="2" t="inlineStr">
+        <is>
+          <t>新疆</t>
+        </is>
+      </c>
+      <c r="V296" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="W296" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="X296" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="Y296" s="4" t="n"/>
-      <c r="Z296" s="2" t="n"/>
-      <c r="AA296" s="2" t="n"/>
+      <c r="Z296" s="2" t="inlineStr">
+        <is>
+          <t>阿勒泰地区</t>
+        </is>
+      </c>
+      <c r="AA296" s="2" t="inlineStr">
+        <is>
+          <t>吉木乃县</t>
+        </is>
+      </c>
       <c r="AB296" s="2" t="n"/>
       <c r="AC296" s="2" t="n"/>
-      <c r="AD296" s="2" t="n"/>
-      <c r="AE296" s="4" t="n"/>
+      <c r="AD296" s="2" t="inlineStr">
+        <is>
+          <t>中国</t>
+        </is>
+      </c>
+      <c r="AE296" s="4" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
       <c r="AF296" s="4" t="n"/>
       <c r="AG296" s="2" t="n"/>
       <c r="AH296" s="2" t="n"/>
     </row>
     <row r="297" ht="24" customHeight="1" s="48">
-      <c r="A297" s="2" t="n"/>
+      <c r="A297" s="2" t="n">
+        <v>296</v>
+      </c>
       <c r="B297" s="2" t="n"/>
       <c r="C297" s="46" t="n"/>
       <c r="D297" s="2" t="n"/>
       <c r="E297" s="4" t="n"/>
-      <c r="F297" s="39" t="n"/>
+      <c r="F297" s="39" t="inlineStr">
+        <is>
+          <t>X7049</t>
+        </is>
+      </c>
       <c r="G297" s="29" t="n"/>
       <c r="H297" s="29" t="n"/>
       <c r="I297" s="2" t="n"/>
-      <c r="J297" s="27" t="n"/>
-      <c r="K297" s="4" t="n"/>
+      <c r="J297" s="27" t="n">
+        <v>12</v>
+      </c>
+      <c r="K297" s="31" t="inlineStr">
+        <is>
+          <t>🇨🇳</t>
+        </is>
+      </c>
       <c r="L297" s="2" t="n"/>
-      <c r="M297" s="14" t="n"/>
+      <c r="M297" s="14" t="inlineStr">
+        <is>
+          <t>珍秦永郎达</t>
+        </is>
+      </c>
       <c r="N297" s="2" t="n"/>
       <c r="O297" s="32" t="n"/>
       <c r="P297" s="32" t="n"/>
       <c r="Q297" s="32" t="n"/>
-      <c r="R297" s="23" t="n"/>
+      <c r="R297" s="23" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="S297" s="37" t="n"/>
-      <c r="T297" s="41" t="n"/>
-      <c r="U297" s="2" t="n"/>
-      <c r="V297" s="4" t="n"/>
-      <c r="W297" s="4" t="n"/>
-      <c r="X297" s="4" t="n"/>
+      <c r="T297" s="41" t="inlineStr">
+        <is>
+          <t>青藏高原&lt;br&gt;青海玉树称多县</t>
+        </is>
+      </c>
+      <c r="U297" s="2" t="inlineStr">
+        <is>
+          <t>青海</t>
+        </is>
+      </c>
+      <c r="V297" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="W297" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="X297" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="Y297" s="4" t="n"/>
-      <c r="Z297" s="2" t="n"/>
-      <c r="AA297" s="2" t="n"/>
+      <c r="Z297" s="2" t="inlineStr">
+        <is>
+          <t>玉树藏族自治州</t>
+        </is>
+      </c>
+      <c r="AA297" s="2" t="inlineStr">
+        <is>
+          <t>称多县</t>
+        </is>
+      </c>
       <c r="AB297" s="2" t="n"/>
       <c r="AC297" s="2" t="n"/>
-      <c r="AD297" s="2" t="n"/>
-      <c r="AE297" s="4" t="n"/>
+      <c r="AD297" s="2" t="inlineStr">
+        <is>
+          <t>中国</t>
+        </is>
+      </c>
+      <c r="AE297" s="4" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
       <c r="AF297" s="4" t="n"/>
-      <c r="AG297" s="2" t="n"/>
+      <c r="AG297" s="2" t="inlineStr">
+        <is>
+          <t>青藏高原</t>
+        </is>
+      </c>
       <c r="AH297" s="2" t="n"/>
     </row>
     <row r="298" ht="24" customHeight="1" s="48">
-      <c r="A298" s="2" t="n"/>
+      <c r="A298" s="2" t="n">
+        <v>297</v>
+      </c>
       <c r="B298" s="2" t="n"/>
-      <c r="C298" s="46" t="n"/>
+      <c r="C298" s="46" t="inlineStr">
+        <is>
+          <t>52633</t>
+        </is>
+      </c>
       <c r="D298" s="2" t="n"/>
       <c r="E298" s="4" t="n"/>
       <c r="F298" s="39" t="n"/>
-      <c r="G298" s="29" t="n"/>
-      <c r="H298" s="29" t="n"/>
-      <c r="I298" s="2" t="n"/>
-      <c r="J298" s="27" t="n"/>
-      <c r="K298" s="4" t="n"/>
+      <c r="G298" s="29" t="n">
+        <v>38.8086</v>
+      </c>
+      <c r="H298" s="29" t="n">
+        <v>98.4181</v>
+      </c>
+      <c r="I298" s="2" t="n">
+        <v>3364.3</v>
+      </c>
+      <c r="J298" s="27" t="n">
+        <v>12</v>
+      </c>
+      <c r="K298" s="31" t="inlineStr">
+        <is>
+          <t>🇨🇳</t>
+        </is>
+      </c>
       <c r="L298" s="2" t="n"/>
-      <c r="M298" s="14" t="n"/>
+      <c r="M298" s="14" t="inlineStr">
+        <is>
+          <t>托勒</t>
+        </is>
+      </c>
       <c r="N298" s="2" t="n"/>
-      <c r="O298" s="32" t="n"/>
-      <c r="P298" s="32" t="n"/>
+      <c r="O298" s="32" t="n">
+        <v>-19.2</v>
+      </c>
+      <c r="P298" s="32" t="n">
+        <v>1.9</v>
+      </c>
       <c r="Q298" s="32" t="n"/>
-      <c r="R298" s="23" t="n"/>
+      <c r="R298" s="23" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="S298" s="37" t="n"/>
-      <c r="T298" s="41" t="n"/>
-      <c r="U298" s="2" t="n"/>
-      <c r="V298" s="4" t="n"/>
-      <c r="W298" s="4" t="n"/>
-      <c r="X298" s="4" t="n"/>
+      <c r="T298" s="41" t="inlineStr">
+        <is>
+          <t>青藏高原 青海</t>
+        </is>
+      </c>
+      <c r="U298" s="2" t="inlineStr">
+        <is>
+          <t>青海</t>
+        </is>
+      </c>
+      <c r="V298" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="W298" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="X298" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="Y298" s="4" t="n"/>
-      <c r="Z298" s="2" t="n"/>
-      <c r="AA298" s="2" t="n"/>
+      <c r="Z298" s="2" t="inlineStr">
+        <is>
+          <t>海北藏族自治州</t>
+        </is>
+      </c>
+      <c r="AA298" s="2" t="inlineStr">
+        <is>
+          <t>祁连县</t>
+        </is>
+      </c>
       <c r="AB298" s="2" t="n"/>
       <c r="AC298" s="2" t="n"/>
-      <c r="AD298" s="2" t="n"/>
-      <c r="AE298" s="4" t="n"/>
+      <c r="AD298" s="2" t="inlineStr">
+        <is>
+          <t>中国</t>
+        </is>
+      </c>
+      <c r="AE298" s="4" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
       <c r="AF298" s="4" t="n"/>
-      <c r="AG298" s="2" t="n"/>
+      <c r="AG298" s="2" t="inlineStr">
+        <is>
+          <t>青藏高原</t>
+        </is>
+      </c>
       <c r="AH298" s="2" t="n"/>
     </row>
     <row r="299" ht="24" customHeight="1" s="48">

--- a/气象/For_Python_站点信息和记录.xlsx
+++ b/气象/For_Python_站点信息和记录.xlsx
@@ -796,8 +796,8 @@
     <col width="18.59765625" customWidth="1" style="8" min="25" max="25"/>
     <col width="12.59765625" customWidth="1" style="5" min="26" max="30"/>
     <col width="12.59765625" customWidth="1" style="8" min="31" max="32"/>
-    <col width="12.59765625" customWidth="1" style="5" min="33" max="349"/>
-    <col width="12.59765625" customWidth="1" style="5" min="350" max="16384"/>
+    <col width="12.59765625" customWidth="1" style="5" min="33" max="350"/>
+    <col width="12.59765625" customWidth="1" style="5" min="351" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="27.75" customFormat="1" customHeight="1" s="11">
@@ -1020,13 +1020,13 @@
         </is>
       </c>
       <c r="O2" s="32" t="n">
-        <v>-11.9</v>
+        <v>-8</v>
       </c>
       <c r="P2" s="32" t="n">
-        <v>-1.4</v>
+        <v>2.7</v>
       </c>
       <c r="Q2" s="32" t="n">
-        <v>-7.1</v>
+        <v>-3.09</v>
       </c>
       <c r="R2" s="23" t="inlineStr">
         <is>
@@ -1126,10 +1126,10 @@
         </is>
       </c>
       <c r="O3" s="32" t="n">
-        <v>-18.9</v>
+        <v>-12.3</v>
       </c>
       <c r="P3" s="32" t="n">
-        <v>-0.4</v>
+        <v>1.5</v>
       </c>
       <c r="Q3" s="32" t="n"/>
       <c r="R3" s="23" t="n"/>
@@ -1418,10 +1418,10 @@
         </is>
       </c>
       <c r="O6" s="32" t="n">
-        <v>-14.7</v>
+        <v>-13.9</v>
       </c>
       <c r="P6" s="32" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="Q6" s="32" t="n"/>
       <c r="R6" s="23" t="n"/>
@@ -1518,10 +1518,10 @@
         </is>
       </c>
       <c r="O7" s="32" t="n">
-        <v>-11.2</v>
+        <v>-7.5</v>
       </c>
       <c r="P7" s="32" t="n">
-        <v>2.7</v>
+        <v>3.4</v>
       </c>
       <c r="Q7" s="32" t="n"/>
       <c r="R7" s="23" t="n"/>
@@ -1626,13 +1626,13 @@
       </c>
       <c r="N8" s="2" t="n"/>
       <c r="O8" s="32" t="n">
-        <v>-6</v>
+        <v>-1.1</v>
       </c>
       <c r="P8" s="32" t="n">
-        <v>11.3</v>
+        <v>13.2</v>
       </c>
       <c r="Q8" s="32" t="n">
-        <v>1.26</v>
+        <v>5.19</v>
       </c>
       <c r="R8" s="23" t="inlineStr">
         <is>
@@ -1738,13 +1738,13 @@
       </c>
       <c r="N9" s="2" t="n"/>
       <c r="O9" s="32" t="n">
-        <v>-5.7</v>
+        <v>-3.3</v>
       </c>
       <c r="P9" s="32" t="n">
-        <v>2.2</v>
+        <v>5.3</v>
       </c>
       <c r="Q9" s="32" t="n">
-        <v>-1.89</v>
+        <v>0.16</v>
       </c>
       <c r="R9" s="23" t="inlineStr">
         <is>
@@ -1858,13 +1858,13 @@
         </is>
       </c>
       <c r="O10" s="32" t="n">
-        <v>-10.2</v>
+        <v>-7.5</v>
       </c>
       <c r="P10" s="32" t="n">
-        <v>0.9</v>
+        <v>4</v>
       </c>
       <c r="Q10" s="32" t="n">
-        <v>-5.18</v>
+        <v>-2.44</v>
       </c>
       <c r="R10" s="23" t="inlineStr">
         <is>
@@ -1974,13 +1974,13 @@
         </is>
       </c>
       <c r="O11" s="32" t="n">
-        <v>-15.6</v>
+        <v>-10.6</v>
       </c>
       <c r="P11" s="32" t="n">
-        <v>3</v>
+        <v>4.5</v>
       </c>
       <c r="Q11" s="32" t="n">
-        <v>-5.81</v>
+        <v>-3.1</v>
       </c>
       <c r="R11" s="23" t="inlineStr">
         <is>
@@ -2086,13 +2086,13 @@
       </c>
       <c r="N12" s="2" t="n"/>
       <c r="O12" s="32" t="n">
-        <v>-8.5</v>
+        <v>-7.7</v>
       </c>
       <c r="P12" s="32" t="n">
-        <v>4.7</v>
+        <v>6.7</v>
       </c>
       <c r="Q12" s="32" t="n">
-        <v>-2.83</v>
+        <v>-1.35</v>
       </c>
       <c r="R12" s="23" t="inlineStr">
         <is>
@@ -2202,13 +2202,13 @@
         </is>
       </c>
       <c r="O13" s="32" t="n">
-        <v>-11.9</v>
+        <v>-7.9</v>
       </c>
       <c r="P13" s="32" t="n">
-        <v>2.3</v>
+        <v>2.9</v>
       </c>
       <c r="Q13" s="32" t="n">
-        <v>-4.61</v>
+        <v>-3.16</v>
       </c>
       <c r="R13" s="23" t="inlineStr">
         <is>
@@ -2314,13 +2314,13 @@
       </c>
       <c r="N14" s="2" t="n"/>
       <c r="O14" s="32" t="n">
-        <v>-9</v>
+        <v>-6.2</v>
       </c>
       <c r="P14" s="32" t="n">
-        <v>6.9</v>
+        <v>10.9</v>
       </c>
       <c r="Q14" s="32" t="n">
-        <v>-1.15</v>
+        <v>2.28</v>
       </c>
       <c r="R14" s="23" t="inlineStr">
         <is>
@@ -2419,12 +2419,8 @@
         </is>
       </c>
       <c r="N15" s="2" t="n"/>
-      <c r="O15" s="32" t="n">
-        <v>-13.1</v>
-      </c>
-      <c r="P15" s="32" t="n">
-        <v>4</v>
-      </c>
+      <c r="O15" s="32" t="n"/>
+      <c r="P15" s="32" t="n"/>
       <c r="Q15" s="32" t="n"/>
       <c r="R15" s="23" t="n"/>
       <c r="S15" s="37" t="n"/>
@@ -8042,13 +8038,13 @@
         </is>
       </c>
       <c r="O77" s="32" t="n">
-        <v>-4.2</v>
+        <v>-8.4</v>
       </c>
       <c r="P77" s="32" t="n">
-        <v>2.3</v>
+        <v>1.4</v>
       </c>
       <c r="Q77" s="32" t="n">
-        <v>-1.59</v>
+        <v>-2.69</v>
       </c>
       <c r="R77" s="23" t="inlineStr">
         <is>
@@ -8468,14 +8464,12 @@
         </is>
       </c>
       <c r="O81" s="32" t="n">
-        <v>-18.2</v>
+        <v>-9.9</v>
       </c>
       <c r="P81" s="32" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="Q81" s="32" t="n">
-        <v>-4.6</v>
-      </c>
+        <v>8.9</v>
+      </c>
+      <c r="Q81" s="32" t="n"/>
       <c r="R81" s="23" t="inlineStr">
         <is>
           <t>Y</t>
@@ -8589,13 +8583,13 @@
         </is>
       </c>
       <c r="O82" s="32" t="n">
-        <v>-17.8</v>
+        <v>-12.7</v>
       </c>
       <c r="P82" s="32" t="n">
-        <v>5.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Q82" s="32" t="n">
-        <v>-5.34</v>
+        <v>-0.36</v>
       </c>
       <c r="R82" s="23" t="inlineStr">
         <is>
@@ -8807,13 +8801,13 @@
         </is>
       </c>
       <c r="O84" s="32" t="n">
-        <v>-2.8</v>
+        <v>-2.6</v>
       </c>
       <c r="P84" s="32" t="n">
-        <v>7.3</v>
+        <v>2.3</v>
       </c>
       <c r="Q84" s="32" t="n">
-        <v>2.26</v>
+        <v>-0.41</v>
       </c>
       <c r="R84" s="23" t="inlineStr">
         <is>
@@ -9025,13 +9019,13 @@
       </c>
       <c r="N86" s="2" t="n"/>
       <c r="O86" s="32" t="n">
-        <v>-5.8</v>
+        <v>-0.4</v>
       </c>
       <c r="P86" s="32" t="n">
-        <v>10.3</v>
+        <v>9.1</v>
       </c>
       <c r="Q86" s="32" t="n">
-        <v>1.7</v>
+        <v>4.27</v>
       </c>
       <c r="R86" s="23" t="inlineStr">
         <is>
@@ -9251,13 +9245,13 @@
       </c>
       <c r="N88" s="2" t="n"/>
       <c r="O88" s="32" t="n">
-        <v>-8.800000000000001</v>
+        <v>-3.4</v>
       </c>
       <c r="P88" s="32" t="n">
-        <v>9.9</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="Q88" s="32" t="n">
-        <v>-0.17</v>
+        <v>3.3</v>
       </c>
       <c r="R88" s="23" t="inlineStr">
         <is>
@@ -9563,13 +9557,13 @@
       </c>
       <c r="N91" s="2" t="n"/>
       <c r="O91" s="32" t="n">
-        <v>-10.9</v>
+        <v>-14</v>
       </c>
       <c r="P91" s="32" t="n">
-        <v>1.6</v>
+        <v>3.2</v>
       </c>
       <c r="Q91" s="32" t="n">
-        <v>-4.81</v>
+        <v>-3.75</v>
       </c>
       <c r="R91" s="23" t="inlineStr">
         <is>
@@ -9671,13 +9665,13 @@
       </c>
       <c r="N92" s="2" t="n"/>
       <c r="O92" s="32" t="n">
-        <v>-3.7</v>
+        <v>-1.7</v>
       </c>
       <c r="P92" s="32" t="n">
-        <v>9.300000000000001</v>
+        <v>6.7</v>
       </c>
       <c r="Q92" s="32" t="n">
-        <v>2.06</v>
+        <v>1.65</v>
       </c>
       <c r="R92" s="23" t="inlineStr">
         <is>
@@ -9783,14 +9777,12 @@
       </c>
       <c r="N93" s="2" t="n"/>
       <c r="O93" s="32" t="n">
-        <v>2.6</v>
+        <v>-0.8</v>
       </c>
       <c r="P93" s="32" t="n">
-        <v>13.6</v>
-      </c>
-      <c r="Q93" s="32" t="n">
-        <v>7.46</v>
-      </c>
+        <v>13.8</v>
+      </c>
+      <c r="Q93" s="32" t="n"/>
       <c r="R93" s="23" t="inlineStr">
         <is>
           <t>Y</t>
@@ -9903,10 +9895,10 @@
         </is>
       </c>
       <c r="O94" s="32" t="n">
-        <v>-3.3</v>
+        <v>-2.4</v>
       </c>
       <c r="P94" s="32" t="n">
-        <v>13.8</v>
+        <v>12.7</v>
       </c>
       <c r="Q94" s="32" t="n"/>
       <c r="R94" s="23" t="inlineStr">
@@ -10021,14 +10013,12 @@
       </c>
       <c r="N95" s="2" t="n"/>
       <c r="O95" s="32" t="n">
-        <v>3</v>
+        <v>-4.4</v>
       </c>
       <c r="P95" s="32" t="n">
-        <v>13.4</v>
-      </c>
-      <c r="Q95" s="32" t="n">
-        <v>8.76</v>
-      </c>
+        <v>11.8</v>
+      </c>
+      <c r="Q95" s="32" t="n"/>
       <c r="R95" s="23" t="inlineStr">
         <is>
           <t>Y</t>
@@ -10149,10 +10139,10 @@
         </is>
       </c>
       <c r="O96" s="32" t="n">
-        <v>-4</v>
+        <v>0.3</v>
       </c>
       <c r="P96" s="32" t="n">
-        <v>14.1</v>
+        <v>12.3</v>
       </c>
       <c r="Q96" s="32" t="n"/>
       <c r="R96" s="23" t="inlineStr">
@@ -10267,14 +10257,12 @@
       </c>
       <c r="N97" s="2" t="n"/>
       <c r="O97" s="32" t="n">
-        <v>-0.5</v>
+        <v>-0.3</v>
       </c>
       <c r="P97" s="32" t="n">
-        <v>12.4</v>
-      </c>
-      <c r="Q97" s="32" t="n">
-        <v>5.14</v>
-      </c>
+        <v>11.2</v>
+      </c>
+      <c r="Q97" s="32" t="n"/>
       <c r="R97" s="23" t="inlineStr">
         <is>
           <t>Y</t>
@@ -10387,10 +10375,10 @@
       </c>
       <c r="N98" s="2" t="n"/>
       <c r="O98" s="32" t="n">
-        <v>-3.8</v>
+        <v>0.3</v>
       </c>
       <c r="P98" s="32" t="n">
-        <v>6.2</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="Q98" s="32" t="n"/>
       <c r="R98" s="23" t="inlineStr">
@@ -10505,14 +10493,12 @@
       </c>
       <c r="N99" s="2" t="n"/>
       <c r="O99" s="32" t="n">
-        <v>-6.9</v>
+        <v>-5.9</v>
       </c>
       <c r="P99" s="32" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="Q99" s="32" t="n">
-        <v>-0.15</v>
-      </c>
+        <v>8.800000000000001</v>
+      </c>
+      <c r="Q99" s="32" t="n"/>
       <c r="R99" s="23" t="inlineStr">
         <is>
           <t>Y</t>
@@ -10837,14 +10823,12 @@
       </c>
       <c r="N102" s="2" t="n"/>
       <c r="O102" s="32" t="n">
-        <v>-6.5</v>
+        <v>-10.1</v>
       </c>
       <c r="P102" s="32" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="Q102" s="32" t="n">
-        <v>0.1</v>
-      </c>
+        <v>9.199999999999999</v>
+      </c>
+      <c r="Q102" s="32" t="n"/>
       <c r="R102" s="23" t="inlineStr">
         <is>
           <t>Y</t>
@@ -10953,10 +10937,10 @@
       </c>
       <c r="N103" s="2" t="n"/>
       <c r="O103" s="32" t="n">
-        <v>-8.6</v>
+        <v>-12.3</v>
       </c>
       <c r="P103" s="32" t="n">
-        <v>7.1</v>
+        <v>10.8</v>
       </c>
       <c r="Q103" s="32" t="n"/>
       <c r="R103" s="23" t="inlineStr">
@@ -11063,10 +11047,10 @@
       </c>
       <c r="N104" s="2" t="n"/>
       <c r="O104" s="32" t="n">
-        <v>-8.699999999999999</v>
+        <v>-13.9</v>
       </c>
       <c r="P104" s="32" t="n">
-        <v>3.1</v>
+        <v>5.7</v>
       </c>
       <c r="Q104" s="32" t="n"/>
       <c r="R104" s="23" t="inlineStr">
@@ -11189,14 +11173,12 @@
         </is>
       </c>
       <c r="O105" s="32" t="n">
-        <v>-12.6</v>
+        <v>-15.2</v>
       </c>
       <c r="P105" s="32" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="Q105" s="32" t="n">
-        <v>-3.4</v>
-      </c>
+        <v>6.1</v>
+      </c>
+      <c r="Q105" s="32" t="n"/>
       <c r="R105" s="23" t="inlineStr">
         <is>
           <t>Y</t>
@@ -11305,10 +11287,10 @@
         </is>
       </c>
       <c r="O106" s="32" t="n">
-        <v>-6.3</v>
+        <v>-7.9</v>
       </c>
       <c r="P106" s="32" t="n">
-        <v>3.5</v>
+        <v>5.9</v>
       </c>
       <c r="Q106" s="32" t="n"/>
       <c r="R106" s="23" t="inlineStr">
@@ -11525,14 +11507,12 @@
       </c>
       <c r="N108" s="2" t="n"/>
       <c r="O108" s="32" t="n">
-        <v>-4.1</v>
+        <v>-7.3</v>
       </c>
       <c r="P108" s="32" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="Q108" s="32" t="n">
-        <v>-1.51</v>
-      </c>
+        <v>7.9</v>
+      </c>
+      <c r="Q108" s="32" t="n"/>
       <c r="R108" s="23" t="inlineStr">
         <is>
           <t>Y</t>
@@ -11853,14 +11833,12 @@
       </c>
       <c r="N111" s="2" t="n"/>
       <c r="O111" s="32" t="n">
-        <v>-4.7</v>
+        <v>-11.1</v>
       </c>
       <c r="P111" s="32" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="Q111" s="32" t="n">
-        <v>-1.85</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="Q111" s="32" t="n"/>
       <c r="R111" s="23" t="inlineStr">
         <is>
           <t>Y</t>
@@ -11965,10 +11943,10 @@
       </c>
       <c r="N112" s="2" t="n"/>
       <c r="O112" s="32" t="n">
-        <v>-2.2</v>
+        <v>-11.2</v>
       </c>
       <c r="P112" s="32" t="n">
-        <v>5.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Q112" s="32" t="n"/>
       <c r="R112" s="23" t="inlineStr">
@@ -12071,10 +12049,10 @@
       </c>
       <c r="N113" s="2" t="n"/>
       <c r="O113" s="32" t="n">
-        <v>-12</v>
+        <v>-3.1</v>
       </c>
       <c r="P113" s="32" t="n">
-        <v>6.7</v>
+        <v>5.8</v>
       </c>
       <c r="Q113" s="32" t="n"/>
       <c r="R113" s="23" t="inlineStr">
@@ -12185,10 +12163,10 @@
         </is>
       </c>
       <c r="O114" s="32" t="n">
-        <v>-8.800000000000001</v>
+        <v>-6.9</v>
       </c>
       <c r="P114" s="32" t="n">
-        <v>1.9</v>
+        <v>-0.3</v>
       </c>
       <c r="Q114" s="32" t="n"/>
       <c r="R114" s="23" t="inlineStr">
@@ -12307,10 +12285,10 @@
         </is>
       </c>
       <c r="O115" s="32" t="n">
-        <v>-15.3</v>
+        <v>-12.4</v>
       </c>
       <c r="P115" s="32" t="n">
-        <v>3.6</v>
+        <v>0.5</v>
       </c>
       <c r="Q115" s="32" t="n"/>
       <c r="R115" s="23" t="inlineStr">
@@ -12425,14 +12403,12 @@
       </c>
       <c r="N116" s="2" t="n"/>
       <c r="O116" s="32" t="n">
-        <v>-4.3</v>
+        <v>-5.1</v>
       </c>
       <c r="P116" s="32" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="Q116" s="32" t="n">
-        <v>2.71</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="Q116" s="32" t="n"/>
       <c r="R116" s="23" t="inlineStr">
         <is>
           <t>Y</t>
@@ -12537,10 +12513,10 @@
       </c>
       <c r="N117" s="2" t="n"/>
       <c r="O117" s="32" t="n">
-        <v>-4.3</v>
+        <v>-2.5</v>
       </c>
       <c r="P117" s="32" t="n">
-        <v>8.5</v>
+        <v>9.9</v>
       </c>
       <c r="Q117" s="32" t="n"/>
       <c r="R117" s="23" t="inlineStr">
@@ -12651,10 +12627,10 @@
         </is>
       </c>
       <c r="O118" s="32" t="n">
-        <v>-3</v>
+        <v>-2.3</v>
       </c>
       <c r="P118" s="32" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="Q118" s="32" t="n"/>
       <c r="R118" s="23" t="inlineStr">
@@ -12769,14 +12745,12 @@
       </c>
       <c r="N119" s="2" t="n"/>
       <c r="O119" s="32" t="n">
-        <v>1.3</v>
+        <v>3.2</v>
       </c>
       <c r="P119" s="32" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="Q119" s="32" t="n">
-        <v>10.38</v>
-      </c>
+        <v>16.2</v>
+      </c>
+      <c r="Q119" s="32" t="n"/>
       <c r="R119" s="23" t="inlineStr">
         <is>
           <t>Y</t>
@@ -13003,14 +12977,12 @@
       </c>
       <c r="N121" s="2" t="n"/>
       <c r="O121" s="32" t="n">
-        <v>3.6</v>
+        <v>6</v>
       </c>
       <c r="P121" s="32" t="n">
-        <v>13.9</v>
-      </c>
-      <c r="Q121" s="32" t="n">
-        <v>8.52</v>
-      </c>
+        <v>18.5</v>
+      </c>
+      <c r="Q121" s="32" t="n"/>
       <c r="R121" s="23" t="inlineStr">
         <is>
           <t>Y</t>
@@ -13127,10 +13099,10 @@
       </c>
       <c r="N122" s="2" t="n"/>
       <c r="O122" s="32" t="n">
-        <v>-5</v>
+        <v>-9.5</v>
       </c>
       <c r="P122" s="32" t="n">
-        <v>8.300000000000001</v>
+        <v>10.6</v>
       </c>
       <c r="Q122" s="32" t="n"/>
       <c r="R122" s="23" t="inlineStr">
@@ -13351,14 +13323,12 @@
       </c>
       <c r="N124" s="2" t="n"/>
       <c r="O124" s="32" t="n">
-        <v>-1</v>
+        <v>-0.7</v>
       </c>
       <c r="P124" s="32" t="n">
-        <v>13.1</v>
-      </c>
-      <c r="Q124" s="32" t="n">
-        <v>6.16</v>
-      </c>
+        <v>13.5</v>
+      </c>
+      <c r="Q124" s="32" t="n"/>
       <c r="R124" s="23" t="inlineStr">
         <is>
           <t>Y</t>
@@ -13475,14 +13445,12 @@
       </c>
       <c r="N125" s="2" t="n"/>
       <c r="O125" s="32" t="n">
-        <v>11.1</v>
+        <v>8.5</v>
       </c>
       <c r="P125" s="32" t="n">
-        <v>23.5</v>
-      </c>
-      <c r="Q125" s="32" t="n">
-        <v>16.32</v>
-      </c>
+        <v>18.2</v>
+      </c>
+      <c r="Q125" s="32" t="n"/>
       <c r="R125" s="23" t="inlineStr">
         <is>
           <t>Y</t>
@@ -13579,10 +13547,10 @@
       </c>
       <c r="N126" s="2" t="n"/>
       <c r="O126" s="32" t="n">
-        <v>10.2</v>
+        <v>9.6</v>
       </c>
       <c r="P126" s="32" t="n">
-        <v>22.1</v>
+        <v>16.7</v>
       </c>
       <c r="Q126" s="32" t="n"/>
       <c r="R126" s="23" t="inlineStr">
@@ -13689,14 +13657,12 @@
       </c>
       <c r="N127" s="2" t="n"/>
       <c r="O127" s="32" t="n">
-        <v>2.1</v>
+        <v>3.9</v>
       </c>
       <c r="P127" s="32" t="n">
         <v>13.8</v>
       </c>
-      <c r="Q127" s="32" t="n">
-        <v>8.619999999999999</v>
-      </c>
+      <c r="Q127" s="32" t="n"/>
       <c r="R127" s="23" t="inlineStr">
         <is>
           <t>Y</t>
@@ -13809,10 +13775,10 @@
       </c>
       <c r="N128" s="2" t="n"/>
       <c r="O128" s="32" t="n">
-        <v>8.4</v>
+        <v>10.5</v>
       </c>
       <c r="P128" s="32" t="n">
-        <v>23.4</v>
+        <v>18.2</v>
       </c>
       <c r="Q128" s="32" t="n"/>
       <c r="R128" s="23" t="inlineStr">
@@ -13919,14 +13885,12 @@
       </c>
       <c r="N129" s="2" t="n"/>
       <c r="O129" s="32" t="n">
-        <v>1.9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="P129" s="32" t="n">
-        <v>20.6</v>
-      </c>
-      <c r="Q129" s="32" t="n">
-        <v>11.19</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="Q129" s="32" t="n"/>
       <c r="R129" s="23" t="inlineStr">
         <is>
           <t>Y</t>
@@ -14039,14 +14003,12 @@
       </c>
       <c r="N130" s="2" t="n"/>
       <c r="O130" s="32" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="P130" s="32" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="Q130" s="32" t="n">
-        <v>4.04</v>
-      </c>
+        <v>6.7</v>
+      </c>
+      <c r="Q130" s="32" t="n"/>
       <c r="R130" s="23" t="inlineStr">
         <is>
           <t>Y</t>
@@ -14159,14 +14121,12 @@
       </c>
       <c r="N131" s="2" t="n"/>
       <c r="O131" s="32" t="n">
-        <v>14.1</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="P131" s="32" t="n">
-        <v>22.1</v>
-      </c>
-      <c r="Q131" s="32" t="n">
-        <v>18.01</v>
-      </c>
+        <v>16.9</v>
+      </c>
+      <c r="Q131" s="32" t="n"/>
       <c r="R131" s="23" t="inlineStr">
         <is>
           <t>Y</t>
@@ -14275,14 +14235,12 @@
       </c>
       <c r="N132" s="2" t="n"/>
       <c r="O132" s="32" t="n">
-        <v>9.800000000000001</v>
+        <v>12.9</v>
       </c>
       <c r="P132" s="32" t="n">
-        <v>24.5</v>
-      </c>
-      <c r="Q132" s="32" t="n">
-        <v>17.99</v>
-      </c>
+        <v>20.8</v>
+      </c>
+      <c r="Q132" s="32" t="n"/>
       <c r="R132" s="23" t="inlineStr">
         <is>
           <t>Y</t>
@@ -14391,14 +14349,12 @@
       </c>
       <c r="N133" s="2" t="n"/>
       <c r="O133" s="32" t="n">
-        <v>10.3</v>
+        <v>10.9</v>
       </c>
       <c r="P133" s="32" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="Q133" s="32" t="n">
-        <v>14.78</v>
-      </c>
+        <v>18.7</v>
+      </c>
+      <c r="Q133" s="32" t="n"/>
       <c r="R133" s="23" t="inlineStr">
         <is>
           <t>Y</t>
@@ -14613,14 +14569,12 @@
       </c>
       <c r="N135" s="2" t="n"/>
       <c r="O135" s="32" t="n">
-        <v>13.1</v>
+        <v>14.3</v>
       </c>
       <c r="P135" s="32" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="Q135" s="32" t="n">
-        <v>15.21</v>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="Q135" s="32" t="n"/>
       <c r="R135" s="23" t="inlineStr">
         <is>
           <t>Y</t>
@@ -14729,14 +14683,12 @@
       </c>
       <c r="N136" s="2" t="n"/>
       <c r="O136" s="32" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="P136" s="32" t="n">
-        <v>22.4</v>
-      </c>
-      <c r="Q136" s="32" t="n">
-        <v>18.91</v>
-      </c>
+        <v>22.1</v>
+      </c>
+      <c r="Q136" s="32" t="n"/>
       <c r="R136" s="23" t="inlineStr">
         <is>
           <t>Y</t>
@@ -14845,14 +14797,12 @@
       </c>
       <c r="N137" s="2" t="n"/>
       <c r="O137" s="32" t="n">
-        <v>11.3</v>
+        <v>15.3</v>
       </c>
       <c r="P137" s="32" t="n">
-        <v>22.6</v>
-      </c>
-      <c r="Q137" s="32" t="n">
-        <v>17.35</v>
-      </c>
+        <v>18</v>
+      </c>
+      <c r="Q137" s="32" t="n"/>
       <c r="R137" s="23" t="inlineStr">
         <is>
           <t>Y</t>
@@ -14961,10 +14911,10 @@
       </c>
       <c r="N138" s="2" t="n"/>
       <c r="O138" s="32" t="n">
-        <v>9.1</v>
+        <v>12.9</v>
       </c>
       <c r="P138" s="32" t="n">
-        <v>25.5</v>
+        <v>20.5</v>
       </c>
       <c r="Q138" s="32" t="n"/>
       <c r="R138" s="23" t="inlineStr">
@@ -15075,14 +15025,12 @@
       </c>
       <c r="N139" s="2" t="n"/>
       <c r="O139" s="32" t="n">
-        <v>12.2</v>
+        <v>13.4</v>
       </c>
       <c r="P139" s="32" t="n">
-        <v>25.7</v>
-      </c>
-      <c r="Q139" s="32" t="n">
-        <v>19.24</v>
-      </c>
+        <v>21.3</v>
+      </c>
+      <c r="Q139" s="32" t="n"/>
       <c r="R139" s="23" t="inlineStr">
         <is>
           <t>Y</t>
@@ -15191,14 +15139,12 @@
       </c>
       <c r="N140" s="2" t="n"/>
       <c r="O140" s="32" t="n">
-        <v>15.5</v>
+        <v>16.7</v>
       </c>
       <c r="P140" s="32" t="n">
-        <v>26</v>
-      </c>
-      <c r="Q140" s="32" t="n">
-        <v>19.46</v>
-      </c>
+        <v>24.8</v>
+      </c>
+      <c r="Q140" s="32" t="n"/>
       <c r="R140" s="23" t="inlineStr">
         <is>
           <t>Y</t>
@@ -15409,14 +15355,12 @@
       </c>
       <c r="N142" s="2" t="n"/>
       <c r="O142" s="32" t="n">
-        <v>15.6</v>
+        <v>16.7</v>
       </c>
       <c r="P142" s="32" t="n">
-        <v>27.1</v>
-      </c>
-      <c r="Q142" s="32" t="n">
-        <v>19.07</v>
-      </c>
+        <v>26.2</v>
+      </c>
+      <c r="Q142" s="32" t="n"/>
       <c r="R142" s="23" t="inlineStr">
         <is>
           <t>Y</t>
@@ -15525,14 +15469,12 @@
       </c>
       <c r="N143" s="2" t="n"/>
       <c r="O143" s="32" t="n">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="P143" s="32" t="n">
-        <v>27.6</v>
-      </c>
-      <c r="Q143" s="32" t="n">
-        <v>23</v>
-      </c>
+        <v>23.6</v>
+      </c>
+      <c r="Q143" s="32" t="n"/>
       <c r="R143" s="23" t="inlineStr">
         <is>
           <t>Y</t>
@@ -15841,14 +15783,12 @@
       </c>
       <c r="N146" s="2" t="n"/>
       <c r="O146" s="32" t="n">
-        <v>23.5</v>
+        <v>26.6</v>
       </c>
       <c r="P146" s="32" t="n">
-        <v>30.9</v>
-      </c>
-      <c r="Q146" s="32" t="n">
-        <v>27.35</v>
-      </c>
+        <v>32.4</v>
+      </c>
+      <c r="Q146" s="32" t="n"/>
       <c r="R146" s="23" t="inlineStr">
         <is>
           <t>Y</t>
@@ -15949,14 +15889,12 @@
       </c>
       <c r="N147" s="2" t="n"/>
       <c r="O147" s="32" t="n">
-        <v>19.5</v>
+        <v>18.8</v>
       </c>
       <c r="P147" s="32" t="n">
-        <v>24.2</v>
-      </c>
-      <c r="Q147" s="32" t="n">
-        <v>21.16</v>
-      </c>
+        <v>30.7</v>
+      </c>
+      <c r="Q147" s="32" t="n"/>
       <c r="R147" s="23" t="inlineStr">
         <is>
           <t>Y</t>
@@ -16167,14 +16105,12 @@
       </c>
       <c r="N149" s="2" t="n"/>
       <c r="O149" s="32" t="n">
-        <v>10.7</v>
+        <v>10.4</v>
       </c>
       <c r="P149" s="32" t="n">
-        <v>21.2</v>
-      </c>
-      <c r="Q149" s="32" t="n">
-        <v>14.46</v>
-      </c>
+        <v>22.7</v>
+      </c>
+      <c r="Q149" s="32" t="n"/>
       <c r="R149" s="23" t="inlineStr">
         <is>
           <t>Y</t>
@@ -16283,14 +16219,12 @@
       </c>
       <c r="N150" s="2" t="n"/>
       <c r="O150" s="32" t="n">
-        <v>11.6</v>
+        <v>12.7</v>
       </c>
       <c r="P150" s="32" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="Q150" s="32" t="n">
-        <v>14.81</v>
-      </c>
+        <v>22.9</v>
+      </c>
+      <c r="Q150" s="32" t="n"/>
       <c r="R150" s="23" t="inlineStr">
         <is>
           <t>Y</t>
@@ -16399,14 +16333,12 @@
       </c>
       <c r="N151" s="2" t="n"/>
       <c r="O151" s="32" t="n">
-        <v>15.3</v>
+        <v>15.8</v>
       </c>
       <c r="P151" s="32" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="Q151" s="32" t="n">
-        <v>17.05</v>
-      </c>
+        <v>22.7</v>
+      </c>
+      <c r="Q151" s="32" t="n"/>
       <c r="R151" s="23" t="inlineStr">
         <is>
           <t>Y</t>
@@ -16605,14 +16537,12 @@
       </c>
       <c r="N153" s="2" t="n"/>
       <c r="O153" s="32" t="n">
-        <v>14.7</v>
+        <v>12.4</v>
       </c>
       <c r="P153" s="32" t="n">
-        <v>19.2</v>
-      </c>
-      <c r="Q153" s="32" t="n">
-        <v>16</v>
-      </c>
+        <v>16.6</v>
+      </c>
+      <c r="Q153" s="32" t="n"/>
       <c r="R153" s="23" t="inlineStr">
         <is>
           <t>Y</t>
@@ -16725,13 +16655,13 @@
       </c>
       <c r="N154" s="2" t="n"/>
       <c r="O154" s="32" t="n">
-        <v>1.7</v>
+        <v>2.6</v>
       </c>
       <c r="P154" s="32" t="n">
-        <v>15.2</v>
+        <v>17.2</v>
       </c>
       <c r="Q154" s="32" t="n">
-        <v>6.85</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="R154" s="23" t="inlineStr">
         <is>
@@ -16927,10 +16857,10 @@
       </c>
       <c r="N156" s="2" t="n"/>
       <c r="O156" s="32" t="n">
-        <v>-4.5</v>
+        <v>-2.3</v>
       </c>
       <c r="P156" s="32" t="n">
-        <v>13.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Q156" s="32" t="n"/>
       <c r="R156" s="23" t="inlineStr">
@@ -17033,10 +16963,10 @@
       </c>
       <c r="N157" s="2" t="n"/>
       <c r="O157" s="32" t="n">
-        <v>14.7</v>
+        <v>15.5</v>
       </c>
       <c r="P157" s="32" t="n">
-        <v>22.1</v>
+        <v>22.2</v>
       </c>
       <c r="Q157" s="32" t="n"/>
       <c r="R157" s="23" t="inlineStr">
@@ -17421,10 +17351,10 @@
       </c>
       <c r="N161" s="2" t="n"/>
       <c r="O161" s="32" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="P161" s="32" t="n">
-        <v>12.5</v>
+        <v>10.9</v>
       </c>
       <c r="Q161" s="32" t="n"/>
       <c r="R161" s="23" t="inlineStr">
@@ -17534,8 +17464,12 @@
           <t>⚡</t>
         </is>
       </c>
-      <c r="O162" s="32" t="n"/>
-      <c r="P162" s="32" t="n"/>
+      <c r="O162" s="32" t="n">
+        <v>-18.5</v>
+      </c>
+      <c r="P162" s="32" t="n">
+        <v>8.5</v>
+      </c>
       <c r="Q162" s="32" t="n"/>
       <c r="R162" s="23" t="inlineStr">
         <is>
@@ -17640,12 +17574,8 @@
         </is>
       </c>
       <c r="N163" s="2" t="n"/>
-      <c r="O163" s="32" t="n">
-        <v>-11.2</v>
-      </c>
-      <c r="P163" s="32" t="n">
-        <v>6</v>
-      </c>
+      <c r="O163" s="32" t="n"/>
+      <c r="P163" s="32" t="n"/>
       <c r="Q163" s="32" t="n"/>
       <c r="R163" s="23" t="inlineStr">
         <is>
@@ -17861,10 +17791,10 @@
         </is>
       </c>
       <c r="O165" s="32" t="n">
-        <v>-8.1</v>
+        <v>-16.8</v>
       </c>
       <c r="P165" s="32" t="n">
-        <v>1.9</v>
+        <v>5.3</v>
       </c>
       <c r="Q165" s="32" t="n"/>
       <c r="R165" s="23" t="inlineStr">
@@ -18080,8 +18010,12 @@
         </is>
       </c>
       <c r="N167" s="2" t="n"/>
-      <c r="O167" s="32" t="n"/>
-      <c r="P167" s="32" t="n"/>
+      <c r="O167" s="32" t="n">
+        <v>-20.5</v>
+      </c>
+      <c r="P167" s="32" t="n">
+        <v>6</v>
+      </c>
       <c r="Q167" s="32" t="n"/>
       <c r="R167" s="23" t="inlineStr">
         <is>
@@ -18186,12 +18120,8 @@
           <t>❄️</t>
         </is>
       </c>
-      <c r="O168" s="32" t="n">
-        <v>-10</v>
-      </c>
-      <c r="P168" s="32" t="n">
-        <v>12.2</v>
-      </c>
+      <c r="O168" s="32" t="n"/>
+      <c r="P168" s="32" t="n"/>
       <c r="Q168" s="32" t="n"/>
       <c r="R168" s="23" t="inlineStr">
         <is>
@@ -18300,12 +18230,8 @@
           <t>↓</t>
         </is>
       </c>
-      <c r="O169" s="32" t="n">
-        <v>-8.4</v>
-      </c>
-      <c r="P169" s="32" t="n">
-        <v>6.7</v>
-      </c>
+      <c r="O169" s="32" t="n"/>
+      <c r="P169" s="32" t="n"/>
       <c r="Q169" s="32" t="n"/>
       <c r="R169" s="23" t="inlineStr">
         <is>
@@ -18415,10 +18341,10 @@
         </is>
       </c>
       <c r="O170" s="32" t="n">
-        <v>-26.9</v>
+        <v>-19.4</v>
       </c>
       <c r="P170" s="32" t="n">
-        <v>0.1</v>
+        <v>2.4</v>
       </c>
       <c r="Q170" s="32" t="n"/>
       <c r="R170" s="23" t="inlineStr">
@@ -18525,10 +18451,10 @@
       </c>
       <c r="N171" s="2" t="n"/>
       <c r="O171" s="32" t="n">
-        <v>-9.1</v>
+        <v>-9.199999999999999</v>
       </c>
       <c r="P171" s="32" t="n">
-        <v>-5.3</v>
+        <v>-3.3</v>
       </c>
       <c r="Q171" s="32" t="n"/>
       <c r="R171" s="23" t="inlineStr">
@@ -18741,10 +18667,10 @@
       </c>
       <c r="N173" s="2" t="n"/>
       <c r="O173" s="32" t="n">
-        <v>-2.9</v>
+        <v>-11.9</v>
       </c>
       <c r="P173" s="32" t="n">
-        <v>8.5</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="Q173" s="32" t="n"/>
       <c r="R173" s="23" t="inlineStr">
@@ -19063,10 +18989,10 @@
       </c>
       <c r="N176" s="2" t="n"/>
       <c r="O176" s="32" t="n">
-        <v>5.7</v>
+        <v>4.6</v>
       </c>
       <c r="P176" s="32" t="n">
-        <v>13</v>
+        <v>10.3</v>
       </c>
       <c r="Q176" s="32" t="n"/>
       <c r="R176" s="23" t="inlineStr">
@@ -19165,10 +19091,10 @@
       </c>
       <c r="N177" s="2" t="n"/>
       <c r="O177" s="32" t="n">
-        <v>-7.4</v>
+        <v>-11.9</v>
       </c>
       <c r="P177" s="32" t="n">
-        <v>-3.5</v>
+        <v>-5.7</v>
       </c>
       <c r="Q177" s="32" t="n"/>
       <c r="R177" s="23" t="inlineStr">
@@ -21275,8 +21201,12 @@
         </is>
       </c>
       <c r="N199" s="2" t="n"/>
-      <c r="O199" s="32" t="n"/>
-      <c r="P199" s="32" t="n"/>
+      <c r="O199" s="32" t="n">
+        <v>-16.5</v>
+      </c>
+      <c r="P199" s="32" t="n">
+        <v>8.800000000000001</v>
+      </c>
       <c r="Q199" s="32" t="n"/>
       <c r="R199" s="23" t="inlineStr">
         <is>
@@ -22682,10 +22612,10 @@
       </c>
       <c r="N213" s="2" t="n"/>
       <c r="O213" s="32" t="n">
-        <v>-15.9</v>
+        <v>-26.2</v>
       </c>
       <c r="P213" s="32" t="n">
-        <v>1.3</v>
+        <v>5</v>
       </c>
       <c r="Q213" s="32" t="n"/>
       <c r="R213" s="23" t="inlineStr">
@@ -25441,12 +25371,8 @@
         </is>
       </c>
       <c r="N241" s="2" t="n"/>
-      <c r="O241" s="32" t="n">
-        <v>-21.5</v>
-      </c>
-      <c r="P241" s="32" t="n">
-        <v>5</v>
-      </c>
+      <c r="O241" s="32" t="n"/>
+      <c r="P241" s="32" t="n"/>
       <c r="Q241" s="32" t="n"/>
       <c r="R241" s="23" t="inlineStr">
         <is>
@@ -26126,13 +26052,13 @@
         </is>
       </c>
       <c r="O248" s="32" t="n">
-        <v>-8.800000000000001</v>
+        <v>-7.5</v>
       </c>
       <c r="P248" s="32" t="n">
-        <v>5.1</v>
+        <v>6</v>
       </c>
       <c r="Q248" s="32" t="n">
-        <v>-1.58</v>
+        <v>-0.66</v>
       </c>
       <c r="R248" s="23" t="inlineStr">
         <is>
@@ -27794,10 +27720,10 @@
       </c>
       <c r="N265" s="2" t="n"/>
       <c r="O265" s="32" t="n">
-        <v>-59.3</v>
+        <v>-58.6</v>
       </c>
       <c r="P265" s="32" t="n">
-        <v>-56.3</v>
+        <v>-48.1</v>
       </c>
       <c r="Q265" s="32" t="n"/>
       <c r="R265" s="23" t="inlineStr">
@@ -30633,12 +30559,8 @@
         </is>
       </c>
       <c r="N295" s="2" t="n"/>
-      <c r="O295" s="32" t="n">
-        <v>-15.2</v>
-      </c>
-      <c r="P295" s="32" t="n">
-        <v>0</v>
-      </c>
+      <c r="O295" s="32" t="n"/>
+      <c r="P295" s="32" t="n"/>
       <c r="Q295" s="32" t="n"/>
       <c r="R295" s="23" t="inlineStr">
         <is>
@@ -30933,12 +30855,8 @@
         </is>
       </c>
       <c r="N298" s="2" t="n"/>
-      <c r="O298" s="32" t="n">
-        <v>-19.2</v>
-      </c>
-      <c r="P298" s="32" t="n">
-        <v>1.9</v>
-      </c>
+      <c r="O298" s="32" t="n"/>
+      <c r="P298" s="32" t="n"/>
       <c r="Q298" s="32" t="n"/>
       <c r="R298" s="23" t="inlineStr">
         <is>

--- a/气象/For_Python_站点信息和记录.xlsx
+++ b/气象/For_Python_站点信息和记录.xlsx
@@ -796,8 +796,8 @@
     <col width="18.59765625" customWidth="1" style="8" min="25" max="25"/>
     <col width="12.59765625" customWidth="1" style="5" min="26" max="30"/>
     <col width="12.59765625" customWidth="1" style="8" min="31" max="32"/>
-    <col width="12.59765625" customWidth="1" style="5" min="33" max="350"/>
-    <col width="12.59765625" customWidth="1" style="5" min="351" max="16384"/>
+    <col width="12.59765625" customWidth="1" style="5" min="33" max="359"/>
+    <col width="12.59765625" customWidth="1" style="5" min="360" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="27.75" customFormat="1" customHeight="1" s="11">
@@ -1020,13 +1020,13 @@
         </is>
       </c>
       <c r="O2" s="32" t="n">
-        <v>-8</v>
+        <v>-3.6</v>
       </c>
       <c r="P2" s="32" t="n">
-        <v>2.7</v>
+        <v>14.6</v>
       </c>
       <c r="Q2" s="32" t="n">
-        <v>-3.09</v>
+        <v>5.55</v>
       </c>
       <c r="R2" s="23" t="inlineStr">
         <is>
@@ -1126,10 +1126,10 @@
         </is>
       </c>
       <c r="O3" s="32" t="n">
-        <v>-12.3</v>
+        <v>-2.2</v>
       </c>
       <c r="P3" s="32" t="n">
-        <v>1.5</v>
+        <v>12</v>
       </c>
       <c r="Q3" s="32" t="n"/>
       <c r="R3" s="23" t="n"/>
@@ -1229,8 +1229,12 @@
           <t>⚡</t>
         </is>
       </c>
-      <c r="O4" s="32" t="n"/>
-      <c r="P4" s="32" t="n"/>
+      <c r="O4" s="32" t="n">
+        <v>-1.9</v>
+      </c>
+      <c r="P4" s="32" t="n">
+        <v>8.6</v>
+      </c>
       <c r="Q4" s="32" t="n"/>
       <c r="R4" s="23" t="n"/>
       <c r="S4" s="37" t="n"/>
@@ -1418,10 +1422,10 @@
         </is>
       </c>
       <c r="O6" s="32" t="n">
-        <v>-13.9</v>
+        <v>-3.7</v>
       </c>
       <c r="P6" s="32" t="n">
-        <v>3</v>
+        <v>6.8</v>
       </c>
       <c r="Q6" s="32" t="n"/>
       <c r="R6" s="23" t="n"/>
@@ -1518,10 +1522,10 @@
         </is>
       </c>
       <c r="O7" s="32" t="n">
-        <v>-7.5</v>
+        <v>-4.8</v>
       </c>
       <c r="P7" s="32" t="n">
-        <v>3.4</v>
+        <v>0.8</v>
       </c>
       <c r="Q7" s="32" t="n"/>
       <c r="R7" s="23" t="n"/>
@@ -1626,13 +1630,13 @@
       </c>
       <c r="N8" s="2" t="n"/>
       <c r="O8" s="32" t="n">
-        <v>-1.1</v>
+        <v>-1.7</v>
       </c>
       <c r="P8" s="32" t="n">
-        <v>13.2</v>
+        <v>6</v>
       </c>
       <c r="Q8" s="32" t="n">
-        <v>5.19</v>
+        <v>1.52</v>
       </c>
       <c r="R8" s="23" t="inlineStr">
         <is>
@@ -1738,13 +1742,13 @@
       </c>
       <c r="N9" s="2" t="n"/>
       <c r="O9" s="32" t="n">
-        <v>-3.3</v>
+        <v>-0.8</v>
       </c>
       <c r="P9" s="32" t="n">
-        <v>5.3</v>
+        <v>16.4</v>
       </c>
       <c r="Q9" s="32" t="n">
-        <v>0.16</v>
+        <v>7.56</v>
       </c>
       <c r="R9" s="23" t="inlineStr">
         <is>
@@ -1858,13 +1862,13 @@
         </is>
       </c>
       <c r="O10" s="32" t="n">
-        <v>-7.5</v>
+        <v>0.2</v>
       </c>
       <c r="P10" s="32" t="n">
-        <v>4</v>
+        <v>6.6</v>
       </c>
       <c r="Q10" s="32" t="n">
-        <v>-2.44</v>
+        <v>3.02</v>
       </c>
       <c r="R10" s="23" t="inlineStr">
         <is>
@@ -1974,13 +1978,13 @@
         </is>
       </c>
       <c r="O11" s="32" t="n">
-        <v>-10.6</v>
+        <v>-3</v>
       </c>
       <c r="P11" s="32" t="n">
-        <v>4.5</v>
+        <v>5.8</v>
       </c>
       <c r="Q11" s="32" t="n">
-        <v>-3.1</v>
+        <v>2.17</v>
       </c>
       <c r="R11" s="23" t="inlineStr">
         <is>
@@ -2086,13 +2090,13 @@
       </c>
       <c r="N12" s="2" t="n"/>
       <c r="O12" s="32" t="n">
-        <v>-7.7</v>
+        <v>-1.3</v>
       </c>
       <c r="P12" s="32" t="n">
-        <v>6.7</v>
+        <v>5.6</v>
       </c>
       <c r="Q12" s="32" t="n">
-        <v>-1.35</v>
+        <v>2.49</v>
       </c>
       <c r="R12" s="23" t="inlineStr">
         <is>
@@ -2202,13 +2206,13 @@
         </is>
       </c>
       <c r="O13" s="32" t="n">
-        <v>-7.9</v>
+        <v>-6.3</v>
       </c>
       <c r="P13" s="32" t="n">
-        <v>2.9</v>
+        <v>0.1</v>
       </c>
       <c r="Q13" s="32" t="n">
-        <v>-3.16</v>
+        <v>-2.75</v>
       </c>
       <c r="R13" s="23" t="inlineStr">
         <is>
@@ -2314,13 +2318,13 @@
       </c>
       <c r="N14" s="2" t="n"/>
       <c r="O14" s="32" t="n">
-        <v>-6.2</v>
+        <v>-4.7</v>
       </c>
       <c r="P14" s="32" t="n">
-        <v>10.9</v>
+        <v>2.9</v>
       </c>
       <c r="Q14" s="32" t="n">
-        <v>2.28</v>
+        <v>-0.1</v>
       </c>
       <c r="R14" s="23" t="inlineStr">
         <is>
@@ -8038,13 +8042,13 @@
         </is>
       </c>
       <c r="O77" s="32" t="n">
-        <v>-8.4</v>
+        <v>-25.7</v>
       </c>
       <c r="P77" s="32" t="n">
-        <v>1.4</v>
+        <v>-2</v>
       </c>
       <c r="Q77" s="32" t="n">
-        <v>-2.69</v>
+        <v>-13.59</v>
       </c>
       <c r="R77" s="23" t="inlineStr">
         <is>
@@ -8464,10 +8468,10 @@
         </is>
       </c>
       <c r="O81" s="32" t="n">
-        <v>-9.9</v>
+        <v>-16.3</v>
       </c>
       <c r="P81" s="32" t="n">
-        <v>8.9</v>
+        <v>2.2</v>
       </c>
       <c r="Q81" s="32" t="n"/>
       <c r="R81" s="23" t="inlineStr">
@@ -8583,13 +8587,13 @@
         </is>
       </c>
       <c r="O82" s="32" t="n">
-        <v>-12.7</v>
+        <v>-14.3</v>
       </c>
       <c r="P82" s="32" t="n">
-        <v>8.199999999999999</v>
+        <v>2.1</v>
       </c>
       <c r="Q82" s="32" t="n">
-        <v>-0.36</v>
+        <v>-4.88</v>
       </c>
       <c r="R82" s="23" t="inlineStr">
         <is>
@@ -8801,13 +8805,13 @@
         </is>
       </c>
       <c r="O84" s="32" t="n">
-        <v>-2.6</v>
+        <v>-2.4</v>
       </c>
       <c r="P84" s="32" t="n">
-        <v>2.3</v>
+        <v>1.3</v>
       </c>
       <c r="Q84" s="32" t="n">
-        <v>-0.41</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="R84" s="23" t="inlineStr">
         <is>
@@ -9022,10 +9026,10 @@
         <v>-0.4</v>
       </c>
       <c r="P86" s="32" t="n">
-        <v>9.1</v>
+        <v>13.2</v>
       </c>
       <c r="Q86" s="32" t="n">
-        <v>4.27</v>
+        <v>6.22</v>
       </c>
       <c r="R86" s="23" t="inlineStr">
         <is>
@@ -9245,13 +9249,13 @@
       </c>
       <c r="N88" s="2" t="n"/>
       <c r="O88" s="32" t="n">
-        <v>-3.4</v>
+        <v>-6.4</v>
       </c>
       <c r="P88" s="32" t="n">
-        <v>9.699999999999999</v>
+        <v>14</v>
       </c>
       <c r="Q88" s="32" t="n">
-        <v>3.3</v>
+        <v>3.47</v>
       </c>
       <c r="R88" s="23" t="inlineStr">
         <is>
@@ -9556,20 +9560,10 @@
         </is>
       </c>
       <c r="N91" s="2" t="n"/>
-      <c r="O91" s="32" t="n">
-        <v>-14</v>
-      </c>
-      <c r="P91" s="32" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="Q91" s="32" t="n">
-        <v>-3.75</v>
-      </c>
-      <c r="R91" s="23" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="O91" s="32" t="n"/>
+      <c r="P91" s="32" t="n"/>
+      <c r="Q91" s="32" t="n"/>
+      <c r="R91" s="23" t="n"/>
       <c r="S91" s="37" t="n"/>
       <c r="T91" s="41" t="inlineStr">
         <is>
@@ -9665,13 +9659,13 @@
       </c>
       <c r="N92" s="2" t="n"/>
       <c r="O92" s="32" t="n">
-        <v>-1.7</v>
+        <v>-2.9</v>
       </c>
       <c r="P92" s="32" t="n">
-        <v>6.7</v>
+        <v>6.6</v>
       </c>
       <c r="Q92" s="32" t="n">
-        <v>1.65</v>
+        <v>3.5</v>
       </c>
       <c r="R92" s="23" t="inlineStr">
         <is>
@@ -9777,12 +9771,14 @@
       </c>
       <c r="N93" s="2" t="n"/>
       <c r="O93" s="32" t="n">
-        <v>-0.8</v>
+        <v>1.2</v>
       </c>
       <c r="P93" s="32" t="n">
-        <v>13.8</v>
-      </c>
-      <c r="Q93" s="32" t="n"/>
+        <v>11.3</v>
+      </c>
+      <c r="Q93" s="32" t="n">
+        <v>5.64</v>
+      </c>
       <c r="R93" s="23" t="inlineStr">
         <is>
           <t>Y</t>
@@ -9895,10 +9891,10 @@
         </is>
       </c>
       <c r="O94" s="32" t="n">
-        <v>-2.4</v>
+        <v>-1.8</v>
       </c>
       <c r="P94" s="32" t="n">
-        <v>12.7</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="Q94" s="32" t="n"/>
       <c r="R94" s="23" t="inlineStr">
@@ -10013,12 +10009,14 @@
       </c>
       <c r="N95" s="2" t="n"/>
       <c r="O95" s="32" t="n">
-        <v>-4.4</v>
+        <v>-3.4</v>
       </c>
       <c r="P95" s="32" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="Q95" s="32" t="n"/>
+        <v>7.1</v>
+      </c>
+      <c r="Q95" s="32" t="n">
+        <v>2.06</v>
+      </c>
       <c r="R95" s="23" t="inlineStr">
         <is>
           <t>Y</t>
@@ -10139,10 +10137,10 @@
         </is>
       </c>
       <c r="O96" s="32" t="n">
-        <v>0.3</v>
+        <v>-0.4</v>
       </c>
       <c r="P96" s="32" t="n">
-        <v>12.3</v>
+        <v>14.1</v>
       </c>
       <c r="Q96" s="32" t="n"/>
       <c r="R96" s="23" t="inlineStr">
@@ -10257,12 +10255,14 @@
       </c>
       <c r="N97" s="2" t="n"/>
       <c r="O97" s="32" t="n">
-        <v>-0.3</v>
+        <v>-4.3</v>
       </c>
       <c r="P97" s="32" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="Q97" s="32" t="n"/>
+        <v>6.2</v>
+      </c>
+      <c r="Q97" s="32" t="n">
+        <v>1.74</v>
+      </c>
       <c r="R97" s="23" t="inlineStr">
         <is>
           <t>Y</t>
@@ -10375,10 +10375,10 @@
       </c>
       <c r="N98" s="2" t="n"/>
       <c r="O98" s="32" t="n">
-        <v>0.3</v>
+        <v>-2.2</v>
       </c>
       <c r="P98" s="32" t="n">
-        <v>8.699999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="Q98" s="32" t="n"/>
       <c r="R98" s="23" t="inlineStr">
@@ -10493,12 +10493,14 @@
       </c>
       <c r="N99" s="2" t="n"/>
       <c r="O99" s="32" t="n">
-        <v>-5.9</v>
+        <v>-7.8</v>
       </c>
       <c r="P99" s="32" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="Q99" s="32" t="n"/>
+        <v>7</v>
+      </c>
+      <c r="Q99" s="32" t="n">
+        <v>-0.04</v>
+      </c>
       <c r="R99" s="23" t="inlineStr">
         <is>
           <t>Y</t>
@@ -10708,8 +10710,12 @@
         </is>
       </c>
       <c r="N101" s="2" t="n"/>
-      <c r="O101" s="32" t="n"/>
-      <c r="P101" s="32" t="n"/>
+      <c r="O101" s="32" t="n">
+        <v>-13.2</v>
+      </c>
+      <c r="P101" s="32" t="n">
+        <v>5.8</v>
+      </c>
       <c r="Q101" s="32" t="n"/>
       <c r="R101" s="23" t="inlineStr">
         <is>
@@ -10823,12 +10829,14 @@
       </c>
       <c r="N102" s="2" t="n"/>
       <c r="O102" s="32" t="n">
-        <v>-10.1</v>
+        <v>-10.7</v>
       </c>
       <c r="P102" s="32" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="Q102" s="32" t="n"/>
+        <v>3.9</v>
+      </c>
+      <c r="Q102" s="32" t="n">
+        <v>-3.91</v>
+      </c>
       <c r="R102" s="23" t="inlineStr">
         <is>
           <t>Y</t>
@@ -10937,10 +10945,10 @@
       </c>
       <c r="N103" s="2" t="n"/>
       <c r="O103" s="32" t="n">
-        <v>-12.3</v>
+        <v>-8.699999999999999</v>
       </c>
       <c r="P103" s="32" t="n">
-        <v>10.8</v>
+        <v>5.1</v>
       </c>
       <c r="Q103" s="32" t="n"/>
       <c r="R103" s="23" t="inlineStr">
@@ -11047,10 +11055,10 @@
       </c>
       <c r="N104" s="2" t="n"/>
       <c r="O104" s="32" t="n">
-        <v>-13.9</v>
+        <v>-8.9</v>
       </c>
       <c r="P104" s="32" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="Q104" s="32" t="n"/>
       <c r="R104" s="23" t="inlineStr">
@@ -11173,12 +11181,14 @@
         </is>
       </c>
       <c r="O105" s="32" t="n">
-        <v>-15.2</v>
+        <v>-11.3</v>
       </c>
       <c r="P105" s="32" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="Q105" s="32" t="n"/>
+        <v>4.6</v>
+      </c>
+      <c r="Q105" s="32" t="n">
+        <v>-2.88</v>
+      </c>
       <c r="R105" s="23" t="inlineStr">
         <is>
           <t>Y</t>
@@ -11287,10 +11297,10 @@
         </is>
       </c>
       <c r="O106" s="32" t="n">
-        <v>-7.9</v>
+        <v>-2.5</v>
       </c>
       <c r="P106" s="32" t="n">
-        <v>5.9</v>
+        <v>6.8</v>
       </c>
       <c r="Q106" s="32" t="n"/>
       <c r="R106" s="23" t="inlineStr">
@@ -11507,12 +11517,14 @@
       </c>
       <c r="N108" s="2" t="n"/>
       <c r="O108" s="32" t="n">
-        <v>-7.3</v>
+        <v>-2.3</v>
       </c>
       <c r="P108" s="32" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="Q108" s="32" t="n"/>
+        <v>6.8</v>
+      </c>
+      <c r="Q108" s="32" t="n">
+        <v>1.36</v>
+      </c>
       <c r="R108" s="23" t="inlineStr">
         <is>
           <t>Y</t>
@@ -11833,12 +11845,14 @@
       </c>
       <c r="N111" s="2" t="n"/>
       <c r="O111" s="32" t="n">
-        <v>-11.1</v>
+        <v>-7.1</v>
       </c>
       <c r="P111" s="32" t="n">
-        <v>8</v>
-      </c>
-      <c r="Q111" s="32" t="n"/>
+        <v>4.2</v>
+      </c>
+      <c r="Q111" s="32" t="n">
+        <v>-1.51</v>
+      </c>
       <c r="R111" s="23" t="inlineStr">
         <is>
           <t>Y</t>
@@ -11943,10 +11957,10 @@
       </c>
       <c r="N112" s="2" t="n"/>
       <c r="O112" s="32" t="n">
-        <v>-11.2</v>
+        <v>-8.6</v>
       </c>
       <c r="P112" s="32" t="n">
-        <v>9.199999999999999</v>
+        <v>12.7</v>
       </c>
       <c r="Q112" s="32" t="n"/>
       <c r="R112" s="23" t="inlineStr">
@@ -12049,10 +12063,10 @@
       </c>
       <c r="N113" s="2" t="n"/>
       <c r="O113" s="32" t="n">
-        <v>-3.1</v>
+        <v>-7.6</v>
       </c>
       <c r="P113" s="32" t="n">
-        <v>5.8</v>
+        <v>10.1</v>
       </c>
       <c r="Q113" s="32" t="n"/>
       <c r="R113" s="23" t="inlineStr">
@@ -12163,10 +12177,10 @@
         </is>
       </c>
       <c r="O114" s="32" t="n">
-        <v>-6.9</v>
+        <v>-15.5</v>
       </c>
       <c r="P114" s="32" t="n">
-        <v>-0.3</v>
+        <v>7.6</v>
       </c>
       <c r="Q114" s="32" t="n"/>
       <c r="R114" s="23" t="inlineStr">
@@ -12285,10 +12299,10 @@
         </is>
       </c>
       <c r="O115" s="32" t="n">
-        <v>-12.4</v>
+        <v>-13.2</v>
       </c>
       <c r="P115" s="32" t="n">
-        <v>0.5</v>
+        <v>7.9</v>
       </c>
       <c r="Q115" s="32" t="n"/>
       <c r="R115" s="23" t="inlineStr">
@@ -12403,12 +12417,14 @@
       </c>
       <c r="N116" s="2" t="n"/>
       <c r="O116" s="32" t="n">
-        <v>-5.1</v>
+        <v>-1.7</v>
       </c>
       <c r="P116" s="32" t="n">
-        <v>13</v>
-      </c>
-      <c r="Q116" s="32" t="n"/>
+        <v>17.3</v>
+      </c>
+      <c r="Q116" s="32" t="n">
+        <v>8.890000000000001</v>
+      </c>
       <c r="R116" s="23" t="inlineStr">
         <is>
           <t>Y</t>
@@ -12513,10 +12529,10 @@
       </c>
       <c r="N117" s="2" t="n"/>
       <c r="O117" s="32" t="n">
-        <v>-2.5</v>
+        <v>-0.3</v>
       </c>
       <c r="P117" s="32" t="n">
-        <v>9.9</v>
+        <v>17.6</v>
       </c>
       <c r="Q117" s="32" t="n"/>
       <c r="R117" s="23" t="inlineStr">
@@ -12627,10 +12643,10 @@
         </is>
       </c>
       <c r="O118" s="32" t="n">
-        <v>-2.3</v>
+        <v>-1.5</v>
       </c>
       <c r="P118" s="32" t="n">
-        <v>13.2</v>
+        <v>20.3</v>
       </c>
       <c r="Q118" s="32" t="n"/>
       <c r="R118" s="23" t="inlineStr">
@@ -12745,12 +12761,14 @@
       </c>
       <c r="N119" s="2" t="n"/>
       <c r="O119" s="32" t="n">
-        <v>3.2</v>
+        <v>2.7</v>
       </c>
       <c r="P119" s="32" t="n">
-        <v>16.2</v>
-      </c>
-      <c r="Q119" s="32" t="n"/>
+        <v>22.3</v>
+      </c>
+      <c r="Q119" s="32" t="n">
+        <v>12.4</v>
+      </c>
       <c r="R119" s="23" t="inlineStr">
         <is>
           <t>Y</t>
@@ -12977,12 +12995,14 @@
       </c>
       <c r="N121" s="2" t="n"/>
       <c r="O121" s="32" t="n">
-        <v>6</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="P121" s="32" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="Q121" s="32" t="n"/>
+        <v>21</v>
+      </c>
+      <c r="Q121" s="32" t="n">
+        <v>14.78</v>
+      </c>
       <c r="R121" s="23" t="inlineStr">
         <is>
           <t>Y</t>
@@ -13099,10 +13119,10 @@
       </c>
       <c r="N122" s="2" t="n"/>
       <c r="O122" s="32" t="n">
-        <v>-9.5</v>
+        <v>-4.8</v>
       </c>
       <c r="P122" s="32" t="n">
-        <v>10.6</v>
+        <v>16.4</v>
       </c>
       <c r="Q122" s="32" t="n"/>
       <c r="R122" s="23" t="inlineStr">
@@ -13323,12 +13343,14 @@
       </c>
       <c r="N124" s="2" t="n"/>
       <c r="O124" s="32" t="n">
-        <v>-0.7</v>
+        <v>-3.7</v>
       </c>
       <c r="P124" s="32" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="Q124" s="32" t="n"/>
+        <v>18.5</v>
+      </c>
+      <c r="Q124" s="32" t="n">
+        <v>6.75</v>
+      </c>
       <c r="R124" s="23" t="inlineStr">
         <is>
           <t>Y</t>
@@ -13445,12 +13467,14 @@
       </c>
       <c r="N125" s="2" t="n"/>
       <c r="O125" s="32" t="n">
-        <v>8.5</v>
+        <v>5.1</v>
       </c>
       <c r="P125" s="32" t="n">
-        <v>18.2</v>
-      </c>
-      <c r="Q125" s="32" t="n"/>
+        <v>17.7</v>
+      </c>
+      <c r="Q125" s="32" t="n">
+        <v>12.85</v>
+      </c>
       <c r="R125" s="23" t="inlineStr">
         <is>
           <t>Y</t>
@@ -13547,10 +13571,10 @@
       </c>
       <c r="N126" s="2" t="n"/>
       <c r="O126" s="32" t="n">
-        <v>9.6</v>
+        <v>6.6</v>
       </c>
       <c r="P126" s="32" t="n">
-        <v>16.7</v>
+        <v>18.3</v>
       </c>
       <c r="Q126" s="32" t="n"/>
       <c r="R126" s="23" t="inlineStr">
@@ -13657,12 +13681,14 @@
       </c>
       <c r="N127" s="2" t="n"/>
       <c r="O127" s="32" t="n">
-        <v>3.9</v>
+        <v>3.2</v>
       </c>
       <c r="P127" s="32" t="n">
-        <v>13.8</v>
-      </c>
-      <c r="Q127" s="32" t="n"/>
+        <v>23</v>
+      </c>
+      <c r="Q127" s="32" t="n">
+        <v>13.19</v>
+      </c>
       <c r="R127" s="23" t="inlineStr">
         <is>
           <t>Y</t>
@@ -13775,10 +13801,10 @@
       </c>
       <c r="N128" s="2" t="n"/>
       <c r="O128" s="32" t="n">
-        <v>10.5</v>
+        <v>7</v>
       </c>
       <c r="P128" s="32" t="n">
-        <v>18.2</v>
+        <v>19.8</v>
       </c>
       <c r="Q128" s="32" t="n"/>
       <c r="R128" s="23" t="inlineStr">
@@ -13885,12 +13911,14 @@
       </c>
       <c r="N129" s="2" t="n"/>
       <c r="O129" s="32" t="n">
-        <v>8.199999999999999</v>
+        <v>0.4</v>
       </c>
       <c r="P129" s="32" t="n">
-        <v>15</v>
-      </c>
-      <c r="Q129" s="32" t="n"/>
+        <v>21.8</v>
+      </c>
+      <c r="Q129" s="32" t="n">
+        <v>12.3</v>
+      </c>
       <c r="R129" s="23" t="inlineStr">
         <is>
           <t>Y</t>
@@ -14003,12 +14031,14 @@
       </c>
       <c r="N130" s="2" t="n"/>
       <c r="O130" s="32" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="P130" s="32" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="Q130" s="32" t="n"/>
+        <v>19</v>
+      </c>
+      <c r="Q130" s="32" t="n">
+        <v>9.74</v>
+      </c>
       <c r="R130" s="23" t="inlineStr">
         <is>
           <t>Y</t>
@@ -14121,12 +14151,14 @@
       </c>
       <c r="N131" s="2" t="n"/>
       <c r="O131" s="32" t="n">
-        <v>9.300000000000001</v>
+        <v>7</v>
       </c>
       <c r="P131" s="32" t="n">
-        <v>16.9</v>
-      </c>
-      <c r="Q131" s="32" t="n"/>
+        <v>20.4</v>
+      </c>
+      <c r="Q131" s="32" t="n">
+        <v>14.38</v>
+      </c>
       <c r="R131" s="23" t="inlineStr">
         <is>
           <t>Y</t>
@@ -14235,12 +14267,14 @@
       </c>
       <c r="N132" s="2" t="n"/>
       <c r="O132" s="32" t="n">
-        <v>12.9</v>
+        <v>13.8</v>
       </c>
       <c r="P132" s="32" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="Q132" s="32" t="n"/>
+        <v>24.3</v>
+      </c>
+      <c r="Q132" s="32" t="n">
+        <v>18.88</v>
+      </c>
       <c r="R132" s="23" t="inlineStr">
         <is>
           <t>Y</t>
@@ -14349,12 +14383,14 @@
       </c>
       <c r="N133" s="2" t="n"/>
       <c r="O133" s="32" t="n">
-        <v>10.9</v>
+        <v>8.4</v>
       </c>
       <c r="P133" s="32" t="n">
-        <v>18.7</v>
-      </c>
-      <c r="Q133" s="32" t="n"/>
+        <v>22.3</v>
+      </c>
+      <c r="Q133" s="32" t="n">
+        <v>15.15</v>
+      </c>
       <c r="R133" s="23" t="inlineStr">
         <is>
           <t>Y</t>
@@ -14569,12 +14605,14 @@
       </c>
       <c r="N135" s="2" t="n"/>
       <c r="O135" s="32" t="n">
-        <v>14.3</v>
+        <v>12.1</v>
       </c>
       <c r="P135" s="32" t="n">
-        <v>17</v>
-      </c>
-      <c r="Q135" s="32" t="n"/>
+        <v>27</v>
+      </c>
+      <c r="Q135" s="32" t="n">
+        <v>18.35</v>
+      </c>
       <c r="R135" s="23" t="inlineStr">
         <is>
           <t>Y</t>
@@ -14683,12 +14721,14 @@
       </c>
       <c r="N136" s="2" t="n"/>
       <c r="O136" s="32" t="n">
-        <v>18</v>
+        <v>13.4</v>
       </c>
       <c r="P136" s="32" t="n">
-        <v>22.1</v>
-      </c>
-      <c r="Q136" s="32" t="n"/>
+        <v>23.2</v>
+      </c>
+      <c r="Q136" s="32" t="n">
+        <v>16.89</v>
+      </c>
       <c r="R136" s="23" t="inlineStr">
         <is>
           <t>Y</t>
@@ -14797,12 +14837,14 @@
       </c>
       <c r="N137" s="2" t="n"/>
       <c r="O137" s="32" t="n">
-        <v>15.3</v>
+        <v>11.6</v>
       </c>
       <c r="P137" s="32" t="n">
-        <v>18</v>
-      </c>
-      <c r="Q137" s="32" t="n"/>
+        <v>26.7</v>
+      </c>
+      <c r="Q137" s="32" t="n">
+        <v>18.8</v>
+      </c>
       <c r="R137" s="23" t="inlineStr">
         <is>
           <t>Y</t>
@@ -14911,10 +14953,10 @@
       </c>
       <c r="N138" s="2" t="n"/>
       <c r="O138" s="32" t="n">
-        <v>12.9</v>
+        <v>11.3</v>
       </c>
       <c r="P138" s="32" t="n">
-        <v>20.5</v>
+        <v>24</v>
       </c>
       <c r="Q138" s="32" t="n"/>
       <c r="R138" s="23" t="inlineStr">
@@ -15028,9 +15070,11 @@
         <v>13.4</v>
       </c>
       <c r="P139" s="32" t="n">
-        <v>21.3</v>
-      </c>
-      <c r="Q139" s="32" t="n"/>
+        <v>24</v>
+      </c>
+      <c r="Q139" s="32" t="n">
+        <v>18.24</v>
+      </c>
       <c r="R139" s="23" t="inlineStr">
         <is>
           <t>Y</t>
@@ -15139,12 +15183,14 @@
       </c>
       <c r="N140" s="2" t="n"/>
       <c r="O140" s="32" t="n">
-        <v>16.7</v>
+        <v>13.2</v>
       </c>
       <c r="P140" s="32" t="n">
-        <v>24.8</v>
-      </c>
-      <c r="Q140" s="32" t="n"/>
+        <v>24</v>
+      </c>
+      <c r="Q140" s="32" t="n">
+        <v>18.96</v>
+      </c>
       <c r="R140" s="23" t="inlineStr">
         <is>
           <t>Y</t>
@@ -15355,12 +15401,14 @@
       </c>
       <c r="N142" s="2" t="n"/>
       <c r="O142" s="32" t="n">
-        <v>16.7</v>
+        <v>17.5</v>
       </c>
       <c r="P142" s="32" t="n">
-        <v>26.2</v>
-      </c>
-      <c r="Q142" s="32" t="n"/>
+        <v>27.9</v>
+      </c>
+      <c r="Q142" s="32" t="n">
+        <v>21.47</v>
+      </c>
       <c r="R142" s="23" t="inlineStr">
         <is>
           <t>Y</t>
@@ -15469,12 +15517,14 @@
       </c>
       <c r="N143" s="2" t="n"/>
       <c r="O143" s="32" t="n">
-        <v>18.5</v>
+        <v>21.1</v>
       </c>
       <c r="P143" s="32" t="n">
-        <v>23.6</v>
-      </c>
-      <c r="Q143" s="32" t="n"/>
+        <v>26.3</v>
+      </c>
+      <c r="Q143" s="32" t="n">
+        <v>22.93</v>
+      </c>
       <c r="R143" s="23" t="inlineStr">
         <is>
           <t>Y</t>
@@ -15783,12 +15833,14 @@
       </c>
       <c r="N146" s="2" t="n"/>
       <c r="O146" s="32" t="n">
-        <v>26.6</v>
+        <v>25</v>
       </c>
       <c r="P146" s="32" t="n">
-        <v>32.4</v>
-      </c>
-      <c r="Q146" s="32" t="n"/>
+        <v>30.6</v>
+      </c>
+      <c r="Q146" s="32" t="n">
+        <v>27.93</v>
+      </c>
       <c r="R146" s="23" t="inlineStr">
         <is>
           <t>Y</t>
@@ -15889,12 +15941,14 @@
       </c>
       <c r="N147" s="2" t="n"/>
       <c r="O147" s="32" t="n">
-        <v>18.8</v>
+        <v>20.9</v>
       </c>
       <c r="P147" s="32" t="n">
-        <v>30.7</v>
-      </c>
-      <c r="Q147" s="32" t="n"/>
+        <v>30.9</v>
+      </c>
+      <c r="Q147" s="32" t="n">
+        <v>25.79</v>
+      </c>
       <c r="R147" s="23" t="inlineStr">
         <is>
           <t>Y</t>
@@ -16105,12 +16159,14 @@
       </c>
       <c r="N149" s="2" t="n"/>
       <c r="O149" s="32" t="n">
-        <v>10.4</v>
+        <v>10.9</v>
       </c>
       <c r="P149" s="32" t="n">
-        <v>22.7</v>
-      </c>
-      <c r="Q149" s="32" t="n"/>
+        <v>26</v>
+      </c>
+      <c r="Q149" s="32" t="n">
+        <v>17.69</v>
+      </c>
       <c r="R149" s="23" t="inlineStr">
         <is>
           <t>Y</t>
@@ -16222,9 +16278,11 @@
         <v>12.7</v>
       </c>
       <c r="P150" s="32" t="n">
-        <v>22.9</v>
-      </c>
-      <c r="Q150" s="32" t="n"/>
+        <v>25.1</v>
+      </c>
+      <c r="Q150" s="32" t="n">
+        <v>18</v>
+      </c>
       <c r="R150" s="23" t="inlineStr">
         <is>
           <t>Y</t>
@@ -16333,12 +16391,14 @@
       </c>
       <c r="N151" s="2" t="n"/>
       <c r="O151" s="32" t="n">
-        <v>15.8</v>
+        <v>16.1</v>
       </c>
       <c r="P151" s="32" t="n">
-        <v>22.7</v>
-      </c>
-      <c r="Q151" s="32" t="n"/>
+        <v>30</v>
+      </c>
+      <c r="Q151" s="32" t="n">
+        <v>22.11</v>
+      </c>
       <c r="R151" s="23" t="inlineStr">
         <is>
           <t>Y</t>
@@ -16537,12 +16597,14 @@
       </c>
       <c r="N153" s="2" t="n"/>
       <c r="O153" s="32" t="n">
-        <v>12.4</v>
+        <v>11.4</v>
       </c>
       <c r="P153" s="32" t="n">
-        <v>16.6</v>
-      </c>
-      <c r="Q153" s="32" t="n"/>
+        <v>27.4</v>
+      </c>
+      <c r="Q153" s="32" t="n">
+        <v>18.95</v>
+      </c>
       <c r="R153" s="23" t="inlineStr">
         <is>
           <t>Y</t>
@@ -16655,13 +16717,13 @@
       </c>
       <c r="N154" s="2" t="n"/>
       <c r="O154" s="32" t="n">
-        <v>2.6</v>
+        <v>4.6</v>
       </c>
       <c r="P154" s="32" t="n">
-        <v>17.2</v>
+        <v>20.6</v>
       </c>
       <c r="Q154" s="32" t="n">
-        <v>9.529999999999999</v>
+        <v>12.09</v>
       </c>
       <c r="R154" s="23" t="inlineStr">
         <is>
@@ -16857,10 +16919,10 @@
       </c>
       <c r="N156" s="2" t="n"/>
       <c r="O156" s="32" t="n">
-        <v>-2.3</v>
+        <v>-8.1</v>
       </c>
       <c r="P156" s="32" t="n">
-        <v>8.800000000000001</v>
+        <v>17</v>
       </c>
       <c r="Q156" s="32" t="n"/>
       <c r="R156" s="23" t="inlineStr">
@@ -16966,7 +17028,7 @@
         <v>15.5</v>
       </c>
       <c r="P157" s="32" t="n">
-        <v>22.2</v>
+        <v>22.9</v>
       </c>
       <c r="Q157" s="32" t="n"/>
       <c r="R157" s="23" t="inlineStr">
@@ -17351,10 +17413,10 @@
       </c>
       <c r="N161" s="2" t="n"/>
       <c r="O161" s="32" t="n">
-        <v>3.1</v>
+        <v>5.9</v>
       </c>
       <c r="P161" s="32" t="n">
-        <v>10.9</v>
+        <v>23</v>
       </c>
       <c r="Q161" s="32" t="n"/>
       <c r="R161" s="23" t="inlineStr">
@@ -17465,10 +17527,10 @@
         </is>
       </c>
       <c r="O162" s="32" t="n">
-        <v>-18.5</v>
+        <v>-17</v>
       </c>
       <c r="P162" s="32" t="n">
-        <v>8.5</v>
+        <v>6.1</v>
       </c>
       <c r="Q162" s="32" t="n"/>
       <c r="R162" s="23" t="inlineStr">
@@ -17791,10 +17853,10 @@
         </is>
       </c>
       <c r="O165" s="32" t="n">
-        <v>-16.8</v>
+        <v>-8.9</v>
       </c>
       <c r="P165" s="32" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="Q165" s="32" t="n"/>
       <c r="R165" s="23" t="inlineStr">
@@ -18010,12 +18072,8 @@
         </is>
       </c>
       <c r="N167" s="2" t="n"/>
-      <c r="O167" s="32" t="n">
-        <v>-20.5</v>
-      </c>
-      <c r="P167" s="32" t="n">
-        <v>6</v>
-      </c>
+      <c r="O167" s="32" t="n"/>
+      <c r="P167" s="32" t="n"/>
       <c r="Q167" s="32" t="n"/>
       <c r="R167" s="23" t="inlineStr">
         <is>
@@ -18340,12 +18398,8 @@
           <t>⚡</t>
         </is>
       </c>
-      <c r="O170" s="32" t="n">
-        <v>-19.4</v>
-      </c>
-      <c r="P170" s="32" t="n">
-        <v>2.4</v>
-      </c>
+      <c r="O170" s="32" t="n"/>
+      <c r="P170" s="32" t="n"/>
       <c r="Q170" s="32" t="n"/>
       <c r="R170" s="23" t="inlineStr">
         <is>
@@ -18450,12 +18504,8 @@
         </is>
       </c>
       <c r="N171" s="2" t="n"/>
-      <c r="O171" s="32" t="n">
-        <v>-9.199999999999999</v>
-      </c>
-      <c r="P171" s="32" t="n">
-        <v>-3.3</v>
-      </c>
+      <c r="O171" s="32" t="n"/>
+      <c r="P171" s="32" t="n"/>
       <c r="Q171" s="32" t="n"/>
       <c r="R171" s="23" t="inlineStr">
         <is>
@@ -18667,10 +18717,10 @@
       </c>
       <c r="N173" s="2" t="n"/>
       <c r="O173" s="32" t="n">
-        <v>-11.9</v>
+        <v>-12</v>
       </c>
       <c r="P173" s="32" t="n">
-        <v>8.300000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Q173" s="32" t="n"/>
       <c r="R173" s="23" t="inlineStr">
@@ -18989,10 +19039,10 @@
       </c>
       <c r="N176" s="2" t="n"/>
       <c r="O176" s="32" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="P176" s="32" t="n">
-        <v>10.3</v>
+        <v>11.7</v>
       </c>
       <c r="Q176" s="32" t="n"/>
       <c r="R176" s="23" t="inlineStr">
@@ -19091,10 +19141,10 @@
       </c>
       <c r="N177" s="2" t="n"/>
       <c r="O177" s="32" t="n">
-        <v>-11.9</v>
+        <v>-11.3</v>
       </c>
       <c r="P177" s="32" t="n">
-        <v>-5.7</v>
+        <v>-5</v>
       </c>
       <c r="Q177" s="32" t="n"/>
       <c r="R177" s="23" t="inlineStr">
@@ -21201,12 +21251,8 @@
         </is>
       </c>
       <c r="N199" s="2" t="n"/>
-      <c r="O199" s="32" t="n">
-        <v>-16.5</v>
-      </c>
-      <c r="P199" s="32" t="n">
-        <v>8.800000000000001</v>
-      </c>
+      <c r="O199" s="32" t="n"/>
+      <c r="P199" s="32" t="n"/>
       <c r="Q199" s="32" t="n"/>
       <c r="R199" s="23" t="inlineStr">
         <is>
@@ -22611,12 +22657,8 @@
         </is>
       </c>
       <c r="N213" s="2" t="n"/>
-      <c r="O213" s="32" t="n">
-        <v>-26.2</v>
-      </c>
-      <c r="P213" s="32" t="n">
-        <v>5</v>
-      </c>
+      <c r="O213" s="32" t="n"/>
+      <c r="P213" s="32" t="n"/>
       <c r="Q213" s="32" t="n"/>
       <c r="R213" s="23" t="inlineStr">
         <is>
@@ -26051,20 +26093,10 @@
           <t>⚡</t>
         </is>
       </c>
-      <c r="O248" s="32" t="n">
-        <v>-7.5</v>
-      </c>
-      <c r="P248" s="32" t="n">
-        <v>6</v>
-      </c>
-      <c r="Q248" s="32" t="n">
-        <v>-0.66</v>
-      </c>
-      <c r="R248" s="23" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="O248" s="32" t="n"/>
+      <c r="P248" s="32" t="n"/>
+      <c r="Q248" s="32" t="n"/>
+      <c r="R248" s="23" t="n"/>
       <c r="S248" s="37" t="n"/>
       <c r="T248" s="41" t="inlineStr">
         <is>
@@ -27720,10 +27752,10 @@
       </c>
       <c r="N265" s="2" t="n"/>
       <c r="O265" s="32" t="n">
-        <v>-58.6</v>
+        <v>-56.5</v>
       </c>
       <c r="P265" s="32" t="n">
-        <v>-48.1</v>
+        <v>-47.1</v>
       </c>
       <c r="Q265" s="32" t="n"/>
       <c r="R265" s="23" t="inlineStr">
@@ -29293,8 +29325,12 @@
         </is>
       </c>
       <c r="N282" s="2" t="n"/>
-      <c r="O282" s="32" t="n"/>
-      <c r="P282" s="32" t="n"/>
+      <c r="O282" s="32" t="n">
+        <v>-15.8</v>
+      </c>
+      <c r="P282" s="32" t="n">
+        <v>3.3</v>
+      </c>
       <c r="Q282" s="32" t="n"/>
       <c r="R282" s="23" t="inlineStr">
         <is>
@@ -30559,8 +30595,12 @@
         </is>
       </c>
       <c r="N295" s="2" t="n"/>
-      <c r="O295" s="32" t="n"/>
-      <c r="P295" s="32" t="n"/>
+      <c r="O295" s="32" t="n">
+        <v>-9.6</v>
+      </c>
+      <c r="P295" s="32" t="n">
+        <v>1.5</v>
+      </c>
       <c r="Q295" s="32" t="n"/>
       <c r="R295" s="23" t="inlineStr">
         <is>
@@ -34635,7 +34675,6 @@
       <c r="AH401" s="2" t="n"/>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1"/>
   <autoFilter ref="A1:AH401"/>
   <conditionalFormatting sqref="A2:N401 R2:AH401">
     <cfRule type="expression" priority="3" dxfId="1">

--- a/气象/For_Python_站点信息和记录.xlsx
+++ b/气象/For_Python_站点信息和记录.xlsx
@@ -22,7 +22,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy\ &quot;年&quot;\ m\ &quot;月&quot;\ d\ &quot;日&quot;"/>
   </numFmts>
-  <fonts count="16">
+  <fonts count="17">
     <font>
       <name val="等线"/>
       <charset val="134"/>
@@ -154,6 +154,13 @@
       <color theme="0"/>
       <sz val="11"/>
     </font>
+    <font>
+      <name val="Segoe UI Symbol"/>
+      <family val="3"/>
+      <b val="1"/>
+      <color theme="0"/>
+      <sz val="11"/>
+    </font>
   </fonts>
   <fills count="8">
     <fill>
@@ -228,7 +235,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -372,6 +379,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="7" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -796,8 +806,8 @@
     <col width="18.59765625" customWidth="1" style="8" min="25" max="25"/>
     <col width="12.59765625" customWidth="1" style="5" min="26" max="30"/>
     <col width="12.59765625" customWidth="1" style="8" min="31" max="32"/>
-    <col width="12.59765625" customWidth="1" style="5" min="33" max="359"/>
-    <col width="12.59765625" customWidth="1" style="5" min="360" max="16384"/>
+    <col width="12.59765625" customWidth="1" style="5" min="33" max="372"/>
+    <col width="12.59765625" customWidth="1" style="5" min="373" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="27.75" customFormat="1" customHeight="1" s="11">
@@ -972,7 +982,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="24" customHeight="1" s="48">
+    <row r="2" ht="24" customHeight="1" s="49">
       <c r="A2" s="2" t="n">
         <v>1</v>
       </c>
@@ -1020,13 +1030,13 @@
         </is>
       </c>
       <c r="O2" s="32" t="n">
-        <v>-3.6</v>
+        <v>1.9</v>
       </c>
       <c r="P2" s="32" t="n">
-        <v>14.6</v>
+        <v>12.8</v>
       </c>
       <c r="Q2" s="32" t="n">
-        <v>5.55</v>
+        <v>7</v>
       </c>
       <c r="R2" s="23" t="inlineStr">
         <is>
@@ -1086,7 +1096,7 @@
       </c>
       <c r="AH2" s="2" t="n"/>
     </row>
-    <row r="3" ht="24" customHeight="1" s="48">
+    <row r="3" ht="24" customHeight="1" s="49">
       <c r="A3" s="2" t="n">
         <v>2</v>
       </c>
@@ -1126,10 +1136,10 @@
         </is>
       </c>
       <c r="O3" s="32" t="n">
-        <v>-2.2</v>
+        <v>3.3</v>
       </c>
       <c r="P3" s="32" t="n">
-        <v>12</v>
+        <v>12.7</v>
       </c>
       <c r="Q3" s="32" t="n"/>
       <c r="R3" s="23" t="n"/>
@@ -1190,7 +1200,7 @@
       </c>
       <c r="AH3" s="2" t="n"/>
     </row>
-    <row r="4" ht="24" customHeight="1" s="48">
+    <row r="4" ht="24" customHeight="1" s="49">
       <c r="A4" s="2" t="n">
         <v>3</v>
       </c>
@@ -1230,10 +1240,10 @@
         </is>
       </c>
       <c r="O4" s="32" t="n">
-        <v>-1.9</v>
+        <v>2.4</v>
       </c>
       <c r="P4" s="32" t="n">
-        <v>8.6</v>
+        <v>12</v>
       </c>
       <c r="Q4" s="32" t="n"/>
       <c r="R4" s="23" t="n"/>
@@ -1290,7 +1300,7 @@
       </c>
       <c r="AH4" s="2" t="n"/>
     </row>
-    <row r="5" ht="24" customHeight="1" s="48">
+    <row r="5" ht="24" customHeight="1" s="49">
       <c r="A5" s="2" t="n">
         <v>4</v>
       </c>
@@ -1382,7 +1392,7 @@
       </c>
       <c r="AH5" s="2" t="n"/>
     </row>
-    <row r="6" ht="24" customHeight="1" s="48">
+    <row r="6" ht="24" customHeight="1" s="49">
       <c r="A6" s="2" t="n">
         <v>5</v>
       </c>
@@ -1422,10 +1432,10 @@
         </is>
       </c>
       <c r="O6" s="32" t="n">
-        <v>-3.7</v>
+        <v>0.6</v>
       </c>
       <c r="P6" s="32" t="n">
-        <v>6.8</v>
+        <v>10.5</v>
       </c>
       <c r="Q6" s="32" t="n"/>
       <c r="R6" s="23" t="n"/>
@@ -1482,7 +1492,7 @@
       </c>
       <c r="AH6" s="2" t="n"/>
     </row>
-    <row r="7" ht="24" customHeight="1" s="48">
+    <row r="7" ht="24" customHeight="1" s="49">
       <c r="A7" s="2" t="n">
         <v>6</v>
       </c>
@@ -1522,10 +1532,10 @@
         </is>
       </c>
       <c r="O7" s="32" t="n">
-        <v>-4.8</v>
+        <v>-5</v>
       </c>
       <c r="P7" s="32" t="n">
-        <v>0.8</v>
+        <v>2.6</v>
       </c>
       <c r="Q7" s="32" t="n"/>
       <c r="R7" s="23" t="n"/>
@@ -1582,7 +1592,7 @@
       </c>
       <c r="AH7" s="2" t="n"/>
     </row>
-    <row r="8" ht="24" customHeight="1" s="48">
+    <row r="8" ht="24" customHeight="1" s="49">
       <c r="A8" s="2" t="n">
         <v>7</v>
       </c>
@@ -1630,13 +1640,13 @@
       </c>
       <c r="N8" s="2" t="n"/>
       <c r="O8" s="32" t="n">
-        <v>-1.7</v>
+        <v>-2.3</v>
       </c>
       <c r="P8" s="32" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="Q8" s="32" t="n">
-        <v>1.52</v>
+        <v>1.36</v>
       </c>
       <c r="R8" s="23" t="inlineStr">
         <is>
@@ -1696,7 +1706,7 @@
       </c>
       <c r="AH8" s="2" t="n"/>
     </row>
-    <row r="9" ht="24" customHeight="1" s="48">
+    <row r="9" ht="24" customHeight="1" s="49">
       <c r="A9" s="2" t="n">
         <v>8</v>
       </c>
@@ -1742,13 +1752,13 @@
       </c>
       <c r="N9" s="2" t="n"/>
       <c r="O9" s="32" t="n">
-        <v>-0.8</v>
+        <v>6</v>
       </c>
       <c r="P9" s="32" t="n">
-        <v>16.4</v>
+        <v>13.1</v>
       </c>
       <c r="Q9" s="32" t="n">
-        <v>7.56</v>
+        <v>9.16</v>
       </c>
       <c r="R9" s="23" t="inlineStr">
         <is>
@@ -1812,7 +1822,7 @@
       </c>
       <c r="AH9" s="2" t="n"/>
     </row>
-    <row r="10" ht="24" customHeight="1" s="48">
+    <row r="10" ht="24" customHeight="1" s="49">
       <c r="A10" s="2" t="n">
         <v>9</v>
       </c>
@@ -1862,13 +1872,13 @@
         </is>
       </c>
       <c r="O10" s="32" t="n">
-        <v>0.2</v>
+        <v>0.9</v>
       </c>
       <c r="P10" s="32" t="n">
-        <v>6.6</v>
+        <v>10.8</v>
       </c>
       <c r="Q10" s="32" t="n">
-        <v>3.02</v>
+        <v>4.41</v>
       </c>
       <c r="R10" s="23" t="inlineStr">
         <is>
@@ -1928,7 +1938,7 @@
       </c>
       <c r="AH10" s="2" t="n"/>
     </row>
-    <row r="11" ht="24" customHeight="1" s="48">
+    <row r="11" ht="24" customHeight="1" s="49">
       <c r="A11" s="2" t="n">
         <v>10</v>
       </c>
@@ -1978,13 +1988,13 @@
         </is>
       </c>
       <c r="O11" s="32" t="n">
-        <v>-3</v>
+        <v>-0.3</v>
       </c>
       <c r="P11" s="32" t="n">
-        <v>5.8</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="Q11" s="32" t="n">
-        <v>2.17</v>
+        <v>4.15</v>
       </c>
       <c r="R11" s="23" t="inlineStr">
         <is>
@@ -2044,7 +2054,7 @@
       </c>
       <c r="AH11" s="2" t="n"/>
     </row>
-    <row r="12" ht="24" customHeight="1" s="48">
+    <row r="12" ht="24" customHeight="1" s="49">
       <c r="A12" s="2" t="n">
         <v>11</v>
       </c>
@@ -2090,13 +2100,13 @@
       </c>
       <c r="N12" s="2" t="n"/>
       <c r="O12" s="32" t="n">
-        <v>-1.3</v>
+        <v>1</v>
       </c>
       <c r="P12" s="32" t="n">
-        <v>5.6</v>
+        <v>12.4</v>
       </c>
       <c r="Q12" s="32" t="n">
-        <v>2.49</v>
+        <v>5.25</v>
       </c>
       <c r="R12" s="23" t="inlineStr">
         <is>
@@ -2156,7 +2166,7 @@
       </c>
       <c r="AH12" s="2" t="n"/>
     </row>
-    <row r="13" ht="24" customHeight="1" s="48">
+    <row r="13" ht="24" customHeight="1" s="49">
       <c r="A13" s="2" t="n">
         <v>12</v>
       </c>
@@ -2206,13 +2216,13 @@
         </is>
       </c>
       <c r="O13" s="32" t="n">
-        <v>-6.3</v>
+        <v>-4.6</v>
       </c>
       <c r="P13" s="32" t="n">
-        <v>0.1</v>
+        <v>3</v>
       </c>
       <c r="Q13" s="32" t="n">
-        <v>-2.75</v>
+        <v>-1.49</v>
       </c>
       <c r="R13" s="23" t="inlineStr">
         <is>
@@ -2272,7 +2282,7 @@
       </c>
       <c r="AH13" s="2" t="n"/>
     </row>
-    <row r="14" ht="24" customHeight="1" s="48">
+    <row r="14" ht="24" customHeight="1" s="49">
       <c r="A14" s="2" t="n">
         <v>13</v>
       </c>
@@ -2318,13 +2328,13 @@
       </c>
       <c r="N14" s="2" t="n"/>
       <c r="O14" s="32" t="n">
-        <v>-4.7</v>
+        <v>-1.8</v>
       </c>
       <c r="P14" s="32" t="n">
-        <v>2.9</v>
+        <v>12.5</v>
       </c>
       <c r="Q14" s="32" t="n">
-        <v>-0.1</v>
+        <v>4.27</v>
       </c>
       <c r="R14" s="23" t="inlineStr">
         <is>
@@ -2388,7 +2398,7 @@
       </c>
       <c r="AH14" s="2" t="n"/>
     </row>
-    <row r="15" ht="24" customHeight="1" s="48">
+    <row r="15" ht="24" customHeight="1" s="49">
       <c r="A15" s="2" t="n">
         <v>14</v>
       </c>
@@ -2476,7 +2486,7 @@
       </c>
       <c r="AH15" s="2" t="n"/>
     </row>
-    <row r="16" ht="24" customHeight="1" s="48">
+    <row r="16" ht="24" customHeight="1" s="49">
       <c r="A16" s="2" t="n">
         <v>15</v>
       </c>
@@ -2576,7 +2586,7 @@
       </c>
       <c r="AH16" s="2" t="n"/>
     </row>
-    <row r="17" ht="24" customHeight="1" s="48">
+    <row r="17" ht="24" customHeight="1" s="49">
       <c r="A17" s="2" t="n">
         <v>16</v>
       </c>
@@ -2668,7 +2678,7 @@
       </c>
       <c r="AH17" s="2" t="n"/>
     </row>
-    <row r="18" ht="24" customHeight="1" s="48">
+    <row r="18" ht="24" customHeight="1" s="49">
       <c r="A18" s="2" t="n">
         <v>17</v>
       </c>
@@ -2756,7 +2766,7 @@
       </c>
       <c r="AH18" s="2" t="n"/>
     </row>
-    <row r="19" ht="24" customHeight="1" s="48">
+    <row r="19" ht="24" customHeight="1" s="49">
       <c r="A19" s="2" t="n">
         <v>18</v>
       </c>
@@ -2856,7 +2866,7 @@
       </c>
       <c r="AH19" s="2" t="n"/>
     </row>
-    <row r="20" ht="24" customHeight="1" s="48">
+    <row r="20" ht="24" customHeight="1" s="49">
       <c r="A20" s="2" t="n">
         <v>19</v>
       </c>
@@ -2956,7 +2966,7 @@
       </c>
       <c r="AH20" s="2" t="n"/>
     </row>
-    <row r="21" ht="24" customHeight="1" s="48">
+    <row r="21" ht="24" customHeight="1" s="49">
       <c r="A21" s="2" t="n">
         <v>20</v>
       </c>
@@ -3044,7 +3054,7 @@
       </c>
       <c r="AH21" s="2" t="n"/>
     </row>
-    <row r="22" ht="24" customHeight="1" s="48">
+    <row r="22" ht="24" customHeight="1" s="49">
       <c r="A22" s="2" t="n">
         <v>21</v>
       </c>
@@ -3132,7 +3142,7 @@
       </c>
       <c r="AH22" s="2" t="n"/>
     </row>
-    <row r="23" ht="24" customHeight="1" s="48">
+    <row r="23" ht="24" customHeight="1" s="49">
       <c r="A23" s="2" t="n">
         <v>22</v>
       </c>
@@ -3220,7 +3230,7 @@
       </c>
       <c r="AH23" s="2" t="n"/>
     </row>
-    <row r="24" ht="24" customHeight="1" s="48">
+    <row r="24" ht="24" customHeight="1" s="49">
       <c r="A24" s="2" t="n">
         <v>23</v>
       </c>
@@ -3320,7 +3330,7 @@
       </c>
       <c r="AH24" s="2" t="n"/>
     </row>
-    <row r="25" ht="24" customHeight="1" s="48">
+    <row r="25" ht="24" customHeight="1" s="49">
       <c r="A25" s="2" t="n">
         <v>24</v>
       </c>
@@ -3408,7 +3418,7 @@
       </c>
       <c r="AH25" s="2" t="n"/>
     </row>
-    <row r="26" ht="24" customHeight="1" s="48">
+    <row r="26" ht="24" customHeight="1" s="49">
       <c r="A26" s="2" t="n">
         <v>25</v>
       </c>
@@ -3496,7 +3506,7 @@
       </c>
       <c r="AH26" s="2" t="n"/>
     </row>
-    <row r="27" ht="24" customHeight="1" s="48">
+    <row r="27" ht="24" customHeight="1" s="49">
       <c r="A27" s="2" t="n">
         <v>26</v>
       </c>
@@ -3600,7 +3610,7 @@
       </c>
       <c r="AH27" s="2" t="n"/>
     </row>
-    <row r="28" ht="24" customHeight="1" s="48">
+    <row r="28" ht="24" customHeight="1" s="49">
       <c r="A28" s="2" t="n">
         <v>27</v>
       </c>
@@ -3684,7 +3694,7 @@
       <c r="AG28" s="2" t="n"/>
       <c r="AH28" s="2" t="n"/>
     </row>
-    <row r="29" ht="24" customHeight="1" s="48">
+    <row r="29" ht="24" customHeight="1" s="49">
       <c r="A29" s="2" t="n">
         <v>28</v>
       </c>
@@ -3772,7 +3782,7 @@
       </c>
       <c r="AH29" s="2" t="n"/>
     </row>
-    <row r="30" ht="24" customHeight="1" s="48">
+    <row r="30" ht="24" customHeight="1" s="49">
       <c r="A30" s="2" t="n">
         <v>29</v>
       </c>
@@ -3860,7 +3870,7 @@
       </c>
       <c r="AH30" s="2" t="n"/>
     </row>
-    <row r="31" ht="24" customHeight="1" s="48">
+    <row r="31" ht="24" customHeight="1" s="49">
       <c r="A31" s="2" t="n">
         <v>30</v>
       </c>
@@ -3948,7 +3958,7 @@
       </c>
       <c r="AH31" s="2" t="n"/>
     </row>
-    <row r="32" ht="24" customHeight="1" s="48">
+    <row r="32" ht="24" customHeight="1" s="49">
       <c r="A32" s="2" t="n">
         <v>31</v>
       </c>
@@ -4048,7 +4058,7 @@
       </c>
       <c r="AH32" s="2" t="n"/>
     </row>
-    <row r="33" ht="24" customHeight="1" s="48">
+    <row r="33" ht="24" customHeight="1" s="49">
       <c r="A33" s="2" t="n">
         <v>32</v>
       </c>
@@ -4148,7 +4158,7 @@
       <c r="AG33" s="2" t="n"/>
       <c r="AH33" s="2" t="n"/>
     </row>
-    <row r="34" ht="24" customHeight="1" s="48">
+    <row r="34" ht="24" customHeight="1" s="49">
       <c r="A34" s="2" t="n">
         <v>33</v>
       </c>
@@ -4232,7 +4242,7 @@
       <c r="AG34" s="2" t="n"/>
       <c r="AH34" s="2" t="n"/>
     </row>
-    <row r="35" ht="24" customHeight="1" s="48">
+    <row r="35" ht="24" customHeight="1" s="49">
       <c r="A35" s="2" t="n">
         <v>34</v>
       </c>
@@ -4320,7 +4330,7 @@
       </c>
       <c r="AH35" s="2" t="n"/>
     </row>
-    <row r="36" ht="24" customHeight="1" s="48">
+    <row r="36" ht="24" customHeight="1" s="49">
       <c r="A36" s="2" t="n">
         <v>35</v>
       </c>
@@ -4408,7 +4418,7 @@
       </c>
       <c r="AH36" s="2" t="n"/>
     </row>
-    <row r="37" ht="24" customHeight="1" s="48">
+    <row r="37" ht="24" customHeight="1" s="49">
       <c r="A37" s="2" t="n">
         <v>36</v>
       </c>
@@ -4496,7 +4506,7 @@
       </c>
       <c r="AH37" s="2" t="n"/>
     </row>
-    <row r="38" ht="24" customHeight="1" s="48">
+    <row r="38" ht="24" customHeight="1" s="49">
       <c r="A38" s="2" t="n">
         <v>37</v>
       </c>
@@ -4584,7 +4594,7 @@
       </c>
       <c r="AH38" s="2" t="n"/>
     </row>
-    <row r="39" ht="24" customHeight="1" s="48">
+    <row r="39" ht="24" customHeight="1" s="49">
       <c r="A39" s="2" t="n">
         <v>38</v>
       </c>
@@ -4668,7 +4678,7 @@
       <c r="AG39" s="2" t="n"/>
       <c r="AH39" s="2" t="n"/>
     </row>
-    <row r="40" ht="24" customHeight="1" s="48">
+    <row r="40" ht="24" customHeight="1" s="49">
       <c r="A40" s="2" t="n">
         <v>39</v>
       </c>
@@ -4756,7 +4766,7 @@
       </c>
       <c r="AH40" s="2" t="n"/>
     </row>
-    <row r="41" ht="24" customHeight="1" s="48">
+    <row r="41" ht="24" customHeight="1" s="49">
       <c r="A41" s="2" t="n">
         <v>40</v>
       </c>
@@ -4840,7 +4850,7 @@
       <c r="AG41" s="2" t="n"/>
       <c r="AH41" s="2" t="n"/>
     </row>
-    <row r="42" ht="24" customHeight="1" s="48">
+    <row r="42" ht="24" customHeight="1" s="49">
       <c r="A42" s="2" t="n">
         <v>41</v>
       </c>
@@ -4928,7 +4938,7 @@
       </c>
       <c r="AH42" s="2" t="n"/>
     </row>
-    <row r="43" ht="24" customHeight="1" s="48">
+    <row r="43" ht="24" customHeight="1" s="49">
       <c r="A43" s="2" t="n">
         <v>42</v>
       </c>
@@ -5020,7 +5030,7 @@
       </c>
       <c r="AH43" s="2" t="n"/>
     </row>
-    <row r="44" ht="24" customHeight="1" s="48">
+    <row r="44" ht="24" customHeight="1" s="49">
       <c r="A44" s="2" t="n">
         <v>43</v>
       </c>
@@ -5108,7 +5118,7 @@
       </c>
       <c r="AH44" s="2" t="n"/>
     </row>
-    <row r="45" ht="24" customHeight="1" s="48">
+    <row r="45" ht="24" customHeight="1" s="49">
       <c r="A45" s="2" t="n">
         <v>44</v>
       </c>
@@ -5208,7 +5218,7 @@
       </c>
       <c r="AH45" s="2" t="n"/>
     </row>
-    <row r="46" ht="24" customHeight="1" s="48">
+    <row r="46" ht="24" customHeight="1" s="49">
       <c r="A46" s="2" t="n">
         <v>45</v>
       </c>
@@ -5296,7 +5306,7 @@
       </c>
       <c r="AH46" s="2" t="n"/>
     </row>
-    <row r="47" ht="24" customHeight="1" s="48">
+    <row r="47" ht="24" customHeight="1" s="49">
       <c r="A47" s="2" t="n">
         <v>46</v>
       </c>
@@ -5384,7 +5394,7 @@
       </c>
       <c r="AH47" s="2" t="n"/>
     </row>
-    <row r="48" ht="24" customHeight="1" s="48">
+    <row r="48" ht="24" customHeight="1" s="49">
       <c r="A48" s="2" t="n">
         <v>47</v>
       </c>
@@ -5484,7 +5494,7 @@
       </c>
       <c r="AH48" s="2" t="n"/>
     </row>
-    <row r="49" ht="24" customHeight="1" s="48">
+    <row r="49" ht="24" customHeight="1" s="49">
       <c r="A49" s="2" t="n">
         <v>48</v>
       </c>
@@ -5572,7 +5582,7 @@
       </c>
       <c r="AH49" s="2" t="n"/>
     </row>
-    <row r="50" ht="24" customHeight="1" s="48">
+    <row r="50" ht="24" customHeight="1" s="49">
       <c r="A50" s="2" t="n">
         <v>49</v>
       </c>
@@ -5656,7 +5666,7 @@
       <c r="AG50" s="2" t="n"/>
       <c r="AH50" s="2" t="n"/>
     </row>
-    <row r="51" ht="24" customHeight="1" s="48">
+    <row r="51" ht="24" customHeight="1" s="49">
       <c r="A51" s="2" t="n">
         <v>50</v>
       </c>
@@ -5740,7 +5750,7 @@
       <c r="AG51" s="2" t="n"/>
       <c r="AH51" s="2" t="n"/>
     </row>
-    <row r="52" ht="24" customHeight="1" s="48">
+    <row r="52" ht="24" customHeight="1" s="49">
       <c r="A52" s="2" t="n">
         <v>51</v>
       </c>
@@ -5828,7 +5838,7 @@
       </c>
       <c r="AH52" s="2" t="n"/>
     </row>
-    <row r="53" ht="24" customHeight="1" s="48">
+    <row r="53" ht="24" customHeight="1" s="49">
       <c r="A53" s="2" t="n">
         <v>52</v>
       </c>
@@ -5916,7 +5926,7 @@
       </c>
       <c r="AH53" s="2" t="n"/>
     </row>
-    <row r="54" ht="24" customHeight="1" s="48">
+    <row r="54" ht="24" customHeight="1" s="49">
       <c r="A54" s="2" t="n">
         <v>53</v>
       </c>
@@ -6004,7 +6014,7 @@
       </c>
       <c r="AH54" s="2" t="n"/>
     </row>
-    <row r="55" ht="24" customHeight="1" s="48">
+    <row r="55" ht="24" customHeight="1" s="49">
       <c r="A55" s="2" t="n">
         <v>54</v>
       </c>
@@ -6092,7 +6102,7 @@
       </c>
       <c r="AH55" s="2" t="n"/>
     </row>
-    <row r="56" ht="24" customHeight="1" s="48">
+    <row r="56" ht="24" customHeight="1" s="49">
       <c r="A56" s="2" t="n">
         <v>55</v>
       </c>
@@ -6180,7 +6190,7 @@
       </c>
       <c r="AH56" s="2" t="n"/>
     </row>
-    <row r="57" ht="24" customHeight="1" s="48">
+    <row r="57" ht="24" customHeight="1" s="49">
       <c r="A57" s="2" t="n">
         <v>56</v>
       </c>
@@ -6264,7 +6274,7 @@
       <c r="AG57" s="2" t="n"/>
       <c r="AH57" s="2" t="n"/>
     </row>
-    <row r="58" ht="24" customHeight="1" s="48">
+    <row r="58" ht="24" customHeight="1" s="49">
       <c r="A58" s="2" t="n">
         <v>57</v>
       </c>
@@ -6352,7 +6362,7 @@
       </c>
       <c r="AH58" s="2" t="n"/>
     </row>
-    <row r="59" ht="24" customHeight="1" s="48">
+    <row r="59" ht="24" customHeight="1" s="49">
       <c r="A59" s="2" t="n">
         <v>58</v>
       </c>
@@ -6440,7 +6450,7 @@
       </c>
       <c r="AH59" s="2" t="n"/>
     </row>
-    <row r="60" ht="24" customHeight="1" s="48">
+    <row r="60" ht="24" customHeight="1" s="49">
       <c r="A60" s="2" t="n">
         <v>59</v>
       </c>
@@ -6528,7 +6538,7 @@
       </c>
       <c r="AH60" s="2" t="n"/>
     </row>
-    <row r="61" ht="24" customHeight="1" s="48">
+    <row r="61" ht="24" customHeight="1" s="49">
       <c r="A61" s="2" t="n">
         <v>60</v>
       </c>
@@ -6620,7 +6630,7 @@
       </c>
       <c r="AH61" s="2" t="n"/>
     </row>
-    <row r="62" ht="24" customHeight="1" s="48">
+    <row r="62" ht="24" customHeight="1" s="49">
       <c r="A62" s="2" t="n">
         <v>61</v>
       </c>
@@ -6708,7 +6718,7 @@
       </c>
       <c r="AH62" s="2" t="n"/>
     </row>
-    <row r="63" ht="24" customHeight="1" s="48">
+    <row r="63" ht="24" customHeight="1" s="49">
       <c r="A63" s="2" t="n">
         <v>62</v>
       </c>
@@ -6808,7 +6818,7 @@
       </c>
       <c r="AH63" s="2" t="n"/>
     </row>
-    <row r="64" ht="24" customHeight="1" s="48">
+    <row r="64" ht="24" customHeight="1" s="49">
       <c r="A64" s="2" t="n">
         <v>63</v>
       </c>
@@ -6896,7 +6906,7 @@
       </c>
       <c r="AH64" s="2" t="n"/>
     </row>
-    <row r="65" ht="24" customHeight="1" s="48">
+    <row r="65" ht="24" customHeight="1" s="49">
       <c r="A65" s="2" t="n">
         <v>64</v>
       </c>
@@ -6984,7 +6994,7 @@
       </c>
       <c r="AH65" s="2" t="n"/>
     </row>
-    <row r="66" ht="24" customHeight="1" s="48">
+    <row r="66" ht="24" customHeight="1" s="49">
       <c r="A66" s="2" t="n">
         <v>65</v>
       </c>
@@ -7072,7 +7082,7 @@
       </c>
       <c r="AH66" s="2" t="n"/>
     </row>
-    <row r="67" ht="24" customHeight="1" s="48">
+    <row r="67" ht="24" customHeight="1" s="49">
       <c r="A67" s="2" t="n">
         <v>66</v>
       </c>
@@ -7160,7 +7170,7 @@
       </c>
       <c r="AH67" s="2" t="n"/>
     </row>
-    <row r="68" ht="24" customHeight="1" s="48">
+    <row r="68" ht="24" customHeight="1" s="49">
       <c r="A68" s="2" t="n">
         <v>67</v>
       </c>
@@ -7260,7 +7270,7 @@
       </c>
       <c r="AH68" s="2" t="n"/>
     </row>
-    <row r="69" ht="24" customHeight="1" s="48">
+    <row r="69" ht="24" customHeight="1" s="49">
       <c r="A69" s="2" t="n">
         <v>68</v>
       </c>
@@ -7348,7 +7358,7 @@
       </c>
       <c r="AH69" s="2" t="n"/>
     </row>
-    <row r="70" ht="24" customHeight="1" s="48">
+    <row r="70" ht="24" customHeight="1" s="49">
       <c r="A70" s="2" t="n">
         <v>69</v>
       </c>
@@ -7436,7 +7446,7 @@
       </c>
       <c r="AH70" s="2" t="n"/>
     </row>
-    <row r="71" ht="24" customHeight="1" s="48">
+    <row r="71" ht="24" customHeight="1" s="49">
       <c r="A71" s="2" t="n">
         <v>70</v>
       </c>
@@ -7524,7 +7534,7 @@
       </c>
       <c r="AH71" s="2" t="n"/>
     </row>
-    <row r="72" ht="24" customHeight="1" s="48">
+    <row r="72" ht="24" customHeight="1" s="49">
       <c r="A72" s="2" t="n">
         <v>71</v>
       </c>
@@ -7612,7 +7622,7 @@
       </c>
       <c r="AH72" s="2" t="n"/>
     </row>
-    <row r="73" ht="24" customHeight="1" s="48">
+    <row r="73" ht="24" customHeight="1" s="49">
       <c r="A73" s="2" t="n">
         <v>72</v>
       </c>
@@ -7700,7 +7710,7 @@
       </c>
       <c r="AH73" s="2" t="n"/>
     </row>
-    <row r="74" ht="24" customHeight="1" s="48">
+    <row r="74" ht="24" customHeight="1" s="49">
       <c r="A74" s="2" t="n">
         <v>73</v>
       </c>
@@ -7784,7 +7794,7 @@
       <c r="AG74" s="2" t="n"/>
       <c r="AH74" s="2" t="n"/>
     </row>
-    <row r="75" ht="24" customHeight="1" s="48">
+    <row r="75" ht="24" customHeight="1" s="49">
       <c r="A75" s="2" t="n">
         <v>74</v>
       </c>
@@ -7886,7 +7896,7 @@
       </c>
       <c r="AH75" s="2" t="n"/>
     </row>
-    <row r="76" ht="24" customHeight="1" s="48">
+    <row r="76" ht="24" customHeight="1" s="49">
       <c r="A76" s="2" t="n">
         <v>75</v>
       </c>
@@ -7992,7 +8002,7 @@
       </c>
       <c r="AH76" s="2" t="n"/>
     </row>
-    <row r="77" ht="24" customHeight="1" s="48">
+    <row r="77" ht="24" customHeight="1" s="49">
       <c r="A77" s="2" t="n">
         <v>76</v>
       </c>
@@ -8042,13 +8052,13 @@
         </is>
       </c>
       <c r="O77" s="32" t="n">
-        <v>-25.7</v>
+        <v>-3.6</v>
       </c>
       <c r="P77" s="32" t="n">
-        <v>-2</v>
+        <v>4.9</v>
       </c>
       <c r="Q77" s="32" t="n">
-        <v>-13.59</v>
+        <v>0.39</v>
       </c>
       <c r="R77" s="23" t="inlineStr">
         <is>
@@ -8108,7 +8118,7 @@
       </c>
       <c r="AH77" s="2" t="n"/>
     </row>
-    <row r="78" ht="24" customHeight="1" s="48">
+    <row r="78" ht="24" customHeight="1" s="49">
       <c r="A78" s="2" t="n">
         <v>77</v>
       </c>
@@ -8210,7 +8220,7 @@
       </c>
       <c r="AH78" s="2" t="n"/>
     </row>
-    <row r="79" ht="24" customHeight="1" s="48">
+    <row r="79" ht="24" customHeight="1" s="49">
       <c r="A79" s="2" t="n">
         <v>78</v>
       </c>
@@ -8316,7 +8326,7 @@
       </c>
       <c r="AH79" s="2" t="n"/>
     </row>
-    <row r="80" ht="24" customHeight="1" s="48">
+    <row r="80" ht="24" customHeight="1" s="49">
       <c r="A80" s="2" t="n">
         <v>79</v>
       </c>
@@ -8418,7 +8428,7 @@
       </c>
       <c r="AH80" s="2" t="n"/>
     </row>
-    <row r="81" ht="24" customHeight="1" s="48">
+    <row r="81" ht="24" customHeight="1" s="49">
       <c r="A81" s="2" t="n">
         <v>80</v>
       </c>
@@ -8468,10 +8478,10 @@
         </is>
       </c>
       <c r="O81" s="32" t="n">
-        <v>-16.3</v>
+        <v>-9.699999999999999</v>
       </c>
       <c r="P81" s="32" t="n">
-        <v>2.2</v>
+        <v>0.8</v>
       </c>
       <c r="Q81" s="32" t="n"/>
       <c r="R81" s="23" t="inlineStr">
@@ -8537,7 +8547,7 @@
         </is>
       </c>
     </row>
-    <row r="82" ht="24" customHeight="1" s="48">
+    <row r="82" ht="24" customHeight="1" s="49">
       <c r="A82" s="2" t="n">
         <v>81</v>
       </c>
@@ -8587,13 +8597,13 @@
         </is>
       </c>
       <c r="O82" s="32" t="n">
-        <v>-14.3</v>
+        <v>-10.3</v>
       </c>
       <c r="P82" s="32" t="n">
-        <v>2.1</v>
+        <v>0.8</v>
       </c>
       <c r="Q82" s="32" t="n">
-        <v>-4.88</v>
+        <v>-3.79</v>
       </c>
       <c r="R82" s="23" t="inlineStr">
         <is>
@@ -8653,7 +8663,7 @@
       </c>
       <c r="AH82" s="2" t="n"/>
     </row>
-    <row r="83" ht="24" customHeight="1" s="48">
+    <row r="83" ht="24" customHeight="1" s="49">
       <c r="A83" s="2" t="n">
         <v>82</v>
       </c>
@@ -8755,7 +8765,7 @@
       </c>
       <c r="AH83" s="2" t="n"/>
     </row>
-    <row r="84" ht="24" customHeight="1" s="48">
+    <row r="84" ht="24" customHeight="1" s="49">
       <c r="A84" s="2" t="n">
         <v>83</v>
       </c>
@@ -8805,13 +8815,13 @@
         </is>
       </c>
       <c r="O84" s="32" t="n">
-        <v>-2.4</v>
+        <v>-7</v>
       </c>
       <c r="P84" s="32" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Q84" s="32" t="n">
-        <v>-0.9399999999999999</v>
+        <v>-3.94</v>
       </c>
       <c r="R84" s="23" t="inlineStr">
         <is>
@@ -8871,7 +8881,7 @@
       </c>
       <c r="AH84" s="2" t="n"/>
     </row>
-    <row r="85" ht="24" customHeight="1" s="48">
+    <row r="85" ht="24" customHeight="1" s="49">
       <c r="A85" s="2" t="n">
         <v>84</v>
       </c>
@@ -8977,7 +8987,7 @@
       </c>
       <c r="AH85" s="2" t="n"/>
     </row>
-    <row r="86" ht="24" customHeight="1" s="48">
+    <row r="86" ht="24" customHeight="1" s="49">
       <c r="A86" s="2" t="n">
         <v>85</v>
       </c>
@@ -9023,13 +9033,13 @@
       </c>
       <c r="N86" s="2" t="n"/>
       <c r="O86" s="32" t="n">
-        <v>-0.4</v>
+        <v>2</v>
       </c>
       <c r="P86" s="32" t="n">
-        <v>13.2</v>
+        <v>11.9</v>
       </c>
       <c r="Q86" s="32" t="n">
-        <v>6.22</v>
+        <v>4.79</v>
       </c>
       <c r="R86" s="23" t="inlineStr">
         <is>
@@ -9097,7 +9107,7 @@
       </c>
       <c r="AH86" s="2" t="n"/>
     </row>
-    <row r="87" ht="24" customHeight="1" s="48">
+    <row r="87" ht="24" customHeight="1" s="49">
       <c r="A87" s="2" t="n">
         <v>86</v>
       </c>
@@ -9203,7 +9213,7 @@
       </c>
       <c r="AH87" s="2" t="n"/>
     </row>
-    <row r="88" ht="24" customHeight="1" s="48">
+    <row r="88" ht="24" customHeight="1" s="49">
       <c r="A88" s="2" t="n">
         <v>87</v>
       </c>
@@ -9249,13 +9259,13 @@
       </c>
       <c r="N88" s="2" t="n"/>
       <c r="O88" s="32" t="n">
-        <v>-6.4</v>
+        <v>1.5</v>
       </c>
       <c r="P88" s="32" t="n">
-        <v>14</v>
+        <v>9.4</v>
       </c>
       <c r="Q88" s="32" t="n">
-        <v>3.47</v>
+        <v>5.19</v>
       </c>
       <c r="R88" s="23" t="inlineStr">
         <is>
@@ -9315,7 +9325,7 @@
       </c>
       <c r="AH88" s="2" t="n"/>
     </row>
-    <row r="89" ht="24" customHeight="1" s="48">
+    <row r="89" ht="24" customHeight="1" s="49">
       <c r="A89" s="2" t="n">
         <v>88</v>
       </c>
@@ -9413,7 +9423,7 @@
       </c>
       <c r="AH89" s="2" t="n"/>
     </row>
-    <row r="90" ht="24" customHeight="1" s="48">
+    <row r="90" ht="24" customHeight="1" s="49">
       <c r="A90" s="2" t="n">
         <v>89</v>
       </c>
@@ -9515,7 +9525,7 @@
       <c r="AG90" s="2" t="n"/>
       <c r="AH90" s="2" t="n"/>
     </row>
-    <row r="91" ht="24" customHeight="1" s="48">
+    <row r="91" ht="24" customHeight="1" s="49">
       <c r="A91" s="2" t="n">
         <v>90</v>
       </c>
@@ -9613,7 +9623,7 @@
       </c>
       <c r="AH91" s="2" t="n"/>
     </row>
-    <row r="92" ht="24" customHeight="1" s="48">
+    <row r="92" ht="24" customHeight="1" s="49">
       <c r="A92" s="2" t="n">
         <v>91</v>
       </c>
@@ -9659,13 +9669,13 @@
       </c>
       <c r="N92" s="2" t="n"/>
       <c r="O92" s="32" t="n">
-        <v>-2.9</v>
+        <v>-5.3</v>
       </c>
       <c r="P92" s="32" t="n">
-        <v>6.6</v>
+        <v>1.3</v>
       </c>
       <c r="Q92" s="32" t="n">
-        <v>3.5</v>
+        <v>-1.59</v>
       </c>
       <c r="R92" s="23" t="inlineStr">
         <is>
@@ -9725,7 +9735,7 @@
       </c>
       <c r="AH92" s="2" t="n"/>
     </row>
-    <row r="93" ht="24" customHeight="1" s="48">
+    <row r="93" ht="24" customHeight="1" s="49">
       <c r="A93" s="2" t="n">
         <v>92</v>
       </c>
@@ -9771,13 +9781,13 @@
       </c>
       <c r="N93" s="2" t="n"/>
       <c r="O93" s="32" t="n">
-        <v>1.2</v>
+        <v>2.7</v>
       </c>
       <c r="P93" s="32" t="n">
-        <v>11.3</v>
+        <v>15.4</v>
       </c>
       <c r="Q93" s="32" t="n">
-        <v>5.64</v>
+        <v>10.06</v>
       </c>
       <c r="R93" s="23" t="inlineStr">
         <is>
@@ -9849,7 +9859,7 @@
       </c>
       <c r="AH93" s="2" t="n"/>
     </row>
-    <row r="94" ht="24" customHeight="1" s="48">
+    <row r="94" ht="24" customHeight="1" s="49">
       <c r="A94" s="2" t="n">
         <v>93</v>
       </c>
@@ -9891,10 +9901,10 @@
         </is>
       </c>
       <c r="O94" s="32" t="n">
-        <v>-1.8</v>
+        <v>2.3</v>
       </c>
       <c r="P94" s="32" t="n">
-        <v>8.699999999999999</v>
+        <v>12.4</v>
       </c>
       <c r="Q94" s="32" t="n"/>
       <c r="R94" s="23" t="inlineStr">
@@ -9963,7 +9973,7 @@
       </c>
       <c r="AH94" s="2" t="n"/>
     </row>
-    <row r="95" ht="24" customHeight="1" s="48">
+    <row r="95" ht="24" customHeight="1" s="49">
       <c r="A95" s="2" t="n">
         <v>94</v>
       </c>
@@ -10009,13 +10019,13 @@
       </c>
       <c r="N95" s="2" t="n"/>
       <c r="O95" s="32" t="n">
-        <v>-3.4</v>
+        <v>1.2</v>
       </c>
       <c r="P95" s="32" t="n">
-        <v>7.1</v>
+        <v>11</v>
       </c>
       <c r="Q95" s="32" t="n">
-        <v>2.06</v>
+        <v>6.22</v>
       </c>
       <c r="R95" s="23" t="inlineStr">
         <is>
@@ -10087,7 +10097,7 @@
       </c>
       <c r="AH95" s="2" t="n"/>
     </row>
-    <row r="96" ht="24" customHeight="1" s="48">
+    <row r="96" ht="24" customHeight="1" s="49">
       <c r="A96" s="2" t="n">
         <v>95</v>
       </c>
@@ -10137,10 +10147,10 @@
         </is>
       </c>
       <c r="O96" s="32" t="n">
-        <v>-0.4</v>
+        <v>1.8</v>
       </c>
       <c r="P96" s="32" t="n">
-        <v>14.1</v>
+        <v>10.9</v>
       </c>
       <c r="Q96" s="32" t="n"/>
       <c r="R96" s="23" t="inlineStr">
@@ -10209,7 +10219,7 @@
       </c>
       <c r="AH96" s="2" t="n"/>
     </row>
-    <row r="97" ht="24" customHeight="1" s="48">
+    <row r="97" ht="24" customHeight="1" s="49">
       <c r="A97" s="2" t="n">
         <v>96</v>
       </c>
@@ -10255,13 +10265,13 @@
       </c>
       <c r="N97" s="2" t="n"/>
       <c r="O97" s="32" t="n">
-        <v>-4.3</v>
+        <v>0.7</v>
       </c>
       <c r="P97" s="32" t="n">
-        <v>6.2</v>
+        <v>7.9</v>
       </c>
       <c r="Q97" s="32" t="n">
-        <v>1.74</v>
+        <v>4.35</v>
       </c>
       <c r="R97" s="23" t="inlineStr">
         <is>
@@ -10337,7 +10347,7 @@
       </c>
       <c r="AH97" s="2" t="n"/>
     </row>
-    <row r="98" ht="24" customHeight="1" s="48">
+    <row r="98" ht="24" customHeight="1" s="49">
       <c r="A98" s="2" t="n">
         <v>97</v>
       </c>
@@ -10375,10 +10385,10 @@
       </c>
       <c r="N98" s="2" t="n"/>
       <c r="O98" s="32" t="n">
-        <v>-2.2</v>
+        <v>0.7</v>
       </c>
       <c r="P98" s="32" t="n">
-        <v>8.6</v>
+        <v>5.3</v>
       </c>
       <c r="Q98" s="32" t="n"/>
       <c r="R98" s="23" t="inlineStr">
@@ -10447,7 +10457,7 @@
       </c>
       <c r="AH98" s="2" t="n"/>
     </row>
-    <row r="99" ht="24" customHeight="1" s="48">
+    <row r="99" ht="24" customHeight="1" s="49">
       <c r="A99" s="2" t="n">
         <v>98</v>
       </c>
@@ -10493,13 +10503,13 @@
       </c>
       <c r="N99" s="2" t="n"/>
       <c r="O99" s="32" t="n">
-        <v>-7.8</v>
+        <v>-0.6</v>
       </c>
       <c r="P99" s="32" t="n">
-        <v>7</v>
+        <v>8.4</v>
       </c>
       <c r="Q99" s="32" t="n">
-        <v>-0.04</v>
+        <v>3.36</v>
       </c>
       <c r="R99" s="23" t="inlineStr">
         <is>
@@ -10567,7 +10577,7 @@
       </c>
       <c r="AH99" s="2" t="n"/>
     </row>
-    <row r="100" ht="24" customHeight="1" s="48">
+    <row r="100" ht="24" customHeight="1" s="49">
       <c r="A100" s="2" t="n">
         <v>99</v>
       </c>
@@ -10673,7 +10683,7 @@
       </c>
       <c r="AH100" s="2" t="n"/>
     </row>
-    <row r="101" ht="24" customHeight="1" s="48">
+    <row r="101" ht="24" customHeight="1" s="49">
       <c r="A101" s="2" t="n">
         <v>100</v>
       </c>
@@ -10710,12 +10720,8 @@
         </is>
       </c>
       <c r="N101" s="2" t="n"/>
-      <c r="O101" s="32" t="n">
-        <v>-13.2</v>
-      </c>
-      <c r="P101" s="32" t="n">
-        <v>5.8</v>
-      </c>
+      <c r="O101" s="32" t="n"/>
+      <c r="P101" s="32" t="n"/>
       <c r="Q101" s="32" t="n"/>
       <c r="R101" s="23" t="inlineStr">
         <is>
@@ -10783,7 +10789,7 @@
       </c>
       <c r="AH101" s="2" t="n"/>
     </row>
-    <row r="102" ht="24" customHeight="1" s="48">
+    <row r="102" ht="24" customHeight="1" s="49">
       <c r="A102" s="2" t="n">
         <v>101</v>
       </c>
@@ -10829,13 +10835,13 @@
       </c>
       <c r="N102" s="2" t="n"/>
       <c r="O102" s="32" t="n">
-        <v>-10.7</v>
+        <v>-1.1</v>
       </c>
       <c r="P102" s="32" t="n">
-        <v>3.9</v>
+        <v>4.5</v>
       </c>
       <c r="Q102" s="32" t="n">
-        <v>-3.91</v>
+        <v>1.2</v>
       </c>
       <c r="R102" s="23" t="inlineStr">
         <is>
@@ -10907,7 +10913,7 @@
       </c>
       <c r="AH102" s="2" t="n"/>
     </row>
-    <row r="103" ht="24" customHeight="1" s="48">
+    <row r="103" ht="24" customHeight="1" s="49">
       <c r="A103" s="2" t="n">
         <v>102</v>
       </c>
@@ -10945,10 +10951,10 @@
       </c>
       <c r="N103" s="2" t="n"/>
       <c r="O103" s="32" t="n">
-        <v>-8.699999999999999</v>
+        <v>-1.4</v>
       </c>
       <c r="P103" s="32" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="Q103" s="32" t="n"/>
       <c r="R103" s="23" t="inlineStr">
@@ -11017,7 +11023,7 @@
       </c>
       <c r="AH103" s="2" t="n"/>
     </row>
-    <row r="104" ht="24" customHeight="1" s="48">
+    <row r="104" ht="24" customHeight="1" s="49">
       <c r="A104" s="2" t="n">
         <v>103</v>
       </c>
@@ -11055,10 +11061,10 @@
       </c>
       <c r="N104" s="2" t="n"/>
       <c r="O104" s="32" t="n">
-        <v>-8.9</v>
+        <v>-2</v>
       </c>
       <c r="P104" s="32" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="Q104" s="32" t="n"/>
       <c r="R104" s="23" t="inlineStr">
@@ -11131,7 +11137,7 @@
       </c>
       <c r="AH104" s="2" t="n"/>
     </row>
-    <row r="105" ht="24" customHeight="1" s="48">
+    <row r="105" ht="24" customHeight="1" s="49">
       <c r="A105" s="2" t="n">
         <v>104</v>
       </c>
@@ -11181,13 +11187,13 @@
         </is>
       </c>
       <c r="O105" s="32" t="n">
-        <v>-11.3</v>
+        <v>-2.5</v>
       </c>
       <c r="P105" s="32" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="Q105" s="32" t="n">
-        <v>-2.88</v>
+        <v>0.22</v>
       </c>
       <c r="R105" s="23" t="inlineStr">
         <is>
@@ -11255,7 +11261,7 @@
       </c>
       <c r="AH105" s="2" t="n"/>
     </row>
-    <row r="106" ht="24" customHeight="1" s="48">
+    <row r="106" ht="24" customHeight="1" s="49">
       <c r="A106" s="2" t="n">
         <v>105</v>
       </c>
@@ -11297,10 +11303,10 @@
         </is>
       </c>
       <c r="O106" s="32" t="n">
-        <v>-2.5</v>
+        <v>-2.6</v>
       </c>
       <c r="P106" s="32" t="n">
-        <v>6.8</v>
+        <v>5.5</v>
       </c>
       <c r="Q106" s="32" t="n"/>
       <c r="R106" s="23" t="inlineStr">
@@ -11369,7 +11375,7 @@
       </c>
       <c r="AH106" s="2" t="n"/>
     </row>
-    <row r="107" ht="24" customHeight="1" s="48">
+    <row r="107" ht="24" customHeight="1" s="49">
       <c r="A107" s="2" t="n">
         <v>106</v>
       </c>
@@ -11471,7 +11477,7 @@
       </c>
       <c r="AH107" s="2" t="n"/>
     </row>
-    <row r="108" ht="24" customHeight="1" s="48">
+    <row r="108" ht="24" customHeight="1" s="49">
       <c r="A108" s="2" t="n">
         <v>107</v>
       </c>
@@ -11517,13 +11523,13 @@
       </c>
       <c r="N108" s="2" t="n"/>
       <c r="O108" s="32" t="n">
-        <v>-2.3</v>
+        <v>-2.6</v>
       </c>
       <c r="P108" s="32" t="n">
-        <v>6.8</v>
+        <v>6.2</v>
       </c>
       <c r="Q108" s="32" t="n">
-        <v>1.36</v>
+        <v>1.11</v>
       </c>
       <c r="R108" s="23" t="inlineStr">
         <is>
@@ -11591,7 +11597,7 @@
       </c>
       <c r="AH108" s="2" t="n"/>
     </row>
-    <row r="109" ht="24" customHeight="1" s="48">
+    <row r="109" ht="24" customHeight="1" s="49">
       <c r="A109" s="2" t="n">
         <v>108</v>
       </c>
@@ -11693,7 +11699,7 @@
       </c>
       <c r="AH109" s="2" t="n"/>
     </row>
-    <row r="110" ht="24" customHeight="1" s="48">
+    <row r="110" ht="24" customHeight="1" s="49">
       <c r="A110" s="2" t="n">
         <v>109</v>
       </c>
@@ -11799,7 +11805,7 @@
       </c>
       <c r="AH110" s="2" t="n"/>
     </row>
-    <row r="111" ht="24" customHeight="1" s="48">
+    <row r="111" ht="24" customHeight="1" s="49">
       <c r="A111" s="2" t="n">
         <v>110</v>
       </c>
@@ -11845,13 +11851,13 @@
       </c>
       <c r="N111" s="2" t="n"/>
       <c r="O111" s="32" t="n">
-        <v>-7.1</v>
+        <v>-6.6</v>
       </c>
       <c r="P111" s="32" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="Q111" s="32" t="n">
-        <v>-1.51</v>
+        <v>-1.23</v>
       </c>
       <c r="R111" s="23" t="inlineStr">
         <is>
@@ -11919,7 +11925,7 @@
       </c>
       <c r="AH111" s="2" t="n"/>
     </row>
-    <row r="112" ht="24" customHeight="1" s="48">
+    <row r="112" ht="24" customHeight="1" s="49">
       <c r="A112" s="2" t="n">
         <v>111</v>
       </c>
@@ -11957,10 +11963,10 @@
       </c>
       <c r="N112" s="2" t="n"/>
       <c r="O112" s="32" t="n">
-        <v>-8.6</v>
+        <v>-4.9</v>
       </c>
       <c r="P112" s="32" t="n">
-        <v>12.7</v>
+        <v>20.5</v>
       </c>
       <c r="Q112" s="32" t="n"/>
       <c r="R112" s="23" t="inlineStr">
@@ -12025,7 +12031,7 @@
       <c r="AG112" s="2" t="n"/>
       <c r="AH112" s="2" t="n"/>
     </row>
-    <row r="113" ht="24" customHeight="1" s="48">
+    <row r="113" ht="24" customHeight="1" s="49">
       <c r="A113" s="2" t="n">
         <v>112</v>
       </c>
@@ -12063,10 +12069,10 @@
       </c>
       <c r="N113" s="2" t="n"/>
       <c r="O113" s="32" t="n">
-        <v>-7.6</v>
+        <v>-12.4</v>
       </c>
       <c r="P113" s="32" t="n">
-        <v>10.1</v>
+        <v>0.3</v>
       </c>
       <c r="Q113" s="32" t="n"/>
       <c r="R113" s="23" t="inlineStr">
@@ -12135,7 +12141,7 @@
       </c>
       <c r="AH113" s="2" t="n"/>
     </row>
-    <row r="114" ht="24" customHeight="1" s="48">
+    <row r="114" ht="24" customHeight="1" s="49">
       <c r="A114" s="2" t="n">
         <v>113</v>
       </c>
@@ -12177,10 +12183,10 @@
         </is>
       </c>
       <c r="O114" s="32" t="n">
-        <v>-15.5</v>
+        <v>-4.9</v>
       </c>
       <c r="P114" s="32" t="n">
-        <v>7.6</v>
+        <v>1.4</v>
       </c>
       <c r="Q114" s="32" t="n"/>
       <c r="R114" s="23" t="inlineStr">
@@ -12249,7 +12255,7 @@
       </c>
       <c r="AH114" s="2" t="n"/>
     </row>
-    <row r="115" ht="24" customHeight="1" s="48">
+    <row r="115" ht="24" customHeight="1" s="49">
       <c r="A115" s="2" t="n">
         <v>114</v>
       </c>
@@ -12299,10 +12305,10 @@
         </is>
       </c>
       <c r="O115" s="32" t="n">
-        <v>-13.2</v>
+        <v>-7.4</v>
       </c>
       <c r="P115" s="32" t="n">
-        <v>7.9</v>
+        <v>0.1</v>
       </c>
       <c r="Q115" s="32" t="n"/>
       <c r="R115" s="23" t="inlineStr">
@@ -12371,7 +12377,7 @@
       </c>
       <c r="AH115" s="2" t="n"/>
     </row>
-    <row r="116" ht="24" customHeight="1" s="48">
+    <row r="116" ht="24" customHeight="1" s="49">
       <c r="A116" s="2" t="n">
         <v>115</v>
       </c>
@@ -12417,13 +12423,13 @@
       </c>
       <c r="N116" s="2" t="n"/>
       <c r="O116" s="32" t="n">
-        <v>-1.7</v>
+        <v>6.5</v>
       </c>
       <c r="P116" s="32" t="n">
-        <v>17.3</v>
+        <v>16.5</v>
       </c>
       <c r="Q116" s="32" t="n">
-        <v>8.890000000000001</v>
+        <v>11.4</v>
       </c>
       <c r="R116" s="23" t="inlineStr">
         <is>
@@ -12491,7 +12497,7 @@
       </c>
       <c r="AH116" s="2" t="n"/>
     </row>
-    <row r="117" ht="24" customHeight="1" s="48">
+    <row r="117" ht="24" customHeight="1" s="49">
       <c r="A117" s="2" t="n">
         <v>116</v>
       </c>
@@ -12528,12 +12534,8 @@
         </is>
       </c>
       <c r="N117" s="2" t="n"/>
-      <c r="O117" s="32" t="n">
-        <v>-0.3</v>
-      </c>
-      <c r="P117" s="32" t="n">
-        <v>17.6</v>
-      </c>
+      <c r="O117" s="32" t="n"/>
+      <c r="P117" s="32" t="n"/>
       <c r="Q117" s="32" t="n"/>
       <c r="R117" s="23" t="inlineStr">
         <is>
@@ -12601,7 +12603,7 @@
       </c>
       <c r="AH117" s="2" t="n"/>
     </row>
-    <row r="118" ht="24" customHeight="1" s="48">
+    <row r="118" ht="24" customHeight="1" s="49">
       <c r="A118" s="2" t="n">
         <v>117</v>
       </c>
@@ -12642,12 +12644,8 @@
           <t>↓</t>
         </is>
       </c>
-      <c r="O118" s="32" t="n">
-        <v>-1.5</v>
-      </c>
-      <c r="P118" s="32" t="n">
-        <v>20.3</v>
-      </c>
+      <c r="O118" s="32" t="n"/>
+      <c r="P118" s="32" t="n"/>
       <c r="Q118" s="32" t="n"/>
       <c r="R118" s="23" t="inlineStr">
         <is>
@@ -12715,7 +12713,7 @@
       </c>
       <c r="AH118" s="2" t="n"/>
     </row>
-    <row r="119" ht="24" customHeight="1" s="48">
+    <row r="119" ht="24" customHeight="1" s="49">
       <c r="A119" s="2" t="n">
         <v>118</v>
       </c>
@@ -12761,13 +12759,13 @@
       </c>
       <c r="N119" s="2" t="n"/>
       <c r="O119" s="32" t="n">
-        <v>2.7</v>
+        <v>5.4</v>
       </c>
       <c r="P119" s="32" t="n">
-        <v>22.3</v>
+        <v>17.1</v>
       </c>
       <c r="Q119" s="32" t="n">
-        <v>12.4</v>
+        <v>12</v>
       </c>
       <c r="R119" s="23" t="inlineStr">
         <is>
@@ -12843,7 +12841,7 @@
       </c>
       <c r="AH119" s="2" t="n"/>
     </row>
-    <row r="120" ht="24" customHeight="1" s="48">
+    <row r="120" ht="24" customHeight="1" s="49">
       <c r="A120" s="2" t="n">
         <v>119</v>
       </c>
@@ -12949,7 +12947,7 @@
       </c>
       <c r="AH120" s="2" t="n"/>
     </row>
-    <row r="121" ht="24" customHeight="1" s="48">
+    <row r="121" ht="24" customHeight="1" s="49">
       <c r="A121" s="2" t="n">
         <v>120</v>
       </c>
@@ -12995,13 +12993,13 @@
       </c>
       <c r="N121" s="2" t="n"/>
       <c r="O121" s="32" t="n">
-        <v>9.300000000000001</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="P121" s="32" t="n">
-        <v>21</v>
+        <v>17.7</v>
       </c>
       <c r="Q121" s="32" t="n">
-        <v>14.78</v>
+        <v>13.73</v>
       </c>
       <c r="R121" s="23" t="inlineStr">
         <is>
@@ -13073,7 +13071,7 @@
       </c>
       <c r="AH121" s="2" t="n"/>
     </row>
-    <row r="122" ht="24" customHeight="1" s="48">
+    <row r="122" ht="24" customHeight="1" s="49">
       <c r="A122" s="2" t="n">
         <v>121</v>
       </c>
@@ -13119,10 +13117,10 @@
       </c>
       <c r="N122" s="2" t="n"/>
       <c r="O122" s="32" t="n">
-        <v>-4.8</v>
+        <v>0.8</v>
       </c>
       <c r="P122" s="32" t="n">
-        <v>16.4</v>
+        <v>8.1</v>
       </c>
       <c r="Q122" s="32" t="n"/>
       <c r="R122" s="23" t="inlineStr">
@@ -13191,7 +13189,7 @@
       </c>
       <c r="AH122" s="2" t="n"/>
     </row>
-    <row r="123" ht="24" customHeight="1" s="48">
+    <row r="123" ht="24" customHeight="1" s="49">
       <c r="A123" s="2" t="n">
         <v>122</v>
       </c>
@@ -13297,7 +13295,7 @@
       </c>
       <c r="AH123" s="2" t="n"/>
     </row>
-    <row r="124" ht="24" customHeight="1" s="48">
+    <row r="124" ht="24" customHeight="1" s="49">
       <c r="A124" s="2" t="n">
         <v>123</v>
       </c>
@@ -13343,13 +13341,13 @@
       </c>
       <c r="N124" s="2" t="n"/>
       <c r="O124" s="32" t="n">
-        <v>-3.7</v>
+        <v>3.4</v>
       </c>
       <c r="P124" s="32" t="n">
-        <v>18.5</v>
+        <v>24</v>
       </c>
       <c r="Q124" s="32" t="n">
-        <v>6.75</v>
+        <v>14.19</v>
       </c>
       <c r="R124" s="23" t="inlineStr">
         <is>
@@ -13421,7 +13419,7 @@
       </c>
       <c r="AH124" s="2" t="n"/>
     </row>
-    <row r="125" ht="24" customHeight="1" s="48">
+    <row r="125" ht="24" customHeight="1" s="49">
       <c r="A125" s="2" t="n">
         <v>124</v>
       </c>
@@ -13467,13 +13465,13 @@
       </c>
       <c r="N125" s="2" t="n"/>
       <c r="O125" s="32" t="n">
-        <v>5.1</v>
+        <v>8</v>
       </c>
       <c r="P125" s="32" t="n">
-        <v>17.7</v>
+        <v>21.6</v>
       </c>
       <c r="Q125" s="32" t="n">
-        <v>12.85</v>
+        <v>15.62</v>
       </c>
       <c r="R125" s="23" t="inlineStr">
         <is>
@@ -13533,7 +13531,7 @@
       <c r="AG125" s="2" t="n"/>
       <c r="AH125" s="2" t="n"/>
     </row>
-    <row r="126" ht="24" customHeight="1" s="48">
+    <row r="126" ht="24" customHeight="1" s="49">
       <c r="A126" s="2" t="n">
         <v>125</v>
       </c>
@@ -13571,10 +13569,10 @@
       </c>
       <c r="N126" s="2" t="n"/>
       <c r="O126" s="32" t="n">
-        <v>6.6</v>
+        <v>10.9</v>
       </c>
       <c r="P126" s="32" t="n">
-        <v>18.3</v>
+        <v>22.1</v>
       </c>
       <c r="Q126" s="32" t="n"/>
       <c r="R126" s="23" t="inlineStr">
@@ -13635,7 +13633,7 @@
         </is>
       </c>
     </row>
-    <row r="127" ht="24" customHeight="1" s="48">
+    <row r="127" ht="24" customHeight="1" s="49">
       <c r="A127" s="2" t="n">
         <v>126</v>
       </c>
@@ -13681,13 +13679,13 @@
       </c>
       <c r="N127" s="2" t="n"/>
       <c r="O127" s="32" t="n">
-        <v>3.2</v>
+        <v>6.3</v>
       </c>
       <c r="P127" s="32" t="n">
-        <v>23</v>
+        <v>26.6</v>
       </c>
       <c r="Q127" s="32" t="n">
-        <v>13.19</v>
+        <v>15.96</v>
       </c>
       <c r="R127" s="23" t="inlineStr">
         <is>
@@ -13755,7 +13753,7 @@
       </c>
       <c r="AH127" s="2" t="n"/>
     </row>
-    <row r="128" ht="24" customHeight="1" s="48">
+    <row r="128" ht="24" customHeight="1" s="49">
       <c r="A128" s="2" t="n">
         <v>127</v>
       </c>
@@ -13801,10 +13799,10 @@
       </c>
       <c r="N128" s="2" t="n"/>
       <c r="O128" s="32" t="n">
-        <v>7</v>
+        <v>11.9</v>
       </c>
       <c r="P128" s="32" t="n">
-        <v>19.8</v>
+        <v>27.4</v>
       </c>
       <c r="Q128" s="32" t="n"/>
       <c r="R128" s="23" t="inlineStr">
@@ -13865,7 +13863,7 @@
       <c r="AG128" s="2" t="n"/>
       <c r="AH128" s="2" t="n"/>
     </row>
-    <row r="129" ht="24" customHeight="1" s="48">
+    <row r="129" ht="24" customHeight="1" s="49">
       <c r="A129" s="2" t="n">
         <v>128</v>
       </c>
@@ -13911,13 +13909,13 @@
       </c>
       <c r="N129" s="2" t="n"/>
       <c r="O129" s="32" t="n">
-        <v>0.4</v>
+        <v>6.1</v>
       </c>
       <c r="P129" s="32" t="n">
-        <v>21.8</v>
+        <v>26.8</v>
       </c>
       <c r="Q129" s="32" t="n">
-        <v>12.3</v>
+        <v>16.6</v>
       </c>
       <c r="R129" s="23" t="inlineStr">
         <is>
@@ -13985,7 +13983,7 @@
       </c>
       <c r="AH129" s="2" t="n"/>
     </row>
-    <row r="130" ht="24" customHeight="1" s="48">
+    <row r="130" ht="24" customHeight="1" s="49">
       <c r="A130" s="2" t="n">
         <v>129</v>
       </c>
@@ -14031,13 +14029,13 @@
       </c>
       <c r="N130" s="2" t="n"/>
       <c r="O130" s="32" t="n">
-        <v>0.8</v>
+        <v>3.2</v>
       </c>
       <c r="P130" s="32" t="n">
-        <v>19</v>
+        <v>19.4</v>
       </c>
       <c r="Q130" s="32" t="n">
-        <v>9.74</v>
+        <v>10.88</v>
       </c>
       <c r="R130" s="23" t="inlineStr">
         <is>
@@ -14105,7 +14103,7 @@
       </c>
       <c r="AH130" s="2" t="n"/>
     </row>
-    <row r="131" ht="24" customHeight="1" s="48">
+    <row r="131" ht="24" customHeight="1" s="49">
       <c r="A131" s="2" t="n">
         <v>130</v>
       </c>
@@ -14151,13 +14149,13 @@
       </c>
       <c r="N131" s="2" t="n"/>
       <c r="O131" s="32" t="n">
-        <v>7</v>
+        <v>16.2</v>
       </c>
       <c r="P131" s="32" t="n">
-        <v>20.4</v>
+        <v>26.7</v>
       </c>
       <c r="Q131" s="32" t="n">
-        <v>14.38</v>
+        <v>20.55</v>
       </c>
       <c r="R131" s="23" t="inlineStr">
         <is>
@@ -14221,7 +14219,7 @@
       </c>
       <c r="AH131" s="2" t="n"/>
     </row>
-    <row r="132" ht="24" customHeight="1" s="48">
+    <row r="132" ht="24" customHeight="1" s="49">
       <c r="A132" s="2" t="n">
         <v>131</v>
       </c>
@@ -14267,13 +14265,13 @@
       </c>
       <c r="N132" s="2" t="n"/>
       <c r="O132" s="32" t="n">
-        <v>13.8</v>
+        <v>13.3</v>
       </c>
       <c r="P132" s="32" t="n">
-        <v>24.3</v>
+        <v>27</v>
       </c>
       <c r="Q132" s="32" t="n">
-        <v>18.88</v>
+        <v>20.59</v>
       </c>
       <c r="R132" s="23" t="inlineStr">
         <is>
@@ -14337,7 +14335,7 @@
       </c>
       <c r="AH132" s="2" t="n"/>
     </row>
-    <row r="133" ht="24" customHeight="1" s="48">
+    <row r="133" ht="24" customHeight="1" s="49">
       <c r="A133" s="2" t="n">
         <v>132</v>
       </c>
@@ -14383,13 +14381,13 @@
       </c>
       <c r="N133" s="2" t="n"/>
       <c r="O133" s="32" t="n">
-        <v>8.4</v>
+        <v>12.3</v>
       </c>
       <c r="P133" s="32" t="n">
-        <v>22.3</v>
+        <v>19.8</v>
       </c>
       <c r="Q133" s="32" t="n">
-        <v>15.15</v>
+        <v>16.08</v>
       </c>
       <c r="R133" s="23" t="inlineStr">
         <is>
@@ -14457,7 +14455,7 @@
         </is>
       </c>
     </row>
-    <row r="134" ht="24" customHeight="1" s="48">
+    <row r="134" ht="24" customHeight="1" s="49">
       <c r="A134" s="2" t="n">
         <v>133</v>
       </c>
@@ -14559,7 +14557,7 @@
       </c>
       <c r="AH134" s="2" t="n"/>
     </row>
-    <row r="135" ht="24" customHeight="1" s="48">
+    <row r="135" ht="24" customHeight="1" s="49">
       <c r="A135" s="2" t="n">
         <v>134</v>
       </c>
@@ -14605,13 +14603,13 @@
       </c>
       <c r="N135" s="2" t="n"/>
       <c r="O135" s="32" t="n">
-        <v>12.1</v>
+        <v>19.2</v>
       </c>
       <c r="P135" s="32" t="n">
-        <v>27</v>
+        <v>22.5</v>
       </c>
       <c r="Q135" s="32" t="n">
-        <v>18.35</v>
+        <v>20.04</v>
       </c>
       <c r="R135" s="23" t="inlineStr">
         <is>
@@ -14675,7 +14673,7 @@
       </c>
       <c r="AH135" s="2" t="n"/>
     </row>
-    <row r="136" ht="24" customHeight="1" s="48">
+    <row r="136" ht="24" customHeight="1" s="49">
       <c r="A136" s="2" t="n">
         <v>135</v>
       </c>
@@ -14721,13 +14719,13 @@
       </c>
       <c r="N136" s="2" t="n"/>
       <c r="O136" s="32" t="n">
-        <v>13.4</v>
+        <v>20.5</v>
       </c>
       <c r="P136" s="32" t="n">
-        <v>23.2</v>
+        <v>23</v>
       </c>
       <c r="Q136" s="32" t="n">
-        <v>16.89</v>
+        <v>21.6</v>
       </c>
       <c r="R136" s="23" t="inlineStr">
         <is>
@@ -14791,7 +14789,7 @@
       </c>
       <c r="AH136" s="2" t="n"/>
     </row>
-    <row r="137" ht="24" customHeight="1" s="48">
+    <row r="137" ht="24" customHeight="1" s="49">
       <c r="A137" s="2" t="n">
         <v>136</v>
       </c>
@@ -14837,13 +14835,13 @@
       </c>
       <c r="N137" s="2" t="n"/>
       <c r="O137" s="32" t="n">
-        <v>11.6</v>
+        <v>18.9</v>
       </c>
       <c r="P137" s="32" t="n">
-        <v>26.7</v>
+        <v>21.4</v>
       </c>
       <c r="Q137" s="32" t="n">
-        <v>18.8</v>
+        <v>19.95</v>
       </c>
       <c r="R137" s="23" t="inlineStr">
         <is>
@@ -14907,7 +14905,7 @@
       </c>
       <c r="AH137" s="2" t="n"/>
     </row>
-    <row r="138" ht="24" customHeight="1" s="48">
+    <row r="138" ht="24" customHeight="1" s="49">
       <c r="A138" s="2" t="n">
         <v>137</v>
       </c>
@@ -14953,10 +14951,10 @@
       </c>
       <c r="N138" s="2" t="n"/>
       <c r="O138" s="32" t="n">
-        <v>11.3</v>
+        <v>16.4</v>
       </c>
       <c r="P138" s="32" t="n">
-        <v>24</v>
+        <v>20.1</v>
       </c>
       <c r="Q138" s="32" t="n"/>
       <c r="R138" s="23" t="inlineStr">
@@ -15021,7 +15019,7 @@
       </c>
       <c r="AH138" s="2" t="n"/>
     </row>
-    <row r="139" ht="24" customHeight="1" s="48">
+    <row r="139" ht="24" customHeight="1" s="49">
       <c r="A139" s="2" t="n">
         <v>138</v>
       </c>
@@ -15067,13 +15065,13 @@
       </c>
       <c r="N139" s="2" t="n"/>
       <c r="O139" s="32" t="n">
-        <v>13.4</v>
+        <v>15.1</v>
       </c>
       <c r="P139" s="32" t="n">
-        <v>24</v>
+        <v>20.6</v>
       </c>
       <c r="Q139" s="32" t="n">
-        <v>18.24</v>
+        <v>17.6</v>
       </c>
       <c r="R139" s="23" t="inlineStr">
         <is>
@@ -15137,7 +15135,7 @@
       </c>
       <c r="AH139" s="2" t="n"/>
     </row>
-    <row r="140" ht="24" customHeight="1" s="48">
+    <row r="140" ht="24" customHeight="1" s="49">
       <c r="A140" s="2" t="n">
         <v>139</v>
       </c>
@@ -15183,13 +15181,13 @@
       </c>
       <c r="N140" s="2" t="n"/>
       <c r="O140" s="32" t="n">
-        <v>13.2</v>
+        <v>14.4</v>
       </c>
       <c r="P140" s="32" t="n">
-        <v>24</v>
+        <v>22.8</v>
       </c>
       <c r="Q140" s="32" t="n">
-        <v>18.96</v>
+        <v>17.82</v>
       </c>
       <c r="R140" s="23" t="inlineStr">
         <is>
@@ -15253,7 +15251,7 @@
       </c>
       <c r="AH140" s="2" t="n"/>
     </row>
-    <row r="141" ht="24" customHeight="1" s="48">
+    <row r="141" ht="24" customHeight="1" s="49">
       <c r="A141" s="2" t="n">
         <v>140</v>
       </c>
@@ -15355,7 +15353,7 @@
       </c>
       <c r="AH141" s="2" t="n"/>
     </row>
-    <row r="142" ht="24" customHeight="1" s="48">
+    <row r="142" ht="24" customHeight="1" s="49">
       <c r="A142" s="2" t="n">
         <v>141</v>
       </c>
@@ -15401,13 +15399,13 @@
       </c>
       <c r="N142" s="2" t="n"/>
       <c r="O142" s="32" t="n">
-        <v>17.5</v>
+        <v>20.4</v>
       </c>
       <c r="P142" s="32" t="n">
-        <v>27.9</v>
+        <v>26.3</v>
       </c>
       <c r="Q142" s="32" t="n">
-        <v>21.47</v>
+        <v>22.85</v>
       </c>
       <c r="R142" s="23" t="inlineStr">
         <is>
@@ -15471,7 +15469,7 @@
       </c>
       <c r="AH142" s="2" t="n"/>
     </row>
-    <row r="143" ht="24" customHeight="1" s="48">
+    <row r="143" ht="24" customHeight="1" s="49">
       <c r="A143" s="2" t="n">
         <v>142</v>
       </c>
@@ -15517,13 +15515,13 @@
       </c>
       <c r="N143" s="2" t="n"/>
       <c r="O143" s="32" t="n">
-        <v>21.1</v>
+        <v>25.3</v>
       </c>
       <c r="P143" s="32" t="n">
-        <v>26.3</v>
+        <v>28.2</v>
       </c>
       <c r="Q143" s="32" t="n">
-        <v>22.93</v>
+        <v>26.34</v>
       </c>
       <c r="R143" s="23" t="inlineStr">
         <is>
@@ -15587,7 +15585,7 @@
       </c>
       <c r="AH143" s="2" t="n"/>
     </row>
-    <row r="144" ht="24" customHeight="1" s="48">
+    <row r="144" ht="24" customHeight="1" s="49">
       <c r="A144" s="2" t="n">
         <v>143</v>
       </c>
@@ -15689,7 +15687,7 @@
       <c r="AG144" s="2" t="n"/>
       <c r="AH144" s="2" t="n"/>
     </row>
-    <row r="145" ht="24" customHeight="1" s="48">
+    <row r="145" ht="24" customHeight="1" s="49">
       <c r="A145" s="2" t="n">
         <v>144</v>
       </c>
@@ -15787,7 +15785,7 @@
       <c r="AG145" s="2" t="n"/>
       <c r="AH145" s="2" t="n"/>
     </row>
-    <row r="146" ht="24" customHeight="1" s="48">
+    <row r="146" ht="24" customHeight="1" s="49">
       <c r="A146" s="2" t="n">
         <v>145</v>
       </c>
@@ -15833,13 +15831,13 @@
       </c>
       <c r="N146" s="2" t="n"/>
       <c r="O146" s="32" t="n">
-        <v>25</v>
+        <v>27.9</v>
       </c>
       <c r="P146" s="32" t="n">
-        <v>30.6</v>
+        <v>34.1</v>
       </c>
       <c r="Q146" s="32" t="n">
-        <v>27.93</v>
+        <v>30.82</v>
       </c>
       <c r="R146" s="23" t="inlineStr">
         <is>
@@ -15895,7 +15893,7 @@
       <c r="AG146" s="2" t="n"/>
       <c r="AH146" s="2" t="n"/>
     </row>
-    <row r="147" ht="24" customHeight="1" s="48">
+    <row r="147" ht="24" customHeight="1" s="49">
       <c r="A147" s="2" t="n">
         <v>146</v>
       </c>
@@ -15941,13 +15939,13 @@
       </c>
       <c r="N147" s="2" t="n"/>
       <c r="O147" s="32" t="n">
-        <v>20.9</v>
+        <v>23</v>
       </c>
       <c r="P147" s="32" t="n">
-        <v>30.9</v>
+        <v>32.6</v>
       </c>
       <c r="Q147" s="32" t="n">
-        <v>25.79</v>
+        <v>27.32</v>
       </c>
       <c r="R147" s="23" t="inlineStr">
         <is>
@@ -16011,7 +16009,7 @@
       </c>
       <c r="AH147" s="2" t="n"/>
     </row>
-    <row r="148" ht="24" customHeight="1" s="48">
+    <row r="148" ht="24" customHeight="1" s="49">
       <c r="A148" s="2" t="n">
         <v>147</v>
       </c>
@@ -16113,7 +16111,7 @@
       </c>
       <c r="AH148" s="2" t="n"/>
     </row>
-    <row r="149" ht="24" customHeight="1" s="48">
+    <row r="149" ht="24" customHeight="1" s="49">
       <c r="A149" s="2" t="n">
         <v>148</v>
       </c>
@@ -16159,13 +16157,13 @@
       </c>
       <c r="N149" s="2" t="n"/>
       <c r="O149" s="32" t="n">
-        <v>10.9</v>
+        <v>12.4</v>
       </c>
       <c r="P149" s="32" t="n">
-        <v>26</v>
+        <v>22.8</v>
       </c>
       <c r="Q149" s="32" t="n">
-        <v>17.69</v>
+        <v>17.4</v>
       </c>
       <c r="R149" s="23" t="inlineStr">
         <is>
@@ -16229,7 +16227,7 @@
       </c>
       <c r="AH149" s="2" t="n"/>
     </row>
-    <row r="150" ht="24" customHeight="1" s="48">
+    <row r="150" ht="24" customHeight="1" s="49">
       <c r="A150" s="2" t="n">
         <v>149</v>
       </c>
@@ -16275,13 +16273,13 @@
       </c>
       <c r="N150" s="2" t="n"/>
       <c r="O150" s="32" t="n">
-        <v>12.7</v>
+        <v>16.5</v>
       </c>
       <c r="P150" s="32" t="n">
-        <v>25.1</v>
+        <v>28.1</v>
       </c>
       <c r="Q150" s="32" t="n">
-        <v>18</v>
+        <v>20.46</v>
       </c>
       <c r="R150" s="23" t="inlineStr">
         <is>
@@ -16345,7 +16343,7 @@
       </c>
       <c r="AH150" s="2" t="n"/>
     </row>
-    <row r="151" ht="24" customHeight="1" s="48">
+    <row r="151" ht="24" customHeight="1" s="49">
       <c r="A151" s="2" t="n">
         <v>150</v>
       </c>
@@ -16391,13 +16389,13 @@
       </c>
       <c r="N151" s="2" t="n"/>
       <c r="O151" s="32" t="n">
-        <v>16.1</v>
+        <v>17.9</v>
       </c>
       <c r="P151" s="32" t="n">
-        <v>30</v>
+        <v>22.5</v>
       </c>
       <c r="Q151" s="32" t="n">
-        <v>22.11</v>
+        <v>19.96</v>
       </c>
       <c r="R151" s="23" t="inlineStr">
         <is>
@@ -16457,7 +16455,7 @@
       </c>
       <c r="AH151" s="2" t="n"/>
     </row>
-    <row r="152" ht="24" customHeight="1" s="48">
+    <row r="152" ht="24" customHeight="1" s="49">
       <c r="A152" s="2" t="n">
         <v>151</v>
       </c>
@@ -16551,7 +16549,7 @@
       </c>
       <c r="AH152" s="2" t="n"/>
     </row>
-    <row r="153" ht="24" customHeight="1" s="48">
+    <row r="153" ht="24" customHeight="1" s="49">
       <c r="A153" s="2" t="n">
         <v>152</v>
       </c>
@@ -16597,13 +16595,13 @@
       </c>
       <c r="N153" s="2" t="n"/>
       <c r="O153" s="32" t="n">
-        <v>11.4</v>
+        <v>14.3</v>
       </c>
       <c r="P153" s="32" t="n">
-        <v>27.4</v>
+        <v>25.2</v>
       </c>
       <c r="Q153" s="32" t="n">
-        <v>18.95</v>
+        <v>19.26</v>
       </c>
       <c r="R153" s="23" t="inlineStr">
         <is>
@@ -16671,7 +16669,7 @@
         </is>
       </c>
     </row>
-    <row r="154" ht="24" customHeight="1" s="48">
+    <row r="154" ht="24" customHeight="1" s="49">
       <c r="A154" s="2" t="n">
         <v>153</v>
       </c>
@@ -16717,13 +16715,13 @@
       </c>
       <c r="N154" s="2" t="n"/>
       <c r="O154" s="32" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="P154" s="32" t="n">
-        <v>20.6</v>
+        <v>15.5</v>
       </c>
       <c r="Q154" s="32" t="n">
-        <v>12.09</v>
+        <v>9.789999999999999</v>
       </c>
       <c r="R154" s="23" t="inlineStr">
         <is>
@@ -16787,7 +16785,7 @@
       </c>
       <c r="AH154" s="2" t="n"/>
     </row>
-    <row r="155" ht="24" customHeight="1" s="48">
+    <row r="155" ht="24" customHeight="1" s="49">
       <c r="A155" s="2" t="n">
         <v>154</v>
       </c>
@@ -16881,7 +16879,7 @@
       </c>
       <c r="AH155" s="2" t="n"/>
     </row>
-    <row r="156" ht="24" customHeight="1" s="48">
+    <row r="156" ht="24" customHeight="1" s="49">
       <c r="A156" s="2" t="n">
         <v>155</v>
       </c>
@@ -16919,10 +16917,10 @@
       </c>
       <c r="N156" s="2" t="n"/>
       <c r="O156" s="32" t="n">
-        <v>-8.1</v>
+        <v>-5.2</v>
       </c>
       <c r="P156" s="32" t="n">
-        <v>17</v>
+        <v>23.8</v>
       </c>
       <c r="Q156" s="32" t="n"/>
       <c r="R156" s="23" t="inlineStr">
@@ -16987,7 +16985,7 @@
       <c r="AG156" s="2" t="n"/>
       <c r="AH156" s="2" t="n"/>
     </row>
-    <row r="157" ht="24" customHeight="1" s="48">
+    <row r="157" ht="24" customHeight="1" s="49">
       <c r="A157" s="2" t="n">
         <v>156</v>
       </c>
@@ -17025,10 +17023,10 @@
       </c>
       <c r="N157" s="2" t="n"/>
       <c r="O157" s="32" t="n">
-        <v>15.5</v>
+        <v>14.3</v>
       </c>
       <c r="P157" s="32" t="n">
-        <v>22.9</v>
+        <v>19.5</v>
       </c>
       <c r="Q157" s="32" t="n"/>
       <c r="R157" s="23" t="inlineStr">
@@ -17093,7 +17091,7 @@
       </c>
       <c r="AH157" s="2" t="n"/>
     </row>
-    <row r="158" ht="24" customHeight="1" s="48">
+    <row r="158" ht="24" customHeight="1" s="49">
       <c r="A158" s="2" t="n">
         <v>157</v>
       </c>
@@ -17187,7 +17185,7 @@
       </c>
       <c r="AH158" s="2" t="n"/>
     </row>
-    <row r="159" ht="24" customHeight="1" s="48">
+    <row r="159" ht="24" customHeight="1" s="49">
       <c r="A159" s="2" t="n">
         <v>158</v>
       </c>
@@ -17281,7 +17279,7 @@
       </c>
       <c r="AH159" s="2" t="n"/>
     </row>
-    <row r="160" ht="24" customHeight="1" s="48">
+    <row r="160" ht="24" customHeight="1" s="49">
       <c r="A160" s="2" t="n">
         <v>159</v>
       </c>
@@ -17375,7 +17373,7 @@
       </c>
       <c r="AH160" s="2" t="n"/>
     </row>
-    <row r="161" ht="24" customHeight="1" s="48">
+    <row r="161" ht="24" customHeight="1" s="49">
       <c r="A161" s="2" t="n">
         <v>160</v>
       </c>
@@ -17413,10 +17411,10 @@
       </c>
       <c r="N161" s="2" t="n"/>
       <c r="O161" s="32" t="n">
-        <v>5.9</v>
+        <v>7.1</v>
       </c>
       <c r="P161" s="32" t="n">
-        <v>23</v>
+        <v>23.6</v>
       </c>
       <c r="Q161" s="32" t="n"/>
       <c r="R161" s="23" t="inlineStr">
@@ -17485,7 +17483,7 @@
         </is>
       </c>
     </row>
-    <row r="162" ht="24" customHeight="1" s="48">
+    <row r="162" ht="24" customHeight="1" s="49">
       <c r="A162" s="2" t="n">
         <v>161</v>
       </c>
@@ -17527,10 +17525,10 @@
         </is>
       </c>
       <c r="O162" s="32" t="n">
-        <v>-17</v>
+        <v>-5</v>
       </c>
       <c r="P162" s="32" t="n">
-        <v>6.1</v>
+        <v>2.3</v>
       </c>
       <c r="Q162" s="32" t="n"/>
       <c r="R162" s="23" t="inlineStr">
@@ -17599,7 +17597,7 @@
         </is>
       </c>
     </row>
-    <row r="163" ht="24" customHeight="1" s="48">
+    <row r="163" ht="24" customHeight="1" s="49">
       <c r="A163" s="2" t="n">
         <v>162</v>
       </c>
@@ -17701,7 +17699,7 @@
       </c>
       <c r="AH163" s="2" t="n"/>
     </row>
-    <row r="164" ht="24" customHeight="1" s="48">
+    <row r="164" ht="24" customHeight="1" s="49">
       <c r="A164" s="2" t="n">
         <v>163</v>
       </c>
@@ -17811,7 +17809,7 @@
       </c>
       <c r="AH164" s="2" t="n"/>
     </row>
-    <row r="165" ht="24" customHeight="1" s="48">
+    <row r="165" ht="24" customHeight="1" s="49">
       <c r="A165" s="2" t="n">
         <v>164</v>
       </c>
@@ -17852,23 +17850,11 @@
           <t>⚡</t>
         </is>
       </c>
-      <c r="O165" s="32" t="n">
-        <v>-8.9</v>
-      </c>
-      <c r="P165" s="32" t="n">
-        <v>5.2</v>
-      </c>
+      <c r="O165" s="32" t="n"/>
+      <c r="P165" s="32" t="n"/>
       <c r="Q165" s="32" t="n"/>
-      <c r="R165" s="23" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="S165" s="37" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="R165" s="23" t="n"/>
+      <c r="S165" s="37" t="n"/>
       <c r="T165" s="44" t="inlineStr">
         <is>
           <t>呼伦贝尔明星站&lt;br&gt;国内一均王</t>
@@ -17925,7 +17911,7 @@
       </c>
       <c r="AH165" s="2" t="n"/>
     </row>
-    <row r="166" ht="24" customHeight="1" s="48">
+    <row r="166" ht="24" customHeight="1" s="49">
       <c r="A166" s="2" t="n">
         <v>165</v>
       </c>
@@ -18035,7 +18021,7 @@
         </is>
       </c>
     </row>
-    <row r="167" ht="24" customHeight="1" s="48">
+    <row r="167" ht="24" customHeight="1" s="49">
       <c r="A167" s="2" t="n">
         <v>166</v>
       </c>
@@ -18137,7 +18123,7 @@
       </c>
       <c r="AH167" s="2" t="n"/>
     </row>
-    <row r="168" ht="24" customHeight="1" s="48">
+    <row r="168" ht="24" customHeight="1" s="49">
       <c r="A168" s="2" t="n">
         <v>167</v>
       </c>
@@ -18247,7 +18233,7 @@
       </c>
       <c r="AH168" s="2" t="n"/>
     </row>
-    <row r="169" ht="24" customHeight="1" s="48">
+    <row r="169" ht="24" customHeight="1" s="49">
       <c r="A169" s="2" t="n">
         <v>168</v>
       </c>
@@ -18357,7 +18343,7 @@
       </c>
       <c r="AH169" s="2" t="n"/>
     </row>
-    <row r="170" ht="24" customHeight="1" s="48">
+    <row r="170" ht="24" customHeight="1" s="49">
       <c r="A170" s="2" t="n">
         <v>169</v>
       </c>
@@ -18398,8 +18384,12 @@
           <t>⚡</t>
         </is>
       </c>
-      <c r="O170" s="32" t="n"/>
-      <c r="P170" s="32" t="n"/>
+      <c r="O170" s="32" t="n">
+        <v>-2.4</v>
+      </c>
+      <c r="P170" s="32" t="n">
+        <v>2.7</v>
+      </c>
       <c r="Q170" s="32" t="n"/>
       <c r="R170" s="23" t="inlineStr">
         <is>
@@ -18467,7 +18457,7 @@
         </is>
       </c>
     </row>
-    <row r="171" ht="24" customHeight="1" s="48">
+    <row r="171" ht="24" customHeight="1" s="49">
       <c r="A171" s="2" t="n">
         <v>170</v>
       </c>
@@ -18504,8 +18494,12 @@
         </is>
       </c>
       <c r="N171" s="2" t="n"/>
-      <c r="O171" s="32" t="n"/>
-      <c r="P171" s="32" t="n"/>
+      <c r="O171" s="32" t="n">
+        <v>-5.4</v>
+      </c>
+      <c r="P171" s="32" t="n">
+        <v>-3.2</v>
+      </c>
       <c r="Q171" s="32" t="n"/>
       <c r="R171" s="23" t="inlineStr">
         <is>
@@ -18573,7 +18567,7 @@
         </is>
       </c>
     </row>
-    <row r="172" ht="24" customHeight="1" s="48">
+    <row r="172" ht="24" customHeight="1" s="49">
       <c r="A172" s="2" t="n">
         <v>171</v>
       </c>
@@ -18679,7 +18673,7 @@
       </c>
       <c r="AH172" s="2" t="n"/>
     </row>
-    <row r="173" ht="24" customHeight="1" s="48">
+    <row r="173" ht="24" customHeight="1" s="49">
       <c r="A173" s="2" t="n">
         <v>172</v>
       </c>
@@ -18717,10 +18711,10 @@
       </c>
       <c r="N173" s="2" t="n"/>
       <c r="O173" s="32" t="n">
-        <v>-12</v>
+        <v>-5.6</v>
       </c>
       <c r="P173" s="32" t="n">
-        <v>8.199999999999999</v>
+        <v>15.7</v>
       </c>
       <c r="Q173" s="32" t="n"/>
       <c r="R173" s="23" t="inlineStr">
@@ -18785,7 +18779,7 @@
       <c r="AG173" s="2" t="n"/>
       <c r="AH173" s="2" t="n"/>
     </row>
-    <row r="174" ht="24" customHeight="1" s="48">
+    <row r="174" ht="24" customHeight="1" s="49">
       <c r="A174" s="2" t="n">
         <v>173</v>
       </c>
@@ -18891,7 +18885,7 @@
         </is>
       </c>
     </row>
-    <row r="175" ht="24" customHeight="1" s="48">
+    <row r="175" ht="24" customHeight="1" s="49">
       <c r="A175" s="2" t="n">
         <v>174</v>
       </c>
@@ -18993,7 +18987,7 @@
       </c>
       <c r="AH175" s="2" t="n"/>
     </row>
-    <row r="176" ht="24" customHeight="1" s="48">
+    <row r="176" ht="24" customHeight="1" s="49">
       <c r="A176" s="2" t="n">
         <v>175</v>
       </c>
@@ -19039,10 +19033,10 @@
       </c>
       <c r="N176" s="2" t="n"/>
       <c r="O176" s="32" t="n">
-        <v>5</v>
+        <v>10.9</v>
       </c>
       <c r="P176" s="32" t="n">
-        <v>11.7</v>
+        <v>13.8</v>
       </c>
       <c r="Q176" s="32" t="n"/>
       <c r="R176" s="23" t="inlineStr">
@@ -19103,7 +19097,7 @@
         </is>
       </c>
     </row>
-    <row r="177" ht="24" customHeight="1" s="48">
+    <row r="177" ht="24" customHeight="1" s="49">
       <c r="A177" s="2" t="n">
         <v>176</v>
       </c>
@@ -19141,10 +19135,10 @@
       </c>
       <c r="N177" s="2" t="n"/>
       <c r="O177" s="32" t="n">
-        <v>-11.3</v>
+        <v>-16</v>
       </c>
       <c r="P177" s="32" t="n">
-        <v>-5</v>
+        <v>-7</v>
       </c>
       <c r="Q177" s="32" t="n"/>
       <c r="R177" s="23" t="inlineStr">
@@ -19217,7 +19211,7 @@
         </is>
       </c>
     </row>
-    <row r="178" ht="24" customHeight="1" s="48">
+    <row r="178" ht="24" customHeight="1" s="49">
       <c r="A178" s="2" t="n">
         <v>177</v>
       </c>
@@ -19327,7 +19321,7 @@
         </is>
       </c>
     </row>
-    <row r="179" ht="24" customHeight="1" s="48">
+    <row r="179" ht="24" customHeight="1" s="49">
       <c r="A179" s="2" t="n">
         <v>178</v>
       </c>
@@ -19433,7 +19427,7 @@
         </is>
       </c>
     </row>
-    <row r="180" ht="24" customHeight="1" s="48">
+    <row r="180" ht="24" customHeight="1" s="49">
       <c r="A180" s="2" t="n">
         <v>179</v>
       </c>
@@ -19535,7 +19529,7 @@
         </is>
       </c>
     </row>
-    <row r="181" ht="24" customHeight="1" s="48">
+    <row r="181" ht="24" customHeight="1" s="49">
       <c r="A181" s="2" t="n">
         <v>180</v>
       </c>
@@ -19633,7 +19627,7 @@
         </is>
       </c>
     </row>
-    <row r="182" ht="24" customHeight="1" s="48">
+    <row r="182" ht="24" customHeight="1" s="49">
       <c r="A182" s="2" t="n">
         <v>181</v>
       </c>
@@ -19719,7 +19713,7 @@
       <c r="AG182" s="2" t="n"/>
       <c r="AH182" s="2" t="n"/>
     </row>
-    <row r="183" ht="24" customHeight="1" s="48">
+    <row r="183" ht="24" customHeight="1" s="49">
       <c r="A183" s="2" t="n">
         <v>182</v>
       </c>
@@ -19801,7 +19795,7 @@
       <c r="AG183" s="2" t="n"/>
       <c r="AH183" s="2" t="n"/>
     </row>
-    <row r="184" ht="24" customHeight="1" s="48">
+    <row r="184" ht="24" customHeight="1" s="49">
       <c r="A184" s="2" t="n">
         <v>183</v>
       </c>
@@ -19883,7 +19877,7 @@
       <c r="AG184" s="2" t="n"/>
       <c r="AH184" s="2" t="n"/>
     </row>
-    <row r="185" ht="24" customHeight="1" s="48">
+    <row r="185" ht="24" customHeight="1" s="49">
       <c r="A185" s="2" t="n">
         <v>184</v>
       </c>
@@ -19982,7 +19976,7 @@
         </is>
       </c>
     </row>
-    <row r="186" ht="24" customHeight="1" s="48">
+    <row r="186" ht="24" customHeight="1" s="49">
       <c r="A186" s="2" t="n">
         <v>185</v>
       </c>
@@ -20081,7 +20075,7 @@
         </is>
       </c>
     </row>
-    <row r="187" ht="24" customHeight="1" s="48">
+    <row r="187" ht="24" customHeight="1" s="49">
       <c r="A187" s="2" t="n">
         <v>186</v>
       </c>
@@ -20175,7 +20169,7 @@
       </c>
       <c r="AH187" s="2" t="n"/>
     </row>
-    <row r="188" ht="24" customHeight="1" s="48">
+    <row r="188" ht="24" customHeight="1" s="49">
       <c r="A188" s="2" t="n">
         <v>187</v>
       </c>
@@ -20269,7 +20263,7 @@
       </c>
       <c r="AH188" s="2" t="n"/>
     </row>
-    <row r="189" ht="24" customHeight="1" s="48">
+    <row r="189" ht="24" customHeight="1" s="49">
       <c r="A189" s="2" t="n">
         <v>188</v>
       </c>
@@ -20363,7 +20357,7 @@
       </c>
       <c r="AH189" s="2" t="n"/>
     </row>
-    <row r="190" ht="24" customHeight="1" s="48">
+    <row r="190" ht="24" customHeight="1" s="49">
       <c r="A190" s="2" t="n">
         <v>189</v>
       </c>
@@ -20457,7 +20451,7 @@
       </c>
       <c r="AH190" s="2" t="n"/>
     </row>
-    <row r="191" ht="24" customHeight="1" s="48">
+    <row r="191" ht="24" customHeight="1" s="49">
       <c r="A191" s="2" t="n">
         <v>190</v>
       </c>
@@ -20547,7 +20541,7 @@
       <c r="AG191" s="2" t="n"/>
       <c r="AH191" s="2" t="n"/>
     </row>
-    <row r="192" ht="24" customHeight="1" s="48">
+    <row r="192" ht="24" customHeight="1" s="49">
       <c r="A192" s="2" t="n">
         <v>191</v>
       </c>
@@ -20642,7 +20636,7 @@
       </c>
       <c r="AH192" s="2" t="n"/>
     </row>
-    <row r="193" ht="24" customHeight="1" s="48">
+    <row r="193" ht="24" customHeight="1" s="49">
       <c r="A193" s="2" t="n">
         <v>192</v>
       </c>
@@ -20740,7 +20734,7 @@
       </c>
       <c r="AH193" s="2" t="n"/>
     </row>
-    <row r="194" ht="24" customHeight="1" s="48">
+    <row r="194" ht="24" customHeight="1" s="49">
       <c r="A194" s="2" t="n">
         <v>193</v>
       </c>
@@ -20830,7 +20824,7 @@
       <c r="AG194" s="2" t="n"/>
       <c r="AH194" s="2" t="n"/>
     </row>
-    <row r="195" ht="24" customHeight="1" s="48">
+    <row r="195" ht="24" customHeight="1" s="49">
       <c r="A195" s="2" t="n">
         <v>194</v>
       </c>
@@ -20924,7 +20918,7 @@
       </c>
       <c r="AH195" s="2" t="n"/>
     </row>
-    <row r="196" ht="24" customHeight="1" s="48">
+    <row r="196" ht="24" customHeight="1" s="49">
       <c r="A196" s="2" t="n">
         <v>195</v>
       </c>
@@ -21018,7 +21012,7 @@
       </c>
       <c r="AH196" s="2" t="n"/>
     </row>
-    <row r="197" ht="24" customHeight="1" s="48">
+    <row r="197" ht="24" customHeight="1" s="49">
       <c r="A197" s="2" t="n">
         <v>196</v>
       </c>
@@ -21112,7 +21106,7 @@
       </c>
       <c r="AH197" s="2" t="n"/>
     </row>
-    <row r="198" ht="24" customHeight="1" s="48">
+    <row r="198" ht="24" customHeight="1" s="49">
       <c r="A198" s="2" t="n">
         <v>197</v>
       </c>
@@ -21214,7 +21208,7 @@
       </c>
       <c r="AH198" s="2" t="n"/>
     </row>
-    <row r="199" ht="24" customHeight="1" s="48">
+    <row r="199" ht="24" customHeight="1" s="49">
       <c r="A199" s="2" t="n">
         <v>198</v>
       </c>
@@ -21312,7 +21306,7 @@
       </c>
       <c r="AH199" s="2" t="n"/>
     </row>
-    <row r="200" ht="24" customHeight="1" s="48">
+    <row r="200" ht="24" customHeight="1" s="49">
       <c r="A200" s="2" t="n">
         <v>199</v>
       </c>
@@ -21414,7 +21408,7 @@
       </c>
       <c r="AH200" s="2" t="n"/>
     </row>
-    <row r="201" ht="24" customHeight="1" s="48">
+    <row r="201" ht="24" customHeight="1" s="49">
       <c r="A201" s="2" t="n">
         <v>200</v>
       </c>
@@ -21516,7 +21510,7 @@
       </c>
       <c r="AH201" s="2" t="n"/>
     </row>
-    <row r="202" ht="24" customHeight="1" s="48">
+    <row r="202" ht="24" customHeight="1" s="49">
       <c r="A202" s="2" t="n">
         <v>201</v>
       </c>
@@ -21618,7 +21612,7 @@
       </c>
       <c r="AH202" s="2" t="n"/>
     </row>
-    <row r="203" ht="24" customHeight="1" s="48">
+    <row r="203" ht="24" customHeight="1" s="49">
       <c r="A203" s="2" t="n">
         <v>202</v>
       </c>
@@ -21720,7 +21714,7 @@
       </c>
       <c r="AH203" s="2" t="n"/>
     </row>
-    <row r="204" ht="24" customHeight="1" s="48">
+    <row r="204" ht="24" customHeight="1" s="49">
       <c r="A204" s="2" t="n">
         <v>203</v>
       </c>
@@ -21822,7 +21816,7 @@
       </c>
       <c r="AH204" s="2" t="n"/>
     </row>
-    <row r="205" ht="24" customHeight="1" s="48">
+    <row r="205" ht="24" customHeight="1" s="49">
       <c r="A205" s="2" t="n">
         <v>204</v>
       </c>
@@ -21924,7 +21918,7 @@
       </c>
       <c r="AH205" s="2" t="n"/>
     </row>
-    <row r="206" ht="24" customHeight="1" s="48">
+    <row r="206" ht="24" customHeight="1" s="49">
       <c r="A206" s="2" t="n">
         <v>205</v>
       </c>
@@ -22026,7 +22020,7 @@
       </c>
       <c r="AH206" s="2" t="n"/>
     </row>
-    <row r="207" ht="24" customHeight="1" s="48">
+    <row r="207" ht="24" customHeight="1" s="49">
       <c r="A207" s="2" t="n">
         <v>206</v>
       </c>
@@ -22124,7 +22118,7 @@
       <c r="AG207" s="2" t="n"/>
       <c r="AH207" s="2" t="n"/>
     </row>
-    <row r="208" ht="24" customHeight="1" s="48">
+    <row r="208" ht="24" customHeight="1" s="49">
       <c r="A208" s="2" t="n">
         <v>207</v>
       </c>
@@ -22216,7 +22210,7 @@
       </c>
       <c r="AH208" s="2" t="n"/>
     </row>
-    <row r="209" ht="24" customHeight="1" s="48">
+    <row r="209" ht="24" customHeight="1" s="49">
       <c r="A209" s="2" t="n">
         <v>208</v>
       </c>
@@ -22318,7 +22312,7 @@
       <c r="AG209" s="2" t="n"/>
       <c r="AH209" s="2" t="n"/>
     </row>
-    <row r="210" ht="24" customHeight="1" s="48">
+    <row r="210" ht="24" customHeight="1" s="49">
       <c r="A210" s="2" t="n">
         <v>209</v>
       </c>
@@ -22416,7 +22410,7 @@
       </c>
       <c r="AH210" s="2" t="n"/>
     </row>
-    <row r="211" ht="24" customHeight="1" s="48">
+    <row r="211" ht="24" customHeight="1" s="49">
       <c r="A211" s="2" t="n">
         <v>210</v>
       </c>
@@ -22518,7 +22512,7 @@
       </c>
       <c r="AH211" s="2" t="n"/>
     </row>
-    <row r="212" ht="24" customHeight="1" s="48">
+    <row r="212" ht="24" customHeight="1" s="49">
       <c r="A212" s="2" t="n">
         <v>211</v>
       </c>
@@ -22620,7 +22614,7 @@
       </c>
       <c r="AH212" s="2" t="n"/>
     </row>
-    <row r="213" ht="24" customHeight="1" s="48">
+    <row r="213" ht="24" customHeight="1" s="49">
       <c r="A213" s="2" t="n">
         <v>212</v>
       </c>
@@ -22657,8 +22651,12 @@
         </is>
       </c>
       <c r="N213" s="2" t="n"/>
-      <c r="O213" s="32" t="n"/>
-      <c r="P213" s="32" t="n"/>
+      <c r="O213" s="32" t="n">
+        <v>-6.5</v>
+      </c>
+      <c r="P213" s="32" t="n">
+        <v>4.7</v>
+      </c>
       <c r="Q213" s="32" t="n"/>
       <c r="R213" s="23" t="inlineStr">
         <is>
@@ -22722,7 +22720,7 @@
       </c>
       <c r="AH213" s="2" t="n"/>
     </row>
-    <row r="214" ht="24" customHeight="1" s="48">
+    <row r="214" ht="24" customHeight="1" s="49">
       <c r="A214" s="2" t="n">
         <v>213</v>
       </c>
@@ -22824,7 +22822,7 @@
       </c>
       <c r="AH214" s="2" t="n"/>
     </row>
-    <row r="215" ht="24" customHeight="1" s="48">
+    <row r="215" ht="24" customHeight="1" s="49">
       <c r="A215" s="2" t="n">
         <v>214</v>
       </c>
@@ -22926,7 +22924,7 @@
       </c>
       <c r="AH215" s="2" t="n"/>
     </row>
-    <row r="216" ht="24" customHeight="1" s="48">
+    <row r="216" ht="24" customHeight="1" s="49">
       <c r="A216" s="2" t="n">
         <v>215</v>
       </c>
@@ -23028,7 +23026,7 @@
       </c>
       <c r="AH216" s="2" t="n"/>
     </row>
-    <row r="217" ht="24" customHeight="1" s="48">
+    <row r="217" ht="24" customHeight="1" s="49">
       <c r="A217" s="2" t="n">
         <v>216</v>
       </c>
@@ -23116,7 +23114,7 @@
       </c>
       <c r="AH217" s="2" t="n"/>
     </row>
-    <row r="218" ht="24" customHeight="1" s="48">
+    <row r="218" ht="24" customHeight="1" s="49">
       <c r="A218" s="2" t="n">
         <v>217</v>
       </c>
@@ -23218,7 +23216,7 @@
       </c>
       <c r="AH218" s="2" t="n"/>
     </row>
-    <row r="219" ht="24" customHeight="1" s="48">
+    <row r="219" ht="24" customHeight="1" s="49">
       <c r="A219" s="2" t="n">
         <v>218</v>
       </c>
@@ -23320,7 +23318,7 @@
       </c>
       <c r="AH219" s="2" t="n"/>
     </row>
-    <row r="220" ht="24" customHeight="1" s="48">
+    <row r="220" ht="24" customHeight="1" s="49">
       <c r="A220" s="2" t="n">
         <v>219</v>
       </c>
@@ -23422,7 +23420,7 @@
       </c>
       <c r="AH220" s="2" t="n"/>
     </row>
-    <row r="221" ht="24" customHeight="1" s="48">
+    <row r="221" ht="24" customHeight="1" s="49">
       <c r="A221" s="2" t="n">
         <v>220</v>
       </c>
@@ -23514,7 +23512,7 @@
       </c>
       <c r="AH221" s="2" t="n"/>
     </row>
-    <row r="222" ht="24" customHeight="1" s="48">
+    <row r="222" ht="24" customHeight="1" s="49">
       <c r="A222" s="2" t="n">
         <v>221</v>
       </c>
@@ -23614,7 +23612,7 @@
       </c>
       <c r="AH222" s="2" t="n"/>
     </row>
-    <row r="223" ht="24" customHeight="1" s="48">
+    <row r="223" ht="24" customHeight="1" s="49">
       <c r="A223" s="2" t="n">
         <v>222</v>
       </c>
@@ -23716,7 +23714,7 @@
       </c>
       <c r="AH223" s="2" t="n"/>
     </row>
-    <row r="224" ht="24" customHeight="1" s="48">
+    <row r="224" ht="24" customHeight="1" s="49">
       <c r="A224" s="2" t="n">
         <v>223</v>
       </c>
@@ -23818,7 +23816,7 @@
       </c>
       <c r="AH224" s="2" t="n"/>
     </row>
-    <row r="225" ht="24" customHeight="1" s="48">
+    <row r="225" ht="24" customHeight="1" s="49">
       <c r="A225" s="2" t="n">
         <v>224</v>
       </c>
@@ -23920,7 +23918,7 @@
       </c>
       <c r="AH225" s="2" t="n"/>
     </row>
-    <row r="226" ht="24" customHeight="1" s="48">
+    <row r="226" ht="24" customHeight="1" s="49">
       <c r="A226" s="2" t="n">
         <v>225</v>
       </c>
@@ -24022,7 +24020,7 @@
       <c r="AG226" s="2" t="n"/>
       <c r="AH226" s="2" t="n"/>
     </row>
-    <row r="227" ht="24" customHeight="1" s="48">
+    <row r="227" ht="24" customHeight="1" s="49">
       <c r="A227" s="2" t="n">
         <v>226</v>
       </c>
@@ -24124,7 +24122,7 @@
       </c>
       <c r="AH227" s="2" t="n"/>
     </row>
-    <row r="228" ht="24" customHeight="1" s="48">
+    <row r="228" ht="24" customHeight="1" s="49">
       <c r="A228" s="2" t="n">
         <v>227</v>
       </c>
@@ -24230,7 +24228,7 @@
       </c>
       <c r="AH228" s="2" t="n"/>
     </row>
-    <row r="229" ht="24" customHeight="1" s="48">
+    <row r="229" ht="24" customHeight="1" s="49">
       <c r="A229" s="2" t="n">
         <v>228</v>
       </c>
@@ -24326,7 +24324,7 @@
       </c>
       <c r="AH229" s="2" t="n"/>
     </row>
-    <row r="230" ht="24" customHeight="1" s="48">
+    <row r="230" ht="24" customHeight="1" s="49">
       <c r="A230" s="2" t="n">
         <v>229</v>
       </c>
@@ -24368,7 +24366,7 @@
       <c r="S230" s="37" t="n"/>
       <c r="T230" s="41" t="inlineStr">
         <is>
-          <t>呼伦贝尔</t>
+          <t>呼伦贝尔&lt;br&gt;根河敖鲁古雅乡</t>
         </is>
       </c>
       <c r="U230" s="2" t="inlineStr">
@@ -24422,7 +24420,7 @@
       </c>
       <c r="AH230" s="2" t="n"/>
     </row>
-    <row r="231" ht="24" customHeight="1" s="48">
+    <row r="231" ht="24" customHeight="1" s="49">
       <c r="A231" s="2" t="n">
         <v>230</v>
       </c>
@@ -24510,7 +24508,7 @@
       </c>
       <c r="AH231" s="2" t="n"/>
     </row>
-    <row r="232" ht="24" customHeight="1" s="48">
+    <row r="232" ht="24" customHeight="1" s="49">
       <c r="A232" s="2" t="n">
         <v>231</v>
       </c>
@@ -24602,7 +24600,7 @@
       </c>
       <c r="AH232" s="2" t="n"/>
     </row>
-    <row r="233" ht="24" customHeight="1" s="48">
+    <row r="233" ht="24" customHeight="1" s="49">
       <c r="A233" s="2" t="n">
         <v>232</v>
       </c>
@@ -24694,7 +24692,7 @@
       </c>
       <c r="AH233" s="2" t="n"/>
     </row>
-    <row r="234" ht="24" customHeight="1" s="48">
+    <row r="234" ht="24" customHeight="1" s="49">
       <c r="A234" s="2" t="n">
         <v>233</v>
       </c>
@@ -24790,7 +24788,7 @@
       </c>
       <c r="AH234" s="2" t="n"/>
     </row>
-    <row r="235" ht="24" customHeight="1" s="48">
+    <row r="235" ht="24" customHeight="1" s="49">
       <c r="A235" s="2" t="n">
         <v>234</v>
       </c>
@@ -24886,7 +24884,7 @@
       </c>
       <c r="AH235" s="2" t="n"/>
     </row>
-    <row r="236" ht="24" customHeight="1" s="48">
+    <row r="236" ht="24" customHeight="1" s="49">
       <c r="A236" s="2" t="n">
         <v>235</v>
       </c>
@@ -24978,7 +24976,7 @@
       </c>
       <c r="AH236" s="2" t="n"/>
     </row>
-    <row r="237" ht="24" customHeight="1" s="48">
+    <row r="237" ht="24" customHeight="1" s="49">
       <c r="A237" s="2" t="n">
         <v>236</v>
       </c>
@@ -25080,7 +25078,7 @@
       </c>
       <c r="AH237" s="2" t="n"/>
     </row>
-    <row r="238" ht="24" customHeight="1" s="48">
+    <row r="238" ht="24" customHeight="1" s="49">
       <c r="A238" s="2" t="n">
         <v>237</v>
       </c>
@@ -25182,7 +25180,7 @@
       </c>
       <c r="AH238" s="2" t="n"/>
     </row>
-    <row r="239" ht="24" customHeight="1" s="48">
+    <row r="239" ht="24" customHeight="1" s="49">
       <c r="A239" s="2" t="n">
         <v>238</v>
       </c>
@@ -25280,7 +25278,7 @@
       <c r="AG239" s="2" t="n"/>
       <c r="AH239" s="2" t="n"/>
     </row>
-    <row r="240" ht="24" customHeight="1" s="48">
+    <row r="240" ht="24" customHeight="1" s="49">
       <c r="A240" s="2" t="n">
         <v>239</v>
       </c>
@@ -25376,7 +25374,7 @@
       </c>
       <c r="AH240" s="2" t="n"/>
     </row>
-    <row r="241" ht="24" customHeight="1" s="48">
+    <row r="241" ht="24" customHeight="1" s="49">
       <c r="A241" s="2" t="n">
         <v>240</v>
       </c>
@@ -25478,7 +25476,7 @@
       </c>
       <c r="AH241" s="2" t="n"/>
     </row>
-    <row r="242" ht="24" customHeight="1" s="48">
+    <row r="242" ht="24" customHeight="1" s="49">
       <c r="A242" s="2" t="n">
         <v>241</v>
       </c>
@@ -25568,7 +25566,7 @@
       <c r="AG242" s="2" t="n"/>
       <c r="AH242" s="2" t="n"/>
     </row>
-    <row r="243" ht="24" customHeight="1" s="48">
+    <row r="243" ht="24" customHeight="1" s="49">
       <c r="A243" s="2" t="n">
         <v>242</v>
       </c>
@@ -25666,7 +25664,7 @@
       <c r="AG243" s="2" t="n"/>
       <c r="AH243" s="2" t="n"/>
     </row>
-    <row r="244" ht="24" customHeight="1" s="48">
+    <row r="244" ht="24" customHeight="1" s="49">
       <c r="A244" s="2" t="n">
         <v>243</v>
       </c>
@@ -25762,7 +25760,7 @@
       </c>
       <c r="AH244" s="2" t="n"/>
     </row>
-    <row r="245" ht="24" customHeight="1" s="48">
+    <row r="245" ht="24" customHeight="1" s="49">
       <c r="A245" s="2" t="n">
         <v>244</v>
       </c>
@@ -25854,7 +25852,7 @@
       <c r="AG245" s="2" t="n"/>
       <c r="AH245" s="2" t="n"/>
     </row>
-    <row r="246" ht="24" customHeight="1" s="48">
+    <row r="246" ht="24" customHeight="1" s="49">
       <c r="A246" s="2" t="n">
         <v>245</v>
       </c>
@@ -25942,7 +25940,7 @@
       <c r="AG246" s="2" t="n"/>
       <c r="AH246" s="2" t="n"/>
     </row>
-    <row r="247" ht="24" customHeight="1" s="48">
+    <row r="247" ht="24" customHeight="1" s="49">
       <c r="A247" s="2" t="n">
         <v>246</v>
       </c>
@@ -26044,7 +26042,7 @@
       <c r="AG247" s="2" t="n"/>
       <c r="AH247" s="2" t="n"/>
     </row>
-    <row r="248" ht="24" customHeight="1" s="48">
+    <row r="248" ht="24" customHeight="1" s="49">
       <c r="A248" s="2" t="n">
         <v>247</v>
       </c>
@@ -26146,7 +26144,7 @@
       </c>
       <c r="AH248" s="2" t="n"/>
     </row>
-    <row r="249" ht="24" customHeight="1" s="48">
+    <row r="249" ht="24" customHeight="1" s="49">
       <c r="A249" s="2" t="n">
         <v>248</v>
       </c>
@@ -26248,7 +26246,7 @@
       <c r="AG249" s="2" t="n"/>
       <c r="AH249" s="2" t="n"/>
     </row>
-    <row r="250" ht="24" customHeight="1" s="48">
+    <row r="250" ht="24" customHeight="1" s="49">
       <c r="A250" s="2" t="n">
         <v>249</v>
       </c>
@@ -26354,7 +26352,7 @@
       </c>
       <c r="AH250" s="2" t="n"/>
     </row>
-    <row r="251" ht="24" customHeight="1" s="48">
+    <row r="251" ht="24" customHeight="1" s="49">
       <c r="A251" s="2" t="n">
         <v>250</v>
       </c>
@@ -26448,7 +26446,7 @@
       <c r="AG251" s="2" t="n"/>
       <c r="AH251" s="2" t="n"/>
     </row>
-    <row r="252" ht="24" customHeight="1" s="48">
+    <row r="252" ht="24" customHeight="1" s="49">
       <c r="A252" s="2" t="n">
         <v>251</v>
       </c>
@@ -26550,7 +26548,7 @@
       <c r="AG252" s="2" t="n"/>
       <c r="AH252" s="2" t="n"/>
     </row>
-    <row r="253" ht="24" customHeight="1" s="48">
+    <row r="253" ht="24" customHeight="1" s="49">
       <c r="A253" s="2" t="n">
         <v>252</v>
       </c>
@@ -26636,7 +26634,7 @@
       <c r="AG253" s="2" t="n"/>
       <c r="AH253" s="2" t="n"/>
     </row>
-    <row r="254" ht="24" customHeight="1" s="48">
+    <row r="254" ht="24" customHeight="1" s="49">
       <c r="A254" s="2" t="n">
         <v>253</v>
       </c>
@@ -26730,7 +26728,7 @@
       <c r="AG254" s="2" t="n"/>
       <c r="AH254" s="2" t="n"/>
     </row>
-    <row r="255" ht="24" customHeight="1" s="48">
+    <row r="255" ht="24" customHeight="1" s="49">
       <c r="A255" s="2" t="n">
         <v>254</v>
       </c>
@@ -26824,7 +26822,7 @@
       <c r="AG255" s="2" t="n"/>
       <c r="AH255" s="2" t="n"/>
     </row>
-    <row r="256" ht="24" customHeight="1" s="48">
+    <row r="256" ht="24" customHeight="1" s="49">
       <c r="A256" s="2" t="n">
         <v>255</v>
       </c>
@@ -26922,7 +26920,7 @@
       </c>
       <c r="AH256" s="2" t="n"/>
     </row>
-    <row r="257" ht="24" customHeight="1" s="48">
+    <row r="257" ht="24" customHeight="1" s="49">
       <c r="A257" s="2" t="n">
         <v>256</v>
       </c>
@@ -27020,7 +27018,7 @@
       </c>
       <c r="AH257" s="2" t="n"/>
     </row>
-    <row r="258" ht="24" customHeight="1" s="48">
+    <row r="258" ht="24" customHeight="1" s="49">
       <c r="A258" s="2" t="n">
         <v>257</v>
       </c>
@@ -27110,7 +27108,7 @@
       <c r="AG258" s="2" t="n"/>
       <c r="AH258" s="2" t="n"/>
     </row>
-    <row r="259" ht="24" customHeight="1" s="48">
+    <row r="259" ht="24" customHeight="1" s="49">
       <c r="A259" s="2" t="n">
         <v>258</v>
       </c>
@@ -27200,7 +27198,7 @@
       <c r="AG259" s="2" t="n"/>
       <c r="AH259" s="2" t="n"/>
     </row>
-    <row r="260" ht="24" customHeight="1" s="48">
+    <row r="260" ht="24" customHeight="1" s="49">
       <c r="A260" s="2" t="n">
         <v>259</v>
       </c>
@@ -27298,7 +27296,7 @@
       </c>
       <c r="AH260" s="2" t="n"/>
     </row>
-    <row r="261" ht="24" customHeight="1" s="48">
+    <row r="261" ht="24" customHeight="1" s="49">
       <c r="A261" s="2" t="n">
         <v>260</v>
       </c>
@@ -27400,7 +27398,7 @@
       <c r="AG261" s="2" t="n"/>
       <c r="AH261" s="2" t="n"/>
     </row>
-    <row r="262" ht="24" customHeight="1" s="48">
+    <row r="262" ht="24" customHeight="1" s="49">
       <c r="A262" s="2" t="n">
         <v>261</v>
       </c>
@@ -27502,7 +27500,7 @@
       <c r="AG262" s="2" t="n"/>
       <c r="AH262" s="2" t="n"/>
     </row>
-    <row r="263" ht="24" customHeight="1" s="48">
+    <row r="263" ht="24" customHeight="1" s="49">
       <c r="A263" s="2" t="n">
         <v>262</v>
       </c>
@@ -27596,7 +27594,7 @@
       </c>
       <c r="AH263" s="2" t="n"/>
     </row>
-    <row r="264" ht="24" customHeight="1" s="48">
+    <row r="264" ht="24" customHeight="1" s="49">
       <c r="A264" s="2" t="n">
         <v>263</v>
       </c>
@@ -27702,7 +27700,7 @@
       </c>
       <c r="AH264" s="2" t="n"/>
     </row>
-    <row r="265" ht="24" customHeight="1" s="48">
+    <row r="265" ht="24" customHeight="1" s="49">
       <c r="A265" s="2" t="n">
         <v>264</v>
       </c>
@@ -27752,10 +27750,10 @@
       </c>
       <c r="N265" s="2" t="n"/>
       <c r="O265" s="32" t="n">
-        <v>-56.5</v>
+        <v>-53.5</v>
       </c>
       <c r="P265" s="32" t="n">
-        <v>-47.1</v>
+        <v>-48.9</v>
       </c>
       <c r="Q265" s="32" t="n"/>
       <c r="R265" s="23" t="inlineStr">
@@ -27804,7 +27802,7 @@
       </c>
       <c r="AH265" s="2" t="n"/>
     </row>
-    <row r="266" ht="24" customHeight="1" s="48">
+    <row r="266" ht="24" customHeight="1" s="49">
       <c r="A266" s="2" t="n">
         <v>265</v>
       </c>
@@ -27896,7 +27894,7 @@
       <c r="AG266" s="2" t="n"/>
       <c r="AH266" s="2" t="n"/>
     </row>
-    <row r="267" ht="24" customHeight="1" s="48">
+    <row r="267" ht="24" customHeight="1" s="49">
       <c r="A267" s="2" t="n">
         <v>266</v>
       </c>
@@ -27982,7 +27980,7 @@
       <c r="AG267" s="2" t="n"/>
       <c r="AH267" s="2" t="n"/>
     </row>
-    <row r="268" ht="24" customHeight="1" s="48">
+    <row r="268" ht="24" customHeight="1" s="49">
       <c r="A268" s="2" t="n">
         <v>267</v>
       </c>
@@ -28074,7 +28072,7 @@
       <c r="AG268" s="2" t="n"/>
       <c r="AH268" s="2" t="n"/>
     </row>
-    <row r="269" ht="24" customHeight="1" s="48">
+    <row r="269" ht="24" customHeight="1" s="49">
       <c r="A269" s="2" t="n">
         <v>268</v>
       </c>
@@ -28172,7 +28170,7 @@
       <c r="AG269" s="2" t="n"/>
       <c r="AH269" s="2" t="n"/>
     </row>
-    <row r="270" ht="24" customHeight="1" s="48">
+    <row r="270" ht="24" customHeight="1" s="49">
       <c r="A270" s="2" t="n">
         <v>269</v>
       </c>
@@ -28266,7 +28264,7 @@
       <c r="AG270" s="2" t="n"/>
       <c r="AH270" s="2" t="n"/>
     </row>
-    <row r="271" ht="24" customHeight="1" s="48">
+    <row r="271" ht="24" customHeight="1" s="49">
       <c r="A271" s="2" t="n">
         <v>270</v>
       </c>
@@ -28364,7 +28362,7 @@
       <c r="AG271" s="2" t="n"/>
       <c r="AH271" s="2" t="n"/>
     </row>
-    <row r="272" ht="24" customHeight="1" s="48">
+    <row r="272" ht="24" customHeight="1" s="49">
       <c r="A272" s="2" t="n">
         <v>271</v>
       </c>
@@ -28466,7 +28464,7 @@
       </c>
       <c r="AH272" s="2" t="n"/>
     </row>
-    <row r="273" ht="24" customHeight="1" s="48">
+    <row r="273" ht="24" customHeight="1" s="49">
       <c r="A273" s="2" t="n">
         <v>272</v>
       </c>
@@ -28560,7 +28558,7 @@
       </c>
       <c r="AH273" s="2" t="n"/>
     </row>
-    <row r="274" ht="24" customHeight="1" s="48">
+    <row r="274" ht="24" customHeight="1" s="49">
       <c r="A274" s="2" t="n">
         <v>273</v>
       </c>
@@ -28662,7 +28660,7 @@
       </c>
       <c r="AH274" s="2" t="n"/>
     </row>
-    <row r="275" ht="24" customHeight="1" s="48">
+    <row r="275" ht="24" customHeight="1" s="49">
       <c r="A275" s="2" t="n">
         <v>274</v>
       </c>
@@ -28750,7 +28748,7 @@
       <c r="AG275" s="2" t="n"/>
       <c r="AH275" s="2" t="n"/>
     </row>
-    <row r="276" ht="24" customHeight="1" s="48">
+    <row r="276" ht="24" customHeight="1" s="49">
       <c r="A276" s="2" t="n">
         <v>275</v>
       </c>
@@ -28844,7 +28842,7 @@
       <c r="AG276" s="2" t="n"/>
       <c r="AH276" s="2" t="n"/>
     </row>
-    <row r="277" ht="24" customHeight="1" s="48">
+    <row r="277" ht="24" customHeight="1" s="49">
       <c r="A277" s="2" t="n">
         <v>276</v>
       </c>
@@ -28932,7 +28930,7 @@
       <c r="AG277" s="2" t="n"/>
       <c r="AH277" s="2" t="n"/>
     </row>
-    <row r="278" ht="24" customHeight="1" s="48">
+    <row r="278" ht="24" customHeight="1" s="49">
       <c r="A278" s="2" t="n">
         <v>277</v>
       </c>
@@ -29030,7 +29028,7 @@
       <c r="AG278" s="2" t="n"/>
       <c r="AH278" s="2" t="n"/>
     </row>
-    <row r="279" ht="24" customHeight="1" s="48">
+    <row r="279" ht="24" customHeight="1" s="49">
       <c r="A279" s="2" t="n">
         <v>278</v>
       </c>
@@ -29122,7 +29120,7 @@
       <c r="AG279" s="2" t="n"/>
       <c r="AH279" s="2" t="n"/>
     </row>
-    <row r="280" ht="24" customHeight="1" s="48">
+    <row r="280" ht="24" customHeight="1" s="49">
       <c r="A280" s="2" t="n">
         <v>279</v>
       </c>
@@ -29206,7 +29204,7 @@
       <c r="AG280" s="2" t="n"/>
       <c r="AH280" s="2" t="n"/>
     </row>
-    <row r="281" ht="24" customHeight="1" s="48">
+    <row r="281" ht="24" customHeight="1" s="49">
       <c r="A281" s="2" t="n">
         <v>280</v>
       </c>
@@ -29298,7 +29296,7 @@
       <c r="AG281" s="2" t="n"/>
       <c r="AH281" s="2" t="n"/>
     </row>
-    <row r="282" ht="24" customHeight="1" s="48">
+    <row r="282" ht="24" customHeight="1" s="49">
       <c r="A282" s="2" t="n">
         <v>281</v>
       </c>
@@ -29325,12 +29323,8 @@
         </is>
       </c>
       <c r="N282" s="2" t="n"/>
-      <c r="O282" s="32" t="n">
-        <v>-15.8</v>
-      </c>
-      <c r="P282" s="32" t="n">
-        <v>3.3</v>
-      </c>
+      <c r="O282" s="32" t="n"/>
+      <c r="P282" s="32" t="n"/>
       <c r="Q282" s="32" t="n"/>
       <c r="R282" s="23" t="inlineStr">
         <is>
@@ -29382,7 +29376,7 @@
       <c r="AG282" s="2" t="n"/>
       <c r="AH282" s="2" t="n"/>
     </row>
-    <row r="283" ht="24" customHeight="1" s="48">
+    <row r="283" ht="24" customHeight="1" s="49">
       <c r="A283" s="2" t="n">
         <v>282</v>
       </c>
@@ -29474,7 +29468,7 @@
       <c r="AG283" s="2" t="n"/>
       <c r="AH283" s="2" t="n"/>
     </row>
-    <row r="284" ht="24" customHeight="1" s="48">
+    <row r="284" ht="24" customHeight="1" s="49">
       <c r="A284" s="2" t="n">
         <v>283</v>
       </c>
@@ -29560,7 +29554,7 @@
       <c r="AG284" s="2" t="n"/>
       <c r="AH284" s="2" t="n"/>
     </row>
-    <row r="285" ht="24" customHeight="1" s="48">
+    <row r="285" ht="24" customHeight="1" s="49">
       <c r="A285" s="2" t="n">
         <v>284</v>
       </c>
@@ -29662,7 +29656,7 @@
       </c>
       <c r="AH285" s="2" t="n"/>
     </row>
-    <row r="286" ht="24" customHeight="1" s="48">
+    <row r="286" ht="24" customHeight="1" s="49">
       <c r="A286" s="2" t="n">
         <v>285</v>
       </c>
@@ -29764,7 +29758,7 @@
       </c>
       <c r="AH286" s="2" t="n"/>
     </row>
-    <row r="287" ht="24" customHeight="1" s="48">
+    <row r="287" ht="24" customHeight="1" s="49">
       <c r="A287" s="2" t="n">
         <v>286</v>
       </c>
@@ -29866,7 +29860,7 @@
       </c>
       <c r="AH287" s="2" t="n"/>
     </row>
-    <row r="288" ht="24" customHeight="1" s="48">
+    <row r="288" ht="24" customHeight="1" s="49">
       <c r="A288" s="2" t="n">
         <v>287</v>
       </c>
@@ -29968,7 +29962,7 @@
       </c>
       <c r="AH288" s="2" t="n"/>
     </row>
-    <row r="289" ht="24" customHeight="1" s="48">
+    <row r="289" ht="24" customHeight="1" s="49">
       <c r="A289" s="2" t="n">
         <v>288</v>
       </c>
@@ -30066,7 +30060,7 @@
       <c r="AG289" s="2" t="n"/>
       <c r="AH289" s="2" t="n"/>
     </row>
-    <row r="290" ht="24" customHeight="1" s="48">
+    <row r="290" ht="24" customHeight="1" s="49">
       <c r="A290" s="2" t="n">
         <v>289</v>
       </c>
@@ -30166,7 +30160,7 @@
       <c r="AG290" s="2" t="n"/>
       <c r="AH290" s="2" t="n"/>
     </row>
-    <row r="291" ht="24" customHeight="1" s="48">
+    <row r="291" ht="24" customHeight="1" s="49">
       <c r="A291" s="2" t="n">
         <v>290</v>
       </c>
@@ -30258,7 +30252,7 @@
       </c>
       <c r="AH291" s="2" t="n"/>
     </row>
-    <row r="292" ht="24" customHeight="1" s="48">
+    <row r="292" ht="24" customHeight="1" s="49">
       <c r="A292" s="2" t="n">
         <v>291</v>
       </c>
@@ -30356,7 +30350,7 @@
       <c r="AG292" s="2" t="n"/>
       <c r="AH292" s="2" t="n"/>
     </row>
-    <row r="293" ht="24" customHeight="1" s="48">
+    <row r="293" ht="24" customHeight="1" s="49">
       <c r="A293" s="2" t="n">
         <v>292</v>
       </c>
@@ -30454,7 +30448,7 @@
       <c r="AG293" s="2" t="n"/>
       <c r="AH293" s="2" t="n"/>
     </row>
-    <row r="294" ht="24" customHeight="1" s="48">
+    <row r="294" ht="24" customHeight="1" s="49">
       <c r="A294" s="2" t="n">
         <v>293</v>
       </c>
@@ -30558,7 +30552,7 @@
       </c>
       <c r="AH294" s="2" t="n"/>
     </row>
-    <row r="295" ht="24" customHeight="1" s="48">
+    <row r="295" ht="24" customHeight="1" s="49">
       <c r="A295" s="2" t="n">
         <v>294</v>
       </c>
@@ -30596,10 +30590,10 @@
       </c>
       <c r="N295" s="2" t="n"/>
       <c r="O295" s="32" t="n">
-        <v>-9.6</v>
+        <v>-17.5</v>
       </c>
       <c r="P295" s="32" t="n">
-        <v>1.5</v>
+        <v>-7.9</v>
       </c>
       <c r="Q295" s="32" t="n"/>
       <c r="R295" s="23" t="inlineStr">
@@ -30664,7 +30658,7 @@
       </c>
       <c r="AH295" s="2" t="n"/>
     </row>
-    <row r="296" ht="24" customHeight="1" s="48">
+    <row r="296" ht="24" customHeight="1" s="49">
       <c r="A296" s="2" t="n">
         <v>295</v>
       </c>
@@ -30762,7 +30756,7 @@
       <c r="AG296" s="2" t="n"/>
       <c r="AH296" s="2" t="n"/>
     </row>
-    <row r="297" ht="24" customHeight="1" s="48">
+    <row r="297" ht="24" customHeight="1" s="49">
       <c r="A297" s="2" t="n">
         <v>296</v>
       </c>
@@ -30858,7 +30852,7 @@
       </c>
       <c r="AH297" s="2" t="n"/>
     </row>
-    <row r="298" ht="24" customHeight="1" s="48">
+    <row r="298" ht="24" customHeight="1" s="49">
       <c r="A298" s="2" t="n">
         <v>297</v>
       </c>
@@ -30960,259 +30954,697 @@
       </c>
       <c r="AH298" s="2" t="n"/>
     </row>
-    <row r="299" ht="24" customHeight="1" s="48">
-      <c r="A299" s="2" t="n"/>
+    <row r="299" ht="24" customHeight="1" s="49">
+      <c r="A299" s="2" t="n">
+        <v>298</v>
+      </c>
       <c r="B299" s="2" t="n"/>
       <c r="C299" s="46" t="n"/>
       <c r="D299" s="2" t="n"/>
       <c r="E299" s="4" t="n"/>
-      <c r="F299" s="39" t="n"/>
-      <c r="G299" s="29" t="n"/>
-      <c r="H299" s="29" t="n"/>
-      <c r="I299" s="2" t="n"/>
-      <c r="J299" s="27" t="n"/>
-      <c r="K299" s="4" t="n"/>
+      <c r="F299" s="39" t="n">
+        <v>915</v>
+      </c>
+      <c r="G299" s="29" t="n">
+        <v>48.694594864531</v>
+      </c>
+      <c r="H299" s="29" t="n">
+        <v>111.996255030991</v>
+      </c>
+      <c r="I299" s="2" t="n">
+        <v>1030</v>
+      </c>
+      <c r="J299" s="27" t="n">
+        <v>12</v>
+      </c>
+      <c r="K299" s="31" t="inlineStr">
+        <is>
+          <t>🇲🇳</t>
+        </is>
+      </c>
       <c r="L299" s="2" t="n"/>
-      <c r="M299" s="14" t="n"/>
+      <c r="M299" s="14" t="inlineStr">
+        <is>
+          <t>瑙罗布林</t>
+        </is>
+      </c>
       <c r="N299" s="2" t="n"/>
       <c r="O299" s="32" t="n"/>
       <c r="P299" s="32" t="n"/>
       <c r="Q299" s="32" t="n"/>
-      <c r="R299" s="23" t="n"/>
+      <c r="R299" s="23" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="S299" s="37" t="n"/>
-      <c r="T299" s="41" t="n"/>
-      <c r="U299" s="2" t="n"/>
-      <c r="V299" s="4" t="n"/>
-      <c r="W299" s="4" t="n"/>
-      <c r="X299" s="4" t="n"/>
+      <c r="T299" s="41" t="inlineStr">
+        <is>
+          <t>肯特省</t>
+        </is>
+      </c>
+      <c r="U299" s="2" t="inlineStr">
+        <is>
+          <t>肯特省</t>
+        </is>
+      </c>
+      <c r="V299" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="W299" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="X299" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="Y299" s="4" t="n"/>
       <c r="Z299" s="2" t="n"/>
       <c r="AA299" s="2" t="n"/>
       <c r="AB299" s="2" t="n"/>
       <c r="AC299" s="2" t="n"/>
-      <c r="AD299" s="2" t="n"/>
-      <c r="AE299" s="4" t="n"/>
+      <c r="AD299" s="2" t="inlineStr">
+        <is>
+          <t>蒙古</t>
+        </is>
+      </c>
+      <c r="AE299" s="4" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
       <c r="AF299" s="4" t="n"/>
       <c r="AG299" s="2" t="n"/>
       <c r="AH299" s="2" t="n"/>
     </row>
-    <row r="300" ht="24" customHeight="1" s="48">
-      <c r="A300" s="2" t="n"/>
+    <row r="300" ht="24" customHeight="1" s="49">
+      <c r="A300" s="2" t="n">
+        <v>299</v>
+      </c>
       <c r="B300" s="2" t="n"/>
       <c r="C300" s="46" t="n"/>
       <c r="D300" s="2" t="n"/>
       <c r="E300" s="4" t="n"/>
-      <c r="F300" s="39" t="n"/>
-      <c r="G300" s="29" t="n"/>
-      <c r="H300" s="29" t="n"/>
-      <c r="I300" s="2" t="n"/>
-      <c r="J300" s="27" t="n"/>
-      <c r="K300" s="4" t="n"/>
+      <c r="F300" s="39" t="inlineStr">
+        <is>
+          <t>C0064</t>
+        </is>
+      </c>
+      <c r="G300" s="29" t="n">
+        <v>51.3308</v>
+      </c>
+      <c r="H300" s="29" t="n">
+        <v>121.5136</v>
+      </c>
+      <c r="I300" s="2" t="n">
+        <v>798.9</v>
+      </c>
+      <c r="J300" s="27" t="n">
+        <v>12</v>
+      </c>
+      <c r="K300" s="31" t="inlineStr">
+        <is>
+          <t>🇨🇳</t>
+        </is>
+      </c>
       <c r="L300" s="2" t="n"/>
-      <c r="M300" s="14" t="n"/>
+      <c r="M300" s="14" t="inlineStr">
+        <is>
+          <t>金河</t>
+        </is>
+      </c>
       <c r="N300" s="2" t="n"/>
       <c r="O300" s="32" t="n"/>
       <c r="P300" s="32" t="n"/>
       <c r="Q300" s="32" t="n"/>
-      <c r="R300" s="23" t="n"/>
+      <c r="R300" s="23" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="S300" s="37" t="n"/>
-      <c r="T300" s="41" t="n"/>
-      <c r="U300" s="2" t="n"/>
-      <c r="V300" s="4" t="n"/>
-      <c r="W300" s="4" t="n"/>
-      <c r="X300" s="4" t="n"/>
+      <c r="T300" s="41" t="inlineStr">
+        <is>
+          <t>呼伦贝尔市根河市</t>
+        </is>
+      </c>
+      <c r="U300" s="2" t="inlineStr">
+        <is>
+          <t>内蒙古</t>
+        </is>
+      </c>
+      <c r="V300" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="W300" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="X300" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="Y300" s="4" t="n"/>
-      <c r="Z300" s="2" t="n"/>
-      <c r="AA300" s="2" t="n"/>
+      <c r="Z300" s="2" t="inlineStr">
+        <is>
+          <t>呼伦贝尔市</t>
+        </is>
+      </c>
+      <c r="AA300" s="2" t="inlineStr">
+        <is>
+          <t>根河市</t>
+        </is>
+      </c>
       <c r="AB300" s="2" t="n"/>
       <c r="AC300" s="2" t="n"/>
-      <c r="AD300" s="2" t="n"/>
-      <c r="AE300" s="4" t="n"/>
+      <c r="AD300" s="2" t="inlineStr">
+        <is>
+          <t>中国</t>
+        </is>
+      </c>
+      <c r="AE300" s="4" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
       <c r="AF300" s="4" t="n"/>
-      <c r="AG300" s="2" t="n"/>
+      <c r="AG300" s="2" t="inlineStr">
+        <is>
+          <t>大兴安岭</t>
+        </is>
+      </c>
       <c r="AH300" s="2" t="n"/>
     </row>
-    <row r="301" ht="24" customHeight="1" s="48">
-      <c r="A301" s="2" t="n"/>
+    <row r="301" ht="24" customHeight="1" s="49">
+      <c r="A301" s="2" t="n">
+        <v>300</v>
+      </c>
       <c r="B301" s="2" t="n"/>
-      <c r="C301" s="46" t="n"/>
+      <c r="C301" s="46" t="inlineStr">
+        <is>
+          <t>59843</t>
+        </is>
+      </c>
       <c r="D301" s="2" t="n"/>
-      <c r="E301" s="4" t="n"/>
+      <c r="E301" s="4" t="n">
+        <v>99999</v>
+      </c>
       <c r="F301" s="39" t="n"/>
-      <c r="G301" s="29" t="n"/>
-      <c r="H301" s="29" t="n"/>
-      <c r="I301" s="2" t="n"/>
-      <c r="J301" s="27" t="n"/>
-      <c r="K301" s="4" t="n"/>
+      <c r="G301" s="29" t="n">
+        <v>19.7364</v>
+      </c>
+      <c r="H301" s="29" t="n">
+        <v>110.0167</v>
+      </c>
+      <c r="I301" s="2" t="n">
+        <v>31.4</v>
+      </c>
+      <c r="J301" s="27" t="n">
+        <v>12</v>
+      </c>
+      <c r="K301" s="31" t="inlineStr">
+        <is>
+          <t>🇨🇳</t>
+        </is>
+      </c>
       <c r="L301" s="2" t="n"/>
-      <c r="M301" s="14" t="n"/>
+      <c r="M301" s="14" t="inlineStr">
+        <is>
+          <t>澄迈</t>
+        </is>
+      </c>
       <c r="N301" s="2" t="n"/>
       <c r="O301" s="32" t="n"/>
       <c r="P301" s="32" t="n"/>
       <c r="Q301" s="32" t="n"/>
-      <c r="R301" s="23" t="n"/>
+      <c r="R301" s="23" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="S301" s="37" t="n"/>
-      <c r="T301" s="41" t="n"/>
-      <c r="U301" s="2" t="n"/>
-      <c r="V301" s="4" t="n"/>
-      <c r="W301" s="4" t="n"/>
-      <c r="X301" s="4" t="n"/>
+      <c r="T301" s="41" t="inlineStr">
+        <is>
+          <t>海南</t>
+        </is>
+      </c>
+      <c r="U301" s="2" t="inlineStr">
+        <is>
+          <t>海南</t>
+        </is>
+      </c>
+      <c r="V301" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="W301" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="X301" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="Y301" s="4" t="n"/>
-      <c r="Z301" s="2" t="n"/>
+      <c r="Z301" s="2" t="inlineStr">
+        <is>
+          <t>澄迈县</t>
+        </is>
+      </c>
       <c r="AA301" s="2" t="n"/>
       <c r="AB301" s="2" t="n"/>
       <c r="AC301" s="2" t="n"/>
-      <c r="AD301" s="2" t="n"/>
-      <c r="AE301" s="4" t="n"/>
+      <c r="AD301" s="2" t="inlineStr">
+        <is>
+          <t>中国</t>
+        </is>
+      </c>
+      <c r="AE301" s="4" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
       <c r="AF301" s="4" t="n"/>
-      <c r="AG301" s="2" t="n"/>
+      <c r="AG301" s="2" t="inlineStr">
+        <is>
+          <t>海南岛</t>
+        </is>
+      </c>
       <c r="AH301" s="2" t="n"/>
     </row>
-    <row r="302" ht="24" customHeight="1" s="48">
-      <c r="A302" s="2" t="n"/>
+    <row r="302" ht="24" customHeight="1" s="49">
+      <c r="A302" s="2" t="n">
+        <v>301</v>
+      </c>
       <c r="B302" s="2" t="n"/>
-      <c r="C302" s="46" t="n"/>
+      <c r="C302" s="46" t="inlineStr">
+        <is>
+          <t>56976</t>
+        </is>
+      </c>
       <c r="D302" s="2" t="n"/>
-      <c r="E302" s="4" t="n"/>
+      <c r="E302" s="4" t="n">
+        <v>99999</v>
+      </c>
       <c r="F302" s="39" t="n"/>
-      <c r="G302" s="29" t="n"/>
-      <c r="H302" s="29" t="n"/>
-      <c r="I302" s="2" t="n"/>
-      <c r="J302" s="27" t="n"/>
-      <c r="K302" s="4" t="n"/>
+      <c r="G302" s="29" t="n">
+        <v>23.2286</v>
+      </c>
+      <c r="H302" s="29" t="n">
+        <v>102.8214</v>
+      </c>
+      <c r="I302" s="2" t="n">
+        <v>312.3</v>
+      </c>
+      <c r="J302" s="27" t="n">
+        <v>12</v>
+      </c>
+      <c r="K302" s="48" t="inlineStr">
+        <is>
+          <t>🇨🇳</t>
+        </is>
+      </c>
       <c r="L302" s="2" t="n"/>
-      <c r="M302" s="14" t="n"/>
+      <c r="M302" s="14" t="inlineStr">
+        <is>
+          <t>元阳</t>
+        </is>
+      </c>
       <c r="N302" s="2" t="n"/>
       <c r="O302" s="32" t="n"/>
       <c r="P302" s="32" t="n"/>
       <c r="Q302" s="32" t="n"/>
-      <c r="R302" s="23" t="n"/>
+      <c r="R302" s="23" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="S302" s="37" t="n"/>
-      <c r="T302" s="41" t="n"/>
-      <c r="U302" s="2" t="n"/>
-      <c r="V302" s="4" t="n"/>
-      <c r="W302" s="4" t="n"/>
-      <c r="X302" s="4" t="n"/>
+      <c r="T302" s="41" t="inlineStr">
+        <is>
+          <t>云南</t>
+        </is>
+      </c>
+      <c r="U302" s="2" t="inlineStr">
+        <is>
+          <t>云南</t>
+        </is>
+      </c>
+      <c r="V302" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="W302" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="X302" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="Y302" s="4" t="n"/>
-      <c r="Z302" s="2" t="n"/>
-      <c r="AA302" s="2" t="n"/>
+      <c r="Z302" s="2" t="inlineStr">
+        <is>
+          <t>红河哈尼族彝族自治州</t>
+        </is>
+      </c>
+      <c r="AA302" s="2" t="inlineStr">
+        <is>
+          <t>元阳县</t>
+        </is>
+      </c>
       <c r="AB302" s="2" t="n"/>
       <c r="AC302" s="2" t="n"/>
-      <c r="AD302" s="2" t="n"/>
-      <c r="AE302" s="4" t="n"/>
+      <c r="AD302" s="2" t="inlineStr">
+        <is>
+          <t>中国</t>
+        </is>
+      </c>
+      <c r="AE302" s="4" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
       <c r="AF302" s="4" t="n"/>
       <c r="AG302" s="2" t="n"/>
       <c r="AH302" s="2" t="n"/>
     </row>
-    <row r="303" ht="24" customHeight="1" s="48">
-      <c r="A303" s="2" t="n"/>
+    <row r="303" ht="24" customHeight="1" s="49">
+      <c r="A303" s="2" t="n">
+        <v>302</v>
+      </c>
       <c r="B303" s="2" t="n"/>
       <c r="C303" s="46" t="n"/>
       <c r="D303" s="2" t="n"/>
       <c r="E303" s="4" t="n"/>
-      <c r="F303" s="39" t="n"/>
-      <c r="G303" s="29" t="n"/>
-      <c r="H303" s="29" t="n"/>
-      <c r="I303" s="2" t="n"/>
-      <c r="J303" s="27" t="n"/>
-      <c r="K303" s="4" t="n"/>
+      <c r="F303" s="39" t="n">
+        <v>854</v>
+      </c>
+      <c r="G303" s="29" t="n">
+        <v>47.5181325169043</v>
+      </c>
+      <c r="H303" s="29" t="n">
+        <v>91.62955958582999</v>
+      </c>
+      <c r="I303" s="2" t="n">
+        <v>2294</v>
+      </c>
+      <c r="J303" s="27" t="n">
+        <v>12</v>
+      </c>
+      <c r="K303" s="31" t="inlineStr">
+        <is>
+          <t>🇲🇳</t>
+        </is>
+      </c>
       <c r="L303" s="2" t="n"/>
-      <c r="M303" s="14" t="n"/>
+      <c r="M303" s="15" t="inlineStr">
+        <is>
+          <t>杜特</t>
+        </is>
+      </c>
       <c r="N303" s="2" t="n"/>
       <c r="O303" s="32" t="n"/>
       <c r="P303" s="32" t="n"/>
       <c r="Q303" s="32" t="n"/>
-      <c r="R303" s="23" t="n"/>
+      <c r="R303" s="23" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="S303" s="37" t="n"/>
-      <c r="T303" s="41" t="n"/>
-      <c r="U303" s="2" t="n"/>
-      <c r="V303" s="4" t="n"/>
-      <c r="W303" s="4" t="n"/>
-      <c r="X303" s="4" t="n"/>
+      <c r="T303" s="41" t="inlineStr">
+        <is>
+          <t>科布多</t>
+        </is>
+      </c>
+      <c r="U303" s="2" t="inlineStr">
+        <is>
+          <t>科布多省</t>
+        </is>
+      </c>
+      <c r="V303" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="W303" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="X303" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="Y303" s="4" t="n"/>
       <c r="Z303" s="2" t="n"/>
       <c r="AA303" s="2" t="n"/>
       <c r="AB303" s="2" t="n"/>
       <c r="AC303" s="2" t="n"/>
-      <c r="AD303" s="2" t="n"/>
-      <c r="AE303" s="4" t="n"/>
+      <c r="AD303" s="2" t="inlineStr">
+        <is>
+          <t>蒙古</t>
+        </is>
+      </c>
+      <c r="AE303" s="4" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
       <c r="AF303" s="4" t="n"/>
-      <c r="AG303" s="2" t="n"/>
+      <c r="AG303" s="2" t="inlineStr">
+        <is>
+          <t>阿尔泰山</t>
+        </is>
+      </c>
       <c r="AH303" s="2" t="n"/>
     </row>
-    <row r="304" ht="24" customHeight="1" s="48">
-      <c r="A304" s="2" t="n"/>
+    <row r="304" ht="24" customHeight="1" s="49">
+      <c r="A304" s="2" t="n">
+        <v>303</v>
+      </c>
       <c r="B304" s="2" t="n"/>
-      <c r="C304" s="46" t="n"/>
+      <c r="C304" s="46" t="inlineStr">
+        <is>
+          <t>59213</t>
+        </is>
+      </c>
       <c r="D304" s="2" t="n"/>
-      <c r="E304" s="4" t="n"/>
+      <c r="E304" s="4" t="n">
+        <v>99999</v>
+      </c>
       <c r="F304" s="39" t="n"/>
-      <c r="G304" s="29" t="n"/>
-      <c r="H304" s="29" t="n"/>
-      <c r="I304" s="2" t="n"/>
-      <c r="J304" s="27" t="n"/>
-      <c r="K304" s="4" t="n"/>
+      <c r="G304" s="29" t="n">
+        <v>23.7556</v>
+      </c>
+      <c r="H304" s="29" t="n">
+        <v>106.9442</v>
+      </c>
+      <c r="I304" s="2" t="n">
+        <v>133</v>
+      </c>
+      <c r="J304" s="27" t="n">
+        <v>12</v>
+      </c>
+      <c r="K304" s="31" t="inlineStr">
+        <is>
+          <t>🇨🇳</t>
+        </is>
+      </c>
       <c r="L304" s="2" t="n"/>
-      <c r="M304" s="14" t="n"/>
+      <c r="M304" s="14" t="inlineStr">
+        <is>
+          <t>田阳</t>
+        </is>
+      </c>
       <c r="N304" s="2" t="n"/>
       <c r="O304" s="32" t="n"/>
       <c r="P304" s="32" t="n"/>
       <c r="Q304" s="32" t="n"/>
-      <c r="R304" s="23" t="n"/>
+      <c r="R304" s="23" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="S304" s="37" t="n"/>
-      <c r="T304" s="41" t="n"/>
-      <c r="U304" s="2" t="n"/>
-      <c r="V304" s="4" t="n"/>
-      <c r="W304" s="4" t="n"/>
-      <c r="X304" s="4" t="n"/>
+      <c r="T304" s="41" t="inlineStr">
+        <is>
+          <t>广西</t>
+        </is>
+      </c>
+      <c r="U304" s="2" t="inlineStr">
+        <is>
+          <t>广西</t>
+        </is>
+      </c>
+      <c r="V304" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="W304" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="X304" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="Y304" s="4" t="n"/>
-      <c r="Z304" s="2" t="n"/>
-      <c r="AA304" s="2" t="n"/>
+      <c r="Z304" s="2" t="inlineStr">
+        <is>
+          <t>百色市</t>
+        </is>
+      </c>
+      <c r="AA304" s="2" t="inlineStr">
+        <is>
+          <t>田阳县</t>
+        </is>
+      </c>
       <c r="AB304" s="2" t="n"/>
       <c r="AC304" s="2" t="n"/>
-      <c r="AD304" s="2" t="n"/>
-      <c r="AE304" s="4" t="n"/>
+      <c r="AD304" s="2" t="inlineStr">
+        <is>
+          <t>中国</t>
+        </is>
+      </c>
+      <c r="AE304" s="4" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
       <c r="AF304" s="4" t="n"/>
       <c r="AG304" s="2" t="n"/>
       <c r="AH304" s="2" t="n"/>
     </row>
-    <row r="305" ht="24" customHeight="1" s="48">
-      <c r="A305" s="2" t="n"/>
+    <row r="305" ht="24" customHeight="1" s="49">
+      <c r="A305" s="2" t="n">
+        <v>304</v>
+      </c>
       <c r="B305" s="2" t="n"/>
-      <c r="C305" s="46" t="n"/>
+      <c r="C305" s="46" t="inlineStr">
+        <is>
+          <t>56001</t>
+        </is>
+      </c>
       <c r="D305" s="2" t="n"/>
-      <c r="E305" s="4" t="n"/>
+      <c r="E305" s="4" t="n">
+        <v>99999</v>
+      </c>
       <c r="F305" s="39" t="n"/>
-      <c r="G305" s="29" t="n"/>
-      <c r="H305" s="29" t="n"/>
-      <c r="I305" s="2" t="n"/>
-      <c r="J305" s="27" t="n"/>
-      <c r="K305" s="4" t="n"/>
+      <c r="G305" s="29" t="n">
+        <v>34.6333</v>
+      </c>
+      <c r="H305" s="29" t="n">
+        <v>92.8553</v>
+      </c>
+      <c r="I305" s="2" t="n">
+        <v>4770</v>
+      </c>
+      <c r="J305" s="27" t="n">
+        <v>12</v>
+      </c>
+      <c r="K305" s="31" t="inlineStr">
+        <is>
+          <t>🇨🇳</t>
+        </is>
+      </c>
       <c r="L305" s="2" t="n"/>
-      <c r="M305" s="14" t="n"/>
+      <c r="M305" s="14" t="inlineStr">
+        <is>
+          <t>沱沱河</t>
+        </is>
+      </c>
       <c r="N305" s="2" t="n"/>
-      <c r="O305" s="32" t="n"/>
-      <c r="P305" s="32" t="n"/>
+      <c r="O305" s="32" t="n">
+        <v>-12.4</v>
+      </c>
+      <c r="P305" s="32" t="n">
+        <v>-0.5</v>
+      </c>
       <c r="Q305" s="32" t="n"/>
-      <c r="R305" s="23" t="n"/>
+      <c r="R305" s="23" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="S305" s="37" t="n"/>
-      <c r="T305" s="41" t="n"/>
-      <c r="U305" s="2" t="n"/>
-      <c r="V305" s="4" t="n"/>
-      <c r="W305" s="4" t="n"/>
-      <c r="X305" s="4" t="n"/>
+      <c r="T305" s="41" t="inlineStr">
+        <is>
+          <t>青藏高原 青海</t>
+        </is>
+      </c>
+      <c r="U305" s="2" t="inlineStr">
+        <is>
+          <t>青海</t>
+        </is>
+      </c>
+      <c r="V305" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="W305" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="X305" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="Y305" s="4" t="n"/>
-      <c r="Z305" s="2" t="n"/>
-      <c r="AA305" s="2" t="n"/>
+      <c r="Z305" s="2" t="inlineStr">
+        <is>
+          <t>海西蒙古族藏族自治州</t>
+        </is>
+      </c>
+      <c r="AA305" s="2" t="inlineStr">
+        <is>
+          <t>格尔木市</t>
+        </is>
+      </c>
       <c r="AB305" s="2" t="n"/>
       <c r="AC305" s="2" t="n"/>
-      <c r="AD305" s="2" t="n"/>
-      <c r="AE305" s="4" t="n"/>
+      <c r="AD305" s="2" t="inlineStr">
+        <is>
+          <t>中国</t>
+        </is>
+      </c>
+      <c r="AE305" s="4" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
       <c r="AF305" s="4" t="n"/>
-      <c r="AG305" s="2" t="n"/>
+      <c r="AG305" s="2" t="inlineStr">
+        <is>
+          <t>青藏高原</t>
+        </is>
+      </c>
       <c r="AH305" s="2" t="n"/>
     </row>
-    <row r="306" ht="24" customHeight="1" s="48">
+    <row r="306" ht="24" customHeight="1" s="49">
       <c r="A306" s="2" t="n"/>
       <c r="B306" s="2" t="n"/>
       <c r="C306" s="46" t="n"/>
@@ -31248,7 +31680,7 @@
       <c r="AG306" s="2" t="n"/>
       <c r="AH306" s="2" t="n"/>
     </row>
-    <row r="307" ht="24" customHeight="1" s="48">
+    <row r="307" ht="24" customHeight="1" s="49">
       <c r="A307" s="2" t="n"/>
       <c r="B307" s="2" t="n"/>
       <c r="C307" s="46" t="n"/>
@@ -31284,7 +31716,7 @@
       <c r="AG307" s="2" t="n"/>
       <c r="AH307" s="2" t="n"/>
     </row>
-    <row r="308" ht="24" customHeight="1" s="48">
+    <row r="308" ht="24" customHeight="1" s="49">
       <c r="A308" s="2" t="n"/>
       <c r="B308" s="2" t="n"/>
       <c r="C308" s="46" t="n"/>
@@ -31320,7 +31752,7 @@
       <c r="AG308" s="2" t="n"/>
       <c r="AH308" s="2" t="n"/>
     </row>
-    <row r="309" ht="24" customHeight="1" s="48">
+    <row r="309" ht="24" customHeight="1" s="49">
       <c r="A309" s="2" t="n"/>
       <c r="B309" s="2" t="n"/>
       <c r="C309" s="46" t="n"/>
@@ -31356,7 +31788,7 @@
       <c r="AG309" s="2" t="n"/>
       <c r="AH309" s="2" t="n"/>
     </row>
-    <row r="310" ht="24" customHeight="1" s="48">
+    <row r="310" ht="24" customHeight="1" s="49">
       <c r="A310" s="2" t="n"/>
       <c r="B310" s="2" t="n"/>
       <c r="C310" s="46" t="n"/>
@@ -31392,7 +31824,7 @@
       <c r="AG310" s="2" t="n"/>
       <c r="AH310" s="2" t="n"/>
     </row>
-    <row r="311" ht="24" customHeight="1" s="48">
+    <row r="311" ht="24" customHeight="1" s="49">
       <c r="A311" s="2" t="n"/>
       <c r="B311" s="2" t="n"/>
       <c r="C311" s="46" t="n"/>
@@ -31428,7 +31860,7 @@
       <c r="AG311" s="2" t="n"/>
       <c r="AH311" s="2" t="n"/>
     </row>
-    <row r="312" ht="24" customHeight="1" s="48">
+    <row r="312" ht="24" customHeight="1" s="49">
       <c r="A312" s="2" t="n"/>
       <c r="B312" s="2" t="n"/>
       <c r="C312" s="46" t="n"/>
@@ -31464,7 +31896,7 @@
       <c r="AG312" s="2" t="n"/>
       <c r="AH312" s="2" t="n"/>
     </row>
-    <row r="313" ht="24" customHeight="1" s="48">
+    <row r="313" ht="24" customHeight="1" s="49">
       <c r="A313" s="2" t="n"/>
       <c r="B313" s="2" t="n"/>
       <c r="C313" s="46" t="n"/>
@@ -31500,7 +31932,7 @@
       <c r="AG313" s="2" t="n"/>
       <c r="AH313" s="2" t="n"/>
     </row>
-    <row r="314" ht="24" customHeight="1" s="48">
+    <row r="314" ht="24" customHeight="1" s="49">
       <c r="A314" s="2" t="n"/>
       <c r="B314" s="2" t="n"/>
       <c r="C314" s="46" t="n"/>
@@ -31536,7 +31968,7 @@
       <c r="AG314" s="2" t="n"/>
       <c r="AH314" s="2" t="n"/>
     </row>
-    <row r="315" ht="24" customHeight="1" s="48">
+    <row r="315" ht="24" customHeight="1" s="49">
       <c r="A315" s="2" t="n"/>
       <c r="B315" s="2" t="n"/>
       <c r="C315" s="46" t="n"/>
@@ -31572,7 +32004,7 @@
       <c r="AG315" s="2" t="n"/>
       <c r="AH315" s="2" t="n"/>
     </row>
-    <row r="316" ht="24" customHeight="1" s="48">
+    <row r="316" ht="24" customHeight="1" s="49">
       <c r="A316" s="2" t="n"/>
       <c r="B316" s="2" t="n"/>
       <c r="C316" s="46" t="n"/>
@@ -31608,7 +32040,7 @@
       <c r="AG316" s="2" t="n"/>
       <c r="AH316" s="2" t="n"/>
     </row>
-    <row r="317" ht="24" customHeight="1" s="48">
+    <row r="317" ht="24" customHeight="1" s="49">
       <c r="A317" s="2" t="n"/>
       <c r="B317" s="2" t="n"/>
       <c r="C317" s="46" t="n"/>
@@ -31644,7 +32076,7 @@
       <c r="AG317" s="2" t="n"/>
       <c r="AH317" s="2" t="n"/>
     </row>
-    <row r="318" ht="24" customHeight="1" s="48">
+    <row r="318" ht="24" customHeight="1" s="49">
       <c r="A318" s="2" t="n"/>
       <c r="B318" s="2" t="n"/>
       <c r="C318" s="46" t="n"/>
@@ -31680,7 +32112,7 @@
       <c r="AG318" s="2" t="n"/>
       <c r="AH318" s="2" t="n"/>
     </row>
-    <row r="319" ht="24" customHeight="1" s="48">
+    <row r="319" ht="24" customHeight="1" s="49">
       <c r="A319" s="2" t="n"/>
       <c r="B319" s="2" t="n"/>
       <c r="C319" s="46" t="n"/>
@@ -31716,7 +32148,7 @@
       <c r="AG319" s="2" t="n"/>
       <c r="AH319" s="2" t="n"/>
     </row>
-    <row r="320" ht="24" customHeight="1" s="48">
+    <row r="320" ht="24" customHeight="1" s="49">
       <c r="A320" s="2" t="n"/>
       <c r="B320" s="2" t="n"/>
       <c r="C320" s="46" t="n"/>
@@ -31752,7 +32184,7 @@
       <c r="AG320" s="2" t="n"/>
       <c r="AH320" s="2" t="n"/>
     </row>
-    <row r="321" ht="24" customHeight="1" s="48">
+    <row r="321" ht="24" customHeight="1" s="49">
       <c r="A321" s="2" t="n"/>
       <c r="B321" s="2" t="n"/>
       <c r="C321" s="46" t="n"/>
@@ -31788,7 +32220,7 @@
       <c r="AG321" s="2" t="n"/>
       <c r="AH321" s="2" t="n"/>
     </row>
-    <row r="322" ht="24" customHeight="1" s="48">
+    <row r="322" ht="24" customHeight="1" s="49">
       <c r="A322" s="2" t="n"/>
       <c r="B322" s="2" t="n"/>
       <c r="C322" s="46" t="n"/>
@@ -31824,7 +32256,7 @@
       <c r="AG322" s="2" t="n"/>
       <c r="AH322" s="2" t="n"/>
     </row>
-    <row r="323" ht="24" customHeight="1" s="48">
+    <row r="323" ht="24" customHeight="1" s="49">
       <c r="A323" s="2" t="n"/>
       <c r="B323" s="2" t="n"/>
       <c r="C323" s="46" t="n"/>
@@ -31860,7 +32292,7 @@
       <c r="AG323" s="2" t="n"/>
       <c r="AH323" s="2" t="n"/>
     </row>
-    <row r="324" ht="24" customHeight="1" s="48">
+    <row r="324" ht="24" customHeight="1" s="49">
       <c r="A324" s="2" t="n"/>
       <c r="B324" s="2" t="n"/>
       <c r="C324" s="46" t="n"/>
@@ -31896,7 +32328,7 @@
       <c r="AG324" s="2" t="n"/>
       <c r="AH324" s="2" t="n"/>
     </row>
-    <row r="325" ht="24" customHeight="1" s="48">
+    <row r="325" ht="24" customHeight="1" s="49">
       <c r="A325" s="2" t="n"/>
       <c r="B325" s="2" t="n"/>
       <c r="C325" s="46" t="n"/>
@@ -31932,7 +32364,7 @@
       <c r="AG325" s="2" t="n"/>
       <c r="AH325" s="2" t="n"/>
     </row>
-    <row r="326" ht="24" customHeight="1" s="48">
+    <row r="326" ht="24" customHeight="1" s="49">
       <c r="A326" s="2" t="n"/>
       <c r="B326" s="2" t="n"/>
       <c r="C326" s="46" t="n"/>
@@ -31968,7 +32400,7 @@
       <c r="AG326" s="2" t="n"/>
       <c r="AH326" s="2" t="n"/>
     </row>
-    <row r="327" ht="24" customHeight="1" s="48">
+    <row r="327" ht="24" customHeight="1" s="49">
       <c r="A327" s="2" t="n"/>
       <c r="B327" s="2" t="n"/>
       <c r="C327" s="46" t="n"/>
@@ -32004,7 +32436,7 @@
       <c r="AG327" s="2" t="n"/>
       <c r="AH327" s="2" t="n"/>
     </row>
-    <row r="328" ht="24" customHeight="1" s="48">
+    <row r="328" ht="24" customHeight="1" s="49">
       <c r="A328" s="2" t="n"/>
       <c r="B328" s="2" t="n"/>
       <c r="C328" s="46" t="n"/>
@@ -32040,7 +32472,7 @@
       <c r="AG328" s="2" t="n"/>
       <c r="AH328" s="2" t="n"/>
     </row>
-    <row r="329" ht="24" customHeight="1" s="48">
+    <row r="329" ht="24" customHeight="1" s="49">
       <c r="A329" s="2" t="n"/>
       <c r="B329" s="2" t="n"/>
       <c r="C329" s="46" t="n"/>
@@ -32076,7 +32508,7 @@
       <c r="AG329" s="2" t="n"/>
       <c r="AH329" s="2" t="n"/>
     </row>
-    <row r="330" ht="24" customHeight="1" s="48">
+    <row r="330" ht="24" customHeight="1" s="49">
       <c r="A330" s="2" t="n"/>
       <c r="B330" s="2" t="n"/>
       <c r="C330" s="46" t="n"/>
@@ -32112,7 +32544,7 @@
       <c r="AG330" s="2" t="n"/>
       <c r="AH330" s="2" t="n"/>
     </row>
-    <row r="331" ht="24" customHeight="1" s="48">
+    <row r="331" ht="24" customHeight="1" s="49">
       <c r="A331" s="2" t="n"/>
       <c r="B331" s="2" t="n"/>
       <c r="C331" s="46" t="n"/>
@@ -32148,7 +32580,7 @@
       <c r="AG331" s="2" t="n"/>
       <c r="AH331" s="2" t="n"/>
     </row>
-    <row r="332" ht="24" customHeight="1" s="48">
+    <row r="332" ht="24" customHeight="1" s="49">
       <c r="A332" s="2" t="n"/>
       <c r="B332" s="2" t="n"/>
       <c r="C332" s="46" t="n"/>
@@ -32184,7 +32616,7 @@
       <c r="AG332" s="2" t="n"/>
       <c r="AH332" s="2" t="n"/>
     </row>
-    <row r="333" ht="24" customHeight="1" s="48">
+    <row r="333" ht="24" customHeight="1" s="49">
       <c r="A333" s="2" t="n"/>
       <c r="B333" s="2" t="n"/>
       <c r="C333" s="46" t="n"/>
@@ -32220,7 +32652,7 @@
       <c r="AG333" s="2" t="n"/>
       <c r="AH333" s="2" t="n"/>
     </row>
-    <row r="334" ht="24" customHeight="1" s="48">
+    <row r="334" ht="24" customHeight="1" s="49">
       <c r="A334" s="2" t="n"/>
       <c r="B334" s="2" t="n"/>
       <c r="C334" s="46" t="n"/>
@@ -32256,7 +32688,7 @@
       <c r="AG334" s="2" t="n"/>
       <c r="AH334" s="2" t="n"/>
     </row>
-    <row r="335" ht="24" customHeight="1" s="48">
+    <row r="335" ht="24" customHeight="1" s="49">
       <c r="A335" s="2" t="n"/>
       <c r="B335" s="2" t="n"/>
       <c r="C335" s="46" t="n"/>
@@ -32292,7 +32724,7 @@
       <c r="AG335" s="2" t="n"/>
       <c r="AH335" s="2" t="n"/>
     </row>
-    <row r="336" ht="24" customHeight="1" s="48">
+    <row r="336" ht="24" customHeight="1" s="49">
       <c r="A336" s="2" t="n"/>
       <c r="B336" s="2" t="n"/>
       <c r="C336" s="46" t="n"/>
@@ -32328,7 +32760,7 @@
       <c r="AG336" s="2" t="n"/>
       <c r="AH336" s="2" t="n"/>
     </row>
-    <row r="337" ht="24" customHeight="1" s="48">
+    <row r="337" ht="24" customHeight="1" s="49">
       <c r="A337" s="2" t="n"/>
       <c r="B337" s="2" t="n"/>
       <c r="C337" s="46" t="n"/>
@@ -32364,7 +32796,7 @@
       <c r="AG337" s="2" t="n"/>
       <c r="AH337" s="2" t="n"/>
     </row>
-    <row r="338" ht="24" customHeight="1" s="48">
+    <row r="338" ht="24" customHeight="1" s="49">
       <c r="A338" s="2" t="n"/>
       <c r="B338" s="2" t="n"/>
       <c r="C338" s="46" t="n"/>
@@ -32400,7 +32832,7 @@
       <c r="AG338" s="2" t="n"/>
       <c r="AH338" s="2" t="n"/>
     </row>
-    <row r="339" ht="24" customHeight="1" s="48">
+    <row r="339" ht="24" customHeight="1" s="49">
       <c r="A339" s="2" t="n"/>
       <c r="B339" s="2" t="n"/>
       <c r="C339" s="46" t="n"/>
@@ -32436,7 +32868,7 @@
       <c r="AG339" s="2" t="n"/>
       <c r="AH339" s="2" t="n"/>
     </row>
-    <row r="340" ht="24" customHeight="1" s="48">
+    <row r="340" ht="24" customHeight="1" s="49">
       <c r="A340" s="2" t="n"/>
       <c r="B340" s="2" t="n"/>
       <c r="C340" s="46" t="n"/>
@@ -32472,7 +32904,7 @@
       <c r="AG340" s="2" t="n"/>
       <c r="AH340" s="2" t="n"/>
     </row>
-    <row r="341" ht="24" customHeight="1" s="48">
+    <row r="341" ht="24" customHeight="1" s="49">
       <c r="A341" s="2" t="n"/>
       <c r="B341" s="2" t="n"/>
       <c r="C341" s="46" t="n"/>
@@ -32508,7 +32940,7 @@
       <c r="AG341" s="2" t="n"/>
       <c r="AH341" s="2" t="n"/>
     </row>
-    <row r="342" ht="24" customHeight="1" s="48">
+    <row r="342" ht="24" customHeight="1" s="49">
       <c r="A342" s="2" t="n"/>
       <c r="B342" s="2" t="n"/>
       <c r="C342" s="46" t="n"/>
@@ -32544,7 +32976,7 @@
       <c r="AG342" s="2" t="n"/>
       <c r="AH342" s="2" t="n"/>
     </row>
-    <row r="343" ht="24" customHeight="1" s="48">
+    <row r="343" ht="24" customHeight="1" s="49">
       <c r="A343" s="2" t="n"/>
       <c r="B343" s="2" t="n"/>
       <c r="C343" s="46" t="n"/>
@@ -32580,7 +33012,7 @@
       <c r="AG343" s="2" t="n"/>
       <c r="AH343" s="2" t="n"/>
     </row>
-    <row r="344" ht="24" customHeight="1" s="48">
+    <row r="344" ht="24" customHeight="1" s="49">
       <c r="A344" s="2" t="n"/>
       <c r="B344" s="2" t="n"/>
       <c r="C344" s="46" t="n"/>
@@ -32616,7 +33048,7 @@
       <c r="AG344" s="2" t="n"/>
       <c r="AH344" s="2" t="n"/>
     </row>
-    <row r="345" ht="24" customHeight="1" s="48">
+    <row r="345" ht="24" customHeight="1" s="49">
       <c r="A345" s="2" t="n"/>
       <c r="B345" s="2" t="n"/>
       <c r="C345" s="46" t="n"/>
@@ -32652,7 +33084,7 @@
       <c r="AG345" s="2" t="n"/>
       <c r="AH345" s="2" t="n"/>
     </row>
-    <row r="346" ht="24" customHeight="1" s="48">
+    <row r="346" ht="24" customHeight="1" s="49">
       <c r="A346" s="2" t="n"/>
       <c r="B346" s="2" t="n"/>
       <c r="C346" s="46" t="n"/>
@@ -32688,7 +33120,7 @@
       <c r="AG346" s="2" t="n"/>
       <c r="AH346" s="2" t="n"/>
     </row>
-    <row r="347" ht="24" customHeight="1" s="48">
+    <row r="347" ht="24" customHeight="1" s="49">
       <c r="A347" s="2" t="n"/>
       <c r="B347" s="2" t="n"/>
       <c r="C347" s="46" t="n"/>
@@ -32724,7 +33156,7 @@
       <c r="AG347" s="2" t="n"/>
       <c r="AH347" s="2" t="n"/>
     </row>
-    <row r="348" ht="24" customHeight="1" s="48">
+    <row r="348" ht="24" customHeight="1" s="49">
       <c r="A348" s="2" t="n"/>
       <c r="B348" s="2" t="n"/>
       <c r="C348" s="46" t="n"/>
@@ -32760,7 +33192,7 @@
       <c r="AG348" s="2" t="n"/>
       <c r="AH348" s="2" t="n"/>
     </row>
-    <row r="349" ht="24" customHeight="1" s="48">
+    <row r="349" ht="24" customHeight="1" s="49">
       <c r="A349" s="2" t="n"/>
       <c r="B349" s="2" t="n"/>
       <c r="C349" s="46" t="n"/>
@@ -32796,7 +33228,7 @@
       <c r="AG349" s="2" t="n"/>
       <c r="AH349" s="2" t="n"/>
     </row>
-    <row r="350" ht="24" customHeight="1" s="48">
+    <row r="350" ht="24" customHeight="1" s="49">
       <c r="A350" s="2" t="n"/>
       <c r="B350" s="2" t="n"/>
       <c r="C350" s="46" t="n"/>
@@ -32832,7 +33264,7 @@
       <c r="AG350" s="2" t="n"/>
       <c r="AH350" s="2" t="n"/>
     </row>
-    <row r="351" ht="24" customHeight="1" s="48">
+    <row r="351" ht="24" customHeight="1" s="49">
       <c r="A351" s="14" t="n"/>
       <c r="B351" s="2" t="n"/>
       <c r="C351" s="46" t="n"/>
@@ -32868,7 +33300,7 @@
       <c r="AG351" s="2" t="n"/>
       <c r="AH351" s="2" t="n"/>
     </row>
-    <row r="352" ht="24" customHeight="1" s="48">
+    <row r="352" ht="24" customHeight="1" s="49">
       <c r="A352" s="13" t="n"/>
       <c r="B352" s="2" t="n"/>
       <c r="C352" s="46" t="n"/>
@@ -32904,7 +33336,7 @@
       <c r="AG352" s="2" t="n"/>
       <c r="AH352" s="2" t="n"/>
     </row>
-    <row r="353" ht="24" customHeight="1" s="48">
+    <row r="353" ht="24" customHeight="1" s="49">
       <c r="A353" s="13" t="n"/>
       <c r="B353" s="2" t="n"/>
       <c r="C353" s="46" t="n"/>
@@ -32940,7 +33372,7 @@
       <c r="AG353" s="2" t="n"/>
       <c r="AH353" s="2" t="n"/>
     </row>
-    <row r="354" ht="24" customHeight="1" s="48">
+    <row r="354" ht="24" customHeight="1" s="49">
       <c r="A354" s="13" t="n"/>
       <c r="B354" s="2" t="n"/>
       <c r="C354" s="46" t="n"/>
@@ -32976,7 +33408,7 @@
       <c r="AG354" s="2" t="n"/>
       <c r="AH354" s="2" t="n"/>
     </row>
-    <row r="355" ht="24" customHeight="1" s="48">
+    <row r="355" ht="24" customHeight="1" s="49">
       <c r="A355" s="13" t="n"/>
       <c r="B355" s="2" t="n"/>
       <c r="C355" s="46" t="n"/>
@@ -33012,7 +33444,7 @@
       <c r="AG355" s="2" t="n"/>
       <c r="AH355" s="2" t="n"/>
     </row>
-    <row r="356" ht="24" customHeight="1" s="48">
+    <row r="356" ht="24" customHeight="1" s="49">
       <c r="A356" s="13" t="n"/>
       <c r="B356" s="2" t="n"/>
       <c r="C356" s="46" t="n"/>
@@ -33048,7 +33480,7 @@
       <c r="AG356" s="2" t="n"/>
       <c r="AH356" s="2" t="n"/>
     </row>
-    <row r="357" ht="24" customHeight="1" s="48">
+    <row r="357" ht="24" customHeight="1" s="49">
       <c r="A357" s="13" t="n"/>
       <c r="B357" s="2" t="n"/>
       <c r="C357" s="46" t="n"/>
@@ -33084,7 +33516,7 @@
       <c r="AG357" s="2" t="n"/>
       <c r="AH357" s="2" t="n"/>
     </row>
-    <row r="358" ht="24" customHeight="1" s="48">
+    <row r="358" ht="24" customHeight="1" s="49">
       <c r="A358" s="13" t="n"/>
       <c r="B358" s="2" t="n"/>
       <c r="C358" s="46" t="n"/>
@@ -33120,7 +33552,7 @@
       <c r="AG358" s="2" t="n"/>
       <c r="AH358" s="2" t="n"/>
     </row>
-    <row r="359" ht="24" customHeight="1" s="48">
+    <row r="359" ht="24" customHeight="1" s="49">
       <c r="A359" s="13" t="n"/>
       <c r="B359" s="2" t="n"/>
       <c r="C359" s="46" t="n"/>
@@ -33156,7 +33588,7 @@
       <c r="AG359" s="2" t="n"/>
       <c r="AH359" s="2" t="n"/>
     </row>
-    <row r="360" ht="24" customHeight="1" s="48">
+    <row r="360" ht="24" customHeight="1" s="49">
       <c r="A360" s="13" t="n"/>
       <c r="B360" s="2" t="n"/>
       <c r="C360" s="46" t="n"/>
@@ -33192,7 +33624,7 @@
       <c r="AG360" s="2" t="n"/>
       <c r="AH360" s="2" t="n"/>
     </row>
-    <row r="361" ht="24" customHeight="1" s="48">
+    <row r="361" ht="24" customHeight="1" s="49">
       <c r="A361" s="13" t="n"/>
       <c r="B361" s="2" t="n"/>
       <c r="C361" s="46" t="n"/>
@@ -33228,7 +33660,7 @@
       <c r="AG361" s="2" t="n"/>
       <c r="AH361" s="2" t="n"/>
     </row>
-    <row r="362" ht="24" customHeight="1" s="48">
+    <row r="362" ht="24" customHeight="1" s="49">
       <c r="A362" s="13" t="n"/>
       <c r="B362" s="2" t="n"/>
       <c r="C362" s="46" t="n"/>
@@ -33264,7 +33696,7 @@
       <c r="AG362" s="2" t="n"/>
       <c r="AH362" s="2" t="n"/>
     </row>
-    <row r="363" ht="24" customHeight="1" s="48">
+    <row r="363" ht="24" customHeight="1" s="49">
       <c r="A363" s="13" t="n"/>
       <c r="B363" s="2" t="n"/>
       <c r="C363" s="46" t="n"/>
@@ -33300,7 +33732,7 @@
       <c r="AG363" s="2" t="n"/>
       <c r="AH363" s="2" t="n"/>
     </row>
-    <row r="364" ht="24" customHeight="1" s="48">
+    <row r="364" ht="24" customHeight="1" s="49">
       <c r="A364" s="13" t="n"/>
       <c r="B364" s="2" t="n"/>
       <c r="C364" s="46" t="n"/>
@@ -33336,7 +33768,7 @@
       <c r="AG364" s="2" t="n"/>
       <c r="AH364" s="2" t="n"/>
     </row>
-    <row r="365" ht="24" customHeight="1" s="48">
+    <row r="365" ht="24" customHeight="1" s="49">
       <c r="A365" s="13" t="n"/>
       <c r="B365" s="2" t="n"/>
       <c r="C365" s="46" t="n"/>
@@ -33372,7 +33804,7 @@
       <c r="AG365" s="2" t="n"/>
       <c r="AH365" s="2" t="n"/>
     </row>
-    <row r="366" ht="24" customHeight="1" s="48">
+    <row r="366" ht="24" customHeight="1" s="49">
       <c r="A366" s="13" t="n"/>
       <c r="B366" s="2" t="n"/>
       <c r="C366" s="46" t="n"/>
@@ -33408,7 +33840,7 @@
       <c r="AG366" s="2" t="n"/>
       <c r="AH366" s="2" t="n"/>
     </row>
-    <row r="367" ht="24" customHeight="1" s="48">
+    <row r="367" ht="24" customHeight="1" s="49">
       <c r="A367" s="13" t="n"/>
       <c r="B367" s="2" t="n"/>
       <c r="C367" s="46" t="n"/>
@@ -33444,7 +33876,7 @@
       <c r="AG367" s="2" t="n"/>
       <c r="AH367" s="2" t="n"/>
     </row>
-    <row r="368" ht="24" customHeight="1" s="48">
+    <row r="368" ht="24" customHeight="1" s="49">
       <c r="A368" s="13" t="n"/>
       <c r="B368" s="2" t="n"/>
       <c r="C368" s="46" t="n"/>
@@ -33480,7 +33912,7 @@
       <c r="AG368" s="2" t="n"/>
       <c r="AH368" s="2" t="n"/>
     </row>
-    <row r="369" ht="24" customHeight="1" s="48">
+    <row r="369" ht="24" customHeight="1" s="49">
       <c r="A369" s="13" t="n"/>
       <c r="B369" s="2" t="n"/>
       <c r="C369" s="46" t="n"/>
@@ -33516,7 +33948,7 @@
       <c r="AG369" s="2" t="n"/>
       <c r="AH369" s="2" t="n"/>
     </row>
-    <row r="370" ht="24" customHeight="1" s="48">
+    <row r="370" ht="24" customHeight="1" s="49">
       <c r="A370" s="13" t="n"/>
       <c r="B370" s="2" t="n"/>
       <c r="C370" s="46" t="n"/>
@@ -33552,7 +33984,7 @@
       <c r="AG370" s="2" t="n"/>
       <c r="AH370" s="2" t="n"/>
     </row>
-    <row r="371" ht="24" customHeight="1" s="48">
+    <row r="371" ht="24" customHeight="1" s="49">
       <c r="A371" s="13" t="n"/>
       <c r="B371" s="2" t="n"/>
       <c r="C371" s="46" t="n"/>
@@ -33588,7 +34020,7 @@
       <c r="AG371" s="2" t="n"/>
       <c r="AH371" s="2" t="n"/>
     </row>
-    <row r="372" ht="24" customHeight="1" s="48">
+    <row r="372" ht="24" customHeight="1" s="49">
       <c r="A372" s="13" t="n"/>
       <c r="B372" s="2" t="n"/>
       <c r="C372" s="46" t="n"/>
@@ -33624,7 +34056,7 @@
       <c r="AG372" s="2" t="n"/>
       <c r="AH372" s="2" t="n"/>
     </row>
-    <row r="373" ht="24" customHeight="1" s="48">
+    <row r="373" ht="24" customHeight="1" s="49">
       <c r="A373" s="13" t="n"/>
       <c r="B373" s="2" t="n"/>
       <c r="C373" s="46" t="n"/>
@@ -33660,7 +34092,7 @@
       <c r="AG373" s="2" t="n"/>
       <c r="AH373" s="2" t="n"/>
     </row>
-    <row r="374" ht="24" customHeight="1" s="48">
+    <row r="374" ht="24" customHeight="1" s="49">
       <c r="A374" s="13" t="n"/>
       <c r="B374" s="2" t="n"/>
       <c r="C374" s="46" t="n"/>
@@ -33696,7 +34128,7 @@
       <c r="AG374" s="2" t="n"/>
       <c r="AH374" s="2" t="n"/>
     </row>
-    <row r="375" ht="24" customHeight="1" s="48">
+    <row r="375" ht="24" customHeight="1" s="49">
       <c r="A375" s="13" t="n"/>
       <c r="B375" s="2" t="n"/>
       <c r="C375" s="46" t="n"/>
@@ -33732,7 +34164,7 @@
       <c r="AG375" s="2" t="n"/>
       <c r="AH375" s="2" t="n"/>
     </row>
-    <row r="376" ht="24" customHeight="1" s="48">
+    <row r="376" ht="24" customHeight="1" s="49">
       <c r="A376" s="13" t="n"/>
       <c r="B376" s="2" t="n"/>
       <c r="C376" s="46" t="n"/>
@@ -33768,7 +34200,7 @@
       <c r="AG376" s="2" t="n"/>
       <c r="AH376" s="2" t="n"/>
     </row>
-    <row r="377" ht="24" customHeight="1" s="48">
+    <row r="377" ht="24" customHeight="1" s="49">
       <c r="A377" s="13" t="n"/>
       <c r="B377" s="2" t="n"/>
       <c r="C377" s="46" t="n"/>
@@ -33804,7 +34236,7 @@
       <c r="AG377" s="2" t="n"/>
       <c r="AH377" s="2" t="n"/>
     </row>
-    <row r="378" ht="24" customHeight="1" s="48">
+    <row r="378" ht="24" customHeight="1" s="49">
       <c r="A378" s="13" t="n"/>
       <c r="B378" s="2" t="n"/>
       <c r="C378" s="46" t="n"/>
@@ -33840,7 +34272,7 @@
       <c r="AG378" s="2" t="n"/>
       <c r="AH378" s="2" t="n"/>
     </row>
-    <row r="379" ht="24" customHeight="1" s="48">
+    <row r="379" ht="24" customHeight="1" s="49">
       <c r="A379" s="13" t="n"/>
       <c r="B379" s="2" t="n"/>
       <c r="C379" s="46" t="n"/>
@@ -33876,7 +34308,7 @@
       <c r="AG379" s="2" t="n"/>
       <c r="AH379" s="2" t="n"/>
     </row>
-    <row r="380" ht="24" customHeight="1" s="48">
+    <row r="380" ht="24" customHeight="1" s="49">
       <c r="A380" s="13" t="n"/>
       <c r="B380" s="2" t="n"/>
       <c r="C380" s="46" t="n"/>
@@ -33912,7 +34344,7 @@
       <c r="AG380" s="2" t="n"/>
       <c r="AH380" s="2" t="n"/>
     </row>
-    <row r="381" ht="24" customHeight="1" s="48">
+    <row r="381" ht="24" customHeight="1" s="49">
       <c r="A381" s="13" t="n"/>
       <c r="B381" s="2" t="n"/>
       <c r="C381" s="46" t="n"/>
@@ -33948,7 +34380,7 @@
       <c r="AG381" s="2" t="n"/>
       <c r="AH381" s="2" t="n"/>
     </row>
-    <row r="382" ht="24" customHeight="1" s="48">
+    <row r="382" ht="24" customHeight="1" s="49">
       <c r="A382" s="13" t="n"/>
       <c r="B382" s="2" t="n"/>
       <c r="C382" s="46" t="n"/>
@@ -33984,7 +34416,7 @@
       <c r="AG382" s="2" t="n"/>
       <c r="AH382" s="2" t="n"/>
     </row>
-    <row r="383" ht="24" customHeight="1" s="48">
+    <row r="383" ht="24" customHeight="1" s="49">
       <c r="A383" s="13" t="n"/>
       <c r="B383" s="2" t="n"/>
       <c r="C383" s="46" t="n"/>
@@ -34020,7 +34452,7 @@
       <c r="AG383" s="2" t="n"/>
       <c r="AH383" s="2" t="n"/>
     </row>
-    <row r="384" ht="24" customHeight="1" s="48">
+    <row r="384" ht="24" customHeight="1" s="49">
       <c r="A384" s="13" t="n"/>
       <c r="B384" s="2" t="n"/>
       <c r="C384" s="46" t="n"/>
@@ -34056,7 +34488,7 @@
       <c r="AG384" s="2" t="n"/>
       <c r="AH384" s="2" t="n"/>
     </row>
-    <row r="385" ht="24" customHeight="1" s="48">
+    <row r="385" ht="24" customHeight="1" s="49">
       <c r="A385" s="13" t="n"/>
       <c r="B385" s="2" t="n"/>
       <c r="C385" s="46" t="n"/>
@@ -34092,7 +34524,7 @@
       <c r="AG385" s="2" t="n"/>
       <c r="AH385" s="2" t="n"/>
     </row>
-    <row r="386" ht="24" customHeight="1" s="48">
+    <row r="386" ht="24" customHeight="1" s="49">
       <c r="A386" s="13" t="n"/>
       <c r="B386" s="2" t="n"/>
       <c r="C386" s="46" t="n"/>
@@ -34128,7 +34560,7 @@
       <c r="AG386" s="2" t="n"/>
       <c r="AH386" s="2" t="n"/>
     </row>
-    <row r="387" ht="24" customHeight="1" s="48">
+    <row r="387" ht="24" customHeight="1" s="49">
       <c r="A387" s="13" t="n"/>
       <c r="B387" s="2" t="n"/>
       <c r="C387" s="46" t="n"/>
@@ -34164,7 +34596,7 @@
       <c r="AG387" s="2" t="n"/>
       <c r="AH387" s="2" t="n"/>
     </row>
-    <row r="388" ht="24" customHeight="1" s="48">
+    <row r="388" ht="24" customHeight="1" s="49">
       <c r="A388" s="13" t="n"/>
       <c r="B388" s="2" t="n"/>
       <c r="C388" s="46" t="n"/>
@@ -34200,7 +34632,7 @@
       <c r="AG388" s="2" t="n"/>
       <c r="AH388" s="2" t="n"/>
     </row>
-    <row r="389" ht="24" customHeight="1" s="48">
+    <row r="389" ht="24" customHeight="1" s="49">
       <c r="A389" s="13" t="n"/>
       <c r="B389" s="2" t="n"/>
       <c r="C389" s="46" t="n"/>
@@ -34236,7 +34668,7 @@
       <c r="AG389" s="2" t="n"/>
       <c r="AH389" s="2" t="n"/>
     </row>
-    <row r="390" ht="24" customHeight="1" s="48">
+    <row r="390" ht="24" customHeight="1" s="49">
       <c r="A390" s="13" t="n"/>
       <c r="B390" s="2" t="n"/>
       <c r="C390" s="46" t="n"/>
@@ -34272,7 +34704,7 @@
       <c r="AG390" s="2" t="n"/>
       <c r="AH390" s="2" t="n"/>
     </row>
-    <row r="391" ht="24" customHeight="1" s="48">
+    <row r="391" ht="24" customHeight="1" s="49">
       <c r="A391" s="13" t="n"/>
       <c r="B391" s="2" t="n"/>
       <c r="C391" s="46" t="n"/>
@@ -34308,7 +34740,7 @@
       <c r="AG391" s="2" t="n"/>
       <c r="AH391" s="2" t="n"/>
     </row>
-    <row r="392" ht="24" customHeight="1" s="48">
+    <row r="392" ht="24" customHeight="1" s="49">
       <c r="A392" s="13" t="n"/>
       <c r="B392" s="2" t="n"/>
       <c r="C392" s="46" t="n"/>
@@ -34344,7 +34776,7 @@
       <c r="AG392" s="2" t="n"/>
       <c r="AH392" s="2" t="n"/>
     </row>
-    <row r="393" ht="24" customHeight="1" s="48">
+    <row r="393" ht="24" customHeight="1" s="49">
       <c r="A393" s="13" t="n"/>
       <c r="B393" s="2" t="n"/>
       <c r="C393" s="46" t="n"/>
@@ -34380,7 +34812,7 @@
       <c r="AG393" s="2" t="n"/>
       <c r="AH393" s="2" t="n"/>
     </row>
-    <row r="394" ht="24" customHeight="1" s="48">
+    <row r="394" ht="24" customHeight="1" s="49">
       <c r="A394" s="13" t="n"/>
       <c r="B394" s="2" t="n"/>
       <c r="C394" s="46" t="n"/>
@@ -34416,7 +34848,7 @@
       <c r="AG394" s="2" t="n"/>
       <c r="AH394" s="2" t="n"/>
     </row>
-    <row r="395" ht="24" customHeight="1" s="48">
+    <row r="395" ht="24" customHeight="1" s="49">
       <c r="A395" s="13" t="n"/>
       <c r="B395" s="2" t="n"/>
       <c r="C395" s="46" t="n"/>
@@ -34452,7 +34884,7 @@
       <c r="AG395" s="2" t="n"/>
       <c r="AH395" s="2" t="n"/>
     </row>
-    <row r="396" ht="24" customHeight="1" s="48">
+    <row r="396" ht="24" customHeight="1" s="49">
       <c r="A396" s="13" t="n"/>
       <c r="B396" s="2" t="n"/>
       <c r="C396" s="46" t="n"/>
@@ -34488,7 +34920,7 @@
       <c r="AG396" s="2" t="n"/>
       <c r="AH396" s="2" t="n"/>
     </row>
-    <row r="397" ht="24" customHeight="1" s="48">
+    <row r="397" ht="24" customHeight="1" s="49">
       <c r="A397" s="13" t="n"/>
       <c r="B397" s="2" t="n"/>
       <c r="C397" s="46" t="n"/>
@@ -34524,7 +34956,7 @@
       <c r="AG397" s="2" t="n"/>
       <c r="AH397" s="2" t="n"/>
     </row>
-    <row r="398" ht="24" customHeight="1" s="48">
+    <row r="398" ht="24" customHeight="1" s="49">
       <c r="A398" s="13" t="n"/>
       <c r="B398" s="2" t="n"/>
       <c r="C398" s="46" t="n"/>
@@ -34560,7 +34992,7 @@
       <c r="AG398" s="2" t="n"/>
       <c r="AH398" s="2" t="n"/>
     </row>
-    <row r="399" ht="24" customHeight="1" s="48">
+    <row r="399" ht="24" customHeight="1" s="49">
       <c r="A399" s="13" t="n"/>
       <c r="B399" s="2" t="n"/>
       <c r="C399" s="46" t="n"/>
@@ -34596,7 +35028,7 @@
       <c r="AG399" s="2" t="n"/>
       <c r="AH399" s="2" t="n"/>
     </row>
-    <row r="400" ht="24" customHeight="1" s="48">
+    <row r="400" ht="24" customHeight="1" s="49">
       <c r="A400" s="13" t="n"/>
       <c r="B400" s="2" t="n"/>
       <c r="C400" s="46" t="n"/>
@@ -34632,7 +35064,7 @@
       <c r="AG400" s="2" t="n"/>
       <c r="AH400" s="2" t="n"/>
     </row>
-    <row r="401" ht="24" customHeight="1" s="48">
+    <row r="401" ht="24" customHeight="1" s="49">
       <c r="A401" s="12" t="n">
         <v>400</v>
       </c>
@@ -34675,6 +35107,7 @@
       <c r="AH401" s="2" t="n"/>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1"/>
   <autoFilter ref="A1:AH401"/>
   <conditionalFormatting sqref="A2:N401 R2:AH401">
     <cfRule type="expression" priority="3" dxfId="1">
@@ -34862,7 +35295,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="27.75" customHeight="1" s="48">
+    <row r="2" ht="27.75" customHeight="1" s="49">
       <c r="A2" s="0" t="n">
         <v>1</v>
       </c>
@@ -34941,7 +35374,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="27.75" customHeight="1" s="48">
+    <row r="3" ht="27.75" customHeight="1" s="49">
       <c r="A3" s="0" t="n">
         <v>2</v>
       </c>
@@ -35382,7 +35815,7 @@
   <dimension ref="A1:K4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.9"/>
   <cols>
-    <col width="18.59765625" customWidth="1" style="49" min="11" max="11"/>
+    <col width="18.59765625" customWidth="1" style="50" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -35436,7 +35869,7 @@
           <t>level2</t>
         </is>
       </c>
-      <c r="K1" s="49" t="inlineStr">
+      <c r="K1" s="50" t="inlineStr">
         <is>
           <t>date</t>
         </is>
@@ -35481,7 +35914,7 @@
           <t>大兴安岭地区</t>
         </is>
       </c>
-      <c r="K2" s="49" t="n">
+      <c r="K2" s="50" t="n">
         <v>25199</v>
       </c>
     </row>
@@ -35521,7 +35954,7 @@
           <t>呼伦贝尔市</t>
         </is>
       </c>
-      <c r="K3" s="49" t="n">
+      <c r="K3" s="50" t="n">
         <v>45993</v>
       </c>
     </row>
@@ -35561,7 +35994,7 @@
           <t>阿勒泰地区</t>
         </is>
       </c>
-      <c r="K4" s="49" t="n">
+      <c r="K4" s="50" t="n">
         <v>45995</v>
       </c>
     </row>

--- a/气象/For_Python_站点信息和记录.xlsx
+++ b/气象/For_Python_站点信息和记录.xlsx
@@ -806,8 +806,8 @@
     <col width="18.59765625" customWidth="1" style="8" min="25" max="25"/>
     <col width="12.59765625" customWidth="1" style="5" min="26" max="30"/>
     <col width="12.59765625" customWidth="1" style="8" min="31" max="32"/>
-    <col width="12.59765625" customWidth="1" style="5" min="33" max="372"/>
-    <col width="12.59765625" customWidth="1" style="5" min="373" max="16384"/>
+    <col width="12.59765625" customWidth="1" style="5" min="33" max="386"/>
+    <col width="12.59765625" customWidth="1" style="5" min="387" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="27.75" customFormat="1" customHeight="1" s="11">
@@ -1030,13 +1030,13 @@
         </is>
       </c>
       <c r="O2" s="32" t="n">
-        <v>1.9</v>
+        <v>-4.7</v>
       </c>
       <c r="P2" s="32" t="n">
-        <v>12.8</v>
+        <v>13.3</v>
       </c>
       <c r="Q2" s="32" t="n">
-        <v>7</v>
+        <v>0.89</v>
       </c>
       <c r="R2" s="23" t="inlineStr">
         <is>
@@ -1136,10 +1136,10 @@
         </is>
       </c>
       <c r="O3" s="32" t="n">
-        <v>3.3</v>
+        <v>-6.9</v>
       </c>
       <c r="P3" s="32" t="n">
-        <v>12.7</v>
+        <v>16</v>
       </c>
       <c r="Q3" s="32" t="n"/>
       <c r="R3" s="23" t="n"/>
@@ -1240,10 +1240,10 @@
         </is>
       </c>
       <c r="O4" s="32" t="n">
-        <v>2.4</v>
+        <v>-5.4</v>
       </c>
       <c r="P4" s="32" t="n">
-        <v>12</v>
+        <v>13.6</v>
       </c>
       <c r="Q4" s="32" t="n"/>
       <c r="R4" s="23" t="n"/>
@@ -1432,10 +1432,10 @@
         </is>
       </c>
       <c r="O6" s="32" t="n">
-        <v>0.6</v>
+        <v>-7.8</v>
       </c>
       <c r="P6" s="32" t="n">
-        <v>10.5</v>
+        <v>3.8</v>
       </c>
       <c r="Q6" s="32" t="n"/>
       <c r="R6" s="23" t="n"/>
@@ -1532,10 +1532,10 @@
         </is>
       </c>
       <c r="O7" s="32" t="n">
-        <v>-5</v>
+        <v>-9.800000000000001</v>
       </c>
       <c r="P7" s="32" t="n">
-        <v>2.6</v>
+        <v>4.6</v>
       </c>
       <c r="Q7" s="32" t="n"/>
       <c r="R7" s="23" t="n"/>
@@ -1640,13 +1640,13 @@
       </c>
       <c r="N8" s="2" t="n"/>
       <c r="O8" s="32" t="n">
-        <v>-2.3</v>
+        <v>-3.5</v>
       </c>
       <c r="P8" s="32" t="n">
-        <v>6.8</v>
+        <v>16.5</v>
       </c>
       <c r="Q8" s="32" t="n">
-        <v>1.36</v>
+        <v>5.1</v>
       </c>
       <c r="R8" s="23" t="inlineStr">
         <is>
@@ -1752,13 +1752,13 @@
       </c>
       <c r="N9" s="2" t="n"/>
       <c r="O9" s="32" t="n">
-        <v>6</v>
+        <v>-6.3</v>
       </c>
       <c r="P9" s="32" t="n">
-        <v>13.1</v>
+        <v>11.4</v>
       </c>
       <c r="Q9" s="32" t="n">
-        <v>9.16</v>
+        <v>-0.3</v>
       </c>
       <c r="R9" s="23" t="inlineStr">
         <is>
@@ -1872,13 +1872,13 @@
         </is>
       </c>
       <c r="O10" s="32" t="n">
-        <v>0.9</v>
+        <v>-6.1</v>
       </c>
       <c r="P10" s="32" t="n">
-        <v>10.8</v>
+        <v>11.6</v>
       </c>
       <c r="Q10" s="32" t="n">
-        <v>4.41</v>
+        <v>-0.52</v>
       </c>
       <c r="R10" s="23" t="inlineStr">
         <is>
@@ -1988,13 +1988,13 @@
         </is>
       </c>
       <c r="O11" s="32" t="n">
-        <v>-0.3</v>
+        <v>-11.2</v>
       </c>
       <c r="P11" s="32" t="n">
-        <v>9.699999999999999</v>
+        <v>5.9</v>
       </c>
       <c r="Q11" s="32" t="n">
-        <v>4.15</v>
+        <v>-4.66</v>
       </c>
       <c r="R11" s="23" t="inlineStr">
         <is>
@@ -2100,13 +2100,13 @@
       </c>
       <c r="N12" s="2" t="n"/>
       <c r="O12" s="32" t="n">
-        <v>1</v>
+        <v>-7.8</v>
       </c>
       <c r="P12" s="32" t="n">
-        <v>12.4</v>
+        <v>4.9</v>
       </c>
       <c r="Q12" s="32" t="n">
-        <v>5.25</v>
+        <v>-1.95</v>
       </c>
       <c r="R12" s="23" t="inlineStr">
         <is>
@@ -2216,13 +2216,13 @@
         </is>
       </c>
       <c r="O13" s="32" t="n">
-        <v>-4.6</v>
+        <v>-10</v>
       </c>
       <c r="P13" s="32" t="n">
-        <v>3</v>
+        <v>4.1</v>
       </c>
       <c r="Q13" s="32" t="n">
-        <v>-1.49</v>
+        <v>-4.45</v>
       </c>
       <c r="R13" s="23" t="inlineStr">
         <is>
@@ -2328,13 +2328,13 @@
       </c>
       <c r="N14" s="2" t="n"/>
       <c r="O14" s="32" t="n">
-        <v>-1.8</v>
+        <v>-2</v>
       </c>
       <c r="P14" s="32" t="n">
-        <v>12.5</v>
+        <v>17.2</v>
       </c>
       <c r="Q14" s="32" t="n">
-        <v>4.27</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="R14" s="23" t="inlineStr">
         <is>
@@ -8052,13 +8052,13 @@
         </is>
       </c>
       <c r="O77" s="32" t="n">
-        <v>-3.6</v>
+        <v>-4.8</v>
       </c>
       <c r="P77" s="32" t="n">
         <v>4.9</v>
       </c>
       <c r="Q77" s="32" t="n">
-        <v>0.39</v>
+        <v>-0.3</v>
       </c>
       <c r="R77" s="23" t="inlineStr">
         <is>
@@ -8481,7 +8481,7 @@
         <v>-9.699999999999999</v>
       </c>
       <c r="P81" s="32" t="n">
-        <v>0.8</v>
+        <v>10.2</v>
       </c>
       <c r="Q81" s="32" t="n"/>
       <c r="R81" s="23" t="inlineStr">
@@ -8597,13 +8597,13 @@
         </is>
       </c>
       <c r="O82" s="32" t="n">
-        <v>-10.3</v>
+        <v>-9.1</v>
       </c>
       <c r="P82" s="32" t="n">
-        <v>0.8</v>
+        <v>9.6</v>
       </c>
       <c r="Q82" s="32" t="n">
-        <v>-3.79</v>
+        <v>0.64</v>
       </c>
       <c r="R82" s="23" t="inlineStr">
         <is>
@@ -8815,13 +8815,13 @@
         </is>
       </c>
       <c r="O84" s="32" t="n">
-        <v>-7</v>
+        <v>-4.3</v>
       </c>
       <c r="P84" s="32" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="Q84" s="32" t="n">
-        <v>-3.94</v>
+        <v>-1.55</v>
       </c>
       <c r="R84" s="23" t="inlineStr">
         <is>
@@ -9033,13 +9033,13 @@
       </c>
       <c r="N86" s="2" t="n"/>
       <c r="O86" s="32" t="n">
-        <v>2</v>
+        <v>-5.2</v>
       </c>
       <c r="P86" s="32" t="n">
-        <v>11.9</v>
+        <v>5.5</v>
       </c>
       <c r="Q86" s="32" t="n">
-        <v>4.79</v>
+        <v>-1.71</v>
       </c>
       <c r="R86" s="23" t="inlineStr">
         <is>
@@ -9259,13 +9259,13 @@
       </c>
       <c r="N88" s="2" t="n"/>
       <c r="O88" s="32" t="n">
-        <v>1.5</v>
+        <v>-13.1</v>
       </c>
       <c r="P88" s="32" t="n">
-        <v>9.4</v>
+        <v>1.8</v>
       </c>
       <c r="Q88" s="32" t="n">
-        <v>5.19</v>
+        <v>-6.11</v>
       </c>
       <c r="R88" s="23" t="inlineStr">
         <is>
@@ -9669,13 +9669,13 @@
       </c>
       <c r="N92" s="2" t="n"/>
       <c r="O92" s="32" t="n">
-        <v>-5.3</v>
+        <v>4.6</v>
       </c>
       <c r="P92" s="32" t="n">
-        <v>1.3</v>
+        <v>15.9</v>
       </c>
       <c r="Q92" s="32" t="n">
-        <v>-1.59</v>
+        <v>8.77</v>
       </c>
       <c r="R92" s="23" t="inlineStr">
         <is>
@@ -9781,13 +9781,13 @@
       </c>
       <c r="N93" s="2" t="n"/>
       <c r="O93" s="32" t="n">
-        <v>2.7</v>
+        <v>8.5</v>
       </c>
       <c r="P93" s="32" t="n">
-        <v>15.4</v>
+        <v>21.4</v>
       </c>
       <c r="Q93" s="32" t="n">
-        <v>10.06</v>
+        <v>15.32</v>
       </c>
       <c r="R93" s="23" t="inlineStr">
         <is>
@@ -9900,18 +9900,10 @@
           <t>↓</t>
         </is>
       </c>
-      <c r="O94" s="32" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="P94" s="32" t="n">
-        <v>12.4</v>
-      </c>
+      <c r="O94" s="32" t="n"/>
+      <c r="P94" s="32" t="n"/>
       <c r="Q94" s="32" t="n"/>
-      <c r="R94" s="23" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="R94" s="23" t="n"/>
       <c r="S94" s="37" t="n"/>
       <c r="T94" s="41" t="inlineStr">
         <is>
@@ -10019,13 +10011,13 @@
       </c>
       <c r="N95" s="2" t="n"/>
       <c r="O95" s="32" t="n">
-        <v>1.2</v>
+        <v>2.9</v>
       </c>
       <c r="P95" s="32" t="n">
-        <v>11</v>
+        <v>16.3</v>
       </c>
       <c r="Q95" s="32" t="n">
-        <v>6.22</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="R95" s="23" t="inlineStr">
         <is>
@@ -10146,18 +10138,10 @@
           <t>↓</t>
         </is>
       </c>
-      <c r="O96" s="32" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="P96" s="32" t="n">
-        <v>10.9</v>
-      </c>
+      <c r="O96" s="32" t="n"/>
+      <c r="P96" s="32" t="n"/>
       <c r="Q96" s="32" t="n"/>
-      <c r="R96" s="23" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="R96" s="23" t="n"/>
       <c r="S96" s="37" t="n"/>
       <c r="T96" s="41" t="inlineStr">
         <is>
@@ -10265,13 +10249,13 @@
       </c>
       <c r="N97" s="2" t="n"/>
       <c r="O97" s="32" t="n">
-        <v>0.7</v>
+        <v>2.7</v>
       </c>
       <c r="P97" s="32" t="n">
-        <v>7.9</v>
+        <v>13.2</v>
       </c>
       <c r="Q97" s="32" t="n">
-        <v>4.35</v>
+        <v>8.09</v>
       </c>
       <c r="R97" s="23" t="inlineStr">
         <is>
@@ -10385,10 +10369,10 @@
       </c>
       <c r="N98" s="2" t="n"/>
       <c r="O98" s="32" t="n">
-        <v>0.7</v>
+        <v>4.2</v>
       </c>
       <c r="P98" s="32" t="n">
-        <v>5.3</v>
+        <v>13.7</v>
       </c>
       <c r="Q98" s="32" t="n"/>
       <c r="R98" s="23" t="inlineStr">
@@ -10502,20 +10486,10 @@
         </is>
       </c>
       <c r="N99" s="2" t="n"/>
-      <c r="O99" s="32" t="n">
-        <v>-0.6</v>
-      </c>
-      <c r="P99" s="32" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="Q99" s="32" t="n">
-        <v>3.36</v>
-      </c>
-      <c r="R99" s="23" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="O99" s="32" t="n"/>
+      <c r="P99" s="32" t="n"/>
+      <c r="Q99" s="32" t="n"/>
+      <c r="R99" s="23" t="n"/>
       <c r="S99" s="37" t="n"/>
       <c r="T99" s="41" t="inlineStr">
         <is>
@@ -10835,13 +10809,13 @@
       </c>
       <c r="N102" s="2" t="n"/>
       <c r="O102" s="32" t="n">
-        <v>-1.1</v>
+        <v>-8.800000000000001</v>
       </c>
       <c r="P102" s="32" t="n">
-        <v>4.5</v>
+        <v>11.3</v>
       </c>
       <c r="Q102" s="32" t="n">
-        <v>1.2</v>
+        <v>1.48</v>
       </c>
       <c r="R102" s="23" t="inlineStr">
         <is>
@@ -10950,18 +10924,10 @@
         </is>
       </c>
       <c r="N103" s="2" t="n"/>
-      <c r="O103" s="32" t="n">
-        <v>-1.4</v>
-      </c>
-      <c r="P103" s="32" t="n">
-        <v>5.3</v>
-      </c>
+      <c r="O103" s="32" t="n"/>
+      <c r="P103" s="32" t="n"/>
       <c r="Q103" s="32" t="n"/>
-      <c r="R103" s="23" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="R103" s="23" t="n"/>
       <c r="S103" s="37" t="n"/>
       <c r="T103" s="41" t="inlineStr">
         <is>
@@ -11060,18 +11026,10 @@
         </is>
       </c>
       <c r="N104" s="2" t="n"/>
-      <c r="O104" s="32" t="n">
-        <v>-2</v>
-      </c>
-      <c r="P104" s="32" t="n">
-        <v>6</v>
-      </c>
+      <c r="O104" s="32" t="n"/>
+      <c r="P104" s="32" t="n"/>
       <c r="Q104" s="32" t="n"/>
-      <c r="R104" s="23" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="R104" s="23" t="n"/>
       <c r="S104" s="37" t="inlineStr">
         <is>
           <t>Y</t>
@@ -11187,13 +11145,13 @@
         </is>
       </c>
       <c r="O105" s="32" t="n">
-        <v>-2.5</v>
+        <v>-10.2</v>
       </c>
       <c r="P105" s="32" t="n">
-        <v>4.5</v>
+        <v>10</v>
       </c>
       <c r="Q105" s="32" t="n">
-        <v>0.22</v>
+        <v>0.71</v>
       </c>
       <c r="R105" s="23" t="inlineStr">
         <is>
@@ -11302,18 +11260,10 @@
           <t>▲</t>
         </is>
       </c>
-      <c r="O106" s="32" t="n">
-        <v>-2.6</v>
-      </c>
-      <c r="P106" s="32" t="n">
-        <v>5.5</v>
-      </c>
+      <c r="O106" s="32" t="n"/>
+      <c r="P106" s="32" t="n"/>
       <c r="Q106" s="32" t="n"/>
-      <c r="R106" s="23" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="R106" s="23" t="n"/>
       <c r="S106" s="37" t="n"/>
       <c r="T106" s="41" t="inlineStr">
         <is>
@@ -11415,11 +11365,7 @@
       <c r="O107" s="32" t="n"/>
       <c r="P107" s="32" t="n"/>
       <c r="Q107" s="32" t="n"/>
-      <c r="R107" s="23" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="R107" s="23" t="n"/>
       <c r="S107" s="37" t="n"/>
       <c r="T107" s="41" t="inlineStr">
         <is>
@@ -11522,20 +11468,10 @@
         </is>
       </c>
       <c r="N108" s="2" t="n"/>
-      <c r="O108" s="32" t="n">
-        <v>-2.6</v>
-      </c>
-      <c r="P108" s="32" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="Q108" s="32" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="R108" s="23" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="O108" s="32" t="n"/>
+      <c r="P108" s="32" t="n"/>
+      <c r="Q108" s="32" t="n"/>
+      <c r="R108" s="23" t="n"/>
       <c r="S108" s="37" t="n"/>
       <c r="T108" s="41" t="inlineStr">
         <is>
@@ -11637,11 +11573,7 @@
       <c r="O109" s="32" t="n"/>
       <c r="P109" s="32" t="n"/>
       <c r="Q109" s="32" t="n"/>
-      <c r="R109" s="23" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="R109" s="23" t="n"/>
       <c r="S109" s="37" t="n"/>
       <c r="T109" s="41" t="inlineStr">
         <is>
@@ -11739,11 +11671,7 @@
       <c r="O110" s="32" t="n"/>
       <c r="P110" s="32" t="n"/>
       <c r="Q110" s="32" t="n"/>
-      <c r="R110" s="23" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="R110" s="23" t="n"/>
       <c r="S110" s="37" t="n"/>
       <c r="T110" s="41" t="inlineStr">
         <is>
@@ -11850,20 +11778,10 @@
         </is>
       </c>
       <c r="N111" s="2" t="n"/>
-      <c r="O111" s="32" t="n">
-        <v>-6.6</v>
-      </c>
-      <c r="P111" s="32" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q111" s="32" t="n">
-        <v>-1.23</v>
-      </c>
-      <c r="R111" s="23" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="O111" s="32" t="n"/>
+      <c r="P111" s="32" t="n"/>
+      <c r="Q111" s="32" t="n"/>
+      <c r="R111" s="23" t="n"/>
       <c r="S111" s="37" t="n"/>
       <c r="T111" s="41" t="inlineStr">
         <is>
@@ -11962,18 +11880,10 @@
         </is>
       </c>
       <c r="N112" s="2" t="n"/>
-      <c r="O112" s="32" t="n">
-        <v>-4.9</v>
-      </c>
-      <c r="P112" s="32" t="n">
-        <v>20.5</v>
-      </c>
+      <c r="O112" s="32" t="n"/>
+      <c r="P112" s="32" t="n"/>
       <c r="Q112" s="32" t="n"/>
-      <c r="R112" s="23" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="R112" s="23" t="n"/>
       <c r="S112" s="37" t="n"/>
       <c r="T112" s="41" t="inlineStr">
         <is>
@@ -12069,10 +11979,10 @@
       </c>
       <c r="N113" s="2" t="n"/>
       <c r="O113" s="32" t="n">
-        <v>-12.4</v>
+        <v>-1.8</v>
       </c>
       <c r="P113" s="32" t="n">
-        <v>0.3</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="Q113" s="32" t="n"/>
       <c r="R113" s="23" t="inlineStr">
@@ -12183,10 +12093,10 @@
         </is>
       </c>
       <c r="O114" s="32" t="n">
-        <v>-4.9</v>
+        <v>-8</v>
       </c>
       <c r="P114" s="32" t="n">
-        <v>1.4</v>
+        <v>10</v>
       </c>
       <c r="Q114" s="32" t="n"/>
       <c r="R114" s="23" t="inlineStr">
@@ -12305,10 +12215,10 @@
         </is>
       </c>
       <c r="O115" s="32" t="n">
-        <v>-7.4</v>
+        <v>-6.5</v>
       </c>
       <c r="P115" s="32" t="n">
-        <v>0.1</v>
+        <v>9.1</v>
       </c>
       <c r="Q115" s="32" t="n"/>
       <c r="R115" s="23" t="inlineStr">
@@ -12422,20 +12332,10 @@
         </is>
       </c>
       <c r="N116" s="2" t="n"/>
-      <c r="O116" s="32" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="P116" s="32" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="Q116" s="32" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="R116" s="23" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="O116" s="32" t="n"/>
+      <c r="P116" s="32" t="n"/>
+      <c r="Q116" s="32" t="n"/>
+      <c r="R116" s="23" t="n"/>
       <c r="S116" s="37" t="n"/>
       <c r="T116" s="41" t="inlineStr">
         <is>
@@ -12537,11 +12437,7 @@
       <c r="O117" s="32" t="n"/>
       <c r="P117" s="32" t="n"/>
       <c r="Q117" s="32" t="n"/>
-      <c r="R117" s="23" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="R117" s="23" t="n"/>
       <c r="S117" s="37" t="n"/>
       <c r="T117" s="41" t="inlineStr">
         <is>
@@ -12647,11 +12543,7 @@
       <c r="O118" s="32" t="n"/>
       <c r="P118" s="32" t="n"/>
       <c r="Q118" s="32" t="n"/>
-      <c r="R118" s="23" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="R118" s="23" t="n"/>
       <c r="S118" s="37" t="n"/>
       <c r="T118" s="41" t="inlineStr">
         <is>
@@ -12758,20 +12650,10 @@
         </is>
       </c>
       <c r="N119" s="2" t="n"/>
-      <c r="O119" s="32" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="P119" s="32" t="n">
-        <v>17.1</v>
-      </c>
-      <c r="Q119" s="32" t="n">
-        <v>12</v>
-      </c>
-      <c r="R119" s="23" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="O119" s="32" t="n"/>
+      <c r="P119" s="32" t="n"/>
+      <c r="Q119" s="32" t="n"/>
+      <c r="R119" s="23" t="n"/>
       <c r="S119" s="37" t="inlineStr">
         <is>
           <t>Y</t>
@@ -12993,13 +12875,13 @@
       </c>
       <c r="N121" s="2" t="n"/>
       <c r="O121" s="32" t="n">
-        <v>9.699999999999999</v>
+        <v>4.7</v>
       </c>
       <c r="P121" s="32" t="n">
-        <v>17.7</v>
+        <v>14.8</v>
       </c>
       <c r="Q121" s="32" t="n">
-        <v>13.73</v>
+        <v>6.64</v>
       </c>
       <c r="R121" s="23" t="inlineStr">
         <is>
@@ -13117,10 +12999,10 @@
       </c>
       <c r="N122" s="2" t="n"/>
       <c r="O122" s="32" t="n">
-        <v>0.8</v>
+        <v>-2.4</v>
       </c>
       <c r="P122" s="32" t="n">
-        <v>8.1</v>
+        <v>5.3</v>
       </c>
       <c r="Q122" s="32" t="n"/>
       <c r="R122" s="23" t="inlineStr">
@@ -13229,11 +13111,7 @@
       <c r="O123" s="32" t="n"/>
       <c r="P123" s="32" t="n"/>
       <c r="Q123" s="32" t="n"/>
-      <c r="R123" s="23" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="R123" s="23" t="n"/>
       <c r="S123" s="37" t="n"/>
       <c r="T123" s="41" t="inlineStr">
         <is>
@@ -13341,13 +13219,13 @@
       </c>
       <c r="N124" s="2" t="n"/>
       <c r="O124" s="32" t="n">
-        <v>3.4</v>
+        <v>5.9</v>
       </c>
       <c r="P124" s="32" t="n">
-        <v>24</v>
+        <v>24.6</v>
       </c>
       <c r="Q124" s="32" t="n">
-        <v>14.19</v>
+        <v>16.81</v>
       </c>
       <c r="R124" s="23" t="inlineStr">
         <is>
@@ -13465,13 +13343,13 @@
       </c>
       <c r="N125" s="2" t="n"/>
       <c r="O125" s="32" t="n">
-        <v>8</v>
+        <v>12.7</v>
       </c>
       <c r="P125" s="32" t="n">
-        <v>21.6</v>
+        <v>26.1</v>
       </c>
       <c r="Q125" s="32" t="n">
-        <v>15.62</v>
+        <v>18.8</v>
       </c>
       <c r="R125" s="23" t="inlineStr">
         <is>
@@ -13569,10 +13447,10 @@
       </c>
       <c r="N126" s="2" t="n"/>
       <c r="O126" s="32" t="n">
-        <v>10.9</v>
+        <v>13.7</v>
       </c>
       <c r="P126" s="32" t="n">
-        <v>22.1</v>
+        <v>30</v>
       </c>
       <c r="Q126" s="32" t="n"/>
       <c r="R126" s="23" t="inlineStr">
@@ -13679,13 +13557,13 @@
       </c>
       <c r="N127" s="2" t="n"/>
       <c r="O127" s="32" t="n">
-        <v>6.3</v>
+        <v>9.9</v>
       </c>
       <c r="P127" s="32" t="n">
-        <v>26.6</v>
+        <v>30.4</v>
       </c>
       <c r="Q127" s="32" t="n">
-        <v>15.96</v>
+        <v>19.99</v>
       </c>
       <c r="R127" s="23" t="inlineStr">
         <is>
@@ -13799,10 +13677,10 @@
       </c>
       <c r="N128" s="2" t="n"/>
       <c r="O128" s="32" t="n">
-        <v>11.9</v>
+        <v>14.6</v>
       </c>
       <c r="P128" s="32" t="n">
-        <v>27.4</v>
+        <v>28.2</v>
       </c>
       <c r="Q128" s="32" t="n"/>
       <c r="R128" s="23" t="inlineStr">
@@ -13909,13 +13787,13 @@
       </c>
       <c r="N129" s="2" t="n"/>
       <c r="O129" s="32" t="n">
-        <v>6.1</v>
+        <v>6.9</v>
       </c>
       <c r="P129" s="32" t="n">
-        <v>26.8</v>
+        <v>27.4</v>
       </c>
       <c r="Q129" s="32" t="n">
-        <v>16.6</v>
+        <v>18.65</v>
       </c>
       <c r="R129" s="23" t="inlineStr">
         <is>
@@ -14029,13 +13907,13 @@
       </c>
       <c r="N130" s="2" t="n"/>
       <c r="O130" s="32" t="n">
-        <v>3.2</v>
+        <v>2.2</v>
       </c>
       <c r="P130" s="32" t="n">
-        <v>19.4</v>
+        <v>24.2</v>
       </c>
       <c r="Q130" s="32" t="n">
-        <v>10.88</v>
+        <v>12.6</v>
       </c>
       <c r="R130" s="23" t="inlineStr">
         <is>
@@ -14149,13 +14027,13 @@
       </c>
       <c r="N131" s="2" t="n"/>
       <c r="O131" s="32" t="n">
-        <v>16.2</v>
+        <v>17.9</v>
       </c>
       <c r="P131" s="32" t="n">
-        <v>26.7</v>
+        <v>28.9</v>
       </c>
       <c r="Q131" s="32" t="n">
-        <v>20.55</v>
+        <v>23.06</v>
       </c>
       <c r="R131" s="23" t="inlineStr">
         <is>
@@ -14265,13 +14143,13 @@
       </c>
       <c r="N132" s="2" t="n"/>
       <c r="O132" s="32" t="n">
-        <v>13.3</v>
+        <v>12.9</v>
       </c>
       <c r="P132" s="32" t="n">
-        <v>27</v>
+        <v>27.7</v>
       </c>
       <c r="Q132" s="32" t="n">
-        <v>20.59</v>
+        <v>21.82</v>
       </c>
       <c r="R132" s="23" t="inlineStr">
         <is>
@@ -14381,13 +14259,13 @@
       </c>
       <c r="N133" s="2" t="n"/>
       <c r="O133" s="32" t="n">
-        <v>12.3</v>
+        <v>13.7</v>
       </c>
       <c r="P133" s="32" t="n">
-        <v>19.8</v>
+        <v>27.8</v>
       </c>
       <c r="Q133" s="32" t="n">
-        <v>16.08</v>
+        <v>20.8</v>
       </c>
       <c r="R133" s="23" t="inlineStr">
         <is>
@@ -14603,13 +14481,13 @@
       </c>
       <c r="N135" s="2" t="n"/>
       <c r="O135" s="32" t="n">
-        <v>19.2</v>
+        <v>15</v>
       </c>
       <c r="P135" s="32" t="n">
-        <v>22.5</v>
+        <v>28.5</v>
       </c>
       <c r="Q135" s="32" t="n">
-        <v>20.04</v>
+        <v>21.34</v>
       </c>
       <c r="R135" s="23" t="inlineStr">
         <is>
@@ -14719,13 +14597,13 @@
       </c>
       <c r="N136" s="2" t="n"/>
       <c r="O136" s="32" t="n">
-        <v>20.5</v>
+        <v>18.7</v>
       </c>
       <c r="P136" s="32" t="n">
-        <v>23</v>
+        <v>28.6</v>
       </c>
       <c r="Q136" s="32" t="n">
-        <v>21.6</v>
+        <v>23.17</v>
       </c>
       <c r="R136" s="23" t="inlineStr">
         <is>
@@ -14835,13 +14713,13 @@
       </c>
       <c r="N137" s="2" t="n"/>
       <c r="O137" s="32" t="n">
-        <v>18.9</v>
+        <v>16.3</v>
       </c>
       <c r="P137" s="32" t="n">
-        <v>21.4</v>
+        <v>28.5</v>
       </c>
       <c r="Q137" s="32" t="n">
-        <v>19.95</v>
+        <v>22.24</v>
       </c>
       <c r="R137" s="23" t="inlineStr">
         <is>
@@ -14951,10 +14829,10 @@
       </c>
       <c r="N138" s="2" t="n"/>
       <c r="O138" s="32" t="n">
-        <v>16.4</v>
+        <v>14.7</v>
       </c>
       <c r="P138" s="32" t="n">
-        <v>20.1</v>
+        <v>25.9</v>
       </c>
       <c r="Q138" s="32" t="n"/>
       <c r="R138" s="23" t="inlineStr">
@@ -15065,13 +14943,13 @@
       </c>
       <c r="N139" s="2" t="n"/>
       <c r="O139" s="32" t="n">
-        <v>15.1</v>
+        <v>16</v>
       </c>
       <c r="P139" s="32" t="n">
-        <v>20.6</v>
+        <v>23.7</v>
       </c>
       <c r="Q139" s="32" t="n">
-        <v>17.6</v>
+        <v>19.19</v>
       </c>
       <c r="R139" s="23" t="inlineStr">
         <is>
@@ -15181,13 +15059,13 @@
       </c>
       <c r="N140" s="2" t="n"/>
       <c r="O140" s="32" t="n">
-        <v>14.4</v>
+        <v>16.9</v>
       </c>
       <c r="P140" s="32" t="n">
-        <v>22.8</v>
+        <v>23.1</v>
       </c>
       <c r="Q140" s="32" t="n">
-        <v>17.82</v>
+        <v>19.45</v>
       </c>
       <c r="R140" s="23" t="inlineStr">
         <is>
@@ -15399,13 +15277,13 @@
       </c>
       <c r="N142" s="2" t="n"/>
       <c r="O142" s="32" t="n">
-        <v>20.4</v>
+        <v>18.5</v>
       </c>
       <c r="P142" s="32" t="n">
-        <v>26.3</v>
+        <v>20.5</v>
       </c>
       <c r="Q142" s="32" t="n">
-        <v>22.85</v>
+        <v>19.65</v>
       </c>
       <c r="R142" s="23" t="inlineStr">
         <is>
@@ -15515,13 +15393,13 @@
       </c>
       <c r="N143" s="2" t="n"/>
       <c r="O143" s="32" t="n">
-        <v>25.3</v>
+        <v>19.8</v>
       </c>
       <c r="P143" s="32" t="n">
-        <v>28.2</v>
+        <v>29.7</v>
       </c>
       <c r="Q143" s="32" t="n">
-        <v>26.34</v>
+        <v>23.94</v>
       </c>
       <c r="R143" s="23" t="inlineStr">
         <is>
@@ -15831,13 +15709,13 @@
       </c>
       <c r="N146" s="2" t="n"/>
       <c r="O146" s="32" t="n">
-        <v>27.9</v>
+        <v>26.9</v>
       </c>
       <c r="P146" s="32" t="n">
-        <v>34.1</v>
+        <v>30.6</v>
       </c>
       <c r="Q146" s="32" t="n">
-        <v>30.82</v>
+        <v>27.94</v>
       </c>
       <c r="R146" s="23" t="inlineStr">
         <is>
@@ -15939,13 +15817,13 @@
       </c>
       <c r="N147" s="2" t="n"/>
       <c r="O147" s="32" t="n">
-        <v>23</v>
+        <v>19.7</v>
       </c>
       <c r="P147" s="32" t="n">
-        <v>32.6</v>
+        <v>28.2</v>
       </c>
       <c r="Q147" s="32" t="n">
-        <v>27.32</v>
+        <v>22.77</v>
       </c>
       <c r="R147" s="23" t="inlineStr">
         <is>
@@ -16054,8 +15932,12 @@
         </is>
       </c>
       <c r="N148" s="2" t="n"/>
-      <c r="O148" s="32" t="n"/>
-      <c r="P148" s="32" t="n"/>
+      <c r="O148" s="32" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="P148" s="32" t="n">
+        <v>38.1</v>
+      </c>
       <c r="Q148" s="32" t="n"/>
       <c r="R148" s="23" t="n"/>
       <c r="S148" s="37" t="n"/>
@@ -16157,13 +16039,13 @@
       </c>
       <c r="N149" s="2" t="n"/>
       <c r="O149" s="32" t="n">
-        <v>12.4</v>
+        <v>12.8</v>
       </c>
       <c r="P149" s="32" t="n">
-        <v>22.8</v>
+        <v>27</v>
       </c>
       <c r="Q149" s="32" t="n">
-        <v>17.4</v>
+        <v>19.95</v>
       </c>
       <c r="R149" s="23" t="inlineStr">
         <is>
@@ -16273,13 +16155,13 @@
       </c>
       <c r="N150" s="2" t="n"/>
       <c r="O150" s="32" t="n">
-        <v>16.5</v>
+        <v>14.4</v>
       </c>
       <c r="P150" s="32" t="n">
-        <v>28.1</v>
+        <v>24.2</v>
       </c>
       <c r="Q150" s="32" t="n">
-        <v>20.46</v>
+        <v>18.73</v>
       </c>
       <c r="R150" s="23" t="inlineStr">
         <is>
@@ -16389,13 +16271,13 @@
       </c>
       <c r="N151" s="2" t="n"/>
       <c r="O151" s="32" t="n">
-        <v>17.9</v>
+        <v>18.7</v>
       </c>
       <c r="P151" s="32" t="n">
-        <v>22.5</v>
+        <v>31.8</v>
       </c>
       <c r="Q151" s="32" t="n">
-        <v>19.96</v>
+        <v>24.79</v>
       </c>
       <c r="R151" s="23" t="inlineStr">
         <is>
@@ -16595,13 +16477,13 @@
       </c>
       <c r="N153" s="2" t="n"/>
       <c r="O153" s="32" t="n">
-        <v>14.3</v>
+        <v>12.7</v>
       </c>
       <c r="P153" s="32" t="n">
-        <v>25.2</v>
+        <v>28.9</v>
       </c>
       <c r="Q153" s="32" t="n">
-        <v>19.26</v>
+        <v>20.55</v>
       </c>
       <c r="R153" s="23" t="inlineStr">
         <is>
@@ -16715,13 +16597,13 @@
       </c>
       <c r="N154" s="2" t="n"/>
       <c r="O154" s="32" t="n">
-        <v>4.7</v>
+        <v>4.2</v>
       </c>
       <c r="P154" s="32" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="Q154" s="32" t="n">
-        <v>9.789999999999999</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="R154" s="23" t="inlineStr">
         <is>
@@ -16916,18 +16798,10 @@
         </is>
       </c>
       <c r="N156" s="2" t="n"/>
-      <c r="O156" s="32" t="n">
-        <v>-5.2</v>
-      </c>
-      <c r="P156" s="32" t="n">
-        <v>23.8</v>
-      </c>
+      <c r="O156" s="32" t="n"/>
+      <c r="P156" s="32" t="n"/>
       <c r="Q156" s="32" t="n"/>
-      <c r="R156" s="23" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="R156" s="23" t="n"/>
       <c r="S156" s="37" t="n"/>
       <c r="T156" s="41" t="inlineStr">
         <is>
@@ -17023,10 +16897,10 @@
       </c>
       <c r="N157" s="2" t="n"/>
       <c r="O157" s="32" t="n">
-        <v>14.3</v>
+        <v>15.4</v>
       </c>
       <c r="P157" s="32" t="n">
-        <v>19.5</v>
+        <v>23</v>
       </c>
       <c r="Q157" s="32" t="n"/>
       <c r="R157" s="23" t="inlineStr">
@@ -17411,10 +17285,10 @@
       </c>
       <c r="N161" s="2" t="n"/>
       <c r="O161" s="32" t="n">
-        <v>7.1</v>
+        <v>6.1</v>
       </c>
       <c r="P161" s="32" t="n">
-        <v>23.6</v>
+        <v>30.1</v>
       </c>
       <c r="Q161" s="32" t="n"/>
       <c r="R161" s="23" t="inlineStr">
@@ -17524,12 +17398,8 @@
           <t>⚡</t>
         </is>
       </c>
-      <c r="O162" s="32" t="n">
-        <v>-5</v>
-      </c>
-      <c r="P162" s="32" t="n">
-        <v>2.3</v>
-      </c>
+      <c r="O162" s="32" t="n"/>
+      <c r="P162" s="32" t="n"/>
       <c r="Q162" s="32" t="n"/>
       <c r="R162" s="23" t="inlineStr">
         <is>
@@ -17634,8 +17504,12 @@
         </is>
       </c>
       <c r="N163" s="2" t="n"/>
-      <c r="O163" s="32" t="n"/>
-      <c r="P163" s="32" t="n"/>
+      <c r="O163" s="32" t="n">
+        <v>-11.9</v>
+      </c>
+      <c r="P163" s="32" t="n">
+        <v>10.3</v>
+      </c>
       <c r="Q163" s="32" t="n"/>
       <c r="R163" s="23" t="inlineStr">
         <is>
@@ -18384,12 +18258,8 @@
           <t>⚡</t>
         </is>
       </c>
-      <c r="O170" s="32" t="n">
-        <v>-2.4</v>
-      </c>
-      <c r="P170" s="32" t="n">
-        <v>2.7</v>
-      </c>
+      <c r="O170" s="32" t="n"/>
+      <c r="P170" s="32" t="n"/>
       <c r="Q170" s="32" t="n"/>
       <c r="R170" s="23" t="inlineStr">
         <is>
@@ -18495,10 +18365,10 @@
       </c>
       <c r="N171" s="2" t="n"/>
       <c r="O171" s="32" t="n">
+        <v>-16</v>
+      </c>
+      <c r="P171" s="32" t="n">
         <v>-5.4</v>
-      </c>
-      <c r="P171" s="32" t="n">
-        <v>-3.2</v>
       </c>
       <c r="Q171" s="32" t="n"/>
       <c r="R171" s="23" t="inlineStr">
@@ -18711,10 +18581,10 @@
       </c>
       <c r="N173" s="2" t="n"/>
       <c r="O173" s="32" t="n">
-        <v>-5.6</v>
+        <v>2.7</v>
       </c>
       <c r="P173" s="32" t="n">
-        <v>15.7</v>
+        <v>19.4</v>
       </c>
       <c r="Q173" s="32" t="n"/>
       <c r="R173" s="23" t="inlineStr">
@@ -19033,10 +18903,10 @@
       </c>
       <c r="N176" s="2" t="n"/>
       <c r="O176" s="32" t="n">
-        <v>10.9</v>
+        <v>6.5</v>
       </c>
       <c r="P176" s="32" t="n">
-        <v>13.8</v>
+        <v>16.1</v>
       </c>
       <c r="Q176" s="32" t="n"/>
       <c r="R176" s="23" t="inlineStr">
@@ -19135,10 +19005,10 @@
       </c>
       <c r="N177" s="2" t="n"/>
       <c r="O177" s="32" t="n">
-        <v>-16</v>
+        <v>-6.6</v>
       </c>
       <c r="P177" s="32" t="n">
-        <v>-7</v>
+        <v>2.2</v>
       </c>
       <c r="Q177" s="32" t="n"/>
       <c r="R177" s="23" t="inlineStr">
@@ -22652,10 +22522,10 @@
       </c>
       <c r="N213" s="2" t="n"/>
       <c r="O213" s="32" t="n">
-        <v>-6.5</v>
+        <v>-14.9</v>
       </c>
       <c r="P213" s="32" t="n">
-        <v>4.7</v>
+        <v>9</v>
       </c>
       <c r="Q213" s="32" t="n"/>
       <c r="R213" s="23" t="inlineStr">
@@ -27750,10 +27620,10 @@
       </c>
       <c r="N265" s="2" t="n"/>
       <c r="O265" s="32" t="n">
-        <v>-53.5</v>
+        <v>-66.2</v>
       </c>
       <c r="P265" s="32" t="n">
-        <v>-48.9</v>
+        <v>-62.3</v>
       </c>
       <c r="Q265" s="32" t="n"/>
       <c r="R265" s="23" t="inlineStr">
@@ -30590,10 +30460,10 @@
       </c>
       <c r="N295" s="2" t="n"/>
       <c r="O295" s="32" t="n">
-        <v>-17.5</v>
+        <v>-11.2</v>
       </c>
       <c r="P295" s="32" t="n">
-        <v>-7.9</v>
+        <v>2.4</v>
       </c>
       <c r="Q295" s="32" t="n"/>
       <c r="R295" s="23" t="inlineStr">
@@ -30695,8 +30565,12 @@
         </is>
       </c>
       <c r="N296" s="2" t="n"/>
-      <c r="O296" s="32" t="n"/>
-      <c r="P296" s="32" t="n"/>
+      <c r="O296" s="32" t="n">
+        <v>-15.9</v>
+      </c>
+      <c r="P296" s="32" t="n">
+        <v>-6.4</v>
+      </c>
       <c r="Q296" s="32" t="n"/>
       <c r="R296" s="23" t="inlineStr">
         <is>
@@ -31575,12 +31449,8 @@
         </is>
       </c>
       <c r="N305" s="2" t="n"/>
-      <c r="O305" s="32" t="n">
-        <v>-12.4</v>
-      </c>
-      <c r="P305" s="32" t="n">
-        <v>-0.5</v>
-      </c>
+      <c r="O305" s="32" t="n"/>
+      <c r="P305" s="32" t="n"/>
       <c r="Q305" s="32" t="n"/>
       <c r="R305" s="23" t="inlineStr">
         <is>

--- a/气象/For_Python_站点信息和记录.xlsx
+++ b/气象/For_Python_站点信息和记录.xlsx
@@ -806,8 +806,8 @@
     <col width="18.59765625" customWidth="1" style="8" min="25" max="25"/>
     <col width="12.59765625" customWidth="1" style="5" min="26" max="30"/>
     <col width="12.59765625" customWidth="1" style="8" min="31" max="32"/>
-    <col width="12.59765625" customWidth="1" style="5" min="33" max="386"/>
-    <col width="12.59765625" customWidth="1" style="5" min="387" max="16384"/>
+    <col width="12.59765625" customWidth="1" style="5" min="33" max="391"/>
+    <col width="12.59765625" customWidth="1" style="5" min="392" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="27.75" customFormat="1" customHeight="1" s="11">
@@ -1030,13 +1030,13 @@
         </is>
       </c>
       <c r="O2" s="32" t="n">
-        <v>-4.7</v>
+        <v>-8.1</v>
       </c>
       <c r="P2" s="32" t="n">
-        <v>13.3</v>
+        <v>13.9</v>
       </c>
       <c r="Q2" s="32" t="n">
-        <v>0.89</v>
+        <v>3.68</v>
       </c>
       <c r="R2" s="23" t="inlineStr">
         <is>
@@ -1136,10 +1136,10 @@
         </is>
       </c>
       <c r="O3" s="32" t="n">
-        <v>-6.9</v>
+        <v>-5.6</v>
       </c>
       <c r="P3" s="32" t="n">
-        <v>16</v>
+        <v>13.8</v>
       </c>
       <c r="Q3" s="32" t="n"/>
       <c r="R3" s="23" t="n"/>
@@ -1240,10 +1240,10 @@
         </is>
       </c>
       <c r="O4" s="32" t="n">
-        <v>-5.4</v>
+        <v>-8.1</v>
       </c>
       <c r="P4" s="32" t="n">
-        <v>13.6</v>
+        <v>12.4</v>
       </c>
       <c r="Q4" s="32" t="n"/>
       <c r="R4" s="23" t="n"/>
@@ -1432,10 +1432,10 @@
         </is>
       </c>
       <c r="O6" s="32" t="n">
-        <v>-7.8</v>
+        <v>-14.9</v>
       </c>
       <c r="P6" s="32" t="n">
-        <v>3.8</v>
+        <v>9.5</v>
       </c>
       <c r="Q6" s="32" t="n"/>
       <c r="R6" s="23" t="n"/>
@@ -1532,10 +1532,10 @@
         </is>
       </c>
       <c r="O7" s="32" t="n">
-        <v>-9.800000000000001</v>
+        <v>-9.699999999999999</v>
       </c>
       <c r="P7" s="32" t="n">
-        <v>4.6</v>
+        <v>6.6</v>
       </c>
       <c r="Q7" s="32" t="n"/>
       <c r="R7" s="23" t="n"/>
@@ -1640,13 +1640,13 @@
       </c>
       <c r="N8" s="2" t="n"/>
       <c r="O8" s="32" t="n">
-        <v>-3.5</v>
+        <v>-8.9</v>
       </c>
       <c r="P8" s="32" t="n">
-        <v>16.5</v>
+        <v>15.7</v>
       </c>
       <c r="Q8" s="32" t="n">
-        <v>5.1</v>
+        <v>2.74</v>
       </c>
       <c r="R8" s="23" t="inlineStr">
         <is>
@@ -1752,13 +1752,13 @@
       </c>
       <c r="N9" s="2" t="n"/>
       <c r="O9" s="32" t="n">
-        <v>-6.3</v>
+        <v>-5.9</v>
       </c>
       <c r="P9" s="32" t="n">
-        <v>11.4</v>
+        <v>12.5</v>
       </c>
       <c r="Q9" s="32" t="n">
-        <v>-0.3</v>
+        <v>3</v>
       </c>
       <c r="R9" s="23" t="inlineStr">
         <is>
@@ -1872,13 +1872,13 @@
         </is>
       </c>
       <c r="O10" s="32" t="n">
-        <v>-6.1</v>
+        <v>-9.5</v>
       </c>
       <c r="P10" s="32" t="n">
-        <v>11.6</v>
+        <v>10.4</v>
       </c>
       <c r="Q10" s="32" t="n">
-        <v>-0.52</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="R10" s="23" t="inlineStr">
         <is>
@@ -1988,13 +1988,13 @@
         </is>
       </c>
       <c r="O11" s="32" t="n">
-        <v>-11.2</v>
+        <v>-9</v>
       </c>
       <c r="P11" s="32" t="n">
-        <v>5.9</v>
+        <v>9.1</v>
       </c>
       <c r="Q11" s="32" t="n">
-        <v>-4.66</v>
+        <v>-0.01</v>
       </c>
       <c r="R11" s="23" t="inlineStr">
         <is>
@@ -2100,13 +2100,13 @@
       </c>
       <c r="N12" s="2" t="n"/>
       <c r="O12" s="32" t="n">
-        <v>-7.8</v>
+        <v>-8.6</v>
       </c>
       <c r="P12" s="32" t="n">
-        <v>4.9</v>
+        <v>11.2</v>
       </c>
       <c r="Q12" s="32" t="n">
-        <v>-1.95</v>
+        <v>1.29</v>
       </c>
       <c r="R12" s="23" t="inlineStr">
         <is>
@@ -2216,13 +2216,13 @@
         </is>
       </c>
       <c r="O13" s="32" t="n">
-        <v>-10</v>
+        <v>-8.5</v>
       </c>
       <c r="P13" s="32" t="n">
-        <v>4.1</v>
+        <v>7.7</v>
       </c>
       <c r="Q13" s="32" t="n">
-        <v>-4.45</v>
+        <v>-0.24</v>
       </c>
       <c r="R13" s="23" t="inlineStr">
         <is>
@@ -2328,13 +2328,13 @@
       </c>
       <c r="N14" s="2" t="n"/>
       <c r="O14" s="32" t="n">
-        <v>-2</v>
+        <v>-7.5</v>
       </c>
       <c r="P14" s="32" t="n">
-        <v>17.2</v>
+        <v>12.5</v>
       </c>
       <c r="Q14" s="32" t="n">
-        <v>8.539999999999999</v>
+        <v>2.5</v>
       </c>
       <c r="R14" s="23" t="inlineStr">
         <is>
@@ -2713,8 +2713,12 @@
         </is>
       </c>
       <c r="N18" s="2" t="n"/>
-      <c r="O18" s="32" t="n"/>
-      <c r="P18" s="32" t="n"/>
+      <c r="O18" s="32" t="n">
+        <v>-14.1</v>
+      </c>
+      <c r="P18" s="32" t="n">
+        <v>11.8</v>
+      </c>
       <c r="Q18" s="32" t="n"/>
       <c r="R18" s="23" t="n"/>
       <c r="S18" s="37" t="n"/>
@@ -8052,13 +8056,13 @@
         </is>
       </c>
       <c r="O77" s="32" t="n">
-        <v>-4.8</v>
+        <v>-3.7</v>
       </c>
       <c r="P77" s="32" t="n">
-        <v>4.9</v>
+        <v>3.6</v>
       </c>
       <c r="Q77" s="32" t="n">
-        <v>-0.3</v>
+        <v>-2.69</v>
       </c>
       <c r="R77" s="23" t="inlineStr">
         <is>
@@ -8478,10 +8482,10 @@
         </is>
       </c>
       <c r="O81" s="32" t="n">
-        <v>-9.699999999999999</v>
+        <v>-3.7</v>
       </c>
       <c r="P81" s="32" t="n">
-        <v>10.2</v>
+        <v>0.8</v>
       </c>
       <c r="Q81" s="32" t="n"/>
       <c r="R81" s="23" t="inlineStr">
@@ -8597,13 +8601,13 @@
         </is>
       </c>
       <c r="O82" s="32" t="n">
-        <v>-9.1</v>
+        <v>-4</v>
       </c>
       <c r="P82" s="32" t="n">
-        <v>9.6</v>
+        <v>2.8</v>
       </c>
       <c r="Q82" s="32" t="n">
-        <v>0.64</v>
+        <v>-1.57</v>
       </c>
       <c r="R82" s="23" t="inlineStr">
         <is>
@@ -8815,13 +8819,13 @@
         </is>
       </c>
       <c r="O84" s="32" t="n">
-        <v>-4.3</v>
+        <v>-7.6</v>
       </c>
       <c r="P84" s="32" t="n">
-        <v>5.9</v>
+        <v>4.7</v>
       </c>
       <c r="Q84" s="32" t="n">
-        <v>-1.55</v>
+        <v>-1.4</v>
       </c>
       <c r="R84" s="23" t="inlineStr">
         <is>
@@ -9033,13 +9037,13 @@
       </c>
       <c r="N86" s="2" t="n"/>
       <c r="O86" s="32" t="n">
-        <v>-5.2</v>
+        <v>-2</v>
       </c>
       <c r="P86" s="32" t="n">
-        <v>5.5</v>
+        <v>14.7</v>
       </c>
       <c r="Q86" s="32" t="n">
-        <v>-1.71</v>
+        <v>5.81</v>
       </c>
       <c r="R86" s="23" t="inlineStr">
         <is>
@@ -9259,13 +9263,13 @@
       </c>
       <c r="N88" s="2" t="n"/>
       <c r="O88" s="32" t="n">
-        <v>-13.1</v>
+        <v>-7</v>
       </c>
       <c r="P88" s="32" t="n">
-        <v>1.8</v>
+        <v>10.4</v>
       </c>
       <c r="Q88" s="32" t="n">
-        <v>-6.11</v>
+        <v>1.11</v>
       </c>
       <c r="R88" s="23" t="inlineStr">
         <is>
@@ -9669,13 +9673,13 @@
       </c>
       <c r="N92" s="2" t="n"/>
       <c r="O92" s="32" t="n">
-        <v>4.6</v>
+        <v>-1.8</v>
       </c>
       <c r="P92" s="32" t="n">
-        <v>15.9</v>
+        <v>13.6</v>
       </c>
       <c r="Q92" s="32" t="n">
-        <v>8.77</v>
+        <v>5.35</v>
       </c>
       <c r="R92" s="23" t="inlineStr">
         <is>
@@ -9781,13 +9785,13 @@
       </c>
       <c r="N93" s="2" t="n"/>
       <c r="O93" s="32" t="n">
-        <v>8.5</v>
+        <v>1.9</v>
       </c>
       <c r="P93" s="32" t="n">
-        <v>21.4</v>
+        <v>16.4</v>
       </c>
       <c r="Q93" s="32" t="n">
-        <v>15.32</v>
+        <v>9.4</v>
       </c>
       <c r="R93" s="23" t="inlineStr">
         <is>
@@ -10011,13 +10015,13 @@
       </c>
       <c r="N95" s="2" t="n"/>
       <c r="O95" s="32" t="n">
-        <v>2.9</v>
+        <v>3.6</v>
       </c>
       <c r="P95" s="32" t="n">
-        <v>16.3</v>
+        <v>12.3</v>
       </c>
       <c r="Q95" s="32" t="n">
-        <v>9.890000000000001</v>
+        <v>7.75</v>
       </c>
       <c r="R95" s="23" t="inlineStr">
         <is>
@@ -10249,13 +10253,13 @@
       </c>
       <c r="N97" s="2" t="n"/>
       <c r="O97" s="32" t="n">
-        <v>2.7</v>
+        <v>3.9</v>
       </c>
       <c r="P97" s="32" t="n">
-        <v>13.2</v>
+        <v>10.6</v>
       </c>
       <c r="Q97" s="32" t="n">
-        <v>8.09</v>
+        <v>6.56</v>
       </c>
       <c r="R97" s="23" t="inlineStr">
         <is>
@@ -10369,10 +10373,10 @@
       </c>
       <c r="N98" s="2" t="n"/>
       <c r="O98" s="32" t="n">
-        <v>4.2</v>
+        <v>2.1</v>
       </c>
       <c r="P98" s="32" t="n">
-        <v>13.7</v>
+        <v>9.4</v>
       </c>
       <c r="Q98" s="32" t="n"/>
       <c r="R98" s="23" t="inlineStr">
@@ -10809,13 +10813,13 @@
       </c>
       <c r="N102" s="2" t="n"/>
       <c r="O102" s="32" t="n">
-        <v>-8.800000000000001</v>
+        <v>0.1</v>
       </c>
       <c r="P102" s="32" t="n">
-        <v>11.3</v>
+        <v>1.6</v>
       </c>
       <c r="Q102" s="32" t="n">
-        <v>1.48</v>
+        <v>0.54</v>
       </c>
       <c r="R102" s="23" t="inlineStr">
         <is>
@@ -11145,13 +11149,13 @@
         </is>
       </c>
       <c r="O105" s="32" t="n">
-        <v>-10.2</v>
+        <v>-5.6</v>
       </c>
       <c r="P105" s="32" t="n">
-        <v>10</v>
+        <v>0.2</v>
       </c>
       <c r="Q105" s="32" t="n">
-        <v>0.71</v>
+        <v>-2.4</v>
       </c>
       <c r="R105" s="23" t="inlineStr">
         <is>
@@ -11979,10 +11983,10 @@
       </c>
       <c r="N113" s="2" t="n"/>
       <c r="O113" s="32" t="n">
-        <v>-1.8</v>
+        <v>-1</v>
       </c>
       <c r="P113" s="32" t="n">
-        <v>9.699999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="Q113" s="32" t="n"/>
       <c r="R113" s="23" t="inlineStr">
@@ -12093,7 +12097,7 @@
         </is>
       </c>
       <c r="O114" s="32" t="n">
-        <v>-8</v>
+        <v>-2.8</v>
       </c>
       <c r="P114" s="32" t="n">
         <v>10</v>
@@ -12218,7 +12222,7 @@
         <v>-6.5</v>
       </c>
       <c r="P115" s="32" t="n">
-        <v>9.1</v>
+        <v>7.1</v>
       </c>
       <c r="Q115" s="32" t="n"/>
       <c r="R115" s="23" t="inlineStr">
@@ -12875,13 +12879,13 @@
       </c>
       <c r="N121" s="2" t="n"/>
       <c r="O121" s="32" t="n">
-        <v>4.7</v>
+        <v>6.4</v>
       </c>
       <c r="P121" s="32" t="n">
-        <v>14.8</v>
+        <v>13.2</v>
       </c>
       <c r="Q121" s="32" t="n">
-        <v>6.64</v>
+        <v>9.74</v>
       </c>
       <c r="R121" s="23" t="inlineStr">
         <is>
@@ -12999,10 +13003,10 @@
       </c>
       <c r="N122" s="2" t="n"/>
       <c r="O122" s="32" t="n">
-        <v>-2.4</v>
+        <v>-1.1</v>
       </c>
       <c r="P122" s="32" t="n">
-        <v>5.3</v>
+        <v>8.5</v>
       </c>
       <c r="Q122" s="32" t="n"/>
       <c r="R122" s="23" t="inlineStr">
@@ -13219,13 +13223,13 @@
       </c>
       <c r="N124" s="2" t="n"/>
       <c r="O124" s="32" t="n">
-        <v>5.9</v>
+        <v>-6.2</v>
       </c>
       <c r="P124" s="32" t="n">
-        <v>24.6</v>
+        <v>14.7</v>
       </c>
       <c r="Q124" s="32" t="n">
-        <v>16.81</v>
+        <v>4.9</v>
       </c>
       <c r="R124" s="23" t="inlineStr">
         <is>
@@ -13343,13 +13347,13 @@
       </c>
       <c r="N125" s="2" t="n"/>
       <c r="O125" s="32" t="n">
-        <v>12.7</v>
+        <v>4.3</v>
       </c>
       <c r="P125" s="32" t="n">
-        <v>26.1</v>
+        <v>21.9</v>
       </c>
       <c r="Q125" s="32" t="n">
-        <v>18.8</v>
+        <v>14.66</v>
       </c>
       <c r="R125" s="23" t="inlineStr">
         <is>
@@ -13447,10 +13451,10 @@
       </c>
       <c r="N126" s="2" t="n"/>
       <c r="O126" s="32" t="n">
-        <v>13.7</v>
+        <v>7.4</v>
       </c>
       <c r="P126" s="32" t="n">
-        <v>30</v>
+        <v>21.3</v>
       </c>
       <c r="Q126" s="32" t="n"/>
       <c r="R126" s="23" t="inlineStr">
@@ -13557,13 +13561,13 @@
       </c>
       <c r="N127" s="2" t="n"/>
       <c r="O127" s="32" t="n">
-        <v>9.9</v>
+        <v>2.4</v>
       </c>
       <c r="P127" s="32" t="n">
-        <v>30.4</v>
+        <v>16.7</v>
       </c>
       <c r="Q127" s="32" t="n">
-        <v>19.99</v>
+        <v>9.83</v>
       </c>
       <c r="R127" s="23" t="inlineStr">
         <is>
@@ -13677,10 +13681,10 @@
       </c>
       <c r="N128" s="2" t="n"/>
       <c r="O128" s="32" t="n">
-        <v>14.6</v>
+        <v>10.5</v>
       </c>
       <c r="P128" s="32" t="n">
-        <v>28.2</v>
+        <v>20.7</v>
       </c>
       <c r="Q128" s="32" t="n"/>
       <c r="R128" s="23" t="inlineStr">
@@ -13787,13 +13791,13 @@
       </c>
       <c r="N129" s="2" t="n"/>
       <c r="O129" s="32" t="n">
-        <v>6.9</v>
+        <v>0.1</v>
       </c>
       <c r="P129" s="32" t="n">
-        <v>27.4</v>
+        <v>18.7</v>
       </c>
       <c r="Q129" s="32" t="n">
-        <v>18.65</v>
+        <v>10.94</v>
       </c>
       <c r="R129" s="23" t="inlineStr">
         <is>
@@ -13907,13 +13911,13 @@
       </c>
       <c r="N130" s="2" t="n"/>
       <c r="O130" s="32" t="n">
-        <v>2.2</v>
+        <v>1.5</v>
       </c>
       <c r="P130" s="32" t="n">
-        <v>24.2</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Q130" s="32" t="n">
-        <v>12.6</v>
+        <v>4.29</v>
       </c>
       <c r="R130" s="23" t="inlineStr">
         <is>
@@ -14027,13 +14031,13 @@
       </c>
       <c r="N131" s="2" t="n"/>
       <c r="O131" s="32" t="n">
-        <v>17.9</v>
+        <v>9.5</v>
       </c>
       <c r="P131" s="32" t="n">
-        <v>28.9</v>
+        <v>19.5</v>
       </c>
       <c r="Q131" s="32" t="n">
-        <v>23.06</v>
+        <v>13.85</v>
       </c>
       <c r="R131" s="23" t="inlineStr">
         <is>
@@ -14146,10 +14150,10 @@
         <v>12.9</v>
       </c>
       <c r="P132" s="32" t="n">
-        <v>27.7</v>
+        <v>20.4</v>
       </c>
       <c r="Q132" s="32" t="n">
-        <v>21.82</v>
+        <v>15.89</v>
       </c>
       <c r="R132" s="23" t="inlineStr">
         <is>
@@ -14259,13 +14263,13 @@
       </c>
       <c r="N133" s="2" t="n"/>
       <c r="O133" s="32" t="n">
-        <v>13.7</v>
+        <v>11</v>
       </c>
       <c r="P133" s="32" t="n">
-        <v>27.8</v>
+        <v>18</v>
       </c>
       <c r="Q133" s="32" t="n">
-        <v>20.8</v>
+        <v>13.79</v>
       </c>
       <c r="R133" s="23" t="inlineStr">
         <is>
@@ -14481,13 +14485,13 @@
       </c>
       <c r="N135" s="2" t="n"/>
       <c r="O135" s="32" t="n">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="P135" s="32" t="n">
-        <v>28.5</v>
+        <v>26.2</v>
       </c>
       <c r="Q135" s="32" t="n">
-        <v>21.34</v>
+        <v>18.55</v>
       </c>
       <c r="R135" s="23" t="inlineStr">
         <is>
@@ -14597,13 +14601,13 @@
       </c>
       <c r="N136" s="2" t="n"/>
       <c r="O136" s="32" t="n">
-        <v>18.7</v>
+        <v>19.7</v>
       </c>
       <c r="P136" s="32" t="n">
-        <v>28.6</v>
+        <v>28</v>
       </c>
       <c r="Q136" s="32" t="n">
-        <v>23.17</v>
+        <v>23.18</v>
       </c>
       <c r="R136" s="23" t="inlineStr">
         <is>
@@ -14716,10 +14720,10 @@
         <v>16.3</v>
       </c>
       <c r="P137" s="32" t="n">
-        <v>28.5</v>
+        <v>22.5</v>
       </c>
       <c r="Q137" s="32" t="n">
-        <v>22.24</v>
+        <v>18.64</v>
       </c>
       <c r="R137" s="23" t="inlineStr">
         <is>
@@ -14829,10 +14833,10 @@
       </c>
       <c r="N138" s="2" t="n"/>
       <c r="O138" s="32" t="n">
-        <v>14.7</v>
+        <v>13.5</v>
       </c>
       <c r="P138" s="32" t="n">
-        <v>25.9</v>
+        <v>19.6</v>
       </c>
       <c r="Q138" s="32" t="n"/>
       <c r="R138" s="23" t="inlineStr">
@@ -14943,13 +14947,13 @@
       </c>
       <c r="N139" s="2" t="n"/>
       <c r="O139" s="32" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="P139" s="32" t="n">
-        <v>23.7</v>
+        <v>20.8</v>
       </c>
       <c r="Q139" s="32" t="n">
-        <v>19.19</v>
+        <v>16.26</v>
       </c>
       <c r="R139" s="23" t="inlineStr">
         <is>
@@ -15059,13 +15063,13 @@
       </c>
       <c r="N140" s="2" t="n"/>
       <c r="O140" s="32" t="n">
-        <v>16.9</v>
+        <v>15.4</v>
       </c>
       <c r="P140" s="32" t="n">
-        <v>23.1</v>
+        <v>25.5</v>
       </c>
       <c r="Q140" s="32" t="n">
-        <v>19.45</v>
+        <v>20.44</v>
       </c>
       <c r="R140" s="23" t="inlineStr">
         <is>
@@ -15277,13 +15281,13 @@
       </c>
       <c r="N142" s="2" t="n"/>
       <c r="O142" s="32" t="n">
-        <v>18.5</v>
+        <v>19.2</v>
       </c>
       <c r="P142" s="32" t="n">
-        <v>20.5</v>
+        <v>30.4</v>
       </c>
       <c r="Q142" s="32" t="n">
-        <v>19.65</v>
+        <v>23.58</v>
       </c>
       <c r="R142" s="23" t="inlineStr">
         <is>
@@ -15393,13 +15397,13 @@
       </c>
       <c r="N143" s="2" t="n"/>
       <c r="O143" s="32" t="n">
-        <v>19.8</v>
+        <v>22.5</v>
       </c>
       <c r="P143" s="32" t="n">
-        <v>29.7</v>
+        <v>29.1</v>
       </c>
       <c r="Q143" s="32" t="n">
-        <v>23.94</v>
+        <v>25.06</v>
       </c>
       <c r="R143" s="23" t="inlineStr">
         <is>
@@ -15709,13 +15713,13 @@
       </c>
       <c r="N146" s="2" t="n"/>
       <c r="O146" s="32" t="n">
-        <v>26.9</v>
+        <v>23.9</v>
       </c>
       <c r="P146" s="32" t="n">
-        <v>30.6</v>
+        <v>30.7</v>
       </c>
       <c r="Q146" s="32" t="n">
-        <v>27.94</v>
+        <v>27.11</v>
       </c>
       <c r="R146" s="23" t="inlineStr">
         <is>
@@ -15817,13 +15821,13 @@
       </c>
       <c r="N147" s="2" t="n"/>
       <c r="O147" s="32" t="n">
-        <v>19.7</v>
+        <v>23.2</v>
       </c>
       <c r="P147" s="32" t="n">
-        <v>28.2</v>
+        <v>29.8</v>
       </c>
       <c r="Q147" s="32" t="n">
-        <v>22.77</v>
+        <v>25.59</v>
       </c>
       <c r="R147" s="23" t="inlineStr">
         <is>
@@ -15933,10 +15937,10 @@
       </c>
       <c r="N148" s="2" t="n"/>
       <c r="O148" s="32" t="n">
-        <v>23.5</v>
+        <v>22.4</v>
       </c>
       <c r="P148" s="32" t="n">
-        <v>38.1</v>
+        <v>37.5</v>
       </c>
       <c r="Q148" s="32" t="n"/>
       <c r="R148" s="23" t="n"/>
@@ -16039,13 +16043,13 @@
       </c>
       <c r="N149" s="2" t="n"/>
       <c r="O149" s="32" t="n">
-        <v>12.8</v>
+        <v>12.6</v>
       </c>
       <c r="P149" s="32" t="n">
-        <v>27</v>
+        <v>26.1</v>
       </c>
       <c r="Q149" s="32" t="n">
-        <v>19.95</v>
+        <v>18.76</v>
       </c>
       <c r="R149" s="23" t="inlineStr">
         <is>
@@ -16155,13 +16159,13 @@
       </c>
       <c r="N150" s="2" t="n"/>
       <c r="O150" s="32" t="n">
-        <v>14.4</v>
+        <v>15.4</v>
       </c>
       <c r="P150" s="32" t="n">
-        <v>24.2</v>
+        <v>23</v>
       </c>
       <c r="Q150" s="32" t="n">
-        <v>18.73</v>
+        <v>17.93</v>
       </c>
       <c r="R150" s="23" t="inlineStr">
         <is>
@@ -16271,13 +16275,13 @@
       </c>
       <c r="N151" s="2" t="n"/>
       <c r="O151" s="32" t="n">
-        <v>18.7</v>
+        <v>18.2</v>
       </c>
       <c r="P151" s="32" t="n">
-        <v>31.8</v>
+        <v>25.5</v>
       </c>
       <c r="Q151" s="32" t="n">
-        <v>24.79</v>
+        <v>19.96</v>
       </c>
       <c r="R151" s="23" t="inlineStr">
         <is>
@@ -16477,13 +16481,13 @@
       </c>
       <c r="N153" s="2" t="n"/>
       <c r="O153" s="32" t="n">
-        <v>12.7</v>
+        <v>16.3</v>
       </c>
       <c r="P153" s="32" t="n">
-        <v>28.9</v>
+        <v>22.8</v>
       </c>
       <c r="Q153" s="32" t="n">
-        <v>20.55</v>
+        <v>19.79</v>
       </c>
       <c r="R153" s="23" t="inlineStr">
         <is>
@@ -16597,13 +16601,13 @@
       </c>
       <c r="N154" s="2" t="n"/>
       <c r="O154" s="32" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="P154" s="32" t="n">
-        <v>14.5</v>
+        <v>20</v>
       </c>
       <c r="Q154" s="32" t="n">
-        <v>9.960000000000001</v>
+        <v>11.45</v>
       </c>
       <c r="R154" s="23" t="inlineStr">
         <is>
@@ -16798,8 +16802,12 @@
         </is>
       </c>
       <c r="N156" s="2" t="n"/>
-      <c r="O156" s="32" t="n"/>
-      <c r="P156" s="32" t="n"/>
+      <c r="O156" s="32" t="n">
+        <v>-9.699999999999999</v>
+      </c>
+      <c r="P156" s="32" t="n">
+        <v>13.7</v>
+      </c>
       <c r="Q156" s="32" t="n"/>
       <c r="R156" s="23" t="n"/>
       <c r="S156" s="37" t="n"/>
@@ -16897,10 +16905,10 @@
       </c>
       <c r="N157" s="2" t="n"/>
       <c r="O157" s="32" t="n">
-        <v>15.4</v>
+        <v>14.8</v>
       </c>
       <c r="P157" s="32" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q157" s="32" t="n"/>
       <c r="R157" s="23" t="inlineStr">
@@ -17285,10 +17293,10 @@
       </c>
       <c r="N161" s="2" t="n"/>
       <c r="O161" s="32" t="n">
-        <v>6.1</v>
+        <v>8.4</v>
       </c>
       <c r="P161" s="32" t="n">
-        <v>30.1</v>
+        <v>18.5</v>
       </c>
       <c r="Q161" s="32" t="n"/>
       <c r="R161" s="23" t="inlineStr">
@@ -17398,8 +17406,12 @@
           <t>⚡</t>
         </is>
       </c>
-      <c r="O162" s="32" t="n"/>
-      <c r="P162" s="32" t="n"/>
+      <c r="O162" s="32" t="n">
+        <v>-4.7</v>
+      </c>
+      <c r="P162" s="32" t="n">
+        <v>3.3</v>
+      </c>
       <c r="Q162" s="32" t="n"/>
       <c r="R162" s="23" t="inlineStr">
         <is>
@@ -17504,12 +17516,8 @@
         </is>
       </c>
       <c r="N163" s="2" t="n"/>
-      <c r="O163" s="32" t="n">
-        <v>-11.9</v>
-      </c>
-      <c r="P163" s="32" t="n">
-        <v>10.3</v>
-      </c>
+      <c r="O163" s="32" t="n"/>
+      <c r="P163" s="32" t="n"/>
       <c r="Q163" s="32" t="n"/>
       <c r="R163" s="23" t="inlineStr">
         <is>
@@ -18258,8 +18266,12 @@
           <t>⚡</t>
         </is>
       </c>
-      <c r="O170" s="32" t="n"/>
-      <c r="P170" s="32" t="n"/>
+      <c r="O170" s="32" t="n">
+        <v>-19.1</v>
+      </c>
+      <c r="P170" s="32" t="n">
+        <v>2.2</v>
+      </c>
       <c r="Q170" s="32" t="n"/>
       <c r="R170" s="23" t="inlineStr">
         <is>
@@ -18365,10 +18377,10 @@
       </c>
       <c r="N171" s="2" t="n"/>
       <c r="O171" s="32" t="n">
-        <v>-16</v>
+        <v>-8.4</v>
       </c>
       <c r="P171" s="32" t="n">
-        <v>-5.4</v>
+        <v>-1.4</v>
       </c>
       <c r="Q171" s="32" t="n"/>
       <c r="R171" s="23" t="inlineStr">
@@ -18581,10 +18593,10 @@
       </c>
       <c r="N173" s="2" t="n"/>
       <c r="O173" s="32" t="n">
-        <v>2.7</v>
+        <v>-7.9</v>
       </c>
       <c r="P173" s="32" t="n">
-        <v>19.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Q173" s="32" t="n"/>
       <c r="R173" s="23" t="inlineStr">
@@ -18903,10 +18915,10 @@
       </c>
       <c r="N176" s="2" t="n"/>
       <c r="O176" s="32" t="n">
-        <v>6.5</v>
+        <v>8.6</v>
       </c>
       <c r="P176" s="32" t="n">
-        <v>16.1</v>
+        <v>17.7</v>
       </c>
       <c r="Q176" s="32" t="n"/>
       <c r="R176" s="23" t="inlineStr">
@@ -19005,10 +19017,10 @@
       </c>
       <c r="N177" s="2" t="n"/>
       <c r="O177" s="32" t="n">
-        <v>-6.6</v>
+        <v>-12.8</v>
       </c>
       <c r="P177" s="32" t="n">
-        <v>2.2</v>
+        <v>2.8</v>
       </c>
       <c r="Q177" s="32" t="n"/>
       <c r="R177" s="23" t="inlineStr">
@@ -22521,12 +22533,8 @@
         </is>
       </c>
       <c r="N213" s="2" t="n"/>
-      <c r="O213" s="32" t="n">
-        <v>-14.9</v>
-      </c>
-      <c r="P213" s="32" t="n">
-        <v>9</v>
-      </c>
+      <c r="O213" s="32" t="n"/>
+      <c r="P213" s="32" t="n"/>
       <c r="Q213" s="32" t="n"/>
       <c r="R213" s="23" t="inlineStr">
         <is>
@@ -24225,8 +24233,12 @@
         </is>
       </c>
       <c r="N230" s="2" t="n"/>
-      <c r="O230" s="32" t="n"/>
-      <c r="P230" s="32" t="n"/>
+      <c r="O230" s="32" t="n">
+        <v>-8.9</v>
+      </c>
+      <c r="P230" s="32" t="n">
+        <v>0.9</v>
+      </c>
       <c r="Q230" s="32" t="n"/>
       <c r="R230" s="23" t="inlineStr">
         <is>
@@ -27620,10 +27632,10 @@
       </c>
       <c r="N265" s="2" t="n"/>
       <c r="O265" s="32" t="n">
-        <v>-66.2</v>
+        <v>-62.8</v>
       </c>
       <c r="P265" s="32" t="n">
-        <v>-62.3</v>
+        <v>-52.7</v>
       </c>
       <c r="Q265" s="32" t="n"/>
       <c r="R265" s="23" t="inlineStr">
@@ -28929,8 +28941,12 @@
         </is>
       </c>
       <c r="N279" s="2" t="n"/>
-      <c r="O279" s="32" t="n"/>
-      <c r="P279" s="32" t="n"/>
+      <c r="O279" s="32" t="n">
+        <v>-10.9</v>
+      </c>
+      <c r="P279" s="32" t="n">
+        <v>16.7</v>
+      </c>
       <c r="Q279" s="32" t="n"/>
       <c r="R279" s="23" t="inlineStr">
         <is>
@@ -30460,10 +30476,10 @@
       </c>
       <c r="N295" s="2" t="n"/>
       <c r="O295" s="32" t="n">
-        <v>-11.2</v>
+        <v>-12.4</v>
       </c>
       <c r="P295" s="32" t="n">
-        <v>2.4</v>
+        <v>-0.6</v>
       </c>
       <c r="Q295" s="32" t="n"/>
       <c r="R295" s="23" t="inlineStr">
@@ -30565,12 +30581,8 @@
         </is>
       </c>
       <c r="N296" s="2" t="n"/>
-      <c r="O296" s="32" t="n">
-        <v>-15.9</v>
-      </c>
-      <c r="P296" s="32" t="n">
-        <v>-6.4</v>
-      </c>
+      <c r="O296" s="32" t="n"/>
+      <c r="P296" s="32" t="n"/>
       <c r="Q296" s="32" t="n"/>
       <c r="R296" s="23" t="inlineStr">
         <is>
@@ -31515,39 +31527,111 @@
       <c r="AH305" s="2" t="n"/>
     </row>
     <row r="306" ht="24" customHeight="1" s="49">
-      <c r="A306" s="2" t="n"/>
+      <c r="A306" s="2" t="n">
+        <v>305</v>
+      </c>
       <c r="B306" s="2" t="n"/>
-      <c r="C306" s="46" t="n"/>
+      <c r="C306" s="46" t="inlineStr">
+        <is>
+          <t>51701</t>
+        </is>
+      </c>
       <c r="D306" s="2" t="n"/>
-      <c r="E306" s="4" t="n"/>
+      <c r="E306" s="4" t="n">
+        <v>99999</v>
+      </c>
       <c r="F306" s="39" t="n"/>
-      <c r="G306" s="29" t="n"/>
-      <c r="H306" s="29" t="n"/>
-      <c r="I306" s="2" t="n"/>
-      <c r="J306" s="27" t="n"/>
-      <c r="K306" s="4" t="n"/>
+      <c r="G306" s="29" t="n">
+        <v>40.5122</v>
+      </c>
+      <c r="H306" s="29" t="n">
+        <v>75.3914</v>
+      </c>
+      <c r="I306" s="2" t="n">
+        <v>3470.2</v>
+      </c>
+      <c r="J306" s="27" t="n">
+        <v>12</v>
+      </c>
+      <c r="K306" s="31" t="inlineStr">
+        <is>
+          <t>🇨🇳</t>
+        </is>
+      </c>
       <c r="L306" s="2" t="n"/>
-      <c r="M306" s="14" t="n"/>
+      <c r="M306" s="14" t="inlineStr">
+        <is>
+          <t>吐尔尕特</t>
+        </is>
+      </c>
       <c r="N306" s="2" t="n"/>
-      <c r="O306" s="32" t="n"/>
-      <c r="P306" s="32" t="n"/>
+      <c r="O306" s="32" t="n">
+        <v>-10</v>
+      </c>
+      <c r="P306" s="32" t="n">
+        <v>2.6</v>
+      </c>
       <c r="Q306" s="32" t="n"/>
-      <c r="R306" s="23" t="n"/>
+      <c r="R306" s="23" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="S306" s="37" t="n"/>
-      <c r="T306" s="41" t="n"/>
-      <c r="U306" s="2" t="n"/>
-      <c r="V306" s="4" t="n"/>
-      <c r="W306" s="4" t="n"/>
-      <c r="X306" s="4" t="n"/>
+      <c r="T306" s="41" t="inlineStr">
+        <is>
+          <t>新疆喀什 天山</t>
+        </is>
+      </c>
+      <c r="U306" s="2" t="inlineStr">
+        <is>
+          <t>新疆</t>
+        </is>
+      </c>
+      <c r="V306" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="W306" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="X306" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="Y306" s="4" t="n"/>
-      <c r="Z306" s="2" t="n"/>
-      <c r="AA306" s="2" t="n"/>
+      <c r="Z306" s="2" t="inlineStr">
+        <is>
+          <t>喀什地区</t>
+        </is>
+      </c>
+      <c r="AA306" s="2" t="inlineStr">
+        <is>
+          <t>喀什市</t>
+        </is>
+      </c>
       <c r="AB306" s="2" t="n"/>
       <c r="AC306" s="2" t="n"/>
-      <c r="AD306" s="2" t="n"/>
-      <c r="AE306" s="4" t="n"/>
+      <c r="AD306" s="2" t="inlineStr">
+        <is>
+          <t>中国</t>
+        </is>
+      </c>
+      <c r="AE306" s="4" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
       <c r="AF306" s="4" t="n"/>
-      <c r="AG306" s="2" t="n"/>
+      <c r="AG306" s="2" t="inlineStr">
+        <is>
+          <t>天山</t>
+        </is>
+      </c>
       <c r="AH306" s="2" t="n"/>
     </row>
     <row r="307" ht="24" customHeight="1" s="49">

--- a/气象/For_Python_站点信息和记录.xlsx
+++ b/气象/For_Python_站点信息和记录.xlsx
@@ -22,7 +22,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy\ &quot;年&quot;\ m\ &quot;月&quot;\ d\ &quot;日&quot;"/>
   </numFmts>
-  <fonts count="17">
+  <fonts count="18">
     <font>
       <name val="等线"/>
       <charset val="134"/>
@@ -161,6 +161,14 @@
       <color theme="0"/>
       <sz val="11"/>
     </font>
+    <font>
+      <name val="Segoe UI"/>
+      <charset val="204"/>
+      <family val="3"/>
+      <b val="1"/>
+      <color rgb="FF00B0F0"/>
+      <sz val="11"/>
+    </font>
   </fonts>
   <fills count="8">
     <fill>
@@ -235,7 +243,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -383,6 +391,9 @@
     </xf>
     <xf numFmtId="0" fontId="16" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -806,8 +817,8 @@
     <col width="18.59765625" customWidth="1" style="8" min="25" max="25"/>
     <col width="12.59765625" customWidth="1" style="5" min="26" max="30"/>
     <col width="12.59765625" customWidth="1" style="8" min="31" max="32"/>
-    <col width="12.59765625" customWidth="1" style="5" min="33" max="391"/>
-    <col width="12.59765625" customWidth="1" style="5" min="392" max="16384"/>
+    <col width="12.59765625" customWidth="1" style="5" min="33" max="420"/>
+    <col width="12.59765625" customWidth="1" style="5" min="421" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="27.75" customFormat="1" customHeight="1" s="11">
@@ -982,7 +993,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="24" customHeight="1" s="49">
+    <row r="2" ht="24" customHeight="1" s="50">
       <c r="A2" s="2" t="n">
         <v>1</v>
       </c>
@@ -1030,13 +1041,13 @@
         </is>
       </c>
       <c r="O2" s="32" t="n">
-        <v>-8.1</v>
+        <v>0.2</v>
       </c>
       <c r="P2" s="32" t="n">
-        <v>13.9</v>
+        <v>24.7</v>
       </c>
       <c r="Q2" s="32" t="n">
-        <v>3.68</v>
+        <v>13.85</v>
       </c>
       <c r="R2" s="23" t="inlineStr">
         <is>
@@ -1096,7 +1107,7 @@
       </c>
       <c r="AH2" s="2" t="n"/>
     </row>
-    <row r="3" ht="24" customHeight="1" s="49">
+    <row r="3" ht="24" customHeight="1" s="50">
       <c r="A3" s="2" t="n">
         <v>2</v>
       </c>
@@ -1136,10 +1147,10 @@
         </is>
       </c>
       <c r="O3" s="32" t="n">
-        <v>-5.6</v>
+        <v>3</v>
       </c>
       <c r="P3" s="32" t="n">
-        <v>13.8</v>
+        <v>24.5</v>
       </c>
       <c r="Q3" s="32" t="n"/>
       <c r="R3" s="23" t="n"/>
@@ -1200,7 +1211,7 @@
       </c>
       <c r="AH3" s="2" t="n"/>
     </row>
-    <row r="4" ht="24" customHeight="1" s="49">
+    <row r="4" ht="24" customHeight="1" s="50">
       <c r="A4" s="2" t="n">
         <v>3</v>
       </c>
@@ -1240,10 +1251,10 @@
         </is>
       </c>
       <c r="O4" s="32" t="n">
-        <v>-8.1</v>
+        <v>-0.6</v>
       </c>
       <c r="P4" s="32" t="n">
-        <v>12.4</v>
+        <v>22.9</v>
       </c>
       <c r="Q4" s="32" t="n"/>
       <c r="R4" s="23" t="n"/>
@@ -1300,7 +1311,7 @@
       </c>
       <c r="AH4" s="2" t="n"/>
     </row>
-    <row r="5" ht="24" customHeight="1" s="49">
+    <row r="5" ht="24" customHeight="1" s="50">
       <c r="A5" s="2" t="n">
         <v>4</v>
       </c>
@@ -1392,7 +1403,7 @@
       </c>
       <c r="AH5" s="2" t="n"/>
     </row>
-    <row r="6" ht="24" customHeight="1" s="49">
+    <row r="6" ht="24" customHeight="1" s="50">
       <c r="A6" s="2" t="n">
         <v>5</v>
       </c>
@@ -1432,10 +1443,10 @@
         </is>
       </c>
       <c r="O6" s="32" t="n">
-        <v>-14.9</v>
+        <v>-5</v>
       </c>
       <c r="P6" s="32" t="n">
-        <v>9.5</v>
+        <v>14.4</v>
       </c>
       <c r="Q6" s="32" t="n"/>
       <c r="R6" s="23" t="n"/>
@@ -1492,7 +1503,7 @@
       </c>
       <c r="AH6" s="2" t="n"/>
     </row>
-    <row r="7" ht="24" customHeight="1" s="49">
+    <row r="7" ht="24" customHeight="1" s="50">
       <c r="A7" s="2" t="n">
         <v>6</v>
       </c>
@@ -1532,10 +1543,10 @@
         </is>
       </c>
       <c r="O7" s="32" t="n">
-        <v>-9.699999999999999</v>
+        <v>-4.7</v>
       </c>
       <c r="P7" s="32" t="n">
-        <v>6.6</v>
+        <v>18.1</v>
       </c>
       <c r="Q7" s="32" t="n"/>
       <c r="R7" s="23" t="n"/>
@@ -1592,13 +1603,13 @@
       </c>
       <c r="AH7" s="2" t="n"/>
     </row>
-    <row r="8" ht="24" customHeight="1" s="49">
+    <row r="8" ht="24" customHeight="1" s="50">
       <c r="A8" s="2" t="n">
         <v>7</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>ogimet</t>
+          <t>rp5</t>
         </is>
       </c>
       <c r="C8" s="46" t="n">
@@ -1640,13 +1651,13 @@
       </c>
       <c r="N8" s="2" t="n"/>
       <c r="O8" s="32" t="n">
-        <v>-8.9</v>
+        <v>-0.3</v>
       </c>
       <c r="P8" s="32" t="n">
-        <v>15.7</v>
+        <v>18.6</v>
       </c>
       <c r="Q8" s="32" t="n">
-        <v>2.74</v>
+        <v>9.59</v>
       </c>
       <c r="R8" s="23" t="inlineStr">
         <is>
@@ -1706,13 +1717,13 @@
       </c>
       <c r="AH8" s="2" t="n"/>
     </row>
-    <row r="9" ht="24" customHeight="1" s="49">
+    <row r="9" ht="24" customHeight="1" s="50">
       <c r="A9" s="2" t="n">
         <v>8</v>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>ogimet</t>
+          <t>rp5</t>
         </is>
       </c>
       <c r="C9" s="46" t="n">
@@ -1752,13 +1763,13 @@
       </c>
       <c r="N9" s="2" t="n"/>
       <c r="O9" s="32" t="n">
-        <v>-5.9</v>
+        <v>2.8</v>
       </c>
       <c r="P9" s="32" t="n">
-        <v>12.5</v>
+        <v>22.3</v>
       </c>
       <c r="Q9" s="32" t="n">
-        <v>3</v>
+        <v>13.1</v>
       </c>
       <c r="R9" s="23" t="inlineStr">
         <is>
@@ -1822,13 +1833,13 @@
       </c>
       <c r="AH9" s="2" t="n"/>
     </row>
-    <row r="10" ht="24" customHeight="1" s="49">
+    <row r="10" ht="24" customHeight="1" s="50">
       <c r="A10" s="2" t="n">
         <v>9</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>ogimet</t>
+          <t>rp5</t>
         </is>
       </c>
       <c r="C10" s="46" t="n">
@@ -1872,13 +1883,13 @@
         </is>
       </c>
       <c r="O10" s="32" t="n">
-        <v>-9.5</v>
+        <v>-2.9</v>
       </c>
       <c r="P10" s="32" t="n">
-        <v>10.4</v>
+        <v>21</v>
       </c>
       <c r="Q10" s="32" t="n">
-        <v>0.6899999999999999</v>
+        <v>10.36</v>
       </c>
       <c r="R10" s="23" t="inlineStr">
         <is>
@@ -1938,13 +1949,13 @@
       </c>
       <c r="AH10" s="2" t="n"/>
     </row>
-    <row r="11" ht="24" customHeight="1" s="49">
+    <row r="11" ht="24" customHeight="1" s="50">
       <c r="A11" s="2" t="n">
         <v>10</v>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>ogimet</t>
+          <t>rp5</t>
         </is>
       </c>
       <c r="C11" s="46" t="n">
@@ -1988,13 +1999,13 @@
         </is>
       </c>
       <c r="O11" s="32" t="n">
-        <v>-9</v>
+        <v>-5.1</v>
       </c>
       <c r="P11" s="32" t="n">
-        <v>9.1</v>
+        <v>15.9</v>
       </c>
       <c r="Q11" s="32" t="n">
-        <v>-0.01</v>
+        <v>6.58</v>
       </c>
       <c r="R11" s="23" t="inlineStr">
         <is>
@@ -2054,13 +2065,13 @@
       </c>
       <c r="AH11" s="2" t="n"/>
     </row>
-    <row r="12" ht="24" customHeight="1" s="49">
+    <row r="12" ht="24" customHeight="1" s="50">
       <c r="A12" s="2" t="n">
         <v>11</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>ogimet</t>
+          <t>rp5</t>
         </is>
       </c>
       <c r="C12" s="46" t="n">
@@ -2100,13 +2111,13 @@
       </c>
       <c r="N12" s="2" t="n"/>
       <c r="O12" s="32" t="n">
-        <v>-8.6</v>
+        <v>-3.1</v>
       </c>
       <c r="P12" s="32" t="n">
-        <v>11.2</v>
+        <v>18.8</v>
       </c>
       <c r="Q12" s="32" t="n">
-        <v>1.29</v>
+        <v>8.34</v>
       </c>
       <c r="R12" s="23" t="inlineStr">
         <is>
@@ -2166,13 +2177,13 @@
       </c>
       <c r="AH12" s="2" t="n"/>
     </row>
-    <row r="13" ht="24" customHeight="1" s="49">
+    <row r="13" ht="24" customHeight="1" s="50">
       <c r="A13" s="2" t="n">
         <v>12</v>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>ogimet</t>
+          <t>rp5</t>
         </is>
       </c>
       <c r="C13" s="46" t="n">
@@ -2216,13 +2227,13 @@
         </is>
       </c>
       <c r="O13" s="32" t="n">
-        <v>-8.5</v>
+        <v>-4.7</v>
       </c>
       <c r="P13" s="32" t="n">
-        <v>7.7</v>
+        <v>17.7</v>
       </c>
       <c r="Q13" s="32" t="n">
-        <v>-0.24</v>
+        <v>6.75</v>
       </c>
       <c r="R13" s="23" t="inlineStr">
         <is>
@@ -2282,13 +2293,13 @@
       </c>
       <c r="AH13" s="2" t="n"/>
     </row>
-    <row r="14" ht="24" customHeight="1" s="49">
+    <row r="14" ht="24" customHeight="1" s="50">
       <c r="A14" s="2" t="n">
         <v>13</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>ogimet</t>
+          <t>rp5</t>
         </is>
       </c>
       <c r="C14" s="46" t="n">
@@ -2328,13 +2339,13 @@
       </c>
       <c r="N14" s="2" t="n"/>
       <c r="O14" s="32" t="n">
-        <v>-7.5</v>
+        <v>0.4</v>
       </c>
       <c r="P14" s="32" t="n">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="Q14" s="32" t="n">
-        <v>2.5</v>
+        <v>7.98</v>
       </c>
       <c r="R14" s="23" t="inlineStr">
         <is>
@@ -2398,7 +2409,7 @@
       </c>
       <c r="AH14" s="2" t="n"/>
     </row>
-    <row r="15" ht="24" customHeight="1" s="49">
+    <row r="15" ht="24" customHeight="1" s="50">
       <c r="A15" s="2" t="n">
         <v>14</v>
       </c>
@@ -2433,8 +2444,12 @@
         </is>
       </c>
       <c r="N15" s="2" t="n"/>
-      <c r="O15" s="32" t="n"/>
-      <c r="P15" s="32" t="n"/>
+      <c r="O15" s="32" t="n">
+        <v>-5.4</v>
+      </c>
+      <c r="P15" s="32" t="n">
+        <v>11.3</v>
+      </c>
       <c r="Q15" s="32" t="n"/>
       <c r="R15" s="23" t="n"/>
       <c r="S15" s="37" t="n"/>
@@ -2486,7 +2501,7 @@
       </c>
       <c r="AH15" s="2" t="n"/>
     </row>
-    <row r="16" ht="24" customHeight="1" s="49">
+    <row r="16" ht="24" customHeight="1" s="50">
       <c r="A16" s="2" t="n">
         <v>15</v>
       </c>
@@ -2586,7 +2601,7 @@
       </c>
       <c r="AH16" s="2" t="n"/>
     </row>
-    <row r="17" ht="24" customHeight="1" s="49">
+    <row r="17" ht="24" customHeight="1" s="50">
       <c r="A17" s="2" t="n">
         <v>16</v>
       </c>
@@ -2678,7 +2693,7 @@
       </c>
       <c r="AH17" s="2" t="n"/>
     </row>
-    <row r="18" ht="24" customHeight="1" s="49">
+    <row r="18" ht="24" customHeight="1" s="50">
       <c r="A18" s="2" t="n">
         <v>17</v>
       </c>
@@ -2714,10 +2729,10 @@
       </c>
       <c r="N18" s="2" t="n"/>
       <c r="O18" s="32" t="n">
-        <v>-14.1</v>
+        <v>-7.3</v>
       </c>
       <c r="P18" s="32" t="n">
-        <v>11.8</v>
+        <v>16.2</v>
       </c>
       <c r="Q18" s="32" t="n"/>
       <c r="R18" s="23" t="n"/>
@@ -2770,7 +2785,7 @@
       </c>
       <c r="AH18" s="2" t="n"/>
     </row>
-    <row r="19" ht="24" customHeight="1" s="49">
+    <row r="19" ht="24" customHeight="1" s="50">
       <c r="A19" s="2" t="n">
         <v>18</v>
       </c>
@@ -2870,7 +2885,7 @@
       </c>
       <c r="AH19" s="2" t="n"/>
     </row>
-    <row r="20" ht="24" customHeight="1" s="49">
+    <row r="20" ht="24" customHeight="1" s="50">
       <c r="A20" s="2" t="n">
         <v>19</v>
       </c>
@@ -2970,7 +2985,7 @@
       </c>
       <c r="AH20" s="2" t="n"/>
     </row>
-    <row r="21" ht="24" customHeight="1" s="49">
+    <row r="21" ht="24" customHeight="1" s="50">
       <c r="A21" s="2" t="n">
         <v>20</v>
       </c>
@@ -3058,7 +3073,7 @@
       </c>
       <c r="AH21" s="2" t="n"/>
     </row>
-    <row r="22" ht="24" customHeight="1" s="49">
+    <row r="22" ht="24" customHeight="1" s="50">
       <c r="A22" s="2" t="n">
         <v>21</v>
       </c>
@@ -3146,7 +3161,7 @@
       </c>
       <c r="AH22" s="2" t="n"/>
     </row>
-    <row r="23" ht="24" customHeight="1" s="49">
+    <row r="23" ht="24" customHeight="1" s="50">
       <c r="A23" s="2" t="n">
         <v>22</v>
       </c>
@@ -3234,7 +3249,7 @@
       </c>
       <c r="AH23" s="2" t="n"/>
     </row>
-    <row r="24" ht="24" customHeight="1" s="49">
+    <row r="24" ht="24" customHeight="1" s="50">
       <c r="A24" s="2" t="n">
         <v>23</v>
       </c>
@@ -3334,7 +3349,7 @@
       </c>
       <c r="AH24" s="2" t="n"/>
     </row>
-    <row r="25" ht="24" customHeight="1" s="49">
+    <row r="25" ht="24" customHeight="1" s="50">
       <c r="A25" s="2" t="n">
         <v>24</v>
       </c>
@@ -3422,7 +3437,7 @@
       </c>
       <c r="AH25" s="2" t="n"/>
     </row>
-    <row r="26" ht="24" customHeight="1" s="49">
+    <row r="26" ht="24" customHeight="1" s="50">
       <c r="A26" s="2" t="n">
         <v>25</v>
       </c>
@@ -3510,7 +3525,7 @@
       </c>
       <c r="AH26" s="2" t="n"/>
     </row>
-    <row r="27" ht="24" customHeight="1" s="49">
+    <row r="27" ht="24" customHeight="1" s="50">
       <c r="A27" s="2" t="n">
         <v>26</v>
       </c>
@@ -3614,7 +3629,7 @@
       </c>
       <c r="AH27" s="2" t="n"/>
     </row>
-    <row r="28" ht="24" customHeight="1" s="49">
+    <row r="28" ht="24" customHeight="1" s="50">
       <c r="A28" s="2" t="n">
         <v>27</v>
       </c>
@@ -3698,7 +3713,7 @@
       <c r="AG28" s="2" t="n"/>
       <c r="AH28" s="2" t="n"/>
     </row>
-    <row r="29" ht="24" customHeight="1" s="49">
+    <row r="29" ht="24" customHeight="1" s="50">
       <c r="A29" s="2" t="n">
         <v>28</v>
       </c>
@@ -3786,7 +3801,7 @@
       </c>
       <c r="AH29" s="2" t="n"/>
     </row>
-    <row r="30" ht="24" customHeight="1" s="49">
+    <row r="30" ht="24" customHeight="1" s="50">
       <c r="A30" s="2" t="n">
         <v>29</v>
       </c>
@@ -3874,7 +3889,7 @@
       </c>
       <c r="AH30" s="2" t="n"/>
     </row>
-    <row r="31" ht="24" customHeight="1" s="49">
+    <row r="31" ht="24" customHeight="1" s="50">
       <c r="A31" s="2" t="n">
         <v>30</v>
       </c>
@@ -3962,7 +3977,7 @@
       </c>
       <c r="AH31" s="2" t="n"/>
     </row>
-    <row r="32" ht="24" customHeight="1" s="49">
+    <row r="32" ht="24" customHeight="1" s="50">
       <c r="A32" s="2" t="n">
         <v>31</v>
       </c>
@@ -4062,7 +4077,7 @@
       </c>
       <c r="AH32" s="2" t="n"/>
     </row>
-    <row r="33" ht="24" customHeight="1" s="49">
+    <row r="33" ht="24" customHeight="1" s="50">
       <c r="A33" s="2" t="n">
         <v>32</v>
       </c>
@@ -4162,7 +4177,7 @@
       <c r="AG33" s="2" t="n"/>
       <c r="AH33" s="2" t="n"/>
     </row>
-    <row r="34" ht="24" customHeight="1" s="49">
+    <row r="34" ht="24" customHeight="1" s="50">
       <c r="A34" s="2" t="n">
         <v>33</v>
       </c>
@@ -4246,7 +4261,7 @@
       <c r="AG34" s="2" t="n"/>
       <c r="AH34" s="2" t="n"/>
     </row>
-    <row r="35" ht="24" customHeight="1" s="49">
+    <row r="35" ht="24" customHeight="1" s="50">
       <c r="A35" s="2" t="n">
         <v>34</v>
       </c>
@@ -4334,7 +4349,7 @@
       </c>
       <c r="AH35" s="2" t="n"/>
     </row>
-    <row r="36" ht="24" customHeight="1" s="49">
+    <row r="36" ht="24" customHeight="1" s="50">
       <c r="A36" s="2" t="n">
         <v>35</v>
       </c>
@@ -4422,7 +4437,7 @@
       </c>
       <c r="AH36" s="2" t="n"/>
     </row>
-    <row r="37" ht="24" customHeight="1" s="49">
+    <row r="37" ht="24" customHeight="1" s="50">
       <c r="A37" s="2" t="n">
         <v>36</v>
       </c>
@@ -4464,7 +4479,7 @@
       <c r="S37" s="37" t="n"/>
       <c r="T37" s="41" t="inlineStr">
         <is>
-          <t>蒙古最北站</t>
+          <t>蒙古最北站&lt;br&gt;库苏古尔湖</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4510,7 +4525,7 @@
       </c>
       <c r="AH37" s="2" t="n"/>
     </row>
-    <row r="38" ht="24" customHeight="1" s="49">
+    <row r="38" ht="24" customHeight="1" s="50">
       <c r="A38" s="2" t="n">
         <v>37</v>
       </c>
@@ -4598,7 +4613,7 @@
       </c>
       <c r="AH38" s="2" t="n"/>
     </row>
-    <row r="39" ht="24" customHeight="1" s="49">
+    <row r="39" ht="24" customHeight="1" s="50">
       <c r="A39" s="2" t="n">
         <v>38</v>
       </c>
@@ -4682,7 +4697,7 @@
       <c r="AG39" s="2" t="n"/>
       <c r="AH39" s="2" t="n"/>
     </row>
-    <row r="40" ht="24" customHeight="1" s="49">
+    <row r="40" ht="24" customHeight="1" s="50">
       <c r="A40" s="2" t="n">
         <v>39</v>
       </c>
@@ -4770,7 +4785,7 @@
       </c>
       <c r="AH40" s="2" t="n"/>
     </row>
-    <row r="41" ht="24" customHeight="1" s="49">
+    <row r="41" ht="24" customHeight="1" s="50">
       <c r="A41" s="2" t="n">
         <v>40</v>
       </c>
@@ -4854,7 +4869,7 @@
       <c r="AG41" s="2" t="n"/>
       <c r="AH41" s="2" t="n"/>
     </row>
-    <row r="42" ht="24" customHeight="1" s="49">
+    <row r="42" ht="24" customHeight="1" s="50">
       <c r="A42" s="2" t="n">
         <v>41</v>
       </c>
@@ -4942,7 +4957,7 @@
       </c>
       <c r="AH42" s="2" t="n"/>
     </row>
-    <row r="43" ht="24" customHeight="1" s="49">
+    <row r="43" ht="24" customHeight="1" s="50">
       <c r="A43" s="2" t="n">
         <v>42</v>
       </c>
@@ -5034,7 +5049,7 @@
       </c>
       <c r="AH43" s="2" t="n"/>
     </row>
-    <row r="44" ht="24" customHeight="1" s="49">
+    <row r="44" ht="24" customHeight="1" s="50">
       <c r="A44" s="2" t="n">
         <v>43</v>
       </c>
@@ -5122,7 +5137,7 @@
       </c>
       <c r="AH44" s="2" t="n"/>
     </row>
-    <row r="45" ht="24" customHeight="1" s="49">
+    <row r="45" ht="24" customHeight="1" s="50">
       <c r="A45" s="2" t="n">
         <v>44</v>
       </c>
@@ -5222,7 +5237,7 @@
       </c>
       <c r="AH45" s="2" t="n"/>
     </row>
-    <row r="46" ht="24" customHeight="1" s="49">
+    <row r="46" ht="24" customHeight="1" s="50">
       <c r="A46" s="2" t="n">
         <v>45</v>
       </c>
@@ -5310,7 +5325,7 @@
       </c>
       <c r="AH46" s="2" t="n"/>
     </row>
-    <row r="47" ht="24" customHeight="1" s="49">
+    <row r="47" ht="24" customHeight="1" s="50">
       <c r="A47" s="2" t="n">
         <v>46</v>
       </c>
@@ -5398,7 +5413,7 @@
       </c>
       <c r="AH47" s="2" t="n"/>
     </row>
-    <row r="48" ht="24" customHeight="1" s="49">
+    <row r="48" ht="24" customHeight="1" s="50">
       <c r="A48" s="2" t="n">
         <v>47</v>
       </c>
@@ -5498,7 +5513,7 @@
       </c>
       <c r="AH48" s="2" t="n"/>
     </row>
-    <row r="49" ht="24" customHeight="1" s="49">
+    <row r="49" ht="24" customHeight="1" s="50">
       <c r="A49" s="2" t="n">
         <v>48</v>
       </c>
@@ -5586,7 +5601,7 @@
       </c>
       <c r="AH49" s="2" t="n"/>
     </row>
-    <row r="50" ht="24" customHeight="1" s="49">
+    <row r="50" ht="24" customHeight="1" s="50">
       <c r="A50" s="2" t="n">
         <v>49</v>
       </c>
@@ -5670,7 +5685,7 @@
       <c r="AG50" s="2" t="n"/>
       <c r="AH50" s="2" t="n"/>
     </row>
-    <row r="51" ht="24" customHeight="1" s="49">
+    <row r="51" ht="24" customHeight="1" s="50">
       <c r="A51" s="2" t="n">
         <v>50</v>
       </c>
@@ -5754,7 +5769,7 @@
       <c r="AG51" s="2" t="n"/>
       <c r="AH51" s="2" t="n"/>
     </row>
-    <row r="52" ht="24" customHeight="1" s="49">
+    <row r="52" ht="24" customHeight="1" s="50">
       <c r="A52" s="2" t="n">
         <v>51</v>
       </c>
@@ -5842,7 +5857,7 @@
       </c>
       <c r="AH52" s="2" t="n"/>
     </row>
-    <row r="53" ht="24" customHeight="1" s="49">
+    <row r="53" ht="24" customHeight="1" s="50">
       <c r="A53" s="2" t="n">
         <v>52</v>
       </c>
@@ -5930,7 +5945,7 @@
       </c>
       <c r="AH53" s="2" t="n"/>
     </row>
-    <row r="54" ht="24" customHeight="1" s="49">
+    <row r="54" ht="24" customHeight="1" s="50">
       <c r="A54" s="2" t="n">
         <v>53</v>
       </c>
@@ -6018,7 +6033,7 @@
       </c>
       <c r="AH54" s="2" t="n"/>
     </row>
-    <row r="55" ht="24" customHeight="1" s="49">
+    <row r="55" ht="24" customHeight="1" s="50">
       <c r="A55" s="2" t="n">
         <v>54</v>
       </c>
@@ -6106,7 +6121,7 @@
       </c>
       <c r="AH55" s="2" t="n"/>
     </row>
-    <row r="56" ht="24" customHeight="1" s="49">
+    <row r="56" ht="24" customHeight="1" s="50">
       <c r="A56" s="2" t="n">
         <v>55</v>
       </c>
@@ -6194,7 +6209,7 @@
       </c>
       <c r="AH56" s="2" t="n"/>
     </row>
-    <row r="57" ht="24" customHeight="1" s="49">
+    <row r="57" ht="24" customHeight="1" s="50">
       <c r="A57" s="2" t="n">
         <v>56</v>
       </c>
@@ -6278,7 +6293,7 @@
       <c r="AG57" s="2" t="n"/>
       <c r="AH57" s="2" t="n"/>
     </row>
-    <row r="58" ht="24" customHeight="1" s="49">
+    <row r="58" ht="24" customHeight="1" s="50">
       <c r="A58" s="2" t="n">
         <v>57</v>
       </c>
@@ -6366,7 +6381,7 @@
       </c>
       <c r="AH58" s="2" t="n"/>
     </row>
-    <row r="59" ht="24" customHeight="1" s="49">
+    <row r="59" ht="24" customHeight="1" s="50">
       <c r="A59" s="2" t="n">
         <v>58</v>
       </c>
@@ -6454,7 +6469,7 @@
       </c>
       <c r="AH59" s="2" t="n"/>
     </row>
-    <row r="60" ht="24" customHeight="1" s="49">
+    <row r="60" ht="24" customHeight="1" s="50">
       <c r="A60" s="2" t="n">
         <v>59</v>
       </c>
@@ -6542,7 +6557,7 @@
       </c>
       <c r="AH60" s="2" t="n"/>
     </row>
-    <row r="61" ht="24" customHeight="1" s="49">
+    <row r="61" ht="24" customHeight="1" s="50">
       <c r="A61" s="2" t="n">
         <v>60</v>
       </c>
@@ -6634,7 +6649,7 @@
       </c>
       <c r="AH61" s="2" t="n"/>
     </row>
-    <row r="62" ht="24" customHeight="1" s="49">
+    <row r="62" ht="24" customHeight="1" s="50">
       <c r="A62" s="2" t="n">
         <v>61</v>
       </c>
@@ -6722,7 +6737,7 @@
       </c>
       <c r="AH62" s="2" t="n"/>
     </row>
-    <row r="63" ht="24" customHeight="1" s="49">
+    <row r="63" ht="24" customHeight="1" s="50">
       <c r="A63" s="2" t="n">
         <v>62</v>
       </c>
@@ -6822,7 +6837,7 @@
       </c>
       <c r="AH63" s="2" t="n"/>
     </row>
-    <row r="64" ht="24" customHeight="1" s="49">
+    <row r="64" ht="24" customHeight="1" s="50">
       <c r="A64" s="2" t="n">
         <v>63</v>
       </c>
@@ -6910,7 +6925,7 @@
       </c>
       <c r="AH64" s="2" t="n"/>
     </row>
-    <row r="65" ht="24" customHeight="1" s="49">
+    <row r="65" ht="24" customHeight="1" s="50">
       <c r="A65" s="2" t="n">
         <v>64</v>
       </c>
@@ -6998,7 +7013,7 @@
       </c>
       <c r="AH65" s="2" t="n"/>
     </row>
-    <row r="66" ht="24" customHeight="1" s="49">
+    <row r="66" ht="24" customHeight="1" s="50">
       <c r="A66" s="2" t="n">
         <v>65</v>
       </c>
@@ -7086,7 +7101,7 @@
       </c>
       <c r="AH66" s="2" t="n"/>
     </row>
-    <row r="67" ht="24" customHeight="1" s="49">
+    <row r="67" ht="24" customHeight="1" s="50">
       <c r="A67" s="2" t="n">
         <v>66</v>
       </c>
@@ -7174,7 +7189,7 @@
       </c>
       <c r="AH67" s="2" t="n"/>
     </row>
-    <row r="68" ht="24" customHeight="1" s="49">
+    <row r="68" ht="24" customHeight="1" s="50">
       <c r="A68" s="2" t="n">
         <v>67</v>
       </c>
@@ -7274,7 +7289,7 @@
       </c>
       <c r="AH68" s="2" t="n"/>
     </row>
-    <row r="69" ht="24" customHeight="1" s="49">
+    <row r="69" ht="24" customHeight="1" s="50">
       <c r="A69" s="2" t="n">
         <v>68</v>
       </c>
@@ -7362,7 +7377,7 @@
       </c>
       <c r="AH69" s="2" t="n"/>
     </row>
-    <row r="70" ht="24" customHeight="1" s="49">
+    <row r="70" ht="24" customHeight="1" s="50">
       <c r="A70" s="2" t="n">
         <v>69</v>
       </c>
@@ -7450,7 +7465,7 @@
       </c>
       <c r="AH70" s="2" t="n"/>
     </row>
-    <row r="71" ht="24" customHeight="1" s="49">
+    <row r="71" ht="24" customHeight="1" s="50">
       <c r="A71" s="2" t="n">
         <v>70</v>
       </c>
@@ -7538,7 +7553,7 @@
       </c>
       <c r="AH71" s="2" t="n"/>
     </row>
-    <row r="72" ht="24" customHeight="1" s="49">
+    <row r="72" ht="24" customHeight="1" s="50">
       <c r="A72" s="2" t="n">
         <v>71</v>
       </c>
@@ -7626,7 +7641,7 @@
       </c>
       <c r="AH72" s="2" t="n"/>
     </row>
-    <row r="73" ht="24" customHeight="1" s="49">
+    <row r="73" ht="24" customHeight="1" s="50">
       <c r="A73" s="2" t="n">
         <v>72</v>
       </c>
@@ -7714,7 +7729,7 @@
       </c>
       <c r="AH73" s="2" t="n"/>
     </row>
-    <row r="74" ht="24" customHeight="1" s="49">
+    <row r="74" ht="24" customHeight="1" s="50">
       <c r="A74" s="2" t="n">
         <v>73</v>
       </c>
@@ -7798,7 +7813,7 @@
       <c r="AG74" s="2" t="n"/>
       <c r="AH74" s="2" t="n"/>
     </row>
-    <row r="75" ht="24" customHeight="1" s="49">
+    <row r="75" ht="24" customHeight="1" s="50">
       <c r="A75" s="2" t="n">
         <v>74</v>
       </c>
@@ -7900,7 +7915,7 @@
       </c>
       <c r="AH75" s="2" t="n"/>
     </row>
-    <row r="76" ht="24" customHeight="1" s="49">
+    <row r="76" ht="24" customHeight="1" s="50">
       <c r="A76" s="2" t="n">
         <v>75</v>
       </c>
@@ -8006,7 +8021,7 @@
       </c>
       <c r="AH76" s="2" t="n"/>
     </row>
-    <row r="77" ht="24" customHeight="1" s="49">
+    <row r="77" ht="24" customHeight="1" s="50">
       <c r="A77" s="2" t="n">
         <v>76</v>
       </c>
@@ -8056,13 +8071,13 @@
         </is>
       </c>
       <c r="O77" s="32" t="n">
-        <v>-3.7</v>
+        <v>-3</v>
       </c>
       <c r="P77" s="32" t="n">
-        <v>3.6</v>
+        <v>6.4</v>
       </c>
       <c r="Q77" s="32" t="n">
-        <v>-2.69</v>
+        <v>0.44</v>
       </c>
       <c r="R77" s="23" t="inlineStr">
         <is>
@@ -8122,7 +8137,7 @@
       </c>
       <c r="AH77" s="2" t="n"/>
     </row>
-    <row r="78" ht="24" customHeight="1" s="49">
+    <row r="78" ht="24" customHeight="1" s="50">
       <c r="A78" s="2" t="n">
         <v>77</v>
       </c>
@@ -8224,7 +8239,7 @@
       </c>
       <c r="AH78" s="2" t="n"/>
     </row>
-    <row r="79" ht="24" customHeight="1" s="49">
+    <row r="79" ht="24" customHeight="1" s="50">
       <c r="A79" s="2" t="n">
         <v>78</v>
       </c>
@@ -8330,7 +8345,7 @@
       </c>
       <c r="AH79" s="2" t="n"/>
     </row>
-    <row r="80" ht="24" customHeight="1" s="49">
+    <row r="80" ht="24" customHeight="1" s="50">
       <c r="A80" s="2" t="n">
         <v>79</v>
       </c>
@@ -8432,13 +8447,13 @@
       </c>
       <c r="AH80" s="2" t="n"/>
     </row>
-    <row r="81" ht="24" customHeight="1" s="49">
+    <row r="81" ht="24" customHeight="1" s="50">
       <c r="A81" s="2" t="n">
         <v>80</v>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>ogimet</t>
+          <t>rp5</t>
         </is>
       </c>
       <c r="C81" s="46" t="n">
@@ -8482,12 +8497,14 @@
         </is>
       </c>
       <c r="O81" s="32" t="n">
-        <v>-3.7</v>
+        <v>-7</v>
       </c>
       <c r="P81" s="32" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="Q81" s="32" t="n"/>
+        <v>9.800000000000001</v>
+      </c>
+      <c r="Q81" s="32" t="n">
+        <v>2.14</v>
+      </c>
       <c r="R81" s="23" t="inlineStr">
         <is>
           <t>Y</t>
@@ -8551,7 +8568,7 @@
         </is>
       </c>
     </row>
-    <row r="82" ht="24" customHeight="1" s="49">
+    <row r="82" ht="24" customHeight="1" s="50">
       <c r="A82" s="2" t="n">
         <v>81</v>
       </c>
@@ -8601,13 +8618,13 @@
         </is>
       </c>
       <c r="O82" s="32" t="n">
-        <v>-4</v>
+        <v>-6.4</v>
       </c>
       <c r="P82" s="32" t="n">
-        <v>2.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Q82" s="32" t="n">
-        <v>-1.57</v>
+        <v>1.7</v>
       </c>
       <c r="R82" s="23" t="inlineStr">
         <is>
@@ -8667,7 +8684,7 @@
       </c>
       <c r="AH82" s="2" t="n"/>
     </row>
-    <row r="83" ht="24" customHeight="1" s="49">
+    <row r="83" ht="24" customHeight="1" s="50">
       <c r="A83" s="2" t="n">
         <v>82</v>
       </c>
@@ -8769,7 +8786,7 @@
       </c>
       <c r="AH83" s="2" t="n"/>
     </row>
-    <row r="84" ht="24" customHeight="1" s="49">
+    <row r="84" ht="24" customHeight="1" s="50">
       <c r="A84" s="2" t="n">
         <v>83</v>
       </c>
@@ -8819,13 +8836,13 @@
         </is>
       </c>
       <c r="O84" s="32" t="n">
-        <v>-7.6</v>
+        <v>-3.9</v>
       </c>
       <c r="P84" s="32" t="n">
-        <v>4.7</v>
+        <v>20.1</v>
       </c>
       <c r="Q84" s="32" t="n">
-        <v>-1.4</v>
+        <v>8.06</v>
       </c>
       <c r="R84" s="23" t="inlineStr">
         <is>
@@ -8885,7 +8902,7 @@
       </c>
       <c r="AH84" s="2" t="n"/>
     </row>
-    <row r="85" ht="24" customHeight="1" s="49">
+    <row r="85" ht="24" customHeight="1" s="50">
       <c r="A85" s="2" t="n">
         <v>84</v>
       </c>
@@ -8991,7 +9008,7 @@
       </c>
       <c r="AH85" s="2" t="n"/>
     </row>
-    <row r="86" ht="24" customHeight="1" s="49">
+    <row r="86" ht="24" customHeight="1" s="50">
       <c r="A86" s="2" t="n">
         <v>85</v>
       </c>
@@ -9037,13 +9054,13 @@
       </c>
       <c r="N86" s="2" t="n"/>
       <c r="O86" s="32" t="n">
-        <v>-2</v>
+        <v>4.3</v>
       </c>
       <c r="P86" s="32" t="n">
-        <v>14.7</v>
+        <v>28.4</v>
       </c>
       <c r="Q86" s="32" t="n">
-        <v>5.81</v>
+        <v>16.98</v>
       </c>
       <c r="R86" s="23" t="inlineStr">
         <is>
@@ -9111,7 +9128,7 @@
       </c>
       <c r="AH86" s="2" t="n"/>
     </row>
-    <row r="87" ht="24" customHeight="1" s="49">
+    <row r="87" ht="24" customHeight="1" s="50">
       <c r="A87" s="2" t="n">
         <v>86</v>
       </c>
@@ -9217,7 +9234,7 @@
       </c>
       <c r="AH87" s="2" t="n"/>
     </row>
-    <row r="88" ht="24" customHeight="1" s="49">
+    <row r="88" ht="24" customHeight="1" s="50">
       <c r="A88" s="2" t="n">
         <v>87</v>
       </c>
@@ -9263,13 +9280,13 @@
       </c>
       <c r="N88" s="2" t="n"/>
       <c r="O88" s="32" t="n">
-        <v>-7</v>
+        <v>-2.5</v>
       </c>
       <c r="P88" s="32" t="n">
-        <v>10.4</v>
+        <v>21.8</v>
       </c>
       <c r="Q88" s="32" t="n">
-        <v>1.11</v>
+        <v>10.64</v>
       </c>
       <c r="R88" s="23" t="inlineStr">
         <is>
@@ -9329,7 +9346,7 @@
       </c>
       <c r="AH88" s="2" t="n"/>
     </row>
-    <row r="89" ht="24" customHeight="1" s="49">
+    <row r="89" ht="24" customHeight="1" s="50">
       <c r="A89" s="2" t="n">
         <v>88</v>
       </c>
@@ -9427,7 +9444,7 @@
       </c>
       <c r="AH89" s="2" t="n"/>
     </row>
-    <row r="90" ht="24" customHeight="1" s="49">
+    <row r="90" ht="24" customHeight="1" s="50">
       <c r="A90" s="2" t="n">
         <v>89</v>
       </c>
@@ -9529,7 +9546,7 @@
       <c r="AG90" s="2" t="n"/>
       <c r="AH90" s="2" t="n"/>
     </row>
-    <row r="91" ht="24" customHeight="1" s="49">
+    <row r="91" ht="24" customHeight="1" s="50">
       <c r="A91" s="2" t="n">
         <v>90</v>
       </c>
@@ -9627,7 +9644,7 @@
       </c>
       <c r="AH91" s="2" t="n"/>
     </row>
-    <row r="92" ht="24" customHeight="1" s="49">
+    <row r="92" ht="24" customHeight="1" s="50">
       <c r="A92" s="2" t="n">
         <v>91</v>
       </c>
@@ -9673,13 +9690,13 @@
       </c>
       <c r="N92" s="2" t="n"/>
       <c r="O92" s="32" t="n">
-        <v>-1.8</v>
+        <v>-3.6</v>
       </c>
       <c r="P92" s="32" t="n">
-        <v>13.6</v>
+        <v>13.9</v>
       </c>
       <c r="Q92" s="32" t="n">
-        <v>5.35</v>
+        <v>7.29</v>
       </c>
       <c r="R92" s="23" t="inlineStr">
         <is>
@@ -9739,7 +9756,7 @@
       </c>
       <c r="AH92" s="2" t="n"/>
     </row>
-    <row r="93" ht="24" customHeight="1" s="49">
+    <row r="93" ht="24" customHeight="1" s="50">
       <c r="A93" s="2" t="n">
         <v>92</v>
       </c>
@@ -9785,13 +9802,13 @@
       </c>
       <c r="N93" s="2" t="n"/>
       <c r="O93" s="32" t="n">
-        <v>1.9</v>
+        <v>5.8</v>
       </c>
       <c r="P93" s="32" t="n">
-        <v>16.4</v>
+        <v>22.5</v>
       </c>
       <c r="Q93" s="32" t="n">
-        <v>9.4</v>
+        <v>14.56</v>
       </c>
       <c r="R93" s="23" t="inlineStr">
         <is>
@@ -9863,7 +9880,7 @@
       </c>
       <c r="AH93" s="2" t="n"/>
     </row>
-    <row r="94" ht="24" customHeight="1" s="49">
+    <row r="94" ht="24" customHeight="1" s="50">
       <c r="A94" s="2" t="n">
         <v>93</v>
       </c>
@@ -9969,7 +9986,7 @@
       </c>
       <c r="AH94" s="2" t="n"/>
     </row>
-    <row r="95" ht="24" customHeight="1" s="49">
+    <row r="95" ht="24" customHeight="1" s="50">
       <c r="A95" s="2" t="n">
         <v>94</v>
       </c>
@@ -10015,13 +10032,13 @@
       </c>
       <c r="N95" s="2" t="n"/>
       <c r="O95" s="32" t="n">
-        <v>3.6</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="P95" s="32" t="n">
-        <v>12.3</v>
+        <v>17.5</v>
       </c>
       <c r="Q95" s="32" t="n">
-        <v>7.75</v>
+        <v>13.88</v>
       </c>
       <c r="R95" s="23" t="inlineStr">
         <is>
@@ -10093,7 +10110,7 @@
       </c>
       <c r="AH95" s="2" t="n"/>
     </row>
-    <row r="96" ht="24" customHeight="1" s="49">
+    <row r="96" ht="24" customHeight="1" s="50">
       <c r="A96" s="2" t="n">
         <v>95</v>
       </c>
@@ -10207,7 +10224,7 @@
       </c>
       <c r="AH96" s="2" t="n"/>
     </row>
-    <row r="97" ht="24" customHeight="1" s="49">
+    <row r="97" ht="24" customHeight="1" s="50">
       <c r="A97" s="2" t="n">
         <v>96</v>
       </c>
@@ -10253,13 +10270,13 @@
       </c>
       <c r="N97" s="2" t="n"/>
       <c r="O97" s="32" t="n">
-        <v>3.9</v>
+        <v>8.4</v>
       </c>
       <c r="P97" s="32" t="n">
-        <v>10.6</v>
+        <v>16.5</v>
       </c>
       <c r="Q97" s="32" t="n">
-        <v>6.56</v>
+        <v>13.15</v>
       </c>
       <c r="R97" s="23" t="inlineStr">
         <is>
@@ -10335,7 +10352,7 @@
       </c>
       <c r="AH97" s="2" t="n"/>
     </row>
-    <row r="98" ht="24" customHeight="1" s="49">
+    <row r="98" ht="24" customHeight="1" s="50">
       <c r="A98" s="2" t="n">
         <v>97</v>
       </c>
@@ -10372,12 +10389,8 @@
         </is>
       </c>
       <c r="N98" s="2" t="n"/>
-      <c r="O98" s="32" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="P98" s="32" t="n">
-        <v>9.4</v>
-      </c>
+      <c r="O98" s="32" t="n"/>
+      <c r="P98" s="32" t="n"/>
       <c r="Q98" s="32" t="n"/>
       <c r="R98" s="23" t="inlineStr">
         <is>
@@ -10445,7 +10458,7 @@
       </c>
       <c r="AH98" s="2" t="n"/>
     </row>
-    <row r="99" ht="24" customHeight="1" s="49">
+    <row r="99" ht="24" customHeight="1" s="50">
       <c r="A99" s="2" t="n">
         <v>98</v>
       </c>
@@ -10555,7 +10568,7 @@
       </c>
       <c r="AH99" s="2" t="n"/>
     </row>
-    <row r="100" ht="24" customHeight="1" s="49">
+    <row r="100" ht="24" customHeight="1" s="50">
       <c r="A100" s="2" t="n">
         <v>99</v>
       </c>
@@ -10661,7 +10674,7 @@
       </c>
       <c r="AH100" s="2" t="n"/>
     </row>
-    <row r="101" ht="24" customHeight="1" s="49">
+    <row r="101" ht="24" customHeight="1" s="50">
       <c r="A101" s="2" t="n">
         <v>100</v>
       </c>
@@ -10767,7 +10780,7 @@
       </c>
       <c r="AH101" s="2" t="n"/>
     </row>
-    <row r="102" ht="24" customHeight="1" s="49">
+    <row r="102" ht="24" customHeight="1" s="50">
       <c r="A102" s="2" t="n">
         <v>101</v>
       </c>
@@ -10813,13 +10826,13 @@
       </c>
       <c r="N102" s="2" t="n"/>
       <c r="O102" s="32" t="n">
-        <v>0.1</v>
+        <v>-1.5</v>
       </c>
       <c r="P102" s="32" t="n">
-        <v>1.6</v>
+        <v>12</v>
       </c>
       <c r="Q102" s="32" t="n">
-        <v>0.54</v>
+        <v>5.59</v>
       </c>
       <c r="R102" s="23" t="inlineStr">
         <is>
@@ -10891,7 +10904,7 @@
       </c>
       <c r="AH102" s="2" t="n"/>
     </row>
-    <row r="103" ht="24" customHeight="1" s="49">
+    <row r="103" ht="24" customHeight="1" s="50">
       <c r="A103" s="2" t="n">
         <v>102</v>
       </c>
@@ -10993,7 +11006,7 @@
       </c>
       <c r="AH103" s="2" t="n"/>
     </row>
-    <row r="104" ht="24" customHeight="1" s="49">
+    <row r="104" ht="24" customHeight="1" s="50">
       <c r="A104" s="2" t="n">
         <v>103</v>
       </c>
@@ -11099,7 +11112,7 @@
       </c>
       <c r="AH104" s="2" t="n"/>
     </row>
-    <row r="105" ht="24" customHeight="1" s="49">
+    <row r="105" ht="24" customHeight="1" s="50">
       <c r="A105" s="2" t="n">
         <v>104</v>
       </c>
@@ -11149,13 +11162,13 @@
         </is>
       </c>
       <c r="O105" s="32" t="n">
-        <v>-5.6</v>
+        <v>-7.5</v>
       </c>
       <c r="P105" s="32" t="n">
-        <v>0.2</v>
+        <v>9.4</v>
       </c>
       <c r="Q105" s="32" t="n">
-        <v>-2.4</v>
+        <v>0.97</v>
       </c>
       <c r="R105" s="23" t="inlineStr">
         <is>
@@ -11223,7 +11236,7 @@
       </c>
       <c r="AH105" s="2" t="n"/>
     </row>
-    <row r="106" ht="24" customHeight="1" s="49">
+    <row r="106" ht="24" customHeight="1" s="50">
       <c r="A106" s="2" t="n">
         <v>105</v>
       </c>
@@ -11329,7 +11342,7 @@
       </c>
       <c r="AH106" s="2" t="n"/>
     </row>
-    <row r="107" ht="24" customHeight="1" s="49">
+    <row r="107" ht="24" customHeight="1" s="50">
       <c r="A107" s="2" t="n">
         <v>106</v>
       </c>
@@ -11427,7 +11440,7 @@
       </c>
       <c r="AH107" s="2" t="n"/>
     </row>
-    <row r="108" ht="24" customHeight="1" s="49">
+    <row r="108" ht="24" customHeight="1" s="50">
       <c r="A108" s="2" t="n">
         <v>107</v>
       </c>
@@ -11537,7 +11550,7 @@
       </c>
       <c r="AH108" s="2" t="n"/>
     </row>
-    <row r="109" ht="24" customHeight="1" s="49">
+    <row r="109" ht="24" customHeight="1" s="50">
       <c r="A109" s="2" t="n">
         <v>108</v>
       </c>
@@ -11635,7 +11648,7 @@
       </c>
       <c r="AH109" s="2" t="n"/>
     </row>
-    <row r="110" ht="24" customHeight="1" s="49">
+    <row r="110" ht="24" customHeight="1" s="50">
       <c r="A110" s="2" t="n">
         <v>109</v>
       </c>
@@ -11737,7 +11750,7 @@
       </c>
       <c r="AH110" s="2" t="n"/>
     </row>
-    <row r="111" ht="24" customHeight="1" s="49">
+    <row r="111" ht="24" customHeight="1" s="50">
       <c r="A111" s="2" t="n">
         <v>110</v>
       </c>
@@ -11847,7 +11860,7 @@
       </c>
       <c r="AH111" s="2" t="n"/>
     </row>
-    <row r="112" ht="24" customHeight="1" s="49">
+    <row r="112" ht="24" customHeight="1" s="50">
       <c r="A112" s="2" t="n">
         <v>111</v>
       </c>
@@ -11945,7 +11958,7 @@
       <c r="AG112" s="2" t="n"/>
       <c r="AH112" s="2" t="n"/>
     </row>
-    <row r="113" ht="24" customHeight="1" s="49">
+    <row r="113" ht="24" customHeight="1" s="50">
       <c r="A113" s="2" t="n">
         <v>112</v>
       </c>
@@ -11983,12 +11996,14 @@
       </c>
       <c r="N113" s="2" t="n"/>
       <c r="O113" s="32" t="n">
-        <v>-1</v>
+        <v>-7.5</v>
       </c>
       <c r="P113" s="32" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="Q113" s="32" t="n"/>
+        <v>0.7</v>
+      </c>
+      <c r="Q113" s="32" t="n">
+        <v>-2.96</v>
+      </c>
       <c r="R113" s="23" t="inlineStr">
         <is>
           <t>Y</t>
@@ -12055,7 +12070,7 @@
       </c>
       <c r="AH113" s="2" t="n"/>
     </row>
-    <row r="114" ht="24" customHeight="1" s="49">
+    <row r="114" ht="24" customHeight="1" s="50">
       <c r="A114" s="2" t="n">
         <v>113</v>
       </c>
@@ -12097,12 +12112,14 @@
         </is>
       </c>
       <c r="O114" s="32" t="n">
-        <v>-2.8</v>
+        <v>-14.2</v>
       </c>
       <c r="P114" s="32" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q114" s="32" t="n"/>
+        <v>-1.1</v>
+      </c>
+      <c r="Q114" s="32" t="n">
+        <v>-7.66</v>
+      </c>
       <c r="R114" s="23" t="inlineStr">
         <is>
           <t>Y</t>
@@ -12169,7 +12186,7 @@
       </c>
       <c r="AH114" s="2" t="n"/>
     </row>
-    <row r="115" ht="24" customHeight="1" s="49">
+    <row r="115" ht="24" customHeight="1" s="50">
       <c r="A115" s="2" t="n">
         <v>114</v>
       </c>
@@ -12219,12 +12236,14 @@
         </is>
       </c>
       <c r="O115" s="32" t="n">
-        <v>-6.5</v>
+        <v>-10.9</v>
       </c>
       <c r="P115" s="32" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="Q115" s="32" t="n"/>
+        <v>0</v>
+      </c>
+      <c r="Q115" s="32" t="n">
+        <v>-5.49</v>
+      </c>
       <c r="R115" s="23" t="inlineStr">
         <is>
           <t>Y</t>
@@ -12291,7 +12310,7 @@
       </c>
       <c r="AH115" s="2" t="n"/>
     </row>
-    <row r="116" ht="24" customHeight="1" s="49">
+    <row r="116" ht="24" customHeight="1" s="50">
       <c r="A116" s="2" t="n">
         <v>115</v>
       </c>
@@ -12401,7 +12420,7 @@
       </c>
       <c r="AH116" s="2" t="n"/>
     </row>
-    <row r="117" ht="24" customHeight="1" s="49">
+    <row r="117" ht="24" customHeight="1" s="50">
       <c r="A117" s="2" t="n">
         <v>116</v>
       </c>
@@ -12503,7 +12522,7 @@
       </c>
       <c r="AH117" s="2" t="n"/>
     </row>
-    <row r="118" ht="24" customHeight="1" s="49">
+    <row r="118" ht="24" customHeight="1" s="50">
       <c r="A118" s="2" t="n">
         <v>117</v>
       </c>
@@ -12609,7 +12628,7 @@
       </c>
       <c r="AH118" s="2" t="n"/>
     </row>
-    <row r="119" ht="24" customHeight="1" s="49">
+    <row r="119" ht="24" customHeight="1" s="50">
       <c r="A119" s="2" t="n">
         <v>118</v>
       </c>
@@ -12727,7 +12746,7 @@
       </c>
       <c r="AH119" s="2" t="n"/>
     </row>
-    <row r="120" ht="24" customHeight="1" s="49">
+    <row r="120" ht="24" customHeight="1" s="50">
       <c r="A120" s="2" t="n">
         <v>119</v>
       </c>
@@ -12772,10 +12791,20 @@
         </is>
       </c>
       <c r="N120" s="2" t="n"/>
-      <c r="O120" s="32" t="n"/>
-      <c r="P120" s="32" t="n"/>
-      <c r="Q120" s="32" t="n"/>
-      <c r="R120" s="23" t="n"/>
+      <c r="O120" s="32" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="P120" s="32" t="n">
+        <v>33.1</v>
+      </c>
+      <c r="Q120" s="32" t="n">
+        <v>24.96</v>
+      </c>
+      <c r="R120" s="23" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="S120" s="37" t="n"/>
       <c r="T120" s="41" t="inlineStr">
         <is>
@@ -12833,7 +12862,7 @@
       </c>
       <c r="AH120" s="2" t="n"/>
     </row>
-    <row r="121" ht="24" customHeight="1" s="49">
+    <row r="121" ht="24" customHeight="1" s="50">
       <c r="A121" s="2" t="n">
         <v>120</v>
       </c>
@@ -12879,13 +12908,13 @@
       </c>
       <c r="N121" s="2" t="n"/>
       <c r="O121" s="32" t="n">
-        <v>6.4</v>
+        <v>14.1</v>
       </c>
       <c r="P121" s="32" t="n">
-        <v>13.2</v>
+        <v>25.4</v>
       </c>
       <c r="Q121" s="32" t="n">
-        <v>9.74</v>
+        <v>19.46</v>
       </c>
       <c r="R121" s="23" t="inlineStr">
         <is>
@@ -12957,7 +12986,7 @@
       </c>
       <c r="AH121" s="2" t="n"/>
     </row>
-    <row r="122" ht="24" customHeight="1" s="49">
+    <row r="122" ht="24" customHeight="1" s="50">
       <c r="A122" s="2" t="n">
         <v>121</v>
       </c>
@@ -13003,12 +13032,14 @@
       </c>
       <c r="N122" s="2" t="n"/>
       <c r="O122" s="32" t="n">
-        <v>-1.1</v>
+        <v>-2.9</v>
       </c>
       <c r="P122" s="32" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="Q122" s="32" t="n"/>
+        <v>16.1</v>
+      </c>
+      <c r="Q122" s="32" t="n">
+        <v>7.3</v>
+      </c>
       <c r="R122" s="23" t="inlineStr">
         <is>
           <t>Y</t>
@@ -13075,7 +13106,7 @@
       </c>
       <c r="AH122" s="2" t="n"/>
     </row>
-    <row r="123" ht="24" customHeight="1" s="49">
+    <row r="123" ht="24" customHeight="1" s="50">
       <c r="A123" s="2" t="n">
         <v>122</v>
       </c>
@@ -13177,7 +13208,7 @@
       </c>
       <c r="AH123" s="2" t="n"/>
     </row>
-    <row r="124" ht="24" customHeight="1" s="49">
+    <row r="124" ht="24" customHeight="1" s="50">
       <c r="A124" s="2" t="n">
         <v>123</v>
       </c>
@@ -13223,13 +13254,13 @@
       </c>
       <c r="N124" s="2" t="n"/>
       <c r="O124" s="32" t="n">
-        <v>-6.2</v>
+        <v>6.2</v>
       </c>
       <c r="P124" s="32" t="n">
-        <v>14.7</v>
+        <v>18.3</v>
       </c>
       <c r="Q124" s="32" t="n">
-        <v>4.9</v>
+        <v>12.09</v>
       </c>
       <c r="R124" s="23" t="inlineStr">
         <is>
@@ -13301,7 +13332,7 @@
       </c>
       <c r="AH124" s="2" t="n"/>
     </row>
-    <row r="125" ht="24" customHeight="1" s="49">
+    <row r="125" ht="24" customHeight="1" s="50">
       <c r="A125" s="2" t="n">
         <v>124</v>
       </c>
@@ -13347,13 +13378,13 @@
       </c>
       <c r="N125" s="2" t="n"/>
       <c r="O125" s="32" t="n">
-        <v>4.3</v>
+        <v>12</v>
       </c>
       <c r="P125" s="32" t="n">
-        <v>21.9</v>
+        <v>23.3</v>
       </c>
       <c r="Q125" s="32" t="n">
-        <v>14.66</v>
+        <v>16.4</v>
       </c>
       <c r="R125" s="23" t="inlineStr">
         <is>
@@ -13413,7 +13444,7 @@
       <c r="AG125" s="2" t="n"/>
       <c r="AH125" s="2" t="n"/>
     </row>
-    <row r="126" ht="24" customHeight="1" s="49">
+    <row r="126" ht="24" customHeight="1" s="50">
       <c r="A126" s="2" t="n">
         <v>125</v>
       </c>
@@ -13450,12 +13481,8 @@
         </is>
       </c>
       <c r="N126" s="2" t="n"/>
-      <c r="O126" s="32" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="P126" s="32" t="n">
-        <v>21.3</v>
-      </c>
+      <c r="O126" s="32" t="n"/>
+      <c r="P126" s="32" t="n"/>
       <c r="Q126" s="32" t="n"/>
       <c r="R126" s="23" t="inlineStr">
         <is>
@@ -13515,7 +13542,7 @@
         </is>
       </c>
     </row>
-    <row r="127" ht="24" customHeight="1" s="49">
+    <row r="127" ht="24" customHeight="1" s="50">
       <c r="A127" s="2" t="n">
         <v>126</v>
       </c>
@@ -13561,13 +13588,13 @@
       </c>
       <c r="N127" s="2" t="n"/>
       <c r="O127" s="32" t="n">
-        <v>2.4</v>
+        <v>9.5</v>
       </c>
       <c r="P127" s="32" t="n">
-        <v>16.7</v>
+        <v>17.2</v>
       </c>
       <c r="Q127" s="32" t="n">
-        <v>9.83</v>
+        <v>13.19</v>
       </c>
       <c r="R127" s="23" t="inlineStr">
         <is>
@@ -13635,7 +13662,7 @@
       </c>
       <c r="AH127" s="2" t="n"/>
     </row>
-    <row r="128" ht="24" customHeight="1" s="49">
+    <row r="128" ht="24" customHeight="1" s="50">
       <c r="A128" s="2" t="n">
         <v>127</v>
       </c>
@@ -13681,12 +13708,14 @@
       </c>
       <c r="N128" s="2" t="n"/>
       <c r="O128" s="32" t="n">
-        <v>10.5</v>
+        <v>14.4</v>
       </c>
       <c r="P128" s="32" t="n">
-        <v>20.7</v>
-      </c>
-      <c r="Q128" s="32" t="n"/>
+        <v>23.4</v>
+      </c>
+      <c r="Q128" s="32" t="n">
+        <v>18.94</v>
+      </c>
       <c r="R128" s="23" t="inlineStr">
         <is>
           <t>Y</t>
@@ -13745,7 +13774,7 @@
       <c r="AG128" s="2" t="n"/>
       <c r="AH128" s="2" t="n"/>
     </row>
-    <row r="129" ht="24" customHeight="1" s="49">
+    <row r="129" ht="24" customHeight="1" s="50">
       <c r="A129" s="2" t="n">
         <v>128</v>
       </c>
@@ -13791,13 +13820,13 @@
       </c>
       <c r="N129" s="2" t="n"/>
       <c r="O129" s="32" t="n">
-        <v>0.1</v>
+        <v>12.4</v>
       </c>
       <c r="P129" s="32" t="n">
-        <v>18.7</v>
+        <v>20.9</v>
       </c>
       <c r="Q129" s="32" t="n">
-        <v>10.94</v>
+        <v>14.97</v>
       </c>
       <c r="R129" s="23" t="inlineStr">
         <is>
@@ -13865,7 +13894,7 @@
       </c>
       <c r="AH129" s="2" t="n"/>
     </row>
-    <row r="130" ht="24" customHeight="1" s="49">
+    <row r="130" ht="24" customHeight="1" s="50">
       <c r="A130" s="2" t="n">
         <v>129</v>
       </c>
@@ -13911,14 +13940,12 @@
       </c>
       <c r="N130" s="2" t="n"/>
       <c r="O130" s="32" t="n">
-        <v>1.5</v>
+        <v>-0.1</v>
       </c>
       <c r="P130" s="32" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="Q130" s="32" t="n">
-        <v>4.29</v>
-      </c>
+        <v>11.3</v>
+      </c>
+      <c r="Q130" s="32" t="n"/>
       <c r="R130" s="23" t="inlineStr">
         <is>
           <t>Y</t>
@@ -13985,7 +14012,7 @@
       </c>
       <c r="AH130" s="2" t="n"/>
     </row>
-    <row r="131" ht="24" customHeight="1" s="49">
+    <row r="131" ht="24" customHeight="1" s="50">
       <c r="A131" s="2" t="n">
         <v>130</v>
       </c>
@@ -14031,13 +14058,13 @@
       </c>
       <c r="N131" s="2" t="n"/>
       <c r="O131" s="32" t="n">
-        <v>9.5</v>
+        <v>16</v>
       </c>
       <c r="P131" s="32" t="n">
-        <v>19.5</v>
+        <v>22.5</v>
       </c>
       <c r="Q131" s="32" t="n">
-        <v>13.85</v>
+        <v>18.85</v>
       </c>
       <c r="R131" s="23" t="inlineStr">
         <is>
@@ -14101,7 +14128,7 @@
       </c>
       <c r="AH131" s="2" t="n"/>
     </row>
-    <row r="132" ht="24" customHeight="1" s="49">
+    <row r="132" ht="24" customHeight="1" s="50">
       <c r="A132" s="2" t="n">
         <v>131</v>
       </c>
@@ -14147,13 +14174,13 @@
       </c>
       <c r="N132" s="2" t="n"/>
       <c r="O132" s="32" t="n">
-        <v>12.9</v>
+        <v>14.9</v>
       </c>
       <c r="P132" s="32" t="n">
-        <v>20.4</v>
+        <v>23.5</v>
       </c>
       <c r="Q132" s="32" t="n">
-        <v>15.89</v>
+        <v>18.36</v>
       </c>
       <c r="R132" s="23" t="inlineStr">
         <is>
@@ -14217,7 +14244,7 @@
       </c>
       <c r="AH132" s="2" t="n"/>
     </row>
-    <row r="133" ht="24" customHeight="1" s="49">
+    <row r="133" ht="24" customHeight="1" s="50">
       <c r="A133" s="2" t="n">
         <v>132</v>
       </c>
@@ -14263,13 +14290,13 @@
       </c>
       <c r="N133" s="2" t="n"/>
       <c r="O133" s="32" t="n">
-        <v>11</v>
+        <v>14.9</v>
       </c>
       <c r="P133" s="32" t="n">
-        <v>18</v>
+        <v>24.8</v>
       </c>
       <c r="Q133" s="32" t="n">
-        <v>13.79</v>
+        <v>18.64</v>
       </c>
       <c r="R133" s="23" t="inlineStr">
         <is>
@@ -14337,7 +14364,7 @@
         </is>
       </c>
     </row>
-    <row r="134" ht="24" customHeight="1" s="49">
+    <row r="134" ht="24" customHeight="1" s="50">
       <c r="A134" s="2" t="n">
         <v>133</v>
       </c>
@@ -14439,7 +14466,7 @@
       </c>
       <c r="AH134" s="2" t="n"/>
     </row>
-    <row r="135" ht="24" customHeight="1" s="49">
+    <row r="135" ht="24" customHeight="1" s="50">
       <c r="A135" s="2" t="n">
         <v>134</v>
       </c>
@@ -14485,13 +14512,13 @@
       </c>
       <c r="N135" s="2" t="n"/>
       <c r="O135" s="32" t="n">
-        <v>13.5</v>
+        <v>16.5</v>
       </c>
       <c r="P135" s="32" t="n">
-        <v>26.2</v>
+        <v>26.7</v>
       </c>
       <c r="Q135" s="32" t="n">
-        <v>18.55</v>
+        <v>19.75</v>
       </c>
       <c r="R135" s="23" t="inlineStr">
         <is>
@@ -14555,7 +14582,7 @@
       </c>
       <c r="AH135" s="2" t="n"/>
     </row>
-    <row r="136" ht="24" customHeight="1" s="49">
+    <row r="136" ht="24" customHeight="1" s="50">
       <c r="A136" s="2" t="n">
         <v>135</v>
       </c>
@@ -14601,13 +14628,13 @@
       </c>
       <c r="N136" s="2" t="n"/>
       <c r="O136" s="32" t="n">
-        <v>19.7</v>
+        <v>18.6</v>
       </c>
       <c r="P136" s="32" t="n">
-        <v>28</v>
+        <v>27.2</v>
       </c>
       <c r="Q136" s="32" t="n">
-        <v>23.18</v>
+        <v>21.99</v>
       </c>
       <c r="R136" s="23" t="inlineStr">
         <is>
@@ -14671,7 +14698,7 @@
       </c>
       <c r="AH136" s="2" t="n"/>
     </row>
-    <row r="137" ht="24" customHeight="1" s="49">
+    <row r="137" ht="24" customHeight="1" s="50">
       <c r="A137" s="2" t="n">
         <v>136</v>
       </c>
@@ -14717,13 +14744,13 @@
       </c>
       <c r="N137" s="2" t="n"/>
       <c r="O137" s="32" t="n">
-        <v>16.3</v>
+        <v>15.7</v>
       </c>
       <c r="P137" s="32" t="n">
-        <v>22.5</v>
+        <v>22</v>
       </c>
       <c r="Q137" s="32" t="n">
-        <v>18.64</v>
+        <v>17.92</v>
       </c>
       <c r="R137" s="23" t="inlineStr">
         <is>
@@ -14787,7 +14814,7 @@
       </c>
       <c r="AH137" s="2" t="n"/>
     </row>
-    <row r="138" ht="24" customHeight="1" s="49">
+    <row r="138" ht="24" customHeight="1" s="50">
       <c r="A138" s="2" t="n">
         <v>137</v>
       </c>
@@ -14833,12 +14860,14 @@
       </c>
       <c r="N138" s="2" t="n"/>
       <c r="O138" s="32" t="n">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="P138" s="32" t="n">
-        <v>19.6</v>
-      </c>
-      <c r="Q138" s="32" t="n"/>
+        <v>22</v>
+      </c>
+      <c r="Q138" s="32" t="n">
+        <v>17.95</v>
+      </c>
       <c r="R138" s="23" t="inlineStr">
         <is>
           <t>Y</t>
@@ -14901,7 +14930,7 @@
       </c>
       <c r="AH138" s="2" t="n"/>
     </row>
-    <row r="139" ht="24" customHeight="1" s="49">
+    <row r="139" ht="24" customHeight="1" s="50">
       <c r="A139" s="2" t="n">
         <v>138</v>
       </c>
@@ -14947,13 +14976,13 @@
       </c>
       <c r="N139" s="2" t="n"/>
       <c r="O139" s="32" t="n">
-        <v>14</v>
+        <v>16.2</v>
       </c>
       <c r="P139" s="32" t="n">
         <v>20.8</v>
       </c>
       <c r="Q139" s="32" t="n">
-        <v>16.26</v>
+        <v>17.67</v>
       </c>
       <c r="R139" s="23" t="inlineStr">
         <is>
@@ -15017,7 +15046,7 @@
       </c>
       <c r="AH139" s="2" t="n"/>
     </row>
-    <row r="140" ht="24" customHeight="1" s="49">
+    <row r="140" ht="24" customHeight="1" s="50">
       <c r="A140" s="2" t="n">
         <v>139</v>
       </c>
@@ -15063,13 +15092,13 @@
       </c>
       <c r="N140" s="2" t="n"/>
       <c r="O140" s="32" t="n">
-        <v>15.4</v>
+        <v>15</v>
       </c>
       <c r="P140" s="32" t="n">
-        <v>25.5</v>
+        <v>22.7</v>
       </c>
       <c r="Q140" s="32" t="n">
-        <v>20.44</v>
+        <v>19.16</v>
       </c>
       <c r="R140" s="23" t="inlineStr">
         <is>
@@ -15133,7 +15162,7 @@
       </c>
       <c r="AH140" s="2" t="n"/>
     </row>
-    <row r="141" ht="24" customHeight="1" s="49">
+    <row r="141" ht="24" customHeight="1" s="50">
       <c r="A141" s="2" t="n">
         <v>140</v>
       </c>
@@ -15235,7 +15264,7 @@
       </c>
       <c r="AH141" s="2" t="n"/>
     </row>
-    <row r="142" ht="24" customHeight="1" s="49">
+    <row r="142" ht="24" customHeight="1" s="50">
       <c r="A142" s="2" t="n">
         <v>141</v>
       </c>
@@ -15281,13 +15310,13 @@
       </c>
       <c r="N142" s="2" t="n"/>
       <c r="O142" s="32" t="n">
-        <v>19.2</v>
+        <v>16.3</v>
       </c>
       <c r="P142" s="32" t="n">
-        <v>30.4</v>
+        <v>28.5</v>
       </c>
       <c r="Q142" s="32" t="n">
-        <v>23.58</v>
+        <v>21.9</v>
       </c>
       <c r="R142" s="23" t="inlineStr">
         <is>
@@ -15351,7 +15380,7 @@
       </c>
       <c r="AH142" s="2" t="n"/>
     </row>
-    <row r="143" ht="24" customHeight="1" s="49">
+    <row r="143" ht="24" customHeight="1" s="50">
       <c r="A143" s="2" t="n">
         <v>142</v>
       </c>
@@ -15397,13 +15426,13 @@
       </c>
       <c r="N143" s="2" t="n"/>
       <c r="O143" s="32" t="n">
-        <v>22.5</v>
+        <v>21.6</v>
       </c>
       <c r="P143" s="32" t="n">
-        <v>29.1</v>
+        <v>27.5</v>
       </c>
       <c r="Q143" s="32" t="n">
-        <v>25.06</v>
+        <v>24.64</v>
       </c>
       <c r="R143" s="23" t="inlineStr">
         <is>
@@ -15467,7 +15496,7 @@
       </c>
       <c r="AH143" s="2" t="n"/>
     </row>
-    <row r="144" ht="24" customHeight="1" s="49">
+    <row r="144" ht="24" customHeight="1" s="50">
       <c r="A144" s="2" t="n">
         <v>143</v>
       </c>
@@ -15569,7 +15598,7 @@
       <c r="AG144" s="2" t="n"/>
       <c r="AH144" s="2" t="n"/>
     </row>
-    <row r="145" ht="24" customHeight="1" s="49">
+    <row r="145" ht="24" customHeight="1" s="50">
       <c r="A145" s="2" t="n">
         <v>144</v>
       </c>
@@ -15667,7 +15696,7 @@
       <c r="AG145" s="2" t="n"/>
       <c r="AH145" s="2" t="n"/>
     </row>
-    <row r="146" ht="24" customHeight="1" s="49">
+    <row r="146" ht="24" customHeight="1" s="50">
       <c r="A146" s="2" t="n">
         <v>145</v>
       </c>
@@ -15713,13 +15742,13 @@
       </c>
       <c r="N146" s="2" t="n"/>
       <c r="O146" s="32" t="n">
-        <v>23.9</v>
+        <v>24.9</v>
       </c>
       <c r="P146" s="32" t="n">
-        <v>30.7</v>
+        <v>31.7</v>
       </c>
       <c r="Q146" s="32" t="n">
-        <v>27.11</v>
+        <v>28.31</v>
       </c>
       <c r="R146" s="23" t="inlineStr">
         <is>
@@ -15775,7 +15804,7 @@
       <c r="AG146" s="2" t="n"/>
       <c r="AH146" s="2" t="n"/>
     </row>
-    <row r="147" ht="24" customHeight="1" s="49">
+    <row r="147" ht="24" customHeight="1" s="50">
       <c r="A147" s="2" t="n">
         <v>146</v>
       </c>
@@ -15821,13 +15850,13 @@
       </c>
       <c r="N147" s="2" t="n"/>
       <c r="O147" s="32" t="n">
-        <v>23.2</v>
+        <v>21.9</v>
       </c>
       <c r="P147" s="32" t="n">
-        <v>29.8</v>
+        <v>30</v>
       </c>
       <c r="Q147" s="32" t="n">
-        <v>25.59</v>
+        <v>24.54</v>
       </c>
       <c r="R147" s="23" t="inlineStr">
         <is>
@@ -15891,7 +15920,7 @@
       </c>
       <c r="AH147" s="2" t="n"/>
     </row>
-    <row r="148" ht="24" customHeight="1" s="49">
+    <row r="148" ht="24" customHeight="1" s="50">
       <c r="A148" s="2" t="n">
         <v>147</v>
       </c>
@@ -15937,13 +15966,19 @@
       </c>
       <c r="N148" s="2" t="n"/>
       <c r="O148" s="32" t="n">
-        <v>22.4</v>
+        <v>20.3</v>
       </c>
       <c r="P148" s="32" t="n">
-        <v>37.5</v>
-      </c>
-      <c r="Q148" s="32" t="n"/>
-      <c r="R148" s="23" t="n"/>
+        <v>25</v>
+      </c>
+      <c r="Q148" s="32" t="n">
+        <v>21.99</v>
+      </c>
+      <c r="R148" s="23" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="S148" s="37" t="n"/>
       <c r="T148" s="41" t="inlineStr">
         <is>
@@ -15997,7 +16032,7 @@
       </c>
       <c r="AH148" s="2" t="n"/>
     </row>
-    <row r="149" ht="24" customHeight="1" s="49">
+    <row r="149" ht="24" customHeight="1" s="50">
       <c r="A149" s="2" t="n">
         <v>148</v>
       </c>
@@ -16043,13 +16078,13 @@
       </c>
       <c r="N149" s="2" t="n"/>
       <c r="O149" s="32" t="n">
-        <v>12.6</v>
+        <v>13.6</v>
       </c>
       <c r="P149" s="32" t="n">
-        <v>26.1</v>
+        <v>19.5</v>
       </c>
       <c r="Q149" s="32" t="n">
-        <v>18.76</v>
+        <v>15.55</v>
       </c>
       <c r="R149" s="23" t="inlineStr">
         <is>
@@ -16113,7 +16148,7 @@
       </c>
       <c r="AH149" s="2" t="n"/>
     </row>
-    <row r="150" ht="24" customHeight="1" s="49">
+    <row r="150" ht="24" customHeight="1" s="50">
       <c r="A150" s="2" t="n">
         <v>149</v>
       </c>
@@ -16159,13 +16194,13 @@
       </c>
       <c r="N150" s="2" t="n"/>
       <c r="O150" s="32" t="n">
-        <v>15.4</v>
+        <v>13.6</v>
       </c>
       <c r="P150" s="32" t="n">
-        <v>23</v>
+        <v>20.1</v>
       </c>
       <c r="Q150" s="32" t="n">
-        <v>17.93</v>
+        <v>16.69</v>
       </c>
       <c r="R150" s="23" t="inlineStr">
         <is>
@@ -16229,7 +16264,7 @@
       </c>
       <c r="AH150" s="2" t="n"/>
     </row>
-    <row r="151" ht="24" customHeight="1" s="49">
+    <row r="151" ht="24" customHeight="1" s="50">
       <c r="A151" s="2" t="n">
         <v>150</v>
       </c>
@@ -16275,10 +16310,10 @@
       </c>
       <c r="N151" s="2" t="n"/>
       <c r="O151" s="32" t="n">
-        <v>18.2</v>
+        <v>16.7</v>
       </c>
       <c r="P151" s="32" t="n">
-        <v>25.5</v>
+        <v>24.2</v>
       </c>
       <c r="Q151" s="32" t="n">
         <v>19.96</v>
@@ -16341,7 +16376,7 @@
       </c>
       <c r="AH151" s="2" t="n"/>
     </row>
-    <row r="152" ht="24" customHeight="1" s="49">
+    <row r="152" ht="24" customHeight="1" s="50">
       <c r="A152" s="2" t="n">
         <v>151</v>
       </c>
@@ -16435,7 +16470,7 @@
       </c>
       <c r="AH152" s="2" t="n"/>
     </row>
-    <row r="153" ht="24" customHeight="1" s="49">
+    <row r="153" ht="24" customHeight="1" s="50">
       <c r="A153" s="2" t="n">
         <v>152</v>
       </c>
@@ -16481,13 +16516,13 @@
       </c>
       <c r="N153" s="2" t="n"/>
       <c r="O153" s="32" t="n">
-        <v>16.3</v>
+        <v>14.8</v>
       </c>
       <c r="P153" s="32" t="n">
-        <v>22.8</v>
+        <v>24.9</v>
       </c>
       <c r="Q153" s="32" t="n">
-        <v>19.79</v>
+        <v>18.96</v>
       </c>
       <c r="R153" s="23" t="inlineStr">
         <is>
@@ -16555,7 +16590,7 @@
         </is>
       </c>
     </row>
-    <row r="154" ht="24" customHeight="1" s="49">
+    <row r="154" ht="24" customHeight="1" s="50">
       <c r="A154" s="2" t="n">
         <v>153</v>
       </c>
@@ -16601,13 +16636,13 @@
       </c>
       <c r="N154" s="2" t="n"/>
       <c r="O154" s="32" t="n">
-        <v>4</v>
+        <v>2.4</v>
       </c>
       <c r="P154" s="32" t="n">
-        <v>20</v>
+        <v>13.9</v>
       </c>
       <c r="Q154" s="32" t="n">
-        <v>11.45</v>
+        <v>8.1</v>
       </c>
       <c r="R154" s="23" t="inlineStr">
         <is>
@@ -16671,7 +16706,7 @@
       </c>
       <c r="AH154" s="2" t="n"/>
     </row>
-    <row r="155" ht="24" customHeight="1" s="49">
+    <row r="155" ht="24" customHeight="1" s="50">
       <c r="A155" s="2" t="n">
         <v>154</v>
       </c>
@@ -16765,7 +16800,7 @@
       </c>
       <c r="AH155" s="2" t="n"/>
     </row>
-    <row r="156" ht="24" customHeight="1" s="49">
+    <row r="156" ht="24" customHeight="1" s="50">
       <c r="A156" s="2" t="n">
         <v>155</v>
       </c>
@@ -16802,12 +16837,8 @@
         </is>
       </c>
       <c r="N156" s="2" t="n"/>
-      <c r="O156" s="32" t="n">
-        <v>-9.699999999999999</v>
-      </c>
-      <c r="P156" s="32" t="n">
-        <v>13.7</v>
-      </c>
+      <c r="O156" s="32" t="n"/>
+      <c r="P156" s="32" t="n"/>
       <c r="Q156" s="32" t="n"/>
       <c r="R156" s="23" t="n"/>
       <c r="S156" s="37" t="n"/>
@@ -16867,7 +16898,7 @@
       <c r="AG156" s="2" t="n"/>
       <c r="AH156" s="2" t="n"/>
     </row>
-    <row r="157" ht="24" customHeight="1" s="49">
+    <row r="157" ht="24" customHeight="1" s="50">
       <c r="A157" s="2" t="n">
         <v>156</v>
       </c>
@@ -16904,12 +16935,8 @@
         </is>
       </c>
       <c r="N157" s="2" t="n"/>
-      <c r="O157" s="32" t="n">
-        <v>14.8</v>
-      </c>
-      <c r="P157" s="32" t="n">
-        <v>22</v>
-      </c>
+      <c r="O157" s="32" t="n"/>
+      <c r="P157" s="32" t="n"/>
       <c r="Q157" s="32" t="n"/>
       <c r="R157" s="23" t="inlineStr">
         <is>
@@ -16973,7 +17000,7 @@
       </c>
       <c r="AH157" s="2" t="n"/>
     </row>
-    <row r="158" ht="24" customHeight="1" s="49">
+    <row r="158" ht="24" customHeight="1" s="50">
       <c r="A158" s="2" t="n">
         <v>157</v>
       </c>
@@ -17067,7 +17094,7 @@
       </c>
       <c r="AH158" s="2" t="n"/>
     </row>
-    <row r="159" ht="24" customHeight="1" s="49">
+    <row r="159" ht="24" customHeight="1" s="50">
       <c r="A159" s="2" t="n">
         <v>158</v>
       </c>
@@ -17161,7 +17188,7 @@
       </c>
       <c r="AH159" s="2" t="n"/>
     </row>
-    <row r="160" ht="24" customHeight="1" s="49">
+    <row r="160" ht="24" customHeight="1" s="50">
       <c r="A160" s="2" t="n">
         <v>159</v>
       </c>
@@ -17255,7 +17282,7 @@
       </c>
       <c r="AH160" s="2" t="n"/>
     </row>
-    <row r="161" ht="24" customHeight="1" s="49">
+    <row r="161" ht="24" customHeight="1" s="50">
       <c r="A161" s="2" t="n">
         <v>160</v>
       </c>
@@ -17292,12 +17319,8 @@
         </is>
       </c>
       <c r="N161" s="2" t="n"/>
-      <c r="O161" s="32" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="P161" s="32" t="n">
-        <v>18.5</v>
-      </c>
+      <c r="O161" s="32" t="n"/>
+      <c r="P161" s="32" t="n"/>
       <c r="Q161" s="32" t="n"/>
       <c r="R161" s="23" t="inlineStr">
         <is>
@@ -17365,7 +17388,7 @@
         </is>
       </c>
     </row>
-    <row r="162" ht="24" customHeight="1" s="49">
+    <row r="162" ht="24" customHeight="1" s="50">
       <c r="A162" s="2" t="n">
         <v>161</v>
       </c>
@@ -17407,10 +17430,10 @@
         </is>
       </c>
       <c r="O162" s="32" t="n">
-        <v>-4.7</v>
+        <v>-3.2</v>
       </c>
       <c r="P162" s="32" t="n">
-        <v>3.3</v>
+        <v>10</v>
       </c>
       <c r="Q162" s="32" t="n"/>
       <c r="R162" s="23" t="inlineStr">
@@ -17421,7 +17444,7 @@
       <c r="S162" s="37" t="n"/>
       <c r="T162" s="41" t="inlineStr">
         <is>
-          <t>大兴安岭</t>
+          <t>黑龙江大兴安岭</t>
         </is>
       </c>
       <c r="U162" s="2" t="inlineStr">
@@ -17479,7 +17502,7 @@
         </is>
       </c>
     </row>
-    <row r="163" ht="24" customHeight="1" s="49">
+    <row r="163" ht="24" customHeight="1" s="50">
       <c r="A163" s="2" t="n">
         <v>162</v>
       </c>
@@ -17527,7 +17550,7 @@
       <c r="S163" s="37" t="n"/>
       <c r="T163" s="41" t="inlineStr">
         <is>
-          <t>国内最低气温记录&lt;br&gt;大兴安岭</t>
+          <t>国内最低气温记录&lt;br&gt;黑龙江大兴安岭</t>
         </is>
       </c>
       <c r="U163" s="2" t="inlineStr">
@@ -17581,7 +17604,7 @@
       </c>
       <c r="AH163" s="2" t="n"/>
     </row>
-    <row r="164" ht="24" customHeight="1" s="49">
+    <row r="164" ht="24" customHeight="1" s="50">
       <c r="A164" s="2" t="n">
         <v>163</v>
       </c>
@@ -17633,7 +17656,7 @@
       <c r="S164" s="37" t="n"/>
       <c r="T164" s="41" t="inlineStr">
         <is>
-          <t>国内昼温王</t>
+          <t>国内昼温王&lt;br&gt;呼伦贝尔额尔古纳</t>
         </is>
       </c>
       <c r="U164" s="2" t="inlineStr">
@@ -17691,7 +17714,7 @@
       </c>
       <c r="AH164" s="2" t="n"/>
     </row>
-    <row r="165" ht="24" customHeight="1" s="49">
+    <row r="165" ht="24" customHeight="1" s="50">
       <c r="A165" s="2" t="n">
         <v>164</v>
       </c>
@@ -17793,7 +17816,7 @@
       </c>
       <c r="AH165" s="2" t="n"/>
     </row>
-    <row r="166" ht="24" customHeight="1" s="49">
+    <row r="166" ht="24" customHeight="1" s="50">
       <c r="A166" s="2" t="n">
         <v>165</v>
       </c>
@@ -17845,7 +17868,7 @@
       <c r="S166" s="37" t="n"/>
       <c r="T166" s="41" t="inlineStr">
         <is>
-          <t>内蒙古最低记录</t>
+          <t>内蒙古最低记录&lt;br&gt;呼伦贝尔额尔古纳</t>
         </is>
       </c>
       <c r="U166" s="2" t="inlineStr">
@@ -17903,7 +17926,7 @@
         </is>
       </c>
     </row>
-    <row r="167" ht="24" customHeight="1" s="49">
+    <row r="167" ht="24" customHeight="1" s="50">
       <c r="A167" s="2" t="n">
         <v>166</v>
       </c>
@@ -17951,7 +17974,7 @@
       <c r="S167" s="37" t="n"/>
       <c r="T167" s="41" t="inlineStr">
         <is>
-          <t>呼伦贝尔</t>
+          <t>呼伦贝尔根河</t>
         </is>
       </c>
       <c r="U167" s="2" t="inlineStr">
@@ -18005,7 +18028,7 @@
       </c>
       <c r="AH167" s="2" t="n"/>
     </row>
-    <row r="168" ht="24" customHeight="1" s="49">
+    <row r="168" ht="24" customHeight="1" s="50">
       <c r="A168" s="2" t="n">
         <v>167</v>
       </c>
@@ -18115,7 +18138,7 @@
       </c>
       <c r="AH168" s="2" t="n"/>
     </row>
-    <row r="169" ht="24" customHeight="1" s="49">
+    <row r="169" ht="24" customHeight="1" s="50">
       <c r="A169" s="2" t="n">
         <v>168</v>
       </c>
@@ -18225,7 +18248,7 @@
       </c>
       <c r="AH169" s="2" t="n"/>
     </row>
-    <row r="170" ht="24" customHeight="1" s="49">
+    <row r="170" ht="24" customHeight="1" s="50">
       <c r="A170" s="2" t="n">
         <v>169</v>
       </c>
@@ -18267,10 +18290,10 @@
         </is>
       </c>
       <c r="O170" s="32" t="n">
-        <v>-19.1</v>
+        <v>-6.1</v>
       </c>
       <c r="P170" s="32" t="n">
-        <v>2.2</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="Q170" s="32" t="n"/>
       <c r="R170" s="23" t="inlineStr">
@@ -18339,7 +18362,7 @@
         </is>
       </c>
     </row>
-    <row r="171" ht="24" customHeight="1" s="49">
+    <row r="171" ht="24" customHeight="1" s="50">
       <c r="A171" s="2" t="n">
         <v>170</v>
       </c>
@@ -18377,10 +18400,10 @@
       </c>
       <c r="N171" s="2" t="n"/>
       <c r="O171" s="32" t="n">
-        <v>-8.4</v>
+        <v>-1.5</v>
       </c>
       <c r="P171" s="32" t="n">
-        <v>-1.4</v>
+        <v>7.3</v>
       </c>
       <c r="Q171" s="32" t="n"/>
       <c r="R171" s="23" t="inlineStr">
@@ -18449,7 +18472,7 @@
         </is>
       </c>
     </row>
-    <row r="172" ht="24" customHeight="1" s="49">
+    <row r="172" ht="24" customHeight="1" s="50">
       <c r="A172" s="2" t="n">
         <v>171</v>
       </c>
@@ -18555,7 +18578,7 @@
       </c>
       <c r="AH172" s="2" t="n"/>
     </row>
-    <row r="173" ht="24" customHeight="1" s="49">
+    <row r="173" ht="24" customHeight="1" s="50">
       <c r="A173" s="2" t="n">
         <v>172</v>
       </c>
@@ -18593,10 +18616,10 @@
       </c>
       <c r="N173" s="2" t="n"/>
       <c r="O173" s="32" t="n">
-        <v>-7.9</v>
+        <v>-0.5</v>
       </c>
       <c r="P173" s="32" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="Q173" s="32" t="n"/>
       <c r="R173" s="23" t="inlineStr">
@@ -18661,7 +18684,7 @@
       <c r="AG173" s="2" t="n"/>
       <c r="AH173" s="2" t="n"/>
     </row>
-    <row r="174" ht="24" customHeight="1" s="49">
+    <row r="174" ht="24" customHeight="1" s="50">
       <c r="A174" s="2" t="n">
         <v>173</v>
       </c>
@@ -18767,7 +18790,7 @@
         </is>
       </c>
     </row>
-    <row r="175" ht="24" customHeight="1" s="49">
+    <row r="175" ht="24" customHeight="1" s="50">
       <c r="A175" s="2" t="n">
         <v>174</v>
       </c>
@@ -18815,7 +18838,7 @@
       <c r="S175" s="37" t="n"/>
       <c r="T175" s="41" t="inlineStr">
         <is>
-          <t>四川 川西</t>
+          <t>四川西部青藏高原&lt;br&gt;石渠</t>
         </is>
       </c>
       <c r="U175" s="2" t="inlineStr">
@@ -18869,7 +18892,7 @@
       </c>
       <c r="AH175" s="2" t="n"/>
     </row>
-    <row r="176" ht="24" customHeight="1" s="49">
+    <row r="176" ht="24" customHeight="1" s="50">
       <c r="A176" s="2" t="n">
         <v>175</v>
       </c>
@@ -18915,12 +18938,14 @@
       </c>
       <c r="N176" s="2" t="n"/>
       <c r="O176" s="32" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="P176" s="32" t="n">
-        <v>17.7</v>
-      </c>
-      <c r="Q176" s="32" t="n"/>
+        <v>12.6</v>
+      </c>
+      <c r="Q176" s="32" t="n">
+        <v>10.5</v>
+      </c>
       <c r="R176" s="23" t="inlineStr">
         <is>
           <t>Y</t>
@@ -18979,7 +19004,7 @@
         </is>
       </c>
     </row>
-    <row r="177" ht="24" customHeight="1" s="49">
+    <row r="177" ht="24" customHeight="1" s="50">
       <c r="A177" s="2" t="n">
         <v>176</v>
       </c>
@@ -19017,12 +19042,14 @@
       </c>
       <c r="N177" s="2" t="n"/>
       <c r="O177" s="32" t="n">
-        <v>-12.8</v>
+        <v>-5.7</v>
       </c>
       <c r="P177" s="32" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="Q177" s="32" t="n"/>
+        <v>0.6</v>
+      </c>
+      <c r="Q177" s="32" t="n">
+        <v>-3.12</v>
+      </c>
       <c r="R177" s="23" t="inlineStr">
         <is>
           <t>Y</t>
@@ -19093,7 +19120,7 @@
         </is>
       </c>
     </row>
-    <row r="178" ht="24" customHeight="1" s="49">
+    <row r="178" ht="24" customHeight="1" s="50">
       <c r="A178" s="2" t="n">
         <v>177</v>
       </c>
@@ -19203,7 +19230,7 @@
         </is>
       </c>
     </row>
-    <row r="179" ht="24" customHeight="1" s="49">
+    <row r="179" ht="24" customHeight="1" s="50">
       <c r="A179" s="2" t="n">
         <v>178</v>
       </c>
@@ -19309,7 +19336,7 @@
         </is>
       </c>
     </row>
-    <row r="180" ht="24" customHeight="1" s="49">
+    <row r="180" ht="24" customHeight="1" s="50">
       <c r="A180" s="2" t="n">
         <v>179</v>
       </c>
@@ -19411,7 +19438,7 @@
         </is>
       </c>
     </row>
-    <row r="181" ht="24" customHeight="1" s="49">
+    <row r="181" ht="24" customHeight="1" s="50">
       <c r="A181" s="2" t="n">
         <v>180</v>
       </c>
@@ -19509,7 +19536,7 @@
         </is>
       </c>
     </row>
-    <row r="182" ht="24" customHeight="1" s="49">
+    <row r="182" ht="24" customHeight="1" s="50">
       <c r="A182" s="2" t="n">
         <v>181</v>
       </c>
@@ -19595,7 +19622,7 @@
       <c r="AG182" s="2" t="n"/>
       <c r="AH182" s="2" t="n"/>
     </row>
-    <row r="183" ht="24" customHeight="1" s="49">
+    <row r="183" ht="24" customHeight="1" s="50">
       <c r="A183" s="2" t="n">
         <v>182</v>
       </c>
@@ -19677,7 +19704,7 @@
       <c r="AG183" s="2" t="n"/>
       <c r="AH183" s="2" t="n"/>
     </row>
-    <row r="184" ht="24" customHeight="1" s="49">
+    <row r="184" ht="24" customHeight="1" s="50">
       <c r="A184" s="2" t="n">
         <v>183</v>
       </c>
@@ -19759,7 +19786,7 @@
       <c r="AG184" s="2" t="n"/>
       <c r="AH184" s="2" t="n"/>
     </row>
-    <row r="185" ht="24" customHeight="1" s="49">
+    <row r="185" ht="24" customHeight="1" s="50">
       <c r="A185" s="2" t="n">
         <v>184</v>
       </c>
@@ -19858,7 +19885,7 @@
         </is>
       </c>
     </row>
-    <row r="186" ht="24" customHeight="1" s="49">
+    <row r="186" ht="24" customHeight="1" s="50">
       <c r="A186" s="2" t="n">
         <v>185</v>
       </c>
@@ -19957,7 +19984,7 @@
         </is>
       </c>
     </row>
-    <row r="187" ht="24" customHeight="1" s="49">
+    <row r="187" ht="24" customHeight="1" s="50">
       <c r="A187" s="2" t="n">
         <v>186</v>
       </c>
@@ -20051,7 +20078,7 @@
       </c>
       <c r="AH187" s="2" t="n"/>
     </row>
-    <row r="188" ht="24" customHeight="1" s="49">
+    <row r="188" ht="24" customHeight="1" s="50">
       <c r="A188" s="2" t="n">
         <v>187</v>
       </c>
@@ -20145,7 +20172,7 @@
       </c>
       <c r="AH188" s="2" t="n"/>
     </row>
-    <row r="189" ht="24" customHeight="1" s="49">
+    <row r="189" ht="24" customHeight="1" s="50">
       <c r="A189" s="2" t="n">
         <v>188</v>
       </c>
@@ -20239,7 +20266,7 @@
       </c>
       <c r="AH189" s="2" t="n"/>
     </row>
-    <row r="190" ht="24" customHeight="1" s="49">
+    <row r="190" ht="24" customHeight="1" s="50">
       <c r="A190" s="2" t="n">
         <v>189</v>
       </c>
@@ -20333,7 +20360,7 @@
       </c>
       <c r="AH190" s="2" t="n"/>
     </row>
-    <row r="191" ht="24" customHeight="1" s="49">
+    <row r="191" ht="24" customHeight="1" s="50">
       <c r="A191" s="2" t="n">
         <v>190</v>
       </c>
@@ -20423,7 +20450,7 @@
       <c r="AG191" s="2" t="n"/>
       <c r="AH191" s="2" t="n"/>
     </row>
-    <row r="192" ht="24" customHeight="1" s="49">
+    <row r="192" ht="24" customHeight="1" s="50">
       <c r="A192" s="2" t="n">
         <v>191</v>
       </c>
@@ -20518,7 +20545,7 @@
       </c>
       <c r="AH192" s="2" t="n"/>
     </row>
-    <row r="193" ht="24" customHeight="1" s="49">
+    <row r="193" ht="24" customHeight="1" s="50">
       <c r="A193" s="2" t="n">
         <v>192</v>
       </c>
@@ -20616,7 +20643,7 @@
       </c>
       <c r="AH193" s="2" t="n"/>
     </row>
-    <row r="194" ht="24" customHeight="1" s="49">
+    <row r="194" ht="24" customHeight="1" s="50">
       <c r="A194" s="2" t="n">
         <v>193</v>
       </c>
@@ -20706,7 +20733,7 @@
       <c r="AG194" s="2" t="n"/>
       <c r="AH194" s="2" t="n"/>
     </row>
-    <row r="195" ht="24" customHeight="1" s="49">
+    <row r="195" ht="24" customHeight="1" s="50">
       <c r="A195" s="2" t="n">
         <v>194</v>
       </c>
@@ -20800,7 +20827,7 @@
       </c>
       <c r="AH195" s="2" t="n"/>
     </row>
-    <row r="196" ht="24" customHeight="1" s="49">
+    <row r="196" ht="24" customHeight="1" s="50">
       <c r="A196" s="2" t="n">
         <v>195</v>
       </c>
@@ -20894,7 +20921,7 @@
       </c>
       <c r="AH196" s="2" t="n"/>
     </row>
-    <row r="197" ht="24" customHeight="1" s="49">
+    <row r="197" ht="24" customHeight="1" s="50">
       <c r="A197" s="2" t="n">
         <v>196</v>
       </c>
@@ -20988,7 +21015,7 @@
       </c>
       <c r="AH197" s="2" t="n"/>
     </row>
-    <row r="198" ht="24" customHeight="1" s="49">
+    <row r="198" ht="24" customHeight="1" s="50">
       <c r="A198" s="2" t="n">
         <v>197</v>
       </c>
@@ -21090,7 +21117,7 @@
       </c>
       <c r="AH198" s="2" t="n"/>
     </row>
-    <row r="199" ht="24" customHeight="1" s="49">
+    <row r="199" ht="24" customHeight="1" s="50">
       <c r="A199" s="2" t="n">
         <v>198</v>
       </c>
@@ -21138,7 +21165,7 @@
       <c r="S199" s="37" t="n"/>
       <c r="T199" s="41" t="inlineStr">
         <is>
-          <t>大兴安岭</t>
+          <t>黑龙江大兴安岭</t>
         </is>
       </c>
       <c r="U199" s="2" t="inlineStr">
@@ -21188,7 +21215,7 @@
       </c>
       <c r="AH199" s="2" t="n"/>
     </row>
-    <row r="200" ht="24" customHeight="1" s="49">
+    <row r="200" ht="24" customHeight="1" s="50">
       <c r="A200" s="2" t="n">
         <v>199</v>
       </c>
@@ -21236,7 +21263,7 @@
       <c r="S200" s="37" t="n"/>
       <c r="T200" s="41" t="inlineStr">
         <is>
-          <t>黑龙江</t>
+          <t>黑龙江&lt;br&gt;黑龙江大兴安岭</t>
         </is>
       </c>
       <c r="U200" s="2" t="inlineStr">
@@ -21290,7 +21317,7 @@
       </c>
       <c r="AH200" s="2" t="n"/>
     </row>
-    <row r="201" ht="24" customHeight="1" s="49">
+    <row r="201" ht="24" customHeight="1" s="50">
       <c r="A201" s="2" t="n">
         <v>200</v>
       </c>
@@ -21338,7 +21365,7 @@
       <c r="S201" s="37" t="n"/>
       <c r="T201" s="41" t="inlineStr">
         <is>
-          <t>大兴安岭</t>
+          <t>黑龙江大兴安岭</t>
         </is>
       </c>
       <c r="U201" s="2" t="inlineStr">
@@ -21392,7 +21419,7 @@
       </c>
       <c r="AH201" s="2" t="n"/>
     </row>
-    <row r="202" ht="24" customHeight="1" s="49">
+    <row r="202" ht="24" customHeight="1" s="50">
       <c r="A202" s="2" t="n">
         <v>201</v>
       </c>
@@ -21440,7 +21467,7 @@
       <c r="S202" s="37" t="n"/>
       <c r="T202" s="41" t="inlineStr">
         <is>
-          <t>小兴安岭</t>
+          <t>小兴安岭&lt;br&gt;黑龙江伊春</t>
         </is>
       </c>
       <c r="U202" s="2" t="inlineStr">
@@ -21494,7 +21521,7 @@
       </c>
       <c r="AH202" s="2" t="n"/>
     </row>
-    <row r="203" ht="24" customHeight="1" s="49">
+    <row r="203" ht="24" customHeight="1" s="50">
       <c r="A203" s="2" t="n">
         <v>202</v>
       </c>
@@ -21596,7 +21623,7 @@
       </c>
       <c r="AH203" s="2" t="n"/>
     </row>
-    <row r="204" ht="24" customHeight="1" s="49">
+    <row r="204" ht="24" customHeight="1" s="50">
       <c r="A204" s="2" t="n">
         <v>203</v>
       </c>
@@ -21644,7 +21671,7 @@
       <c r="S204" s="37" t="n"/>
       <c r="T204" s="41" t="inlineStr">
         <is>
-          <t>大兴安岭</t>
+          <t>黑龙江大兴安岭</t>
         </is>
       </c>
       <c r="U204" s="2" t="inlineStr">
@@ -21698,7 +21725,7 @@
       </c>
       <c r="AH204" s="2" t="n"/>
     </row>
-    <row r="205" ht="24" customHeight="1" s="49">
+    <row r="205" ht="24" customHeight="1" s="50">
       <c r="A205" s="2" t="n">
         <v>204</v>
       </c>
@@ -21746,7 +21773,7 @@
       <c r="S205" s="37" t="n"/>
       <c r="T205" s="41" t="inlineStr">
         <is>
-          <t>大兴安岭</t>
+          <t>黑龙江大兴安岭</t>
         </is>
       </c>
       <c r="U205" s="2" t="inlineStr">
@@ -21800,7 +21827,7 @@
       </c>
       <c r="AH205" s="2" t="n"/>
     </row>
-    <row r="206" ht="24" customHeight="1" s="49">
+    <row r="206" ht="24" customHeight="1" s="50">
       <c r="A206" s="2" t="n">
         <v>205</v>
       </c>
@@ -21848,7 +21875,7 @@
       <c r="S206" s="37" t="n"/>
       <c r="T206" s="41" t="inlineStr">
         <is>
-          <t>大兴安岭</t>
+          <t>黑龙江大兴安岭</t>
         </is>
       </c>
       <c r="U206" s="2" t="inlineStr">
@@ -21902,7 +21929,7 @@
       </c>
       <c r="AH206" s="2" t="n"/>
     </row>
-    <row r="207" ht="24" customHeight="1" s="49">
+    <row r="207" ht="24" customHeight="1" s="50">
       <c r="A207" s="2" t="n">
         <v>206</v>
       </c>
@@ -22000,7 +22027,7 @@
       <c r="AG207" s="2" t="n"/>
       <c r="AH207" s="2" t="n"/>
     </row>
-    <row r="208" ht="24" customHeight="1" s="49">
+    <row r="208" ht="24" customHeight="1" s="50">
       <c r="A208" s="2" t="n">
         <v>207</v>
       </c>
@@ -22092,7 +22119,7 @@
       </c>
       <c r="AH208" s="2" t="n"/>
     </row>
-    <row r="209" ht="24" customHeight="1" s="49">
+    <row r="209" ht="24" customHeight="1" s="50">
       <c r="A209" s="2" t="n">
         <v>208</v>
       </c>
@@ -22194,7 +22221,7 @@
       <c r="AG209" s="2" t="n"/>
       <c r="AH209" s="2" t="n"/>
     </row>
-    <row r="210" ht="24" customHeight="1" s="49">
+    <row r="210" ht="24" customHeight="1" s="50">
       <c r="A210" s="2" t="n">
         <v>209</v>
       </c>
@@ -22242,7 +22269,7 @@
       <c r="S210" s="37" t="n"/>
       <c r="T210" s="41" t="inlineStr">
         <is>
-          <t>大兴安岭</t>
+          <t>黑龙江大兴安岭</t>
         </is>
       </c>
       <c r="U210" s="2" t="inlineStr">
@@ -22292,7 +22319,7 @@
       </c>
       <c r="AH210" s="2" t="n"/>
     </row>
-    <row r="211" ht="24" customHeight="1" s="49">
+    <row r="211" ht="24" customHeight="1" s="50">
       <c r="A211" s="2" t="n">
         <v>210</v>
       </c>
@@ -22340,7 +22367,7 @@
       <c r="S211" s="37" t="n"/>
       <c r="T211" s="41" t="inlineStr">
         <is>
-          <t>呼伦贝尔</t>
+          <t>呼伦贝尔根河</t>
         </is>
       </c>
       <c r="U211" s="2" t="inlineStr">
@@ -22394,7 +22421,7 @@
       </c>
       <c r="AH211" s="2" t="n"/>
     </row>
-    <row r="212" ht="24" customHeight="1" s="49">
+    <row r="212" ht="24" customHeight="1" s="50">
       <c r="A212" s="2" t="n">
         <v>211</v>
       </c>
@@ -22442,7 +22469,7 @@
       <c r="S212" s="37" t="n"/>
       <c r="T212" s="41" t="inlineStr">
         <is>
-          <t>呼伦贝尔</t>
+          <t>呼伦贝尔根河</t>
         </is>
       </c>
       <c r="U212" s="2" t="inlineStr">
@@ -22496,7 +22523,7 @@
       </c>
       <c r="AH212" s="2" t="n"/>
     </row>
-    <row r="213" ht="24" customHeight="1" s="49">
+    <row r="213" ht="24" customHeight="1" s="50">
       <c r="A213" s="2" t="n">
         <v>212</v>
       </c>
@@ -22598,7 +22625,7 @@
       </c>
       <c r="AH213" s="2" t="n"/>
     </row>
-    <row r="214" ht="24" customHeight="1" s="49">
+    <row r="214" ht="24" customHeight="1" s="50">
       <c r="A214" s="2" t="n">
         <v>213</v>
       </c>
@@ -22646,7 +22673,7 @@
       <c r="S214" s="37" t="n"/>
       <c r="T214" s="41" t="inlineStr">
         <is>
-          <t>呼伦贝尔</t>
+          <t>呼伦贝尔额尔古纳</t>
         </is>
       </c>
       <c r="U214" s="2" t="inlineStr">
@@ -22700,7 +22727,7 @@
       </c>
       <c r="AH214" s="2" t="n"/>
     </row>
-    <row r="215" ht="24" customHeight="1" s="49">
+    <row r="215" ht="24" customHeight="1" s="50">
       <c r="A215" s="2" t="n">
         <v>214</v>
       </c>
@@ -22737,8 +22764,12 @@
         </is>
       </c>
       <c r="N215" s="2" t="n"/>
-      <c r="O215" s="32" t="n"/>
-      <c r="P215" s="32" t="n"/>
+      <c r="O215" s="32" t="n">
+        <v>-8.4</v>
+      </c>
+      <c r="P215" s="32" t="n">
+        <v>10.5</v>
+      </c>
       <c r="Q215" s="32" t="n"/>
       <c r="R215" s="23" t="inlineStr">
         <is>
@@ -22748,7 +22779,7 @@
       <c r="S215" s="37" t="n"/>
       <c r="T215" s="41" t="inlineStr">
         <is>
-          <t>呼伦贝尔</t>
+          <t>呼伦贝尔牙克石</t>
         </is>
       </c>
       <c r="U215" s="2" t="inlineStr">
@@ -22802,7 +22833,7 @@
       </c>
       <c r="AH215" s="2" t="n"/>
     </row>
-    <row r="216" ht="24" customHeight="1" s="49">
+    <row r="216" ht="24" customHeight="1" s="50">
       <c r="A216" s="2" t="n">
         <v>215</v>
       </c>
@@ -22850,7 +22881,7 @@
       <c r="S216" s="37" t="n"/>
       <c r="T216" s="41" t="inlineStr">
         <is>
-          <t>呼伦贝尔</t>
+          <t>呼伦贝尔额尔古纳</t>
         </is>
       </c>
       <c r="U216" s="2" t="inlineStr">
@@ -22904,7 +22935,7 @@
       </c>
       <c r="AH216" s="2" t="n"/>
     </row>
-    <row r="217" ht="24" customHeight="1" s="49">
+    <row r="217" ht="24" customHeight="1" s="50">
       <c r="A217" s="2" t="n">
         <v>216</v>
       </c>
@@ -22992,7 +23023,7 @@
       </c>
       <c r="AH217" s="2" t="n"/>
     </row>
-    <row r="218" ht="24" customHeight="1" s="49">
+    <row r="218" ht="24" customHeight="1" s="50">
       <c r="A218" s="2" t="n">
         <v>217</v>
       </c>
@@ -23040,7 +23071,7 @@
       <c r="S218" s="37" t="n"/>
       <c r="T218" s="41" t="inlineStr">
         <is>
-          <t>呼伦贝尔</t>
+          <t>呼伦贝尔额尔古纳</t>
         </is>
       </c>
       <c r="U218" s="2" t="inlineStr">
@@ -23094,7 +23125,7 @@
       </c>
       <c r="AH218" s="2" t="n"/>
     </row>
-    <row r="219" ht="24" customHeight="1" s="49">
+    <row r="219" ht="24" customHeight="1" s="50">
       <c r="A219" s="2" t="n">
         <v>218</v>
       </c>
@@ -23196,7 +23227,7 @@
       </c>
       <c r="AH219" s="2" t="n"/>
     </row>
-    <row r="220" ht="24" customHeight="1" s="49">
+    <row r="220" ht="24" customHeight="1" s="50">
       <c r="A220" s="2" t="n">
         <v>219</v>
       </c>
@@ -23244,7 +23275,7 @@
       <c r="S220" s="37" t="n"/>
       <c r="T220" s="41" t="inlineStr">
         <is>
-          <t>呼伦贝尔</t>
+          <t>呼伦贝尔额尔古纳</t>
         </is>
       </c>
       <c r="U220" s="2" t="inlineStr">
@@ -23298,7 +23329,7 @@
       </c>
       <c r="AH220" s="2" t="n"/>
     </row>
-    <row r="221" ht="24" customHeight="1" s="49">
+    <row r="221" ht="24" customHeight="1" s="50">
       <c r="A221" s="2" t="n">
         <v>220</v>
       </c>
@@ -23336,7 +23367,7 @@
       <c r="S221" s="37" t="n"/>
       <c r="T221" s="41" t="inlineStr">
         <is>
-          <t>呼伦贝尔</t>
+          <t>呼伦贝尔额尔古纳</t>
         </is>
       </c>
       <c r="U221" s="2" t="inlineStr">
@@ -23390,7 +23421,7 @@
       </c>
       <c r="AH221" s="2" t="n"/>
     </row>
-    <row r="222" ht="24" customHeight="1" s="49">
+    <row r="222" ht="24" customHeight="1" s="50">
       <c r="A222" s="2" t="n">
         <v>221</v>
       </c>
@@ -23436,7 +23467,7 @@
       <c r="S222" s="37" t="n"/>
       <c r="T222" s="41" t="inlineStr">
         <is>
-          <t>呼伦贝尔</t>
+          <t>呼伦贝尔鄂伦春</t>
         </is>
       </c>
       <c r="U222" s="2" t="inlineStr">
@@ -23490,7 +23521,7 @@
       </c>
       <c r="AH222" s="2" t="n"/>
     </row>
-    <row r="223" ht="24" customHeight="1" s="49">
+    <row r="223" ht="24" customHeight="1" s="50">
       <c r="A223" s="2" t="n">
         <v>222</v>
       </c>
@@ -23538,7 +23569,7 @@
       <c r="S223" s="37" t="n"/>
       <c r="T223" s="41" t="inlineStr">
         <is>
-          <t>呼伦贝尔</t>
+          <t>呼伦贝尔根河</t>
         </is>
       </c>
       <c r="U223" s="2" t="inlineStr">
@@ -23592,7 +23623,7 @@
       </c>
       <c r="AH223" s="2" t="n"/>
     </row>
-    <row r="224" ht="24" customHeight="1" s="49">
+    <row r="224" ht="24" customHeight="1" s="50">
       <c r="A224" s="2" t="n">
         <v>223</v>
       </c>
@@ -23640,7 +23671,7 @@
       <c r="S224" s="37" t="n"/>
       <c r="T224" s="41" t="inlineStr">
         <is>
-          <t>呼伦贝尔</t>
+          <t>呼伦贝尔额尔古纳</t>
         </is>
       </c>
       <c r="U224" s="2" t="inlineStr">
@@ -23694,7 +23725,7 @@
       </c>
       <c r="AH224" s="2" t="n"/>
     </row>
-    <row r="225" ht="24" customHeight="1" s="49">
+    <row r="225" ht="24" customHeight="1" s="50">
       <c r="A225" s="2" t="n">
         <v>224</v>
       </c>
@@ -23796,7 +23827,7 @@
       </c>
       <c r="AH225" s="2" t="n"/>
     </row>
-    <row r="226" ht="24" customHeight="1" s="49">
+    <row r="226" ht="24" customHeight="1" s="50">
       <c r="A226" s="2" t="n">
         <v>225</v>
       </c>
@@ -23898,7 +23929,7 @@
       <c r="AG226" s="2" t="n"/>
       <c r="AH226" s="2" t="n"/>
     </row>
-    <row r="227" ht="24" customHeight="1" s="49">
+    <row r="227" ht="24" customHeight="1" s="50">
       <c r="A227" s="2" t="n">
         <v>226</v>
       </c>
@@ -24000,7 +24031,7 @@
       </c>
       <c r="AH227" s="2" t="n"/>
     </row>
-    <row r="228" ht="24" customHeight="1" s="49">
+    <row r="228" ht="24" customHeight="1" s="50">
       <c r="A228" s="2" t="n">
         <v>227</v>
       </c>
@@ -24052,7 +24083,7 @@
       <c r="S228" s="37" t="n"/>
       <c r="T228" s="41" t="inlineStr">
         <is>
-          <t>呼伦贝尔</t>
+          <t>呼伦贝尔鄂伦春</t>
         </is>
       </c>
       <c r="U228" s="2" t="inlineStr">
@@ -24106,7 +24137,7 @@
       </c>
       <c r="AH228" s="2" t="n"/>
     </row>
-    <row r="229" ht="24" customHeight="1" s="49">
+    <row r="229" ht="24" customHeight="1" s="50">
       <c r="A229" s="2" t="n">
         <v>228</v>
       </c>
@@ -24148,7 +24179,7 @@
       <c r="S229" s="37" t="n"/>
       <c r="T229" s="41" t="inlineStr">
         <is>
-          <t>呼伦贝尔</t>
+          <t>呼伦贝尔额尔古纳</t>
         </is>
       </c>
       <c r="U229" s="2" t="inlineStr">
@@ -24202,7 +24233,7 @@
       </c>
       <c r="AH229" s="2" t="n"/>
     </row>
-    <row r="230" ht="24" customHeight="1" s="49">
+    <row r="230" ht="24" customHeight="1" s="50">
       <c r="A230" s="2" t="n">
         <v>229</v>
       </c>
@@ -24233,12 +24264,8 @@
         </is>
       </c>
       <c r="N230" s="2" t="n"/>
-      <c r="O230" s="32" t="n">
-        <v>-8.9</v>
-      </c>
-      <c r="P230" s="32" t="n">
-        <v>0.9</v>
-      </c>
+      <c r="O230" s="32" t="n"/>
+      <c r="P230" s="32" t="n"/>
       <c r="Q230" s="32" t="n"/>
       <c r="R230" s="23" t="inlineStr">
         <is>
@@ -24302,7 +24329,7 @@
       </c>
       <c r="AH230" s="2" t="n"/>
     </row>
-    <row r="231" ht="24" customHeight="1" s="49">
+    <row r="231" ht="24" customHeight="1" s="50">
       <c r="A231" s="2" t="n">
         <v>230</v>
       </c>
@@ -24390,7 +24417,7 @@
       </c>
       <c r="AH231" s="2" t="n"/>
     </row>
-    <row r="232" ht="24" customHeight="1" s="49">
+    <row r="232" ht="24" customHeight="1" s="50">
       <c r="A232" s="2" t="n">
         <v>231</v>
       </c>
@@ -24428,7 +24455,7 @@
       <c r="S232" s="37" t="n"/>
       <c r="T232" s="41" t="inlineStr">
         <is>
-          <t>呼伦贝尔</t>
+          <t>呼伦贝尔额尔古纳</t>
         </is>
       </c>
       <c r="U232" s="2" t="inlineStr">
@@ -24482,7 +24509,7 @@
       </c>
       <c r="AH232" s="2" t="n"/>
     </row>
-    <row r="233" ht="24" customHeight="1" s="49">
+    <row r="233" ht="24" customHeight="1" s="50">
       <c r="A233" s="2" t="n">
         <v>232</v>
       </c>
@@ -24520,7 +24547,7 @@
       <c r="S233" s="37" t="n"/>
       <c r="T233" s="41" t="inlineStr">
         <is>
-          <t>呼伦贝尔</t>
+          <t>呼伦贝尔额尔古纳</t>
         </is>
       </c>
       <c r="U233" s="2" t="inlineStr">
@@ -24574,7 +24601,7 @@
       </c>
       <c r="AH233" s="2" t="n"/>
     </row>
-    <row r="234" ht="24" customHeight="1" s="49">
+    <row r="234" ht="24" customHeight="1" s="50">
       <c r="A234" s="2" t="n">
         <v>233</v>
       </c>
@@ -24616,7 +24643,7 @@
       <c r="S234" s="37" t="n"/>
       <c r="T234" s="41" t="inlineStr">
         <is>
-          <t>呼伦贝尔</t>
+          <t>呼伦贝尔额尔古纳</t>
         </is>
       </c>
       <c r="U234" s="2" t="inlineStr">
@@ -24670,7 +24697,7 @@
       </c>
       <c r="AH234" s="2" t="n"/>
     </row>
-    <row r="235" ht="24" customHeight="1" s="49">
+    <row r="235" ht="24" customHeight="1" s="50">
       <c r="A235" s="2" t="n">
         <v>234</v>
       </c>
@@ -24712,7 +24739,7 @@
       <c r="S235" s="37" t="n"/>
       <c r="T235" s="41" t="inlineStr">
         <is>
-          <t>呼伦贝尔</t>
+          <t>呼伦贝尔额尔古纳</t>
         </is>
       </c>
       <c r="U235" s="2" t="inlineStr">
@@ -24766,7 +24793,7 @@
       </c>
       <c r="AH235" s="2" t="n"/>
     </row>
-    <row r="236" ht="24" customHeight="1" s="49">
+    <row r="236" ht="24" customHeight="1" s="50">
       <c r="A236" s="2" t="n">
         <v>235</v>
       </c>
@@ -24858,7 +24885,7 @@
       </c>
       <c r="AH236" s="2" t="n"/>
     </row>
-    <row r="237" ht="24" customHeight="1" s="49">
+    <row r="237" ht="24" customHeight="1" s="50">
       <c r="A237" s="2" t="n">
         <v>236</v>
       </c>
@@ -24960,7 +24987,7 @@
       </c>
       <c r="AH237" s="2" t="n"/>
     </row>
-    <row r="238" ht="24" customHeight="1" s="49">
+    <row r="238" ht="24" customHeight="1" s="50">
       <c r="A238" s="2" t="n">
         <v>237</v>
       </c>
@@ -25062,7 +25089,7 @@
       </c>
       <c r="AH238" s="2" t="n"/>
     </row>
-    <row r="239" ht="24" customHeight="1" s="49">
+    <row r="239" ht="24" customHeight="1" s="50">
       <c r="A239" s="2" t="n">
         <v>238</v>
       </c>
@@ -25160,7 +25187,7 @@
       <c r="AG239" s="2" t="n"/>
       <c r="AH239" s="2" t="n"/>
     </row>
-    <row r="240" ht="24" customHeight="1" s="49">
+    <row r="240" ht="24" customHeight="1" s="50">
       <c r="A240" s="2" t="n">
         <v>239</v>
       </c>
@@ -25256,7 +25283,7 @@
       </c>
       <c r="AH240" s="2" t="n"/>
     </row>
-    <row r="241" ht="24" customHeight="1" s="49">
+    <row r="241" ht="24" customHeight="1" s="50">
       <c r="A241" s="2" t="n">
         <v>240</v>
       </c>
@@ -25358,7 +25385,7 @@
       </c>
       <c r="AH241" s="2" t="n"/>
     </row>
-    <row r="242" ht="24" customHeight="1" s="49">
+    <row r="242" ht="24" customHeight="1" s="50">
       <c r="A242" s="2" t="n">
         <v>241</v>
       </c>
@@ -25448,7 +25475,7 @@
       <c r="AG242" s="2" t="n"/>
       <c r="AH242" s="2" t="n"/>
     </row>
-    <row r="243" ht="24" customHeight="1" s="49">
+    <row r="243" ht="24" customHeight="1" s="50">
       <c r="A243" s="2" t="n">
         <v>242</v>
       </c>
@@ -25546,7 +25573,7 @@
       <c r="AG243" s="2" t="n"/>
       <c r="AH243" s="2" t="n"/>
     </row>
-    <row r="244" ht="24" customHeight="1" s="49">
+    <row r="244" ht="24" customHeight="1" s="50">
       <c r="A244" s="2" t="n">
         <v>243</v>
       </c>
@@ -25642,7 +25669,7 @@
       </c>
       <c r="AH244" s="2" t="n"/>
     </row>
-    <row r="245" ht="24" customHeight="1" s="49">
+    <row r="245" ht="24" customHeight="1" s="50">
       <c r="A245" s="2" t="n">
         <v>244</v>
       </c>
@@ -25734,7 +25761,7 @@
       <c r="AG245" s="2" t="n"/>
       <c r="AH245" s="2" t="n"/>
     </row>
-    <row r="246" ht="24" customHeight="1" s="49">
+    <row r="246" ht="24" customHeight="1" s="50">
       <c r="A246" s="2" t="n">
         <v>245</v>
       </c>
@@ -25822,7 +25849,7 @@
       <c r="AG246" s="2" t="n"/>
       <c r="AH246" s="2" t="n"/>
     </row>
-    <row r="247" ht="24" customHeight="1" s="49">
+    <row r="247" ht="24" customHeight="1" s="50">
       <c r="A247" s="2" t="n">
         <v>246</v>
       </c>
@@ -25924,7 +25951,7 @@
       <c r="AG247" s="2" t="n"/>
       <c r="AH247" s="2" t="n"/>
     </row>
-    <row r="248" ht="24" customHeight="1" s="49">
+    <row r="248" ht="24" customHeight="1" s="50">
       <c r="A248" s="2" t="n">
         <v>247</v>
       </c>
@@ -26026,7 +26053,7 @@
       </c>
       <c r="AH248" s="2" t="n"/>
     </row>
-    <row r="249" ht="24" customHeight="1" s="49">
+    <row r="249" ht="24" customHeight="1" s="50">
       <c r="A249" s="2" t="n">
         <v>248</v>
       </c>
@@ -26128,7 +26155,7 @@
       <c r="AG249" s="2" t="n"/>
       <c r="AH249" s="2" t="n"/>
     </row>
-    <row r="250" ht="24" customHeight="1" s="49">
+    <row r="250" ht="24" customHeight="1" s="50">
       <c r="A250" s="2" t="n">
         <v>249</v>
       </c>
@@ -26234,7 +26261,7 @@
       </c>
       <c r="AH250" s="2" t="n"/>
     </row>
-    <row r="251" ht="24" customHeight="1" s="49">
+    <row r="251" ht="24" customHeight="1" s="50">
       <c r="A251" s="2" t="n">
         <v>250</v>
       </c>
@@ -26328,13 +26355,13 @@
       <c r="AG251" s="2" t="n"/>
       <c r="AH251" s="2" t="n"/>
     </row>
-    <row r="252" ht="24" customHeight="1" s="49">
+    <row r="252" ht="24" customHeight="1" s="50">
       <c r="A252" s="2" t="n">
         <v>251</v>
       </c>
       <c r="B252" s="2" t="inlineStr">
         <is>
-          <t>ogimet</t>
+          <t>rp5</t>
         </is>
       </c>
       <c r="C252" s="46" t="n">
@@ -26430,7 +26457,7 @@
       <c r="AG252" s="2" t="n"/>
       <c r="AH252" s="2" t="n"/>
     </row>
-    <row r="253" ht="24" customHeight="1" s="49">
+    <row r="253" ht="24" customHeight="1" s="50">
       <c r="A253" s="2" t="n">
         <v>252</v>
       </c>
@@ -26516,7 +26543,7 @@
       <c r="AG253" s="2" t="n"/>
       <c r="AH253" s="2" t="n"/>
     </row>
-    <row r="254" ht="24" customHeight="1" s="49">
+    <row r="254" ht="24" customHeight="1" s="50">
       <c r="A254" s="2" t="n">
         <v>253</v>
       </c>
@@ -26610,7 +26637,7 @@
       <c r="AG254" s="2" t="n"/>
       <c r="AH254" s="2" t="n"/>
     </row>
-    <row r="255" ht="24" customHeight="1" s="49">
+    <row r="255" ht="24" customHeight="1" s="50">
       <c r="A255" s="2" t="n">
         <v>254</v>
       </c>
@@ -26704,7 +26731,7 @@
       <c r="AG255" s="2" t="n"/>
       <c r="AH255" s="2" t="n"/>
     </row>
-    <row r="256" ht="24" customHeight="1" s="49">
+    <row r="256" ht="24" customHeight="1" s="50">
       <c r="A256" s="2" t="n">
         <v>255</v>
       </c>
@@ -26802,7 +26829,7 @@
       </c>
       <c r="AH256" s="2" t="n"/>
     </row>
-    <row r="257" ht="24" customHeight="1" s="49">
+    <row r="257" ht="24" customHeight="1" s="50">
       <c r="A257" s="2" t="n">
         <v>256</v>
       </c>
@@ -26900,7 +26927,7 @@
       </c>
       <c r="AH257" s="2" t="n"/>
     </row>
-    <row r="258" ht="24" customHeight="1" s="49">
+    <row r="258" ht="24" customHeight="1" s="50">
       <c r="A258" s="2" t="n">
         <v>257</v>
       </c>
@@ -26990,7 +27017,7 @@
       <c r="AG258" s="2" t="n"/>
       <c r="AH258" s="2" t="n"/>
     </row>
-    <row r="259" ht="24" customHeight="1" s="49">
+    <row r="259" ht="24" customHeight="1" s="50">
       <c r="A259" s="2" t="n">
         <v>258</v>
       </c>
@@ -27080,7 +27107,7 @@
       <c r="AG259" s="2" t="n"/>
       <c r="AH259" s="2" t="n"/>
     </row>
-    <row r="260" ht="24" customHeight="1" s="49">
+    <row r="260" ht="24" customHeight="1" s="50">
       <c r="A260" s="2" t="n">
         <v>259</v>
       </c>
@@ -27178,7 +27205,7 @@
       </c>
       <c r="AH260" s="2" t="n"/>
     </row>
-    <row r="261" ht="24" customHeight="1" s="49">
+    <row r="261" ht="24" customHeight="1" s="50">
       <c r="A261" s="2" t="n">
         <v>260</v>
       </c>
@@ -27280,7 +27307,7 @@
       <c r="AG261" s="2" t="n"/>
       <c r="AH261" s="2" t="n"/>
     </row>
-    <row r="262" ht="24" customHeight="1" s="49">
+    <row r="262" ht="24" customHeight="1" s="50">
       <c r="A262" s="2" t="n">
         <v>261</v>
       </c>
@@ -27382,7 +27409,7 @@
       <c r="AG262" s="2" t="n"/>
       <c r="AH262" s="2" t="n"/>
     </row>
-    <row r="263" ht="24" customHeight="1" s="49">
+    <row r="263" ht="24" customHeight="1" s="50">
       <c r="A263" s="2" t="n">
         <v>262</v>
       </c>
@@ -27476,7 +27503,7 @@
       </c>
       <c r="AH263" s="2" t="n"/>
     </row>
-    <row r="264" ht="24" customHeight="1" s="49">
+    <row r="264" ht="24" customHeight="1" s="50">
       <c r="A264" s="2" t="n">
         <v>263</v>
       </c>
@@ -27582,7 +27609,7 @@
       </c>
       <c r="AH264" s="2" t="n"/>
     </row>
-    <row r="265" ht="24" customHeight="1" s="49">
+    <row r="265" ht="24" customHeight="1" s="50">
       <c r="A265" s="2" t="n">
         <v>264</v>
       </c>
@@ -27632,10 +27659,10 @@
       </c>
       <c r="N265" s="2" t="n"/>
       <c r="O265" s="32" t="n">
-        <v>-62.8</v>
+        <v>-60.2</v>
       </c>
       <c r="P265" s="32" t="n">
-        <v>-52.7</v>
+        <v>-55.1</v>
       </c>
       <c r="Q265" s="32" t="n"/>
       <c r="R265" s="23" t="inlineStr">
@@ -27684,7 +27711,7 @@
       </c>
       <c r="AH265" s="2" t="n"/>
     </row>
-    <row r="266" ht="24" customHeight="1" s="49">
+    <row r="266" ht="24" customHeight="1" s="50">
       <c r="A266" s="2" t="n">
         <v>265</v>
       </c>
@@ -27776,7 +27803,7 @@
       <c r="AG266" s="2" t="n"/>
       <c r="AH266" s="2" t="n"/>
     </row>
-    <row r="267" ht="24" customHeight="1" s="49">
+    <row r="267" ht="24" customHeight="1" s="50">
       <c r="A267" s="2" t="n">
         <v>266</v>
       </c>
@@ -27862,7 +27889,7 @@
       <c r="AG267" s="2" t="n"/>
       <c r="AH267" s="2" t="n"/>
     </row>
-    <row r="268" ht="24" customHeight="1" s="49">
+    <row r="268" ht="24" customHeight="1" s="50">
       <c r="A268" s="2" t="n">
         <v>267</v>
       </c>
@@ -27954,7 +27981,7 @@
       <c r="AG268" s="2" t="n"/>
       <c r="AH268" s="2" t="n"/>
     </row>
-    <row r="269" ht="24" customHeight="1" s="49">
+    <row r="269" ht="24" customHeight="1" s="50">
       <c r="A269" s="2" t="n">
         <v>268</v>
       </c>
@@ -28052,7 +28079,7 @@
       <c r="AG269" s="2" t="n"/>
       <c r="AH269" s="2" t="n"/>
     </row>
-    <row r="270" ht="24" customHeight="1" s="49">
+    <row r="270" ht="24" customHeight="1" s="50">
       <c r="A270" s="2" t="n">
         <v>269</v>
       </c>
@@ -28146,7 +28173,7 @@
       <c r="AG270" s="2" t="n"/>
       <c r="AH270" s="2" t="n"/>
     </row>
-    <row r="271" ht="24" customHeight="1" s="49">
+    <row r="271" ht="24" customHeight="1" s="50">
       <c r="A271" s="2" t="n">
         <v>270</v>
       </c>
@@ -28244,7 +28271,7 @@
       <c r="AG271" s="2" t="n"/>
       <c r="AH271" s="2" t="n"/>
     </row>
-    <row r="272" ht="24" customHeight="1" s="49">
+    <row r="272" ht="24" customHeight="1" s="50">
       <c r="A272" s="2" t="n">
         <v>271</v>
       </c>
@@ -28346,7 +28373,7 @@
       </c>
       <c r="AH272" s="2" t="n"/>
     </row>
-    <row r="273" ht="24" customHeight="1" s="49">
+    <row r="273" ht="24" customHeight="1" s="50">
       <c r="A273" s="2" t="n">
         <v>272</v>
       </c>
@@ -28440,7 +28467,7 @@
       </c>
       <c r="AH273" s="2" t="n"/>
     </row>
-    <row r="274" ht="24" customHeight="1" s="49">
+    <row r="274" ht="24" customHeight="1" s="50">
       <c r="A274" s="2" t="n">
         <v>273</v>
       </c>
@@ -28542,7 +28569,7 @@
       </c>
       <c r="AH274" s="2" t="n"/>
     </row>
-    <row r="275" ht="24" customHeight="1" s="49">
+    <row r="275" ht="24" customHeight="1" s="50">
       <c r="A275" s="2" t="n">
         <v>274</v>
       </c>
@@ -28630,7 +28657,7 @@
       <c r="AG275" s="2" t="n"/>
       <c r="AH275" s="2" t="n"/>
     </row>
-    <row r="276" ht="24" customHeight="1" s="49">
+    <row r="276" ht="24" customHeight="1" s="50">
       <c r="A276" s="2" t="n">
         <v>275</v>
       </c>
@@ -28724,7 +28751,7 @@
       <c r="AG276" s="2" t="n"/>
       <c r="AH276" s="2" t="n"/>
     </row>
-    <row r="277" ht="24" customHeight="1" s="49">
+    <row r="277" ht="24" customHeight="1" s="50">
       <c r="A277" s="2" t="n">
         <v>276</v>
       </c>
@@ -28812,7 +28839,7 @@
       <c r="AG277" s="2" t="n"/>
       <c r="AH277" s="2" t="n"/>
     </row>
-    <row r="278" ht="24" customHeight="1" s="49">
+    <row r="278" ht="24" customHeight="1" s="50">
       <c r="A278" s="2" t="n">
         <v>277</v>
       </c>
@@ -28910,7 +28937,7 @@
       <c r="AG278" s="2" t="n"/>
       <c r="AH278" s="2" t="n"/>
     </row>
-    <row r="279" ht="24" customHeight="1" s="49">
+    <row r="279" ht="24" customHeight="1" s="50">
       <c r="A279" s="2" t="n">
         <v>278</v>
       </c>
@@ -28941,12 +28968,8 @@
         </is>
       </c>
       <c r="N279" s="2" t="n"/>
-      <c r="O279" s="32" t="n">
-        <v>-10.9</v>
-      </c>
-      <c r="P279" s="32" t="n">
-        <v>16.7</v>
-      </c>
+      <c r="O279" s="32" t="n"/>
+      <c r="P279" s="32" t="n"/>
       <c r="Q279" s="32" t="n"/>
       <c r="R279" s="23" t="inlineStr">
         <is>
@@ -29006,7 +29029,7 @@
       <c r="AG279" s="2" t="n"/>
       <c r="AH279" s="2" t="n"/>
     </row>
-    <row r="280" ht="24" customHeight="1" s="49">
+    <row r="280" ht="24" customHeight="1" s="50">
       <c r="A280" s="2" t="n">
         <v>279</v>
       </c>
@@ -29090,7 +29113,7 @@
       <c r="AG280" s="2" t="n"/>
       <c r="AH280" s="2" t="n"/>
     </row>
-    <row r="281" ht="24" customHeight="1" s="49">
+    <row r="281" ht="24" customHeight="1" s="50">
       <c r="A281" s="2" t="n">
         <v>280</v>
       </c>
@@ -29182,7 +29205,7 @@
       <c r="AG281" s="2" t="n"/>
       <c r="AH281" s="2" t="n"/>
     </row>
-    <row r="282" ht="24" customHeight="1" s="49">
+    <row r="282" ht="24" customHeight="1" s="50">
       <c r="A282" s="2" t="n">
         <v>281</v>
       </c>
@@ -29262,7 +29285,7 @@
       <c r="AG282" s="2" t="n"/>
       <c r="AH282" s="2" t="n"/>
     </row>
-    <row r="283" ht="24" customHeight="1" s="49">
+    <row r="283" ht="24" customHeight="1" s="50">
       <c r="A283" s="2" t="n">
         <v>282</v>
       </c>
@@ -29354,7 +29377,7 @@
       <c r="AG283" s="2" t="n"/>
       <c r="AH283" s="2" t="n"/>
     </row>
-    <row r="284" ht="24" customHeight="1" s="49">
+    <row r="284" ht="24" customHeight="1" s="50">
       <c r="A284" s="2" t="n">
         <v>283</v>
       </c>
@@ -29440,7 +29463,7 @@
       <c r="AG284" s="2" t="n"/>
       <c r="AH284" s="2" t="n"/>
     </row>
-    <row r="285" ht="24" customHeight="1" s="49">
+    <row r="285" ht="24" customHeight="1" s="50">
       <c r="A285" s="2" t="n">
         <v>284</v>
       </c>
@@ -29542,7 +29565,7 @@
       </c>
       <c r="AH285" s="2" t="n"/>
     </row>
-    <row r="286" ht="24" customHeight="1" s="49">
+    <row r="286" ht="24" customHeight="1" s="50">
       <c r="A286" s="2" t="n">
         <v>285</v>
       </c>
@@ -29644,7 +29667,7 @@
       </c>
       <c r="AH286" s="2" t="n"/>
     </row>
-    <row r="287" ht="24" customHeight="1" s="49">
+    <row r="287" ht="24" customHeight="1" s="50">
       <c r="A287" s="2" t="n">
         <v>286</v>
       </c>
@@ -29746,7 +29769,7 @@
       </c>
       <c r="AH287" s="2" t="n"/>
     </row>
-    <row r="288" ht="24" customHeight="1" s="49">
+    <row r="288" ht="24" customHeight="1" s="50">
       <c r="A288" s="2" t="n">
         <v>287</v>
       </c>
@@ -29848,7 +29871,7 @@
       </c>
       <c r="AH288" s="2" t="n"/>
     </row>
-    <row r="289" ht="24" customHeight="1" s="49">
+    <row r="289" ht="24" customHeight="1" s="50">
       <c r="A289" s="2" t="n">
         <v>288</v>
       </c>
@@ -29946,7 +29969,7 @@
       <c r="AG289" s="2" t="n"/>
       <c r="AH289" s="2" t="n"/>
     </row>
-    <row r="290" ht="24" customHeight="1" s="49">
+    <row r="290" ht="24" customHeight="1" s="50">
       <c r="A290" s="2" t="n">
         <v>289</v>
       </c>
@@ -30046,7 +30069,7 @@
       <c r="AG290" s="2" t="n"/>
       <c r="AH290" s="2" t="n"/>
     </row>
-    <row r="291" ht="24" customHeight="1" s="49">
+    <row r="291" ht="24" customHeight="1" s="50">
       <c r="A291" s="2" t="n">
         <v>290</v>
       </c>
@@ -30138,7 +30161,7 @@
       </c>
       <c r="AH291" s="2" t="n"/>
     </row>
-    <row r="292" ht="24" customHeight="1" s="49">
+    <row r="292" ht="24" customHeight="1" s="50">
       <c r="A292" s="2" t="n">
         <v>291</v>
       </c>
@@ -30236,7 +30259,7 @@
       <c r="AG292" s="2" t="n"/>
       <c r="AH292" s="2" t="n"/>
     </row>
-    <row r="293" ht="24" customHeight="1" s="49">
+    <row r="293" ht="24" customHeight="1" s="50">
       <c r="A293" s="2" t="n">
         <v>292</v>
       </c>
@@ -30334,7 +30357,7 @@
       <c r="AG293" s="2" t="n"/>
       <c r="AH293" s="2" t="n"/>
     </row>
-    <row r="294" ht="24" customHeight="1" s="49">
+    <row r="294" ht="24" customHeight="1" s="50">
       <c r="A294" s="2" t="n">
         <v>293</v>
       </c>
@@ -30438,7 +30461,7 @@
       </c>
       <c r="AH294" s="2" t="n"/>
     </row>
-    <row r="295" ht="24" customHeight="1" s="49">
+    <row r="295" ht="24" customHeight="1" s="50">
       <c r="A295" s="2" t="n">
         <v>294</v>
       </c>
@@ -30476,10 +30499,10 @@
       </c>
       <c r="N295" s="2" t="n"/>
       <c r="O295" s="32" t="n">
-        <v>-12.4</v>
+        <v>-13.2</v>
       </c>
       <c r="P295" s="32" t="n">
-        <v>-0.6</v>
+        <v>1.5</v>
       </c>
       <c r="Q295" s="32" t="n"/>
       <c r="R295" s="23" t="inlineStr">
@@ -30544,7 +30567,7 @@
       </c>
       <c r="AH295" s="2" t="n"/>
     </row>
-    <row r="296" ht="24" customHeight="1" s="49">
+    <row r="296" ht="24" customHeight="1" s="50">
       <c r="A296" s="2" t="n">
         <v>295</v>
       </c>
@@ -30642,7 +30665,7 @@
       <c r="AG296" s="2" t="n"/>
       <c r="AH296" s="2" t="n"/>
     </row>
-    <row r="297" ht="24" customHeight="1" s="49">
+    <row r="297" ht="24" customHeight="1" s="50">
       <c r="A297" s="2" t="n">
         <v>296</v>
       </c>
@@ -30738,7 +30761,7 @@
       </c>
       <c r="AH297" s="2" t="n"/>
     </row>
-    <row r="298" ht="24" customHeight="1" s="49">
+    <row r="298" ht="24" customHeight="1" s="50">
       <c r="A298" s="2" t="n">
         <v>297</v>
       </c>
@@ -30840,7 +30863,7 @@
       </c>
       <c r="AH298" s="2" t="n"/>
     </row>
-    <row r="299" ht="24" customHeight="1" s="49">
+    <row r="299" ht="24" customHeight="1" s="50">
       <c r="A299" s="2" t="n">
         <v>298</v>
       </c>
@@ -30869,7 +30892,7 @@
         </is>
       </c>
       <c r="L299" s="2" t="n"/>
-      <c r="M299" s="14" t="inlineStr">
+      <c r="M299" s="15" t="inlineStr">
         <is>
           <t>瑙罗布林</t>
         </is>
@@ -30928,7 +30951,7 @@
       <c r="AG299" s="2" t="n"/>
       <c r="AH299" s="2" t="n"/>
     </row>
-    <row r="300" ht="24" customHeight="1" s="49">
+    <row r="300" ht="24" customHeight="1" s="50">
       <c r="A300" s="2" t="n">
         <v>299</v>
       </c>
@@ -31030,7 +31053,7 @@
       </c>
       <c r="AH300" s="2" t="n"/>
     </row>
-    <row r="301" ht="24" customHeight="1" s="49">
+    <row r="301" ht="24" customHeight="1" s="50">
       <c r="A301" s="2" t="n">
         <v>300</v>
       </c>
@@ -31069,9 +31092,15 @@
         </is>
       </c>
       <c r="N301" s="2" t="n"/>
-      <c r="O301" s="32" t="n"/>
-      <c r="P301" s="32" t="n"/>
-      <c r="Q301" s="32" t="n"/>
+      <c r="O301" s="32" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="P301" s="32" t="n">
+        <v>35.5</v>
+      </c>
+      <c r="Q301" s="32" t="n">
+        <v>28.49</v>
+      </c>
       <c r="R301" s="23" t="inlineStr">
         <is>
           <t>Y</t>
@@ -31130,7 +31159,7 @@
       </c>
       <c r="AH301" s="2" t="n"/>
     </row>
-    <row r="302" ht="24" customHeight="1" s="49">
+    <row r="302" ht="24" customHeight="1" s="50">
       <c r="A302" s="2" t="n">
         <v>301</v>
       </c>
@@ -31230,7 +31259,7 @@
       <c r="AG302" s="2" t="n"/>
       <c r="AH302" s="2" t="n"/>
     </row>
-    <row r="303" ht="24" customHeight="1" s="49">
+    <row r="303" ht="24" customHeight="1" s="50">
       <c r="A303" s="2" t="n">
         <v>302</v>
       </c>
@@ -31322,7 +31351,7 @@
       </c>
       <c r="AH303" s="2" t="n"/>
     </row>
-    <row r="304" ht="24" customHeight="1" s="49">
+    <row r="304" ht="24" customHeight="1" s="50">
       <c r="A304" s="2" t="n">
         <v>303</v>
       </c>
@@ -31422,7 +31451,7 @@
       <c r="AG304" s="2" t="n"/>
       <c r="AH304" s="2" t="n"/>
     </row>
-    <row r="305" ht="24" customHeight="1" s="49">
+    <row r="305" ht="24" customHeight="1" s="50">
       <c r="A305" s="2" t="n">
         <v>304</v>
       </c>
@@ -31526,7 +31555,7 @@
       </c>
       <c r="AH305" s="2" t="n"/>
     </row>
-    <row r="306" ht="24" customHeight="1" s="49">
+    <row r="306" ht="24" customHeight="1" s="50">
       <c r="A306" s="2" t="n">
         <v>305</v>
       </c>
@@ -31565,12 +31594,8 @@
         </is>
       </c>
       <c r="N306" s="2" t="n"/>
-      <c r="O306" s="32" t="n">
-        <v>-10</v>
-      </c>
-      <c r="P306" s="32" t="n">
-        <v>2.6</v>
-      </c>
+      <c r="O306" s="32" t="n"/>
+      <c r="P306" s="32" t="n"/>
       <c r="Q306" s="32" t="n"/>
       <c r="R306" s="23" t="inlineStr">
         <is>
@@ -31634,151 +31659,401 @@
       </c>
       <c r="AH306" s="2" t="n"/>
     </row>
-    <row r="307" ht="24" customHeight="1" s="49">
-      <c r="A307" s="2" t="n"/>
+    <row r="307" ht="24" customHeight="1" s="50">
+      <c r="A307" s="2" t="n">
+        <v>306</v>
+      </c>
       <c r="B307" s="2" t="n"/>
-      <c r="C307" s="46" t="n"/>
+      <c r="C307" s="46" t="inlineStr">
+        <is>
+          <t>56038</t>
+        </is>
+      </c>
       <c r="D307" s="2" t="n"/>
-      <c r="E307" s="4" t="n"/>
+      <c r="E307" s="4" t="n">
+        <v>99999</v>
+      </c>
       <c r="F307" s="39" t="n"/>
-      <c r="G307" s="29" t="n"/>
-      <c r="H307" s="29" t="n"/>
-      <c r="I307" s="2" t="n"/>
-      <c r="J307" s="27" t="n"/>
-      <c r="K307" s="4" t="n"/>
+      <c r="G307" s="29" t="n">
+        <v>32.9764</v>
+      </c>
+      <c r="H307" s="29" t="n">
+        <v>98.09690000000001</v>
+      </c>
+      <c r="I307" s="2" t="n">
+        <v>4181.2</v>
+      </c>
+      <c r="J307" s="27" t="n">
+        <v>12</v>
+      </c>
+      <c r="K307" s="31" t="inlineStr">
+        <is>
+          <t>🇨🇳</t>
+        </is>
+      </c>
       <c r="L307" s="2" t="n"/>
-      <c r="M307" s="14" t="n"/>
+      <c r="M307" s="14" t="inlineStr">
+        <is>
+          <t>石渠</t>
+        </is>
+      </c>
       <c r="N307" s="2" t="n"/>
       <c r="O307" s="32" t="n"/>
       <c r="P307" s="32" t="n"/>
       <c r="Q307" s="32" t="n"/>
-      <c r="R307" s="23" t="n"/>
+      <c r="R307" s="23" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="S307" s="37" t="n"/>
-      <c r="T307" s="41" t="n"/>
-      <c r="U307" s="2" t="n"/>
-      <c r="V307" s="4" t="n"/>
-      <c r="W307" s="4" t="n"/>
-      <c r="X307" s="4" t="n"/>
+      <c r="T307" s="41" t="inlineStr">
+        <is>
+          <t>四川甘孜</t>
+        </is>
+      </c>
+      <c r="U307" s="2" t="inlineStr">
+        <is>
+          <t>四川</t>
+        </is>
+      </c>
+      <c r="V307" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="W307" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="X307" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="Y307" s="4" t="n"/>
-      <c r="Z307" s="2" t="n"/>
-      <c r="AA307" s="2" t="n"/>
+      <c r="Z307" s="2" t="inlineStr">
+        <is>
+          <t>甘孜藏族自治州</t>
+        </is>
+      </c>
+      <c r="AA307" s="2" t="inlineStr">
+        <is>
+          <t>石渠县</t>
+        </is>
+      </c>
       <c r="AB307" s="2" t="n"/>
       <c r="AC307" s="2" t="n"/>
-      <c r="AD307" s="2" t="n"/>
-      <c r="AE307" s="4" t="n"/>
+      <c r="AD307" s="2" t="inlineStr">
+        <is>
+          <t>中国</t>
+        </is>
+      </c>
+      <c r="AE307" s="4" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
       <c r="AF307" s="4" t="n"/>
-      <c r="AG307" s="2" t="n"/>
+      <c r="AG307" s="2" t="inlineStr">
+        <is>
+          <t>青藏高原</t>
+        </is>
+      </c>
       <c r="AH307" s="2" t="n"/>
     </row>
-    <row r="308" ht="24" customHeight="1" s="49">
-      <c r="A308" s="2" t="n"/>
+    <row r="308" ht="24" customHeight="1" s="50">
+      <c r="A308" s="2" t="n">
+        <v>307</v>
+      </c>
       <c r="B308" s="2" t="n"/>
       <c r="C308" s="46" t="n"/>
       <c r="D308" s="2" t="n"/>
       <c r="E308" s="4" t="n"/>
-      <c r="F308" s="39" t="n"/>
-      <c r="G308" s="29" t="n"/>
-      <c r="H308" s="29" t="n"/>
-      <c r="I308" s="2" t="n"/>
-      <c r="J308" s="27" t="n"/>
-      <c r="K308" s="4" t="n"/>
+      <c r="F308" s="39" t="inlineStr">
+        <is>
+          <t>U6801</t>
+        </is>
+      </c>
+      <c r="G308" s="29" t="n">
+        <v>32.8814</v>
+      </c>
+      <c r="H308" s="29" t="n">
+        <v>91.9178</v>
+      </c>
+      <c r="I308" s="2" t="n">
+        <v>5231</v>
+      </c>
+      <c r="J308" s="27" t="n">
+        <v>12</v>
+      </c>
+      <c r="K308" s="31" t="inlineStr">
+        <is>
+          <t>🇨🇳</t>
+        </is>
+      </c>
       <c r="L308" s="2" t="n"/>
-      <c r="M308" s="14" t="n"/>
+      <c r="M308" s="14" t="inlineStr">
+        <is>
+          <t>唐古拉山</t>
+        </is>
+      </c>
       <c r="N308" s="2" t="n"/>
-      <c r="O308" s="32" t="n"/>
-      <c r="P308" s="32" t="n"/>
+      <c r="O308" s="32" t="n">
+        <v>-15.6</v>
+      </c>
+      <c r="P308" s="32" t="n">
+        <v>-5.1</v>
+      </c>
       <c r="Q308" s="32" t="n"/>
-      <c r="R308" s="23" t="n"/>
+      <c r="R308" s="23" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="S308" s="37" t="n"/>
-      <c r="T308" s="41" t="n"/>
-      <c r="U308" s="2" t="n"/>
-      <c r="V308" s="4" t="n"/>
-      <c r="W308" s="4" t="n"/>
-      <c r="X308" s="4" t="n"/>
+      <c r="T308" s="41" t="inlineStr">
+        <is>
+          <t>西藏那曲安多县</t>
+        </is>
+      </c>
+      <c r="U308" s="2" t="inlineStr">
+        <is>
+          <t>西藏</t>
+        </is>
+      </c>
+      <c r="V308" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="W308" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="X308" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="Y308" s="4" t="n"/>
-      <c r="Z308" s="2" t="n"/>
-      <c r="AA308" s="2" t="n"/>
+      <c r="Z308" s="2" t="inlineStr">
+        <is>
+          <t>那曲市</t>
+        </is>
+      </c>
+      <c r="AA308" s="2" t="inlineStr">
+        <is>
+          <t>安多县</t>
+        </is>
+      </c>
       <c r="AB308" s="2" t="n"/>
       <c r="AC308" s="2" t="n"/>
-      <c r="AD308" s="2" t="n"/>
-      <c r="AE308" s="4" t="n"/>
+      <c r="AD308" s="2" t="inlineStr">
+        <is>
+          <t>中国</t>
+        </is>
+      </c>
+      <c r="AE308" s="4" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
       <c r="AF308" s="4" t="n"/>
-      <c r="AG308" s="2" t="n"/>
+      <c r="AG308" s="2" t="inlineStr">
+        <is>
+          <t>青藏高原</t>
+        </is>
+      </c>
       <c r="AH308" s="2" t="n"/>
     </row>
-    <row r="309" ht="24" customHeight="1" s="49">
-      <c r="A309" s="2" t="n"/>
+    <row r="309" ht="24" customHeight="1" s="50">
+      <c r="A309" s="2" t="n">
+        <v>308</v>
+      </c>
       <c r="B309" s="2" t="n"/>
       <c r="C309" s="46" t="n"/>
       <c r="D309" s="2" t="n"/>
       <c r="E309" s="4" t="n"/>
-      <c r="F309" s="39" t="n"/>
-      <c r="G309" s="29" t="n"/>
-      <c r="H309" s="29" t="n"/>
-      <c r="I309" s="2" t="n"/>
-      <c r="J309" s="27" t="n"/>
-      <c r="K309" s="4" t="n"/>
+      <c r="F309" s="39" t="n">
+        <v>916</v>
+      </c>
+      <c r="G309" s="29" t="n">
+        <v>47.5041468369939</v>
+      </c>
+      <c r="H309" s="29" t="n">
+        <v>110.174625367388</v>
+      </c>
+      <c r="I309" s="2" t="n">
+        <v>1133</v>
+      </c>
+      <c r="J309" s="27" t="n">
+        <v>12</v>
+      </c>
+      <c r="K309" s="31" t="inlineStr">
+        <is>
+          <t>🇲🇳</t>
+        </is>
+      </c>
       <c r="L309" s="2" t="n"/>
-      <c r="M309" s="14" t="n"/>
+      <c r="M309" s="49" t="inlineStr">
+        <is>
+          <t>Өлзийт</t>
+        </is>
+      </c>
       <c r="N309" s="2" t="n"/>
       <c r="O309" s="32" t="n"/>
       <c r="P309" s="32" t="n"/>
       <c r="Q309" s="32" t="n"/>
-      <c r="R309" s="23" t="n"/>
+      <c r="R309" s="23" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="S309" s="37" t="n"/>
-      <c r="T309" s="41" t="n"/>
-      <c r="U309" s="2" t="n"/>
-      <c r="V309" s="4" t="n"/>
-      <c r="W309" s="4" t="n"/>
-      <c r="X309" s="4" t="n"/>
+      <c r="T309" s="41" t="inlineStr">
+        <is>
+          <t>肯特省&lt;br&gt;Өлзийт тосгон</t>
+        </is>
+      </c>
+      <c r="U309" s="2" t="inlineStr">
+        <is>
+          <t>肯特省</t>
+        </is>
+      </c>
+      <c r="V309" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="W309" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="X309" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="Y309" s="4" t="n"/>
       <c r="Z309" s="2" t="n"/>
       <c r="AA309" s="2" t="n"/>
       <c r="AB309" s="2" t="n"/>
       <c r="AC309" s="2" t="n"/>
-      <c r="AD309" s="2" t="n"/>
-      <c r="AE309" s="4" t="n"/>
+      <c r="AD309" s="2" t="inlineStr">
+        <is>
+          <t>蒙古</t>
+        </is>
+      </c>
+      <c r="AE309" s="4" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
       <c r="AF309" s="4" t="n"/>
       <c r="AG309" s="2" t="n"/>
       <c r="AH309" s="2" t="n"/>
     </row>
-    <row r="310" ht="24" customHeight="1" s="49">
-      <c r="A310" s="2" t="n"/>
-      <c r="B310" s="2" t="n"/>
-      <c r="C310" s="46" t="n"/>
+    <row r="310" ht="24" customHeight="1" s="50">
+      <c r="A310" s="2" t="n">
+        <v>309</v>
+      </c>
+      <c r="B310" s="2" t="inlineStr">
+        <is>
+          <t>ogimet</t>
+        </is>
+      </c>
+      <c r="C310" s="46" t="inlineStr">
+        <is>
+          <t>21802</t>
+        </is>
+      </c>
       <c r="D310" s="2" t="n"/>
-      <c r="E310" s="4" t="n"/>
+      <c r="E310" s="4" t="n">
+        <v>99999</v>
+      </c>
       <c r="F310" s="39" t="n"/>
-      <c r="G310" s="29" t="n"/>
-      <c r="H310" s="29" t="n"/>
-      <c r="I310" s="2" t="n"/>
-      <c r="J310" s="27" t="n"/>
-      <c r="K310" s="4" t="n"/>
+      <c r="G310" s="29" t="n">
+        <v>71.97</v>
+      </c>
+      <c r="H310" s="29" t="n">
+        <v>114.08</v>
+      </c>
+      <c r="I310" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="J310" s="27" t="n">
+        <v>12</v>
+      </c>
+      <c r="K310" s="31" t="inlineStr">
+        <is>
+          <t>🇨🇳</t>
+        </is>
+      </c>
       <c r="L310" s="2" t="n"/>
-      <c r="M310" s="14" t="n"/>
+      <c r="M310" s="16" t="inlineStr">
+        <is>
+          <t>萨斯克拉赫</t>
+        </is>
+      </c>
       <c r="N310" s="2" t="n"/>
-      <c r="O310" s="32" t="n"/>
-      <c r="P310" s="32" t="n"/>
+      <c r="O310" s="32" t="n">
+        <v>-22.1</v>
+      </c>
+      <c r="P310" s="32" t="n">
+        <v>-6.8</v>
+      </c>
       <c r="Q310" s="32" t="n"/>
-      <c r="R310" s="23" t="n"/>
+      <c r="R310" s="23" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="S310" s="37" t="n"/>
-      <c r="T310" s="41" t="n"/>
-      <c r="U310" s="2" t="n"/>
-      <c r="V310" s="4" t="n"/>
+      <c r="T310" s="41" t="inlineStr">
+        <is>
+          <t>雅库特</t>
+        </is>
+      </c>
+      <c r="U310" s="2" t="inlineStr">
+        <is>
+          <t>萨哈共和国</t>
+        </is>
+      </c>
+      <c r="V310" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="W310" s="4" t="n"/>
-      <c r="X310" s="4" t="n"/>
+      <c r="X310" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="Y310" s="4" t="n"/>
       <c r="Z310" s="2" t="n"/>
       <c r="AA310" s="2" t="n"/>
       <c r="AB310" s="2" t="n"/>
       <c r="AC310" s="2" t="n"/>
-      <c r="AD310" s="2" t="n"/>
-      <c r="AE310" s="4" t="n"/>
+      <c r="AD310" s="2" t="inlineStr">
+        <is>
+          <t>俄罗斯</t>
+        </is>
+      </c>
+      <c r="AE310" s="4" t="inlineStr">
+        <is>
+          <t>Z</t>
+        </is>
+      </c>
       <c r="AF310" s="4" t="n"/>
       <c r="AG310" s="2" t="n"/>
       <c r="AH310" s="2" t="n"/>
     </row>
-    <row r="311" ht="24" customHeight="1" s="49">
+    <row r="311" ht="24" customHeight="1" s="50">
       <c r="A311" s="2" t="n"/>
       <c r="B311" s="2" t="n"/>
       <c r="C311" s="46" t="n"/>
@@ -31814,7 +32089,7 @@
       <c r="AG311" s="2" t="n"/>
       <c r="AH311" s="2" t="n"/>
     </row>
-    <row r="312" ht="24" customHeight="1" s="49">
+    <row r="312" ht="24" customHeight="1" s="50">
       <c r="A312" s="2" t="n"/>
       <c r="B312" s="2" t="n"/>
       <c r="C312" s="46" t="n"/>
@@ -31850,7 +32125,7 @@
       <c r="AG312" s="2" t="n"/>
       <c r="AH312" s="2" t="n"/>
     </row>
-    <row r="313" ht="24" customHeight="1" s="49">
+    <row r="313" ht="24" customHeight="1" s="50">
       <c r="A313" s="2" t="n"/>
       <c r="B313" s="2" t="n"/>
       <c r="C313" s="46" t="n"/>
@@ -31886,7 +32161,7 @@
       <c r="AG313" s="2" t="n"/>
       <c r="AH313" s="2" t="n"/>
     </row>
-    <row r="314" ht="24" customHeight="1" s="49">
+    <row r="314" ht="24" customHeight="1" s="50">
       <c r="A314" s="2" t="n"/>
       <c r="B314" s="2" t="n"/>
       <c r="C314" s="46" t="n"/>
@@ -31922,7 +32197,7 @@
       <c r="AG314" s="2" t="n"/>
       <c r="AH314" s="2" t="n"/>
     </row>
-    <row r="315" ht="24" customHeight="1" s="49">
+    <row r="315" ht="24" customHeight="1" s="50">
       <c r="A315" s="2" t="n"/>
       <c r="B315" s="2" t="n"/>
       <c r="C315" s="46" t="n"/>
@@ -31958,7 +32233,7 @@
       <c r="AG315" s="2" t="n"/>
       <c r="AH315" s="2" t="n"/>
     </row>
-    <row r="316" ht="24" customHeight="1" s="49">
+    <row r="316" ht="24" customHeight="1" s="50">
       <c r="A316" s="2" t="n"/>
       <c r="B316" s="2" t="n"/>
       <c r="C316" s="46" t="n"/>
@@ -31994,7 +32269,7 @@
       <c r="AG316" s="2" t="n"/>
       <c r="AH316" s="2" t="n"/>
     </row>
-    <row r="317" ht="24" customHeight="1" s="49">
+    <row r="317" ht="24" customHeight="1" s="50">
       <c r="A317" s="2" t="n"/>
       <c r="B317" s="2" t="n"/>
       <c r="C317" s="46" t="n"/>
@@ -32030,7 +32305,7 @@
       <c r="AG317" s="2" t="n"/>
       <c r="AH317" s="2" t="n"/>
     </row>
-    <row r="318" ht="24" customHeight="1" s="49">
+    <row r="318" ht="24" customHeight="1" s="50">
       <c r="A318" s="2" t="n"/>
       <c r="B318" s="2" t="n"/>
       <c r="C318" s="46" t="n"/>
@@ -32066,7 +32341,7 @@
       <c r="AG318" s="2" t="n"/>
       <c r="AH318" s="2" t="n"/>
     </row>
-    <row r="319" ht="24" customHeight="1" s="49">
+    <row r="319" ht="24" customHeight="1" s="50">
       <c r="A319" s="2" t="n"/>
       <c r="B319" s="2" t="n"/>
       <c r="C319" s="46" t="n"/>
@@ -32102,7 +32377,7 @@
       <c r="AG319" s="2" t="n"/>
       <c r="AH319" s="2" t="n"/>
     </row>
-    <row r="320" ht="24" customHeight="1" s="49">
+    <row r="320" ht="24" customHeight="1" s="50">
       <c r="A320" s="2" t="n"/>
       <c r="B320" s="2" t="n"/>
       <c r="C320" s="46" t="n"/>
@@ -32138,7 +32413,7 @@
       <c r="AG320" s="2" t="n"/>
       <c r="AH320" s="2" t="n"/>
     </row>
-    <row r="321" ht="24" customHeight="1" s="49">
+    <row r="321" ht="24" customHeight="1" s="50">
       <c r="A321" s="2" t="n"/>
       <c r="B321" s="2" t="n"/>
       <c r="C321" s="46" t="n"/>
@@ -32174,7 +32449,7 @@
       <c r="AG321" s="2" t="n"/>
       <c r="AH321" s="2" t="n"/>
     </row>
-    <row r="322" ht="24" customHeight="1" s="49">
+    <row r="322" ht="24" customHeight="1" s="50">
       <c r="A322" s="2" t="n"/>
       <c r="B322" s="2" t="n"/>
       <c r="C322" s="46" t="n"/>
@@ -32210,7 +32485,7 @@
       <c r="AG322" s="2" t="n"/>
       <c r="AH322" s="2" t="n"/>
     </row>
-    <row r="323" ht="24" customHeight="1" s="49">
+    <row r="323" ht="24" customHeight="1" s="50">
       <c r="A323" s="2" t="n"/>
       <c r="B323" s="2" t="n"/>
       <c r="C323" s="46" t="n"/>
@@ -32246,7 +32521,7 @@
       <c r="AG323" s="2" t="n"/>
       <c r="AH323" s="2" t="n"/>
     </row>
-    <row r="324" ht="24" customHeight="1" s="49">
+    <row r="324" ht="24" customHeight="1" s="50">
       <c r="A324" s="2" t="n"/>
       <c r="B324" s="2" t="n"/>
       <c r="C324" s="46" t="n"/>
@@ -32282,7 +32557,7 @@
       <c r="AG324" s="2" t="n"/>
       <c r="AH324" s="2" t="n"/>
     </row>
-    <row r="325" ht="24" customHeight="1" s="49">
+    <row r="325" ht="24" customHeight="1" s="50">
       <c r="A325" s="2" t="n"/>
       <c r="B325" s="2" t="n"/>
       <c r="C325" s="46" t="n"/>
@@ -32318,7 +32593,7 @@
       <c r="AG325" s="2" t="n"/>
       <c r="AH325" s="2" t="n"/>
     </row>
-    <row r="326" ht="24" customHeight="1" s="49">
+    <row r="326" ht="24" customHeight="1" s="50">
       <c r="A326" s="2" t="n"/>
       <c r="B326" s="2" t="n"/>
       <c r="C326" s="46" t="n"/>
@@ -32354,7 +32629,7 @@
       <c r="AG326" s="2" t="n"/>
       <c r="AH326" s="2" t="n"/>
     </row>
-    <row r="327" ht="24" customHeight="1" s="49">
+    <row r="327" ht="24" customHeight="1" s="50">
       <c r="A327" s="2" t="n"/>
       <c r="B327" s="2" t="n"/>
       <c r="C327" s="46" t="n"/>
@@ -32390,7 +32665,7 @@
       <c r="AG327" s="2" t="n"/>
       <c r="AH327" s="2" t="n"/>
     </row>
-    <row r="328" ht="24" customHeight="1" s="49">
+    <row r="328" ht="24" customHeight="1" s="50">
       <c r="A328" s="2" t="n"/>
       <c r="B328" s="2" t="n"/>
       <c r="C328" s="46" t="n"/>
@@ -32426,7 +32701,7 @@
       <c r="AG328" s="2" t="n"/>
       <c r="AH328" s="2" t="n"/>
     </row>
-    <row r="329" ht="24" customHeight="1" s="49">
+    <row r="329" ht="24" customHeight="1" s="50">
       <c r="A329" s="2" t="n"/>
       <c r="B329" s="2" t="n"/>
       <c r="C329" s="46" t="n"/>
@@ -32462,7 +32737,7 @@
       <c r="AG329" s="2" t="n"/>
       <c r="AH329" s="2" t="n"/>
     </row>
-    <row r="330" ht="24" customHeight="1" s="49">
+    <row r="330" ht="24" customHeight="1" s="50">
       <c r="A330" s="2" t="n"/>
       <c r="B330" s="2" t="n"/>
       <c r="C330" s="46" t="n"/>
@@ -32498,7 +32773,7 @@
       <c r="AG330" s="2" t="n"/>
       <c r="AH330" s="2" t="n"/>
     </row>
-    <row r="331" ht="24" customHeight="1" s="49">
+    <row r="331" ht="24" customHeight="1" s="50">
       <c r="A331" s="2" t="n"/>
       <c r="B331" s="2" t="n"/>
       <c r="C331" s="46" t="n"/>
@@ -32534,7 +32809,7 @@
       <c r="AG331" s="2" t="n"/>
       <c r="AH331" s="2" t="n"/>
     </row>
-    <row r="332" ht="24" customHeight="1" s="49">
+    <row r="332" ht="24" customHeight="1" s="50">
       <c r="A332" s="2" t="n"/>
       <c r="B332" s="2" t="n"/>
       <c r="C332" s="46" t="n"/>
@@ -32570,7 +32845,7 @@
       <c r="AG332" s="2" t="n"/>
       <c r="AH332" s="2" t="n"/>
     </row>
-    <row r="333" ht="24" customHeight="1" s="49">
+    <row r="333" ht="24" customHeight="1" s="50">
       <c r="A333" s="2" t="n"/>
       <c r="B333" s="2" t="n"/>
       <c r="C333" s="46" t="n"/>
@@ -32606,7 +32881,7 @@
       <c r="AG333" s="2" t="n"/>
       <c r="AH333" s="2" t="n"/>
     </row>
-    <row r="334" ht="24" customHeight="1" s="49">
+    <row r="334" ht="24" customHeight="1" s="50">
       <c r="A334" s="2" t="n"/>
       <c r="B334" s="2" t="n"/>
       <c r="C334" s="46" t="n"/>
@@ -32642,7 +32917,7 @@
       <c r="AG334" s="2" t="n"/>
       <c r="AH334" s="2" t="n"/>
     </row>
-    <row r="335" ht="24" customHeight="1" s="49">
+    <row r="335" ht="24" customHeight="1" s="50">
       <c r="A335" s="2" t="n"/>
       <c r="B335" s="2" t="n"/>
       <c r="C335" s="46" t="n"/>
@@ -32678,7 +32953,7 @@
       <c r="AG335" s="2" t="n"/>
       <c r="AH335" s="2" t="n"/>
     </row>
-    <row r="336" ht="24" customHeight="1" s="49">
+    <row r="336" ht="24" customHeight="1" s="50">
       <c r="A336" s="2" t="n"/>
       <c r="B336" s="2" t="n"/>
       <c r="C336" s="46" t="n"/>
@@ -32714,7 +32989,7 @@
       <c r="AG336" s="2" t="n"/>
       <c r="AH336" s="2" t="n"/>
     </row>
-    <row r="337" ht="24" customHeight="1" s="49">
+    <row r="337" ht="24" customHeight="1" s="50">
       <c r="A337" s="2" t="n"/>
       <c r="B337" s="2" t="n"/>
       <c r="C337" s="46" t="n"/>
@@ -32750,7 +33025,7 @@
       <c r="AG337" s="2" t="n"/>
       <c r="AH337" s="2" t="n"/>
     </row>
-    <row r="338" ht="24" customHeight="1" s="49">
+    <row r="338" ht="24" customHeight="1" s="50">
       <c r="A338" s="2" t="n"/>
       <c r="B338" s="2" t="n"/>
       <c r="C338" s="46" t="n"/>
@@ -32786,7 +33061,7 @@
       <c r="AG338" s="2" t="n"/>
       <c r="AH338" s="2" t="n"/>
     </row>
-    <row r="339" ht="24" customHeight="1" s="49">
+    <row r="339" ht="24" customHeight="1" s="50">
       <c r="A339" s="2" t="n"/>
       <c r="B339" s="2" t="n"/>
       <c r="C339" s="46" t="n"/>
@@ -32822,7 +33097,7 @@
       <c r="AG339" s="2" t="n"/>
       <c r="AH339" s="2" t="n"/>
     </row>
-    <row r="340" ht="24" customHeight="1" s="49">
+    <row r="340" ht="24" customHeight="1" s="50">
       <c r="A340" s="2" t="n"/>
       <c r="B340" s="2" t="n"/>
       <c r="C340" s="46" t="n"/>
@@ -32858,7 +33133,7 @@
       <c r="AG340" s="2" t="n"/>
       <c r="AH340" s="2" t="n"/>
     </row>
-    <row r="341" ht="24" customHeight="1" s="49">
+    <row r="341" ht="24" customHeight="1" s="50">
       <c r="A341" s="2" t="n"/>
       <c r="B341" s="2" t="n"/>
       <c r="C341" s="46" t="n"/>
@@ -32894,7 +33169,7 @@
       <c r="AG341" s="2" t="n"/>
       <c r="AH341" s="2" t="n"/>
     </row>
-    <row r="342" ht="24" customHeight="1" s="49">
+    <row r="342" ht="24" customHeight="1" s="50">
       <c r="A342" s="2" t="n"/>
       <c r="B342" s="2" t="n"/>
       <c r="C342" s="46" t="n"/>
@@ -32930,7 +33205,7 @@
       <c r="AG342" s="2" t="n"/>
       <c r="AH342" s="2" t="n"/>
     </row>
-    <row r="343" ht="24" customHeight="1" s="49">
+    <row r="343" ht="24" customHeight="1" s="50">
       <c r="A343" s="2" t="n"/>
       <c r="B343" s="2" t="n"/>
       <c r="C343" s="46" t="n"/>
@@ -32966,7 +33241,7 @@
       <c r="AG343" s="2" t="n"/>
       <c r="AH343" s="2" t="n"/>
     </row>
-    <row r="344" ht="24" customHeight="1" s="49">
+    <row r="344" ht="24" customHeight="1" s="50">
       <c r="A344" s="2" t="n"/>
       <c r="B344" s="2" t="n"/>
       <c r="C344" s="46" t="n"/>
@@ -33002,7 +33277,7 @@
       <c r="AG344" s="2" t="n"/>
       <c r="AH344" s="2" t="n"/>
     </row>
-    <row r="345" ht="24" customHeight="1" s="49">
+    <row r="345" ht="24" customHeight="1" s="50">
       <c r="A345" s="2" t="n"/>
       <c r="B345" s="2" t="n"/>
       <c r="C345" s="46" t="n"/>
@@ -33038,7 +33313,7 @@
       <c r="AG345" s="2" t="n"/>
       <c r="AH345" s="2" t="n"/>
     </row>
-    <row r="346" ht="24" customHeight="1" s="49">
+    <row r="346" ht="24" customHeight="1" s="50">
       <c r="A346" s="2" t="n"/>
       <c r="B346" s="2" t="n"/>
       <c r="C346" s="46" t="n"/>
@@ -33074,7 +33349,7 @@
       <c r="AG346" s="2" t="n"/>
       <c r="AH346" s="2" t="n"/>
     </row>
-    <row r="347" ht="24" customHeight="1" s="49">
+    <row r="347" ht="24" customHeight="1" s="50">
       <c r="A347" s="2" t="n"/>
       <c r="B347" s="2" t="n"/>
       <c r="C347" s="46" t="n"/>
@@ -33110,7 +33385,7 @@
       <c r="AG347" s="2" t="n"/>
       <c r="AH347" s="2" t="n"/>
     </row>
-    <row r="348" ht="24" customHeight="1" s="49">
+    <row r="348" ht="24" customHeight="1" s="50">
       <c r="A348" s="2" t="n"/>
       <c r="B348" s="2" t="n"/>
       <c r="C348" s="46" t="n"/>
@@ -33146,7 +33421,7 @@
       <c r="AG348" s="2" t="n"/>
       <c r="AH348" s="2" t="n"/>
     </row>
-    <row r="349" ht="24" customHeight="1" s="49">
+    <row r="349" ht="24" customHeight="1" s="50">
       <c r="A349" s="2" t="n"/>
       <c r="B349" s="2" t="n"/>
       <c r="C349" s="46" t="n"/>
@@ -33182,7 +33457,7 @@
       <c r="AG349" s="2" t="n"/>
       <c r="AH349" s="2" t="n"/>
     </row>
-    <row r="350" ht="24" customHeight="1" s="49">
+    <row r="350" ht="24" customHeight="1" s="50">
       <c r="A350" s="2" t="n"/>
       <c r="B350" s="2" t="n"/>
       <c r="C350" s="46" t="n"/>
@@ -33218,7 +33493,7 @@
       <c r="AG350" s="2" t="n"/>
       <c r="AH350" s="2" t="n"/>
     </row>
-    <row r="351" ht="24" customHeight="1" s="49">
+    <row r="351" ht="24" customHeight="1" s="50">
       <c r="A351" s="14" t="n"/>
       <c r="B351" s="2" t="n"/>
       <c r="C351" s="46" t="n"/>
@@ -33254,7 +33529,7 @@
       <c r="AG351" s="2" t="n"/>
       <c r="AH351" s="2" t="n"/>
     </row>
-    <row r="352" ht="24" customHeight="1" s="49">
+    <row r="352" ht="24" customHeight="1" s="50">
       <c r="A352" s="13" t="n"/>
       <c r="B352" s="2" t="n"/>
       <c r="C352" s="46" t="n"/>
@@ -33290,7 +33565,7 @@
       <c r="AG352" s="2" t="n"/>
       <c r="AH352" s="2" t="n"/>
     </row>
-    <row r="353" ht="24" customHeight="1" s="49">
+    <row r="353" ht="24" customHeight="1" s="50">
       <c r="A353" s="13" t="n"/>
       <c r="B353" s="2" t="n"/>
       <c r="C353" s="46" t="n"/>
@@ -33326,7 +33601,7 @@
       <c r="AG353" s="2" t="n"/>
       <c r="AH353" s="2" t="n"/>
     </row>
-    <row r="354" ht="24" customHeight="1" s="49">
+    <row r="354" ht="24" customHeight="1" s="50">
       <c r="A354" s="13" t="n"/>
       <c r="B354" s="2" t="n"/>
       <c r="C354" s="46" t="n"/>
@@ -33362,7 +33637,7 @@
       <c r="AG354" s="2" t="n"/>
       <c r="AH354" s="2" t="n"/>
     </row>
-    <row r="355" ht="24" customHeight="1" s="49">
+    <row r="355" ht="24" customHeight="1" s="50">
       <c r="A355" s="13" t="n"/>
       <c r="B355" s="2" t="n"/>
       <c r="C355" s="46" t="n"/>
@@ -33398,7 +33673,7 @@
       <c r="AG355" s="2" t="n"/>
       <c r="AH355" s="2" t="n"/>
     </row>
-    <row r="356" ht="24" customHeight="1" s="49">
+    <row r="356" ht="24" customHeight="1" s="50">
       <c r="A356" s="13" t="n"/>
       <c r="B356" s="2" t="n"/>
       <c r="C356" s="46" t="n"/>
@@ -33434,7 +33709,7 @@
       <c r="AG356" s="2" t="n"/>
       <c r="AH356" s="2" t="n"/>
     </row>
-    <row r="357" ht="24" customHeight="1" s="49">
+    <row r="357" ht="24" customHeight="1" s="50">
       <c r="A357" s="13" t="n"/>
       <c r="B357" s="2" t="n"/>
       <c r="C357" s="46" t="n"/>
@@ -33470,7 +33745,7 @@
       <c r="AG357" s="2" t="n"/>
       <c r="AH357" s="2" t="n"/>
     </row>
-    <row r="358" ht="24" customHeight="1" s="49">
+    <row r="358" ht="24" customHeight="1" s="50">
       <c r="A358" s="13" t="n"/>
       <c r="B358" s="2" t="n"/>
       <c r="C358" s="46" t="n"/>
@@ -33506,7 +33781,7 @@
       <c r="AG358" s="2" t="n"/>
       <c r="AH358" s="2" t="n"/>
     </row>
-    <row r="359" ht="24" customHeight="1" s="49">
+    <row r="359" ht="24" customHeight="1" s="50">
       <c r="A359" s="13" t="n"/>
       <c r="B359" s="2" t="n"/>
       <c r="C359" s="46" t="n"/>
@@ -33542,7 +33817,7 @@
       <c r="AG359" s="2" t="n"/>
       <c r="AH359" s="2" t="n"/>
     </row>
-    <row r="360" ht="24" customHeight="1" s="49">
+    <row r="360" ht="24" customHeight="1" s="50">
       <c r="A360" s="13" t="n"/>
       <c r="B360" s="2" t="n"/>
       <c r="C360" s="46" t="n"/>
@@ -33578,7 +33853,7 @@
       <c r="AG360" s="2" t="n"/>
       <c r="AH360" s="2" t="n"/>
     </row>
-    <row r="361" ht="24" customHeight="1" s="49">
+    <row r="361" ht="24" customHeight="1" s="50">
       <c r="A361" s="13" t="n"/>
       <c r="B361" s="2" t="n"/>
       <c r="C361" s="46" t="n"/>
@@ -33614,7 +33889,7 @@
       <c r="AG361" s="2" t="n"/>
       <c r="AH361" s="2" t="n"/>
     </row>
-    <row r="362" ht="24" customHeight="1" s="49">
+    <row r="362" ht="24" customHeight="1" s="50">
       <c r="A362" s="13" t="n"/>
       <c r="B362" s="2" t="n"/>
       <c r="C362" s="46" t="n"/>
@@ -33650,7 +33925,7 @@
       <c r="AG362" s="2" t="n"/>
       <c r="AH362" s="2" t="n"/>
     </row>
-    <row r="363" ht="24" customHeight="1" s="49">
+    <row r="363" ht="24" customHeight="1" s="50">
       <c r="A363" s="13" t="n"/>
       <c r="B363" s="2" t="n"/>
       <c r="C363" s="46" t="n"/>
@@ -33686,7 +33961,7 @@
       <c r="AG363" s="2" t="n"/>
       <c r="AH363" s="2" t="n"/>
     </row>
-    <row r="364" ht="24" customHeight="1" s="49">
+    <row r="364" ht="24" customHeight="1" s="50">
       <c r="A364" s="13" t="n"/>
       <c r="B364" s="2" t="n"/>
       <c r="C364" s="46" t="n"/>
@@ -33722,7 +33997,7 @@
       <c r="AG364" s="2" t="n"/>
       <c r="AH364" s="2" t="n"/>
     </row>
-    <row r="365" ht="24" customHeight="1" s="49">
+    <row r="365" ht="24" customHeight="1" s="50">
       <c r="A365" s="13" t="n"/>
       <c r="B365" s="2" t="n"/>
       <c r="C365" s="46" t="n"/>
@@ -33758,7 +34033,7 @@
       <c r="AG365" s="2" t="n"/>
       <c r="AH365" s="2" t="n"/>
     </row>
-    <row r="366" ht="24" customHeight="1" s="49">
+    <row r="366" ht="24" customHeight="1" s="50">
       <c r="A366" s="13" t="n"/>
       <c r="B366" s="2" t="n"/>
       <c r="C366" s="46" t="n"/>
@@ -33794,7 +34069,7 @@
       <c r="AG366" s="2" t="n"/>
       <c r="AH366" s="2" t="n"/>
     </row>
-    <row r="367" ht="24" customHeight="1" s="49">
+    <row r="367" ht="24" customHeight="1" s="50">
       <c r="A367" s="13" t="n"/>
       <c r="B367" s="2" t="n"/>
       <c r="C367" s="46" t="n"/>
@@ -33830,7 +34105,7 @@
       <c r="AG367" s="2" t="n"/>
       <c r="AH367" s="2" t="n"/>
     </row>
-    <row r="368" ht="24" customHeight="1" s="49">
+    <row r="368" ht="24" customHeight="1" s="50">
       <c r="A368" s="13" t="n"/>
       <c r="B368" s="2" t="n"/>
       <c r="C368" s="46" t="n"/>
@@ -33866,7 +34141,7 @@
       <c r="AG368" s="2" t="n"/>
       <c r="AH368" s="2" t="n"/>
     </row>
-    <row r="369" ht="24" customHeight="1" s="49">
+    <row r="369" ht="24" customHeight="1" s="50">
       <c r="A369" s="13" t="n"/>
       <c r="B369" s="2" t="n"/>
       <c r="C369" s="46" t="n"/>
@@ -33902,7 +34177,7 @@
       <c r="AG369" s="2" t="n"/>
       <c r="AH369" s="2" t="n"/>
     </row>
-    <row r="370" ht="24" customHeight="1" s="49">
+    <row r="370" ht="24" customHeight="1" s="50">
       <c r="A370" s="13" t="n"/>
       <c r="B370" s="2" t="n"/>
       <c r="C370" s="46" t="n"/>
@@ -33938,7 +34213,7 @@
       <c r="AG370" s="2" t="n"/>
       <c r="AH370" s="2" t="n"/>
     </row>
-    <row r="371" ht="24" customHeight="1" s="49">
+    <row r="371" ht="24" customHeight="1" s="50">
       <c r="A371" s="13" t="n"/>
       <c r="B371" s="2" t="n"/>
       <c r="C371" s="46" t="n"/>
@@ -33974,7 +34249,7 @@
       <c r="AG371" s="2" t="n"/>
       <c r="AH371" s="2" t="n"/>
     </row>
-    <row r="372" ht="24" customHeight="1" s="49">
+    <row r="372" ht="24" customHeight="1" s="50">
       <c r="A372" s="13" t="n"/>
       <c r="B372" s="2" t="n"/>
       <c r="C372" s="46" t="n"/>
@@ -34010,7 +34285,7 @@
       <c r="AG372" s="2" t="n"/>
       <c r="AH372" s="2" t="n"/>
     </row>
-    <row r="373" ht="24" customHeight="1" s="49">
+    <row r="373" ht="24" customHeight="1" s="50">
       <c r="A373" s="13" t="n"/>
       <c r="B373" s="2" t="n"/>
       <c r="C373" s="46" t="n"/>
@@ -34046,7 +34321,7 @@
       <c r="AG373" s="2" t="n"/>
       <c r="AH373" s="2" t="n"/>
     </row>
-    <row r="374" ht="24" customHeight="1" s="49">
+    <row r="374" ht="24" customHeight="1" s="50">
       <c r="A374" s="13" t="n"/>
       <c r="B374" s="2" t="n"/>
       <c r="C374" s="46" t="n"/>
@@ -34082,7 +34357,7 @@
       <c r="AG374" s="2" t="n"/>
       <c r="AH374" s="2" t="n"/>
     </row>
-    <row r="375" ht="24" customHeight="1" s="49">
+    <row r="375" ht="24" customHeight="1" s="50">
       <c r="A375" s="13" t="n"/>
       <c r="B375" s="2" t="n"/>
       <c r="C375" s="46" t="n"/>
@@ -34118,7 +34393,7 @@
       <c r="AG375" s="2" t="n"/>
       <c r="AH375" s="2" t="n"/>
     </row>
-    <row r="376" ht="24" customHeight="1" s="49">
+    <row r="376" ht="24" customHeight="1" s="50">
       <c r="A376" s="13" t="n"/>
       <c r="B376" s="2" t="n"/>
       <c r="C376" s="46" t="n"/>
@@ -34154,7 +34429,7 @@
       <c r="AG376" s="2" t="n"/>
       <c r="AH376" s="2" t="n"/>
     </row>
-    <row r="377" ht="24" customHeight="1" s="49">
+    <row r="377" ht="24" customHeight="1" s="50">
       <c r="A377" s="13" t="n"/>
       <c r="B377" s="2" t="n"/>
       <c r="C377" s="46" t="n"/>
@@ -34190,7 +34465,7 @@
       <c r="AG377" s="2" t="n"/>
       <c r="AH377" s="2" t="n"/>
     </row>
-    <row r="378" ht="24" customHeight="1" s="49">
+    <row r="378" ht="24" customHeight="1" s="50">
       <c r="A378" s="13" t="n"/>
       <c r="B378" s="2" t="n"/>
       <c r="C378" s="46" t="n"/>
@@ -34226,7 +34501,7 @@
       <c r="AG378" s="2" t="n"/>
       <c r="AH378" s="2" t="n"/>
     </row>
-    <row r="379" ht="24" customHeight="1" s="49">
+    <row r="379" ht="24" customHeight="1" s="50">
       <c r="A379" s="13" t="n"/>
       <c r="B379" s="2" t="n"/>
       <c r="C379" s="46" t="n"/>
@@ -34262,7 +34537,7 @@
       <c r="AG379" s="2" t="n"/>
       <c r="AH379" s="2" t="n"/>
     </row>
-    <row r="380" ht="24" customHeight="1" s="49">
+    <row r="380" ht="24" customHeight="1" s="50">
       <c r="A380" s="13" t="n"/>
       <c r="B380" s="2" t="n"/>
       <c r="C380" s="46" t="n"/>
@@ -34298,7 +34573,7 @@
       <c r="AG380" s="2" t="n"/>
       <c r="AH380" s="2" t="n"/>
     </row>
-    <row r="381" ht="24" customHeight="1" s="49">
+    <row r="381" ht="24" customHeight="1" s="50">
       <c r="A381" s="13" t="n"/>
       <c r="B381" s="2" t="n"/>
       <c r="C381" s="46" t="n"/>
@@ -34334,7 +34609,7 @@
       <c r="AG381" s="2" t="n"/>
       <c r="AH381" s="2" t="n"/>
     </row>
-    <row r="382" ht="24" customHeight="1" s="49">
+    <row r="382" ht="24" customHeight="1" s="50">
       <c r="A382" s="13" t="n"/>
       <c r="B382" s="2" t="n"/>
       <c r="C382" s="46" t="n"/>
@@ -34370,7 +34645,7 @@
       <c r="AG382" s="2" t="n"/>
       <c r="AH382" s="2" t="n"/>
     </row>
-    <row r="383" ht="24" customHeight="1" s="49">
+    <row r="383" ht="24" customHeight="1" s="50">
       <c r="A383" s="13" t="n"/>
       <c r="B383" s="2" t="n"/>
       <c r="C383" s="46" t="n"/>
@@ -34406,7 +34681,7 @@
       <c r="AG383" s="2" t="n"/>
       <c r="AH383" s="2" t="n"/>
     </row>
-    <row r="384" ht="24" customHeight="1" s="49">
+    <row r="384" ht="24" customHeight="1" s="50">
       <c r="A384" s="13" t="n"/>
       <c r="B384" s="2" t="n"/>
       <c r="C384" s="46" t="n"/>
@@ -34442,7 +34717,7 @@
       <c r="AG384" s="2" t="n"/>
       <c r="AH384" s="2" t="n"/>
     </row>
-    <row r="385" ht="24" customHeight="1" s="49">
+    <row r="385" ht="24" customHeight="1" s="50">
       <c r="A385" s="13" t="n"/>
       <c r="B385" s="2" t="n"/>
       <c r="C385" s="46" t="n"/>
@@ -34478,7 +34753,7 @@
       <c r="AG385" s="2" t="n"/>
       <c r="AH385" s="2" t="n"/>
     </row>
-    <row r="386" ht="24" customHeight="1" s="49">
+    <row r="386" ht="24" customHeight="1" s="50">
       <c r="A386" s="13" t="n"/>
       <c r="B386" s="2" t="n"/>
       <c r="C386" s="46" t="n"/>
@@ -34514,7 +34789,7 @@
       <c r="AG386" s="2" t="n"/>
       <c r="AH386" s="2" t="n"/>
     </row>
-    <row r="387" ht="24" customHeight="1" s="49">
+    <row r="387" ht="24" customHeight="1" s="50">
       <c r="A387" s="13" t="n"/>
       <c r="B387" s="2" t="n"/>
       <c r="C387" s="46" t="n"/>
@@ -34550,7 +34825,7 @@
       <c r="AG387" s="2" t="n"/>
       <c r="AH387" s="2" t="n"/>
     </row>
-    <row r="388" ht="24" customHeight="1" s="49">
+    <row r="388" ht="24" customHeight="1" s="50">
       <c r="A388" s="13" t="n"/>
       <c r="B388" s="2" t="n"/>
       <c r="C388" s="46" t="n"/>
@@ -34586,7 +34861,7 @@
       <c r="AG388" s="2" t="n"/>
       <c r="AH388" s="2" t="n"/>
     </row>
-    <row r="389" ht="24" customHeight="1" s="49">
+    <row r="389" ht="24" customHeight="1" s="50">
       <c r="A389" s="13" t="n"/>
       <c r="B389" s="2" t="n"/>
       <c r="C389" s="46" t="n"/>
@@ -34622,7 +34897,7 @@
       <c r="AG389" s="2" t="n"/>
       <c r="AH389" s="2" t="n"/>
     </row>
-    <row r="390" ht="24" customHeight="1" s="49">
+    <row r="390" ht="24" customHeight="1" s="50">
       <c r="A390" s="13" t="n"/>
       <c r="B390" s="2" t="n"/>
       <c r="C390" s="46" t="n"/>
@@ -34658,7 +34933,7 @@
       <c r="AG390" s="2" t="n"/>
       <c r="AH390" s="2" t="n"/>
     </row>
-    <row r="391" ht="24" customHeight="1" s="49">
+    <row r="391" ht="24" customHeight="1" s="50">
       <c r="A391" s="13" t="n"/>
       <c r="B391" s="2" t="n"/>
       <c r="C391" s="46" t="n"/>
@@ -34694,7 +34969,7 @@
       <c r="AG391" s="2" t="n"/>
       <c r="AH391" s="2" t="n"/>
     </row>
-    <row r="392" ht="24" customHeight="1" s="49">
+    <row r="392" ht="24" customHeight="1" s="50">
       <c r="A392" s="13" t="n"/>
       <c r="B392" s="2" t="n"/>
       <c r="C392" s="46" t="n"/>
@@ -34730,7 +35005,7 @@
       <c r="AG392" s="2" t="n"/>
       <c r="AH392" s="2" t="n"/>
     </row>
-    <row r="393" ht="24" customHeight="1" s="49">
+    <row r="393" ht="24" customHeight="1" s="50">
       <c r="A393" s="13" t="n"/>
       <c r="B393" s="2" t="n"/>
       <c r="C393" s="46" t="n"/>
@@ -34766,7 +35041,7 @@
       <c r="AG393" s="2" t="n"/>
       <c r="AH393" s="2" t="n"/>
     </row>
-    <row r="394" ht="24" customHeight="1" s="49">
+    <row r="394" ht="24" customHeight="1" s="50">
       <c r="A394" s="13" t="n"/>
       <c r="B394" s="2" t="n"/>
       <c r="C394" s="46" t="n"/>
@@ -34802,7 +35077,7 @@
       <c r="AG394" s="2" t="n"/>
       <c r="AH394" s="2" t="n"/>
     </row>
-    <row r="395" ht="24" customHeight="1" s="49">
+    <row r="395" ht="24" customHeight="1" s="50">
       <c r="A395" s="13" t="n"/>
       <c r="B395" s="2" t="n"/>
       <c r="C395" s="46" t="n"/>
@@ -34838,7 +35113,7 @@
       <c r="AG395" s="2" t="n"/>
       <c r="AH395" s="2" t="n"/>
     </row>
-    <row r="396" ht="24" customHeight="1" s="49">
+    <row r="396" ht="24" customHeight="1" s="50">
       <c r="A396" s="13" t="n"/>
       <c r="B396" s="2" t="n"/>
       <c r="C396" s="46" t="n"/>
@@ -34874,7 +35149,7 @@
       <c r="AG396" s="2" t="n"/>
       <c r="AH396" s="2" t="n"/>
     </row>
-    <row r="397" ht="24" customHeight="1" s="49">
+    <row r="397" ht="24" customHeight="1" s="50">
       <c r="A397" s="13" t="n"/>
       <c r="B397" s="2" t="n"/>
       <c r="C397" s="46" t="n"/>
@@ -34910,7 +35185,7 @@
       <c r="AG397" s="2" t="n"/>
       <c r="AH397" s="2" t="n"/>
     </row>
-    <row r="398" ht="24" customHeight="1" s="49">
+    <row r="398" ht="24" customHeight="1" s="50">
       <c r="A398" s="13" t="n"/>
       <c r="B398" s="2" t="n"/>
       <c r="C398" s="46" t="n"/>
@@ -34946,7 +35221,7 @@
       <c r="AG398" s="2" t="n"/>
       <c r="AH398" s="2" t="n"/>
     </row>
-    <row r="399" ht="24" customHeight="1" s="49">
+    <row r="399" ht="24" customHeight="1" s="50">
       <c r="A399" s="13" t="n"/>
       <c r="B399" s="2" t="n"/>
       <c r="C399" s="46" t="n"/>
@@ -34982,7 +35257,7 @@
       <c r="AG399" s="2" t="n"/>
       <c r="AH399" s="2" t="n"/>
     </row>
-    <row r="400" ht="24" customHeight="1" s="49">
+    <row r="400" ht="24" customHeight="1" s="50">
       <c r="A400" s="13" t="n"/>
       <c r="B400" s="2" t="n"/>
       <c r="C400" s="46" t="n"/>
@@ -35018,7 +35293,7 @@
       <c r="AG400" s="2" t="n"/>
       <c r="AH400" s="2" t="n"/>
     </row>
-    <row r="401" ht="24" customHeight="1" s="49">
+    <row r="401" ht="24" customHeight="1" s="50">
       <c r="A401" s="12" t="n">
         <v>400</v>
       </c>
@@ -35249,7 +35524,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="27.75" customHeight="1" s="49">
+    <row r="2" ht="27.75" customHeight="1" s="50">
       <c r="A2" s="0" t="n">
         <v>1</v>
       </c>
@@ -35328,7 +35603,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="27.75" customHeight="1" s="49">
+    <row r="3" ht="27.75" customHeight="1" s="50">
       <c r="A3" s="0" t="n">
         <v>2</v>
       </c>
@@ -35769,7 +36044,7 @@
   <dimension ref="A1:K4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.9"/>
   <cols>
-    <col width="18.59765625" customWidth="1" style="50" min="11" max="11"/>
+    <col width="18.59765625" customWidth="1" style="51" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -35823,7 +36098,7 @@
           <t>level2</t>
         </is>
       </c>
-      <c r="K1" s="50" t="inlineStr">
+      <c r="K1" s="51" t="inlineStr">
         <is>
           <t>date</t>
         </is>
@@ -35868,7 +36143,7 @@
           <t>大兴安岭地区</t>
         </is>
       </c>
-      <c r="K2" s="50" t="n">
+      <c r="K2" s="51" t="n">
         <v>25199</v>
       </c>
     </row>
@@ -35908,7 +36183,7 @@
           <t>呼伦贝尔市</t>
         </is>
       </c>
-      <c r="K3" s="50" t="n">
+      <c r="K3" s="51" t="n">
         <v>45993</v>
       </c>
     </row>
@@ -35948,7 +36223,7 @@
           <t>阿勒泰地区</t>
         </is>
       </c>
-      <c r="K4" s="50" t="n">
+      <c r="K4" s="51" t="n">
         <v>45995</v>
       </c>
     </row>

--- a/气象/For_Python_站点信息和记录.xlsx
+++ b/气象/For_Python_站点信息和记录.xlsx
@@ -817,8 +817,8 @@
     <col width="18.59765625" customWidth="1" style="8" min="25" max="25"/>
     <col width="12.59765625" customWidth="1" style="5" min="26" max="30"/>
     <col width="12.59765625" customWidth="1" style="8" min="31" max="32"/>
-    <col width="12.59765625" customWidth="1" style="5" min="33" max="420"/>
-    <col width="12.59765625" customWidth="1" style="5" min="421" max="16384"/>
+    <col width="12.59765625" customWidth="1" style="5" min="33" max="422"/>
+    <col width="12.59765625" customWidth="1" style="5" min="423" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="27.75" customFormat="1" customHeight="1" s="11">
@@ -1041,13 +1041,13 @@
         </is>
       </c>
       <c r="O2" s="32" t="n">
-        <v>0.2</v>
+        <v>2.8</v>
       </c>
       <c r="P2" s="32" t="n">
-        <v>24.7</v>
+        <v>27.3</v>
       </c>
       <c r="Q2" s="32" t="n">
-        <v>13.85</v>
+        <v>15.64</v>
       </c>
       <c r="R2" s="23" t="inlineStr">
         <is>
@@ -1147,10 +1147,10 @@
         </is>
       </c>
       <c r="O3" s="32" t="n">
-        <v>3</v>
+        <v>4.7</v>
       </c>
       <c r="P3" s="32" t="n">
-        <v>24.5</v>
+        <v>25.4</v>
       </c>
       <c r="Q3" s="32" t="n"/>
       <c r="R3" s="23" t="n"/>
@@ -1251,10 +1251,10 @@
         </is>
       </c>
       <c r="O4" s="32" t="n">
-        <v>-0.6</v>
+        <v>0.6</v>
       </c>
       <c r="P4" s="32" t="n">
-        <v>22.9</v>
+        <v>24.8</v>
       </c>
       <c r="Q4" s="32" t="n"/>
       <c r="R4" s="23" t="n"/>
@@ -1443,10 +1443,10 @@
         </is>
       </c>
       <c r="O6" s="32" t="n">
-        <v>-5</v>
+        <v>-4.4</v>
       </c>
       <c r="P6" s="32" t="n">
-        <v>14.4</v>
+        <v>17.5</v>
       </c>
       <c r="Q6" s="32" t="n"/>
       <c r="R6" s="23" t="n"/>
@@ -1543,10 +1543,10 @@
         </is>
       </c>
       <c r="O7" s="32" t="n">
-        <v>-4.7</v>
+        <v>-1.5</v>
       </c>
       <c r="P7" s="32" t="n">
-        <v>18.1</v>
+        <v>20.7</v>
       </c>
       <c r="Q7" s="32" t="n"/>
       <c r="R7" s="23" t="n"/>
@@ -1651,13 +1651,13 @@
       </c>
       <c r="N8" s="2" t="n"/>
       <c r="O8" s="32" t="n">
-        <v>-0.3</v>
+        <v>-1.6</v>
       </c>
       <c r="P8" s="32" t="n">
-        <v>18.6</v>
+        <v>24.8</v>
       </c>
       <c r="Q8" s="32" t="n">
-        <v>9.59</v>
+        <v>11.88</v>
       </c>
       <c r="R8" s="23" t="inlineStr">
         <is>
@@ -1763,13 +1763,13 @@
       </c>
       <c r="N9" s="2" t="n"/>
       <c r="O9" s="32" t="n">
-        <v>2.8</v>
+        <v>5.5</v>
       </c>
       <c r="P9" s="32" t="n">
-        <v>22.3</v>
+        <v>26.8</v>
       </c>
       <c r="Q9" s="32" t="n">
-        <v>13.1</v>
+        <v>16.65</v>
       </c>
       <c r="R9" s="23" t="inlineStr">
         <is>
@@ -1883,13 +1883,13 @@
         </is>
       </c>
       <c r="O10" s="32" t="n">
-        <v>-2.9</v>
+        <v>-1.8</v>
       </c>
       <c r="P10" s="32" t="n">
-        <v>21</v>
+        <v>23.3</v>
       </c>
       <c r="Q10" s="32" t="n">
-        <v>10.36</v>
+        <v>11.71</v>
       </c>
       <c r="R10" s="23" t="inlineStr">
         <is>
@@ -1999,13 +1999,13 @@
         </is>
       </c>
       <c r="O11" s="32" t="n">
-        <v>-5.1</v>
+        <v>-3.2</v>
       </c>
       <c r="P11" s="32" t="n">
-        <v>15.9</v>
+        <v>18.9</v>
       </c>
       <c r="Q11" s="32" t="n">
-        <v>6.58</v>
+        <v>9.44</v>
       </c>
       <c r="R11" s="23" t="inlineStr">
         <is>
@@ -2111,13 +2111,13 @@
       </c>
       <c r="N12" s="2" t="n"/>
       <c r="O12" s="32" t="n">
-        <v>-3.1</v>
+        <v>-1.3</v>
       </c>
       <c r="P12" s="32" t="n">
-        <v>18.8</v>
+        <v>21</v>
       </c>
       <c r="Q12" s="32" t="n">
-        <v>8.34</v>
+        <v>10.75</v>
       </c>
       <c r="R12" s="23" t="inlineStr">
         <is>
@@ -2227,13 +2227,13 @@
         </is>
       </c>
       <c r="O13" s="32" t="n">
-        <v>-4.7</v>
+        <v>-2.5</v>
       </c>
       <c r="P13" s="32" t="n">
-        <v>17.7</v>
+        <v>21</v>
       </c>
       <c r="Q13" s="32" t="n">
-        <v>6.75</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="R13" s="23" t="inlineStr">
         <is>
@@ -2339,13 +2339,13 @@
       </c>
       <c r="N14" s="2" t="n"/>
       <c r="O14" s="32" t="n">
-        <v>0.4</v>
+        <v>2.1</v>
       </c>
       <c r="P14" s="32" t="n">
-        <v>14.5</v>
+        <v>21.1</v>
       </c>
       <c r="Q14" s="32" t="n">
-        <v>7.98</v>
+        <v>11.31</v>
       </c>
       <c r="R14" s="23" t="inlineStr">
         <is>
@@ -2445,10 +2445,10 @@
       </c>
       <c r="N15" s="2" t="n"/>
       <c r="O15" s="32" t="n">
-        <v>-5.4</v>
+        <v>-6.3</v>
       </c>
       <c r="P15" s="32" t="n">
-        <v>11.3</v>
+        <v>17.9</v>
       </c>
       <c r="Q15" s="32" t="n"/>
       <c r="R15" s="23" t="n"/>
@@ -2728,12 +2728,8 @@
         </is>
       </c>
       <c r="N18" s="2" t="n"/>
-      <c r="O18" s="32" t="n">
-        <v>-7.3</v>
-      </c>
-      <c r="P18" s="32" t="n">
-        <v>16.2</v>
-      </c>
+      <c r="O18" s="32" t="n"/>
+      <c r="P18" s="32" t="n"/>
       <c r="Q18" s="32" t="n"/>
       <c r="R18" s="23" t="n"/>
       <c r="S18" s="37" t="n"/>
@@ -7676,8 +7672,12 @@
         </is>
       </c>
       <c r="N73" s="2" t="n"/>
-      <c r="O73" s="32" t="n"/>
-      <c r="P73" s="32" t="n"/>
+      <c r="O73" s="32" t="n">
+        <v>-6.4</v>
+      </c>
+      <c r="P73" s="32" t="n">
+        <v>20.8</v>
+      </c>
       <c r="Q73" s="32" t="n"/>
       <c r="R73" s="23" t="n"/>
       <c r="S73" s="37" t="n"/>
@@ -8071,13 +8071,13 @@
         </is>
       </c>
       <c r="O77" s="32" t="n">
-        <v>-3</v>
+        <v>-9.5</v>
       </c>
       <c r="P77" s="32" t="n">
-        <v>6.4</v>
+        <v>6.9</v>
       </c>
       <c r="Q77" s="32" t="n">
-        <v>0.44</v>
+        <v>-0.49</v>
       </c>
       <c r="R77" s="23" t="inlineStr">
         <is>
@@ -8497,13 +8497,13 @@
         </is>
       </c>
       <c r="O81" s="32" t="n">
-        <v>-7</v>
+        <v>-6.9</v>
       </c>
       <c r="P81" s="32" t="n">
-        <v>9.800000000000001</v>
+        <v>14.5</v>
       </c>
       <c r="Q81" s="32" t="n">
-        <v>2.14</v>
+        <v>4.49</v>
       </c>
       <c r="R81" s="23" t="inlineStr">
         <is>
@@ -8621,10 +8621,10 @@
         <v>-6.4</v>
       </c>
       <c r="P82" s="32" t="n">
-        <v>9.199999999999999</v>
+        <v>14.5</v>
       </c>
       <c r="Q82" s="32" t="n">
-        <v>1.7</v>
+        <v>4.34</v>
       </c>
       <c r="R82" s="23" t="inlineStr">
         <is>
@@ -8836,13 +8836,13 @@
         </is>
       </c>
       <c r="O84" s="32" t="n">
-        <v>-3.9</v>
+        <v>-3.3</v>
       </c>
       <c r="P84" s="32" t="n">
-        <v>20.1</v>
+        <v>25.5</v>
       </c>
       <c r="Q84" s="32" t="n">
-        <v>8.06</v>
+        <v>10.71</v>
       </c>
       <c r="R84" s="23" t="inlineStr">
         <is>
@@ -9054,13 +9054,13 @@
       </c>
       <c r="N86" s="2" t="n"/>
       <c r="O86" s="32" t="n">
-        <v>4.3</v>
+        <v>6.2</v>
       </c>
       <c r="P86" s="32" t="n">
-        <v>28.4</v>
+        <v>28.5</v>
       </c>
       <c r="Q86" s="32" t="n">
-        <v>16.98</v>
+        <v>18.16</v>
       </c>
       <c r="R86" s="23" t="inlineStr">
         <is>
@@ -9280,13 +9280,13 @@
       </c>
       <c r="N88" s="2" t="n"/>
       <c r="O88" s="32" t="n">
-        <v>-2.5</v>
+        <v>1.7</v>
       </c>
       <c r="P88" s="32" t="n">
-        <v>21.8</v>
+        <v>19.7</v>
       </c>
       <c r="Q88" s="32" t="n">
-        <v>10.64</v>
+        <v>11.82</v>
       </c>
       <c r="R88" s="23" t="inlineStr">
         <is>
@@ -9690,13 +9690,13 @@
       </c>
       <c r="N92" s="2" t="n"/>
       <c r="O92" s="32" t="n">
-        <v>-3.6</v>
+        <v>0</v>
       </c>
       <c r="P92" s="32" t="n">
-        <v>13.9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Q92" s="32" t="n">
-        <v>7.29</v>
+        <v>1.27</v>
       </c>
       <c r="R92" s="23" t="inlineStr">
         <is>
@@ -9802,13 +9802,13 @@
       </c>
       <c r="N93" s="2" t="n"/>
       <c r="O93" s="32" t="n">
-        <v>5.8</v>
+        <v>8.6</v>
       </c>
       <c r="P93" s="32" t="n">
-        <v>22.5</v>
+        <v>19.3</v>
       </c>
       <c r="Q93" s="32" t="n">
-        <v>14.56</v>
+        <v>13.47</v>
       </c>
       <c r="R93" s="23" t="inlineStr">
         <is>
@@ -10032,13 +10032,13 @@
       </c>
       <c r="N95" s="2" t="n"/>
       <c r="O95" s="32" t="n">
-        <v>8.300000000000001</v>
+        <v>5.3</v>
       </c>
       <c r="P95" s="32" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="Q95" s="32" t="n">
-        <v>13.88</v>
+        <v>11.71</v>
       </c>
       <c r="R95" s="23" t="inlineStr">
         <is>
@@ -10270,13 +10270,13 @@
       </c>
       <c r="N97" s="2" t="n"/>
       <c r="O97" s="32" t="n">
-        <v>8.4</v>
+        <v>1.7</v>
       </c>
       <c r="P97" s="32" t="n">
-        <v>16.5</v>
+        <v>16.7</v>
       </c>
       <c r="Q97" s="32" t="n">
-        <v>13.15</v>
+        <v>10.52</v>
       </c>
       <c r="R97" s="23" t="inlineStr">
         <is>
@@ -10826,13 +10826,13 @@
       </c>
       <c r="N102" s="2" t="n"/>
       <c r="O102" s="32" t="n">
-        <v>-1.5</v>
+        <v>-6.3</v>
       </c>
       <c r="P102" s="32" t="n">
-        <v>12</v>
+        <v>13.7</v>
       </c>
       <c r="Q102" s="32" t="n">
-        <v>5.59</v>
+        <v>4.85</v>
       </c>
       <c r="R102" s="23" t="inlineStr">
         <is>
@@ -11162,13 +11162,13 @@
         </is>
       </c>
       <c r="O105" s="32" t="n">
-        <v>-7.5</v>
+        <v>-8.300000000000001</v>
       </c>
       <c r="P105" s="32" t="n">
-        <v>9.4</v>
+        <v>12.2</v>
       </c>
       <c r="Q105" s="32" t="n">
-        <v>0.97</v>
+        <v>2.96</v>
       </c>
       <c r="R105" s="23" t="inlineStr">
         <is>
@@ -11996,13 +11996,13 @@
       </c>
       <c r="N113" s="2" t="n"/>
       <c r="O113" s="32" t="n">
-        <v>-7.5</v>
+        <v>-8.4</v>
       </c>
       <c r="P113" s="32" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="Q113" s="32" t="n">
-        <v>-2.96</v>
+        <v>-3.33</v>
       </c>
       <c r="R113" s="23" t="inlineStr">
         <is>
@@ -12112,13 +12112,13 @@
         </is>
       </c>
       <c r="O114" s="32" t="n">
-        <v>-14.2</v>
+        <v>-14.4</v>
       </c>
       <c r="P114" s="32" t="n">
-        <v>-1.1</v>
+        <v>-0.8</v>
       </c>
       <c r="Q114" s="32" t="n">
-        <v>-7.66</v>
+        <v>-6.23</v>
       </c>
       <c r="R114" s="23" t="inlineStr">
         <is>
@@ -12236,13 +12236,13 @@
         </is>
       </c>
       <c r="O115" s="32" t="n">
-        <v>-10.9</v>
+        <v>-12.6</v>
       </c>
       <c r="P115" s="32" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q115" s="32" t="n">
-        <v>-5.49</v>
+        <v>-5.35</v>
       </c>
       <c r="R115" s="23" t="inlineStr">
         <is>
@@ -12792,13 +12792,13 @@
       </c>
       <c r="N120" s="2" t="n"/>
       <c r="O120" s="32" t="n">
-        <v>15.3</v>
+        <v>18.7</v>
       </c>
       <c r="P120" s="32" t="n">
-        <v>33.1</v>
+        <v>34.8</v>
       </c>
       <c r="Q120" s="32" t="n">
-        <v>24.96</v>
+        <v>27.2</v>
       </c>
       <c r="R120" s="23" t="inlineStr">
         <is>
@@ -12908,13 +12908,13 @@
       </c>
       <c r="N121" s="2" t="n"/>
       <c r="O121" s="32" t="n">
-        <v>14.1</v>
+        <v>15.6</v>
       </c>
       <c r="P121" s="32" t="n">
-        <v>25.4</v>
+        <v>26.6</v>
       </c>
       <c r="Q121" s="32" t="n">
-        <v>19.46</v>
+        <v>21.6</v>
       </c>
       <c r="R121" s="23" t="inlineStr">
         <is>
@@ -13032,13 +13032,13 @@
       </c>
       <c r="N122" s="2" t="n"/>
       <c r="O122" s="32" t="n">
-        <v>-2.9</v>
+        <v>-4.3</v>
       </c>
       <c r="P122" s="32" t="n">
-        <v>16.1</v>
+        <v>18.3</v>
       </c>
       <c r="Q122" s="32" t="n">
-        <v>7.3</v>
+        <v>7.29</v>
       </c>
       <c r="R122" s="23" t="inlineStr">
         <is>
@@ -13254,13 +13254,13 @@
       </c>
       <c r="N124" s="2" t="n"/>
       <c r="O124" s="32" t="n">
-        <v>6.2</v>
+        <v>4.8</v>
       </c>
       <c r="P124" s="32" t="n">
-        <v>18.3</v>
+        <v>18.4</v>
       </c>
       <c r="Q124" s="32" t="n">
-        <v>12.09</v>
+        <v>11.61</v>
       </c>
       <c r="R124" s="23" t="inlineStr">
         <is>
@@ -13378,13 +13378,13 @@
       </c>
       <c r="N125" s="2" t="n"/>
       <c r="O125" s="32" t="n">
-        <v>12</v>
+        <v>6.8</v>
       </c>
       <c r="P125" s="32" t="n">
-        <v>23.3</v>
+        <v>20.9</v>
       </c>
       <c r="Q125" s="32" t="n">
-        <v>16.4</v>
+        <v>14.25</v>
       </c>
       <c r="R125" s="23" t="inlineStr">
         <is>
@@ -13481,9 +13481,15 @@
         </is>
       </c>
       <c r="N126" s="2" t="n"/>
-      <c r="O126" s="32" t="n"/>
-      <c r="P126" s="32" t="n"/>
-      <c r="Q126" s="32" t="n"/>
+      <c r="O126" s="32" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="P126" s="32" t="n">
+        <v>20.3</v>
+      </c>
+      <c r="Q126" s="32" t="n">
+        <v>14.4</v>
+      </c>
       <c r="R126" s="23" t="inlineStr">
         <is>
           <t>Y</t>
@@ -13588,13 +13594,13 @@
       </c>
       <c r="N127" s="2" t="n"/>
       <c r="O127" s="32" t="n">
-        <v>9.5</v>
+        <v>4.8</v>
       </c>
       <c r="P127" s="32" t="n">
-        <v>17.2</v>
+        <v>24.1</v>
       </c>
       <c r="Q127" s="32" t="n">
-        <v>13.19</v>
+        <v>14.58</v>
       </c>
       <c r="R127" s="23" t="inlineStr">
         <is>
@@ -13708,13 +13714,13 @@
       </c>
       <c r="N128" s="2" t="n"/>
       <c r="O128" s="32" t="n">
-        <v>14.4</v>
+        <v>9.1</v>
       </c>
       <c r="P128" s="32" t="n">
-        <v>23.4</v>
+        <v>25.4</v>
       </c>
       <c r="Q128" s="32" t="n">
-        <v>18.94</v>
+        <v>17.43</v>
       </c>
       <c r="R128" s="23" t="inlineStr">
         <is>
@@ -13820,13 +13826,13 @@
       </c>
       <c r="N129" s="2" t="n"/>
       <c r="O129" s="32" t="n">
-        <v>12.4</v>
+        <v>1.9</v>
       </c>
       <c r="P129" s="32" t="n">
-        <v>20.9</v>
+        <v>24.3</v>
       </c>
       <c r="Q129" s="32" t="n">
-        <v>14.97</v>
+        <v>13.89</v>
       </c>
       <c r="R129" s="23" t="inlineStr">
         <is>
@@ -13940,12 +13946,14 @@
       </c>
       <c r="N130" s="2" t="n"/>
       <c r="O130" s="32" t="n">
-        <v>-0.1</v>
+        <v>-1.3</v>
       </c>
       <c r="P130" s="32" t="n">
-        <v>11.3</v>
-      </c>
-      <c r="Q130" s="32" t="n"/>
+        <v>17.5</v>
+      </c>
+      <c r="Q130" s="32" t="n">
+        <v>7.25</v>
+      </c>
       <c r="R130" s="23" t="inlineStr">
         <is>
           <t>Y</t>
@@ -14058,13 +14066,13 @@
       </c>
       <c r="N131" s="2" t="n"/>
       <c r="O131" s="32" t="n">
-        <v>16</v>
+        <v>11.2</v>
       </c>
       <c r="P131" s="32" t="n">
-        <v>22.5</v>
+        <v>22.4</v>
       </c>
       <c r="Q131" s="32" t="n">
-        <v>18.85</v>
+        <v>14.9</v>
       </c>
       <c r="R131" s="23" t="inlineStr">
         <is>
@@ -14174,13 +14182,13 @@
       </c>
       <c r="N132" s="2" t="n"/>
       <c r="O132" s="32" t="n">
-        <v>14.9</v>
+        <v>11.3</v>
       </c>
       <c r="P132" s="32" t="n">
-        <v>23.5</v>
+        <v>27.6</v>
       </c>
       <c r="Q132" s="32" t="n">
-        <v>18.36</v>
+        <v>20.98</v>
       </c>
       <c r="R132" s="23" t="inlineStr">
         <is>
@@ -14290,13 +14298,13 @@
       </c>
       <c r="N133" s="2" t="n"/>
       <c r="O133" s="32" t="n">
-        <v>14.9</v>
+        <v>13.1</v>
       </c>
       <c r="P133" s="32" t="n">
-        <v>24.8</v>
+        <v>25.2</v>
       </c>
       <c r="Q133" s="32" t="n">
-        <v>18.64</v>
+        <v>19.39</v>
       </c>
       <c r="R133" s="23" t="inlineStr">
         <is>
@@ -14512,13 +14520,13 @@
       </c>
       <c r="N135" s="2" t="n"/>
       <c r="O135" s="32" t="n">
-        <v>16.5</v>
+        <v>16.2</v>
       </c>
       <c r="P135" s="32" t="n">
-        <v>26.7</v>
+        <v>24.2</v>
       </c>
       <c r="Q135" s="32" t="n">
-        <v>19.75</v>
+        <v>19.43</v>
       </c>
       <c r="R135" s="23" t="inlineStr">
         <is>
@@ -14628,13 +14636,13 @@
       </c>
       <c r="N136" s="2" t="n"/>
       <c r="O136" s="32" t="n">
-        <v>18.6</v>
+        <v>17.8</v>
       </c>
       <c r="P136" s="32" t="n">
-        <v>27.2</v>
+        <v>26.4</v>
       </c>
       <c r="Q136" s="32" t="n">
-        <v>21.99</v>
+        <v>21.48</v>
       </c>
       <c r="R136" s="23" t="inlineStr">
         <is>
@@ -14744,13 +14752,13 @@
       </c>
       <c r="N137" s="2" t="n"/>
       <c r="O137" s="32" t="n">
-        <v>15.7</v>
+        <v>14.7</v>
       </c>
       <c r="P137" s="32" t="n">
-        <v>22</v>
+        <v>25.8</v>
       </c>
       <c r="Q137" s="32" t="n">
-        <v>17.92</v>
+        <v>19.44</v>
       </c>
       <c r="R137" s="23" t="inlineStr">
         <is>
@@ -14860,13 +14868,13 @@
       </c>
       <c r="N138" s="2" t="n"/>
       <c r="O138" s="32" t="n">
-        <v>15.5</v>
+        <v>14.8</v>
       </c>
       <c r="P138" s="32" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q138" s="32" t="n">
-        <v>17.95</v>
+        <v>17.89</v>
       </c>
       <c r="R138" s="23" t="inlineStr">
         <is>
@@ -14976,13 +14984,13 @@
       </c>
       <c r="N139" s="2" t="n"/>
       <c r="O139" s="32" t="n">
-        <v>16.2</v>
+        <v>15.2</v>
       </c>
       <c r="P139" s="32" t="n">
-        <v>20.8</v>
+        <v>23.3</v>
       </c>
       <c r="Q139" s="32" t="n">
-        <v>17.67</v>
+        <v>18.38</v>
       </c>
       <c r="R139" s="23" t="inlineStr">
         <is>
@@ -15092,13 +15100,13 @@
       </c>
       <c r="N140" s="2" t="n"/>
       <c r="O140" s="32" t="n">
-        <v>15</v>
+        <v>16.3</v>
       </c>
       <c r="P140" s="32" t="n">
-        <v>22.7</v>
+        <v>23.2</v>
       </c>
       <c r="Q140" s="32" t="n">
-        <v>19.16</v>
+        <v>19.48</v>
       </c>
       <c r="R140" s="23" t="inlineStr">
         <is>
@@ -15310,13 +15318,13 @@
       </c>
       <c r="N142" s="2" t="n"/>
       <c r="O142" s="32" t="n">
-        <v>16.3</v>
+        <v>21.1</v>
       </c>
       <c r="P142" s="32" t="n">
-        <v>28.5</v>
+        <v>27.7</v>
       </c>
       <c r="Q142" s="32" t="n">
-        <v>21.9</v>
+        <v>23.57</v>
       </c>
       <c r="R142" s="23" t="inlineStr">
         <is>
@@ -15426,13 +15434,13 @@
       </c>
       <c r="N143" s="2" t="n"/>
       <c r="O143" s="32" t="n">
-        <v>21.6</v>
+        <v>22</v>
       </c>
       <c r="P143" s="32" t="n">
-        <v>27.5</v>
+        <v>26.9</v>
       </c>
       <c r="Q143" s="32" t="n">
-        <v>24.64</v>
+        <v>24.38</v>
       </c>
       <c r="R143" s="23" t="inlineStr">
         <is>
@@ -15742,13 +15750,13 @@
       </c>
       <c r="N146" s="2" t="n"/>
       <c r="O146" s="32" t="n">
-        <v>24.9</v>
+        <v>26.6</v>
       </c>
       <c r="P146" s="32" t="n">
-        <v>31.7</v>
+        <v>32.1</v>
       </c>
       <c r="Q146" s="32" t="n">
-        <v>28.31</v>
+        <v>28.96</v>
       </c>
       <c r="R146" s="23" t="inlineStr">
         <is>
@@ -15850,13 +15858,13 @@
       </c>
       <c r="N147" s="2" t="n"/>
       <c r="O147" s="32" t="n">
-        <v>21.9</v>
+        <v>19.9</v>
       </c>
       <c r="P147" s="32" t="n">
-        <v>30</v>
+        <v>25.2</v>
       </c>
       <c r="Q147" s="32" t="n">
-        <v>24.54</v>
+        <v>22.27</v>
       </c>
       <c r="R147" s="23" t="inlineStr">
         <is>
@@ -15966,13 +15974,13 @@
       </c>
       <c r="N148" s="2" t="n"/>
       <c r="O148" s="32" t="n">
-        <v>20.3</v>
+        <v>20.2</v>
       </c>
       <c r="P148" s="32" t="n">
-        <v>25</v>
+        <v>28.4</v>
       </c>
       <c r="Q148" s="32" t="n">
-        <v>21.99</v>
+        <v>22.76</v>
       </c>
       <c r="R148" s="23" t="inlineStr">
         <is>
@@ -16078,13 +16086,13 @@
       </c>
       <c r="N149" s="2" t="n"/>
       <c r="O149" s="32" t="n">
-        <v>13.6</v>
+        <v>9</v>
       </c>
       <c r="P149" s="32" t="n">
-        <v>19.5</v>
+        <v>16.6</v>
       </c>
       <c r="Q149" s="32" t="n">
-        <v>15.55</v>
+        <v>11.96</v>
       </c>
       <c r="R149" s="23" t="inlineStr">
         <is>
@@ -16194,13 +16202,13 @@
       </c>
       <c r="N150" s="2" t="n"/>
       <c r="O150" s="32" t="n">
-        <v>13.6</v>
+        <v>11.9</v>
       </c>
       <c r="P150" s="32" t="n">
-        <v>20.1</v>
+        <v>14.2</v>
       </c>
       <c r="Q150" s="32" t="n">
-        <v>16.69</v>
+        <v>13.01</v>
       </c>
       <c r="R150" s="23" t="inlineStr">
         <is>
@@ -16310,13 +16318,13 @@
       </c>
       <c r="N151" s="2" t="n"/>
       <c r="O151" s="32" t="n">
-        <v>16.7</v>
+        <v>19.1</v>
       </c>
       <c r="P151" s="32" t="n">
-        <v>24.2</v>
+        <v>23.6</v>
       </c>
       <c r="Q151" s="32" t="n">
-        <v>19.96</v>
+        <v>21.15</v>
       </c>
       <c r="R151" s="23" t="inlineStr">
         <is>
@@ -16519,10 +16527,10 @@
         <v>14.8</v>
       </c>
       <c r="P153" s="32" t="n">
-        <v>24.9</v>
+        <v>22.4</v>
       </c>
       <c r="Q153" s="32" t="n">
-        <v>18.96</v>
+        <v>18.48</v>
       </c>
       <c r="R153" s="23" t="inlineStr">
         <is>
@@ -16636,13 +16644,13 @@
       </c>
       <c r="N154" s="2" t="n"/>
       <c r="O154" s="32" t="n">
-        <v>2.4</v>
+        <v>3.5</v>
       </c>
       <c r="P154" s="32" t="n">
-        <v>13.9</v>
+        <v>18</v>
       </c>
       <c r="Q154" s="32" t="n">
-        <v>8.1</v>
+        <v>10.61</v>
       </c>
       <c r="R154" s="23" t="inlineStr">
         <is>
@@ -16935,9 +16943,15 @@
         </is>
       </c>
       <c r="N157" s="2" t="n"/>
-      <c r="O157" s="32" t="n"/>
-      <c r="P157" s="32" t="n"/>
-      <c r="Q157" s="32" t="n"/>
+      <c r="O157" s="32" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="P157" s="32" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="Q157" s="32" t="n">
+        <v>19.25</v>
+      </c>
       <c r="R157" s="23" t="inlineStr">
         <is>
           <t>Y</t>
@@ -17319,9 +17333,15 @@
         </is>
       </c>
       <c r="N161" s="2" t="n"/>
-      <c r="O161" s="32" t="n"/>
-      <c r="P161" s="32" t="n"/>
-      <c r="Q161" s="32" t="n"/>
+      <c r="O161" s="32" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="P161" s="32" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="Q161" s="32" t="n">
+        <v>12.61</v>
+      </c>
       <c r="R161" s="23" t="inlineStr">
         <is>
           <t>Y</t>
@@ -17430,10 +17450,10 @@
         </is>
       </c>
       <c r="O162" s="32" t="n">
-        <v>-3.2</v>
+        <v>-10</v>
       </c>
       <c r="P162" s="32" t="n">
-        <v>10</v>
+        <v>12.9</v>
       </c>
       <c r="Q162" s="32" t="n"/>
       <c r="R162" s="23" t="inlineStr">
@@ -18290,10 +18310,10 @@
         </is>
       </c>
       <c r="O170" s="32" t="n">
-        <v>-6.1</v>
+        <v>-4.9</v>
       </c>
       <c r="P170" s="32" t="n">
-        <v>9.300000000000001</v>
+        <v>11.3</v>
       </c>
       <c r="Q170" s="32" t="n"/>
       <c r="R170" s="23" t="inlineStr">
@@ -18400,7 +18420,7 @@
       </c>
       <c r="N171" s="2" t="n"/>
       <c r="O171" s="32" t="n">
-        <v>-1.5</v>
+        <v>-0.2</v>
       </c>
       <c r="P171" s="32" t="n">
         <v>7.3</v>
@@ -18616,10 +18636,10 @@
       </c>
       <c r="N173" s="2" t="n"/>
       <c r="O173" s="32" t="n">
-        <v>-0.5</v>
+        <v>-4.2</v>
       </c>
       <c r="P173" s="32" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Q173" s="32" t="n"/>
       <c r="R173" s="23" t="inlineStr">
@@ -18721,8 +18741,12 @@
         </is>
       </c>
       <c r="N174" s="2" t="n"/>
-      <c r="O174" s="32" t="n"/>
-      <c r="P174" s="32" t="n"/>
+      <c r="O174" s="32" t="n">
+        <v>-7.3</v>
+      </c>
+      <c r="P174" s="32" t="n">
+        <v>-1.3</v>
+      </c>
       <c r="Q174" s="32" t="n"/>
       <c r="R174" s="23" t="inlineStr">
         <is>
@@ -18938,13 +18962,13 @@
       </c>
       <c r="N176" s="2" t="n"/>
       <c r="O176" s="32" t="n">
-        <v>9.199999999999999</v>
+        <v>4</v>
       </c>
       <c r="P176" s="32" t="n">
-        <v>12.6</v>
+        <v>12.4</v>
       </c>
       <c r="Q176" s="32" t="n">
-        <v>10.5</v>
+        <v>6.71</v>
       </c>
       <c r="R176" s="23" t="inlineStr">
         <is>
@@ -19042,13 +19066,13 @@
       </c>
       <c r="N177" s="2" t="n"/>
       <c r="O177" s="32" t="n">
-        <v>-5.7</v>
+        <v>-8.6</v>
       </c>
       <c r="P177" s="32" t="n">
-        <v>0.6</v>
+        <v>-2.8</v>
       </c>
       <c r="Q177" s="32" t="n">
-        <v>-3.12</v>
+        <v>-5.88</v>
       </c>
       <c r="R177" s="23" t="inlineStr">
         <is>
@@ -22560,8 +22584,12 @@
         </is>
       </c>
       <c r="N213" s="2" t="n"/>
-      <c r="O213" s="32" t="n"/>
-      <c r="P213" s="32" t="n"/>
+      <c r="O213" s="32" t="n">
+        <v>-10.7</v>
+      </c>
+      <c r="P213" s="32" t="n">
+        <v>13.1</v>
+      </c>
       <c r="Q213" s="32" t="n"/>
       <c r="R213" s="23" t="inlineStr">
         <is>
@@ -22764,12 +22792,8 @@
         </is>
       </c>
       <c r="N215" s="2" t="n"/>
-      <c r="O215" s="32" t="n">
-        <v>-8.4</v>
-      </c>
-      <c r="P215" s="32" t="n">
-        <v>10.5</v>
-      </c>
+      <c r="O215" s="32" t="n"/>
+      <c r="P215" s="32" t="n"/>
       <c r="Q215" s="32" t="n"/>
       <c r="R215" s="23" t="inlineStr">
         <is>
@@ -25218,8 +25242,12 @@
         </is>
       </c>
       <c r="N240" s="2" t="n"/>
-      <c r="O240" s="32" t="n"/>
-      <c r="P240" s="32" t="n"/>
+      <c r="O240" s="32" t="n">
+        <v>-8.800000000000001</v>
+      </c>
+      <c r="P240" s="32" t="n">
+        <v>-3.5</v>
+      </c>
       <c r="Q240" s="32" t="n"/>
       <c r="R240" s="23" t="inlineStr">
         <is>
@@ -27659,10 +27687,10 @@
       </c>
       <c r="N265" s="2" t="n"/>
       <c r="O265" s="32" t="n">
-        <v>-60.2</v>
+        <v>-59.8</v>
       </c>
       <c r="P265" s="32" t="n">
-        <v>-55.1</v>
+        <v>-51.9</v>
       </c>
       <c r="Q265" s="32" t="n"/>
       <c r="R265" s="23" t="inlineStr">
@@ -30499,10 +30527,10 @@
       </c>
       <c r="N295" s="2" t="n"/>
       <c r="O295" s="32" t="n">
-        <v>-13.2</v>
+        <v>-10.9</v>
       </c>
       <c r="P295" s="32" t="n">
-        <v>1.5</v>
+        <v>4.1</v>
       </c>
       <c r="Q295" s="32" t="n"/>
       <c r="R295" s="23" t="inlineStr">
@@ -31093,13 +31121,13 @@
       </c>
       <c r="N301" s="2" t="n"/>
       <c r="O301" s="32" t="n">
-        <v>23.1</v>
+        <v>23.2</v>
       </c>
       <c r="P301" s="32" t="n">
-        <v>35.5</v>
+        <v>35.2</v>
       </c>
       <c r="Q301" s="32" t="n">
-        <v>28.49</v>
+        <v>27.2</v>
       </c>
       <c r="R301" s="23" t="inlineStr">
         <is>
@@ -31490,9 +31518,15 @@
         </is>
       </c>
       <c r="N305" s="2" t="n"/>
-      <c r="O305" s="32" t="n"/>
-      <c r="P305" s="32" t="n"/>
-      <c r="Q305" s="32" t="n"/>
+      <c r="O305" s="32" t="n">
+        <v>-12.5</v>
+      </c>
+      <c r="P305" s="32" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="Q305" s="32" t="n">
+        <v>-3.38</v>
+      </c>
       <c r="R305" s="23" t="inlineStr">
         <is>
           <t>Y</t>
@@ -31801,10 +31835,10 @@
       </c>
       <c r="N308" s="2" t="n"/>
       <c r="O308" s="32" t="n">
-        <v>-15.6</v>
+        <v>-16.1</v>
       </c>
       <c r="P308" s="32" t="n">
-        <v>-5.1</v>
+        <v>-3.7</v>
       </c>
       <c r="Q308" s="32" t="n"/>
       <c r="R308" s="23" t="inlineStr">
@@ -31990,7 +32024,7 @@
       </c>
       <c r="K310" s="31" t="inlineStr">
         <is>
-          <t>🇨🇳</t>
+          <t>🇷🇺</t>
         </is>
       </c>
       <c r="L310" s="2" t="n"/>
@@ -32000,12 +32034,8 @@
         </is>
       </c>
       <c r="N310" s="2" t="n"/>
-      <c r="O310" s="32" t="n">
-        <v>-22.1</v>
-      </c>
-      <c r="P310" s="32" t="n">
-        <v>-6.8</v>
-      </c>
+      <c r="O310" s="32" t="n"/>
+      <c r="P310" s="32" t="n"/>
       <c r="Q310" s="32" t="n"/>
       <c r="R310" s="23" t="inlineStr">
         <is>

--- a/气象/For_Python_站点信息和记录.xlsx
+++ b/气象/For_Python_站点信息和记录.xlsx
@@ -817,8 +817,8 @@
     <col width="18.59765625" customWidth="1" style="8" min="25" max="25"/>
     <col width="12.59765625" customWidth="1" style="5" min="26" max="30"/>
     <col width="12.59765625" customWidth="1" style="8" min="31" max="32"/>
-    <col width="12.59765625" customWidth="1" style="5" min="33" max="422"/>
-    <col width="12.59765625" customWidth="1" style="5" min="423" max="16384"/>
+    <col width="12.59765625" customWidth="1" style="5" min="33" max="433"/>
+    <col width="12.59765625" customWidth="1" style="5" min="434" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="27.75" customFormat="1" customHeight="1" s="11">
@@ -1041,13 +1041,13 @@
         </is>
       </c>
       <c r="O2" s="32" t="n">
-        <v>2.8</v>
+        <v>6.3</v>
       </c>
       <c r="P2" s="32" t="n">
-        <v>27.3</v>
+        <v>24.2</v>
       </c>
       <c r="Q2" s="32" t="n">
-        <v>15.64</v>
+        <v>15.07</v>
       </c>
       <c r="R2" s="23" t="inlineStr">
         <is>
@@ -1147,10 +1147,10 @@
         </is>
       </c>
       <c r="O3" s="32" t="n">
-        <v>4.7</v>
+        <v>3.7</v>
       </c>
       <c r="P3" s="32" t="n">
-        <v>25.4</v>
+        <v>22.5</v>
       </c>
       <c r="Q3" s="32" t="n"/>
       <c r="R3" s="23" t="n"/>
@@ -1251,10 +1251,10 @@
         </is>
       </c>
       <c r="O4" s="32" t="n">
-        <v>0.6</v>
+        <v>2.5</v>
       </c>
       <c r="P4" s="32" t="n">
-        <v>24.8</v>
+        <v>23.2</v>
       </c>
       <c r="Q4" s="32" t="n"/>
       <c r="R4" s="23" t="n"/>
@@ -1443,12 +1443,14 @@
         </is>
       </c>
       <c r="O6" s="32" t="n">
-        <v>-4.4</v>
+        <v>-3.5</v>
       </c>
       <c r="P6" s="32" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="Q6" s="32" t="n"/>
+        <v>19</v>
+      </c>
+      <c r="Q6" s="32" t="n">
+        <v>7.46</v>
+      </c>
       <c r="R6" s="23" t="n"/>
       <c r="S6" s="37" t="n"/>
       <c r="T6" s="41" t="inlineStr">
@@ -1543,10 +1545,10 @@
         </is>
       </c>
       <c r="O7" s="32" t="n">
-        <v>-1.5</v>
+        <v>-0.1</v>
       </c>
       <c r="P7" s="32" t="n">
-        <v>20.7</v>
+        <v>17.2</v>
       </c>
       <c r="Q7" s="32" t="n"/>
       <c r="R7" s="23" t="n"/>
@@ -1651,13 +1653,13 @@
       </c>
       <c r="N8" s="2" t="n"/>
       <c r="O8" s="32" t="n">
-        <v>-1.6</v>
+        <v>-4.2</v>
       </c>
       <c r="P8" s="32" t="n">
-        <v>24.8</v>
+        <v>21.5</v>
       </c>
       <c r="Q8" s="32" t="n">
-        <v>11.88</v>
+        <v>9.25</v>
       </c>
       <c r="R8" s="23" t="inlineStr">
         <is>
@@ -1763,13 +1765,13 @@
       </c>
       <c r="N9" s="2" t="n"/>
       <c r="O9" s="32" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="P9" s="32" t="n">
-        <v>26.8</v>
+        <v>23.9</v>
       </c>
       <c r="Q9" s="32" t="n">
-        <v>16.65</v>
+        <v>14.59</v>
       </c>
       <c r="R9" s="23" t="inlineStr">
         <is>
@@ -1883,13 +1885,13 @@
         </is>
       </c>
       <c r="O10" s="32" t="n">
-        <v>-1.8</v>
+        <v>-1</v>
       </c>
       <c r="P10" s="32" t="n">
-        <v>23.3</v>
+        <v>22.3</v>
       </c>
       <c r="Q10" s="32" t="n">
-        <v>11.71</v>
+        <v>12.02</v>
       </c>
       <c r="R10" s="23" t="inlineStr">
         <is>
@@ -1999,13 +2001,13 @@
         </is>
       </c>
       <c r="O11" s="32" t="n">
-        <v>-3.2</v>
+        <v>-3.5</v>
       </c>
       <c r="P11" s="32" t="n">
-        <v>18.9</v>
+        <v>18.6</v>
       </c>
       <c r="Q11" s="32" t="n">
-        <v>9.44</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="R11" s="23" t="inlineStr">
         <is>
@@ -2111,13 +2113,13 @@
       </c>
       <c r="N12" s="2" t="n"/>
       <c r="O12" s="32" t="n">
-        <v>-1.3</v>
+        <v>-1.6</v>
       </c>
       <c r="P12" s="32" t="n">
-        <v>21</v>
+        <v>21.5</v>
       </c>
       <c r="Q12" s="32" t="n">
-        <v>10.75</v>
+        <v>10.56</v>
       </c>
       <c r="R12" s="23" t="inlineStr">
         <is>
@@ -2227,13 +2229,13 @@
         </is>
       </c>
       <c r="O13" s="32" t="n">
-        <v>-2.5</v>
+        <v>-0.3</v>
       </c>
       <c r="P13" s="32" t="n">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="Q13" s="32" t="n">
-        <v>9.960000000000001</v>
+        <v>8.34</v>
       </c>
       <c r="R13" s="23" t="inlineStr">
         <is>
@@ -2339,13 +2341,13 @@
       </c>
       <c r="N14" s="2" t="n"/>
       <c r="O14" s="32" t="n">
-        <v>2.1</v>
+        <v>-1.5</v>
       </c>
       <c r="P14" s="32" t="n">
-        <v>21.1</v>
+        <v>17.4</v>
       </c>
       <c r="Q14" s="32" t="n">
-        <v>11.31</v>
+        <v>8.15</v>
       </c>
       <c r="R14" s="23" t="inlineStr">
         <is>
@@ -2445,12 +2447,14 @@
       </c>
       <c r="N15" s="2" t="n"/>
       <c r="O15" s="32" t="n">
-        <v>-6.3</v>
+        <v>-9</v>
       </c>
       <c r="P15" s="32" t="n">
-        <v>17.9</v>
-      </c>
-      <c r="Q15" s="32" t="n"/>
+        <v>14.4</v>
+      </c>
+      <c r="Q15" s="32" t="n">
+        <v>3</v>
+      </c>
       <c r="R15" s="23" t="n"/>
       <c r="S15" s="37" t="n"/>
       <c r="T15" s="41" t="inlineStr">
@@ -7673,10 +7677,10 @@
       </c>
       <c r="N73" s="2" t="n"/>
       <c r="O73" s="32" t="n">
-        <v>-6.4</v>
+        <v>-10.3</v>
       </c>
       <c r="P73" s="32" t="n">
-        <v>20.8</v>
+        <v>17.1</v>
       </c>
       <c r="Q73" s="32" t="n"/>
       <c r="R73" s="23" t="n"/>
@@ -8071,13 +8075,13 @@
         </is>
       </c>
       <c r="O77" s="32" t="n">
-        <v>-9.5</v>
+        <v>-0.8</v>
       </c>
       <c r="P77" s="32" t="n">
-        <v>6.9</v>
+        <v>7.8</v>
       </c>
       <c r="Q77" s="32" t="n">
-        <v>-0.49</v>
+        <v>2.43</v>
       </c>
       <c r="R77" s="23" t="inlineStr">
         <is>
@@ -8497,13 +8501,13 @@
         </is>
       </c>
       <c r="O81" s="32" t="n">
-        <v>-6.9</v>
+        <v>-6.8</v>
       </c>
       <c r="P81" s="32" t="n">
-        <v>14.5</v>
+        <v>13.7</v>
       </c>
       <c r="Q81" s="32" t="n">
-        <v>4.49</v>
+        <v>4.56</v>
       </c>
       <c r="R81" s="23" t="inlineStr">
         <is>
@@ -8618,13 +8622,13 @@
         </is>
       </c>
       <c r="O82" s="32" t="n">
-        <v>-6.4</v>
+        <v>-6.8</v>
       </c>
       <c r="P82" s="32" t="n">
-        <v>14.5</v>
+        <v>13.7</v>
       </c>
       <c r="Q82" s="32" t="n">
-        <v>4.34</v>
+        <v>3.79</v>
       </c>
       <c r="R82" s="23" t="inlineStr">
         <is>
@@ -8836,13 +8840,13 @@
         </is>
       </c>
       <c r="O84" s="32" t="n">
-        <v>-3.3</v>
+        <v>-3.6</v>
       </c>
       <c r="P84" s="32" t="n">
-        <v>25.5</v>
+        <v>21</v>
       </c>
       <c r="Q84" s="32" t="n">
-        <v>10.71</v>
+        <v>7.8</v>
       </c>
       <c r="R84" s="23" t="inlineStr">
         <is>
@@ -9054,13 +9058,13 @@
       </c>
       <c r="N86" s="2" t="n"/>
       <c r="O86" s="32" t="n">
-        <v>6.2</v>
+        <v>5.5</v>
       </c>
       <c r="P86" s="32" t="n">
-        <v>28.5</v>
+        <v>21</v>
       </c>
       <c r="Q86" s="32" t="n">
-        <v>18.16</v>
+        <v>13.12</v>
       </c>
       <c r="R86" s="23" t="inlineStr">
         <is>
@@ -9280,13 +9284,13 @@
       </c>
       <c r="N88" s="2" t="n"/>
       <c r="O88" s="32" t="n">
-        <v>1.7</v>
+        <v>0.9</v>
       </c>
       <c r="P88" s="32" t="n">
-        <v>19.7</v>
+        <v>16.8</v>
       </c>
       <c r="Q88" s="32" t="n">
-        <v>11.82</v>
+        <v>10.38</v>
       </c>
       <c r="R88" s="23" t="inlineStr">
         <is>
@@ -9690,13 +9694,13 @@
       </c>
       <c r="N92" s="2" t="n"/>
       <c r="O92" s="32" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P92" s="32" t="n">
-        <v>9.199999999999999</v>
+        <v>11.8</v>
       </c>
       <c r="Q92" s="32" t="n">
-        <v>1.27</v>
+        <v>5.74</v>
       </c>
       <c r="R92" s="23" t="inlineStr">
         <is>
@@ -9802,13 +9806,13 @@
       </c>
       <c r="N93" s="2" t="n"/>
       <c r="O93" s="32" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="P93" s="32" t="n">
-        <v>19.3</v>
+        <v>17.4</v>
       </c>
       <c r="Q93" s="32" t="n">
-        <v>13.47</v>
+        <v>12.81</v>
       </c>
       <c r="R93" s="23" t="inlineStr">
         <is>
@@ -10032,13 +10036,13 @@
       </c>
       <c r="N95" s="2" t="n"/>
       <c r="O95" s="32" t="n">
-        <v>5.3</v>
+        <v>4.5</v>
       </c>
       <c r="P95" s="32" t="n">
-        <v>16.5</v>
+        <v>16.6</v>
       </c>
       <c r="Q95" s="32" t="n">
-        <v>11.71</v>
+        <v>10.7</v>
       </c>
       <c r="R95" s="23" t="inlineStr">
         <is>
@@ -10270,13 +10274,13 @@
       </c>
       <c r="N97" s="2" t="n"/>
       <c r="O97" s="32" t="n">
-        <v>1.7</v>
+        <v>5.2</v>
       </c>
       <c r="P97" s="32" t="n">
-        <v>16.7</v>
+        <v>16.5</v>
       </c>
       <c r="Q97" s="32" t="n">
-        <v>10.52</v>
+        <v>10.99</v>
       </c>
       <c r="R97" s="23" t="inlineStr">
         <is>
@@ -10389,9 +10393,15 @@
         </is>
       </c>
       <c r="N98" s="2" t="n"/>
-      <c r="O98" s="32" t="n"/>
-      <c r="P98" s="32" t="n"/>
-      <c r="Q98" s="32" t="n"/>
+      <c r="O98" s="32" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="P98" s="32" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="Q98" s="32" t="n">
+        <v>10.81</v>
+      </c>
       <c r="R98" s="23" t="inlineStr">
         <is>
           <t>Y</t>
@@ -10826,13 +10836,13 @@
       </c>
       <c r="N102" s="2" t="n"/>
       <c r="O102" s="32" t="n">
-        <v>-6.3</v>
+        <v>-4.9</v>
       </c>
       <c r="P102" s="32" t="n">
-        <v>13.7</v>
+        <v>14.2</v>
       </c>
       <c r="Q102" s="32" t="n">
-        <v>4.85</v>
+        <v>5.03</v>
       </c>
       <c r="R102" s="23" t="inlineStr">
         <is>
@@ -11162,13 +11172,13 @@
         </is>
       </c>
       <c r="O105" s="32" t="n">
-        <v>-8.300000000000001</v>
+        <v>-9.1</v>
       </c>
       <c r="P105" s="32" t="n">
-        <v>12.2</v>
+        <v>13.7</v>
       </c>
       <c r="Q105" s="32" t="n">
-        <v>2.96</v>
+        <v>3.54</v>
       </c>
       <c r="R105" s="23" t="inlineStr">
         <is>
@@ -11996,13 +12006,13 @@
       </c>
       <c r="N113" s="2" t="n"/>
       <c r="O113" s="32" t="n">
-        <v>-8.4</v>
+        <v>-2.8</v>
       </c>
       <c r="P113" s="32" t="n">
-        <v>0.9</v>
+        <v>3.7</v>
       </c>
       <c r="Q113" s="32" t="n">
-        <v>-3.33</v>
+        <v>-1.36</v>
       </c>
       <c r="R113" s="23" t="inlineStr">
         <is>
@@ -12112,13 +12122,13 @@
         </is>
       </c>
       <c r="O114" s="32" t="n">
-        <v>-14.4</v>
+        <v>-3.7</v>
       </c>
       <c r="P114" s="32" t="n">
-        <v>-0.8</v>
+        <v>3.2</v>
       </c>
       <c r="Q114" s="32" t="n">
-        <v>-6.23</v>
+        <v>-1.24</v>
       </c>
       <c r="R114" s="23" t="inlineStr">
         <is>
@@ -12236,13 +12246,13 @@
         </is>
       </c>
       <c r="O115" s="32" t="n">
-        <v>-12.6</v>
+        <v>-5.5</v>
       </c>
       <c r="P115" s="32" t="n">
-        <v>2.6</v>
+        <v>-0.9</v>
       </c>
       <c r="Q115" s="32" t="n">
-        <v>-5.35</v>
+        <v>-3.69</v>
       </c>
       <c r="R115" s="23" t="inlineStr">
         <is>
@@ -12792,13 +12802,13 @@
       </c>
       <c r="N120" s="2" t="n"/>
       <c r="O120" s="32" t="n">
-        <v>18.7</v>
+        <v>18.1</v>
       </c>
       <c r="P120" s="32" t="n">
-        <v>34.8</v>
+        <v>37.3</v>
       </c>
       <c r="Q120" s="32" t="n">
-        <v>27.2</v>
+        <v>28.88</v>
       </c>
       <c r="R120" s="23" t="inlineStr">
         <is>
@@ -12908,13 +12918,13 @@
       </c>
       <c r="N121" s="2" t="n"/>
       <c r="O121" s="32" t="n">
-        <v>15.6</v>
+        <v>15.2</v>
       </c>
       <c r="P121" s="32" t="n">
-        <v>26.6</v>
+        <v>29.3</v>
       </c>
       <c r="Q121" s="32" t="n">
-        <v>21.6</v>
+        <v>22.1</v>
       </c>
       <c r="R121" s="23" t="inlineStr">
         <is>
@@ -13032,13 +13042,13 @@
       </c>
       <c r="N122" s="2" t="n"/>
       <c r="O122" s="32" t="n">
-        <v>-4.3</v>
+        <v>-3.5</v>
       </c>
       <c r="P122" s="32" t="n">
-        <v>18.3</v>
+        <v>18.7</v>
       </c>
       <c r="Q122" s="32" t="n">
-        <v>7.29</v>
+        <v>7.48</v>
       </c>
       <c r="R122" s="23" t="inlineStr">
         <is>
@@ -13254,13 +13264,13 @@
       </c>
       <c r="N124" s="2" t="n"/>
       <c r="O124" s="32" t="n">
-        <v>4.8</v>
+        <v>0.1</v>
       </c>
       <c r="P124" s="32" t="n">
-        <v>18.4</v>
+        <v>18.8</v>
       </c>
       <c r="Q124" s="32" t="n">
-        <v>11.61</v>
+        <v>9.609999999999999</v>
       </c>
       <c r="R124" s="23" t="inlineStr">
         <is>
@@ -13378,13 +13388,13 @@
       </c>
       <c r="N125" s="2" t="n"/>
       <c r="O125" s="32" t="n">
-        <v>6.8</v>
+        <v>14.8</v>
       </c>
       <c r="P125" s="32" t="n">
-        <v>20.9</v>
+        <v>24.5</v>
       </c>
       <c r="Q125" s="32" t="n">
-        <v>14.25</v>
+        <v>19.45</v>
       </c>
       <c r="R125" s="23" t="inlineStr">
         <is>
@@ -13482,13 +13492,13 @@
       </c>
       <c r="N126" s="2" t="n"/>
       <c r="O126" s="32" t="n">
-        <v>9.199999999999999</v>
+        <v>15.4</v>
       </c>
       <c r="P126" s="32" t="n">
-        <v>20.3</v>
+        <v>23.5</v>
       </c>
       <c r="Q126" s="32" t="n">
-        <v>14.4</v>
+        <v>18.56</v>
       </c>
       <c r="R126" s="23" t="inlineStr">
         <is>
@@ -13594,13 +13604,13 @@
       </c>
       <c r="N127" s="2" t="n"/>
       <c r="O127" s="32" t="n">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
       <c r="P127" s="32" t="n">
-        <v>24.1</v>
+        <v>23.7</v>
       </c>
       <c r="Q127" s="32" t="n">
-        <v>14.58</v>
+        <v>15.35</v>
       </c>
       <c r="R127" s="23" t="inlineStr">
         <is>
@@ -13714,13 +13724,13 @@
       </c>
       <c r="N128" s="2" t="n"/>
       <c r="O128" s="32" t="n">
-        <v>9.1</v>
+        <v>16</v>
       </c>
       <c r="P128" s="32" t="n">
-        <v>25.4</v>
+        <v>24.3</v>
       </c>
       <c r="Q128" s="32" t="n">
-        <v>17.43</v>
+        <v>20.09</v>
       </c>
       <c r="R128" s="23" t="inlineStr">
         <is>
@@ -13826,13 +13836,13 @@
       </c>
       <c r="N129" s="2" t="n"/>
       <c r="O129" s="32" t="n">
-        <v>1.9</v>
+        <v>10.7</v>
       </c>
       <c r="P129" s="32" t="n">
-        <v>24.3</v>
+        <v>21.1</v>
       </c>
       <c r="Q129" s="32" t="n">
-        <v>13.89</v>
+        <v>16.11</v>
       </c>
       <c r="R129" s="23" t="inlineStr">
         <is>
@@ -13946,13 +13956,13 @@
       </c>
       <c r="N130" s="2" t="n"/>
       <c r="O130" s="32" t="n">
-        <v>-1.3</v>
+        <v>5.6</v>
       </c>
       <c r="P130" s="32" t="n">
-        <v>17.5</v>
+        <v>15.8</v>
       </c>
       <c r="Q130" s="32" t="n">
-        <v>7.25</v>
+        <v>9.85</v>
       </c>
       <c r="R130" s="23" t="inlineStr">
         <is>
@@ -14066,13 +14076,13 @@
       </c>
       <c r="N131" s="2" t="n"/>
       <c r="O131" s="32" t="n">
-        <v>11.2</v>
+        <v>13.9</v>
       </c>
       <c r="P131" s="32" t="n">
-        <v>22.4</v>
+        <v>21.4</v>
       </c>
       <c r="Q131" s="32" t="n">
-        <v>14.9</v>
+        <v>17.78</v>
       </c>
       <c r="R131" s="23" t="inlineStr">
         <is>
@@ -14182,13 +14192,13 @@
       </c>
       <c r="N132" s="2" t="n"/>
       <c r="O132" s="32" t="n">
-        <v>11.3</v>
+        <v>19.7</v>
       </c>
       <c r="P132" s="32" t="n">
-        <v>27.6</v>
+        <v>26.7</v>
       </c>
       <c r="Q132" s="32" t="n">
-        <v>20.98</v>
+        <v>22.14</v>
       </c>
       <c r="R132" s="23" t="inlineStr">
         <is>
@@ -14298,13 +14308,13 @@
       </c>
       <c r="N133" s="2" t="n"/>
       <c r="O133" s="32" t="n">
-        <v>13.1</v>
+        <v>14.4</v>
       </c>
       <c r="P133" s="32" t="n">
-        <v>25.2</v>
+        <v>24.3</v>
       </c>
       <c r="Q133" s="32" t="n">
-        <v>19.39</v>
+        <v>19.05</v>
       </c>
       <c r="R133" s="23" t="inlineStr">
         <is>
@@ -14520,13 +14530,13 @@
       </c>
       <c r="N135" s="2" t="n"/>
       <c r="O135" s="32" t="n">
-        <v>16.2</v>
+        <v>19.1</v>
       </c>
       <c r="P135" s="32" t="n">
-        <v>24.2</v>
+        <v>28</v>
       </c>
       <c r="Q135" s="32" t="n">
-        <v>19.43</v>
+        <v>21.84</v>
       </c>
       <c r="R135" s="23" t="inlineStr">
         <is>
@@ -14636,13 +14646,13 @@
       </c>
       <c r="N136" s="2" t="n"/>
       <c r="O136" s="32" t="n">
-        <v>17.8</v>
+        <v>20.1</v>
       </c>
       <c r="P136" s="32" t="n">
-        <v>26.4</v>
+        <v>25.2</v>
       </c>
       <c r="Q136" s="32" t="n">
-        <v>21.48</v>
+        <v>22.07</v>
       </c>
       <c r="R136" s="23" t="inlineStr">
         <is>
@@ -14752,13 +14762,13 @@
       </c>
       <c r="N137" s="2" t="n"/>
       <c r="O137" s="32" t="n">
-        <v>14.7</v>
+        <v>20</v>
       </c>
       <c r="P137" s="32" t="n">
-        <v>25.8</v>
+        <v>25.6</v>
       </c>
       <c r="Q137" s="32" t="n">
-        <v>19.44</v>
+        <v>21.96</v>
       </c>
       <c r="R137" s="23" t="inlineStr">
         <is>
@@ -14868,13 +14878,13 @@
       </c>
       <c r="N138" s="2" t="n"/>
       <c r="O138" s="32" t="n">
-        <v>14.8</v>
+        <v>16.1</v>
       </c>
       <c r="P138" s="32" t="n">
-        <v>23</v>
+        <v>24.5</v>
       </c>
       <c r="Q138" s="32" t="n">
-        <v>17.89</v>
+        <v>19.74</v>
       </c>
       <c r="R138" s="23" t="inlineStr">
         <is>
@@ -14984,13 +14994,13 @@
       </c>
       <c r="N139" s="2" t="n"/>
       <c r="O139" s="32" t="n">
-        <v>15.2</v>
+        <v>17.4</v>
       </c>
       <c r="P139" s="32" t="n">
-        <v>23.3</v>
+        <v>26</v>
       </c>
       <c r="Q139" s="32" t="n">
-        <v>18.38</v>
+        <v>21.04</v>
       </c>
       <c r="R139" s="23" t="inlineStr">
         <is>
@@ -15100,13 +15110,13 @@
       </c>
       <c r="N140" s="2" t="n"/>
       <c r="O140" s="32" t="n">
-        <v>16.3</v>
+        <v>16.7</v>
       </c>
       <c r="P140" s="32" t="n">
-        <v>23.2</v>
+        <v>29.8</v>
       </c>
       <c r="Q140" s="32" t="n">
-        <v>19.48</v>
+        <v>22.77</v>
       </c>
       <c r="R140" s="23" t="inlineStr">
         <is>
@@ -15318,13 +15328,13 @@
       </c>
       <c r="N142" s="2" t="n"/>
       <c r="O142" s="32" t="n">
-        <v>21.1</v>
+        <v>19.9</v>
       </c>
       <c r="P142" s="32" t="n">
-        <v>27.7</v>
+        <v>30.2</v>
       </c>
       <c r="Q142" s="32" t="n">
-        <v>23.57</v>
+        <v>24.01</v>
       </c>
       <c r="R142" s="23" t="inlineStr">
         <is>
@@ -15434,13 +15444,13 @@
       </c>
       <c r="N143" s="2" t="n"/>
       <c r="O143" s="32" t="n">
-        <v>22</v>
+        <v>21.9</v>
       </c>
       <c r="P143" s="32" t="n">
-        <v>26.9</v>
+        <v>30.8</v>
       </c>
       <c r="Q143" s="32" t="n">
-        <v>24.38</v>
+        <v>25.94</v>
       </c>
       <c r="R143" s="23" t="inlineStr">
         <is>
@@ -15750,13 +15760,13 @@
       </c>
       <c r="N146" s="2" t="n"/>
       <c r="O146" s="32" t="n">
-        <v>26.6</v>
+        <v>25.8</v>
       </c>
       <c r="P146" s="32" t="n">
-        <v>32.1</v>
+        <v>31.8</v>
       </c>
       <c r="Q146" s="32" t="n">
-        <v>28.96</v>
+        <v>28.85</v>
       </c>
       <c r="R146" s="23" t="inlineStr">
         <is>
@@ -15858,13 +15868,13 @@
       </c>
       <c r="N147" s="2" t="n"/>
       <c r="O147" s="32" t="n">
-        <v>19.9</v>
+        <v>24.1</v>
       </c>
       <c r="P147" s="32" t="n">
-        <v>25.2</v>
+        <v>29.4</v>
       </c>
       <c r="Q147" s="32" t="n">
-        <v>22.27</v>
+        <v>26.02</v>
       </c>
       <c r="R147" s="23" t="inlineStr">
         <is>
@@ -15974,13 +15984,13 @@
       </c>
       <c r="N148" s="2" t="n"/>
       <c r="O148" s="32" t="n">
-        <v>20.2</v>
+        <v>21.4</v>
       </c>
       <c r="P148" s="32" t="n">
-        <v>28.4</v>
+        <v>33.7</v>
       </c>
       <c r="Q148" s="32" t="n">
-        <v>22.76</v>
+        <v>25.77</v>
       </c>
       <c r="R148" s="23" t="inlineStr">
         <is>
@@ -16086,13 +16096,13 @@
       </c>
       <c r="N149" s="2" t="n"/>
       <c r="O149" s="32" t="n">
-        <v>9</v>
+        <v>12.3</v>
       </c>
       <c r="P149" s="32" t="n">
-        <v>16.6</v>
+        <v>23</v>
       </c>
       <c r="Q149" s="32" t="n">
-        <v>11.96</v>
+        <v>17.41</v>
       </c>
       <c r="R149" s="23" t="inlineStr">
         <is>
@@ -16202,13 +16212,13 @@
       </c>
       <c r="N150" s="2" t="n"/>
       <c r="O150" s="32" t="n">
-        <v>11.9</v>
+        <v>15.3</v>
       </c>
       <c r="P150" s="32" t="n">
-        <v>14.2</v>
+        <v>21.9</v>
       </c>
       <c r="Q150" s="32" t="n">
-        <v>13.01</v>
+        <v>18.71</v>
       </c>
       <c r="R150" s="23" t="inlineStr">
         <is>
@@ -16318,13 +16328,13 @@
       </c>
       <c r="N151" s="2" t="n"/>
       <c r="O151" s="32" t="n">
-        <v>19.1</v>
+        <v>20.7</v>
       </c>
       <c r="P151" s="32" t="n">
-        <v>23.6</v>
+        <v>26.4</v>
       </c>
       <c r="Q151" s="32" t="n">
-        <v>21.15</v>
+        <v>22.93</v>
       </c>
       <c r="R151" s="23" t="inlineStr">
         <is>
@@ -16524,13 +16534,13 @@
       </c>
       <c r="N153" s="2" t="n"/>
       <c r="O153" s="32" t="n">
-        <v>14.8</v>
+        <v>17.9</v>
       </c>
       <c r="P153" s="32" t="n">
-        <v>22.4</v>
+        <v>28.3</v>
       </c>
       <c r="Q153" s="32" t="n">
-        <v>18.48</v>
+        <v>21.96</v>
       </c>
       <c r="R153" s="23" t="inlineStr">
         <is>
@@ -16644,13 +16654,13 @@
       </c>
       <c r="N154" s="2" t="n"/>
       <c r="O154" s="32" t="n">
-        <v>3.5</v>
+        <v>4.9</v>
       </c>
       <c r="P154" s="32" t="n">
-        <v>18</v>
+        <v>18.9</v>
       </c>
       <c r="Q154" s="32" t="n">
-        <v>10.61</v>
+        <v>11.59</v>
       </c>
       <c r="R154" s="23" t="inlineStr">
         <is>
@@ -16944,13 +16954,13 @@
       </c>
       <c r="N157" s="2" t="n"/>
       <c r="O157" s="32" t="n">
-        <v>16.6</v>
+        <v>17.4</v>
       </c>
       <c r="P157" s="32" t="n">
-        <v>22.5</v>
+        <v>30.4</v>
       </c>
       <c r="Q157" s="32" t="n">
-        <v>19.25</v>
+        <v>22.02</v>
       </c>
       <c r="R157" s="23" t="inlineStr">
         <is>
@@ -17334,13 +17344,13 @@
       </c>
       <c r="N161" s="2" t="n"/>
       <c r="O161" s="32" t="n">
-        <v>4.1</v>
+        <v>9</v>
       </c>
       <c r="P161" s="32" t="n">
-        <v>22.9</v>
+        <v>22</v>
       </c>
       <c r="Q161" s="32" t="n">
-        <v>12.61</v>
+        <v>16.26</v>
       </c>
       <c r="R161" s="23" t="inlineStr">
         <is>
@@ -17449,12 +17459,8 @@
           <t>⚡</t>
         </is>
       </c>
-      <c r="O162" s="32" t="n">
-        <v>-10</v>
-      </c>
-      <c r="P162" s="32" t="n">
-        <v>12.9</v>
-      </c>
+      <c r="O162" s="32" t="n"/>
+      <c r="P162" s="32" t="n"/>
       <c r="Q162" s="32" t="n"/>
       <c r="R162" s="23" t="inlineStr">
         <is>
@@ -17559,8 +17565,12 @@
         </is>
       </c>
       <c r="N163" s="2" t="n"/>
-      <c r="O163" s="32" t="n"/>
-      <c r="P163" s="32" t="n"/>
+      <c r="O163" s="32" t="n">
+        <v>-7.2</v>
+      </c>
+      <c r="P163" s="32" t="n">
+        <v>14.3</v>
+      </c>
       <c r="Q163" s="32" t="n"/>
       <c r="R163" s="23" t="inlineStr">
         <is>
@@ -18310,10 +18320,10 @@
         </is>
       </c>
       <c r="O170" s="32" t="n">
-        <v>-4.9</v>
+        <v>-3</v>
       </c>
       <c r="P170" s="32" t="n">
-        <v>11.3</v>
+        <v>11.8</v>
       </c>
       <c r="Q170" s="32" t="n"/>
       <c r="R170" s="23" t="inlineStr">
@@ -18420,10 +18430,10 @@
       </c>
       <c r="N171" s="2" t="n"/>
       <c r="O171" s="32" t="n">
-        <v>-0.2</v>
+        <v>1.4</v>
       </c>
       <c r="P171" s="32" t="n">
-        <v>7.3</v>
+        <v>5.6</v>
       </c>
       <c r="Q171" s="32" t="n"/>
       <c r="R171" s="23" t="inlineStr">
@@ -18636,10 +18646,10 @@
       </c>
       <c r="N173" s="2" t="n"/>
       <c r="O173" s="32" t="n">
-        <v>-4.2</v>
+        <v>-1.3</v>
       </c>
       <c r="P173" s="32" t="n">
-        <v>8.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="Q173" s="32" t="n"/>
       <c r="R173" s="23" t="inlineStr">
@@ -18741,12 +18751,8 @@
         </is>
       </c>
       <c r="N174" s="2" t="n"/>
-      <c r="O174" s="32" t="n">
-        <v>-7.3</v>
-      </c>
-      <c r="P174" s="32" t="n">
-        <v>-1.3</v>
-      </c>
+      <c r="O174" s="32" t="n"/>
+      <c r="P174" s="32" t="n"/>
       <c r="Q174" s="32" t="n"/>
       <c r="R174" s="23" t="inlineStr">
         <is>
@@ -18962,13 +18968,13 @@
       </c>
       <c r="N176" s="2" t="n"/>
       <c r="O176" s="32" t="n">
-        <v>4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="P176" s="32" t="n">
-        <v>12.4</v>
+        <v>15.4</v>
       </c>
       <c r="Q176" s="32" t="n">
-        <v>6.71</v>
+        <v>11.85</v>
       </c>
       <c r="R176" s="23" t="inlineStr">
         <is>
@@ -19066,13 +19072,13 @@
       </c>
       <c r="N177" s="2" t="n"/>
       <c r="O177" s="32" t="n">
-        <v>-8.6</v>
+        <v>-5.9</v>
       </c>
       <c r="P177" s="32" t="n">
-        <v>-2.8</v>
+        <v>0.4</v>
       </c>
       <c r="Q177" s="32" t="n">
-        <v>-5.88</v>
+        <v>-2.65</v>
       </c>
       <c r="R177" s="23" t="inlineStr">
         <is>
@@ -22585,10 +22591,10 @@
       </c>
       <c r="N213" s="2" t="n"/>
       <c r="O213" s="32" t="n">
-        <v>-10.7</v>
+        <v>-11.2</v>
       </c>
       <c r="P213" s="32" t="n">
-        <v>13.1</v>
+        <v>13.3</v>
       </c>
       <c r="Q213" s="32" t="n"/>
       <c r="R213" s="23" t="inlineStr">
@@ -25243,10 +25249,10 @@
       </c>
       <c r="N240" s="2" t="n"/>
       <c r="O240" s="32" t="n">
-        <v>-8.800000000000001</v>
+        <v>-11.5</v>
       </c>
       <c r="P240" s="32" t="n">
-        <v>-3.5</v>
+        <v>-1.4</v>
       </c>
       <c r="Q240" s="32" t="n"/>
       <c r="R240" s="23" t="inlineStr">
@@ -27687,10 +27693,10 @@
       </c>
       <c r="N265" s="2" t="n"/>
       <c r="O265" s="32" t="n">
-        <v>-59.8</v>
+        <v>-67.59999999999999</v>
       </c>
       <c r="P265" s="32" t="n">
-        <v>-51.9</v>
+        <v>-66.5</v>
       </c>
       <c r="Q265" s="32" t="n"/>
       <c r="R265" s="23" t="inlineStr">
@@ -30527,10 +30533,10 @@
       </c>
       <c r="N295" s="2" t="n"/>
       <c r="O295" s="32" t="n">
-        <v>-10.9</v>
+        <v>-16.9</v>
       </c>
       <c r="P295" s="32" t="n">
-        <v>4.1</v>
+        <v>-5.6</v>
       </c>
       <c r="Q295" s="32" t="n"/>
       <c r="R295" s="23" t="inlineStr">
@@ -31120,15 +31126,9 @@
         </is>
       </c>
       <c r="N301" s="2" t="n"/>
-      <c r="O301" s="32" t="n">
-        <v>23.2</v>
-      </c>
-      <c r="P301" s="32" t="n">
-        <v>35.2</v>
-      </c>
-      <c r="Q301" s="32" t="n">
-        <v>27.2</v>
-      </c>
+      <c r="O301" s="32" t="n"/>
+      <c r="P301" s="32" t="n"/>
+      <c r="Q301" s="32" t="n"/>
       <c r="R301" s="23" t="inlineStr">
         <is>
           <t>Y</t>
@@ -31518,15 +31518,9 @@
         </is>
       </c>
       <c r="N305" s="2" t="n"/>
-      <c r="O305" s="32" t="n">
-        <v>-12.5</v>
-      </c>
-      <c r="P305" s="32" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="Q305" s="32" t="n">
-        <v>-3.38</v>
-      </c>
+      <c r="O305" s="32" t="n"/>
+      <c r="P305" s="32" t="n"/>
+      <c r="Q305" s="32" t="n"/>
       <c r="R305" s="23" t="inlineStr">
         <is>
           <t>Y</t>
@@ -31834,12 +31828,8 @@
         </is>
       </c>
       <c r="N308" s="2" t="n"/>
-      <c r="O308" s="32" t="n">
-        <v>-16.1</v>
-      </c>
-      <c r="P308" s="32" t="n">
-        <v>-3.7</v>
-      </c>
+      <c r="O308" s="32" t="n"/>
+      <c r="P308" s="32" t="n"/>
       <c r="Q308" s="32" t="n"/>
       <c r="R308" s="23" t="inlineStr">
         <is>
@@ -32037,11 +32027,7 @@
       <c r="O310" s="32" t="n"/>
       <c r="P310" s="32" t="n"/>
       <c r="Q310" s="32" t="n"/>
-      <c r="R310" s="23" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="R310" s="23" t="n"/>
       <c r="S310" s="37" t="n"/>
       <c r="T310" s="41" t="inlineStr">
         <is>
@@ -32084,109 +32070,309 @@
       <c r="AH310" s="2" t="n"/>
     </row>
     <row r="311" ht="24" customHeight="1" s="50">
-      <c r="A311" s="2" t="n"/>
-      <c r="B311" s="2" t="n"/>
-      <c r="C311" s="46" t="n"/>
-      <c r="D311" s="2" t="n"/>
-      <c r="E311" s="4" t="n"/>
+      <c r="A311" s="2" t="n">
+        <v>310</v>
+      </c>
+      <c r="B311" s="2" t="inlineStr">
+        <is>
+          <t>rp5</t>
+        </is>
+      </c>
+      <c r="C311" s="46" t="inlineStr">
+        <is>
+          <t>47639</t>
+        </is>
+      </c>
+      <c r="D311" s="2" t="inlineStr">
+        <is>
+          <t>Fujisan</t>
+        </is>
+      </c>
+      <c r="E311" s="4" t="n">
+        <v>99999</v>
+      </c>
       <c r="F311" s="39" t="n"/>
-      <c r="G311" s="29" t="n"/>
-      <c r="H311" s="29" t="n"/>
-      <c r="I311" s="2" t="n"/>
-      <c r="J311" s="27" t="n"/>
-      <c r="K311" s="4" t="n"/>
+      <c r="G311" s="29" t="n">
+        <v>35.367</v>
+      </c>
+      <c r="H311" s="29" t="n">
+        <v>138.733</v>
+      </c>
+      <c r="I311" s="2" t="n">
+        <v>3777.5</v>
+      </c>
+      <c r="J311" s="27" t="n">
+        <v>12</v>
+      </c>
+      <c r="K311" s="31" t="inlineStr">
+        <is>
+          <t>🇯🇵</t>
+        </is>
+      </c>
       <c r="L311" s="2" t="n"/>
-      <c r="M311" s="14" t="n"/>
+      <c r="M311" s="17" t="inlineStr">
+        <is>
+          <t>富士山</t>
+        </is>
+      </c>
       <c r="N311" s="2" t="n"/>
-      <c r="O311" s="32" t="n"/>
-      <c r="P311" s="32" t="n"/>
-      <c r="Q311" s="32" t="n"/>
-      <c r="R311" s="23" t="n"/>
+      <c r="O311" s="32" t="n">
+        <v>-5.8</v>
+      </c>
+      <c r="P311" s="32" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Q311" s="32" t="n">
+        <v>-1.82</v>
+      </c>
+      <c r="R311" s="23" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="S311" s="37" t="n"/>
-      <c r="T311" s="41" t="n"/>
-      <c r="U311" s="2" t="n"/>
-      <c r="V311" s="4" t="n"/>
-      <c r="W311" s="4" t="n"/>
-      <c r="X311" s="4" t="n"/>
+      <c r="T311" s="41" t="inlineStr">
+        <is>
+          <t>日本</t>
+        </is>
+      </c>
+      <c r="U311" s="2" t="inlineStr">
+        <is>
+          <t>中部地方</t>
+        </is>
+      </c>
+      <c r="V311" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="W311" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="X311" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="Y311" s="4" t="n"/>
       <c r="Z311" s="2" t="n"/>
       <c r="AA311" s="2" t="n"/>
       <c r="AB311" s="2" t="n"/>
       <c r="AC311" s="2" t="n"/>
-      <c r="AD311" s="2" t="n"/>
-      <c r="AE311" s="4" t="n"/>
+      <c r="AD311" s="2" t="inlineStr">
+        <is>
+          <t>日本</t>
+        </is>
+      </c>
+      <c r="AE311" s="4" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
       <c r="AF311" s="4" t="n"/>
       <c r="AG311" s="2" t="n"/>
       <c r="AH311" s="2" t="n"/>
     </row>
     <row r="312" ht="24" customHeight="1" s="50">
-      <c r="A312" s="2" t="n"/>
+      <c r="A312" s="2" t="n">
+        <v>311</v>
+      </c>
       <c r="B312" s="2" t="n"/>
-      <c r="C312" s="46" t="n"/>
+      <c r="C312" s="46" t="inlineStr">
+        <is>
+          <t>56673</t>
+        </is>
+      </c>
       <c r="D312" s="2" t="n"/>
-      <c r="E312" s="4" t="n"/>
+      <c r="E312" s="4" t="n">
+        <v>99999</v>
+      </c>
       <c r="F312" s="39" t="n"/>
-      <c r="G312" s="29" t="n"/>
-      <c r="H312" s="29" t="n"/>
-      <c r="I312" s="2" t="n"/>
-      <c r="J312" s="27" t="n"/>
-      <c r="K312" s="4" t="n"/>
+      <c r="G312" s="29" t="n">
+        <v>26.9181</v>
+      </c>
+      <c r="H312" s="29" t="n">
+        <v>102.9267</v>
+      </c>
+      <c r="I312" s="2" t="n">
+        <v>893.9</v>
+      </c>
+      <c r="J312" s="27" t="n">
+        <v>12</v>
+      </c>
+      <c r="K312" s="31" t="inlineStr">
+        <is>
+          <t>🇨🇳</t>
+        </is>
+      </c>
       <c r="L312" s="2" t="n"/>
-      <c r="M312" s="14" t="n"/>
+      <c r="M312" s="14" t="inlineStr">
+        <is>
+          <t>巧家</t>
+        </is>
+      </c>
       <c r="N312" s="2" t="n"/>
       <c r="O312" s="32" t="n"/>
       <c r="P312" s="32" t="n"/>
       <c r="Q312" s="32" t="n"/>
-      <c r="R312" s="23" t="n"/>
+      <c r="R312" s="23" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="S312" s="37" t="n"/>
-      <c r="T312" s="41" t="n"/>
-      <c r="U312" s="2" t="n"/>
-      <c r="V312" s="4" t="n"/>
-      <c r="W312" s="4" t="n"/>
-      <c r="X312" s="4" t="n"/>
+      <c r="T312" s="41" t="inlineStr">
+        <is>
+          <t>云南</t>
+        </is>
+      </c>
+      <c r="U312" s="2" t="inlineStr">
+        <is>
+          <t>云南</t>
+        </is>
+      </c>
+      <c r="V312" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="W312" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="X312" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="Y312" s="4" t="n"/>
-      <c r="Z312" s="2" t="n"/>
-      <c r="AA312" s="2" t="n"/>
+      <c r="Z312" s="2" t="inlineStr">
+        <is>
+          <t>昭通市</t>
+        </is>
+      </c>
+      <c r="AA312" s="2" t="inlineStr">
+        <is>
+          <t>巧家县</t>
+        </is>
+      </c>
       <c r="AB312" s="2" t="n"/>
       <c r="AC312" s="2" t="n"/>
-      <c r="AD312" s="2" t="n"/>
-      <c r="AE312" s="4" t="n"/>
+      <c r="AD312" s="2" t="inlineStr">
+        <is>
+          <t>中国</t>
+        </is>
+      </c>
+      <c r="AE312" s="4" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
       <c r="AF312" s="4" t="n"/>
       <c r="AG312" s="2" t="n"/>
       <c r="AH312" s="2" t="n"/>
     </row>
     <row r="313" ht="24" customHeight="1" s="50">
-      <c r="A313" s="2" t="n"/>
-      <c r="B313" s="2" t="n"/>
-      <c r="C313" s="46" t="n"/>
-      <c r="D313" s="2" t="n"/>
-      <c r="E313" s="4" t="n"/>
+      <c r="A313" s="2" t="n">
+        <v>312</v>
+      </c>
+      <c r="B313" s="2" t="inlineStr">
+        <is>
+          <t>ogimet</t>
+        </is>
+      </c>
+      <c r="C313" s="46" t="inlineStr">
+        <is>
+          <t>24076</t>
+        </is>
+      </c>
+      <c r="D313" s="2" t="inlineStr">
+        <is>
+          <t>Deputatsky</t>
+        </is>
+      </c>
+      <c r="E313" s="4" t="n">
+        <v>99999</v>
+      </c>
       <c r="F313" s="39" t="n"/>
-      <c r="G313" s="29" t="n"/>
-      <c r="H313" s="29" t="n"/>
-      <c r="I313" s="2" t="n"/>
-      <c r="J313" s="27" t="n"/>
-      <c r="K313" s="4" t="n"/>
+      <c r="G313" s="29" t="n">
+        <v>69.33</v>
+      </c>
+      <c r="H313" s="29" t="n">
+        <v>139.6697</v>
+      </c>
+      <c r="I313" s="2" t="n">
+        <v>282</v>
+      </c>
+      <c r="J313" s="27" t="n">
+        <v>15</v>
+      </c>
+      <c r="K313" s="31" t="inlineStr">
+        <is>
+          <t>🇷🇺</t>
+        </is>
+      </c>
       <c r="L313" s="2" t="n"/>
-      <c r="M313" s="14" t="n"/>
+      <c r="M313" s="16" t="inlineStr">
+        <is>
+          <t>Deputatskii</t>
+        </is>
+      </c>
       <c r="N313" s="2" t="n"/>
-      <c r="O313" s="32" t="n"/>
-      <c r="P313" s="32" t="n"/>
-      <c r="Q313" s="32" t="n"/>
-      <c r="R313" s="23" t="n"/>
+      <c r="O313" s="32" t="n">
+        <v>-24.2</v>
+      </c>
+      <c r="P313" s="32" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="Q313" s="32" t="n">
+        <v>-9.84</v>
+      </c>
+      <c r="R313" s="23" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="S313" s="37" t="n"/>
-      <c r="T313" s="41" t="n"/>
-      <c r="U313" s="2" t="n"/>
-      <c r="V313" s="4" t="n"/>
+      <c r="T313" s="41" t="inlineStr">
+        <is>
+          <t>雅库特</t>
+        </is>
+      </c>
+      <c r="U313" s="2" t="inlineStr">
+        <is>
+          <t>萨哈共和国</t>
+        </is>
+      </c>
+      <c r="V313" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="W313" s="4" t="n"/>
-      <c r="X313" s="4" t="n"/>
+      <c r="X313" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="Y313" s="4" t="n"/>
       <c r="Z313" s="2" t="n"/>
       <c r="AA313" s="2" t="n"/>
       <c r="AB313" s="2" t="n"/>
       <c r="AC313" s="2" t="n"/>
-      <c r="AD313" s="2" t="n"/>
-      <c r="AE313" s="4" t="n"/>
+      <c r="AD313" s="2" t="inlineStr">
+        <is>
+          <t>俄罗斯</t>
+        </is>
+      </c>
+      <c r="AE313" s="4" t="inlineStr">
+        <is>
+          <t>Z</t>
+        </is>
+      </c>
       <c r="AF313" s="4" t="n"/>
       <c r="AG313" s="2" t="n"/>
       <c r="AH313" s="2" t="n"/>

--- a/气象/For_Python_站点信息和记录.xlsx
+++ b/气象/For_Python_站点信息和记录.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\文档\GIT SYNC\default\气象\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E29FFA63-5A9E-4F78-80F1-485F8E2BFDFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B782982F-A8A9-4835-B7E9-00C84CE9FB4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/气象/For_Python_站点信息和记录.xlsx
+++ b/气象/For_Python_站点信息和记录.xlsx
@@ -840,8 +840,8 @@
     <col width="18.59765625" customWidth="1" style="8" min="26" max="26"/>
     <col width="12.59765625" customWidth="1" style="5" min="27" max="31"/>
     <col width="12.59765625" customWidth="1" style="8" min="32" max="33"/>
-    <col width="12.59765625" customWidth="1" style="5" min="34" max="557"/>
-    <col width="12.59765625" customWidth="1" style="5" min="558" max="16384"/>
+    <col width="12.59765625" customWidth="1" style="5" min="34" max="623"/>
+    <col width="12.59765625" customWidth="1" style="5" min="624" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="27.75" customFormat="1" customHeight="1" s="11">
@@ -1069,13 +1069,13 @@
         </is>
       </c>
       <c r="O2" s="31" t="n">
-        <v>8.300000000000001</v>
+        <v>15.9</v>
       </c>
       <c r="P2" s="31" t="n">
-        <v>28.1</v>
+        <v>27.1</v>
       </c>
       <c r="Q2" s="31" t="n">
-        <v>19.06</v>
+        <v>20.4</v>
       </c>
       <c r="R2" s="50" t="n"/>
       <c r="S2" s="22" t="inlineStr">
@@ -1086,7 +1086,7 @@
       <c r="T2" s="36" t="n"/>
       <c r="U2" s="40" t="inlineStr">
         <is>
-          <t>乌布苏湖&lt;br&gt;特斯河</t>
+          <t>特斯河 乌布苏湖&lt;br&gt;明星站</t>
         </is>
       </c>
       <c r="V2" s="2" t="inlineStr">
@@ -1176,10 +1176,10 @@
         </is>
       </c>
       <c r="O3" s="31" t="n">
-        <v>9.300000000000001</v>
+        <v>13.2</v>
       </c>
       <c r="P3" s="31" t="n">
-        <v>27.4</v>
+        <v>27</v>
       </c>
       <c r="Q3" s="31" t="n"/>
       <c r="R3" s="50" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="U3" s="40" t="inlineStr">
         <is>
-          <t>乌布苏湖</t>
+          <t>乌布苏湖&lt;br&gt;明星站</t>
         </is>
       </c>
       <c r="V3" s="2" t="inlineStr">
@@ -1285,10 +1285,10 @@
         </is>
       </c>
       <c r="O4" s="31" t="n">
-        <v>9.5</v>
+        <v>14.4</v>
       </c>
       <c r="P4" s="31" t="n">
-        <v>26.6</v>
+        <v>25.7</v>
       </c>
       <c r="Q4" s="31" t="n"/>
       <c r="R4" s="50" t="inlineStr">
@@ -1300,7 +1300,7 @@
       <c r="T4" s="36" t="n"/>
       <c r="U4" s="40" t="inlineStr">
         <is>
-          <t>明星站</t>
+          <t>特斯河&lt;br&gt;明星站</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
@@ -1393,7 +1393,7 @@
       <c r="T5" s="36" t="n"/>
       <c r="U5" s="40" t="inlineStr">
         <is>
-          <t>杭爱山</t>
+          <t>伊德尔河 杭爱山</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
@@ -1483,13 +1483,13 @@
         </is>
       </c>
       <c r="O6" s="31" t="n">
-        <v>8.699999999999999</v>
+        <v>9</v>
       </c>
       <c r="P6" s="31" t="n">
-        <v>17.3</v>
+        <v>23.9</v>
       </c>
       <c r="Q6" s="31" t="n">
-        <v>11.39</v>
+        <v>15.99</v>
       </c>
       <c r="R6" s="52" t="inlineStr">
         <is>
@@ -1500,7 +1500,7 @@
       <c r="T6" s="36" t="n"/>
       <c r="U6" s="40" t="inlineStr">
         <is>
-          <t>杭爱山</t>
+          <t>扎布汗河 杭爱山&lt;br&gt;明星站</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="O7" s="31" t="n">
-        <v>1.6</v>
+        <v>13.4</v>
       </c>
       <c r="P7" s="31" t="n">
-        <v>20.7</v>
+        <v>23.6</v>
       </c>
       <c r="Q7" s="31" t="n"/>
       <c r="R7" s="50" t="n"/>
@@ -1601,7 +1601,7 @@
       <c r="T7" s="36" t="n"/>
       <c r="U7" s="40" t="inlineStr">
         <is>
-          <t>库苏古尔湖</t>
+          <t>希希黑德河&lt;br&gt;库苏古尔湖</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
@@ -1699,13 +1699,13 @@
       </c>
       <c r="N8" s="2" t="n"/>
       <c r="O8" s="31" t="n">
-        <v>9.699999999999999</v>
+        <v>18.3</v>
       </c>
       <c r="P8" s="31" t="n">
-        <v>18.3</v>
+        <v>26.6</v>
       </c>
       <c r="Q8" s="31" t="n">
-        <v>13.34</v>
+        <v>21.16</v>
       </c>
       <c r="R8" s="50" t="n"/>
       <c r="S8" s="22" t="inlineStr">
@@ -1716,7 +1716,7 @@
       <c r="T8" s="36" t="n"/>
       <c r="U8" s="40" t="inlineStr">
         <is>
-          <t>色楞格</t>
+          <t>鄂尔浑河&lt;br&gt;色楞格 明星站</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
@@ -1812,13 +1812,13 @@
       </c>
       <c r="N9" s="2" t="n"/>
       <c r="O9" s="31" t="n">
-        <v>10.4</v>
+        <v>11.3</v>
       </c>
       <c r="P9" s="31" t="n">
-        <v>24.5</v>
+        <v>27.8</v>
       </c>
       <c r="Q9" s="31" t="n">
-        <v>18.51</v>
+        <v>19.64</v>
       </c>
       <c r="R9" s="50" t="n"/>
       <c r="S9" s="22" t="inlineStr">
@@ -1933,13 +1933,13 @@
         </is>
       </c>
       <c r="O10" s="31" t="n">
-        <v>4.2</v>
+        <v>14.3</v>
       </c>
       <c r="P10" s="31" t="n">
-        <v>25.1</v>
+        <v>24.2</v>
       </c>
       <c r="Q10" s="31" t="n">
-        <v>15.53</v>
+        <v>18.24</v>
       </c>
       <c r="R10" s="50" t="n"/>
       <c r="S10" s="22" t="inlineStr">
@@ -1950,7 +1950,7 @@
       <c r="T10" s="36" t="n"/>
       <c r="U10" s="40" t="inlineStr">
         <is>
-          <t>特斯河</t>
+          <t>特斯河&lt;br&gt;明星站</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
@@ -2050,13 +2050,13 @@
         </is>
       </c>
       <c r="O11" s="31" t="n">
-        <v>6.2</v>
+        <v>10.7</v>
       </c>
       <c r="P11" s="31" t="n">
-        <v>21</v>
+        <v>21.7</v>
       </c>
       <c r="Q11" s="31" t="n">
-        <v>13.98</v>
+        <v>16.04</v>
       </c>
       <c r="R11" s="50" t="inlineStr">
         <is>
@@ -2167,13 +2167,13 @@
       </c>
       <c r="N12" s="2" t="n"/>
       <c r="O12" s="31" t="n">
-        <v>4.3</v>
+        <v>11.9</v>
       </c>
       <c r="P12" s="31" t="n">
-        <v>22.2</v>
+        <v>26.3</v>
       </c>
       <c r="Q12" s="31" t="n">
-        <v>13.82</v>
+        <v>18.43</v>
       </c>
       <c r="R12" s="50" t="inlineStr">
         <is>
@@ -2188,7 +2188,7 @@
       <c r="T12" s="36" t="n"/>
       <c r="U12" s="40" t="inlineStr">
         <is>
-          <t>杭爱山</t>
+          <t>伊德尔河 杭爱山</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
@@ -2288,13 +2288,13 @@
         </is>
       </c>
       <c r="O13" s="31" t="n">
-        <v>2.7</v>
+        <v>12.3</v>
       </c>
       <c r="P13" s="31" t="n">
-        <v>20.2</v>
+        <v>23.7</v>
       </c>
       <c r="Q13" s="31" t="n">
-        <v>11.75</v>
+        <v>17.36</v>
       </c>
       <c r="R13" s="50" t="inlineStr">
         <is>
@@ -2309,7 +2309,7 @@
       <c r="T13" s="36" t="n"/>
       <c r="U13" s="40" t="inlineStr">
         <is>
-          <t>库苏古尔湖</t>
+          <t>库苏古尔湖&lt;br&gt;明星站</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
@@ -2405,13 +2405,13 @@
       </c>
       <c r="N14" s="2" t="n"/>
       <c r="O14" s="31" t="n">
-        <v>7.1</v>
+        <v>17</v>
       </c>
       <c r="P14" s="31" t="n">
-        <v>15.4</v>
+        <v>28.8</v>
       </c>
       <c r="Q14" s="31" t="n">
-        <v>11.18</v>
+        <v>21.06</v>
       </c>
       <c r="R14" s="50" t="n"/>
       <c r="S14" s="22" t="inlineStr">
@@ -2526,13 +2526,13 @@
       </c>
       <c r="N15" s="2" t="n"/>
       <c r="O15" s="31" t="n">
-        <v>4.3</v>
+        <v>14.6</v>
       </c>
       <c r="P15" s="31" t="n">
-        <v>17</v>
+        <v>27.4</v>
       </c>
       <c r="Q15" s="31" t="n">
-        <v>9.82</v>
+        <v>19.21</v>
       </c>
       <c r="R15" s="50" t="n"/>
       <c r="S15" s="22" t="inlineStr">
@@ -2737,7 +2737,7 @@
       <c r="T17" s="36" t="n"/>
       <c r="U17" s="40" t="inlineStr">
         <is>
-          <t>明星站</t>
+          <t>杭爱山&lt;br&gt;明星站</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
@@ -3117,7 +3117,7 @@
       <c r="T21" s="36" t="n"/>
       <c r="U21" s="40" t="inlineStr">
         <is>
-          <t>科布多</t>
+          <t>哈儿乌苏湖&lt;br&gt;科布多</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
@@ -3396,7 +3396,7 @@
       <c r="T24" s="36" t="n"/>
       <c r="U24" s="40" t="inlineStr">
         <is>
-          <t>科布多</t>
+          <t>阿尔泰山&lt;br&gt;科布多</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
@@ -4848,7 +4848,7 @@
       <c r="T40" s="36" t="n"/>
       <c r="U40" s="40" t="inlineStr">
         <is>
-          <t>色楞格</t>
+          <t>色楞格河</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
@@ -5022,7 +5022,7 @@
       <c r="T42" s="36" t="n"/>
       <c r="U42" s="40" t="inlineStr">
         <is>
-          <t>色楞格</t>
+          <t>鄂尔浑河&lt;br&gt;色楞格</t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
@@ -5115,7 +5115,7 @@
       <c r="T43" s="36" t="n"/>
       <c r="U43" s="40" t="inlineStr">
         <is>
-          <t>乌布苏湖</t>
+          <t>乌布苏湖&lt;br&gt;唐努乌拉山</t>
         </is>
       </c>
       <c r="V43" s="2" t="inlineStr">
@@ -6551,7 +6551,7 @@
       <c r="T59" s="36" t="n"/>
       <c r="U59" s="40" t="inlineStr">
         <is>
-          <t>扎布汗</t>
+          <t>伊德尔河&lt;br&gt;扎布汗</t>
         </is>
       </c>
       <c r="V59" s="2" t="inlineStr">
@@ -6733,7 +6733,7 @@
       <c r="T61" s="36" t="n"/>
       <c r="U61" s="40" t="inlineStr">
         <is>
-          <t>阿尔泰山</t>
+          <t>阿尔泰山&lt;br&gt;巴彦乌列盖</t>
         </is>
       </c>
       <c r="V61" s="2" t="inlineStr">
@@ -8002,13 +8002,13 @@
       </c>
       <c r="N75" s="2" t="n"/>
       <c r="O75" s="31" t="n">
-        <v>20.8</v>
+        <v>20.5</v>
       </c>
       <c r="P75" s="31" t="n">
-        <v>34</v>
+        <v>29.6</v>
       </c>
       <c r="Q75" s="31" t="n">
-        <v>25.91</v>
+        <v>24.23</v>
       </c>
       <c r="R75" s="50" t="n"/>
       <c r="S75" s="22" t="inlineStr">
@@ -8321,13 +8321,13 @@
         </is>
       </c>
       <c r="O78" s="31" t="n">
-        <v>4.1</v>
+        <v>13.4</v>
       </c>
       <c r="P78" s="31" t="n">
-        <v>26.8</v>
+        <v>23.6</v>
       </c>
       <c r="Q78" s="31" t="n">
-        <v>16.03</v>
+        <v>17.98</v>
       </c>
       <c r="R78" s="50" t="inlineStr">
         <is>
@@ -8755,13 +8755,13 @@
         </is>
       </c>
       <c r="O82" s="31" t="n">
-        <v>7</v>
+        <v>16.7</v>
       </c>
       <c r="P82" s="31" t="n">
-        <v>28.9</v>
+        <v>25.2</v>
       </c>
       <c r="Q82" s="31" t="n">
-        <v>17.88</v>
+        <v>20.73</v>
       </c>
       <c r="R82" s="50" t="n"/>
       <c r="S82" s="22" t="inlineStr">
@@ -8877,13 +8877,13 @@
         </is>
       </c>
       <c r="O83" s="31" t="n">
-        <v>6.9</v>
+        <v>13.8</v>
       </c>
       <c r="P83" s="31" t="n">
-        <v>26.3</v>
+        <v>25.9</v>
       </c>
       <c r="Q83" s="31" t="n">
-        <v>17.27</v>
+        <v>19.59</v>
       </c>
       <c r="R83" s="50" t="n"/>
       <c r="S83" s="22" t="inlineStr">
@@ -9097,13 +9097,13 @@
         </is>
       </c>
       <c r="O85" s="31" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="P85" s="31" t="n">
-        <v>24.5</v>
+        <v>25.7</v>
       </c>
       <c r="Q85" s="31" t="n">
-        <v>16.43</v>
+        <v>19.01</v>
       </c>
       <c r="R85" s="50" t="n"/>
       <c r="S85" s="22" t="inlineStr">
@@ -9317,13 +9317,13 @@
       </c>
       <c r="N87" s="2" t="n"/>
       <c r="O87" s="31" t="n">
-        <v>12.4</v>
+        <v>16.6</v>
       </c>
       <c r="P87" s="31" t="n">
-        <v>28.7</v>
+        <v>25</v>
       </c>
       <c r="Q87" s="31" t="n">
-        <v>20.96</v>
+        <v>19.54</v>
       </c>
       <c r="R87" s="50" t="n"/>
       <c r="S87" s="22" t="inlineStr">
@@ -9545,13 +9545,13 @@
       </c>
       <c r="N89" s="2" t="n"/>
       <c r="O89" s="31" t="n">
-        <v>8.199999999999999</v>
+        <v>6.4</v>
       </c>
       <c r="P89" s="31" t="n">
-        <v>21</v>
+        <v>20.9</v>
       </c>
       <c r="Q89" s="31" t="n">
-        <v>13.79</v>
+        <v>13.65</v>
       </c>
       <c r="R89" s="50" t="inlineStr">
         <is>
@@ -9967,13 +9967,13 @@
       </c>
       <c r="N93" s="2" t="n"/>
       <c r="O93" s="31" t="n">
-        <v>6.4</v>
+        <v>16.3</v>
       </c>
       <c r="P93" s="31" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="Q93" s="31" t="n">
-        <v>12.89</v>
+        <v>20.53</v>
       </c>
       <c r="R93" s="50" t="n"/>
       <c r="S93" s="22" t="inlineStr">
@@ -10080,13 +10080,13 @@
       </c>
       <c r="N94" s="2" t="n"/>
       <c r="O94" s="31" t="n">
-        <v>17.1</v>
+        <v>24</v>
       </c>
       <c r="P94" s="31" t="n">
-        <v>26.8</v>
+        <v>33.8</v>
       </c>
       <c r="Q94" s="31" t="n">
-        <v>23</v>
+        <v>29.08</v>
       </c>
       <c r="R94" s="50" t="n"/>
       <c r="S94" s="22" t="inlineStr">
@@ -10316,13 +10316,13 @@
       </c>
       <c r="N96" s="2" t="n"/>
       <c r="O96" s="31" t="n">
-        <v>18.8</v>
+        <v>24.4</v>
       </c>
       <c r="P96" s="31" t="n">
-        <v>26.6</v>
+        <v>32.2</v>
       </c>
       <c r="Q96" s="31" t="n">
-        <v>22.71</v>
+        <v>28.08</v>
       </c>
       <c r="R96" s="50" t="n"/>
       <c r="S96" s="22" t="inlineStr">
@@ -10560,13 +10560,13 @@
       </c>
       <c r="N98" s="2" t="n"/>
       <c r="O98" s="31" t="n">
-        <v>18.5</v>
+        <v>24</v>
       </c>
       <c r="P98" s="31" t="n">
-        <v>28.6</v>
+        <v>31.8</v>
       </c>
       <c r="Q98" s="31" t="n">
-        <v>23.16</v>
+        <v>27.24</v>
       </c>
       <c r="R98" s="50" t="n"/>
       <c r="S98" s="22" t="inlineStr">
@@ -11121,13 +11121,13 @@
       </c>
       <c r="N103" s="2" t="n"/>
       <c r="O103" s="31" t="n">
-        <v>9.6</v>
+        <v>18.7</v>
       </c>
       <c r="P103" s="31" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="Q103" s="31" t="n">
-        <v>19</v>
+        <v>21.71</v>
       </c>
       <c r="R103" s="50" t="n"/>
       <c r="S103" s="22" t="inlineStr">
@@ -11460,13 +11460,13 @@
         </is>
       </c>
       <c r="O106" s="31" t="n">
-        <v>9.9</v>
+        <v>15.7</v>
       </c>
       <c r="P106" s="31" t="n">
-        <v>23.7</v>
+        <v>28.3</v>
       </c>
       <c r="Q106" s="31" t="n">
-        <v>17.01</v>
+        <v>21.88</v>
       </c>
       <c r="R106" s="50" t="n"/>
       <c r="S106" s="22" t="inlineStr">
@@ -12302,13 +12302,13 @@
       </c>
       <c r="N114" s="2" t="n"/>
       <c r="O114" s="31" t="n">
-        <v>3.9</v>
+        <v>6.6</v>
       </c>
       <c r="P114" s="31" t="n">
-        <v>12.3</v>
+        <v>18.5</v>
       </c>
       <c r="Q114" s="31" t="n">
-        <v>7.71</v>
+        <v>11.65</v>
       </c>
       <c r="R114" s="50" t="n"/>
       <c r="S114" s="22" t="inlineStr">
@@ -12419,13 +12419,13 @@
         </is>
       </c>
       <c r="O115" s="31" t="n">
-        <v>2</v>
+        <v>1.2</v>
       </c>
       <c r="P115" s="31" t="n">
-        <v>12.3</v>
+        <v>18.2</v>
       </c>
       <c r="Q115" s="31" t="n">
-        <v>6.89</v>
+        <v>10.41</v>
       </c>
       <c r="R115" s="50" t="n"/>
       <c r="S115" s="22" t="inlineStr">
@@ -12544,13 +12544,13 @@
         </is>
       </c>
       <c r="O116" s="31" t="n">
-        <v>0.1</v>
+        <v>5.8</v>
       </c>
       <c r="P116" s="31" t="n">
-        <v>9.300000000000001</v>
+        <v>15.2</v>
       </c>
       <c r="Q116" s="31" t="n">
-        <v>3.66</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="R116" s="50" t="n"/>
       <c r="S116" s="22" t="inlineStr">
@@ -13109,13 +13109,13 @@
       </c>
       <c r="N121" s="2" t="n"/>
       <c r="O121" s="31" t="n">
-        <v>30.1</v>
+        <v>28.8</v>
       </c>
       <c r="P121" s="31" t="n">
-        <v>36.9</v>
+        <v>39.3</v>
       </c>
       <c r="Q121" s="31" t="n">
-        <v>32</v>
+        <v>34.14</v>
       </c>
       <c r="R121" s="50" t="n"/>
       <c r="S121" s="22" t="inlineStr">
@@ -13226,13 +13226,13 @@
       </c>
       <c r="N122" s="2" t="n"/>
       <c r="O122" s="31" t="n">
-        <v>20.8</v>
+        <v>18.5</v>
       </c>
       <c r="P122" s="31" t="n">
-        <v>29.1</v>
+        <v>25.8</v>
       </c>
       <c r="Q122" s="31" t="n">
-        <v>24.7</v>
+        <v>22.03</v>
       </c>
       <c r="R122" s="50" t="n"/>
       <c r="S122" s="22" t="inlineStr">
@@ -13351,13 +13351,13 @@
       </c>
       <c r="N123" s="2" t="n"/>
       <c r="O123" s="31" t="n">
-        <v>7.4</v>
+        <v>7.7</v>
       </c>
       <c r="P123" s="31" t="n">
-        <v>15.8</v>
+        <v>17.3</v>
       </c>
       <c r="Q123" s="31" t="n">
-        <v>11.7</v>
+        <v>11.36</v>
       </c>
       <c r="R123" s="50" t="n"/>
       <c r="S123" s="22" t="inlineStr">
@@ -13575,13 +13575,13 @@
       </c>
       <c r="N125" s="2" t="n"/>
       <c r="O125" s="31" t="n">
-        <v>16.4</v>
+        <v>20.1</v>
       </c>
       <c r="P125" s="31" t="n">
-        <v>27</v>
+        <v>30.6</v>
       </c>
       <c r="Q125" s="31" t="n">
-        <v>21.54</v>
+        <v>25.41</v>
       </c>
       <c r="R125" s="50" t="n"/>
       <c r="S125" s="22" t="inlineStr">
@@ -13700,13 +13700,13 @@
       </c>
       <c r="N126" s="2" t="n"/>
       <c r="O126" s="31" t="n">
-        <v>19.8</v>
+        <v>26.3</v>
       </c>
       <c r="P126" s="31" t="n">
-        <v>28.6</v>
+        <v>34.2</v>
       </c>
       <c r="Q126" s="31" t="n">
-        <v>23.6</v>
+        <v>30.44</v>
       </c>
       <c r="R126" s="50" t="n"/>
       <c r="S126" s="22" t="inlineStr">
@@ -13805,13 +13805,13 @@
       </c>
       <c r="N127" s="2" t="n"/>
       <c r="O127" s="31" t="n">
-        <v>21.9</v>
+        <v>26.5</v>
       </c>
       <c r="P127" s="31" t="n">
-        <v>30.3</v>
+        <v>35.5</v>
       </c>
       <c r="Q127" s="31" t="n">
-        <v>26.15</v>
+        <v>30.8</v>
       </c>
       <c r="R127" s="50" t="n"/>
       <c r="S127" s="22" t="inlineStr">
@@ -13918,13 +13918,13 @@
       </c>
       <c r="N128" s="2" t="n"/>
       <c r="O128" s="31" t="n">
-        <v>18</v>
+        <v>21.6</v>
       </c>
       <c r="P128" s="31" t="n">
-        <v>27.3</v>
+        <v>32.1</v>
       </c>
       <c r="Q128" s="31" t="n">
-        <v>22.99</v>
+        <v>26.31</v>
       </c>
       <c r="R128" s="50" t="n"/>
       <c r="S128" s="22" t="inlineStr">
@@ -14039,12 +14039,14 @@
       </c>
       <c r="N129" s="2" t="n"/>
       <c r="O129" s="31" t="n">
-        <v>20.4</v>
+        <v>25.1</v>
       </c>
       <c r="P129" s="31" t="n">
-        <v>31.9</v>
-      </c>
-      <c r="Q129" s="31" t="n"/>
+        <v>32.5</v>
+      </c>
+      <c r="Q129" s="31" t="n">
+        <v>28.02</v>
+      </c>
       <c r="R129" s="50" t="n"/>
       <c r="S129" s="22" t="inlineStr">
         <is>
@@ -14150,13 +14152,13 @@
       </c>
       <c r="N130" s="2" t="n"/>
       <c r="O130" s="31" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="P130" s="31" t="n">
-        <v>29.6</v>
+        <v>32</v>
       </c>
       <c r="Q130" s="31" t="n">
-        <v>22.66</v>
+        <v>26.12</v>
       </c>
       <c r="R130" s="50" t="n"/>
       <c r="S130" s="22" t="inlineStr">
@@ -14271,13 +14273,13 @@
       </c>
       <c r="N131" s="2" t="n"/>
       <c r="O131" s="31" t="n">
-        <v>12.9</v>
+        <v>13.7</v>
       </c>
       <c r="P131" s="31" t="n">
-        <v>22.5</v>
+        <v>31.5</v>
       </c>
       <c r="Q131" s="31" t="n">
-        <v>16.71</v>
+        <v>21.93</v>
       </c>
       <c r="R131" s="50" t="n"/>
       <c r="S131" s="22" t="inlineStr">
@@ -14392,13 +14394,13 @@
       </c>
       <c r="N132" s="2" t="n"/>
       <c r="O132" s="31" t="n">
-        <v>21.3</v>
+        <v>24.8</v>
       </c>
       <c r="P132" s="31" t="n">
         <v>32.3</v>
       </c>
       <c r="Q132" s="31" t="n">
-        <v>27.14</v>
+        <v>28.34</v>
       </c>
       <c r="R132" s="50" t="n"/>
       <c r="S132" s="22" t="inlineStr">
@@ -14509,13 +14511,13 @@
       </c>
       <c r="N133" s="2" t="n"/>
       <c r="O133" s="31" t="n">
-        <v>20</v>
+        <v>25.2</v>
       </c>
       <c r="P133" s="31" t="n">
-        <v>29.7</v>
+        <v>32</v>
       </c>
       <c r="Q133" s="31" t="n">
-        <v>24.96</v>
+        <v>28.11</v>
       </c>
       <c r="R133" s="50" t="n"/>
       <c r="S133" s="22" t="inlineStr">
@@ -14626,13 +14628,13 @@
       </c>
       <c r="N134" s="2" t="n"/>
       <c r="O134" s="31" t="n">
-        <v>21.1</v>
+        <v>25.3</v>
       </c>
       <c r="P134" s="31" t="n">
-        <v>29.7</v>
+        <v>34.9</v>
       </c>
       <c r="Q134" s="31" t="n">
-        <v>24.96</v>
+        <v>29.26</v>
       </c>
       <c r="R134" s="50" t="n"/>
       <c r="S134" s="22" t="inlineStr">
@@ -14850,13 +14852,13 @@
       </c>
       <c r="N136" s="2" t="n"/>
       <c r="O136" s="31" t="n">
-        <v>20.5</v>
+        <v>25.2</v>
       </c>
       <c r="P136" s="31" t="n">
-        <v>22.5</v>
+        <v>30.2</v>
       </c>
       <c r="Q136" s="31" t="n">
-        <v>21.4</v>
+        <v>27.05</v>
       </c>
       <c r="R136" s="50" t="n"/>
       <c r="S136" s="22" t="inlineStr">
@@ -14967,13 +14969,13 @@
       </c>
       <c r="N137" s="2" t="n"/>
       <c r="O137" s="31" t="n">
-        <v>23.8</v>
+        <v>27.7</v>
       </c>
       <c r="P137" s="31" t="n">
-        <v>27.5</v>
+        <v>32.8</v>
       </c>
       <c r="Q137" s="31" t="n">
-        <v>24.82</v>
+        <v>29.79</v>
       </c>
       <c r="R137" s="50" t="n"/>
       <c r="S137" s="22" t="inlineStr">
@@ -15084,13 +15086,13 @@
       </c>
       <c r="N138" s="2" t="n"/>
       <c r="O138" s="31" t="n">
-        <v>21.3</v>
+        <v>26</v>
       </c>
       <c r="P138" s="31" t="n">
-        <v>23.4</v>
+        <v>32.5</v>
       </c>
       <c r="Q138" s="31" t="n">
-        <v>22.18</v>
+        <v>29.61</v>
       </c>
       <c r="R138" s="50" t="n"/>
       <c r="S138" s="22" t="inlineStr">
@@ -15201,12 +15203,14 @@
       </c>
       <c r="N139" s="2" t="n"/>
       <c r="O139" s="31" t="n">
-        <v>20.6</v>
+        <v>26.6</v>
       </c>
       <c r="P139" s="31" t="n">
-        <v>24.4</v>
-      </c>
-      <c r="Q139" s="31" t="n"/>
+        <v>34.2</v>
+      </c>
+      <c r="Q139" s="31" t="n">
+        <v>29.68</v>
+      </c>
       <c r="R139" s="50" t="n"/>
       <c r="S139" s="22" t="inlineStr">
         <is>
@@ -15316,13 +15320,13 @@
       </c>
       <c r="N140" s="2" t="n"/>
       <c r="O140" s="31" t="n">
-        <v>20.8</v>
+        <v>28.6</v>
       </c>
       <c r="P140" s="31" t="n">
-        <v>23.2</v>
+        <v>33.5</v>
       </c>
       <c r="Q140" s="31" t="n">
-        <v>21.95</v>
+        <v>30.79</v>
       </c>
       <c r="R140" s="50" t="n"/>
       <c r="S140" s="22" t="inlineStr">
@@ -15433,13 +15437,13 @@
       </c>
       <c r="N141" s="2" t="n"/>
       <c r="O141" s="31" t="n">
-        <v>22.5</v>
+        <v>28.8</v>
       </c>
       <c r="P141" s="31" t="n">
-        <v>25.3</v>
+        <v>35.2</v>
       </c>
       <c r="Q141" s="31" t="n">
-        <v>23.6</v>
+        <v>31.79</v>
       </c>
       <c r="R141" s="50" t="n"/>
       <c r="S141" s="22" t="inlineStr">
@@ -15653,13 +15657,13 @@
       </c>
       <c r="N143" s="2" t="n"/>
       <c r="O143" s="31" t="n">
-        <v>27.4</v>
+        <v>25.3</v>
       </c>
       <c r="P143" s="31" t="n">
-        <v>37.4</v>
+        <v>35.5</v>
       </c>
       <c r="Q143" s="31" t="n">
-        <v>30.76</v>
+        <v>28.8</v>
       </c>
       <c r="R143" s="50" t="n"/>
       <c r="S143" s="22" t="inlineStr">
@@ -15770,13 +15774,13 @@
       </c>
       <c r="N144" s="2" t="n"/>
       <c r="O144" s="31" t="n">
-        <v>28.2</v>
+        <v>24.9</v>
       </c>
       <c r="P144" s="31" t="n">
-        <v>33.8</v>
+        <v>32.4</v>
       </c>
       <c r="Q144" s="31" t="n">
-        <v>30.23</v>
+        <v>27.48</v>
       </c>
       <c r="R144" s="50" t="n"/>
       <c r="S144" s="22" t="inlineStr">
@@ -16089,13 +16093,13 @@
       </c>
       <c r="N147" s="2" t="n"/>
       <c r="O147" s="31" t="n">
-        <v>30.1</v>
+        <v>25.4</v>
       </c>
       <c r="P147" s="31" t="n">
-        <v>34.2</v>
+        <v>33.7</v>
       </c>
       <c r="Q147" s="31" t="n">
-        <v>32.23</v>
+        <v>30.77</v>
       </c>
       <c r="R147" s="50" t="n"/>
       <c r="S147" s="22" t="inlineStr">
@@ -16198,13 +16202,13 @@
       </c>
       <c r="N148" s="2" t="n"/>
       <c r="O148" s="31" t="n">
-        <v>26</v>
+        <v>26.4</v>
       </c>
       <c r="P148" s="31" t="n">
-        <v>33.8</v>
+        <v>33.9</v>
       </c>
       <c r="Q148" s="31" t="n">
-        <v>29.75</v>
+        <v>30.12</v>
       </c>
       <c r="R148" s="50" t="n"/>
       <c r="S148" s="22" t="inlineStr">
@@ -16315,13 +16319,13 @@
       </c>
       <c r="N149" s="2" t="n"/>
       <c r="O149" s="31" t="n">
-        <v>27.7</v>
+        <v>25.2</v>
       </c>
       <c r="P149" s="31" t="n">
-        <v>33.7</v>
+        <v>31.6</v>
       </c>
       <c r="Q149" s="31" t="n">
-        <v>30.91</v>
+        <v>28.2</v>
       </c>
       <c r="R149" s="50" t="n"/>
       <c r="S149" s="22" t="inlineStr">
@@ -16428,13 +16432,13 @@
       </c>
       <c r="N150" s="2" t="n"/>
       <c r="O150" s="31" t="n">
-        <v>19.1</v>
+        <v>17.3</v>
       </c>
       <c r="P150" s="31" t="n">
-        <v>26.4</v>
+        <v>24</v>
       </c>
       <c r="Q150" s="31" t="n">
-        <v>22.25</v>
+        <v>19.94</v>
       </c>
       <c r="R150" s="50" t="n"/>
       <c r="S150" s="22" t="inlineStr">
@@ -16545,13 +16549,13 @@
       </c>
       <c r="N151" s="2" t="n"/>
       <c r="O151" s="31" t="n">
-        <v>18.9</v>
+        <v>19.2</v>
       </c>
       <c r="P151" s="31" t="n">
-        <v>23.5</v>
+        <v>27.4</v>
       </c>
       <c r="Q151" s="31" t="n">
-        <v>20</v>
+        <v>21.31</v>
       </c>
       <c r="R151" s="50" t="n"/>
       <c r="S151" s="22" t="inlineStr">
@@ -16662,13 +16666,13 @@
       </c>
       <c r="N152" s="2" t="n"/>
       <c r="O152" s="31" t="n">
-        <v>23.3</v>
+        <v>24.9</v>
       </c>
       <c r="P152" s="31" t="n">
-        <v>25.7</v>
+        <v>37</v>
       </c>
       <c r="Q152" s="31" t="n">
-        <v>24.25</v>
+        <v>30.14</v>
       </c>
       <c r="R152" s="50" t="n"/>
       <c r="S152" s="22" t="inlineStr">
@@ -16870,13 +16874,13 @@
       </c>
       <c r="N154" s="2" t="n"/>
       <c r="O154" s="31" t="n">
-        <v>22.1</v>
+        <v>21.8</v>
       </c>
       <c r="P154" s="31" t="n">
-        <v>28.6</v>
+        <v>31.8</v>
       </c>
       <c r="Q154" s="31" t="n">
-        <v>24.8</v>
+        <v>25.95</v>
       </c>
       <c r="R154" s="50" t="n"/>
       <c r="S154" s="22" t="inlineStr">
@@ -16991,13 +16995,13 @@
       </c>
       <c r="N155" s="2" t="n"/>
       <c r="O155" s="31" t="n">
-        <v>15</v>
+        <v>16.2</v>
       </c>
       <c r="P155" s="31" t="n">
-        <v>28.1</v>
+        <v>27.6</v>
       </c>
       <c r="Q155" s="31" t="n">
-        <v>19.94</v>
+        <v>21.1</v>
       </c>
       <c r="R155" s="50" t="n"/>
       <c r="S155" s="22" t="inlineStr">
@@ -17294,13 +17298,13 @@
       </c>
       <c r="N158" s="2" t="n"/>
       <c r="O158" s="31" t="n">
-        <v>22</v>
+        <v>28.7</v>
       </c>
       <c r="P158" s="31" t="n">
-        <v>23.4</v>
+        <v>34.3</v>
       </c>
       <c r="Q158" s="31" t="n">
-        <v>22.6</v>
+        <v>30.69</v>
       </c>
       <c r="R158" s="50" t="n"/>
       <c r="S158" s="22" t="inlineStr">
@@ -17688,12 +17692,14 @@
       </c>
       <c r="N162" s="2" t="n"/>
       <c r="O162" s="31" t="n">
-        <v>18.5</v>
+        <v>21.2</v>
       </c>
       <c r="P162" s="31" t="n">
-        <v>32.3</v>
-      </c>
-      <c r="Q162" s="31" t="n"/>
+        <v>33</v>
+      </c>
+      <c r="Q162" s="31" t="n">
+        <v>26.19</v>
+      </c>
       <c r="R162" s="50" t="n"/>
       <c r="S162" s="22" t="inlineStr">
         <is>
@@ -17907,12 +17913,8 @@
           <t>⚡</t>
         </is>
       </c>
-      <c r="O164" s="31" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="P164" s="31" t="n">
-        <v>27</v>
-      </c>
+      <c r="O164" s="31" t="n"/>
+      <c r="P164" s="31" t="n"/>
       <c r="Q164" s="31" t="n"/>
       <c r="R164" s="50" t="n"/>
       <c r="S164" s="22" t="inlineStr">
@@ -18788,10 +18790,10 @@
         </is>
       </c>
       <c r="O172" s="31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P172" s="31" t="n">
-        <v>12.6</v>
+        <v>14.6</v>
       </c>
       <c r="Q172" s="31" t="n"/>
       <c r="R172" s="50" t="n"/>
@@ -19117,10 +19119,10 @@
       </c>
       <c r="N175" s="2" t="n"/>
       <c r="O175" s="31" t="n">
-        <v>5.4</v>
+        <v>12.9</v>
       </c>
       <c r="P175" s="31" t="n">
-        <v>18.7</v>
+        <v>26.7</v>
       </c>
       <c r="Q175" s="31" t="n"/>
       <c r="R175" s="50" t="inlineStr">
@@ -19446,12 +19448,14 @@
       </c>
       <c r="N178" s="2" t="n"/>
       <c r="O178" s="31" t="n">
-        <v>16.7</v>
+        <v>16.2</v>
       </c>
       <c r="P178" s="31" t="n">
-        <v>17.7</v>
-      </c>
-      <c r="Q178" s="31" t="n"/>
+        <v>18.3</v>
+      </c>
+      <c r="Q178" s="31" t="n">
+        <v>17.12</v>
+      </c>
       <c r="R178" s="50" t="n"/>
       <c r="S178" s="22" t="inlineStr">
         <is>
@@ -19553,13 +19557,13 @@
         </is>
       </c>
       <c r="O179" s="31" t="n">
-        <v>4.4</v>
+        <v>10.5</v>
       </c>
       <c r="P179" s="31" t="n">
-        <v>9.199999999999999</v>
+        <v>18</v>
       </c>
       <c r="Q179" s="31" t="n">
-        <v>6.41</v>
+        <v>13.45</v>
       </c>
       <c r="R179" s="50" t="n"/>
       <c r="S179" s="22" t="inlineStr">
@@ -19888,10 +19892,10 @@
       </c>
       <c r="N182" s="2" t="n"/>
       <c r="O182" s="31" t="n">
-        <v>7.5</v>
+        <v>10.1</v>
       </c>
       <c r="P182" s="31" t="n">
-        <v>13.3</v>
+        <v>18.6</v>
       </c>
       <c r="Q182" s="31" t="n"/>
       <c r="R182" s="50" t="n"/>
@@ -23107,8 +23111,12 @@
         </is>
       </c>
       <c r="N215" s="2" t="n"/>
-      <c r="O215" s="31" t="n"/>
-      <c r="P215" s="31" t="n"/>
+      <c r="O215" s="31" t="n">
+        <v>13</v>
+      </c>
+      <c r="P215" s="31" t="n">
+        <v>29.2</v>
+      </c>
       <c r="Q215" s="31" t="n"/>
       <c r="R215" s="50" t="n"/>
       <c r="S215" s="22" t="inlineStr">
@@ -28254,10 +28262,10 @@
       </c>
       <c r="N267" s="2" t="n"/>
       <c r="O267" s="31" t="n">
-        <v>-70.7</v>
+        <v>-79.8</v>
       </c>
       <c r="P267" s="31" t="n">
-        <v>-62.1</v>
+        <v>-77.2</v>
       </c>
       <c r="Q267" s="31" t="n"/>
       <c r="R267" s="50" t="n"/>
@@ -30736,7 +30744,7 @@
       </c>
       <c r="N293" s="2" t="n"/>
       <c r="O293" s="31" t="n">
-        <v>-15.1</v>
+        <v>-22.1</v>
       </c>
       <c r="P293" s="31" t="n"/>
       <c r="Q293" s="31" t="n"/>
@@ -31135,9 +31143,15 @@
           <t>🔵</t>
         </is>
       </c>
-      <c r="O297" s="31" t="n"/>
-      <c r="P297" s="31" t="n"/>
-      <c r="Q297" s="31" t="n"/>
+      <c r="O297" s="31" t="n">
+        <v>-0.6</v>
+      </c>
+      <c r="P297" s="31" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="Q297" s="31" t="n">
+        <v>2.4</v>
+      </c>
       <c r="R297" s="50" t="n"/>
       <c r="S297" s="22" t="inlineStr">
         <is>
@@ -31626,12 +31640,8 @@
         </is>
       </c>
       <c r="N302" s="2" t="n"/>
-      <c r="O302" s="31" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="P302" s="31" t="n">
-        <v>25.5</v>
-      </c>
+      <c r="O302" s="31" t="n"/>
+      <c r="P302" s="31" t="n"/>
       <c r="Q302" s="31" t="n"/>
       <c r="R302" s="50" t="n"/>
       <c r="S302" s="22" t="inlineStr">
@@ -31735,15 +31745,9 @@
         </is>
       </c>
       <c r="N303" s="2" t="n"/>
-      <c r="O303" s="31" t="n">
-        <v>27.6</v>
-      </c>
-      <c r="P303" s="31" t="n">
-        <v>40.9</v>
-      </c>
-      <c r="Q303" s="31" t="n">
-        <v>33.49</v>
-      </c>
+      <c r="O303" s="31" t="n"/>
+      <c r="P303" s="31" t="n"/>
+      <c r="Q303" s="31" t="n"/>
       <c r="R303" s="50" t="n"/>
       <c r="S303" s="22" t="inlineStr">
         <is>
@@ -33229,12 +33233,14 @@
       </c>
       <c r="N318" s="2" t="n"/>
       <c r="O318" s="31" t="n">
-        <v>31.3</v>
+        <v>24.3</v>
       </c>
       <c r="P318" s="31" t="n">
-        <v>39.9</v>
-      </c>
-      <c r="Q318" s="31" t="n"/>
+        <v>42.3</v>
+      </c>
+      <c r="Q318" s="31" t="n">
+        <v>34.6</v>
+      </c>
       <c r="R318" s="50" t="n"/>
       <c r="S318" s="22" t="inlineStr">
         <is>
@@ -34607,9 +34613,7 @@
         </is>
       </c>
       <c r="N333" s="2" t="n"/>
-      <c r="O333" s="31" t="n">
-        <v>-5.7</v>
-      </c>
+      <c r="O333" s="31" t="n"/>
       <c r="P333" s="31" t="n"/>
       <c r="Q333" s="31" t="n"/>
       <c r="R333" s="50" t="n"/>
@@ -34941,19 +34945,43 @@
       <c r="AI336" s="2" t="n"/>
     </row>
     <row r="337" ht="24" customHeight="1" s="55">
-      <c r="A337" s="2" t="n"/>
+      <c r="A337" s="2" t="n">
+        <v>336</v>
+      </c>
       <c r="B337" s="2" t="n"/>
-      <c r="C337" s="45" t="n"/>
+      <c r="C337" s="45" t="inlineStr">
+        <is>
+          <t>55026</t>
+        </is>
+      </c>
       <c r="D337" s="2" t="n"/>
-      <c r="E337" s="4" t="n"/>
+      <c r="E337" s="4" t="n">
+        <v>99999</v>
+      </c>
       <c r="F337" s="38" t="n"/>
-      <c r="G337" s="28" t="n"/>
-      <c r="H337" s="28" t="n"/>
-      <c r="I337" s="2" t="n"/>
-      <c r="J337" s="26" t="n"/>
-      <c r="K337" s="30" t="n"/>
+      <c r="G337" s="28" t="n">
+        <v>34.4264</v>
+      </c>
+      <c r="H337" s="28" t="n">
+        <v>80.3861</v>
+      </c>
+      <c r="I337" s="2" t="n">
+        <v>5188.6</v>
+      </c>
+      <c r="J337" s="26" t="n">
+        <v>12</v>
+      </c>
+      <c r="K337" s="30" t="inlineStr">
+        <is>
+          <t>🇨🇳</t>
+        </is>
+      </c>
       <c r="L337" s="2" t="n"/>
-      <c r="M337" s="14" t="n"/>
+      <c r="M337" s="14" t="inlineStr">
+        <is>
+          <t>松西</t>
+        </is>
+      </c>
       <c r="N337" s="2" t="n"/>
       <c r="O337" s="31" t="n"/>
       <c r="P337" s="31" t="n"/>
@@ -34961,36 +34989,86 @@
       <c r="R337" s="50" t="n"/>
       <c r="S337" s="22" t="n"/>
       <c r="T337" s="36" t="n"/>
-      <c r="U337" s="40" t="n"/>
-      <c r="V337" s="2" t="n"/>
-      <c r="W337" s="4" t="n"/>
-      <c r="X337" s="4" t="n"/>
-      <c r="Y337" s="4" t="n"/>
+      <c r="U337" s="40" t="inlineStr">
+        <is>
+          <t>西藏</t>
+        </is>
+      </c>
+      <c r="V337" s="2" t="inlineStr">
+        <is>
+          <t>西藏</t>
+        </is>
+      </c>
+      <c r="W337" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="X337" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="Y337" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="Z337" s="4" t="n"/>
       <c r="AA337" s="2" t="n"/>
       <c r="AB337" s="2" t="n"/>
       <c r="AC337" s="2" t="n"/>
       <c r="AD337" s="2" t="n"/>
-      <c r="AE337" s="2" t="n"/>
-      <c r="AF337" s="4" t="n"/>
+      <c r="AE337" s="2" t="inlineStr">
+        <is>
+          <t>中国</t>
+        </is>
+      </c>
+      <c r="AF337" s="4" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
       <c r="AG337" s="4" t="n"/>
       <c r="AH337" s="2" t="n"/>
       <c r="AI337" s="2" t="n"/>
     </row>
     <row r="338" ht="24" customHeight="1" s="55">
-      <c r="A338" s="2" t="n"/>
+      <c r="A338" s="2" t="n">
+        <v>337</v>
+      </c>
       <c r="B338" s="2" t="n"/>
       <c r="C338" s="45" t="n"/>
       <c r="D338" s="2" t="n"/>
       <c r="E338" s="4" t="n"/>
-      <c r="F338" s="38" t="n"/>
-      <c r="G338" s="28" t="n"/>
-      <c r="H338" s="28" t="n"/>
-      <c r="I338" s="2" t="n"/>
-      <c r="J338" s="26" t="n"/>
-      <c r="K338" s="30" t="n"/>
+      <c r="F338" s="38" t="inlineStr">
+        <is>
+          <t>Y8049</t>
+        </is>
+      </c>
+      <c r="G338" s="28" t="n">
+        <v>42.6856</v>
+      </c>
+      <c r="H338" s="28" t="n">
+        <v>89.0656</v>
+      </c>
+      <c r="I338" s="2" t="n">
+        <v>-106.4</v>
+      </c>
+      <c r="J338" s="26" t="n">
+        <v>12</v>
+      </c>
+      <c r="K338" s="30" t="inlineStr">
+        <is>
+          <t>🇨🇳</t>
+        </is>
+      </c>
       <c r="L338" s="2" t="n"/>
-      <c r="M338" s="14" t="n"/>
+      <c r="M338" s="14" t="inlineStr">
+        <is>
+          <t>新鑫盐矿</t>
+        </is>
+      </c>
       <c r="N338" s="2" t="n"/>
       <c r="O338" s="31" t="n"/>
       <c r="P338" s="31" t="n"/>
@@ -34998,36 +35076,94 @@
       <c r="R338" s="50" t="n"/>
       <c r="S338" s="22" t="n"/>
       <c r="T338" s="36" t="n"/>
-      <c r="U338" s="40" t="n"/>
-      <c r="V338" s="2" t="n"/>
-      <c r="W338" s="4" t="n"/>
-      <c r="X338" s="4" t="n"/>
-      <c r="Y338" s="4" t="n"/>
+      <c r="U338" s="40" t="inlineStr">
+        <is>
+          <t>吐鲁番</t>
+        </is>
+      </c>
+      <c r="V338" s="2" t="inlineStr">
+        <is>
+          <t>新疆</t>
+        </is>
+      </c>
+      <c r="W338" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="X338" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="Y338" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="Z338" s="4" t="n"/>
-      <c r="AA338" s="2" t="n"/>
-      <c r="AB338" s="2" t="n"/>
+      <c r="AA338" s="2" t="inlineStr">
+        <is>
+          <t>吐鲁番市</t>
+        </is>
+      </c>
+      <c r="AB338" s="2" t="inlineStr">
+        <is>
+          <t>高昌区</t>
+        </is>
+      </c>
       <c r="AC338" s="2" t="n"/>
       <c r="AD338" s="2" t="n"/>
-      <c r="AE338" s="2" t="n"/>
-      <c r="AF338" s="4" t="n"/>
+      <c r="AE338" s="2" t="inlineStr">
+        <is>
+          <t>中国</t>
+        </is>
+      </c>
+      <c r="AF338" s="4" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
       <c r="AG338" s="4" t="n"/>
       <c r="AH338" s="2" t="n"/>
       <c r="AI338" s="2" t="n"/>
     </row>
     <row r="339" ht="24" customHeight="1" s="55">
-      <c r="A339" s="2" t="n"/>
+      <c r="A339" s="2" t="n">
+        <v>338</v>
+      </c>
       <c r="B339" s="2" t="n"/>
       <c r="C339" s="45" t="n"/>
       <c r="D339" s="2" t="n"/>
       <c r="E339" s="4" t="n"/>
-      <c r="F339" s="38" t="n"/>
-      <c r="G339" s="28" t="n"/>
-      <c r="H339" s="28" t="n"/>
-      <c r="I339" s="2" t="n"/>
-      <c r="J339" s="26" t="n"/>
-      <c r="K339" s="30" t="n"/>
+      <c r="F339" s="38" t="inlineStr">
+        <is>
+          <t>Y5774</t>
+        </is>
+      </c>
+      <c r="G339" s="28" t="n">
+        <v>42.9044</v>
+      </c>
+      <c r="H339" s="28" t="n">
+        <v>89.4422</v>
+      </c>
+      <c r="I339" s="2" t="n">
+        <v>-52</v>
+      </c>
+      <c r="J339" s="26" t="n">
+        <v>12</v>
+      </c>
+      <c r="K339" s="30" t="inlineStr">
+        <is>
+          <t>🇨🇳</t>
+        </is>
+      </c>
       <c r="L339" s="2" t="n"/>
-      <c r="M339" s="14" t="n"/>
+      <c r="M339" s="14" t="inlineStr">
+        <is>
+          <t>三堡乡</t>
+        </is>
+      </c>
       <c r="N339" s="2" t="n"/>
       <c r="O339" s="31" t="n"/>
       <c r="P339" s="31" t="n"/>
@@ -35035,36 +35171,94 @@
       <c r="R339" s="50" t="n"/>
       <c r="S339" s="22" t="n"/>
       <c r="T339" s="36" t="n"/>
-      <c r="U339" s="40" t="n"/>
-      <c r="V339" s="2" t="n"/>
-      <c r="W339" s="4" t="n"/>
-      <c r="X339" s="4" t="n"/>
-      <c r="Y339" s="4" t="n"/>
+      <c r="U339" s="40" t="inlineStr">
+        <is>
+          <t>吐鲁番</t>
+        </is>
+      </c>
+      <c r="V339" s="2" t="inlineStr">
+        <is>
+          <t>新疆</t>
+        </is>
+      </c>
+      <c r="W339" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="X339" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="Y339" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="Z339" s="4" t="n"/>
-      <c r="AA339" s="2" t="n"/>
-      <c r="AB339" s="2" t="n"/>
+      <c r="AA339" s="2" t="inlineStr">
+        <is>
+          <t>吐鲁番市</t>
+        </is>
+      </c>
+      <c r="AB339" s="2" t="inlineStr">
+        <is>
+          <t>高昌区</t>
+        </is>
+      </c>
       <c r="AC339" s="2" t="n"/>
       <c r="AD339" s="2" t="n"/>
-      <c r="AE339" s="2" t="n"/>
-      <c r="AF339" s="4" t="n"/>
+      <c r="AE339" s="2" t="inlineStr">
+        <is>
+          <t>中国</t>
+        </is>
+      </c>
+      <c r="AF339" s="4" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
       <c r="AG339" s="4" t="n"/>
       <c r="AH339" s="2" t="n"/>
       <c r="AI339" s="2" t="n"/>
     </row>
     <row r="340" ht="24" customHeight="1" s="55">
-      <c r="A340" s="2" t="n"/>
+      <c r="A340" s="2" t="n">
+        <v>339</v>
+      </c>
       <c r="B340" s="2" t="n"/>
       <c r="C340" s="45" t="n"/>
       <c r="D340" s="2" t="n"/>
       <c r="E340" s="4" t="n"/>
-      <c r="F340" s="38" t="n"/>
-      <c r="G340" s="28" t="n"/>
-      <c r="H340" s="28" t="n"/>
-      <c r="I340" s="2" t="n"/>
-      <c r="J340" s="26" t="n"/>
-      <c r="K340" s="30" t="n"/>
+      <c r="F340" s="38" t="inlineStr">
+        <is>
+          <t>C0239</t>
+        </is>
+      </c>
+      <c r="G340" s="28" t="n">
+        <v>52.7464</v>
+      </c>
+      <c r="H340" s="28" t="n">
+        <v>120.2683</v>
+      </c>
+      <c r="I340" s="2" t="n">
+        <v>545.7</v>
+      </c>
+      <c r="J340" s="26" t="n">
+        <v>12</v>
+      </c>
+      <c r="K340" s="30" t="inlineStr">
+        <is>
+          <t>🇨🇳</t>
+        </is>
+      </c>
       <c r="L340" s="2" t="n"/>
-      <c r="M340" s="14" t="n"/>
+      <c r="M340" s="14" t="inlineStr">
+        <is>
+          <t>伊木河</t>
+        </is>
+      </c>
       <c r="N340" s="2" t="n"/>
       <c r="O340" s="31" t="n"/>
       <c r="P340" s="31" t="n"/>
@@ -35072,18 +35266,54 @@
       <c r="R340" s="50" t="n"/>
       <c r="S340" s="22" t="n"/>
       <c r="T340" s="36" t="n"/>
-      <c r="U340" s="40" t="n"/>
-      <c r="V340" s="2" t="n"/>
-      <c r="W340" s="4" t="n"/>
-      <c r="X340" s="4" t="n"/>
-      <c r="Y340" s="4" t="n"/>
+      <c r="U340" s="40" t="inlineStr">
+        <is>
+          <t>额尔古纳</t>
+        </is>
+      </c>
+      <c r="V340" s="2" t="inlineStr">
+        <is>
+          <t>内蒙古</t>
+        </is>
+      </c>
+      <c r="W340" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="X340" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="Y340" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="Z340" s="4" t="n"/>
-      <c r="AA340" s="2" t="n"/>
-      <c r="AB340" s="2" t="n"/>
+      <c r="AA340" s="2" t="inlineStr">
+        <is>
+          <t>呼伦贝尔市</t>
+        </is>
+      </c>
+      <c r="AB340" s="2" t="inlineStr">
+        <is>
+          <t>额尔古纳市</t>
+        </is>
+      </c>
       <c r="AC340" s="2" t="n"/>
       <c r="AD340" s="2" t="n"/>
-      <c r="AE340" s="2" t="n"/>
-      <c r="AF340" s="4" t="n"/>
+      <c r="AE340" s="2" t="inlineStr">
+        <is>
+          <t>中国</t>
+        </is>
+      </c>
+      <c r="AF340" s="4" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
       <c r="AG340" s="4" t="n"/>
       <c r="AH340" s="2" t="n"/>
       <c r="AI340" s="2" t="n"/>

--- a/气象/For_Python_站点信息和记录.xlsx
+++ b/气象/For_Python_站点信息和记录.xlsx
@@ -22,7 +22,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy\ &quot;年&quot;\ m\ &quot;月&quot;\ d\ &quot;日&quot;"/>
   </numFmts>
-  <fonts count="18">
+  <fonts count="19">
     <font>
       <name val="等线"/>
       <charset val="134"/>
@@ -168,6 +168,14 @@
       <b val="1"/>
       <color rgb="FF00B0F0"/>
       <sz val="11"/>
+    </font>
+    <font>
+      <name val="等线"/>
+      <charset val="134"/>
+      <family val="3"/>
+      <color rgb="FFFF0000"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="8">
@@ -840,8 +848,8 @@
     <col width="18.59765625" customWidth="1" style="8" min="26" max="26"/>
     <col width="12.59765625" customWidth="1" style="5" min="27" max="31"/>
     <col width="12.59765625" customWidth="1" style="8" min="32" max="33"/>
-    <col width="12.59765625" customWidth="1" style="5" min="34" max="623"/>
-    <col width="12.59765625" customWidth="1" style="5" min="624" max="16384"/>
+    <col width="12.59765625" customWidth="1" style="5" min="34" max="669"/>
+    <col width="12.59765625" customWidth="1" style="5" min="670" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="27.75" customFormat="1" customHeight="1" s="11">
@@ -1069,13 +1077,13 @@
         </is>
       </c>
       <c r="O2" s="31" t="n">
-        <v>15.9</v>
+        <v>12.4</v>
       </c>
       <c r="P2" s="31" t="n">
-        <v>27.1</v>
+        <v>25.5</v>
       </c>
       <c r="Q2" s="31" t="n">
-        <v>20.4</v>
+        <v>19.7</v>
       </c>
       <c r="R2" s="50" t="n"/>
       <c r="S2" s="22" t="inlineStr">
@@ -1086,7 +1094,7 @@
       <c r="T2" s="36" t="n"/>
       <c r="U2" s="40" t="inlineStr">
         <is>
-          <t>特斯河 乌布苏湖&lt;br&gt;明星站</t>
+          <t>特斯河 乌布苏湖</t>
         </is>
       </c>
       <c r="V2" s="2" t="inlineStr">
@@ -1176,10 +1184,10 @@
         </is>
       </c>
       <c r="O3" s="31" t="n">
-        <v>13.2</v>
+        <v>12.7</v>
       </c>
       <c r="P3" s="31" t="n">
-        <v>27</v>
+        <v>26.6</v>
       </c>
       <c r="Q3" s="31" t="n"/>
       <c r="R3" s="50" t="inlineStr">
@@ -1195,7 +1203,7 @@
       </c>
       <c r="U3" s="40" t="inlineStr">
         <is>
-          <t>乌布苏湖&lt;br&gt;明星站</t>
+          <t>乌布苏湖</t>
         </is>
       </c>
       <c r="V3" s="2" t="inlineStr">
@@ -1285,10 +1293,10 @@
         </is>
       </c>
       <c r="O4" s="31" t="n">
-        <v>14.4</v>
+        <v>10.7</v>
       </c>
       <c r="P4" s="31" t="n">
-        <v>25.7</v>
+        <v>27.7</v>
       </c>
       <c r="Q4" s="31" t="n"/>
       <c r="R4" s="50" t="inlineStr">
@@ -1300,7 +1308,7 @@
       <c r="T4" s="36" t="n"/>
       <c r="U4" s="40" t="inlineStr">
         <is>
-          <t>特斯河&lt;br&gt;明星站</t>
+          <t>特斯河</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
@@ -1483,13 +1491,13 @@
         </is>
       </c>
       <c r="O6" s="31" t="n">
-        <v>9</v>
+        <v>9.9</v>
       </c>
       <c r="P6" s="31" t="n">
-        <v>23.9</v>
+        <v>23.3</v>
       </c>
       <c r="Q6" s="31" t="n">
-        <v>15.99</v>
+        <v>17.3</v>
       </c>
       <c r="R6" s="52" t="inlineStr">
         <is>
@@ -1500,7 +1508,7 @@
       <c r="T6" s="36" t="n"/>
       <c r="U6" s="40" t="inlineStr">
         <is>
-          <t>扎布汗河 杭爱山&lt;br&gt;明星站</t>
+          <t>扎布汗河 杭爱山</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
@@ -1590,10 +1598,10 @@
         </is>
       </c>
       <c r="O7" s="31" t="n">
-        <v>13.4</v>
+        <v>7</v>
       </c>
       <c r="P7" s="31" t="n">
-        <v>23.6</v>
+        <v>21.7</v>
       </c>
       <c r="Q7" s="31" t="n"/>
       <c r="R7" s="50" t="n"/>
@@ -1601,7 +1609,7 @@
       <c r="T7" s="36" t="n"/>
       <c r="U7" s="40" t="inlineStr">
         <is>
-          <t>希希黑德河&lt;br&gt;库苏古尔湖</t>
+          <t>库苏古尔湖</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
@@ -1699,13 +1707,13 @@
       </c>
       <c r="N8" s="2" t="n"/>
       <c r="O8" s="31" t="n">
-        <v>18.3</v>
+        <v>10.6</v>
       </c>
       <c r="P8" s="31" t="n">
-        <v>26.6</v>
+        <v>28.2</v>
       </c>
       <c r="Q8" s="31" t="n">
-        <v>21.16</v>
+        <v>19.01</v>
       </c>
       <c r="R8" s="50" t="n"/>
       <c r="S8" s="22" t="inlineStr">
@@ -1716,7 +1724,7 @@
       <c r="T8" s="36" t="n"/>
       <c r="U8" s="40" t="inlineStr">
         <is>
-          <t>鄂尔浑河&lt;br&gt;色楞格 明星站</t>
+          <t>鄂尔浑河</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
@@ -1812,13 +1820,13 @@
       </c>
       <c r="N9" s="2" t="n"/>
       <c r="O9" s="31" t="n">
-        <v>11.3</v>
+        <v>11.5</v>
       </c>
       <c r="P9" s="31" t="n">
-        <v>27.8</v>
+        <v>24.4</v>
       </c>
       <c r="Q9" s="31" t="n">
-        <v>19.64</v>
+        <v>17.76</v>
       </c>
       <c r="R9" s="50" t="n"/>
       <c r="S9" s="22" t="inlineStr">
@@ -1933,13 +1941,13 @@
         </is>
       </c>
       <c r="O10" s="31" t="n">
-        <v>14.3</v>
+        <v>12.8</v>
       </c>
       <c r="P10" s="31" t="n">
-        <v>24.2</v>
+        <v>26.8</v>
       </c>
       <c r="Q10" s="31" t="n">
-        <v>18.24</v>
+        <v>18.89</v>
       </c>
       <c r="R10" s="50" t="n"/>
       <c r="S10" s="22" t="inlineStr">
@@ -1950,7 +1958,7 @@
       <c r="T10" s="36" t="n"/>
       <c r="U10" s="40" t="inlineStr">
         <is>
-          <t>特斯河&lt;br&gt;明星站</t>
+          <t>特斯河</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
@@ -2050,13 +2058,13 @@
         </is>
       </c>
       <c r="O11" s="31" t="n">
-        <v>10.7</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="P11" s="31" t="n">
-        <v>21.7</v>
+        <v>22.2</v>
       </c>
       <c r="Q11" s="31" t="n">
-        <v>16.04</v>
+        <v>15.05</v>
       </c>
       <c r="R11" s="50" t="inlineStr">
         <is>
@@ -2069,11 +2077,7 @@
         </is>
       </c>
       <c r="T11" s="36" t="n"/>
-      <c r="U11" s="40" t="inlineStr">
-        <is>
-          <t>明星站</t>
-        </is>
-      </c>
+      <c r="U11" s="40" t="n"/>
       <c r="V11" s="2" t="inlineStr">
         <is>
           <t>扎布汗</t>
@@ -2167,13 +2171,13 @@
       </c>
       <c r="N12" s="2" t="n"/>
       <c r="O12" s="31" t="n">
-        <v>11.9</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="P12" s="31" t="n">
-        <v>26.3</v>
+        <v>24.9</v>
       </c>
       <c r="Q12" s="31" t="n">
-        <v>18.43</v>
+        <v>16.84</v>
       </c>
       <c r="R12" s="50" t="inlineStr">
         <is>
@@ -2288,13 +2292,13 @@
         </is>
       </c>
       <c r="O13" s="31" t="n">
-        <v>12.3</v>
+        <v>5.9</v>
       </c>
       <c r="P13" s="31" t="n">
-        <v>23.7</v>
+        <v>24.1</v>
       </c>
       <c r="Q13" s="31" t="n">
-        <v>17.36</v>
+        <v>15.12</v>
       </c>
       <c r="R13" s="50" t="inlineStr">
         <is>
@@ -2309,7 +2313,7 @@
       <c r="T13" s="36" t="n"/>
       <c r="U13" s="40" t="inlineStr">
         <is>
-          <t>库苏古尔湖&lt;br&gt;明星站</t>
+          <t>库苏古尔湖</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
@@ -2405,13 +2409,13 @@
       </c>
       <c r="N14" s="2" t="n"/>
       <c r="O14" s="31" t="n">
-        <v>17</v>
+        <v>12.7</v>
       </c>
       <c r="P14" s="31" t="n">
-        <v>28.8</v>
+        <v>24.3</v>
       </c>
       <c r="Q14" s="31" t="n">
-        <v>21.06</v>
+        <v>18.19</v>
       </c>
       <c r="R14" s="50" t="n"/>
       <c r="S14" s="22" t="inlineStr">
@@ -2526,13 +2530,13 @@
       </c>
       <c r="N15" s="2" t="n"/>
       <c r="O15" s="31" t="n">
-        <v>14.6</v>
+        <v>4.7</v>
       </c>
       <c r="P15" s="31" t="n">
-        <v>27.4</v>
+        <v>20.9</v>
       </c>
       <c r="Q15" s="31" t="n">
-        <v>19.21</v>
+        <v>12.6</v>
       </c>
       <c r="R15" s="50" t="n"/>
       <c r="S15" s="22" t="inlineStr">
@@ -2737,7 +2741,7 @@
       <c r="T17" s="36" t="n"/>
       <c r="U17" s="40" t="inlineStr">
         <is>
-          <t>杭爱山&lt;br&gt;明星站</t>
+          <t>杭爱山</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
@@ -8002,13 +8006,13 @@
       </c>
       <c r="N75" s="2" t="n"/>
       <c r="O75" s="31" t="n">
-        <v>20.5</v>
+        <v>19.6</v>
       </c>
       <c r="P75" s="31" t="n">
-        <v>29.6</v>
+        <v>33.6</v>
       </c>
       <c r="Q75" s="31" t="n">
-        <v>24.23</v>
+        <v>26.59</v>
       </c>
       <c r="R75" s="50" t="n"/>
       <c r="S75" s="22" t="inlineStr">
@@ -8114,7 +8118,7 @@
       <c r="T76" s="36" t="n"/>
       <c r="U76" s="40" t="inlineStr">
         <is>
-          <t>俄罗斯犹太州</t>
+          <t>犹太州</t>
         </is>
       </c>
       <c r="V76" s="2" t="inlineStr">
@@ -8321,13 +8325,13 @@
         </is>
       </c>
       <c r="O78" s="31" t="n">
-        <v>13.4</v>
+        <v>11.7</v>
       </c>
       <c r="P78" s="31" t="n">
-        <v>23.6</v>
+        <v>19.1</v>
       </c>
       <c r="Q78" s="31" t="n">
-        <v>17.98</v>
+        <v>14.36</v>
       </c>
       <c r="R78" s="50" t="inlineStr">
         <is>
@@ -8342,7 +8346,7 @@
       <c r="T78" s="36" t="n"/>
       <c r="U78" s="40" t="inlineStr">
         <is>
-          <t>明星站</t>
+          <t>谢列姆贾山区</t>
         </is>
       </c>
       <c r="V78" s="2" t="inlineStr">
@@ -8755,14 +8759,12 @@
         </is>
       </c>
       <c r="O82" s="31" t="n">
-        <v>16.7</v>
+        <v>6.5</v>
       </c>
       <c r="P82" s="31" t="n">
-        <v>25.2</v>
-      </c>
-      <c r="Q82" s="31" t="n">
-        <v>20.73</v>
-      </c>
+        <v>20.8</v>
+      </c>
+      <c r="Q82" s="31" t="n"/>
       <c r="R82" s="50" t="n"/>
       <c r="S82" s="22" t="inlineStr">
         <is>
@@ -8772,7 +8774,7 @@
       <c r="T82" s="36" t="n"/>
       <c r="U82" s="40" t="inlineStr">
         <is>
-          <t>明星站</t>
+          <t>卡连加河&lt;br&gt;外贝加尔</t>
         </is>
       </c>
       <c r="V82" s="2" t="inlineStr">
@@ -8877,13 +8879,13 @@
         </is>
       </c>
       <c r="O83" s="31" t="n">
-        <v>13.8</v>
+        <v>8.4</v>
       </c>
       <c r="P83" s="31" t="n">
-        <v>25.9</v>
+        <v>20.5</v>
       </c>
       <c r="Q83" s="31" t="n">
-        <v>19.59</v>
+        <v>13.81</v>
       </c>
       <c r="R83" s="50" t="n"/>
       <c r="S83" s="22" t="inlineStr">
@@ -8894,7 +8896,7 @@
       <c r="T83" s="36" t="n"/>
       <c r="U83" s="40" t="inlineStr">
         <is>
-          <t>明星站</t>
+          <t>卡连加河&lt;br&gt;外贝加尔</t>
         </is>
       </c>
       <c r="V83" s="2" t="inlineStr">
@@ -8997,7 +8999,7 @@
       <c r="T84" s="36" t="n"/>
       <c r="U84" s="40" t="inlineStr">
         <is>
-          <t>贝加尔湖</t>
+          <t>贝加尔湖&lt;br&gt;布里亚特</t>
         </is>
       </c>
       <c r="V84" s="2" t="inlineStr">
@@ -9097,13 +9099,13 @@
         </is>
       </c>
       <c r="O85" s="31" t="n">
-        <v>13.3</v>
+        <v>10</v>
       </c>
       <c r="P85" s="31" t="n">
-        <v>25.7</v>
+        <v>24.6</v>
       </c>
       <c r="Q85" s="31" t="n">
-        <v>19.01</v>
+        <v>15.94</v>
       </c>
       <c r="R85" s="50" t="n"/>
       <c r="S85" s="22" t="inlineStr">
@@ -9114,7 +9116,7 @@
       <c r="T85" s="36" t="n"/>
       <c r="U85" s="40" t="inlineStr">
         <is>
-          <t>贝加尔湖</t>
+          <t>贝加尔湖&lt;br&gt;伊尔库茨克</t>
         </is>
       </c>
       <c r="V85" s="2" t="inlineStr">
@@ -9317,13 +9319,13 @@
       </c>
       <c r="N87" s="2" t="n"/>
       <c r="O87" s="31" t="n">
-        <v>16.6</v>
+        <v>13.2</v>
       </c>
       <c r="P87" s="31" t="n">
         <v>25</v>
       </c>
       <c r="Q87" s="31" t="n">
-        <v>19.54</v>
+        <v>18.62</v>
       </c>
       <c r="R87" s="50" t="n"/>
       <c r="S87" s="22" t="inlineStr">
@@ -9338,7 +9340,7 @@
       </c>
       <c r="U87" s="40" t="inlineStr">
         <is>
-          <t>叶尼塞河</t>
+          <t>叶尼塞河&lt;br&gt;图瓦</t>
         </is>
       </c>
       <c r="V87" s="2" t="inlineStr">
@@ -9449,7 +9451,7 @@
       <c r="T88" s="36" t="n"/>
       <c r="U88" s="40" t="inlineStr">
         <is>
-          <t>特斯河</t>
+          <t>特斯河&lt;br&gt;图瓦</t>
         </is>
       </c>
       <c r="V88" s="2" t="inlineStr">
@@ -9545,13 +9547,13 @@
       </c>
       <c r="N89" s="2" t="n"/>
       <c r="O89" s="31" t="n">
-        <v>6.4</v>
+        <v>7.1</v>
       </c>
       <c r="P89" s="31" t="n">
-        <v>20.9</v>
+        <v>15.2</v>
       </c>
       <c r="Q89" s="31" t="n">
-        <v>13.65</v>
+        <v>10.04</v>
       </c>
       <c r="R89" s="50" t="inlineStr">
         <is>
@@ -9566,7 +9568,7 @@
       <c r="T89" s="36" t="n"/>
       <c r="U89" s="40" t="inlineStr">
         <is>
-          <t>阿尔泰山</t>
+          <t>阿尔泰山&lt;br&gt;阿尔泰共和国</t>
         </is>
       </c>
       <c r="V89" s="2" t="inlineStr">
@@ -9673,7 +9675,7 @@
       <c r="T90" s="36" t="n"/>
       <c r="U90" s="40" t="inlineStr">
         <is>
-          <t>额尔古纳河</t>
+          <t>额尔古纳河&lt;br&gt;外贝加尔</t>
         </is>
       </c>
       <c r="V90" s="2" t="inlineStr">
@@ -9776,7 +9778,7 @@
       <c r="T91" s="36" t="n"/>
       <c r="U91" s="40" t="inlineStr">
         <is>
-          <t>哈萨克斯坦</t>
+          <t>东哈萨克斯坦州</t>
         </is>
       </c>
       <c r="V91" s="2" t="inlineStr">
@@ -9967,13 +9969,13 @@
       </c>
       <c r="N93" s="2" t="n"/>
       <c r="O93" s="31" t="n">
-        <v>16.3</v>
+        <v>13.5</v>
       </c>
       <c r="P93" s="31" t="n">
-        <v>27</v>
+        <v>24.8</v>
       </c>
       <c r="Q93" s="31" t="n">
-        <v>20.53</v>
+        <v>18.24</v>
       </c>
       <c r="R93" s="50" t="n"/>
       <c r="S93" s="22" t="inlineStr">
@@ -10080,13 +10082,13 @@
       </c>
       <c r="N94" s="2" t="n"/>
       <c r="O94" s="31" t="n">
-        <v>24</v>
+        <v>21.6</v>
       </c>
       <c r="P94" s="31" t="n">
-        <v>33.8</v>
+        <v>32.4</v>
       </c>
       <c r="Q94" s="31" t="n">
-        <v>29.08</v>
+        <v>26.76</v>
       </c>
       <c r="R94" s="50" t="n"/>
       <c r="S94" s="22" t="inlineStr">
@@ -10316,13 +10318,13 @@
       </c>
       <c r="N96" s="2" t="n"/>
       <c r="O96" s="31" t="n">
-        <v>24.4</v>
+        <v>22.3</v>
       </c>
       <c r="P96" s="31" t="n">
-        <v>32.2</v>
+        <v>30.6</v>
       </c>
       <c r="Q96" s="31" t="n">
-        <v>28.08</v>
+        <v>26.2</v>
       </c>
       <c r="R96" s="50" t="n"/>
       <c r="S96" s="22" t="inlineStr">
@@ -10560,13 +10562,13 @@
       </c>
       <c r="N98" s="2" t="n"/>
       <c r="O98" s="31" t="n">
-        <v>24</v>
+        <v>21.5</v>
       </c>
       <c r="P98" s="31" t="n">
-        <v>31.8</v>
+        <v>30.7</v>
       </c>
       <c r="Q98" s="31" t="n">
-        <v>27.24</v>
+        <v>25.29</v>
       </c>
       <c r="R98" s="50" t="n"/>
       <c r="S98" s="22" t="inlineStr">
@@ -10692,7 +10694,7 @@
       <c r="T99" s="36" t="n"/>
       <c r="U99" s="40" t="inlineStr">
         <is>
-          <t>小兴安岭</t>
+          <t>黑龙江 小兴安岭</t>
         </is>
       </c>
       <c r="V99" s="2" t="inlineStr">
@@ -10803,7 +10805,7 @@
       <c r="T100" s="36" t="n"/>
       <c r="U100" s="40" t="inlineStr">
         <is>
-          <t>大兴安岭</t>
+          <t>黑龙江大兴安岭</t>
         </is>
       </c>
       <c r="V100" s="2" t="inlineStr">
@@ -10910,7 +10912,7 @@
       <c r="T101" s="36" t="n"/>
       <c r="U101" s="40" t="inlineStr">
         <is>
-          <t>大兴安岭</t>
+          <t>黑龙江大兴安岭</t>
         </is>
       </c>
       <c r="V101" s="2" t="inlineStr">
@@ -11017,7 +11019,7 @@
       <c r="T102" s="36" t="n"/>
       <c r="U102" s="40" t="inlineStr">
         <is>
-          <t>大兴安岭</t>
+          <t>黑龙江大兴安岭</t>
         </is>
       </c>
       <c r="V102" s="2" t="inlineStr">
@@ -11121,13 +11123,13 @@
       </c>
       <c r="N103" s="2" t="n"/>
       <c r="O103" s="31" t="n">
-        <v>18.7</v>
+        <v>5.2</v>
       </c>
       <c r="P103" s="31" t="n">
-        <v>27</v>
+        <v>20.6</v>
       </c>
       <c r="Q103" s="31" t="n">
-        <v>21.71</v>
+        <v>12.35</v>
       </c>
       <c r="R103" s="50" t="n"/>
       <c r="S103" s="22" t="inlineStr">
@@ -11142,7 +11144,7 @@
       </c>
       <c r="U103" s="40" t="inlineStr">
         <is>
-          <t>大兴安岭</t>
+          <t>黑龙江大兴安岭</t>
         </is>
       </c>
       <c r="V103" s="2" t="inlineStr">
@@ -11245,7 +11247,7 @@
       <c r="T104" s="36" t="n"/>
       <c r="U104" s="40" t="inlineStr">
         <is>
-          <t>大兴安岭</t>
+          <t>黑龙江 大兴安岭</t>
         </is>
       </c>
       <c r="V104" s="2" t="inlineStr">
@@ -11460,13 +11462,13 @@
         </is>
       </c>
       <c r="O106" s="31" t="n">
-        <v>15.7</v>
+        <v>10</v>
       </c>
       <c r="P106" s="31" t="n">
-        <v>28.3</v>
+        <v>21.1</v>
       </c>
       <c r="Q106" s="31" t="n">
-        <v>21.88</v>
+        <v>14.92</v>
       </c>
       <c r="R106" s="50" t="n"/>
       <c r="S106" s="22" t="inlineStr">
@@ -11477,7 +11479,7 @@
       <c r="T106" s="36" t="n"/>
       <c r="U106" s="40" t="inlineStr">
         <is>
-          <t>呼伦贝尔</t>
+          <t>牙克石</t>
         </is>
       </c>
       <c r="V106" s="2" t="inlineStr">
@@ -12302,13 +12304,13 @@
       </c>
       <c r="N114" s="2" t="n"/>
       <c r="O114" s="31" t="n">
-        <v>6.6</v>
+        <v>5.7</v>
       </c>
       <c r="P114" s="31" t="n">
-        <v>18.5</v>
+        <v>12.8</v>
       </c>
       <c r="Q114" s="31" t="n">
-        <v>11.65</v>
+        <v>7.86</v>
       </c>
       <c r="R114" s="50" t="n"/>
       <c r="S114" s="22" t="inlineStr">
@@ -12419,13 +12421,13 @@
         </is>
       </c>
       <c r="O115" s="31" t="n">
-        <v>1.2</v>
+        <v>2.2</v>
       </c>
       <c r="P115" s="31" t="n">
-        <v>18.2</v>
+        <v>14.6</v>
       </c>
       <c r="Q115" s="31" t="n">
-        <v>10.41</v>
+        <v>7.7</v>
       </c>
       <c r="R115" s="50" t="n"/>
       <c r="S115" s="22" t="inlineStr">
@@ -12544,13 +12546,13 @@
         </is>
       </c>
       <c r="O116" s="31" t="n">
-        <v>5.8</v>
+        <v>-0.5</v>
       </c>
       <c r="P116" s="31" t="n">
-        <v>15.2</v>
+        <v>15</v>
       </c>
       <c r="Q116" s="31" t="n">
-        <v>9.220000000000001</v>
+        <v>5.12</v>
       </c>
       <c r="R116" s="50" t="n"/>
       <c r="S116" s="22" t="inlineStr">
@@ -13109,13 +13111,13 @@
       </c>
       <c r="N121" s="2" t="n"/>
       <c r="O121" s="31" t="n">
-        <v>28.8</v>
+        <v>28</v>
       </c>
       <c r="P121" s="31" t="n">
-        <v>39.3</v>
+        <v>41.2</v>
       </c>
       <c r="Q121" s="31" t="n">
-        <v>34.14</v>
+        <v>34.4</v>
       </c>
       <c r="R121" s="50" t="n"/>
       <c r="S121" s="22" t="inlineStr">
@@ -13226,13 +13228,13 @@
       </c>
       <c r="N122" s="2" t="n"/>
       <c r="O122" s="31" t="n">
-        <v>18.5</v>
+        <v>18.9</v>
       </c>
       <c r="P122" s="31" t="n">
-        <v>25.8</v>
+        <v>26</v>
       </c>
       <c r="Q122" s="31" t="n">
-        <v>22.03</v>
+        <v>22.14</v>
       </c>
       <c r="R122" s="50" t="n"/>
       <c r="S122" s="22" t="inlineStr">
@@ -13351,13 +13353,13 @@
       </c>
       <c r="N123" s="2" t="n"/>
       <c r="O123" s="31" t="n">
-        <v>7.7</v>
+        <v>6.5</v>
       </c>
       <c r="P123" s="31" t="n">
-        <v>17.3</v>
+        <v>16.2</v>
       </c>
       <c r="Q123" s="31" t="n">
-        <v>11.36</v>
+        <v>11.31</v>
       </c>
       <c r="R123" s="50" t="n"/>
       <c r="S123" s="22" t="inlineStr">
@@ -13575,13 +13577,13 @@
       </c>
       <c r="N125" s="2" t="n"/>
       <c r="O125" s="31" t="n">
-        <v>20.1</v>
+        <v>15.7</v>
       </c>
       <c r="P125" s="31" t="n">
-        <v>30.6</v>
+        <v>28.7</v>
       </c>
       <c r="Q125" s="31" t="n">
-        <v>25.41</v>
+        <v>21.69</v>
       </c>
       <c r="R125" s="50" t="n"/>
       <c r="S125" s="22" t="inlineStr">
@@ -13700,13 +13702,13 @@
       </c>
       <c r="N126" s="2" t="n"/>
       <c r="O126" s="31" t="n">
-        <v>26.3</v>
+        <v>24.6</v>
       </c>
       <c r="P126" s="31" t="n">
-        <v>34.2</v>
+        <v>33.3</v>
       </c>
       <c r="Q126" s="31" t="n">
-        <v>30.44</v>
+        <v>28.67</v>
       </c>
       <c r="R126" s="50" t="n"/>
       <c r="S126" s="22" t="inlineStr">
@@ -13805,13 +13807,13 @@
       </c>
       <c r="N127" s="2" t="n"/>
       <c r="O127" s="31" t="n">
-        <v>26.5</v>
+        <v>25.6</v>
       </c>
       <c r="P127" s="31" t="n">
-        <v>35.5</v>
+        <v>33</v>
       </c>
       <c r="Q127" s="31" t="n">
-        <v>30.8</v>
+        <v>29.16</v>
       </c>
       <c r="R127" s="50" t="n"/>
       <c r="S127" s="22" t="inlineStr">
@@ -13918,13 +13920,13 @@
       </c>
       <c r="N128" s="2" t="n"/>
       <c r="O128" s="31" t="n">
-        <v>21.6</v>
+        <v>18.9</v>
       </c>
       <c r="P128" s="31" t="n">
-        <v>32.1</v>
+        <v>34.4</v>
       </c>
       <c r="Q128" s="31" t="n">
-        <v>26.31</v>
+        <v>26.32</v>
       </c>
       <c r="R128" s="50" t="n"/>
       <c r="S128" s="22" t="inlineStr">
@@ -14039,13 +14041,13 @@
       </c>
       <c r="N129" s="2" t="n"/>
       <c r="O129" s="31" t="n">
-        <v>25.1</v>
+        <v>25</v>
       </c>
       <c r="P129" s="31" t="n">
-        <v>32.5</v>
+        <v>32.6</v>
       </c>
       <c r="Q129" s="31" t="n">
-        <v>28.02</v>
+        <v>28.39</v>
       </c>
       <c r="R129" s="50" t="n"/>
       <c r="S129" s="22" t="inlineStr">
@@ -14152,13 +14154,13 @@
       </c>
       <c r="N130" s="2" t="n"/>
       <c r="O130" s="31" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="P130" s="31" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="Q130" s="31" t="n">
-        <v>26.12</v>
+        <v>24.86</v>
       </c>
       <c r="R130" s="50" t="n"/>
       <c r="S130" s="22" t="inlineStr">
@@ -14273,13 +14275,13 @@
       </c>
       <c r="N131" s="2" t="n"/>
       <c r="O131" s="31" t="n">
-        <v>13.7</v>
+        <v>12</v>
       </c>
       <c r="P131" s="31" t="n">
-        <v>31.5</v>
+        <v>26.7</v>
       </c>
       <c r="Q131" s="31" t="n">
-        <v>21.93</v>
+        <v>18.56</v>
       </c>
       <c r="R131" s="50" t="n"/>
       <c r="S131" s="22" t="inlineStr">
@@ -14397,10 +14399,10 @@
         <v>24.8</v>
       </c>
       <c r="P132" s="31" t="n">
-        <v>32.3</v>
+        <v>33.8</v>
       </c>
       <c r="Q132" s="31" t="n">
-        <v>28.34</v>
+        <v>27.85</v>
       </c>
       <c r="R132" s="50" t="n"/>
       <c r="S132" s="22" t="inlineStr">
@@ -14511,13 +14513,13 @@
       </c>
       <c r="N133" s="2" t="n"/>
       <c r="O133" s="31" t="n">
-        <v>25.2</v>
+        <v>25.3</v>
       </c>
       <c r="P133" s="31" t="n">
-        <v>32</v>
+        <v>32.9</v>
       </c>
       <c r="Q133" s="31" t="n">
-        <v>28.11</v>
+        <v>29.02</v>
       </c>
       <c r="R133" s="50" t="n"/>
       <c r="S133" s="22" t="inlineStr">
@@ -14628,13 +14630,13 @@
       </c>
       <c r="N134" s="2" t="n"/>
       <c r="O134" s="31" t="n">
-        <v>25.3</v>
+        <v>24.6</v>
       </c>
       <c r="P134" s="31" t="n">
-        <v>34.9</v>
+        <v>32.9</v>
       </c>
       <c r="Q134" s="31" t="n">
-        <v>29.26</v>
+        <v>28.66</v>
       </c>
       <c r="R134" s="50" t="n"/>
       <c r="S134" s="22" t="inlineStr">
@@ -14852,13 +14854,13 @@
       </c>
       <c r="N136" s="2" t="n"/>
       <c r="O136" s="31" t="n">
-        <v>25.2</v>
+        <v>27.2</v>
       </c>
       <c r="P136" s="31" t="n">
-        <v>30.2</v>
+        <v>33.3</v>
       </c>
       <c r="Q136" s="31" t="n">
-        <v>27.05</v>
+        <v>30.12</v>
       </c>
       <c r="R136" s="50" t="n"/>
       <c r="S136" s="22" t="inlineStr">
@@ -14969,13 +14971,13 @@
       </c>
       <c r="N137" s="2" t="n"/>
       <c r="O137" s="31" t="n">
-        <v>27.7</v>
+        <v>28.5</v>
       </c>
       <c r="P137" s="31" t="n">
-        <v>32.8</v>
+        <v>35.3</v>
       </c>
       <c r="Q137" s="31" t="n">
-        <v>29.79</v>
+        <v>31.2</v>
       </c>
       <c r="R137" s="50" t="n"/>
       <c r="S137" s="22" t="inlineStr">
@@ -15086,13 +15088,13 @@
       </c>
       <c r="N138" s="2" t="n"/>
       <c r="O138" s="31" t="n">
-        <v>26</v>
+        <v>26.9</v>
       </c>
       <c r="P138" s="31" t="n">
-        <v>32.5</v>
+        <v>35.7</v>
       </c>
       <c r="Q138" s="31" t="n">
-        <v>29.61</v>
+        <v>31.26</v>
       </c>
       <c r="R138" s="50" t="n"/>
       <c r="S138" s="22" t="inlineStr">
@@ -15203,13 +15205,13 @@
       </c>
       <c r="N139" s="2" t="n"/>
       <c r="O139" s="31" t="n">
-        <v>26.6</v>
+        <v>26</v>
       </c>
       <c r="P139" s="31" t="n">
-        <v>34.2</v>
+        <v>33.6</v>
       </c>
       <c r="Q139" s="31" t="n">
-        <v>29.68</v>
+        <v>29.14</v>
       </c>
       <c r="R139" s="50" t="n"/>
       <c r="S139" s="22" t="inlineStr">
@@ -15320,13 +15322,13 @@
       </c>
       <c r="N140" s="2" t="n"/>
       <c r="O140" s="31" t="n">
-        <v>28.6</v>
+        <v>26.7</v>
       </c>
       <c r="P140" s="31" t="n">
-        <v>33.5</v>
+        <v>33.2</v>
       </c>
       <c r="Q140" s="31" t="n">
-        <v>30.79</v>
+        <v>29.23</v>
       </c>
       <c r="R140" s="50" t="n"/>
       <c r="S140" s="22" t="inlineStr">
@@ -15437,13 +15439,13 @@
       </c>
       <c r="N141" s="2" t="n"/>
       <c r="O141" s="31" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="P141" s="31" t="n">
+        <v>33.2</v>
+      </c>
+      <c r="Q141" s="31" t="n">
         <v>28.8</v>
-      </c>
-      <c r="P141" s="31" t="n">
-        <v>35.2</v>
-      </c>
-      <c r="Q141" s="31" t="n">
-        <v>31.79</v>
       </c>
       <c r="R141" s="50" t="n"/>
       <c r="S141" s="22" t="inlineStr">
@@ -15657,13 +15659,13 @@
       </c>
       <c r="N143" s="2" t="n"/>
       <c r="O143" s="31" t="n">
-        <v>25.3</v>
+        <v>25.6</v>
       </c>
       <c r="P143" s="31" t="n">
-        <v>35.5</v>
+        <v>31.2</v>
       </c>
       <c r="Q143" s="31" t="n">
-        <v>28.8</v>
+        <v>27.78</v>
       </c>
       <c r="R143" s="50" t="n"/>
       <c r="S143" s="22" t="inlineStr">
@@ -15774,13 +15776,13 @@
       </c>
       <c r="N144" s="2" t="n"/>
       <c r="O144" s="31" t="n">
-        <v>24.9</v>
+        <v>25.5</v>
       </c>
       <c r="P144" s="31" t="n">
-        <v>32.4</v>
+        <v>32.6</v>
       </c>
       <c r="Q144" s="31" t="n">
-        <v>27.48</v>
+        <v>28.41</v>
       </c>
       <c r="R144" s="50" t="n"/>
       <c r="S144" s="22" t="inlineStr">
@@ -16093,13 +16095,13 @@
       </c>
       <c r="N147" s="2" t="n"/>
       <c r="O147" s="31" t="n">
-        <v>25.4</v>
+        <v>26</v>
       </c>
       <c r="P147" s="31" t="n">
-        <v>33.7</v>
+        <v>28.9</v>
       </c>
       <c r="Q147" s="31" t="n">
-        <v>30.77</v>
+        <v>27.45</v>
       </c>
       <c r="R147" s="50" t="n"/>
       <c r="S147" s="22" t="inlineStr">
@@ -16202,13 +16204,13 @@
       </c>
       <c r="N148" s="2" t="n"/>
       <c r="O148" s="31" t="n">
-        <v>26.4</v>
+        <v>25.7</v>
       </c>
       <c r="P148" s="31" t="n">
-        <v>33.9</v>
+        <v>31.8</v>
       </c>
       <c r="Q148" s="31" t="n">
-        <v>30.12</v>
+        <v>27.76</v>
       </c>
       <c r="R148" s="50" t="n"/>
       <c r="S148" s="22" t="inlineStr">
@@ -16319,13 +16321,13 @@
       </c>
       <c r="N149" s="2" t="n"/>
       <c r="O149" s="31" t="n">
-        <v>25.2</v>
+        <v>24.1</v>
       </c>
       <c r="P149" s="31" t="n">
-        <v>31.6</v>
+        <v>38</v>
       </c>
       <c r="Q149" s="31" t="n">
-        <v>28.2</v>
+        <v>29.89</v>
       </c>
       <c r="R149" s="50" t="n"/>
       <c r="S149" s="22" t="inlineStr">
@@ -16432,13 +16434,13 @@
       </c>
       <c r="N150" s="2" t="n"/>
       <c r="O150" s="31" t="n">
-        <v>17.3</v>
+        <v>16.9</v>
       </c>
       <c r="P150" s="31" t="n">
-        <v>24</v>
+        <v>27.4</v>
       </c>
       <c r="Q150" s="31" t="n">
-        <v>19.94</v>
+        <v>21.77</v>
       </c>
       <c r="R150" s="50" t="n"/>
       <c r="S150" s="22" t="inlineStr">
@@ -16549,13 +16551,13 @@
       </c>
       <c r="N151" s="2" t="n"/>
       <c r="O151" s="31" t="n">
-        <v>19.2</v>
+        <v>20.4</v>
       </c>
       <c r="P151" s="31" t="n">
-        <v>27.4</v>
+        <v>29.6</v>
       </c>
       <c r="Q151" s="31" t="n">
-        <v>21.31</v>
+        <v>24.11</v>
       </c>
       <c r="R151" s="50" t="n"/>
       <c r="S151" s="22" t="inlineStr">
@@ -16666,13 +16668,13 @@
       </c>
       <c r="N152" s="2" t="n"/>
       <c r="O152" s="31" t="n">
-        <v>24.9</v>
+        <v>27.1</v>
       </c>
       <c r="P152" s="31" t="n">
-        <v>37</v>
+        <v>34.9</v>
       </c>
       <c r="Q152" s="31" t="n">
-        <v>30.14</v>
+        <v>28.97</v>
       </c>
       <c r="R152" s="50" t="n"/>
       <c r="S152" s="22" t="inlineStr">
@@ -16874,13 +16876,13 @@
       </c>
       <c r="N154" s="2" t="n"/>
       <c r="O154" s="31" t="n">
-        <v>21.8</v>
+        <v>22.7</v>
       </c>
       <c r="P154" s="31" t="n">
-        <v>31.8</v>
+        <v>30.9</v>
       </c>
       <c r="Q154" s="31" t="n">
-        <v>25.95</v>
+        <v>25.93</v>
       </c>
       <c r="R154" s="50" t="n"/>
       <c r="S154" s="22" t="inlineStr">
@@ -16995,13 +16997,13 @@
       </c>
       <c r="N155" s="2" t="n"/>
       <c r="O155" s="31" t="n">
-        <v>16.2</v>
+        <v>11.7</v>
       </c>
       <c r="P155" s="31" t="n">
-        <v>27.6</v>
+        <v>19.2</v>
       </c>
       <c r="Q155" s="31" t="n">
-        <v>21.1</v>
+        <v>15.04</v>
       </c>
       <c r="R155" s="50" t="n"/>
       <c r="S155" s="22" t="inlineStr">
@@ -17298,13 +17300,13 @@
       </c>
       <c r="N158" s="2" t="n"/>
       <c r="O158" s="31" t="n">
-        <v>28.7</v>
+        <v>27.5</v>
       </c>
       <c r="P158" s="31" t="n">
-        <v>34.3</v>
+        <v>32.9</v>
       </c>
       <c r="Q158" s="31" t="n">
-        <v>30.69</v>
+        <v>29.38</v>
       </c>
       <c r="R158" s="50" t="n"/>
       <c r="S158" s="22" t="inlineStr">
@@ -17692,13 +17694,13 @@
       </c>
       <c r="N162" s="2" t="n"/>
       <c r="O162" s="31" t="n">
-        <v>21.2</v>
+        <v>18.9</v>
       </c>
       <c r="P162" s="31" t="n">
-        <v>33</v>
+        <v>33.5</v>
       </c>
       <c r="Q162" s="31" t="n">
-        <v>26.19</v>
+        <v>26.05</v>
       </c>
       <c r="R162" s="50" t="n"/>
       <c r="S162" s="22" t="inlineStr">
@@ -17818,7 +17820,7 @@
       <c r="T163" s="36" t="n"/>
       <c r="U163" s="40" t="inlineStr">
         <is>
-          <t>大兴安岭</t>
+          <t>黑龙江大兴安岭</t>
         </is>
       </c>
       <c r="V163" s="2" t="inlineStr">
@@ -17913,8 +17915,12 @@
           <t>⚡</t>
         </is>
       </c>
-      <c r="O164" s="31" t="n"/>
-      <c r="P164" s="31" t="n"/>
+      <c r="O164" s="31" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="P164" s="31" t="n">
+        <v>20.5</v>
+      </c>
       <c r="Q164" s="31" t="n"/>
       <c r="R164" s="50" t="n"/>
       <c r="S164" s="22" t="inlineStr">
@@ -17925,7 +17931,7 @@
       <c r="T164" s="36" t="n"/>
       <c r="U164" s="40" t="inlineStr">
         <is>
-          <t>明星站</t>
+          <t>黑龙江大兴安岭</t>
         </is>
       </c>
       <c r="V164" s="2" t="inlineStr">
@@ -18036,7 +18042,7 @@
       <c r="T165" s="36" t="n"/>
       <c r="U165" s="40" t="inlineStr">
         <is>
-          <t>大兴安岭</t>
+          <t>黑龙江大兴安岭</t>
         </is>
       </c>
       <c r="V165" s="2" t="inlineStr">
@@ -18250,7 +18256,7 @@
       <c r="T167" s="36" t="n"/>
       <c r="U167" s="43" t="inlineStr">
         <is>
-          <t>明星站</t>
+          <t>陈巴尔虎旗</t>
         </is>
       </c>
       <c r="V167" s="2" t="inlineStr">
@@ -18690,7 +18696,7 @@
       <c r="T171" s="36" t="n"/>
       <c r="U171" s="40" t="inlineStr">
         <is>
-          <t>明星站</t>
+          <t>阿尔泰山</t>
         </is>
       </c>
       <c r="V171" s="2" t="inlineStr">
@@ -18790,10 +18796,10 @@
         </is>
       </c>
       <c r="O172" s="31" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="P172" s="31" t="n">
-        <v>14.6</v>
+        <v>11.3</v>
       </c>
       <c r="Q172" s="31" t="n"/>
       <c r="R172" s="50" t="n"/>
@@ -18805,7 +18811,7 @@
       <c r="T172" s="36" t="n"/>
       <c r="U172" s="40" t="inlineStr">
         <is>
-          <t>明星站</t>
+          <t>阿尔泰山</t>
         </is>
       </c>
       <c r="V172" s="2" t="inlineStr">
@@ -19119,10 +19125,10 @@
       </c>
       <c r="N175" s="2" t="n"/>
       <c r="O175" s="31" t="n">
-        <v>12.9</v>
+        <v>12.6</v>
       </c>
       <c r="P175" s="31" t="n">
-        <v>26.7</v>
+        <v>26.8</v>
       </c>
       <c r="Q175" s="31" t="n"/>
       <c r="R175" s="50" t="inlineStr">
@@ -19142,7 +19148,7 @@
       </c>
       <c r="U175" s="40" t="inlineStr">
         <is>
-          <t>明星站</t>
+          <t>河北围场</t>
         </is>
       </c>
       <c r="V175" s="2" t="inlineStr">
@@ -19448,13 +19454,13 @@
       </c>
       <c r="N178" s="2" t="n"/>
       <c r="O178" s="31" t="n">
-        <v>16.2</v>
+        <v>15.6</v>
       </c>
       <c r="P178" s="31" t="n">
-        <v>18.3</v>
+        <v>22.4</v>
       </c>
       <c r="Q178" s="31" t="n">
-        <v>17.12</v>
+        <v>18.93</v>
       </c>
       <c r="R178" s="50" t="n"/>
       <c r="S178" s="22" t="inlineStr">
@@ -19557,13 +19563,13 @@
         </is>
       </c>
       <c r="O179" s="31" t="n">
-        <v>10.5</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="P179" s="31" t="n">
-        <v>18</v>
+        <v>14.5</v>
       </c>
       <c r="Q179" s="31" t="n">
-        <v>13.45</v>
+        <v>11</v>
       </c>
       <c r="R179" s="50" t="n"/>
       <c r="S179" s="22" t="inlineStr">
@@ -19891,12 +19897,8 @@
         </is>
       </c>
       <c r="N182" s="2" t="n"/>
-      <c r="O182" s="31" t="n">
-        <v>10.1</v>
-      </c>
-      <c r="P182" s="31" t="n">
-        <v>18.6</v>
-      </c>
+      <c r="O182" s="31" t="n"/>
+      <c r="P182" s="31" t="n"/>
       <c r="Q182" s="31" t="n"/>
       <c r="R182" s="50" t="n"/>
       <c r="S182" s="22" t="inlineStr">
@@ -20370,7 +20372,7 @@
       <c r="T187" s="36" t="n"/>
       <c r="U187" s="40" t="inlineStr">
         <is>
-          <t>明星站</t>
+          <t>外兴安岭</t>
         </is>
       </c>
       <c r="V187" s="2" t="inlineStr">
@@ -20470,7 +20472,7 @@
       <c r="T188" s="36" t="n"/>
       <c r="U188" s="40" t="inlineStr">
         <is>
-          <t>明星站</t>
+          <t>奥伊米亚康</t>
         </is>
       </c>
       <c r="V188" s="2" t="inlineStr">
@@ -20853,11 +20855,7 @@
       <c r="R192" s="50" t="n"/>
       <c r="S192" s="22" t="n"/>
       <c r="T192" s="36" t="n"/>
-      <c r="U192" s="40" t="inlineStr">
-        <is>
-          <t>明星站</t>
-        </is>
-      </c>
+      <c r="U192" s="40" t="n"/>
       <c r="V192" s="2" t="inlineStr">
         <is>
           <t>萨哈</t>
@@ -21604,7 +21602,7 @@
       <c r="T200" s="36" t="n"/>
       <c r="U200" s="40" t="inlineStr">
         <is>
-          <t>黑龙江</t>
+          <t>黑龙江 大兴安岭</t>
         </is>
       </c>
       <c r="V200" s="2" t="inlineStr">
@@ -21707,7 +21705,7 @@
       <c r="T201" s="36" t="n"/>
       <c r="U201" s="40" t="inlineStr">
         <is>
-          <t>大兴安岭</t>
+          <t>黑龙江大兴安岭</t>
         </is>
       </c>
       <c r="V201" s="2" t="inlineStr">
@@ -21806,7 +21804,7 @@
       <c r="T202" s="36" t="n"/>
       <c r="U202" s="40" t="inlineStr">
         <is>
-          <t>大兴安岭&lt;br&gt;黑龙江</t>
+          <t>黑龙江 大兴安岭</t>
         </is>
       </c>
       <c r="V202" s="2" t="inlineStr">
@@ -21909,7 +21907,7 @@
       <c r="T203" s="36" t="n"/>
       <c r="U203" s="40" t="inlineStr">
         <is>
-          <t>大兴安岭</t>
+          <t>黑龙江大兴安岭</t>
         </is>
       </c>
       <c r="V203" s="2" t="inlineStr">
@@ -22012,7 +22010,7 @@
       <c r="T204" s="36" t="n"/>
       <c r="U204" s="40" t="inlineStr">
         <is>
-          <t>小兴安岭</t>
+          <t>黑龙江小兴安岭</t>
         </is>
       </c>
       <c r="V204" s="2" t="inlineStr">
@@ -22218,7 +22216,7 @@
       <c r="T206" s="36" t="n"/>
       <c r="U206" s="40" t="inlineStr">
         <is>
-          <t>大兴安岭</t>
+          <t>黑龙江大兴安岭</t>
         </is>
       </c>
       <c r="V206" s="2" t="inlineStr">
@@ -22321,7 +22319,7 @@
       <c r="T207" s="36" t="n"/>
       <c r="U207" s="40" t="inlineStr">
         <is>
-          <t>大兴安岭</t>
+          <t>黑龙江大兴安岭</t>
         </is>
       </c>
       <c r="V207" s="2" t="inlineStr">
@@ -22424,7 +22422,7 @@
       <c r="T208" s="36" t="n"/>
       <c r="U208" s="40" t="inlineStr">
         <is>
-          <t>大兴安岭</t>
+          <t>黑龙江大兴安岭</t>
         </is>
       </c>
       <c r="V208" s="2" t="inlineStr">
@@ -22527,7 +22525,7 @@
       <c r="T209" s="36" t="n"/>
       <c r="U209" s="40" t="inlineStr">
         <is>
-          <t>黑河</t>
+          <t>黑龙江黑河</t>
         </is>
       </c>
       <c r="V209" s="2" t="inlineStr">
@@ -22616,7 +22614,7 @@
       <c r="T210" s="36" t="n"/>
       <c r="U210" s="40" t="inlineStr">
         <is>
-          <t>黑河</t>
+          <t>黑龙江黑河</t>
         </is>
       </c>
       <c r="V210" s="2" t="inlineStr">
@@ -22818,7 +22816,7 @@
       <c r="T212" s="36" t="n"/>
       <c r="U212" s="40" t="inlineStr">
         <is>
-          <t>大兴安岭</t>
+          <t>黑龙江大兴安岭</t>
         </is>
       </c>
       <c r="V212" s="2" t="inlineStr">
@@ -22905,8 +22903,12 @@
         </is>
       </c>
       <c r="N213" s="2" t="n"/>
-      <c r="O213" s="31" t="n"/>
-      <c r="P213" s="31" t="n"/>
+      <c r="O213" s="31" t="n">
+        <v>5</v>
+      </c>
+      <c r="P213" s="31" t="n">
+        <v>21.1</v>
+      </c>
       <c r="Q213" s="31" t="n"/>
       <c r="R213" s="50" t="n"/>
       <c r="S213" s="22" t="inlineStr">
@@ -23111,12 +23113,8 @@
         </is>
       </c>
       <c r="N215" s="2" t="n"/>
-      <c r="O215" s="31" t="n">
-        <v>13</v>
-      </c>
-      <c r="P215" s="31" t="n">
-        <v>29.2</v>
-      </c>
+      <c r="O215" s="31" t="n"/>
+      <c r="P215" s="31" t="n"/>
       <c r="Q215" s="31" t="n"/>
       <c r="R215" s="50" t="n"/>
       <c r="S215" s="22" t="inlineStr">
@@ -23127,7 +23125,7 @@
       <c r="T215" s="36" t="n"/>
       <c r="U215" s="40" t="inlineStr">
         <is>
-          <t>明星站</t>
+          <t>根河</t>
         </is>
       </c>
       <c r="V215" s="2" t="inlineStr">
@@ -23333,7 +23331,7 @@
       <c r="T217" s="36" t="n"/>
       <c r="U217" s="40" t="inlineStr">
         <is>
-          <t>呼伦贝尔牙克石</t>
+          <t>牙克石</t>
         </is>
       </c>
       <c r="V217" s="2" t="inlineStr">
@@ -24028,7 +24026,7 @@
       <c r="T224" s="36" t="n"/>
       <c r="U224" s="40" t="inlineStr">
         <is>
-          <t>呼伦贝尔鄂伦春</t>
+          <t>鄂伦春自治旗</t>
         </is>
       </c>
       <c r="V224" s="2" t="inlineStr">
@@ -24543,7 +24541,7 @@
       <c r="T229" s="36" t="n"/>
       <c r="U229" s="40" t="inlineStr">
         <is>
-          <t>呼伦贝尔</t>
+          <t>陈巴尔虎旗</t>
         </is>
       </c>
       <c r="V229" s="2" t="inlineStr">
@@ -24650,7 +24648,7 @@
       <c r="T230" s="36" t="n"/>
       <c r="U230" s="40" t="inlineStr">
         <is>
-          <t>呼伦贝尔鄂伦春</t>
+          <t>鄂伦春</t>
         </is>
       </c>
       <c r="V230" s="2" t="inlineStr">
@@ -26594,7 +26592,7 @@
       <c r="T250" s="36" t="n"/>
       <c r="U250" s="40" t="inlineStr">
         <is>
-          <t>明星站</t>
+          <t>阿尔泰山</t>
         </is>
       </c>
       <c r="V250" s="2" t="inlineStr">
@@ -28262,10 +28260,10 @@
       </c>
       <c r="N267" s="2" t="n"/>
       <c r="O267" s="31" t="n">
-        <v>-79.8</v>
+        <v>-61</v>
       </c>
       <c r="P267" s="31" t="n">
-        <v>-77.2</v>
+        <v>-57.5</v>
       </c>
       <c r="Q267" s="31" t="n"/>
       <c r="R267" s="50" t="n"/>
@@ -28277,7 +28275,7 @@
       <c r="T267" s="36" t="n"/>
       <c r="U267" s="40" t="inlineStr">
         <is>
-          <t>明星站</t>
+          <t>南极&lt;br&gt;世界最低气温记录</t>
         </is>
       </c>
       <c r="V267" s="2" t="n"/>
@@ -28358,7 +28356,7 @@
       <c r="T268" s="36" t="n"/>
       <c r="U268" s="40" t="inlineStr">
         <is>
-          <t>呼伦贝尔</t>
+          <t>海拉尔</t>
         </is>
       </c>
       <c r="V268" s="2" t="inlineStr">
@@ -28538,7 +28536,7 @@
       <c r="T270" s="36" t="n"/>
       <c r="U270" s="40" t="inlineStr">
         <is>
-          <t>呼伦贝尔</t>
+          <t>海拉尔</t>
         </is>
       </c>
       <c r="V270" s="2" t="inlineStr">
@@ -29221,7 +29219,7 @@
       <c r="T277" s="36" t="n"/>
       <c r="U277" s="40" t="inlineStr">
         <is>
-          <t>呼伦贝尔</t>
+          <t>新巴尔虎左旗</t>
         </is>
       </c>
       <c r="V277" s="2" t="inlineStr">
@@ -29870,7 +29868,7 @@
       <c r="T284" s="36" t="n"/>
       <c r="U284" s="40" t="inlineStr">
         <is>
-          <t>呼伦贝尔</t>
+          <t>牙克石</t>
         </is>
       </c>
       <c r="V284" s="2" t="inlineStr">
@@ -29894,8 +29892,16 @@
         </is>
       </c>
       <c r="Z284" s="4" t="n"/>
-      <c r="AA284" s="2" t="n"/>
-      <c r="AB284" s="2" t="n"/>
+      <c r="AA284" s="2" t="inlineStr">
+        <is>
+          <t>呼伦贝尔市</t>
+        </is>
+      </c>
+      <c r="AB284" s="2" t="inlineStr">
+        <is>
+          <t>牙克石市</t>
+        </is>
+      </c>
       <c r="AC284" s="2" t="n"/>
       <c r="AD284" s="2" t="n"/>
       <c r="AE284" s="2" t="inlineStr">
@@ -30244,7 +30250,7 @@
       <c r="T288" s="36" t="n"/>
       <c r="U288" s="40" t="inlineStr">
         <is>
-          <t>呼伦贝尔</t>
+          <t>额尔古纳</t>
         </is>
       </c>
       <c r="V288" s="2" t="inlineStr">
@@ -30553,7 +30559,7 @@
       <c r="T291" s="36" t="n"/>
       <c r="U291" s="40" t="inlineStr">
         <is>
-          <t>呼伦贝尔</t>
+          <t>新巴尔虎右旗</t>
         </is>
       </c>
       <c r="V291" s="2" t="inlineStr">
@@ -30744,7 +30750,7 @@
       </c>
       <c r="N293" s="2" t="n"/>
       <c r="O293" s="31" t="n">
-        <v>-22.1</v>
+        <v>-19.2</v>
       </c>
       <c r="P293" s="31" t="n"/>
       <c r="Q293" s="31" t="n"/>
@@ -30848,7 +30854,7 @@
       <c r="T294" s="36" t="n"/>
       <c r="U294" s="40" t="inlineStr">
         <is>
-          <t>呼伦贝尔</t>
+          <t>鄂伦春自治旗</t>
         </is>
       </c>
       <c r="V294" s="2" t="inlineStr">
@@ -30947,7 +30953,7 @@
       <c r="T295" s="36" t="n"/>
       <c r="U295" s="40" t="inlineStr">
         <is>
-          <t>呼伦贝尔</t>
+          <t>鄂伦春自治旗</t>
         </is>
       </c>
       <c r="V295" s="2" t="inlineStr">
@@ -31144,13 +31150,13 @@
         </is>
       </c>
       <c r="O297" s="31" t="n">
-        <v>-0.6</v>
+        <v>-0.3</v>
       </c>
       <c r="P297" s="31" t="n">
-        <v>8.300000000000001</v>
+        <v>7</v>
       </c>
       <c r="Q297" s="31" t="n">
-        <v>2.4</v>
+        <v>1.3</v>
       </c>
       <c r="R297" s="50" t="n"/>
       <c r="S297" s="22" t="inlineStr">
@@ -33233,13 +33239,13 @@
       </c>
       <c r="N318" s="2" t="n"/>
       <c r="O318" s="31" t="n">
-        <v>24.3</v>
+        <v>25.4</v>
       </c>
       <c r="P318" s="31" t="n">
-        <v>42.3</v>
+        <v>43.7</v>
       </c>
       <c r="Q318" s="31" t="n">
-        <v>34.6</v>
+        <v>35.2</v>
       </c>
       <c r="R318" s="50" t="n"/>
       <c r="S318" s="22" t="inlineStr">
@@ -33529,7 +33535,7 @@
       <c r="T321" s="36" t="n"/>
       <c r="U321" s="40" t="inlineStr">
         <is>
-          <t>明星站</t>
+          <t>石勒喀河&lt;br&gt;外贝加尔</t>
         </is>
       </c>
       <c r="V321" s="2" t="inlineStr">
@@ -33626,7 +33632,7 @@
       <c r="T322" s="36" t="n"/>
       <c r="U322" s="40" t="inlineStr">
         <is>
-          <t>外贝加尔</t>
+          <t>石勒喀河支流&lt;br&gt;外贝加尔</t>
         </is>
       </c>
       <c r="V322" s="2" t="inlineStr">
@@ -33715,7 +33721,7 @@
       <c r="T323" s="36" t="n"/>
       <c r="U323" s="40" t="inlineStr">
         <is>
-          <t>明星站</t>
+          <t>谢列姆贾河&lt;br&gt;阿穆尔州</t>
         </is>
       </c>
       <c r="V323" s="2" t="inlineStr">
@@ -33893,7 +33899,7 @@
       <c r="T325" s="36" t="n"/>
       <c r="U325" s="40" t="inlineStr">
         <is>
-          <t>明星站</t>
+          <t>卡拉尔河 外兴安岭&lt;br&gt;外贝加尔</t>
         </is>
       </c>
       <c r="V325" s="2" t="inlineStr">

--- a/气象/For_Python_站点信息和记录.xlsx
+++ b/气象/For_Python_站点信息和记录.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\文档\GIT SYNC\default\气象\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D6493EF-DA75-41A0-BDA0-7F4666F2612A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA2C3DA3-B49E-45F7-8C43-B5420C3FE050}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4484" uniqueCount="1099">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4485" uniqueCount="1099">
   <si>
     <t>id</t>
   </si>
@@ -1942,6 +1942,9 @@
     <t>巴音郭楞乡</t>
   </si>
   <si>
+    <t>天山&lt;br&gt;巴音布鲁克</t>
+  </si>
+  <si>
     <t>B3521</t>
   </si>
   <si>
@@ -3291,9 +3294,6 @@
     <t>德尔比勒金牧场</t>
   </si>
   <si>
-    <t>天山&lt;br&gt;巴音布鲁克</t>
-  </si>
-  <si>
     <t>END</t>
   </si>
   <si>
@@ -3321,11 +3321,11 @@
     <t>特尼河试验站</t>
   </si>
   <si>
-    <t>扎布汗</t>
+    <t>44220</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>天山&lt;br&gt;巴音布鲁克</t>
+    <t>44222</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -4086,8 +4086,8 @@
     <col min="26" max="26" width="18.59765625" style="8" customWidth="1"/>
     <col min="27" max="31" width="12.59765625" style="5" customWidth="1"/>
     <col min="32" max="33" width="12.59765625" style="8" customWidth="1"/>
-    <col min="34" max="671" width="12.59765625" style="5" customWidth="1"/>
-    <col min="672" max="16384" width="12.59765625" style="5"/>
+    <col min="34" max="683" width="12.59765625" style="5" customWidth="1"/>
+    <col min="684" max="16384" width="12.59765625" style="5"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:35" s="11" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -4236,15 +4236,9 @@
       <c r="N2" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="O2" s="31">
-        <v>11.5</v>
-      </c>
-      <c r="P2" s="31">
-        <v>21.7</v>
-      </c>
-      <c r="Q2" s="31">
-        <v>14.92</v>
-      </c>
+      <c r="O2" s="31"/>
+      <c r="P2" s="31"/>
+      <c r="Q2" s="31"/>
       <c r="R2" s="50"/>
       <c r="S2" s="22" t="s">
         <v>39</v>
@@ -4317,12 +4311,8 @@
       <c r="N3" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="O3" s="31">
-        <v>10.3</v>
-      </c>
-      <c r="P3" s="31">
-        <v>20.8</v>
-      </c>
+      <c r="O3" s="31"/>
+      <c r="P3" s="31"/>
       <c r="Q3" s="31"/>
       <c r="R3" s="50" t="s">
         <v>47</v>
@@ -4398,12 +4388,8 @@
       <c r="N4" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="O4" s="31">
-        <v>10.9</v>
-      </c>
-      <c r="P4" s="31">
-        <v>19.399999999999999</v>
-      </c>
+      <c r="O4" s="31"/>
+      <c r="P4" s="31"/>
       <c r="Q4" s="31"/>
       <c r="R4" s="50" t="s">
         <v>51</v>
@@ -4548,15 +4534,9 @@
       <c r="N6" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="O6" s="31">
-        <v>8.6</v>
-      </c>
-      <c r="P6" s="31">
-        <v>18.8</v>
-      </c>
-      <c r="Q6" s="31">
-        <v>13.78</v>
-      </c>
+      <c r="O6" s="31"/>
+      <c r="P6" s="31"/>
+      <c r="Q6" s="31"/>
       <c r="R6" s="52" t="s">
         <v>59</v>
       </c>
@@ -4629,12 +4609,8 @@
       <c r="N7" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="O7" s="31">
-        <v>8.4</v>
-      </c>
-      <c r="P7" s="31">
-        <v>16.3</v>
-      </c>
+      <c r="O7" s="31"/>
+      <c r="P7" s="31"/>
       <c r="Q7" s="31"/>
       <c r="R7" s="50"/>
       <c r="S7" s="22"/>
@@ -4712,15 +4688,9 @@
         <v>67</v>
       </c>
       <c r="N8" s="2"/>
-      <c r="O8" s="31">
-        <v>12.3</v>
-      </c>
-      <c r="P8" s="31">
-        <v>28.1</v>
-      </c>
-      <c r="Q8" s="31">
-        <v>20.04</v>
-      </c>
+      <c r="O8" s="31"/>
+      <c r="P8" s="31"/>
+      <c r="Q8" s="31"/>
       <c r="R8" s="50"/>
       <c r="S8" s="22" t="s">
         <v>39</v>
@@ -4797,15 +4767,9 @@
         <v>72</v>
       </c>
       <c r="N9" s="2"/>
-      <c r="O9" s="31">
-        <v>9.6</v>
-      </c>
-      <c r="P9" s="31">
-        <v>21.7</v>
-      </c>
-      <c r="Q9" s="31">
-        <v>16.23</v>
-      </c>
+      <c r="O9" s="31"/>
+      <c r="P9" s="31"/>
+      <c r="Q9" s="31"/>
       <c r="R9" s="50"/>
       <c r="S9" s="22" t="s">
         <v>39</v>
@@ -4886,15 +4850,9 @@
       <c r="N10" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="O10" s="31">
-        <v>11.2</v>
-      </c>
-      <c r="P10" s="31">
-        <v>21.1</v>
-      </c>
-      <c r="Q10" s="31">
-        <v>13.01</v>
-      </c>
+      <c r="O10" s="31"/>
+      <c r="P10" s="31"/>
+      <c r="Q10" s="31"/>
       <c r="R10" s="50"/>
       <c r="S10" s="22" t="s">
         <v>39</v>
@@ -4973,15 +4931,9 @@
       <c r="N11" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="O11" s="31">
-        <v>6</v>
-      </c>
-      <c r="P11" s="31">
-        <v>17.399999999999999</v>
-      </c>
-      <c r="Q11" s="31">
-        <v>9.6</v>
-      </c>
+      <c r="O11" s="31"/>
+      <c r="P11" s="31"/>
+      <c r="Q11" s="31"/>
       <c r="R11" s="50" t="s">
         <v>77</v>
       </c>
@@ -4990,7 +4942,7 @@
       </c>
       <c r="T11" s="36"/>
       <c r="U11" s="40" t="s">
-        <v>1097</v>
+        <v>53</v>
       </c>
       <c r="V11" s="2" t="s">
         <v>53</v>
@@ -5060,15 +5012,9 @@
         <v>80</v>
       </c>
       <c r="N12" s="2"/>
-      <c r="O12" s="31">
-        <v>9.1999999999999993</v>
-      </c>
-      <c r="P12" s="31">
-        <v>22.3</v>
-      </c>
-      <c r="Q12" s="31">
-        <v>13.45</v>
-      </c>
+      <c r="O12" s="31"/>
+      <c r="P12" s="31"/>
+      <c r="Q12" s="31"/>
       <c r="R12" s="50" t="s">
         <v>81</v>
       </c>
@@ -5149,15 +5095,9 @@
       <c r="N13" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="O13" s="31">
-        <v>5.9</v>
-      </c>
-      <c r="P13" s="31">
-        <v>20.8</v>
-      </c>
-      <c r="Q13" s="31">
-        <v>11.03</v>
-      </c>
+      <c r="O13" s="31"/>
+      <c r="P13" s="31"/>
+      <c r="Q13" s="31"/>
       <c r="R13" s="50" t="s">
         <v>84</v>
       </c>
@@ -5236,15 +5176,9 @@
         <v>86</v>
       </c>
       <c r="N14" s="2"/>
-      <c r="O14" s="31">
-        <v>13</v>
-      </c>
-      <c r="P14" s="31">
-        <v>24.8</v>
-      </c>
-      <c r="Q14" s="31">
-        <v>17.82</v>
-      </c>
+      <c r="O14" s="31"/>
+      <c r="P14" s="31"/>
+      <c r="Q14" s="31"/>
       <c r="R14" s="50"/>
       <c r="S14" s="22" t="s">
         <v>39</v>
@@ -5325,15 +5259,9 @@
         <v>91</v>
       </c>
       <c r="N15" s="2"/>
-      <c r="O15" s="31">
-        <v>3.6</v>
-      </c>
-      <c r="P15" s="31">
-        <v>22.4</v>
-      </c>
-      <c r="Q15" s="31">
-        <v>12.74</v>
-      </c>
+      <c r="O15" s="31"/>
+      <c r="P15" s="31"/>
+      <c r="Q15" s="31"/>
       <c r="R15" s="50"/>
       <c r="S15" s="22" t="s">
         <v>39</v>
@@ -5481,7 +5409,9 @@
       <c r="N17" s="23" t="s">
         <v>97</v>
       </c>
-      <c r="O17" s="31"/>
+      <c r="O17" s="31">
+        <v>-5.6</v>
+      </c>
       <c r="P17" s="31"/>
       <c r="Q17" s="31"/>
       <c r="R17" s="50"/>
@@ -6743,7 +6673,9 @@
         <v>34</v>
       </c>
       <c r="B35" s="2"/>
-      <c r="C35" s="45"/>
+      <c r="C35" s="45" t="s">
+        <v>1098</v>
+      </c>
       <c r="D35" s="2"/>
       <c r="E35" s="4"/>
       <c r="F35" s="38">
@@ -7952,12 +7884,8 @@
         <v>157</v>
       </c>
       <c r="N52" s="2"/>
-      <c r="O52" s="31">
-        <v>3.1</v>
-      </c>
-      <c r="P52" s="31">
-        <v>18.899999999999999</v>
-      </c>
+      <c r="O52" s="31"/>
+      <c r="P52" s="31"/>
       <c r="Q52" s="31"/>
       <c r="R52" s="50"/>
       <c r="S52" s="22"/>
@@ -8068,7 +7996,9 @@
         <v>53</v>
       </c>
       <c r="B54" s="2"/>
-      <c r="C54" s="45"/>
+      <c r="C54" s="45" t="s">
+        <v>1097</v>
+      </c>
       <c r="D54" s="2"/>
       <c r="E54" s="4"/>
       <c r="F54" s="38">
@@ -9563,19 +9493,11 @@
         <v>193</v>
       </c>
       <c r="N75" s="2"/>
-      <c r="O75" s="31">
-        <v>17.399999999999999</v>
-      </c>
-      <c r="P75" s="31">
-        <v>30.3</v>
-      </c>
-      <c r="Q75" s="31">
-        <v>24.01</v>
-      </c>
+      <c r="O75" s="31"/>
+      <c r="P75" s="31"/>
+      <c r="Q75" s="31"/>
       <c r="R75" s="50"/>
-      <c r="S75" s="22" t="s">
-        <v>39</v>
-      </c>
+      <c r="S75" s="22"/>
       <c r="T75" s="36"/>
       <c r="U75" s="40" t="s">
         <v>98</v>
@@ -9802,15 +9724,9 @@
       <c r="N78" s="23" t="s">
         <v>97</v>
       </c>
-      <c r="O78" s="31">
-        <v>7.4</v>
-      </c>
-      <c r="P78" s="31">
-        <v>20</v>
-      </c>
-      <c r="Q78" s="31">
-        <v>13.74</v>
-      </c>
+      <c r="O78" s="31"/>
+      <c r="P78" s="31"/>
+      <c r="Q78" s="31"/>
       <c r="R78" s="50" t="s">
         <v>208</v>
       </c>
@@ -10124,15 +10040,9 @@
       <c r="N82" s="3" t="s">
         <v>223</v>
       </c>
-      <c r="O82" s="31">
-        <v>8.6999999999999993</v>
-      </c>
-      <c r="P82" s="31">
-        <v>22.4</v>
-      </c>
-      <c r="Q82" s="31">
-        <v>15.36</v>
-      </c>
+      <c r="O82" s="31"/>
+      <c r="P82" s="31"/>
+      <c r="Q82" s="31"/>
       <c r="R82" s="50"/>
       <c r="S82" s="22" t="s">
         <v>39</v>
@@ -10213,15 +10123,9 @@
       <c r="N83" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="O83" s="31">
-        <v>6.8</v>
-      </c>
-      <c r="P83" s="31">
-        <v>21.8</v>
-      </c>
-      <c r="Q83" s="31">
-        <v>13.61</v>
-      </c>
+      <c r="O83" s="31"/>
+      <c r="P83" s="31"/>
+      <c r="Q83" s="31"/>
       <c r="R83" s="50"/>
       <c r="S83" s="22" t="s">
         <v>39</v>
@@ -10377,15 +10281,9 @@
       <c r="N85" s="23" t="s">
         <v>236</v>
       </c>
-      <c r="O85" s="31">
-        <v>10.6</v>
-      </c>
-      <c r="P85" s="31">
-        <v>25.9</v>
-      </c>
-      <c r="Q85" s="31">
-        <v>17.43</v>
-      </c>
+      <c r="O85" s="31"/>
+      <c r="P85" s="31"/>
+      <c r="Q85" s="31"/>
       <c r="R85" s="50"/>
       <c r="S85" s="22" t="s">
         <v>39</v>
@@ -10541,15 +10439,9 @@
         <v>245</v>
       </c>
       <c r="N87" s="2"/>
-      <c r="O87" s="31">
-        <v>13</v>
-      </c>
-      <c r="P87" s="31">
-        <v>20</v>
-      </c>
-      <c r="Q87" s="31">
-        <v>15.34</v>
-      </c>
+      <c r="O87" s="31"/>
+      <c r="P87" s="31"/>
+      <c r="Q87" s="31"/>
       <c r="R87" s="50"/>
       <c r="S87" s="22" t="s">
         <v>39</v>
@@ -10709,15 +10601,9 @@
         <v>252</v>
       </c>
       <c r="N89" s="2"/>
-      <c r="O89" s="31">
-        <v>4.8</v>
-      </c>
-      <c r="P89" s="31">
-        <v>14.8</v>
-      </c>
-      <c r="Q89" s="31">
-        <v>9.17</v>
-      </c>
+      <c r="O89" s="31"/>
+      <c r="P89" s="31"/>
+      <c r="Q89" s="31"/>
       <c r="R89" s="50" t="s">
         <v>253</v>
       </c>
@@ -11025,15 +10911,9 @@
         <v>273</v>
       </c>
       <c r="N93" s="2"/>
-      <c r="O93" s="31">
-        <v>10.9</v>
-      </c>
-      <c r="P93" s="31">
-        <v>25.2</v>
-      </c>
-      <c r="Q93" s="31">
-        <v>17.690000000000001</v>
-      </c>
+      <c r="O93" s="31"/>
+      <c r="P93" s="31"/>
+      <c r="Q93" s="31"/>
       <c r="R93" s="50"/>
       <c r="S93" s="22" t="s">
         <v>39</v>
@@ -11110,15 +10990,9 @@
         <v>280</v>
       </c>
       <c r="N94" s="2"/>
-      <c r="O94" s="31">
-        <v>21.9</v>
-      </c>
-      <c r="P94" s="31">
-        <v>32.799999999999997</v>
-      </c>
-      <c r="Q94" s="31">
-        <v>26.24</v>
-      </c>
+      <c r="O94" s="31"/>
+      <c r="P94" s="31"/>
+      <c r="Q94" s="31"/>
       <c r="R94" s="50"/>
       <c r="S94" s="22" t="s">
         <v>39</v>
@@ -11282,15 +11156,9 @@
         <v>293</v>
       </c>
       <c r="N96" s="2"/>
-      <c r="O96" s="31">
-        <v>21.1</v>
-      </c>
-      <c r="P96" s="31">
-        <v>29.1</v>
-      </c>
-      <c r="Q96" s="31">
-        <v>25.17</v>
-      </c>
+      <c r="O96" s="31"/>
+      <c r="P96" s="31"/>
+      <c r="Q96" s="31"/>
       <c r="R96" s="50"/>
       <c r="S96" s="22" t="s">
         <v>39</v>
@@ -11458,15 +11326,9 @@
         <v>307</v>
       </c>
       <c r="N98" s="2"/>
-      <c r="O98" s="31">
-        <v>20.2</v>
-      </c>
-      <c r="P98" s="31">
-        <v>28.9</v>
-      </c>
-      <c r="Q98" s="31">
-        <v>23.29</v>
-      </c>
+      <c r="O98" s="31"/>
+      <c r="P98" s="31"/>
+      <c r="Q98" s="31"/>
       <c r="R98" s="50"/>
       <c r="S98" s="22" t="s">
         <v>39</v>
@@ -11869,15 +11731,9 @@
         <v>330</v>
       </c>
       <c r="N103" s="2"/>
-      <c r="O103" s="31">
-        <v>6.5</v>
-      </c>
-      <c r="P103" s="31">
-        <v>23.1</v>
-      </c>
-      <c r="Q103" s="31">
-        <v>13.61</v>
-      </c>
+      <c r="O103" s="31"/>
+      <c r="P103" s="31"/>
+      <c r="Q103" s="31"/>
       <c r="R103" s="50"/>
       <c r="S103" s="22" t="s">
         <v>39</v>
@@ -12118,15 +11974,9 @@
       <c r="N106" s="2" t="s">
         <v>223</v>
       </c>
-      <c r="O106" s="31">
-        <v>4.8</v>
-      </c>
-      <c r="P106" s="31">
-        <v>17.8</v>
-      </c>
-      <c r="Q106" s="31">
-        <v>11.29</v>
-      </c>
+      <c r="O106" s="31"/>
+      <c r="P106" s="31"/>
+      <c r="Q106" s="31"/>
       <c r="R106" s="50"/>
       <c r="S106" s="22" t="s">
         <v>39</v>
@@ -12746,15 +12596,9 @@
         <v>363</v>
       </c>
       <c r="N114" s="2"/>
-      <c r="O114" s="31">
-        <v>5</v>
-      </c>
-      <c r="P114" s="31">
-        <v>13.5</v>
-      </c>
-      <c r="Q114" s="31">
-        <v>8.75</v>
-      </c>
+      <c r="O114" s="31"/>
+      <c r="P114" s="31"/>
+      <c r="Q114" s="31"/>
       <c r="R114" s="50"/>
       <c r="S114" s="22" t="s">
         <v>39</v>
@@ -12833,15 +12677,9 @@
       <c r="N115" s="23" t="s">
         <v>97</v>
       </c>
-      <c r="O115" s="31">
-        <v>6.2</v>
-      </c>
-      <c r="P115" s="31">
-        <v>10.1</v>
-      </c>
-      <c r="Q115" s="31">
-        <v>8.14</v>
-      </c>
+      <c r="O115" s="31"/>
+      <c r="P115" s="31"/>
+      <c r="Q115" s="31"/>
       <c r="R115" s="50"/>
       <c r="S115" s="22" t="s">
         <v>39</v>
@@ -12924,15 +12762,9 @@
       <c r="N116" s="23" t="s">
         <v>97</v>
       </c>
-      <c r="O116" s="31">
-        <v>1.7</v>
-      </c>
-      <c r="P116" s="31">
-        <v>11.3</v>
-      </c>
-      <c r="Q116" s="31">
-        <v>5.26</v>
-      </c>
+      <c r="O116" s="31"/>
+      <c r="P116" s="31"/>
+      <c r="Q116" s="31"/>
       <c r="R116" s="50"/>
       <c r="S116" s="22" t="s">
         <v>39</v>
@@ -13337,15 +13169,9 @@
         <v>397</v>
       </c>
       <c r="N121" s="2"/>
-      <c r="O121" s="31">
-        <v>26.8</v>
-      </c>
-      <c r="P121" s="31">
-        <v>39</v>
-      </c>
-      <c r="Q121" s="31">
-        <v>33.380000000000003</v>
-      </c>
+      <c r="O121" s="31"/>
+      <c r="P121" s="31"/>
+      <c r="Q121" s="31"/>
       <c r="R121" s="50"/>
       <c r="S121" s="22" t="s">
         <v>39</v>
@@ -13424,15 +13250,9 @@
         <v>402</v>
       </c>
       <c r="N122" s="2"/>
-      <c r="O122" s="31">
-        <v>15.7</v>
-      </c>
-      <c r="P122" s="31">
-        <v>27.9</v>
-      </c>
-      <c r="Q122" s="31">
-        <v>21.19</v>
-      </c>
+      <c r="O122" s="31"/>
+      <c r="P122" s="31"/>
+      <c r="Q122" s="31"/>
       <c r="R122" s="50"/>
       <c r="S122" s="22" t="s">
         <v>39</v>
@@ -13515,15 +13335,9 @@
         <v>406</v>
       </c>
       <c r="N123" s="2"/>
-      <c r="O123" s="31">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="P123" s="31">
-        <v>19.5</v>
-      </c>
-      <c r="Q123" s="31">
-        <v>10.24</v>
-      </c>
+      <c r="O123" s="31"/>
+      <c r="P123" s="31"/>
+      <c r="Q123" s="31"/>
       <c r="R123" s="50"/>
       <c r="S123" s="22" t="s">
         <v>39</v>
@@ -13681,15 +13495,9 @@
         <v>414</v>
       </c>
       <c r="N125" s="2"/>
-      <c r="O125" s="31">
-        <v>15.3</v>
-      </c>
-      <c r="P125" s="31">
-        <v>23.5</v>
-      </c>
-      <c r="Q125" s="31">
-        <v>18.850000000000001</v>
-      </c>
+      <c r="O125" s="31"/>
+      <c r="P125" s="31"/>
+      <c r="Q125" s="31"/>
       <c r="R125" s="50"/>
       <c r="S125" s="22" t="s">
         <v>39</v>
@@ -13772,15 +13580,9 @@
         <v>419</v>
       </c>
       <c r="N126" s="2"/>
-      <c r="O126" s="31">
-        <v>23.9</v>
-      </c>
-      <c r="P126" s="31">
-        <v>30.7</v>
-      </c>
-      <c r="Q126" s="31">
-        <v>26.96</v>
-      </c>
+      <c r="O126" s="31"/>
+      <c r="P126" s="31"/>
+      <c r="Q126" s="31"/>
       <c r="R126" s="50"/>
       <c r="S126" s="22" t="s">
         <v>39</v>
@@ -13853,15 +13655,9 @@
         <v>422</v>
       </c>
       <c r="N127" s="2"/>
-      <c r="O127" s="31">
-        <v>25.5</v>
-      </c>
-      <c r="P127" s="31">
-        <v>32.6</v>
-      </c>
-      <c r="Q127" s="31">
-        <v>28.81</v>
-      </c>
+      <c r="O127" s="31"/>
+      <c r="P127" s="31"/>
+      <c r="Q127" s="31"/>
       <c r="R127" s="50"/>
       <c r="S127" s="22" t="s">
         <v>39</v>
@@ -13938,15 +13734,9 @@
         <v>428</v>
       </c>
       <c r="N128" s="2"/>
-      <c r="O128" s="31">
-        <v>22.5</v>
-      </c>
-      <c r="P128" s="31">
-        <v>31.1</v>
-      </c>
-      <c r="Q128" s="31">
-        <v>26.23</v>
-      </c>
+      <c r="O128" s="31"/>
+      <c r="P128" s="31"/>
+      <c r="Q128" s="31"/>
       <c r="R128" s="50"/>
       <c r="S128" s="22" t="s">
         <v>39</v>
@@ -14027,15 +13817,9 @@
         <v>434</v>
       </c>
       <c r="N129" s="2"/>
-      <c r="O129" s="31">
-        <v>25</v>
-      </c>
-      <c r="P129" s="31">
-        <v>33.799999999999997</v>
-      </c>
-      <c r="Q129" s="31">
-        <v>29.09</v>
-      </c>
+      <c r="O129" s="31"/>
+      <c r="P129" s="31"/>
+      <c r="Q129" s="31"/>
       <c r="R129" s="50"/>
       <c r="S129" s="22" t="s">
         <v>39</v>
@@ -14112,15 +13896,9 @@
         <v>438</v>
       </c>
       <c r="N130" s="2"/>
-      <c r="O130" s="31">
-        <v>20.2</v>
-      </c>
-      <c r="P130" s="31">
-        <v>32.1</v>
-      </c>
-      <c r="Q130" s="31">
-        <v>25.74</v>
-      </c>
+      <c r="O130" s="31"/>
+      <c r="P130" s="31"/>
+      <c r="Q130" s="31"/>
       <c r="R130" s="50"/>
       <c r="S130" s="22" t="s">
         <v>39</v>
@@ -14201,15 +13979,9 @@
         <v>444</v>
       </c>
       <c r="N131" s="2"/>
-      <c r="O131" s="31">
-        <v>12.3</v>
-      </c>
-      <c r="P131" s="31">
-        <v>22.5</v>
-      </c>
-      <c r="Q131" s="31">
-        <v>15.98</v>
-      </c>
+      <c r="O131" s="31"/>
+      <c r="P131" s="31"/>
+      <c r="Q131" s="31"/>
       <c r="R131" s="50"/>
       <c r="S131" s="22" t="s">
         <v>39</v>
@@ -14290,15 +14062,9 @@
         <v>449</v>
       </c>
       <c r="N132" s="2"/>
-      <c r="O132" s="31">
-        <v>24</v>
-      </c>
-      <c r="P132" s="31">
-        <v>33.1</v>
-      </c>
-      <c r="Q132" s="31">
-        <v>28.72</v>
-      </c>
+      <c r="O132" s="31"/>
+      <c r="P132" s="31"/>
+      <c r="Q132" s="31"/>
       <c r="R132" s="50"/>
       <c r="S132" s="22" t="s">
         <v>39</v>
@@ -14377,15 +14143,9 @@
         <v>455</v>
       </c>
       <c r="N133" s="2"/>
-      <c r="O133" s="31">
-        <v>26.1</v>
-      </c>
-      <c r="P133" s="31">
-        <v>34.4</v>
-      </c>
-      <c r="Q133" s="31">
-        <v>30.15</v>
-      </c>
+      <c r="O133" s="31"/>
+      <c r="P133" s="31"/>
+      <c r="Q133" s="31"/>
       <c r="R133" s="50"/>
       <c r="S133" s="22" t="s">
         <v>39</v>
@@ -14464,15 +14224,9 @@
         <v>461</v>
       </c>
       <c r="N134" s="2"/>
-      <c r="O134" s="31">
-        <v>25.5</v>
-      </c>
-      <c r="P134" s="31">
-        <v>33.6</v>
-      </c>
-      <c r="Q134" s="31">
-        <v>29.43</v>
-      </c>
+      <c r="O134" s="31"/>
+      <c r="P134" s="31"/>
+      <c r="Q134" s="31"/>
       <c r="R134" s="50"/>
       <c r="S134" s="22" t="s">
         <v>39</v>
@@ -14630,15 +14384,9 @@
         <v>473</v>
       </c>
       <c r="N136" s="2"/>
-      <c r="O136" s="31">
-        <v>27.5</v>
-      </c>
-      <c r="P136" s="31">
-        <v>33.700000000000003</v>
-      </c>
-      <c r="Q136" s="31">
-        <v>29.46</v>
-      </c>
+      <c r="O136" s="31"/>
+      <c r="P136" s="31"/>
+      <c r="Q136" s="31"/>
       <c r="R136" s="50"/>
       <c r="S136" s="22" t="s">
         <v>39</v>
@@ -14717,15 +14465,9 @@
         <v>479</v>
       </c>
       <c r="N137" s="2"/>
-      <c r="O137" s="31">
-        <v>28.5</v>
-      </c>
-      <c r="P137" s="31">
-        <v>33.700000000000003</v>
-      </c>
-      <c r="Q137" s="31">
-        <v>31.05</v>
-      </c>
+      <c r="O137" s="31"/>
+      <c r="P137" s="31"/>
+      <c r="Q137" s="31"/>
       <c r="R137" s="50"/>
       <c r="S137" s="22" t="s">
         <v>39</v>
@@ -14804,15 +14546,9 @@
         <v>485</v>
       </c>
       <c r="N138" s="2"/>
-      <c r="O138" s="31">
-        <v>28.2</v>
-      </c>
-      <c r="P138" s="31">
-        <v>35.6</v>
-      </c>
-      <c r="Q138" s="31">
-        <v>31.38</v>
-      </c>
+      <c r="O138" s="31"/>
+      <c r="P138" s="31"/>
+      <c r="Q138" s="31"/>
       <c r="R138" s="50"/>
       <c r="S138" s="22" t="s">
         <v>39</v>
@@ -14891,15 +14627,9 @@
         <v>492</v>
       </c>
       <c r="N139" s="2"/>
-      <c r="O139" s="31">
-        <v>26.2</v>
-      </c>
-      <c r="P139" s="31">
-        <v>32.799999999999997</v>
-      </c>
-      <c r="Q139" s="31">
-        <v>28.99</v>
-      </c>
+      <c r="O139" s="31"/>
+      <c r="P139" s="31"/>
+      <c r="Q139" s="31"/>
       <c r="R139" s="50"/>
       <c r="S139" s="22" t="s">
         <v>39</v>
@@ -14978,15 +14708,9 @@
         <v>498</v>
       </c>
       <c r="N140" s="2"/>
-      <c r="O140" s="31">
-        <v>27.1</v>
-      </c>
-      <c r="P140" s="31">
-        <v>33.200000000000003</v>
-      </c>
-      <c r="Q140" s="31">
-        <v>29.51</v>
-      </c>
+      <c r="O140" s="31"/>
+      <c r="P140" s="31"/>
+      <c r="Q140" s="31"/>
       <c r="R140" s="50"/>
       <c r="S140" s="22" t="s">
         <v>39</v>
@@ -15065,15 +14789,9 @@
         <v>503</v>
       </c>
       <c r="N141" s="2"/>
-      <c r="O141" s="31">
-        <v>25.9</v>
-      </c>
-      <c r="P141" s="31">
-        <v>33</v>
-      </c>
-      <c r="Q141" s="31">
-        <v>28.82</v>
-      </c>
+      <c r="O141" s="31"/>
+      <c r="P141" s="31"/>
+      <c r="Q141" s="31"/>
       <c r="R141" s="50"/>
       <c r="S141" s="22" t="s">
         <v>39</v>
@@ -15229,15 +14947,9 @@
         <v>514</v>
       </c>
       <c r="N143" s="2"/>
-      <c r="O143" s="31">
-        <v>25.9</v>
-      </c>
-      <c r="P143" s="31">
-        <v>34.200000000000003</v>
-      </c>
-      <c r="Q143" s="31">
-        <v>29.54</v>
-      </c>
+      <c r="O143" s="31"/>
+      <c r="P143" s="31"/>
+      <c r="Q143" s="31"/>
       <c r="R143" s="50"/>
       <c r="S143" s="22" t="s">
         <v>39</v>
@@ -15316,15 +15028,9 @@
         <v>520</v>
       </c>
       <c r="N144" s="2"/>
-      <c r="O144" s="31">
-        <v>26.3</v>
-      </c>
-      <c r="P144" s="31">
-        <v>32.6</v>
-      </c>
-      <c r="Q144" s="31">
-        <v>29</v>
-      </c>
+      <c r="O144" s="31"/>
+      <c r="P144" s="31"/>
+      <c r="Q144" s="31"/>
       <c r="R144" s="50"/>
       <c r="S144" s="22" t="s">
         <v>39</v>
@@ -15555,15 +15261,9 @@
         <v>535</v>
       </c>
       <c r="N147" s="2"/>
-      <c r="O147" s="31">
-        <v>27.2</v>
-      </c>
-      <c r="P147" s="31">
-        <v>29.9</v>
-      </c>
-      <c r="Q147" s="31">
-        <v>28.75</v>
-      </c>
+      <c r="O147" s="31"/>
+      <c r="P147" s="31"/>
+      <c r="Q147" s="31"/>
       <c r="R147" s="50"/>
       <c r="S147" s="22" t="s">
         <v>39</v>
@@ -15638,15 +15338,9 @@
         <v>538</v>
       </c>
       <c r="N148" s="2"/>
-      <c r="O148" s="31">
-        <v>25.5</v>
-      </c>
-      <c r="P148" s="31">
-        <v>30</v>
-      </c>
-      <c r="Q148" s="31">
-        <v>27.38</v>
-      </c>
+      <c r="O148" s="31"/>
+      <c r="P148" s="31"/>
+      <c r="Q148" s="31"/>
       <c r="R148" s="50"/>
       <c r="S148" s="22" t="s">
         <v>39</v>
@@ -15725,15 +15419,9 @@
         <v>544</v>
       </c>
       <c r="N149" s="2"/>
-      <c r="O149" s="31">
-        <v>25.8</v>
-      </c>
-      <c r="P149" s="31">
-        <v>32.799999999999997</v>
-      </c>
-      <c r="Q149" s="31">
-        <v>28.57</v>
-      </c>
+      <c r="O149" s="31"/>
+      <c r="P149" s="31"/>
+      <c r="Q149" s="31"/>
       <c r="R149" s="50"/>
       <c r="S149" s="22" t="s">
         <v>39</v>
@@ -15810,15 +15498,9 @@
         <v>549</v>
       </c>
       <c r="N150" s="2"/>
-      <c r="O150" s="31">
-        <v>17.8</v>
-      </c>
-      <c r="P150" s="31">
-        <v>25.7</v>
-      </c>
-      <c r="Q150" s="31">
-        <v>19.940000000000001</v>
-      </c>
+      <c r="O150" s="31"/>
+      <c r="P150" s="31"/>
+      <c r="Q150" s="31"/>
       <c r="R150" s="50"/>
       <c r="S150" s="22" t="s">
         <v>39</v>
@@ -15897,15 +15579,9 @@
         <v>554</v>
       </c>
       <c r="N151" s="2"/>
-      <c r="O151" s="31">
-        <v>20.9</v>
-      </c>
-      <c r="P151" s="31">
-        <v>31.4</v>
-      </c>
-      <c r="Q151" s="31">
-        <v>25.52</v>
-      </c>
+      <c r="O151" s="31"/>
+      <c r="P151" s="31"/>
+      <c r="Q151" s="31"/>
       <c r="R151" s="50"/>
       <c r="S151" s="22" t="s">
         <v>39</v>
@@ -15984,15 +15660,9 @@
         <v>560</v>
       </c>
       <c r="N152" s="2"/>
-      <c r="O152" s="31">
-        <v>26.9</v>
-      </c>
-      <c r="P152" s="31">
-        <v>38.6</v>
-      </c>
-      <c r="Q152" s="31">
-        <v>31.64</v>
-      </c>
+      <c r="O152" s="31"/>
+      <c r="P152" s="31"/>
+      <c r="Q152" s="31"/>
       <c r="R152" s="50"/>
       <c r="S152" s="22" t="s">
         <v>39</v>
@@ -16142,15 +15812,9 @@
         <v>570</v>
       </c>
       <c r="N154" s="2"/>
-      <c r="O154" s="31">
-        <v>22.8</v>
-      </c>
-      <c r="P154" s="31">
-        <v>30.7</v>
-      </c>
-      <c r="Q154" s="31">
-        <v>26.49</v>
-      </c>
+      <c r="O154" s="31"/>
+      <c r="P154" s="31"/>
+      <c r="Q154" s="31"/>
       <c r="R154" s="50"/>
       <c r="S154" s="22" t="s">
         <v>39</v>
@@ -16231,15 +15895,9 @@
         <v>577</v>
       </c>
       <c r="N155" s="2"/>
-      <c r="O155" s="31">
-        <v>12.8</v>
-      </c>
-      <c r="P155" s="31">
-        <v>22.4</v>
-      </c>
-      <c r="Q155" s="31">
-        <v>16.16</v>
-      </c>
+      <c r="O155" s="31"/>
+      <c r="P155" s="31"/>
+      <c r="Q155" s="31"/>
       <c r="R155" s="50"/>
       <c r="S155" s="22" t="s">
         <v>39</v>
@@ -16462,15 +16120,9 @@
         <v>587</v>
       </c>
       <c r="N158" s="2"/>
-      <c r="O158" s="31">
-        <v>27</v>
-      </c>
-      <c r="P158" s="31">
-        <v>31.2</v>
-      </c>
-      <c r="Q158" s="31">
-        <v>28.62</v>
-      </c>
+      <c r="O158" s="31"/>
+      <c r="P158" s="31"/>
+      <c r="Q158" s="31"/>
       <c r="R158" s="50"/>
       <c r="S158" s="22" t="s">
         <v>39</v>
@@ -16764,15 +16416,9 @@
         <v>602</v>
       </c>
       <c r="N162" s="2"/>
-      <c r="O162" s="31">
-        <v>21.2</v>
-      </c>
-      <c r="P162" s="31">
-        <v>30.3</v>
-      </c>
-      <c r="Q162" s="31">
-        <v>25.34</v>
-      </c>
+      <c r="O162" s="31"/>
+      <c r="P162" s="31"/>
+      <c r="Q162" s="31"/>
       <c r="R162" s="50"/>
       <c r="S162" s="22" t="s">
         <v>39</v>
@@ -16928,12 +16574,8 @@
       <c r="N164" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="O164" s="31">
-        <v>2.7</v>
-      </c>
-      <c r="P164" s="31">
-        <v>21.9</v>
-      </c>
+      <c r="O164" s="31"/>
+      <c r="P164" s="31"/>
       <c r="Q164" s="31"/>
       <c r="R164" s="50"/>
       <c r="S164" s="22" t="s">
@@ -17558,12 +17200,8 @@
       <c r="N172" s="3" t="s">
         <v>633</v>
       </c>
-      <c r="O172" s="31">
-        <v>2.2000000000000002</v>
-      </c>
-      <c r="P172" s="31">
-        <v>9.4</v>
-      </c>
+      <c r="O172" s="31"/>
+      <c r="P172" s="31"/>
       <c r="Q172" s="31"/>
       <c r="R172" s="50"/>
       <c r="S172" s="22" t="s">
@@ -17641,15 +17279,9 @@
       <c r="N173" s="23" t="s">
         <v>97</v>
       </c>
-      <c r="O173" s="31">
-        <v>-2.1</v>
-      </c>
-      <c r="P173" s="31">
-        <v>3.5</v>
-      </c>
-      <c r="Q173" s="31">
-        <v>0.2</v>
-      </c>
+      <c r="O173" s="31"/>
+      <c r="P173" s="31"/>
+      <c r="Q173" s="31"/>
       <c r="R173" s="50"/>
       <c r="S173" s="22" t="s">
         <v>39</v>
@@ -17724,12 +17356,8 @@
         <v>637</v>
       </c>
       <c r="N174" s="3"/>
-      <c r="O174" s="31">
-        <v>-2.6</v>
-      </c>
-      <c r="P174" s="31">
-        <v>19.600000000000001</v>
-      </c>
+      <c r="O174" s="31"/>
+      <c r="P174" s="31"/>
       <c r="Q174" s="31"/>
       <c r="R174" s="50"/>
       <c r="S174" s="22" t="s">
@@ -17737,7 +17365,7 @@
       </c>
       <c r="T174" s="36"/>
       <c r="U174" s="40" t="s">
-        <v>1098</v>
+        <v>638</v>
       </c>
       <c r="V174" s="2" t="s">
         <v>383</v>
@@ -17783,7 +17411,7 @@
       <c r="D175" s="2"/>
       <c r="E175" s="4"/>
       <c r="F175" s="38" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="G175" s="28">
         <v>42.410299999999999</v>
@@ -17802,18 +17430,14 @@
       </c>
       <c r="L175" s="3"/>
       <c r="M175" s="14" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="N175" s="2"/>
-      <c r="O175" s="31">
-        <v>13.6</v>
-      </c>
-      <c r="P175" s="31">
-        <v>23.1</v>
-      </c>
+      <c r="O175" s="31"/>
+      <c r="P175" s="31"/>
       <c r="Q175" s="31"/>
       <c r="R175" s="50" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="S175" s="22" t="s">
         <v>39</v>
@@ -17822,7 +17446,7 @@
         <v>39</v>
       </c>
       <c r="U175" s="40" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="V175" s="2" t="s">
         <v>360</v>
@@ -17838,10 +17462,10 @@
       </c>
       <c r="Z175" s="4"/>
       <c r="AA175" s="2" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="AB175" s="2" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="AC175" s="2"/>
       <c r="AD175" s="2"/>
@@ -17885,7 +17509,7 @@
       </c>
       <c r="L176" s="3"/>
       <c r="M176" s="14" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="N176" s="2"/>
       <c r="O176" s="31"/>
@@ -17913,10 +17537,10 @@
       </c>
       <c r="Z176" s="4"/>
       <c r="AA176" s="2" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="AB176" s="2" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="AC176" s="2"/>
       <c r="AD176" s="2"/>
@@ -17928,7 +17552,7 @@
       </c>
       <c r="AG176" s="4"/>
       <c r="AH176" s="2" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="AI176" s="2" t="s">
         <v>609</v>
@@ -17943,7 +17567,7 @@
       <c r="D177" s="2"/>
       <c r="E177" s="4"/>
       <c r="F177" s="38" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="G177" s="28">
         <v>33.0672</v>
@@ -17962,7 +17586,7 @@
       </c>
       <c r="L177" s="3"/>
       <c r="M177" s="14" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="N177" s="2"/>
       <c r="O177" s="31"/>
@@ -17974,7 +17598,7 @@
       </c>
       <c r="T177" s="36"/>
       <c r="U177" s="40" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="V177" s="2" t="s">
         <v>566</v>
@@ -17990,10 +17614,10 @@
       </c>
       <c r="Z177" s="4"/>
       <c r="AA177" s="2" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="AB177" s="2" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="AC177" s="2"/>
       <c r="AD177" s="2"/>
@@ -18020,7 +17644,7 @@
         <v>58437</v>
       </c>
       <c r="D178" s="2" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="E178" s="4">
         <v>99999</v>
@@ -18043,18 +17667,12 @@
       </c>
       <c r="L178" s="3"/>
       <c r="M178" s="12" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="N178" s="2"/>
-      <c r="O178" s="31">
-        <v>16.399999999999999</v>
-      </c>
-      <c r="P178" s="31">
-        <v>21.6</v>
-      </c>
-      <c r="Q178" s="31">
-        <v>18.68</v>
-      </c>
+      <c r="O178" s="31"/>
+      <c r="P178" s="31"/>
+      <c r="Q178" s="31"/>
       <c r="R178" s="50"/>
       <c r="S178" s="22" t="s">
         <v>39</v>
@@ -18075,10 +17693,10 @@
       </c>
       <c r="Z178" s="4"/>
       <c r="AA178" s="2" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="AB178" s="2" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="AC178" s="2"/>
       <c r="AD178" s="2"/>
@@ -18124,20 +17742,14 @@
       </c>
       <c r="L179" s="3"/>
       <c r="M179" s="14" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="N179" s="23" t="s">
         <v>97</v>
       </c>
-      <c r="O179" s="31">
-        <v>9.4</v>
-      </c>
-      <c r="P179" s="31">
-        <v>15</v>
-      </c>
-      <c r="Q179" s="31">
-        <v>11.09</v>
-      </c>
+      <c r="O179" s="31"/>
+      <c r="P179" s="31"/>
+      <c r="Q179" s="31"/>
       <c r="R179" s="50"/>
       <c r="S179" s="22" t="s">
         <v>39</v>
@@ -18162,10 +17774,10 @@
       </c>
       <c r="Z179" s="4"/>
       <c r="AA179" s="2" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="AB179" s="2" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="AC179" s="2"/>
       <c r="AD179" s="2"/>
@@ -18192,7 +17804,7 @@
       <c r="D180" s="2"/>
       <c r="E180" s="4"/>
       <c r="F180" s="38" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="G180" s="28">
         <v>48.721699999999998</v>
@@ -18211,7 +17823,7 @@
       </c>
       <c r="L180" s="3"/>
       <c r="M180" s="14" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="N180" s="2"/>
       <c r="O180" s="31"/>
@@ -18292,7 +17904,7 @@
       </c>
       <c r="L181" s="3"/>
       <c r="M181" s="14" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="N181" s="2"/>
       <c r="O181" s="31"/>
@@ -18320,10 +17932,10 @@
       </c>
       <c r="Z181" s="4"/>
       <c r="AA181" s="2" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="AB181" s="2" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="AC181" s="2"/>
       <c r="AD181" s="2"/>
@@ -18350,7 +17962,7 @@
       <c r="D182" s="2"/>
       <c r="E182" s="4"/>
       <c r="F182" s="38" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="G182" s="28">
         <v>33.043300000000002</v>
@@ -18369,15 +17981,11 @@
       </c>
       <c r="L182" s="3"/>
       <c r="M182" s="14" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="N182" s="2"/>
-      <c r="O182" s="31">
-        <v>7.8</v>
-      </c>
-      <c r="P182" s="31">
-        <v>23.3</v>
-      </c>
+      <c r="O182" s="31"/>
+      <c r="P182" s="31"/>
       <c r="Q182" s="31"/>
       <c r="R182" s="50"/>
       <c r="S182" s="22" t="s">
@@ -18399,10 +18007,10 @@
       </c>
       <c r="Z182" s="4"/>
       <c r="AA182" s="2" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="AB182" s="2" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="AC182" s="2"/>
       <c r="AD182" s="2"/>
@@ -18429,7 +18037,7 @@
       <c r="D183" s="2"/>
       <c r="E183" s="4"/>
       <c r="F183" s="38" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="G183" s="28">
         <v>29.041899999999998</v>
@@ -18448,7 +18056,7 @@
       </c>
       <c r="L183" s="3"/>
       <c r="M183" s="14" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="N183" s="2"/>
       <c r="O183" s="31"/>
@@ -18474,10 +18082,10 @@
       </c>
       <c r="Z183" s="4"/>
       <c r="AA183" s="2" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="AB183" s="2" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="AC183" s="2"/>
       <c r="AD183" s="2"/>
@@ -18502,7 +18110,7 @@
         <v>58968</v>
       </c>
       <c r="D184" s="2" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="E184" s="4">
         <v>99999</v>
@@ -18525,7 +18133,7 @@
       </c>
       <c r="L184" s="3"/>
       <c r="M184" s="14" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="N184" s="2"/>
       <c r="O184" s="31"/>
@@ -18535,10 +18143,10 @@
       <c r="S184" s="22"/>
       <c r="T184" s="36"/>
       <c r="U184" s="40" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="V184" s="2" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="W184" s="4"/>
       <c r="X184" s="4" t="s">
@@ -18571,7 +18179,7 @@
         <v>45007</v>
       </c>
       <c r="D185" s="2" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="E185" s="4">
         <v>99999</v>
@@ -18594,7 +18202,7 @@
       </c>
       <c r="L185" s="3"/>
       <c r="M185" s="14" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="N185" s="2"/>
       <c r="O185" s="31"/>
@@ -18605,7 +18213,7 @@
       <c r="T185" s="36"/>
       <c r="U185" s="40"/>
       <c r="V185" s="2" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="W185" s="4"/>
       <c r="X185" s="4" t="s">
@@ -18638,7 +18246,7 @@
         <v>45011</v>
       </c>
       <c r="D186" s="2" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="E186" s="4">
         <v>99999</v>
@@ -18661,20 +18269,20 @@
       </c>
       <c r="L186" s="3"/>
       <c r="M186" s="14" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="N186" s="2"/>
       <c r="O186" s="31"/>
       <c r="P186" s="31"/>
       <c r="Q186" s="31"/>
       <c r="R186" s="50" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="S186" s="22"/>
       <c r="T186" s="36"/>
       <c r="U186" s="40"/>
       <c r="V186" s="2" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="W186" s="4"/>
       <c r="X186" s="4" t="s">
@@ -18709,7 +18317,7 @@
         <v>31137</v>
       </c>
       <c r="D187" s="2" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="E187" s="4">
         <v>99999</v>
@@ -18732,7 +18340,7 @@
       </c>
       <c r="L187" s="3"/>
       <c r="M187" s="12" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="N187" s="2"/>
       <c r="O187" s="31"/>
@@ -18742,10 +18350,10 @@
       <c r="S187" s="22"/>
       <c r="T187" s="36"/>
       <c r="U187" s="40" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="V187" s="2" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="W187" s="4" t="s">
         <v>39</v>
@@ -18763,14 +18371,14 @@
         <v>199</v>
       </c>
       <c r="AF187" s="4" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="AG187" s="4"/>
       <c r="AH187" s="2" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="AI187" s="6" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
     </row>
     <row r="188" spans="1:35" ht="24" customHeight="1" x14ac:dyDescent="0.4">
@@ -18784,7 +18392,7 @@
         <v>24688</v>
       </c>
       <c r="D188" s="2" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="E188" s="4">
         <v>99999</v>
@@ -18807,7 +18415,7 @@
       </c>
       <c r="L188" s="3"/>
       <c r="M188" s="16" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="N188" s="2"/>
       <c r="O188" s="31"/>
@@ -18817,10 +18425,10 @@
       <c r="S188" s="22"/>
       <c r="T188" s="36"/>
       <c r="U188" s="40" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="V188" s="2" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="W188" s="4" t="s">
         <v>39</v>
@@ -18838,14 +18446,14 @@
         <v>199</v>
       </c>
       <c r="AF188" s="4" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="AG188" s="4"/>
       <c r="AH188" s="2" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="AI188" s="6" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
     </row>
     <row r="189" spans="1:35" ht="24" customHeight="1" x14ac:dyDescent="0.4">
@@ -18859,7 +18467,7 @@
         <v>24585</v>
       </c>
       <c r="D189" s="2" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="E189" s="4">
         <v>99999</v>
@@ -18882,7 +18490,7 @@
       </c>
       <c r="L189" s="3"/>
       <c r="M189" s="16" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="N189" s="2"/>
       <c r="O189" s="31"/>
@@ -18892,10 +18500,10 @@
       <c r="S189" s="22"/>
       <c r="T189" s="36"/>
       <c r="U189" s="40" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="V189" s="2" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="W189" s="4" t="s">
         <v>39</v>
@@ -18913,11 +18521,11 @@
         <v>199</v>
       </c>
       <c r="AF189" s="4" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="AG189" s="4"/>
       <c r="AH189" s="2" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="AI189" s="2"/>
     </row>
@@ -18932,7 +18540,7 @@
         <v>24588</v>
       </c>
       <c r="D190" s="2" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="E190" s="4">
         <v>99999</v>
@@ -18955,7 +18563,7 @@
       </c>
       <c r="L190" s="3"/>
       <c r="M190" s="16" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="N190" s="2"/>
       <c r="O190" s="31"/>
@@ -18965,10 +18573,10 @@
       <c r="S190" s="22"/>
       <c r="T190" s="36"/>
       <c r="U190" s="40" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="V190" s="2" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="W190" s="4" t="s">
         <v>39</v>
@@ -18986,11 +18594,11 @@
         <v>199</v>
       </c>
       <c r="AF190" s="4" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="AG190" s="4"/>
       <c r="AH190" s="2" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="AI190" s="2"/>
     </row>
@@ -19005,7 +18613,7 @@
         <v>24691</v>
       </c>
       <c r="D191" s="2" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="E191" s="4">
         <v>99999</v>
@@ -19028,7 +18636,7 @@
       </c>
       <c r="L191" s="3"/>
       <c r="M191" s="16" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="N191" s="2"/>
       <c r="O191" s="31"/>
@@ -19038,10 +18646,10 @@
       <c r="S191" s="22"/>
       <c r="T191" s="36"/>
       <c r="U191" s="40" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="V191" s="2" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="W191" s="4" t="s">
         <v>39</v>
@@ -19059,11 +18667,11 @@
         <v>199</v>
       </c>
       <c r="AF191" s="4" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="AG191" s="4"/>
       <c r="AH191" s="2" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="AI191" s="2"/>
     </row>
@@ -19078,7 +18686,7 @@
         <v>24266</v>
       </c>
       <c r="D192" s="2" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="E192" s="4">
         <v>99999</v>
@@ -19101,7 +18709,7 @@
       </c>
       <c r="L192" s="3"/>
       <c r="M192" s="16" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="N192" s="2"/>
       <c r="O192" s="31"/>
@@ -19112,7 +18720,7 @@
       <c r="T192" s="36"/>
       <c r="U192" s="40"/>
       <c r="V192" s="2" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="W192" s="4" t="s">
         <v>39</v>
@@ -19130,11 +18738,11 @@
         <v>199</v>
       </c>
       <c r="AF192" s="4" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="AG192" s="4"/>
       <c r="AH192" s="2" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="AI192" s="2"/>
     </row>
@@ -19149,7 +18757,7 @@
         <v>24684</v>
       </c>
       <c r="D193" s="2" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="E193" s="4">
         <v>99999</v>
@@ -19172,7 +18780,7 @@
       </c>
       <c r="L193" s="3"/>
       <c r="M193" s="16" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="N193" s="2"/>
       <c r="O193" s="31"/>
@@ -19182,10 +18790,10 @@
       <c r="S193" s="22"/>
       <c r="T193" s="36"/>
       <c r="U193" s="40" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="V193" s="2" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="W193" s="4" t="s">
         <v>39</v>
@@ -19203,7 +18811,7 @@
         <v>199</v>
       </c>
       <c r="AF193" s="4" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="AG193" s="4"/>
       <c r="AH193" s="2"/>
@@ -19220,7 +18828,7 @@
         <v>24382</v>
       </c>
       <c r="D194" s="2" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="E194" s="4">
         <v>99999</v>
@@ -19243,7 +18851,7 @@
       </c>
       <c r="L194" s="3"/>
       <c r="M194" s="16" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="N194" s="2"/>
       <c r="O194" s="31"/>
@@ -19253,10 +18861,10 @@
       <c r="S194" s="22"/>
       <c r="T194" s="36"/>
       <c r="U194" s="40" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="V194" s="2" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="W194" s="4" t="s">
         <v>39</v>
@@ -19274,11 +18882,11 @@
         <v>199</v>
       </c>
       <c r="AF194" s="4" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="AG194" s="4"/>
       <c r="AH194" s="6" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="AI194" s="2"/>
     </row>
@@ -19293,7 +18901,7 @@
         <v>24959</v>
       </c>
       <c r="D195" s="2" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="E195" s="4">
         <v>99999</v>
@@ -19316,7 +18924,7 @@
       </c>
       <c r="L195" s="3"/>
       <c r="M195" s="16" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="N195" s="2"/>
       <c r="O195" s="31"/>
@@ -19326,10 +18934,10 @@
       <c r="S195" s="22"/>
       <c r="T195" s="36"/>
       <c r="U195" s="40" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="V195" s="2" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="W195" s="4" t="s">
         <v>39</v>
@@ -19349,11 +18957,11 @@
         <v>199</v>
       </c>
       <c r="AF195" s="4" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="AG195" s="4"/>
       <c r="AH195" s="2" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="AI195" s="2"/>
     </row>
@@ -19368,7 +18976,7 @@
         <v>24477</v>
       </c>
       <c r="D196" s="2" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="E196" s="4">
         <v>99999</v>
@@ -19391,7 +18999,7 @@
       </c>
       <c r="L196" s="3"/>
       <c r="M196" s="12" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="N196" s="2"/>
       <c r="O196" s="31"/>
@@ -19401,10 +19009,10 @@
       <c r="S196" s="22"/>
       <c r="T196" s="36"/>
       <c r="U196" s="40" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="V196" s="2" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="W196" s="4" t="s">
         <v>39</v>
@@ -19422,7 +19030,7 @@
         <v>199</v>
       </c>
       <c r="AF196" s="4" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="AG196" s="4"/>
       <c r="AH196" s="2"/>
@@ -19439,7 +19047,7 @@
         <v>25428</v>
       </c>
       <c r="D197" s="2" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="E197" s="4">
         <v>99999</v>
@@ -19462,7 +19070,7 @@
       </c>
       <c r="L197" s="3"/>
       <c r="M197" s="16" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="N197" s="2"/>
       <c r="O197" s="31"/>
@@ -19472,10 +19080,10 @@
       <c r="S197" s="22"/>
       <c r="T197" s="36"/>
       <c r="U197" s="40" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="V197" s="2" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="W197" s="4" t="s">
         <v>39</v>
@@ -19493,11 +19101,11 @@
         <v>199</v>
       </c>
       <c r="AF197" s="4" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="AG197" s="4"/>
       <c r="AH197" s="2" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="AI197" s="2"/>
     </row>
@@ -19512,7 +19120,7 @@
         <v>25700</v>
       </c>
       <c r="D198" s="2" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="E198" s="4">
         <v>99999</v>
@@ -19535,7 +19143,7 @@
       </c>
       <c r="L198" s="3"/>
       <c r="M198" s="16" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="N198" s="2"/>
       <c r="O198" s="31"/>
@@ -19545,10 +19153,10 @@
       <c r="S198" s="22"/>
       <c r="T198" s="36"/>
       <c r="U198" s="40" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="V198" s="2" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="W198" s="4" t="s">
         <v>39</v>
@@ -19566,7 +19174,7 @@
         <v>199</v>
       </c>
       <c r="AF198" s="4" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="AG198" s="4"/>
       <c r="AH198" s="2"/>
@@ -19583,7 +19191,7 @@
         <v>24507</v>
       </c>
       <c r="D199" s="2" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="E199" s="4">
         <v>99999</v>
@@ -19606,7 +19214,7 @@
       </c>
       <c r="L199" s="3"/>
       <c r="M199" s="16" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="N199" s="23"/>
       <c r="O199" s="31"/>
@@ -19616,10 +19224,10 @@
       <c r="S199" s="22"/>
       <c r="T199" s="36"/>
       <c r="U199" s="40" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="V199" s="2" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="W199" s="4" t="s">
         <v>39</v>
@@ -19637,11 +19245,11 @@
         <v>199</v>
       </c>
       <c r="AF199" s="4" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="AG199" s="4"/>
       <c r="AH199" s="2" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="AI199" s="2"/>
     </row>
@@ -19654,7 +19262,7 @@
       <c r="D200" s="2"/>
       <c r="E200" s="4"/>
       <c r="F200" s="38" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="G200" s="28">
         <v>53.491900000000001</v>
@@ -19673,7 +19281,7 @@
       </c>
       <c r="L200" s="3"/>
       <c r="M200" s="14" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="N200" s="2"/>
       <c r="O200" s="31"/>
@@ -19716,7 +19324,7 @@
       </c>
       <c r="AG200" s="4"/>
       <c r="AH200" s="2" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="AI200" s="2"/>
     </row>
@@ -19750,7 +19358,7 @@
       </c>
       <c r="L201" s="3"/>
       <c r="M201" s="14" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="N201" s="2"/>
       <c r="O201" s="31"/>
@@ -19825,7 +19433,7 @@
       </c>
       <c r="L202" s="3"/>
       <c r="M202" s="14" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="N202" s="2"/>
       <c r="O202" s="31"/>
@@ -19868,7 +19476,7 @@
       </c>
       <c r="AG202" s="4"/>
       <c r="AH202" s="2" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="AI202" s="2"/>
     </row>
@@ -19881,7 +19489,7 @@
       <c r="D203" s="2"/>
       <c r="E203" s="4"/>
       <c r="F203" s="38" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="G203" s="28">
         <v>52.758600000000001</v>
@@ -19900,7 +19508,7 @@
       </c>
       <c r="L203" s="3"/>
       <c r="M203" s="14" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="N203" s="2"/>
       <c r="O203" s="31"/>
@@ -19977,7 +19585,7 @@
       </c>
       <c r="L204" s="3"/>
       <c r="M204" s="14" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="N204" s="2"/>
       <c r="O204" s="31"/>
@@ -19989,7 +19597,7 @@
       </c>
       <c r="T204" s="36"/>
       <c r="U204" s="40" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="V204" s="2" t="s">
         <v>309</v>
@@ -20008,7 +19616,7 @@
         <v>314</v>
       </c>
       <c r="AB204" s="2" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="AC204" s="2"/>
       <c r="AD204" s="2"/>
@@ -20020,7 +19628,7 @@
       </c>
       <c r="AG204" s="4"/>
       <c r="AH204" s="2" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="AI204" s="2"/>
     </row>
@@ -20054,7 +19662,7 @@
       </c>
       <c r="L205" s="3"/>
       <c r="M205" s="14" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="N205" s="2"/>
       <c r="O205" s="31"/>
@@ -20066,7 +19674,7 @@
       </c>
       <c r="T205" s="36"/>
       <c r="U205" s="40" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="V205" s="2" t="s">
         <v>309</v>
@@ -20082,10 +19690,10 @@
       </c>
       <c r="Z205" s="4"/>
       <c r="AA205" s="2" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="AB205" s="2" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="AC205" s="2"/>
       <c r="AD205" s="2"/>
@@ -20097,7 +19705,7 @@
       </c>
       <c r="AG205" s="4"/>
       <c r="AH205" s="2" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="AI205" s="2"/>
     </row>
@@ -20110,7 +19718,7 @@
       <c r="D206" s="2"/>
       <c r="E206" s="4"/>
       <c r="F206" s="38" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="G206" s="28">
         <v>51.7881</v>
@@ -20129,7 +19737,7 @@
       </c>
       <c r="L206" s="3"/>
       <c r="M206" s="14" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="N206" s="2"/>
       <c r="O206" s="31"/>
@@ -20160,7 +19768,7 @@
         <v>320</v>
       </c>
       <c r="AB206" s="2" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="AC206" s="2"/>
       <c r="AD206" s="2"/>
@@ -20185,7 +19793,7 @@
       <c r="D207" s="2"/>
       <c r="E207" s="4"/>
       <c r="F207" s="38" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="G207" s="28">
         <v>52.875599999999999</v>
@@ -20204,7 +19812,7 @@
       </c>
       <c r="L207" s="3"/>
       <c r="M207" s="14" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="N207" s="2"/>
       <c r="O207" s="31"/>
@@ -20260,7 +19868,7 @@
       <c r="D208" s="2"/>
       <c r="E208" s="4"/>
       <c r="F208" s="38" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="G208" s="28">
         <v>50.928600000000003</v>
@@ -20279,7 +19887,7 @@
       </c>
       <c r="L208" s="3"/>
       <c r="M208" s="14" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="N208" s="2"/>
       <c r="O208" s="31"/>
@@ -20310,7 +19918,7 @@
         <v>320</v>
       </c>
       <c r="AB208" s="2" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="AC208" s="2"/>
       <c r="AD208" s="2"/>
@@ -20335,7 +19943,7 @@
       <c r="D209" s="2"/>
       <c r="E209" s="4"/>
       <c r="F209" s="38" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="G209" s="28">
         <v>50.508600000000001</v>
@@ -20354,7 +19962,7 @@
       </c>
       <c r="L209" s="3"/>
       <c r="M209" s="14" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="N209" s="2"/>
       <c r="O209" s="31"/>
@@ -20366,7 +19974,7 @@
       </c>
       <c r="T209" s="36"/>
       <c r="U209" s="40" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="V209" s="2" t="s">
         <v>309</v>
@@ -20382,10 +19990,10 @@
       </c>
       <c r="Z209" s="4"/>
       <c r="AA209" s="2" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="AB209" s="2" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="AC209" s="2"/>
       <c r="AD209" s="2"/>
@@ -20419,7 +20027,7 @@
       </c>
       <c r="L210" s="3"/>
       <c r="M210" s="14" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="N210" s="2"/>
       <c r="O210" s="31"/>
@@ -20431,7 +20039,7 @@
       </c>
       <c r="T210" s="36"/>
       <c r="U210" s="40" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="V210" s="2" t="s">
         <v>309</v>
@@ -20447,10 +20055,10 @@
       </c>
       <c r="Z210" s="4"/>
       <c r="AA210" s="2" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="AB210" s="2" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="AC210" s="2"/>
       <c r="AD210" s="2"/>
@@ -20462,7 +20070,7 @@
       </c>
       <c r="AG210" s="4"/>
       <c r="AH210" s="2" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="AI210" s="2"/>
     </row>
@@ -20496,7 +20104,7 @@
       </c>
       <c r="L211" s="3"/>
       <c r="M211" s="14" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="N211" s="2"/>
       <c r="O211" s="31"/>
@@ -20525,11 +20133,11 @@
         <v>310</v>
       </c>
       <c r="AB211" s="2" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="AC211" s="2"/>
       <c r="AD211" s="2" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="AE211" s="2" t="s">
         <v>284</v>
@@ -20571,7 +20179,7 @@
       </c>
       <c r="L212" s="3"/>
       <c r="M212" s="14" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="N212" s="2"/>
       <c r="O212" s="31"/>
@@ -20625,7 +20233,7 @@
       <c r="D213" s="2"/>
       <c r="E213" s="4"/>
       <c r="F213" s="38" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="G213" s="28">
         <v>50.875300000000003</v>
@@ -20644,7 +20252,7 @@
       </c>
       <c r="L213" s="3"/>
       <c r="M213" s="14" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="N213" s="2"/>
       <c r="O213" s="31"/>
@@ -20700,7 +20308,7 @@
       <c r="D214" s="2"/>
       <c r="E214" s="4"/>
       <c r="F214" s="38" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="G214" s="28">
         <v>50.698099999999997</v>
@@ -20719,7 +20327,7 @@
       </c>
       <c r="L214" s="3"/>
       <c r="M214" s="14" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="N214" s="2"/>
       <c r="O214" s="31"/>
@@ -20775,7 +20383,7 @@
       <c r="D215" s="2"/>
       <c r="E215" s="4"/>
       <c r="F215" s="38" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="G215" s="28">
         <v>51.150799999999997</v>
@@ -20794,15 +20402,11 @@
       </c>
       <c r="L215" s="3"/>
       <c r="M215" s="14" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="N215" s="2"/>
-      <c r="O215" s="31">
-        <v>3.6</v>
-      </c>
-      <c r="P215" s="31">
-        <v>21.1</v>
-      </c>
+      <c r="O215" s="31"/>
+      <c r="P215" s="31"/>
       <c r="Q215" s="31"/>
       <c r="R215" s="50"/>
       <c r="S215" s="22" t="s">
@@ -20854,7 +20458,7 @@
       <c r="D216" s="2"/>
       <c r="E216" s="4"/>
       <c r="F216" s="38" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="G216" s="28">
         <v>50.44</v>
@@ -20873,7 +20477,7 @@
       </c>
       <c r="L216" s="3"/>
       <c r="M216" s="14" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="N216" s="2"/>
       <c r="O216" s="31"/>
@@ -20929,7 +20533,7 @@
       <c r="D217" s="2"/>
       <c r="E217" s="4"/>
       <c r="F217" s="38" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="G217" s="28">
         <v>50.637799999999999</v>
@@ -20948,7 +20552,7 @@
       </c>
       <c r="L217" s="3"/>
       <c r="M217" s="14" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="N217" s="2"/>
       <c r="O217" s="31"/>
@@ -21004,7 +20608,7 @@
       <c r="D218" s="2"/>
       <c r="E218" s="4"/>
       <c r="F218" s="38" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="G218" s="28">
         <v>50.581899999999997</v>
@@ -21023,7 +20627,7 @@
       </c>
       <c r="L218" s="3"/>
       <c r="M218" s="14" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="N218" s="2"/>
       <c r="O218" s="31"/>
@@ -21090,7 +20694,7 @@
       </c>
       <c r="L219" s="3"/>
       <c r="M219" s="14" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="N219" s="2"/>
       <c r="O219" s="31"/>
@@ -21144,7 +20748,7 @@
       <c r="D220" s="2"/>
       <c r="E220" s="4"/>
       <c r="F220" s="38" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="G220" s="28">
         <v>50.467199999999998</v>
@@ -21163,7 +20767,7 @@
       </c>
       <c r="L220" s="3"/>
       <c r="M220" s="14" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="N220" s="2"/>
       <c r="O220" s="31"/>
@@ -21240,7 +20844,7 @@
       </c>
       <c r="L221" s="3"/>
       <c r="M221" s="14" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="N221" s="2"/>
       <c r="O221" s="31"/>
@@ -21271,7 +20875,7 @@
         <v>338</v>
       </c>
       <c r="AB221" s="2" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="AC221" s="2"/>
       <c r="AD221" s="2"/>
@@ -21296,7 +20900,7 @@
       <c r="D222" s="2"/>
       <c r="E222" s="4"/>
       <c r="F222" s="38" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="G222" s="28">
         <v>50.46</v>
@@ -21315,7 +20919,7 @@
       </c>
       <c r="L222" s="3"/>
       <c r="M222" s="14" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="N222" s="2"/>
       <c r="O222" s="31"/>
@@ -21382,7 +20986,7 @@
       </c>
       <c r="L223" s="3"/>
       <c r="M223" s="14" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="N223" s="2"/>
       <c r="O223" s="31"/>
@@ -21438,7 +21042,7 @@
       <c r="D224" s="2"/>
       <c r="E224" s="4"/>
       <c r="F224" s="38" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="G224" s="28">
         <v>49.32</v>
@@ -21455,7 +21059,7 @@
       </c>
       <c r="L224" s="3"/>
       <c r="M224" s="14" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="N224" s="2"/>
       <c r="O224" s="31"/>
@@ -21467,7 +21071,7 @@
       </c>
       <c r="T224" s="36"/>
       <c r="U224" s="40" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="V224" s="2" t="s">
         <v>337</v>
@@ -21486,7 +21090,7 @@
         <v>338</v>
       </c>
       <c r="AB224" s="2" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="AC224" s="2"/>
       <c r="AD224" s="2"/>
@@ -21511,7 +21115,7 @@
       <c r="D225" s="2"/>
       <c r="E225" s="4"/>
       <c r="F225" s="38" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="G225" s="28">
         <v>52.041899999999998</v>
@@ -21530,7 +21134,7 @@
       </c>
       <c r="L225" s="3"/>
       <c r="M225" s="14" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="N225" s="2"/>
       <c r="O225" s="31"/>
@@ -21586,7 +21190,7 @@
       <c r="D226" s="2"/>
       <c r="E226" s="4"/>
       <c r="F226" s="38" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="G226" s="28">
         <v>52.22</v>
@@ -21605,7 +21209,7 @@
       </c>
       <c r="L226" s="3"/>
       <c r="M226" s="14" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="N226" s="2"/>
       <c r="O226" s="31"/>
@@ -21682,7 +21286,7 @@
       </c>
       <c r="L227" s="3"/>
       <c r="M227" s="14" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="N227" s="2"/>
       <c r="O227" s="31"/>
@@ -21713,7 +21317,7 @@
         <v>338</v>
       </c>
       <c r="AB227" s="2" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="AC227" s="2"/>
       <c r="AD227" s="2"/>
@@ -21740,7 +21344,7 @@
         <v>53083</v>
       </c>
       <c r="D228" s="2" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="E228" s="4">
         <v>99999</v>
@@ -21763,7 +21367,7 @@
       </c>
       <c r="L228" s="3"/>
       <c r="M228" s="14" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="N228" s="2"/>
       <c r="O228" s="31"/>
@@ -21773,7 +21377,7 @@
       <c r="S228" s="22"/>
       <c r="T228" s="36"/>
       <c r="U228" s="40" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="V228" s="2" t="s">
         <v>337</v>
@@ -21789,10 +21393,10 @@
       </c>
       <c r="Z228" s="4"/>
       <c r="AA228" s="2" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="AB228" s="2" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="AC228" s="2"/>
       <c r="AD228" s="2"/>
@@ -21815,7 +21419,7 @@
       <c r="D229" s="2"/>
       <c r="E229" s="4"/>
       <c r="F229" s="38" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="G229" s="28">
         <v>49.888100000000001</v>
@@ -21834,7 +21438,7 @@
       </c>
       <c r="L229" s="3"/>
       <c r="M229" s="14" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="N229" s="2"/>
       <c r="O229" s="31"/>
@@ -21892,7 +21496,7 @@
         <v>50548</v>
       </c>
       <c r="D230" s="2" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="E230" s="4">
         <v>99999</v>
@@ -21915,7 +21519,7 @@
       </c>
       <c r="L230" s="3"/>
       <c r="M230" s="14" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="N230" s="2"/>
       <c r="O230" s="31"/>
@@ -21925,7 +21529,7 @@
       <c r="S230" s="22"/>
       <c r="T230" s="36"/>
       <c r="U230" s="40" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="V230" s="2" t="s">
         <v>337</v>
@@ -21944,7 +21548,7 @@
         <v>338</v>
       </c>
       <c r="AB230" s="2" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="AC230" s="2"/>
       <c r="AD230" s="2"/>
@@ -21969,7 +21573,7 @@
       <c r="D231" s="2"/>
       <c r="E231" s="4"/>
       <c r="F231" s="38" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="G231" s="28"/>
       <c r="H231" s="28"/>
@@ -21982,7 +21586,7 @@
       </c>
       <c r="L231" s="3"/>
       <c r="M231" s="14" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="N231" s="2"/>
       <c r="O231" s="31"/>
@@ -22038,7 +21642,7 @@
       <c r="D232" s="2"/>
       <c r="E232" s="4"/>
       <c r="F232" s="38" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="G232" s="28"/>
       <c r="H232" s="28"/>
@@ -22051,7 +21655,7 @@
       </c>
       <c r="L232" s="3"/>
       <c r="M232" s="14" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="N232" s="2"/>
       <c r="O232" s="31"/>
@@ -22063,7 +21667,7 @@
       </c>
       <c r="T232" s="36"/>
       <c r="U232" s="40" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="V232" s="2" t="s">
         <v>337</v>
@@ -22118,7 +21722,7 @@
       </c>
       <c r="L233" s="3"/>
       <c r="M233" s="14" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="N233" s="2"/>
       <c r="O233" s="31"/>
@@ -22183,7 +21787,7 @@
       </c>
       <c r="L234" s="3"/>
       <c r="M234" s="14" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="N234" s="2"/>
       <c r="O234" s="31"/>
@@ -22250,7 +21854,7 @@
       </c>
       <c r="L235" s="3"/>
       <c r="M235" s="14" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="N235" s="2"/>
       <c r="O235" s="31"/>
@@ -22306,7 +21910,7 @@
       <c r="D236" s="2"/>
       <c r="E236" s="4"/>
       <c r="F236" s="38" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="G236" s="28"/>
       <c r="H236" s="28"/>
@@ -22319,7 +21923,7 @@
       </c>
       <c r="L236" s="2"/>
       <c r="M236" s="14" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="N236" s="2"/>
       <c r="O236" s="31"/>
@@ -22375,7 +21979,7 @@
       <c r="D237" s="2"/>
       <c r="E237" s="4"/>
       <c r="F237" s="38" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="G237" s="28"/>
       <c r="H237" s="28"/>
@@ -22388,7 +21992,7 @@
       </c>
       <c r="L237" s="2"/>
       <c r="M237" s="14" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="N237" s="2"/>
       <c r="O237" s="31"/>
@@ -22455,7 +22059,7 @@
       </c>
       <c r="L238" s="2"/>
       <c r="M238" s="14" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="N238" s="2"/>
       <c r="O238" s="31"/>
@@ -22532,7 +22136,7 @@
       </c>
       <c r="L239" s="3"/>
       <c r="M239" s="14" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="N239" s="2"/>
       <c r="O239" s="31"/>
@@ -22560,10 +22164,10 @@
       </c>
       <c r="Z239" s="4"/>
       <c r="AA239" s="2" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="AB239" s="2" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="AC239" s="2"/>
       <c r="AD239" s="2"/>
@@ -22588,7 +22192,7 @@
       <c r="D240" s="2"/>
       <c r="E240" s="4"/>
       <c r="F240" s="38" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="G240" s="28">
         <v>34.2742</v>
@@ -22607,7 +22211,7 @@
       </c>
       <c r="L240" s="3"/>
       <c r="M240" s="14" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="N240" s="2"/>
       <c r="O240" s="31"/>
@@ -22635,10 +22239,10 @@
       </c>
       <c r="Z240" s="4"/>
       <c r="AA240" s="2" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="AB240" s="2" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="AC240" s="2"/>
       <c r="AD240" s="2"/>
@@ -22663,7 +22267,7 @@
       <c r="D241" s="2"/>
       <c r="E241" s="4"/>
       <c r="F241" s="38" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="G241" s="28">
         <v>39.788600000000002</v>
@@ -22682,7 +22286,7 @@
       </c>
       <c r="L241" s="3"/>
       <c r="M241" s="14" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="N241" s="2"/>
       <c r="O241" s="31"/>
@@ -22713,7 +22317,7 @@
         <v>585</v>
       </c>
       <c r="AB241" s="2" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="AC241" s="2"/>
       <c r="AD241" s="2"/>
@@ -22736,7 +22340,7 @@
       <c r="D242" s="2"/>
       <c r="E242" s="4"/>
       <c r="F242" s="38" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="G242" s="28"/>
       <c r="H242" s="28"/>
@@ -22749,7 +22353,7 @@
       </c>
       <c r="L242" s="2"/>
       <c r="M242" s="14" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="N242" s="2"/>
       <c r="O242" s="31"/>
@@ -22777,10 +22381,10 @@
       </c>
       <c r="Z242" s="4"/>
       <c r="AA242" s="2" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="AB242" s="2" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="AC242" s="2"/>
       <c r="AD242" s="2"/>
@@ -22792,7 +22396,7 @@
       </c>
       <c r="AG242" s="4"/>
       <c r="AH242" s="2" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="AI242" s="2"/>
     </row>
@@ -22805,7 +22409,7 @@
       <c r="D243" s="2"/>
       <c r="E243" s="4"/>
       <c r="F243" s="38" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="G243" s="28">
         <v>48.414000000000001</v>
@@ -22824,7 +22428,7 @@
       </c>
       <c r="L243" s="2"/>
       <c r="M243" s="14" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="N243" s="2"/>
       <c r="O243" s="31"/>
@@ -22897,7 +22501,7 @@
       </c>
       <c r="L244" s="3"/>
       <c r="M244" s="15" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="N244" s="2"/>
       <c r="O244" s="31"/>
@@ -22928,7 +22532,7 @@
       <c r="AB244" s="2"/>
       <c r="AC244" s="2"/>
       <c r="AD244" s="2" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="AE244" s="2" t="s">
         <v>42</v>
@@ -22951,7 +22555,7 @@
         <v>44313</v>
       </c>
       <c r="D245" s="2" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="E245" s="4">
         <v>99999</v>
@@ -22974,7 +22578,7 @@
       </c>
       <c r="L245" s="3"/>
       <c r="M245" s="15" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="N245" s="2"/>
       <c r="O245" s="31"/>
@@ -22984,10 +22588,10 @@
       <c r="S245" s="22"/>
       <c r="T245" s="36"/>
       <c r="U245" s="40" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="V245" s="2" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="W245" s="4" t="s">
         <v>39</v>
@@ -23003,7 +22607,7 @@
       <c r="AB245" s="2"/>
       <c r="AC245" s="2"/>
       <c r="AD245" s="2" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="AE245" s="2" t="s">
         <v>42</v>
@@ -23043,7 +22647,7 @@
       </c>
       <c r="L246" s="3"/>
       <c r="M246" s="15" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="N246" s="2"/>
       <c r="O246" s="31"/>
@@ -23055,7 +22659,7 @@
       </c>
       <c r="T246" s="36"/>
       <c r="U246" s="40" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="V246" s="2" t="s">
         <v>88</v>
@@ -23074,7 +22678,7 @@
       <c r="AB246" s="4"/>
       <c r="AC246" s="2"/>
       <c r="AD246" s="2" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="AE246" s="2" t="s">
         <v>42</v>
@@ -23084,7 +22688,7 @@
       </c>
       <c r="AG246" s="4"/>
       <c r="AH246" s="2" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="AI246" s="2"/>
     </row>
@@ -23116,7 +22720,7 @@
       </c>
       <c r="L247" s="3"/>
       <c r="M247" s="15" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="N247" s="2"/>
       <c r="O247" s="31"/>
@@ -23147,7 +22751,7 @@
       <c r="AB247" s="2"/>
       <c r="AC247" s="2"/>
       <c r="AD247" s="2" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="AE247" s="2" t="s">
         <v>42</v>
@@ -23187,7 +22791,7 @@
       </c>
       <c r="L248" s="3"/>
       <c r="M248" s="15" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="N248" s="2"/>
       <c r="O248" s="31"/>
@@ -23239,7 +22843,7 @@
         <v>35188</v>
       </c>
       <c r="D249" s="2" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="E249" s="4">
         <v>99999</v>
@@ -23262,7 +22866,7 @@
       </c>
       <c r="L249" s="3"/>
       <c r="M249" s="17" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="N249" s="2"/>
       <c r="O249" s="31"/>
@@ -23272,10 +22876,10 @@
       <c r="S249" s="22"/>
       <c r="T249" s="36"/>
       <c r="U249" s="40" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="V249" s="2" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="W249" s="4" t="s">
         <v>39</v>
@@ -23293,13 +22897,13 @@
       <c r="AB249" s="2"/>
       <c r="AC249" s="2"/>
       <c r="AD249" s="2" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="AE249" s="2" t="s">
         <v>267</v>
       </c>
       <c r="AF249" s="4" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="AG249" s="4"/>
       <c r="AH249" s="2"/>
@@ -23316,7 +22920,7 @@
         <v>36421</v>
       </c>
       <c r="D250" s="2" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="E250" s="4">
         <v>99999</v>
@@ -23393,7 +22997,7 @@
         <v>31960</v>
       </c>
       <c r="D251" s="2" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="E251" s="4">
         <v>99999</v>
@@ -23416,7 +23020,7 @@
       </c>
       <c r="L251" s="3"/>
       <c r="M251" s="16" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="N251" s="2"/>
       <c r="O251" s="31"/>
@@ -23426,10 +23030,10 @@
       <c r="S251" s="22"/>
       <c r="T251" s="36"/>
       <c r="U251" s="40" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="V251" s="2" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="W251" s="4" t="s">
         <v>39</v>
@@ -23447,7 +23051,7 @@
       <c r="AB251" s="2"/>
       <c r="AC251" s="2"/>
       <c r="AD251" s="2" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="AE251" s="2" t="s">
         <v>199</v>
@@ -23470,7 +23074,7 @@
         <v>30823</v>
       </c>
       <c r="D252" s="2" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="E252" s="4">
         <v>99999</v>
@@ -23493,7 +23097,7 @@
       </c>
       <c r="L252" s="3"/>
       <c r="M252" s="16" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="N252" s="2"/>
       <c r="O252" s="31"/>
@@ -23503,7 +23107,7 @@
       <c r="S252" s="22"/>
       <c r="T252" s="36"/>
       <c r="U252" s="40" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="V252" s="2" t="s">
         <v>232</v>
@@ -23524,7 +23128,7 @@
       <c r="AB252" s="2"/>
       <c r="AC252" s="2"/>
       <c r="AD252" s="2" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="AE252" s="2" t="s">
         <v>199</v>
@@ -23534,7 +23138,7 @@
       </c>
       <c r="AG252" s="4"/>
       <c r="AH252" s="2" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="AI252" s="2"/>
     </row>
@@ -23549,7 +23153,7 @@
         <v>23699</v>
       </c>
       <c r="D253" s="2" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="E253" s="4">
         <v>99999</v>
@@ -23572,7 +23176,7 @@
       </c>
       <c r="L253" s="3"/>
       <c r="M253" s="12" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="N253" s="23" t="s">
         <v>236</v>
@@ -23584,10 +23188,10 @@
       <c r="S253" s="22"/>
       <c r="T253" s="36"/>
       <c r="U253" s="40" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="V253" s="2" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="W253" s="4" t="s">
         <v>39</v>
@@ -23605,7 +23209,7 @@
         <v>199</v>
       </c>
       <c r="AF253" s="4" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="AG253" s="4"/>
       <c r="AH253" s="2"/>
@@ -23622,7 +23226,7 @@
         <v>29570</v>
       </c>
       <c r="D254" s="2" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="E254" s="4">
         <v>99999</v>
@@ -23645,7 +23249,7 @@
       </c>
       <c r="L254" s="3"/>
       <c r="M254" s="16" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="N254" s="2"/>
       <c r="O254" s="31"/>
@@ -23658,7 +23262,7 @@
         <v>247</v>
       </c>
       <c r="V254" s="2" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="W254" s="4" t="s">
         <v>39</v>
@@ -23676,7 +23280,7 @@
       <c r="AB254" s="2"/>
       <c r="AC254" s="2"/>
       <c r="AD254" s="2" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="AE254" s="2" t="s">
         <v>199</v>
@@ -23718,7 +23322,7 @@
       </c>
       <c r="L255" s="3"/>
       <c r="M255" s="16" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="N255" s="2"/>
       <c r="O255" s="31"/>
@@ -23728,10 +23332,10 @@
       <c r="S255" s="22"/>
       <c r="T255" s="36"/>
       <c r="U255" s="40" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="V255" s="2" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="W255" s="4" t="s">
         <v>39</v>
@@ -23745,13 +23349,13 @@
       <c r="AB255" s="2"/>
       <c r="AC255" s="2"/>
       <c r="AD255" s="2" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="AE255" s="2" t="s">
         <v>199</v>
       </c>
       <c r="AF255" s="4" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="AG255" s="4"/>
       <c r="AH255" s="2"/>
@@ -23768,7 +23372,7 @@
         <v>24136</v>
       </c>
       <c r="D256" s="2" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="E256" s="4">
         <v>99999</v>
@@ -23791,7 +23395,7 @@
       </c>
       <c r="L256" s="3"/>
       <c r="M256" s="16" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="N256" s="2"/>
       <c r="O256" s="31"/>
@@ -23801,10 +23405,10 @@
       <c r="S256" s="22"/>
       <c r="T256" s="36"/>
       <c r="U256" s="40" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="V256" s="2" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="W256" s="4" t="s">
         <v>39</v>
@@ -23818,13 +23422,13 @@
       <c r="AB256" s="2"/>
       <c r="AC256" s="2"/>
       <c r="AD256" s="2" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="AE256" s="2" t="s">
         <v>199</v>
       </c>
       <c r="AF256" s="4" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="AG256" s="4"/>
       <c r="AH256" s="2"/>
@@ -23841,7 +23445,7 @@
         <v>24525</v>
       </c>
       <c r="D257" s="2" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="E257" s="4">
         <v>99999</v>
@@ -23864,7 +23468,7 @@
       </c>
       <c r="L257" s="3"/>
       <c r="M257" s="16" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="N257" s="2"/>
       <c r="O257" s="31"/>
@@ -23874,10 +23478,10 @@
       <c r="S257" s="22"/>
       <c r="T257" s="36"/>
       <c r="U257" s="40" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="V257" s="2" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="W257" s="4" t="s">
         <v>39</v>
@@ -23891,13 +23495,13 @@
       <c r="AB257" s="2"/>
       <c r="AC257" s="2"/>
       <c r="AD257" s="2" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="AE257" s="2" t="s">
         <v>199</v>
       </c>
       <c r="AF257" s="4" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="AG257" s="4"/>
       <c r="AH257" s="2"/>
@@ -23914,7 +23518,7 @@
         <v>24856</v>
       </c>
       <c r="D258" s="2" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="E258" s="4">
         <v>99999</v>
@@ -23937,7 +23541,7 @@
       </c>
       <c r="L258" s="3"/>
       <c r="M258" s="16" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="N258" s="2"/>
       <c r="O258" s="31"/>
@@ -23947,10 +23551,10 @@
       <c r="S258" s="22"/>
       <c r="T258" s="36"/>
       <c r="U258" s="40" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="V258" s="2" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="W258" s="4" t="s">
         <v>39</v>
@@ -23964,17 +23568,17 @@
       <c r="AB258" s="2"/>
       <c r="AC258" s="2"/>
       <c r="AD258" s="2" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="AE258" s="2" t="s">
         <v>199</v>
       </c>
       <c r="AF258" s="4" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="AG258" s="4"/>
       <c r="AH258" s="2" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="AI258" s="2"/>
     </row>
@@ -23989,7 +23593,7 @@
         <v>24668</v>
       </c>
       <c r="D259" s="2" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="E259" s="4">
         <v>99999</v>
@@ -24012,7 +23616,7 @@
       </c>
       <c r="L259" s="3"/>
       <c r="M259" s="16" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="N259" s="2"/>
       <c r="O259" s="31"/>
@@ -24022,10 +23626,10 @@
       <c r="S259" s="22"/>
       <c r="T259" s="36"/>
       <c r="U259" s="40" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="V259" s="2" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="W259" s="4" t="s">
         <v>39</v>
@@ -24039,17 +23643,17 @@
       <c r="AB259" s="2"/>
       <c r="AC259" s="2"/>
       <c r="AD259" s="2" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="AE259" s="2" t="s">
         <v>199</v>
       </c>
       <c r="AF259" s="4" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="AG259" s="4"/>
       <c r="AH259" s="2" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="AI259" s="2"/>
     </row>
@@ -24064,7 +23668,7 @@
         <v>31005</v>
       </c>
       <c r="D260" s="2" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="E260" s="4">
         <v>99999</v>
@@ -24087,7 +23691,7 @@
       </c>
       <c r="L260" s="3"/>
       <c r="M260" s="16" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="N260" s="2"/>
       <c r="O260" s="31"/>
@@ -24097,10 +23701,10 @@
       <c r="S260" s="22"/>
       <c r="T260" s="36"/>
       <c r="U260" s="40" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="V260" s="2" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="W260" s="4" t="s">
         <v>39</v>
@@ -24118,7 +23722,7 @@
         <v>199</v>
       </c>
       <c r="AF260" s="4" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="AG260" s="4"/>
       <c r="AH260" s="2"/>
@@ -24135,7 +23739,7 @@
         <v>24538</v>
       </c>
       <c r="D261" s="2" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="E261" s="4">
         <v>99999</v>
@@ -24158,7 +23762,7 @@
       </c>
       <c r="L261" s="2"/>
       <c r="M261" s="16" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="N261" s="2"/>
       <c r="O261" s="31"/>
@@ -24168,10 +23772,10 @@
       <c r="S261" s="22"/>
       <c r="T261" s="36"/>
       <c r="U261" s="40" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="V261" s="2" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="W261" s="4" t="s">
         <v>39</v>
@@ -24189,7 +23793,7 @@
         <v>199</v>
       </c>
       <c r="AF261" s="4" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="AG261" s="4"/>
       <c r="AH261" s="2"/>
@@ -24206,7 +23810,7 @@
         <v>36103</v>
       </c>
       <c r="D262" s="2" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="E262" s="4">
         <v>99999</v>
@@ -24229,14 +23833,14 @@
       </c>
       <c r="L262" s="3"/>
       <c r="M262" s="16" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="N262" s="2"/>
       <c r="O262" s="31"/>
       <c r="P262" s="31"/>
       <c r="Q262" s="31"/>
       <c r="R262" s="50" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="S262" s="22"/>
       <c r="T262" s="36"/>
@@ -24283,7 +23887,7 @@
         <v>30758</v>
       </c>
       <c r="D263" s="2" t="s">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="E263" s="4">
         <v>99999</v>
@@ -24306,7 +23910,7 @@
       </c>
       <c r="L263" s="3"/>
       <c r="M263" s="16" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="N263" s="2"/>
       <c r="O263" s="31"/>
@@ -24316,7 +23920,7 @@
       <c r="S263" s="22"/>
       <c r="T263" s="36"/>
       <c r="U263" s="40" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="V263" s="2" t="s">
         <v>219</v>
@@ -24337,7 +23941,7 @@
       <c r="AB263" s="2"/>
       <c r="AC263" s="2"/>
       <c r="AD263" s="2" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="AE263" s="2" t="s">
         <v>199</v>
@@ -24360,7 +23964,7 @@
         <v>29638</v>
       </c>
       <c r="D264" s="2" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="E264" s="4">
         <v>99999</v>
@@ -24383,7 +23987,7 @@
       </c>
       <c r="L264" s="3"/>
       <c r="M264" s="16" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="N264" s="2"/>
       <c r="O264" s="31"/>
@@ -24393,10 +23997,10 @@
       <c r="S264" s="22"/>
       <c r="T264" s="36"/>
       <c r="U264" s="40" t="s">
+        <v>878</v>
+      </c>
+      <c r="V264" s="2" t="s">
         <v>877</v>
-      </c>
-      <c r="V264" s="2" t="s">
-        <v>876</v>
       </c>
       <c r="W264" s="4" t="s">
         <v>39</v>
@@ -24414,7 +24018,7 @@
       <c r="AB264" s="2"/>
       <c r="AC264" s="2"/>
       <c r="AD264" s="2" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="AE264" s="2" t="s">
         <v>199</v>
@@ -24437,7 +24041,7 @@
         <v>30337</v>
       </c>
       <c r="D265" s="2" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="E265" s="4">
         <v>99999</v>
@@ -24460,7 +24064,7 @@
       </c>
       <c r="L265" s="3"/>
       <c r="M265" s="16" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="N265" s="2"/>
       <c r="O265" s="31"/>
@@ -24470,7 +24074,7 @@
       <c r="S265" s="22"/>
       <c r="T265" s="36"/>
       <c r="U265" s="40" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="V265" s="2" t="s">
         <v>238</v>
@@ -24491,11 +24095,11 @@
         <v>199</v>
       </c>
       <c r="AF265" s="4" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="AG265" s="4"/>
       <c r="AH265" s="2" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="AI265" s="2"/>
     </row>
@@ -24510,7 +24114,7 @@
         <v>30710</v>
       </c>
       <c r="D266" s="2" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="E266" s="4">
         <v>99999</v>
@@ -24543,7 +24147,7 @@
       <c r="S266" s="22"/>
       <c r="T266" s="36"/>
       <c r="U266" s="40" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="V266" s="2" t="s">
         <v>238</v>
@@ -24564,7 +24168,7 @@
       <c r="AB266" s="2"/>
       <c r="AC266" s="2"/>
       <c r="AD266" s="2" t="s">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="AE266" s="2" t="s">
         <v>199</v>
@@ -24574,7 +24178,7 @@
       </c>
       <c r="AG266" s="4"/>
       <c r="AH266" s="2" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="AI266" s="2"/>
     </row>
@@ -24589,7 +24193,7 @@
         <v>89606</v>
       </c>
       <c r="D267" s="2" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="E267" s="4">
         <v>99999</v>
@@ -24608,19 +24212,15 @@
         <v>12</v>
       </c>
       <c r="K267" s="30" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="L267" s="42"/>
       <c r="M267" s="16" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="N267" s="2"/>
-      <c r="O267" s="31">
-        <v>-62.9</v>
-      </c>
-      <c r="P267" s="31">
-        <v>-54.6</v>
-      </c>
+      <c r="O267" s="31"/>
+      <c r="P267" s="31"/>
       <c r="Q267" s="31"/>
       <c r="R267" s="50"/>
       <c r="S267" s="22" t="s">
@@ -24628,7 +24228,7 @@
       </c>
       <c r="T267" s="36"/>
       <c r="U267" s="40" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="V267" s="2"/>
       <c r="W267" s="4" t="s">
@@ -24647,11 +24247,11 @@
         <v>199</v>
       </c>
       <c r="AF267" s="4" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="AG267" s="4"/>
       <c r="AH267" s="2" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="AI267" s="2"/>
     </row>
@@ -24664,7 +24264,7 @@
       <c r="D268" s="2"/>
       <c r="E268" s="4"/>
       <c r="F268" s="38" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="G268" s="28"/>
       <c r="H268" s="28"/>
@@ -24677,7 +24277,7 @@
       </c>
       <c r="L268" s="2"/>
       <c r="M268" s="14" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="N268" s="2"/>
       <c r="O268" s="31"/>
@@ -24748,7 +24348,7 @@
       </c>
       <c r="L269" s="2"/>
       <c r="M269" s="15" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="N269" s="2"/>
       <c r="O269" s="31"/>
@@ -24758,10 +24358,10 @@
       <c r="S269" s="22"/>
       <c r="T269" s="36"/>
       <c r="U269" s="40" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="V269" s="2" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="W269" s="4" t="s">
         <v>39</v>
@@ -24777,7 +24377,7 @@
       <c r="AB269" s="2"/>
       <c r="AC269" s="2"/>
       <c r="AD269" s="2" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="AE269" s="2" t="s">
         <v>42</v>
@@ -24798,7 +24398,7 @@
       <c r="D270" s="2"/>
       <c r="E270" s="4"/>
       <c r="F270" s="38" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="G270" s="28"/>
       <c r="H270" s="28"/>
@@ -24811,7 +24411,7 @@
       </c>
       <c r="L270" s="2"/>
       <c r="M270" s="14" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="N270" s="2"/>
       <c r="O270" s="31"/>
@@ -24867,7 +24467,7 @@
         <v>50915</v>
       </c>
       <c r="D271" s="2" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="E271" s="4">
         <v>99999</v>
@@ -24890,7 +24490,7 @@
       </c>
       <c r="L271" s="2"/>
       <c r="M271" s="14" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="N271" s="2"/>
       <c r="O271" s="31"/>
@@ -24900,7 +24500,7 @@
       <c r="S271" s="22"/>
       <c r="T271" s="36"/>
       <c r="U271" s="40" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="V271" s="2" t="s">
         <v>337</v>
@@ -24916,7 +24516,7 @@
       </c>
       <c r="Z271" s="4"/>
       <c r="AA271" s="2" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="AB271" s="2"/>
       <c r="AC271" s="2"/>
@@ -24961,7 +24561,7 @@
       </c>
       <c r="L272" s="2"/>
       <c r="M272" s="14" t="s">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="N272" s="2"/>
       <c r="O272" s="31"/>
@@ -24973,7 +24573,7 @@
       </c>
       <c r="T272" s="36"/>
       <c r="U272" s="40" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="V272" s="2" t="s">
         <v>337</v>
@@ -24989,7 +24589,7 @@
       </c>
       <c r="Z272" s="4"/>
       <c r="AA272" s="2" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="AB272" s="2"/>
       <c r="AC272" s="2"/>
@@ -25015,7 +24615,7 @@
         <v>54012</v>
       </c>
       <c r="D273" s="2" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="E273" s="4">
         <v>99999</v>
@@ -25038,7 +24638,7 @@
       </c>
       <c r="L273" s="2"/>
       <c r="M273" s="14" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="N273" s="2"/>
       <c r="O273" s="31"/>
@@ -25048,7 +24648,7 @@
       <c r="S273" s="22"/>
       <c r="T273" s="36"/>
       <c r="U273" s="40" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="V273" s="2" t="s">
         <v>337</v>
@@ -25064,7 +24664,7 @@
       </c>
       <c r="Z273" s="4"/>
       <c r="AA273" s="2" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="AB273" s="2"/>
       <c r="AC273" s="2"/>
@@ -25090,7 +24690,7 @@
         <v>51087</v>
       </c>
       <c r="D274" s="2" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="E274" s="4">
         <v>99999</v>
@@ -25113,7 +24713,7 @@
       </c>
       <c r="L274" s="2"/>
       <c r="M274" s="14" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="N274" s="2"/>
       <c r="O274" s="31"/>
@@ -25186,7 +24786,7 @@
       </c>
       <c r="L275" s="2"/>
       <c r="M275" s="14" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="N275" s="2"/>
       <c r="O275" s="31"/>
@@ -25196,7 +24796,7 @@
       <c r="S275" s="22"/>
       <c r="T275" s="36"/>
       <c r="U275" s="40" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="V275" s="2" t="s">
         <v>383</v>
@@ -25225,7 +24825,7 @@
       </c>
       <c r="AG275" s="4"/>
       <c r="AH275" s="2" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="AI275" s="2"/>
     </row>
@@ -25259,7 +24859,7 @@
       </c>
       <c r="L276" s="2"/>
       <c r="M276" s="14" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="N276" s="2"/>
       <c r="O276" s="31"/>
@@ -25271,7 +24871,7 @@
       </c>
       <c r="T276" s="36"/>
       <c r="U276" s="40" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="V276" s="2" t="s">
         <v>309</v>
@@ -25287,10 +24887,10 @@
       </c>
       <c r="Z276" s="4"/>
       <c r="AA276" s="2" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="AB276" s="2" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="AC276" s="2"/>
       <c r="AD276" s="2"/>
@@ -25302,7 +24902,7 @@
       </c>
       <c r="AG276" s="4"/>
       <c r="AH276" s="2" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="AI276" s="2"/>
     </row>
@@ -25326,7 +24926,7 @@
       </c>
       <c r="L277" s="2"/>
       <c r="M277" s="14" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="N277" s="2"/>
       <c r="O277" s="31"/>
@@ -25338,7 +24938,7 @@
       </c>
       <c r="T277" s="36"/>
       <c r="U277" s="40" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="V277" s="2" t="s">
         <v>337</v>
@@ -25357,7 +24957,7 @@
         <v>338</v>
       </c>
       <c r="AB277" s="2" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="AC277" s="2"/>
       <c r="AD277" s="2"/>
@@ -25382,7 +24982,7 @@
         <v>25248</v>
       </c>
       <c r="D278" s="2" t="s">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="E278" s="4">
         <v>99999</v>
@@ -25405,7 +25005,7 @@
       </c>
       <c r="L278" s="2"/>
       <c r="M278" s="16" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="N278" s="2"/>
       <c r="O278" s="31"/>
@@ -25415,10 +25015,10 @@
       <c r="S278" s="22"/>
       <c r="T278" s="36"/>
       <c r="U278" s="40" t="s">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="V278" s="2" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="W278" s="4" t="s">
         <v>39</v>
@@ -25432,13 +25032,13 @@
       <c r="AB278" s="2"/>
       <c r="AC278" s="2"/>
       <c r="AD278" s="2" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="AE278" s="2" t="s">
         <v>199</v>
       </c>
       <c r="AF278" s="4" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="AG278" s="4"/>
       <c r="AH278" s="2"/>
@@ -25453,7 +25053,7 @@
       <c r="D279" s="2"/>
       <c r="E279" s="4"/>
       <c r="F279" s="38" t="s">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="G279" s="28"/>
       <c r="H279" s="28"/>
@@ -25466,7 +25066,7 @@
       </c>
       <c r="L279" s="2"/>
       <c r="M279" s="14" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="N279" s="2"/>
       <c r="O279" s="31"/>
@@ -25478,7 +25078,7 @@
       </c>
       <c r="T279" s="36"/>
       <c r="U279" s="40" t="s">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="V279" s="2" t="s">
         <v>337</v>
@@ -25494,7 +25094,7 @@
       </c>
       <c r="Z279" s="4"/>
       <c r="AA279" s="2" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="AB279" s="2"/>
       <c r="AC279" s="2"/>
@@ -25539,7 +25139,7 @@
       </c>
       <c r="L280" s="2"/>
       <c r="M280" s="14" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="N280" s="2"/>
       <c r="O280" s="31"/>
@@ -25567,10 +25167,10 @@
       </c>
       <c r="Z280" s="4"/>
       <c r="AA280" s="2" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="AB280" s="2" t="s">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="AC280" s="2"/>
       <c r="AD280" s="2"/>
@@ -25593,7 +25193,7 @@
       <c r="D281" s="2"/>
       <c r="E281" s="4"/>
       <c r="F281" s="38" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="G281" s="28">
         <v>40.245800000000003</v>
@@ -25612,7 +25212,7 @@
       </c>
       <c r="L281" s="2"/>
       <c r="M281" s="14" t="s">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="N281" s="2"/>
       <c r="O281" s="31"/>
@@ -25677,7 +25277,7 @@
       </c>
       <c r="L282" s="2"/>
       <c r="M282" s="14" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="N282" s="2"/>
       <c r="O282" s="31"/>
@@ -25729,7 +25329,7 @@
       <c r="D283" s="2"/>
       <c r="E283" s="4"/>
       <c r="F283" s="38" t="s">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c r="G283" s="28"/>
       <c r="H283" s="28"/>
@@ -25742,7 +25342,7 @@
       </c>
       <c r="L283" s="2"/>
       <c r="M283" s="14" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="N283" s="2"/>
       <c r="O283" s="31"/>
@@ -25770,10 +25370,10 @@
       </c>
       <c r="Z283" s="4"/>
       <c r="AA283" s="2" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="AB283" s="2" t="s">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="AC283" s="2"/>
       <c r="AD283" s="2"/>
@@ -25807,7 +25407,7 @@
       </c>
       <c r="L284" s="2"/>
       <c r="M284" s="14" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="N284" s="2"/>
       <c r="O284" s="31"/>
@@ -25876,7 +25476,7 @@
       </c>
       <c r="L285" s="2"/>
       <c r="M285" s="14" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="N285" s="2"/>
       <c r="O285" s="31"/>
@@ -25888,7 +25488,7 @@
       </c>
       <c r="T285" s="36"/>
       <c r="U285" s="40" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="V285" s="2" t="s">
         <v>309</v>
@@ -25904,10 +25504,10 @@
       </c>
       <c r="Z285" s="4"/>
       <c r="AA285" s="2" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="AB285" s="2" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="AC285" s="2"/>
       <c r="AD285" s="2"/>
@@ -25943,7 +25543,7 @@
       </c>
       <c r="L286" s="2"/>
       <c r="M286" s="14" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="N286" s="2"/>
       <c r="O286" s="31"/>
@@ -25955,7 +25555,7 @@
       </c>
       <c r="T286" s="36"/>
       <c r="U286" s="40" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="V286" s="2" t="s">
         <v>383</v>
@@ -26016,7 +25616,7 @@
       </c>
       <c r="L287" s="2"/>
       <c r="M287" s="14" t="s">
-        <v>934</v>
+        <v>935</v>
       </c>
       <c r="N287" s="2"/>
       <c r="O287" s="31"/>
@@ -26028,7 +25628,7 @@
       </c>
       <c r="T287" s="36"/>
       <c r="U287" s="40" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="V287" s="2" t="s">
         <v>383</v>
@@ -26047,7 +25647,7 @@
         <v>388</v>
       </c>
       <c r="AB287" s="2" t="s">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="AC287" s="2"/>
       <c r="AD287" s="2"/>
@@ -26059,7 +25659,7 @@
       </c>
       <c r="AG287" s="4"/>
       <c r="AH287" s="2" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="AI287" s="2"/>
     </row>
@@ -26093,7 +25693,7 @@
       </c>
       <c r="L288" s="2"/>
       <c r="M288" s="14" t="s">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="N288" s="2"/>
       <c r="O288" s="31"/>
@@ -26149,7 +25749,7 @@
       <c r="D289" s="2"/>
       <c r="E289" s="4"/>
       <c r="F289" s="38" t="s">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="G289" s="28">
         <v>48.0197</v>
@@ -26168,7 +25768,7 @@
       </c>
       <c r="L289" s="2"/>
       <c r="M289" s="14" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="N289" s="2"/>
       <c r="O289" s="31"/>
@@ -26224,7 +25824,7 @@
       <c r="D290" s="2"/>
       <c r="E290" s="4"/>
       <c r="F290" s="38" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="G290" s="28">
         <v>46.177199999999999</v>
@@ -26243,7 +25843,7 @@
       </c>
       <c r="L290" s="2"/>
       <c r="M290" s="14" t="s">
-        <v>940</v>
+        <v>941</v>
       </c>
       <c r="N290" s="2"/>
       <c r="O290" s="31"/>
@@ -26299,7 +25899,7 @@
       <c r="D291" s="2"/>
       <c r="E291" s="4"/>
       <c r="F291" s="38" t="s">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="G291" s="28">
         <v>49.679699999999997</v>
@@ -26318,7 +25918,7 @@
       </c>
       <c r="L291" s="2"/>
       <c r="M291" s="14" t="s">
-        <v>942</v>
+        <v>943</v>
       </c>
       <c r="N291" s="2"/>
       <c r="O291" s="31"/>
@@ -26330,7 +25930,7 @@
       </c>
       <c r="T291" s="36"/>
       <c r="U291" s="40" t="s">
-        <v>943</v>
+        <v>944</v>
       </c>
       <c r="V291" s="2" t="s">
         <v>337</v>
@@ -26349,7 +25949,7 @@
         <v>338</v>
       </c>
       <c r="AB291" s="2" t="s">
-        <v>943</v>
+        <v>944</v>
       </c>
       <c r="AC291" s="2"/>
       <c r="AD291" s="2"/>
@@ -26369,7 +25969,7 @@
       </c>
       <c r="B292" s="2"/>
       <c r="C292" s="45" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="D292" s="2"/>
       <c r="E292" s="4">
@@ -26393,7 +25993,7 @@
       </c>
       <c r="L292" s="2"/>
       <c r="M292" s="14" t="s">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="N292" s="2"/>
       <c r="O292" s="31"/>
@@ -26424,7 +26024,7 @@
         <v>338</v>
       </c>
       <c r="AB292" s="2" t="s">
-        <v>946</v>
+        <v>947</v>
       </c>
       <c r="AC292" s="2"/>
       <c r="AD292" s="2"/>
@@ -26444,7 +26044,7 @@
       </c>
       <c r="B293" s="2"/>
       <c r="C293" s="45" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="D293" s="2"/>
       <c r="E293" s="4">
@@ -26464,16 +26064,14 @@
         <v>12</v>
       </c>
       <c r="K293" s="30" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="L293" s="2"/>
       <c r="M293" s="14" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="N293" s="2"/>
-      <c r="O293" s="31">
-        <v>-28.4</v>
-      </c>
+      <c r="O293" s="31"/>
       <c r="P293" s="31"/>
       <c r="Q293" s="31"/>
       <c r="R293" s="50"/>
@@ -26482,10 +26080,10 @@
       </c>
       <c r="T293" s="36"/>
       <c r="U293" s="40" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="V293" s="2" t="s">
-        <v>951</v>
+        <v>952</v>
       </c>
       <c r="W293" s="4" t="s">
         <v>39</v>
@@ -26500,14 +26098,14 @@
       <c r="AC293" s="2"/>
       <c r="AD293" s="2"/>
       <c r="AE293" s="2" t="s">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="AF293" s="4" t="s">
         <v>268</v>
       </c>
       <c r="AG293" s="4"/>
       <c r="AH293" s="2" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="AI293" s="2"/>
     </row>
@@ -26520,7 +26118,7 @@
       <c r="D294" s="2"/>
       <c r="E294" s="4"/>
       <c r="F294" s="38" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="G294" s="28">
         <v>50.008600000000001</v>
@@ -26539,7 +26137,7 @@
       </c>
       <c r="L294" s="2"/>
       <c r="M294" s="14" t="s">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="N294" s="2"/>
       <c r="O294" s="31"/>
@@ -26551,7 +26149,7 @@
       </c>
       <c r="T294" s="36"/>
       <c r="U294" s="40" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="V294" s="2" t="s">
         <v>337</v>
@@ -26570,7 +26168,7 @@
         <v>338</v>
       </c>
       <c r="AB294" s="2" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="AC294" s="2"/>
       <c r="AD294" s="2"/>
@@ -26593,7 +26191,7 @@
       <c r="D295" s="2"/>
       <c r="E295" s="4"/>
       <c r="F295" s="38" t="s">
-        <v>956</v>
+        <v>957</v>
       </c>
       <c r="G295" s="28">
         <v>50.064700000000002</v>
@@ -26612,7 +26210,7 @@
       </c>
       <c r="L295" s="2"/>
       <c r="M295" s="14" t="s">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="N295" s="2"/>
       <c r="O295" s="31"/>
@@ -26624,7 +26222,7 @@
       </c>
       <c r="T295" s="36"/>
       <c r="U295" s="40" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="V295" s="2" t="s">
         <v>337</v>
@@ -26643,7 +26241,7 @@
         <v>338</v>
       </c>
       <c r="AB295" s="2" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="AC295" s="2"/>
       <c r="AD295" s="2"/>
@@ -26663,7 +26261,7 @@
       </c>
       <c r="B296" s="2"/>
       <c r="C296" s="45" t="s">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="D296" s="2"/>
       <c r="E296" s="4">
@@ -26687,18 +26285,12 @@
       </c>
       <c r="L296" s="2"/>
       <c r="M296" s="14" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="N296" s="2"/>
-      <c r="O296" s="31">
-        <v>-0.4</v>
-      </c>
-      <c r="P296" s="31">
-        <v>10.9</v>
-      </c>
-      <c r="Q296" s="31">
-        <v>4.6100000000000003</v>
-      </c>
+      <c r="O296" s="31"/>
+      <c r="P296" s="31"/>
+      <c r="Q296" s="31"/>
       <c r="R296" s="50"/>
       <c r="S296" s="22" t="s">
         <v>39</v>
@@ -26724,7 +26316,7 @@
         <v>403</v>
       </c>
       <c r="AB296" s="2" t="s">
-        <v>960</v>
+        <v>961</v>
       </c>
       <c r="AC296" s="2"/>
       <c r="AD296" s="2"/>
@@ -26749,7 +26341,7 @@
       <c r="D297" s="2"/>
       <c r="E297" s="4"/>
       <c r="F297" s="38" t="s">
-        <v>961</v>
+        <v>962</v>
       </c>
       <c r="G297" s="28">
         <v>35.685000000000002</v>
@@ -26768,27 +26360,21 @@
       </c>
       <c r="L297" s="2"/>
       <c r="M297" s="14" t="s">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="N297" s="3" t="s">
-        <v>963</v>
-      </c>
-      <c r="O297" s="31">
-        <v>-2.8</v>
-      </c>
-      <c r="P297" s="31">
-        <v>6.2</v>
-      </c>
-      <c r="Q297" s="31">
-        <v>0.5</v>
-      </c>
+        <v>964</v>
+      </c>
+      <c r="O297" s="31"/>
+      <c r="P297" s="31"/>
+      <c r="Q297" s="31"/>
       <c r="R297" s="50"/>
       <c r="S297" s="22" t="s">
         <v>39</v>
       </c>
       <c r="T297" s="36"/>
       <c r="U297" s="40" t="s">
-        <v>964</v>
+        <v>965</v>
       </c>
       <c r="V297" s="2" t="s">
         <v>383</v>
@@ -26804,10 +26390,10 @@
       </c>
       <c r="Z297" s="4"/>
       <c r="AA297" s="2" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="AB297" s="2" t="s">
-        <v>966</v>
+        <v>967</v>
       </c>
       <c r="AC297" s="2"/>
       <c r="AD297" s="2"/>
@@ -26819,7 +26405,7 @@
       </c>
       <c r="AG297" s="4"/>
       <c r="AH297" s="2" t="s">
-        <v>964</v>
+        <v>965</v>
       </c>
       <c r="AI297" s="2"/>
     </row>
@@ -26832,7 +26418,7 @@
       <c r="D298" s="2"/>
       <c r="E298" s="4"/>
       <c r="F298" s="38" t="s">
-        <v>967</v>
+        <v>968</v>
       </c>
       <c r="G298" s="28">
         <v>47.138100000000001</v>
@@ -26851,7 +26437,7 @@
       </c>
       <c r="L298" s="2"/>
       <c r="M298" s="14" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="N298" s="23"/>
       <c r="O298" s="31"/>
@@ -26882,7 +26468,7 @@
         <v>388</v>
       </c>
       <c r="AB298" s="2" t="s">
-        <v>969</v>
+        <v>970</v>
       </c>
       <c r="AC298" s="2"/>
       <c r="AD298" s="2"/>
@@ -26905,7 +26491,7 @@
       <c r="D299" s="2"/>
       <c r="E299" s="4"/>
       <c r="F299" s="38" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="G299" s="28"/>
       <c r="H299" s="28"/>
@@ -26918,7 +26504,7 @@
       </c>
       <c r="L299" s="2"/>
       <c r="M299" s="14" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="N299" s="2"/>
       <c r="O299" s="31"/>
@@ -26971,7 +26557,7 @@
       </c>
       <c r="B300" s="2"/>
       <c r="C300" s="45" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="D300" s="2"/>
       <c r="E300" s="4"/>
@@ -26993,7 +26579,7 @@
       </c>
       <c r="L300" s="2"/>
       <c r="M300" s="14" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="N300" s="2"/>
       <c r="O300" s="31"/>
@@ -27021,10 +26607,10 @@
       </c>
       <c r="Z300" s="4"/>
       <c r="AA300" s="2" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="AB300" s="2" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="AC300" s="2"/>
       <c r="AD300" s="2"/>
@@ -27068,7 +26654,7 @@
       </c>
       <c r="L301" s="2"/>
       <c r="M301" s="15" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="N301" s="2"/>
       <c r="O301" s="31"/>
@@ -27118,7 +26704,7 @@
       <c r="D302" s="2"/>
       <c r="E302" s="4"/>
       <c r="F302" s="38" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="G302" s="28">
         <v>51.330800000000004</v>
@@ -27137,7 +26723,7 @@
       </c>
       <c r="L302" s="2"/>
       <c r="M302" s="14" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="N302" s="2"/>
       <c r="O302" s="31"/>
@@ -27190,7 +26776,7 @@
       </c>
       <c r="B303" s="2"/>
       <c r="C303" s="45" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="D303" s="2"/>
       <c r="E303" s="4">
@@ -27214,7 +26800,7 @@
       </c>
       <c r="L303" s="2"/>
       <c r="M303" s="14" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="N303" s="2"/>
       <c r="O303" s="31"/>
@@ -27242,7 +26828,7 @@
       </c>
       <c r="Z303" s="4"/>
       <c r="AA303" s="2" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="AB303" s="2"/>
       <c r="AC303" s="2"/>
@@ -27255,7 +26841,7 @@
       </c>
       <c r="AG303" s="4"/>
       <c r="AH303" s="2" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="AI303" s="2"/>
     </row>
@@ -27265,7 +26851,7 @@
       </c>
       <c r="B304" s="2"/>
       <c r="C304" s="45" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="D304" s="2"/>
       <c r="E304" s="4">
@@ -27289,7 +26875,7 @@
       </c>
       <c r="L304" s="2"/>
       <c r="M304" s="14" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="N304" s="2"/>
       <c r="O304" s="31"/>
@@ -27317,10 +26903,10 @@
       </c>
       <c r="Z304" s="4"/>
       <c r="AA304" s="2" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="AB304" s="2" t="s">
-        <v>984</v>
+        <v>985</v>
       </c>
       <c r="AC304" s="2"/>
       <c r="AD304" s="2"/>
@@ -27362,7 +26948,7 @@
       </c>
       <c r="L305" s="2"/>
       <c r="M305" s="15" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="N305" s="2"/>
       <c r="O305" s="31"/>
@@ -27411,7 +26997,7 @@
       </c>
       <c r="B306" s="2"/>
       <c r="C306" s="45" t="s">
-        <v>986</v>
+        <v>987</v>
       </c>
       <c r="D306" s="2"/>
       <c r="E306" s="4">
@@ -27435,7 +27021,7 @@
       </c>
       <c r="L306" s="2"/>
       <c r="M306" s="14" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="N306" s="2"/>
       <c r="O306" s="31"/>
@@ -27463,10 +27049,10 @@
       </c>
       <c r="Z306" s="4"/>
       <c r="AA306" s="2" t="s">
-        <v>988</v>
+        <v>989</v>
       </c>
       <c r="AB306" s="2" t="s">
-        <v>989</v>
+        <v>990</v>
       </c>
       <c r="AC306" s="2"/>
       <c r="AD306" s="2"/>
@@ -27486,7 +27072,7 @@
       </c>
       <c r="B307" s="2"/>
       <c r="C307" s="45" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="D307" s="2"/>
       <c r="E307" s="4">
@@ -27510,7 +27096,7 @@
       </c>
       <c r="L307" s="2"/>
       <c r="M307" s="14" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="N307" s="2"/>
       <c r="O307" s="31"/>
@@ -27538,10 +27124,10 @@
       </c>
       <c r="Z307" s="4"/>
       <c r="AA307" s="2" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="AB307" s="2" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="AC307" s="2"/>
       <c r="AD307" s="2"/>
@@ -27563,7 +27149,7 @@
       </c>
       <c r="B308" s="2"/>
       <c r="C308" s="45" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="D308" s="2"/>
       <c r="E308" s="4">
@@ -27587,7 +27173,7 @@
       </c>
       <c r="L308" s="2"/>
       <c r="M308" s="14" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="N308" s="2"/>
       <c r="O308" s="31"/>
@@ -27615,10 +27201,10 @@
       </c>
       <c r="Z308" s="4"/>
       <c r="AA308" s="2" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="AB308" s="2" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="AC308" s="2"/>
       <c r="AD308" s="2"/>
@@ -27640,7 +27226,7 @@
       </c>
       <c r="B309" s="2"/>
       <c r="C309" s="45" t="s">
-        <v>998</v>
+        <v>999</v>
       </c>
       <c r="D309" s="2"/>
       <c r="E309" s="4">
@@ -27664,21 +27250,21 @@
       </c>
       <c r="L309" s="2"/>
       <c r="M309" s="14" t="s">
-        <v>999</v>
+        <v>1000</v>
       </c>
       <c r="N309" s="2"/>
       <c r="O309" s="31"/>
       <c r="P309" s="31"/>
       <c r="Q309" s="31"/>
       <c r="R309" s="50" t="s">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="S309" s="22" t="s">
         <v>39</v>
       </c>
       <c r="T309" s="36"/>
       <c r="U309" s="40" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="V309" s="2" t="s">
         <v>566</v>
@@ -27694,10 +27280,10 @@
       </c>
       <c r="Z309" s="4"/>
       <c r="AA309" s="2" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="AB309" s="2" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="AC309" s="2"/>
       <c r="AD309" s="2"/>
@@ -27722,7 +27308,7 @@
       <c r="D310" s="2"/>
       <c r="E310" s="4"/>
       <c r="F310" s="38" t="s">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="G310" s="28">
         <v>32.881399999999999</v>
@@ -27741,7 +27327,7 @@
       </c>
       <c r="L310" s="2"/>
       <c r="M310" s="14" t="s">
-        <v>1003</v>
+        <v>1004</v>
       </c>
       <c r="N310" s="23" t="s">
         <v>97</v>
@@ -27771,7 +27357,7 @@
       </c>
       <c r="Z310" s="4"/>
       <c r="AA310" s="2" t="s">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="AB310" s="2" t="s">
         <v>366</v>
@@ -27818,7 +27404,7 @@
       </c>
       <c r="L311" s="2"/>
       <c r="M311" s="48" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="N311" s="2"/>
       <c r="O311" s="31"/>
@@ -27830,7 +27416,7 @@
       </c>
       <c r="T311" s="36"/>
       <c r="U311" s="40" t="s">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="V311" s="2" t="s">
         <v>190</v>
@@ -27867,7 +27453,7 @@
         <v>35</v>
       </c>
       <c r="C312" s="45" t="s">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="D312" s="2"/>
       <c r="E312" s="4">
@@ -27891,7 +27477,7 @@
       </c>
       <c r="L312" s="2"/>
       <c r="M312" s="16" t="s">
-        <v>1008</v>
+        <v>1009</v>
       </c>
       <c r="N312" s="2"/>
       <c r="O312" s="31"/>
@@ -27901,10 +27487,10 @@
       <c r="S312" s="22"/>
       <c r="T312" s="36"/>
       <c r="U312" s="40" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="V312" s="2" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="W312" s="4" t="s">
         <v>39</v>
@@ -27922,7 +27508,7 @@
         <v>199</v>
       </c>
       <c r="AF312" s="4" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="AG312" s="4"/>
       <c r="AH312" s="2"/>
@@ -27936,10 +27522,10 @@
         <v>3</v>
       </c>
       <c r="C313" s="45" t="s">
-        <v>1009</v>
+        <v>1010</v>
       </c>
       <c r="D313" s="2" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="E313" s="4">
         <v>99999</v>
@@ -27958,11 +27544,11 @@
         <v>12</v>
       </c>
       <c r="K313" s="30" t="s">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="L313" s="2"/>
       <c r="M313" s="17" t="s">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="N313" s="23" t="s">
         <v>97</v>
@@ -27974,10 +27560,10 @@
       <c r="S313" s="22"/>
       <c r="T313" s="36"/>
       <c r="U313" s="40" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="V313" s="2" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="W313" s="4" t="s">
         <v>39</v>
@@ -27994,7 +27580,7 @@
       <c r="AC313" s="2"/>
       <c r="AD313" s="2"/>
       <c r="AE313" s="2" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="AF313" s="4" t="s">
         <v>268</v>
@@ -28009,7 +27595,7 @@
       </c>
       <c r="B314" s="2"/>
       <c r="C314" s="45" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="D314" s="2"/>
       <c r="E314" s="4">
@@ -28033,7 +27619,7 @@
       </c>
       <c r="L314" s="2"/>
       <c r="M314" s="14" t="s">
-        <v>1016</v>
+        <v>1017</v>
       </c>
       <c r="N314" s="2"/>
       <c r="O314" s="31"/>
@@ -28061,10 +27647,10 @@
       </c>
       <c r="Z314" s="4"/>
       <c r="AA314" s="2" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
       <c r="AB314" s="2" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="AC314" s="2"/>
       <c r="AD314" s="2"/>
@@ -28086,10 +27672,10 @@
         <v>35</v>
       </c>
       <c r="C315" s="45" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="D315" s="2" t="s">
-        <v>1020</v>
+        <v>1021</v>
       </c>
       <c r="E315" s="4">
         <v>99999</v>
@@ -28112,7 +27698,7 @@
       </c>
       <c r="L315" s="2"/>
       <c r="M315" s="16" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="N315" s="2"/>
       <c r="O315" s="31"/>
@@ -28122,10 +27708,10 @@
       <c r="S315" s="22"/>
       <c r="T315" s="36"/>
       <c r="U315" s="40" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="V315" s="2" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="W315" s="4" t="s">
         <v>39</v>
@@ -28143,7 +27729,7 @@
         <v>199</v>
       </c>
       <c r="AF315" s="4" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="AG315" s="4"/>
       <c r="AH315" s="2"/>
@@ -28155,7 +27741,7 @@
       </c>
       <c r="B316" s="2"/>
       <c r="C316" s="45" t="s">
-        <v>1022</v>
+        <v>1023</v>
       </c>
       <c r="D316" s="2"/>
       <c r="E316" s="4">
@@ -28179,7 +27765,7 @@
       </c>
       <c r="L316" s="2"/>
       <c r="M316" s="14" t="s">
-        <v>1023</v>
+        <v>1024</v>
       </c>
       <c r="N316" s="2"/>
       <c r="O316" s="31"/>
@@ -28208,7 +27794,7 @@
         <v>398</v>
       </c>
       <c r="AB316" s="2" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="AC316" s="2"/>
       <c r="AD316" s="2"/>
@@ -28228,7 +27814,7 @@
       </c>
       <c r="B317" s="2"/>
       <c r="C317" s="45" t="s">
-        <v>1025</v>
+        <v>1026</v>
       </c>
       <c r="D317" s="2"/>
       <c r="E317" s="4">
@@ -28252,7 +27838,7 @@
       </c>
       <c r="L317" s="2"/>
       <c r="M317" s="14" t="s">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="N317" s="2"/>
       <c r="O317" s="31"/>
@@ -28304,7 +27890,7 @@
       <c r="D318" s="2"/>
       <c r="E318" s="4"/>
       <c r="F318" s="38" t="s">
-        <v>1027</v>
+        <v>1028</v>
       </c>
       <c r="G318" s="28">
         <v>42.665300000000002</v>
@@ -28323,18 +27909,12 @@
       </c>
       <c r="L318" s="2"/>
       <c r="M318" s="14" t="s">
-        <v>1028</v>
+        <v>1029</v>
       </c>
       <c r="N318" s="2"/>
-      <c r="O318" s="31">
-        <v>25.9</v>
-      </c>
-      <c r="P318" s="31">
-        <v>41.5</v>
-      </c>
-      <c r="Q318" s="31">
-        <v>34.6</v>
-      </c>
+      <c r="O318" s="31"/>
+      <c r="P318" s="31"/>
+      <c r="Q318" s="31"/>
       <c r="R318" s="50"/>
       <c r="S318" s="22" t="s">
         <v>39</v>
@@ -28394,7 +27974,7 @@
       </c>
       <c r="L319" s="2"/>
       <c r="M319" s="14" t="s">
-        <v>1029</v>
+        <v>1030</v>
       </c>
       <c r="N319" s="2"/>
       <c r="O319" s="31"/>
@@ -28467,7 +28047,7 @@
       </c>
       <c r="L320" s="2"/>
       <c r="M320" s="15" t="s">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="N320" s="2"/>
       <c r="O320" s="31"/>
@@ -28516,7 +28096,7 @@
       </c>
       <c r="B321" s="2"/>
       <c r="C321" s="45" t="s">
-        <v>1031</v>
+        <v>1032</v>
       </c>
       <c r="D321" s="2"/>
       <c r="E321" s="4">
@@ -28540,7 +28120,7 @@
       </c>
       <c r="L321" s="2"/>
       <c r="M321" s="16" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="N321" s="2"/>
       <c r="O321" s="31"/>
@@ -28550,7 +28130,7 @@
       <c r="S321" s="22"/>
       <c r="T321" s="36"/>
       <c r="U321" s="40" t="s">
-        <v>1033</v>
+        <v>1034</v>
       </c>
       <c r="V321" s="2" t="s">
         <v>219</v>
@@ -28573,7 +28153,7 @@
         <v>199</v>
       </c>
       <c r="AF321" s="4" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="AG321" s="4"/>
       <c r="AH321" s="2"/>
@@ -28587,10 +28167,10 @@
         <v>3</v>
       </c>
       <c r="C322" s="45" t="s">
-        <v>1034</v>
+        <v>1035</v>
       </c>
       <c r="D322" s="2" t="s">
-        <v>1035</v>
+        <v>1036</v>
       </c>
       <c r="E322" s="4">
         <v>99999</v>
@@ -28613,7 +28193,7 @@
       </c>
       <c r="L322" s="2"/>
       <c r="M322" s="16" t="s">
-        <v>1036</v>
+        <v>1037</v>
       </c>
       <c r="N322" s="2"/>
       <c r="O322" s="31"/>
@@ -28623,7 +28203,7 @@
       <c r="S322" s="22"/>
       <c r="T322" s="36"/>
       <c r="U322" s="40" t="s">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="V322" s="2" t="s">
         <v>219</v>
@@ -28646,7 +28226,7 @@
         <v>199</v>
       </c>
       <c r="AF322" s="4" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="AG322" s="4"/>
       <c r="AH322" s="2"/>
@@ -28658,7 +28238,7 @@
       </c>
       <c r="B323" s="2"/>
       <c r="C323" s="45" t="s">
-        <v>1038</v>
+        <v>1039</v>
       </c>
       <c r="D323" s="2"/>
       <c r="E323" s="4">
@@ -28682,7 +28262,7 @@
       </c>
       <c r="L323" s="2"/>
       <c r="M323" s="16" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="N323" s="2"/>
       <c r="O323" s="31"/>
@@ -28692,7 +28272,7 @@
       <c r="S323" s="22"/>
       <c r="T323" s="36"/>
       <c r="U323" s="40" t="s">
-        <v>1040</v>
+        <v>1041</v>
       </c>
       <c r="V323" s="2" t="s">
         <v>213</v>
@@ -28715,7 +28295,7 @@
         <v>199</v>
       </c>
       <c r="AF323" s="4" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="AG323" s="4"/>
       <c r="AH323" s="2"/>
@@ -28727,7 +28307,7 @@
       </c>
       <c r="B324" s="2"/>
       <c r="C324" s="45" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="D324" s="2"/>
       <c r="E324" s="4">
@@ -28751,7 +28331,7 @@
       </c>
       <c r="L324" s="2"/>
       <c r="M324" s="16" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="N324" s="2"/>
       <c r="O324" s="31"/>
@@ -28784,7 +28364,7 @@
         <v>199</v>
       </c>
       <c r="AF324" s="4" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="AG324" s="4"/>
       <c r="AH324" s="2"/>
@@ -28796,7 +28376,7 @@
       </c>
       <c r="B325" s="2"/>
       <c r="C325" s="45" t="s">
-        <v>1043</v>
+        <v>1044</v>
       </c>
       <c r="D325" s="2"/>
       <c r="E325" s="4">
@@ -28820,7 +28400,7 @@
       </c>
       <c r="L325" s="2"/>
       <c r="M325" s="16" t="s">
-        <v>1044</v>
+        <v>1045</v>
       </c>
       <c r="N325" s="2"/>
       <c r="O325" s="31"/>
@@ -28830,7 +28410,7 @@
       <c r="S325" s="22"/>
       <c r="T325" s="36"/>
       <c r="U325" s="40" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="V325" s="2" t="s">
         <v>219</v>
@@ -28851,7 +28431,7 @@
         <v>199</v>
       </c>
       <c r="AF325" s="4" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="AG325" s="4"/>
       <c r="AH325" s="2"/>
@@ -28865,10 +28445,10 @@
         <v>35</v>
       </c>
       <c r="C326" s="45" t="s">
-        <v>1046</v>
+        <v>1047</v>
       </c>
       <c r="D326" s="2" t="s">
-        <v>1047</v>
+        <v>1048</v>
       </c>
       <c r="E326" s="4">
         <v>99999</v>
@@ -28891,7 +28471,7 @@
       </c>
       <c r="L326" s="2"/>
       <c r="M326" s="16" t="s">
-        <v>1048</v>
+        <v>1049</v>
       </c>
       <c r="N326" s="2"/>
       <c r="O326" s="31"/>
@@ -28924,7 +28504,7 @@
         <v>199</v>
       </c>
       <c r="AF326" s="4" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="AG326" s="4"/>
       <c r="AH326" s="2"/>
@@ -28936,7 +28516,7 @@
       </c>
       <c r="B327" s="2"/>
       <c r="C327" s="45" t="s">
-        <v>1049</v>
+        <v>1050</v>
       </c>
       <c r="D327" s="2"/>
       <c r="E327" s="4">
@@ -28960,7 +28540,7 @@
       </c>
       <c r="L327" s="2"/>
       <c r="M327" s="16" t="s">
-        <v>1050</v>
+        <v>1051</v>
       </c>
       <c r="N327" s="2"/>
       <c r="O327" s="31"/>
@@ -28993,7 +28573,7 @@
         <v>199</v>
       </c>
       <c r="AF327" s="4" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="AG327" s="4"/>
       <c r="AH327" s="2"/>
@@ -29005,7 +28585,7 @@
       </c>
       <c r="B328" s="2"/>
       <c r="C328" s="45" t="s">
-        <v>1051</v>
+        <v>1052</v>
       </c>
       <c r="D328" s="2"/>
       <c r="E328" s="4">
@@ -29029,7 +28609,7 @@
       </c>
       <c r="L328" s="2"/>
       <c r="M328" s="16" t="s">
-        <v>1052</v>
+        <v>1053</v>
       </c>
       <c r="N328" s="2"/>
       <c r="O328" s="31"/>
@@ -29060,7 +28640,7 @@
         <v>199</v>
       </c>
       <c r="AF328" s="4" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="AG328" s="4"/>
       <c r="AH328" s="2"/>
@@ -29074,10 +28654,10 @@
         <v>35</v>
       </c>
       <c r="C329" s="45" t="s">
-        <v>1053</v>
+        <v>1054</v>
       </c>
       <c r="D329" s="2" t="s">
-        <v>1054</v>
+        <v>1055</v>
       </c>
       <c r="E329" s="4">
         <v>99999</v>
@@ -29096,11 +28676,11 @@
         <v>12</v>
       </c>
       <c r="K329" s="53" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="L329" s="2"/>
       <c r="M329" s="17" t="s">
-        <v>1054</v>
+        <v>1055</v>
       </c>
       <c r="N329" s="2"/>
       <c r="O329" s="31"/>
@@ -29110,7 +28690,7 @@
       <c r="S329" s="22"/>
       <c r="T329" s="36"/>
       <c r="U329" s="40" t="s">
-        <v>1055</v>
+        <v>1056</v>
       </c>
       <c r="V329" s="2"/>
       <c r="W329" s="4" t="s">
@@ -29126,14 +28706,14 @@
       <c r="AC329" s="2"/>
       <c r="AD329" s="2"/>
       <c r="AE329" s="2" t="s">
-        <v>1056</v>
+        <v>1057</v>
       </c>
       <c r="AF329" s="4" t="s">
         <v>268</v>
       </c>
       <c r="AG329" s="4"/>
       <c r="AH329" s="2" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="AI329" s="2"/>
     </row>
@@ -29146,7 +28726,7 @@
       <c r="D330" s="2"/>
       <c r="E330" s="4"/>
       <c r="F330" s="38" t="s">
-        <v>1058</v>
+        <v>1059</v>
       </c>
       <c r="G330" s="28">
         <v>33.8431</v>
@@ -29165,15 +28745,11 @@
       </c>
       <c r="L330" s="2"/>
       <c r="M330" s="14" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
       <c r="N330" s="2"/>
-      <c r="O330" s="31">
-        <v>-3.2</v>
-      </c>
-      <c r="P330" s="31">
-        <v>9.5</v>
-      </c>
+      <c r="O330" s="31"/>
+      <c r="P330" s="31"/>
       <c r="Q330" s="31"/>
       <c r="R330" s="50"/>
       <c r="S330" s="22"/>
@@ -29198,7 +28774,7 @@
         <v>365</v>
       </c>
       <c r="AB330" s="2" t="s">
-        <v>1060</v>
+        <v>1061</v>
       </c>
       <c r="AC330" s="2"/>
       <c r="AD330" s="2"/>
@@ -29220,7 +28796,7 @@
       </c>
       <c r="B331" s="2"/>
       <c r="C331" s="45" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="D331" s="2"/>
       <c r="E331" s="4">
@@ -29244,7 +28820,7 @@
       </c>
       <c r="L331" s="2"/>
       <c r="M331" s="14" t="s">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="N331" s="2"/>
       <c r="O331" s="31"/>
@@ -29281,7 +28857,7 @@
       </c>
       <c r="AG331" s="4"/>
       <c r="AH331" s="2" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="AI331" s="2"/>
     </row>
@@ -29294,7 +28870,7 @@
       <c r="D332" s="2"/>
       <c r="E332" s="4"/>
       <c r="F332" s="38" t="s">
-        <v>1064</v>
+        <v>1065</v>
       </c>
       <c r="G332" s="28">
         <v>31.095800000000001</v>
@@ -29313,7 +28889,7 @@
       </c>
       <c r="L332" s="2"/>
       <c r="M332" s="14" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
       <c r="N332" s="2"/>
       <c r="O332" s="31"/>
@@ -29339,10 +28915,10 @@
       </c>
       <c r="Z332" s="4"/>
       <c r="AA332" s="2" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="AB332" s="2" t="s">
-        <v>1067</v>
+        <v>1068</v>
       </c>
       <c r="AC332" s="2"/>
       <c r="AD332" s="2"/>
@@ -29365,7 +28941,7 @@
       <c r="D333" s="2"/>
       <c r="E333" s="4"/>
       <c r="F333" s="38" t="s">
-        <v>1068</v>
+        <v>1069</v>
       </c>
       <c r="G333" s="28"/>
       <c r="H333" s="28"/>
@@ -29378,7 +28954,7 @@
       </c>
       <c r="L333" s="2"/>
       <c r="M333" s="14" t="s">
-        <v>1069</v>
+        <v>1070</v>
       </c>
       <c r="N333" s="2"/>
       <c r="O333" s="31"/>
@@ -29404,10 +28980,10 @@
       </c>
       <c r="Z333" s="4"/>
       <c r="AA333" s="2" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="AB333" s="2" t="s">
-        <v>1067</v>
+        <v>1068</v>
       </c>
       <c r="AC333" s="2"/>
       <c r="AD333" s="2"/>
@@ -29430,7 +29006,7 @@
       <c r="D334" s="2"/>
       <c r="E334" s="4"/>
       <c r="F334" s="38" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
       <c r="G334" s="28">
         <v>49.072200000000002</v>
@@ -29449,7 +29025,7 @@
       </c>
       <c r="L334" s="2"/>
       <c r="M334" s="14" t="s">
-        <v>1071</v>
+        <v>1072</v>
       </c>
       <c r="N334" s="2"/>
       <c r="O334" s="31"/>
@@ -29498,7 +29074,7 @@
       </c>
       <c r="B335" s="2"/>
       <c r="C335" s="45" t="s">
-        <v>1072</v>
+        <v>1073</v>
       </c>
       <c r="D335" s="2"/>
       <c r="E335" s="4">
@@ -29522,7 +29098,7 @@
       </c>
       <c r="L335" s="2"/>
       <c r="M335" s="16" t="s">
-        <v>1073</v>
+        <v>1074</v>
       </c>
       <c r="N335" s="2"/>
       <c r="O335" s="31"/>
@@ -29555,7 +29131,7 @@
         <v>199</v>
       </c>
       <c r="AF335" s="4" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="AG335" s="4"/>
       <c r="AH335" s="2"/>
@@ -29570,7 +29146,7 @@
       <c r="D336" s="2"/>
       <c r="E336" s="4"/>
       <c r="F336" s="38" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="G336" s="28"/>
       <c r="H336" s="28"/>
@@ -29583,7 +29159,7 @@
       </c>
       <c r="L336" s="2"/>
       <c r="M336" s="14" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="N336" s="2"/>
       <c r="O336" s="31"/>
@@ -29609,10 +29185,10 @@
       </c>
       <c r="Z336" s="4"/>
       <c r="AA336" s="2" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="AB336" s="2" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="AC336" s="2"/>
       <c r="AD336" s="2"/>
@@ -29632,7 +29208,7 @@
       </c>
       <c r="B337" s="2"/>
       <c r="C337" s="45" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="D337" s="2"/>
       <c r="E337" s="4">
@@ -29656,7 +29232,7 @@
       </c>
       <c r="L337" s="2"/>
       <c r="M337" s="14" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="N337" s="2"/>
       <c r="O337" s="31"/>
@@ -29704,7 +29280,7 @@
       <c r="D338" s="2"/>
       <c r="E338" s="4"/>
       <c r="F338" s="38" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="G338" s="28">
         <v>42.685600000000001</v>
@@ -29723,7 +29299,7 @@
       </c>
       <c r="L338" s="2"/>
       <c r="M338" s="14" t="s">
-        <v>1080</v>
+        <v>1081</v>
       </c>
       <c r="N338" s="2"/>
       <c r="O338" s="31"/>
@@ -29775,7 +29351,7 @@
       <c r="D339" s="2"/>
       <c r="E339" s="4"/>
       <c r="F339" s="38" t="s">
-        <v>1081</v>
+        <v>1082</v>
       </c>
       <c r="G339" s="28">
         <v>42.904400000000003</v>
@@ -29794,7 +29370,7 @@
       </c>
       <c r="L339" s="2"/>
       <c r="M339" s="14" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="N339" s="2"/>
       <c r="O339" s="31"/>
@@ -29846,7 +29422,7 @@
       <c r="D340" s="2"/>
       <c r="E340" s="4"/>
       <c r="F340" s="38" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="G340" s="28">
         <v>52.746400000000001</v>
@@ -29865,7 +29441,7 @@
       </c>
       <c r="L340" s="2"/>
       <c r="M340" s="14" t="s">
-        <v>1084</v>
+        <v>1085</v>
       </c>
       <c r="N340" s="2"/>
       <c r="O340" s="31"/>
@@ -29917,7 +29493,7 @@
       <c r="D341" s="2"/>
       <c r="E341" s="4"/>
       <c r="F341" s="38" t="s">
-        <v>1085</v>
+        <v>1086</v>
       </c>
       <c r="G341" s="28">
         <v>42.716000000000001</v>
@@ -29936,21 +29512,17 @@
       </c>
       <c r="L341" s="2"/>
       <c r="M341" s="14" t="s">
-        <v>1086</v>
+        <v>1087</v>
       </c>
       <c r="N341" s="2"/>
-      <c r="O341" s="31">
-        <v>-2.6</v>
-      </c>
-      <c r="P341" s="31">
-        <v>20.2</v>
-      </c>
+      <c r="O341" s="31"/>
+      <c r="P341" s="31"/>
       <c r="Q341" s="31"/>
       <c r="R341" s="50"/>
       <c r="S341" s="22"/>
       <c r="T341" s="36"/>
       <c r="U341" s="40" t="s">
-        <v>1087</v>
+        <v>638</v>
       </c>
       <c r="V341" s="2" t="s">
         <v>383</v>
@@ -32424,7 +31996,7 @@
         <v>31137</v>
       </c>
       <c r="D2" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="E2">
         <v>99999</v>
@@ -32460,13 +32032,13 @@
         <v>199</v>
       </c>
       <c r="AC2" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="AE2" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="AF2" s="1" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
     </row>
     <row r="3" spans="1:32" ht="27.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -32480,7 +32052,7 @@
         <v>24688</v>
       </c>
       <c r="D3" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="E3">
         <v>99999</v>
@@ -32501,7 +32073,7 @@
         <v>1091</v>
       </c>
       <c r="M3" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="R3" t="s">
         <v>39</v>
@@ -32519,13 +32091,13 @@
         <v>199</v>
       </c>
       <c r="AC3" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="AE3" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="AF3" s="1" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
     </row>
     <row r="4" spans="1:32" x14ac:dyDescent="0.4">
@@ -32539,7 +32111,7 @@
         <v>24585</v>
       </c>
       <c r="D4" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="E4">
         <v>99999</v>
@@ -32557,7 +32129,7 @@
         <v>15</v>
       </c>
       <c r="M4" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="R4" t="s">
         <v>39</v>
@@ -32575,10 +32147,10 @@
         <v>199</v>
       </c>
       <c r="AC4" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="AE4" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
     </row>
     <row r="5" spans="1:32" x14ac:dyDescent="0.4">

--- a/气象/For_Python_站点信息和记录.xlsx
+++ b/气象/For_Python_站点信息和记录.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\文档\GIT SYNC\default\气象\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA2C3DA3-B49E-45F7-8C43-B5420C3FE050}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB1112A2-E379-411E-9D67-B5F44C0C5272}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4485" uniqueCount="1099">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4485" uniqueCount="1106">
   <si>
     <t>id</t>
   </si>
@@ -420,6 +420,9 @@
     <t>阿尔布拉格</t>
   </si>
   <si>
+    <t>44222</t>
+  </si>
+  <si>
     <t>车车尔勒格</t>
   </si>
   <si>
@@ -507,6 +510,9 @@
     <t>大乌拉</t>
   </si>
   <si>
+    <t>44220</t>
+  </si>
+  <si>
     <t>讷木勒格</t>
   </si>
   <si>
@@ -652,9 +658,6 @@
   </si>
   <si>
     <t>1952-12-21</t>
-  </si>
-  <si>
-    <t>谢列姆贾山区</t>
   </si>
   <si>
     <t>谢列姆贾盆地</t>
@@ -766,9 +769,6 @@
     <t>克孜勒</t>
   </si>
   <si>
-    <t>叶尼塞河&lt;br&gt;图瓦</t>
-  </si>
-  <si>
     <t>叶尼塞河</t>
   </si>
   <si>
@@ -3321,11 +3321,39 @@
     <t>特尼河试验站</t>
   </si>
   <si>
-    <t>44220</t>
+    <t>谢列姆贾河&lt;br&gt;阿穆尔</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>44222</t>
+    <t>谢列姆贾沿山河谷&lt;br&gt;哈巴罗夫斯克</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>布列亚河 布列亚山</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>小叶尼塞河&lt;br&gt;图瓦</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>叶尼塞河&lt;br&gt;图瓦首府 人口10万+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>马尔卡湖&lt;br&gt;阿尔泰山</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>额尔齐斯河支流&lt;br&gt;东哈萨克斯坦州</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>额尔齐斯河支流&lt;br&gt;阿尔泰山</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>呼伦贝尔</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -4086,8 +4114,8 @@
     <col min="26" max="26" width="18.59765625" style="8" customWidth="1"/>
     <col min="27" max="31" width="12.59765625" style="5" customWidth="1"/>
     <col min="32" max="33" width="12.59765625" style="8" customWidth="1"/>
-    <col min="34" max="683" width="12.59765625" style="5" customWidth="1"/>
-    <col min="684" max="16384" width="12.59765625" style="5"/>
+    <col min="34" max="684" width="12.59765625" style="5" customWidth="1"/>
+    <col min="685" max="16384" width="12.59765625" style="5"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:35" s="11" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -4236,9 +4264,15 @@
       <c r="N2" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="O2" s="31"/>
-      <c r="P2" s="31"/>
-      <c r="Q2" s="31"/>
+      <c r="O2" s="31">
+        <v>8.3000000000000007</v>
+      </c>
+      <c r="P2" s="31">
+        <v>26.4</v>
+      </c>
+      <c r="Q2" s="31">
+        <v>16.690000000000001</v>
+      </c>
       <c r="R2" s="50"/>
       <c r="S2" s="22" t="s">
         <v>39</v>
@@ -4311,8 +4345,12 @@
       <c r="N3" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="O3" s="31"/>
-      <c r="P3" s="31"/>
+      <c r="O3" s="31">
+        <v>6.5</v>
+      </c>
+      <c r="P3" s="31">
+        <v>26.1</v>
+      </c>
       <c r="Q3" s="31"/>
       <c r="R3" s="50" t="s">
         <v>47</v>
@@ -4388,8 +4426,12 @@
       <c r="N4" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="O4" s="31"/>
-      <c r="P4" s="31"/>
+      <c r="O4" s="31">
+        <v>5.4</v>
+      </c>
+      <c r="P4" s="31">
+        <v>24.3</v>
+      </c>
       <c r="Q4" s="31"/>
       <c r="R4" s="50" t="s">
         <v>51</v>
@@ -4534,9 +4576,15 @@
       <c r="N6" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="O6" s="31"/>
-      <c r="P6" s="31"/>
-      <c r="Q6" s="31"/>
+      <c r="O6" s="31">
+        <v>-1.1000000000000001</v>
+      </c>
+      <c r="P6" s="31">
+        <v>20.5</v>
+      </c>
+      <c r="Q6" s="31">
+        <v>9.24</v>
+      </c>
       <c r="R6" s="52" t="s">
         <v>59</v>
       </c>
@@ -4609,8 +4657,12 @@
       <c r="N7" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="O7" s="31"/>
-      <c r="P7" s="31"/>
+      <c r="O7" s="31">
+        <v>0.4</v>
+      </c>
+      <c r="P7" s="31">
+        <v>16.2</v>
+      </c>
       <c r="Q7" s="31"/>
       <c r="R7" s="50"/>
       <c r="S7" s="22"/>
@@ -4688,9 +4740,15 @@
         <v>67</v>
       </c>
       <c r="N8" s="2"/>
-      <c r="O8" s="31"/>
-      <c r="P8" s="31"/>
-      <c r="Q8" s="31"/>
+      <c r="O8" s="31">
+        <v>4.5</v>
+      </c>
+      <c r="P8" s="31">
+        <v>22.3</v>
+      </c>
+      <c r="Q8" s="31">
+        <v>13.61</v>
+      </c>
       <c r="R8" s="50"/>
       <c r="S8" s="22" t="s">
         <v>39</v>
@@ -4767,9 +4825,15 @@
         <v>72</v>
       </c>
       <c r="N9" s="2"/>
-      <c r="O9" s="31"/>
-      <c r="P9" s="31"/>
-      <c r="Q9" s="31"/>
+      <c r="O9" s="31">
+        <v>7.8</v>
+      </c>
+      <c r="P9" s="31">
+        <v>24.5</v>
+      </c>
+      <c r="Q9" s="31">
+        <v>16.16</v>
+      </c>
       <c r="R9" s="50"/>
       <c r="S9" s="22" t="s">
         <v>39</v>
@@ -4850,9 +4914,15 @@
       <c r="N10" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="O10" s="31"/>
-      <c r="P10" s="31"/>
-      <c r="Q10" s="31"/>
+      <c r="O10" s="31">
+        <v>0.1</v>
+      </c>
+      <c r="P10" s="31">
+        <v>22.8</v>
+      </c>
+      <c r="Q10" s="31">
+        <v>12.32</v>
+      </c>
       <c r="R10" s="50"/>
       <c r="S10" s="22" t="s">
         <v>39</v>
@@ -4931,9 +5001,15 @@
       <c r="N11" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="O11" s="31"/>
-      <c r="P11" s="31"/>
-      <c r="Q11" s="31"/>
+      <c r="O11" s="31">
+        <v>-0.8</v>
+      </c>
+      <c r="P11" s="31">
+        <v>19.3</v>
+      </c>
+      <c r="Q11" s="31">
+        <v>9.8000000000000007</v>
+      </c>
       <c r="R11" s="50" t="s">
         <v>77</v>
       </c>
@@ -5012,9 +5088,15 @@
         <v>80</v>
       </c>
       <c r="N12" s="2"/>
-      <c r="O12" s="31"/>
-      <c r="P12" s="31"/>
-      <c r="Q12" s="31"/>
+      <c r="O12" s="31">
+        <v>1.5</v>
+      </c>
+      <c r="P12" s="31">
+        <v>19.100000000000001</v>
+      </c>
+      <c r="Q12" s="31">
+        <v>10.4</v>
+      </c>
       <c r="R12" s="50" t="s">
         <v>81</v>
       </c>
@@ -5095,9 +5177,15 @@
       <c r="N13" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="O13" s="31"/>
-      <c r="P13" s="31"/>
-      <c r="Q13" s="31"/>
+      <c r="O13" s="31">
+        <v>0.4</v>
+      </c>
+      <c r="P13" s="31">
+        <v>17.2</v>
+      </c>
+      <c r="Q13" s="31">
+        <v>8.84</v>
+      </c>
       <c r="R13" s="50" t="s">
         <v>84</v>
       </c>
@@ -5176,9 +5264,15 @@
         <v>86</v>
       </c>
       <c r="N14" s="2"/>
-      <c r="O14" s="31"/>
-      <c r="P14" s="31"/>
-      <c r="Q14" s="31"/>
+      <c r="O14" s="31">
+        <v>5.4</v>
+      </c>
+      <c r="P14" s="31">
+        <v>19</v>
+      </c>
+      <c r="Q14" s="31">
+        <v>12.28</v>
+      </c>
       <c r="R14" s="50"/>
       <c r="S14" s="22" t="s">
         <v>39</v>
@@ -5259,9 +5353,15 @@
         <v>91</v>
       </c>
       <c r="N15" s="2"/>
-      <c r="O15" s="31"/>
-      <c r="P15" s="31"/>
-      <c r="Q15" s="31"/>
+      <c r="O15" s="31">
+        <v>3.4</v>
+      </c>
+      <c r="P15" s="31">
+        <v>16.3</v>
+      </c>
+      <c r="Q15" s="31">
+        <v>10.55</v>
+      </c>
       <c r="R15" s="50"/>
       <c r="S15" s="22" t="s">
         <v>39</v>
@@ -5338,9 +5438,15 @@
         <v>94</v>
       </c>
       <c r="N16" s="2"/>
-      <c r="O16" s="31"/>
-      <c r="P16" s="31"/>
-      <c r="Q16" s="31"/>
+      <c r="O16" s="31">
+        <v>1.8</v>
+      </c>
+      <c r="P16" s="31">
+        <v>19.2</v>
+      </c>
+      <c r="Q16" s="31">
+        <v>11.34</v>
+      </c>
       <c r="R16" s="50"/>
       <c r="S16" s="22"/>
       <c r="T16" s="36"/>
@@ -6674,7 +6780,7 @@
       </c>
       <c r="B35" s="2"/>
       <c r="C35" s="45" t="s">
-        <v>1098</v>
+        <v>131</v>
       </c>
       <c r="D35" s="2"/>
       <c r="E35" s="4"/>
@@ -6698,7 +6804,7 @@
       </c>
       <c r="L35" s="3"/>
       <c r="M35" s="15" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="31"/>
@@ -6767,7 +6873,7 @@
       </c>
       <c r="L36" s="3"/>
       <c r="M36" s="15" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="31"/>
@@ -6836,7 +6942,7 @@
       </c>
       <c r="L37" s="3"/>
       <c r="M37" s="15" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="31"/>
@@ -6905,7 +7011,7 @@
       </c>
       <c r="L38" s="3"/>
       <c r="M38" s="15" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="31"/>
@@ -6974,7 +7080,7 @@
       </c>
       <c r="L39" s="3"/>
       <c r="M39" s="15" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="N39" s="3"/>
       <c r="O39" s="31"/>
@@ -7041,7 +7147,7 @@
       </c>
       <c r="L40" s="3"/>
       <c r="M40" s="15" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="N40" s="3"/>
       <c r="O40" s="31"/>
@@ -7051,7 +7157,7 @@
       <c r="S40" s="22"/>
       <c r="T40" s="36"/>
       <c r="U40" s="40" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="V40" s="2" t="s">
         <v>69</v>
@@ -7078,7 +7184,7 @@
       </c>
       <c r="AG40" s="4"/>
       <c r="AH40" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="AI40" s="2"/>
     </row>
@@ -7110,7 +7216,7 @@
       </c>
       <c r="L41" s="3"/>
       <c r="M41" s="15" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="31"/>
@@ -7177,7 +7283,7 @@
       </c>
       <c r="L42" s="3"/>
       <c r="M42" s="15" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="31"/>
@@ -7187,7 +7293,7 @@
       <c r="S42" s="22"/>
       <c r="T42" s="36"/>
       <c r="U42" s="40" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="V42" s="2" t="s">
         <v>69</v>
@@ -7214,7 +7320,7 @@
       </c>
       <c r="AG42" s="4"/>
       <c r="AH42" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="AI42" s="2"/>
     </row>
@@ -7246,7 +7352,7 @@
       </c>
       <c r="L43" s="3"/>
       <c r="M43" s="15" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="N43" s="2" t="s">
         <v>38</v>
@@ -7258,7 +7364,7 @@
       <c r="S43" s="22"/>
       <c r="T43" s="36"/>
       <c r="U43" s="40" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="V43" s="2" t="s">
         <v>41</v>
@@ -7285,7 +7391,7 @@
       </c>
       <c r="AG43" s="4"/>
       <c r="AH43" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="AI43" s="2"/>
     </row>
@@ -7317,7 +7423,7 @@
       </c>
       <c r="L44" s="3"/>
       <c r="M44" s="15" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="31"/>
@@ -7369,7 +7475,7 @@
         <v>44215</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E45" s="4">
         <v>99999</v>
@@ -7394,7 +7500,7 @@
       </c>
       <c r="L45" s="3"/>
       <c r="M45" s="15" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="31"/>
@@ -7431,7 +7537,7 @@
       </c>
       <c r="AG45" s="4"/>
       <c r="AH45" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="AI45" s="2"/>
     </row>
@@ -7463,7 +7569,7 @@
       </c>
       <c r="L46" s="3"/>
       <c r="M46" s="15" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="31"/>
@@ -7500,7 +7606,7 @@
       </c>
       <c r="AG46" s="4"/>
       <c r="AH46" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="AI46" s="2"/>
     </row>
@@ -7532,7 +7638,7 @@
       </c>
       <c r="L47" s="3"/>
       <c r="M47" s="15" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="31"/>
@@ -7569,7 +7675,7 @@
       </c>
       <c r="AG47" s="4"/>
       <c r="AH47" s="2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AI47" s="2"/>
     </row>
@@ -7584,7 +7690,7 @@
         <v>44213</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E48" s="4">
         <v>99999</v>
@@ -7609,7 +7715,7 @@
       </c>
       <c r="L48" s="3"/>
       <c r="M48" s="15" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="31"/>
@@ -7715,7 +7821,7 @@
       </c>
       <c r="AG49" s="4"/>
       <c r="AH49" s="2" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="AI49" s="2"/>
     </row>
@@ -7747,7 +7853,7 @@
       </c>
       <c r="L50" s="3"/>
       <c r="M50" s="15" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="31"/>
@@ -7814,7 +7920,7 @@
       </c>
       <c r="L51" s="3"/>
       <c r="M51" s="15" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="31"/>
@@ -7881,7 +7987,7 @@
       </c>
       <c r="L52" s="3"/>
       <c r="M52" s="15" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="31"/>
@@ -7918,7 +8024,7 @@
       </c>
       <c r="AG52" s="4"/>
       <c r="AH52" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AI52" s="2"/>
     </row>
@@ -7950,7 +8056,7 @@
       </c>
       <c r="L53" s="3"/>
       <c r="M53" s="15" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="31"/>
@@ -7997,7 +8103,7 @@
       </c>
       <c r="B54" s="2"/>
       <c r="C54" s="45" t="s">
-        <v>1097</v>
+        <v>161</v>
       </c>
       <c r="D54" s="2"/>
       <c r="E54" s="4"/>
@@ -8021,7 +8127,7 @@
       </c>
       <c r="L54" s="3"/>
       <c r="M54" s="15" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="31"/>
@@ -8058,7 +8164,7 @@
       </c>
       <c r="AG54" s="4"/>
       <c r="AH54" s="2" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="AI54" s="2"/>
     </row>
@@ -8090,7 +8196,7 @@
       </c>
       <c r="L55" s="3"/>
       <c r="M55" s="15" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="31"/>
@@ -8127,7 +8233,7 @@
       </c>
       <c r="AG55" s="4"/>
       <c r="AH55" s="2" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="AI55" s="2"/>
     </row>
@@ -8159,7 +8265,7 @@
       </c>
       <c r="L56" s="3"/>
       <c r="M56" s="15" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="31"/>
@@ -8196,7 +8302,7 @@
       </c>
       <c r="AG56" s="4"/>
       <c r="AH56" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AI56" s="2"/>
     </row>
@@ -8228,7 +8334,7 @@
       </c>
       <c r="L57" s="3"/>
       <c r="M57" s="15" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="31"/>
@@ -8295,7 +8401,7 @@
       </c>
       <c r="L58" s="3"/>
       <c r="M58" s="15" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="31"/>
@@ -8364,7 +8470,7 @@
       </c>
       <c r="L59" s="3"/>
       <c r="M59" s="15" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="31"/>
@@ -8374,7 +8480,7 @@
       <c r="S59" s="22"/>
       <c r="T59" s="36"/>
       <c r="U59" s="40" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="V59" s="2" t="s">
         <v>53</v>
@@ -8433,7 +8539,7 @@
       </c>
       <c r="L60" s="3"/>
       <c r="M60" s="15" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="31"/>
@@ -8470,7 +8576,7 @@
       </c>
       <c r="AG60" s="4"/>
       <c r="AH60" s="2" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="AI60" s="2"/>
     </row>
@@ -8502,7 +8608,7 @@
       </c>
       <c r="L61" s="3"/>
       <c r="M61" s="15" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="N61" s="23" t="s">
         <v>97</v>
@@ -8514,10 +8620,10 @@
       <c r="S61" s="22"/>
       <c r="T61" s="36"/>
       <c r="U61" s="40" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="V61" s="2" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="W61" s="4" t="s">
         <v>39</v>
@@ -8583,10 +8689,10 @@
       <c r="S62" s="22"/>
       <c r="T62" s="36"/>
       <c r="U62" s="40" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="V62" s="2" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="W62" s="4" t="s">
         <v>39</v>
@@ -8625,7 +8731,7 @@
         <v>44263</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="E63" s="4">
         <v>99999</v>
@@ -8660,10 +8766,10 @@
       <c r="S63" s="22"/>
       <c r="T63" s="36"/>
       <c r="U63" s="40" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="V63" s="2" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="W63" s="4" t="s">
         <v>39</v>
@@ -8719,7 +8825,7 @@
       </c>
       <c r="L64" s="3"/>
       <c r="M64" s="15" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="31"/>
@@ -8729,10 +8835,10 @@
       <c r="S64" s="22"/>
       <c r="T64" s="36"/>
       <c r="U64" s="40" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="V64" s="2" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="W64" s="4" t="s">
         <v>39</v>
@@ -8788,7 +8894,7 @@
       </c>
       <c r="L65" s="3"/>
       <c r="M65" s="15" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="31"/>
@@ -8798,10 +8904,10 @@
       <c r="S65" s="22"/>
       <c r="T65" s="36"/>
       <c r="U65" s="40" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="V65" s="2" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="W65" s="4" t="s">
         <v>39</v>
@@ -8857,7 +8963,7 @@
       </c>
       <c r="L66" s="3"/>
       <c r="M66" s="15" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="31"/>
@@ -8867,10 +8973,10 @@
       <c r="S66" s="22"/>
       <c r="T66" s="36"/>
       <c r="U66" s="40" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="V66" s="2" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="W66" s="4" t="s">
         <v>39</v>
@@ -8894,7 +9000,7 @@
       </c>
       <c r="AG66" s="4"/>
       <c r="AH66" s="2" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="AI66" s="2"/>
     </row>
@@ -8926,7 +9032,7 @@
       </c>
       <c r="L67" s="3"/>
       <c r="M67" s="15" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="31"/>
@@ -8936,10 +9042,10 @@
       <c r="S67" s="22"/>
       <c r="T67" s="36"/>
       <c r="U67" s="40" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="V67" s="2" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="W67" s="4" t="s">
         <v>39</v>
@@ -8978,7 +9084,7 @@
         <v>44229</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="E68" s="4">
         <v>99999</v>
@@ -9003,7 +9109,7 @@
       </c>
       <c r="L68" s="3"/>
       <c r="M68" s="15" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="31"/>
@@ -9013,10 +9119,10 @@
       <c r="S68" s="22"/>
       <c r="T68" s="36"/>
       <c r="U68" s="40" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="V68" s="2" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="W68" s="4" t="s">
         <v>39</v>
@@ -9072,7 +9178,7 @@
       </c>
       <c r="L69" s="3"/>
       <c r="M69" s="15" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="31"/>
@@ -9082,10 +9188,10 @@
       <c r="S69" s="22"/>
       <c r="T69" s="36"/>
       <c r="U69" s="40" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="V69" s="2" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="W69" s="4" t="s">
         <v>39</v>
@@ -9141,7 +9247,7 @@
       </c>
       <c r="L70" s="3"/>
       <c r="M70" s="15" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="31"/>
@@ -9151,10 +9257,10 @@
       <c r="S70" s="22"/>
       <c r="T70" s="36"/>
       <c r="U70" s="40" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="V70" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="W70" s="4" t="s">
         <v>39</v>
@@ -9210,7 +9316,7 @@
       </c>
       <c r="L71" s="3"/>
       <c r="M71" s="15" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" s="31"/>
@@ -9220,10 +9326,10 @@
       <c r="S71" s="22"/>
       <c r="T71" s="36"/>
       <c r="U71" s="40" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="V71" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="W71" s="4" t="s">
         <v>39</v>
@@ -9279,7 +9385,7 @@
       </c>
       <c r="L72" s="3"/>
       <c r="M72" s="15" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" s="31"/>
@@ -9289,10 +9395,10 @@
       <c r="S72" s="22"/>
       <c r="T72" s="36"/>
       <c r="U72" s="40" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="V72" s="2" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="W72" s="4" t="s">
         <v>39</v>
@@ -9348,7 +9454,7 @@
       </c>
       <c r="L73" s="3"/>
       <c r="M73" s="15" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" s="31"/>
@@ -9358,10 +9464,10 @@
       <c r="S73" s="22"/>
       <c r="T73" s="36"/>
       <c r="U73" s="40" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="V73" s="2" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="W73" s="4" t="s">
         <v>39</v>
@@ -9417,7 +9523,7 @@
       </c>
       <c r="L74" s="3"/>
       <c r="M74" s="15" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" s="31"/>
@@ -9427,10 +9533,10 @@
       <c r="S74" s="22"/>
       <c r="T74" s="36"/>
       <c r="U74" s="40" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="V74" s="2" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="W74" s="4" t="s">
         <v>39</v>
@@ -9464,7 +9570,7 @@
         <v>35</v>
       </c>
       <c r="C75" s="45" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="D75" s="2"/>
       <c r="E75" s="4">
@@ -9490,7 +9596,7 @@
       </c>
       <c r="L75" s="3"/>
       <c r="M75" s="15" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" s="31"/>
@@ -9540,7 +9646,7 @@
         <v>31702</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="E76" s="4">
         <v>99999</v>
@@ -9559,11 +9665,11 @@
         <v>15</v>
       </c>
       <c r="K76" s="30" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="L76" s="3"/>
       <c r="M76" s="16" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="N76" s="2"/>
       <c r="O76" s="31"/>
@@ -9573,10 +9679,10 @@
       <c r="S76" s="22"/>
       <c r="T76" s="36"/>
       <c r="U76" s="40" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="V76" s="2" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="W76" s="4" t="s">
         <v>39</v>
@@ -9593,16 +9699,16 @@
       <c r="AC76" s="2"/>
       <c r="AD76" s="2"/>
       <c r="AE76" s="2" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="AF76" s="4" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="AG76" s="4" t="s">
         <v>39</v>
       </c>
       <c r="AH76" s="2" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="AI76" s="2"/>
     </row>
@@ -9617,7 +9723,7 @@
         <v>31532</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="E77" s="4">
         <v>99999</v>
@@ -9636,11 +9742,11 @@
         <v>15</v>
       </c>
       <c r="K77" s="30" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="L77" s="3"/>
       <c r="M77" s="16" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="N77" s="2" t="s">
         <v>38</v>
@@ -9652,10 +9758,10 @@
       <c r="S77" s="22"/>
       <c r="T77" s="36"/>
       <c r="U77" s="40" t="s">
-        <v>201</v>
+        <v>1099</v>
       </c>
       <c r="V77" s="2" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="W77" s="4" t="s">
         <v>39</v>
@@ -9672,16 +9778,16 @@
       <c r="AC77" s="2"/>
       <c r="AD77" s="2"/>
       <c r="AE77" s="2" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="AF77" s="4" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="AG77" s="4" t="s">
         <v>39</v>
       </c>
       <c r="AH77" s="2" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="AI77" s="2"/>
     </row>
@@ -9696,7 +9802,7 @@
         <v>31478</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="E78" s="4">
         <v>99999</v>
@@ -9715,30 +9821,36 @@
         <v>15</v>
       </c>
       <c r="K78" s="30" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="L78" s="42"/>
       <c r="M78" s="16" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="N78" s="23" t="s">
         <v>97</v>
       </c>
-      <c r="O78" s="31"/>
-      <c r="P78" s="31"/>
-      <c r="Q78" s="31"/>
+      <c r="O78" s="31">
+        <v>6.3</v>
+      </c>
+      <c r="P78" s="31">
+        <v>17</v>
+      </c>
+      <c r="Q78" s="31">
+        <v>10.85</v>
+      </c>
       <c r="R78" s="50" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="S78" s="22" t="s">
         <v>39</v>
       </c>
       <c r="T78" s="36"/>
       <c r="U78" s="40" t="s">
-        <v>209</v>
+        <v>1098</v>
       </c>
       <c r="V78" s="2" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="W78" s="4" t="s">
         <v>39</v>
@@ -9755,16 +9867,16 @@
       <c r="AC78" s="2"/>
       <c r="AD78" s="2"/>
       <c r="AE78" s="2" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="AF78" s="4" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="AG78" s="4" t="s">
         <v>39</v>
       </c>
       <c r="AH78" s="2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="AI78" s="2"/>
     </row>
@@ -9779,7 +9891,7 @@
         <v>31329</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E79" s="4">
         <v>99999</v>
@@ -9798,11 +9910,11 @@
         <v>12</v>
       </c>
       <c r="K79" s="30" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="L79" s="3"/>
       <c r="M79" s="16" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" s="31"/>
@@ -9812,10 +9924,10 @@
       <c r="S79" s="22"/>
       <c r="T79" s="36"/>
       <c r="U79" s="40" t="s">
-        <v>213</v>
+        <v>1097</v>
       </c>
       <c r="V79" s="2" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="W79" s="4" t="s">
         <v>39</v>
@@ -9832,16 +9944,16 @@
       <c r="AC79" s="2"/>
       <c r="AD79" s="2"/>
       <c r="AE79" s="2" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="AF79" s="4" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="AG79" s="4" t="s">
         <v>39</v>
       </c>
       <c r="AH79" s="2" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="AI79" s="2"/>
     </row>
@@ -9856,7 +9968,7 @@
         <v>31348</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="E80" s="4">
         <v>99999</v>
@@ -9875,11 +9987,11 @@
         <v>15</v>
       </c>
       <c r="K80" s="30" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="L80" s="3"/>
       <c r="M80" s="16" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="N80" s="3" t="s">
         <v>50</v>
@@ -9891,10 +10003,10 @@
       <c r="S80" s="22"/>
       <c r="T80" s="36"/>
       <c r="U80" s="40" t="s">
-        <v>204</v>
+        <v>1098</v>
       </c>
       <c r="V80" s="2" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="W80" s="4" t="s">
         <v>39</v>
@@ -9911,16 +10023,16 @@
       <c r="AC80" s="2"/>
       <c r="AD80" s="2"/>
       <c r="AE80" s="2" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="AF80" s="4" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="AG80" s="4" t="s">
         <v>39</v>
       </c>
       <c r="AH80" s="2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="AI80" s="2"/>
     </row>
@@ -9935,7 +10047,7 @@
         <v>30673</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="E81" s="4">
         <v>99999</v>
@@ -9954,11 +10066,11 @@
         <v>12</v>
       </c>
       <c r="K81" s="30" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="L81" s="3"/>
       <c r="M81" s="16" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="N81" s="2"/>
       <c r="O81" s="31"/>
@@ -9968,10 +10080,10 @@
       <c r="S81" s="22"/>
       <c r="T81" s="36"/>
       <c r="U81" s="40" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="V81" s="2" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="W81" s="4" t="s">
         <v>39</v>
@@ -9988,16 +10100,16 @@
       <c r="AC81" s="2"/>
       <c r="AD81" s="2"/>
       <c r="AE81" s="2" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="AF81" s="4" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="AG81" s="4" t="s">
         <v>39</v>
       </c>
       <c r="AH81" s="2" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AI81" s="2"/>
     </row>
@@ -10012,7 +10124,7 @@
         <v>30565</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="E82" s="4">
         <v>99999</v>
@@ -10031,28 +10143,34 @@
         <v>12</v>
       </c>
       <c r="K82" s="30" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="L82" s="3"/>
       <c r="M82" s="16" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="N82" s="3" t="s">
-        <v>223</v>
-      </c>
-      <c r="O82" s="31"/>
-      <c r="P82" s="31"/>
-      <c r="Q82" s="31"/>
+        <v>224</v>
+      </c>
+      <c r="O82" s="31">
+        <v>10.8</v>
+      </c>
+      <c r="P82" s="31">
+        <v>21.7</v>
+      </c>
+      <c r="Q82" s="31">
+        <v>15.15</v>
+      </c>
       <c r="R82" s="50"/>
       <c r="S82" s="22" t="s">
         <v>39</v>
       </c>
       <c r="T82" s="36"/>
       <c r="U82" s="40" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="V82" s="2" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="W82" s="4" t="s">
         <v>39</v>
@@ -10069,19 +10187,19 @@
       <c r="AC82" s="2"/>
       <c r="AD82" s="2"/>
       <c r="AE82" s="2" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="AF82" s="4" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="AG82" s="4" t="s">
         <v>39</v>
       </c>
       <c r="AH82" s="2" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="AI82" s="6" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="83" spans="1:35" ht="24" customHeight="1" x14ac:dyDescent="0.4">
@@ -10095,7 +10213,7 @@
         <v>30664</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E83" s="4">
         <v>99999</v>
@@ -10114,28 +10232,34 @@
         <v>12</v>
       </c>
       <c r="K83" s="30" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="L83" s="3"/>
       <c r="M83" s="16" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="N83" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="O83" s="31"/>
-      <c r="P83" s="31"/>
-      <c r="Q83" s="31"/>
+      <c r="O83" s="31">
+        <v>9.5</v>
+      </c>
+      <c r="P83" s="31">
+        <v>19.5</v>
+      </c>
+      <c r="Q83" s="31">
+        <v>13.49</v>
+      </c>
       <c r="R83" s="50"/>
       <c r="S83" s="22" t="s">
         <v>39</v>
       </c>
       <c r="T83" s="36"/>
       <c r="U83" s="40" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="V83" s="2" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="W83" s="4" t="s">
         <v>39</v>
@@ -10152,16 +10276,16 @@
       <c r="AC83" s="2"/>
       <c r="AD83" s="2"/>
       <c r="AE83" s="2" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="AF83" s="4" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="AG83" s="4" t="s">
         <v>39</v>
       </c>
       <c r="AH83" s="2" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="AI83" s="2"/>
     </row>
@@ -10176,7 +10300,7 @@
         <v>30636</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="E84" s="4">
         <v>99999</v>
@@ -10195,11 +10319,11 @@
         <v>12</v>
       </c>
       <c r="K84" s="30" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="L84" s="3"/>
       <c r="M84" s="16" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="N84" s="2"/>
       <c r="O84" s="31"/>
@@ -10209,10 +10333,10 @@
       <c r="S84" s="22"/>
       <c r="T84" s="36"/>
       <c r="U84" s="40" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="V84" s="2" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="W84" s="4" t="s">
         <v>39</v>
@@ -10229,16 +10353,16 @@
       <c r="AC84" s="2"/>
       <c r="AD84" s="2"/>
       <c r="AE84" s="2" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="AF84" s="4" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="AG84" s="4" t="s">
         <v>39</v>
       </c>
       <c r="AH84" s="2" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AI84" s="2"/>
     </row>
@@ -10253,7 +10377,7 @@
         <v>30622</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="E85" s="4">
         <v>99999</v>
@@ -10272,28 +10396,34 @@
         <v>12</v>
       </c>
       <c r="K85" s="30" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="L85" s="3"/>
       <c r="M85" s="16" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="N85" s="23" t="s">
-        <v>236</v>
-      </c>
-      <c r="O85" s="31"/>
-      <c r="P85" s="31"/>
-      <c r="Q85" s="31"/>
+        <v>237</v>
+      </c>
+      <c r="O85" s="31">
+        <v>6.5</v>
+      </c>
+      <c r="P85" s="31">
+        <v>23</v>
+      </c>
+      <c r="Q85" s="31">
+        <v>13.41</v>
+      </c>
       <c r="R85" s="50"/>
       <c r="S85" s="22" t="s">
         <v>39</v>
       </c>
       <c r="T85" s="36"/>
       <c r="U85" s="40" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="V85" s="2" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="W85" s="4" t="s">
         <v>39</v>
@@ -10310,16 +10440,16 @@
       <c r="AC85" s="2"/>
       <c r="AD85" s="2"/>
       <c r="AE85" s="2" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="AF85" s="4" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="AG85" s="4" t="s">
         <v>39</v>
       </c>
       <c r="AH85" s="2" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="AI85" s="2"/>
     </row>
@@ -10334,7 +10464,7 @@
         <v>36104</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="E86" s="4">
         <v>99999</v>
@@ -10353,11 +10483,11 @@
         <v>12</v>
       </c>
       <c r="K86" s="30" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="L86" s="3"/>
       <c r="M86" s="16" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="N86" s="3" t="s">
         <v>50</v>
@@ -10369,10 +10499,10 @@
       <c r="S86" s="22"/>
       <c r="T86" s="36"/>
       <c r="U86" s="40" t="s">
-        <v>242</v>
+        <v>1100</v>
       </c>
       <c r="V86" s="2" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="W86" s="4" t="s">
         <v>39</v>
@@ -10389,16 +10519,16 @@
       <c r="AC86" s="2"/>
       <c r="AD86" s="2"/>
       <c r="AE86" s="2" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="AF86" s="4" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="AG86" s="4" t="s">
         <v>39</v>
       </c>
       <c r="AH86" s="2" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="AI86" s="2"/>
     </row>
@@ -10413,7 +10543,7 @@
         <v>36096</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="E87" s="4">
         <v>99999</v>
@@ -10432,16 +10562,22 @@
         <v>12</v>
       </c>
       <c r="K87" s="30" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="L87" s="3"/>
       <c r="M87" s="16" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N87" s="2"/>
-      <c r="O87" s="31"/>
-      <c r="P87" s="31"/>
-      <c r="Q87" s="31"/>
+      <c r="O87" s="31">
+        <v>8</v>
+      </c>
+      <c r="P87" s="31">
+        <v>26.4</v>
+      </c>
+      <c r="Q87" s="31">
+        <v>17.190000000000001</v>
+      </c>
       <c r="R87" s="50"/>
       <c r="S87" s="22" t="s">
         <v>39</v>
@@ -10450,10 +10586,10 @@
         <v>39</v>
       </c>
       <c r="U87" s="40" t="s">
-        <v>246</v>
+        <v>1101</v>
       </c>
       <c r="V87" s="2" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="W87" s="4" t="s">
         <v>39</v>
@@ -10472,10 +10608,10 @@
       <c r="AC87" s="2"/>
       <c r="AD87" s="2"/>
       <c r="AE87" s="2" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="AF87" s="4" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="AG87" s="4" t="s">
         <v>39</v>
@@ -10515,7 +10651,7 @@
         <v>12</v>
       </c>
       <c r="K88" s="30" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="L88" s="3"/>
       <c r="M88" s="16" t="s">
@@ -10534,7 +10670,7 @@
         <v>250</v>
       </c>
       <c r="V88" s="2" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="W88" s="4" t="s">
         <v>39</v>
@@ -10551,10 +10687,10 @@
       <c r="AC88" s="2"/>
       <c r="AD88" s="2"/>
       <c r="AE88" s="2" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="AF88" s="4" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="AG88" s="4" t="s">
         <v>39</v>
@@ -10594,16 +10730,22 @@
         <v>12</v>
       </c>
       <c r="K89" s="30" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="L89" s="3"/>
       <c r="M89" s="16" t="s">
         <v>252</v>
       </c>
       <c r="N89" s="2"/>
-      <c r="O89" s="31"/>
-      <c r="P89" s="31"/>
-      <c r="Q89" s="31"/>
+      <c r="O89" s="31">
+        <v>3.2</v>
+      </c>
+      <c r="P89" s="31">
+        <v>23.8</v>
+      </c>
+      <c r="Q89" s="31">
+        <v>12.91</v>
+      </c>
       <c r="R89" s="50" t="s">
         <v>253</v>
       </c>
@@ -10632,10 +10774,10 @@
       <c r="AC89" s="2"/>
       <c r="AD89" s="2"/>
       <c r="AE89" s="2" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="AF89" s="4" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="AG89" s="4" t="s">
         <v>39</v>
@@ -10675,7 +10817,7 @@
         <v>12</v>
       </c>
       <c r="K90" s="30" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="L90" s="3"/>
       <c r="M90" s="12" t="s">
@@ -10694,7 +10836,7 @@
         <v>259</v>
       </c>
       <c r="V90" s="2" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="W90" s="4" t="s">
         <v>39</v>
@@ -10711,10 +10853,10 @@
       <c r="AC90" s="2"/>
       <c r="AD90" s="2"/>
       <c r="AE90" s="2" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="AF90" s="4" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="AG90" s="4"/>
       <c r="AH90" s="2" t="s">
@@ -10768,7 +10910,7 @@
       <c r="S91" s="22"/>
       <c r="T91" s="36"/>
       <c r="U91" s="40" t="s">
-        <v>265</v>
+        <v>1103</v>
       </c>
       <c r="V91" s="2" t="s">
         <v>266</v>
@@ -10843,7 +10985,7 @@
       <c r="S92" s="22"/>
       <c r="T92" s="36"/>
       <c r="U92" s="40" t="s">
-        <v>115</v>
+        <v>1102</v>
       </c>
       <c r="V92" s="2" t="s">
         <v>265</v>
@@ -10911,9 +11053,15 @@
         <v>273</v>
       </c>
       <c r="N93" s="2"/>
-      <c r="O93" s="31"/>
-      <c r="P93" s="31"/>
-      <c r="Q93" s="31"/>
+      <c r="O93" s="31">
+        <v>11.9</v>
+      </c>
+      <c r="P93" s="31">
+        <v>15.3</v>
+      </c>
+      <c r="Q93" s="31">
+        <v>13.55</v>
+      </c>
       <c r="R93" s="50"/>
       <c r="S93" s="22" t="s">
         <v>39</v>
@@ -10990,9 +11138,15 @@
         <v>280</v>
       </c>
       <c r="N94" s="2"/>
-      <c r="O94" s="31"/>
-      <c r="P94" s="31"/>
-      <c r="Q94" s="31"/>
+      <c r="O94" s="31">
+        <v>19.2</v>
+      </c>
+      <c r="P94" s="31">
+        <v>24.6</v>
+      </c>
+      <c r="Q94" s="31">
+        <v>22.1</v>
+      </c>
       <c r="R94" s="50"/>
       <c r="S94" s="22" t="s">
         <v>39</v>
@@ -11156,9 +11310,15 @@
         <v>293</v>
       </c>
       <c r="N96" s="2"/>
-      <c r="O96" s="31"/>
-      <c r="P96" s="31"/>
-      <c r="Q96" s="31"/>
+      <c r="O96" s="31">
+        <v>16</v>
+      </c>
+      <c r="P96" s="31">
+        <v>25.3</v>
+      </c>
+      <c r="Q96" s="31">
+        <v>20.5</v>
+      </c>
       <c r="R96" s="50"/>
       <c r="S96" s="22" t="s">
         <v>39</v>
@@ -11326,9 +11486,15 @@
         <v>307</v>
       </c>
       <c r="N98" s="2"/>
-      <c r="O98" s="31"/>
-      <c r="P98" s="31"/>
-      <c r="Q98" s="31"/>
+      <c r="O98" s="31">
+        <v>17.100000000000001</v>
+      </c>
+      <c r="P98" s="31">
+        <v>25.1</v>
+      </c>
+      <c r="Q98" s="31">
+        <v>20.38</v>
+      </c>
       <c r="R98" s="50"/>
       <c r="S98" s="22" t="s">
         <v>39</v>
@@ -11731,9 +11897,15 @@
         <v>330</v>
       </c>
       <c r="N103" s="2"/>
-      <c r="O103" s="31"/>
-      <c r="P103" s="31"/>
-      <c r="Q103" s="31"/>
+      <c r="O103" s="31">
+        <v>6</v>
+      </c>
+      <c r="P103" s="31">
+        <v>21.8</v>
+      </c>
+      <c r="Q103" s="31">
+        <v>12.95</v>
+      </c>
       <c r="R103" s="50"/>
       <c r="S103" s="22" t="s">
         <v>39</v>
@@ -11972,11 +12144,17 @@
         <v>342</v>
       </c>
       <c r="N106" s="2" t="s">
-        <v>223</v>
-      </c>
-      <c r="O106" s="31"/>
-      <c r="P106" s="31"/>
-      <c r="Q106" s="31"/>
+        <v>224</v>
+      </c>
+      <c r="O106" s="31">
+        <v>10.8</v>
+      </c>
+      <c r="P106" s="31">
+        <v>13.8</v>
+      </c>
+      <c r="Q106" s="31">
+        <v>11.84</v>
+      </c>
       <c r="R106" s="50"/>
       <c r="S106" s="22" t="s">
         <v>39</v>
@@ -12370,7 +12548,7 @@
       <c r="S111" s="22"/>
       <c r="T111" s="36"/>
       <c r="U111" s="40" t="s">
-        <v>336</v>
+        <v>1105</v>
       </c>
       <c r="V111" s="2" t="s">
         <v>337</v>
@@ -12596,9 +12774,15 @@
         <v>363</v>
       </c>
       <c r="N114" s="2"/>
-      <c r="O114" s="31"/>
-      <c r="P114" s="31"/>
-      <c r="Q114" s="31"/>
+      <c r="O114" s="31">
+        <v>4.5</v>
+      </c>
+      <c r="P114" s="31">
+        <v>14.3</v>
+      </c>
+      <c r="Q114" s="31">
+        <v>8.56</v>
+      </c>
       <c r="R114" s="50"/>
       <c r="S114" s="22" t="s">
         <v>39</v>
@@ -12677,9 +12861,15 @@
       <c r="N115" s="23" t="s">
         <v>97</v>
       </c>
-      <c r="O115" s="31"/>
-      <c r="P115" s="31"/>
-      <c r="Q115" s="31"/>
+      <c r="O115" s="31">
+        <v>-1.8</v>
+      </c>
+      <c r="P115" s="31">
+        <v>12.9</v>
+      </c>
+      <c r="Q115" s="31">
+        <v>4.78</v>
+      </c>
       <c r="R115" s="50"/>
       <c r="S115" s="22" t="s">
         <v>39</v>
@@ -12762,9 +12952,15 @@
       <c r="N116" s="23" t="s">
         <v>97</v>
       </c>
-      <c r="O116" s="31"/>
-      <c r="P116" s="31"/>
-      <c r="Q116" s="31"/>
+      <c r="O116" s="31">
+        <v>1.4</v>
+      </c>
+      <c r="P116" s="31">
+        <v>10.1</v>
+      </c>
+      <c r="Q116" s="31">
+        <v>4.59</v>
+      </c>
       <c r="R116" s="50"/>
       <c r="S116" s="22" t="s">
         <v>39</v>
@@ -13169,9 +13365,15 @@
         <v>397</v>
       </c>
       <c r="N121" s="2"/>
-      <c r="O121" s="31"/>
-      <c r="P121" s="31"/>
-      <c r="Q121" s="31"/>
+      <c r="O121" s="31">
+        <v>23.7</v>
+      </c>
+      <c r="P121" s="31">
+        <v>40.200000000000003</v>
+      </c>
+      <c r="Q121" s="31">
+        <v>32.42</v>
+      </c>
       <c r="R121" s="50"/>
       <c r="S121" s="22" t="s">
         <v>39</v>
@@ -13250,9 +13452,15 @@
         <v>402</v>
       </c>
       <c r="N122" s="2"/>
-      <c r="O122" s="31"/>
-      <c r="P122" s="31"/>
-      <c r="Q122" s="31"/>
+      <c r="O122" s="31">
+        <v>18.899999999999999</v>
+      </c>
+      <c r="P122" s="31">
+        <v>32.6</v>
+      </c>
+      <c r="Q122" s="31">
+        <v>24.39</v>
+      </c>
       <c r="R122" s="50"/>
       <c r="S122" s="22" t="s">
         <v>39</v>
@@ -13335,9 +13543,15 @@
         <v>406</v>
       </c>
       <c r="N123" s="2"/>
-      <c r="O123" s="31"/>
-      <c r="P123" s="31"/>
-      <c r="Q123" s="31"/>
+      <c r="O123" s="31">
+        <v>2.8</v>
+      </c>
+      <c r="P123" s="31">
+        <v>23.2</v>
+      </c>
+      <c r="Q123" s="31">
+        <v>13.43</v>
+      </c>
       <c r="R123" s="50"/>
       <c r="S123" s="22" t="s">
         <v>39</v>
@@ -13495,9 +13709,15 @@
         <v>414</v>
       </c>
       <c r="N125" s="2"/>
-      <c r="O125" s="31"/>
-      <c r="P125" s="31"/>
-      <c r="Q125" s="31"/>
+      <c r="O125" s="31">
+        <v>15.3</v>
+      </c>
+      <c r="P125" s="31">
+        <v>23.8</v>
+      </c>
+      <c r="Q125" s="31">
+        <v>19</v>
+      </c>
       <c r="R125" s="50"/>
       <c r="S125" s="22" t="s">
         <v>39</v>
@@ -13580,9 +13800,15 @@
         <v>419</v>
       </c>
       <c r="N126" s="2"/>
-      <c r="O126" s="31"/>
-      <c r="P126" s="31"/>
-      <c r="Q126" s="31"/>
+      <c r="O126" s="31">
+        <v>18.399999999999999</v>
+      </c>
+      <c r="P126" s="31">
+        <v>28.2</v>
+      </c>
+      <c r="Q126" s="31">
+        <v>22.26</v>
+      </c>
       <c r="R126" s="50"/>
       <c r="S126" s="22" t="s">
         <v>39</v>
@@ -13655,9 +13881,15 @@
         <v>422</v>
       </c>
       <c r="N127" s="2"/>
-      <c r="O127" s="31"/>
-      <c r="P127" s="31"/>
-      <c r="Q127" s="31"/>
+      <c r="O127" s="31">
+        <v>18.899999999999999</v>
+      </c>
+      <c r="P127" s="31">
+        <v>27.8</v>
+      </c>
+      <c r="Q127" s="31">
+        <v>22.52</v>
+      </c>
       <c r="R127" s="50"/>
       <c r="S127" s="22" t="s">
         <v>39</v>
@@ -13734,9 +13966,15 @@
         <v>428</v>
       </c>
       <c r="N128" s="2"/>
-      <c r="O128" s="31"/>
-      <c r="P128" s="31"/>
-      <c r="Q128" s="31"/>
+      <c r="O128" s="31">
+        <v>15.4</v>
+      </c>
+      <c r="P128" s="31">
+        <v>29.1</v>
+      </c>
+      <c r="Q128" s="31">
+        <v>22.19</v>
+      </c>
       <c r="R128" s="50"/>
       <c r="S128" s="22" t="s">
         <v>39</v>
@@ -13817,9 +14055,15 @@
         <v>434</v>
       </c>
       <c r="N129" s="2"/>
-      <c r="O129" s="31"/>
-      <c r="P129" s="31"/>
-      <c r="Q129" s="31"/>
+      <c r="O129" s="31">
+        <v>16.899999999999999</v>
+      </c>
+      <c r="P129" s="31">
+        <v>27.6</v>
+      </c>
+      <c r="Q129" s="31">
+        <v>21.88</v>
+      </c>
       <c r="R129" s="50"/>
       <c r="S129" s="22" t="s">
         <v>39</v>
@@ -13896,9 +14140,15 @@
         <v>438</v>
       </c>
       <c r="N130" s="2"/>
-      <c r="O130" s="31"/>
-      <c r="P130" s="31"/>
-      <c r="Q130" s="31"/>
+      <c r="O130" s="31">
+        <v>16</v>
+      </c>
+      <c r="P130" s="31">
+        <v>27.1</v>
+      </c>
+      <c r="Q130" s="31">
+        <v>20.25</v>
+      </c>
       <c r="R130" s="50"/>
       <c r="S130" s="22" t="s">
         <v>39</v>
@@ -13979,9 +14229,15 @@
         <v>444</v>
       </c>
       <c r="N131" s="2"/>
-      <c r="O131" s="31"/>
-      <c r="P131" s="31"/>
-      <c r="Q131" s="31"/>
+      <c r="O131" s="31">
+        <v>7.1</v>
+      </c>
+      <c r="P131" s="31">
+        <v>22.8</v>
+      </c>
+      <c r="Q131" s="31">
+        <v>13.46</v>
+      </c>
       <c r="R131" s="50"/>
       <c r="S131" s="22" t="s">
         <v>39</v>
@@ -14062,9 +14318,15 @@
         <v>449</v>
       </c>
       <c r="N132" s="2"/>
-      <c r="O132" s="31"/>
-      <c r="P132" s="31"/>
-      <c r="Q132" s="31"/>
+      <c r="O132" s="31">
+        <v>19.600000000000001</v>
+      </c>
+      <c r="P132" s="31">
+        <v>26</v>
+      </c>
+      <c r="Q132" s="31">
+        <v>21.84</v>
+      </c>
       <c r="R132" s="50"/>
       <c r="S132" s="22" t="s">
         <v>39</v>
@@ -14143,9 +14405,15 @@
         <v>455</v>
       </c>
       <c r="N133" s="2"/>
-      <c r="O133" s="31"/>
-      <c r="P133" s="31"/>
-      <c r="Q133" s="31"/>
+      <c r="O133" s="31">
+        <v>20.5</v>
+      </c>
+      <c r="P133" s="31">
+        <v>31.5</v>
+      </c>
+      <c r="Q133" s="31">
+        <v>25.65</v>
+      </c>
       <c r="R133" s="50"/>
       <c r="S133" s="22" t="s">
         <v>39</v>
@@ -14224,9 +14492,15 @@
         <v>461</v>
       </c>
       <c r="N134" s="2"/>
-      <c r="O134" s="31"/>
-      <c r="P134" s="31"/>
-      <c r="Q134" s="31"/>
+      <c r="O134" s="31">
+        <v>22.7</v>
+      </c>
+      <c r="P134" s="31">
+        <v>30.1</v>
+      </c>
+      <c r="Q134" s="31">
+        <v>25.57</v>
+      </c>
       <c r="R134" s="50"/>
       <c r="S134" s="22" t="s">
         <v>39</v>
@@ -14384,9 +14658,15 @@
         <v>473</v>
       </c>
       <c r="N136" s="2"/>
-      <c r="O136" s="31"/>
-      <c r="P136" s="31"/>
-      <c r="Q136" s="31"/>
+      <c r="O136" s="31">
+        <v>24.2</v>
+      </c>
+      <c r="P136" s="31">
+        <v>30.8</v>
+      </c>
+      <c r="Q136" s="31">
+        <v>26.31</v>
+      </c>
       <c r="R136" s="50"/>
       <c r="S136" s="22" t="s">
         <v>39</v>
@@ -14465,9 +14745,15 @@
         <v>479</v>
       </c>
       <c r="N137" s="2"/>
-      <c r="O137" s="31"/>
-      <c r="P137" s="31"/>
-      <c r="Q137" s="31"/>
+      <c r="O137" s="31">
+        <v>27.9</v>
+      </c>
+      <c r="P137" s="31">
+        <v>32</v>
+      </c>
+      <c r="Q137" s="31">
+        <v>29.94</v>
+      </c>
       <c r="R137" s="50"/>
       <c r="S137" s="22" t="s">
         <v>39</v>
@@ -14546,9 +14832,15 @@
         <v>485</v>
       </c>
       <c r="N138" s="2"/>
-      <c r="O138" s="31"/>
-      <c r="P138" s="31"/>
-      <c r="Q138" s="31"/>
+      <c r="O138" s="31">
+        <v>24.2</v>
+      </c>
+      <c r="P138" s="31">
+        <v>31.5</v>
+      </c>
+      <c r="Q138" s="31">
+        <v>27.05</v>
+      </c>
       <c r="R138" s="50"/>
       <c r="S138" s="22" t="s">
         <v>39</v>
@@ -14627,9 +14919,15 @@
         <v>492</v>
       </c>
       <c r="N139" s="2"/>
-      <c r="O139" s="31"/>
-      <c r="P139" s="31"/>
-      <c r="Q139" s="31"/>
+      <c r="O139" s="31">
+        <v>26.2</v>
+      </c>
+      <c r="P139" s="31">
+        <v>32.6</v>
+      </c>
+      <c r="Q139" s="31">
+        <v>28.4</v>
+      </c>
       <c r="R139" s="50"/>
       <c r="S139" s="22" t="s">
         <v>39</v>
@@ -14708,9 +15006,15 @@
         <v>498</v>
       </c>
       <c r="N140" s="2"/>
-      <c r="O140" s="31"/>
-      <c r="P140" s="31"/>
-      <c r="Q140" s="31"/>
+      <c r="O140" s="31">
+        <v>26.5</v>
+      </c>
+      <c r="P140" s="31">
+        <v>33.700000000000003</v>
+      </c>
+      <c r="Q140" s="31">
+        <v>29.57</v>
+      </c>
       <c r="R140" s="50"/>
       <c r="S140" s="22" t="s">
         <v>39</v>
@@ -14789,9 +15093,15 @@
         <v>503</v>
       </c>
       <c r="N141" s="2"/>
-      <c r="O141" s="31"/>
-      <c r="P141" s="31"/>
-      <c r="Q141" s="31"/>
+      <c r="O141" s="31">
+        <v>26.5</v>
+      </c>
+      <c r="P141" s="31">
+        <v>32.700000000000003</v>
+      </c>
+      <c r="Q141" s="31">
+        <v>29.36</v>
+      </c>
       <c r="R141" s="50"/>
       <c r="S141" s="22" t="s">
         <v>39</v>
@@ -14947,9 +15257,15 @@
         <v>514</v>
       </c>
       <c r="N143" s="2"/>
-      <c r="O143" s="31"/>
-      <c r="P143" s="31"/>
-      <c r="Q143" s="31"/>
+      <c r="O143" s="31">
+        <v>25.7</v>
+      </c>
+      <c r="P143" s="31">
+        <v>30.4</v>
+      </c>
+      <c r="Q143" s="31">
+        <v>27.05</v>
+      </c>
       <c r="R143" s="50"/>
       <c r="S143" s="22" t="s">
         <v>39</v>
@@ -15028,9 +15344,15 @@
         <v>520</v>
       </c>
       <c r="N144" s="2"/>
-      <c r="O144" s="31"/>
-      <c r="P144" s="31"/>
-      <c r="Q144" s="31"/>
+      <c r="O144" s="31">
+        <v>25.9</v>
+      </c>
+      <c r="P144" s="31">
+        <v>36.299999999999997</v>
+      </c>
+      <c r="Q144" s="31">
+        <v>29.54</v>
+      </c>
       <c r="R144" s="50"/>
       <c r="S144" s="22" t="s">
         <v>39</v>
@@ -15261,9 +15583,15 @@
         <v>535</v>
       </c>
       <c r="N147" s="2"/>
-      <c r="O147" s="31"/>
-      <c r="P147" s="31"/>
-      <c r="Q147" s="31"/>
+      <c r="O147" s="31">
+        <v>29.1</v>
+      </c>
+      <c r="P147" s="31">
+        <v>31.4</v>
+      </c>
+      <c r="Q147" s="31">
+        <v>29.8</v>
+      </c>
       <c r="R147" s="50"/>
       <c r="S147" s="22" t="s">
         <v>39</v>
@@ -15338,9 +15666,15 @@
         <v>538</v>
       </c>
       <c r="N148" s="2"/>
-      <c r="O148" s="31"/>
-      <c r="P148" s="31"/>
-      <c r="Q148" s="31"/>
+      <c r="O148" s="31">
+        <v>26.4</v>
+      </c>
+      <c r="P148" s="31">
+        <v>31.3</v>
+      </c>
+      <c r="Q148" s="31">
+        <v>27.96</v>
+      </c>
       <c r="R148" s="50"/>
       <c r="S148" s="22" t="s">
         <v>39</v>
@@ -15419,9 +15753,15 @@
         <v>544</v>
       </c>
       <c r="N149" s="2"/>
-      <c r="O149" s="31"/>
-      <c r="P149" s="31"/>
-      <c r="Q149" s="31"/>
+      <c r="O149" s="31">
+        <v>23</v>
+      </c>
+      <c r="P149" s="31">
+        <v>32.9</v>
+      </c>
+      <c r="Q149" s="31">
+        <v>26.9</v>
+      </c>
       <c r="R149" s="50"/>
       <c r="S149" s="22" t="s">
         <v>39</v>
@@ -15498,9 +15838,15 @@
         <v>549</v>
       </c>
       <c r="N150" s="2"/>
-      <c r="O150" s="31"/>
-      <c r="P150" s="31"/>
-      <c r="Q150" s="31"/>
+      <c r="O150" s="31">
+        <v>19.3</v>
+      </c>
+      <c r="P150" s="31">
+        <v>24.4</v>
+      </c>
+      <c r="Q150" s="31">
+        <v>20.79</v>
+      </c>
       <c r="R150" s="50"/>
       <c r="S150" s="22" t="s">
         <v>39</v>
@@ -15579,9 +15925,15 @@
         <v>554</v>
       </c>
       <c r="N151" s="2"/>
-      <c r="O151" s="31"/>
-      <c r="P151" s="31"/>
-      <c r="Q151" s="31"/>
+      <c r="O151" s="31">
+        <v>20.9</v>
+      </c>
+      <c r="P151" s="31">
+        <v>29.4</v>
+      </c>
+      <c r="Q151" s="31">
+        <v>24.58</v>
+      </c>
       <c r="R151" s="50"/>
       <c r="S151" s="22" t="s">
         <v>39</v>
@@ -15660,9 +16012,15 @@
         <v>560</v>
       </c>
       <c r="N152" s="2"/>
-      <c r="O152" s="31"/>
-      <c r="P152" s="31"/>
-      <c r="Q152" s="31"/>
+      <c r="O152" s="31">
+        <v>25.5</v>
+      </c>
+      <c r="P152" s="31">
+        <v>31</v>
+      </c>
+      <c r="Q152" s="31">
+        <v>26.89</v>
+      </c>
       <c r="R152" s="50"/>
       <c r="S152" s="22" t="s">
         <v>39</v>
@@ -15812,9 +16170,15 @@
         <v>570</v>
       </c>
       <c r="N154" s="2"/>
-      <c r="O154" s="31"/>
-      <c r="P154" s="31"/>
-      <c r="Q154" s="31"/>
+      <c r="O154" s="31">
+        <v>23.6</v>
+      </c>
+      <c r="P154" s="31">
+        <v>31.7</v>
+      </c>
+      <c r="Q154" s="31">
+        <v>26.91</v>
+      </c>
       <c r="R154" s="50"/>
       <c r="S154" s="22" t="s">
         <v>39</v>
@@ -15895,9 +16259,15 @@
         <v>577</v>
       </c>
       <c r="N155" s="2"/>
-      <c r="O155" s="31"/>
-      <c r="P155" s="31"/>
-      <c r="Q155" s="31"/>
+      <c r="O155" s="31">
+        <v>12.2</v>
+      </c>
+      <c r="P155" s="31">
+        <v>20</v>
+      </c>
+      <c r="Q155" s="31">
+        <v>15.49</v>
+      </c>
       <c r="R155" s="50"/>
       <c r="S155" s="22" t="s">
         <v>39</v>
@@ -16120,9 +16490,15 @@
         <v>587</v>
       </c>
       <c r="N158" s="2"/>
-      <c r="O158" s="31"/>
-      <c r="P158" s="31"/>
-      <c r="Q158" s="31"/>
+      <c r="O158" s="31">
+        <v>27.6</v>
+      </c>
+      <c r="P158" s="31">
+        <v>32.799999999999997</v>
+      </c>
+      <c r="Q158" s="31">
+        <v>29.65</v>
+      </c>
       <c r="R158" s="50"/>
       <c r="S158" s="22" t="s">
         <v>39</v>
@@ -16416,9 +16792,15 @@
         <v>602</v>
       </c>
       <c r="N162" s="2"/>
-      <c r="O162" s="31"/>
-      <c r="P162" s="31"/>
-      <c r="Q162" s="31"/>
+      <c r="O162" s="31">
+        <v>14.2</v>
+      </c>
+      <c r="P162" s="31">
+        <v>28.1</v>
+      </c>
+      <c r="Q162" s="31">
+        <v>20.04</v>
+      </c>
       <c r="R162" s="50"/>
       <c r="S162" s="22" t="s">
         <v>39</v>
@@ -16574,8 +16956,12 @@
       <c r="N164" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="O164" s="31"/>
-      <c r="P164" s="31"/>
+      <c r="O164" s="31">
+        <v>-0.5</v>
+      </c>
+      <c r="P164" s="31">
+        <v>21.1</v>
+      </c>
       <c r="Q164" s="31"/>
       <c r="R164" s="50"/>
       <c r="S164" s="22" t="s">
@@ -16882,7 +17268,7 @@
         <v>619</v>
       </c>
       <c r="N168" s="2" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="O168" s="31"/>
       <c r="P168" s="31"/>
@@ -17200,8 +17586,12 @@
       <c r="N172" s="3" t="s">
         <v>633</v>
       </c>
-      <c r="O172" s="31"/>
-      <c r="P172" s="31"/>
+      <c r="O172" s="31">
+        <v>-1.3</v>
+      </c>
+      <c r="P172" s="31">
+        <v>16</v>
+      </c>
       <c r="Q172" s="31"/>
       <c r="R172" s="50"/>
       <c r="S172" s="22" t="s">
@@ -17356,8 +17746,12 @@
         <v>637</v>
       </c>
       <c r="N174" s="3"/>
-      <c r="O174" s="31"/>
-      <c r="P174" s="31"/>
+      <c r="O174" s="31">
+        <v>0.1</v>
+      </c>
+      <c r="P174" s="31">
+        <v>23.7</v>
+      </c>
       <c r="Q174" s="31"/>
       <c r="R174" s="50"/>
       <c r="S174" s="22" t="s">
@@ -17433,8 +17827,12 @@
         <v>640</v>
       </c>
       <c r="N175" s="2"/>
-      <c r="O175" s="31"/>
-      <c r="P175" s="31"/>
+      <c r="O175" s="31">
+        <v>10.199999999999999</v>
+      </c>
+      <c r="P175" s="31">
+        <v>19.399999999999999</v>
+      </c>
       <c r="Q175" s="31"/>
       <c r="R175" s="50" t="s">
         <v>641</v>
@@ -17670,9 +18068,15 @@
         <v>655</v>
       </c>
       <c r="N178" s="2"/>
-      <c r="O178" s="31"/>
-      <c r="P178" s="31"/>
-      <c r="Q178" s="31"/>
+      <c r="O178" s="31">
+        <v>16.7</v>
+      </c>
+      <c r="P178" s="31">
+        <v>21.6</v>
+      </c>
+      <c r="Q178" s="31">
+        <v>18.21</v>
+      </c>
       <c r="R178" s="50"/>
       <c r="S178" s="22" t="s">
         <v>39</v>
@@ -17747,9 +18151,15 @@
       <c r="N179" s="23" t="s">
         <v>97</v>
       </c>
-      <c r="O179" s="31"/>
-      <c r="P179" s="31"/>
-      <c r="Q179" s="31"/>
+      <c r="O179" s="31">
+        <v>5.2</v>
+      </c>
+      <c r="P179" s="31">
+        <v>8.4</v>
+      </c>
+      <c r="Q179" s="31">
+        <v>7</v>
+      </c>
       <c r="R179" s="50"/>
       <c r="S179" s="22" t="s">
         <v>39</v>
@@ -17984,8 +18394,12 @@
         <v>667</v>
       </c>
       <c r="N182" s="2"/>
-      <c r="O182" s="31"/>
-      <c r="P182" s="31"/>
+      <c r="O182" s="31">
+        <v>7.4</v>
+      </c>
+      <c r="P182" s="31">
+        <v>13.6</v>
+      </c>
       <c r="Q182" s="31"/>
       <c r="R182" s="50"/>
       <c r="S182" s="22" t="s">
@@ -18336,7 +18750,7 @@
         <v>12</v>
       </c>
       <c r="K187" s="30" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="L187" s="3"/>
       <c r="M187" s="12" t="s">
@@ -18368,7 +18782,7 @@
       <c r="AC187" s="2"/>
       <c r="AD187" s="2"/>
       <c r="AE187" s="2" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="AF187" s="4" t="s">
         <v>685</v>
@@ -18411,7 +18825,7 @@
         <v>15</v>
       </c>
       <c r="K188" s="30" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="L188" s="3"/>
       <c r="M188" s="16" t="s">
@@ -18443,7 +18857,7 @@
       <c r="AC188" s="2"/>
       <c r="AD188" s="2"/>
       <c r="AE188" s="2" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="AF188" s="4" t="s">
         <v>685</v>
@@ -18486,7 +18900,7 @@
         <v>15</v>
       </c>
       <c r="K189" s="30" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="L189" s="3"/>
       <c r="M189" s="16" t="s">
@@ -18518,7 +18932,7 @@
       <c r="AC189" s="2"/>
       <c r="AD189" s="2"/>
       <c r="AE189" s="2" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="AF189" s="4" t="s">
         <v>685</v>
@@ -18559,7 +18973,7 @@
         <v>15</v>
       </c>
       <c r="K190" s="30" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="L190" s="3"/>
       <c r="M190" s="16" t="s">
@@ -18591,7 +19005,7 @@
       <c r="AC190" s="2"/>
       <c r="AD190" s="2"/>
       <c r="AE190" s="2" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="AF190" s="4" t="s">
         <v>685</v>
@@ -18632,7 +19046,7 @@
         <v>15</v>
       </c>
       <c r="K191" s="30" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="L191" s="3"/>
       <c r="M191" s="16" t="s">
@@ -18664,7 +19078,7 @@
       <c r="AC191" s="2"/>
       <c r="AD191" s="2"/>
       <c r="AE191" s="2" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="AF191" s="4" t="s">
         <v>685</v>
@@ -18705,7 +19119,7 @@
         <v>15</v>
       </c>
       <c r="K192" s="30" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="L192" s="3"/>
       <c r="M192" s="16" t="s">
@@ -18735,7 +19149,7 @@
       <c r="AC192" s="2"/>
       <c r="AD192" s="2"/>
       <c r="AE192" s="2" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="AF192" s="4" t="s">
         <v>685</v>
@@ -18776,7 +19190,7 @@
         <v>15</v>
       </c>
       <c r="K193" s="30" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="L193" s="3"/>
       <c r="M193" s="16" t="s">
@@ -18808,7 +19222,7 @@
       <c r="AC193" s="2"/>
       <c r="AD193" s="2"/>
       <c r="AE193" s="2" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="AF193" s="4" t="s">
         <v>685</v>
@@ -18847,7 +19261,7 @@
         <v>15</v>
       </c>
       <c r="K194" s="30" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="L194" s="3"/>
       <c r="M194" s="16" t="s">
@@ -18879,7 +19293,7 @@
       <c r="AC194" s="2"/>
       <c r="AD194" s="2"/>
       <c r="AE194" s="2" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="AF194" s="4" t="s">
         <v>685</v>
@@ -18920,7 +19334,7 @@
         <v>12</v>
       </c>
       <c r="K195" s="30" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="L195" s="3"/>
       <c r="M195" s="16" t="s">
@@ -18954,7 +19368,7 @@
       <c r="AC195" s="2"/>
       <c r="AD195" s="2"/>
       <c r="AE195" s="2" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="AF195" s="4" t="s">
         <v>685</v>
@@ -18995,7 +19409,7 @@
         <v>15</v>
       </c>
       <c r="K196" s="30" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="L196" s="3"/>
       <c r="M196" s="12" t="s">
@@ -19027,7 +19441,7 @@
       <c r="AC196" s="2"/>
       <c r="AD196" s="2"/>
       <c r="AE196" s="2" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="AF196" s="4" t="s">
         <v>685</v>
@@ -19066,7 +19480,7 @@
         <v>15</v>
       </c>
       <c r="K197" s="30" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="L197" s="3"/>
       <c r="M197" s="16" t="s">
@@ -19098,7 +19512,7 @@
       <c r="AC197" s="2"/>
       <c r="AD197" s="2"/>
       <c r="AE197" s="2" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="AF197" s="4" t="s">
         <v>685</v>
@@ -19139,7 +19553,7 @@
         <v>15</v>
       </c>
       <c r="K198" s="30" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="L198" s="3"/>
       <c r="M198" s="16" t="s">
@@ -19171,7 +19585,7 @@
       <c r="AC198" s="2"/>
       <c r="AD198" s="2"/>
       <c r="AE198" s="2" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="AF198" s="4" t="s">
         <v>685</v>
@@ -19210,7 +19624,7 @@
         <v>12</v>
       </c>
       <c r="K199" s="30" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="L199" s="3"/>
       <c r="M199" s="16" t="s">
@@ -19242,7 +19656,7 @@
       <c r="AC199" s="2"/>
       <c r="AD199" s="2"/>
       <c r="AE199" s="2" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="AF199" s="4" t="s">
         <v>685</v>
@@ -21137,8 +21551,12 @@
         <v>777</v>
       </c>
       <c r="N225" s="2"/>
-      <c r="O225" s="31"/>
-      <c r="P225" s="31"/>
+      <c r="O225" s="31">
+        <v>2.5</v>
+      </c>
+      <c r="P225" s="31">
+        <v>21.1</v>
+      </c>
       <c r="Q225" s="31"/>
       <c r="R225" s="50"/>
       <c r="S225" s="22" t="s">
@@ -22732,10 +23150,10 @@
       </c>
       <c r="T247" s="36"/>
       <c r="U247" s="40" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="V247" s="2" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="W247" s="4" t="s">
         <v>39</v>
@@ -22803,10 +23221,10 @@
       </c>
       <c r="T248" s="36"/>
       <c r="U248" s="40" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="V248" s="2" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="W248" s="4" t="s">
         <v>39</v>
@@ -22955,7 +23373,7 @@
       <c r="S250" s="22"/>
       <c r="T250" s="36"/>
       <c r="U250" s="40" t="s">
-        <v>115</v>
+        <v>1104</v>
       </c>
       <c r="V250" s="2" t="s">
         <v>265</v>
@@ -23016,7 +23434,7 @@
         <v>15</v>
       </c>
       <c r="K251" s="30" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="L251" s="3"/>
       <c r="M251" s="16" t="s">
@@ -23054,10 +23472,10 @@
         <v>838</v>
       </c>
       <c r="AE251" s="2" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="AF251" s="4" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="AG251" s="4"/>
       <c r="AH251" s="2"/>
@@ -23093,7 +23511,7 @@
         <v>12</v>
       </c>
       <c r="K252" s="30" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="L252" s="3"/>
       <c r="M252" s="16" t="s">
@@ -23110,7 +23528,7 @@
         <v>841</v>
       </c>
       <c r="V252" s="2" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="W252" s="4" t="s">
         <v>39</v>
@@ -23131,10 +23549,10 @@
         <v>842</v>
       </c>
       <c r="AE252" s="2" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="AF252" s="4" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="AG252" s="4"/>
       <c r="AH252" s="2" t="s">
@@ -23172,14 +23590,14 @@
         <v>12</v>
       </c>
       <c r="K253" s="30" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="L253" s="3"/>
       <c r="M253" s="12" t="s">
         <v>844</v>
       </c>
       <c r="N253" s="23" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="O253" s="31"/>
       <c r="P253" s="31"/>
@@ -23206,7 +23624,7 @@
       <c r="AC253" s="2"/>
       <c r="AD253" s="2"/>
       <c r="AE253" s="2" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="AF253" s="4" t="s">
         <v>685</v>
@@ -23245,7 +23663,7 @@
         <v>12</v>
       </c>
       <c r="K254" s="30" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="L254" s="3"/>
       <c r="M254" s="16" t="s">
@@ -23283,10 +23701,10 @@
         <v>847</v>
       </c>
       <c r="AE254" s="2" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="AF254" s="4" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="AG254" s="4"/>
       <c r="AH254" s="2"/>
@@ -23318,7 +23736,7 @@
         <v>12</v>
       </c>
       <c r="K255" s="30" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="L255" s="3"/>
       <c r="M255" s="16" t="s">
@@ -23352,7 +23770,7 @@
         <v>850</v>
       </c>
       <c r="AE255" s="2" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="AF255" s="4" t="s">
         <v>685</v>
@@ -23391,7 +23809,7 @@
         <v>12</v>
       </c>
       <c r="K256" s="30" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="L256" s="3"/>
       <c r="M256" s="16" t="s">
@@ -23425,7 +23843,7 @@
         <v>854</v>
       </c>
       <c r="AE256" s="2" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="AF256" s="4" t="s">
         <v>685</v>
@@ -23464,7 +23882,7 @@
         <v>12</v>
       </c>
       <c r="K257" s="30" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="L257" s="3"/>
       <c r="M257" s="16" t="s">
@@ -23498,7 +23916,7 @@
         <v>858</v>
       </c>
       <c r="AE257" s="2" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="AF257" s="4" t="s">
         <v>685</v>
@@ -23537,7 +23955,7 @@
         <v>12</v>
       </c>
       <c r="K258" s="30" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="L258" s="3"/>
       <c r="M258" s="16" t="s">
@@ -23571,7 +23989,7 @@
         <v>860</v>
       </c>
       <c r="AE258" s="2" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="AF258" s="4" t="s">
         <v>685</v>
@@ -23612,7 +24030,7 @@
         <v>12</v>
       </c>
       <c r="K259" s="30" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="L259" s="3"/>
       <c r="M259" s="16" t="s">
@@ -23646,7 +24064,7 @@
         <v>864</v>
       </c>
       <c r="AE259" s="2" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="AF259" s="4" t="s">
         <v>685</v>
@@ -23687,7 +24105,7 @@
         <v>12</v>
       </c>
       <c r="K260" s="30" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="L260" s="3"/>
       <c r="M260" s="16" t="s">
@@ -23719,7 +24137,7 @@
       <c r="AC260" s="2"/>
       <c r="AD260" s="2"/>
       <c r="AE260" s="2" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="AF260" s="4" t="s">
         <v>685</v>
@@ -23758,7 +24176,7 @@
         <v>12</v>
       </c>
       <c r="K261" s="30" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="L261" s="2"/>
       <c r="M261" s="16" t="s">
@@ -23790,7 +24208,7 @@
       <c r="AC261" s="2"/>
       <c r="AD261" s="2"/>
       <c r="AE261" s="2" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="AF261" s="4" t="s">
         <v>685</v>
@@ -23829,7 +24247,7 @@
         <v>12</v>
       </c>
       <c r="K262" s="30" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="L262" s="3"/>
       <c r="M262" s="16" t="s">
@@ -23845,10 +24263,10 @@
       <c r="S262" s="22"/>
       <c r="T262" s="36"/>
       <c r="U262" s="40" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="V262" s="2" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="W262" s="4" t="s">
         <v>39</v>
@@ -23865,10 +24283,10 @@
       <c r="AC262" s="2"/>
       <c r="AD262" s="2"/>
       <c r="AE262" s="2" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="AF262" s="4" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="AG262" s="4"/>
       <c r="AH262" s="2" t="s">
@@ -23906,7 +24324,7 @@
         <v>12</v>
       </c>
       <c r="K263" s="30" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="L263" s="3"/>
       <c r="M263" s="16" t="s">
@@ -23923,7 +24341,7 @@
         <v>874</v>
       </c>
       <c r="V263" s="2" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="W263" s="4" t="s">
         <v>39</v>
@@ -23944,10 +24362,10 @@
         <v>875</v>
       </c>
       <c r="AE263" s="2" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="AF263" s="4" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="AG263" s="4"/>
       <c r="AH263" s="2"/>
@@ -23983,7 +24401,7 @@
         <v>12</v>
       </c>
       <c r="K264" s="30" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="L264" s="3"/>
       <c r="M264" s="16" t="s">
@@ -24021,10 +24439,10 @@
         <v>879</v>
       </c>
       <c r="AE264" s="2" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="AF264" s="4" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="AG264" s="4"/>
       <c r="AH264" s="2"/>
@@ -24060,7 +24478,7 @@
         <v>12</v>
       </c>
       <c r="K265" s="30" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="L265" s="3"/>
       <c r="M265" s="16" t="s">
@@ -24077,7 +24495,7 @@
         <v>843</v>
       </c>
       <c r="V265" s="2" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="W265" s="4" t="s">
         <v>39</v>
@@ -24092,7 +24510,7 @@
       <c r="AC265" s="2"/>
       <c r="AD265" s="2"/>
       <c r="AE265" s="2" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="AF265" s="4" t="s">
         <v>685</v>
@@ -24133,11 +24551,11 @@
         <v>12</v>
       </c>
       <c r="K266" s="30" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="L266" s="3"/>
       <c r="M266" s="16" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="N266" s="2"/>
       <c r="O266" s="31"/>
@@ -24150,7 +24568,7 @@
         <v>843</v>
       </c>
       <c r="V266" s="2" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="W266" s="4" t="s">
         <v>39</v>
@@ -24171,10 +24589,10 @@
         <v>883</v>
       </c>
       <c r="AE266" s="2" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="AF266" s="4" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="AG266" s="4"/>
       <c r="AH266" s="2" t="s">
@@ -24219,8 +24637,12 @@
         <v>886</v>
       </c>
       <c r="N267" s="2"/>
-      <c r="O267" s="31"/>
-      <c r="P267" s="31"/>
+      <c r="O267" s="31">
+        <v>-67</v>
+      </c>
+      <c r="P267" s="31">
+        <v>-62</v>
+      </c>
       <c r="Q267" s="31"/>
       <c r="R267" s="50"/>
       <c r="S267" s="22" t="s">
@@ -24244,7 +24666,7 @@
       <c r="AC267" s="2"/>
       <c r="AD267" s="2"/>
       <c r="AE267" s="2" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="AF267" s="4" t="s">
         <v>685</v>
@@ -25001,7 +25423,7 @@
         <v>15</v>
       </c>
       <c r="K278" s="30" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="L278" s="2"/>
       <c r="M278" s="16" t="s">
@@ -25035,7 +25457,7 @@
         <v>915</v>
       </c>
       <c r="AE278" s="2" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="AF278" s="4" t="s">
         <v>685</v>
@@ -26365,9 +26787,15 @@
       <c r="N297" s="3" t="s">
         <v>964</v>
       </c>
-      <c r="O297" s="31"/>
-      <c r="P297" s="31"/>
-      <c r="Q297" s="31"/>
+      <c r="O297" s="31">
+        <v>-4.5</v>
+      </c>
+      <c r="P297" s="31">
+        <v>8.4</v>
+      </c>
+      <c r="Q297" s="31">
+        <v>0.8</v>
+      </c>
       <c r="R297" s="50"/>
       <c r="S297" s="22" t="s">
         <v>39</v>
@@ -26666,10 +27094,10 @@
       </c>
       <c r="T301" s="36"/>
       <c r="U301" s="40" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="V301" s="2" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="W301" s="4" t="s">
         <v>39</v>
@@ -27419,7 +27847,7 @@
         <v>1007</v>
       </c>
       <c r="V311" s="2" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="W311" s="4" t="s">
         <v>39</v>
@@ -27473,7 +27901,7 @@
         <v>12</v>
       </c>
       <c r="K312" s="30" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="L312" s="2"/>
       <c r="M312" s="16" t="s">
@@ -27505,7 +27933,7 @@
       <c r="AC312" s="2"/>
       <c r="AD312" s="2"/>
       <c r="AE312" s="2" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="AF312" s="4" t="s">
         <v>685</v>
@@ -27694,7 +28122,7 @@
         <v>15</v>
       </c>
       <c r="K315" s="30" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="L315" s="2"/>
       <c r="M315" s="16" t="s">
@@ -27726,7 +28154,7 @@
       <c r="AC315" s="2"/>
       <c r="AD315" s="2"/>
       <c r="AE315" s="2" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="AF315" s="4" t="s">
         <v>685</v>
@@ -27912,9 +28340,15 @@
         <v>1029</v>
       </c>
       <c r="N318" s="2"/>
-      <c r="O318" s="31"/>
-      <c r="P318" s="31"/>
-      <c r="Q318" s="31"/>
+      <c r="O318" s="31">
+        <v>18.899999999999999</v>
+      </c>
+      <c r="P318" s="31">
+        <v>43.7</v>
+      </c>
+      <c r="Q318" s="31">
+        <v>31.6</v>
+      </c>
       <c r="R318" s="50"/>
       <c r="S318" s="22" t="s">
         <v>39</v>
@@ -28116,7 +28550,7 @@
         <v>12</v>
       </c>
       <c r="K321" s="30" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="L321" s="2"/>
       <c r="M321" s="16" t="s">
@@ -28133,7 +28567,7 @@
         <v>1034</v>
       </c>
       <c r="V321" s="2" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="W321" s="4" t="s">
         <v>39</v>
@@ -28150,7 +28584,7 @@
       <c r="AC321" s="2"/>
       <c r="AD321" s="2"/>
       <c r="AE321" s="2" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="AF321" s="4" t="s">
         <v>685</v>
@@ -28189,7 +28623,7 @@
         <v>12</v>
       </c>
       <c r="K322" s="30" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="L322" s="2"/>
       <c r="M322" s="16" t="s">
@@ -28206,7 +28640,7 @@
         <v>1038</v>
       </c>
       <c r="V322" s="2" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="W322" s="4" t="s">
         <v>39</v>
@@ -28223,7 +28657,7 @@
       <c r="AC322" s="2"/>
       <c r="AD322" s="2"/>
       <c r="AE322" s="2" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="AF322" s="4" t="s">
         <v>685</v>
@@ -28258,7 +28692,7 @@
         <v>15</v>
       </c>
       <c r="K323" s="30" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="L323" s="2"/>
       <c r="M323" s="16" t="s">
@@ -28275,7 +28709,7 @@
         <v>1041</v>
       </c>
       <c r="V323" s="2" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="W323" s="4" t="s">
         <v>39</v>
@@ -28292,7 +28726,7 @@
       <c r="AC323" s="2"/>
       <c r="AD323" s="2"/>
       <c r="AE323" s="2" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="AF323" s="4" t="s">
         <v>685</v>
@@ -28327,7 +28761,7 @@
         <v>15</v>
       </c>
       <c r="K324" s="30" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="L324" s="2"/>
       <c r="M324" s="16" t="s">
@@ -28341,10 +28775,10 @@
       <c r="S324" s="22"/>
       <c r="T324" s="36"/>
       <c r="U324" s="40" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="V324" s="2" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="W324" s="4" t="s">
         <v>39</v>
@@ -28361,7 +28795,7 @@
       <c r="AC324" s="2"/>
       <c r="AD324" s="2"/>
       <c r="AE324" s="2" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="AF324" s="4" t="s">
         <v>685</v>
@@ -28396,7 +28830,7 @@
         <v>12</v>
       </c>
       <c r="K325" s="30" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="L325" s="2"/>
       <c r="M325" s="16" t="s">
@@ -28413,7 +28847,7 @@
         <v>1046</v>
       </c>
       <c r="V325" s="2" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="W325" s="4" t="s">
         <v>39</v>
@@ -28428,7 +28862,7 @@
       <c r="AC325" s="2"/>
       <c r="AD325" s="2"/>
       <c r="AE325" s="2" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="AF325" s="4" t="s">
         <v>685</v>
@@ -28467,7 +28901,7 @@
         <v>12</v>
       </c>
       <c r="K326" s="30" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="L326" s="2"/>
       <c r="M326" s="16" t="s">
@@ -28481,10 +28915,10 @@
       <c r="S326" s="22"/>
       <c r="T326" s="36"/>
       <c r="U326" s="40" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="V326" s="2" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="W326" s="4" t="s">
         <v>39</v>
@@ -28501,7 +28935,7 @@
       <c r="AC326" s="2"/>
       <c r="AD326" s="2"/>
       <c r="AE326" s="2" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="AF326" s="4" t="s">
         <v>685</v>
@@ -28536,7 +28970,7 @@
         <v>15</v>
       </c>
       <c r="K327" s="30" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="L327" s="2"/>
       <c r="M327" s="16" t="s">
@@ -28550,10 +28984,10 @@
       <c r="S327" s="22"/>
       <c r="T327" s="36"/>
       <c r="U327" s="40" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="V327" s="2" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="W327" s="4" t="s">
         <v>39</v>
@@ -28570,7 +29004,7 @@
       <c r="AC327" s="2"/>
       <c r="AD327" s="2"/>
       <c r="AE327" s="2" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="AF327" s="4" t="s">
         <v>685</v>
@@ -28605,7 +29039,7 @@
         <v>12</v>
       </c>
       <c r="K328" s="30" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="L328" s="2"/>
       <c r="M328" s="16" t="s">
@@ -28619,10 +29053,10 @@
       <c r="S328" s="22"/>
       <c r="T328" s="36"/>
       <c r="U328" s="40" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="V328" s="2" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="W328" s="4" t="s">
         <v>39</v>
@@ -28637,7 +29071,7 @@
       <c r="AC328" s="2"/>
       <c r="AD328" s="2"/>
       <c r="AE328" s="2" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="AF328" s="4" t="s">
         <v>685</v>
@@ -29094,7 +29528,7 @@
         <v>12</v>
       </c>
       <c r="K335" s="30" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="L335" s="2"/>
       <c r="M335" s="16" t="s">
@@ -29108,10 +29542,10 @@
       <c r="S335" s="22"/>
       <c r="T335" s="36"/>
       <c r="U335" s="40" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="V335" s="2" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="W335" s="4" t="s">
         <v>39</v>
@@ -29128,7 +29562,7 @@
       <c r="AC335" s="2"/>
       <c r="AD335" s="2"/>
       <c r="AE335" s="2" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="AF335" s="4" t="s">
         <v>685</v>
@@ -32029,7 +32463,7 @@
         <v>39</v>
       </c>
       <c r="AB2" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="AC2" t="s">
         <v>685</v>
@@ -32088,7 +32522,7 @@
         <v>39</v>
       </c>
       <c r="AB3" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="AC3" t="s">
         <v>685</v>
@@ -32144,7 +32578,7 @@
         <v>39</v>
       </c>
       <c r="AB4" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="AC4" t="s">
         <v>685</v>
@@ -32229,7 +32663,7 @@
         <v>31478</v>
       </c>
       <c r="D6" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="E6">
         <v>99999</v>
@@ -32250,7 +32684,7 @@
         <v>1092</v>
       </c>
       <c r="M6" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="N6" t="s">
         <v>97</v>
@@ -32271,16 +32705,16 @@
         <v>39</v>
       </c>
       <c r="AB6" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="AC6" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="AD6" t="s">
         <v>39</v>
       </c>
       <c r="AE6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="7" spans="1:32" x14ac:dyDescent="0.4">
@@ -32294,7 +32728,7 @@
         <v>31329</v>
       </c>
       <c r="D7" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E7">
         <v>99999</v>
@@ -32312,7 +32746,7 @@
         <v>12</v>
       </c>
       <c r="M7" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="R7" t="s">
         <v>39</v>
@@ -32330,16 +32764,16 @@
         <v>39</v>
       </c>
       <c r="AB7" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="AC7" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="AD7" t="s">
         <v>39</v>
       </c>
       <c r="AE7" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
   </sheetData>

--- a/气象/For_Python_站点信息和记录.xlsx
+++ b/气象/For_Python_站点信息和记录.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\文档\GIT SYNC\default\气象\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB1112A2-E379-411E-9D67-B5F44C0C5272}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C730FE82-B28D-4BF2-A3FA-61B1C5365E51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4264,15 +4264,9 @@
       <c r="N2" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="O2" s="31">
-        <v>8.3000000000000007</v>
-      </c>
-      <c r="P2" s="31">
-        <v>26.4</v>
-      </c>
-      <c r="Q2" s="31">
-        <v>16.690000000000001</v>
-      </c>
+      <c r="O2" s="31"/>
+      <c r="P2" s="31"/>
+      <c r="Q2" s="31"/>
       <c r="R2" s="50"/>
       <c r="S2" s="22" t="s">
         <v>39</v>
@@ -4345,12 +4339,8 @@
       <c r="N3" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="O3" s="31">
-        <v>6.5</v>
-      </c>
-      <c r="P3" s="31">
-        <v>26.1</v>
-      </c>
+      <c r="O3" s="31"/>
+      <c r="P3" s="31"/>
       <c r="Q3" s="31"/>
       <c r="R3" s="50" t="s">
         <v>47</v>
@@ -4426,12 +4416,8 @@
       <c r="N4" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="O4" s="31">
-        <v>5.4</v>
-      </c>
-      <c r="P4" s="31">
-        <v>24.3</v>
-      </c>
+      <c r="O4" s="31"/>
+      <c r="P4" s="31"/>
       <c r="Q4" s="31"/>
       <c r="R4" s="50" t="s">
         <v>51</v>
@@ -4576,15 +4562,9 @@
       <c r="N6" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="O6" s="31">
-        <v>-1.1000000000000001</v>
-      </c>
-      <c r="P6" s="31">
-        <v>20.5</v>
-      </c>
-      <c r="Q6" s="31">
-        <v>9.24</v>
-      </c>
+      <c r="O6" s="31"/>
+      <c r="P6" s="31"/>
+      <c r="Q6" s="31"/>
       <c r="R6" s="52" t="s">
         <v>59</v>
       </c>
@@ -4657,12 +4637,8 @@
       <c r="N7" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="O7" s="31">
-        <v>0.4</v>
-      </c>
-      <c r="P7" s="31">
-        <v>16.2</v>
-      </c>
+      <c r="O7" s="31"/>
+      <c r="P7" s="31"/>
       <c r="Q7" s="31"/>
       <c r="R7" s="50"/>
       <c r="S7" s="22"/>
@@ -4740,15 +4716,9 @@
         <v>67</v>
       </c>
       <c r="N8" s="2"/>
-      <c r="O8" s="31">
-        <v>4.5</v>
-      </c>
-      <c r="P8" s="31">
-        <v>22.3</v>
-      </c>
-      <c r="Q8" s="31">
-        <v>13.61</v>
-      </c>
+      <c r="O8" s="31"/>
+      <c r="P8" s="31"/>
+      <c r="Q8" s="31"/>
       <c r="R8" s="50"/>
       <c r="S8" s="22" t="s">
         <v>39</v>
@@ -4825,15 +4795,9 @@
         <v>72</v>
       </c>
       <c r="N9" s="2"/>
-      <c r="O9" s="31">
-        <v>7.8</v>
-      </c>
-      <c r="P9" s="31">
-        <v>24.5</v>
-      </c>
-      <c r="Q9" s="31">
-        <v>16.16</v>
-      </c>
+      <c r="O9" s="31"/>
+      <c r="P9" s="31"/>
+      <c r="Q9" s="31"/>
       <c r="R9" s="50"/>
       <c r="S9" s="22" t="s">
         <v>39</v>
@@ -4914,15 +4878,9 @@
       <c r="N10" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="O10" s="31">
-        <v>0.1</v>
-      </c>
-      <c r="P10" s="31">
-        <v>22.8</v>
-      </c>
-      <c r="Q10" s="31">
-        <v>12.32</v>
-      </c>
+      <c r="O10" s="31"/>
+      <c r="P10" s="31"/>
+      <c r="Q10" s="31"/>
       <c r="R10" s="50"/>
       <c r="S10" s="22" t="s">
         <v>39</v>
@@ -5001,15 +4959,9 @@
       <c r="N11" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="O11" s="31">
-        <v>-0.8</v>
-      </c>
-      <c r="P11" s="31">
-        <v>19.3</v>
-      </c>
-      <c r="Q11" s="31">
-        <v>9.8000000000000007</v>
-      </c>
+      <c r="O11" s="31"/>
+      <c r="P11" s="31"/>
+      <c r="Q11" s="31"/>
       <c r="R11" s="50" t="s">
         <v>77</v>
       </c>
@@ -5088,15 +5040,9 @@
         <v>80</v>
       </c>
       <c r="N12" s="2"/>
-      <c r="O12" s="31">
-        <v>1.5</v>
-      </c>
-      <c r="P12" s="31">
-        <v>19.100000000000001</v>
-      </c>
-      <c r="Q12" s="31">
-        <v>10.4</v>
-      </c>
+      <c r="O12" s="31"/>
+      <c r="P12" s="31"/>
+      <c r="Q12" s="31"/>
       <c r="R12" s="50" t="s">
         <v>81</v>
       </c>
@@ -5177,15 +5123,9 @@
       <c r="N13" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="O13" s="31">
-        <v>0.4</v>
-      </c>
-      <c r="P13" s="31">
-        <v>17.2</v>
-      </c>
-      <c r="Q13" s="31">
-        <v>8.84</v>
-      </c>
+      <c r="O13" s="31"/>
+      <c r="P13" s="31"/>
+      <c r="Q13" s="31"/>
       <c r="R13" s="50" t="s">
         <v>84</v>
       </c>
@@ -5264,15 +5204,9 @@
         <v>86</v>
       </c>
       <c r="N14" s="2"/>
-      <c r="O14" s="31">
-        <v>5.4</v>
-      </c>
-      <c r="P14" s="31">
-        <v>19</v>
-      </c>
-      <c r="Q14" s="31">
-        <v>12.28</v>
-      </c>
+      <c r="O14" s="31"/>
+      <c r="P14" s="31"/>
+      <c r="Q14" s="31"/>
       <c r="R14" s="50"/>
       <c r="S14" s="22" t="s">
         <v>39</v>
@@ -5353,15 +5287,9 @@
         <v>91</v>
       </c>
       <c r="N15" s="2"/>
-      <c r="O15" s="31">
-        <v>3.4</v>
-      </c>
-      <c r="P15" s="31">
-        <v>16.3</v>
-      </c>
-      <c r="Q15" s="31">
-        <v>10.55</v>
-      </c>
+      <c r="O15" s="31"/>
+      <c r="P15" s="31"/>
+      <c r="Q15" s="31"/>
       <c r="R15" s="50"/>
       <c r="S15" s="22" t="s">
         <v>39</v>
@@ -5438,15 +5366,9 @@
         <v>94</v>
       </c>
       <c r="N16" s="2"/>
-      <c r="O16" s="31">
-        <v>1.8</v>
-      </c>
-      <c r="P16" s="31">
-        <v>19.2</v>
-      </c>
-      <c r="Q16" s="31">
-        <v>11.34</v>
-      </c>
+      <c r="O16" s="31"/>
+      <c r="P16" s="31"/>
+      <c r="Q16" s="31"/>
       <c r="R16" s="50"/>
       <c r="S16" s="22"/>
       <c r="T16" s="36"/>
@@ -5516,7 +5438,7 @@
         <v>97</v>
       </c>
       <c r="O17" s="31">
-        <v>-5.6</v>
+        <v>-4.7</v>
       </c>
       <c r="P17" s="31"/>
       <c r="Q17" s="31"/>
@@ -9830,15 +9752,9 @@
       <c r="N78" s="23" t="s">
         <v>97</v>
       </c>
-      <c r="O78" s="31">
-        <v>6.3</v>
-      </c>
-      <c r="P78" s="31">
-        <v>17</v>
-      </c>
-      <c r="Q78" s="31">
-        <v>10.85</v>
-      </c>
+      <c r="O78" s="31"/>
+      <c r="P78" s="31"/>
+      <c r="Q78" s="31"/>
       <c r="R78" s="50" t="s">
         <v>210</v>
       </c>
@@ -10152,15 +10068,9 @@
       <c r="N82" s="3" t="s">
         <v>224</v>
       </c>
-      <c r="O82" s="31">
-        <v>10.8</v>
-      </c>
-      <c r="P82" s="31">
-        <v>21.7</v>
-      </c>
-      <c r="Q82" s="31">
-        <v>15.15</v>
-      </c>
+      <c r="O82" s="31"/>
+      <c r="P82" s="31"/>
+      <c r="Q82" s="31"/>
       <c r="R82" s="50"/>
       <c r="S82" s="22" t="s">
         <v>39</v>
@@ -10241,15 +10151,9 @@
       <c r="N83" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="O83" s="31">
-        <v>9.5</v>
-      </c>
-      <c r="P83" s="31">
-        <v>19.5</v>
-      </c>
-      <c r="Q83" s="31">
-        <v>13.49</v>
-      </c>
+      <c r="O83" s="31"/>
+      <c r="P83" s="31"/>
+      <c r="Q83" s="31"/>
       <c r="R83" s="50"/>
       <c r="S83" s="22" t="s">
         <v>39</v>
@@ -10405,15 +10309,9 @@
       <c r="N85" s="23" t="s">
         <v>237</v>
       </c>
-      <c r="O85" s="31">
-        <v>6.5</v>
-      </c>
-      <c r="P85" s="31">
-        <v>23</v>
-      </c>
-      <c r="Q85" s="31">
-        <v>13.41</v>
-      </c>
+      <c r="O85" s="31"/>
+      <c r="P85" s="31"/>
+      <c r="Q85" s="31"/>
       <c r="R85" s="50"/>
       <c r="S85" s="22" t="s">
         <v>39</v>
@@ -10569,15 +10467,9 @@
         <v>246</v>
       </c>
       <c r="N87" s="2"/>
-      <c r="O87" s="31">
-        <v>8</v>
-      </c>
-      <c r="P87" s="31">
-        <v>26.4</v>
-      </c>
-      <c r="Q87" s="31">
-        <v>17.190000000000001</v>
-      </c>
+      <c r="O87" s="31"/>
+      <c r="P87" s="31"/>
+      <c r="Q87" s="31"/>
       <c r="R87" s="50"/>
       <c r="S87" s="22" t="s">
         <v>39</v>
@@ -10737,15 +10629,9 @@
         <v>252</v>
       </c>
       <c r="N89" s="2"/>
-      <c r="O89" s="31">
-        <v>3.2</v>
-      </c>
-      <c r="P89" s="31">
-        <v>23.8</v>
-      </c>
-      <c r="Q89" s="31">
-        <v>12.91</v>
-      </c>
+      <c r="O89" s="31"/>
+      <c r="P89" s="31"/>
+      <c r="Q89" s="31"/>
       <c r="R89" s="50" t="s">
         <v>253</v>
       </c>
@@ -11053,15 +10939,9 @@
         <v>273</v>
       </c>
       <c r="N93" s="2"/>
-      <c r="O93" s="31">
-        <v>11.9</v>
-      </c>
-      <c r="P93" s="31">
-        <v>15.3</v>
-      </c>
-      <c r="Q93" s="31">
-        <v>13.55</v>
-      </c>
+      <c r="O93" s="31"/>
+      <c r="P93" s="31"/>
+      <c r="Q93" s="31"/>
       <c r="R93" s="50"/>
       <c r="S93" s="22" t="s">
         <v>39</v>
@@ -11138,15 +11018,9 @@
         <v>280</v>
       </c>
       <c r="N94" s="2"/>
-      <c r="O94" s="31">
-        <v>19.2</v>
-      </c>
-      <c r="P94" s="31">
-        <v>24.6</v>
-      </c>
-      <c r="Q94" s="31">
-        <v>22.1</v>
-      </c>
+      <c r="O94" s="31"/>
+      <c r="P94" s="31"/>
+      <c r="Q94" s="31"/>
       <c r="R94" s="50"/>
       <c r="S94" s="22" t="s">
         <v>39</v>
@@ -11310,15 +11184,9 @@
         <v>293</v>
       </c>
       <c r="N96" s="2"/>
-      <c r="O96" s="31">
-        <v>16</v>
-      </c>
-      <c r="P96" s="31">
-        <v>25.3</v>
-      </c>
-      <c r="Q96" s="31">
-        <v>20.5</v>
-      </c>
+      <c r="O96" s="31"/>
+      <c r="P96" s="31"/>
+      <c r="Q96" s="31"/>
       <c r="R96" s="50"/>
       <c r="S96" s="22" t="s">
         <v>39</v>
@@ -11486,15 +11354,9 @@
         <v>307</v>
       </c>
       <c r="N98" s="2"/>
-      <c r="O98" s="31">
-        <v>17.100000000000001</v>
-      </c>
-      <c r="P98" s="31">
-        <v>25.1</v>
-      </c>
-      <c r="Q98" s="31">
-        <v>20.38</v>
-      </c>
+      <c r="O98" s="31"/>
+      <c r="P98" s="31"/>
+      <c r="Q98" s="31"/>
       <c r="R98" s="50"/>
       <c r="S98" s="22" t="s">
         <v>39</v>
@@ -11897,15 +11759,9 @@
         <v>330</v>
       </c>
       <c r="N103" s="2"/>
-      <c r="O103" s="31">
-        <v>6</v>
-      </c>
-      <c r="P103" s="31">
-        <v>21.8</v>
-      </c>
-      <c r="Q103" s="31">
-        <v>12.95</v>
-      </c>
+      <c r="O103" s="31"/>
+      <c r="P103" s="31"/>
+      <c r="Q103" s="31"/>
       <c r="R103" s="50"/>
       <c r="S103" s="22" t="s">
         <v>39</v>
@@ -12146,15 +12002,9 @@
       <c r="N106" s="2" t="s">
         <v>224</v>
       </c>
-      <c r="O106" s="31">
-        <v>10.8</v>
-      </c>
-      <c r="P106" s="31">
-        <v>13.8</v>
-      </c>
-      <c r="Q106" s="31">
-        <v>11.84</v>
-      </c>
+      <c r="O106" s="31"/>
+      <c r="P106" s="31"/>
+      <c r="Q106" s="31"/>
       <c r="R106" s="50"/>
       <c r="S106" s="22" t="s">
         <v>39</v>
@@ -12774,15 +12624,9 @@
         <v>363</v>
       </c>
       <c r="N114" s="2"/>
-      <c r="O114" s="31">
-        <v>4.5</v>
-      </c>
-      <c r="P114" s="31">
-        <v>14.3</v>
-      </c>
-      <c r="Q114" s="31">
-        <v>8.56</v>
-      </c>
+      <c r="O114" s="31"/>
+      <c r="P114" s="31"/>
+      <c r="Q114" s="31"/>
       <c r="R114" s="50"/>
       <c r="S114" s="22" t="s">
         <v>39</v>
@@ -12861,15 +12705,9 @@
       <c r="N115" s="23" t="s">
         <v>97</v>
       </c>
-      <c r="O115" s="31">
-        <v>-1.8</v>
-      </c>
-      <c r="P115" s="31">
-        <v>12.9</v>
-      </c>
-      <c r="Q115" s="31">
-        <v>4.78</v>
-      </c>
+      <c r="O115" s="31"/>
+      <c r="P115" s="31"/>
+      <c r="Q115" s="31"/>
       <c r="R115" s="50"/>
       <c r="S115" s="22" t="s">
         <v>39</v>
@@ -12952,15 +12790,9 @@
       <c r="N116" s="23" t="s">
         <v>97</v>
       </c>
-      <c r="O116" s="31">
-        <v>1.4</v>
-      </c>
-      <c r="P116" s="31">
-        <v>10.1</v>
-      </c>
-      <c r="Q116" s="31">
-        <v>4.59</v>
-      </c>
+      <c r="O116" s="31"/>
+      <c r="P116" s="31"/>
+      <c r="Q116" s="31"/>
       <c r="R116" s="50"/>
       <c r="S116" s="22" t="s">
         <v>39</v>
@@ -13365,15 +13197,9 @@
         <v>397</v>
       </c>
       <c r="N121" s="2"/>
-      <c r="O121" s="31">
-        <v>23.7</v>
-      </c>
-      <c r="P121" s="31">
-        <v>40.200000000000003</v>
-      </c>
-      <c r="Q121" s="31">
-        <v>32.42</v>
-      </c>
+      <c r="O121" s="31"/>
+      <c r="P121" s="31"/>
+      <c r="Q121" s="31"/>
       <c r="R121" s="50"/>
       <c r="S121" s="22" t="s">
         <v>39</v>
@@ -13452,15 +13278,9 @@
         <v>402</v>
       </c>
       <c r="N122" s="2"/>
-      <c r="O122" s="31">
-        <v>18.899999999999999</v>
-      </c>
-      <c r="P122" s="31">
-        <v>32.6</v>
-      </c>
-      <c r="Q122" s="31">
-        <v>24.39</v>
-      </c>
+      <c r="O122" s="31"/>
+      <c r="P122" s="31"/>
+      <c r="Q122" s="31"/>
       <c r="R122" s="50"/>
       <c r="S122" s="22" t="s">
         <v>39</v>
@@ -13543,15 +13363,9 @@
         <v>406</v>
       </c>
       <c r="N123" s="2"/>
-      <c r="O123" s="31">
-        <v>2.8</v>
-      </c>
-      <c r="P123" s="31">
-        <v>23.2</v>
-      </c>
-      <c r="Q123" s="31">
-        <v>13.43</v>
-      </c>
+      <c r="O123" s="31"/>
+      <c r="P123" s="31"/>
+      <c r="Q123" s="31"/>
       <c r="R123" s="50"/>
       <c r="S123" s="22" t="s">
         <v>39</v>
@@ -13709,15 +13523,9 @@
         <v>414</v>
       </c>
       <c r="N125" s="2"/>
-      <c r="O125" s="31">
-        <v>15.3</v>
-      </c>
-      <c r="P125" s="31">
-        <v>23.8</v>
-      </c>
-      <c r="Q125" s="31">
-        <v>19</v>
-      </c>
+      <c r="O125" s="31"/>
+      <c r="P125" s="31"/>
+      <c r="Q125" s="31"/>
       <c r="R125" s="50"/>
       <c r="S125" s="22" t="s">
         <v>39</v>
@@ -13800,15 +13608,9 @@
         <v>419</v>
       </c>
       <c r="N126" s="2"/>
-      <c r="O126" s="31">
-        <v>18.399999999999999</v>
-      </c>
-      <c r="P126" s="31">
-        <v>28.2</v>
-      </c>
-      <c r="Q126" s="31">
-        <v>22.26</v>
-      </c>
+      <c r="O126" s="31"/>
+      <c r="P126" s="31"/>
+      <c r="Q126" s="31"/>
       <c r="R126" s="50"/>
       <c r="S126" s="22" t="s">
         <v>39</v>
@@ -13881,15 +13683,9 @@
         <v>422</v>
       </c>
       <c r="N127" s="2"/>
-      <c r="O127" s="31">
-        <v>18.899999999999999</v>
-      </c>
-      <c r="P127" s="31">
-        <v>27.8</v>
-      </c>
-      <c r="Q127" s="31">
-        <v>22.52</v>
-      </c>
+      <c r="O127" s="31"/>
+      <c r="P127" s="31"/>
+      <c r="Q127" s="31"/>
       <c r="R127" s="50"/>
       <c r="S127" s="22" t="s">
         <v>39</v>
@@ -13966,15 +13762,9 @@
         <v>428</v>
       </c>
       <c r="N128" s="2"/>
-      <c r="O128" s="31">
-        <v>15.4</v>
-      </c>
-      <c r="P128" s="31">
-        <v>29.1</v>
-      </c>
-      <c r="Q128" s="31">
-        <v>22.19</v>
-      </c>
+      <c r="O128" s="31"/>
+      <c r="P128" s="31"/>
+      <c r="Q128" s="31"/>
       <c r="R128" s="50"/>
       <c r="S128" s="22" t="s">
         <v>39</v>
@@ -14055,15 +13845,9 @@
         <v>434</v>
       </c>
       <c r="N129" s="2"/>
-      <c r="O129" s="31">
-        <v>16.899999999999999</v>
-      </c>
-      <c r="P129" s="31">
-        <v>27.6</v>
-      </c>
-      <c r="Q129" s="31">
-        <v>21.88</v>
-      </c>
+      <c r="O129" s="31"/>
+      <c r="P129" s="31"/>
+      <c r="Q129" s="31"/>
       <c r="R129" s="50"/>
       <c r="S129" s="22" t="s">
         <v>39</v>
@@ -14140,15 +13924,9 @@
         <v>438</v>
       </c>
       <c r="N130" s="2"/>
-      <c r="O130" s="31">
-        <v>16</v>
-      </c>
-      <c r="P130" s="31">
-        <v>27.1</v>
-      </c>
-      <c r="Q130" s="31">
-        <v>20.25</v>
-      </c>
+      <c r="O130" s="31"/>
+      <c r="P130" s="31"/>
+      <c r="Q130" s="31"/>
       <c r="R130" s="50"/>
       <c r="S130" s="22" t="s">
         <v>39</v>
@@ -14229,15 +14007,9 @@
         <v>444</v>
       </c>
       <c r="N131" s="2"/>
-      <c r="O131" s="31">
-        <v>7.1</v>
-      </c>
-      <c r="P131" s="31">
-        <v>22.8</v>
-      </c>
-      <c r="Q131" s="31">
-        <v>13.46</v>
-      </c>
+      <c r="O131" s="31"/>
+      <c r="P131" s="31"/>
+      <c r="Q131" s="31"/>
       <c r="R131" s="50"/>
       <c r="S131" s="22" t="s">
         <v>39</v>
@@ -14318,15 +14090,9 @@
         <v>449</v>
       </c>
       <c r="N132" s="2"/>
-      <c r="O132" s="31">
-        <v>19.600000000000001</v>
-      </c>
-      <c r="P132" s="31">
-        <v>26</v>
-      </c>
-      <c r="Q132" s="31">
-        <v>21.84</v>
-      </c>
+      <c r="O132" s="31"/>
+      <c r="P132" s="31"/>
+      <c r="Q132" s="31"/>
       <c r="R132" s="50"/>
       <c r="S132" s="22" t="s">
         <v>39</v>
@@ -14405,15 +14171,9 @@
         <v>455</v>
       </c>
       <c r="N133" s="2"/>
-      <c r="O133" s="31">
-        <v>20.5</v>
-      </c>
-      <c r="P133" s="31">
-        <v>31.5</v>
-      </c>
-      <c r="Q133" s="31">
-        <v>25.65</v>
-      </c>
+      <c r="O133" s="31"/>
+      <c r="P133" s="31"/>
+      <c r="Q133" s="31"/>
       <c r="R133" s="50"/>
       <c r="S133" s="22" t="s">
         <v>39</v>
@@ -14492,15 +14252,9 @@
         <v>461</v>
       </c>
       <c r="N134" s="2"/>
-      <c r="O134" s="31">
-        <v>22.7</v>
-      </c>
-      <c r="P134" s="31">
-        <v>30.1</v>
-      </c>
-      <c r="Q134" s="31">
-        <v>25.57</v>
-      </c>
+      <c r="O134" s="31"/>
+      <c r="P134" s="31"/>
+      <c r="Q134" s="31"/>
       <c r="R134" s="50"/>
       <c r="S134" s="22" t="s">
         <v>39</v>
@@ -14658,15 +14412,9 @@
         <v>473</v>
       </c>
       <c r="N136" s="2"/>
-      <c r="O136" s="31">
-        <v>24.2</v>
-      </c>
-      <c r="P136" s="31">
-        <v>30.8</v>
-      </c>
-      <c r="Q136" s="31">
-        <v>26.31</v>
-      </c>
+      <c r="O136" s="31"/>
+      <c r="P136" s="31"/>
+      <c r="Q136" s="31"/>
       <c r="R136" s="50"/>
       <c r="S136" s="22" t="s">
         <v>39</v>
@@ -14745,15 +14493,9 @@
         <v>479</v>
       </c>
       <c r="N137" s="2"/>
-      <c r="O137" s="31">
-        <v>27.9</v>
-      </c>
-      <c r="P137" s="31">
-        <v>32</v>
-      </c>
-      <c r="Q137" s="31">
-        <v>29.94</v>
-      </c>
+      <c r="O137" s="31"/>
+      <c r="P137" s="31"/>
+      <c r="Q137" s="31"/>
       <c r="R137" s="50"/>
       <c r="S137" s="22" t="s">
         <v>39</v>
@@ -14832,15 +14574,9 @@
         <v>485</v>
       </c>
       <c r="N138" s="2"/>
-      <c r="O138" s="31">
-        <v>24.2</v>
-      </c>
-      <c r="P138" s="31">
-        <v>31.5</v>
-      </c>
-      <c r="Q138" s="31">
-        <v>27.05</v>
-      </c>
+      <c r="O138" s="31"/>
+      <c r="P138" s="31"/>
+      <c r="Q138" s="31"/>
       <c r="R138" s="50"/>
       <c r="S138" s="22" t="s">
         <v>39</v>
@@ -14919,15 +14655,9 @@
         <v>492</v>
       </c>
       <c r="N139" s="2"/>
-      <c r="O139" s="31">
-        <v>26.2</v>
-      </c>
-      <c r="P139" s="31">
-        <v>32.6</v>
-      </c>
-      <c r="Q139" s="31">
-        <v>28.4</v>
-      </c>
+      <c r="O139" s="31"/>
+      <c r="P139" s="31"/>
+      <c r="Q139" s="31"/>
       <c r="R139" s="50"/>
       <c r="S139" s="22" t="s">
         <v>39</v>
@@ -15006,15 +14736,9 @@
         <v>498</v>
       </c>
       <c r="N140" s="2"/>
-      <c r="O140" s="31">
-        <v>26.5</v>
-      </c>
-      <c r="P140" s="31">
-        <v>33.700000000000003</v>
-      </c>
-      <c r="Q140" s="31">
-        <v>29.57</v>
-      </c>
+      <c r="O140" s="31"/>
+      <c r="P140" s="31"/>
+      <c r="Q140" s="31"/>
       <c r="R140" s="50"/>
       <c r="S140" s="22" t="s">
         <v>39</v>
@@ -15093,15 +14817,9 @@
         <v>503</v>
       </c>
       <c r="N141" s="2"/>
-      <c r="O141" s="31">
-        <v>26.5</v>
-      </c>
-      <c r="P141" s="31">
-        <v>32.700000000000003</v>
-      </c>
-      <c r="Q141" s="31">
-        <v>29.36</v>
-      </c>
+      <c r="O141" s="31"/>
+      <c r="P141" s="31"/>
+      <c r="Q141" s="31"/>
       <c r="R141" s="50"/>
       <c r="S141" s="22" t="s">
         <v>39</v>
@@ -15257,15 +14975,9 @@
         <v>514</v>
       </c>
       <c r="N143" s="2"/>
-      <c r="O143" s="31">
-        <v>25.7</v>
-      </c>
-      <c r="P143" s="31">
-        <v>30.4</v>
-      </c>
-      <c r="Q143" s="31">
-        <v>27.05</v>
-      </c>
+      <c r="O143" s="31"/>
+      <c r="P143" s="31"/>
+      <c r="Q143" s="31"/>
       <c r="R143" s="50"/>
       <c r="S143" s="22" t="s">
         <v>39</v>
@@ -15344,15 +15056,9 @@
         <v>520</v>
       </c>
       <c r="N144" s="2"/>
-      <c r="O144" s="31">
-        <v>25.9</v>
-      </c>
-      <c r="P144" s="31">
-        <v>36.299999999999997</v>
-      </c>
-      <c r="Q144" s="31">
-        <v>29.54</v>
-      </c>
+      <c r="O144" s="31"/>
+      <c r="P144" s="31"/>
+      <c r="Q144" s="31"/>
       <c r="R144" s="50"/>
       <c r="S144" s="22" t="s">
         <v>39</v>
@@ -15583,15 +15289,9 @@
         <v>535</v>
       </c>
       <c r="N147" s="2"/>
-      <c r="O147" s="31">
-        <v>29.1</v>
-      </c>
-      <c r="P147" s="31">
-        <v>31.4</v>
-      </c>
-      <c r="Q147" s="31">
-        <v>29.8</v>
-      </c>
+      <c r="O147" s="31"/>
+      <c r="P147" s="31"/>
+      <c r="Q147" s="31"/>
       <c r="R147" s="50"/>
       <c r="S147" s="22" t="s">
         <v>39</v>
@@ -15666,15 +15366,9 @@
         <v>538</v>
       </c>
       <c r="N148" s="2"/>
-      <c r="O148" s="31">
-        <v>26.4</v>
-      </c>
-      <c r="P148" s="31">
-        <v>31.3</v>
-      </c>
-      <c r="Q148" s="31">
-        <v>27.96</v>
-      </c>
+      <c r="O148" s="31"/>
+      <c r="P148" s="31"/>
+      <c r="Q148" s="31"/>
       <c r="R148" s="50"/>
       <c r="S148" s="22" t="s">
         <v>39</v>
@@ -15753,15 +15447,9 @@
         <v>544</v>
       </c>
       <c r="N149" s="2"/>
-      <c r="O149" s="31">
-        <v>23</v>
-      </c>
-      <c r="P149" s="31">
-        <v>32.9</v>
-      </c>
-      <c r="Q149" s="31">
-        <v>26.9</v>
-      </c>
+      <c r="O149" s="31"/>
+      <c r="P149" s="31"/>
+      <c r="Q149" s="31"/>
       <c r="R149" s="50"/>
       <c r="S149" s="22" t="s">
         <v>39</v>
@@ -15838,15 +15526,9 @@
         <v>549</v>
       </c>
       <c r="N150" s="2"/>
-      <c r="O150" s="31">
-        <v>19.3</v>
-      </c>
-      <c r="P150" s="31">
-        <v>24.4</v>
-      </c>
-      <c r="Q150" s="31">
-        <v>20.79</v>
-      </c>
+      <c r="O150" s="31"/>
+      <c r="P150" s="31"/>
+      <c r="Q150" s="31"/>
       <c r="R150" s="50"/>
       <c r="S150" s="22" t="s">
         <v>39</v>
@@ -15925,15 +15607,9 @@
         <v>554</v>
       </c>
       <c r="N151" s="2"/>
-      <c r="O151" s="31">
-        <v>20.9</v>
-      </c>
-      <c r="P151" s="31">
-        <v>29.4</v>
-      </c>
-      <c r="Q151" s="31">
-        <v>24.58</v>
-      </c>
+      <c r="O151" s="31"/>
+      <c r="P151" s="31"/>
+      <c r="Q151" s="31"/>
       <c r="R151" s="50"/>
       <c r="S151" s="22" t="s">
         <v>39</v>
@@ -16012,15 +15688,9 @@
         <v>560</v>
       </c>
       <c r="N152" s="2"/>
-      <c r="O152" s="31">
-        <v>25.5</v>
-      </c>
-      <c r="P152" s="31">
-        <v>31</v>
-      </c>
-      <c r="Q152" s="31">
-        <v>26.89</v>
-      </c>
+      <c r="O152" s="31"/>
+      <c r="P152" s="31"/>
+      <c r="Q152" s="31"/>
       <c r="R152" s="50"/>
       <c r="S152" s="22" t="s">
         <v>39</v>
@@ -16170,15 +15840,9 @@
         <v>570</v>
       </c>
       <c r="N154" s="2"/>
-      <c r="O154" s="31">
-        <v>23.6</v>
-      </c>
-      <c r="P154" s="31">
-        <v>31.7</v>
-      </c>
-      <c r="Q154" s="31">
-        <v>26.91</v>
-      </c>
+      <c r="O154" s="31"/>
+      <c r="P154" s="31"/>
+      <c r="Q154" s="31"/>
       <c r="R154" s="50"/>
       <c r="S154" s="22" t="s">
         <v>39</v>
@@ -16259,15 +15923,9 @@
         <v>577</v>
       </c>
       <c r="N155" s="2"/>
-      <c r="O155" s="31">
-        <v>12.2</v>
-      </c>
-      <c r="P155" s="31">
-        <v>20</v>
-      </c>
-      <c r="Q155" s="31">
-        <v>15.49</v>
-      </c>
+      <c r="O155" s="31"/>
+      <c r="P155" s="31"/>
+      <c r="Q155" s="31"/>
       <c r="R155" s="50"/>
       <c r="S155" s="22" t="s">
         <v>39</v>
@@ -16490,15 +16148,9 @@
         <v>587</v>
       </c>
       <c r="N158" s="2"/>
-      <c r="O158" s="31">
-        <v>27.6</v>
-      </c>
-      <c r="P158" s="31">
-        <v>32.799999999999997</v>
-      </c>
-      <c r="Q158" s="31">
-        <v>29.65</v>
-      </c>
+      <c r="O158" s="31"/>
+      <c r="P158" s="31"/>
+      <c r="Q158" s="31"/>
       <c r="R158" s="50"/>
       <c r="S158" s="22" t="s">
         <v>39</v>
@@ -16792,15 +16444,9 @@
         <v>602</v>
       </c>
       <c r="N162" s="2"/>
-      <c r="O162" s="31">
-        <v>14.2</v>
-      </c>
-      <c r="P162" s="31">
-        <v>28.1</v>
-      </c>
-      <c r="Q162" s="31">
-        <v>20.04</v>
-      </c>
+      <c r="O162" s="31"/>
+      <c r="P162" s="31"/>
+      <c r="Q162" s="31"/>
       <c r="R162" s="50"/>
       <c r="S162" s="22" t="s">
         <v>39</v>
@@ -16956,12 +16602,8 @@
       <c r="N164" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="O164" s="31">
-        <v>-0.5</v>
-      </c>
-      <c r="P164" s="31">
-        <v>21.1</v>
-      </c>
+      <c r="O164" s="31"/>
+      <c r="P164" s="31"/>
       <c r="Q164" s="31"/>
       <c r="R164" s="50"/>
       <c r="S164" s="22" t="s">
@@ -17586,12 +17228,8 @@
       <c r="N172" s="3" t="s">
         <v>633</v>
       </c>
-      <c r="O172" s="31">
-        <v>-1.3</v>
-      </c>
-      <c r="P172" s="31">
-        <v>16</v>
-      </c>
+      <c r="O172" s="31"/>
+      <c r="P172" s="31"/>
       <c r="Q172" s="31"/>
       <c r="R172" s="50"/>
       <c r="S172" s="22" t="s">
@@ -17746,12 +17384,8 @@
         <v>637</v>
       </c>
       <c r="N174" s="3"/>
-      <c r="O174" s="31">
-        <v>0.1</v>
-      </c>
-      <c r="P174" s="31">
-        <v>23.7</v>
-      </c>
+      <c r="O174" s="31"/>
+      <c r="P174" s="31"/>
       <c r="Q174" s="31"/>
       <c r="R174" s="50"/>
       <c r="S174" s="22" t="s">
@@ -17827,12 +17461,8 @@
         <v>640</v>
       </c>
       <c r="N175" s="2"/>
-      <c r="O175" s="31">
-        <v>10.199999999999999</v>
-      </c>
-      <c r="P175" s="31">
-        <v>19.399999999999999</v>
-      </c>
+      <c r="O175" s="31"/>
+      <c r="P175" s="31"/>
       <c r="Q175" s="31"/>
       <c r="R175" s="50" t="s">
         <v>641</v>
@@ -18068,15 +17698,9 @@
         <v>655</v>
       </c>
       <c r="N178" s="2"/>
-      <c r="O178" s="31">
-        <v>16.7</v>
-      </c>
-      <c r="P178" s="31">
-        <v>21.6</v>
-      </c>
-      <c r="Q178" s="31">
-        <v>18.21</v>
-      </c>
+      <c r="O178" s="31"/>
+      <c r="P178" s="31"/>
+      <c r="Q178" s="31"/>
       <c r="R178" s="50"/>
       <c r="S178" s="22" t="s">
         <v>39</v>
@@ -18151,15 +17775,9 @@
       <c r="N179" s="23" t="s">
         <v>97</v>
       </c>
-      <c r="O179" s="31">
-        <v>5.2</v>
-      </c>
-      <c r="P179" s="31">
-        <v>8.4</v>
-      </c>
-      <c r="Q179" s="31">
-        <v>7</v>
-      </c>
+      <c r="O179" s="31"/>
+      <c r="P179" s="31"/>
+      <c r="Q179" s="31"/>
       <c r="R179" s="50"/>
       <c r="S179" s="22" t="s">
         <v>39</v>
@@ -18394,12 +18012,8 @@
         <v>667</v>
       </c>
       <c r="N182" s="2"/>
-      <c r="O182" s="31">
-        <v>7.4</v>
-      </c>
-      <c r="P182" s="31">
-        <v>13.6</v>
-      </c>
+      <c r="O182" s="31"/>
+      <c r="P182" s="31"/>
       <c r="Q182" s="31"/>
       <c r="R182" s="50"/>
       <c r="S182" s="22" t="s">
@@ -21551,12 +21165,8 @@
         <v>777</v>
       </c>
       <c r="N225" s="2"/>
-      <c r="O225" s="31">
-        <v>2.5</v>
-      </c>
-      <c r="P225" s="31">
-        <v>21.1</v>
-      </c>
+      <c r="O225" s="31"/>
+      <c r="P225" s="31"/>
       <c r="Q225" s="31"/>
       <c r="R225" s="50"/>
       <c r="S225" s="22" t="s">
@@ -24637,12 +24247,8 @@
         <v>886</v>
       </c>
       <c r="N267" s="2"/>
-      <c r="O267" s="31">
-        <v>-67</v>
-      </c>
-      <c r="P267" s="31">
-        <v>-62</v>
-      </c>
+      <c r="O267" s="31"/>
+      <c r="P267" s="31"/>
       <c r="Q267" s="31"/>
       <c r="R267" s="50"/>
       <c r="S267" s="22" t="s">
@@ -26787,15 +26393,9 @@
       <c r="N297" s="3" t="s">
         <v>964</v>
       </c>
-      <c r="O297" s="31">
-        <v>-4.5</v>
-      </c>
-      <c r="P297" s="31">
-        <v>8.4</v>
-      </c>
-      <c r="Q297" s="31">
-        <v>0.8</v>
-      </c>
+      <c r="O297" s="31"/>
+      <c r="P297" s="31"/>
+      <c r="Q297" s="31"/>
       <c r="R297" s="50"/>
       <c r="S297" s="22" t="s">
         <v>39</v>
@@ -28340,15 +27940,9 @@
         <v>1029</v>
       </c>
       <c r="N318" s="2"/>
-      <c r="O318" s="31">
-        <v>18.899999999999999</v>
-      </c>
-      <c r="P318" s="31">
-        <v>43.7</v>
-      </c>
-      <c r="Q318" s="31">
-        <v>31.6</v>
-      </c>
+      <c r="O318" s="31"/>
+      <c r="P318" s="31"/>
+      <c r="Q318" s="31"/>
       <c r="R318" s="50"/>
       <c r="S318" s="22" t="s">
         <v>39</v>

--- a/气象/For_Python_站点信息和记录.xlsx
+++ b/气象/For_Python_站点信息和记录.xlsx
@@ -840,8 +840,8 @@
     <col width="18.59765625" customWidth="1" style="8" min="26" max="26"/>
     <col width="12.59765625" customWidth="1" style="5" min="27" max="31"/>
     <col width="12.59765625" customWidth="1" style="8" min="32" max="33"/>
-    <col width="12.59765625" customWidth="1" style="5" min="34" max="690"/>
-    <col width="12.59765625" customWidth="1" style="5" min="691" max="16384"/>
+    <col width="12.59765625" customWidth="1" style="5" min="34" max="694"/>
+    <col width="12.59765625" customWidth="1" style="5" min="695" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="27.75" customFormat="1" customHeight="1" s="11">
@@ -1069,13 +1069,13 @@
         </is>
       </c>
       <c r="O2" s="31" t="n">
-        <v>13.3</v>
+        <v>6</v>
       </c>
       <c r="P2" s="31" t="n">
-        <v>24.5</v>
+        <v>19.2</v>
       </c>
       <c r="Q2" s="31" t="n">
-        <v>17.88</v>
+        <v>11.99</v>
       </c>
       <c r="R2" s="50" t="n"/>
       <c r="S2" s="22" t="inlineStr">
@@ -1176,10 +1176,10 @@
         </is>
       </c>
       <c r="O3" s="31" t="n">
-        <v>15.2</v>
+        <v>7.2</v>
       </c>
       <c r="P3" s="31" t="n">
-        <v>25.7</v>
+        <v>18.7</v>
       </c>
       <c r="Q3" s="31" t="n"/>
       <c r="R3" s="50" t="inlineStr">
@@ -1285,10 +1285,10 @@
         </is>
       </c>
       <c r="O4" s="31" t="n">
-        <v>13.5</v>
+        <v>7.4</v>
       </c>
       <c r="P4" s="31" t="n">
-        <v>26.1</v>
+        <v>20.3</v>
       </c>
       <c r="Q4" s="31" t="n"/>
       <c r="R4" s="50" t="inlineStr">
@@ -1483,13 +1483,13 @@
         </is>
       </c>
       <c r="O6" s="31" t="n">
-        <v>2.6</v>
+        <v>9</v>
       </c>
       <c r="P6" s="31" t="n">
-        <v>26.7</v>
+        <v>18.4</v>
       </c>
       <c r="Q6" s="31" t="n">
-        <v>14.1</v>
+        <v>12.09</v>
       </c>
       <c r="R6" s="52" t="inlineStr">
         <is>
@@ -1695,13 +1695,13 @@
       </c>
       <c r="N8" s="2" t="n"/>
       <c r="O8" s="31" t="n">
-        <v>7.9</v>
+        <v>10.7</v>
       </c>
       <c r="P8" s="31" t="n">
-        <v>31.4</v>
+        <v>23.3</v>
       </c>
       <c r="Q8" s="31" t="n">
-        <v>18.91</v>
+        <v>16.54</v>
       </c>
       <c r="R8" s="50" t="n"/>
       <c r="S8" s="22" t="inlineStr">
@@ -1808,13 +1808,13 @@
       </c>
       <c r="N9" s="2" t="n"/>
       <c r="O9" s="31" t="n">
-        <v>13.4</v>
+        <v>7.4</v>
       </c>
       <c r="P9" s="31" t="n">
-        <v>24.3</v>
+        <v>17.1</v>
       </c>
       <c r="Q9" s="31" t="n">
-        <v>18.06</v>
+        <v>11.78</v>
       </c>
       <c r="R9" s="50" t="n"/>
       <c r="S9" s="22" t="inlineStr">
@@ -1929,13 +1929,13 @@
         </is>
       </c>
       <c r="O10" s="31" t="n">
-        <v>12</v>
+        <v>6.8</v>
       </c>
       <c r="P10" s="31" t="n">
-        <v>26.8</v>
+        <v>19.3</v>
       </c>
       <c r="Q10" s="31" t="n">
-        <v>17.72</v>
+        <v>10.31</v>
       </c>
       <c r="R10" s="50" t="n"/>
       <c r="S10" s="22" t="inlineStr">
@@ -2046,13 +2046,13 @@
         </is>
       </c>
       <c r="O11" s="31" t="n">
-        <v>9.199999999999999</v>
+        <v>4.8</v>
       </c>
       <c r="P11" s="31" t="n">
-        <v>24.1</v>
+        <v>11.9</v>
       </c>
       <c r="Q11" s="31" t="n">
-        <v>16.82</v>
+        <v>8.85</v>
       </c>
       <c r="R11" s="50" t="inlineStr">
         <is>
@@ -2163,13 +2163,13 @@
       </c>
       <c r="N12" s="2" t="n"/>
       <c r="O12" s="31" t="n">
-        <v>6.2</v>
+        <v>9.4</v>
       </c>
       <c r="P12" s="31" t="n">
-        <v>29.4</v>
+        <v>19.3</v>
       </c>
       <c r="Q12" s="31" t="n">
-        <v>16.07</v>
+        <v>11.38</v>
       </c>
       <c r="R12" s="50" t="inlineStr">
         <is>
@@ -2284,13 +2284,13 @@
         </is>
       </c>
       <c r="O13" s="31" t="n">
-        <v>4.6</v>
+        <v>5.9</v>
       </c>
       <c r="P13" s="31" t="n">
-        <v>27.9</v>
+        <v>17.2</v>
       </c>
       <c r="Q13" s="31" t="n">
-        <v>15.8</v>
+        <v>10.58</v>
       </c>
       <c r="R13" s="50" t="inlineStr">
         <is>
@@ -2401,13 +2401,13 @@
       </c>
       <c r="N14" s="2" t="n"/>
       <c r="O14" s="31" t="n">
-        <v>14.7</v>
+        <v>14.2</v>
       </c>
       <c r="P14" s="31" t="n">
-        <v>30.1</v>
+        <v>30.4</v>
       </c>
       <c r="Q14" s="31" t="n">
-        <v>22</v>
+        <v>22.59</v>
       </c>
       <c r="R14" s="50" t="n"/>
       <c r="S14" s="22" t="inlineStr">
@@ -2522,13 +2522,13 @@
       </c>
       <c r="N15" s="2" t="n"/>
       <c r="O15" s="31" t="n">
-        <v>2.5</v>
+        <v>5.3</v>
       </c>
       <c r="P15" s="31" t="n">
-        <v>26.2</v>
+        <v>27.7</v>
       </c>
       <c r="Q15" s="31" t="n">
-        <v>13.09</v>
+        <v>16.24</v>
       </c>
       <c r="R15" s="50" t="n"/>
       <c r="S15" s="22" t="inlineStr">
@@ -2725,9 +2725,7 @@
           <t>🧊</t>
         </is>
       </c>
-      <c r="O17" s="31" t="n">
-        <v>-1.4</v>
-      </c>
+      <c r="O17" s="31" t="n"/>
       <c r="P17" s="31" t="n"/>
       <c r="Q17" s="31" t="n"/>
       <c r="R17" s="50" t="n"/>
@@ -6731,7 +6729,9 @@
           <t>🧊</t>
         </is>
       </c>
-      <c r="O61" s="31" t="n"/>
+      <c r="O61" s="31" t="n">
+        <v>-3.3</v>
+      </c>
       <c r="P61" s="31" t="n"/>
       <c r="Q61" s="31" t="n"/>
       <c r="R61" s="50" t="n"/>
@@ -8317,13 +8317,13 @@
         </is>
       </c>
       <c r="O78" s="31" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="P78" s="31" t="n">
-        <v>20</v>
+        <v>21.7</v>
       </c>
       <c r="Q78" s="31" t="n">
-        <v>10.1</v>
+        <v>12.29</v>
       </c>
       <c r="R78" s="50" t="inlineStr">
         <is>
@@ -8751,10 +8751,10 @@
         </is>
       </c>
       <c r="O82" s="31" t="n">
-        <v>1.8</v>
+        <v>10.7</v>
       </c>
       <c r="P82" s="31" t="n">
-        <v>24.1</v>
+        <v>23.1</v>
       </c>
       <c r="Q82" s="31" t="n"/>
       <c r="R82" s="50" t="n"/>
@@ -8871,13 +8871,13 @@
         </is>
       </c>
       <c r="O83" s="31" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="P83" s="31" t="n">
-        <v>22.8</v>
+        <v>21.6</v>
       </c>
       <c r="Q83" s="31" t="n">
-        <v>11.38</v>
+        <v>14.97</v>
       </c>
       <c r="R83" s="50" t="n"/>
       <c r="S83" s="22" t="inlineStr">
@@ -9091,13 +9091,13 @@
         </is>
       </c>
       <c r="O85" s="31" t="n">
-        <v>6.7</v>
+        <v>4.4</v>
       </c>
       <c r="P85" s="31" t="n">
-        <v>29.1</v>
+        <v>10.8</v>
       </c>
       <c r="Q85" s="31" t="n">
-        <v>17.05</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="R85" s="50" t="n"/>
       <c r="S85" s="22" t="inlineStr">
@@ -9311,13 +9311,13 @@
       </c>
       <c r="N87" s="2" t="n"/>
       <c r="O87" s="31" t="n">
-        <v>12.5</v>
+        <v>6.7</v>
       </c>
       <c r="P87" s="31" t="n">
-        <v>23.6</v>
+        <v>18.3</v>
       </c>
       <c r="Q87" s="31" t="n">
-        <v>14.24</v>
+        <v>9.92</v>
       </c>
       <c r="R87" s="50" t="n"/>
       <c r="S87" s="22" t="inlineStr">
@@ -9539,13 +9539,13 @@
       </c>
       <c r="N89" s="2" t="n"/>
       <c r="O89" s="31" t="n">
-        <v>8</v>
+        <v>-3.9</v>
       </c>
       <c r="P89" s="31" t="n">
-        <v>18.6</v>
+        <v>11.6</v>
       </c>
       <c r="Q89" s="31" t="n">
-        <v>12.22</v>
+        <v>4.21</v>
       </c>
       <c r="R89" s="50" t="inlineStr">
         <is>
@@ -9961,13 +9961,13 @@
       </c>
       <c r="N93" s="2" t="n"/>
       <c r="O93" s="31" t="n">
-        <v>12.1</v>
+        <v>0.6</v>
       </c>
       <c r="P93" s="31" t="n">
-        <v>21.6</v>
+        <v>20.5</v>
       </c>
       <c r="Q93" s="31" t="n">
-        <v>15.45</v>
+        <v>10.84</v>
       </c>
       <c r="R93" s="50" t="n"/>
       <c r="S93" s="22" t="inlineStr">
@@ -10074,13 +10074,13 @@
       </c>
       <c r="N94" s="2" t="n"/>
       <c r="O94" s="31" t="n">
-        <v>17</v>
+        <v>12.7</v>
       </c>
       <c r="P94" s="31" t="n">
-        <v>26.5</v>
+        <v>28.9</v>
       </c>
       <c r="Q94" s="31" t="n">
-        <v>21.31</v>
+        <v>21.01</v>
       </c>
       <c r="R94" s="50" t="n"/>
       <c r="S94" s="22" t="inlineStr">
@@ -10310,13 +10310,13 @@
       </c>
       <c r="N96" s="2" t="n"/>
       <c r="O96" s="31" t="n">
-        <v>11.3</v>
+        <v>12</v>
       </c>
       <c r="P96" s="31" t="n">
-        <v>23.7</v>
+        <v>25.5</v>
       </c>
       <c r="Q96" s="31" t="n">
-        <v>17.86</v>
+        <v>18.72</v>
       </c>
       <c r="R96" s="50" t="n"/>
       <c r="S96" s="22" t="inlineStr">
@@ -10554,13 +10554,13 @@
       </c>
       <c r="N98" s="2" t="n"/>
       <c r="O98" s="31" t="n">
-        <v>12.1</v>
+        <v>12.9</v>
       </c>
       <c r="P98" s="31" t="n">
-        <v>22.8</v>
+        <v>24.8</v>
       </c>
       <c r="Q98" s="31" t="n">
-        <v>17.09</v>
+        <v>18.84</v>
       </c>
       <c r="R98" s="50" t="n"/>
       <c r="S98" s="22" t="inlineStr">
@@ -11115,13 +11115,13 @@
       </c>
       <c r="N103" s="2" t="n"/>
       <c r="O103" s="31" t="n">
-        <v>3.9</v>
+        <v>4.6</v>
       </c>
       <c r="P103" s="31" t="n">
-        <v>19.8</v>
+        <v>24.3</v>
       </c>
       <c r="Q103" s="31" t="n">
-        <v>10.62</v>
+        <v>12.76</v>
       </c>
       <c r="R103" s="50" t="n"/>
       <c r="S103" s="22" t="inlineStr">
@@ -11454,13 +11454,13 @@
         </is>
       </c>
       <c r="O106" s="31" t="n">
-        <v>9.4</v>
+        <v>3.6</v>
       </c>
       <c r="P106" s="31" t="n">
-        <v>18</v>
+        <v>24.8</v>
       </c>
       <c r="Q106" s="31" t="n">
-        <v>11.95</v>
+        <v>12.36</v>
       </c>
       <c r="R106" s="50" t="n"/>
       <c r="S106" s="22" t="inlineStr">
@@ -12296,13 +12296,13 @@
       </c>
       <c r="N114" s="2" t="n"/>
       <c r="O114" s="31" t="n">
-        <v>1.7</v>
+        <v>4.5</v>
       </c>
       <c r="P114" s="31" t="n">
-        <v>14.9</v>
+        <v>10.9</v>
       </c>
       <c r="Q114" s="31" t="n">
-        <v>7.91</v>
+        <v>7.05</v>
       </c>
       <c r="R114" s="50" t="n"/>
       <c r="S114" s="22" t="inlineStr">
@@ -12413,13 +12413,13 @@
         </is>
       </c>
       <c r="O115" s="31" t="n">
-        <v>-1.6</v>
+        <v>-0.6</v>
       </c>
       <c r="P115" s="31" t="n">
-        <v>14.5</v>
+        <v>15.4</v>
       </c>
       <c r="Q115" s="31" t="n">
-        <v>5.89</v>
+        <v>5.38</v>
       </c>
       <c r="R115" s="50" t="n"/>
       <c r="S115" s="22" t="inlineStr">
@@ -12538,13 +12538,13 @@
         </is>
       </c>
       <c r="O116" s="31" t="n">
-        <v>1.8</v>
+        <v>1.4</v>
       </c>
       <c r="P116" s="31" t="n">
-        <v>14.7</v>
+        <v>9.1</v>
       </c>
       <c r="Q116" s="31" t="n">
-        <v>7.11</v>
+        <v>5.09</v>
       </c>
       <c r="R116" s="50" t="n"/>
       <c r="S116" s="22" t="inlineStr">
@@ -13103,13 +13103,13 @@
       </c>
       <c r="N121" s="2" t="n"/>
       <c r="O121" s="31" t="n">
-        <v>27.8</v>
+        <v>27.3</v>
       </c>
       <c r="P121" s="31" t="n">
-        <v>42</v>
+        <v>34.6</v>
       </c>
       <c r="Q121" s="31" t="n">
-        <v>35.09</v>
+        <v>30.44</v>
       </c>
       <c r="R121" s="50" t="n"/>
       <c r="S121" s="22" t="inlineStr">
@@ -13220,13 +13220,13 @@
       </c>
       <c r="N122" s="2" t="n"/>
       <c r="O122" s="31" t="n">
-        <v>17.9</v>
+        <v>11</v>
       </c>
       <c r="P122" s="31" t="n">
-        <v>29.3</v>
+        <v>18.5</v>
       </c>
       <c r="Q122" s="31" t="n">
-        <v>21.58</v>
+        <v>13.96</v>
       </c>
       <c r="R122" s="50" t="n"/>
       <c r="S122" s="22" t="inlineStr">
@@ -13345,13 +13345,13 @@
       </c>
       <c r="N123" s="2" t="n"/>
       <c r="O123" s="31" t="n">
-        <v>8.6</v>
+        <v>4.9</v>
       </c>
       <c r="P123" s="31" t="n">
-        <v>19</v>
+        <v>12.3</v>
       </c>
       <c r="Q123" s="31" t="n">
-        <v>12.99</v>
+        <v>7.84</v>
       </c>
       <c r="R123" s="50" t="n"/>
       <c r="S123" s="22" t="inlineStr">
@@ -13569,13 +13569,13 @@
       </c>
       <c r="N125" s="2" t="n"/>
       <c r="O125" s="31" t="n">
-        <v>12.7</v>
+        <v>13.7</v>
       </c>
       <c r="P125" s="31" t="n">
-        <v>27.4</v>
+        <v>26.7</v>
       </c>
       <c r="Q125" s="31" t="n">
-        <v>19.98</v>
+        <v>20.39</v>
       </c>
       <c r="R125" s="50" t="n"/>
       <c r="S125" s="22" t="inlineStr">
@@ -13694,13 +13694,13 @@
       </c>
       <c r="N126" s="2" t="n"/>
       <c r="O126" s="31" t="n">
-        <v>18</v>
+        <v>18.3</v>
       </c>
       <c r="P126" s="31" t="n">
-        <v>30.1</v>
+        <v>31.8</v>
       </c>
       <c r="Q126" s="31" t="n">
-        <v>24.07</v>
+        <v>25.02</v>
       </c>
       <c r="R126" s="50" t="n"/>
       <c r="S126" s="22" t="inlineStr">
@@ -13799,13 +13799,13 @@
       </c>
       <c r="N127" s="2" t="n"/>
       <c r="O127" s="31" t="n">
-        <v>19.6</v>
+        <v>18.4</v>
       </c>
       <c r="P127" s="31" t="n">
-        <v>30.3</v>
+        <v>32.4</v>
       </c>
       <c r="Q127" s="31" t="n">
-        <v>24.96</v>
+        <v>25.95</v>
       </c>
       <c r="R127" s="50" t="n"/>
       <c r="S127" s="22" t="inlineStr">
@@ -13912,13 +13912,13 @@
       </c>
       <c r="N128" s="2" t="n"/>
       <c r="O128" s="31" t="n">
-        <v>13.1</v>
+        <v>14.3</v>
       </c>
       <c r="P128" s="31" t="n">
-        <v>30.7</v>
+        <v>28.5</v>
       </c>
       <c r="Q128" s="31" t="n">
-        <v>21.85</v>
+        <v>21.59</v>
       </c>
       <c r="R128" s="50" t="n"/>
       <c r="S128" s="22" t="inlineStr">
@@ -14033,13 +14033,13 @@
       </c>
       <c r="N129" s="2" t="n"/>
       <c r="O129" s="31" t="n">
-        <v>19.3</v>
+        <v>19</v>
       </c>
       <c r="P129" s="31" t="n">
-        <v>30.8</v>
+        <v>30.4</v>
       </c>
       <c r="Q129" s="31" t="n">
-        <v>25.02</v>
+        <v>24.69</v>
       </c>
       <c r="R129" s="50" t="n"/>
       <c r="S129" s="22" t="inlineStr">
@@ -14146,13 +14146,13 @@
       </c>
       <c r="N130" s="2" t="n"/>
       <c r="O130" s="31" t="n">
-        <v>14.4</v>
+        <v>16.6</v>
       </c>
       <c r="P130" s="31" t="n">
-        <v>29.9</v>
+        <v>27.6</v>
       </c>
       <c r="Q130" s="31" t="n">
-        <v>22.51</v>
+        <v>21.92</v>
       </c>
       <c r="R130" s="50" t="n"/>
       <c r="S130" s="22" t="inlineStr">
@@ -14267,13 +14267,13 @@
       </c>
       <c r="N131" s="2" t="n"/>
       <c r="O131" s="31" t="n">
-        <v>8.800000000000001</v>
+        <v>10.1</v>
       </c>
       <c r="P131" s="31" t="n">
-        <v>25.8</v>
+        <v>24.2</v>
       </c>
       <c r="Q131" s="31" t="n">
-        <v>16.35</v>
+        <v>16.77</v>
       </c>
       <c r="R131" s="50" t="n"/>
       <c r="S131" s="22" t="inlineStr">
@@ -14388,13 +14388,13 @@
       </c>
       <c r="N132" s="2" t="n"/>
       <c r="O132" s="31" t="n">
-        <v>20.6</v>
+        <v>16.2</v>
       </c>
       <c r="P132" s="31" t="n">
-        <v>30.2</v>
+        <v>29.7</v>
       </c>
       <c r="Q132" s="31" t="n">
-        <v>25.05</v>
+        <v>23.48</v>
       </c>
       <c r="R132" s="50" t="n"/>
       <c r="S132" s="22" t="inlineStr">
@@ -14505,13 +14505,13 @@
       </c>
       <c r="N133" s="2" t="n"/>
       <c r="O133" s="31" t="n">
-        <v>24.5</v>
+        <v>21.4</v>
       </c>
       <c r="P133" s="31" t="n">
-        <v>30.9</v>
+        <v>28.8</v>
       </c>
       <c r="Q133" s="31" t="n">
-        <v>27.79</v>
+        <v>25.64</v>
       </c>
       <c r="R133" s="50" t="n"/>
       <c r="S133" s="22" t="inlineStr">
@@ -14622,13 +14622,13 @@
       </c>
       <c r="N134" s="2" t="n"/>
       <c r="O134" s="31" t="n">
-        <v>18.8</v>
+        <v>20.3</v>
       </c>
       <c r="P134" s="31" t="n">
-        <v>31.1</v>
+        <v>29.7</v>
       </c>
       <c r="Q134" s="31" t="n">
-        <v>25.02</v>
+        <v>25.09</v>
       </c>
       <c r="R134" s="50" t="n"/>
       <c r="S134" s="22" t="inlineStr">
@@ -14846,13 +14846,13 @@
       </c>
       <c r="N136" s="2" t="n"/>
       <c r="O136" s="31" t="n">
-        <v>19.9</v>
+        <v>18.6</v>
       </c>
       <c r="P136" s="31" t="n">
-        <v>25.8</v>
+        <v>24.1</v>
       </c>
       <c r="Q136" s="31" t="n">
-        <v>21.76</v>
+        <v>20.3</v>
       </c>
       <c r="R136" s="50" t="n"/>
       <c r="S136" s="22" t="inlineStr">
@@ -14963,13 +14963,13 @@
       </c>
       <c r="N137" s="2" t="n"/>
       <c r="O137" s="31" t="n">
-        <v>24.1</v>
+        <v>22.6</v>
       </c>
       <c r="P137" s="31" t="n">
-        <v>30.1</v>
+        <v>26.5</v>
       </c>
       <c r="Q137" s="31" t="n">
-        <v>27.04</v>
+        <v>24.62</v>
       </c>
       <c r="R137" s="50" t="n"/>
       <c r="S137" s="22" t="inlineStr">
@@ -15080,13 +15080,13 @@
       </c>
       <c r="N138" s="2" t="n"/>
       <c r="O138" s="31" t="n">
-        <v>23.8</v>
+        <v>23.7</v>
       </c>
       <c r="P138" s="31" t="n">
-        <v>29.5</v>
+        <v>27.2</v>
       </c>
       <c r="Q138" s="31" t="n">
-        <v>26.62</v>
+        <v>25.26</v>
       </c>
       <c r="R138" s="50" t="n"/>
       <c r="S138" s="22" t="inlineStr">
@@ -15197,13 +15197,13 @@
       </c>
       <c r="N139" s="2" t="n"/>
       <c r="O139" s="31" t="n">
-        <v>23.6</v>
+        <v>22.8</v>
       </c>
       <c r="P139" s="31" t="n">
-        <v>29.4</v>
+        <v>27.7</v>
       </c>
       <c r="Q139" s="31" t="n">
-        <v>26.04</v>
+        <v>24.82</v>
       </c>
       <c r="R139" s="50" t="n"/>
       <c r="S139" s="22" t="inlineStr">
@@ -15314,13 +15314,13 @@
       </c>
       <c r="N140" s="2" t="n"/>
       <c r="O140" s="31" t="n">
-        <v>23.8</v>
+        <v>24</v>
       </c>
       <c r="P140" s="31" t="n">
-        <v>26.7</v>
+        <v>30.2</v>
       </c>
       <c r="Q140" s="31" t="n">
-        <v>25.12</v>
+        <v>26.2</v>
       </c>
       <c r="R140" s="50" t="n"/>
       <c r="S140" s="22" t="inlineStr">
@@ -15431,13 +15431,13 @@
       </c>
       <c r="N141" s="2" t="n"/>
       <c r="O141" s="31" t="n">
-        <v>25.4</v>
+        <v>24.8</v>
       </c>
       <c r="P141" s="31" t="n">
-        <v>33.2</v>
+        <v>32.2</v>
       </c>
       <c r="Q141" s="31" t="n">
-        <v>28.34</v>
+        <v>27.76</v>
       </c>
       <c r="R141" s="50" t="n"/>
       <c r="S141" s="22" t="inlineStr">
@@ -15651,13 +15651,13 @@
       </c>
       <c r="N143" s="2" t="n"/>
       <c r="O143" s="31" t="n">
-        <v>25.7</v>
+        <v>24.7</v>
       </c>
       <c r="P143" s="31" t="n">
-        <v>29.9</v>
+        <v>28.5</v>
       </c>
       <c r="Q143" s="31" t="n">
-        <v>26.95</v>
+        <v>26.47</v>
       </c>
       <c r="R143" s="50" t="n"/>
       <c r="S143" s="22" t="inlineStr">
@@ -15768,13 +15768,13 @@
       </c>
       <c r="N144" s="2" t="n"/>
       <c r="O144" s="31" t="n">
-        <v>24.7</v>
+        <v>23.8</v>
       </c>
       <c r="P144" s="31" t="n">
-        <v>29.4</v>
+        <v>30.2</v>
       </c>
       <c r="Q144" s="31" t="n">
-        <v>26.69</v>
+        <v>26.5</v>
       </c>
       <c r="R144" s="50" t="n"/>
       <c r="S144" s="22" t="inlineStr">
@@ -16087,13 +16087,13 @@
       </c>
       <c r="N147" s="2" t="n"/>
       <c r="O147" s="31" t="n">
-        <v>25.8</v>
+        <v>24.3</v>
       </c>
       <c r="P147" s="31" t="n">
-        <v>29.4</v>
+        <v>31.1</v>
       </c>
       <c r="Q147" s="31" t="n">
-        <v>27.84</v>
+        <v>27.54</v>
       </c>
       <c r="R147" s="50" t="n"/>
       <c r="S147" s="22" t="inlineStr">
@@ -16196,13 +16196,13 @@
       </c>
       <c r="N148" s="2" t="n"/>
       <c r="O148" s="31" t="n">
-        <v>26.8</v>
+        <v>23.8</v>
       </c>
       <c r="P148" s="31" t="n">
-        <v>29.6</v>
+        <v>32</v>
       </c>
       <c r="Q148" s="31" t="n">
-        <v>28.04</v>
+        <v>27.53</v>
       </c>
       <c r="R148" s="50" t="n"/>
       <c r="S148" s="22" t="inlineStr">
@@ -16313,10 +16313,10 @@
       </c>
       <c r="N149" s="2" t="n"/>
       <c r="O149" s="31" t="n">
-        <v>22.9</v>
+        <v>22.7</v>
       </c>
       <c r="P149" s="31" t="n">
-        <v>35.6</v>
+        <v>35.8</v>
       </c>
       <c r="Q149" s="31" t="n">
         <v>27.88</v>
@@ -16426,13 +16426,13 @@
       </c>
       <c r="N150" s="2" t="n"/>
       <c r="O150" s="31" t="n">
-        <v>16.2</v>
+        <v>18.2</v>
       </c>
       <c r="P150" s="31" t="n">
-        <v>26</v>
+        <v>24.9</v>
       </c>
       <c r="Q150" s="31" t="n">
-        <v>21.61</v>
+        <v>20.55</v>
       </c>
       <c r="R150" s="50" t="n"/>
       <c r="S150" s="22" t="inlineStr">
@@ -16543,13 +16543,13 @@
       </c>
       <c r="N151" s="2" t="n"/>
       <c r="O151" s="31" t="n">
-        <v>18.5</v>
+        <v>16.6</v>
       </c>
       <c r="P151" s="31" t="n">
-        <v>27.4</v>
+        <v>26.3</v>
       </c>
       <c r="Q151" s="31" t="n">
-        <v>22.93</v>
+        <v>20.29</v>
       </c>
       <c r="R151" s="50" t="n"/>
       <c r="S151" s="22" t="inlineStr">
@@ -16660,13 +16660,13 @@
       </c>
       <c r="N152" s="2" t="n"/>
       <c r="O152" s="31" t="n">
-        <v>25.3</v>
+        <v>24.3</v>
       </c>
       <c r="P152" s="31" t="n">
-        <v>35.6</v>
+        <v>34.9</v>
       </c>
       <c r="Q152" s="31" t="n">
-        <v>30.31</v>
+        <v>29.36</v>
       </c>
       <c r="R152" s="50" t="n"/>
       <c r="S152" s="22" t="inlineStr">
@@ -16868,13 +16868,13 @@
       </c>
       <c r="N154" s="2" t="n"/>
       <c r="O154" s="31" t="n">
-        <v>21.4</v>
+        <v>22.3</v>
       </c>
       <c r="P154" s="31" t="n">
-        <v>32.4</v>
+        <v>27.7</v>
       </c>
       <c r="Q154" s="31" t="n">
-        <v>27.09</v>
+        <v>24.46</v>
       </c>
       <c r="R154" s="50" t="n"/>
       <c r="S154" s="22" t="inlineStr">
@@ -16989,13 +16989,13 @@
       </c>
       <c r="N155" s="2" t="n"/>
       <c r="O155" s="31" t="n">
-        <v>9.5</v>
+        <v>12.9</v>
       </c>
       <c r="P155" s="31" t="n">
-        <v>23.9</v>
+        <v>20.5</v>
       </c>
       <c r="Q155" s="31" t="n">
-        <v>16.35</v>
+        <v>16.14</v>
       </c>
       <c r="R155" s="50" t="n"/>
       <c r="S155" s="22" t="inlineStr">
@@ -17292,13 +17292,13 @@
       </c>
       <c r="N158" s="2" t="n"/>
       <c r="O158" s="31" t="n">
-        <v>27.4</v>
+        <v>26.1</v>
       </c>
       <c r="P158" s="31" t="n">
-        <v>30.6</v>
+        <v>32.5</v>
       </c>
       <c r="Q158" s="31" t="n">
-        <v>29.02</v>
+        <v>28.44</v>
       </c>
       <c r="R158" s="50" t="n"/>
       <c r="S158" s="22" t="inlineStr">
@@ -17686,13 +17686,13 @@
       </c>
       <c r="N162" s="2" t="n"/>
       <c r="O162" s="31" t="n">
-        <v>14.1</v>
+        <v>15.2</v>
       </c>
       <c r="P162" s="31" t="n">
-        <v>31.2</v>
+        <v>28.9</v>
       </c>
       <c r="Q162" s="31" t="n">
-        <v>22.6</v>
+        <v>22.16</v>
       </c>
       <c r="R162" s="50" t="n"/>
       <c r="S162" s="22" t="inlineStr">
@@ -17908,10 +17908,10 @@
         </is>
       </c>
       <c r="O164" s="31" t="n">
-        <v>9.4</v>
+        <v>2.4</v>
       </c>
       <c r="P164" s="31" t="n">
-        <v>16.2</v>
+        <v>23.5</v>
       </c>
       <c r="Q164" s="31" t="n"/>
       <c r="R164" s="50" t="n"/>
@@ -18343,12 +18343,8 @@
           <t>▼</t>
         </is>
       </c>
-      <c r="O168" s="31" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="P168" s="31" t="n">
-        <v>24</v>
-      </c>
+      <c r="O168" s="31" t="n"/>
+      <c r="P168" s="31" t="n"/>
       <c r="Q168" s="31" t="n"/>
       <c r="R168" s="50" t="inlineStr">
         <is>
@@ -18565,8 +18561,12 @@
           <t>❄️</t>
         </is>
       </c>
-      <c r="O170" s="31" t="n"/>
-      <c r="P170" s="31" t="n"/>
+      <c r="O170" s="31" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="P170" s="31" t="n">
+        <v>19.3</v>
+      </c>
       <c r="Q170" s="31" t="n"/>
       <c r="R170" s="50" t="n"/>
       <c r="S170" s="22" t="inlineStr">
@@ -18792,10 +18792,10 @@
         </is>
       </c>
       <c r="O172" s="31" t="n">
-        <v>1.3</v>
+        <v>-6.4</v>
       </c>
       <c r="P172" s="31" t="n">
-        <v>14.6</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="Q172" s="31" t="n"/>
       <c r="R172" s="50" t="n"/>
@@ -18907,13 +18907,13 @@
         </is>
       </c>
       <c r="O173" s="31" t="n">
-        <v>0.1</v>
+        <v>-3.2</v>
       </c>
       <c r="P173" s="31" t="n">
-        <v>11.4</v>
+        <v>3.3</v>
       </c>
       <c r="Q173" s="31" t="n">
-        <v>4.8</v>
+        <v>-0.7</v>
       </c>
       <c r="R173" s="50" t="n"/>
       <c r="S173" s="22" t="inlineStr">
@@ -19127,13 +19127,13 @@
       </c>
       <c r="N175" s="2" t="n"/>
       <c r="O175" s="31" t="n">
-        <v>0.7</v>
+        <v>3.9</v>
       </c>
       <c r="P175" s="31" t="n">
-        <v>19</v>
+        <v>25.5</v>
       </c>
       <c r="Q175" s="31" t="n">
-        <v>10.13</v>
+        <v>14.53</v>
       </c>
       <c r="R175" s="50" t="inlineStr">
         <is>
@@ -19346,8 +19346,12 @@
         </is>
       </c>
       <c r="N177" s="2" t="n"/>
-      <c r="O177" s="31" t="n"/>
-      <c r="P177" s="31" t="n"/>
+      <c r="O177" s="31" t="n">
+        <v>-3.4</v>
+      </c>
+      <c r="P177" s="31" t="n">
+        <v>16.9</v>
+      </c>
       <c r="Q177" s="31" t="n"/>
       <c r="R177" s="50" t="n"/>
       <c r="S177" s="22" t="inlineStr">
@@ -19458,13 +19462,13 @@
       </c>
       <c r="N178" s="2" t="n"/>
       <c r="O178" s="31" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="P178" s="31" t="n">
         <v>16.1</v>
       </c>
-      <c r="P178" s="31" t="n">
-        <v>18.2</v>
-      </c>
       <c r="Q178" s="31" t="n">
-        <v>16.82</v>
+        <v>15.62</v>
       </c>
       <c r="R178" s="50" t="n"/>
       <c r="S178" s="22" t="inlineStr">
@@ -19567,13 +19571,13 @@
         </is>
       </c>
       <c r="O179" s="31" t="n">
-        <v>4.8</v>
+        <v>0.2</v>
       </c>
       <c r="P179" s="31" t="n">
-        <v>11.8</v>
+        <v>7.2</v>
       </c>
       <c r="Q179" s="31" t="n">
-        <v>7.84</v>
+        <v>2.79</v>
       </c>
       <c r="R179" s="50" t="n"/>
       <c r="S179" s="22" t="inlineStr">
@@ -19683,8 +19687,12 @@
         </is>
       </c>
       <c r="N180" s="2" t="n"/>
-      <c r="O180" s="31" t="n"/>
-      <c r="P180" s="31" t="n"/>
+      <c r="O180" s="31" t="n">
+        <v>-2.8</v>
+      </c>
+      <c r="P180" s="31" t="n">
+        <v>16.9</v>
+      </c>
       <c r="Q180" s="31" t="n"/>
       <c r="R180" s="50" t="n"/>
       <c r="S180" s="22" t="inlineStr">
@@ -19902,10 +19910,10 @@
       </c>
       <c r="N182" s="2" t="n"/>
       <c r="O182" s="31" t="n">
-        <v>2.7</v>
+        <v>6.9</v>
       </c>
       <c r="P182" s="31" t="n">
-        <v>21.8</v>
+        <v>20.5</v>
       </c>
       <c r="Q182" s="31" t="n"/>
       <c r="R182" s="50" t="n"/>
@@ -23117,8 +23125,12 @@
         </is>
       </c>
       <c r="N215" s="2" t="n"/>
-      <c r="O215" s="31" t="n"/>
-      <c r="P215" s="31" t="n"/>
+      <c r="O215" s="31" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="P215" s="31" t="n">
+        <v>26.3</v>
+      </c>
       <c r="Q215" s="31" t="n"/>
       <c r="R215" s="50" t="n"/>
       <c r="S215" s="22" t="inlineStr">
@@ -25499,15 +25511,9 @@
         </is>
       </c>
       <c r="N239" s="2" t="n"/>
-      <c r="O239" s="31" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="P239" s="31" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="Q239" s="31" t="n">
-        <v>9.51</v>
-      </c>
+      <c r="O239" s="31" t="n"/>
+      <c r="P239" s="31" t="n"/>
+      <c r="Q239" s="31" t="n"/>
       <c r="R239" s="50" t="n"/>
       <c r="S239" s="22" t="inlineStr">
         <is>
@@ -25608,12 +25614,8 @@
         </is>
       </c>
       <c r="N240" s="2" t="n"/>
-      <c r="O240" s="31" t="n">
-        <v>-2.3</v>
-      </c>
-      <c r="P240" s="31" t="n">
-        <v>15.8</v>
-      </c>
+      <c r="O240" s="31" t="n"/>
+      <c r="P240" s="31" t="n"/>
       <c r="Q240" s="31" t="n"/>
       <c r="R240" s="50" t="n"/>
       <c r="S240" s="22" t="inlineStr">
@@ -25911,8 +25913,12 @@
         </is>
       </c>
       <c r="N243" s="2" t="n"/>
-      <c r="O243" s="31" t="n"/>
-      <c r="P243" s="31" t="n"/>
+      <c r="O243" s="31" t="n">
+        <v>-4.6</v>
+      </c>
+      <c r="P243" s="31" t="n">
+        <v>13.3</v>
+      </c>
       <c r="Q243" s="31" t="n"/>
       <c r="R243" s="50" t="n"/>
       <c r="S243" s="22" t="inlineStr">
@@ -28274,10 +28280,10 @@
       </c>
       <c r="N267" s="2" t="n"/>
       <c r="O267" s="31" t="n">
-        <v>-69.7</v>
+        <v>-66</v>
       </c>
       <c r="P267" s="31" t="n">
-        <v>-57.7</v>
+        <v>-56.2</v>
       </c>
       <c r="Q267" s="31" t="n"/>
       <c r="R267" s="50" t="n"/>
@@ -30764,7 +30770,7 @@
       </c>
       <c r="N293" s="2" t="n"/>
       <c r="O293" s="31" t="n">
-        <v>-30.4</v>
+        <v>-38.3</v>
       </c>
       <c r="P293" s="31" t="n"/>
       <c r="Q293" s="31" t="n"/>
@@ -31056,9 +31062,15 @@
         </is>
       </c>
       <c r="N296" s="2" t="n"/>
-      <c r="O296" s="31" t="n"/>
-      <c r="P296" s="31" t="n"/>
-      <c r="Q296" s="31" t="n"/>
+      <c r="O296" s="31" t="n">
+        <v>-1.7</v>
+      </c>
+      <c r="P296" s="31" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="Q296" s="31" t="n">
+        <v>2.2</v>
+      </c>
       <c r="R296" s="50" t="n"/>
       <c r="S296" s="22" t="inlineStr">
         <is>
@@ -31164,12 +31176,14 @@
         </is>
       </c>
       <c r="O297" s="31" t="n">
-        <v>-1.8</v>
+        <v>-3.4</v>
       </c>
       <c r="P297" s="31" t="n">
-        <v>11.6</v>
-      </c>
-      <c r="Q297" s="31" t="n"/>
+        <v>6.9</v>
+      </c>
+      <c r="Q297" s="31" t="n">
+        <v>0.4</v>
+      </c>
       <c r="R297" s="50" t="n"/>
       <c r="S297" s="22" t="inlineStr">
         <is>
@@ -31270,9 +31284,15 @@
         </is>
       </c>
       <c r="N298" s="23" t="n"/>
-      <c r="O298" s="31" t="n"/>
-      <c r="P298" s="31" t="n"/>
-      <c r="Q298" s="31" t="n"/>
+      <c r="O298" s="31" t="n">
+        <v>-4.9</v>
+      </c>
+      <c r="P298" s="31" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Q298" s="31" t="n">
+        <v>-0.9</v>
+      </c>
       <c r="R298" s="50" t="n"/>
       <c r="S298" s="22" t="inlineStr">
         <is>
@@ -33250,15 +33270,9 @@
         </is>
       </c>
       <c r="N318" s="2" t="n"/>
-      <c r="O318" s="31" t="n">
-        <v>21.9</v>
-      </c>
-      <c r="P318" s="31" t="n">
-        <v>44.6</v>
-      </c>
-      <c r="Q318" s="31" t="n">
-        <v>32.8</v>
-      </c>
+      <c r="O318" s="31" t="n"/>
+      <c r="P318" s="31" t="n"/>
+      <c r="Q318" s="31" t="n"/>
       <c r="R318" s="50" t="n"/>
       <c r="S318" s="22" t="inlineStr">
         <is>
@@ -33636,9 +33650,7 @@
         </is>
       </c>
       <c r="N322" s="2" t="n"/>
-      <c r="O322" s="31" t="n">
-        <v>4.6</v>
-      </c>
+      <c r="O322" s="31" t="n"/>
       <c r="P322" s="31" t="n"/>
       <c r="Q322" s="31" t="n"/>
       <c r="R322" s="50" t="n"/>
@@ -34352,15 +34364,9 @@
         </is>
       </c>
       <c r="N330" s="2" t="n"/>
-      <c r="O330" s="31" t="n">
-        <v>-2.4</v>
-      </c>
-      <c r="P330" s="31" t="n">
-        <v>10.1</v>
-      </c>
-      <c r="Q330" s="31" t="n">
-        <v>3.1</v>
-      </c>
+      <c r="O330" s="31" t="n"/>
+      <c r="P330" s="31" t="n"/>
+      <c r="Q330" s="31" t="n"/>
       <c r="R330" s="50" t="n"/>
       <c r="S330" s="22" t="n"/>
       <c r="T330" s="36" t="n"/>
@@ -35481,14 +35487,12 @@
       </c>
       <c r="N342" s="2" t="n"/>
       <c r="O342" s="31" t="n">
-        <v>-3</v>
+        <v>-2.1</v>
       </c>
       <c r="P342" s="31" t="n">
-        <v>6</v>
-      </c>
-      <c r="Q342" s="31" t="n">
-        <v>1.2</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="Q342" s="31" t="n"/>
       <c r="R342" s="50" t="n"/>
       <c r="S342" s="22" t="n"/>
       <c r="T342" s="36" t="n"/>

--- a/气象/For_Python_站点信息和记录.xlsx
+++ b/气象/For_Python_站点信息和记录.xlsx
@@ -840,8 +840,8 @@
     <col width="18.59765625" customWidth="1" style="8" min="26" max="26"/>
     <col width="12.59765625" customWidth="1" style="5" min="27" max="31"/>
     <col width="12.59765625" customWidth="1" style="8" min="32" max="33"/>
-    <col width="12.59765625" customWidth="1" style="5" min="34" max="703"/>
-    <col width="12.59765625" customWidth="1" style="5" min="704" max="16384"/>
+    <col width="12.59765625" customWidth="1" style="5" min="34" max="704"/>
+    <col width="12.59765625" customWidth="1" style="5" min="705" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="27.75" customFormat="1" customHeight="1" s="11">
@@ -1069,13 +1069,13 @@
         </is>
       </c>
       <c r="O2" s="31" t="n">
-        <v>2.5</v>
+        <v>1.9</v>
       </c>
       <c r="P2" s="31" t="n">
-        <v>24.3</v>
+        <v>25.1</v>
       </c>
       <c r="Q2" s="31" t="n">
-        <v>13.75</v>
+        <v>14.04</v>
       </c>
       <c r="R2" s="50" t="n"/>
       <c r="S2" s="22" t="inlineStr">
@@ -1176,10 +1176,10 @@
         </is>
       </c>
       <c r="O3" s="31" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="P3" s="31" t="n">
-        <v>23</v>
+        <v>24.3</v>
       </c>
       <c r="Q3" s="31" t="n"/>
       <c r="R3" s="50" t="inlineStr">
@@ -1285,10 +1285,10 @@
         </is>
       </c>
       <c r="O4" s="31" t="n">
-        <v>1.1</v>
+        <v>0.6</v>
       </c>
       <c r="P4" s="31" t="n">
-        <v>21</v>
+        <v>23.3</v>
       </c>
       <c r="Q4" s="31" t="n"/>
       <c r="R4" s="50" t="inlineStr">
@@ -1483,13 +1483,13 @@
         </is>
       </c>
       <c r="O6" s="31" t="n">
-        <v>-1.8</v>
+        <v>-4.4</v>
       </c>
       <c r="P6" s="31" t="n">
-        <v>15.6</v>
+        <v>18.1</v>
       </c>
       <c r="Q6" s="31" t="n">
-        <v>7.46</v>
+        <v>6.99</v>
       </c>
       <c r="R6" s="52" t="inlineStr">
         <is>
@@ -1695,13 +1695,13 @@
       </c>
       <c r="N8" s="2" t="n"/>
       <c r="O8" s="31" t="n">
-        <v>0.8</v>
+        <v>3.9</v>
       </c>
       <c r="P8" s="31" t="n">
-        <v>23.1</v>
+        <v>20.5</v>
       </c>
       <c r="Q8" s="31" t="n">
-        <v>11.46</v>
+        <v>12.65</v>
       </c>
       <c r="R8" s="50" t="n"/>
       <c r="S8" s="22" t="inlineStr">
@@ -1808,13 +1808,13 @@
       </c>
       <c r="N9" s="2" t="n"/>
       <c r="O9" s="31" t="n">
-        <v>5.3</v>
+        <v>4.9</v>
       </c>
       <c r="P9" s="31" t="n">
-        <v>22.7</v>
+        <v>23.8</v>
       </c>
       <c r="Q9" s="31" t="n">
-        <v>14.17</v>
+        <v>13.86</v>
       </c>
       <c r="R9" s="50" t="n"/>
       <c r="S9" s="22" t="inlineStr">
@@ -1929,13 +1929,13 @@
         </is>
       </c>
       <c r="O10" s="31" t="n">
-        <v>0.3</v>
+        <v>-0.7</v>
       </c>
       <c r="P10" s="31" t="n">
-        <v>19.9</v>
+        <v>22.2</v>
       </c>
       <c r="Q10" s="31" t="n">
-        <v>11.99</v>
+        <v>13.86</v>
       </c>
       <c r="R10" s="50" t="n"/>
       <c r="S10" s="22" t="inlineStr">
@@ -2046,13 +2046,13 @@
         </is>
       </c>
       <c r="O11" s="31" t="n">
-        <v>-2.2</v>
+        <v>-6.4</v>
       </c>
       <c r="P11" s="31" t="n">
-        <v>17.4</v>
+        <v>22.2</v>
       </c>
       <c r="Q11" s="31" t="n">
-        <v>8.380000000000001</v>
+        <v>13.86</v>
       </c>
       <c r="R11" s="50" t="inlineStr">
         <is>
@@ -2163,13 +2163,13 @@
       </c>
       <c r="N12" s="2" t="n"/>
       <c r="O12" s="31" t="n">
-        <v>0.4</v>
+        <v>-1.6</v>
       </c>
       <c r="P12" s="31" t="n">
-        <v>18.6</v>
+        <v>22.2</v>
       </c>
       <c r="Q12" s="31" t="n">
-        <v>8.890000000000001</v>
+        <v>13.86</v>
       </c>
       <c r="R12" s="50" t="inlineStr">
         <is>
@@ -2284,13 +2284,13 @@
         </is>
       </c>
       <c r="O13" s="31" t="n">
-        <v>1.6</v>
+        <v>-3.4</v>
       </c>
       <c r="P13" s="31" t="n">
-        <v>17.5</v>
+        <v>19.8</v>
       </c>
       <c r="Q13" s="31" t="n">
-        <v>9.82</v>
+        <v>7.87</v>
       </c>
       <c r="R13" s="50" t="inlineStr">
         <is>
@@ -2401,13 +2401,13 @@
       </c>
       <c r="N14" s="2" t="n"/>
       <c r="O14" s="31" t="n">
-        <v>2.5</v>
+        <v>4.6</v>
       </c>
       <c r="P14" s="31" t="n">
-        <v>18.2</v>
+        <v>16.5</v>
       </c>
       <c r="Q14" s="31" t="n">
-        <v>10.02</v>
+        <v>10.75</v>
       </c>
       <c r="R14" s="50" t="n"/>
       <c r="S14" s="22" t="inlineStr">
@@ -2522,13 +2522,13 @@
       </c>
       <c r="N15" s="2" t="n"/>
       <c r="O15" s="31" t="n">
-        <v>-5.5</v>
+        <v>-3</v>
       </c>
       <c r="P15" s="31" t="n">
-        <v>16.4</v>
+        <v>13.8</v>
       </c>
       <c r="Q15" s="31" t="n">
-        <v>5.74</v>
+        <v>5.88</v>
       </c>
       <c r="R15" s="50" t="n"/>
       <c r="S15" s="22" t="inlineStr">
@@ -2633,13 +2633,13 @@
       </c>
       <c r="N16" s="2" t="n"/>
       <c r="O16" s="31" t="n">
-        <v>-3.7</v>
+        <v>-1.3</v>
       </c>
       <c r="P16" s="31" t="n">
-        <v>18.6</v>
+        <v>17.2</v>
       </c>
       <c r="Q16" s="31" t="n">
-        <v>7.19</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="R16" s="50" t="n"/>
       <c r="S16" s="22" t="n"/>
@@ -2732,7 +2732,7 @@
         </is>
       </c>
       <c r="O17" s="31" t="n">
-        <v>-6.3</v>
+        <v>-8.800000000000001</v>
       </c>
       <c r="P17" s="31" t="n"/>
       <c r="Q17" s="31" t="n"/>
@@ -8323,13 +8323,13 @@
         </is>
       </c>
       <c r="O78" s="31" t="n">
-        <v>3.1</v>
+        <v>-2.5</v>
       </c>
       <c r="P78" s="31" t="n">
-        <v>10.4</v>
+        <v>12.7</v>
       </c>
       <c r="Q78" s="31" t="n">
-        <v>5.1</v>
+        <v>3.11</v>
       </c>
       <c r="R78" s="50" t="inlineStr">
         <is>
@@ -8757,13 +8757,13 @@
         </is>
       </c>
       <c r="O82" s="31" t="n">
-        <v>-4.6</v>
+        <v>-1.9</v>
       </c>
       <c r="P82" s="31" t="n">
-        <v>17.5</v>
+        <v>17.6</v>
       </c>
       <c r="Q82" s="31" t="n">
-        <v>5.65</v>
+        <v>7.71</v>
       </c>
       <c r="R82" s="50" t="n"/>
       <c r="S82" s="22" t="inlineStr">
@@ -8879,13 +8879,13 @@
         </is>
       </c>
       <c r="O83" s="31" t="n">
-        <v>-5</v>
+        <v>-0.4</v>
       </c>
       <c r="P83" s="31" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="Q83" s="31" t="n">
-        <v>5.31</v>
+        <v>7.65</v>
       </c>
       <c r="R83" s="50" t="n"/>
       <c r="S83" s="22" t="inlineStr">
@@ -9099,13 +9099,13 @@
         </is>
       </c>
       <c r="O85" s="31" t="n">
-        <v>-2.4</v>
+        <v>-1.3</v>
       </c>
       <c r="P85" s="31" t="n">
-        <v>19.8</v>
+        <v>21.2</v>
       </c>
       <c r="Q85" s="31" t="n">
-        <v>6.22</v>
+        <v>8.44</v>
       </c>
       <c r="R85" s="50" t="n"/>
       <c r="S85" s="22" t="inlineStr">
@@ -9319,13 +9319,13 @@
       </c>
       <c r="N87" s="2" t="n"/>
       <c r="O87" s="31" t="n">
-        <v>4.9</v>
+        <v>5.8</v>
       </c>
       <c r="P87" s="31" t="n">
-        <v>23.9</v>
+        <v>26</v>
       </c>
       <c r="Q87" s="31" t="n">
-        <v>13.12</v>
+        <v>14.19</v>
       </c>
       <c r="R87" s="50" t="n"/>
       <c r="S87" s="22" t="inlineStr">
@@ -9547,13 +9547,13 @@
       </c>
       <c r="N89" s="2" t="n"/>
       <c r="O89" s="31" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="P89" s="31" t="n">
-        <v>20.8</v>
+        <v>21.8</v>
       </c>
       <c r="Q89" s="31" t="n">
-        <v>12.1</v>
+        <v>12.7</v>
       </c>
       <c r="R89" s="50" t="inlineStr">
         <is>
@@ -9969,13 +9969,13 @@
       </c>
       <c r="N93" s="2" t="n"/>
       <c r="O93" s="31" t="n">
-        <v>5.7</v>
+        <v>-2</v>
       </c>
       <c r="P93" s="31" t="n">
-        <v>14.3</v>
+        <v>14.9</v>
       </c>
       <c r="Q93" s="31" t="n">
-        <v>8.449999999999999</v>
+        <v>6.2</v>
       </c>
       <c r="R93" s="50" t="n"/>
       <c r="S93" s="22" t="inlineStr">
@@ -10082,13 +10082,13 @@
       </c>
       <c r="N94" s="2" t="n"/>
       <c r="O94" s="31" t="n">
-        <v>13.7</v>
+        <v>8.9</v>
       </c>
       <c r="P94" s="31" t="n">
-        <v>21.8</v>
+        <v>23.3</v>
       </c>
       <c r="Q94" s="31" t="n">
-        <v>16.62</v>
+        <v>17</v>
       </c>
       <c r="R94" s="50" t="n"/>
       <c r="S94" s="22" t="inlineStr">
@@ -10318,13 +10318,13 @@
       </c>
       <c r="N96" s="2" t="n"/>
       <c r="O96" s="31" t="n">
-        <v>8</v>
+        <v>5.2</v>
       </c>
       <c r="P96" s="31" t="n">
-        <v>20.8</v>
+        <v>21.8</v>
       </c>
       <c r="Q96" s="31" t="n">
-        <v>14.35</v>
+        <v>14.18</v>
       </c>
       <c r="R96" s="50" t="n"/>
       <c r="S96" s="22" t="inlineStr">
@@ -10562,13 +10562,13 @@
       </c>
       <c r="N98" s="2" t="n"/>
       <c r="O98" s="31" t="n">
-        <v>6</v>
+        <v>8.5</v>
       </c>
       <c r="P98" s="31" t="n">
-        <v>20</v>
+        <v>21.8</v>
       </c>
       <c r="Q98" s="31" t="n">
-        <v>13.1</v>
+        <v>14.89</v>
       </c>
       <c r="R98" s="50" t="n"/>
       <c r="S98" s="22" t="inlineStr">
@@ -11123,13 +11123,13 @@
       </c>
       <c r="N103" s="2" t="n"/>
       <c r="O103" s="31" t="n">
-        <v>0</v>
+        <v>-0.3</v>
       </c>
       <c r="P103" s="31" t="n">
-        <v>17.8</v>
+        <v>18.9</v>
       </c>
       <c r="Q103" s="31" t="n">
-        <v>8.66</v>
+        <v>8.85</v>
       </c>
       <c r="R103" s="50" t="n"/>
       <c r="S103" s="22" t="inlineStr">
@@ -11342,9 +11342,15 @@
         </is>
       </c>
       <c r="N105" s="2" t="n"/>
-      <c r="O105" s="31" t="n"/>
-      <c r="P105" s="31" t="n"/>
-      <c r="Q105" s="31" t="n"/>
+      <c r="O105" s="31" t="n">
+        <v>-2.6</v>
+      </c>
+      <c r="P105" s="31" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="Q105" s="31" t="n">
+        <v>7.72</v>
+      </c>
       <c r="R105" s="50" t="n"/>
       <c r="S105" s="22" t="n"/>
       <c r="T105" s="36" t="inlineStr">
@@ -11462,13 +11468,13 @@
         </is>
       </c>
       <c r="O106" s="31" t="n">
-        <v>-2.4</v>
+        <v>-4.5</v>
       </c>
       <c r="P106" s="31" t="n">
-        <v>16</v>
+        <v>18.6</v>
       </c>
       <c r="Q106" s="31" t="n">
-        <v>5.69</v>
+        <v>6.7</v>
       </c>
       <c r="R106" s="50" t="n"/>
       <c r="S106" s="22" t="inlineStr">
@@ -12304,13 +12310,13 @@
       </c>
       <c r="N114" s="2" t="n"/>
       <c r="O114" s="31" t="n">
-        <v>5.2</v>
+        <v>4.2</v>
       </c>
       <c r="P114" s="31" t="n">
-        <v>13.9</v>
+        <v>12.8</v>
       </c>
       <c r="Q114" s="31" t="n">
-        <v>8.449999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="R114" s="50" t="n"/>
       <c r="S114" s="22" t="inlineStr">
@@ -12421,13 +12427,13 @@
         </is>
       </c>
       <c r="O115" s="31" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="P115" s="31" t="n">
-        <v>14.1</v>
+        <v>10.7</v>
       </c>
       <c r="Q115" s="31" t="n">
-        <v>8.16</v>
+        <v>6.79</v>
       </c>
       <c r="R115" s="50" t="n"/>
       <c r="S115" s="22" t="inlineStr">
@@ -12546,13 +12552,13 @@
         </is>
       </c>
       <c r="O116" s="31" t="n">
-        <v>2.9</v>
+        <v>1.1</v>
       </c>
       <c r="P116" s="31" t="n">
-        <v>10.1</v>
+        <v>8</v>
       </c>
       <c r="Q116" s="31" t="n">
-        <v>4.88</v>
+        <v>3.88</v>
       </c>
       <c r="R116" s="50" t="n"/>
       <c r="S116" s="22" t="inlineStr">
@@ -13111,13 +13117,13 @@
       </c>
       <c r="N121" s="2" t="n"/>
       <c r="O121" s="31" t="n">
-        <v>23.8</v>
+        <v>25.3</v>
       </c>
       <c r="P121" s="31" t="n">
-        <v>33.1</v>
+        <v>32.9</v>
       </c>
       <c r="Q121" s="31" t="n">
-        <v>28.61</v>
+        <v>28.85</v>
       </c>
       <c r="R121" s="50" t="n"/>
       <c r="S121" s="22" t="inlineStr">
@@ -13228,13 +13234,13 @@
       </c>
       <c r="N122" s="2" t="n"/>
       <c r="O122" s="31" t="n">
-        <v>20.3</v>
+        <v>21.3</v>
       </c>
       <c r="P122" s="31" t="n">
-        <v>28</v>
+        <v>25.9</v>
       </c>
       <c r="Q122" s="31" t="n">
-        <v>23.75</v>
+        <v>23.5</v>
       </c>
       <c r="R122" s="50" t="n"/>
       <c r="S122" s="22" t="inlineStr">
@@ -13353,13 +13359,13 @@
       </c>
       <c r="N123" s="2" t="n"/>
       <c r="O123" s="31" t="n">
-        <v>-0.4</v>
+        <v>4.1</v>
       </c>
       <c r="P123" s="31" t="n">
-        <v>15.8</v>
+        <v>15.5</v>
       </c>
       <c r="Q123" s="31" t="n">
-        <v>6.84</v>
+        <v>8.75</v>
       </c>
       <c r="R123" s="50" t="n"/>
       <c r="S123" s="22" t="inlineStr">
@@ -13577,13 +13583,13 @@
       </c>
       <c r="N125" s="2" t="n"/>
       <c r="O125" s="31" t="n">
-        <v>8.800000000000001</v>
+        <v>7.5</v>
       </c>
       <c r="P125" s="31" t="n">
-        <v>18.5</v>
+        <v>20.8</v>
       </c>
       <c r="Q125" s="31" t="n">
-        <v>13.15</v>
+        <v>13.51</v>
       </c>
       <c r="R125" s="50" t="n"/>
       <c r="S125" s="22" t="inlineStr">
@@ -13702,13 +13708,13 @@
       </c>
       <c r="N126" s="2" t="n"/>
       <c r="O126" s="31" t="n">
-        <v>16.6</v>
+        <v>16</v>
       </c>
       <c r="P126" s="31" t="n">
-        <v>24.7</v>
+        <v>26.4</v>
       </c>
       <c r="Q126" s="31" t="n">
-        <v>19.38</v>
+        <v>20.15</v>
       </c>
       <c r="R126" s="50" t="n"/>
       <c r="S126" s="22" t="inlineStr">
@@ -13807,13 +13813,13 @@
       </c>
       <c r="N127" s="2" t="n"/>
       <c r="O127" s="31" t="n">
-        <v>15.4</v>
+        <v>16.2</v>
       </c>
       <c r="P127" s="31" t="n">
-        <v>22.9</v>
+        <v>24.2</v>
       </c>
       <c r="Q127" s="31" t="n">
-        <v>18.49</v>
+        <v>19.98</v>
       </c>
       <c r="R127" s="50" t="n"/>
       <c r="S127" s="22" t="inlineStr">
@@ -13920,13 +13926,13 @@
       </c>
       <c r="N128" s="2" t="n"/>
       <c r="O128" s="31" t="n">
-        <v>12.5</v>
+        <v>13.1</v>
       </c>
       <c r="P128" s="31" t="n">
-        <v>15.1</v>
+        <v>20.9</v>
       </c>
       <c r="Q128" s="31" t="n">
-        <v>13.61</v>
+        <v>15.84</v>
       </c>
       <c r="R128" s="50" t="n"/>
       <c r="S128" s="22" t="inlineStr">
@@ -14041,13 +14047,13 @@
       </c>
       <c r="N129" s="2" t="n"/>
       <c r="O129" s="31" t="n">
-        <v>14.3</v>
+        <v>16.3</v>
       </c>
       <c r="P129" s="31" t="n">
-        <v>25.1</v>
+        <v>23.5</v>
       </c>
       <c r="Q129" s="31" t="n">
-        <v>17.7</v>
+        <v>18.93</v>
       </c>
       <c r="R129" s="50" t="n"/>
       <c r="S129" s="22" t="inlineStr">
@@ -14154,13 +14160,13 @@
       </c>
       <c r="N130" s="2" t="n"/>
       <c r="O130" s="31" t="n">
-        <v>13.7</v>
+        <v>11.6</v>
       </c>
       <c r="P130" s="31" t="n">
-        <v>18.7</v>
+        <v>18</v>
       </c>
       <c r="Q130" s="31" t="n">
-        <v>15.28</v>
+        <v>13.77</v>
       </c>
       <c r="R130" s="50" t="n"/>
       <c r="S130" s="22" t="inlineStr">
@@ -14275,13 +14281,13 @@
       </c>
       <c r="N131" s="2" t="n"/>
       <c r="O131" s="31" t="n">
-        <v>9.199999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="P131" s="31" t="n">
-        <v>13.1</v>
+        <v>16</v>
       </c>
       <c r="Q131" s="31" t="n">
-        <v>10.36</v>
+        <v>10.85</v>
       </c>
       <c r="R131" s="50" t="n"/>
       <c r="S131" s="22" t="inlineStr">
@@ -14396,13 +14402,13 @@
       </c>
       <c r="N132" s="2" t="n"/>
       <c r="O132" s="31" t="n">
-        <v>19</v>
+        <v>16.2</v>
       </c>
       <c r="P132" s="31" t="n">
-        <v>26.7</v>
+        <v>23.5</v>
       </c>
       <c r="Q132" s="31" t="n">
-        <v>21.2</v>
+        <v>19.75</v>
       </c>
       <c r="R132" s="50" t="n"/>
       <c r="S132" s="22" t="inlineStr">
@@ -14513,13 +14519,13 @@
       </c>
       <c r="N133" s="2" t="n"/>
       <c r="O133" s="31" t="n">
-        <v>16.1</v>
+        <v>15</v>
       </c>
       <c r="P133" s="31" t="n">
-        <v>29.6</v>
+        <v>18.4</v>
       </c>
       <c r="Q133" s="31" t="n">
-        <v>21.5</v>
+        <v>16.89</v>
       </c>
       <c r="R133" s="50" t="n"/>
       <c r="S133" s="22" t="inlineStr">
@@ -14630,13 +14636,13 @@
       </c>
       <c r="N134" s="2" t="n"/>
       <c r="O134" s="31" t="n">
-        <v>19.9</v>
+        <v>13.8</v>
       </c>
       <c r="P134" s="31" t="n">
-        <v>27.5</v>
+        <v>20</v>
       </c>
       <c r="Q134" s="31" t="n">
-        <v>21.66</v>
+        <v>15.29</v>
       </c>
       <c r="R134" s="50" t="n"/>
       <c r="S134" s="22" t="inlineStr">
@@ -14854,13 +14860,13 @@
       </c>
       <c r="N136" s="2" t="n"/>
       <c r="O136" s="31" t="n">
-        <v>21.3</v>
+        <v>20.7</v>
       </c>
       <c r="P136" s="31" t="n">
-        <v>32.2</v>
+        <v>30.4</v>
       </c>
       <c r="Q136" s="31" t="n">
-        <v>26.36</v>
+        <v>25.3</v>
       </c>
       <c r="R136" s="50" t="n"/>
       <c r="S136" s="22" t="inlineStr">
@@ -14971,13 +14977,13 @@
       </c>
       <c r="N137" s="2" t="n"/>
       <c r="O137" s="31" t="n">
-        <v>23.8</v>
+        <v>24.5</v>
       </c>
       <c r="P137" s="31" t="n">
-        <v>31.9</v>
+        <v>30.5</v>
       </c>
       <c r="Q137" s="31" t="n">
-        <v>28</v>
+        <v>27.19</v>
       </c>
       <c r="R137" s="50" t="n"/>
       <c r="S137" s="22" t="inlineStr">
@@ -15088,13 +15094,13 @@
       </c>
       <c r="N138" s="2" t="n"/>
       <c r="O138" s="31" t="n">
-        <v>21.4</v>
+        <v>20.6</v>
       </c>
       <c r="P138" s="31" t="n">
-        <v>33.7</v>
+        <v>30.5</v>
       </c>
       <c r="Q138" s="31" t="n">
-        <v>27.89</v>
+        <v>22.68</v>
       </c>
       <c r="R138" s="50" t="n"/>
       <c r="S138" s="22" t="inlineStr">
@@ -15205,13 +15211,13 @@
       </c>
       <c r="N139" s="2" t="n"/>
       <c r="O139" s="31" t="n">
-        <v>19.3</v>
+        <v>20.2</v>
       </c>
       <c r="P139" s="31" t="n">
-        <v>30.6</v>
+        <v>26.3</v>
       </c>
       <c r="Q139" s="31" t="n">
-        <v>25.02</v>
+        <v>22.77</v>
       </c>
       <c r="R139" s="50" t="n"/>
       <c r="S139" s="22" t="inlineStr">
@@ -15322,13 +15328,13 @@
       </c>
       <c r="N140" s="2" t="n"/>
       <c r="O140" s="31" t="n">
-        <v>20.9</v>
+        <v>21.2</v>
       </c>
       <c r="P140" s="31" t="n">
-        <v>29.8</v>
+        <v>27.4</v>
       </c>
       <c r="Q140" s="31" t="n">
-        <v>25.64</v>
+        <v>24.2</v>
       </c>
       <c r="R140" s="50" t="n"/>
       <c r="S140" s="22" t="inlineStr">
@@ -15439,13 +15445,13 @@
       </c>
       <c r="N141" s="2" t="n"/>
       <c r="O141" s="31" t="n">
-        <v>22.1</v>
+        <v>23.1</v>
       </c>
       <c r="P141" s="31" t="n">
-        <v>30.8</v>
+        <v>28.7</v>
       </c>
       <c r="Q141" s="31" t="n">
-        <v>26.66</v>
+        <v>25.76</v>
       </c>
       <c r="R141" s="50" t="n"/>
       <c r="S141" s="22" t="inlineStr">
@@ -15659,13 +15665,13 @@
       </c>
       <c r="N143" s="2" t="n"/>
       <c r="O143" s="31" t="n">
-        <v>24.1</v>
+        <v>22.2</v>
       </c>
       <c r="P143" s="31" t="n">
-        <v>32.7</v>
+        <v>30.4</v>
       </c>
       <c r="Q143" s="31" t="n">
-        <v>27.56</v>
+        <v>26.32</v>
       </c>
       <c r="R143" s="50" t="n"/>
       <c r="S143" s="22" t="inlineStr">
@@ -15776,13 +15782,13 @@
       </c>
       <c r="N144" s="2" t="n"/>
       <c r="O144" s="31" t="n">
-        <v>25.2</v>
+        <v>24.3</v>
       </c>
       <c r="P144" s="31" t="n">
-        <v>34.9</v>
+        <v>33.3</v>
       </c>
       <c r="Q144" s="31" t="n">
-        <v>28.81</v>
+        <v>28.6</v>
       </c>
       <c r="R144" s="50" t="n"/>
       <c r="S144" s="22" t="inlineStr">
@@ -16095,13 +16101,13 @@
       </c>
       <c r="N147" s="2" t="n"/>
       <c r="O147" s="31" t="n">
-        <v>26.2</v>
+        <v>27</v>
       </c>
       <c r="P147" s="31" t="n">
-        <v>30.7</v>
+        <v>32</v>
       </c>
       <c r="Q147" s="31" t="n">
-        <v>28.61</v>
+        <v>29.38</v>
       </c>
       <c r="R147" s="50" t="n"/>
       <c r="S147" s="22" t="inlineStr">
@@ -16204,13 +16210,13 @@
       </c>
       <c r="N148" s="2" t="n"/>
       <c r="O148" s="31" t="n">
-        <v>24.8</v>
+        <v>25.4</v>
       </c>
       <c r="P148" s="31" t="n">
-        <v>34.7</v>
+        <v>34.6</v>
       </c>
       <c r="Q148" s="31" t="n">
-        <v>29.19</v>
+        <v>29.45</v>
       </c>
       <c r="R148" s="50" t="n"/>
       <c r="S148" s="22" t="inlineStr">
@@ -16321,13 +16327,13 @@
       </c>
       <c r="N149" s="2" t="n"/>
       <c r="O149" s="31" t="n">
-        <v>26.5</v>
+        <v>24.3</v>
       </c>
       <c r="P149" s="31" t="n">
-        <v>32.6</v>
+        <v>36.8</v>
       </c>
       <c r="Q149" s="31" t="n">
-        <v>28.91</v>
+        <v>29.36</v>
       </c>
       <c r="R149" s="50" t="n"/>
       <c r="S149" s="22" t="inlineStr">
@@ -16434,13 +16440,13 @@
       </c>
       <c r="N150" s="2" t="n"/>
       <c r="O150" s="31" t="n">
-        <v>18.4</v>
+        <v>18.5</v>
       </c>
       <c r="P150" s="31" t="n">
         <v>27.5</v>
       </c>
       <c r="Q150" s="31" t="n">
-        <v>22.64</v>
+        <v>22.45</v>
       </c>
       <c r="R150" s="50" t="n"/>
       <c r="S150" s="22" t="inlineStr">
@@ -16551,13 +16557,13 @@
       </c>
       <c r="N151" s="2" t="n"/>
       <c r="O151" s="31" t="n">
-        <v>19.3</v>
+        <v>21</v>
       </c>
       <c r="P151" s="31" t="n">
-        <v>30.4</v>
+        <v>29.9</v>
       </c>
       <c r="Q151" s="31" t="n">
-        <v>24.08</v>
+        <v>24.32</v>
       </c>
       <c r="R151" s="50" t="n"/>
       <c r="S151" s="22" t="inlineStr">
@@ -16668,13 +16674,13 @@
       </c>
       <c r="N152" s="2" t="n"/>
       <c r="O152" s="31" t="n">
-        <v>29.2</v>
+        <v>31</v>
       </c>
       <c r="P152" s="31" t="n">
-        <v>38.9</v>
+        <v>37.5</v>
       </c>
       <c r="Q152" s="31" t="n">
-        <v>33.54</v>
+        <v>33.65</v>
       </c>
       <c r="R152" s="50" t="n"/>
       <c r="S152" s="22" t="inlineStr">
@@ -16876,13 +16882,13 @@
       </c>
       <c r="N154" s="2" t="n"/>
       <c r="O154" s="31" t="n">
-        <v>22.7</v>
+        <v>19.3</v>
       </c>
       <c r="P154" s="31" t="n">
-        <v>29.2</v>
+        <v>26.3</v>
       </c>
       <c r="Q154" s="31" t="n">
-        <v>25.76</v>
+        <v>21.96</v>
       </c>
       <c r="R154" s="50" t="n"/>
       <c r="S154" s="22" t="inlineStr">
@@ -16997,12 +17003,14 @@
       </c>
       <c r="N155" s="2" t="n"/>
       <c r="O155" s="31" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="P155" s="31" t="n">
-        <v>23.8</v>
-      </c>
-      <c r="Q155" s="31" t="n"/>
+        <v>21</v>
+      </c>
+      <c r="Q155" s="31" t="n">
+        <v>15.66</v>
+      </c>
       <c r="R155" s="50" t="n"/>
       <c r="S155" s="22" t="inlineStr">
         <is>
@@ -17298,13 +17306,13 @@
       </c>
       <c r="N158" s="2" t="n"/>
       <c r="O158" s="31" t="n">
-        <v>24.2</v>
+        <v>23.9</v>
       </c>
       <c r="P158" s="31" t="n">
-        <v>30.1</v>
+        <v>28.2</v>
       </c>
       <c r="Q158" s="31" t="n">
-        <v>26.98</v>
+        <v>25.9</v>
       </c>
       <c r="R158" s="50" t="n"/>
       <c r="S158" s="22" t="inlineStr">
@@ -17692,13 +17700,13 @@
       </c>
       <c r="N162" s="2" t="n"/>
       <c r="O162" s="31" t="n">
-        <v>12.9</v>
+        <v>11.9</v>
       </c>
       <c r="P162" s="31" t="n">
-        <v>16.9</v>
+        <v>16.5</v>
       </c>
       <c r="Q162" s="31" t="n">
-        <v>14.08</v>
+        <v>13.74</v>
       </c>
       <c r="R162" s="50" t="n"/>
       <c r="S162" s="22" t="inlineStr">
@@ -17813,10 +17821,10 @@
       </c>
       <c r="N163" s="2" t="n"/>
       <c r="O163" s="31" t="n">
-        <v>-67.8</v>
+        <v>-64.3</v>
       </c>
       <c r="P163" s="31" t="n">
-        <v>-60.9</v>
+        <v>-59.8</v>
       </c>
       <c r="Q163" s="31" t="n"/>
       <c r="R163" s="50" t="n"/>
@@ -17912,13 +17920,13 @@
       </c>
       <c r="N164" s="2" t="n"/>
       <c r="O164" s="31" t="n">
-        <v>10.9</v>
+        <v>11</v>
       </c>
       <c r="P164" s="31" t="n">
-        <v>19</v>
+        <v>13.3</v>
       </c>
       <c r="Q164" s="31" t="n">
-        <v>13.82</v>
+        <v>11.78</v>
       </c>
       <c r="R164" s="50" t="n"/>
       <c r="S164" s="22" t="inlineStr">
@@ -18019,7 +18027,7 @@
       </c>
       <c r="N165" s="2" t="n"/>
       <c r="O165" s="31" t="n">
-        <v>-20.1</v>
+        <v>-33.3</v>
       </c>
       <c r="P165" s="31" t="n"/>
       <c r="Q165" s="31" t="n"/>
@@ -18846,10 +18854,10 @@
       </c>
       <c r="N174" s="2" t="n"/>
       <c r="O174" s="31" t="n">
-        <v>10.8</v>
+        <v>6.7</v>
       </c>
       <c r="P174" s="31" t="n">
-        <v>16.2</v>
+        <v>11.5</v>
       </c>
       <c r="Q174" s="31" t="n"/>
       <c r="R174" s="50" t="n"/>
@@ -18957,10 +18965,10 @@
         </is>
       </c>
       <c r="O175" s="31" t="n">
-        <v>-0.8</v>
+        <v>1.5</v>
       </c>
       <c r="P175" s="31" t="n">
-        <v>12.3</v>
+        <v>13.8</v>
       </c>
       <c r="Q175" s="31" t="n"/>
       <c r="R175" s="50" t="n"/>
@@ -19516,10 +19524,10 @@
       </c>
       <c r="N180" s="2" t="n"/>
       <c r="O180" s="31" t="n">
-        <v>-2.2</v>
+        <v>-1.4</v>
       </c>
       <c r="P180" s="31" t="n">
-        <v>17.9</v>
+        <v>18.7</v>
       </c>
       <c r="Q180" s="31" t="n"/>
       <c r="R180" s="50" t="n"/>
@@ -20117,12 +20125,8 @@
         </is>
       </c>
       <c r="N186" s="3" t="n"/>
-      <c r="O186" s="31" t="n">
-        <v>-1.1</v>
-      </c>
-      <c r="P186" s="31" t="n">
-        <v>16</v>
-      </c>
+      <c r="O186" s="31" t="n"/>
+      <c r="P186" s="31" t="n"/>
       <c r="Q186" s="31" t="n"/>
       <c r="R186" s="50" t="n"/>
       <c r="S186" s="22" t="inlineStr">
@@ -20629,13 +20633,13 @@
       </c>
       <c r="N191" s="2" t="n"/>
       <c r="O191" s="31" t="n">
-        <v>4.4</v>
+        <v>-3.6</v>
       </c>
       <c r="P191" s="31" t="n">
-        <v>13.9</v>
+        <v>16.4</v>
       </c>
       <c r="Q191" s="31" t="n">
-        <v>8.66</v>
+        <v>5.96</v>
       </c>
       <c r="R191" s="50" t="inlineStr">
         <is>
@@ -20936,10 +20940,10 @@
         </is>
       </c>
       <c r="O194" s="31" t="n">
-        <v>-6.4</v>
+        <v>-4.8</v>
       </c>
       <c r="P194" s="31" t="n">
-        <v>16.8</v>
+        <v>19</v>
       </c>
       <c r="Q194" s="31" t="n"/>
       <c r="R194" s="50" t="n"/>
@@ -21151,12 +21155,8 @@
         </is>
       </c>
       <c r="N196" s="2" t="n"/>
-      <c r="O196" s="31" t="n">
-        <v>-3.9</v>
-      </c>
-      <c r="P196" s="31" t="n">
-        <v>17.3</v>
-      </c>
+      <c r="O196" s="31" t="n"/>
+      <c r="P196" s="31" t="n"/>
       <c r="Q196" s="31" t="n"/>
       <c r="R196" s="50" t="inlineStr">
         <is>
@@ -22903,13 +22903,13 @@
         </is>
       </c>
       <c r="O213" s="31" t="n">
-        <v>-6.8</v>
+        <v>-6.4</v>
       </c>
       <c r="P213" s="31" t="n">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="Q213" s="31" t="n">
-        <v>-2.4</v>
+        <v>-2.7</v>
       </c>
       <c r="R213" s="50" t="n"/>
       <c r="S213" s="22" t="inlineStr">
@@ -23633,12 +23633,8 @@
         </is>
       </c>
       <c r="N220" s="2" t="n"/>
-      <c r="O220" s="31" t="n">
-        <v>-4.3</v>
-      </c>
-      <c r="P220" s="31" t="n">
-        <v>15.8</v>
-      </c>
+      <c r="O220" s="31" t="n"/>
+      <c r="P220" s="31" t="n"/>
       <c r="Q220" s="31" t="n"/>
       <c r="R220" s="50" t="n"/>
       <c r="S220" s="22" t="inlineStr">
@@ -23947,10 +23943,10 @@
       </c>
       <c r="N223" s="2" t="n"/>
       <c r="O223" s="31" t="n">
-        <v>-7.4</v>
+        <v>-6.6</v>
       </c>
       <c r="P223" s="31" t="n">
-        <v>18.1</v>
+        <v>20.8</v>
       </c>
       <c r="Q223" s="31" t="n"/>
       <c r="R223" s="50" t="n"/>
@@ -27570,14 +27566,12 @@
       </c>
       <c r="N260" s="2" t="n"/>
       <c r="O260" s="31" t="n">
-        <v>-4.9</v>
+        <v>-6</v>
       </c>
       <c r="P260" s="31" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q260" s="31" t="n">
-        <v>-2.2</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="Q260" s="31" t="n"/>
       <c r="R260" s="50" t="n"/>
       <c r="S260" s="22" t="inlineStr">
         <is>
@@ -28391,8 +28385,12 @@
         </is>
       </c>
       <c r="N268" s="2" t="n"/>
-      <c r="O268" s="31" t="n"/>
-      <c r="P268" s="31" t="n"/>
+      <c r="O268" s="31" t="n">
+        <v>-1.9</v>
+      </c>
+      <c r="P268" s="31" t="n">
+        <v>1.4</v>
+      </c>
       <c r="Q268" s="31" t="n"/>
       <c r="R268" s="50" t="n"/>
       <c r="S268" s="22" t="inlineStr">
@@ -28499,13 +28497,13 @@
         </is>
       </c>
       <c r="O269" s="31" t="n">
-        <v>-3.2</v>
+        <v>-7.5</v>
       </c>
       <c r="P269" s="31" t="n">
-        <v>6.5</v>
+        <v>2.7</v>
       </c>
       <c r="Q269" s="31" t="n">
-        <v>1.11</v>
+        <v>-2.25</v>
       </c>
       <c r="R269" s="50" t="n"/>
       <c r="S269" s="22" t="inlineStr">
@@ -29235,12 +29233,8 @@
         </is>
       </c>
       <c r="N276" s="2" t="n"/>
-      <c r="O276" s="31" t="n">
-        <v>-5.3</v>
-      </c>
-      <c r="P276" s="31" t="n">
-        <v>15.6</v>
-      </c>
+      <c r="O276" s="31" t="n"/>
+      <c r="P276" s="31" t="n"/>
       <c r="Q276" s="31" t="n"/>
       <c r="R276" s="50" t="n"/>
       <c r="S276" s="22" t="n"/>

--- a/气象/For_Python_站点信息和记录.xlsx
+++ b/气象/For_Python_站点信息和记录.xlsx
@@ -840,8 +840,8 @@
     <col width="18.59765625" customWidth="1" style="8" min="26" max="26"/>
     <col width="12.59765625" customWidth="1" style="5" min="27" max="31"/>
     <col width="12.59765625" customWidth="1" style="8" min="32" max="33"/>
-    <col width="12.59765625" customWidth="1" style="5" min="34" max="704"/>
-    <col width="12.59765625" customWidth="1" style="5" min="705" max="16384"/>
+    <col width="12.59765625" customWidth="1" style="5" min="34" max="706"/>
+    <col width="12.59765625" customWidth="1" style="5" min="707" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="27.75" customFormat="1" customHeight="1" s="11">
@@ -1069,13 +1069,13 @@
         </is>
       </c>
       <c r="O2" s="31" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="P2" s="31" t="n">
-        <v>25.1</v>
+        <v>25.5</v>
       </c>
       <c r="Q2" s="31" t="n">
-        <v>14.04</v>
+        <v>13.93</v>
       </c>
       <c r="R2" s="50" t="n"/>
       <c r="S2" s="22" t="inlineStr">
@@ -1176,10 +1176,10 @@
         </is>
       </c>
       <c r="O3" s="31" t="n">
-        <v>3.5</v>
+        <v>2.8</v>
       </c>
       <c r="P3" s="31" t="n">
-        <v>24.3</v>
+        <v>26</v>
       </c>
       <c r="Q3" s="31" t="n"/>
       <c r="R3" s="50" t="inlineStr">
@@ -1285,10 +1285,10 @@
         </is>
       </c>
       <c r="O4" s="31" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="P4" s="31" t="n">
-        <v>23.3</v>
+        <v>24.2</v>
       </c>
       <c r="Q4" s="31" t="n"/>
       <c r="R4" s="50" t="inlineStr">
@@ -1483,13 +1483,13 @@
         </is>
       </c>
       <c r="O6" s="31" t="n">
-        <v>-4.4</v>
+        <v>-4</v>
       </c>
       <c r="P6" s="31" t="n">
-        <v>18.1</v>
+        <v>19</v>
       </c>
       <c r="Q6" s="31" t="n">
-        <v>6.99</v>
+        <v>7.29</v>
       </c>
       <c r="R6" s="52" t="inlineStr">
         <is>
@@ -1695,13 +1695,13 @@
       </c>
       <c r="N8" s="2" t="n"/>
       <c r="O8" s="31" t="n">
-        <v>3.9</v>
+        <v>2.3</v>
       </c>
       <c r="P8" s="31" t="n">
-        <v>20.5</v>
+        <v>22.6</v>
       </c>
       <c r="Q8" s="31" t="n">
-        <v>12.65</v>
+        <v>10.63</v>
       </c>
       <c r="R8" s="50" t="n"/>
       <c r="S8" s="22" t="inlineStr">
@@ -1808,13 +1808,13 @@
       </c>
       <c r="N9" s="2" t="n"/>
       <c r="O9" s="31" t="n">
-        <v>4.9</v>
+        <v>3</v>
       </c>
       <c r="P9" s="31" t="n">
-        <v>23.8</v>
+        <v>24.9</v>
       </c>
       <c r="Q9" s="31" t="n">
-        <v>13.86</v>
+        <v>11.13</v>
       </c>
       <c r="R9" s="50" t="n"/>
       <c r="S9" s="22" t="inlineStr">
@@ -1929,13 +1929,13 @@
         </is>
       </c>
       <c r="O10" s="31" t="n">
-        <v>-0.7</v>
+        <v>-2</v>
       </c>
       <c r="P10" s="31" t="n">
-        <v>22.2</v>
+        <v>23.1</v>
       </c>
       <c r="Q10" s="31" t="n">
-        <v>13.86</v>
+        <v>11.53</v>
       </c>
       <c r="R10" s="50" t="n"/>
       <c r="S10" s="22" t="inlineStr">
@@ -2046,13 +2046,13 @@
         </is>
       </c>
       <c r="O11" s="31" t="n">
-        <v>-6.4</v>
+        <v>-5.1</v>
       </c>
       <c r="P11" s="31" t="n">
-        <v>22.2</v>
+        <v>19.1</v>
       </c>
       <c r="Q11" s="31" t="n">
-        <v>13.86</v>
+        <v>8.35</v>
       </c>
       <c r="R11" s="50" t="inlineStr">
         <is>
@@ -2163,13 +2163,13 @@
       </c>
       <c r="N12" s="2" t="n"/>
       <c r="O12" s="31" t="n">
-        <v>-1.6</v>
+        <v>-1.4</v>
       </c>
       <c r="P12" s="31" t="n">
-        <v>22.2</v>
+        <v>22.5</v>
       </c>
       <c r="Q12" s="31" t="n">
-        <v>13.86</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="R12" s="50" t="inlineStr">
         <is>
@@ -2284,13 +2284,13 @@
         </is>
       </c>
       <c r="O13" s="31" t="n">
-        <v>-3.4</v>
+        <v>-2.1</v>
       </c>
       <c r="P13" s="31" t="n">
-        <v>19.8</v>
+        <v>21.4</v>
       </c>
       <c r="Q13" s="31" t="n">
-        <v>7.87</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="R13" s="50" t="inlineStr">
         <is>
@@ -2401,13 +2401,13 @@
       </c>
       <c r="N14" s="2" t="n"/>
       <c r="O14" s="31" t="n">
-        <v>4.6</v>
+        <v>3.9</v>
       </c>
       <c r="P14" s="31" t="n">
-        <v>16.5</v>
+        <v>21.9</v>
       </c>
       <c r="Q14" s="31" t="n">
-        <v>10.75</v>
+        <v>12.21</v>
       </c>
       <c r="R14" s="50" t="n"/>
       <c r="S14" s="22" t="inlineStr">
@@ -2522,13 +2522,13 @@
       </c>
       <c r="N15" s="2" t="n"/>
       <c r="O15" s="31" t="n">
-        <v>-3</v>
+        <v>-2.1</v>
       </c>
       <c r="P15" s="31" t="n">
-        <v>13.8</v>
+        <v>19.2</v>
       </c>
       <c r="Q15" s="31" t="n">
-        <v>5.88</v>
+        <v>8.35</v>
       </c>
       <c r="R15" s="50" t="n"/>
       <c r="S15" s="22" t="inlineStr">
@@ -2633,13 +2633,13 @@
       </c>
       <c r="N16" s="2" t="n"/>
       <c r="O16" s="31" t="n">
-        <v>-1.3</v>
+        <v>-1.7</v>
       </c>
       <c r="P16" s="31" t="n">
-        <v>17.2</v>
+        <v>23</v>
       </c>
       <c r="Q16" s="31" t="n">
-        <v>8.539999999999999</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="R16" s="50" t="n"/>
       <c r="S16" s="22" t="n"/>
@@ -8323,13 +8323,13 @@
         </is>
       </c>
       <c r="O78" s="31" t="n">
-        <v>-2.5</v>
+        <v>-4.2</v>
       </c>
       <c r="P78" s="31" t="n">
-        <v>12.7</v>
+        <v>8.9</v>
       </c>
       <c r="Q78" s="31" t="n">
-        <v>3.11</v>
+        <v>2.57</v>
       </c>
       <c r="R78" s="50" t="inlineStr">
         <is>
@@ -8757,13 +8757,13 @@
         </is>
       </c>
       <c r="O82" s="31" t="n">
-        <v>-1.9</v>
+        <v>3.7</v>
       </c>
       <c r="P82" s="31" t="n">
-        <v>17.6</v>
+        <v>17.5</v>
       </c>
       <c r="Q82" s="31" t="n">
-        <v>7.71</v>
+        <v>9.6</v>
       </c>
       <c r="R82" s="50" t="n"/>
       <c r="S82" s="22" t="inlineStr">
@@ -8879,13 +8879,13 @@
         </is>
       </c>
       <c r="O83" s="31" t="n">
-        <v>-0.4</v>
+        <v>1</v>
       </c>
       <c r="P83" s="31" t="n">
-        <v>17.4</v>
+        <v>17.9</v>
       </c>
       <c r="Q83" s="31" t="n">
-        <v>7.65</v>
+        <v>13.3</v>
       </c>
       <c r="R83" s="50" t="n"/>
       <c r="S83" s="22" t="inlineStr">
@@ -9099,13 +9099,13 @@
         </is>
       </c>
       <c r="O85" s="31" t="n">
-        <v>-1.3</v>
+        <v>6.6</v>
       </c>
       <c r="P85" s="31" t="n">
-        <v>21.2</v>
+        <v>24.5</v>
       </c>
       <c r="Q85" s="31" t="n">
-        <v>8.44</v>
+        <v>14.87</v>
       </c>
       <c r="R85" s="50" t="n"/>
       <c r="S85" s="22" t="inlineStr">
@@ -9319,13 +9319,13 @@
       </c>
       <c r="N87" s="2" t="n"/>
       <c r="O87" s="31" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="P87" s="31" t="n">
-        <v>26</v>
+        <v>26.3</v>
       </c>
       <c r="Q87" s="31" t="n">
-        <v>14.19</v>
+        <v>14.74</v>
       </c>
       <c r="R87" s="50" t="n"/>
       <c r="S87" s="22" t="inlineStr">
@@ -9547,13 +9547,13 @@
       </c>
       <c r="N89" s="2" t="n"/>
       <c r="O89" s="31" t="n">
-        <v>1.4</v>
+        <v>2.8</v>
       </c>
       <c r="P89" s="31" t="n">
-        <v>21.8</v>
+        <v>21.7</v>
       </c>
       <c r="Q89" s="31" t="n">
-        <v>12.7</v>
+        <v>12.82</v>
       </c>
       <c r="R89" s="50" t="inlineStr">
         <is>
@@ -9969,13 +9969,13 @@
       </c>
       <c r="N93" s="2" t="n"/>
       <c r="O93" s="31" t="n">
-        <v>-2</v>
+        <v>-3.3</v>
       </c>
       <c r="P93" s="31" t="n">
-        <v>14.9</v>
+        <v>18.5</v>
       </c>
       <c r="Q93" s="31" t="n">
-        <v>6.2</v>
+        <v>7.69</v>
       </c>
       <c r="R93" s="50" t="n"/>
       <c r="S93" s="22" t="inlineStr">
@@ -10082,13 +10082,13 @@
       </c>
       <c r="N94" s="2" t="n"/>
       <c r="O94" s="31" t="n">
-        <v>8.9</v>
+        <v>6.7</v>
       </c>
       <c r="P94" s="31" t="n">
-        <v>23.3</v>
+        <v>26.3</v>
       </c>
       <c r="Q94" s="31" t="n">
-        <v>17</v>
+        <v>16.76</v>
       </c>
       <c r="R94" s="50" t="n"/>
       <c r="S94" s="22" t="inlineStr">
@@ -10318,13 +10318,13 @@
       </c>
       <c r="N96" s="2" t="n"/>
       <c r="O96" s="31" t="n">
-        <v>5.2</v>
+        <v>12.9</v>
       </c>
       <c r="P96" s="31" t="n">
-        <v>21.8</v>
+        <v>23.9</v>
       </c>
       <c r="Q96" s="31" t="n">
-        <v>14.18</v>
+        <v>18.51</v>
       </c>
       <c r="R96" s="50" t="n"/>
       <c r="S96" s="22" t="inlineStr">
@@ -10562,13 +10562,13 @@
       </c>
       <c r="N98" s="2" t="n"/>
       <c r="O98" s="31" t="n">
-        <v>8.5</v>
+        <v>12.9</v>
       </c>
       <c r="P98" s="31" t="n">
-        <v>21.8</v>
+        <v>22.6</v>
       </c>
       <c r="Q98" s="31" t="n">
-        <v>14.89</v>
+        <v>17.38</v>
       </c>
       <c r="R98" s="50" t="n"/>
       <c r="S98" s="22" t="inlineStr">
@@ -11123,13 +11123,13 @@
       </c>
       <c r="N103" s="2" t="n"/>
       <c r="O103" s="31" t="n">
-        <v>-0.3</v>
+        <v>5.9</v>
       </c>
       <c r="P103" s="31" t="n">
-        <v>18.9</v>
+        <v>19</v>
       </c>
       <c r="Q103" s="31" t="n">
-        <v>8.85</v>
+        <v>11.66</v>
       </c>
       <c r="R103" s="50" t="n"/>
       <c r="S103" s="22" t="inlineStr">
@@ -11342,15 +11342,9 @@
         </is>
       </c>
       <c r="N105" s="2" t="n"/>
-      <c r="O105" s="31" t="n">
-        <v>-2.6</v>
-      </c>
-      <c r="P105" s="31" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="Q105" s="31" t="n">
-        <v>7.72</v>
-      </c>
+      <c r="O105" s="31" t="n"/>
+      <c r="P105" s="31" t="n"/>
+      <c r="Q105" s="31" t="n"/>
       <c r="R105" s="50" t="n"/>
       <c r="S105" s="22" t="n"/>
       <c r="T105" s="36" t="inlineStr">
@@ -11468,13 +11462,13 @@
         </is>
       </c>
       <c r="O106" s="31" t="n">
-        <v>-4.5</v>
+        <v>-1.3</v>
       </c>
       <c r="P106" s="31" t="n">
-        <v>18.6</v>
+        <v>17.1</v>
       </c>
       <c r="Q106" s="31" t="n">
-        <v>6.7</v>
+        <v>8.31</v>
       </c>
       <c r="R106" s="50" t="n"/>
       <c r="S106" s="22" t="inlineStr">
@@ -12310,13 +12304,13 @@
       </c>
       <c r="N114" s="2" t="n"/>
       <c r="O114" s="31" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="P114" s="31" t="n">
-        <v>12.8</v>
+        <v>10.6</v>
       </c>
       <c r="Q114" s="31" t="n">
-        <v>7.6</v>
+        <v>6.24</v>
       </c>
       <c r="R114" s="50" t="n"/>
       <c r="S114" s="22" t="inlineStr">
@@ -12427,13 +12421,13 @@
         </is>
       </c>
       <c r="O115" s="31" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P115" s="31" t="n">
-        <v>10.7</v>
+        <v>7.7</v>
       </c>
       <c r="Q115" s="31" t="n">
-        <v>6.79</v>
+        <v>5.49</v>
       </c>
       <c r="R115" s="50" t="n"/>
       <c r="S115" s="22" t="inlineStr">
@@ -12552,13 +12546,13 @@
         </is>
       </c>
       <c r="O116" s="31" t="n">
-        <v>1.1</v>
+        <v>-0.7</v>
       </c>
       <c r="P116" s="31" t="n">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Q116" s="31" t="n">
-        <v>3.88</v>
+        <v>3.2</v>
       </c>
       <c r="R116" s="50" t="n"/>
       <c r="S116" s="22" t="inlineStr">
@@ -13117,13 +13111,13 @@
       </c>
       <c r="N121" s="2" t="n"/>
       <c r="O121" s="31" t="n">
-        <v>25.3</v>
+        <v>23.9</v>
       </c>
       <c r="P121" s="31" t="n">
-        <v>32.9</v>
+        <v>34.8</v>
       </c>
       <c r="Q121" s="31" t="n">
-        <v>28.85</v>
+        <v>29.29</v>
       </c>
       <c r="R121" s="50" t="n"/>
       <c r="S121" s="22" t="inlineStr">
@@ -13234,13 +13228,13 @@
       </c>
       <c r="N122" s="2" t="n"/>
       <c r="O122" s="31" t="n">
-        <v>21.3</v>
+        <v>17.3</v>
       </c>
       <c r="P122" s="31" t="n">
-        <v>25.9</v>
+        <v>27.5</v>
       </c>
       <c r="Q122" s="31" t="n">
-        <v>23.5</v>
+        <v>22.54</v>
       </c>
       <c r="R122" s="50" t="n"/>
       <c r="S122" s="22" t="inlineStr">
@@ -13359,13 +13353,13 @@
       </c>
       <c r="N123" s="2" t="n"/>
       <c r="O123" s="31" t="n">
-        <v>4.1</v>
+        <v>2.5</v>
       </c>
       <c r="P123" s="31" t="n">
-        <v>15.5</v>
+        <v>17.7</v>
       </c>
       <c r="Q123" s="31" t="n">
-        <v>8.75</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="R123" s="50" t="n"/>
       <c r="S123" s="22" t="inlineStr">
@@ -13583,13 +13577,13 @@
       </c>
       <c r="N125" s="2" t="n"/>
       <c r="O125" s="31" t="n">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="P125" s="31" t="n">
-        <v>20.8</v>
+        <v>22.3</v>
       </c>
       <c r="Q125" s="31" t="n">
-        <v>13.51</v>
+        <v>15.59</v>
       </c>
       <c r="R125" s="50" t="n"/>
       <c r="S125" s="22" t="inlineStr">
@@ -13708,13 +13702,13 @@
       </c>
       <c r="N126" s="2" t="n"/>
       <c r="O126" s="31" t="n">
-        <v>16</v>
+        <v>12.1</v>
       </c>
       <c r="P126" s="31" t="n">
-        <v>26.4</v>
+        <v>30.4</v>
       </c>
       <c r="Q126" s="31" t="n">
-        <v>20.15</v>
+        <v>21.02</v>
       </c>
       <c r="R126" s="50" t="n"/>
       <c r="S126" s="22" t="inlineStr">
@@ -13813,13 +13807,13 @@
       </c>
       <c r="N127" s="2" t="n"/>
       <c r="O127" s="31" t="n">
-        <v>16.2</v>
+        <v>12.3</v>
       </c>
       <c r="P127" s="31" t="n">
-        <v>24.2</v>
+        <v>29.3</v>
       </c>
       <c r="Q127" s="31" t="n">
-        <v>19.98</v>
+        <v>21.1</v>
       </c>
       <c r="R127" s="50" t="n"/>
       <c r="S127" s="22" t="inlineStr">
@@ -13926,10 +13920,10 @@
       </c>
       <c r="N128" s="2" t="n"/>
       <c r="O128" s="31" t="n">
-        <v>13.1</v>
+        <v>9.5</v>
       </c>
       <c r="P128" s="31" t="n">
-        <v>20.9</v>
+        <v>23.3</v>
       </c>
       <c r="Q128" s="31" t="n">
         <v>15.84</v>
@@ -14047,13 +14041,13 @@
       </c>
       <c r="N129" s="2" t="n"/>
       <c r="O129" s="31" t="n">
-        <v>16.3</v>
+        <v>14.2</v>
       </c>
       <c r="P129" s="31" t="n">
-        <v>23.5</v>
+        <v>29.1</v>
       </c>
       <c r="Q129" s="31" t="n">
-        <v>18.93</v>
+        <v>21.44</v>
       </c>
       <c r="R129" s="50" t="n"/>
       <c r="S129" s="22" t="inlineStr">
@@ -14160,13 +14154,13 @@
       </c>
       <c r="N130" s="2" t="n"/>
       <c r="O130" s="31" t="n">
-        <v>11.6</v>
+        <v>8.1</v>
       </c>
       <c r="P130" s="31" t="n">
-        <v>18</v>
+        <v>24.5</v>
       </c>
       <c r="Q130" s="31" t="n">
-        <v>13.77</v>
+        <v>15.31</v>
       </c>
       <c r="R130" s="50" t="n"/>
       <c r="S130" s="22" t="inlineStr">
@@ -14281,13 +14275,13 @@
       </c>
       <c r="N131" s="2" t="n"/>
       <c r="O131" s="31" t="n">
-        <v>8.300000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="P131" s="31" t="n">
-        <v>16</v>
+        <v>14.3</v>
       </c>
       <c r="Q131" s="31" t="n">
-        <v>10.85</v>
+        <v>10.62</v>
       </c>
       <c r="R131" s="50" t="n"/>
       <c r="S131" s="22" t="inlineStr">
@@ -14402,13 +14396,13 @@
       </c>
       <c r="N132" s="2" t="n"/>
       <c r="O132" s="31" t="n">
-        <v>16.2</v>
+        <v>14.8</v>
       </c>
       <c r="P132" s="31" t="n">
-        <v>23.5</v>
+        <v>26.6</v>
       </c>
       <c r="Q132" s="31" t="n">
-        <v>19.75</v>
+        <v>20.4</v>
       </c>
       <c r="R132" s="50" t="n"/>
       <c r="S132" s="22" t="inlineStr">
@@ -14519,13 +14513,13 @@
       </c>
       <c r="N133" s="2" t="n"/>
       <c r="O133" s="31" t="n">
-        <v>15</v>
+        <v>16.4</v>
       </c>
       <c r="P133" s="31" t="n">
-        <v>18.4</v>
+        <v>27</v>
       </c>
       <c r="Q133" s="31" t="n">
-        <v>16.89</v>
+        <v>20.66</v>
       </c>
       <c r="R133" s="50" t="n"/>
       <c r="S133" s="22" t="inlineStr">
@@ -14639,10 +14633,10 @@
         <v>13.8</v>
       </c>
       <c r="P134" s="31" t="n">
-        <v>20</v>
+        <v>19.8</v>
       </c>
       <c r="Q134" s="31" t="n">
-        <v>15.29</v>
+        <v>16.4</v>
       </c>
       <c r="R134" s="50" t="n"/>
       <c r="S134" s="22" t="inlineStr">
@@ -14860,13 +14854,13 @@
       </c>
       <c r="N136" s="2" t="n"/>
       <c r="O136" s="31" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="P136" s="31" t="n">
         <v>20.7</v>
       </c>
-      <c r="P136" s="31" t="n">
-        <v>30.4</v>
-      </c>
       <c r="Q136" s="31" t="n">
-        <v>25.3</v>
+        <v>19.12</v>
       </c>
       <c r="R136" s="50" t="n"/>
       <c r="S136" s="22" t="inlineStr">
@@ -14977,13 +14971,13 @@
       </c>
       <c r="N137" s="2" t="n"/>
       <c r="O137" s="31" t="n">
-        <v>24.5</v>
+        <v>22</v>
       </c>
       <c r="P137" s="31" t="n">
-        <v>30.5</v>
+        <v>28.4</v>
       </c>
       <c r="Q137" s="31" t="n">
-        <v>27.19</v>
+        <v>24.86</v>
       </c>
       <c r="R137" s="50" t="n"/>
       <c r="S137" s="22" t="inlineStr">
@@ -15094,13 +15088,13 @@
       </c>
       <c r="N138" s="2" t="n"/>
       <c r="O138" s="31" t="n">
-        <v>20.6</v>
+        <v>19.4</v>
       </c>
       <c r="P138" s="31" t="n">
-        <v>30.5</v>
+        <v>24.2</v>
       </c>
       <c r="Q138" s="31" t="n">
-        <v>22.68</v>
+        <v>21.64</v>
       </c>
       <c r="R138" s="50" t="n"/>
       <c r="S138" s="22" t="inlineStr">
@@ -15211,13 +15205,13 @@
       </c>
       <c r="N139" s="2" t="n"/>
       <c r="O139" s="31" t="n">
-        <v>20.2</v>
+        <v>17.7</v>
       </c>
       <c r="P139" s="31" t="n">
-        <v>26.3</v>
+        <v>26.1</v>
       </c>
       <c r="Q139" s="31" t="n">
-        <v>22.77</v>
+        <v>21.11</v>
       </c>
       <c r="R139" s="50" t="n"/>
       <c r="S139" s="22" t="inlineStr">
@@ -15328,13 +15322,13 @@
       </c>
       <c r="N140" s="2" t="n"/>
       <c r="O140" s="31" t="n">
-        <v>21.2</v>
+        <v>18.7</v>
       </c>
       <c r="P140" s="31" t="n">
         <v>27.4</v>
       </c>
       <c r="Q140" s="31" t="n">
-        <v>24.2</v>
+        <v>22.61</v>
       </c>
       <c r="R140" s="50" t="n"/>
       <c r="S140" s="22" t="inlineStr">
@@ -15445,13 +15439,13 @@
       </c>
       <c r="N141" s="2" t="n"/>
       <c r="O141" s="31" t="n">
-        <v>23.1</v>
+        <v>20.6</v>
       </c>
       <c r="P141" s="31" t="n">
-        <v>28.7</v>
+        <v>28.6</v>
       </c>
       <c r="Q141" s="31" t="n">
-        <v>25.76</v>
+        <v>24.77</v>
       </c>
       <c r="R141" s="50" t="n"/>
       <c r="S141" s="22" t="inlineStr">
@@ -15665,13 +15659,13 @@
       </c>
       <c r="N143" s="2" t="n"/>
       <c r="O143" s="31" t="n">
-        <v>22.2</v>
+        <v>22.7</v>
       </c>
       <c r="P143" s="31" t="n">
-        <v>30.4</v>
+        <v>30.3</v>
       </c>
       <c r="Q143" s="31" t="n">
-        <v>26.32</v>
+        <v>26.2</v>
       </c>
       <c r="R143" s="50" t="n"/>
       <c r="S143" s="22" t="inlineStr">
@@ -15782,13 +15776,13 @@
       </c>
       <c r="N144" s="2" t="n"/>
       <c r="O144" s="31" t="n">
-        <v>24.3</v>
+        <v>22.6</v>
       </c>
       <c r="P144" s="31" t="n">
-        <v>33.3</v>
+        <v>31.7</v>
       </c>
       <c r="Q144" s="31" t="n">
-        <v>28.6</v>
+        <v>26.36</v>
       </c>
       <c r="R144" s="50" t="n"/>
       <c r="S144" s="22" t="inlineStr">
@@ -16101,13 +16095,13 @@
       </c>
       <c r="N147" s="2" t="n"/>
       <c r="O147" s="31" t="n">
-        <v>27</v>
+        <v>26.4</v>
       </c>
       <c r="P147" s="31" t="n">
-        <v>32</v>
+        <v>34.9</v>
       </c>
       <c r="Q147" s="31" t="n">
-        <v>29.38</v>
+        <v>29.61</v>
       </c>
       <c r="R147" s="50" t="n"/>
       <c r="S147" s="22" t="inlineStr">
@@ -16210,13 +16204,13 @@
       </c>
       <c r="N148" s="2" t="n"/>
       <c r="O148" s="31" t="n">
-        <v>25.4</v>
+        <v>25</v>
       </c>
       <c r="P148" s="31" t="n">
-        <v>34.6</v>
+        <v>31.2</v>
       </c>
       <c r="Q148" s="31" t="n">
-        <v>29.45</v>
+        <v>27.59</v>
       </c>
       <c r="R148" s="50" t="n"/>
       <c r="S148" s="22" t="inlineStr">
@@ -16327,13 +16321,13 @@
       </c>
       <c r="N149" s="2" t="n"/>
       <c r="O149" s="31" t="n">
-        <v>24.3</v>
+        <v>23.4</v>
       </c>
       <c r="P149" s="31" t="n">
-        <v>36.8</v>
+        <v>31.1</v>
       </c>
       <c r="Q149" s="31" t="n">
-        <v>29.36</v>
+        <v>26.38</v>
       </c>
       <c r="R149" s="50" t="n"/>
       <c r="S149" s="22" t="inlineStr">
@@ -16443,10 +16437,10 @@
         <v>18.5</v>
       </c>
       <c r="P150" s="31" t="n">
-        <v>27.5</v>
+        <v>22.9</v>
       </c>
       <c r="Q150" s="31" t="n">
-        <v>22.45</v>
+        <v>20.34</v>
       </c>
       <c r="R150" s="50" t="n"/>
       <c r="S150" s="22" t="inlineStr">
@@ -16557,13 +16551,13 @@
       </c>
       <c r="N151" s="2" t="n"/>
       <c r="O151" s="31" t="n">
-        <v>21</v>
+        <v>18.3</v>
       </c>
       <c r="P151" s="31" t="n">
-        <v>29.9</v>
+        <v>23.5</v>
       </c>
       <c r="Q151" s="31" t="n">
-        <v>24.32</v>
+        <v>20.59</v>
       </c>
       <c r="R151" s="50" t="n"/>
       <c r="S151" s="22" t="inlineStr">
@@ -16674,13 +16668,13 @@
       </c>
       <c r="N152" s="2" t="n"/>
       <c r="O152" s="31" t="n">
-        <v>31</v>
+        <v>22.3</v>
       </c>
       <c r="P152" s="31" t="n">
-        <v>37.5</v>
+        <v>34.5</v>
       </c>
       <c r="Q152" s="31" t="n">
-        <v>33.65</v>
+        <v>25.22</v>
       </c>
       <c r="R152" s="50" t="n"/>
       <c r="S152" s="22" t="inlineStr">
@@ -16882,13 +16876,13 @@
       </c>
       <c r="N154" s="2" t="n"/>
       <c r="O154" s="31" t="n">
-        <v>19.3</v>
+        <v>17.7</v>
       </c>
       <c r="P154" s="31" t="n">
-        <v>26.3</v>
+        <v>23</v>
       </c>
       <c r="Q154" s="31" t="n">
-        <v>21.96</v>
+        <v>19.85</v>
       </c>
       <c r="R154" s="50" t="n"/>
       <c r="S154" s="22" t="inlineStr">
@@ -17003,13 +16997,13 @@
       </c>
       <c r="N155" s="2" t="n"/>
       <c r="O155" s="31" t="n">
-        <v>10.5</v>
+        <v>11.6</v>
       </c>
       <c r="P155" s="31" t="n">
-        <v>21</v>
+        <v>19.9</v>
       </c>
       <c r="Q155" s="31" t="n">
-        <v>15.66</v>
+        <v>15.38</v>
       </c>
       <c r="R155" s="50" t="n"/>
       <c r="S155" s="22" t="inlineStr">
@@ -17306,13 +17300,13 @@
       </c>
       <c r="N158" s="2" t="n"/>
       <c r="O158" s="31" t="n">
-        <v>23.9</v>
+        <v>21.4</v>
       </c>
       <c r="P158" s="31" t="n">
-        <v>28.2</v>
+        <v>29.1</v>
       </c>
       <c r="Q158" s="31" t="n">
-        <v>25.9</v>
+        <v>24.71</v>
       </c>
       <c r="R158" s="50" t="n"/>
       <c r="S158" s="22" t="inlineStr">
@@ -17703,10 +17697,10 @@
         <v>11.9</v>
       </c>
       <c r="P162" s="31" t="n">
-        <v>16.5</v>
+        <v>20.2</v>
       </c>
       <c r="Q162" s="31" t="n">
-        <v>13.74</v>
+        <v>16.34</v>
       </c>
       <c r="R162" s="50" t="n"/>
       <c r="S162" s="22" t="inlineStr">
@@ -17821,10 +17815,10 @@
       </c>
       <c r="N163" s="2" t="n"/>
       <c r="O163" s="31" t="n">
+        <v>-72.7</v>
+      </c>
+      <c r="P163" s="31" t="n">
         <v>-64.3</v>
-      </c>
-      <c r="P163" s="31" t="n">
-        <v>-59.8</v>
       </c>
       <c r="Q163" s="31" t="n"/>
       <c r="R163" s="50" t="n"/>
@@ -17920,13 +17914,13 @@
       </c>
       <c r="N164" s="2" t="n"/>
       <c r="O164" s="31" t="n">
-        <v>11</v>
+        <v>7.3</v>
       </c>
       <c r="P164" s="31" t="n">
-        <v>13.3</v>
+        <v>15.8</v>
       </c>
       <c r="Q164" s="31" t="n">
-        <v>11.78</v>
+        <v>10.67</v>
       </c>
       <c r="R164" s="50" t="n"/>
       <c r="S164" s="22" t="inlineStr">
@@ -18027,7 +18021,7 @@
       </c>
       <c r="N165" s="2" t="n"/>
       <c r="O165" s="31" t="n">
-        <v>-33.3</v>
+        <v>-33.9</v>
       </c>
       <c r="P165" s="31" t="n"/>
       <c r="Q165" s="31" t="n"/>
@@ -18854,10 +18848,10 @@
       </c>
       <c r="N174" s="2" t="n"/>
       <c r="O174" s="31" t="n">
-        <v>6.7</v>
+        <v>3.6</v>
       </c>
       <c r="P174" s="31" t="n">
-        <v>11.5</v>
+        <v>6.8</v>
       </c>
       <c r="Q174" s="31" t="n"/>
       <c r="R174" s="50" t="n"/>
@@ -18965,10 +18959,10 @@
         </is>
       </c>
       <c r="O175" s="31" t="n">
-        <v>1.5</v>
+        <v>5.3</v>
       </c>
       <c r="P175" s="31" t="n">
-        <v>13.8</v>
+        <v>10.4</v>
       </c>
       <c r="Q175" s="31" t="n"/>
       <c r="R175" s="50" t="n"/>
@@ -19524,10 +19518,10 @@
       </c>
       <c r="N180" s="2" t="n"/>
       <c r="O180" s="31" t="n">
-        <v>-1.4</v>
+        <v>2.4</v>
       </c>
       <c r="P180" s="31" t="n">
-        <v>18.7</v>
+        <v>19.4</v>
       </c>
       <c r="Q180" s="31" t="n"/>
       <c r="R180" s="50" t="n"/>
@@ -20125,8 +20119,12 @@
         </is>
       </c>
       <c r="N186" s="3" t="n"/>
-      <c r="O186" s="31" t="n"/>
-      <c r="P186" s="31" t="n"/>
+      <c r="O186" s="31" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="P186" s="31" t="n">
+        <v>19.1</v>
+      </c>
       <c r="Q186" s="31" t="n"/>
       <c r="R186" s="50" t="n"/>
       <c r="S186" s="22" t="inlineStr">
@@ -20633,13 +20631,13 @@
       </c>
       <c r="N191" s="2" t="n"/>
       <c r="O191" s="31" t="n">
-        <v>-3.6</v>
+        <v>-2.5</v>
       </c>
       <c r="P191" s="31" t="n">
-        <v>16.4</v>
+        <v>17.7</v>
       </c>
       <c r="Q191" s="31" t="n">
-        <v>5.96</v>
+        <v>7.51</v>
       </c>
       <c r="R191" s="50" t="inlineStr">
         <is>
@@ -20940,10 +20938,10 @@
         </is>
       </c>
       <c r="O194" s="31" t="n">
-        <v>-4.8</v>
+        <v>-2.7</v>
       </c>
       <c r="P194" s="31" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="Q194" s="31" t="n"/>
       <c r="R194" s="50" t="n"/>
@@ -22903,13 +22901,13 @@
         </is>
       </c>
       <c r="O213" s="31" t="n">
-        <v>-6.4</v>
+        <v>-5.7</v>
       </c>
       <c r="P213" s="31" t="n">
-        <v>3.6</v>
+        <v>6.6</v>
       </c>
       <c r="Q213" s="31" t="n">
-        <v>-2.7</v>
+        <v>-1.2</v>
       </c>
       <c r="R213" s="50" t="n"/>
       <c r="S213" s="22" t="inlineStr">
@@ -23633,8 +23631,12 @@
         </is>
       </c>
       <c r="N220" s="2" t="n"/>
-      <c r="O220" s="31" t="n"/>
-      <c r="P220" s="31" t="n"/>
+      <c r="O220" s="31" t="n">
+        <v>-3</v>
+      </c>
+      <c r="P220" s="31" t="n">
+        <v>18.5</v>
+      </c>
       <c r="Q220" s="31" t="n"/>
       <c r="R220" s="50" t="n"/>
       <c r="S220" s="22" t="inlineStr">
@@ -23942,12 +23944,8 @@
         </is>
       </c>
       <c r="N223" s="2" t="n"/>
-      <c r="O223" s="31" t="n">
-        <v>-6.6</v>
-      </c>
-      <c r="P223" s="31" t="n">
-        <v>20.8</v>
-      </c>
+      <c r="O223" s="31" t="n"/>
+      <c r="P223" s="31" t="n"/>
       <c r="Q223" s="31" t="n"/>
       <c r="R223" s="50" t="n"/>
       <c r="S223" s="22" t="inlineStr">
@@ -27566,12 +27564,14 @@
       </c>
       <c r="N260" s="2" t="n"/>
       <c r="O260" s="31" t="n">
-        <v>-6</v>
+        <v>-4.9</v>
       </c>
       <c r="P260" s="31" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q260" s="31" t="n"/>
+        <v>3.1</v>
+      </c>
+      <c r="Q260" s="31" t="n">
+        <v>-2.3</v>
+      </c>
       <c r="R260" s="50" t="n"/>
       <c r="S260" s="22" t="inlineStr">
         <is>
@@ -27878,8 +27878,12 @@
         </is>
       </c>
       <c r="N263" s="2" t="n"/>
-      <c r="O263" s="31" t="n"/>
-      <c r="P263" s="31" t="n"/>
+      <c r="O263" s="31" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="P263" s="31" t="n">
+        <v>21.5</v>
+      </c>
       <c r="Q263" s="31" t="n"/>
       <c r="R263" s="50" t="n"/>
       <c r="S263" s="22" t="inlineStr">
@@ -28386,10 +28390,10 @@
       </c>
       <c r="N268" s="2" t="n"/>
       <c r="O268" s="31" t="n">
-        <v>-1.9</v>
+        <v>-2.2</v>
       </c>
       <c r="P268" s="31" t="n">
-        <v>1.4</v>
+        <v>3.4</v>
       </c>
       <c r="Q268" s="31" t="n"/>
       <c r="R268" s="50" t="n"/>
@@ -28497,14 +28501,12 @@
         </is>
       </c>
       <c r="O269" s="31" t="n">
-        <v>-7.5</v>
+        <v>-1.2</v>
       </c>
       <c r="P269" s="31" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="Q269" s="31" t="n">
-        <v>-2.25</v>
-      </c>
+        <v>6.4</v>
+      </c>
+      <c r="Q269" s="31" t="n"/>
       <c r="R269" s="50" t="n"/>
       <c r="S269" s="22" t="inlineStr">
         <is>

--- a/气象/For_Python_站点信息和记录.xlsx
+++ b/气象/For_Python_站点信息和记录.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\文档\GIT SYNC\default\气象\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10F3E5C3-32B8-4CAF-A81C-82E332DE1F87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7E328E4-8DB0-4513-95A9-E58B11158FF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,14 +18,14 @@
     <sheet name="极寒收集" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">站点信息和记录!$A$1:$AI$404</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">站点信息和记录!$A$1:$AI$405</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4680" uniqueCount="1163">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4691" uniqueCount="1167">
   <si>
     <t>id</t>
   </si>
@@ -3518,6 +3518,22 @@
   </si>
   <si>
     <t>特尼河试验站</t>
+  </si>
+  <si>
+    <t>24462</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sebyan-kyuel</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ogimet</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sebyan-Kyuel</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -4244,7 +4260,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AI404"/>
+  <dimension ref="A1:AI405"/>
   <sheetFormatPr defaultColWidth="12.59765625" defaultRowHeight="20.25" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="4.59765625" style="5" customWidth="1"/>
@@ -10772,7 +10788,9 @@
       <c r="N90" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="O90" s="31"/>
+      <c r="O90" s="31">
+        <v>-6.3</v>
+      </c>
       <c r="P90" s="31"/>
       <c r="Q90" s="31"/>
       <c r="R90" s="50"/>
@@ -21709,7 +21727,9 @@
         <v>828</v>
       </c>
       <c r="N231" s="2"/>
-      <c r="O231" s="31"/>
+      <c r="O231" s="31">
+        <v>-8.9</v>
+      </c>
       <c r="P231" s="31"/>
       <c r="Q231" s="31"/>
       <c r="R231" s="50"/>
@@ -21922,7 +21942,9 @@
         <v>837</v>
       </c>
       <c r="N234" s="2"/>
-      <c r="O234" s="31"/>
+      <c r="O234" s="31">
+        <v>-9.5</v>
+      </c>
       <c r="P234" s="31"/>
       <c r="Q234" s="31"/>
       <c r="R234" s="50"/>
@@ -21993,7 +22015,9 @@
         <v>840</v>
       </c>
       <c r="N235" s="2"/>
-      <c r="O235" s="31"/>
+      <c r="O235" s="31">
+        <v>-10.9</v>
+      </c>
       <c r="P235" s="31"/>
       <c r="Q235" s="31"/>
       <c r="R235" s="50"/>
@@ -22137,7 +22161,9 @@
         <v>845</v>
       </c>
       <c r="N237" s="2"/>
-      <c r="O237" s="31"/>
+      <c r="O237" s="31">
+        <v>-9.6</v>
+      </c>
       <c r="P237" s="31"/>
       <c r="Q237" s="31"/>
       <c r="R237" s="50"/>
@@ -22425,7 +22451,9 @@
         <v>856</v>
       </c>
       <c r="N241" s="2"/>
-      <c r="O241" s="31"/>
+      <c r="O241" s="31">
+        <v>-9</v>
+      </c>
       <c r="P241" s="31"/>
       <c r="Q241" s="31"/>
       <c r="R241" s="50"/>
@@ -22608,26 +22636,26 @@
         <v>243</v>
       </c>
       <c r="B244" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="C244" s="45">
-        <v>24668</v>
+        <v>1165</v>
+      </c>
+      <c r="C244" s="45" t="s">
+        <v>1163</v>
       </c>
       <c r="D244" s="2" t="s">
-        <v>863</v>
+        <v>1164</v>
       </c>
       <c r="E244" s="4">
         <v>99999</v>
       </c>
       <c r="F244" s="38"/>
       <c r="G244" s="28">
-        <v>63.316666599999998</v>
+        <v>65.3</v>
       </c>
       <c r="H244" s="28">
-        <v>132.01666660000001</v>
+        <v>130</v>
       </c>
       <c r="I244" s="2">
-        <v>90.92</v>
+        <v>777.2</v>
       </c>
       <c r="J244" s="26">
         <v>12</v>
@@ -22635,19 +22663,21 @@
       <c r="K244" s="30" t="s">
         <v>216</v>
       </c>
-      <c r="L244" s="3"/>
+      <c r="L244" s="2"/>
       <c r="M244" s="16" t="s">
-        <v>864</v>
+        <v>1166</v>
       </c>
       <c r="N244" s="2"/>
-      <c r="O244" s="31"/>
-      <c r="P244" s="31"/>
-      <c r="Q244" s="31"/>
+      <c r="O244" s="32">
+        <v>-11.2</v>
+      </c>
+      <c r="P244" s="32"/>
+      <c r="Q244" s="32"/>
       <c r="R244" s="50"/>
       <c r="S244" s="22"/>
       <c r="T244" s="36"/>
       <c r="U244" s="40" t="s">
-        <v>865</v>
+        <v>822</v>
       </c>
       <c r="V244" s="2" t="s">
         <v>822</v>
@@ -22663,9 +22693,7 @@
       <c r="AA244" s="2"/>
       <c r="AB244" s="2"/>
       <c r="AC244" s="2"/>
-      <c r="AD244" s="2" t="s">
-        <v>866</v>
-      </c>
+      <c r="AD244" s="2"/>
       <c r="AE244" s="2" t="s">
         <v>220</v>
       </c>
@@ -22673,9 +22701,7 @@
         <v>796</v>
       </c>
       <c r="AG244" s="4"/>
-      <c r="AH244" s="2" t="s">
-        <v>865</v>
-      </c>
+      <c r="AH244" s="2"/>
       <c r="AI244" s="2"/>
     </row>
     <row r="245" spans="1:35" ht="24" customHeight="1" x14ac:dyDescent="0.4">
@@ -22685,34 +22711,34 @@
       <c r="B245" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="C245" s="45" t="s">
-        <v>867</v>
+      <c r="C245" s="45">
+        <v>24668</v>
       </c>
       <c r="D245" s="2" t="s">
-        <v>868</v>
+        <v>863</v>
       </c>
       <c r="E245" s="4">
         <v>99999</v>
       </c>
       <c r="F245" s="38"/>
       <c r="G245" s="28">
-        <v>63.95</v>
+        <v>63.316666599999998</v>
       </c>
       <c r="H245" s="28">
-        <v>135.87</v>
+        <v>132.01666660000001</v>
       </c>
       <c r="I245" s="2">
-        <v>399</v>
+        <v>90.92</v>
       </c>
       <c r="J245" s="26">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="K245" s="30" t="s">
         <v>216</v>
       </c>
-      <c r="L245" s="2"/>
+      <c r="L245" s="3"/>
       <c r="M245" s="16" t="s">
-        <v>869</v>
+        <v>864</v>
       </c>
       <c r="N245" s="2"/>
       <c r="O245" s="31"/>
@@ -22722,7 +22748,7 @@
       <c r="S245" s="22"/>
       <c r="T245" s="36"/>
       <c r="U245" s="40" t="s">
-        <v>870</v>
+        <v>865</v>
       </c>
       <c r="V245" s="2" t="s">
         <v>822</v>
@@ -22738,7 +22764,9 @@
       <c r="AA245" s="2"/>
       <c r="AB245" s="2"/>
       <c r="AC245" s="2"/>
-      <c r="AD245" s="2"/>
+      <c r="AD245" s="2" t="s">
+        <v>866</v>
+      </c>
       <c r="AE245" s="2" t="s">
         <v>220</v>
       </c>
@@ -22746,7 +22774,9 @@
         <v>796</v>
       </c>
       <c r="AG245" s="4"/>
-      <c r="AH245" s="2"/>
+      <c r="AH245" s="2" t="s">
+        <v>865</v>
+      </c>
       <c r="AI245" s="2"/>
     </row>
     <row r="246" spans="1:35" ht="24" customHeight="1" x14ac:dyDescent="0.4">
@@ -22756,24 +22786,24 @@
       <c r="B246" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="C246" s="45">
-        <v>24684</v>
+      <c r="C246" s="45" t="s">
+        <v>867</v>
       </c>
       <c r="D246" s="2" t="s">
-        <v>871</v>
+        <v>868</v>
       </c>
       <c r="E246" s="4">
         <v>99999</v>
       </c>
       <c r="F246" s="38"/>
       <c r="G246" s="28">
-        <v>63.3333333</v>
+        <v>63.95</v>
       </c>
       <c r="H246" s="28">
-        <v>141.7333333</v>
+        <v>135.87</v>
       </c>
       <c r="I246" s="2">
-        <v>776.93</v>
+        <v>399</v>
       </c>
       <c r="J246" s="26">
         <v>15</v>
@@ -22781,9 +22811,9 @@
       <c r="K246" s="30" t="s">
         <v>216</v>
       </c>
-      <c r="L246" s="3"/>
+      <c r="L246" s="2"/>
       <c r="M246" s="16" t="s">
-        <v>872</v>
+        <v>869</v>
       </c>
       <c r="N246" s="2"/>
       <c r="O246" s="31"/>
@@ -22793,7 +22823,7 @@
       <c r="S246" s="22"/>
       <c r="T246" s="36"/>
       <c r="U246" s="40" t="s">
-        <v>843</v>
+        <v>870</v>
       </c>
       <c r="V246" s="2" t="s">
         <v>822</v>
@@ -22828,23 +22858,23 @@
         <v>35</v>
       </c>
       <c r="C247" s="45">
-        <v>24688</v>
+        <v>24684</v>
       </c>
       <c r="D247" s="2" t="s">
-        <v>873</v>
+        <v>871</v>
       </c>
       <c r="E247" s="4">
         <v>99999</v>
       </c>
       <c r="F247" s="38"/>
       <c r="G247" s="28">
-        <v>63.251199999999997</v>
+        <v>63.3333333</v>
       </c>
       <c r="H247" s="28">
-        <v>143.18559999999999</v>
+        <v>141.7333333</v>
       </c>
       <c r="I247" s="2">
-        <v>740</v>
+        <v>776.93</v>
       </c>
       <c r="J247" s="26">
         <v>15</v>
@@ -22854,7 +22884,7 @@
       </c>
       <c r="L247" s="3"/>
       <c r="M247" s="16" t="s">
-        <v>874</v>
+        <v>872</v>
       </c>
       <c r="N247" s="2"/>
       <c r="O247" s="31"/>
@@ -22864,7 +22894,7 @@
       <c r="S247" s="22"/>
       <c r="T247" s="36"/>
       <c r="U247" s="40" t="s">
-        <v>875</v>
+        <v>843</v>
       </c>
       <c r="V247" s="2" t="s">
         <v>822</v>
@@ -22888,12 +22918,8 @@
         <v>796</v>
       </c>
       <c r="AG247" s="4"/>
-      <c r="AH247" s="2" t="s">
-        <v>843</v>
-      </c>
-      <c r="AI247" s="6" t="s">
-        <v>876</v>
-      </c>
+      <c r="AH247" s="2"/>
+      <c r="AI247" s="2"/>
     </row>
     <row r="248" spans="1:35" ht="24" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A248" s="2">
@@ -22903,23 +22929,23 @@
         <v>35</v>
       </c>
       <c r="C248" s="45">
-        <v>24691</v>
+        <v>24688</v>
       </c>
       <c r="D248" s="2" t="s">
-        <v>877</v>
+        <v>873</v>
       </c>
       <c r="E248" s="4">
         <v>99999</v>
       </c>
       <c r="F248" s="38"/>
       <c r="G248" s="28">
-        <v>63.8333333</v>
+        <v>63.251199999999997</v>
       </c>
       <c r="H248" s="28">
-        <v>145.6</v>
+        <v>143.18559999999999</v>
       </c>
       <c r="I248" s="2">
-        <v>800.92</v>
+        <v>740</v>
       </c>
       <c r="J248" s="26">
         <v>15</v>
@@ -22929,7 +22955,7 @@
       </c>
       <c r="L248" s="3"/>
       <c r="M248" s="16" t="s">
-        <v>877</v>
+        <v>874</v>
       </c>
       <c r="N248" s="2"/>
       <c r="O248" s="31"/>
@@ -22939,7 +22965,7 @@
       <c r="S248" s="22"/>
       <c r="T248" s="36"/>
       <c r="U248" s="40" t="s">
-        <v>822</v>
+        <v>875</v>
       </c>
       <c r="V248" s="2" t="s">
         <v>822</v>
@@ -22964,9 +22990,11 @@
       </c>
       <c r="AG248" s="4"/>
       <c r="AH248" s="2" t="s">
-        <v>855</v>
-      </c>
-      <c r="AI248" s="2"/>
+        <v>843</v>
+      </c>
+      <c r="AI248" s="6" t="s">
+        <v>876</v>
+      </c>
     </row>
     <row r="249" spans="1:35" ht="24" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A249" s="2">
@@ -22976,33 +23004,33 @@
         <v>35</v>
       </c>
       <c r="C249" s="45">
-        <v>24856</v>
+        <v>24691</v>
       </c>
       <c r="D249" s="2" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="E249" s="4">
         <v>99999</v>
       </c>
       <c r="F249" s="38"/>
       <c r="G249" s="28">
-        <v>61.495399999999997</v>
+        <v>63.8333333</v>
       </c>
       <c r="H249" s="28">
-        <v>129.16669999999999</v>
+        <v>145.6</v>
       </c>
       <c r="I249" s="2">
-        <v>115</v>
+        <v>800.92</v>
       </c>
       <c r="J249" s="26">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="K249" s="30" t="s">
         <v>216</v>
       </c>
       <c r="L249" s="3"/>
       <c r="M249" s="16" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="N249" s="2"/>
       <c r="O249" s="31"/>
@@ -23012,7 +23040,7 @@
       <c r="S249" s="22"/>
       <c r="T249" s="36"/>
       <c r="U249" s="40" t="s">
-        <v>879</v>
+        <v>822</v>
       </c>
       <c r="V249" s="2" t="s">
         <v>822</v>
@@ -23028,9 +23056,7 @@
       <c r="AA249" s="2"/>
       <c r="AB249" s="2"/>
       <c r="AC249" s="2"/>
-      <c r="AD249" s="2" t="s">
-        <v>880</v>
-      </c>
+      <c r="AD249" s="2"/>
       <c r="AE249" s="2" t="s">
         <v>220</v>
       </c>
@@ -23039,7 +23065,7 @@
       </c>
       <c r="AG249" s="4"/>
       <c r="AH249" s="2" t="s">
-        <v>879</v>
+        <v>855</v>
       </c>
       <c r="AI249" s="2"/>
     </row>
@@ -23051,23 +23077,23 @@
         <v>35</v>
       </c>
       <c r="C250" s="45">
-        <v>24959</v>
+        <v>24856</v>
       </c>
       <c r="D250" s="2" t="s">
-        <v>881</v>
+        <v>878</v>
       </c>
       <c r="E250" s="4">
         <v>99999</v>
       </c>
       <c r="F250" s="38"/>
       <c r="G250" s="28">
-        <v>62.016666600000001</v>
+        <v>61.495399999999997</v>
       </c>
       <c r="H250" s="28">
-        <v>129.7166666</v>
+        <v>129.16669999999999</v>
       </c>
       <c r="I250" s="2">
-        <v>101</v>
+        <v>115</v>
       </c>
       <c r="J250" s="26">
         <v>12</v>
@@ -23077,7 +23103,7 @@
       </c>
       <c r="L250" s="3"/>
       <c r="M250" s="16" t="s">
-        <v>882</v>
+        <v>878</v>
       </c>
       <c r="N250" s="2"/>
       <c r="O250" s="31"/>
@@ -23099,13 +23125,13 @@
       <c r="Y250" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="Z250" s="4" t="s">
-        <v>39</v>
-      </c>
+      <c r="Z250" s="4"/>
       <c r="AA250" s="2"/>
       <c r="AB250" s="2"/>
       <c r="AC250" s="2"/>
-      <c r="AD250" s="2"/>
+      <c r="AD250" s="2" t="s">
+        <v>880</v>
+      </c>
       <c r="AE250" s="2" t="s">
         <v>220</v>
       </c>
@@ -23126,23 +23152,23 @@
         <v>35</v>
       </c>
       <c r="C251" s="45">
-        <v>31005</v>
+        <v>24959</v>
       </c>
       <c r="D251" s="2" t="s">
-        <v>883</v>
+        <v>881</v>
       </c>
       <c r="E251" s="4">
         <v>99999</v>
       </c>
       <c r="F251" s="38"/>
       <c r="G251" s="28">
-        <v>58.966999999999999</v>
+        <v>62.016666600000001</v>
       </c>
       <c r="H251" s="28">
-        <v>126.267</v>
+        <v>129.7166666</v>
       </c>
       <c r="I251" s="2">
-        <v>283.5</v>
+        <v>101</v>
       </c>
       <c r="J251" s="26">
         <v>12</v>
@@ -23152,7 +23178,7 @@
       </c>
       <c r="L251" s="3"/>
       <c r="M251" s="16" t="s">
-        <v>884</v>
+        <v>882</v>
       </c>
       <c r="N251" s="2"/>
       <c r="O251" s="31"/>
@@ -23162,7 +23188,7 @@
       <c r="S251" s="22"/>
       <c r="T251" s="36"/>
       <c r="U251" s="40" t="s">
-        <v>865</v>
+        <v>879</v>
       </c>
       <c r="V251" s="2" t="s">
         <v>822</v>
@@ -23174,7 +23200,9 @@
       <c r="Y251" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="Z251" s="4"/>
+      <c r="Z251" s="4" t="s">
+        <v>39</v>
+      </c>
       <c r="AA251" s="2"/>
       <c r="AB251" s="2"/>
       <c r="AC251" s="2"/>
@@ -23186,7 +23214,9 @@
         <v>796</v>
       </c>
       <c r="AG251" s="4"/>
-      <c r="AH251" s="2"/>
+      <c r="AH251" s="2" t="s">
+        <v>879</v>
+      </c>
       <c r="AI251" s="2"/>
     </row>
     <row r="252" spans="1:35" ht="24" customHeight="1" x14ac:dyDescent="0.4">
@@ -23197,23 +23227,23 @@
         <v>35</v>
       </c>
       <c r="C252" s="45">
-        <v>31137</v>
+        <v>31005</v>
       </c>
       <c r="D252" s="2" t="s">
-        <v>885</v>
+        <v>883</v>
       </c>
       <c r="E252" s="4">
         <v>99999</v>
       </c>
       <c r="F252" s="38"/>
       <c r="G252" s="28">
-        <v>56.283333300000002</v>
+        <v>58.966999999999999</v>
       </c>
       <c r="H252" s="28">
-        <v>131.1333333</v>
+        <v>126.267</v>
       </c>
       <c r="I252" s="2">
-        <v>850</v>
+        <v>283.5</v>
       </c>
       <c r="J252" s="26">
         <v>12</v>
@@ -23222,8 +23252,8 @@
         <v>216</v>
       </c>
       <c r="L252" s="3"/>
-      <c r="M252" s="12" t="s">
-        <v>885</v>
+      <c r="M252" s="16" t="s">
+        <v>884</v>
       </c>
       <c r="N252" s="2"/>
       <c r="O252" s="31"/>
@@ -23233,7 +23263,7 @@
       <c r="S252" s="22"/>
       <c r="T252" s="36"/>
       <c r="U252" s="40" t="s">
-        <v>886</v>
+        <v>865</v>
       </c>
       <c r="V252" s="2" t="s">
         <v>822</v>
@@ -23257,34 +23287,34 @@
         <v>796</v>
       </c>
       <c r="AG252" s="4"/>
-      <c r="AH252" s="2" t="s">
-        <v>887</v>
-      </c>
-      <c r="AI252" s="6" t="s">
-        <v>888</v>
-      </c>
+      <c r="AH252" s="2"/>
+      <c r="AI252" s="2"/>
     </row>
     <row r="253" spans="1:35" ht="24" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A253" s="2">
         <v>252</v>
       </c>
-      <c r="B253" s="2"/>
-      <c r="C253" s="45" t="s">
-        <v>889</v>
-      </c>
-      <c r="D253" s="2"/>
+      <c r="B253" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C253" s="45">
+        <v>31137</v>
+      </c>
+      <c r="D253" s="2" t="s">
+        <v>885</v>
+      </c>
       <c r="E253" s="4">
         <v>99999</v>
       </c>
       <c r="F253" s="38"/>
       <c r="G253" s="28">
-        <v>55.87</v>
+        <v>56.283333300000002</v>
       </c>
       <c r="H253" s="28">
-        <v>117.37</v>
+        <v>131.1333333</v>
       </c>
       <c r="I253" s="2">
-        <v>748</v>
+        <v>850</v>
       </c>
       <c r="J253" s="26">
         <v>12</v>
@@ -23292,9 +23322,9 @@
       <c r="K253" s="30" t="s">
         <v>216</v>
       </c>
-      <c r="L253" s="2"/>
-      <c r="M253" s="16" t="s">
-        <v>890</v>
+      <c r="L253" s="3"/>
+      <c r="M253" s="12" t="s">
+        <v>885</v>
       </c>
       <c r="N253" s="2"/>
       <c r="O253" s="31"/>
@@ -23304,10 +23334,10 @@
       <c r="S253" s="22"/>
       <c r="T253" s="36"/>
       <c r="U253" s="40" t="s">
-        <v>891</v>
+        <v>886</v>
       </c>
       <c r="V253" s="2" t="s">
-        <v>242</v>
+        <v>822</v>
       </c>
       <c r="W253" s="4" t="s">
         <v>39</v>
@@ -23328,9 +23358,11 @@
         <v>796</v>
       </c>
       <c r="AG253" s="4"/>
-      <c r="AH253" s="2"/>
-      <c r="AI253" s="2" t="s">
-        <v>736</v>
+      <c r="AH253" s="2" t="s">
+        <v>887</v>
+      </c>
+      <c r="AI253" s="6" t="s">
+        <v>888</v>
       </c>
     </row>
     <row r="254" spans="1:35" ht="24" customHeight="1" x14ac:dyDescent="0.4">
@@ -23339,7 +23371,7 @@
       </c>
       <c r="B254" s="2"/>
       <c r="C254" s="45" t="s">
-        <v>892</v>
+        <v>889</v>
       </c>
       <c r="D254" s="2"/>
       <c r="E254" s="4">
@@ -23347,13 +23379,13 @@
       </c>
       <c r="F254" s="38"/>
       <c r="G254" s="28">
-        <v>55.9</v>
+        <v>55.87</v>
       </c>
       <c r="H254" s="28">
-        <v>119.6</v>
+        <v>117.37</v>
       </c>
       <c r="I254" s="2">
-        <v>1080</v>
+        <v>748</v>
       </c>
       <c r="J254" s="26">
         <v>12</v>
@@ -23363,7 +23395,7 @@
       </c>
       <c r="L254" s="2"/>
       <c r="M254" s="16" t="s">
-        <v>893</v>
+        <v>890</v>
       </c>
       <c r="N254" s="2"/>
       <c r="O254" s="31"/>
@@ -23373,7 +23405,7 @@
       <c r="S254" s="22"/>
       <c r="T254" s="36"/>
       <c r="U254" s="40" t="s">
-        <v>242</v>
+        <v>891</v>
       </c>
       <c r="V254" s="2" t="s">
         <v>242</v>
@@ -23406,27 +23438,23 @@
       <c r="A255" s="2">
         <v>254</v>
       </c>
-      <c r="B255" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="C255" s="45">
-        <v>30337</v>
-      </c>
-      <c r="D255" s="2" t="s">
-        <v>894</v>
-      </c>
+      <c r="B255" s="2"/>
+      <c r="C255" s="45" t="s">
+        <v>892</v>
+      </c>
+      <c r="D255" s="2"/>
       <c r="E255" s="4">
         <v>99999</v>
       </c>
       <c r="F255" s="38"/>
       <c r="G255" s="28">
-        <v>56.316666599999998</v>
+        <v>55.9</v>
       </c>
       <c r="H255" s="28">
-        <v>107.6166666</v>
+        <v>119.6</v>
       </c>
       <c r="I255" s="2">
-        <v>362</v>
+        <v>1080</v>
       </c>
       <c r="J255" s="26">
         <v>12</v>
@@ -23434,9 +23462,9 @@
       <c r="K255" s="30" t="s">
         <v>216</v>
       </c>
-      <c r="L255" s="3"/>
+      <c r="L255" s="2"/>
       <c r="M255" s="16" t="s">
-        <v>895</v>
+        <v>893</v>
       </c>
       <c r="N255" s="2"/>
       <c r="O255" s="31"/>
@@ -23446,10 +23474,10 @@
       <c r="S255" s="22"/>
       <c r="T255" s="36"/>
       <c r="U255" s="40" t="s">
-        <v>758</v>
+        <v>242</v>
       </c>
       <c r="V255" s="2" t="s">
-        <v>261</v>
+        <v>242</v>
       </c>
       <c r="W255" s="4" t="s">
         <v>39</v>
@@ -23470,10 +23498,10 @@
         <v>796</v>
       </c>
       <c r="AG255" s="4"/>
-      <c r="AH255" s="2" t="s">
-        <v>758</v>
-      </c>
-      <c r="AI255" s="2"/>
+      <c r="AH255" s="2"/>
+      <c r="AI255" s="2" t="s">
+        <v>736</v>
+      </c>
     </row>
     <row r="256" spans="1:35" ht="24" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A256" s="2">
@@ -23483,47 +23511,47 @@
         <v>35</v>
       </c>
       <c r="C256" s="45">
-        <v>89606</v>
+        <v>30337</v>
       </c>
       <c r="D256" s="2" t="s">
-        <v>896</v>
+        <v>894</v>
       </c>
       <c r="E256" s="4">
         <v>99999</v>
       </c>
       <c r="F256" s="38"/>
       <c r="G256" s="28">
-        <v>-78.464399999999998</v>
+        <v>56.316666599999998</v>
       </c>
       <c r="H256" s="28">
-        <v>106.8323</v>
+        <v>107.6166666</v>
       </c>
       <c r="I256" s="2">
-        <v>3488</v>
+        <v>362</v>
       </c>
       <c r="J256" s="26">
         <v>12</v>
       </c>
       <c r="K256" s="30" t="s">
-        <v>897</v>
-      </c>
-      <c r="L256" s="42"/>
+        <v>216</v>
+      </c>
+      <c r="L256" s="3"/>
       <c r="M256" s="16" t="s">
-        <v>898</v>
+        <v>895</v>
       </c>
       <c r="N256" s="2"/>
       <c r="O256" s="31"/>
       <c r="P256" s="31"/>
       <c r="Q256" s="31"/>
       <c r="R256" s="50"/>
-      <c r="S256" s="22" t="s">
-        <v>39</v>
-      </c>
+      <c r="S256" s="22"/>
       <c r="T256" s="36"/>
       <c r="U256" s="40" t="s">
-        <v>899</v>
-      </c>
-      <c r="V256" s="2"/>
+        <v>758</v>
+      </c>
+      <c r="V256" s="2" t="s">
+        <v>261</v>
+      </c>
       <c r="W256" s="4" t="s">
         <v>39</v>
       </c>
@@ -23544,7 +23572,7 @@
       </c>
       <c r="AG256" s="4"/>
       <c r="AH256" s="2" t="s">
-        <v>900</v>
+        <v>758</v>
       </c>
       <c r="AI256" s="2"/>
     </row>
@@ -23555,44 +23583,46 @@
       <c r="B257" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="C257" s="45" t="s">
-        <v>901</v>
+      <c r="C257" s="45">
+        <v>89606</v>
       </c>
       <c r="D257" s="2" t="s">
-        <v>902</v>
+        <v>896</v>
       </c>
       <c r="E257" s="4">
         <v>99999</v>
       </c>
       <c r="F257" s="38"/>
       <c r="G257" s="28">
-        <v>-75.099999999999994</v>
+        <v>-78.464399999999998</v>
       </c>
       <c r="H257" s="28">
-        <v>123.4</v>
-      </c>
-      <c r="I257" s="54">
-        <v>3233</v>
+        <v>106.8323</v>
+      </c>
+      <c r="I257" s="2">
+        <v>3488</v>
       </c>
       <c r="J257" s="26">
         <v>12</v>
       </c>
-      <c r="K257" s="53" t="s">
+      <c r="K257" s="30" t="s">
         <v>897</v>
       </c>
-      <c r="L257" s="2"/>
-      <c r="M257" s="17" t="s">
-        <v>902</v>
+      <c r="L257" s="42"/>
+      <c r="M257" s="16" t="s">
+        <v>898</v>
       </c>
       <c r="N257" s="2"/>
       <c r="O257" s="31"/>
       <c r="P257" s="31"/>
       <c r="Q257" s="31"/>
       <c r="R257" s="50"/>
-      <c r="S257" s="22"/>
+      <c r="S257" s="22" t="s">
+        <v>39</v>
+      </c>
       <c r="T257" s="36"/>
       <c r="U257" s="40" t="s">
-        <v>903</v>
+        <v>899</v>
       </c>
       <c r="V257" s="2"/>
       <c r="W257" s="4" t="s">
@@ -23608,14 +23638,14 @@
       <c r="AC257" s="2"/>
       <c r="AD257" s="2"/>
       <c r="AE257" s="2" t="s">
-        <v>904</v>
+        <v>220</v>
       </c>
       <c r="AF257" s="4" t="s">
-        <v>290</v>
+        <v>796</v>
       </c>
       <c r="AG257" s="4"/>
       <c r="AH257" s="2" t="s">
-        <v>905</v>
+        <v>900</v>
       </c>
       <c r="AI257" s="2"/>
     </row>
@@ -23626,34 +23656,34 @@
       <c r="B258" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="C258" s="45">
-        <v>35188</v>
+      <c r="C258" s="45" t="s">
+        <v>901</v>
       </c>
       <c r="D258" s="2" t="s">
-        <v>906</v>
+        <v>902</v>
       </c>
       <c r="E258" s="4">
         <v>99999</v>
       </c>
       <c r="F258" s="38"/>
       <c r="G258" s="28">
-        <v>51.022221999999999</v>
+        <v>-75.099999999999994</v>
       </c>
       <c r="H258" s="28">
-        <v>71.466943999999998</v>
-      </c>
-      <c r="I258" s="2">
-        <v>355.09</v>
+        <v>123.4</v>
+      </c>
+      <c r="I258" s="54">
+        <v>3233</v>
       </c>
       <c r="J258" s="26">
         <v>12</v>
       </c>
-      <c r="K258" s="30" t="s">
-        <v>286</v>
-      </c>
-      <c r="L258" s="3"/>
+      <c r="K258" s="53" t="s">
+        <v>897</v>
+      </c>
+      <c r="L258" s="2"/>
       <c r="M258" s="17" t="s">
-        <v>907</v>
+        <v>902</v>
       </c>
       <c r="N258" s="2"/>
       <c r="O258" s="31"/>
@@ -23663,37 +23693,31 @@
       <c r="S258" s="22"/>
       <c r="T258" s="36"/>
       <c r="U258" s="40" t="s">
-        <v>908</v>
-      </c>
-      <c r="V258" s="2" t="s">
-        <v>909</v>
-      </c>
+        <v>903</v>
+      </c>
+      <c r="V258" s="2"/>
       <c r="W258" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="X258" s="4" t="s">
-        <v>39</v>
-      </c>
+      <c r="X258" s="4"/>
       <c r="Y258" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="Z258" s="4" t="s">
-        <v>39</v>
-      </c>
+      <c r="Z258" s="4"/>
       <c r="AA258" s="2"/>
       <c r="AB258" s="2"/>
       <c r="AC258" s="2"/>
-      <c r="AD258" s="2" t="s">
-        <v>910</v>
-      </c>
+      <c r="AD258" s="2"/>
       <c r="AE258" s="2" t="s">
-        <v>289</v>
+        <v>904</v>
       </c>
       <c r="AF258" s="4" t="s">
         <v>290</v>
       </c>
       <c r="AG258" s="4"/>
-      <c r="AH258" s="2"/>
+      <c r="AH258" s="2" t="s">
+        <v>905</v>
+      </c>
       <c r="AI258" s="2"/>
     </row>
     <row r="259" spans="1:35" ht="24" customHeight="1" x14ac:dyDescent="0.4">
@@ -23701,40 +23725,38 @@
         <v>258</v>
       </c>
       <c r="B259" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C259" s="45" t="s">
-        <v>911</v>
+        <v>35</v>
+      </c>
+      <c r="C259" s="45">
+        <v>35188</v>
       </c>
       <c r="D259" s="2" t="s">
-        <v>912</v>
+        <v>906</v>
       </c>
       <c r="E259" s="4">
         <v>99999</v>
       </c>
       <c r="F259" s="38"/>
       <c r="G259" s="28">
-        <v>35.366999999999997</v>
+        <v>51.022221999999999</v>
       </c>
       <c r="H259" s="28">
-        <v>138.733</v>
+        <v>71.466943999999998</v>
       </c>
       <c r="I259" s="2">
-        <v>3777.5</v>
+        <v>355.09</v>
       </c>
       <c r="J259" s="26">
         <v>12</v>
       </c>
       <c r="K259" s="30" t="s">
-        <v>913</v>
-      </c>
-      <c r="L259" s="2"/>
+        <v>286</v>
+      </c>
+      <c r="L259" s="3"/>
       <c r="M259" s="17" t="s">
-        <v>914</v>
-      </c>
-      <c r="N259" s="23" t="s">
-        <v>101</v>
-      </c>
+        <v>907</v>
+      </c>
+      <c r="N259" s="2"/>
       <c r="O259" s="31"/>
       <c r="P259" s="31"/>
       <c r="Q259" s="31"/>
@@ -23742,10 +23764,10 @@
       <c r="S259" s="22"/>
       <c r="T259" s="36"/>
       <c r="U259" s="40" t="s">
-        <v>915</v>
+        <v>908</v>
       </c>
       <c r="V259" s="2" t="s">
-        <v>916</v>
+        <v>909</v>
       </c>
       <c r="W259" s="4" t="s">
         <v>39</v>
@@ -23756,13 +23778,17 @@
       <c r="Y259" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="Z259" s="4"/>
+      <c r="Z259" s="4" t="s">
+        <v>39</v>
+      </c>
       <c r="AA259" s="2"/>
       <c r="AB259" s="2"/>
       <c r="AC259" s="2"/>
-      <c r="AD259" s="2"/>
+      <c r="AD259" s="2" t="s">
+        <v>910</v>
+      </c>
       <c r="AE259" s="2" t="s">
-        <v>915</v>
+        <v>289</v>
       </c>
       <c r="AF259" s="4" t="s">
         <v>290</v>
@@ -23775,50 +23801,56 @@
       <c r="A260" s="2">
         <v>259</v>
       </c>
-      <c r="B260" s="2"/>
-      <c r="C260" s="45">
-        <v>45011</v>
+      <c r="B260" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C260" s="45" t="s">
+        <v>911</v>
       </c>
       <c r="D260" s="2" t="s">
-        <v>917</v>
+        <v>912</v>
       </c>
       <c r="E260" s="4">
         <v>99999</v>
       </c>
       <c r="F260" s="38"/>
       <c r="G260" s="28">
-        <v>22.149556</v>
+        <v>35.366999999999997</v>
       </c>
       <c r="H260" s="28">
-        <v>113.59155800000001</v>
+        <v>138.733</v>
       </c>
       <c r="I260" s="2">
-        <v>6.09</v>
+        <v>3777.5</v>
       </c>
       <c r="J260" s="26">
         <v>12</v>
       </c>
       <c r="K260" s="30" t="s">
-        <v>307</v>
-      </c>
-      <c r="L260" s="3"/>
-      <c r="M260" s="14" t="s">
-        <v>918</v>
-      </c>
-      <c r="N260" s="2"/>
+        <v>913</v>
+      </c>
+      <c r="L260" s="2"/>
+      <c r="M260" s="17" t="s">
+        <v>914</v>
+      </c>
+      <c r="N260" s="23" t="s">
+        <v>101</v>
+      </c>
       <c r="O260" s="31"/>
       <c r="P260" s="31"/>
       <c r="Q260" s="31"/>
-      <c r="R260" s="50" t="s">
-        <v>919</v>
-      </c>
+      <c r="R260" s="50"/>
       <c r="S260" s="22"/>
       <c r="T260" s="36"/>
-      <c r="U260" s="40"/>
+      <c r="U260" s="40" t="s">
+        <v>915</v>
+      </c>
       <c r="V260" s="2" t="s">
-        <v>918</v>
-      </c>
-      <c r="W260" s="4"/>
+        <v>916</v>
+      </c>
+      <c r="W260" s="4" t="s">
+        <v>39</v>
+      </c>
       <c r="X260" s="4" t="s">
         <v>39</v>
       </c>
@@ -23831,10 +23863,10 @@
       <c r="AC260" s="2"/>
       <c r="AD260" s="2"/>
       <c r="AE260" s="2" t="s">
-        <v>312</v>
+        <v>915</v>
       </c>
       <c r="AF260" s="4" t="s">
-        <v>313</v>
+        <v>290</v>
       </c>
       <c r="AG260" s="4"/>
       <c r="AH260" s="2"/>
@@ -23845,22 +23877,24 @@
         <v>260</v>
       </c>
       <c r="B261" s="2"/>
-      <c r="C261" s="45" t="s">
-        <v>920</v>
-      </c>
-      <c r="D261" s="2"/>
+      <c r="C261" s="45">
+        <v>45011</v>
+      </c>
+      <c r="D261" s="2" t="s">
+        <v>917</v>
+      </c>
       <c r="E261" s="4">
         <v>99999</v>
       </c>
       <c r="F261" s="38"/>
       <c r="G261" s="28">
-        <v>23.755600000000001</v>
+        <v>22.149556</v>
       </c>
       <c r="H261" s="28">
-        <v>106.9442</v>
+        <v>113.59155800000001</v>
       </c>
       <c r="I261" s="2">
-        <v>133</v>
+        <v>6.09</v>
       </c>
       <c r="J261" s="26">
         <v>12</v>
@@ -23868,28 +23902,24 @@
       <c r="K261" s="30" t="s">
         <v>307</v>
       </c>
-      <c r="L261" s="2"/>
+      <c r="L261" s="3"/>
       <c r="M261" s="14" t="s">
-        <v>921</v>
+        <v>918</v>
       </c>
       <c r="N261" s="2"/>
       <c r="O261" s="31"/>
       <c r="P261" s="31"/>
       <c r="Q261" s="31"/>
-      <c r="R261" s="50"/>
-      <c r="S261" s="22" t="s">
-        <v>39</v>
-      </c>
+      <c r="R261" s="50" t="s">
+        <v>919</v>
+      </c>
+      <c r="S261" s="22"/>
       <c r="T261" s="36"/>
-      <c r="U261" s="40" t="s">
-        <v>529</v>
-      </c>
+      <c r="U261" s="40"/>
       <c r="V261" s="2" t="s">
-        <v>529</v>
-      </c>
-      <c r="W261" s="4" t="s">
-        <v>39</v>
-      </c>
+        <v>918</v>
+      </c>
+      <c r="W261" s="4"/>
       <c r="X261" s="4" t="s">
         <v>39</v>
       </c>
@@ -23897,12 +23927,8 @@
         <v>39</v>
       </c>
       <c r="Z261" s="4"/>
-      <c r="AA261" s="2" t="s">
-        <v>922</v>
-      </c>
-      <c r="AB261" s="2" t="s">
-        <v>923</v>
-      </c>
+      <c r="AA261" s="2"/>
+      <c r="AB261" s="2"/>
       <c r="AC261" s="2"/>
       <c r="AD261" s="2"/>
       <c r="AE261" s="2" t="s">
@@ -23921,7 +23947,7 @@
       </c>
       <c r="B262" s="2"/>
       <c r="C262" s="45" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="D262" s="2"/>
       <c r="E262" s="4">
@@ -23929,13 +23955,13 @@
       </c>
       <c r="F262" s="38"/>
       <c r="G262" s="28">
-        <v>19.7364</v>
+        <v>23.755600000000001</v>
       </c>
       <c r="H262" s="28">
-        <v>110.0167</v>
+        <v>106.9442</v>
       </c>
       <c r="I262" s="2">
-        <v>31.4</v>
+        <v>133</v>
       </c>
       <c r="J262" s="26">
         <v>12</v>
@@ -23945,7 +23971,7 @@
       </c>
       <c r="L262" s="2"/>
       <c r="M262" s="14" t="s">
-        <v>925</v>
+        <v>921</v>
       </c>
       <c r="N262" s="2"/>
       <c r="O262" s="31"/>
@@ -23957,10 +23983,10 @@
       </c>
       <c r="T262" s="36"/>
       <c r="U262" s="40" t="s">
-        <v>517</v>
+        <v>529</v>
       </c>
       <c r="V262" s="2" t="s">
-        <v>517</v>
+        <v>529</v>
       </c>
       <c r="W262" s="4" t="s">
         <v>39</v>
@@ -23973,9 +23999,11 @@
       </c>
       <c r="Z262" s="4"/>
       <c r="AA262" s="2" t="s">
-        <v>926</v>
-      </c>
-      <c r="AB262" s="2"/>
+        <v>922</v>
+      </c>
+      <c r="AB262" s="2" t="s">
+        <v>923</v>
+      </c>
       <c r="AC262" s="2"/>
       <c r="AD262" s="2"/>
       <c r="AE262" s="2" t="s">
@@ -23985,9 +24013,7 @@
         <v>313</v>
       </c>
       <c r="AG262" s="4"/>
-      <c r="AH262" s="2" t="s">
-        <v>927</v>
-      </c>
+      <c r="AH262" s="2"/>
       <c r="AI262" s="2"/>
     </row>
     <row r="263" spans="1:35" ht="24" customHeight="1" x14ac:dyDescent="0.4">
@@ -23996,7 +24022,7 @@
       </c>
       <c r="B263" s="2"/>
       <c r="C263" s="45" t="s">
-        <v>928</v>
+        <v>924</v>
       </c>
       <c r="D263" s="2"/>
       <c r="E263" s="4">
@@ -24004,13 +24030,13 @@
       </c>
       <c r="F263" s="38"/>
       <c r="G263" s="28">
-        <v>51.616700000000002</v>
+        <v>19.7364</v>
       </c>
       <c r="H263" s="28">
-        <v>123.5167</v>
+        <v>110.0167</v>
       </c>
       <c r="I263" s="2">
-        <v>1402</v>
+        <v>31.4</v>
       </c>
       <c r="J263" s="26">
         <v>12</v>
@@ -24018,9 +24044,9 @@
       <c r="K263" s="30" t="s">
         <v>307</v>
       </c>
-      <c r="L263" s="3"/>
+      <c r="L263" s="2"/>
       <c r="M263" s="14" t="s">
-        <v>929</v>
+        <v>925</v>
       </c>
       <c r="N263" s="2"/>
       <c r="O263" s="31"/>
@@ -24032,10 +24058,10 @@
       </c>
       <c r="T263" s="36"/>
       <c r="U263" s="40" t="s">
-        <v>340</v>
+        <v>517</v>
       </c>
       <c r="V263" s="2" t="s">
-        <v>330</v>
+        <v>517</v>
       </c>
       <c r="W263" s="4" t="s">
         <v>39</v>
@@ -24048,11 +24074,9 @@
       </c>
       <c r="Z263" s="4"/>
       <c r="AA263" s="2" t="s">
-        <v>341</v>
-      </c>
-      <c r="AB263" s="2" t="s">
-        <v>348</v>
-      </c>
+        <v>926</v>
+      </c>
+      <c r="AB263" s="2"/>
       <c r="AC263" s="2"/>
       <c r="AD263" s="2"/>
       <c r="AE263" s="2" t="s">
@@ -24063,7 +24087,7 @@
       </c>
       <c r="AG263" s="4"/>
       <c r="AH263" s="2" t="s">
-        <v>705</v>
+        <v>927</v>
       </c>
       <c r="AI263" s="2"/>
     </row>
@@ -24072,20 +24096,22 @@
         <v>263</v>
       </c>
       <c r="B264" s="2"/>
-      <c r="C264" s="45"/>
+      <c r="C264" s="45" t="s">
+        <v>928</v>
+      </c>
       <c r="D264" s="2"/>
-      <c r="E264" s="4"/>
-      <c r="F264" s="38" t="s">
-        <v>930</v>
-      </c>
+      <c r="E264" s="4">
+        <v>99999</v>
+      </c>
+      <c r="F264" s="38"/>
       <c r="G264" s="28">
-        <v>53.491900000000001</v>
+        <v>51.616700000000002</v>
       </c>
       <c r="H264" s="28">
-        <v>123.0519</v>
+        <v>123.5167</v>
       </c>
       <c r="I264" s="2">
-        <v>278.10000000000002</v>
+        <v>1402</v>
       </c>
       <c r="J264" s="26">
         <v>12</v>
@@ -24095,7 +24121,7 @@
       </c>
       <c r="L264" s="3"/>
       <c r="M264" s="14" t="s">
-        <v>931</v>
+        <v>929</v>
       </c>
       <c r="N264" s="2"/>
       <c r="O264" s="31"/>
@@ -24107,7 +24133,7 @@
       </c>
       <c r="T264" s="36"/>
       <c r="U264" s="40" t="s">
-        <v>355</v>
+        <v>340</v>
       </c>
       <c r="V264" s="2" t="s">
         <v>330</v>
@@ -24122,11 +24148,11 @@
         <v>39</v>
       </c>
       <c r="Z264" s="4"/>
-      <c r="AA264" s="4" t="s">
+      <c r="AA264" s="2" t="s">
         <v>341</v>
       </c>
-      <c r="AB264" s="4" t="s">
-        <v>352</v>
+      <c r="AB264" s="2" t="s">
+        <v>348</v>
       </c>
       <c r="AC264" s="2"/>
       <c r="AD264" s="2"/>
@@ -24138,7 +24164,7 @@
       </c>
       <c r="AG264" s="4"/>
       <c r="AH264" s="2" t="s">
-        <v>711</v>
+        <v>705</v>
       </c>
       <c r="AI264" s="2"/>
     </row>
@@ -24151,16 +24177,16 @@
       <c r="D265" s="2"/>
       <c r="E265" s="4"/>
       <c r="F265" s="38" t="s">
-        <v>932</v>
+        <v>930</v>
       </c>
       <c r="G265" s="28">
-        <v>50.928600000000003</v>
+        <v>53.491900000000001</v>
       </c>
       <c r="H265" s="28">
-        <v>124.31359999999999</v>
+        <v>123.0519</v>
       </c>
       <c r="I265" s="2">
-        <v>444.5</v>
+        <v>278.10000000000002</v>
       </c>
       <c r="J265" s="26">
         <v>12</v>
@@ -24170,7 +24196,7 @@
       </c>
       <c r="L265" s="3"/>
       <c r="M265" s="14" t="s">
-        <v>933</v>
+        <v>931</v>
       </c>
       <c r="N265" s="2"/>
       <c r="O265" s="31"/>
@@ -24182,7 +24208,7 @@
       </c>
       <c r="T265" s="36"/>
       <c r="U265" s="40" t="s">
-        <v>340</v>
+        <v>355</v>
       </c>
       <c r="V265" s="2" t="s">
         <v>330</v>
@@ -24197,11 +24223,11 @@
         <v>39</v>
       </c>
       <c r="Z265" s="4"/>
-      <c r="AA265" s="2" t="s">
+      <c r="AA265" s="4" t="s">
         <v>341</v>
       </c>
-      <c r="AB265" s="2" t="s">
-        <v>934</v>
+      <c r="AB265" s="4" t="s">
+        <v>352</v>
       </c>
       <c r="AC265" s="2"/>
       <c r="AD265" s="2"/>
@@ -24213,7 +24239,7 @@
       </c>
       <c r="AG265" s="4"/>
       <c r="AH265" s="2" t="s">
-        <v>349</v>
+        <v>711</v>
       </c>
       <c r="AI265" s="2"/>
     </row>
@@ -24226,16 +24252,16 @@
       <c r="D266" s="2"/>
       <c r="E266" s="4"/>
       <c r="F266" s="38" t="s">
-        <v>935</v>
+        <v>932</v>
       </c>
       <c r="G266" s="28">
-        <v>52.875599999999999</v>
+        <v>50.928600000000003</v>
       </c>
       <c r="H266" s="28">
-        <v>124.5578</v>
+        <v>124.31359999999999</v>
       </c>
       <c r="I266" s="2">
-        <v>358.8</v>
+        <v>444.5</v>
       </c>
       <c r="J266" s="26">
         <v>12</v>
@@ -24245,7 +24271,7 @@
       </c>
       <c r="L266" s="3"/>
       <c r="M266" s="14" t="s">
-        <v>936</v>
+        <v>933</v>
       </c>
       <c r="N266" s="2"/>
       <c r="O266" s="31"/>
@@ -24276,7 +24302,7 @@
         <v>341</v>
       </c>
       <c r="AB266" s="2" t="s">
-        <v>345</v>
+        <v>934</v>
       </c>
       <c r="AC266" s="2"/>
       <c r="AD266" s="2"/>
@@ -24301,16 +24327,16 @@
       <c r="D267" s="2"/>
       <c r="E267" s="4"/>
       <c r="F267" s="38" t="s">
-        <v>937</v>
+        <v>935</v>
       </c>
       <c r="G267" s="28">
-        <v>51.7881</v>
+        <v>52.875599999999999</v>
       </c>
       <c r="H267" s="28">
-        <v>124.5244</v>
+        <v>124.5578</v>
       </c>
       <c r="I267" s="2">
-        <v>466</v>
+        <v>358.8</v>
       </c>
       <c r="J267" s="26">
         <v>12</v>
@@ -24320,7 +24346,7 @@
       </c>
       <c r="L267" s="3"/>
       <c r="M267" s="14" t="s">
-        <v>938</v>
+        <v>936</v>
       </c>
       <c r="N267" s="2"/>
       <c r="O267" s="31"/>
@@ -24351,7 +24377,7 @@
         <v>341</v>
       </c>
       <c r="AB267" s="2" t="s">
-        <v>939</v>
+        <v>345</v>
       </c>
       <c r="AC267" s="2"/>
       <c r="AD267" s="2"/>
@@ -24372,22 +24398,20 @@
         <v>267</v>
       </c>
       <c r="B268" s="2"/>
-      <c r="C268" s="45">
-        <v>50349</v>
-      </c>
+      <c r="C268" s="45"/>
       <c r="D268" s="2"/>
-      <c r="E268" s="4">
-        <v>99999</v>
-      </c>
-      <c r="F268" s="38"/>
+      <c r="E268" s="4"/>
+      <c r="F268" s="38" t="s">
+        <v>937</v>
+      </c>
       <c r="G268" s="28">
-        <v>51.664999999999999</v>
+        <v>51.7881</v>
       </c>
       <c r="H268" s="28">
-        <v>124.3917</v>
+        <v>124.5244</v>
       </c>
       <c r="I268" s="2">
-        <v>501.5</v>
+        <v>466</v>
       </c>
       <c r="J268" s="26">
         <v>12</v>
@@ -24397,7 +24421,7 @@
       </c>
       <c r="L268" s="3"/>
       <c r="M268" s="14" t="s">
-        <v>940</v>
+        <v>938</v>
       </c>
       <c r="N268" s="2"/>
       <c r="O268" s="31"/>
@@ -24424,10 +24448,12 @@
         <v>39</v>
       </c>
       <c r="Z268" s="4"/>
-      <c r="AA268" s="4" t="s">
+      <c r="AA268" s="2" t="s">
         <v>341</v>
       </c>
-      <c r="AB268" s="2"/>
+      <c r="AB268" s="2" t="s">
+        <v>939</v>
+      </c>
       <c r="AC268" s="2"/>
       <c r="AD268" s="2"/>
       <c r="AE268" s="2" t="s">
@@ -24448,7 +24474,7 @@
       </c>
       <c r="B269" s="2"/>
       <c r="C269" s="45">
-        <v>50442</v>
+        <v>50349</v>
       </c>
       <c r="D269" s="2"/>
       <c r="E269" s="4">
@@ -24456,13 +24482,13 @@
       </c>
       <c r="F269" s="38"/>
       <c r="G269" s="28">
-        <v>50.4</v>
+        <v>51.664999999999999</v>
       </c>
       <c r="H269" s="28">
-        <v>124.12</v>
+        <v>124.3917</v>
       </c>
       <c r="I269" s="2">
-        <v>371.7</v>
+        <v>501.5</v>
       </c>
       <c r="J269" s="26">
         <v>12</v>
@@ -24472,7 +24498,7 @@
       </c>
       <c r="L269" s="3"/>
       <c r="M269" s="14" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="N269" s="2"/>
       <c r="O269" s="31"/>
@@ -24499,7 +24525,7 @@
         <v>39</v>
       </c>
       <c r="Z269" s="4"/>
-      <c r="AA269" s="2" t="s">
+      <c r="AA269" s="4" t="s">
         <v>341</v>
       </c>
       <c r="AB269" s="2"/>
@@ -24523,7 +24549,7 @@
       </c>
       <c r="B270" s="2"/>
       <c r="C270" s="45">
-        <v>50962</v>
+        <v>50442</v>
       </c>
       <c r="D270" s="2"/>
       <c r="E270" s="4">
@@ -24531,13 +24557,13 @@
       </c>
       <c r="F270" s="38"/>
       <c r="G270" s="28">
-        <v>45.9756</v>
+        <v>50.4</v>
       </c>
       <c r="H270" s="28">
-        <v>128.0453</v>
+        <v>124.12</v>
       </c>
       <c r="I270" s="2">
-        <v>116.9</v>
+        <v>371.7</v>
       </c>
       <c r="J270" s="26">
         <v>12</v>
@@ -24547,7 +24573,7 @@
       </c>
       <c r="L270" s="3"/>
       <c r="M270" s="14" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="N270" s="2"/>
       <c r="O270" s="31"/>
@@ -24558,7 +24584,9 @@
         <v>39</v>
       </c>
       <c r="T270" s="36"/>
-      <c r="U270" s="40"/>
+      <c r="U270" s="40" t="s">
+        <v>340</v>
+      </c>
       <c r="V270" s="2" t="s">
         <v>330</v>
       </c>
@@ -24573,15 +24601,11 @@
       </c>
       <c r="Z270" s="4"/>
       <c r="AA270" s="2" t="s">
-        <v>331</v>
-      </c>
-      <c r="AB270" s="2" t="s">
-        <v>943</v>
-      </c>
+        <v>341</v>
+      </c>
+      <c r="AB270" s="2"/>
       <c r="AC270" s="2"/>
-      <c r="AD270" s="2" t="s">
-        <v>944</v>
-      </c>
+      <c r="AD270" s="2"/>
       <c r="AE270" s="2" t="s">
         <v>312</v>
       </c>
@@ -24589,34 +24613,32 @@
         <v>313</v>
       </c>
       <c r="AG270" s="4"/>
-      <c r="AH270" s="2"/>
+      <c r="AH270" s="2" t="s">
+        <v>349</v>
+      </c>
       <c r="AI270" s="2"/>
     </row>
     <row r="271" spans="1:35" ht="24" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A271" s="2">
         <v>270</v>
       </c>
-      <c r="B271" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="C271" s="45" t="s">
-        <v>945</v>
-      </c>
-      <c r="D271" s="2" t="s">
-        <v>946</v>
-      </c>
+      <c r="B271" s="2"/>
+      <c r="C271" s="45">
+        <v>50962</v>
+      </c>
+      <c r="D271" s="2"/>
       <c r="E271" s="4">
-        <v>9999</v>
+        <v>99999</v>
       </c>
       <c r="F271" s="38"/>
       <c r="G271" s="28">
-        <v>50.248100000000001</v>
+        <v>45.9756</v>
       </c>
       <c r="H271" s="28">
-        <v>127.4619</v>
+        <v>128.0453</v>
       </c>
       <c r="I271" s="2">
-        <v>166.4</v>
+        <v>116.9</v>
       </c>
       <c r="J271" s="26">
         <v>12</v>
@@ -24624,20 +24646,20 @@
       <c r="K271" s="30" t="s">
         <v>307</v>
       </c>
-      <c r="L271" s="2"/>
+      <c r="L271" s="3"/>
       <c r="M271" s="14" t="s">
-        <v>947</v>
+        <v>942</v>
       </c>
       <c r="N271" s="2"/>
       <c r="O271" s="31"/>
       <c r="P271" s="31"/>
       <c r="Q271" s="31"/>
       <c r="R271" s="50"/>
-      <c r="S271" s="22"/>
+      <c r="S271" s="22" t="s">
+        <v>39</v>
+      </c>
       <c r="T271" s="36"/>
-      <c r="U271" s="40" t="s">
-        <v>948</v>
-      </c>
+      <c r="U271" s="40"/>
       <c r="V271" s="2" t="s">
         <v>330</v>
       </c>
@@ -24652,13 +24674,15 @@
       </c>
       <c r="Z271" s="4"/>
       <c r="AA271" s="2" t="s">
-        <v>677</v>
+        <v>331</v>
       </c>
       <c r="AB271" s="2" t="s">
-        <v>678</v>
+        <v>943</v>
       </c>
       <c r="AC271" s="2"/>
-      <c r="AD271" s="2"/>
+      <c r="AD271" s="2" t="s">
+        <v>944</v>
+      </c>
       <c r="AE271" s="2" t="s">
         <v>312</v>
       </c>
@@ -24666,44 +24690,54 @@
         <v>313</v>
       </c>
       <c r="AG271" s="4"/>
-      <c r="AH271" s="2" t="s">
-        <v>949</v>
-      </c>
+      <c r="AH271" s="2"/>
       <c r="AI271" s="2"/>
     </row>
     <row r="272" spans="1:35" ht="24" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A272" s="2">
         <v>271</v>
       </c>
-      <c r="B272" s="2"/>
-      <c r="C272" s="45"/>
-      <c r="D272" s="2"/>
-      <c r="E272" s="4"/>
+      <c r="B272" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C272" s="45" t="s">
+        <v>945</v>
+      </c>
+      <c r="D272" s="2" t="s">
+        <v>946</v>
+      </c>
+      <c r="E272" s="4">
+        <v>9999</v>
+      </c>
       <c r="F272" s="38"/>
-      <c r="G272" s="28"/>
-      <c r="H272" s="28"/>
-      <c r="I272" s="2"/>
+      <c r="G272" s="28">
+        <v>50.248100000000001</v>
+      </c>
+      <c r="H272" s="28">
+        <v>127.4619</v>
+      </c>
+      <c r="I272" s="2">
+        <v>166.4</v>
+      </c>
       <c r="J272" s="26">
         <v>12</v>
       </c>
       <c r="K272" s="30" t="s">
         <v>307</v>
       </c>
-      <c r="L272" s="3"/>
+      <c r="L272" s="2"/>
       <c r="M272" s="14" t="s">
-        <v>950</v>
+        <v>947</v>
       </c>
       <c r="N272" s="2"/>
       <c r="O272" s="31"/>
       <c r="P272" s="31"/>
       <c r="Q272" s="31"/>
       <c r="R272" s="50"/>
-      <c r="S272" s="22" t="s">
-        <v>39</v>
-      </c>
+      <c r="S272" s="22"/>
       <c r="T272" s="36"/>
       <c r="U272" s="40" t="s">
-        <v>676</v>
+        <v>948</v>
       </c>
       <c r="V272" s="2" t="s">
         <v>330</v>
@@ -24722,7 +24756,7 @@
         <v>677</v>
       </c>
       <c r="AB272" s="2" t="s">
-        <v>951</v>
+        <v>678</v>
       </c>
       <c r="AC272" s="2"/>
       <c r="AD272" s="2"/>
@@ -24734,7 +24768,7 @@
       </c>
       <c r="AG272" s="4"/>
       <c r="AH272" s="2" t="s">
-        <v>682</v>
+        <v>949</v>
       </c>
       <c r="AI272" s="2"/>
     </row>
@@ -24743,23 +24777,13 @@
         <v>272</v>
       </c>
       <c r="B273" s="2"/>
-      <c r="C273" s="45">
-        <v>50655</v>
-      </c>
+      <c r="C273" s="45"/>
       <c r="D273" s="2"/>
-      <c r="E273" s="4">
-        <v>99999</v>
-      </c>
+      <c r="E273" s="4"/>
       <c r="F273" s="38"/>
-      <c r="G273" s="28">
-        <v>48.498100000000001</v>
-      </c>
-      <c r="H273" s="28">
-        <v>126.1908</v>
-      </c>
-      <c r="I273" s="2">
-        <v>271.89999999999998</v>
-      </c>
+      <c r="G273" s="28"/>
+      <c r="H273" s="28"/>
+      <c r="I273" s="2"/>
       <c r="J273" s="26">
         <v>12</v>
       </c>
@@ -24768,7 +24792,7 @@
       </c>
       <c r="L273" s="3"/>
       <c r="M273" s="14" t="s">
-        <v>952</v>
+        <v>950</v>
       </c>
       <c r="N273" s="2"/>
       <c r="O273" s="31"/>
@@ -24780,7 +24804,7 @@
       </c>
       <c r="T273" s="36"/>
       <c r="U273" s="40" t="s">
-        <v>953</v>
+        <v>676</v>
       </c>
       <c r="V273" s="2" t="s">
         <v>330</v>
@@ -24799,7 +24823,7 @@
         <v>677</v>
       </c>
       <c r="AB273" s="2" t="s">
-        <v>954</v>
+        <v>951</v>
       </c>
       <c r="AC273" s="2"/>
       <c r="AD273" s="2"/>
@@ -24821,25 +24845,31 @@
       </c>
       <c r="B274" s="2"/>
       <c r="C274" s="45">
-        <v>50779</v>
+        <v>50655</v>
       </c>
       <c r="D274" s="2"/>
       <c r="E274" s="4">
         <v>99999</v>
       </c>
       <c r="F274" s="38"/>
-      <c r="G274" s="28"/>
-      <c r="H274" s="28"/>
-      <c r="I274" s="2"/>
+      <c r="G274" s="28">
+        <v>48.498100000000001</v>
+      </c>
+      <c r="H274" s="28">
+        <v>126.1908</v>
+      </c>
+      <c r="I274" s="2">
+        <v>271.89999999999998</v>
+      </c>
       <c r="J274" s="26">
         <v>12</v>
       </c>
       <c r="K274" s="30" t="s">
         <v>307</v>
       </c>
-      <c r="L274" s="2"/>
+      <c r="L274" s="3"/>
       <c r="M274" s="14" t="s">
-        <v>955</v>
+        <v>952</v>
       </c>
       <c r="N274" s="2"/>
       <c r="O274" s="31"/>
@@ -24851,7 +24881,7 @@
       </c>
       <c r="T274" s="36"/>
       <c r="U274" s="40" t="s">
-        <v>956</v>
+        <v>953</v>
       </c>
       <c r="V274" s="2" t="s">
         <v>330</v>
@@ -24867,10 +24897,10 @@
       </c>
       <c r="Z274" s="4"/>
       <c r="AA274" s="2" t="s">
-        <v>957</v>
+        <v>677</v>
       </c>
       <c r="AB274" s="2" t="s">
-        <v>958</v>
+        <v>954</v>
       </c>
       <c r="AC274" s="2"/>
       <c r="AD274" s="2"/>
@@ -24881,7 +24911,9 @@
         <v>313</v>
       </c>
       <c r="AG274" s="4"/>
-      <c r="AH274" s="2"/>
+      <c r="AH274" s="2" t="s">
+        <v>682</v>
+      </c>
       <c r="AI274" s="2"/>
     </row>
     <row r="275" spans="1:35" ht="24" customHeight="1" x14ac:dyDescent="0.4">
@@ -24890,22 +24922,16 @@
       </c>
       <c r="B275" s="2"/>
       <c r="C275" s="45">
-        <v>50861</v>
+        <v>50779</v>
       </c>
       <c r="D275" s="2"/>
       <c r="E275" s="4">
         <v>99999</v>
       </c>
       <c r="F275" s="38"/>
-      <c r="G275" s="28">
-        <v>46.88</v>
-      </c>
-      <c r="H275" s="28">
-        <v>127.48</v>
-      </c>
-      <c r="I275" s="2">
-        <v>182.4</v>
-      </c>
+      <c r="G275" s="28"/>
+      <c r="H275" s="28"/>
+      <c r="I275" s="2"/>
       <c r="J275" s="26">
         <v>12</v>
       </c>
@@ -24914,7 +24940,7 @@
       </c>
       <c r="L275" s="2"/>
       <c r="M275" s="14" t="s">
-        <v>959</v>
+        <v>955</v>
       </c>
       <c r="N275" s="2"/>
       <c r="O275" s="31"/>
@@ -24926,7 +24952,7 @@
       </c>
       <c r="T275" s="36"/>
       <c r="U275" s="40" t="s">
-        <v>960</v>
+        <v>956</v>
       </c>
       <c r="V275" s="2" t="s">
         <v>330</v>
@@ -24942,10 +24968,10 @@
       </c>
       <c r="Z275" s="4"/>
       <c r="AA275" s="2" t="s">
-        <v>961</v>
+        <v>957</v>
       </c>
       <c r="AB275" s="2" t="s">
-        <v>962</v>
+        <v>958</v>
       </c>
       <c r="AC275" s="2"/>
       <c r="AD275" s="2"/>
@@ -24956,9 +24982,7 @@
         <v>313</v>
       </c>
       <c r="AG275" s="4"/>
-      <c r="AH275" s="2" t="s">
-        <v>682</v>
-      </c>
+      <c r="AH275" s="2"/>
       <c r="AI275" s="2"/>
     </row>
     <row r="276" spans="1:35" ht="24" customHeight="1" x14ac:dyDescent="0.4">
@@ -24966,8 +24990,8 @@
         <v>275</v>
       </c>
       <c r="B276" s="2"/>
-      <c r="C276" s="45" t="s">
-        <v>963</v>
+      <c r="C276" s="45">
+        <v>50861</v>
       </c>
       <c r="D276" s="2"/>
       <c r="E276" s="4">
@@ -24975,13 +24999,13 @@
       </c>
       <c r="F276" s="38"/>
       <c r="G276" s="28">
-        <v>31.4558</v>
+        <v>46.88</v>
       </c>
       <c r="H276" s="28">
-        <v>110.2711</v>
+        <v>127.48</v>
       </c>
       <c r="I276" s="2">
-        <v>2948.1</v>
+        <v>182.4</v>
       </c>
       <c r="J276" s="26">
         <v>12</v>
@@ -24991,20 +25015,22 @@
       </c>
       <c r="L276" s="2"/>
       <c r="M276" s="14" t="s">
-        <v>964</v>
+        <v>959</v>
       </c>
       <c r="N276" s="2"/>
       <c r="O276" s="31"/>
       <c r="P276" s="31"/>
       <c r="Q276" s="31"/>
       <c r="R276" s="50"/>
-      <c r="S276" s="22"/>
+      <c r="S276" s="22" t="s">
+        <v>39</v>
+      </c>
       <c r="T276" s="36"/>
       <c r="U276" s="40" t="s">
-        <v>483</v>
+        <v>960</v>
       </c>
       <c r="V276" s="2" t="s">
-        <v>483</v>
+        <v>330</v>
       </c>
       <c r="W276" s="4" t="s">
         <v>39</v>
@@ -25016,8 +25042,12 @@
         <v>39</v>
       </c>
       <c r="Z276" s="4"/>
-      <c r="AA276" s="2"/>
-      <c r="AB276" s="2"/>
+      <c r="AA276" s="2" t="s">
+        <v>961</v>
+      </c>
+      <c r="AB276" s="2" t="s">
+        <v>962</v>
+      </c>
       <c r="AC276" s="2"/>
       <c r="AD276" s="2"/>
       <c r="AE276" s="2" t="s">
@@ -25028,7 +25058,7 @@
       </c>
       <c r="AG276" s="4"/>
       <c r="AH276" s="2" t="s">
-        <v>965</v>
+        <v>682</v>
       </c>
       <c r="AI276" s="2"/>
     </row>
@@ -25037,20 +25067,22 @@
         <v>276</v>
       </c>
       <c r="B277" s="2"/>
-      <c r="C277" s="45"/>
+      <c r="C277" s="45" t="s">
+        <v>963</v>
+      </c>
       <c r="D277" s="2"/>
-      <c r="E277" s="4"/>
-      <c r="F277" s="38" t="s">
-        <v>966</v>
-      </c>
+      <c r="E277" s="4">
+        <v>99999</v>
+      </c>
+      <c r="F277" s="38"/>
       <c r="G277" s="28">
-        <v>29.041899999999998</v>
+        <v>31.4558</v>
       </c>
       <c r="H277" s="28">
-        <v>110.4725</v>
+        <v>110.2711</v>
       </c>
       <c r="I277" s="2">
-        <v>1443.4</v>
+        <v>2948.1</v>
       </c>
       <c r="J277" s="26">
         <v>12</v>
@@ -25058,26 +25090,26 @@
       <c r="K277" s="30" t="s">
         <v>307</v>
       </c>
-      <c r="L277" s="3"/>
+      <c r="L277" s="2"/>
       <c r="M277" s="14" t="s">
-        <v>967</v>
+        <v>964</v>
       </c>
       <c r="N277" s="2"/>
       <c r="O277" s="31"/>
       <c r="P277" s="31"/>
       <c r="Q277" s="31"/>
       <c r="R277" s="50"/>
-      <c r="S277" s="22" t="s">
-        <v>39</v>
-      </c>
+      <c r="S277" s="22"/>
       <c r="T277" s="36"/>
       <c r="U277" s="40" t="s">
         <v>483</v>
       </c>
       <c r="V277" s="2" t="s">
-        <v>470</v>
-      </c>
-      <c r="W277" s="4"/>
+        <v>483</v>
+      </c>
+      <c r="W277" s="4" t="s">
+        <v>39</v>
+      </c>
       <c r="X277" s="4" t="s">
         <v>39</v>
       </c>
@@ -25085,12 +25117,8 @@
         <v>39</v>
       </c>
       <c r="Z277" s="4"/>
-      <c r="AA277" s="2" t="s">
-        <v>968</v>
-      </c>
-      <c r="AB277" s="2" t="s">
-        <v>969</v>
-      </c>
+      <c r="AA277" s="2"/>
+      <c r="AB277" s="2"/>
       <c r="AC277" s="2"/>
       <c r="AD277" s="2"/>
       <c r="AE277" s="2" t="s">
@@ -25100,32 +25128,30 @@
         <v>313</v>
       </c>
       <c r="AG277" s="4"/>
-      <c r="AH277" s="2"/>
-      <c r="AI277" s="2" t="s">
-        <v>637</v>
-      </c>
+      <c r="AH277" s="2" t="s">
+        <v>965</v>
+      </c>
+      <c r="AI277" s="2"/>
     </row>
     <row r="278" spans="1:35" ht="24" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A278" s="2">
         <v>277</v>
       </c>
       <c r="B278" s="2"/>
-      <c r="C278" s="45">
-        <v>54276</v>
-      </c>
+      <c r="C278" s="45"/>
       <c r="D278" s="2"/>
-      <c r="E278" s="4">
-        <v>99999</v>
-      </c>
-      <c r="F278" s="38"/>
+      <c r="E278" s="4"/>
+      <c r="F278" s="38" t="s">
+        <v>966</v>
+      </c>
       <c r="G278" s="28">
-        <v>42.4</v>
+        <v>29.041899999999998</v>
       </c>
       <c r="H278" s="28">
-        <v>126.8</v>
+        <v>110.4725</v>
       </c>
       <c r="I278" s="2">
-        <v>570</v>
+        <v>1443.4</v>
       </c>
       <c r="J278" s="26">
         <v>12</v>
@@ -25133,9 +25159,9 @@
       <c r="K278" s="30" t="s">
         <v>307</v>
       </c>
-      <c r="L278" s="2"/>
+      <c r="L278" s="3"/>
       <c r="M278" s="14" t="s">
-        <v>970</v>
+        <v>967</v>
       </c>
       <c r="N278" s="2"/>
       <c r="O278" s="31"/>
@@ -25147,14 +25173,12 @@
       </c>
       <c r="T278" s="36"/>
       <c r="U278" s="40" t="s">
-        <v>322</v>
+        <v>483</v>
       </c>
       <c r="V278" s="2" t="s">
-        <v>322</v>
-      </c>
-      <c r="W278" s="4" t="s">
-        <v>39</v>
-      </c>
+        <v>470</v>
+      </c>
+      <c r="W278" s="4"/>
       <c r="X278" s="4" t="s">
         <v>39</v>
       </c>
@@ -25163,10 +25187,10 @@
       </c>
       <c r="Z278" s="4"/>
       <c r="AA278" s="2" t="s">
-        <v>971</v>
+        <v>968</v>
       </c>
       <c r="AB278" s="2" t="s">
-        <v>972</v>
+        <v>969</v>
       </c>
       <c r="AC278" s="2"/>
       <c r="AD278" s="2"/>
@@ -25178,22 +25202,32 @@
       </c>
       <c r="AG278" s="4"/>
       <c r="AH278" s="2"/>
-      <c r="AI278" s="2"/>
+      <c r="AI278" s="2" t="s">
+        <v>637</v>
+      </c>
     </row>
     <row r="279" spans="1:35" ht="24" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A279" s="2">
         <v>278</v>
       </c>
       <c r="B279" s="2"/>
-      <c r="C279" s="45"/>
+      <c r="C279" s="45">
+        <v>54276</v>
+      </c>
       <c r="D279" s="2"/>
-      <c r="E279" s="4"/>
-      <c r="F279" s="38" t="s">
-        <v>973</v>
-      </c>
-      <c r="G279" s="28"/>
-      <c r="H279" s="28"/>
-      <c r="I279" s="2"/>
+      <c r="E279" s="4">
+        <v>99999</v>
+      </c>
+      <c r="F279" s="38"/>
+      <c r="G279" s="28">
+        <v>42.4</v>
+      </c>
+      <c r="H279" s="28">
+        <v>126.8</v>
+      </c>
+      <c r="I279" s="2">
+        <v>570</v>
+      </c>
       <c r="J279" s="26">
         <v>12</v>
       </c>
@@ -25202,7 +25236,7 @@
       </c>
       <c r="L279" s="2"/>
       <c r="M279" s="14" t="s">
-        <v>974</v>
+        <v>970</v>
       </c>
       <c r="N279" s="2"/>
       <c r="O279" s="31"/>
@@ -25256,7 +25290,7 @@
       <c r="D280" s="2"/>
       <c r="E280" s="4"/>
       <c r="F280" s="38" t="s">
-        <v>975</v>
+        <v>973</v>
       </c>
       <c r="G280" s="28"/>
       <c r="H280" s="28"/>
@@ -25269,7 +25303,7 @@
       </c>
       <c r="L280" s="2"/>
       <c r="M280" s="14" t="s">
-        <v>976</v>
+        <v>974</v>
       </c>
       <c r="N280" s="2"/>
       <c r="O280" s="31"/>
@@ -25281,10 +25315,10 @@
       </c>
       <c r="T280" s="36"/>
       <c r="U280" s="40" t="s">
-        <v>977</v>
+        <v>322</v>
       </c>
       <c r="V280" s="2" t="s">
-        <v>358</v>
+        <v>322</v>
       </c>
       <c r="W280" s="4" t="s">
         <v>39</v>
@@ -25297,9 +25331,11 @@
       </c>
       <c r="Z280" s="4"/>
       <c r="AA280" s="2" t="s">
-        <v>978</v>
-      </c>
-      <c r="AB280" s="2"/>
+        <v>971</v>
+      </c>
+      <c r="AB280" s="2" t="s">
+        <v>972</v>
+      </c>
       <c r="AC280" s="2"/>
       <c r="AD280" s="2"/>
       <c r="AE280" s="2" t="s">
@@ -25316,28 +25352,16 @@
       <c r="A281" s="2">
         <v>280</v>
       </c>
-      <c r="B281" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="C281" s="45">
-        <v>50915</v>
-      </c>
-      <c r="D281" s="2" t="s">
-        <v>979</v>
-      </c>
-      <c r="E281" s="4">
-        <v>99999</v>
-      </c>
-      <c r="F281" s="38"/>
-      <c r="G281" s="28">
-        <v>45.52</v>
-      </c>
-      <c r="H281" s="28">
-        <v>116.97</v>
-      </c>
-      <c r="I281" s="2">
-        <v>838.9</v>
-      </c>
+      <c r="B281" s="2"/>
+      <c r="C281" s="45"/>
+      <c r="D281" s="2"/>
+      <c r="E281" s="4"/>
+      <c r="F281" s="38" t="s">
+        <v>975</v>
+      </c>
+      <c r="G281" s="28"/>
+      <c r="H281" s="28"/>
+      <c r="I281" s="2"/>
       <c r="J281" s="26">
         <v>12</v>
       </c>
@@ -25346,17 +25370,19 @@
       </c>
       <c r="L281" s="2"/>
       <c r="M281" s="14" t="s">
-        <v>980</v>
+        <v>976</v>
       </c>
       <c r="N281" s="2"/>
       <c r="O281" s="31"/>
       <c r="P281" s="31"/>
       <c r="Q281" s="31"/>
       <c r="R281" s="50"/>
-      <c r="S281" s="22"/>
+      <c r="S281" s="22" t="s">
+        <v>39</v>
+      </c>
       <c r="T281" s="36"/>
       <c r="U281" s="40" t="s">
-        <v>981</v>
+        <v>977</v>
       </c>
       <c r="V281" s="2" t="s">
         <v>358</v>
@@ -25372,7 +25398,7 @@
       </c>
       <c r="Z281" s="4"/>
       <c r="AA281" s="2" t="s">
-        <v>982</v>
+        <v>978</v>
       </c>
       <c r="AB281" s="2"/>
       <c r="AC281" s="2"/>
@@ -25391,23 +25417,27 @@
       <c r="A282" s="2">
         <v>281</v>
       </c>
-      <c r="B282" s="2"/>
+      <c r="B282" s="2" t="s">
+        <v>35</v>
+      </c>
       <c r="C282" s="45">
-        <v>50913</v>
-      </c>
-      <c r="D282" s="2"/>
+        <v>50915</v>
+      </c>
+      <c r="D282" s="2" t="s">
+        <v>979</v>
+      </c>
       <c r="E282" s="4">
         <v>99999</v>
       </c>
       <c r="F282" s="38"/>
       <c r="G282" s="28">
-        <v>45.72</v>
+        <v>45.52</v>
       </c>
       <c r="H282" s="28">
-        <v>118.83</v>
+        <v>116.97</v>
       </c>
       <c r="I282" s="2">
-        <v>865</v>
+        <v>838.9</v>
       </c>
       <c r="J282" s="26">
         <v>12</v>
@@ -25417,16 +25447,14 @@
       </c>
       <c r="L282" s="2"/>
       <c r="M282" s="14" t="s">
-        <v>983</v>
+        <v>980</v>
       </c>
       <c r="N282" s="2"/>
       <c r="O282" s="31"/>
       <c r="P282" s="31"/>
       <c r="Q282" s="31"/>
       <c r="R282" s="50"/>
-      <c r="S282" s="22" t="s">
-        <v>39</v>
-      </c>
+      <c r="S282" s="22"/>
       <c r="T282" s="36"/>
       <c r="U282" s="40" t="s">
         <v>981</v>
@@ -25465,20 +25493,22 @@
         <v>282</v>
       </c>
       <c r="B283" s="2"/>
-      <c r="C283" s="45"/>
+      <c r="C283" s="45">
+        <v>50913</v>
+      </c>
       <c r="D283" s="2"/>
-      <c r="E283" s="4"/>
-      <c r="F283" s="38" t="s">
-        <v>984</v>
-      </c>
+      <c r="E283" s="4">
+        <v>99999</v>
+      </c>
+      <c r="F283" s="38"/>
       <c r="G283" s="28">
-        <v>49.888100000000001</v>
+        <v>45.72</v>
       </c>
       <c r="H283" s="28">
-        <v>120.4333</v>
+        <v>118.83</v>
       </c>
       <c r="I283" s="2">
-        <v>701.2</v>
+        <v>865</v>
       </c>
       <c r="J283" s="26">
         <v>12</v>
@@ -25486,9 +25516,9 @@
       <c r="K283" s="30" t="s">
         <v>307</v>
       </c>
-      <c r="L283" s="3"/>
+      <c r="L283" s="2"/>
       <c r="M283" s="14" t="s">
-        <v>985</v>
+        <v>983</v>
       </c>
       <c r="N283" s="2"/>
       <c r="O283" s="31"/>
@@ -25500,7 +25530,7 @@
       </c>
       <c r="T283" s="36"/>
       <c r="U283" s="40" t="s">
-        <v>368</v>
+        <v>981</v>
       </c>
       <c r="V283" s="2" t="s">
         <v>358</v>
@@ -25516,11 +25546,9 @@
       </c>
       <c r="Z283" s="4"/>
       <c r="AA283" s="2" t="s">
-        <v>359</v>
-      </c>
-      <c r="AB283" s="2" t="s">
-        <v>368</v>
-      </c>
+        <v>982</v>
+      </c>
+      <c r="AB283" s="2"/>
       <c r="AC283" s="2"/>
       <c r="AD283" s="2"/>
       <c r="AE283" s="2" t="s">
@@ -25530,9 +25558,7 @@
         <v>313</v>
       </c>
       <c r="AG283" s="4"/>
-      <c r="AH283" s="2" t="s">
-        <v>349</v>
-      </c>
+      <c r="AH283" s="2"/>
       <c r="AI283" s="2"/>
     </row>
     <row r="284" spans="1:35" ht="24" customHeight="1" x14ac:dyDescent="0.4">
@@ -25544,16 +25570,16 @@
       <c r="D284" s="2"/>
       <c r="E284" s="4"/>
       <c r="F284" s="38" t="s">
-        <v>986</v>
+        <v>984</v>
       </c>
       <c r="G284" s="28">
-        <v>51.3264</v>
+        <v>49.888100000000001</v>
       </c>
       <c r="H284" s="28">
-        <v>119.8869</v>
+        <v>120.4333</v>
       </c>
       <c r="I284" s="2">
-        <v>496.2</v>
+        <v>701.2</v>
       </c>
       <c r="J284" s="26">
         <v>12</v>
@@ -25563,11 +25589,9 @@
       </c>
       <c r="L284" s="3"/>
       <c r="M284" s="14" t="s">
-        <v>987</v>
-      </c>
-      <c r="N284" s="2" t="s">
-        <v>38</v>
-      </c>
+        <v>985</v>
+      </c>
+      <c r="N284" s="2"/>
       <c r="O284" s="31"/>
       <c r="P284" s="31"/>
       <c r="Q284" s="31"/>
@@ -25577,7 +25601,7 @@
       </c>
       <c r="T284" s="36"/>
       <c r="U284" s="40" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="V284" s="2" t="s">
         <v>358</v>
@@ -25596,11 +25620,9 @@
         <v>359</v>
       </c>
       <c r="AB284" s="2" t="s">
-        <v>367</v>
-      </c>
-      <c r="AC284" s="2" t="s">
-        <v>988</v>
-      </c>
+        <v>368</v>
+      </c>
+      <c r="AC284" s="2"/>
       <c r="AD284" s="2"/>
       <c r="AE284" s="2" t="s">
         <v>312</v>
@@ -25610,7 +25632,7 @@
       </c>
       <c r="AG284" s="4"/>
       <c r="AH284" s="2" t="s">
-        <v>989</v>
+        <v>349</v>
       </c>
       <c r="AI284" s="2"/>
     </row>
@@ -25619,22 +25641,20 @@
         <v>284</v>
       </c>
       <c r="B285" s="2"/>
-      <c r="C285" s="45">
-        <v>50429</v>
-      </c>
+      <c r="C285" s="45"/>
       <c r="D285" s="2"/>
-      <c r="E285" s="4">
-        <v>99999</v>
-      </c>
-      <c r="F285" s="38"/>
+      <c r="E285" s="4"/>
+      <c r="F285" s="38" t="s">
+        <v>986</v>
+      </c>
       <c r="G285" s="28">
-        <v>51.286900000000003</v>
+        <v>51.3264</v>
       </c>
       <c r="H285" s="28">
-        <v>120.7311</v>
+        <v>119.8869</v>
       </c>
       <c r="I285" s="2">
-        <v>666.4</v>
+        <v>496.2</v>
       </c>
       <c r="J285" s="26">
         <v>12</v>
@@ -25642,11 +25662,13 @@
       <c r="K285" s="30" t="s">
         <v>307</v>
       </c>
-      <c r="L285" s="2"/>
+      <c r="L285" s="3"/>
       <c r="M285" s="14" t="s">
-        <v>990</v>
-      </c>
-      <c r="N285" s="2"/>
+        <v>987</v>
+      </c>
+      <c r="N285" s="2" t="s">
+        <v>38</v>
+      </c>
       <c r="O285" s="31"/>
       <c r="P285" s="31"/>
       <c r="Q285" s="31"/>
@@ -25677,7 +25699,9 @@
       <c r="AB285" s="2" t="s">
         <v>367</v>
       </c>
-      <c r="AC285" s="2"/>
+      <c r="AC285" s="2" t="s">
+        <v>988</v>
+      </c>
       <c r="AD285" s="2"/>
       <c r="AE285" s="2" t="s">
         <v>312</v>
@@ -25687,7 +25711,7 @@
       </c>
       <c r="AG285" s="4"/>
       <c r="AH285" s="2" t="s">
-        <v>349</v>
+        <v>989</v>
       </c>
       <c r="AI285" s="2"/>
     </row>
@@ -25696,20 +25720,22 @@
         <v>285</v>
       </c>
       <c r="B286" s="2"/>
-      <c r="C286" s="45"/>
+      <c r="C286" s="45">
+        <v>50429</v>
+      </c>
       <c r="D286" s="2"/>
-      <c r="E286" s="4"/>
-      <c r="F286" s="38" t="s">
-        <v>991</v>
-      </c>
+      <c r="E286" s="4">
+        <v>99999</v>
+      </c>
+      <c r="F286" s="38"/>
       <c r="G286" s="28">
-        <v>52.6633</v>
+        <v>51.286900000000003</v>
       </c>
       <c r="H286" s="28">
-        <v>120.82470000000001</v>
+        <v>120.7311</v>
       </c>
       <c r="I286" s="2">
-        <v>430</v>
+        <v>666.4</v>
       </c>
       <c r="J286" s="26">
         <v>12</v>
@@ -25717,19 +25743,15 @@
       <c r="K286" s="30" t="s">
         <v>307</v>
       </c>
-      <c r="L286" s="3"/>
+      <c r="L286" s="2"/>
       <c r="M286" s="14" t="s">
-        <v>992</v>
-      </c>
-      <c r="N286" s="2" t="s">
-        <v>246</v>
-      </c>
+        <v>990</v>
+      </c>
+      <c r="N286" s="2"/>
       <c r="O286" s="31"/>
       <c r="P286" s="31"/>
       <c r="Q286" s="31"/>
-      <c r="R286" s="50" t="s">
-        <v>282</v>
-      </c>
+      <c r="R286" s="50"/>
       <c r="S286" s="22" t="s">
         <v>39</v>
       </c>
@@ -25768,9 +25790,7 @@
       <c r="AH286" s="2" t="s">
         <v>349</v>
       </c>
-      <c r="AI286" s="2" t="s">
-        <v>637</v>
-      </c>
+      <c r="AI286" s="2"/>
     </row>
     <row r="287" spans="1:35" ht="24" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A287" s="2">
@@ -25781,16 +25801,16 @@
       <c r="D287" s="2"/>
       <c r="E287" s="4"/>
       <c r="F287" s="38" t="s">
-        <v>993</v>
+        <v>991</v>
       </c>
       <c r="G287" s="28">
-        <v>50.44</v>
+        <v>52.6633</v>
       </c>
       <c r="H287" s="28">
-        <v>119.7453</v>
+        <v>120.82470000000001</v>
       </c>
       <c r="I287" s="2">
-        <v>558.6</v>
+        <v>430</v>
       </c>
       <c r="J287" s="26">
         <v>12</v>
@@ -25800,13 +25820,17 @@
       </c>
       <c r="L287" s="3"/>
       <c r="M287" s="14" t="s">
-        <v>994</v>
-      </c>
-      <c r="N287" s="2"/>
+        <v>992</v>
+      </c>
+      <c r="N287" s="2" t="s">
+        <v>246</v>
+      </c>
       <c r="O287" s="31"/>
       <c r="P287" s="31"/>
       <c r="Q287" s="31"/>
-      <c r="R287" s="50"/>
+      <c r="R287" s="50" t="s">
+        <v>282</v>
+      </c>
       <c r="S287" s="22" t="s">
         <v>39</v>
       </c>
@@ -25845,7 +25869,9 @@
       <c r="AH287" s="2" t="s">
         <v>349</v>
       </c>
-      <c r="AI287" s="2"/>
+      <c r="AI287" s="2" t="s">
+        <v>637</v>
+      </c>
     </row>
     <row r="288" spans="1:35" ht="24" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A288" s="2">
@@ -25856,16 +25882,16 @@
       <c r="D288" s="2"/>
       <c r="E288" s="4"/>
       <c r="F288" s="38" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
       <c r="G288" s="28">
-        <v>50.581899999999997</v>
+        <v>50.44</v>
       </c>
       <c r="H288" s="28">
-        <v>120.0264</v>
+        <v>119.7453</v>
       </c>
       <c r="I288" s="2">
-        <v>589</v>
+        <v>558.6</v>
       </c>
       <c r="J288" s="26">
         <v>12</v>
@@ -25875,7 +25901,7 @@
       </c>
       <c r="L288" s="3"/>
       <c r="M288" s="14" t="s">
-        <v>996</v>
+        <v>994</v>
       </c>
       <c r="N288" s="2"/>
       <c r="O288" s="31"/>
@@ -25931,16 +25957,16 @@
       <c r="D289" s="2"/>
       <c r="E289" s="4"/>
       <c r="F289" s="38" t="s">
-        <v>997</v>
+        <v>995</v>
       </c>
       <c r="G289" s="28">
-        <v>50.467199999999998</v>
+        <v>50.581899999999997</v>
       </c>
       <c r="H289" s="28">
-        <v>119.8522</v>
+        <v>120.0264</v>
       </c>
       <c r="I289" s="2">
-        <v>567.6</v>
+        <v>589</v>
       </c>
       <c r="J289" s="26">
         <v>12</v>
@@ -25950,7 +25976,7 @@
       </c>
       <c r="L289" s="3"/>
       <c r="M289" s="14" t="s">
-        <v>998</v>
+        <v>996</v>
       </c>
       <c r="N289" s="2"/>
       <c r="O289" s="31"/>
@@ -26006,16 +26032,16 @@
       <c r="D290" s="2"/>
       <c r="E290" s="4"/>
       <c r="F290" s="38" t="s">
-        <v>999</v>
+        <v>997</v>
       </c>
       <c r="G290" s="28">
-        <v>50.46</v>
+        <v>50.467199999999998</v>
       </c>
       <c r="H290" s="28">
-        <v>120.0806</v>
+        <v>119.8522</v>
       </c>
       <c r="I290" s="2">
-        <v>625.6</v>
+        <v>567.6</v>
       </c>
       <c r="J290" s="26">
         <v>12</v>
@@ -26025,7 +26051,7 @@
       </c>
       <c r="L290" s="3"/>
       <c r="M290" s="14" t="s">
-        <v>1000</v>
+        <v>998</v>
       </c>
       <c r="N290" s="2"/>
       <c r="O290" s="31"/>
@@ -26080,10 +26106,18 @@
       <c r="C291" s="45"/>
       <c r="D291" s="2"/>
       <c r="E291" s="4"/>
-      <c r="F291" s="38"/>
-      <c r="G291" s="28"/>
-      <c r="H291" s="28"/>
-      <c r="I291" s="2"/>
+      <c r="F291" s="38" t="s">
+        <v>999</v>
+      </c>
+      <c r="G291" s="28">
+        <v>50.46</v>
+      </c>
+      <c r="H291" s="28">
+        <v>120.0806</v>
+      </c>
+      <c r="I291" s="2">
+        <v>625.6</v>
+      </c>
       <c r="J291" s="26">
         <v>12</v>
       </c>
@@ -26092,7 +26126,7 @@
       </c>
       <c r="L291" s="3"/>
       <c r="M291" s="14" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
       <c r="N291" s="2"/>
       <c r="O291" s="31"/>
@@ -26147,18 +26181,10 @@
       <c r="C292" s="45"/>
       <c r="D292" s="2"/>
       <c r="E292" s="4"/>
-      <c r="F292" s="38" t="s">
-        <v>1002</v>
-      </c>
-      <c r="G292" s="28">
-        <v>52.22</v>
-      </c>
-      <c r="H292" s="28">
-        <v>121.5317</v>
-      </c>
-      <c r="I292" s="2">
-        <v>907.9</v>
-      </c>
+      <c r="F292" s="38"/>
+      <c r="G292" s="28"/>
+      <c r="H292" s="28"/>
+      <c r="I292" s="2"/>
       <c r="J292" s="26">
         <v>12</v>
       </c>
@@ -26167,7 +26193,7 @@
       </c>
       <c r="L292" s="3"/>
       <c r="M292" s="14" t="s">
-        <v>1003</v>
+        <v>1001</v>
       </c>
       <c r="N292" s="2"/>
       <c r="O292" s="31"/>
@@ -26223,11 +26249,17 @@
       <c r="D293" s="2"/>
       <c r="E293" s="4"/>
       <c r="F293" s="38" t="s">
-        <v>1004</v>
-      </c>
-      <c r="G293" s="28"/>
-      <c r="H293" s="28"/>
-      <c r="I293" s="2"/>
+        <v>1002</v>
+      </c>
+      <c r="G293" s="28">
+        <v>52.22</v>
+      </c>
+      <c r="H293" s="28">
+        <v>121.5317</v>
+      </c>
+      <c r="I293" s="2">
+        <v>907.9</v>
+      </c>
       <c r="J293" s="26">
         <v>12</v>
       </c>
@@ -26236,7 +26268,7 @@
       </c>
       <c r="L293" s="3"/>
       <c r="M293" s="14" t="s">
-        <v>1005</v>
+        <v>1003</v>
       </c>
       <c r="N293" s="2"/>
       <c r="O293" s="31"/>
@@ -26291,7 +26323,9 @@
       <c r="C294" s="45"/>
       <c r="D294" s="2"/>
       <c r="E294" s="4"/>
-      <c r="F294" s="38"/>
+      <c r="F294" s="38" t="s">
+        <v>1004</v>
+      </c>
       <c r="G294" s="28"/>
       <c r="H294" s="28"/>
       <c r="I294" s="2"/>
@@ -26303,7 +26337,7 @@
       </c>
       <c r="L294" s="3"/>
       <c r="M294" s="14" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="N294" s="2"/>
       <c r="O294" s="31"/>
@@ -26370,7 +26404,7 @@
       </c>
       <c r="L295" s="3"/>
       <c r="M295" s="14" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="N295" s="2"/>
       <c r="O295" s="31"/>
@@ -26425,9 +26459,7 @@
       <c r="C296" s="45"/>
       <c r="D296" s="2"/>
       <c r="E296" s="4"/>
-      <c r="F296" s="38" t="s">
-        <v>1008</v>
-      </c>
+      <c r="F296" s="38"/>
       <c r="G296" s="28"/>
       <c r="H296" s="28"/>
       <c r="I296" s="2"/>
@@ -26437,9 +26469,9 @@
       <c r="K296" s="30" t="s">
         <v>307</v>
       </c>
-      <c r="L296" s="2"/>
+      <c r="L296" s="3"/>
       <c r="M296" s="14" t="s">
-        <v>1009</v>
+        <v>1007</v>
       </c>
       <c r="N296" s="2"/>
       <c r="O296" s="31"/>
@@ -26495,7 +26527,7 @@
       <c r="D297" s="2"/>
       <c r="E297" s="4"/>
       <c r="F297" s="38" t="s">
-        <v>1010</v>
+        <v>1008</v>
       </c>
       <c r="G297" s="28"/>
       <c r="H297" s="28"/>
@@ -26508,7 +26540,7 @@
       </c>
       <c r="L297" s="2"/>
       <c r="M297" s="14" t="s">
-        <v>1011</v>
+        <v>1009</v>
       </c>
       <c r="N297" s="2"/>
       <c r="O297" s="31"/>
@@ -26563,7 +26595,9 @@
       <c r="C298" s="45"/>
       <c r="D298" s="2"/>
       <c r="E298" s="4"/>
-      <c r="F298" s="38"/>
+      <c r="F298" s="38" t="s">
+        <v>1010</v>
+      </c>
       <c r="G298" s="28"/>
       <c r="H298" s="28"/>
       <c r="I298" s="2"/>
@@ -26575,7 +26609,7 @@
       </c>
       <c r="L298" s="2"/>
       <c r="M298" s="14" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="N298" s="2"/>
       <c r="O298" s="31"/>
@@ -26617,7 +26651,9 @@
         <v>313</v>
       </c>
       <c r="AG298" s="4"/>
-      <c r="AH298" s="2"/>
+      <c r="AH298" s="2" t="s">
+        <v>349</v>
+      </c>
       <c r="AI298" s="2"/>
     </row>
     <row r="299" spans="1:35" ht="24" customHeight="1" x14ac:dyDescent="0.4">
@@ -26628,18 +26664,10 @@
       <c r="C299" s="45"/>
       <c r="D299" s="2"/>
       <c r="E299" s="4"/>
-      <c r="F299" s="38" t="s">
-        <v>1013</v>
-      </c>
-      <c r="G299" s="28">
-        <v>52.746400000000001</v>
-      </c>
-      <c r="H299" s="28">
-        <v>120.2683</v>
-      </c>
-      <c r="I299" s="2">
-        <v>545.70000000000005</v>
-      </c>
+      <c r="F299" s="38"/>
+      <c r="G299" s="28"/>
+      <c r="H299" s="28"/>
+      <c r="I299" s="2"/>
       <c r="J299" s="26">
         <v>12</v>
       </c>
@@ -26648,14 +26676,16 @@
       </c>
       <c r="L299" s="2"/>
       <c r="M299" s="14" t="s">
-        <v>1014</v>
+        <v>1012</v>
       </c>
       <c r="N299" s="2"/>
       <c r="O299" s="31"/>
       <c r="P299" s="31"/>
       <c r="Q299" s="31"/>
       <c r="R299" s="50"/>
-      <c r="S299" s="22"/>
+      <c r="S299" s="22" t="s">
+        <v>39</v>
+      </c>
       <c r="T299" s="36"/>
       <c r="U299" s="40" t="s">
         <v>366</v>
@@ -26695,27 +26725,21 @@
       <c r="A300" s="2">
         <v>299</v>
       </c>
-      <c r="B300" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="C300" s="45">
-        <v>50548</v>
-      </c>
-      <c r="D300" s="2" t="s">
-        <v>1015</v>
-      </c>
-      <c r="E300" s="4">
-        <v>99999</v>
-      </c>
-      <c r="F300" s="38"/>
+      <c r="B300" s="2"/>
+      <c r="C300" s="45"/>
+      <c r="D300" s="2"/>
+      <c r="E300" s="4"/>
+      <c r="F300" s="38" t="s">
+        <v>1013</v>
+      </c>
       <c r="G300" s="28">
-        <v>49.2</v>
+        <v>52.746400000000001</v>
       </c>
       <c r="H300" s="28">
-        <v>123.72</v>
+        <v>120.2683</v>
       </c>
       <c r="I300" s="2">
-        <v>286.10000000000002</v>
+        <v>545.70000000000005</v>
       </c>
       <c r="J300" s="26">
         <v>12</v>
@@ -26723,9 +26747,9 @@
       <c r="K300" s="30" t="s">
         <v>307</v>
       </c>
-      <c r="L300" s="3"/>
+      <c r="L300" s="2"/>
       <c r="M300" s="14" t="s">
-        <v>1016</v>
+        <v>1014</v>
       </c>
       <c r="N300" s="2"/>
       <c r="O300" s="31"/>
@@ -26735,7 +26759,7 @@
       <c r="S300" s="22"/>
       <c r="T300" s="36"/>
       <c r="U300" s="40" t="s">
-        <v>1017</v>
+        <v>366</v>
       </c>
       <c r="V300" s="2" t="s">
         <v>358</v>
@@ -26754,7 +26778,7 @@
         <v>359</v>
       </c>
       <c r="AB300" s="2" t="s">
-        <v>1018</v>
+        <v>367</v>
       </c>
       <c r="AC300" s="2"/>
       <c r="AD300" s="2"/>
@@ -26765,32 +26789,34 @@
         <v>313</v>
       </c>
       <c r="AG300" s="4"/>
-      <c r="AH300" s="2" t="s">
-        <v>349</v>
-      </c>
+      <c r="AH300" s="2"/>
       <c r="AI300" s="2"/>
     </row>
     <row r="301" spans="1:35" ht="24" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A301" s="2">
         <v>300</v>
       </c>
-      <c r="B301" s="2"/>
+      <c r="B301" s="2" t="s">
+        <v>35</v>
+      </c>
       <c r="C301" s="45">
-        <v>50445</v>
-      </c>
-      <c r="D301" s="2"/>
+        <v>50548</v>
+      </c>
+      <c r="D301" s="2" t="s">
+        <v>1015</v>
+      </c>
       <c r="E301" s="4">
         <v>99999</v>
       </c>
       <c r="F301" s="38"/>
       <c r="G301" s="28">
-        <v>50.5764</v>
+        <v>49.2</v>
       </c>
       <c r="H301" s="28">
-        <v>123.7281</v>
+        <v>123.72</v>
       </c>
       <c r="I301" s="2">
-        <v>425.5</v>
+        <v>286.10000000000002</v>
       </c>
       <c r="J301" s="26">
         <v>12</v>
@@ -26800,19 +26826,17 @@
       </c>
       <c r="L301" s="3"/>
       <c r="M301" s="14" t="s">
-        <v>1018</v>
+        <v>1016</v>
       </c>
       <c r="N301" s="2"/>
       <c r="O301" s="31"/>
       <c r="P301" s="31"/>
       <c r="Q301" s="31"/>
       <c r="R301" s="50"/>
-      <c r="S301" s="22" t="s">
-        <v>39</v>
-      </c>
+      <c r="S301" s="22"/>
       <c r="T301" s="36"/>
       <c r="U301" s="40" t="s">
-        <v>357</v>
+        <v>1017</v>
       </c>
       <c r="V301" s="2" t="s">
         <v>358</v>
@@ -26852,19 +26876,23 @@
         <v>301</v>
       </c>
       <c r="B302" s="2"/>
-      <c r="C302" s="45"/>
+      <c r="C302" s="45">
+        <v>50445</v>
+      </c>
       <c r="D302" s="2"/>
-      <c r="E302" s="4"/>
-      <c r="F302" s="38" t="s">
-        <v>1019</v>
-      </c>
+      <c r="E302" s="4">
+        <v>99999</v>
+      </c>
+      <c r="F302" s="38"/>
       <c r="G302" s="28">
-        <v>49.32</v>
+        <v>50.5764</v>
       </c>
       <c r="H302" s="28">
-        <v>123.61</v>
-      </c>
-      <c r="I302" s="2"/>
+        <v>123.7281</v>
+      </c>
+      <c r="I302" s="2">
+        <v>425.5</v>
+      </c>
       <c r="J302" s="26">
         <v>12</v>
       </c>
@@ -26873,7 +26901,7 @@
       </c>
       <c r="L302" s="3"/>
       <c r="M302" s="14" t="s">
-        <v>1020</v>
+        <v>1018</v>
       </c>
       <c r="N302" s="2"/>
       <c r="O302" s="31"/>
@@ -26885,7 +26913,7 @@
       </c>
       <c r="T302" s="36"/>
       <c r="U302" s="40" t="s">
-        <v>1018</v>
+        <v>357</v>
       </c>
       <c r="V302" s="2" t="s">
         <v>358</v>
@@ -26929,26 +26957,24 @@
       <c r="D303" s="2"/>
       <c r="E303" s="4"/>
       <c r="F303" s="38" t="s">
-        <v>1021</v>
+        <v>1019</v>
       </c>
       <c r="G303" s="28">
-        <v>50.008600000000001</v>
+        <v>49.32</v>
       </c>
       <c r="H303" s="28">
-        <v>125.0403</v>
-      </c>
-      <c r="I303" s="2">
-        <v>365</v>
-      </c>
+        <v>123.61</v>
+      </c>
+      <c r="I303" s="2"/>
       <c r="J303" s="26">
         <v>12</v>
       </c>
       <c r="K303" s="30" t="s">
         <v>307</v>
       </c>
-      <c r="L303" s="2"/>
+      <c r="L303" s="3"/>
       <c r="M303" s="14" t="s">
-        <v>1022</v>
+        <v>1020</v>
       </c>
       <c r="N303" s="2"/>
       <c r="O303" s="31"/>
@@ -26990,7 +27016,9 @@
         <v>313</v>
       </c>
       <c r="AG303" s="4"/>
-      <c r="AH303" s="2"/>
+      <c r="AH303" s="2" t="s">
+        <v>349</v>
+      </c>
       <c r="AI303" s="2"/>
     </row>
     <row r="304" spans="1:35" ht="24" customHeight="1" x14ac:dyDescent="0.4">
@@ -27002,16 +27030,16 @@
       <c r="D304" s="2"/>
       <c r="E304" s="4"/>
       <c r="F304" s="38" t="s">
-        <v>1023</v>
+        <v>1021</v>
       </c>
       <c r="G304" s="28">
-        <v>50.064700000000002</v>
+        <v>50.008600000000001</v>
       </c>
       <c r="H304" s="28">
-        <v>124.9303</v>
+        <v>125.0403</v>
       </c>
       <c r="I304" s="2">
-        <v>293.2</v>
+        <v>365</v>
       </c>
       <c r="J304" s="26">
         <v>12</v>
@@ -27021,7 +27049,7 @@
       </c>
       <c r="L304" s="2"/>
       <c r="M304" s="14" t="s">
-        <v>1024</v>
+        <v>1022</v>
       </c>
       <c r="N304" s="2"/>
       <c r="O304" s="31"/>
@@ -27075,16 +27103,16 @@
       <c r="D305" s="2"/>
       <c r="E305" s="4"/>
       <c r="F305" s="38" t="s">
-        <v>1025</v>
+        <v>1023</v>
       </c>
       <c r="G305" s="28">
-        <v>50.995800000000003</v>
+        <v>50.064700000000002</v>
       </c>
       <c r="H305" s="28">
-        <v>121.0483</v>
+        <v>124.9303</v>
       </c>
       <c r="I305" s="2">
-        <v>817.2</v>
+        <v>293.2</v>
       </c>
       <c r="J305" s="26">
         <v>12</v>
@@ -27092,9 +27120,9 @@
       <c r="K305" s="30" t="s">
         <v>307</v>
       </c>
-      <c r="L305" s="3"/>
+      <c r="L305" s="2"/>
       <c r="M305" s="14" t="s">
-        <v>1026</v>
+        <v>1024</v>
       </c>
       <c r="N305" s="2"/>
       <c r="O305" s="31"/>
@@ -27106,7 +27134,7 @@
       </c>
       <c r="T305" s="36"/>
       <c r="U305" s="40" t="s">
-        <v>356</v>
+        <v>1018</v>
       </c>
       <c r="V305" s="2" t="s">
         <v>358</v>
@@ -27125,7 +27153,7 @@
         <v>359</v>
       </c>
       <c r="AB305" s="2" t="s">
-        <v>360</v>
+        <v>1018</v>
       </c>
       <c r="AC305" s="2"/>
       <c r="AD305" s="2"/>
@@ -27136,9 +27164,7 @@
         <v>313</v>
       </c>
       <c r="AG305" s="4"/>
-      <c r="AH305" s="2" t="s">
-        <v>349</v>
-      </c>
+      <c r="AH305" s="2"/>
       <c r="AI305" s="2"/>
     </row>
     <row r="306" spans="1:35" ht="24" customHeight="1" x14ac:dyDescent="0.4">
@@ -27150,16 +27176,16 @@
       <c r="D306" s="2"/>
       <c r="E306" s="4"/>
       <c r="F306" s="38" t="s">
-        <v>1027</v>
+        <v>1025</v>
       </c>
       <c r="G306" s="28">
-        <v>50.875300000000003</v>
+        <v>50.995800000000003</v>
       </c>
       <c r="H306" s="28">
-        <v>121.68</v>
+        <v>121.0483</v>
       </c>
       <c r="I306" s="2">
-        <v>740</v>
+        <v>817.2</v>
       </c>
       <c r="J306" s="26">
         <v>12</v>
@@ -27169,7 +27195,7 @@
       </c>
       <c r="L306" s="3"/>
       <c r="M306" s="14" t="s">
-        <v>1028</v>
+        <v>1026</v>
       </c>
       <c r="N306" s="2"/>
       <c r="O306" s="31"/>
@@ -27196,10 +27222,10 @@
         <v>39</v>
       </c>
       <c r="Z306" s="4"/>
-      <c r="AA306" s="4" t="s">
+      <c r="AA306" s="2" t="s">
         <v>359</v>
       </c>
-      <c r="AB306" s="4" t="s">
+      <c r="AB306" s="2" t="s">
         <v>360</v>
       </c>
       <c r="AC306" s="2"/>
@@ -27225,16 +27251,16 @@
       <c r="D307" s="2"/>
       <c r="E307" s="4"/>
       <c r="F307" s="38" t="s">
-        <v>1029</v>
+        <v>1027</v>
       </c>
       <c r="G307" s="28">
-        <v>50.698099999999997</v>
+        <v>50.875300000000003</v>
       </c>
       <c r="H307" s="28">
-        <v>121.3706</v>
+        <v>121.68</v>
       </c>
       <c r="I307" s="2">
-        <v>687.5</v>
+        <v>740</v>
       </c>
       <c r="J307" s="26">
         <v>12</v>
@@ -27244,7 +27270,7 @@
       </c>
       <c r="L307" s="3"/>
       <c r="M307" s="14" t="s">
-        <v>1030</v>
+        <v>1028</v>
       </c>
       <c r="N307" s="2"/>
       <c r="O307" s="31"/>
@@ -27271,10 +27297,10 @@
         <v>39</v>
       </c>
       <c r="Z307" s="4"/>
-      <c r="AA307" s="2" t="s">
+      <c r="AA307" s="4" t="s">
         <v>359</v>
       </c>
-      <c r="AB307" s="2" t="s">
+      <c r="AB307" s="4" t="s">
         <v>360</v>
       </c>
       <c r="AC307" s="2"/>
@@ -27300,16 +27326,16 @@
       <c r="D308" s="2"/>
       <c r="E308" s="4"/>
       <c r="F308" s="38" t="s">
-        <v>1031</v>
+        <v>1029</v>
       </c>
       <c r="G308" s="28">
-        <v>52.041899999999998</v>
+        <v>50.698099999999997</v>
       </c>
       <c r="H308" s="28">
-        <v>122.0761</v>
+        <v>121.3706</v>
       </c>
       <c r="I308" s="2">
-        <v>632</v>
+        <v>687.5</v>
       </c>
       <c r="J308" s="26">
         <v>12</v>
@@ -27319,7 +27345,7 @@
       </c>
       <c r="L308" s="3"/>
       <c r="M308" s="14" t="s">
-        <v>1032</v>
+        <v>1030</v>
       </c>
       <c r="N308" s="2"/>
       <c r="O308" s="31"/>
@@ -27375,11 +27401,17 @@
       <c r="D309" s="2"/>
       <c r="E309" s="4"/>
       <c r="F309" s="38" t="s">
-        <v>1033</v>
-      </c>
-      <c r="G309" s="28"/>
-      <c r="H309" s="28"/>
-      <c r="I309" s="2"/>
+        <v>1031</v>
+      </c>
+      <c r="G309" s="28">
+        <v>52.041899999999998</v>
+      </c>
+      <c r="H309" s="28">
+        <v>122.0761</v>
+      </c>
+      <c r="I309" s="2">
+        <v>632</v>
+      </c>
       <c r="J309" s="26">
         <v>12</v>
       </c>
@@ -27388,7 +27420,7 @@
       </c>
       <c r="L309" s="3"/>
       <c r="M309" s="14" t="s">
-        <v>1034</v>
+        <v>1032</v>
       </c>
       <c r="N309" s="2"/>
       <c r="O309" s="31"/>
@@ -27400,7 +27432,7 @@
       </c>
       <c r="T309" s="36"/>
       <c r="U309" s="40" t="s">
-        <v>1035</v>
+        <v>356</v>
       </c>
       <c r="V309" s="2" t="s">
         <v>358</v>
@@ -27443,7 +27475,9 @@
       <c r="C310" s="45"/>
       <c r="D310" s="2"/>
       <c r="E310" s="4"/>
-      <c r="F310" s="38"/>
+      <c r="F310" s="38" t="s">
+        <v>1033</v>
+      </c>
       <c r="G310" s="28"/>
       <c r="H310" s="28"/>
       <c r="I310" s="2"/>
@@ -27453,9 +27487,9 @@
       <c r="K310" s="30" t="s">
         <v>307</v>
       </c>
-      <c r="L310" s="2"/>
+      <c r="L310" s="3"/>
       <c r="M310" s="14" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="N310" s="2"/>
       <c r="O310" s="31"/>
@@ -27467,7 +27501,7 @@
       </c>
       <c r="T310" s="36"/>
       <c r="U310" s="40" t="s">
-        <v>356</v>
+        <v>1035</v>
       </c>
       <c r="V310" s="2" t="s">
         <v>358</v>
@@ -27510,18 +27544,10 @@
       <c r="C311" s="45"/>
       <c r="D311" s="2"/>
       <c r="E311" s="4"/>
-      <c r="F311" s="38" t="s">
-        <v>1037</v>
-      </c>
-      <c r="G311" s="28">
-        <v>51.330800000000004</v>
-      </c>
-      <c r="H311" s="28">
-        <v>121.5136</v>
-      </c>
-      <c r="I311" s="2">
-        <v>798.9</v>
-      </c>
+      <c r="F311" s="38"/>
+      <c r="G311" s="28"/>
+      <c r="H311" s="28"/>
+      <c r="I311" s="2"/>
       <c r="J311" s="26">
         <v>12</v>
       </c>
@@ -27530,7 +27556,7 @@
       </c>
       <c r="L311" s="2"/>
       <c r="M311" s="14" t="s">
-        <v>1038</v>
+        <v>1036</v>
       </c>
       <c r="N311" s="2"/>
       <c r="O311" s="31"/>
@@ -27586,11 +27612,17 @@
       <c r="D312" s="2"/>
       <c r="E312" s="4"/>
       <c r="F312" s="38" t="s">
-        <v>1039</v>
-      </c>
-      <c r="G312" s="28"/>
-      <c r="H312" s="28"/>
-      <c r="I312" s="2"/>
+        <v>1037</v>
+      </c>
+      <c r="G312" s="28">
+        <v>51.330800000000004</v>
+      </c>
+      <c r="H312" s="28">
+        <v>121.5136</v>
+      </c>
+      <c r="I312" s="2">
+        <v>798.9</v>
+      </c>
       <c r="J312" s="26">
         <v>12</v>
       </c>
@@ -27599,7 +27631,7 @@
       </c>
       <c r="L312" s="2"/>
       <c r="M312" s="14" t="s">
-        <v>1040</v>
+        <v>1038</v>
       </c>
       <c r="N312" s="2"/>
       <c r="O312" s="31"/>
@@ -27611,7 +27643,7 @@
       </c>
       <c r="T312" s="36"/>
       <c r="U312" s="40" t="s">
-        <v>371</v>
+        <v>356</v>
       </c>
       <c r="V312" s="2" t="s">
         <v>358</v>
@@ -27630,7 +27662,7 @@
         <v>359</v>
       </c>
       <c r="AB312" s="2" t="s">
-        <v>372</v>
+        <v>360</v>
       </c>
       <c r="AC312" s="2"/>
       <c r="AD312" s="2"/>
@@ -27641,7 +27673,9 @@
         <v>313</v>
       </c>
       <c r="AG312" s="4"/>
-      <c r="AH312" s="2"/>
+      <c r="AH312" s="2" t="s">
+        <v>349</v>
+      </c>
       <c r="AI312" s="2"/>
     </row>
     <row r="313" spans="1:35" ht="24" customHeight="1" x14ac:dyDescent="0.4">
@@ -27653,7 +27687,7 @@
       <c r="D313" s="2"/>
       <c r="E313" s="4"/>
       <c r="F313" s="38" t="s">
-        <v>1041</v>
+        <v>1039</v>
       </c>
       <c r="G313" s="28"/>
       <c r="H313" s="28"/>
@@ -27666,7 +27700,7 @@
       </c>
       <c r="L313" s="2"/>
       <c r="M313" s="14" t="s">
-        <v>1042</v>
+        <v>1040</v>
       </c>
       <c r="N313" s="2"/>
       <c r="O313" s="31"/>
@@ -27716,23 +27750,15 @@
         <v>313</v>
       </c>
       <c r="B314" s="2"/>
-      <c r="C314" s="45" t="s">
-        <v>1043</v>
-      </c>
+      <c r="C314" s="45"/>
       <c r="D314" s="2"/>
-      <c r="E314" s="4">
-        <v>99999</v>
-      </c>
-      <c r="F314" s="38"/>
-      <c r="G314" s="28">
-        <v>49.581699999999998</v>
-      </c>
-      <c r="H314" s="28">
-        <v>117.32689999999999</v>
-      </c>
-      <c r="I314" s="2">
-        <v>660.4</v>
-      </c>
+      <c r="E314" s="4"/>
+      <c r="F314" s="38" t="s">
+        <v>1041</v>
+      </c>
+      <c r="G314" s="28"/>
+      <c r="H314" s="28"/>
+      <c r="I314" s="2"/>
       <c r="J314" s="26">
         <v>12</v>
       </c>
@@ -27741,7 +27767,7 @@
       </c>
       <c r="L314" s="2"/>
       <c r="M314" s="14" t="s">
-        <v>1044</v>
+        <v>1042</v>
       </c>
       <c r="N314" s="2"/>
       <c r="O314" s="31"/>
@@ -27753,7 +27779,7 @@
       </c>
       <c r="T314" s="36"/>
       <c r="U314" s="40" t="s">
-        <v>357</v>
+        <v>371</v>
       </c>
       <c r="V314" s="2" t="s">
         <v>358</v>
@@ -27772,7 +27798,7 @@
         <v>359</v>
       </c>
       <c r="AB314" s="2" t="s">
-        <v>1045</v>
+        <v>372</v>
       </c>
       <c r="AC314" s="2"/>
       <c r="AD314" s="2"/>
@@ -27791,20 +27817,22 @@
         <v>314</v>
       </c>
       <c r="B315" s="2"/>
-      <c r="C315" s="45"/>
+      <c r="C315" s="45" t="s">
+        <v>1043</v>
+      </c>
       <c r="D315" s="2"/>
-      <c r="E315" s="4"/>
-      <c r="F315" s="38" t="s">
-        <v>1046</v>
-      </c>
+      <c r="E315" s="4">
+        <v>99999</v>
+      </c>
+      <c r="F315" s="38"/>
       <c r="G315" s="28">
-        <v>49.679699999999997</v>
+        <v>49.581699999999998</v>
       </c>
       <c r="H315" s="28">
-        <v>116.81359999999999</v>
+        <v>117.32689999999999</v>
       </c>
       <c r="I315" s="2">
-        <v>710</v>
+        <v>660.4</v>
       </c>
       <c r="J315" s="26">
         <v>12</v>
@@ -27814,7 +27842,7 @@
       </c>
       <c r="L315" s="2"/>
       <c r="M315" s="14" t="s">
-        <v>1047</v>
+        <v>1044</v>
       </c>
       <c r="N315" s="2"/>
       <c r="O315" s="31"/>
@@ -27826,7 +27854,7 @@
       </c>
       <c r="T315" s="36"/>
       <c r="U315" s="40" t="s">
-        <v>1048</v>
+        <v>357</v>
       </c>
       <c r="V315" s="2" t="s">
         <v>358</v>
@@ -27845,7 +27873,7 @@
         <v>359</v>
       </c>
       <c r="AB315" s="2" t="s">
-        <v>1048</v>
+        <v>1045</v>
       </c>
       <c r="AC315" s="2"/>
       <c r="AD315" s="2"/>
@@ -27864,22 +27892,20 @@
         <v>315</v>
       </c>
       <c r="B316" s="2"/>
-      <c r="C316" s="45">
-        <v>50618</v>
-      </c>
+      <c r="C316" s="45"/>
       <c r="D316" s="2"/>
-      <c r="E316" s="4">
-        <v>99999</v>
-      </c>
-      <c r="F316" s="38"/>
+      <c r="E316" s="4"/>
+      <c r="F316" s="38" t="s">
+        <v>1046</v>
+      </c>
       <c r="G316" s="28">
-        <v>48.186399999999999</v>
+        <v>49.679699999999997</v>
       </c>
       <c r="H316" s="28">
-        <v>118.26139999999999</v>
+        <v>116.81359999999999</v>
       </c>
       <c r="I316" s="2">
-        <v>622</v>
+        <v>710</v>
       </c>
       <c r="J316" s="26">
         <v>12</v>
@@ -27887,9 +27913,9 @@
       <c r="K316" s="30" t="s">
         <v>307</v>
       </c>
-      <c r="L316" s="3"/>
+      <c r="L316" s="2"/>
       <c r="M316" s="14" t="s">
-        <v>1049</v>
+        <v>1047</v>
       </c>
       <c r="N316" s="2"/>
       <c r="O316" s="31"/>
@@ -27901,7 +27927,7 @@
       </c>
       <c r="T316" s="36"/>
       <c r="U316" s="40" t="s">
-        <v>357</v>
+        <v>1048</v>
       </c>
       <c r="V316" s="2" t="s">
         <v>358</v>
@@ -27920,7 +27946,7 @@
         <v>359</v>
       </c>
       <c r="AB316" s="2" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
       <c r="AC316" s="2"/>
       <c r="AD316" s="2"/>
@@ -27931,9 +27957,7 @@
         <v>313</v>
       </c>
       <c r="AG316" s="4"/>
-      <c r="AH316" s="2" t="s">
-        <v>349</v>
-      </c>
+      <c r="AH316" s="2"/>
       <c r="AI316" s="2"/>
     </row>
     <row r="317" spans="1:35" ht="24" customHeight="1" x14ac:dyDescent="0.4">
@@ -27941,22 +27965,32 @@
         <v>316</v>
       </c>
       <c r="B317" s="2"/>
-      <c r="C317" s="45"/>
+      <c r="C317" s="45">
+        <v>50618</v>
+      </c>
       <c r="D317" s="2"/>
-      <c r="E317" s="4"/>
+      <c r="E317" s="4">
+        <v>99999</v>
+      </c>
       <c r="F317" s="38"/>
-      <c r="G317" s="28"/>
-      <c r="H317" s="28"/>
-      <c r="I317" s="2"/>
+      <c r="G317" s="28">
+        <v>48.186399999999999</v>
+      </c>
+      <c r="H317" s="28">
+        <v>118.26139999999999</v>
+      </c>
+      <c r="I317" s="2">
+        <v>622</v>
+      </c>
       <c r="J317" s="26">
         <v>12</v>
       </c>
       <c r="K317" s="30" t="s">
         <v>307</v>
       </c>
-      <c r="L317" s="2"/>
+      <c r="L317" s="3"/>
       <c r="M317" s="14" t="s">
-        <v>1050</v>
+        <v>1049</v>
       </c>
       <c r="N317" s="2"/>
       <c r="O317" s="31"/>
@@ -27968,7 +28002,7 @@
       </c>
       <c r="T317" s="36"/>
       <c r="U317" s="40" t="s">
-        <v>1049</v>
+        <v>357</v>
       </c>
       <c r="V317" s="2" t="s">
         <v>358</v>
@@ -27998,7 +28032,9 @@
         <v>313</v>
       </c>
       <c r="AG317" s="4"/>
-      <c r="AH317" s="2"/>
+      <c r="AH317" s="2" t="s">
+        <v>349</v>
+      </c>
       <c r="AI317" s="2"/>
     </row>
     <row r="318" spans="1:35" ht="24" customHeight="1" x14ac:dyDescent="0.4">
@@ -28009,27 +28045,19 @@
       <c r="C318" s="45"/>
       <c r="D318" s="2"/>
       <c r="E318" s="4"/>
-      <c r="F318" s="38" t="s">
-        <v>1051</v>
-      </c>
-      <c r="G318" s="28">
-        <v>50.637799999999999</v>
-      </c>
-      <c r="H318" s="28">
-        <v>121.5664</v>
-      </c>
-      <c r="I318" s="2">
-        <v>733.8</v>
-      </c>
+      <c r="F318" s="38"/>
+      <c r="G318" s="28"/>
+      <c r="H318" s="28"/>
+      <c r="I318" s="2"/>
       <c r="J318" s="26">
         <v>12</v>
       </c>
       <c r="K318" s="30" t="s">
         <v>307</v>
       </c>
-      <c r="L318" s="3"/>
+      <c r="L318" s="2"/>
       <c r="M318" s="14" t="s">
-        <v>1052</v>
+        <v>1050</v>
       </c>
       <c r="N318" s="2"/>
       <c r="O318" s="31"/>
@@ -28041,7 +28069,7 @@
       </c>
       <c r="T318" s="36"/>
       <c r="U318" s="40" t="s">
-        <v>364</v>
+        <v>1049</v>
       </c>
       <c r="V318" s="2" t="s">
         <v>358</v>
@@ -28060,7 +28088,7 @@
         <v>359</v>
       </c>
       <c r="AB318" s="2" t="s">
-        <v>365</v>
+        <v>1049</v>
       </c>
       <c r="AC318" s="2"/>
       <c r="AD318" s="2"/>
@@ -28071,9 +28099,7 @@
         <v>313</v>
       </c>
       <c r="AG318" s="4"/>
-      <c r="AH318" s="2" t="s">
-        <v>349</v>
-      </c>
+      <c r="AH318" s="2"/>
       <c r="AI318" s="2"/>
     </row>
     <row r="319" spans="1:35" ht="24" customHeight="1" x14ac:dyDescent="0.4">
@@ -28084,19 +28110,27 @@
       <c r="C319" s="45"/>
       <c r="D319" s="2"/>
       <c r="E319" s="4"/>
-      <c r="F319" s="38"/>
-      <c r="G319" s="28"/>
-      <c r="H319" s="28"/>
-      <c r="I319" s="2"/>
+      <c r="F319" s="38" t="s">
+        <v>1051</v>
+      </c>
+      <c r="G319" s="28">
+        <v>50.637799999999999</v>
+      </c>
+      <c r="H319" s="28">
+        <v>121.5664</v>
+      </c>
+      <c r="I319" s="2">
+        <v>733.8</v>
+      </c>
       <c r="J319" s="26">
         <v>12</v>
       </c>
       <c r="K319" s="30" t="s">
         <v>307</v>
       </c>
-      <c r="L319" s="2"/>
+      <c r="L319" s="3"/>
       <c r="M319" s="14" t="s">
-        <v>1053</v>
+        <v>1052</v>
       </c>
       <c r="N319" s="2"/>
       <c r="O319" s="31"/>
@@ -28138,7 +28172,9 @@
         <v>313</v>
       </c>
       <c r="AG319" s="4"/>
-      <c r="AH319" s="2"/>
+      <c r="AH319" s="2" t="s">
+        <v>349</v>
+      </c>
       <c r="AI319" s="2"/>
     </row>
     <row r="320" spans="1:35" ht="24" customHeight="1" x14ac:dyDescent="0.4">
@@ -28149,18 +28185,10 @@
       <c r="C320" s="45"/>
       <c r="D320" s="2"/>
       <c r="E320" s="4"/>
-      <c r="F320" s="38" t="s">
-        <v>1054</v>
-      </c>
-      <c r="G320" s="28">
-        <v>49.072200000000002</v>
-      </c>
-      <c r="H320" s="28">
-        <v>121.6139</v>
-      </c>
-      <c r="I320" s="2">
-        <v>775.4</v>
-      </c>
+      <c r="F320" s="38"/>
+      <c r="G320" s="28"/>
+      <c r="H320" s="28"/>
+      <c r="I320" s="2"/>
       <c r="J320" s="26">
         <v>12</v>
       </c>
@@ -28169,14 +28197,16 @@
       </c>
       <c r="L320" s="2"/>
       <c r="M320" s="14" t="s">
-        <v>1055</v>
+        <v>1053</v>
       </c>
       <c r="N320" s="2"/>
       <c r="O320" s="31"/>
       <c r="P320" s="31"/>
       <c r="Q320" s="31"/>
       <c r="R320" s="50"/>
-      <c r="S320" s="22"/>
+      <c r="S320" s="22" t="s">
+        <v>39</v>
+      </c>
       <c r="T320" s="36"/>
       <c r="U320" s="40" t="s">
         <v>364</v>
@@ -28220,31 +28250,37 @@
       <c r="C321" s="45"/>
       <c r="D321" s="2"/>
       <c r="E321" s="4"/>
-      <c r="F321" s="38"/>
-      <c r="G321" s="28"/>
-      <c r="H321" s="28"/>
-      <c r="I321" s="2"/>
+      <c r="F321" s="38" t="s">
+        <v>1054</v>
+      </c>
+      <c r="G321" s="28">
+        <v>49.072200000000002</v>
+      </c>
+      <c r="H321" s="28">
+        <v>121.6139</v>
+      </c>
+      <c r="I321" s="2">
+        <v>775.4</v>
+      </c>
       <c r="J321" s="26">
         <v>12</v>
       </c>
       <c r="K321" s="30" t="s">
         <v>307</v>
       </c>
-      <c r="L321" s="3"/>
+      <c r="L321" s="2"/>
       <c r="M321" s="14" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
       <c r="N321" s="2"/>
       <c r="O321" s="31"/>
       <c r="P321" s="31"/>
       <c r="Q321" s="31"/>
       <c r="R321" s="50"/>
-      <c r="S321" s="22" t="s">
-        <v>39</v>
-      </c>
+      <c r="S321" s="22"/>
       <c r="T321" s="36"/>
       <c r="U321" s="40" t="s">
-        <v>357</v>
+        <v>364</v>
       </c>
       <c r="V321" s="2" t="s">
         <v>358</v>
@@ -28262,7 +28298,9 @@
       <c r="AA321" s="2" t="s">
         <v>359</v>
       </c>
-      <c r="AB321" s="2"/>
+      <c r="AB321" s="2" t="s">
+        <v>365</v>
+      </c>
       <c r="AC321" s="2"/>
       <c r="AD321" s="2"/>
       <c r="AE321" s="2" t="s">
@@ -28272,9 +28310,7 @@
         <v>313</v>
       </c>
       <c r="AG321" s="4"/>
-      <c r="AH321" s="2" t="s">
-        <v>349</v>
-      </c>
+      <c r="AH321" s="2"/>
       <c r="AI321" s="2"/>
     </row>
     <row r="322" spans="1:35" ht="24" customHeight="1" x14ac:dyDescent="0.4">
@@ -28297,7 +28333,7 @@
       </c>
       <c r="L322" s="3"/>
       <c r="M322" s="14" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
       <c r="N322" s="2"/>
       <c r="O322" s="31"/>
@@ -28360,9 +28396,9 @@
       <c r="K323" s="30" t="s">
         <v>307</v>
       </c>
-      <c r="L323" s="2"/>
+      <c r="L323" s="3"/>
       <c r="M323" s="14" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="N323" s="2"/>
       <c r="O323" s="31"/>
@@ -28402,35 +28438,23 @@
         <v>313</v>
       </c>
       <c r="AG323" s="4"/>
-      <c r="AH323" s="2"/>
+      <c r="AH323" s="2" t="s">
+        <v>349</v>
+      </c>
       <c r="AI323" s="2"/>
     </row>
     <row r="324" spans="1:35" ht="24" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A324" s="2">
         <v>323</v>
       </c>
-      <c r="B324" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="C324" s="45">
-        <v>54012</v>
-      </c>
-      <c r="D324" s="2" t="s">
-        <v>1059</v>
-      </c>
-      <c r="E324" s="4">
-        <v>99999</v>
-      </c>
+      <c r="B324" s="2"/>
+      <c r="C324" s="45"/>
+      <c r="D324" s="2"/>
+      <c r="E324" s="4"/>
       <c r="F324" s="38"/>
-      <c r="G324" s="28">
-        <v>44.57</v>
-      </c>
-      <c r="H324" s="28">
-        <v>117.63</v>
-      </c>
-      <c r="I324" s="2">
-        <v>1001.7</v>
-      </c>
+      <c r="G324" s="28"/>
+      <c r="H324" s="28"/>
+      <c r="I324" s="2"/>
       <c r="J324" s="26">
         <v>12</v>
       </c>
@@ -28439,17 +28463,19 @@
       </c>
       <c r="L324" s="2"/>
       <c r="M324" s="14" t="s">
-        <v>1060</v>
+        <v>1058</v>
       </c>
       <c r="N324" s="2"/>
       <c r="O324" s="31"/>
       <c r="P324" s="31"/>
       <c r="Q324" s="31"/>
       <c r="R324" s="50"/>
-      <c r="S324" s="22"/>
+      <c r="S324" s="22" t="s">
+        <v>39</v>
+      </c>
       <c r="T324" s="36"/>
       <c r="U324" s="40" t="s">
-        <v>981</v>
+        <v>357</v>
       </c>
       <c r="V324" s="2" t="s">
         <v>358</v>
@@ -28465,7 +28491,7 @@
       </c>
       <c r="Z324" s="4"/>
       <c r="AA324" s="2" t="s">
-        <v>1061</v>
+        <v>359</v>
       </c>
       <c r="AB324" s="2"/>
       <c r="AC324" s="2"/>
@@ -28488,23 +28514,23 @@
         <v>35</v>
       </c>
       <c r="C325" s="45">
-        <v>53083</v>
+        <v>54012</v>
       </c>
       <c r="D325" s="2" t="s">
-        <v>1062</v>
+        <v>1059</v>
       </c>
       <c r="E325" s="4">
         <v>99999</v>
       </c>
       <c r="F325" s="38"/>
       <c r="G325" s="28">
-        <v>44.6175</v>
+        <v>44.57</v>
       </c>
       <c r="H325" s="28">
-        <v>114.15219999999999</v>
+        <v>117.63</v>
       </c>
       <c r="I325" s="2">
-        <v>1181.5999999999999</v>
+        <v>1001.7</v>
       </c>
       <c r="J325" s="26">
         <v>12</v>
@@ -28512,9 +28538,9 @@
       <c r="K325" s="30" t="s">
         <v>307</v>
       </c>
-      <c r="L325" s="3"/>
+      <c r="L325" s="2"/>
       <c r="M325" s="14" t="s">
-        <v>1063</v>
+        <v>1060</v>
       </c>
       <c r="N325" s="2"/>
       <c r="O325" s="31"/>
@@ -28524,7 +28550,7 @@
       <c r="S325" s="22"/>
       <c r="T325" s="36"/>
       <c r="U325" s="40" t="s">
-        <v>1064</v>
+        <v>981</v>
       </c>
       <c r="V325" s="2" t="s">
         <v>358</v>
@@ -28540,11 +28566,9 @@
       </c>
       <c r="Z325" s="4"/>
       <c r="AA325" s="2" t="s">
-        <v>1064</v>
-      </c>
-      <c r="AB325" s="2" t="s">
-        <v>1065</v>
-      </c>
+        <v>1061</v>
+      </c>
+      <c r="AB325" s="2"/>
       <c r="AC325" s="2"/>
       <c r="AD325" s="2"/>
       <c r="AE325" s="2" t="s">
@@ -28561,21 +28585,27 @@
       <c r="A326" s="2">
         <v>325</v>
       </c>
-      <c r="B326" s="2"/>
-      <c r="C326" s="45" t="s">
-        <v>1066</v>
-      </c>
-      <c r="D326" s="2"/>
-      <c r="E326" s="4"/>
+      <c r="B326" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C326" s="45">
+        <v>53083</v>
+      </c>
+      <c r="D326" s="2" t="s">
+        <v>1062</v>
+      </c>
+      <c r="E326" s="4">
+        <v>99999</v>
+      </c>
       <c r="F326" s="38"/>
       <c r="G326" s="28">
-        <v>38.808599999999998</v>
+        <v>44.6175</v>
       </c>
       <c r="H326" s="28">
-        <v>98.418099999999995</v>
+        <v>114.15219999999999</v>
       </c>
       <c r="I326" s="2">
-        <v>3364.3</v>
+        <v>1181.5999999999999</v>
       </c>
       <c r="J326" s="26">
         <v>12</v>
@@ -28583,24 +28613,22 @@
       <c r="K326" s="30" t="s">
         <v>307</v>
       </c>
-      <c r="L326" s="2"/>
+      <c r="L326" s="3"/>
       <c r="M326" s="14" t="s">
-        <v>1067</v>
+        <v>1063</v>
       </c>
       <c r="N326" s="2"/>
       <c r="O326" s="31"/>
       <c r="P326" s="31"/>
       <c r="Q326" s="31"/>
       <c r="R326" s="50"/>
-      <c r="S326" s="22" t="s">
-        <v>39</v>
-      </c>
+      <c r="S326" s="22"/>
       <c r="T326" s="36"/>
       <c r="U326" s="40" t="s">
-        <v>440</v>
+        <v>1064</v>
       </c>
       <c r="V326" s="2" t="s">
-        <v>440</v>
+        <v>358</v>
       </c>
       <c r="W326" s="4" t="s">
         <v>39</v>
@@ -28613,10 +28641,10 @@
       </c>
       <c r="Z326" s="4"/>
       <c r="AA326" s="2" t="s">
-        <v>1068</v>
+        <v>1064</v>
       </c>
       <c r="AB326" s="2" t="s">
-        <v>1069</v>
+        <v>1065</v>
       </c>
       <c r="AC326" s="2"/>
       <c r="AD326" s="2"/>
@@ -28627,9 +28655,7 @@
         <v>313</v>
       </c>
       <c r="AG326" s="4"/>
-      <c r="AH326" s="2" t="s">
-        <v>588</v>
-      </c>
+      <c r="AH326" s="2"/>
       <c r="AI326" s="2"/>
     </row>
     <row r="327" spans="1:35" ht="24" customHeight="1" x14ac:dyDescent="0.4">
@@ -28637,22 +28663,20 @@
         <v>326</v>
       </c>
       <c r="B327" s="2"/>
-      <c r="C327" s="45">
-        <v>52645</v>
+      <c r="C327" s="45" t="s">
+        <v>1066</v>
       </c>
       <c r="D327" s="2"/>
-      <c r="E327" s="4">
-        <v>99999</v>
-      </c>
+      <c r="E327" s="4"/>
       <c r="F327" s="38"/>
       <c r="G327" s="28">
-        <v>38.43</v>
+        <v>38.808599999999998</v>
       </c>
       <c r="H327" s="28">
-        <v>99.6</v>
+        <v>98.418099999999995</v>
       </c>
       <c r="I327" s="2">
-        <v>3314</v>
+        <v>3364.3</v>
       </c>
       <c r="J327" s="26">
         <v>12</v>
@@ -28660,9 +28684,9 @@
       <c r="K327" s="30" t="s">
         <v>307</v>
       </c>
-      <c r="L327" s="3"/>
+      <c r="L327" s="2"/>
       <c r="M327" s="14" t="s">
-        <v>1070</v>
+        <v>1067</v>
       </c>
       <c r="N327" s="2"/>
       <c r="O327" s="31"/>
@@ -28714,8 +28738,8 @@
         <v>327</v>
       </c>
       <c r="B328" s="2"/>
-      <c r="C328" s="45" t="s">
-        <v>1071</v>
+      <c r="C328" s="45">
+        <v>52645</v>
       </c>
       <c r="D328" s="2"/>
       <c r="E328" s="4">
@@ -28723,13 +28747,13 @@
       </c>
       <c r="F328" s="38"/>
       <c r="G328" s="28">
-        <v>34.633299999999998</v>
+        <v>38.43</v>
       </c>
       <c r="H328" s="28">
-        <v>92.8553</v>
+        <v>99.6</v>
       </c>
       <c r="I328" s="2">
-        <v>4770</v>
+        <v>3314</v>
       </c>
       <c r="J328" s="26">
         <v>12</v>
@@ -28737,9 +28761,9 @@
       <c r="K328" s="30" t="s">
         <v>307</v>
       </c>
-      <c r="L328" s="2"/>
+      <c r="L328" s="3"/>
       <c r="M328" s="14" t="s">
-        <v>1072</v>
+        <v>1070</v>
       </c>
       <c r="N328" s="2"/>
       <c r="O328" s="31"/>
@@ -28767,10 +28791,10 @@
       </c>
       <c r="Z328" s="4"/>
       <c r="AA328" s="2" t="s">
-        <v>1073</v>
+        <v>1068</v>
       </c>
       <c r="AB328" s="2" t="s">
-        <v>1074</v>
+        <v>1069</v>
       </c>
       <c r="AC328" s="2"/>
       <c r="AD328" s="2"/>
@@ -28791,15 +28815,23 @@
         <v>328</v>
       </c>
       <c r="B329" s="2"/>
-      <c r="C329" s="45"/>
+      <c r="C329" s="45" t="s">
+        <v>1071</v>
+      </c>
       <c r="D329" s="2"/>
-      <c r="E329" s="4"/>
-      <c r="F329" s="38" t="s">
-        <v>1075</v>
-      </c>
-      <c r="G329" s="28"/>
-      <c r="H329" s="28"/>
-      <c r="I329" s="2"/>
+      <c r="E329" s="4">
+        <v>99999</v>
+      </c>
+      <c r="F329" s="38"/>
+      <c r="G329" s="28">
+        <v>34.633299999999998</v>
+      </c>
+      <c r="H329" s="28">
+        <v>92.8553</v>
+      </c>
+      <c r="I329" s="2">
+        <v>4770</v>
+      </c>
       <c r="J329" s="26">
         <v>12</v>
       </c>
@@ -28808,7 +28840,7 @@
       </c>
       <c r="L329" s="2"/>
       <c r="M329" s="14" t="s">
-        <v>1076</v>
+        <v>1072</v>
       </c>
       <c r="N329" s="2"/>
       <c r="O329" s="31"/>
@@ -28836,10 +28868,10 @@
       </c>
       <c r="Z329" s="4"/>
       <c r="AA329" s="2" t="s">
-        <v>590</v>
+        <v>1073</v>
       </c>
       <c r="AB329" s="2" t="s">
-        <v>591</v>
+        <v>1074</v>
       </c>
       <c r="AC329" s="2"/>
       <c r="AD329" s="2"/>
@@ -28853,9 +28885,7 @@
       <c r="AH329" s="2" t="s">
         <v>588</v>
       </c>
-      <c r="AI329" s="2" t="s">
-        <v>1077</v>
-      </c>
+      <c r="AI329" s="2"/>
     </row>
     <row r="330" spans="1:35" ht="24" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A330" s="2">
@@ -28866,26 +28896,20 @@
       <c r="D330" s="2"/>
       <c r="E330" s="4"/>
       <c r="F330" s="38" t="s">
-        <v>1078</v>
-      </c>
-      <c r="G330" s="28">
-        <v>39.788600000000002</v>
-      </c>
-      <c r="H330" s="28">
-        <v>112.82559999999999</v>
-      </c>
-      <c r="I330" s="2">
-        <v>1349</v>
-      </c>
+        <v>1075</v>
+      </c>
+      <c r="G330" s="28"/>
+      <c r="H330" s="28"/>
+      <c r="I330" s="2"/>
       <c r="J330" s="26">
         <v>12</v>
       </c>
       <c r="K330" s="30" t="s">
         <v>307</v>
       </c>
-      <c r="L330" s="3"/>
+      <c r="L330" s="2"/>
       <c r="M330" s="14" t="s">
-        <v>1079</v>
+        <v>1076</v>
       </c>
       <c r="N330" s="2"/>
       <c r="O330" s="31"/>
@@ -28897,10 +28921,10 @@
       </c>
       <c r="T330" s="36"/>
       <c r="U330" s="40" t="s">
-        <v>434</v>
+        <v>440</v>
       </c>
       <c r="V330" s="2" t="s">
-        <v>434</v>
+        <v>440</v>
       </c>
       <c r="W330" s="4" t="s">
         <v>39</v>
@@ -28913,10 +28937,10 @@
       </c>
       <c r="Z330" s="4"/>
       <c r="AA330" s="2" t="s">
-        <v>572</v>
+        <v>590</v>
       </c>
       <c r="AB330" s="2" t="s">
-        <v>1080</v>
+        <v>591</v>
       </c>
       <c r="AC330" s="2"/>
       <c r="AD330" s="2"/>
@@ -28927,30 +28951,32 @@
         <v>313</v>
       </c>
       <c r="AG330" s="4"/>
-      <c r="AH330" s="2"/>
-      <c r="AI330" s="2"/>
+      <c r="AH330" s="2" t="s">
+        <v>588</v>
+      </c>
+      <c r="AI330" s="2" t="s">
+        <v>1077</v>
+      </c>
     </row>
     <row r="331" spans="1:35" ht="24" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A331" s="2">
         <v>330</v>
       </c>
       <c r="B331" s="2"/>
-      <c r="C331" s="45" t="s">
-        <v>1081</v>
-      </c>
+      <c r="C331" s="45"/>
       <c r="D331" s="2"/>
-      <c r="E331" s="4">
-        <v>99999</v>
-      </c>
-      <c r="F331" s="38"/>
+      <c r="E331" s="4"/>
+      <c r="F331" s="38" t="s">
+        <v>1078</v>
+      </c>
       <c r="G331" s="28">
-        <v>32.976399999999998</v>
+        <v>39.788600000000002</v>
       </c>
       <c r="H331" s="28">
-        <v>98.096900000000005</v>
+        <v>112.82559999999999</v>
       </c>
       <c r="I331" s="2">
-        <v>4181.2</v>
+        <v>1349</v>
       </c>
       <c r="J331" s="26">
         <v>12</v>
@@ -28958,26 +28984,24 @@
       <c r="K331" s="30" t="s">
         <v>307</v>
       </c>
-      <c r="L331" s="2"/>
+      <c r="L331" s="3"/>
       <c r="M331" s="14" t="s">
-        <v>1082</v>
+        <v>1079</v>
       </c>
       <c r="N331" s="2"/>
       <c r="O331" s="31"/>
       <c r="P331" s="31"/>
       <c r="Q331" s="31"/>
-      <c r="R331" s="50" t="s">
-        <v>1083</v>
-      </c>
+      <c r="R331" s="50"/>
       <c r="S331" s="22" t="s">
         <v>39</v>
       </c>
       <c r="T331" s="36"/>
       <c r="U331" s="40" t="s">
-        <v>689</v>
+        <v>434</v>
       </c>
       <c r="V331" s="2" t="s">
-        <v>552</v>
+        <v>434</v>
       </c>
       <c r="W331" s="4" t="s">
         <v>39</v>
@@ -28990,10 +29014,10 @@
       </c>
       <c r="Z331" s="4"/>
       <c r="AA331" s="2" t="s">
-        <v>1084</v>
+        <v>572</v>
       </c>
       <c r="AB331" s="2" t="s">
-        <v>691</v>
+        <v>1080</v>
       </c>
       <c r="AC331" s="2"/>
       <c r="AD331" s="2"/>
@@ -29004,9 +29028,7 @@
         <v>313</v>
       </c>
       <c r="AG331" s="4"/>
-      <c r="AH331" s="2" t="s">
-        <v>588</v>
-      </c>
+      <c r="AH331" s="2"/>
       <c r="AI331" s="2"/>
     </row>
     <row r="332" spans="1:35" ht="24" customHeight="1" x14ac:dyDescent="0.4">
@@ -29014,24 +29036,22 @@
         <v>331</v>
       </c>
       <c r="B332" s="2"/>
-      <c r="C332" s="45">
-        <v>58968</v>
-      </c>
-      <c r="D332" s="2" t="s">
-        <v>1085</v>
-      </c>
+      <c r="C332" s="45" t="s">
+        <v>1081</v>
+      </c>
+      <c r="D332" s="2"/>
       <c r="E332" s="4">
         <v>99999</v>
       </c>
       <c r="F332" s="38"/>
       <c r="G332" s="28">
-        <v>25.033333299999999</v>
+        <v>32.976399999999998</v>
       </c>
       <c r="H332" s="28">
-        <v>121.51666659999999</v>
+        <v>98.096900000000005</v>
       </c>
       <c r="I332" s="2">
-        <v>9</v>
+        <v>4181.2</v>
       </c>
       <c r="J332" s="26">
         <v>12</v>
@@ -29039,24 +29059,30 @@
       <c r="K332" s="30" t="s">
         <v>307</v>
       </c>
-      <c r="L332" s="3"/>
+      <c r="L332" s="2"/>
       <c r="M332" s="14" t="s">
-        <v>1086</v>
+        <v>1082</v>
       </c>
       <c r="N332" s="2"/>
       <c r="O332" s="31"/>
       <c r="P332" s="31"/>
       <c r="Q332" s="31"/>
-      <c r="R332" s="50"/>
-      <c r="S332" s="22"/>
+      <c r="R332" s="50" t="s">
+        <v>1083</v>
+      </c>
+      <c r="S332" s="22" t="s">
+        <v>39</v>
+      </c>
       <c r="T332" s="36"/>
       <c r="U332" s="40" t="s">
-        <v>1087</v>
+        <v>689</v>
       </c>
       <c r="V332" s="2" t="s">
-        <v>1087</v>
-      </c>
-      <c r="W332" s="4"/>
+        <v>552</v>
+      </c>
+      <c r="W332" s="4" t="s">
+        <v>39</v>
+      </c>
       <c r="X332" s="4" t="s">
         <v>39</v>
       </c>
@@ -29064,8 +29090,12 @@
         <v>39</v>
       </c>
       <c r="Z332" s="4"/>
-      <c r="AA332" s="2"/>
-      <c r="AB332" s="2"/>
+      <c r="AA332" s="2" t="s">
+        <v>1084</v>
+      </c>
+      <c r="AB332" s="2" t="s">
+        <v>691</v>
+      </c>
       <c r="AC332" s="2"/>
       <c r="AD332" s="2"/>
       <c r="AE332" s="2" t="s">
@@ -29075,7 +29105,9 @@
         <v>313</v>
       </c>
       <c r="AG332" s="4"/>
-      <c r="AH332" s="2"/>
+      <c r="AH332" s="2" t="s">
+        <v>588</v>
+      </c>
       <c r="AI332" s="2"/>
     </row>
     <row r="333" spans="1:35" ht="24" customHeight="1" x14ac:dyDescent="0.4">
@@ -29083,24 +29115,34 @@
         <v>332</v>
       </c>
       <c r="B333" s="2"/>
-      <c r="C333" s="45"/>
-      <c r="D333" s="2"/>
-      <c r="E333" s="4"/>
-      <c r="F333" s="38" t="s">
-        <v>1088</v>
-      </c>
-      <c r="G333" s="28"/>
-      <c r="H333" s="28"/>
-      <c r="I333" s="2"/>
+      <c r="C333" s="45">
+        <v>58968</v>
+      </c>
+      <c r="D333" s="2" t="s">
+        <v>1085</v>
+      </c>
+      <c r="E333" s="4">
+        <v>99999</v>
+      </c>
+      <c r="F333" s="38"/>
+      <c r="G333" s="28">
+        <v>25.033333299999999</v>
+      </c>
+      <c r="H333" s="28">
+        <v>121.51666659999999</v>
+      </c>
+      <c r="I333" s="2">
+        <v>9</v>
+      </c>
       <c r="J333" s="26">
         <v>12</v>
       </c>
       <c r="K333" s="30" t="s">
         <v>307</v>
       </c>
-      <c r="L333" s="2"/>
+      <c r="L333" s="3"/>
       <c r="M333" s="14" t="s">
-        <v>1089</v>
+        <v>1086</v>
       </c>
       <c r="N333" s="2"/>
       <c r="O333" s="31"/>
@@ -29110,14 +29152,12 @@
       <c r="S333" s="22"/>
       <c r="T333" s="36"/>
       <c r="U333" s="40" t="s">
-        <v>564</v>
+        <v>1087</v>
       </c>
       <c r="V333" s="2" t="s">
-        <v>564</v>
-      </c>
-      <c r="W333" s="4" t="s">
-        <v>39</v>
-      </c>
+        <v>1087</v>
+      </c>
+      <c r="W333" s="4"/>
       <c r="X333" s="4" t="s">
         <v>39</v>
       </c>
@@ -29125,12 +29165,8 @@
         <v>39</v>
       </c>
       <c r="Z333" s="4"/>
-      <c r="AA333" s="2" t="s">
-        <v>1090</v>
-      </c>
-      <c r="AB333" s="2" t="s">
-        <v>1091</v>
-      </c>
+      <c r="AA333" s="2"/>
+      <c r="AB333" s="2"/>
       <c r="AC333" s="2"/>
       <c r="AD333" s="2"/>
       <c r="AE333" s="2" t="s">
@@ -29152,17 +29188,11 @@
       <c r="D334" s="2"/>
       <c r="E334" s="4"/>
       <c r="F334" s="38" t="s">
-        <v>1092</v>
-      </c>
-      <c r="G334" s="28">
-        <v>31.095800000000001</v>
-      </c>
-      <c r="H334" s="28">
-        <v>81.369699999999995</v>
-      </c>
-      <c r="I334" s="2">
-        <v>5642</v>
-      </c>
+        <v>1088</v>
+      </c>
+      <c r="G334" s="28"/>
+      <c r="H334" s="28"/>
+      <c r="I334" s="2"/>
       <c r="J334" s="26">
         <v>12</v>
       </c>
@@ -29171,7 +29201,7 @@
       </c>
       <c r="L334" s="2"/>
       <c r="M334" s="14" t="s">
-        <v>1093</v>
+        <v>1089</v>
       </c>
       <c r="N334" s="2"/>
       <c r="O334" s="31"/>
@@ -29200,7 +29230,7 @@
         <v>1090</v>
       </c>
       <c r="AB334" s="2" t="s">
-        <v>1094</v>
+        <v>1091</v>
       </c>
       <c r="AC334" s="2"/>
       <c r="AD334" s="2"/>
@@ -29223,11 +29253,17 @@
       <c r="D335" s="2"/>
       <c r="E335" s="4"/>
       <c r="F335" s="38" t="s">
-        <v>1095</v>
-      </c>
-      <c r="G335" s="28"/>
-      <c r="H335" s="28"/>
-      <c r="I335" s="2"/>
+        <v>1092</v>
+      </c>
+      <c r="G335" s="28">
+        <v>31.095800000000001</v>
+      </c>
+      <c r="H335" s="28">
+        <v>81.369699999999995</v>
+      </c>
+      <c r="I335" s="2">
+        <v>5642</v>
+      </c>
       <c r="J335" s="26">
         <v>12</v>
       </c>
@@ -29236,7 +29272,7 @@
       </c>
       <c r="L335" s="2"/>
       <c r="M335" s="14" t="s">
-        <v>1096</v>
+        <v>1093</v>
       </c>
       <c r="N335" s="2"/>
       <c r="O335" s="31"/>
@@ -29284,23 +29320,15 @@
         <v>335</v>
       </c>
       <c r="B336" s="2"/>
-      <c r="C336" s="45" t="s">
-        <v>1097</v>
-      </c>
+      <c r="C336" s="45"/>
       <c r="D336" s="2"/>
-      <c r="E336" s="4">
-        <v>99999</v>
-      </c>
-      <c r="F336" s="38"/>
-      <c r="G336" s="28">
-        <v>34.426400000000001</v>
-      </c>
-      <c r="H336" s="28">
-        <v>80.386099999999999</v>
-      </c>
-      <c r="I336" s="2">
-        <v>5188.6000000000004</v>
-      </c>
+      <c r="E336" s="4"/>
+      <c r="F336" s="38" t="s">
+        <v>1095</v>
+      </c>
+      <c r="G336" s="28"/>
+      <c r="H336" s="28"/>
+      <c r="I336" s="2"/>
       <c r="J336" s="26">
         <v>12</v>
       </c>
@@ -29309,7 +29337,7 @@
       </c>
       <c r="L336" s="2"/>
       <c r="M336" s="14" t="s">
-        <v>1098</v>
+        <v>1096</v>
       </c>
       <c r="N336" s="2"/>
       <c r="O336" s="31"/>
@@ -29334,8 +29362,12 @@
         <v>39</v>
       </c>
       <c r="Z336" s="4"/>
-      <c r="AA336" s="2"/>
-      <c r="AB336" s="2"/>
+      <c r="AA336" s="2" t="s">
+        <v>1090</v>
+      </c>
+      <c r="AB336" s="2" t="s">
+        <v>1094</v>
+      </c>
       <c r="AC336" s="2"/>
       <c r="AD336" s="2"/>
       <c r="AE336" s="2" t="s">
@@ -29353,24 +29385,22 @@
         <v>336</v>
       </c>
       <c r="B337" s="2"/>
-      <c r="C337" s="45">
-        <v>45007</v>
-      </c>
-      <c r="D337" s="2" t="s">
-        <v>1099</v>
-      </c>
+      <c r="C337" s="45" t="s">
+        <v>1097</v>
+      </c>
+      <c r="D337" s="2"/>
       <c r="E337" s="4">
         <v>99999</v>
       </c>
       <c r="F337" s="38"/>
       <c r="G337" s="28">
-        <v>22.308918999999999</v>
+        <v>34.426400000000001</v>
       </c>
       <c r="H337" s="28">
-        <v>113.914603</v>
+        <v>80.386099999999999</v>
       </c>
       <c r="I337" s="2">
-        <v>8.5299999999999994</v>
+        <v>5188.6000000000004</v>
       </c>
       <c r="J337" s="26">
         <v>12</v>
@@ -29378,9 +29408,9 @@
       <c r="K337" s="30" t="s">
         <v>307</v>
       </c>
-      <c r="L337" s="3"/>
+      <c r="L337" s="2"/>
       <c r="M337" s="14" t="s">
-        <v>1100</v>
+        <v>1098</v>
       </c>
       <c r="N337" s="2"/>
       <c r="O337" s="31"/>
@@ -29389,11 +29419,15 @@
       <c r="R337" s="50"/>
       <c r="S337" s="22"/>
       <c r="T337" s="36"/>
-      <c r="U337" s="40"/>
+      <c r="U337" s="40" t="s">
+        <v>564</v>
+      </c>
       <c r="V337" s="2" t="s">
-        <v>1100</v>
-      </c>
-      <c r="W337" s="4"/>
+        <v>564</v>
+      </c>
+      <c r="W337" s="4" t="s">
+        <v>39</v>
+      </c>
       <c r="X337" s="4" t="s">
         <v>39</v>
       </c>
@@ -29420,20 +29454,24 @@
         <v>337</v>
       </c>
       <c r="B338" s="2"/>
-      <c r="C338" s="45"/>
-      <c r="D338" s="2"/>
-      <c r="E338" s="4"/>
-      <c r="F338" s="38" t="s">
-        <v>1101</v>
-      </c>
+      <c r="C338" s="45">
+        <v>45007</v>
+      </c>
+      <c r="D338" s="2" t="s">
+        <v>1099</v>
+      </c>
+      <c r="E338" s="4">
+        <v>99999</v>
+      </c>
+      <c r="F338" s="38"/>
       <c r="G338" s="28">
-        <v>48.0197</v>
+        <v>22.308918999999999</v>
       </c>
       <c r="H338" s="28">
-        <v>87.551699999999997</v>
+        <v>113.914603</v>
       </c>
       <c r="I338" s="2">
-        <v>1194</v>
+        <v>8.5299999999999994</v>
       </c>
       <c r="J338" s="26">
         <v>12</v>
@@ -29441,28 +29479,22 @@
       <c r="K338" s="30" t="s">
         <v>307</v>
       </c>
-      <c r="L338" s="2"/>
+      <c r="L338" s="3"/>
       <c r="M338" s="14" t="s">
-        <v>1102</v>
+        <v>1100</v>
       </c>
       <c r="N338" s="2"/>
       <c r="O338" s="31"/>
       <c r="P338" s="31"/>
       <c r="Q338" s="31"/>
       <c r="R338" s="50"/>
-      <c r="S338" s="22" t="s">
-        <v>39</v>
-      </c>
+      <c r="S338" s="22"/>
       <c r="T338" s="36"/>
-      <c r="U338" s="40" t="s">
-        <v>121</v>
-      </c>
+      <c r="U338" s="40"/>
       <c r="V338" s="2" t="s">
-        <v>392</v>
-      </c>
-      <c r="W338" s="4" t="s">
-        <v>39</v>
-      </c>
+        <v>1100</v>
+      </c>
+      <c r="W338" s="4"/>
       <c r="X338" s="4" t="s">
         <v>39</v>
       </c>
@@ -29470,12 +29502,8 @@
         <v>39</v>
       </c>
       <c r="Z338" s="4"/>
-      <c r="AA338" s="2" t="s">
-        <v>397</v>
-      </c>
-      <c r="AB338" s="2" t="s">
-        <v>402</v>
-      </c>
+      <c r="AA338" s="2"/>
+      <c r="AB338" s="2"/>
       <c r="AC338" s="2"/>
       <c r="AD338" s="2"/>
       <c r="AE338" s="2" t="s">
@@ -29485,9 +29513,7 @@
         <v>313</v>
       </c>
       <c r="AG338" s="4"/>
-      <c r="AH338" s="2" t="s">
-        <v>121</v>
-      </c>
+      <c r="AH338" s="2"/>
       <c r="AI338" s="2"/>
     </row>
     <row r="339" spans="1:35" ht="24" customHeight="1" x14ac:dyDescent="0.4">
@@ -29499,16 +29525,16 @@
       <c r="D339" s="2"/>
       <c r="E339" s="4"/>
       <c r="F339" s="38" t="s">
-        <v>1103</v>
+        <v>1101</v>
       </c>
       <c r="G339" s="28">
-        <v>48.721699999999998</v>
+        <v>48.0197</v>
       </c>
       <c r="H339" s="28">
-        <v>87.030600000000007</v>
+        <v>87.551699999999997</v>
       </c>
       <c r="I339" s="2">
-        <v>1367</v>
+        <v>1194</v>
       </c>
       <c r="J339" s="26">
         <v>12</v>
@@ -29516,9 +29542,9 @@
       <c r="K339" s="30" t="s">
         <v>307</v>
       </c>
-      <c r="L339" s="3"/>
+      <c r="L339" s="2"/>
       <c r="M339" s="14" t="s">
-        <v>1104</v>
+        <v>1102</v>
       </c>
       <c r="N339" s="2"/>
       <c r="O339" s="31"/>
@@ -29549,11 +29575,9 @@
         <v>397</v>
       </c>
       <c r="AB339" s="2" t="s">
-        <v>1105</v>
-      </c>
-      <c r="AC339" s="2" t="s">
-        <v>1106</v>
-      </c>
+        <v>402</v>
+      </c>
+      <c r="AC339" s="2"/>
       <c r="AD339" s="2"/>
       <c r="AE339" s="2" t="s">
         <v>312</v>
@@ -29565,9 +29589,7 @@
       <c r="AH339" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="AI339" s="2" t="s">
-        <v>637</v>
-      </c>
+      <c r="AI339" s="2"/>
     </row>
     <row r="340" spans="1:35" ht="24" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A340" s="2">
@@ -29578,16 +29600,16 @@
       <c r="D340" s="2"/>
       <c r="E340" s="4"/>
       <c r="F340" s="38" t="s">
-        <v>1107</v>
+        <v>1103</v>
       </c>
       <c r="G340" s="28">
-        <v>48.584200000000003</v>
+        <v>48.721699999999998</v>
       </c>
       <c r="H340" s="28">
-        <v>87.457800000000006</v>
+        <v>87.030600000000007</v>
       </c>
       <c r="I340" s="2">
-        <v>1223</v>
+        <v>1367</v>
       </c>
       <c r="J340" s="26">
         <v>12</v>
@@ -29597,11 +29619,9 @@
       </c>
       <c r="L340" s="3"/>
       <c r="M340" s="14" t="s">
-        <v>1108</v>
-      </c>
-      <c r="N340" s="23" t="s">
-        <v>1109</v>
-      </c>
+        <v>1104</v>
+      </c>
+      <c r="N340" s="2"/>
       <c r="O340" s="31"/>
       <c r="P340" s="31"/>
       <c r="Q340" s="31"/>
@@ -29646,29 +29666,29 @@
       <c r="AH340" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="AI340" s="2"/>
+      <c r="AI340" s="2" t="s">
+        <v>637</v>
+      </c>
     </row>
     <row r="341" spans="1:35" ht="24" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A341" s="2">
         <v>340</v>
       </c>
       <c r="B341" s="2"/>
-      <c r="C341" s="45">
-        <v>51068</v>
-      </c>
+      <c r="C341" s="45"/>
       <c r="D341" s="2"/>
-      <c r="E341" s="4">
-        <v>99999</v>
-      </c>
-      <c r="F341" s="38"/>
+      <c r="E341" s="4"/>
+      <c r="F341" s="38" t="s">
+        <v>1107</v>
+      </c>
       <c r="G341" s="28">
-        <v>47.125</v>
+        <v>48.584200000000003</v>
       </c>
       <c r="H341" s="28">
-        <v>87.481399999999994</v>
+        <v>87.457800000000006</v>
       </c>
       <c r="I341" s="2">
-        <v>497.1</v>
+        <v>1223</v>
       </c>
       <c r="J341" s="26">
         <v>12</v>
@@ -29676,11 +29696,13 @@
       <c r="K341" s="30" t="s">
         <v>307</v>
       </c>
-      <c r="L341" s="2"/>
+      <c r="L341" s="3"/>
       <c r="M341" s="14" t="s">
-        <v>1110</v>
-      </c>
-      <c r="N341" s="2"/>
+        <v>1108</v>
+      </c>
+      <c r="N341" s="23" t="s">
+        <v>1109</v>
+      </c>
       <c r="O341" s="31"/>
       <c r="P341" s="31"/>
       <c r="Q341" s="31"/>
@@ -29690,7 +29712,7 @@
       </c>
       <c r="T341" s="36"/>
       <c r="U341" s="40" t="s">
-        <v>1111</v>
+        <v>121</v>
       </c>
       <c r="V341" s="2" t="s">
         <v>392</v>
@@ -29709,9 +29731,11 @@
         <v>397</v>
       </c>
       <c r="AB341" s="2" t="s">
-        <v>1112</v>
-      </c>
-      <c r="AC341" s="2"/>
+        <v>1105</v>
+      </c>
+      <c r="AC341" s="2" t="s">
+        <v>1106</v>
+      </c>
       <c r="AD341" s="2"/>
       <c r="AE341" s="2" t="s">
         <v>312</v>
@@ -29721,7 +29745,7 @@
       </c>
       <c r="AG341" s="4"/>
       <c r="AH341" s="2" t="s">
-        <v>1111</v>
+        <v>121</v>
       </c>
       <c r="AI341" s="2"/>
     </row>
@@ -29730,20 +29754,22 @@
         <v>341</v>
       </c>
       <c r="B342" s="2"/>
-      <c r="C342" s="45"/>
+      <c r="C342" s="45">
+        <v>51068</v>
+      </c>
       <c r="D342" s="2"/>
-      <c r="E342" s="4"/>
-      <c r="F342" s="38" t="s">
-        <v>1113</v>
-      </c>
+      <c r="E342" s="4">
+        <v>99999</v>
+      </c>
+      <c r="F342" s="38"/>
       <c r="G342" s="28">
-        <v>47.168100000000003</v>
+        <v>47.125</v>
       </c>
       <c r="H342" s="28">
-        <v>90.090299999999999</v>
+        <v>87.481399999999994</v>
       </c>
       <c r="I342" s="2">
-        <v>3084</v>
+        <v>497.1</v>
       </c>
       <c r="J342" s="26">
         <v>12</v>
@@ -29751,13 +29777,11 @@
       <c r="K342" s="30" t="s">
         <v>307</v>
       </c>
-      <c r="L342" s="3"/>
+      <c r="L342" s="2"/>
       <c r="M342" s="14" t="s">
-        <v>1114</v>
-      </c>
-      <c r="N342" s="23" t="s">
-        <v>101</v>
-      </c>
+        <v>1110</v>
+      </c>
+      <c r="N342" s="2"/>
       <c r="O342" s="31"/>
       <c r="P342" s="31"/>
       <c r="Q342" s="31"/>
@@ -29767,7 +29791,7 @@
       </c>
       <c r="T342" s="36"/>
       <c r="U342" s="40" t="s">
-        <v>121</v>
+        <v>1111</v>
       </c>
       <c r="V342" s="2" t="s">
         <v>392</v>
@@ -29786,7 +29810,7 @@
         <v>397</v>
       </c>
       <c r="AB342" s="2" t="s">
-        <v>718</v>
+        <v>1112</v>
       </c>
       <c r="AC342" s="2"/>
       <c r="AD342" s="2"/>
@@ -29798,11 +29822,9 @@
       </c>
       <c r="AG342" s="4"/>
       <c r="AH342" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="AI342" s="2" t="s">
-        <v>637</v>
-      </c>
+        <v>1111</v>
+      </c>
+      <c r="AI342" s="2"/>
     </row>
     <row r="343" spans="1:35" ht="24" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A343" s="2">
@@ -29813,16 +29835,16 @@
       <c r="D343" s="2"/>
       <c r="E343" s="4"/>
       <c r="F343" s="38" t="s">
-        <v>1115</v>
+        <v>1113</v>
       </c>
       <c r="G343" s="28">
-        <v>47.138100000000001</v>
+        <v>47.168100000000003</v>
       </c>
       <c r="H343" s="28">
-        <v>85.597499999999997</v>
+        <v>90.090299999999999</v>
       </c>
       <c r="I343" s="2">
-        <v>2914</v>
+        <v>3084</v>
       </c>
       <c r="J343" s="26">
         <v>12</v>
@@ -29830,11 +29852,13 @@
       <c r="K343" s="30" t="s">
         <v>307</v>
       </c>
-      <c r="L343" s="2"/>
+      <c r="L343" s="3"/>
       <c r="M343" s="14" t="s">
-        <v>1116</v>
-      </c>
-      <c r="N343" s="23"/>
+        <v>1114</v>
+      </c>
+      <c r="N343" s="23" t="s">
+        <v>101</v>
+      </c>
       <c r="O343" s="31"/>
       <c r="P343" s="31"/>
       <c r="Q343" s="31"/>
@@ -29844,7 +29868,7 @@
       </c>
       <c r="T343" s="36"/>
       <c r="U343" s="40" t="s">
-        <v>400</v>
+        <v>121</v>
       </c>
       <c r="V343" s="2" t="s">
         <v>392</v>
@@ -29863,7 +29887,7 @@
         <v>397</v>
       </c>
       <c r="AB343" s="2" t="s">
-        <v>1117</v>
+        <v>718</v>
       </c>
       <c r="AC343" s="2"/>
       <c r="AD343" s="2"/>
@@ -29874,8 +29898,12 @@
         <v>313</v>
       </c>
       <c r="AG343" s="4"/>
-      <c r="AH343" s="2"/>
-      <c r="AI343" s="2"/>
+      <c r="AH343" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="AI343" s="2" t="s">
+        <v>637</v>
+      </c>
     </row>
     <row r="344" spans="1:35" ht="24" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A344" s="2">
@@ -29886,16 +29914,16 @@
       <c r="D344" s="2"/>
       <c r="E344" s="4"/>
       <c r="F344" s="38" t="s">
-        <v>1118</v>
+        <v>1115</v>
       </c>
       <c r="G344" s="28">
-        <v>46.177199999999999</v>
+        <v>47.138100000000001</v>
       </c>
       <c r="H344" s="28">
-        <v>90.535600000000002</v>
+        <v>85.597499999999997</v>
       </c>
       <c r="I344" s="2">
-        <v>1071.0999999999999</v>
+        <v>2914</v>
       </c>
       <c r="J344" s="26">
         <v>12</v>
@@ -29905,9 +29933,9 @@
       </c>
       <c r="L344" s="2"/>
       <c r="M344" s="14" t="s">
-        <v>1119</v>
-      </c>
-      <c r="N344" s="2"/>
+        <v>1116</v>
+      </c>
+      <c r="N344" s="23"/>
       <c r="O344" s="31"/>
       <c r="P344" s="31"/>
       <c r="Q344" s="31"/>
@@ -29917,7 +29945,7 @@
       </c>
       <c r="T344" s="36"/>
       <c r="U344" s="40" t="s">
-        <v>121</v>
+        <v>400</v>
       </c>
       <c r="V344" s="2" t="s">
         <v>392</v>
@@ -29936,7 +29964,7 @@
         <v>397</v>
       </c>
       <c r="AB344" s="2" t="s">
-        <v>398</v>
+        <v>1117</v>
       </c>
       <c r="AC344" s="2"/>
       <c r="AD344" s="2"/>
@@ -29947,36 +29975,28 @@
         <v>313</v>
       </c>
       <c r="AG344" s="4"/>
-      <c r="AH344" s="2" t="s">
-        <v>121</v>
-      </c>
+      <c r="AH344" s="2"/>
       <c r="AI344" s="2"/>
     </row>
     <row r="345" spans="1:35" ht="24" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A345" s="2">
         <v>344</v>
       </c>
-      <c r="B345" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="C345" s="45">
-        <v>51087</v>
-      </c>
-      <c r="D345" s="2" t="s">
-        <v>1120</v>
-      </c>
-      <c r="E345" s="4">
-        <v>99999</v>
-      </c>
-      <c r="F345" s="38"/>
+      <c r="B345" s="2"/>
+      <c r="C345" s="45"/>
+      <c r="D345" s="2"/>
+      <c r="E345" s="4"/>
+      <c r="F345" s="38" t="s">
+        <v>1118</v>
+      </c>
       <c r="G345" s="28">
-        <v>47.02</v>
+        <v>46.177199999999999</v>
       </c>
       <c r="H345" s="28">
-        <v>89.5</v>
+        <v>90.535600000000002</v>
       </c>
       <c r="I345" s="2">
-        <v>860.4</v>
+        <v>1071.0999999999999</v>
       </c>
       <c r="J345" s="26">
         <v>12</v>
@@ -29986,17 +30006,19 @@
       </c>
       <c r="L345" s="2"/>
       <c r="M345" s="14" t="s">
-        <v>1121</v>
+        <v>1119</v>
       </c>
       <c r="N345" s="2"/>
       <c r="O345" s="31"/>
       <c r="P345" s="31"/>
       <c r="Q345" s="31"/>
       <c r="R345" s="50"/>
-      <c r="S345" s="22"/>
+      <c r="S345" s="22" t="s">
+        <v>39</v>
+      </c>
       <c r="T345" s="36"/>
       <c r="U345" s="40" t="s">
-        <v>1122</v>
+        <v>121</v>
       </c>
       <c r="V345" s="2" t="s">
         <v>392</v>
@@ -30014,7 +30036,9 @@
       <c r="AA345" s="2" t="s">
         <v>397</v>
       </c>
-      <c r="AB345" s="2"/>
+      <c r="AB345" s="2" t="s">
+        <v>398</v>
+      </c>
       <c r="AC345" s="2"/>
       <c r="AD345" s="2"/>
       <c r="AE345" s="2" t="s">
@@ -30033,16 +30057,28 @@
       <c r="A346" s="2">
         <v>345</v>
       </c>
-      <c r="B346" s="2"/>
+      <c r="B346" s="2" t="s">
+        <v>35</v>
+      </c>
       <c r="C346" s="45">
-        <v>51058</v>
-      </c>
-      <c r="D346" s="2"/>
-      <c r="E346" s="4"/>
+        <v>51087</v>
+      </c>
+      <c r="D346" s="2" t="s">
+        <v>1120</v>
+      </c>
+      <c r="E346" s="4">
+        <v>99999</v>
+      </c>
       <c r="F346" s="38"/>
-      <c r="G346" s="28"/>
-      <c r="H346" s="28"/>
-      <c r="I346" s="2"/>
+      <c r="G346" s="28">
+        <v>47.02</v>
+      </c>
+      <c r="H346" s="28">
+        <v>89.5</v>
+      </c>
+      <c r="I346" s="2">
+        <v>860.4</v>
+      </c>
       <c r="J346" s="26">
         <v>12</v>
       </c>
@@ -30051,19 +30087,17 @@
       </c>
       <c r="L346" s="2"/>
       <c r="M346" s="14" t="s">
-        <v>1123</v>
+        <v>1121</v>
       </c>
       <c r="N346" s="2"/>
       <c r="O346" s="31"/>
       <c r="P346" s="31"/>
       <c r="Q346" s="31"/>
       <c r="R346" s="50"/>
-      <c r="S346" s="22" t="s">
-        <v>39</v>
-      </c>
+      <c r="S346" s="22"/>
       <c r="T346" s="36"/>
       <c r="U346" s="40" t="s">
-        <v>1111</v>
+        <v>1122</v>
       </c>
       <c r="V346" s="2" t="s">
         <v>392</v>
@@ -30091,7 +30125,9 @@
         <v>313</v>
       </c>
       <c r="AG346" s="4"/>
-      <c r="AH346" s="2"/>
+      <c r="AH346" s="2" t="s">
+        <v>121</v>
+      </c>
       <c r="AI346" s="2"/>
     </row>
     <row r="347" spans="1:35" ht="24" customHeight="1" x14ac:dyDescent="0.4">
@@ -30100,22 +30136,14 @@
       </c>
       <c r="B347" s="2"/>
       <c r="C347" s="45">
-        <v>51060</v>
+        <v>51058</v>
       </c>
       <c r="D347" s="2"/>
-      <c r="E347" s="4">
-        <v>99999</v>
-      </c>
+      <c r="E347" s="4"/>
       <c r="F347" s="38"/>
-      <c r="G347" s="28">
-        <v>47.7</v>
-      </c>
-      <c r="H347" s="28">
-        <v>86.87</v>
-      </c>
-      <c r="I347" s="2">
-        <v>473.9</v>
-      </c>
+      <c r="G347" s="28"/>
+      <c r="H347" s="28"/>
+      <c r="I347" s="2"/>
       <c r="J347" s="26">
         <v>12</v>
       </c>
@@ -30124,17 +30152,19 @@
       </c>
       <c r="L347" s="2"/>
       <c r="M347" s="14" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="N347" s="2"/>
       <c r="O347" s="31"/>
       <c r="P347" s="31"/>
       <c r="Q347" s="31"/>
       <c r="R347" s="50"/>
-      <c r="S347" s="22"/>
+      <c r="S347" s="22" t="s">
+        <v>39</v>
+      </c>
       <c r="T347" s="36"/>
       <c r="U347" s="40" t="s">
-        <v>1125</v>
+        <v>1111</v>
       </c>
       <c r="V347" s="2" t="s">
         <v>392</v>
@@ -30162,9 +30192,7 @@
         <v>313</v>
       </c>
       <c r="AG347" s="4"/>
-      <c r="AH347" s="2" t="s">
-        <v>1125</v>
-      </c>
+      <c r="AH347" s="2"/>
       <c r="AI347" s="2"/>
     </row>
     <row r="348" spans="1:35" ht="24" customHeight="1" x14ac:dyDescent="0.4">
@@ -30172,20 +30200,22 @@
         <v>347</v>
       </c>
       <c r="B348" s="2"/>
-      <c r="C348" s="45"/>
+      <c r="C348" s="45">
+        <v>51060</v>
+      </c>
       <c r="D348" s="2"/>
-      <c r="E348" s="4"/>
-      <c r="F348" s="38" t="s">
-        <v>1126</v>
-      </c>
+      <c r="E348" s="4">
+        <v>99999</v>
+      </c>
+      <c r="F348" s="38"/>
       <c r="G348" s="28">
-        <v>42.716000000000001</v>
+        <v>47.7</v>
       </c>
       <c r="H348" s="28">
-        <v>84.272000000000006</v>
+        <v>86.87</v>
       </c>
       <c r="I348" s="2">
-        <v>2404.3000000000002</v>
+        <v>473.9</v>
       </c>
       <c r="J348" s="26">
         <v>12</v>
@@ -30195,7 +30225,7 @@
       </c>
       <c r="L348" s="2"/>
       <c r="M348" s="14" t="s">
-        <v>1127</v>
+        <v>1124</v>
       </c>
       <c r="N348" s="2"/>
       <c r="O348" s="31"/>
@@ -30205,7 +30235,7 @@
       <c r="S348" s="22"/>
       <c r="T348" s="36"/>
       <c r="U348" s="40" t="s">
-        <v>670</v>
+        <v>1125</v>
       </c>
       <c r="V348" s="2" t="s">
         <v>392</v>
@@ -30221,11 +30251,9 @@
       </c>
       <c r="Z348" s="4"/>
       <c r="AA348" s="2" t="s">
-        <v>616</v>
-      </c>
-      <c r="AB348" s="2" t="s">
-        <v>617</v>
-      </c>
+        <v>397</v>
+      </c>
+      <c r="AB348" s="2"/>
       <c r="AC348" s="2"/>
       <c r="AD348" s="2"/>
       <c r="AE348" s="2" t="s">
@@ -30236,7 +30264,7 @@
       </c>
       <c r="AG348" s="4"/>
       <c r="AH348" s="2" t="s">
-        <v>391</v>
+        <v>1125</v>
       </c>
       <c r="AI348" s="2"/>
     </row>
@@ -30245,22 +30273,20 @@
         <v>348</v>
       </c>
       <c r="B349" s="2"/>
-      <c r="C349" s="45">
-        <v>51337</v>
-      </c>
+      <c r="C349" s="45"/>
       <c r="D349" s="2"/>
-      <c r="E349" s="4">
-        <v>99999</v>
-      </c>
-      <c r="F349" s="38"/>
+      <c r="E349" s="4"/>
+      <c r="F349" s="38" t="s">
+        <v>1126</v>
+      </c>
       <c r="G349" s="28">
-        <v>44.602800000000002</v>
+        <v>42.716000000000001</v>
       </c>
       <c r="H349" s="28">
-        <v>81.387799999999999</v>
+        <v>84.272000000000006</v>
       </c>
       <c r="I349" s="2">
-        <v>2100</v>
+        <v>2404.3000000000002</v>
       </c>
       <c r="J349" s="26">
         <v>12</v>
@@ -30268,21 +30294,19 @@
       <c r="K349" s="30" t="s">
         <v>307</v>
       </c>
-      <c r="L349" s="3"/>
+      <c r="L349" s="2"/>
       <c r="M349" s="14" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
       <c r="N349" s="2"/>
       <c r="O349" s="31"/>
       <c r="P349" s="31"/>
       <c r="Q349" s="31"/>
       <c r="R349" s="50"/>
-      <c r="S349" s="22" t="s">
-        <v>39</v>
-      </c>
+      <c r="S349" s="22"/>
       <c r="T349" s="36"/>
       <c r="U349" s="40" t="s">
-        <v>391</v>
+        <v>670</v>
       </c>
       <c r="V349" s="2" t="s">
         <v>392</v>
@@ -30298,10 +30322,10 @@
       </c>
       <c r="Z349" s="4"/>
       <c r="AA349" s="2" t="s">
-        <v>1129</v>
+        <v>616</v>
       </c>
       <c r="AB349" s="2" t="s">
-        <v>1130</v>
+        <v>617</v>
       </c>
       <c r="AC349" s="2"/>
       <c r="AD349" s="2"/>
@@ -30315,17 +30339,15 @@
       <c r="AH349" s="2" t="s">
         <v>391</v>
       </c>
-      <c r="AI349" s="2" t="s">
-        <v>637</v>
-      </c>
+      <c r="AI349" s="2"/>
     </row>
     <row r="350" spans="1:35" ht="24" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A350" s="2">
         <v>349</v>
       </c>
       <c r="B350" s="2"/>
-      <c r="C350" s="45" t="s">
-        <v>1131</v>
+      <c r="C350" s="45">
+        <v>51337</v>
       </c>
       <c r="D350" s="2"/>
       <c r="E350" s="4">
@@ -30333,13 +30355,13 @@
       </c>
       <c r="F350" s="38"/>
       <c r="G350" s="28">
-        <v>40.5122</v>
+        <v>44.602800000000002</v>
       </c>
       <c r="H350" s="28">
-        <v>75.391400000000004</v>
+        <v>81.387799999999999</v>
       </c>
       <c r="I350" s="2">
-        <v>3470.2</v>
+        <v>2100</v>
       </c>
       <c r="J350" s="26">
         <v>12</v>
@@ -30347,9 +30369,9 @@
       <c r="K350" s="30" t="s">
         <v>307</v>
       </c>
-      <c r="L350" s="2"/>
+      <c r="L350" s="3"/>
       <c r="M350" s="14" t="s">
-        <v>1132</v>
+        <v>1128</v>
       </c>
       <c r="N350" s="2"/>
       <c r="O350" s="31"/>
@@ -30377,10 +30399,10 @@
       </c>
       <c r="Z350" s="4"/>
       <c r="AA350" s="2" t="s">
-        <v>649</v>
+        <v>1129</v>
       </c>
       <c r="AB350" s="2" t="s">
-        <v>1133</v>
+        <v>1130</v>
       </c>
       <c r="AC350" s="2"/>
       <c r="AD350" s="2"/>
@@ -30394,7 +30416,9 @@
       <c r="AH350" s="2" t="s">
         <v>391</v>
       </c>
-      <c r="AI350" s="2"/>
+      <c r="AI350" s="2" t="s">
+        <v>637</v>
+      </c>
     </row>
     <row r="351" spans="1:35" ht="24" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A351" s="2">
@@ -30402,7 +30426,7 @@
       </c>
       <c r="B351" s="2"/>
       <c r="C351" s="45" t="s">
-        <v>1134</v>
+        <v>1131</v>
       </c>
       <c r="D351" s="2"/>
       <c r="E351" s="4">
@@ -30410,13 +30434,13 @@
       </c>
       <c r="F351" s="38"/>
       <c r="G351" s="28">
-        <v>42.890799999999999</v>
+        <v>40.5122</v>
       </c>
       <c r="H351" s="28">
-        <v>89.305599999999998</v>
+        <v>75.391400000000004</v>
       </c>
       <c r="I351" s="2">
-        <v>-48.8</v>
+        <v>3470.2</v>
       </c>
       <c r="J351" s="26">
         <v>12</v>
@@ -30426,17 +30450,19 @@
       </c>
       <c r="L351" s="2"/>
       <c r="M351" s="14" t="s">
-        <v>1135</v>
+        <v>1132</v>
       </c>
       <c r="N351" s="2"/>
       <c r="O351" s="31"/>
       <c r="P351" s="31"/>
       <c r="Q351" s="31"/>
       <c r="R351" s="50"/>
-      <c r="S351" s="22"/>
+      <c r="S351" s="22" t="s">
+        <v>39</v>
+      </c>
       <c r="T351" s="36"/>
       <c r="U351" s="40" t="s">
-        <v>406</v>
+        <v>391</v>
       </c>
       <c r="V351" s="2" t="s">
         <v>392</v>
@@ -30452,10 +30478,10 @@
       </c>
       <c r="Z351" s="4"/>
       <c r="AA351" s="2" t="s">
-        <v>407</v>
+        <v>649</v>
       </c>
       <c r="AB351" s="2" t="s">
-        <v>408</v>
+        <v>1133</v>
       </c>
       <c r="AC351" s="2"/>
       <c r="AD351" s="2"/>
@@ -30466,7 +30492,9 @@
         <v>313</v>
       </c>
       <c r="AG351" s="4"/>
-      <c r="AH351" s="2"/>
+      <c r="AH351" s="2" t="s">
+        <v>391</v>
+      </c>
       <c r="AI351" s="2"/>
     </row>
     <row r="352" spans="1:35" ht="24" customHeight="1" x14ac:dyDescent="0.4">
@@ -30474,20 +30502,22 @@
         <v>351</v>
       </c>
       <c r="B352" s="2"/>
-      <c r="C352" s="45"/>
+      <c r="C352" s="45" t="s">
+        <v>1134</v>
+      </c>
       <c r="D352" s="2"/>
-      <c r="E352" s="4"/>
-      <c r="F352" s="38" t="s">
-        <v>1136</v>
-      </c>
+      <c r="E352" s="4">
+        <v>99999</v>
+      </c>
+      <c r="F352" s="38"/>
       <c r="G352" s="28">
-        <v>42.685600000000001</v>
+        <v>42.890799999999999</v>
       </c>
       <c r="H352" s="28">
-        <v>89.065600000000003</v>
+        <v>89.305599999999998</v>
       </c>
       <c r="I352" s="2">
-        <v>-106.4</v>
+        <v>-48.8</v>
       </c>
       <c r="J352" s="26">
         <v>12</v>
@@ -30497,7 +30527,7 @@
       </c>
       <c r="L352" s="2"/>
       <c r="M352" s="14" t="s">
-        <v>1137</v>
+        <v>1135</v>
       </c>
       <c r="N352" s="2"/>
       <c r="O352" s="31"/>
@@ -30549,16 +30579,16 @@
       <c r="D353" s="2"/>
       <c r="E353" s="4"/>
       <c r="F353" s="38" t="s">
-        <v>1138</v>
+        <v>1136</v>
       </c>
       <c r="G353" s="28">
-        <v>42.904400000000003</v>
+        <v>42.685600000000001</v>
       </c>
       <c r="H353" s="28">
-        <v>89.4422</v>
+        <v>89.065600000000003</v>
       </c>
       <c r="I353" s="2">
-        <v>-52</v>
+        <v>-106.4</v>
       </c>
       <c r="J353" s="26">
         <v>12</v>
@@ -30568,7 +30598,7 @@
       </c>
       <c r="L353" s="2"/>
       <c r="M353" s="14" t="s">
-        <v>1139</v>
+        <v>1137</v>
       </c>
       <c r="N353" s="2"/>
       <c r="O353" s="31"/>
@@ -30616,22 +30646,20 @@
         <v>353</v>
       </c>
       <c r="B354" s="2"/>
-      <c r="C354" s="45" t="s">
-        <v>1140</v>
-      </c>
+      <c r="C354" s="45"/>
       <c r="D354" s="2"/>
-      <c r="E354" s="4">
-        <v>99999</v>
-      </c>
-      <c r="F354" s="38"/>
+      <c r="E354" s="4"/>
+      <c r="F354" s="38" t="s">
+        <v>1138</v>
+      </c>
       <c r="G354" s="28">
-        <v>42.7669</v>
+        <v>42.904400000000003</v>
       </c>
       <c r="H354" s="28">
-        <v>88.600800000000007</v>
+        <v>89.4422</v>
       </c>
       <c r="I354" s="2">
-        <v>43.9</v>
+        <v>-52</v>
       </c>
       <c r="J354" s="26">
         <v>12</v>
@@ -30641,7 +30669,7 @@
       </c>
       <c r="L354" s="2"/>
       <c r="M354" s="14" t="s">
-        <v>1141</v>
+        <v>1139</v>
       </c>
       <c r="N354" s="2"/>
       <c r="O354" s="31"/>
@@ -30670,7 +30698,7 @@
         <v>407</v>
       </c>
       <c r="AB354" s="2" t="s">
-        <v>1142</v>
+        <v>408</v>
       </c>
       <c r="AC354" s="2"/>
       <c r="AD354" s="2"/>
@@ -30690,7 +30718,7 @@
       </c>
       <c r="B355" s="2"/>
       <c r="C355" s="45" t="s">
-        <v>1143</v>
+        <v>1140</v>
       </c>
       <c r="D355" s="2"/>
       <c r="E355" s="4">
@@ -30698,13 +30726,13 @@
       </c>
       <c r="F355" s="38"/>
       <c r="G355" s="28">
-        <v>43.113100000000003</v>
+        <v>42.7669</v>
       </c>
       <c r="H355" s="28">
-        <v>86.843100000000007</v>
+        <v>88.600800000000007</v>
       </c>
       <c r="I355" s="2">
-        <v>3540.5</v>
+        <v>43.9</v>
       </c>
       <c r="J355" s="26">
         <v>12</v>
@@ -30714,19 +30742,17 @@
       </c>
       <c r="L355" s="2"/>
       <c r="M355" s="14" t="s">
-        <v>1144</v>
+        <v>1141</v>
       </c>
       <c r="N355" s="2"/>
       <c r="O355" s="31"/>
       <c r="P355" s="31"/>
       <c r="Q355" s="31"/>
       <c r="R355" s="50"/>
-      <c r="S355" s="22" t="s">
-        <v>39</v>
-      </c>
+      <c r="S355" s="22"/>
       <c r="T355" s="36"/>
       <c r="U355" s="40" t="s">
-        <v>391</v>
+        <v>406</v>
       </c>
       <c r="V355" s="2" t="s">
         <v>392</v>
@@ -30742,10 +30768,10 @@
       </c>
       <c r="Z355" s="4"/>
       <c r="AA355" s="2" t="s">
-        <v>412</v>
+        <v>407</v>
       </c>
       <c r="AB355" s="2" t="s">
-        <v>1145</v>
+        <v>1142</v>
       </c>
       <c r="AC355" s="2"/>
       <c r="AD355" s="2"/>
@@ -30756,9 +30782,7 @@
         <v>313</v>
       </c>
       <c r="AG355" s="4"/>
-      <c r="AH355" s="2" t="s">
-        <v>391</v>
-      </c>
+      <c r="AH355" s="2"/>
       <c r="AI355" s="2"/>
     </row>
     <row r="356" spans="1:35" ht="24" customHeight="1" x14ac:dyDescent="0.4">
@@ -30767,7 +30791,7 @@
       </c>
       <c r="B356" s="2"/>
       <c r="C356" s="45" t="s">
-        <v>1146</v>
+        <v>1143</v>
       </c>
       <c r="D356" s="2"/>
       <c r="E356" s="4">
@@ -30775,23 +30799,23 @@
       </c>
       <c r="F356" s="38"/>
       <c r="G356" s="28">
-        <v>23.2286</v>
+        <v>43.113100000000003</v>
       </c>
       <c r="H356" s="28">
-        <v>102.8214</v>
+        <v>86.843100000000007</v>
       </c>
       <c r="I356" s="2">
-        <v>312.3</v>
+        <v>3540.5</v>
       </c>
       <c r="J356" s="26">
         <v>12</v>
       </c>
-      <c r="K356" s="47" t="s">
+      <c r="K356" s="30" t="s">
         <v>307</v>
       </c>
       <c r="L356" s="2"/>
       <c r="M356" s="14" t="s">
-        <v>1147</v>
+        <v>1144</v>
       </c>
       <c r="N356" s="2"/>
       <c r="O356" s="31"/>
@@ -30803,10 +30827,10 @@
       </c>
       <c r="T356" s="36"/>
       <c r="U356" s="40" t="s">
-        <v>535</v>
+        <v>391</v>
       </c>
       <c r="V356" s="2" t="s">
-        <v>535</v>
+        <v>392</v>
       </c>
       <c r="W356" s="4" t="s">
         <v>39</v>
@@ -30819,10 +30843,10 @@
       </c>
       <c r="Z356" s="4"/>
       <c r="AA356" s="2" t="s">
-        <v>1148</v>
+        <v>412</v>
       </c>
       <c r="AB356" s="2" t="s">
-        <v>1149</v>
+        <v>1145</v>
       </c>
       <c r="AC356" s="2"/>
       <c r="AD356" s="2"/>
@@ -30833,7 +30857,9 @@
         <v>313</v>
       </c>
       <c r="AG356" s="4"/>
-      <c r="AH356" s="2"/>
+      <c r="AH356" s="2" t="s">
+        <v>391</v>
+      </c>
       <c r="AI356" s="2"/>
     </row>
     <row r="357" spans="1:35" ht="24" customHeight="1" x14ac:dyDescent="0.4">
@@ -30842,7 +30868,7 @@
       </c>
       <c r="B357" s="2"/>
       <c r="C357" s="45" t="s">
-        <v>1150</v>
+        <v>1146</v>
       </c>
       <c r="D357" s="2"/>
       <c r="E357" s="4">
@@ -30850,23 +30876,23 @@
       </c>
       <c r="F357" s="38"/>
       <c r="G357" s="28">
-        <v>26.918099999999999</v>
+        <v>23.2286</v>
       </c>
       <c r="H357" s="28">
-        <v>102.9267</v>
+        <v>102.8214</v>
       </c>
       <c r="I357" s="2">
-        <v>893.9</v>
+        <v>312.3</v>
       </c>
       <c r="J357" s="26">
         <v>12</v>
       </c>
-      <c r="K357" s="30" t="s">
+      <c r="K357" s="47" t="s">
         <v>307</v>
       </c>
       <c r="L357" s="2"/>
       <c r="M357" s="14" t="s">
-        <v>1151</v>
+        <v>1147</v>
       </c>
       <c r="N357" s="2"/>
       <c r="O357" s="31"/>
@@ -30894,10 +30920,10 @@
       </c>
       <c r="Z357" s="4"/>
       <c r="AA357" s="2" t="s">
-        <v>1152</v>
+        <v>1148</v>
       </c>
       <c r="AB357" s="2" t="s">
-        <v>1153</v>
+        <v>1149</v>
       </c>
       <c r="AC357" s="2"/>
       <c r="AD357" s="2"/>
@@ -30912,38 +30938,76 @@
       <c r="AI357" s="2"/>
     </row>
     <row r="358" spans="1:35" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A358" s="13"/>
+      <c r="A358" s="2">
+        <v>357</v>
+      </c>
       <c r="B358" s="2"/>
-      <c r="C358" s="45"/>
+      <c r="C358" s="45" t="s">
+        <v>1150</v>
+      </c>
       <c r="D358" s="2"/>
-      <c r="E358" s="4"/>
+      <c r="E358" s="4">
+        <v>99999</v>
+      </c>
       <c r="F358" s="38"/>
-      <c r="G358" s="28"/>
-      <c r="H358" s="28"/>
-      <c r="I358" s="2"/>
-      <c r="J358" s="26"/>
-      <c r="K358" s="30"/>
+      <c r="G358" s="28">
+        <v>26.918099999999999</v>
+      </c>
+      <c r="H358" s="28">
+        <v>102.9267</v>
+      </c>
+      <c r="I358" s="2">
+        <v>893.9</v>
+      </c>
+      <c r="J358" s="26">
+        <v>12</v>
+      </c>
+      <c r="K358" s="30" t="s">
+        <v>307</v>
+      </c>
       <c r="L358" s="2"/>
-      <c r="M358" s="14"/>
+      <c r="M358" s="14" t="s">
+        <v>1151</v>
+      </c>
       <c r="N358" s="2"/>
-      <c r="O358" s="32"/>
-      <c r="P358" s="32"/>
-      <c r="Q358" s="32"/>
+      <c r="O358" s="31"/>
+      <c r="P358" s="31"/>
+      <c r="Q358" s="31"/>
       <c r="R358" s="50"/>
-      <c r="S358" s="22"/>
+      <c r="S358" s="22" t="s">
+        <v>39</v>
+      </c>
       <c r="T358" s="36"/>
-      <c r="U358" s="40"/>
-      <c r="V358" s="2"/>
-      <c r="W358" s="4"/>
-      <c r="X358" s="4"/>
-      <c r="Y358" s="4"/>
+      <c r="U358" s="40" t="s">
+        <v>535</v>
+      </c>
+      <c r="V358" s="2" t="s">
+        <v>535</v>
+      </c>
+      <c r="W358" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="X358" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="Y358" s="4" t="s">
+        <v>39</v>
+      </c>
       <c r="Z358" s="4"/>
-      <c r="AA358" s="2"/>
-      <c r="AB358" s="2"/>
+      <c r="AA358" s="2" t="s">
+        <v>1152</v>
+      </c>
+      <c r="AB358" s="2" t="s">
+        <v>1153</v>
+      </c>
       <c r="AC358" s="2"/>
       <c r="AD358" s="2"/>
-      <c r="AE358" s="2"/>
-      <c r="AF358" s="4"/>
+      <c r="AE358" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="AF358" s="4" t="s">
+        <v>313</v>
+      </c>
       <c r="AG358" s="4"/>
       <c r="AH358" s="2"/>
       <c r="AI358" s="2"/>
@@ -32439,7 +32503,7 @@
       <c r="H399" s="28"/>
       <c r="I399" s="2"/>
       <c r="J399" s="26"/>
-      <c r="K399" s="4"/>
+      <c r="K399" s="30"/>
       <c r="L399" s="2"/>
       <c r="M399" s="14"/>
       <c r="N399" s="2"/>
@@ -32614,9 +32678,7 @@
       <c r="AI403" s="2"/>
     </row>
     <row r="404" spans="1:35" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A404" s="12">
-        <v>999</v>
-      </c>
+      <c r="A404" s="13"/>
       <c r="B404" s="2"/>
       <c r="C404" s="45"/>
       <c r="D404" s="2"/>
@@ -32630,9 +32692,7 @@
       <c r="L404" s="2"/>
       <c r="M404" s="14"/>
       <c r="N404" s="2"/>
-      <c r="O404" s="32" t="s">
-        <v>1154</v>
-      </c>
+      <c r="O404" s="32"/>
       <c r="P404" s="32"/>
       <c r="Q404" s="32"/>
       <c r="R404" s="50"/>
@@ -32654,19 +32714,60 @@
       <c r="AH404" s="2"/>
       <c r="AI404" s="2"/>
     </row>
+    <row r="405" spans="1:35" ht="24" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A405" s="12">
+        <v>999</v>
+      </c>
+      <c r="B405" s="2"/>
+      <c r="C405" s="45"/>
+      <c r="D405" s="2"/>
+      <c r="E405" s="4"/>
+      <c r="F405" s="38"/>
+      <c r="G405" s="28"/>
+      <c r="H405" s="28"/>
+      <c r="I405" s="2"/>
+      <c r="J405" s="26"/>
+      <c r="K405" s="4"/>
+      <c r="L405" s="2"/>
+      <c r="M405" s="14"/>
+      <c r="N405" s="2"/>
+      <c r="O405" s="32" t="s">
+        <v>1154</v>
+      </c>
+      <c r="P405" s="32"/>
+      <c r="Q405" s="32"/>
+      <c r="R405" s="50"/>
+      <c r="S405" s="22"/>
+      <c r="T405" s="36"/>
+      <c r="U405" s="40"/>
+      <c r="V405" s="2"/>
+      <c r="W405" s="4"/>
+      <c r="X405" s="4"/>
+      <c r="Y405" s="4"/>
+      <c r="Z405" s="4"/>
+      <c r="AA405" s="2"/>
+      <c r="AB405" s="2"/>
+      <c r="AC405" s="2"/>
+      <c r="AD405" s="2"/>
+      <c r="AE405" s="2"/>
+      <c r="AF405" s="4"/>
+      <c r="AG405" s="4"/>
+      <c r="AH405" s="2"/>
+      <c r="AI405" s="2"/>
+    </row>
   </sheetData>
   <sheetProtection sheet="1" objects="1" scenarios="1"/>
   <protectedRanges>
-    <protectedRange sqref="O2:Q404" name="区域1"/>
+    <protectedRange sqref="O2:Q405" name="区域1"/>
   </protectedRanges>
-  <autoFilter ref="A1:AI404" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:AI405" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="A2:N404 R2:AI404">
+  <conditionalFormatting sqref="R2:AI405 A2:N405">
     <cfRule type="expression" dxfId="1" priority="4">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:Q404">
+  <conditionalFormatting sqref="O2:Q405">
     <cfRule type="expression" dxfId="0" priority="2">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
